--- a/results-list/pagina12.xlsx
+++ b/results-list/pagina12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="938">
   <si>
     <t>Título</t>
   </si>
@@ -40,7 +40,20 @@
     <t>https://www.pagina12.com.ar/793657-asamblea-indigena-contra-los-desmontes</t>
   </si>
   <si>
-    <t>2024-12-30T03:44:31Z</t>
+    <t xml:space="preserve">Título: Asamblea indígena contra los desmontes
+Chapeau: El ordenamiento de bosques nativos y la derogación de la ley 26160, el eje de la atención
+Subtítulo: Organizaciones, comunidades, consejeros, vocales y referentes indígenas se reunirán hoy en la ciudad de Salta para analizar y tomar decisiones sobre los "atropellos a los derechos constitucionales" de los pueblos indígenas que vienen sufriendo.
+Editoria: Salta|12
+Tags: Desmontes, Pueblos indígenas, pueblos-indigenas, diario
+URL: https://www.pagina12.com.ar/793657-asamblea-indigena-contra-los-desmontes/
+Notícia completa (7 blocos):
+"Nos convocamos a tomar decisiones y a elaborar una agenda en el marco de los atropellos a los derechos constitucionales de los Pueblos Indígenas", comienza la convocatoria a la asamblea provincial de organizaciones, comunidades, consejeros, vocales y referentes de pueblos indígenas que se realizará esta tarde en la ciudad de Salta.
+La preocupación inmediata es la nueva “Ley de Desmontes”, como llaman a la ley por la que la Legislatura provincial aprobó el nuevo Ordenamiento Territorial de Bosques Nativos que "pone en el mercado más 700.000 hectáreas", "decisiones tomadas por el estado provincial sin consulta libre, previa e informada (Ley 24.071) a los sujetos de derechos que son los Pueblos preexistentes al Estado argentino, al provincial y a los municipios", se señala en la convocatoria al encuentro de esta tarde, realizada por la Mesa de Derechos Indígenas y que se desarrollará a partir de las 18.30 en la Casa Artivista La Bartolina (Urquiza 1112).
+"La representatividad indígena, materializada en sus autoridades tradicionales, Curacas, Colal, Mborubichas, Pel, Caciques, y asambleas territoriales debe pronunciarse, ante la más cruda indiferencia estatal, y el resultado de sus actos que recaen sobre las comunidades indígenas que son despojadas, desalojadas, olvidadas a su suerte, padeciendo muertes por desnutrición, deshidratación, falta de atención médica, falta de medicamentos, inseguridad", se afirma en la convocatoria.
+También se destaca que las comunidades originarias "son víctimas de la sobreexplotación laboral, violencia de género, discriminacion e indiferencia institucional".
+Asimismo, denuncian la muerte de niños y niñas, y gran número de adultos "producto de los desmontes, fumigación, avance de la frontera agrícola, los agronegocios, la minería y las actividades extractivistas que explotan los recursos naturales a costa del buen vivir de las comunidades, la sociedad en general y las generaciones venideras".
+Además, ya en la convocatoria se señala que la provincia de Salta tiene proporcionalmente "la mayor cantidad de tierras en manos extranjeras, la mayor cantidad de hectáreas desmontadas", y además se sitúa en el primer lugar en cuanto a mortalidad infantil y femicidios, con "notable presencia del narcotráfico de manera estructural, altos porcentajes de personas bajo los niveles de pobreza, e indigencia", y un "fracaso de las políticas públicas para pueblos indígenas y sectores sociales en estado de vulnerabilidad, como mujeres, niños, discapacitados, diversidades y disidencias".
+La convocatoria concluye exigiendo "la plena aplicación de los derechos constitucionales, para el resguardo cultural y territorial, y respeto por los derechos, políticos, económicos, sociales y humanos".</t>
   </si>
   <si>
     <t>Logo salta12</t>
@@ -58,7 +71,35 @@
     <t>https://www.pagina12.com.ar/790702-desmontes-sin-proteccion-del-territorio-indigena-un-combo-ex</t>
   </si>
   <si>
-    <t>2024-12-16T06:06:51Z</t>
+    <t xml:space="preserve">Título: Desmontes sin protección del territorio indígena: “un combo explosivo”
+Chapeau: La votación del OTBN se pospuso una semana en el Senado
+Subtítulo: La antropóloga Norma Naharro advirtió sobre el peligro que se cierne sobre las comunidades indígenas ante la inminente aprobación del nuevo ordenamiento de bosques nativos en la provincia justo cuando el gobierno nacional eliminó la ley que las protegía de desalojos.
+Editoria: Salta|12
+Tags: Greenpeace, OTBN, Desmontes, Comunidades originarias, comunidades-originarias, diario
+URL: https://www.pagina12.com.ar/790702-desmontes-sin-proteccion-del-territorio-indigena-un-combo-ex/
+Notícia completa (22 blocos):
+La combinación de la actualización propuesta para el nuevo Ordenamiento Territorial de Bosques Nativos (OTBN) de Salta que permitirá el desmonte de más de 700 mil hectáreas y la derogación de la ley 26160, que frenaba desalojos de comunidades originarias, “es un combo explosivo”, aseguró la antropóloga y especialista en temas indígenas, Norma Naharro, quien participó junto a referentes de diferentes asociaciones civiles de una reunión en la Cámara de Senadores de la provincia.
+La ley 26160, de emergencia de la propiedad comunitaria indígena, protegía a las comunidades originarias de desalojos de sus territorios. Pero el presidente Javier Milei decidió derogar el decreto de necesidad y urgencia que había establecido la última prórroga hasta el 23 de noviembre de 2025.
+Esta nueva realidad, conocida el martes último tras su publicación en el Boletín Oficial de la República Argentina, pone ahora más presión en el tratamiento del proyecto de OTBN que fue aprobado ese mismo día por la Cámara de Diputados de Salta, que la remitió para su tratamiento al Senado de la provincia.
+En ese marco el miércoles último Naharro participó de una reunión, junto a referentes de asociaciones civiles y comunidades indígenas, con al menos 16 senadores provinciales. El tema del encuentro fue el proyecto de nuevo ordenamiento territorial de los bosques de la provincia. Por el momento, se pospuso el tratamiento del ordenamiento por una semana, y se prevé que el proyecto sea considerado en la sesión del jueves próximo.
+“Siempre cuidaremos el medio ambiente, pero también la queremos productiva. Queremos una Salta con trabajo genuino y en crecimiento. Respetando siempre el lema de producir conservando y conservar produciendo”, había dicho la semana pasada el gobernador Gustavo Sáenz al anunciar el envío del proyecto a la Legislatura.
+“El Gobierno Nacional ha establecido como uno de sus pilares principales el respeto irrestricto a la propiedad privada, considerando este derecho no solo como un principio de justicia, sino también, como un factor clave para atraer las inversiones necesarias para el verdadero bienestar del país”, indica entre sus fundamentos el decreto que deroga la norma que mantenía suspendidos los desalojos de comunidades.
+Sobre el OTBN, Naharro dijo que lo único que produjo el modelo de desmonte que ponderaron los últimos tres gobiernos provinciales, y también el nacional, “fue hambre, miseria, muerte y migración”. Puso como ejemplo que tanto Rivadavia como San Martín, dos de los departamentos en donde se impulsó este modelo de desarrollo, “son los más pobres de todo el país”.
+Añadió que no se trata solamente de las comunidades indígenas, sino también de otros factores que atraviesan la problemática como el cambio climático, el deterioro ambiental, las inundaciones y las sequías, entre otras consecuencias negativas.
+“No se trata de decir no al desarrollo. Sino de buscar otro modelo de desarrollo”, planteó. Mencionó también que con el desmonte y los agronegocios “viene la fumigación. Entonces es todo un paquete; instalan los agronegocios, no toman mano de obra local y fumigan a la población local. ¿Queremos que siga pasando? Que se intensifiquen las nefastas consecuencias del modelo impulsado en años anteriores? ¿Dónde están los beneficios que han traídos los desmontes?”.
+[H2] Cuestionamientos al proyecto
+Fueron varios los cuestionamientos planteados al proyecto de Ordenamiento presentado por el equipo técnico que encabezó Lucas Seghezzo, investigador del INENCO (Instituto de Investigaciones en Energía No Convencional).
+Entre ellos, se señaló que, de aprobarse este nuevo OTBN, se permitiría autorizar desmontes en zonas que antes estaban protegidas por pertenecer a la categoría 2 o amarilla. Se recordó que en estas zonas viven numerosas comunidades indígenas y familias campesinas criollas cuyo principal sustento proviene del bosque nativo.
+Se destacó como avance del proyecto lo incluido en el Anexo VIII que dispone una propuesta de protocolo de consulta con carácter vinculante. Sin embargo, en caso de no llegar a un acuerdo entre el proponente y las comunidades o campesinos afectados, se establece que se deberá resolver por vía judicial. En este punto, se recordó que la judicialización es una vía históricamente desfavorable a las comunidades e implica un enorme esfuerzo económico y de tiempo que la mayoría de las veces no están en condiciones de afrontar.
+“Decir que esta población podrá defender sus derechos al territorio basándose en procedimientos administrativos o judiciales de manera fragmentada es una manifestación de ignorancia o de perverso sarcasmo”, evaluó Naharro. Puso como ejemplo los mecanismos de audiencias públicas, hasta ahora vigentes, con los que nunca se pudo modificar un proyecto de cambio de uso de suelo, por más que las comunidades y el campesinado hayan hecho un enorme esfuerzo por participar de ellas y exponer su situación.
+Naharro afirmó que si bien hubo grupos de la Universidad Nacional de Salta (UNSa), que participaron en la elaboración de la propuesta, no se convocó a especialistas de la Facultad de Humanidades, “Como si la problemática de los Bbosques nativos fuera un tema exclusivo de las ciencias naturales, sin tener en cuenta la complejidad social que encierra, y lo mucho que afecta la vida de las personas”, afirmó.
+Se mostró en una posición antagónica respecto del modelo participativo que se planteó en los encuentros en tanto “la metodología ‘Q’ no es apropiada en este tipo de cuestiones, o por lo menos no es suficiente en contextos interculturales”, afirmó.
+“Lo que haya producido el grupo (liderado por Seghezzo), no es la voz de toda la Universidad, ni el producto de un trabajo interdisciplinario”, afirmó.
+[H2] Manifestación en la Legislatura
+El jueves último, día de sesión del Senado de la provincia, se realizó una manifestación en la Legislatura para solicitar nuevamente que se deje afuera la posibilidad de continuar con los desmontes.
+La responsable de la Campaña de Bosques de Greenpeace, Noemí Cruz, sostuvo que el proyecto de OTBN presentado es regresivo porque permite desmontar en donde antes no se podía.
+“Deberían conocer más la situación de su gente”, dijo con respecto a los legisladores de los departamentos ubicados en el Chaco salteño (Orán, Rivadavia, San Martín y Anta en general), que pese a conocer las consecuencias de los desmontes, apoyan esta iniciativa.
+Criticó además que la zonificación de las áreas a desmontar no sea clara, dado que esto quita a la población la posibilidad de hacer un control.</t>
   </si>
   <si>
     <t>Laura Urbano</t>
@@ -73,7 +114,32 @@
     <t>https://www.pagina12.com.ar/786264-lula-y-xi-relanzan-el-vinculo-bilateral</t>
   </si>
   <si>
-    <t>2024-12-01T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula y Xi relanzan el vínculo bilateral
+Chapeau: El gobierno de Brasil firmó 37 acuerdos y memorandos con China
+Subtítulo: La diplomacia brasilera brilló por su profesionalismo durante la visita del presidente de China a Río por la cumbre del G20 y a Brasilia para reunirse con Lula.
+Editoria: Cash
+Tags: Lula Da Silva, Xi Jinping, printed-edition, lula-da-silva, xi-jinping
+URL: https://www.pagina12.com.ar/786264-lula-y-xi-relanzan-el-vinculo-bilateral/
+Notícia completa (19 blocos):
+En el marco de la celebración del 50 aniversario del establecimiento de las relaciones diplomáticas entre Brasil y la República Popular China, la semana pasada el Presidente Lula da Silva recibió en el Palacio de Alvorada a su par chino Xi Jinping.
+Luego de haber participado de la Cumbre del G20 en Río de Janeiro, el mandatario de la potencia asiática se trasladó a la capital brasileña, donde mantuvo reuniones bilaterales con el presidente y varios de sus ministros. El gobierno brasileño firmó 37 acuerdos y memorandos promoviendo la apertura de mercados de nuevos productos brasileños, acuerdos de inversiones energéticas, intercambio educativo, científico tecnológico, telecomunicaciones, salud, entre otros.
+El punto más destacado es la adhesión del gobierno brasileño a un protocolo de “sinergias” vinculado a la Iniciativa de la Franja y la Ruta. El llamado Plan de Cooperación se propone el establecimiento de sinergias entre el Programa de Aceleración del Crecimiento, el Plan Nueva Industria Brasil, el Plan de Transformación Ecológica, el Programa Rutas de la Integración Sudamericana y la Iniciativa de la Franja y la Ruta.
+El acuerdo prevé la creación de un Grupo de trabajo para lanzar líneas de financiamiento para la infraestructura, desarrollo de cadenas productivas (alta tecnología, inteligencia artificial, salud, digitalización, aviación y espacial), así como la transformación ecológica y la promoción de programas de transferencia tecnológica.
+[H2] Profesionalismo
+Con este gesto, Brasil se aproxima a la Iniciativa de la Franja y la Ruta sin adherir oficialmente. Es una movida que busca un equilibrio, por un lado, con las relaciones con EEUU y, por otro, deja abierto un margen de negociación para modificar la pauta comercial brasileña, fuertemente motorizada por las exportaciones de bajo valor agregado.
+En Brasil existe preocupación por la desindustrialización de la economía local y consideran que con las medidas proteccionistas de Trump, China va a necesitar aumentar más sus exportaciones industrializadas al Sur Global.
+China tenía mucho más para ganar con el gesto simbólico de la adhesión a la Iniciativa de la Franja y la Ruta y la diplomacia brasileña se guarda la medalla de equilibrista defendiendo la histórica posición de no-alineamiento. Cabe resaltar el profesionalismo del Itamaraty brasileño, conducido exclusivamente por diplomáticos de carrera que defienden una política de inserción internacional de Estado, frente a los devenires pendulares, poco profesionalizados y cortoplacistas de una larga lista de Cancilleres, Secretarios y Embajadores políticos en puestos claves de los distintos gobiernos de Argentina.
+Brasil viene motorizando las Rutas de Integración Sudamericana en coordinación con el agronegocio brasileño, que busca diversificar las inversiones en logísticas para salir por el Océano Pacífico, un proyecto que incluye a Bolivia y Perú y podría tener efectos en las provincias del norte de Argentina.
+A partir de la inauguración del magapuerto de Chancay, al norte de Lima, China profundiza su rol estratégico y consolida a dicho puerto como el más importante en el Cono Sur Pacífico.
+[H2] Estrategia del Pacífico
+Con una inversión de 3.600 millones de dólares, el gobierno peruano espera atraer alrededor de un 50% de los cerca de 580.000 millones de dólares que mueve cada año el comercio entre China y América del Sur. Las nuevas Rutas del Cuadrante de Rondón, que conectarán directamente el Centro Oeste de Brasil, epicentro del agronegocio brasileño, con el puerto de Chancay, tienen como objetivo reducir en más de 7.000 km la distancia actual que se recorre para llegar a China, en comparación con la ruta tradicional a través del Atlántico.
+Este cambio en las rutas comerciales no solo promete agilizar el acceso de Brasil, Bolivia y Perú a los mercados asiáticos, sino que también tiene el potencial de transformar la dinámica logística y económica en el norte de Argentina, que podría beneficiarse de nuevas oportunidades de conectividad y comercio internacional.
+Los acuerdos buscan promover aún más el comercio bilateral y la coordinación estratégica con China. Desde 2009, China reemplazó a EE.UU. como principal socio comercial de Brasil y hoy responde por el 30% de las exportaciones brasileñas. En 2023, Brasil alcanzó un superávit comercial con China de más de 53 mil millones de dólares y de enero a octubre de 2024, el intercambio entre los países fue de 136.300 millones de dólares. Las exportaciones brasileñas alcanzaron 83.400 millones de dólares y las importaciones, 52.900 millones de dólares, con un superávit de 30.400 millones de dólares. La expansión del comercio fue clave en la estabilidad macroeconómica brasileña, que acumula más de 370 mil millones de dólares de reservas netas.
+Es interesante destacar que los sucesivos gobiernos brasileños, incluso los del Partido de los Trabajadores con Lula da Silva y Dilma Rousseff, incluyeron dentro de sus estrategias políticas al sector del agronegocio. El famoso plan Safra ha generado líneas de financiamiento de los bancos de desarrollo (nacional y regionales) por más de 400 mil millones de reales anuales. El agronegocio con fuerte presencia en el Parlamento y en el Ejecutivo, ha conseguido conseguir financiamiento así como también obtener excepciones impositivas que le permitieron dinamizar exportaciones.
+Entre los acuerdos más destacados de los firmados con China se encuentran el de Telecomunicaciones Brasileñas S.A. Telebras, empresa vinculada al Ministerio de las Comunicaciones de Brasil, con la firma china Shanghai Spacesail Technologies Co., Ltd., cuyo objetivo es la provisión de servicios y soluciones de telecomunicaciones vía satélite.
+Spacesail es la principal competidora de SpaceX de Elon Musk. La participación China en el sector de telecomunicaciones y espacial es de larga data, Huawei concentra cerca del 40% de la infraestructura de 4G y, a pesar de los reclamos norteamericanos, el Gobierno de Bolsonaro habilitó la compra de insumos chinos en las licitaciones de 5G.
+Además, Brasil cuenta con el lanzamiento de seis satélites binacionales en el marco del programa CBERS (Programa de Satélites de Recursos Terrestres Brasil-China). La cooperación con SpaceSail constituye un nuevo nivel de cooperación con el sector. Otro de los acuerdos claves busca incrementar las capacidades tecnológicas de Brasil en Aplicaciones de Tecnología Nuclear y Mecanización e Inteligencia Artificial.
+*Candidata doctoral en Johns Hopkins University</t>
   </si>
   <si>
     <t>Logo cash</t>
@@ -91,7 +157,30 @@
     <t>https://www.pagina12.com.ar/784235-bioinsumos-una-oportunidad-para-reducir-el-uso-de-agroquimic</t>
   </si>
   <si>
-    <t>2024-11-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: Bioinsumos, una oportunidad para reducir el uso de agroquímicos
+Chapeau: Ventajas y riesgos de un mercado chico pero en franco ascenso
+Subtítulo: La producción de este tipo de insumos mejora el rendimiento del agro, fomenta las economías regionales y cooperativas y reduce la necesidad de divisas.
+Editoria: Cash
+Tags: Agroquímicos, Alimentos, printed-edition, agroquimicos
+URL: https://www.pagina12.com.ar/784235-bioinsumos-una-oportunidad-para-reducir-el-uso-de-agroquimic/
+Notícia completa (17 blocos):
+El informe Bioinsumos: Oportunidades de Inversión en América Latina, elaborado el año pasado por el Centro de Inversiones de la FAO-ONU, estipula que, en los últimos cinco años, el mercado de bioinsumos en América Latina, si bien sigue siendo marginal, verifica un crecimiento promedio de ventas del 15 por ciento anual.
+“En Argentina, la perspectiva de crecimiento es mayor que en químicos. Mientras que el uso de biológico crece entre el 10 y 12 por ciento anual, el uso de químicos está casi estancado, con una expectativa de crecimiento de entre el 3 y 5 por ciento”, afirmó Gustavo González Anta, director científico de la empresa Indrasa, en el Tercer Encuentro Nacional sobre Producción con Biológicos realizado este año en Villa María, Córdoba.
+El mercado de bioinsumos agrícolas ya mueve en el país unos 8.600 millones de dólares, con la ventaja que son de producción nacional y hasta pueden ser una solución al eterno problema de la falta de dólares.
+[H2] Ética ecológica
+Según el informe de la FAO, se estima que América Latina gastó alrededor de 42.000 millones de dólares en agroquímicos durante 2021, el 90 por ciento producido en países fuera de la región. El gasto en bioinsumos para el mismo año fue de sólo 1.100 millones de dólares, un 3 por ciento del mercado de agroquímicos y por debajo de la media global. El mercado global de bioinsumos alcanzó en 2021 los 10.600 millones de dólares y se prevé que en 2026 alcance los 18.500 millones de dólares.
+Las organizaciones de pequeños productores vienen hace años desarrollando este tipo de bioinsumos, incluso con cooperativas o pequeñas empresas especializadas en la producción y distribución. En la provincia de Buenos Aires, la Unión de Trabajadoras de la Tierra (UTT) tiene tres biofábricas en La Plata, Mar del Plata y Luján, que abastecen unas 300 familias.
+“La primera biofábrica la fundamos allá por 2018. En principio, para financiar Cotepo, que es el Consultorio Técnico Popular. Ahora ya genera trabajo a varios compañeros y es una solución para otros que no tienen el tiempo, o las ganas de hacer bioinsumos”, cuenta Rubén Gutiérrez, integrante de Cotepo y de la fábrica de bioinsumos de la UTT en La Plata. “Muchas familias empezaron a buscar estos productos porque no eran nocivos para la salud humana, se sentían con la total tranquilidad de poder estar en la quinta y poder fumigar sin el miedo de que no estén los niños o no tocar la verdura y todo eso”, explica.
+Los bioinsumos son más baratos, no dependen del dólar ni de las grandes corporaciones y pueden ser producidos por las propias familias, generando un circuito virtuoso dentro de las economías regionales y de pequeños y medianos productores o cooperativas. Además de la UTT, son varias las organizaciones de la Mesa Agroalimentaria Argentina que están llevando adelante estos proyectos, en articulación con otros esquemas como las redes, ferias y locales de comercialización o el Sistema Participativo de Garantías (SPG).
+[H2] Cooperativas y pymes
+“El mercado biológico creció muchísimo en los últimos años. No porque quisieran que creciera, sino porque se dieron cuenta que los otros sistemas no generaban resultados. Las empresas proveedoras de insumos químicos empezaron a tomar parte del negocio y a apropiarse de la renta. Todavía no está la convicción del cambio cultural, pero ese cambio está empezando desde el bolsillo, como muchas cosas”, cuenta Benjamín Antonio, fundador hace 10 años de la empresa de bioinsumos El Caburé.
+Los estudios del especialista Martín Torres Duggan para la Asociación Argentina de Productores en Siembra Directa (Apresid) muestran que, en la Región Pampeana Díaz Zorita, después de 9 años de experimentación de bioinsumos en condiciones extensivas, la producción de maíz y trigo aumenta un 6 por ciento promedio en el rinde y hay una respuesta económica en el 81 por ciento de los casos.
+“Apresid este año ha invitado por primera vez a empresas productoras de bioinsumos de origen 100 por ciento biológico a participar en sus eventos, porque ve la necesidad de cambiar las prácticas en el suelo. Estamos llegando a problemas de agotamiento, pérdida de fertilidad o impermeabilización, producto del abuso de agroquímicos, además de las consecuencias que hay para el ambiente, los cursos de agua y las personas. Las perspectivas en el país yo creo que son muy positivas para este cambio”, opina Pablo Bobadilla, director de bioinsumos.ar.
+[H2] Amenaza del mercado
+“Es importante que esta tecnología no se desperdicie, porque es muy fácil que el diablo meta la cola. En los últimos dos años, las grandes multinacionales, proveedoras de insumos químicos, vieron que se les complicaba el panorama y están tomando sus estrategias. Los europeos están muy evolucionados en eso. Y los brasileros nos llevan la punta”, advierte Antonio. En el último año, Brasil aprobó 600 productos de este tipo. La misma cantidad que se han aprobado en Argentina desde 1998.
+“Estamos viendo el avance del lobby del agronegocio con empresas que, teniendo productos basados en hidrocarburos, ya están presentando productos verdes llamados biol”, coincide Bobadilla. Y advierte: “Es importante el papel del Estado. En su momento estaban la Dirección Nacional de Agroecología y la presidencia del SENASA en manos de personas que se habían puesto de acuerdo con actores del sector agropecuario para darle una regularización al uso de biopreparados y bioinsumos. Hoy tenemos una ley”.
+La provincia de Buenos Aires está llevando adelante una iniciativa para que los biopreparados puedan ser certificados dentro de los sistemas participativos de garantía y puedan ser comercializados. “En Formosa también hay un proyecto muy interesante, que es la primera planta de biopreparados y bioinsumos estatal. La fábrica está preparada, pero faltan las maquinarias, porque el gobierno actual no envió los fondos que ya estaban pactados desde la gestión anterior”, concluye el director de bioinsumos.ar.
+* Licenciado en Economía de la Universidad Torcuato Di Tella y master en Periodismo de la Universidad del País Vasco.</t>
   </si>
   <si>
     <t>Tomás Astelarra*</t>
@@ -106,7 +195,15 @@
     <t>https://www.pagina12.com.ar/781911-el-pais-que-a-milei-no-le-interesa-conicet-perdio-1055-traba</t>
   </si>
   <si>
-    <t>2024-11-12T03:01:00Z</t>
+    <t xml:space="preserve">Título: El país que a Milei no le interesa: Conicet perdió 1055 trabajadores
+Chapeau: Fuga de cerebros
+Subtítulo: El retroceso actual no tiene equivalentes en la historia reciente del organismo
+Editoria: Sociedad
+Tags: Conicet, printed-edition, diario
+URL: https://www.pagina12.com.ar/781911-el-pais-que-a-milei-no-le-interesa-conicet-perdio-1055-traba/
+Notícia completa (2 blocos):
+Por primera vez en 20 años, el Conicet tiene menos personal. En lo que va de 2024, el principal organismo de investigación científica de la Argentina registró una pérdida de 1055 trabajadores, entre los que se encuentran 598 investigadores de carrera, 457 becarios y personal administrativo. El retroceso actual no tiene equivalentes en la historia reciente del organismo.
+Los datos se desprenden del último estudio de Evolución de Empleo y Recursos Humanos del Sistema Nacional de Ciencia, Tecnología e Innovación, elaborado por el Grupo EPC-CIICTI. Esta caída, según expone el informe, se da en el marco de un descenso generalizado de puestos de trabajo en el sector científico público, en el que ya se perdieron 2696 empleos, pasando de 75.051 en diciembre de 2023 a 72.355 en septiembre de este año.</t>
   </si>
   <si>
     <t>Logo socios</t>
@@ -121,7 +218,20 @@
     <t>https://www.pagina12.com.ar/781647-desde-el-conicet-denuncian-una-politica-de-discriminacion-a-</t>
   </si>
   <si>
-    <t>2024-11-10T18:53:28Z</t>
+    <t xml:space="preserve">Título: Desde el Conicet denuncian una "política de discriminación" a becarios e investigadores
+Chapeau: Las razones de la renuncia Manuel García Solá
+Subtítulo: El doctor en Bioquímica e investigador, Jorge Geffner, aseguró que al presidente Javier Milei "le molesta" el organismo científico porque "es un lugar donde hay libertad de pensamiento".
+Editoria: Radio 750
+Tags: Conicet, Escuchá Página|12, aqui-alla-y-en-todas-partes
+URL: https://www.pagina12.com.ar/781647-desde-el-conicet-denuncian-una-politica-de-discriminacion-a-/
+Notícia completa (7 blocos):
+El doctor en Bioquímica e investigador del Conicet, Jorge Geffner, se refirió a la renuncia del integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, quien denunció persecución política e ideológica a los becarios e investigadores del organismo.
+“Sorprende en los motivos por los cuales se fundamenta la decisión de Solá de renunciar, denunciando persecución ideológica, que era algo que desde el retorno de la democracia no se había visto”, advirtió Geffner en diálogo con la 750.
+"Se habían visto periodos de ajuste pero no de persecución ideológica. En ese sentido es muy grave”, lamentó.
+Según el investigador del Conicet, Solá “habló particularmente sobre los ingresos que están congelados”.
+“Todo esto se da en un marco de ajuste en el sistema científico tecnológico nacional. En otros momentos se sufría el ajuste, no como ahora, es otra dimensión. Esto está provocando un éxodo mucho mayor de investigadores, pero incluso en ese momento no se sentía esta discriminación. En este sentido, es algo novedoso”, insistió.
+“Acá no solamente hay un feroz ajuste, sino que hay una política de discriminación, que claramente Solá la expresa en su renuncia, quien es una persona de pensamientos más conservadores pero dice ‘acá hay un límite ético que es este y no lo puedo transgredir’”, afirmó.
+Por último, Geffner aseguró que el Conicet “molesta” al presidente Javier Milei “porque, como organismo científico, es un lugar donde tiene que haber libertad de pensamiento. Ese pensamiento crítico le molesta. Pero si no hay pensamiento crítico, no se puede hacer ciencia en ningún campo, porque lo nuevo surge de replantearse lo viejo en ciencia”, concluyó.</t>
   </si>
   <si>
     <t>Logo am750</t>
@@ -136,7 +246,28 @@
     <t>https://www.pagina12.com.ar/780931-la-inseguridad-alimentaria-avanza</t>
   </si>
   <si>
-    <t>2024-11-10T03:01:00Z</t>
+    <t xml:space="preserve">Título: La inseguridad alimentaria, avanza
+Chapeau: Se deteriora el acceso de la población a los bienes básicos
+Subtítulo: El consumo de alimentos se redujo, pero las empresas del sector incrementaron su rentabilidad en un 1300 por ciento.
+Editoria: Cash
+Tags: Recesión, Javier Milei, Consumo, printed-edition, recesion, javier-milei
+URL: https://www.pagina12.com.ar/780931-la-inseguridad-alimentaria-avanza/
+Notícia completa (15 blocos):
+El ajuste fiscal y la devaluación elevaron los precios de los alimentos y redujeron la capacidad de compra de los sectores vulnerables, concluye la investigación titulada “Rascar la olla. Informe sobre el desmantelamiento de políticas agroalimentarias en los primeros meses del gobierno de Milei”, elaborado por el Programa de Estudios Regionales y Territoriales de la Universidad de Buenos Aires (UBA) y publicado por el Centro de Estudios Legales y Sociales (CELS) en conjunto con la Fundación Rosa Luxemburgo.
+El informe registra una caída del 11 por ciento en el consumo general de alimentos y de un 16 por ciento en supermercados y mayoristas. A su vez, detalla el modo en que la eliminación de políticas de apoyo a la agricultura familiar perjudicó tanto a productores como a consumidores, dado que se debilitaron las instancias que apoyaban a la producción familiar y a los espacios comunitarios de distribución alimentaria.
+La investigación también destaca que esta crisis favoreció a las grandes empresas de sectores estratégicos y oligopólicos, que pudieron maximizar sus beneficios. Utilizando datos del Instituto de Pensamiento y Políticas Públicas (IPyPP), informe sostiene que mientras crece la inseguridad alimentaria, las empresas de ese sector que cotizan en la Bolsa de Buenos Aires aumentaron sus ganancias un 1300 por ciento, y el complejo exportador de granos hizo lo propio en un 4900 por ciento.
+La escalada de precios en los primeros meses del año, que llevó el índice de pobreza al 52,9 por ciento, ubicó a la Argentina primera en el ranking de inflación nominal, con un 135 por ciento en alimentos, según datos proporcionados por el Banco Mundial.
+Desde noviembre hasta julio, el gobierno de La Libertad Avanza incrementó los precios de lo que comen los argentinos a nivel general un 128 por ciento, ubicándose así entre los países con mayor inseguridad alimentaria. “La política de devaluación del peso frente al dólar, junto con el recorte del gasto público, desregulación económica y aumentos en las tarifas de servicios y combustibles, ha intensificado la crisis alimentaria en el país”, denuncia el informe.
+[H2] Transferencia de recursos
+La política de ajustes y la transferencia de recursos hacia sectores exportadores y de mayores ingresos ha tenido un impacto devastador en el ingreso de los hogares promedio. Aunque el gobierno nacional celebró los aumentos salariales implementados desde marzo, la mayoría se encuentran muy por debajo de la inflación, especialmente en el sector público y en el privado no registrado, donde la pérdida en términos reales alcanzó el 19 por ciento.
+El informe analiza que las medidas adoptadas por el gobierno de Javier Milei generaron “una caída en el poder adquisitivo, una contracción del consumo interno y una grave pérdida de seguridad alimentaria, afectando tanto la producción como el acceso de la población a alimentos básicos”. El presupuesto estatal se ajustó drásticamente, mientras que la desregulación de precios y los acuerdos salariales a la baja golpearon el poder adquisitivo y desincentivaron el consumo interno, complicando el acceso a bienes esenciales y profundizando la crisis económica.
+Las políticas actuales están configurando un modelo de producción agraria concentrado y orientado al exterior. Se eliminó el “Compre Nacional” y se promovió la importación de alimentos más baratos, en un intento por controlar precios. Paralelamente se flexibilizó el uso de tecnologías e insumos que favorecen al agronegocio en detrimento de las economías regionales. Sectores tradicionales como el de la yerba, azúcar, olivo y vid enfrentan “desprotección, costos de insumos elevados y precarización laboral, comprometiendo así la soberanía alimentaria y las oportunidades de desarrollo económico en el interior del país”.
+[H2] Inseguridad alimentaria
+La falta de incentivos para el mercado interno y las desregulaciones continuas proyectan un futuro desafiante, en el que la recuperación del consumo y la producción nacional podrían estar cada vez más fuera del alcance de la mayoría de los argentinos. Por ejemplo, el presupuesto destinado a la Secretaría de Agricultura, Ganadería y Pesca cayó un 95 por ciento en términos reales. El Instituto Nacional de Semillas tuvo una ejecución de tan solo el 20 por ciento y los programas con financiamiento internacional, por debajo del 2 por ciento.
+Los sectores excluidos experimentaron un deterioro significativo en los ingresos. El Programa Potenciar Trabajo “fue congelado y desdoblado en dos nuevos, que no suponen una contraprestación laboral. Por su parte, el Programa Nexo directamente fue eliminado. De esta manera, quienes percibían Potenciar (ahora Volver al Trabajo o Acompañamiento Social) y Nexo entre noviembre y julio perdieron un 71,4 por ciento de sus ingresos en términos reales”, señala el informe.
+Por otro lado, la Asignación Universal por Hijo y la Tarjeta Alimentar aumentaron 40,8 por ciento en términos reales, sin ser este incremento suficiente para cubrir la Canasta Básica Alimentaria (CBA), que en julio se ubicó en $131.294 para el adulto equivalente.
+La combinación de devaluación, inflación y aumento de tarifas dejó a una gran parte de la población en una situación de extrema vulnerabilidad alimentaria, acentuando la brecha entre los sectores más favorecidos, como el exportador, y los trabajadores del sector público y privado no registrado. La crisis no solo expone las dificultades del presente, sino que plantea desafíos profundos para la estabilidad social y económica.
+*Comunicador social, Universidad Nacional de La Plata (UNLP).</t>
   </si>
   <si>
     <t>Fernando Gómez*</t>
@@ -151,7 +282,23 @@
     <t>https://www.pagina12.com.ar/781344-nunca-podria-callar-mi-voz-cuando-se-intentara-cometer-algun</t>
   </si>
   <si>
-    <t>2024-11-08T21:04:46Z</t>
+    <t xml:space="preserve">Título: "Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución"
+Chapeau: La explicación de Manuel García Solá sobre su salida del Conicet
+Subtítulo: El integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, renunció a su puesto y dejó en evidencia el alineamiento total del presidente
+Editoria: El País
+Tags: Conicet, Sociedad Rural Argentina, sociedad-rural-argentina, diario
+URL: https://www.pagina12.com.ar/781344-nunca-podria-callar-mi-voz-cuando-se-intentara-cometer-algun/
+Notícia completa (10 blocos):
+El integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, renunció a su puesto y dejó en evidencia el alineamiento total del presidente de la Sociedad Rural Argentina (SRA), Nicolás Pino, con el presidente Javier Milei. Solá hizo público que dio un paso al costado en contra de su voluntad y por un pedido expreso de Pino, durante una reunión privada, como castigo por expresar sus diferencias por la persecución política e ideológica que ocurre con los becarios e investigadores del organismo.
+Solá, ex ministro de Educación del menemismo, fue nominado por la SRA (con acuerdo de Confederaciones Rurales, Federación Agraria y Coninagro) en junio de 2022 y nombrado en el directorio por el presidente Alberto Fernández. Su desvinculación la relató en una carta pública en la que dejó claro su "disenso con la causa" que llevó a Pino "a hacerme esta solicitud". Más allá de la "prudencia" que mantuvo en su carta, Solá dejó en claro los motivos del presidente de la entidad tradicional del agro.
+"Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución por ideas científicas, políticas, religiosas, tecnológicas o las que fueran", sentenció Solá y le advirtió a Pino que "jamás se alcanzó la libertad económica, en la que coincidimos y por la que bregamos en la SRA, sin libertad política, de pensamiento y disenso democrático, sin respeto a las ideas del otro".
+El ex intengrante del directorio del Conicet, en diálogo con Radio Con Vos, marcó que se refería a la política desplegada por la Casa Rosada en el directorio del Conicet y ejemplificó con la respuesta a la pregunta 177 que dio el jefe de Gabinete, Guillermo Francos, en su última visita al Senado, en la que explicita que la evaluación a los investigadores del organismo condiciona que "sean pertinentes los temas que trabajen", o sea, "que se va a someter a una segunda evaluación de corte político".
+"Algo parecido ocurrió en las últimas semana con algunos becarios y fue lo que me llevó a mí a señalar que estaba en desacuerdo con esos procedimiento y, evidentemente, eso no gustó. A alguien no le gustó y se canalizó de la manera que se canalizó", volvió a dejar en claro la tarea encargada por la Casa Rosada al presidente de la SRA.
+En su carta, Solá también le recordó a Pino que, al momento de su nominación, desconocía la silla que las entidades del agronegocio tienen en el Directorio del Conicet y le citó un textual de cómo, normativamente, deben cumplir sus funciones: "Los miembros del directorio actuarán con independencia de criterio y no en representación de sus proponentes".
+"Como usted podrá entender, con su fina inteligencia y sensibilidad, no tiene, ni puede tener, ningún tipo de cortapisas", le dedicó Solá a Pino y remató: "Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución por ideas científicas, políticas, religiosas, tecnológicas o las que fueran".
+Solá, en diálogo con Radio con Vos, también reivindicó su pasado como funcionario de la gestión de Carlos Menem y le recordó al Ejecutivo, que reivindica aquellos años, que entonces no existían persecución ni condicionamientos ideológicos; más allá del alineamiento de mercado que las entidades del campo representan dentro del modelo de negocios que se ejecuta gobierno tras gobierno.
+El ex integrante del directorio también apuntó contra la paralización de los proyectos que se llevaban adelante desde el organismo y puso como ejemplo la asociación entre la Sociedad Rural, el Conicet, la Universidad Nacional de La Plata y Asociación de Criadores "para transformar nuestro laboratorio de genética aplicada en un centro de análisis e investigación genómica multiespecies, que lleve a consolidar el liderazgo argentino en selección genética a nivel latinoamericano".
+"Espero que, rápidamente, y a través de sus interlocutores con el actual gobierno se retome aquel ritmo que había logrado imprimirle a la relación", le reclamó a Pino.</t>
   </si>
   <si>
     <t>El nuevo trabajo de Diana Mondino</t>
@@ -163,7 +310,23 @@
     <t>https://www.pagina12.com.ar/780463-el-nuevo-trabajo-de-diana-mondino</t>
   </si>
   <si>
-    <t>2024-11-05T18:50:24Z</t>
+    <t xml:space="preserve">Título: El nuevo trabajo de Diana Mondino
+Chapeau: A qué se dedica la excanciller luego de la expulsión del Gobierno
+Subtítulo: Mientras sigue masticando bronca por su abrupta expulsión del Ministerio de Rela
+Editoria: El País
+Tags: Diana Mondino, diana-mondino, diario
+URL: https://www.pagina12.com.ar/780463-el-nuevo-trabajo-de-diana-mondino/
+Notícia completa (10 blocos):
+Mientras sigue masticando bronca por su abrupta expulsión del Ministerio de Relaciones Exteriores, Comercio Internacional y Culto, la excanciller Diana Mondino consiguió un nuevo trabajo en el ámbito privado.
+En realidad, no se trata de un trabajo "nuevo" sino que volverá al antiguo empleo que tenía antes de llegar a la Cancillería, un cargo docente en la Universidad del Centro de Estudios Macroeconómicos de Argentina (UCEMA), una institución privada ubicada en el barrio porteño de Retiro.
+La noticia la confirmó el profesor Marcos Gallacher, director del Departamento de Economía Agrícola, Recursos Naturales y Agronegocios. “¡Salimos ganando! UCEMA recupera a su destacada profesora y mejor persona @DianaMondino. Welcome back! Gracias @JMilei”, escribió el docente en X, junto a una foto con la excanciller.
+Antes de que Milei la nombrara al frente del Ministerio de Relaciones Exteriores, Comercio Internacional y Culto, Mondino daba clases de finanzas en el Master en Dirección de Empresas y en el Master en Finanzas de la universidad privada, que se especializa en negocios.
+Según la página web de UCEMA, la excanciller tiene experiencia temas económicos y de management, así como en evaluación de riesgos y análisis de mercados. "Diana es Master in Business Administration MBA de IESE, España, y Lic. en Economía de la Universidad Nacional de Córdoba" y "ha tomado cursos en las Universidades de Yale (CT.), Columbia (NY.) y Darden (Virginia), EE.UU.", resume la institución.
+Mondino fue expulsada del Gobierno de La Libertad Avanza el pasado 30 de octubre, luego de haber votado en la ONU en contra del bloqueo en Cuba, siendo Argentina uno de los 186 países que acompañaron el reclamo de la isla caribeña, con la excepción de Estados Unidos, Israel y Moldavia, una acción que Milei calificó -durante la bizarra entrevista que le concedió este lunes a su novia, Amalia "Yuyito" González, como "un error imperdonable".
+“La Canciller no consultó si el Gobierno quería mantener la tradición diplomática”, dijo luego de la salida de Mondino el jefe de Gabinete, Guillermo Francos. "No estamos para sacar conclusiones propias en términos de decisiones que hay que tomar en voz o en cabeza del Presidente. Lo que dice el Presidente se hace. Si no se hace, todos estamos invitados dentro de nuestras libertades individuales a retirarnos del gobierno", sumó, por su parte, el vocero presidencial Manuel Adorni.
+Tras ser notificada de su salida, Mondino publicó una carta dirigida a Milei en sus redes sociales, que decía: "Ha sido un gran honor trabajar estos meses con Ud. y todo el gobierno en este proyecto para levantar Argentina. Sé que tiene ideas firmes y sobre todo que tiene el coraje para mantenerlas. Sólo puedo decir que hay muchísimo trabajo por delante y le acompañaré desde el lugar que sea". Quienes la conocen de larga data, sin embargo, dicen que "quedó re caliente" por su eyección, y apuntan contra la secretaria general de la Presidencia, Karina Milei, a quien acusar de haber "intervenido de hecho" la Cancillería.
+Para contener esa bronca, el Gobierno evalúa ofrecerle algún otro puesto o función en el esquema de decisiones de La Libertad Avanza (LLA). “Por supuesto que el Gobierno la tiene totalmente en cuenta. Pues, la considera una persona valiosa y seguramente vamos a encontrar una posición donde le sea de utilidad no solamente al Gobierno, sino al país”, dijo en ese sentido Francos.
+Sin embargo, Mondino aún no se expresó sobre este ofrecimiento. “Hay que ver si quiere, quedó muy golpeada”, reconocen fuentes del Gobierno.</t>
   </si>
   <si>
     <t>Contra la violencia y la represión a las comunidades indígenas</t>
@@ -175,7 +338,20 @@
     <t>https://www.pagina12.com.ar/775845-contra-la-violencia-y-la-represion-a-las-comunidades-indigen</t>
   </si>
   <si>
-    <t>2024-10-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: Contra la violencia y la represión a las comunidades indígenas
+Chapeau: Denuncia de la Iglesia Católica
+Subtítulo: A través de un mensaje de la Comisión Episcopal para la Pastoral Aborigen, la Iglesia Católica solicitó a los gobiernos, nacional y provinciales, que cese la represión y la violencia contra las comunidades indígenas, a raíz de hechos recientes que se han venido registrando sobre todo en las últimas semanas en el norte del país. Pedido de Francisco a las “grandes corporaciones extractivas”.
+Editoria: El País
+Tags: Comunidades indígenas, Violencia, printed-edition, comunidades-indigenas, diario
+URL: https://www.pagina12.com.ar/775845-contra-la-violencia-y-la-represion-a-las-comunidades-indigen/
+Notícia completa (7 blocos):
+Bajo el título “Cuidar y defender el derecho de los más vulnerables” y con la firma de su presidente, el obispo Luis Scozzina, la Comisión Episcopal para la Pastoral Aborigen dependiente de la Conferencia Episcopal Argentina, expresó en un comunicado su “preocupación” por “el avance de resoluciones y políticas de Estado que desconocen y vulneran derechos de los Pueblos Indígenas adquiridos a partir de Convenios institucionales y la misma Constitución Nacional” y se pide a los gobiernos “abandonar actitudes de violencia y represión frente a las comunidades indígenas”.
+En el mensaje los obispos hacen suya la advertencia del Equipo Nacional de Pastoral Aborigen (ENDEPA) que denunció “múltiples atropellos sufridos por las comunidades” que, a sus vez, se ven “agudizados en este tiempo donde se exacerba el individualismo y la sobre explotación de nuestros bienes naturales y culturales y ante el creciente discurso estigmatizante contra los pueblos indígenas y de quienes acompañamos sus caminos de lucha”.
+En el mismo texto se hace mención a una intervención pública del papa Francisco en la que pidió “en nombre de Dios a las grandes corporaciones extractivas —mineras, petroleras—, forestales, inmobiliarias, agronegocios, que dejen de destruir los bosques, humedales y montañas, dejen de contaminar los ríos y los mares, dejen de intoxicar los pueblos y los alimentos”.
+ENDEPA había expresado también su preocupación porque “desde el poder político y económico se pretende nuevamente negar su preexistencia y pertenencia (de las comunidades) al Estado Argentino, con dolor volvemos a escuchar discursos y afirmaciones referentes a los pueblos indígenas como ‘los otros’, ‘los extranjeros’ retrotrayéndonos a un pasado violento y excluyente”.
+En el mensaje de la Comisión Episcopal de Pastoral Aborigen y “frente a la escalada de conflictos, a partir del desconocimiento de la propiedad comunitaria indígena por parte de aquellos que usurpan sus territorios como así también la violencia ejercida contra las comunidades y contra aquellos que las acompañan, en su mayoría agentes de pastoral de ENDEPA” se reitera el llamado “en especial a los gobiernos, a abandonar actitudes de violencia y represión frente a las comunidades indígenas, e involucrarse en la superación positiva de los conflictos en sus territorios, en un marco de respeto por la verdad y las normas jurídicas vigentes, incluyendo a los indígenas como parte esencial de la solución mediante medidas no violentas que propicien el diálogo, la amistad social y la paz”.
+El mensaje firmado por el obispo Scozzina, finaliza con una oración a Jesucristo a quien se le pide “danos la valentía de la libertad de los hijos de Dios para amar a todos sin excluir a nadie, privilegiando a los pobres, aborreciendo el odio y construyendo la paz”.
+wuranga@pagina12.com.ar</t>
   </si>
   <si>
     <t>Washington Uranga</t>
@@ -190,7 +366,23 @@
     <t>https://www.pagina12.com.ar/774190-pidieron-a-la-legislatura-rechazar-el-nuevo-ordenamiento-de-</t>
   </si>
   <si>
-    <t>2024-10-12T05:13:19Z</t>
+    <t xml:space="preserve">Título: Pidieron a la Legislatura rechazar el nuevo ordenamiento de bosques
+Chapeau: Asociaciones ambientalistas volvieron a cuestionar el mapa
+Subtítulo: Pese a las persistentes promesas de enviar la iniciativa para que sea aprobada en la Legislatura provincial, el gobierno demora su ingreso.
+Editoria: Salta|12
+Tags: OTBN, ambientalistas, legislatura de Salta, legislatura-de-salta, diario
+URL: https://www.pagina12.com.ar/774190-pidieron-a-la-legislatura-rechazar-el-nuevo-ordenamiento-de-/
+Notícia completa (10 blocos):
+Las organizaciones ambientalistas Greenpece, Fundación Cebil y Red de Defensoras del Ambiente y el Buen Vivir solicitaron a los legisladores provinciales no aprobar la propuesta de actualización del Ordenamiento Territorial de Bosques Nativos (OTBN) de Salta por entender que el procedimiento con el cual se realizó implica un retroceso en lo establecido por la Ley Nacional de Bosques Nativos.
+Pese a los reiterados anuncios de envíos de la iniciativa al recinto legislativo, y de haberse presentado en diciembre del año pasado, el gobierno provincial no presentó todavía la propuesta en la Legislatura provincial para su tratamiento.
+Entre otros puntos, las organzaciones ambientalistas cuestionaron que la nueva propuesta no defina qué sucederá con las tierras desmontadas de manera ilegal durante el gobierno de Juan Manuel Urtubey, ya sea por no estar autorizadas, o por haber sido autorizadas por un decreto que violaba la Ley Nacional de Bosques Nativos.
+Recordaron que las tierras desmontadas bajo la posibilidad del proceso de “recategorización”, “deberían mantener su categoría original en la actualización del OTBN”, y en todo caso, ser restauradas. Lo cual hasta el momento no sucedió.
+Cuestionaron también que el nuevo ordenamiento permita el desmonte legal de 721.568 hectáreas, una superficie “sumamente excesiva”, aseguraron; más cuando la provincia ha tenido una alta tasa de deforestación en las últimas tres décadas.
+Asimismo, afirmaron que la zonificación propuesta no respeta el principio de no regresión ambiental, dado que permite el desmonte en zonas actualmente clasificadas en las categorías 1 (rojo) y 2 (amarillo), en las que no se puede desmontar. En este punto, sostuvieron que el mecanismo propuesto por el equipo técnico que realizó el nuevo OTBN es similar al “utilizado para permitir las recategorizaciones prediales ilegales realizadas en la anterior gestión”. “Se trata de una zonificación flexible (…), no determina claramente donde se puede y dónde no se puede desmontar”, advirtieron.
+La nueva propuesta también habla de una zona de “color marrón”, que es la categoría que permite la flexibilidad de la ubicación de los desmontes. Las organizaciones ambientalistas entendieron que la propia existencia de esta categoría no incluida en la Ley de Bosques “puede implicar decisiones arbitrarias del Poder Ejecutivo provincial y (que) no favorecen al control social de los desmontes ilegales”.
+Además, nuevamente la región de los Valles Calchaquíes queda sin categorizar, como sucede hasta la actualidad, “desconociendo los montes nativos de algarrobos, talas, chañares, y a las especies en peligro de extinción, como los ejemplares en cardones y los retamos”. Este desconocimiento de los bosques nativos “incrementa el desmonte indiscriminado, el avance del agronegocio y genera conflictos socioambientales con las distintas comunidades originarias que habitan el valle”, afirmaron.
+Al permitir que algunos desmontes puedan hacerse sobre categorías que estén en rojo o amarillo, se promueve la “fragmentación de los bosques al no garantizar áreas boscosas continas”, agregaron. También criticaron que se haya dejado fuera de la Ley la falta de relevamiento de los territorios indígenas y la falta de talleres interculturales que incluyeran a las comunidades en sus territorios.
+Mientras se espera que la propuesta de OTBN obtenga estado parlamentario en Salta, surgió lo ocurrido en la provincia del Chaco, donde se presentó y aprobó una propuesta de OTBN que tenía mucha resistencia. La Dirección de Bosques de la Nación ya observó la propuesta aprobada y sostuvo que cuenta con “graves deficiencias”, algunas de ellas parecidas a las objeciones que realizan los ambientalistas en Salta al nuevo OTBN.</t>
   </si>
   <si>
     <t>"Nos estamos quedando sin agua"</t>
@@ -202,7 +394,29 @@
     <t>https://www.pagina12.com.ar/773972-cuando-la-via-navegable-es-la-prioridad</t>
   </si>
   <si>
-    <t>2024-10-11T11:23:03Z</t>
+    <t xml:space="preserve">Título: "Nos estamos quedando sin agua"
+Chapeau: Consecuencias de la Hidrovía en la localidad entrerriana de Victoria
+Subtítulo: La Coordinadora del Agua agrupa a cooperativas de pescadores, organizaciones sociales, ganaderos y un amplio abanico de sectores que incluye a las organizaciones feministas. Reclaman el dragado de las bocas de los riachos que están tapadas por la acumulación de sedimentos que provoca el calado a 34 pies del río Paraná. Evalúan cortar el puente Rosario-Victoria.
+Editoria: Las12
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/773972-cuando-la-via-navegable-es-la-prioridad/
+Notícia completa (16 blocos):
+La ciudad de Victoria, una localidad de 40.000 habitantes ubicada en medio del delta del Paraná, está a punto de quedarse sin agua. La Coordinadora del agua, que nuclea a diferentes organizaciones de pescadores, la sociedad civil y feministas, reclama el dragado de las bocas de los riachos tapados por el sedimento que se acumula debido al calado del río a 34 pies para hacer una vía navegable para las barcazas que trasladan las exportaciones granarias. Con bajante y sequía, la situación se hace dramática. Ante la falta de respuestas de las autoridades, evalúan cortar el puente Rosario-Victoria. “Nos estamos quedando sin agua, real”, enfatiza Ana Julia Bustos, integrante de Taller Flotante, que impulsó la Red Río Feminista.
+La Coordinadora del Agua aglutina a sectores de lo más heterogéneos. Entre quienes participan -además de Taller Flotante-, está la colectiva Orilleras, también de Río Feminista y Cuidadores de la Casa Común. “No se puede defender al mismo tiempo la vida y la ganancia sin límite de las corporaciones”, subraya Ana Fiol, integrante de Orilleras, que vive en Victoria y es la directora académica de la.Diplomatura de Extensión en "Ecofeminismos, cuerpos y territorios en peligro", de la Universidad de Mar del Plata.
+En el origen de la crisis del agua, está “primero, la Hidrovía (así se sigue llamando a la vía navegable por el nombre de la empresa que la explotó desde los años 90), y segundo, la presión de la frontera agrícola, del agronegocio, por el tema del ganado. El principal objetivo, creo que forma parte de una especie de plan, es la pampeanización”, dice Fiol, que se convirtió en ecofeminista en la defensa del Humedal, a partir de las quemas que arrasaron con la tercera parte de la superficie del humedal entre 2020 y 2021. En las islas de Victoria, que en realidad abarcan una amplia zona que llega hasta el límite norte de la provincia de Buenos Aires, la explotación ganadera es una de las actividades económicas más importantes.
+Lo que provoca el calado a 34 pies es que el cauce principal de la vía navegable funcione como un embudo de agua. Entonces, la laguna Grande y la Del Pescado, reservas de agua para abastecer a Victoria, en lugar de recibir caudal por los riachos, se vacían. En otras ocasiones, el riacho Victoria se vaciaba, pero las otras reservas tenían caudal.
+La falta de agua, antes de comprometer -en breve- la provisión de agua potable, trae la escasez de peces, una fuentes de trabajo en Victoria, donde hay alrededor de 1000 familias que viven de la pesca artesanal.
+Carolina Cabrera integra la cooperativa Frutos del Rìo, también parte de la Coordinadora, y exige que la intendenta Isa Castagnino y el gobernador Rogelio Frigerio tomen cartas en el asunto. Las propuestas que reciben no van al fondo de la cuestión: un pedido urgente para que se draguen de las bocas y se realicen de forma permanente trabajos que impidan la acumulación de sedimentos allí. El jueves de la semana pasada, hubo una reunión en el Concejo municipal de Victoria, donde la Coordinadora fue marginada, y no se dio lugar a sus propuestas.
+Desde que empezó a hacerse acuciante la falta de agua, la Coordinadora realizó manifestaciones públicas, una “pescadeada” e incesantes pedidos de reuniones con las autoridades.
+La actual gestión municipal es peronista, y la anterior, de Domingo Maiocco, era de Cambiemos. De todos modos, la capacidad de acción municipal es limitada. “La obra que hicieron para cerrar el ingreso de las bocas y encauzar no es suficiente, con obras internas para que el agua llegue directamente al riacho Victoria no solucionas todo el problema. No alcanza porque no hay perspectivas de que suba el río de acá muchos meses, ya que estamos en época de sequías, y la solución tiene que ser mucho más de fondo, porque si no esto cada vez va a ser peor”, plantea Bustos.
+Por eso es necesaria la intervención provincial. “El plan que tiene la Municipalidad no es dragar las bocas. En realidad, no tiene ningún plan porque prácticamente no puede hacer nada, está juntando firmas como si fuera una sociedad civil, pero un par de Ingenieros municipales están abriendo y cerrando algunos pasos, por los que se escurre el agua del humedal. El problema es el puente Rosario-Victoria, que sabemos que le hizo un tajo al río, a su ecosistema”, expresa Fiol sobre la ruta 174, que atraviesa el Paraná con una extensión de 60 kilómetros.
+Esta obra generó un cambio radical en las formas de vida humana y no humana. “Hay una parte del río que ha cambiado de cauce, y los pescadores están muy enojados porque les cortan el paso de los peces”, agrega.
+“Así como, con el cambio climático, nuestro planeta pasó el umbral de lo que la naturaleza puede regenerar por sí misma, me pregunto si en este humedal no estamos a punto de pasar el umbral del daño irreparable que la naturaleza después ya no puede por sí misma regeneraer, y po eso dudamos de las intervenciones a ciegas”, sostiene Fiol.
+De la Coordinadora del Agua participan pescadores artesanales, pero también algunos isleños que se dedican a la ganadería, pequeños proveedores de turismo, distintos partidos politicos, organizaciones piqueteras y feministas.
+Bustos es también docente en una escuela de la isla, en la extensa zona que pertenece a la jurisdicción de Victoria, que tiene 376 mil hectáreas de islas, un humedal. “Veníamos diciendo que la Hidrovía es un problema. Pero este año, la cosa se puso tan difícil que los pescadores no tienen agua en Laguna Grande, ni en la del Pescado, ni en el Barrancoso, no hay agua y no hay peces desde mucho antes de que empezara la preocupación por el agua potable. También les maestres de las islas empezamos a darnos cuenta antes de que no hay agua, porque es más difícil llegar a las escuelas, hay que dar un vueltón bárbaro”, sigue Bustos.
+La Laguna Grande está jaqueada porque sus bocas están complicadas. La “Del Bobo” está tapada y la Boya 500 (o “Cuatro bocas”), semitabicada. Otros 15 arroyitos que suelen llevar agua a Victoria están secos.
+El riacho Victoria es la única fuente de agua, pero es una pequeña lonja, irreconocible en relación a su caudal habitual. El nivel está muy bajo, hubo mortandad de peces (por falta de oxígeno). Las imágenes de toda la zona muestran una tierra seca, cuarteada, allí donde corrían ríos, riachos y arroyos.
+Para Bustos, es necesario que se hagan obras de infraestructura que minimicen el impacto ambiental. “La consecuencia directa de la vía troncal navegable es que se seque el humedal, que es un pulmón para todo el planeta, y que es la esponja que va a hacer que no se te inunde tu casa cuando vengan las lluvias que van a venir”, enfatiza.</t>
   </si>
   <si>
     <t>Logo las12</t>
@@ -220,7 +434,30 @@
     <t>https://www.pagina12.com.ar/772422-la-trama-oculta-detras-de-los-incendios-forestales-en-cordob</t>
   </si>
   <si>
-    <t>2024-10-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: La trama oculta detrás de los incendios forestales en Córdoba
+Chapeau: Negocios, cambio climático, brigadistas imputados y denuncias silenciadas
+Subtítulo: En el último tiempo se instaló una idea de nueva normalidad: año a año la provincia vive una “temporada de incendios”. ¿Qué hay detrás de la quema recurrente de tierras en una provincia donde la sequía golpea con fuerza y sólo en lo que va de 2024 ardieron 70 mil hectáreas? Las tensiones en el combate de las llamas y los reclamos al gobierno provincial.
+Editoria: Sociedad
+Tags: Córdoba, Incendio forestal, printed-edition, cordoba, incendio-forestal, diario
+URL: https://www.pagina12.com.ar/772422-la-trama-oculta-detras-de-los-incendios-forestales-en-cordob/
+Notícia completa (17 blocos):
+Año a año las imágenes de Córdoba prendiéndose fuego sacuden al país durante unos pocos días. La imagen de estupor se prolonga hasta que semanas más tarde surgirá la preocupante cifra de hectáreas arrasadas por las llamas. Desde hace al menos una década se ha instalado la idea de que la provincia vive dos temporadas: la turística y la de incendios.
+Los vecinos, que todavía no pueden acostumbrarse a esta dinámica del terror que golpea a sus comunidades con focos que barren con vidas y sueños, sacan cuentas y conclusiones. Enumeran justificaciones: negocios inmobiliarios, la autovía de Punilla - una obra de 43 kilómetros de extensión en marcha hace años para la que se avanzó en el desmonte de bosques nativos ubicados en zona roja de preservación -, extracción de recursos naturales con la minería metalífera y el agronegocio picando en punta. Y aparecen agravantes: cambio climático, recortes presupuestarios y dinámicas agrarias del manejo del suelo sin control.
+Los datos parecen darle sustento a sus ideas. En 2020 se quemaron 321.688 hectáreas —convirtiéndose en el año más extremo de la memoria reciente—; en 2021, 65.740 hectáreas; en 2022, 81.544 hectáreas: en 2023, 40.803 hectáreas; y en lo que va del 2024 ya van 69.000 hectáreas quemadas.
+[H2] ¿Brigadistas imputados por apagar incendios?
+Entre la bronca y el enojo los vecinos mascullan más motivos, como el Régimen de Incentivo para Grandes Inversiones (RIGI), que da rienda suelta a la explotación minera y forestal. Y le suman lo que ocurre en el día a día, que tiene que ver con un trato muchas veces hostil de la policía local y los bomberos de la provincia hacia los brigadistas vecinales organizados de manera autónoma.
+Esto pasó durante las últimas semanas en algunos lugares de Córdoba, como San Marcos Sierra y Capilla del Monte, en el departamento de Punilla. Allí vecinos y brigadistas denunciaron cruces con la policía, con Equipo Técnico de Acción ante Catástrofes (ETAC) y con el Departamento de Unidades de Alto Riesgo (DUAR). Además de acusaciones graves sobre el mal manejo del fuego.
+“Hemos tenido situaciones con la DUAR, quienes nos intentaron hacer bajar del fuego. Están iniciando contrafuegos en lugares con mucho viento, prenden y se van. No dejan gente trabajando en el lugar ni están las aguas disponibles, y así fue como este fuego fue creciendo”, contó una brigadista de la zona a Página|12.
+Por su lado, Gabriel Brizuela, guardaparque y delegado de ATE en el Parque Nacional Quebrada del Condorito, explicó a este diario que “con la creación de estas unidades de élite (ETAC y DUAR), que han sido más marketing político que otra cosa, los cuarteles de bomberos voluntarios han sido desmantelados”. Y que esto se debe a que “el gobierno de Córdoba, que promueve un modelo extractivista” buscar armar una “puesta en escena para mostrar que se preocupa por resolver los incendios”.
+[H2] Es caso de Lalo y la agresión a los bomberos
+Hay dos casos que exponen estas tensiones de una manera contundente. Uno tiene que ver con la imputación de Lautaro "Lalo" Burgos, un vecino de San Marcos que fue detenido cuando intentaba ir con su camioneta a una zona afectada por el fuego para hacer un recambio de brigadistas en la zona y bajar nuevamente al pueblo a quienes desde hacía horas estaban trabajando.
+Su abogado, Pablo Olmos, explicó a Página|12 que hasta hoy no terminan de entender los motivos del procesamiento, y que están esperando a la indagatoria para conocer las acusaciones en una causa cuya calificación penal es “lesiones leves calificadas”. Para el defensor, “existe un encono de la policía que ante cualquier circunstancia en la que puedan verduguear a esta gente, lo hace”.
+Este no fue el único episodio de tensión con la policía. “El miércoles vieron a dos personas prendiendo fuego, llamaron a la policía y nunca llegó. Y vos perdiste la oportunidad de saber quién está prendido el fuego. Se van a encontrar con que existe un incumplimiento de deberes de funcionario público”, relató.
+Como contracara está el ataque que recibieron los Bomberos Voluntarios de Valle Hermoso por parte de algunos vecinos, quienes rompieron los vidrios del autobomba con piedrazos. Según explicó el jefe del cuerpo, Fernando López, los agresores serían “propietarios de campos que no quieren que los bomberos ingresen a la zona”. Pero la escena aparece muy vinculada con estas tensiones.
+[H2] La respuesta del Gobierno de Córdoba
+El secretario de Seguridad de Córdoba, Ángel “Lito” Bevilacqua, explicó a Página|12 que los incidentes con vecinos ocurrieron en el lugar donde apedrearon a los bomberos y que “ahí hay un grupo de ambientalistas” a los que no se los dejó trabajar “para preservar a los vecinos a los que se les pide que acaten las ordenes” en una situación de riesgo.
+Un argumento similar fue desplegado a este medio por Roberto Schreiner, bombero voluntario y vocero de la Secretaría de Gestión de Riesgo: “No se debe hacer un trabajo conjunto porque hay normas a completar, requisitos a cubrir. El índice de peligro es muy alto, es uno de los trabajos más peligrosos del mundo y nos complica todo el trabajo y la maniobra”.
+“Por supuesto que los entiendo y conozco los malestares de los vecinos, porque tengo muchos amigos. Este es un problema de cambio climático. Nos da miedo, porque los autoconvocados andan con remeras y alpargatas, y no tienen idea (de cómo trabajar). El equipo nuestro sale un palo y medio. Mirá si no vamos a tener miedo que se nos queme un vecino, porque después imputan al que está a cargo de la jurisdicción”, añadió.</t>
   </si>
   <si>
     <t>Dylan Resnik</t>
@@ -235,7 +472,24 @@
     <t>https://www.pagina12.com.ar/772297-que-se-ve-cuando-se-mira-a-brasil</t>
   </si>
   <si>
-    <t>2024-10-04T03:01:00Z</t>
+    <t xml:space="preserve">Título: ¿Qué se ve cuando se mira a Brasil?
+Chapeau: Opinión
+Subtítulo: Desde Río de Janeiro
+Editoria: El Mundo
+Tags: Luiz Inácio Lula da Silva, Brasil, medioambiente, printed-edition, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/772297-que-se-ve-cuando-se-mira-a-brasil/
+Notícia completa (11 blocos):
+Desde Río de Janeiro
+Hace poco, al hablar en la apertura de la nueva sesión de la Asamblea General de las Naciones Unidas, cumpliendo el ritual existente desde su implantación en 1948 y que asegura ese rol a Brasil, el presidente Lula da Silva ha sido enfático al cobrar de todos los países del mundo un esfuerzo sin límites para controlar la devastación del medio ambiente.
+Tal compromiso es exactamente el mismo que él se comprometió a cumplir cuando asumió la primera de sus tres presidencias, en 2003. La segunda vino enseguida, y duró hasta 2013. En 2023 inauguró la tercera, que sigue a pleno vapor.
+Es verdad que en sus dos primeros mandatos se avanzó de manera concreta. Insuficiente, por supuesto, pero concreta. En la primera presidencia de la sucesora, Dilma Rousseff, ese avance perdió fuerza. En el segundo, perdió más. Luego vino el golpe llevado a cabo por el Congreso, que la tumbó y puso en el sillón presidencial a un mequetrefe llamado Michel Temer, y todo se paralizó.
+Fue entonces que adentró en el tablado -y en el despacho presidencial – un desequilibrado y corrupto llamado Jair Bolsonaro y el escenario cambió de manera radical. Bolsonaro no sólo permitió como incentivó, y muchas veces financió con millonarios recursos públicos, a los devastadores del medio ambiente que integran el llamado “agronegocio’, y que en buena parte tienen como verdadero negocio destrozar todo que encuentran en su camino con tal de llenar sus billeteras hasta reventarlas.
+Mucho se equivocan los que dicen que lo que se ve cuando se mira a Brasil es pura devastación. Ese tiempo ya pasó. Acorde a lo que indican – y comprueban - científicos de aquí y de otras latitudes-, hoy día lo que se ve cuando se mira a Brasil son nubes, pesados nubarrones que cubren a casi 85% del territorio de ese país que tiene dimensiones continentales. Nubarrones que son pura contaminación.
+Si en agosto y septiembre hubo largos periodos en que los nubarrones cubrían cubrían 60% del espacio brasileño, en los últimos días se llegó a 80%. El calor intenso – e insólito – vivido en el pasado invierno contribuyó para alastrar las nubes que tapan el cielo.
+El domingo que viene habrá elecciones locales en los casi seis mil municipios brasileños. Y mientras los partidos políticos y sus candidatos tratan de encontrar un medio eficaz para sacar la buena parte del electorado que se encuentra indiferente a la fecha, la Justicia Electoral trata de encontrar medios eficaces para enviar urnas electrónicas y fiscales a municipios – algunos regionalmente importantes – que se encuentran al borde del aislamiento, gracias a la sequía.
+Sí, sí, es verdad que Lula da Silva tiene buenos – y son varios – datos positivos para celebrar cuando el segundo año de su tercer mandato se acerca al final. El desempleo, por ejemplo, bajó a 6,6 %, nueva marca histórica. La renta de los empleados, mientras tanto, creció. Solamente en agosto fueron registrados poco más de 230 mil nuevos puestos de trabajo formal, es decir, al amparo de toda la legislación.
+Pero hay otros datos alarmantes o, cuando menos, indignantes. Por ejemplo: pese a ser uno de los países con las mayores poblaciones carcelarias del mundo – pierde con Estados Unidos y China, y nada más – hay solamente 374 presos por crímenes ambientales, como los incendios intencionales. Conozco a dos cafés en Ipanema que, sumadas sus mesas, en las noches de sábado abrigan a más gente.
+Así de desigual es la Justicia frente a la destrucción de lo que queda de mi pobre país. Hay que ver hasta cuándo queda algo…</t>
   </si>
   <si>
     <t>Eric Nepomuceno</t>
@@ -250,7 +504,21 @@
     <t>https://www.pagina12.com.ar/771945-exportaciones-y-deforestacion</t>
   </si>
   <si>
-    <t>2024-10-03T03:01:00Z</t>
+    <t xml:space="preserve">Título: Exportaciones y deforestación
+Chapeau: La UE posterga exigencias de garantías a exportadores de soja y de carne
+Subtítulo: En medio de presiones de sectores de los países productores de materias primas, la Comisión Europea propondrá un retraso de su ley para aplicar normas de deforestación a nivel mundial.
+Editoria: Economia
+Tags: Deforestación, unión europea, printed-edition, deforestacion, union-europea, diario
+URL: https://www.pagina12.com.ar/771945-exportaciones-y-deforestacion/
+Notícia completa (8 blocos):
+En medio de presiones de sectores de los países productores de materias primas, la Comisión Europea propondrá un retraso de su ley para aplicar normas de deforestación a nivel mundial. La exigencia de certificación de que los productos agrícolas y ganaderos que se le venden a la Unión Europea no estuvieran originados en tierras desforestadas iba a comenzar a regir desde enero de 2025. La nueva fecha de aplicación sería enero de 2026.
+En el caso de Argentina, implicaba que las exportaciones de carne y soja a la Unión Europea, que rondan los US$ 4.000 millones anuales, debían quedar sometidos a la presentación de las correspondientes garantías para ingresar al Viejo Continente a partir de enero.
+Según datos de la Bolsa de Cereales de Buenos Aires, el promedio de exportaciones de carne a Europa del 2021 a 2023 fue de US$ 462 millones, el 14% del total embarcado por este sector. Mientras que en el complejo sojero, tomando el mismo período, fue de US$ 3.556 millones.
+El bloque europeo presentó un proyecto de enmienda para posponer 12 meses las normas que tienen como objetivo frenar la parte de la deforestación de la que la Unión Europea es responsable a través de sus importaciones de materias primas clave, como el café, el cacao, la soja y la carne de vacuno.
+La regulación de la UE debía entrar en vigencia el próximo 30 de diciembre y ha recibido el rechazo de distintas entidades del agronegocio argentino, que se vería afectado al tener que dar garantías de libre deforestación en sus producciones de soja y carne.
+"Celebramos la reprogramación de la implementación del reglamento europeo de libre deforestación, fruto de un enorme esfuerzo de gobiernos y cadenas de valor", dijo la Cámara de la Industria Aceitera Argentina (CIARA).
+Por su parte, la Sociedad Rural Argentina (SRA) destacó "la decisión que ha tomado la Comisión de la UE de pedir posponer y rever la aplicación de la norma 1115/2023 respecto a la deforestación agregada para los productos con destino a ese mercado".
+Si el Parlamento Europeo y el Consejo lo aprueban, la ley entrará en vigor el 30 de diciembre de 2025 para grandes empresas, y el 30 de junio de 2026 para micro y pequeñas empresas.</t>
   </si>
   <si>
     <t>"Deje de incentivar la violencia"</t>
@@ -262,7 +530,25 @@
     <t>https://www.pagina12.com.ar/770724-deje-de-incentivar-la-violencia</t>
   </si>
   <si>
-    <t>2024-09-27T22:37:02Z</t>
+    <t xml:space="preserve">Título: "Deje de incentivar la violencia"
+Chapeau: La respuesta de Máximo Kirchner a Milei por la falsa acusación en torno a los incendios en Córdoba
+Subtítulo: El dirigente de La Cámpora salió a responderle al mandatario, quien había acusado a la organización de tener vínculo con las quemas de miles de hectáreas. Además, la ministra de Ambiente bonaerense, Daniela Vilar, denunció el vaciamiento de los fondos destinados a manejo del fuego.
+Editoria: El País
+Tags: Máximo Kirchner, maximo-kirchner, diario
+URL: https://www.pagina12.com.ar/770724-deje-de-incentivar-la-violencia/
+Notícia completa (12 blocos):
+El diputado y referente de La Cámpora, Máximo Kirchner, junto a la ministra de Ambiente bonaerense, Daniela Vilar, salieron a responder a la falsa noticia difundida por el presidente Javier Milei respecto de que la organización kirchnerista había estado detrás de los incendios en Córdoba. "Deje de incentivar la violencia porque después va alguien y la aplica. Es mucho mejor sentarse hablar, discutir y dialogar", le respondió Kirchner, quien junto a Vilar recordaron la sanción la modificación a la Ley de Manejo del Fuego impulsada y aprobada durante el gobierno del Frente de Todos para limitar la especulación inmobiliaria y del agronegocio sobre las tierras incendiadas.
+"Estamos viviendo una situación crítica. Nos preocupa y también nos ocupa", marcó Kirchner sobre el incendio de más de 45 mil hectáreas de bosques en la provincia mediterránea que encontró un pequeño alivio en las últimas horas tras estar una semana bajo fuego. En tono crítico, Kirchner recordó la sanción de la modificación a la Ley de Manejo del Fuego que fue aprobada en 2020 por el Congreso, tras una año en el que los incendios habían arrasado un millón de hectáreas, en particular, en Córdoba y el Delta del Paraná.
+Vilar, diputada durante el debate de modificación de la normativa, explicó que Ley de Manejo del Fuego sienta un piso mínimo de cuidados a través del Sistema Federal de Manejo del Fuego. Destacó además que en 2022, fue modificada para ampliar los cuidados sobre otros ecosistemas, además de los bosques nativos, como bosques implatandos, humedales, pastizales y áreas naturales. La modificación marcó la prohibición de que se modifique el uso de suelo, entre 30 a 60 años, para evitar el fin especulativo de los incendios con objetivo de explotarlos a través del negocio inmobiliario o agropecuario.
+El presidente Javier Milei tiene entres cejas esa normativa, a la que mencionó en la cadena nacional de diciembre cuando anunció el aún vigente DNU 70/2023 -a pesar de que no estaba incluida- y que luego intentó modificar en la versión ómnibus de la Ley Bases, algo que quedó en el camino por la lucha de las organizaciones socioambientales. En la versión negociada de la Ley Bases, el Gobierno sí logró quedarse con las facultades para "eliminar" a gusto fondos fiduciarios, entre los que podría estar el el Fondo Nacional del Manejo del Fuego.
+"Este Gobierno congeló el presupuesto destinado para el Servicio Nacional del Manejo del Fuego y durante el primer trimestre no ejecutó ni un solo peso", denunció la ministra de Ambiente bonaerense e ironizó: "Hay cosas que el mercado no va a hacer". "No apaga incedios (el mercado), generalmente los genera", agregó Kirchner en sintonía con la ley modificada en 2022.
+En ese punto, ambos dirigentes de La Cámpora invitaron al Gobierno a debatir los 28 mil millones de pesos destinados, según el Presupuesto 2025, al Servicio del Manejo del Fuego. "Acá tenemos una buena oportunidad para mostrar que podemos construir buenos consensos en función del interés colectivo", sostuvo Kirchner y recordó que también, durante la gestión del Frente de Todos, se aprobó una ley que mejoraba el trabajo de los bomberos voluntarios.
+[H2] "Presidente, usted incentiva el odio a través de las redes sociales"
+Tras marcar las propuestas del espacio para combartir los incendios y sus causas, el dirigente de La Cámpora se encargó de responder a la falsa acusación que Milei cargó contra la organización política. "Presidente, usted es el presidente de todos y todas los argentinos... Me da mucha pena que acuse a una organización política, en este caso La Cámpora, pero que puede ser otra, depende de cómo se levante, porque eso tiene consecuencias", le señaló.
+El diputado de Unión por la Patria enmarcó la falsa acusación en el clima de violencia política que generó el intento de maginicidio contra la entonces vicepresidenta Cristina Kirchner. "Cuando usted dice esas cosas, hay gente que cree, como creyeron Sabag Montiel y Brenda Uliarte, que hay que suprimir a los que piensan diferente. Usted lo que hace es incentivar ese odio a traves de las redes y después, quizá, hay alguien que lo toma en serio y lo lleva adelante como pasó el 1° de septiembre de 2022 con Cristina."
+Kirchner le recordó a Milei que entre otras acusaciones que el mandatario lanzó por redes, lo había acusado de "urdir una trampa legislativa" para la aprobación de la ley que aumentaba los haberes jubilatorios, y que luego el presidente vetó y logró un pacto con la oposición para ratificar la impugnación en la Cámara de Diputados.
+"Usted me acusó de tramposo legislativo y dio vuelta a seis diputados que dijeron que sí y 20 días después dijeron que no. Me parece que el tramposo está en otro lugar", le sugirió el diputado de UxP e invitó a Milei a "asumir el Gobierno y dejar la cuenta de Twitter tranquila un rato".
+"Hágase cargo del día a día de un Gobierno que, realmente, nuestro pueblo la está pasando muy mal", le exigió el diputado e insistió con plantaer las disputas en instancias de diálogo político: "Nos podemos encontrar en el lugar que usted quiera. Ya Cristina le dijo que vaya al Patria y no fue... Cuando esté diga, estamos dispuestos a dar todos los debates que la Argentina necesita, sin show ni tanta parafernaria de custodias".</t>
   </si>
   <si>
     <t>Salta, otra vez bajo la nube de humo de los incendios en el Amazonas</t>
@@ -274,7 +560,25 @@
     <t>https://www.pagina12.com.ar/768833-salta-otra-vez-bajo-la-nube-de-humo-de-los-incendios-en-el-a</t>
   </si>
   <si>
-    <t>2024-09-20T03:57:53Z</t>
+    <t xml:space="preserve">Título: Salta, otra vez bajo la nube de humo de los incendios en el Amazonas
+Chapeau: Villamontes y Yacuiba bajo riesgo de propagación del fuego
+Subtítulo: El viento norte la posicionó nuevamente sobre parte de la provincia, aunque su concentración solo compromete parcialmente la visibilidad. Defensa Civil de Bolivia declaró el miércoles a municipios de Tarija, La Paz y el Beni en zona de alto riesgo. El polvo en suspensión contiene monóxido de carbono que disminuye la calidad del aire.
+Editoria: Salta|12
+Tags: Incendios forestales, Amazonas, Salta, Cambio climático, incendios-forestales, cambio-climatico, diario
+URL: https://www.pagina12.com.ar/768833-salta-otra-vez-bajo-la-nube-de-humo-de-los-incendios-en-el-a/
+Notícia completa (12 blocos):
+La nube de humo, consecuencia directa de varios meses de incendios forestales en Paraguay, Brasil, Bolivia y Perú, regresó al norte argentino ayer jueves.
+El último boletín por alerta de riesgo por propagación de incendios forestales que publicó el Viceministerio de Defensa Civil del Estado Plurinacional de Bolivia, declaró en alto riesgo a tres municipios de la jurisdicción de Tarija, entre ellos Yacuiba y Villamontes, comunas vecinas de Argentina y la provincia de Salta. Se sumaban 27 municipios del departamento Santa Cruz, 9 del departamento del Beni, y una comuna del departamento La Paz.
+Hasta ayer, la nube se extendía desde el norte de Perú hasta el noreste de Argentina, con concentraciones variables de monóxido de carbono producto de cuatro meses de incendios en el corazón del continente suramericano.
+“El humo de los incendios no solo cubre el cielo de Bolivia, sino que ha comenzado a afectar a provincias argentinas, un recordatorio de que esta crisis no conoce fronteras”, subrayó en un comunicado la organización civil Redes Chaco. Recordó que “desde 2019 Bolivia sufre consecuencias devastadoras, no solo por la destrucción de bosques, sino también por el impacto en el hábitat de más de 40 pueblos indígenas”. En ese sentido, la ong señaló que los incendios representan sobre todo una crisis humanitaria, porque las comunidades locales "sufren ante la pérdida de sus medios de vida y sus territorios”. Además, manifestó su preocupación por el impacto a largo plazo de los incendios en el cambio climático, porque liberan cantidades masivas de carbono a la atmósfera.
+En diálogo con Salta/12, Oswaldo Maillard, biólogo con lugar de trabajo en el observatorio de la Fundación para la Conservación del Bosque Chiquitano en Santa Cruz de la Sierra, recordó que los incendios forestales comenzaron en esa región del Estado boliviano en junio pasado. Agregó que los organismos nacionales indican que el fuego ya superó los 4 millones de hectáreas de bosques consumidos por las llamas, muchos situados en áreas protegidas, parques nacionales y reservas privadas. "Creemos que esa cifra será mucho mayor", anticipó. El 7 de septiembre, el departamento Santa Cruz se declaró en emergencia, y el departamento del Beni, en zona de desastre. Son dos jurisdicciones con más incendios forestales.
+Maillard explicó que, aislados primero, los focos ígneos comenzaron en zonas ubicadas entre las frontera de su país con Paraguay y Brasil, y que por el mal manejo del fuego de productores ganaderos y campesinos, rápidamente se salieron de control debido a la sequía predominante y los vientos. "Estimamos que esas quemas de cordones (la quema de pastizales) comenzaron a generar frentes entre el 6 y 11 de agosto", indicó. El biólogo aseguró que todavía permanecen activos varios frentes de fuego y que superan, en algunos casos, los 50 kilómetros de largo.
+"Tan solo en el Área Natural de San Matías", una reserva de manejo integrado en el departamento Santa Cruz, "el fuego quemó el 70 por ciento de su superficie boscosa y continúa avanzando", sostuvo. Como tiene una extensión de 2.930.000 hectáreas, Maillard estimó que el fuego ya degradó más de millón y medio de hectáreas. Detalló que hay incendios activos en áreas protegidas del norte del departamento, como el Parque Nacional Noel Kempff Mercado, el Parque Nacional Otuquis y la Reserva Municipal Copaibo, entre otras áreas boscosas.
+[H2] El humo y el ecocidio
+"La gente recién tomó conciencia del desastre ambiental cuando el humo llegó a sus casas", reflexionó el investigador boliviano. "Eso ocurrió en Santa Cruz entre finales de agosto y principios de setiembre", precisó. Durante esas semanas la nube de humo también se posó sobre territorio salteño, aunque con mayor densidad que la que reingresó ayer el jueves.
+"Las personas pierden calidad de vida y biodiversidad por los incendios. Se ha naturalizado la quema de bosques y es lo realmente preocupante", continuó. Maillard analizó que si bien la sequía persiste hace algunos años, ese fenómeno se complejiza bajo "la cultura del rebrote", porque implica un manejo del fuego orientado a acelerar el crecimiento de algunas pasturas para consumo animal.
+"El fuego se utiliza ahora para abrir territorio al agronegocio, para pasturas o cultivo", analizó por su parte el ambientalista salteño Martín Herrán. "Se trata de un fenómeno que también se observa en Salta, porque permanentemente se incendian espacios de los departamentos San Martín y Orán", argumentó, aludiendo a las jurisdicciones provinciales con mayor área de bosques o reservas forestales. El último gran incendio de 2022 consumió casi 200 mil hectáreas de la Reserva de Biósfera de Yungas. "Hace décadas que no se registran grandes incendios en Rivadavia Banda Sur y Norte, tampoco sobre el departamento Anta", recordó. "La lógica de los productores pasa por ganar tierra conquistando bosque degradado, algo que ya hicieron antes del primer Ordenamiento Territorial del Bosques Nativo" de 2008, sostuvo.
+En la misma línea, el abogado ambientalista Enrique Viale también relacionó los incendios con el modelo de agronegocios que se instaló en el Cono Sur en la década del 90. “Es transgénico y provocó el desastre de la deforestación para extender la frontera agropecuaria, principalmente para el cultivo de soja", analizó. "Ahora ese panorama se agrava por el cambio climático global", opinó. Para el activista, los eventos ígneos, recurrentes sobre distintas áreas de Argentina y Sudamérica, "son imágenes de un colapso parcializado”. “Lo peor es que nos vamos acostumbrando mientras transitamos la Era del Piroceno donde el fuego nos resulta incontrolable", cerró en referencia al concepto del historiador ambiental norteamericano Stephen Pyne.</t>
   </si>
   <si>
     <t>Analía Brizuela</t>
@@ -289,7 +593,23 @@
     <t>https://www.pagina12.com.ar/765440-nicolas-pino-aseguro-que-no-hay-conjeturas-sobre-el-atentado</t>
   </si>
   <si>
-    <t>2024-09-07T03:01:00Z</t>
+    <t xml:space="preserve">Título: Nicolás Pino aseguró que "no hay conjeturas" sobre el atentado en la sede de la Rural
+Chapeau: En una conferencia de prensa
+Subtítulo: Tras el alerta y la preocupación por el paquete explosivo recibido en la sede de la Sociedad Rural, el presidente de la entidad centenaria del agronegocio, Nicolás Pino, descartó que
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/765440-nicolas-pino-aseguro-que-no-hay-conjeturas-sobre-el-atentado/
+Notícia completa (10 blocos):
+Tras el alerta y la preocupación por el paquete explosivo recibido en la sede de la Sociedad Rural, el presidente de la entidad centenaria del agronegocio, Nicolás Pino, descartó que lo ocurrido haya estado relación con su "relación de empatía personal" con el presidente Javier Milei ni lo relacionó a "extremistas veganos" y "anarquistas", como hizo la ministra de Seguridad, Patricia Bullrich.
+En conferencia de prensa, Pino aseguró no tener miedo por lo ocurrido y que lo sucedido no marcará las decisiones de "cómo seguir en el día a día", aunque se mostró abierto a recibir recomendaciones y "opiniones de la gente que conoce" sobre temas de seguridad.
+La conferencia ocurrió en la sede de la SRA, ubicada en la calle Juncal al 4450, en el barrio porteño de Palermo, donde Pino estuvo acompañado por el vicepresidente primero de la SRA, Marcos Pereda, y el vicepresidente segundo, Raúl Etchebehere.
+Ante las consultas sobre el relato que intentaron imponer Bullrich y los trolls del gobierno nacional respecto de una relación con un ataque "terrorista", Pino dijo que lo sucedido recuerda a "algo de la Argentina del pasado", pero confió en que "como sociedad, seguramente no es lo que la sociedad argentina quisiera volver a refrescar".
+En cuanto a la hipótesis de que el atentado ocurrió por la cercanía de Pino con el presidente Milei, el titular de la SRA consideró: "No puedo decir que este episodio tenga referencia a la relación que tengo con el Presidente". En ese tono, intentó evitar cualquier tipo de acusación: “No tenemos conjeturas porque, realmente no sabemos o no tenemos idea. Sí son situaciones que traen a la memoria épocas pasadas".
+Pino también agradeció las llamadas de respaldo que recibió en las últimas horas, en particular de funcionarios del gobierno nacional, pero descartó tener en agenda una próxima reunión con Milei a partir de lo ocurrido y señaló que como parte de a investigación le sacaron el celular.
+Sin embargo, volvió a marcar que continuará trabajando por el sector del campo al que defiende y destacó su afinidad con el gobierno de La Libertad Avanza: "Hay una oportunidad inmensa y no la tenemos que dejar pasar. Tenemos todo para hacer las cosas que tenemos que hacer, tenemos todo para hacer lo que el mundo entero demanda."
+Más temprano, el vicepresidente primero de la SRA también había descartado las versiones de que ya acusaban a grupos veganos o ambientalistas por el atentado, ni tampoco descartó la hipótesis de que se trata de algo armado por el Gobierno en medio del debate por el decreto de fondos reservados para la SIDE.
+“Todo puede ser en esta Argentina nuestra”, dijo Pereda y señaló que “hacer especulaciones temprano, como estamos todavía, en un momento donde no tenemos ni siquiera perspectiva y sin ningún dato más fáctico desde el lado de las investigaciones, me parece un poco prematuro”.
+La investigación sobre lo ocurrido con el artefacto explosivo quedó en manos del juez Daniel Rafecas, que este viernes le tomó declaración a Nicolás Pino y a su secretaria, quien resultó herida al abrir el paquete. "Coincidieron en que no advierten móviles o motivos para lo ocurrido", informaron a la Agencia Noticias Argentinas fuentes judiciales. Desde la oficina de Rafecas dejaron trascender que se está reconstruyendo el recorrido del sospechoso.</t>
   </si>
   <si>
     <t>Colonialismo 2.0: el RIGI, la ofensiva extractivista de pobreza programada</t>
@@ -301,7 +621,29 @@
     <t>https://www.pagina12.com.ar/765219-colonialismo-2-0-el-rigi-la-ofensiva-extractivista-de-pobrez</t>
   </si>
   <si>
-    <t>2024-09-06T03:05:03Z</t>
+    <t xml:space="preserve">Título: Colonialismo 2.0: el RIGI, la ofensiva extractivista de pobreza programada
+Chapeau: Zona de promesas (para los ultramillonarios)
+Subtítulo: ¿Sabés cuántos años vas a tener cuando se termine el RIGI? Sumale treinta a tu edad. En esta nota, te contamos cómo es uno de los caballitos de batalla de la Ley Bases: un régimen extractivista que garantiza saqueo neocolonial en favor de los grandes capitales concentrados, mientras que condena a los territorios argentinos a ser nuevas zonas de sacrificios. Repasamos los antecedentes, cómo el neoliberalismo construye la idea de que el RIGI es lo mejor que le puede pasar al país y cómo será nuestro paisaje, cuando volvamos a ser el nuevo enclave colonial. Perspectivas para abordar las distintas aristas de un problema urgente que requerirá un plan de lucha a la altura.
+Editoria: Las12
+Tags: RIGI, Ley Bases, extractivismo, Ambiente, Javier Milei, Neoliberalismo, ley-bases, javier-milei
+URL: https://www.pagina12.com.ar/765219-colonialismo-2-0-el-rigi-la-ofensiva-extractivista-de-pobrez/
+Notícia completa (16 blocos):
+Una de las características de las políticas neoliberales es promover la apropiación privada y explotación intensiva por el gran capital de los bienes naturales para su exportación y valorización en el mercado mundial; eso que se llama habitualmente el modelo extractivo exportador o, sucintamente, extractivismo. Así, cada una de las cuatro olas neoliberales que sufrió nuestro país trajo su cuota extractiva: la de la dictadura de Videla y Cía. con la liberalización y reprimarización económica; la del menemismo con las privatizaciones y las reformas legales pro-corporaciones; la del macrismo con la devaluación y la disminución de las retenciones y regulaciones; y ahora la del actual gobierno.
+No es una casualidad que estos sectores del gran poder económico local y trasnacional (el agronegocio, las megamineras, las petroleras, etc.) hayan sido y sean hoy en Nuestra América uno de los principales sostenes de los gobiernos de extrema derecha y de facto que vienen a profundizar aún más el despojo y la destrucción socioambiental propios de la agenda neoliberal.
+De este modo, bajo el gobierno de Milei se acentúa una ofensiva extractivista que golpea territorios y poblaciones bajo la expansión de la frontera agrícola y la deforestación, o con desplazamiento de pobladores y ataques y criminalización a las comunidades campesinas y de pueblos originarios, o con la autorización de nuevos emprendimientos extractivos. Hechos repetidos en estos meses en diferentes regiones de nuestro país. Y, claro está, acompañados las más de las veces con violencias estatales o paraestatales.
+En ese camino se inscribe la sanción de la Ley Bases -con la declaración de la emergencia, la reforma del Estado, las privatizaciones y la reforma energética- y, en particular, uno de sus apartados principales, el Régimen de Incentivos para Grandes Inversiones, o RIGI. Abarcando 65 artículos en 12 capítulos, más de un cuarto de la extensión de la Ley Bases, el RIGI condensa una serie de descomunales privilegios y concesiones al gran capital que decida invertir como mínimo 200 millones de dólares en la industria forestal, turismo, infraestructura, minería, tecnología, siderurgia, energía, petróleo y gas.
+A estos sectores el RIGI les otorga estabilidad fiscal, tributaria, cambiaria y jurídica por un período de 30 años; les permite exenciones de ganancias e IVA que reducen a insignificante su tributación; excluye a sus exportaciones de cualquier gravamen (retenciones) a partir del segundo o tercer año que es cuando fructifican estos proyectos y los habilita a importar máquinas e insumos sin pagar aranceles ni priorizar proveedores y empleo locales en detrimento de la industria y el trabajo argentinos; les asegura libre y completa disponibilidad de las divisas obtenidas por la exportación a partir del tercer año y desde el primero a las que ingresen para la inversión.
+Es decir, desfinancia al Estado, bloquea toda política de redistribución de sus hiperganancias, golpea a los territorios y poblaciones locales por su impacto socioambiental y a las pequeñas y medianas industrias; mientras facilita el saqueo de nuestros bienes comunes naturales. Y, por si todo esto fuera poco, dispone que toda controversia se dirima en tribunales extranjeros, entre ellos el tristemente famoso CIADI; un verdadero nuevo estatuto legal del coloniaje, como ha sido señalado.
+Las consecuencias de este régimen de promoción del extractivismo pueden estimarse con precisión a la luz de su pasado reciente que lejos de las falaces promesas de progreso y desarrollo solo dejó pobreza y destrucción ambiental en las provincias donde se realizó la extracción; y saqueo y crisis a nivel nacional. Su examen sería largo, pero quisiéramos, en esta ocasión, concentrarnos en cuatro cuestiones.
+Como señalamos esta ofensiva extractivista no es nueva, y tampoco lo son sus concesiones legislativas. El RIGI se parece a la Ley N° 24.196 de Inversiones Mineras sancionada bajo el menemismo en 1993 que también aseguraba tres décadas de estabilidad fiscal, tributaria, arancelaria y cambiaria a ese sector. Ya se sabe cuánto el actual gobierno admira y se inspira en los 90 del menemato, en una reedición más farsesca, y también más trágica.
+El RIGI amplia esos beneficios a otras muchas actividades. Pero no es la única novedad. La reforma constitucional del 94 otorgó a las provincias la potestad sobre los recursos del subsuelo acorde a los vientos descentralizadores que inflamaban al neoliberalismo de entonces. En contraposición, el RIGI se impone a las provincias e impide e inhabilita cualquier tributación y regulación que los gobiernos locales decidan. Un unitarismo del ajuste que se ha expresado en otros campos (y en la tensión con los ejecutivos provinciales) y que señala el mayor autoritarismo de la ola neoliberal actual.
+Por otra parte, aquella descentralización de la soberanía sobre los bienes naturales no solo favoreció a las corporaciones y las élites provinciales sino que modeló también las resistencias. Desde la victoria de Esquel de 2003 que detuvo el proyecto megaminero, un sinnúmero de conflictos y movimientos se desplegaron por todo el país en confrontación con estos emprendimientos obteniendo conquistas. En esta dirección, entre 2007 y 2010 en nueve provincias se conquistaron legislaciones que regulaban o prohibían la minería contaminante y, a nivel nacional, se sancionaron la Ley de Bosques y la de glaciares.
+La violación de estas legislaciones o su derogación posterior no opacan los logros de las resistencias que, posteriormente, se manifestaron como los “azos” contra el extractivismo en el Mendozazo (2019) y el Chubutazo (2022) ante los intentos de derogar las conquistas legislativas pasadas. El RIGI al imponer una ley nacional por sobre toda regulación provincial se yergue contra todos estos logros y contra los movimientos y poblaciones que vienen rechazando al extractivismo en el país.
+Pero este adversario principal del RIGI y del extractivismo es nominado por el propio presidente y sus comunicadores como los “ambientalistas”. Hemos escuchado cuanto esta identidad de ecologistas radicales es sindicada como responsable de impedir el progreso, el desarrollo y el bienestar. Una campaña que construye su estigmatización y criminalización. Como todo en este neoliberalismo rancio se trata de un discurso antiguo. Construye una falaz oposición entre la resolución de las necesidades económicas y sociales y la afectación del ambiente, entre lo social y lo ambiental.
+Falaz porque como sabemos las olas extractivistas pasadas, particularmente cuando se privó de toda política redistributiva, solo trajeron más miseria y deterioro ambiental. Allá están las cifras de la pobreza y la indigencia de las llamadas provincias mineras. Falaz también porque promueve una idea de los territorios como vacíos de poblaciones, economías, cultura y vida, como de pura naturaleza, y resignifica las resistencias asociándolas a un ambientalismo bobo.
+Resuenan todavía las palabras de Patricia Bullrich y tantos dirigentes y casta afirmando que en Chubut, en la meseta patagónica, no vive nadie, solo hay guanacos. Allí están los vecinos, los maestros, los trabajadores de la salud y de otros sectores, los pueblos originarios, los campesinos, los pequeños y medianos productores y comerciantes, los científicos, los técnicos, dando vida a los “azos”.
+Las injustificadas concesiones al gran capital que promueve el RIGI merecen una última reflexión. Se fundan en razones ideológicas; las de este anarcopitalismo que extrema la teoría del derrame y llega a considerar verdaderos héroes a los grandes empresarios, a los milmillonarios del neoliberalismo. Da cuenta también de otras razones más menudas, las urgencias prácticas de un plan de ajuste sin fin que requiere de modo apremiante el ingreso de divisas para evitar su colapso. Y no debemos olvidar que ese fue el final de las tres olas neoliberales anteriores.
+[1] Profesor e investigador del Instituto de Estudios de América Latina y el Caribe, F.Soc., UBA.</t>
   </si>
   <si>
     <t>Ines Hayes</t>
@@ -316,7 +658,15 @@
     <t>https://www.pagina12.com.ar/764876-las-retenciones-agrarias-firmes-como-el-cepo-cambiario</t>
   </si>
   <si>
-    <t>2024-09-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: Las retenciones agrarias firmes como el cepo cambiario
+Chapeau: Entre enero y agosto, el aporte de los Derechos de Exportación a la recaudación fue 4,7%
+Subtítulo: En un contexto donde la recaudación tributaria viene creciendo por debajo de la inflación y de cara a un menor aporte proveniente del impuesto PAÍS a partir de septiembre, no parece sencillo pensar en una reducción o eliminación de las retenciones
+Editoria: Economia
+Tags: Campo, Retenciones, printed-edition, diario
+URL: https://www.pagina12.com.ar/764876-las-retenciones-agrarias-firmes-como-el-cepo-cambiario/
+Notícia completa (2 blocos):
+La promesa de bajar las retenciones que Milei le hizo al campo, apenas días atrás en la Rural, se aleja de la realidad al concebir que la recaudación tributaria total viene creciendo por debajo de la inflación y que en paralelo disminuirá el aporte proveniente del impuesto PAÍS. Inclusive en 2025 este último será cero, de acuerdo a otras promesas del Gobierno. Si el “déficit cero” es intocable el Gobierno debería poder explicar cómo reemplazará los ingresos por retenciones, que han sido históricamente relevantes para las cuentas fiscales.
+Pese a que la liquidación del agro en agosto fue buena, la recaudación fiscal por Derechos de Exportación cayó: pasó de representar 4,7 por ciento de la recaudación total en julio a 3,7 por ciento en agosto, según cálculos del especialista en agronegocios, Javier Preciado Patiño, en su cuenta de la red X.</t>
   </si>
   <si>
     <t>Mara Pedrazzoli</t>
@@ -331,7 +681,29 @@
     <t>https://www.pagina12.com.ar/762029-atanor-clausura-despidos-y-audiencia-judicial</t>
   </si>
   <si>
-    <t>2024-08-22T22:46:33Z</t>
+    <t xml:space="preserve">Título: Atanor: clausura, despidos y audiencia judicial
+Chapeau: Contrapunto entre los ambientalistas, el sindicato y la empresa
+Subtítulo: La comunidad de San Nicolás teme por una ola de despidos en la química. Conflictividad por una posible relocalización.
+Editoria: Buenos Aires|12
+Tags: Despidos, San Nicolás, trabajadores, san-nicolas
+URL: https://www.pagina12.com.ar/762029-atanor-clausura-despidos-y-audiencia-judicial/
+Notícia completa (16 blocos):
+A cinco meses de la explosión de uno de sus tanques de atrazina, un químico altamente contaminante, que impregnó el aire en un radio de al menos tres kilómetros, la planta de Atanor, que nunca reabrió, comenzó a enviar telegramas de despido y crece la preocupación entre los trabajadores. Este viernes 23 tendrá lugar una audiencia judicial clave para definir el futuro de la fábrica.
+Consultado por Buenos Aires/12, el secretario general de la regional local de los trabajadores de la industria química, Ricardo García, desmiente que la empresa tenga interés en reducir su operación por caída de ventas o para recontratar personal bajo una legislación más ventajosa.
+"Veníamos trabajando mucho, hasta había personal contratado, que es el paso previo a ampliarse", afirma, y agrega que "desde marzo hasta hoy pagaron el 75 por ciento de los salarios. Es probable que ahora, si no se abre, haya que rediscutir el porcentaje a la baja".
+Sin embargo, fuentes con acceso al expediente, en manos de la jueza penal Luciana Díaz Bancalari, sostienen que la empresa nunca tuvo vocación de reabrir y que, a lo largo de estos cinco meses, más allá de las declaraciones públicas en contrario, Atanor incurrió en sucesivas demoras y maniobras dilatorias.
+En paralelo, la empresa, que cuenta con unos 150 trabajadores, abrió un programa de retiros voluntarios, al que sólo adhirieron una decena. Como antecedente reciente, entre 2017 y 2018, Atanor cerró dos de sus plantas, en las localidades bonaerenses de Munro y Baradero y despidió a casi 150 trabajadores. Entonces, desde el sindicato los acusaron de dejar de producir para importar. Ese mismo año, meses más tarde, la firma amplió y reinauguró su planta de San Nicolás.
+[H2] La gota que rebalsó el vaso
+La explosión a principios de este año, lejos de ser un hecho sorpresivo, fue el último eslabón de una larga cadena. A lo largo de toda la mañana del 20 de marzo, la atrazina diseminada causó irritación de ojos y garganta de gran parte de la comunidad nicoleña. Además, Atanor fue condenada por causarle un daño irreparable al río Paraná, al volcar en sus aguas efluentes sin tratar.
+La planta de Atanor en San Nicolás arrastra conflictos y demandas ambientales desde 2015. Ese año, fueron los propios trabajadores los que denunciaron la contaminación, primero ante el sindicato y luego, a través de sus familiares, ante la opinión pública. Con el correr de los siguientes meses y años se fueron movilizando y sumando a las denuncias los vecinos de los barrios linderos (Química, Belgrano, Obrero y San Isidro), entre los que la prevalencia del cáncer es mucho mayor que en otras zonas.
+Actualmente, la posición del sindicato es que la planta de atrazina permanezca cerrada pero se habilite la producción en los demás sectores, porque el proceso de relocalización de esa planta podría demorar tres, cuatro o más años.
+La relocalización es un reclamo histórico de los vecinos, ya que con el crecimiento demográfico de la ciudad, la planta quedó en medio de una zona residencial. Pero, a la vez, es apenas la mitad del problema. Por el tipo de actividad que desarrolla, Atanor debería estar localizada, sí o sí, dentro de un parque industrial, donde los controles e inspecciones son habituales y exhaustivos.
+La realidad de Atanor es que produce agroquímicos y fertilizantes, que provee al agronegocio, especialmente en toda la zona núcleo. Las perspectivas del sector para el futuro no son alentadoras: el precio internacional de la soja está en mínimos históricos y el Gobierno nacional no cede a los reclamos, ni de devaluación ni de eliminación de retenciones.
+Las partes (el sindicato y la empresa, por un lado, y las organizaciones ambientalistas querellantes, por otro), están citadas para una audiencia en el juzgado de Díaz Bancalari este viernes. Todos los consultados entienden que ese será el día D, para definir si Atanor vuelve a producir.
+[H2] Parque Aguiar
+El de Atanor no es el único conflicto ambiental en San Nicolás. En 2020, el Ejecutivo que entonces encabezaba Manuel Passaglia, hermano del actual intendente, comenzó una serie de obras en el área natural protegida Parque Rafael Aguiar, frente a la costa del Paraná, en abierta violación del plan de manejo del parque, que tiene rango de ordenanza municipal, con el objetivo de facilitar el acceso vehicular y concesionar las playas.
+La Comisión Nicoleña por el Ambiente (CONA) denunció los hechos ante la Justicia provinical y la demanda fue escalando hasta llegar a la suprema corte, que meses atrás declaró la clausura y ordenó retirar todas las máquinas y equipamiento vial.
+Según la CONA, las aguas a esa altura están contaminadas por efluentes cloacales, que el municipio vuelca directamente en el río, ya que la planta de tratamiento no está en condiciones por falta de mantenimiento.</t>
   </si>
   <si>
     <t>Logo buenos-aires12</t>
@@ -346,7 +718,19 @@
     <t>https://www.pagina12.com.ar/758764-vale-decir</t>
   </si>
   <si>
-    <t>2024-08-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: Vale decir
+Editoria: Radar
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/758764-vale-decir/
+Notícia completa (8 blocos):
+El interior profundo
+Entre 1979 y 1984 Richard Avedon abandonó los retratos glamorosos de estrellas de Hollywood que había inmortalizado hasta entonces para meterse en el oeste profundo, su mitología y su gente, cincelada a fuerza de trabajo y de una vida que no siempre les sonreía. Pero una vida verdadera. Esa es una de las influencias a las que volvió el fotógrafo Tony Valdez para su serie En el sur americano, que se exhibe desde el próximo sábado hasta el 18 de noviembre en el Museo Provincial de Fotografía Palacio Dionisi de Córdoba. “Comencé a fotografiar gauchos en las fiestas patronales cordobesas con la intención de dejar registro de esa gente que va desapareciendo a medida que avanza el agronegocio, pero que todavía existe en el interior profundo”, explica Valdez sobre el origen de su indagación. “Utilicé primero como base un fondo de estudio, que luego se transformó en una tela blanca más portátil. Pero no sólo eso cambió. Porque también decidí sumar al proyecto a otras personas que conviven con esos gauchos y quizás son más invisibles aún”, agrega. Otra de las singularidades fue la pregunta sobre si las fotos debían ser a color o en blanco y negro. No se trata, obviamente, de una indagación meramente técnica sino sobre todo, del impacto expresivo de cualquier decisión que tomara. Y al final decidió incorporar ambas posibilidades para crear una tercera, mestiza, que atraviesa conceptualmente el conjunto de estas imágenes. “En el proceso de edición empecé a dudar sobre una cuestión que en las épocas analógicas se resolvía antes de comenzar un proyecto pero que la era digital permite abrir el juego antes de tomar la decisión final. Así fue como en el proceso de pruebas y más pruebas, una copia monocroma se superpuso sobre la misma foto en color, y esa combinación me gustó, me pareció interesante”, relata. Confiesa, además, que para esa decisión volvió a aquella frase de Godard que dice: “No es de donde tomamos las cosas, lo que importa es hacia donde las llevamos”. Valdez cree, justamente, que casi nada es original pero sí distinto. Y es la búsqueda que privilegió.
+Una pasión de otro mundo
+El ilusionista británico-israelí Uri Geller se hizo famoso en los años setenta por doblar cucharas con la mente y otras proezas que le valieron luego un lugar destacado en realities de todo el mundo. También le interesaban los fenónemos extraterrestres. Con el tiempo se retiró y abrió un museo personal donde exhibe memorabilia de aquella época. En ese museo, a partir de ahora, habrá un par de lentes de marco redondo que pertenecieron a John Lennon, a quien Geller no duda de calificar como “un gran amigo”. La subasta la llevó a cabo Catherine Southon Auctioneers de Chislehurst y Geller pagó 40 mil libras por este objeto icónico. Geller argumentó que, más allá del valor histórico, los lentes tenían un significado único para él “porque los lentes son como una extensión del alma de la persona” y por la “relación especial” que tuvo con el artista. “Vivíamos muy cerca el uno del otro en Nueva York en los años 70 y él cambió mi vida. Nos conocimos porque ambos creíamos en los extraterrestres y a él le fascinaba mi colección de objetos alienígenas”, explicó Geller, de 77 años. Y añadió como si tal cosa: “Una vez me regaló un huevo que le había sido dado un ser extraterrestre”. Estos lentes tienen, también, una historia interesante detrás porque Lennon se los regaló a un fan durante una recorrida por Abbey Road mientras cumplía años. Los lentes estaban sobre el piano, el pibe no pudo evitar agarrarlos y Lennon le dijo “son tuyos, feliz cumple”.
+Pollitos sin fuga
+El robo de cables para vender luego el cobre es una de las tantas postales tétricas de nuestros días (sí, es una práctica peligrosa). Pero no son cosas que sólo ocurran en los países donde gobiernan señores con peluca. Desde Japón llega la noticia de que alguno tuvo la idea de robarse todos los cables en una granja de pollos. Ocurrió en Shibukawa, prefectura de Gunma, en una madrugada, estos días. Según la policía, faltaron 170 metros de cable valorados en cinco millones de yenes (o sea, unos 33 mil dólares). Los cables conectaban la instalación y un transformador de energía especial para que el asunto marche. El corte, sin embargo, provocó que se detuviera el aire acondicionado y, en consecuencia, casi un millón de pollos murieron. Estas instalaciones funcionan con energía solar pero eso, necesariamente, incluye una estructura que requiere este tipo de cables. Como los japoneses no tienen problemas de seguridad, tampoco tienen sistemas de alarmas sofisticados y estos robos han comenzado a ser sistemáticos. En esta historia se mezcla el uso de energías renovables, tan en boga en un mundo que se está quedando sin recursos, con la milenaria costumbre de comer pollos a mansalva. Pero donde a los japoneses se le queman los cables, es con el asunto del robo ya que no entienden por qué alguien haría algo así en una de las tres economías más importantes del mundo. He aquí un argumento para otra historia distópica.
+Detrás de la máscara
+La sala entera contuvo la respiración. Y no porque Ian McKellen hubiera salvado una vez más a la Tierra Media del temible Sauron. El actor, mundialmente conocido como Gandalf, de la saga El señor de los anillos, esa noche se cayó del escenario, demostrando que los dioses también son falibles. McKellen, de 85 años, estaba interpretando a Faltstaff en una puesta de Enrique IV de Shakespeare, en Londres, dirigido por Robert Icke. Se sabe, Falstaff es un caballero tan voluminoso como desaliñado y Señor de las Tabernas. Así que McKellen aparecía de ese modo en escena, con una barba descuidada y una melena cuya desprolijidad Gandalf, que mantenía su estilo elegantísimo aunque se le vinieran encima mil espíritus oscuros, hubiera desaprobado. Pero bueno, el asunto es que McKellen se cayó del escenario y a partir de ahí decidió no continuar la obra. Pero el actor es un grande que mantiene su sentido del humor contra viento y marea y sabe cómo darle una vuelta de tuerca incluso a la tragedia. Primero, apareció en un video bailando con gracia junto a su amigo Anthony Hopkins para demostrar que un tropezón no es caída. Pero además, ahora registró, a través de una serie de fotos maravillosas, el momento donde se corta pone en manos de un experto para que le corte el pelo y la barba. Toma tras toma, Faltsaff desaparece mientras McKellen vuelve a tomar su lugar. Es una auténtica deconstrucción del physique du rôle y en consecuencia, una lección sobre el modo en que los actores y actrices viven en un borde peculiar entre la realidad y la ficción. Ahora, McKellen se ha convertido una vez más en el elegante actor británico que se pasea por Limehouse, la zona donde vive en East London. Claro que en su sonrisa pervive algo de Faltsaff y de cada personaje que viene interpretando desde los años sesenta. Porque podrá perder el pelo pero nunca sus deliciosas mañas.</t>
   </si>
   <si>
     <t>Logo radar</t>
@@ -361,7 +745,25 @@
     <t>https://www.pagina12.com.ar/754999-emergencia-alimentaria-la-peor-violencia-es-el-hambre</t>
   </si>
   <si>
-    <t>2024-07-26T03:01:00Z</t>
+    <t xml:space="preserve">Título: Emergencia alimentaria: "La peor violencia es el hambre"
+Chapeau: Organizaciones campesinas, sociales y gremios protestaron frente a la Exposición Rural
+Subtítulo: Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, mov
+Editoria: El País
+Tags: Protesta, Organizaciones sociales, Unión de Trabajadores de la Tierra, Emergencia Alimentaria, printed-edition, organizaciones-sociales, union-de-trabajadores-de-la-tierra, emergencia-alimentaria, diario
+URL: https://www.pagina12.com.ar/754999-emergencia-alimentaria-la-peor-violencia-es-el-hambre/
+Notícia completa (12 blocos):
+Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, movimientos sociales, sindicatos y organismos de derechos humanos hicieron una actividad de la campaña “La peor violencia es el hambre”. Esta campaña tiene un doble planteo: hacer visible la emergencia alimentaria que atraviesan miles de familias, por el alto precio de los alimentos, y advertir que se trata de una situación que coexiste con el agronegocio como modelo productivo principal para el campo, concentrador de la economía, expulsor de la población rural y contaminador de la tierra.
+“La peor violencia es el hambre” es una iniciativa del premio Nobel de la Paz, Adolfo Pérez Esquivel. “Estamos haciendo un llamamiento a unirnos frente a este panorama en el que el gobierno le ha quitado los alimentos a los comedores y merenderos comunitarios, y en el que además de mantener cautivos los alimentos hace gala de hostigar y perseguir a quienes se organizan”, dijo frente al ingreso a la Rural Leonardo, hijo del titular del Serpaj. La propuesta tiene más de una faceta, ya que además de difundir conceptos en favor de la soberanía alimentaria, busca también dar un respaldo a las organizaciones sociales, hacerles de paraguas en la persecución que vienen sufriendo de parte del gobierno.
+La Unión de Trabajadores de la Tierra armó un un verdurazo en el lugar de la protesta, mientras que los sindicatos de la CTA Autónoma hicieron una radio abierta. A su vez, los movimientos sociales Libres del Sur y Barrios de Pie instalaron gazebos para mostrar las actividades de control nutricional que realizan en las zonas más postergadas.
+De fondo, a pocos metros de estas actividades, la gente que se acercaba para visitar la 136ª Exposición Rural hacía la cola de ingreso. Pasado el mediodía estuvo en la Exposición Rural la ministra de Capital Humano, Sandra Pettovello, acompañada por el vocero presidencial, Manuel Adoni, sin cruzarse con los manifestantes.
+[H2] Cero políticas para la Agricultura Familiar
+Pamela Mackey es una de las despedidas del Instituto Nacional de Promoción de la Agricultura Familiar, Campesina e Indígena. “El cierre del INAPCI dejó 900 personas sin trabajo y desatendidas a 250 mil familias que trabajan la tierra a lo largo y ancho del país y que recibían capacitación técnica y apoyo financiero. No sólo los programas nacionales, sino también proyectos de líneas internacionales quedaron discontinuados. Como nos despidieron de un día para el otro, incluso quedaron rendiciones de fondos sin terminar”.
+En nombre de los despedidos también habló Leonor Cruz, otra de las cesanteadas y secretaria de Género de la CTA Autónoma. “El campo no son estos poderosos que siembran soja para alimentar a los chanchos de Europa. El Instituto tiene tres décadas de historia en las que nuestra gran lucha fue que los productores rurales no abandonaran su lugar, que no fueran expulsados para terminar hacinados y empobrecidos en las villas”.
+El Instituto había sido creado en 1993 y desde entonces tuvo a su cargo programas de fomento de la agricultura familiar durante 31 años, pese a lo que sus trabajadores no llegaron a ser incorporados nunca a planta permanente. Al ser su relación laboral la de contratados, despedirlos resultó fácil: no les renovaron los convenios.
+Durante la presidencia de Mauricio Macri el organismo ya había sufrido despidos masivos, que los trabajadores pudieron revertir. Ahora, organizados en la Asociación de Trabajadores del Estado, mantienen el reclamo de ser reincorporados.
+“Estamos discutiendo el derecho a la alimentación, pero no a cualquiera sino a una sana, segura y soberana”, señaló ante los concurrentes Carlos Carballo, docente de la Cátedra Libre de Soberanía Alimentaria de la Facultad de Agronomía de la UBA. El profesor indicó que no es sostenible un país en el que, como sucede en Argentina, el 90 por ciento de la población es urbana: “muchas de las experiencias que se hicieron en los últimos años para impulsar una nueva ruralidad deberían se transformadas en políticas públicas. Necesitamos que los habitantes empiecen a preguntarse quiénes y cómo producen los alimentos, algo que no viene pasando a pesar de las luchas que venimos dando”.
+Nahuel Levaggi, de la UTT, advirtió que con el gobierno libertario “hubo un vaciamiento de las políticas de apoyo a los productores de alimentos. Han pasado heladas, tornados y no llegó una sola ayuda”.
+Silvia Saravia, de Libres del Sur, habló en nombre de los movimientos sociales. "El modelo que defiende la Sociedad Rural es el de un extractivismo que deja campo arrasado. Nuestras organizaciones discuten, en cambio, la necesidad de ir hacia la soberanía alimentaria. No es un planteo idealizado, sino que tiene como base a experiencias que se vienen haciendo hace muchos años y que el Estado debe impulsar. Debemos preguntarnos por que hay tantos millones de personas viviendo en los conurbanos, en situación de pobreza, ¿ese es el modelo que queremos? Necesitamos construir, desde las raíces, otro modelo de país".</t>
   </si>
   <si>
     <t>Laura Vales</t>
@@ -373,7 +775,17 @@
     <t>https://www.pagina12.com.ar/2024/07/26/h1la-peor-violencia-es-el-hambreh1/</t>
   </si>
   <si>
-    <t>2024-07-26T02:32:16Z</t>
+    <t xml:space="preserve">Título: &lt;h1&gt;"La peor violencia es el hambre"&lt;/h1&gt;
+Chapeau: &lt;h1&gt;"La peor violencia es el hambre"&lt;/h1&gt;
+Editoria: El País
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/2024/07/26/h1la-peor-violencia-es-el-hambreh1/
+Notícia completa (5 blocos):
+Por Laura Vales
+Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, movimientos sociales, sindicatos y organismos de derechos humanos hicieron una actividad de la campaña “La peor violencia es el hambre”. Esta campaña tiene un doble planteo: hacer visible la emergencia alimentaria que atraviesan miles de familias, por el alto precio de los alimentos, y advertir que se trata de una situación que coexiste con el agronegocio como modelo productivo principal para el campo, concentrador de la economía, expulsor de la población rural y contaminador de la tierra.
+“La peor violencia es el hambre” es una iniciativa del premio Nobel de la Paz, Adolfo Pérez Esquivel. “Estamos haciendo un llamamiento a unirnos frente a este panorama en el que el gobierno le ha quitado los alimentos a los comedores y merenderos comunitarios, y en el que además de mantener cautivos los alimentos hace gala de hostigar y perseguir a quienes se organizan”, dijo frente al ingreso a la Rural Leonardo, hijo del titular del Serpaj. La propuesta tiene más de una faceta, ya que además de difundir conceptos en favor de la soberanía alimentaria, busca también dar un respaldo a las organizaciones sociales, hacerles de paraguas en la persecución que vienen sufriendo de parte del gobierno.
+Leer más acá
+(c) 2025 Página 12</t>
   </si>
   <si>
     <t>¿Esto no tiene límites?</t>
@@ -382,7 +794,15 @@
     <t>https://www.pagina12.com.ar/754257-esto-no-tiene-limites</t>
   </si>
   <si>
-    <t>2024-07-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: ¿Esto no tiene límites?
+Subtítulo: El multicondenado Jorge Eduardo Acosta (¿se preguntará por qué no lo invitaron a la reunión con los excursionistas de La Libertad Avanza que fueron a Ezeiza?) gatillaba como afirmació
+Editoria: El País
+Tags: Javier Milei, Alfredo Astiz, Victoria Villarruel, Opinión, printed-edition, javier-milei, alfredo-astiz, victoria-villarruel, opinion, diario
+URL: https://www.pagina12.com.ar/754257-esto-no-tiene-limites/
+Notícia completa (3 blocos):
+El multicondenado Jorge Eduardo Acosta (¿se preguntará por qué no lo invitaron a la reunión con los excursionistas de La Libertad Avanza que fueron a Ezeiza?) gatillaba como afirmación, no como interrogante, “esto no tiene límites”. “Esto” era lo que el Grupo de Tareas 3.3 perpetraba minuto a minuto en la ESMA. Lo que la dictadura militar genocida perpetró minuto a minuto en nuestro país.
+Al hilvanar acontecimientos, hechos, declaraciones de funcionarios estatales, figuras políticas, empresas de comunicación y activistas del pulgar sobre pantallas, referidos a los crímenes dictatoriales –y no solo-, volvió aquel lema del jefe de Inteligencia de la ESMA. Volvió como ¿interrogante o afirmación? ahora que los gobernantes, con cada decreto, cada ley aprobada a fuerza de extorsión, claudicaciones y traiciones de supuestos opositores, en cada arenga, reiteran que están dedicados a acabar con parte de la población vía despidos, persecución y hambre, a demoler el Estado, los derechos individuales y colectivos, la soberanía, a sacrificar lo humano en el altar del “mercado” y el “déficit cero”…
+El batallar a favor de la impunidad de los genocidas no lo inauguraron los seis diputados de LLA con su visita a Ezeiza. Son años de prédica de los editoriales de La Nación; de los Reato y afines recitando la doctrina de los excesos, y/o la de los dos demonios en programas de TV; de los defensores de los dictadores para impugnar los juicios, hostigando a testigos y sobrevivientes en las audiencias y desde el anonimato de “las redes”. Julio López desaparecido en septiembre de 2006 es la prueba más extrema… Insuficiente enumeración de un trayecto con tácticas diversas, caras visibles que se renuevan, y un propósito compartido: que la impunidad de los dictadores –militares y sus socios civiles- sirva como antecedente y sostén para las represiones de hoy que el “protocolo Bullrich” habilita.</t>
   </si>
   <si>
     <t>Graciela Daleo</t>
@@ -397,7 +817,30 @@
     <t>https://www.pagina12.com.ar/751738-la-ley-bases-contra-los-humedales</t>
   </si>
   <si>
-    <t>2024-07-13T03:01:00Z</t>
+    <t xml:space="preserve">Título: La ley Bases contra los humedales
+Chapeau: En la provincia de Santa Fe hay alarma por un punto del Pacto de Mayo y el negacionismo ambiental
+Subtítulo: “Sospechamos que para ampliar las fronteras agropecuarias, irán por los humedales y bosques", declararon los ecologistas.
+Editoria: Sociedad
+Tags: Rosario, Ley de Humedales, printed-edition, ley-de-humedales, diario
+URL: https://www.pagina12.com.ar/751738-la-ley-bases-contra-los-humedales/
+Notícia completa (17 blocos):
+Desde Rosario
+El punto número siete del Pacto de Mayo, que garantiza el compromiso de las provincias argentinas para avanzar en la explotación de los recursos naturales del país, mantiene en alerta a las organizaciones ambientales de la ciudad de Rosario y la región.
+Desde la Multisectorial Humedales emitieron un comunicado donde cuestionan la posición del gobernador, Maximiliano Pullaro, por acompañar con su firma una política “que permitirá vender humedales y bosques” del territorio provincial. “Lamentablemente, el cuarto intento de poder sancionar una Ley de Humedales ha quedado trunco otra vez y no tenemos una herramienta legislativa que nos pueda proteger en ese sentido”, señaló Ivo Perugino, referente de la multisectorial, en diálogo con Página/12. “Creo que se vienen retrocesos, pero va a depender de la capacidad de articulación que tenga la sociedad, que hoy no está muy receptiva a la problemática ambiental”, agregó el ambientalista César Massi a este medio.
+[H2] El papel del gobernador Pullaro
+El 9 de julio, el presidente Javier Milei convocó a todos los gobernadores a la firma del Pacto de Mayo en Tucumán. El cónclave tenía como fin que los mandatarios provinciales adhieran a diez consignas “refundacionales” que puedan sostenerse en el tiempo, independientemente de las gestiones. No todos los gobernadores asistieron. En el caso de Pullaro, desde el primer momento supeditó su participación a la incorporación de dos temas que considera clave: la educación y la producción del interior del país. Como el primero de los puntos fue contemplado, finalmente el mandatario asistió al evento. Pero el séptimo punto es el que despierta la preocupación de las organizaciones ambientalistas de la ciudad: “El compromiso de las provincias argentinas de avanzar en la explotación de los recursos naturales del país”.
+En ese marco, este viernes la Multisectorial Humedales de Rosario emitió un comunicado donde sostienen que ese apartado “corre de un soplo” cualquier discusión que pueda darse respecto a la protección del territorio para adaptarse a un contexto de cambio climático. “Desconocemos qué recursos naturales están en la mira en la Provincia de Santa Fe, pero sospechamos que, a fin de ampliar las fronteras agropecuarias, irán por los humedales y los bosques, los cuales cumplen importantes funciones ecosistémicas y albergan biodiversidad. Habrá más quemas, más contaminación, más destrucción”, describen.
+[H2] El negacionismo climático
+Desde ese espacio sostienen que el gobierno es “negacionista del cambio climático” y quiere volver a imponer mitos que ya fueron derribados por la comunidad científica. “El punto siete del Pacto de Mayo, junto al DNU (70/2023), el RIGI de la Ley Bases y el proyecto del gobernador de Entre Ríos, Rogelio Frigerio, para la creación de una agencia que administre y enajene bienes del estado, incluido el amplio sistema de humedal del Delta del Paraná, es el peor escenario posible para afrontar el presente y el futuro a corto plazo”, añadieron.
+Ivo Peruggino consideró que las medidas que viene impulsando el gobierno “son un peligro socioambiental” para toda la región. “Se van a habilitar muchísimas más actividades productivas que son incompatibles con la idea de conservación a la cual tenemos que ir de forma urgente porque el contexto nos obliga. A la par de eso, vemos que se viene dando una suerte de persecución y desprestigio contra todas las asambleas territoriales y de los activistas socioambientales”, expresó y agregó: “Lo que más nos preocupa es que ese saqueo se profundice en nuestra región y en nuestro país”.
+El activista recordó que la provincia de Santa Fe tiene una extensión de bosques y humedales muy valiosa en la zona del delta del Paraná y en los bajos submeridionales. Uno de los temores de la organización es que, habilitados por un clima de época, quienes generaban los incendios intencionales en la zona de islas entre 2020 y 2022, vuelvan a la carga con su objetivo y las localidades de la región vuelvan a sufrir el humo y la problemática ambiental que genera.
+[H2] Mucho que perder
+“Tanto este año como el que viene, se prevé otra bajante del río Paraná y eso hace que queden superficies de humedal descubiertas y que se quieran usar para tierras productivas. Lamentablemente, el cuarto intento de poder sancionar una ley de humedales ha quedado trunco otra vez y no tenemos esa herramienta legislativa que nos pueda proteger. Y tenemos mucho miedo de que vuelva a darse ese intento por correr la frontera del agronegocio, que busca llevar cada vez más vacas a las islas para sembrar más soja en el continente”, analizó. “En Santa Fe, como en el resto del país, hay mucho para perder si estas cosas avanzan. Y lamentablemente avanzan de la mano de un discurso negacionista”, añadió.
+Peruggino se refirió a la intención del gobierno de Entre Ríos de avanzar en la venta de terrenos pertenecientes al humedal, que podrían afectar una zona que impacta también en la provincia de Santa Fe: “El gobernador de Entre Ríos presentó un proyecto para hacer una agencia del Estado, en el cual les incluyen casi 200 mil hectáreas de humedal del delta del Paraná. Que eso quede en manos de privados sería malísimo para los ecosistemas, pero también para los habitantes de la región”.
+[H2] Antiecologismo expreso
+Según Massi, ya era preocupante cuando el año pasado la situación ambiental “quedaba relegada” en función de lo político electo-electoral primero y de lo económico después. En el contexto actual, la preocupación escala un nuevo peldaño: “Ahora hay una decisión de cargarse todo lo que tenga que ver con protección ambiental y tenerlo como bandera política. Se plantea una suerte de enemistad con el ambientalismo y se habilita pasar por arriba todo lo que se pueda destruir para traer dólares”.
+En declaraciones a Página/12, el activista ambiental evaluó que además de un nivel de agresividad “muy fuerte”, directamente se baja una línea de confrontación discursiva contra el ambientalismo, que consideró peligrosa: “Todo eso se da en un contexto donde más que nunca tenemos que discutir la cuestión ambiental, porque los hechos lo marcan. Venimos de dos años donde la cosecha falló, primero por la sequía y después por la chicharrita. El país viene perdiendo un montón de guita por tener vulnerabilidad climática, porque la mayoría de nuestras divisas entran por el campo. Entonces es necesario discutir cómo cuidamos eso”.
+Massi remarcó que en Santa Fe puede llegar a darse una pelea “con un poco más de igualdad” en relación a provincias y localidades más chicas, donde las comunidades quedan indefensas ante el poder económico y político. “Ya vimos los problemas que tuvimos para defender los humedales, cuando hubo que sentar en una misma mesa a cuatro gobernadores y todo se complicaba. Creo que se vienen retrocesos, pero va a depender de la capacidad de articulación que tenga la sociedad, que no está muy receptiva a la problemática ambiental”, manifestó.</t>
   </si>
   <si>
     <t>Ignacio Cagliero</t>
@@ -412,7 +855,25 @@
     <t>https://www.pagina12.com.ar/750898-cambiar-la-salud-de-nuestro-suelo</t>
   </si>
   <si>
-    <t>2024-07-10T03:01:00Z</t>
+    <t xml:space="preserve">Título: Cambiar la salud de nuestro suelo
+Chapeau: Marcela y sus hermanos apuestan por la agroecología
+Subtítulo: En Baigorrita, entre Junín y General Viamonte, la organización Cambio Rural practica nuevos cuidados sobre nuestra tierra para comer y vivir mejor.
+Editoria: Buenos Aires|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/750898-cambiar-la-salud-de-nuestro-suelo/
+Notícia completa (12 blocos):
+“Tres veces al día necesitamos un agricultor y uno no toma conciencia de quién es tu agricultor, quién está produciendo tu alimento o quién está cultivando el alimento que tenés en el plato. Si el campesino, el agricultor desaparece, ¿en manos de quién queda nuestra alimentación? ¿Quién decide aquello que comemos? Hay mucha desinformación sobre los alimentos sanos, sobre qué es lo orgánico, qué es la agroecología y el impacto que tienen en la salud", afirma Marcela Calderon, agricultora agroecológica y parte de la organización Cambio Rural.
+Hace doce años, en Baigorrita, entre los campos fértiles entre Junín y General Viamonte, en la provincia de Buenos Aires, Marcela y sus hermanos emprendieron un camino transformador hacia la agroecología. Después de más de una década dedicados al agronegocio convencional y gestionando 2.500 hectáreas con tecnología avanzada, decidieron cambiar radicalmente su enfoque hacia prácticas más sostenibles y respetuosas con el medio ambiente.
+"Veníamos de un modelo donde todo giraba en torno al aumento de hectáreas y el uso intensivo de maquinaria y químicos", explica Marcela. "Pero nos dimos cuenta de que este modelo no solo afectaba nuestra calidad de vida, sino también la salud del suelo y la biodiversidad que lo habita".
+La decisión de cambiar surgió a partir de un accidente que tuvo su hermano con un tractor. “Nosotros hacía treinta años que estábamos haciendo siembra directa y no era sustentable. El suelo estaba cada vez peor, sin estructura, sin vida. Necesitábamos cada vez más insumos para lograr que rinda lo mismo. Nos dábamos cuenta de que estábamos perdiendo calidad de vida. Mi hermano se iba a las seis de la mañana y volvía a las doce de la noche. La dedicación cada vez era mayor, el modelo de la agricultura agroindustrial o convencional nos esclavizaba cada vez más. Y empezamos a tomar conciencia del efecto de los agroquímicos sobre la tierra", afirma Marcelo.
+Se pusieron a investigar de forma autodidacta metodologías agrícolas alternativas. Desde la permacultura hasta la agricultura orgánica y biodinámica, exploraron métodos que promueven la producción de alimentos, la regeneración del suelo y la biodiversidad.
+Marcela relata que en lo orgánico a veces no busca desarrollar una conciencia plena sobre la producción y el cultivo, mientras que en la agroecología, hay una preocupación por la salud humana. Si en el agronegocio se tiene en cuenta lo físico y lo químico, en la agroecología se toma en cuenta lo biológico. “En el agro tradicional se agregan tres fertilizantes: nitrógeno, fósforo y potasio. Como si las plantas se alimentaran solo de esos tres ingredientes. Si yo a una persona, le doy leche, huevo y carne, no va a estar bien nutrida porque no se nutre nada más que de esos tres alimentos. Hay muchísimos más. Hoy a los alimentos les está pasando eso. Hay una deficiencia en las vitaminas y los minerales que cada alimento tiene porque el suelo está degradado, el suelo ya no está equilibrado. Las plantas extraen, extraen, extraen. Y si uno no recompone o no reequilibra, no regenera la vida del suelo. Por ende, los alimentos van a estar deficientes a nivel nutricional”, afirma.
+La transición implicó la eliminación total de químicos de síntesis en sus 81 hectáreas cultivadas. Adoptaron prácticas como la siembra directa y el cultivo asociado, reduciendo así el impacto ambiental y aumentando la eficiencia del uso del suelo. Además, incorporaron ganadería ovina con pastoreo racional, adaptado a sus sistemas agrícolas. Tienen como valores fundamentales el respeto hacia la naturaleza, sus ciclos y leyes, con el fin de obtener productos genuinamente saludables y naturales desde su origen. Este enfoque no solo promueve la soberanía alimentaria y el arraigo, sino que también fomenta una relación más armoniosa con el entorno. El proyecto no se limita a la producción agrícola. "Con la marca "El Huerto Interior", vendemos harina integral agroecológica y corderos pastoriles.", afirma Marcela.
+“Un suelo sano, equilibrado, funciona igual que el sistema inmunológico de una planta, de un animal y del individuo. Si nosotros tenemos el sistema inmunológico sano, si el sistema inmunológico de la Tierra está sano, está completo, está íntegro, las plantas van a estar sanas, los alimentos y los animales van a estar sanos. Es una cadena. La salud está en la comida. La salud de la comida está en el suelo. Y si el suelo no es saludable, no tenemos salud. No hay salud”, afirma. Además, optar por alimentos agroecológicos de temporada y locales es una manera de respaldar el comercio justo y responsable, concluye Marcela.
+[H3] Grupo Cambio Rural
+Hoy en día forman parte del Grupo Cambio Rural, donde comparten su experiencia y conocimientos para inspirar a otros agricultores a seguir su camino hacia prácticas más amigables con el medio ambiente. “Solemos hacer una reunión para invitar a posibles agricultores que les llegue a interesar o que estén interesados para que lo puedan vivenciar. Uno puede ver el cambio del suelo, cómo se va regenerando, cómo se va descompactando, cómo se va vivificando. Desde la pandemia se incrementó el interés de otros productores. Los primeros años para nosotros fueron difíciles, estábamos solos en esta zona y bueno, éramos medio los hippies raros”, recuerda.
+“Ya somos varios los que estamos cultivando de esta manera, que en realidad es como se hacia antes, en la época de mis abuelos, no es magia. Lo que pasa es que estamos cooptados por el otro modelo, donde está todo resuelto y cuesta cambiar un modelo productivo. Es un gran desafío. El tema es tener claro si estás a favor de la vida o a favor de la muerte. Si vos estás a favor de la vida, todo va a estar acorde a eso y la naturaleza te va a compensar. No hay una recompensa económica, hay una recompensa en calidad de vida, en buen vivir. En este modelo no pasa por lo económico, sino pasa por la salud tuya y de los otros", afirma.
+Con el grupo, priman los principios de asociación y cooperación, entre ellos realizan visitas mensuales rotativas, para promover una mirada colectiva sobre los problemas que puedan presentarse. Hoy en día, son doce productores. Se organizan para hacer compras comunitarias, comparten sus experiencias y colaboran con los CEPT de la zona. "Estamos comprometidos no solo con la producción de alimentos, sino también con educar y crear conciencia sobre la importancia de una agricultura consciente y sostenible", concluye Marcela, convencida de que la labor que realizan genera cambios tangibles.</t>
   </si>
   <si>
     <t>Malena Saito</t>
@@ -427,7 +888,25 @@
     <t>https://www.pagina12.com.ar/750289-fugadores-y-recuerdos-del-futuro</t>
   </si>
   <si>
-    <t>2024-07-08T03:40:09Z</t>
+    <t xml:space="preserve">Título: Fugadores y recuerdos del futuro
+Chapeau: Vicentin, cuatro años después de una resolución del fiscal Gerardo Pollicita
+Subtítulo: Este lunes 8 de julio de 2024 se cumplirán cuatro años de una resolución judicial que determinaba la fuga de millones de dólares de parte de un grupo de directivos del consorcio Vicentin en complic
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/750289-fugadores-y-recuerdos-del-futuro/
+Notícia completa (12 blocos):
+Este lunes 8 de julio de 2024 se cumplirán cuatro años de una resolución judicial que determinaba la fuga de millones de dólares de parte de un grupo de directivos del consorcio Vicentin en complicidad con funcionarios nacionales ubicados en el Banco Central de la República Argentina, en el Banco Nación y en el gobierno nacional del ingeniero Mauricio Macri. Un robo descarado al pueblo argentino que hasta el día de hoy permanece impune y que remarca la triste costumbre de hacerle pagar a las mayorías las fiestas privadas de los delincuentes de guantes y cuellos blancos.
+El 8 de julio de 2020, el fiscal federal en lo Criminal y Correccional Federal número 11, Gerardo Pollicita hizo público un documento que muestra la facilidad con la que algunos directivos de la empresa Vicentin accedían a los créditos del Banco Nación. Dice el texto en su página 24: “El 26 de noviembre de 2019, los funcionarios del Banco de la Nación Argentina -Bled, Tortul, Testa, Moschini y González- en menos de una hora -entre las 10.38 y las 11.17- y a pedido de los empresarios Herman Vicentin y Máximo J. Padoán, le concedieron a la firma Vicentin un nuevo crédito por la suma de USD 6.000.000”.
+Herman Vicentin nació el 21 de septiembre de 1937 y en 2018 recibió el premio “Konex” como referente del empresario dedicado al agronegocio. Máximo Padoán, uno de los hijos del “Beto” Padoán, tuvo la organización de su segundo casamiento en manos de la conocida “weeding planner” Bárbara Diez, esposa de Horacio Rodríguez Larreta. Herman Vicentin y Máximo Padoán, aquel 26 de noviembre de 2019, en solamente 39 minutos se llevaron seis millones de dólares del Banco Nación, del pueblo argentino.
+39 minutos les llevó a los directivos de Vicentin quedarse con 6 millones de dólares del pueblo argentino.
+No todos somos Vicentin. El contraste con el tiempo que deben esperar miles y miles de familias en Argentina explica la impunidad del privilegio en un país de robusta desigualdad.
+En realidad, durante noviembre de 2019, la empresa tuvo 28 créditos por más de 105 millones de dólares. Una obscenidad.
+Dice el escrito del fiscal federal: Lo expuesto demuestra que durante el mismo período en el que la firma Vicentin tenía deudas vencidas con el Banco de la Nación Argentina, el dinero para cobrar dichas deudas se encontraba a resguardo del banco en dos cuentas específicamente creadas ante un eventual incumplimiento, sin embargo los funcionarios del Banco de la Nación Argentina a pedido de los empresarios, decidieron liberar 43.449.104.966 pesos – 41.592.204.966 pesos de la cuenta de cobranzas en el exterior y 1.856.900.000 pesos de la local – movilizándolo, hasta el día 3 de diciembre inclusiva, hasta una cuenta corriente de la firma Vicentin que no poseía ninguna limitación, lo que le permitió a estos últimos disponer de los miles de millones de pesos que garantizaban los préstamos, burlando de tal forma, toda posibilidad de cobro por parte de la entidad bancaria (...) una vez que los fondos se encontraban en la cuenta corriente de la firma en la misma entidad, los titulares de la firma Vicentíi usaron parte del dinero para pagar gastos de la firma -tales como proveedores, impuestos, salarios- pero otra parte significativa de los fondos eran transferidos mes a mes a 'cuentas propias' que la firma mantenía en otros bancos, por lo que el destino final de estos últimos resulta de momento desconocido”.
+El dinero del pueblo argentino iba a parar a una cuenta que tenía Vicentin sin “ninguna limitación” y desde allí, los señores empresarios hicieron 1.418 transferencias a cuentas propias entre agosto de 2019 y enero de 2020. Dinero del banco público para cuentas propias. Un robo descarado al pueblo.
+En la página 50 Pollicita informa: “De los casi de 800 millones de dólares y más de 2.000 millones de pesos que el Banco de la Nación Argentina a lo largo del período agosto a diciembre de 2019 tuvo en las cuentas en garantía de las deudas de Vicentin, al momento en que se efectuó la afectación de los fondos sólo se hallaron en las cuentas apenas poco menos de 8 millones de dólares, lo que demuestra la magnitud del daño ocasionado al patrimonio del Banco de la Nación Argentina”.
+Parecen los escritos de la década del treinta del siglo pasado, cuando los bienes del pueblo eran ultrajados desde el interior del Estado. Son, sin embargo, hechos del pasado reciente que tienen alto impacto en miles de familias en el presente.
+Detrás de estos números y afirmaciones, la cuestión pendiente es resolver si siempre las mafias le ganarán a la democracia. Una respuesta que, otra vez, dependerá del protagonismo de los que son más en estos atribulados arrabales del mundo.
+Diputado Provincial de Santa Fe por el Frente Amplio por la Soberanía.</t>
   </si>
   <si>
     <t>Logo rosario12</t>
@@ -445,7 +924,29 @@
     <t>https://www.pagina12.com.ar/749168-la-economia-popular-en-la-agenda-de-la-cidh</t>
   </si>
   <si>
-    <t>2024-07-03T03:01:00Z</t>
+    <t xml:space="preserve">Título: La economía popular, en la agenda de la CIDH
+Chapeau: Entrevista a Javier Palummo, relator especial de la Comisión Interamericana de Derechos Humanos
+Subtítulo: Javier Palummo es relator especial sobre Derechos Económicos, Sociales, Culturales y Ambientales de la CIDH. De paso por Buenos Aires participó de una serie de charlas con trabajadores de la economía popular. Su relatoría busca poner en agenda los derechos de estos trabajadores, que en la región son el 50 por ciento de la fuerza laboral.
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/749168-la-economia-popular-en-la-agenda-de-la-cidh/
+Notícia completa (16 blocos):
+Javier Palummo, relator especial de la Comisión Interamericana de Derechos Humanos (CIDH), estuvo en Buenos Aires, donde participó de una serie de debates sobre los derechos de los trabajadores de la economía popular. La CIDH ha decidido darle prioridad a este tema en su agenda por una razón de peso: hoy, en la región, más del 50 por ciento de los trabajadores se ganan la vida en la economía informal. El relator, en esta gira que incluyó también a Paraguay y Uruguay, compartió aquí paneles con cartoneros y vendedores ambulantes y habló de la necesidad de que los estados avancen en el reconocimiento de los trabajos de la economía informal.
+--En Argentina conocemos a la CIDH por su trabajo en derechos humanos; ¿qué interés tiene la Comisión en cuestiones que son de carácter más económico o de reconocimiento de derechos sociales?
+--La Comisión tiene dos relatorías especiales, una sobre libertad de expresión, que es conocida, y otra más reciente, una Relatoría Especial sobre Derechos Económicos, Sociales, Culturales y Ambientales. Esta Relatoría está a mi cargo desde septiembre del año pasado y hemos elaborado un plan de trabajo, que tuvo la aprobación unánime de la CIDH; el tema de los derechos de los trabajadores de la economía informal está incluido en ese plan de trabajo.
+--¿Por qué decidieron ponerlo en agenda?
+--Hay varias razones. Primero, porque estamos en una región donde según los datos de la OIT, en promedio el 50 por ciento de la fuerza laboral se encuentra en la economía informal. Ese es el promedio general, con países en los que el 70 u 80 por ciento de la economía es informal. Esto implica dos problemas: uno es que estos trabajadores suelen no contar con derechos laborales, no tienen protección social, seguridad social, etc… y estamos hablando de millones de personas, que se han incrementado luego de la pandemia de COVID-19; por otro lado, es una población que se desempeña sin condiciones de dignidad. Y no se trata de algo marginal, sino de porcentajes muy importantes en la economía de nuestros países. Otro tema especialmente relevante a considerar es que hay una correlación entre la imposibilidad de los Estados de tener servicios públicos de calidad, como buenos hospitales públicos o un buen sistema de educación pública, y la existencia de este alto porcentaje de la economía que se mueve en el ámbito de la informalidad.
+--¿Por qué?
+--Porque esas economías informales no tributan, no cotizan, no permiten mejorar la capacidad recaudadora de los estados. En un país donde el 80 por ciento de la actividad económica se desarrolla en el ámbito de la informalidad, los recursos para sostener sistemas educativos, de salud o políticas culturales se encuentran claramente mermados. De ahí viene la importancia de poner este tema en la agenda y tratar de generar avances, desde una perspectiva que no sólo tenga en cuenta las estrategias de desarrollo de los países, sino también la garantía de los derechos humanos de las personas trabajadoras.
+--¿Qué panorama encontró en Argentina?
+--Quiero aclarar que no estoy en el marco de una visita de trabajo de la CIDH, sino en una visita académica, en la cual he participado sólo en actividades de carácter público donde se han tratado estos temas. Compartí paneles con trabajadores de la economía informal y así tuve la oportunidad de escuchar sus posiciones y preocupaciones. Hecha esa aclaración, puedo decir que las preocupaciones son similares a las que se manifiestan en otros países de la región, pero con un ingrediente especial, que es que en la Argentina los trabajadores de la economía informal tienen sus organizaciones, lo que no se ve en otros lados. Por eso, en algún sentido, aquí hay una discusión más avanzada, sobre todo teniendo en cuenta las conquistas de derechos que han ocurrido aquí.
+--Cuando habla de la necesidad de poner en agenda los derechos sociales de los trabajadores de la economía informal, ¿a qué derechos se refiere?
+--El principal problema que tienen los trabajadores de la economía informal es que no son reconocidos como trabajadores. Eso implica que en muchos casos no se les reconoce el derecho a asociarse, a reunirse y generar colectivos para la defensa de sus intereses, un tema muy básico. El primer paso es es ese, reconocer que se trata de personas que están trabajando y que por lo tanto tienen que tener determinado nivel de cobertura. La otra gran dificultad es que la vulneración de los derechos de los trabajadores de la economía informal afecta a grupos que han sido históricamente discriminados: las mujeres, los migrantes, las personas afrodescendientes también, esto es clarísimo en prácticamente toda la región. Algunas actividades no necesariamente están vinculadas a la economía informal, pero sí a la economía del cuidado, como por ejemplo el trabajo doméstico, lo que se llama de casas particulares. Lo mismo ocurre con los trabajadores de plataformas digitales, donde las personas migrantes encuentran la forma más rápida de obtener ingresos en ciudades que no conocen, en las que no tienen redes sociales, donde pueden inclusive no cumplir los requisitos documentales necesarios para una inserción laboral formal.
+--Los Estados, ¿cómo pueden reconocer derechos a estas formas de trabajo en las que no existe un empleador y que son formas de subsistencia?
+--Creo que los Estados, en primera instancia, deben lograr que haya más formalización, reducir la informalidad. Eso es lo primero porque es lo que va a posibilitar avanzar en otros sentidos. Si estuviéramos hablando de un porcentaje muy bajo de la población, uno podría pensar en otro tipo de alternativa, pero cuando hablamos de que en toda la región el 50 por ciento de la fuerza de trabajo se desempeña en la economía informal, necesariamente tenemos que pensar de que existen intereses detrás de que haya mucha informalidad. Eso, como cuestión fundamental. Ningún país es sostenible, desde el punto de vista de su capacidad recaudatoria para brindar derechos económicos, sociales, culturales y servicios públicos de calidad, mientras tenga porcentajes tan altos de su economía en el ámbito informal.
+--¿Es un problema que se resuelve con mayores controles o la salida es de otro tipo?
+--Yo creo en un enfoque de protección social: que haya una mirada centrada en la dignidad de las personas desde la perspectiva de la inclusión, que le permita al Estado obtener nuevos recursos para garantizar mejores servicios. Estamos hablando de ese tipo de enfoque, con la mirada no centrada en formas de control sino en lógicas de reconocimiento.
+El plan de trabajo de la Relatoría tiene cuatro prioridades o ejes: el primero es Cambio Climático y Protección del Medio Ambiente (su impacto en relación al derecho a la salud, al trabajo, al derecho al agua, a la seguridad alimentaria). El segundo eje es Empresas y Derechos Humanos, que aborda actividades empresariales como las industrias extractivas, el agronegocio, las industrias tecnológicas y la alimentaria. El tercer eje es Políticas Fiscales, con la mira puesta en la necesidad de contar con sistemas más redistributivos, y el cuarto eje es Democracia y derechos, con el planteo de que para que existan democracias fortalecidas se necesita de políticas públicas que garanticen los derechos económicos, sociales, culturales y ambientales.</t>
   </si>
   <si>
     <t>Seguridad alimentaria o festín empresario</t>
@@ -457,7 +958,33 @@
     <t>https://www.pagina12.com.ar/747658-seguridad-alimentaria-o-festin-empresario</t>
   </si>
   <si>
-    <t>2024-06-30T03:01:00Z</t>
+    <t xml:space="preserve">Título: Seguridad alimentaria o festín empresario
+Chapeau: Brutal transferencia de ingresos en favor de las alimenticias
+Subtítulo: Mientras crece la indigencia, se registraron ganancias siderales por parte de un puñado de empresas oligopólicas de alimentos.
+Editoria: Cash
+Tags: devaluación, printed-edition, devaluacion
+URL: https://www.pagina12.com.ar/747658-seguridad-alimentaria-o-festin-empresario/
+Notícia completa (20 blocos):
+La Argentina, y en general el mundo, vive en tiempos de una frazada cada vez más corta. Las decisiones de los gobiernos no pueden satisfacer a todos los sectores. Pero los datos estadísticos nacionales hablan de una decisión clara en favor de un sector.
+Mientras que el informe del Observatorio Social de la UCA estima que en el primer trimestre de este año la indigencia llegó al 17,5 por ciento (era de 9,6 por ciento en el tercer trimestre de 2023), el último informe de la Comisión de Valores arroja que en este mismo período las ganancias de las megaempresas alimentarias se sextuplicaron.
+Según el informe Ganadores y Perdedores en los primeros meses del gobierno de Milei elaborado por Instituto de Pensamiento y Políticas Públicas (IPyPP), si se suman las tres empresas alimentarias que cotizan en bolsa (Arcor, Mastellone y Río de la Plata), las ganancias acumulan 75.632 millones de pesos en términos operativos (solo la actividad principal), con un incremento de 598 por ciento.
+Si se incorpora la ganancia financiera, participación en sociedades y el pago del impuesto a las ganancias, entre otros conceptos, el resultado neto es de 201.336 millones de pesos, con un crecimiento de 1.331 por ciento. El informe no incluye a otras grandes empresas alimentarias que no cotizan en bolsa, como Molino Cañuelas, Quilmes, Molfino, Mondelez o Nestlé.
+El incremento de las ganancias de las megaempresas alimentarias es mucho mayor que el registrado por las empresas del rubro bancario (945 por ciento) o hidrocarburífero (790 por ciento) y que el promedio de las 15 empresas analizadas (831 por ciento).
+Todas están por encima de la inflación, que en ese mismo período fue del 273 por ciento. Ni que hablar respecto del salario privado, que cayó 12,1 por ciento en términos reales o que el público, que cayó 26,9 por ciento. Al mismo tiempo, el Salario Social Complementario (Potenciar Trabajo) se redujo un 40,9 por ciento.
+[H2] Sálvese quien pueda
+“La Argentina que viene es una Argentina muy desigual, de exclusión, violencia, del sálvese quien pueda. Desde el sector cooperativo bregamos para que haya una enorme reflexión sobre la enorme crisis social que esto genera. Nosotros somos la economía que incluye y hoy vemos un panorama negro. La libertad, si no tiene inclusión ni equidad, no es libertad, decía Alberdi”, opina Ricardo Garzia, secretario de la Federación de Cooperativas Federadas (Fecofe), que integra la Mesa Agroalimentaria Argentina.
+“Los precios de insumos para la producción (semillas, plantines, gasoil o nylons) se han disparado por la devaluación y por la especulación de las tres o cuatro empresas que manejan el 100 por ciento de estos materiales. Esto va acompañado de problemas climáticos, como inundaciones, con el agravante de que las familias no tienen la posibilidad de reinvertir en la producción y se están retirando del campo o están endeudadas a tasas altísimas. El reflejo de esto es la disparada de los precios de la verdura”, describe Zulma Molloja de la UTT.
+¿Por qué unos ganan tanto y otros tan poco? ¿Es el libre mercado? El estudio del IPyPP es claro al respecto: “Los exorbitantes excedentes económicos que cosecharon las compañías alimenticias durante el primer trimestre fueron fruto del desmantelamiento de los mecanismos regulatorios vigentes hasta el año pasado, permitiendo a los grandes operadores del mercado captar amplios márgenes de rentabilidad por vía de la fijación oligopólica de precios en los alimentos que conforman la canasta básica familiar”.
+[H2] Herencia monopólica
+Para muestra hace falta un botón. La empresa Molinos Río de la Plata tiene el 79,4 por ciento de la oferta de fideos secos en grandes supermercados, el 82,1 por ciento en harinas (junto a Molinos Cañuelas) y está entre las tres empresas que concentran el 90,5 por ciento de las ventas de aceite (junto a Aceitera General Deheza y Molinos Cañuelas).
+Entre las analizadas por IPyPP, fue la empresa que experimentó el mayor aumento en las ganancias operativas en el primer trimestre de 2024. Además, su rama de agronegocio Molinos Agro tuvo un resultado operativo de 1918 millones de pesos con un 189 por ciento de incremento.
+El índice de Precios en Origen y Destino (IPOD), elaborado por el sector de Economías Regionales de Cámara Argentina de Mediana Empresa (CAME), muestra que luego de la devaluación de diciembre de 2023, los agroalimentos multiplicaron su precios por 3,5 veces del campo a la góndola. La participación del productor explicó el 26,3 por ciento de los precios de venta final.
+No es casualidad que Molinos Río de La Plata halla multiplicado sideralmente sus ganancias mientras que los productores deben cerrar sus emprendimientos. Tampoco sorprende que el recientemente fallecido Goyo Perez Companc tuviera la cuarta fortuna familiar más grande de la Argentina, valuada en 4.200 millones de dólares, según la revista Forbes.
+Si la ley Bases finalmente sale refrendada en Diputados, la familia Pérez Companc pagará menos impuestos por bienes personales y podrá repatriar sin demasiados costes el dinero en cuentas del exterior producto de la evasión o elusión fiscal.
+[H2] Desalojo
+“Es una bomba de tiempo. Esto hace que las familias productoras dejen los campos y se vayan a engrosar los bolsones de pobreza de los asentamientos. Lo que queda es un campo cada vez más concentrado y más especulativo, solo para exportación. Es un problema cíclico que se repite en gobiernos como éste, donde las políticas están claramente orientadas a que esto suceda”, explica Agustín Suárez, también de UTT.
+Según el último informe de la UCA, en las ciudades donde el “mercado” desplaza a los pequeños productores de alimentos, la inseguridad alimentaria alcanza al 20,8 por ciento de los hogares y al 32,2 por ciento de los niños, niñas y adolescentes.
+*Licenciado en Economía de la Universidad Torcuato Di Tella y master en Periodismo de la Universidad del País Vasco.</t>
   </si>
   <si>
     <t>Los dólares que nunca llegaron</t>
@@ -469,7 +996,24 @@
     <t>https://www.pagina12.com.ar/746515-los-dolares-que-nunca-llegaron</t>
   </si>
   <si>
-    <t>2024-06-23T03:01:00Z</t>
+    <t xml:space="preserve">Título: Los dólares que nunca llegaron
+Chapeau: Devaluación de diciembre, saldos exportables y reservas
+Subtítulo: El Banco Central no está teniendo los resultados que esperaba en materia de acumulación de reservas.
+Editoria: Economia
+Tags: Dólar, devaluación, printed-edition, dolar, devaluacion, diario
+URL: https://www.pagina12.com.ar/746515-los-dolares-que-nunca-llegaron/
+Notícia completa (11 blocos):
+El Banco Central no está teniendo los resultados que esperaba en materia de acumulación de reservas. Tras una megadevaluación en diciembre y una recuperación de la cosecha y los saldos exportables tras la sequía de la temporada anterior, se esperaba un saldo importante en la cuenta corriente externa para esta altura del año. Adicionalmente, el impacto de la recesión se está sintiendo en la forma de una abrupta caída en las importaciones. Sin embargo, tras un desconcertante inicio de mandato, con la devaluación más grande en décadas, el efecto cambiario fue un bálsamo para las reservas del Banco Central apenas por un lapso corto que pareciera agotarse.
+Las bondades de la devaluación son efímeras y el ministro Caputo debe saberlo, pero se confió o “hicieron mal las cuentas”, como dicen en la jerga, porque especuló fuerte a la posibilidad de empalmar el enflaquecimiento del efecto cambiario con la liquidación de una cosecha que sería récord considerando la sequía de 2023 y que el campo tendría menos espalda para especular en torno a la liquidación. Sin embargo. las cosas no salieron como lo esperado.
+El especialista en agronegocios Javier Preciado Patiño lo pone de esta manera: “La cuestión de fondo es que el Gobierno esperaba un aluvión de dólares para esta época del año, porque creía que con el dólar a 850 pesos explotaba la cosecha, como en 2002. Pero en verdad, el agro venía con un dólar exportador de 650 pesos, con lo cual la devaluación no fue gran cosa. Igualmente, en diciembre se vendió mucho, gracias a las exportaciones entraron dólares. Pero después el crawling peg (devaluación pautada anticipadamente del dos por ciento mensual) y los insumos, con costo en dólares más impuesto PAIS, redujeron los márgenes del negocio. Entonces, ¿se vende?, sí, pero más o menos dentro del promedio”.
+En fino, observa que la molienda de soja evoluciona favorablemente con volúmenes mensuales promedio en torno a los 4 millones de toneladas, similares a los de 2019/2020. “Igualmente, considerando que la cosecha este año alcanzó un nivel cercano a 50 millones de toneladas y que las importaciones temporales de porotos son las segundas en importancia --en abril y mayo, el 20 por ciento de lo procesado vino de afuera--, la trituración podría estar por encima de este nivel”, advierte.
+Los volúmenes de exportación del complejo soja también están en línea con el mayor tonelaje exportado en los últimos diez años. Así lo expone un reciente informe de la Bolsa de Cereales de Rosario, que muestra que en mayo se enviaron al exterior más de 5,1 millones de tonelada de soja, por encima del promedio de los últimos diez años para el mes (4,6 millones de toneladas) y 60 por ciento más que el año pasado.
+Asimismo, estimaron que para la segunda mitad de junio, se deberían cargar buques con 2,8 millones de toneladas del complejo soja. De concretarse esas proyecciones, junio finalizaría con 4,6 millones de toneladas embarcadas, también por encima del promedio de los últimos diez años.
+Sin embargo, las compras netas de divisas de parte del Banco Central que tocaron un techo de 3.300 millones de dólares en diciembre y en abril, estuvieron lejos de superarse en mayo: mes que cerró en torno a los 2.500 millones de dólares y –como difundió Indec la semana pasada- con un superávit comercial de 2.656 millones más que relevante para el mes en curso, vinculado a la fuerte recesión interna y a la caída de las importaciones (29,6 por ciento interanual medidas en cantidades).
+Para Sergio Chouza, titular de la consultora Sarandí, la canaleta de las reservas es el “dólar blend” exportador (habilita a liquidar el 20 por ciento de exportaciones por el -CCL) y los esfuerzos que hace el Gobierno por sostener las cotizaciones del Mep y CCL. De acuerdo a sus estimaciones, cerca de 16.000 millones de dólares se usarán este año para mantener a raya los dólares financieros. “Ese monto equivale a casi la totalidad de divisas que destinó la administración Fernández en sus cuatro años para contener a los dólares financieros”.
+La deuda con importadores ocupa otro lugar importante en la canaleta de las reservas. “El grueso de las compras netas de divisas por parte del Banco Central entre diciembre y abril se dio por la postergación del pago de importaciones, más allá de que las importaciones cayeron fuerte. El Central pagaba poco menos del 20 por ciento del monto involucrado, de modo que acumulaba una deuda con importadores cercana a 13.000 millones de dólares, ese fue casi exactamente el monto total de divisas que adquirió en esos cinco meses. Luego ese ratio fue subiendo, pero en la primera mitad del año se pagó menos del 40 por ciento del total importado. De acuerdo a la agenda que planteó el ministro Caputo, en estos meses se cancela en torno al 70 por ciento de esa deuda, sumado al pago a organismos internacionales, arrojan una ecuación con poco margen para el Gobierno”, describe Pedro Gaite de Fundación de Investigaciones para el Desarrollo Económico (FIDE).
+Pese al discurso grandilocuente de este Gobierno, ni Javier Milei vino a hacer lo que nunca nadie se animó, ni su programa económico es aplaudido por los mercados ni mucho menos la comunidad internacional. El propio FMI viene manifestando hace tiempo la inconveniencia del regimen cambiario exportador, además de exigir acelerar el crawling peg.
+Los especialistas consultados por Página/12 coinciden en señalar que el tipo de cambio “permanece lo suficientemente competitivo”, al menos mientras la economía mantenga estos niveles de contracción que hacen disminuir las importaciones. A la vuelta de una lejana esquina, un modelo económico anclado en un crecimiento virtuoso parece esperar toparse con el mismo fantasma de 70 años atrás: la restricción externa o insuficiencia de divisas.</t>
   </si>
   <si>
     <t>Recorrido por la vida empresarial de Gregorio Pérez Companc</t>
@@ -481,7 +1025,16 @@
     <t>https://www.pagina12.com.ar/744778-recorrido-por-la-vida-empresarial-de-gregorio-perez-companc</t>
   </si>
   <si>
-    <t>2024-06-15T03:01:00Z</t>
+    <t xml:space="preserve">Título: Recorrido por la vida empresarial de Gregorio Pérez Companc
+Chapeau: "Goyo" era el cuarto hombre más rico de la Argentina
+Subtítulo: Este viernes falleció a los 89 años Gregorio Pérez Companc, referente del empresariado argentino en los últimos 50 años.
+Editoria: Economia
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/744778-recorrido-por-la-vida-empresarial-de-gregorio-perez-companc/
+Notícia completa (3 blocos):
+Este viernes falleció a los 89 años el empresario Gregorio Pérez Companc, dueño de la alimenticia Molinos Río de la Plata y de la petrolera Pecom, una de las primeras dedicadas al segmento upstream (exploración y explotación) y downstream (refinación, comercialización y distribución) de la industria.
+“Goyo” era el cuarto hombre más rico de Argentina, según la revista Forbes. Su talla se compara con la de pocos nombres, protagonistas del mundo de los grandes negocios del país. Pérez Companc cultivaba un bajo perfil y su fortuna se distribuye entre seis de sus hijos.
+Gregorio Pérez Companc fue uno de los empresarios más destacados de la Argentina. Construyó en 1968 el conglomerado energético Pérez Companc, uno de los contratistas más importantes de la petrolera estatal YPF. En 1980, el holding siguió su expansión con el ingreso al rubro de la construcción, a través de la empresa Sade.</t>
   </si>
   <si>
     <t>Paraguay: ¿un reflejo de la Argentina que se viene?</t>
@@ -493,7 +1046,30 @@
     <t>https://www.pagina12.com.ar/740859-paraguay-un-reflejo-de-la-argentina-que-se-viene</t>
   </si>
   <si>
-    <t>2024-05-30T14:39:33Z</t>
+    <t xml:space="preserve">Título: Paraguay: ¿un reflejo de la Argentina que se viene?
+Chapeau: Cómo funciona el modelo que Javier Milei intenta replicar
+Subtítulo: Cuenta con una presión tributaria y una inflación baja. Estas aparentes ventajas se contrarrestan con un 70% de informalidad laboral y precariedad salarial de la mayoría de la población
+Editoria: Cash
+Tags: Paraguay, Javier Milei, printed-edition, javier-milei
+URL: https://www.pagina12.com.ar/740859-paraguay-un-reflejo-de-la-argentina-que-se-viene/
+Notícia completa (17 blocos):
+El presidente de Paraguay, Santiago Peña, señaló recientemente que "Milei intenta replicar el modelo económico de Paraguay". Esta afirmación ha generado un interés creciente sobre las similitudes entre ambas economías. Para comprender más sobre este modelo, consultamos a dos economistas paraguayos destacados: Fernando Masi, director e investigador de CADEP (Centro de Análisis y Difusión de la Economía Paraguaya) y a Luis Rojas, investigador del Centro de Estudios Heñói y miembro fundador de SEPPY (Sociedad de Economía Política de Paraguay).
+[H3] Claudia Sheinbaum gana las elecciones en MéxicoLa ola importadora que llegó a los alimentosCristina Kirchner le respondió a Milei: "Teorizar en los canales de televisión es muy fácil, gobernar es otra cosa"
+Masi comenzó destacando la interacción entre la presión tributaria y la informalidad laboral en Paraguay, desafiando la noción convencional de una relación lineal entre ambos factores. Analizó cómo la falta de correlación directa entre impuestos y formalización del empleo puede enraizar la situación económica en una complejidad que requiere un análisis más matizado. A partir de los comentarios del economista, se evidencia que la menor presión tributaria en Paraguay, que ronda el 10 por ciento (con una alícuota del IVA del 10 por ciento), no logra generar una mayor formalidad en la economía, contradiciendo las expectativas de la corriente libertaria en Argentina.
+En términos de inversión extranjera, Masi identificó varios obstáculos que enfrenta Paraguay para atraer inversiones significativas al país. Si bien resaltó la existencia de incentivos fiscales y otras medidas para fomentar la inversión extranjera, enfatizó la necesidad urgente de mejorar la infraestructura y la seguridad jurídica para atraer inversiones sostenibles y a largo plazo. A pesar de los esfuerzos realizados, la inversión extranjera directa apenas fluctúa entre el 1 por ciento y el 1,7 por ciento del PBI, lo que constituye un valor bajo. Además, se señala la apertura de zonas libres de impuestos como una estrategia para continuar atrayendo inversiones, lo que sugiere que, desde esa perspectiva, parece que nada es suficiente.
+Rojas también destaca que la corrupción y la impunidad son endémicas en Paraguay, especialmente en el sistema judicial, donde el poder político y económico ejercen una influencia desproporcionada. Se resalta la estrecha relación entre ambos poderes, lo que dificulta la separación y perpetúa un círculo vicioso de poder. Estos factores representan importantes obstáculos para el desarrollo económico y social del país.
+También se abordó la complejidad de la economía paraguaya en términos de desigualdad social y desarrollo humano. Masi analizó cómo la economía “exitosa” del país no necesariamente se traduce en una distribución equitativa de la riqueza ni en un aumento significativo del bienestar social para todos los ciudadanos. Destacó las deficiencias sanitarias, que quedan expuestas cuando los paraguayos utilizan los sistemas sanitarios de Argentina o Brasil, evidenciando la necesidad de mejorar los servicios básicos para toda la población.
+Rojas también examina el modelo económico paraguayo, caracterizado por un fuerte enfoque en el agronegocio y la exportación, así como una dependencia significativa del Estado en sectores como la obra pública y el transporte. Según Rojas, esta dependencia ha generado una burguesía empresarial que está estrechamente ligada al Estado, lo que dificulta la implementación de políticas que promuevan una competencia más equitativa en el mercado y una distribución más justa de la riqueza.
+En cuanto a la relación con Argentina, Rojas expresa preocupación por las políticas económicas que apuntan hacia la privatización y la desregulación, y destaca la importancia del comercio fronterizo para ambas naciones. También comenta sobre la influencia del modelo paraguayo en Argentina y las diferencias entre ambos países en términos de desarrollo industrial y estabilidad macroeconómica. Estos aspectos reflejan la complejidad de las relaciones económicas entre Paraguay y Argentina y sugieren la necesidad de una cooperación más estrecha para abordar los desafíos comunes.
+[H2] Retroceso paraguayo
+Un ejemplo claro del retroceso paraguayo es la red ferroviaria, que había sido uno de los países precursores en desarrollarla y que terminó por desmantelarla. Esta situación representa una pérdida significativa en términos de infraestructura y conectividad, lo que limita las oportunidades de desarrollo económico y social en el país.
+A este escenario decadente podemos sumarle el continuo flujo migratorio de paraguayos que no regresan, lo cual deja expuesto en términos concretos las dificultades del país vecino. Este fenómeno refleja las limitaciones y los desafíos que enfrenta Paraguay en términos de crecimiento económico y desarrollo social, y subraya la importancia de implementar políticas efectivas para mejorar las condiciones de vida de su población.
+En definitiva, Paraguay cuenta con una presión tributaria bajísima, en línea con las preferencias del oficialismo en Argentina, y registra una inflación baja y un crecimiento económico que beneficia principalmente a los sectores concentrados. Sin embargo, estas aparentes ventajas se ven contrarrestadas por la alta tasa de informalidad laboral, que alcanza casi el 70 por ciento, y la precariedad salarial que afecta a la mayoría de la población. Es preocupante observar que tres de cada cuatro personas no alcanzan el salario mínimo, que funciona más como un techo que como un piso salarial. Este panorama cuestiona la efectividad de las políticas económicas basadas en la reducción de impuestos y el ajuste feroz.
+En Paraguay, se evidencia claramente que menos impuestos no generan una reducción en la informalidad laboral ni atraen inversiones significativas. La estabilidad económica lograda a través de un Estado reducido y políticas de ajuste severo solo perpetúa la desigualdad y la pobreza. En lugar de promover el bienestar social, estas políticas cristalizan las condiciones sociales precarias y subrayan la necesidad de adoptar enfoques más equilibrados y orientados hacia el desarrollo inclusivo y sostenible.
+Argentina ya se encaminaba a un destino similar por las políticas llevadas adelante por los últimos dos gobiernos, pero con la llegada de Milei al poder este proceso comenzó a acelerarse aún más.
+* Economista, miembro de Fundus
+[H3] Seguí leyendo
+[H3] ¿Quién es Claudia Sheinbaum, la nueva presidenta de México?El nutrido plantel de ñoquis de Roberto García Moritán en el Ministerio de Desarrollo de CABASturzenegger, en modo bombero: propuso una fórmula privatizadora como salida al escándalo de los alimentos</t>
   </si>
   <si>
     <t>Guido Agostinelli *</t>
@@ -508,7 +1084,23 @@
     <t>https://www.pagina12.com.ar/739539-la-promesa-de-javier-milei-en-la-rural-ante-la-presion-del-a</t>
   </si>
   <si>
-    <t>2024-05-24T21:52:26Z</t>
+    <t xml:space="preserve">Título: La promesa de Javier Milei en La Rural ante la presión del agro por la devaluación del dólar
+Chapeau: El Presidente visitó una muestra en el predio de Palermo
+Subtítulo: En un momento de tensión con sector agropecuario que demora la liquidación de la cosecha a la espera de una suba del tipo de cambio, el mandatario se mostró junto al titular de la Sociedad Rural, Nicolás Pino. Fue en busca de aplausos y de aplacar los ánimos de los productores.
+Editoria: Economia
+Tags: diario
+URL: https://www.pagina12.com.ar/739539-la-promesa-de-javier-milei-en-la-rural-ante-la-presion-del-a/
+Notícia completa (10 blocos):
+Con el respaldo del presidente de la Sociedad Rural, Nicolás Pino, el presidente Javier Milei fue al predio de Palermo a buscar aplausos de "el campo" en semanas de tensión con el sector del agronegocio que, hasta la corrida de esta semana, se mostró reticente a liquidar los granos de la cosecha gruesa, y complica el plan económico del gobierno. "Primero vamos a eliminar el impuesto PAIS y después le van a seguir las retenciones, para que el campo sea totalmente libre", prometió el presidente en la Expo Angus de Otoño.
+La promesa de terminar con el Impuesto PAÍS --que el Gobierno aumentó en los primeros días de gestión-- y quitar la retenciones --que el primer borrador de la Ley Ómnibus incrementaba para todas los sectores del agro-- no tiene fecha; como ocurre con el cepo cambiario, que Milei se encarga de posponer en cada entrevista hasta que "se termine de sanear el Banco Central y toda la cuestión monetaria".
+Milei reconoció esta viernes en La Rural sus "promesas de campaña", algo que las entidades agropecuarias y las empresas del sector vienen recordándole a sus funcionarios. "Estamos terminando de desactivar las bombas que nos dejó el kirchnerismo, pero créanme que vamos a ser libres y vamos a salir adelante. El campo va a tener un rol fundamental", aseguró ante un público receptivo a las críticas a los gobiernos peronistas.
+El anfitrión para que Milei se muestrara cercano al sector fue Pino, quien dijo que la invitación al presidente para participar de Expo Angus era "una clara señal de apoyo a este sector que es tan importante en el pueblo argentino y para el futuro del país". El presidente de la Sociedad Rural, a diferencia del propio jefe de Gabinete Nicolás Posse, fue uno de los asistentes al show que el presidente montó en el Luna Park para presentar su nuevo libro.
+El mismo miércoles, otra entidad de la Mesa de Enlace, Coninagro emitió un comunicado en el que dejó en claro cómo el sector le estaba mostrando los dientes al Poder Ejecutivo: "a mediados de mayo sólo se ha vendido el 34% de la producción de soja de la campaña. Por debajo del 36% de los 2 años previos y el promedio de 40% de los 5 años previos, para el mismo momento del año".
+Como ocurre cada marzo, en la previa de la cosecha gruesa, los sectores del agronegocio especulan con la devaluación de la moneda o marcan el juego a la espera de un tipo de cambio más favorable. Por eso, los funcionarios del Ministerio de Economía estuvieron en mayo llevando el mensaje de que no habría devaluación a los congresos del sector como Maizar --que reúne a las empresas de la cadena de valor de ese cultivo-- y A Todo Trigo, para cerrar las especulaciones sobre la liquidación de la cosecha gruesa.
+A principios de mayo, en el encuentro A Todo Trigo, realizado en Mar del Plata, el secretario de Planeamiento y Gestión para el Desarrollo Productivo y de la Bioeconomía, Juan Pazo, aseguró que "se acabaron las devaluaciones para generar competitividad", se quejó de "la falta de paciencia" con el Gobierno y les confesó: "Yo también soy productor y no me gustan nada las retenciones". Pazo tiene inversiones en el sector ganadero, que fue beneficiado con la eliminación de los cupos de exportación.
+El secretario de Bioeconomía también fue a pedir comprensión esta semana al congreso de Maizar. "Los pesares de hoy esta vez tienen sentido y vamos a salir de la decadencia", les prometió a los empresarios y productores; y destacó la eliminación de los fideicomisos, volúmenes de equilibrios y cuotas --medidas que liberaron la exportación en detrimento del abastecimiento interno--, así como la reducción de la brecha cambiaria, antes de prometes como Milei terminar con las retenciones a futuro: "Pudimos avanzar rápido y prometemos hacerlo con los derechos de exportacióncuando las condiciones macro lo permita".
+Esta tarde, en La Rural, acompañado por su hermana Karina, Milei volvió a insistir: "Las promesas de campaña las estamos cumpliendo. Créanme que vamos a salir a delante y vamos a ser libres y el campo va a tener un rol fundamental". El anfitrión y presidente de la Sociedad Rural le agradeció: "Dentro de la tristeza profunda que vive el sector, la visita del presidente de es un gesto que valoramos mucho todos los productores”, en referencia a la muerte del titular de la Federación Agraria, Carlos Achetoni.
+Achetoni fue crítico del gobierno en su última intervención pública en Maizar. No solo por el reclamo de la quita de retenciones sino también por la desregulación económica impuesta sobre las economías regionales y en cultivos con gran presencia de los pequeños y medianos productores y chacareros a los que representaba. Achetoni había hablado de "propuestas y condiciones alternativas que el Gobierno no ve" al referirse a "medida que degrada a las producciones, como la yerba, el vino y producciones que si no se lo indicás, ellos van a creer que está todo bien".</t>
   </si>
   <si>
     <t>Brasil: "hay plata" para las víctimas de las inundaciones</t>
@@ -520,7 +1112,45 @@
     <t>https://www.pagina12.com.ar/737899-brasil-hay-plata-para-las-victimas-de-las-inundaciones</t>
   </si>
   <si>
-    <t>2024-05-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: Brasil: "hay plata" para las víctimas de las inundaciones
+Chapeau: Lula pone a disposición de los damnificados los recursos del Estado
+Subtítulo: El “tamaño de las partidas” de dinero destinados al estado sureño será proporcional a la “magnitud de los problemas”.
+Editoria: El Mundo
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/737899-brasil-hay-plata-para-las-victimas-de-las-inundaciones/
+Notícia completa (32 blocos):
+Desde Brasilia
+“Hay plata”. Lula da Silva no ha dejado de repetir como si fuera un mantra que el Estado desembolsará “todos los recursos que sean necesarios” para socorrer a la provincia de Rio Grande do Sul asolada por los temporales más graves de su historia.
+El “tamaño de las partidas” de dinero destinados al estado sureño será proporcional a la “magnitud de los problemas” que sólo se conocerá por entero "cuando hayan bajado las aguas”, afirmó el presidente y líder del Partido de los Trabajadores (PT) en las tres visitas realizadas a la zona del desastre en sólo catorce días.
+[H2] Ministro extraordinario
+El mandatario se reunió este sábado con el político gaúcho Paulo Pimenta, su flamante ministro extraordinario para la reconstrucción de Rio Grande do Sul, cargo cuya creación pone de manifiesto la importancia dada al diluvio que dejó de ser , por mucho, un asunto regional.
+La atención dada a esta crisis está en línea con la política de combate al cambio climático con la cual la administración petista puso punto final al negacionismo que caracterizó al gobierno anterior. Ese corte vale para el plano doméstico y en el externo: reinstalando a Brasil como referencia en el debate global sobre el clima.
+[H2] Lluvias
+El presidente y el ministro ad hoc Pimenta conversaron en Brasilia donde fueron informados sobre las lluvias que volvieron a caer con fuerza este sábado en el norte gaúcho.En el oeste provincial, la capital Porto Alegre y su área metropolitana, siguen cubiertas por el rio Guaíba aunque el nivel de las aguas está decreciendo desde hace tres días.
+Este sábado el Guaíba , donde desaguan otros ríos nacidos en las sierras, midió 4,54 metros, su menor altura desde el inicio de las lluvias, pero 1,54 metros por sobre la cota de inundación.
+[H2] El BNDES
+Mientras buena parte del gabinete nacional , al cual se unieron los comandantes del Ejército, la Marina y la Aeronáutica ( dato importante) , observaba in situ los estragos causados por los temporales en la provincia sureña, unida a Argentina por una extensa frontera fluvial, las autoridades del Banco Nacional de Desarrollo Económico y Social (BNDES), presentaban un programa de cinco mil millones de reales (poco menos de mil millones de dólares) de créditos con tasas de interés inferiores a las del mercado.
+Ese financiamiento blando tendrá como destinatarias a las micro, pequeñas y medias empresas al tiempo que ser postergará el cobro de las deudas de los productores rurales, sector donde se concentra el Producto Bruto de una provincia que está entre las principales productoras de arroz, soja y carne del país.
+Presidido por el economista y ex senador petista Aloízio Mercadante, el BNDES reasumió su papel de banco estímulo al desarrollo y el consumo interno desde 2023. Mercadante es un cuadro con peso en el PT, que lo escogió como candidato a vicepresidente en la fórmula liderada por Lula en las elecciones de 1998, vencidas por Fernando Henrique Cardoso.
+“Esa idea de Estado mínimo está siendo substituida por una retomada de la política industrial y de fomento al desarrollo. El Consenso de Washington (de 1989) ya no tiene consenso ni en Washington”, declaró Mercadante, hace tres semanas, cuando se registraban las primeras lluvias de lo que luego fue el diluvio riograndense.
+Debido a declaraciones de ese tipo y su programa de apoyo a la petrolera estatal Petrobras y financiamiento de obras de infraestructura Mercadante es visto como la cara “desarrollista” del gobierno. Por esa razón es tan elogiado en el PT como descalificado la prensa dominante, de sabida adhesión a la ortodoxia neoliberal.
+[H2] Dilma Rousseff
+Desde Shangai, Dilma Rousseff, presidenta del Nuevo Banco de Desarrollo del grupo BRICS, anunció el aporte de 5,7 mil millones de reales (1,1 mil millones dólares) para obras de infraestructura y proyectos para prevenir desastres climáticos.
+El dinero será asignado, en parte, al BNDES, banco asociado al BRICS en diversos emprendimientos.
+En un video la ex mandataria brasileña (2011-2016) hizo precisiones técnicas sobre el aporte y, a la vez, empleó un tono discretamente político. Dijo que el “pueblo gaúcho puede contar conmigo” en esta coyuntura difícil y mencionó que hace 50 años se radicó en ese estado, donde desarrolló su vida pública y se afilió al PT . Esta y otras señales indicarían un posible retorno de Dilma a la escena nacional una vez finalizada su labor en el banco de las potencias emergentes.
+Dilma es otra de las economistas “desarrollistas” - a la cual el mercado nunca dejará de reprocharle medidas de su gobierno orientadas a mitigar el lucro exorbitantes de la banca privada - con quien Lula mantiene consultas. La última de ellas fue la semana pasada antes de que el gobierno anunciara una nueva conducción de la petrolera estatal Petrobras.
+[H2] “Bolonaro y yo”
+Al hablar en el auditorio de una universidad católica de São Leopoldo, ciudad muy castigada por las tempestades, Lula contrastó el empeño de su gobierno en dar respuesta a los temporales, con la desidia medioambiental observada a lo largo de los cuatro años de gestión de Jair Bolsonaro .
+En más de una ocasión el presidente de centro izquierda recordó que su antecesor de extrema derecha se hacía fotografiar a bordo de su jet sky en playas soleadas mientras miles de personas aguardaban, en vano , la ayuda gubernamental. Y le enrostró la falta de financiamiento para este tipo de calamidades. Antes de dejar el Palacio del Planalto, a fines de 2022, Bolsonaro destinó irrisorios 25 mil reales para hacer frente a catástrofes en 2023, primer año de la gestión petista.
+[H2] Armonía política
+El ministro Rui Costa, actual jefe de gabinete, estimó en unos 50 mil millones de reales (poco menos de 10 mil millones de dólares ) será el total de recursos federales enviados para campear la crisis "gaúcha".
+Esa cifra corresponde a la construcción de miles de viviendas dentro del programa Mi Casa, Mi Vida, la reparación de carreteras y represas averiadas y pagos adicionales del plan social Bolsa Familia.
+Dentro de ese paquete se incluyen créditos para empresarios, eliminación de impuestos y la suspensión del cobro, durante tres años, de la deuda del gobierno provincial, comandado por el conservador , Eduardo Leite, un persistente opositor al gobierno nacional.
+Leite pertenece al Partido de la Socialdemocracia Brasileña (PSDB), cuyo presidente honorario es el ex mandatario Fernando Henrique Cardoso. Su administración aplicó a pies juntillas el recetario neoliberal, incluyendo la reducción de los recursos para prevenir eventos climáticos extremos y una legislación favorable a la explotación depredatoria del suelo, como lo exige el agronegocio.
+[H2] Toda inundación es política
+A pesar de sus reservas frente al neoliberal Leite, el gobierno optó por una alianza provisoria con el gobernador que permita llevar adelante las iniciativas que debe gestionar el nuevo ministro para la reconstrucción Paulo Pimenta.
+Con ese movimiento, se excluyó implícitamente, al intendente de Porto Alegre, Sebastião Melo. Bolsonarista en lo político y negacionista en lo ambiental Melo propuso contratar una consultora estadounidense , que ya tuvo una cuestionable performance en la reconstrucción de Nueva Orelans tras el huracán Katrina, y sugirió la creación de ciudades emergenciales donde reunir a todos los damnificados, principalmente de las favelas.
+Propuesta en la que algunos sospechan la intención disimulada de “higienizar” la ciudad, llevando a la población humilde a zonas alejadas del centro.</t>
   </si>
   <si>
     <t>Darío Pignotti</t>
@@ -535,7 +1165,31 @@
     <t>https://www.pagina12.com.ar/736282-miguel-angel-pichetto-reclamos-cambios-en-el-gobierno-de-mil</t>
   </si>
   <si>
-    <t>2024-05-14T03:01:00Z</t>
+    <t xml:space="preserve">Título: Miguel Ángel Pichetto reclamó cambios en el gobierno de Milei
+Chapeau: Las áreas a las que apuntó
+Subtítulo: "Oxigenaría algunas áreas", dijo el titular del bloque de diputados de Hacemos Cambio Federal. También analizó la marcha del debate de la Ley Bases.
+Editoria: El País
+Tags: Miguel Angel Pichetto, printed-edition, miguel-angel-pichetto, diario
+URL: https://www.pagina12.com.ar/736282-miguel-angel-pichetto-reclamos-cambios-en-el-gobierno-de-mil/
+Notícia completa (18 blocos):
+A cinco meses del inicio del gobierno de Javier Milei, el diputado y titular del bloque Hacemos Coalición Federal, Miguel Ángel Pichetto, consideró que es momento de "oxigenar" la gestión e impulsar algunos cambios en el Gabinete. Pichetto, protagonista de la oposición dialoguista en la Cámara baja, apuntó sobre tres áreas donde deberían ocurrir los cambios e involucran al Ministerio de Economía, el Ministerio de Capital Humano y la comunicación.
+"Entrás en el plano de informaciones más reservadas de la entraña del Gobierno, pero yo creo que oxigenaría algunas áreas", respondió Pichetto a un consulta sobre los rumores de cambios en el Gabinete de La Libertad Avanza. En una entrevista al canal de streaming C+, Pichetto aprovechó para apuntar sobre algunas áreas de gestión.
+Unsupported embed [https://www.dailymotion.com/video/x8yfs4u]
+[H2] Los ministros a los que apuntó Pichetto
+"A mí no me preocupa tanto tener 8 o 12 ministerios. Creo que la Argentina agroindustrial necesita un ministro de agricultura o un secretario de agricultura que tenga independencia y autonomía y que dependa del presidente únicamente", dirigió el diputado el primer dardo contra un área que está bajo la órbita del ministro de Economía, Luis Caputo.
+El Ministerio de Agricultura fue relegado a secretaría tras la asunción de Sergio Massa al frente de la cartera de Economía y continuó así con la llegada de Milei. El hombre en el cargo es Fernando Vilella, exdecano de la Facultad de Agronomía de la UBA, que renombró la secretaría como "Bioeconomía". La Secretaría fue confirmada recién a principios de abril, entre rumores de renuncia de Vilella, pero en paralelo se creó la Secretaría de Planeamiento y Gestión para el Desarrollo Productivo y de la Bioeconomía, a cargo de Juan Pazo, hombre de Caputo y la persona que lleva adelante las negociaciones con las entidades y empresas del agronegocio.
+Unsupported embed [https://www.dailymotion.com/video/x8yfqy4]
+Por otro lado, y tras el golpe que significó la marcha universitaria del 23 de abril, Pichetto apuntó sobre la Educación como "un factor importante". "Hay un área que está muy sobrecargada, que no estoy descalificando a la persona que la lleva adelante Capital Humano, pero me parece que tiene muchas responsabilidades muy sensibles, en términos de la vida cotidiana de la gente", sentenció el titular del bloque de Hacemos Coalición Federal sobre el rol que cumple la ministra Sandra Pettovello.
+Por último, Pichetto apuntó sobre un área dispersa pero con muchos fondos y cargos jerárquicos, la comunicación de la Casa Rosada. "La comunicación no puede ser solamente por tuit, es importante ese mundo, no lo desconozco. Todos los hechos prescriben a los 35 minutos de haber hecho el tuit", indicó.
+Las tareas de comunicación están dividas entre el vocero presidencial Manuel Adorni y el secretario de Medios, Eduardo Serenellini, ambos con rango ministerial desde fines de abril; y bajo la mirada de la Secretaría General de la Presidencia, comandada por Karina Milei. Además, el asesor presidencial Santiago Caputo comanda al grupo de trolls oficial.
+[H2] Los buenos deseos de Pichetto
+A pesar de aprovechar el momento para marcar sus críticas en la gestión, Pichetto deseó que un buen futuro para el gobierno de Milei al considerar que "es un presente que está en construcción. Esperemos que se consolide porque está justo en la instancia del cambio".
+Para eso, el diputado le recomendó a la gestión liberal libertaria tener "la sensibilidad social para poder amortiguar los efectos de ajuste que son muy duros en la gente. Hay que cuidar el empleo, hay que retomar la construcción".
+En su rol como parte de la oposición dialoguista, Pichetto destacó que el Gobierno "aprendió" que debe mantener diálogo con el Congreso y los gobernadores para poder aprobar leyes y reconoció que mantiene buen diálogo con Karina Milei, Santiago Caputo y la vicepresidenta Victoria Villaruel.
+[H2] El futuro de la Ley Bases
+En ese sentido, confió en que "no hay chances de que se rechace la Ley Bases", aunque anticipó que podrá haber cambios en el Senado respecto del Impuesto a las Ganancias y el Régimen de Incentivo para Grandes Inversiones (RIGI). En ese caso, resaltó que en la Cámara baja no se volverá a debatir toda la norma si no, solo los puntos que modifique el Senado para aprobarlos o rechazarlos con los dos tercios de la cámara, algo casi imposible.
+Unsupported embed [https://www.dailymotion.com/video/x8yfrmq]
+Pichetto se mostró crítico respecto de las advertencias de muchos sectores sobre los peligros que significa el RIGI y se mostró permeable a los intereses que trae detrás. Sobre el peligro que significa la libre importación de maquinaria y la primarización de la economía, Pichetto dijo que las críticas de la UIA son exageradas y que las pymes trabajarán por "efecto derrame"; mientras que sobre los impactos de la actividades extractivas se mostró a favor de la actividad minera en todo el país: "Algunas provincias patagónica tienen la tara mental de no hacer minería: han perdido la batalla cultural frente a grupos minoritarios hiperambientalistas".</t>
   </si>
   <si>
     <t>Inundaciones en Brasil: las devastadoras consecuencias económicas que produce el cambio climático</t>
@@ -547,7 +1201,23 @@
     <t>https://www.pagina12.com.ar/736262-inundaciones-en-brasil-las-devastadoras-consecuencias-econom</t>
   </si>
   <si>
-    <t>2024-05-13T12:49:01Z</t>
+    <t xml:space="preserve">Título: Inundaciones en Brasil: las devastadoras consecuencias económicas que produce el cambio climático
+Chapeau: Una problemática sin lugar en la agenda de Milei
+Subtítulo: Por qué es grave que las consecuencias del cambio climático no formen parte de la agenda oficial y la toma de decisiones.
+Editoria: Radio 750
+Tags: Javier Milei, La García, javier-milei, la-garcia
+URL: https://www.pagina12.com.ar/736262-inundaciones-en-brasil-las-devastadoras-consecuencias-econom/
+Notícia completa (10 blocos):
+En medio de las inundaciones que sacuden al sur de Brasil y que ya provocaron la muerte de más de 140 personas y afectan especialmente al estado de Rio Grande do Sul, expertos ponen el foco en las graves consecuencias económicas que podría provocar no considerar al cambio climático entre las políticas públicas.
+Para Gabriela Vizental, periodista especializada en ambiente y columnista de la 750, es clave poner especial atención en las problemáticas económicas que traerán las inundaciones históricas en el sur de Brasil. “La noticia ya se ha contado en todos los medios. Hubo una hiperinundación en el sur de Brasil. Esto está exacerbado por el cambio climático. No hay que olvidarnos de este tema. Porque este cambio climático que la ciencia viene advirtiendo tiene eventos extremos”, explicó.
+Además, recalcó que “con la combinación de una gran lluvia y una mayor humedad se exacerba todo y hace que la magnitud sea mayor. Lo dijo Lula estos últimos días. Lo que sucedió es una alerta del planeta. Y el cambio climático no es algo que estudian solo los científicos. Es algo socio ambiental y económico. Hoy ocupa un lugar central”.
+Por eso, no es cuestión de mirar para otro lado. Hoy es Brasil, sí. Pero meses atrás fue Argentina con los incendios. Y ya hay, también, grandes inundaciones en el país. “Creo que no hay que dejar de lado el cambio climático vinculado con la economía”, explicó Vizental y expuso una serie de datos alarmantes.
+Por ejemplo, dijo, en esta zona de Brasil afectada por el agua, que es una de las máximas productoras de soja, se calcula que la inundación va a hacer que pierda el 25 por ciento de la cosecha. Lo mismo con la produccion de arroz.
+“La primera reflexión es que es un gran contrasentido para el agronegocio, que se pasó deforestando durante la época de Bolsonaro miles de kilómetros. 4.500 kilómetros cuadrados. Son más de 20 veces la Ciudad de Buenos Aires deforestadas”, explicó.
+Y añadió: “Vos sacás el bosque y los estudiosos te dicen que se reduce la capacidad de absorción de la tierra y cambia la temperatura. Nadie se puede sorprender de que la ciencia no lo ha estado contando y que hoy las cosechas les quede debajo del agua”.
+Por su parte, Gabriel Blanco, profesor titular e investigador de la Facultad de Ingeniería de la UNICEN en las áreas de energías renovables, cambio climático y sustentabilidad, explicó a la 750 que “en el capitalismo se dejó de lado todos los efectos negativos externos” como la contaminación.
+“Hay que considerar todas las cuestiones de manera sistémica. Tener en cuenta las consecuencias socioambientales de determinadas acciones, socioeconómicas, políticas, institucionales, cada cosa con el valor que tiene. El valor no tiene un precio. Se mide por otras cosas”, expresó.
+Luego, finalizó: “Y hay una cosa más. Los tomadores de decisiones en Argentina no sienten la misma presión de parte de las masas, de las grandes audiencias. Ellos no se ven amenazados porque no van a ganar una próxima elección. No está el tema en la agenda pública. Hay mucha desinformación. Las elites dominantes no sienten el mínimo reclamo de las bases sobre este tema”.</t>
   </si>
   <si>
     <t>Una catástrofe que recuerda la devastación de la Amazonia</t>
@@ -559,7 +1229,42 @@
     <t>https://www.pagina12.com.ar/734569-una-catastrofe-que-recuerda-la-devastacion-de-la-amazonia</t>
   </si>
   <si>
-    <t>2024-05-07T03:01:00Z</t>
+    <t xml:space="preserve">Título: Una catástrofe que recuerda la devastación de la Amazonia
+Chapeau: Las inundaciones en Río Grande do Sul, consecuencia del cambio climático
+Subtítulo: La devastación de la Amazonia, ubicada en el norte brasileño y donde se encuentran las mayores reservas de biodiversidad y agua del planeta, a menudo causa “efectos en una región lejana como está pasando ahora en Rio Grande do Sul”, advierte el gobierno de Lula.
+Editoria: El Mundo
+Tags: Inundaciones, Brasil, Luiz Inácio Lula da Silva, printed-edition, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/734569-una-catastrofe-que-recuerda-la-devastacion-de-la-amazonia/
+Notícia completa (29 blocos):
+Desde Brasilia
+El desastre ambiental que dejó más 200 muertos y desparecidos en el sur de Brasil pudo ser evitado, o al menos atenuado. Ese fue uno de los planteos formulados este lunes por el gobierno brasileño al realizar un balance de los estragos que causaron las tempestades en el estado de Rio Grande do Sul.
+La devastación de la Amazonia, ubicada en el norte brasileño y donde se encuentran las mayores reservas de biodiversidad y agua del planeta, a menudo causa “efectos en una región lejana como está pasando ahora en Rio Grande do Sul”, explicó el jefe de gabinete, ministro Rui Costa.
+Junto a Costa se encontraban la ministra de Medio Ambiente y Cambio Climático, Marina Silva, y el titular de Minas y Energía, Alexandre Silveira.
+Unsupported embed [https://www.dailymotion.com/video/x8y5g26]
+[H2] Cambio climático
+Cuando una región tan basta como es la floresta brasileña con sus 4,5 millones de km2 -una superficie similar a la de Argentina, Colombia y Venezuela sumadas - es desmatada sistemáticamente por agricultores, ganaderos y mineros, suceden desequilibrios de consecuencias gigantescas que alteran el régimen de lluvias además de modificar la temperatura.
+En lo que va de 2024, además de los diluvios inéditos ocurridos en Rio Grande do Sul, hubo cinco ondas de calor atípicas, en ciudades como San Pablo, Rio de Janeiro y Brasilia. El último ejemplo de ello sucedió el sábado, cuando los termómetros rozaron los 34 grados, bastante por encima de la temperatura habitual, en Copacabana horas antes del show de Madonna.
+[H2] Devastación
+La modificación intencional de la geografía amazónica (con el uso de sus tierras para producir soja o alimentar ganado) es uno de los factores que, al quebrar el equilibrio ecológico, desencadenaron el desastre sucedido en Rio Grande do Sul, en el otro extremo del país.
+Según los informes divulgados en la noche de este lunes las lluvias intensas en esa provincia sureña causaron 85 muertos y 134 desaparecidos mientras 200 mil personas debieron dejar sus viviendas para alojarse albergues públicos o ser acogidas por sus familiares.
+El jefe de gabinete Rui Costa presentó el punto de vista del gobierno durante un evento, realizado en el Palacio del Planalto, al cual acudió tras reunirse con el presidente Lula da Silva para ultimar los detalles de un paquete de medidas de emergencia.
+[H2] Medidas
+La prioridad del gobierno es socorrer a los ciudadanos cuyas casas están amenazadas por los deslaves de tierra en la región serrana, situada en el centro de Rio Grande do Sul, donde comenzó el temporal la semana pasada.
+Paralelamente comenzó el rescate de miles de vecinos de la capital Porto Alegre, ubicada en el este de la provincia, casi a nivel del mar, cercada por las aguas del rio Guaíba.
+Para hacer un seguimiento de la ayuda enviada desde Brasilia, el gobierno montó un gabinete de crisis en Porto Alegre, formado por los ministros Paulo Pimenta (Comunicación Social) , Nícia Trinidade (Salud) y Waldez Goes (Integración Regional).
+Una vez resuelto estos problemas acuciantes en un segundo momento, “cuando bajen las aguas”, el gobierno planea restablecer los servicios de agua y luz de los cuales hoy están privados unos 800 mil ciudadanos, y se reconstruirá la infraestructura afectada por la fuerza de las aguas.
+En un tercer momento el gobierno va a aumentar las partidas para la construcción de viviendas populares en el marco del programa Mi Casa, Mi Vida.
+[H2] Lula entra en campo
+Lula viajó dos veces a la provincia sureña castigada por los temporales. La primera visita ocurrió el jueves cuando aterrizó en la ciudad de Santa Maria, en la región central y este domingo viajó a Porto Alegre, donde sobrevoló la ciudad cubierta por las aguas.
+“Yo sé que el estado está en una situación financiera difícil y quiero que sepan que el gobierno federal los va a apoyar”, dijo el mandatario del Partido de los Trabajadores (PT), ante el gobernador Eduardo Leite, del conservador Partido de la Socialdemocracia Brasileña (PSDB).
+[H2] Frontera con Argentina
+La provincia de Rio Grande do Sul está en el extremo sur del país, donde comparte fronteras con Argentina y Uruguay, y al igual que estos dos países su economía está basada en la agricultura, gracias a sus planicies extensas, y un parque fabril ligado en parte a la agroindustria.
+Desde la década del 90 el estado y su capital fueron, más allá de algunos impases, bastiones del PT. Pero esa hegemonía de izquierda se fue diluyendo y en los últimos años quedó eclipsada por el ascenso de una derecha ligada a los grandes productores agropecuarios bastante sintonizada con el bolsonarismo.
+[H2] Negacionismo
+Buena parte de los parlamentarios gaúchos, oriundos de Rio Grande do Sul, integra la bancada del agronegocios en el Congreso nacional conocida por sabotear los proyectos del gobierno para mitigar el cambio climático.
+Esos legisladores trabajan “día y noche para destruir la legislación ambiental” y las políticas impulsadas por Lula desde enero 2023, denunció Marcio Astrini, secretario ejecutivo del Observatorio del Clima.
+Para estos congresistas el cambio climático es una invención de los “globalistas”, entre quienes incluyen a la ministras Marina Silva y Sonia Guajajara (Pueblos Indígenas).
+Con la misma intensidad la “Bancada del Buey”, así se la conoce en la jerga política, sostiene el avance de la frontera agrícola sobre la Amazonia, incluyendo la invasión de tierras de los pueblos originarios, garantiza el progreso económico y soberanía. Tesis que en los años 70 fueron parte del discurso de la dictadura y en la actualidad tienen como principal publicista a Jair Bolsonaro.</t>
   </si>
   <si>
     <t>Masiva protesta indígena en Brasil por la demarcación de sus tierras ancestrales</t>
@@ -571,7 +1276,27 @@
     <t>https://www.pagina12.com.ar/731425-masiva-protesta-indigena-en-brasil-por-la-demarcacion-de-sus</t>
   </si>
   <si>
-    <t>2024-04-24T14:36:16Z</t>
+    <t xml:space="preserve">Título: Masiva protesta indígena en Brasil por la demarcación de sus tierras ancestrales
+Chapeau: Le pidieron a Lula que cumpla su promesa de campaña
+Subtítulo: Miles de indígenas marcharon este martes en la capital de Brasil para reclamar seguridad y la demarcación de sus tierras, un asunto que enfrenta al gobierno del presidente Luiz Inácio Lula d
+Editoria: Brasil
+Tags: Brasil, pueblos originarios, pueblos-originarios
+URL: https://www.pagina12.com.ar/731425-masiva-protesta-indigena-en-brasil-por-la-demarcacion-de-sus/
+Notícia completa (14 blocos):
+Miles de indígenas marcharon este martes en la capital de Brasil para reclamar seguridad y la demarcación de sus tierras, un asunto que enfrenta al gobierno del presidente Luiz Inácio Lula da Silva con el parlamento de mayoría conservadora.
+Con plumas, arcos, flechas y otros atuendos tradicionales, hombres y mujeres marcharon por la Explanada de los Ministerios hacia el Congreso Nacional. La marcha incluyó bailes y cantos, en el marco del campamento anual Tierra Libre que tiene lugar en la capital brasileña esta semana.
+"Hay una emergencia indígena", explicó Jaqueline Arandurah, dirigente del pueblo guaraní kaiowá ubicado en el estado de Mato Grosso do Sul. "Ya van más de 400 días del gobierno de Lula y nuestras tierras no fueron demarcadas", completó.
+La líder señaló que marcha "para decirle al gobierno brasileño que es necesario garantizar los derechos de los pueblos indígenas para mitigar la violencia" en los territorios ancestrales.
+La delimitación de las tierras indígenas fue una promesa de campaña de Lula, quien desde que volvió al poder en enero de 2023 retomó esa política abandonada por Jair Bolsonaro (2019-2022).
+Además, la demarcación de esas zonas es una medida que, según científicos, contribuye a la preservación del medioambiente.
+Hasta el momento, fueron homologadas durante el gobierno de Lula da Silva diez nuevas tierras indígenas, incluidas dos anunciadas la semana pasada, pero los manifestantes reclaman más acciones.
+[H2] El conflicto por el “marco temporal”
+La demarcación de tierras es un asunto conflictivo en Brasil. Sus críticos se concentran en el poderoso agronegocio y sus aliados en el Congreso, que mantuvieron en la ley una controvertida tesis que limita los derechos de los indígenas sobre sus territorios.
+Se trata del llamado "marco temporal", que limita el derecho de los pueblos nativos, que totalizan 1,7 millones de los 203 millones de habitantes de Brasil, a reivindicar como propios los territorios que ocupaban en 1988, cuando se promulgó la Constitución.
+"Eso es una ofensa, es decir que somos los invasores y no lo somos", dijo Walderir Tupari, del pueblo Tupari, basado en el estado de Rondonia (norte), al afirmar que la Constitución "está siendo violada". "No estamos aquí desde 1988. Estamos desde hace mucho, mucho tiempo", añadió.
+El Supremo Tribunal Federal (STF) ya había declarado inconstitucional esa tesis en septiembre pasado, pero ahora debe repetir el debate sobre la nueva ley.
+El juez del STF Gilmar Mendes decidió suspender todos los procesos judiciales sobre la constitucionalidad de la ley hasta que la máxima corte se manifieste definitivamente sobre el tema.
+La relatora especial de Naciones Unidas para defensores de derechos humanos, Mary Lawlor, cerró el viernes una visita a Brasil resaltando la importancia de demarcar las tierras para detener la violencia contra las comunidades.</t>
   </si>
   <si>
     <t>Logo latinoamerica-piensa</t>
@@ -586,7 +1311,23 @@
     <t>https://www.pagina12.com.ar/728316-tecnologia-aplicada-con-una-mirada-social</t>
   </si>
   <si>
-    <t>2024-04-14T03:01:00Z</t>
+    <t xml:space="preserve">Título: Tecnología aplicada con una mirada social
+Chapeau: Sector agropecuario, función social y desafío ambiental
+Subtítulo: El programa Argentina Productiva, Sustentable, Federal e Inclusiva apunta a aumentar la producción, generar más puestos de trabajo y exportaciones.
+Editoria: Cash
+Tags: Alimentos, printed-edition
+URL: https://www.pagina12.com.ar/728316-tecnologia-aplicada-con-una-mirada-social/
+Notícia completa (10 blocos):
+Desde la mirada del agronegocio, por estos días se plantea "poner a la agricultura del lado bueno". "El primer paso en cualquier intento por mejorar el medio ambiente es la productividad”, dice Héctor Huergo, de Clarín Rural, y toma como ejemplo al sector lechero, que apuntaría a independizar la “función vaca” de la “función pasto”. “La nueva concepción parte de que la vaca lechera es una biofábrica que convierte energía, proteína y fibra vegetal, en el producto leche”, indica, para detallar que los empresarios del grupo Duhau van a instalar un tambo de seis mil vacas bajo techo en Arenaza con la promesa de que "las mismas vacas que muy bien manejadas en sistemas pastoriles andan por los 25 litros diarios, pasarán a dar 40 litros”.
+Mientras el modelo de agronegocios ve en primer lugar eficiencia, productividad y economía circular, desde la mirada del ser humano organizado en comunidad, se ve al alimento como un bien social y el cuidado de nuestra casa común, es decir de la biosfera y su biodiversidad.
+Claro que también se tiene en cuenta la eficiencia, la productividad, la economía circular, la competitividad global, la generación de divisas y la generación de puestos de trabajo. Por ello se plantea el programa Argentina Productiva, Sustentable, Federal e Inclusiva, para aumentar la producción agroalimentaria, generar más puestos de trabajo y más exportaciones del sector agropecuario.
+Este programa se basa en la aplicación de las nuevas tecnologías y conectividad rural de todo el territorio nacional. En la unión de lo real, lo virtual y lo biológico se materializan las acciones con estas nuevas herramientas que potencian y eficientizan las tareas realizadas por hombres y mujeres, haciéndolas más productivas, más competitivas, sorteando las contingencias de la naturaleza de manera sustentable. Pero además de eficientizar los procesos productivos, mejoran las condiciones de las labores de quienes trabajan la tierra.
+[H2] Tecnología
+En Expoagro 2024 se observó el potencial tecnológico nacional. Solo con mencionar la VAX de Metalfor, demuestra el nivel argentino en materia de tecnología aplicada al campo. Estamos convencidos de que es por ahí, con conocimiento, ciencia, con innovación, con tecnología y bioeconomía. Se necesita estar preparado para el agro de este momento de informatización-digitalización-virtualización del sistema capitalista global, lo cual requiere capacitar a los productores de manera intensiva en las nuevas tecnologías: robótica, Startupps, Blockchain, Big Data, IoT y genómica.
+La pelea no es contra la tecnología. Por eso este programa se expande más allá de la región central, zona núcleo o región pampeana para aprovechar las ventajas competitivas que aporta cada territorio de la Argentina, maximizando su potencial productivo de agroalimentos con bioprocesos, biotecnologías, bioenergías, biomateriales y biocéuticos.
+Ante un mundo en crisis que necesita producir alimentos, y al mismo tiempo debe proteger la biosfera y su biodiversidad, es fundamental construir un modelo agroalimentario productivo y sustentable, con soberanía tecnológica y agroalimentaria, un modelo Agro Bio Industrial Federal e Inclusivo.
+Nosotros vemos la potencialidad de que toda la Argentina sea viable, por eso a los agronegocios, le contraponemos lo agrobiohumano, la Argentina Productiva, Sustentable, Federal e inclusiva. El único lado bueno posible para la agricultura es el de la centralidad del ser humano organizado en comunidad, el de los alimentos cumpliendo su rol social de alimentar, y el de ser una producción sustentable ambiental, social y económicamente.
+*Centro de Estudios Agrarios (CEA)</t>
   </si>
   <si>
     <t>Matías Strasorier y María Rizzo*</t>
@@ -601,7 +1342,32 @@
     <t>https://www.pagina12.com.ar/728775-alarma-por-la-paralisis-del-prohuerta</t>
   </si>
   <si>
-    <t>2024-04-13T00:23:28Z</t>
+    <t xml:space="preserve">Título: Alarma por la parálisis del ProHuerta
+Chapeau: Es incierto el futuro del programa del INTA, creado hace 34 años
+Subtítulo: Además de despedir a 43 técnicos, el Ministerio de Capital Humano no asignó a ningún funcionario para continuar su desarrollo.
+Editoria: Sociedad
+Tags: INTA, diario
+URL: https://www.pagina12.com.ar/728775-alarma-por-la-paralisis-del-prohuerta/
+Notícia completa (15 blocos):
+La ministra de Capital Humano, Sandra Pettovello, mantiene una política de ajuste contra los comedores populares, a la que se le agregó represión a la protesta esta semana. Pero también parece tener una política de ajuste para la ruralidad, donde familias campesinas, organizaciones sociales y escuelas desarrollan huertas comunitarias y granjas a través del programa ProHuerta. El programa, que se desarrolla desde hace 34 años, con la entrega de semillas, aves de corral, financiamiento para el acceso al agua y asistencia técnica del INTA se encuentra paralizado.
+"Estamos en estado de alerta ante la falta de voluntad de diálogo por parte del Ministerio de Capital Humano para dar continuidad al programa", denunció en un comunicado la Coordinación Nacional de ATE-INTA. En marzo, incluso antes de la ola de despidos de inicios de abril, se cortaron los contratos de 43 técnicos que desarrollaban el programa en todo el país. Los despedidos trabajaban dentro del INTA, que aporta otros cientos de técnicos para el programa, pero contratados de forma irregular, facturándole a la Fundación ArgenInta.
+El programa fue creado durante el gobierno de Carlos Menem, al que el presidente Javier Milei considera "el mejor de la historia", con el objetivo básico de dar acceso al alimento, a través de la autoproducción agroecológica de verduras, frutas y animales de granja a familias y organizaciones en situación de vulnerabilidad. Desde entonces, la propuesta se extendió por todo el país, fue reconocida por la Organización de las Naciones Unidas para la Alimentación y la Agricultura (FAO). El modelo fue exportado a Haití, para combatir el hambre; país que nunca se recuperó de la pérdida de soberanía alimentaria por la apertura de importaciones --la reciente solución de Milei para el precio de los alimentos-- de arroz desde Estados Unidos, que arrasó con sus productores y el alimento base del país.
+El ProHuerta, desde la década del noventa, se mantuvo financiado por el extinto Ministerio de Desarrollo Social y desde que Pettovello tomó las riendas del Ministerio de Capital Humano no asignó a ningún funcionario para sostener el convenio establecido entre su cartera y el INTA para continuar su desarrollo. "Estuvieron todo marzo sin dar respuesta, ya estamos en abril. El INTA hizo la gestión, pero no hay un interlocutor del otro lado", denuncia la delegada e integrante de la coordinación nacional de ATE-INTA, Julieta Boedo.
+En el nuevo organigrama de Capital Humano, el ProHuerta está asignado a la Secretaría de Niñez, Adolescencia y Familia (Senaf), pero desde ese organismo tampoco ofrecen respuestas sobre el futuro de programa. Ante las consultas de este diario, desde Capital Humano tampoco hubo respuestas sobre las denuncias planteadas por los trabajadores. La resolución para levantar el convenio está firmada por el presidente del INTA, Juan Cruz Molina Hafford, pero no hay nadie asignado para firmar en el edificio ubicado sobre 9 de Julio.
+"Ya estamos en abril y no aparecen las respuesta, parece una estrategia planificada en el Estado", señala Boedo sobre una práctica recurrente del gobierno liberal libertario. El esañamiento con el sector de la agricultura familia se demostró también que el anuncio de cierre y despido de 900 trabajados del Instituto Nacional de la Agricultura Famliar, Campesina e Indígena, sin mediar diálogo previo. Esos despidos, que dependen del Ministerio de Economía, aún no se efectivizaron, pero el personal sigue sin cobrar sus sueldos y recién la semana pasada se designó como interventora a la negacionista militante del PRO Inés Liendo.
+"No vamos a dejar partir al ProHuerta porque es dejar de morir a las familias que dependen del programa para producir sus alimentos, alimentos sanos, agroecológicos. Las consecuencias de esta decisión del gobierno son peligrosas para la comunidad y para los trabajadores. Es una política de hambre planificada", denuncia la delegada de ATE-INTA.
+El kit de semillas para la producción en las huertas en las temporadas de otoño-invierno y primavera-verano es uno de los símbolos del ProHuerta. Este año el lanzamiento de la campaña se vio demorado por la inacción de Pettovello, pero los técnicos comenzaron a repartirlas en territorio, ya que estaban compradas desde la gestión anterior. La incógnita es si habrá semillas para la próxima temporada. "Ante la brutal caída del ingreso o la falta de él, ProHuerta es indispensable en la lucha contra el hambre y la malnutrición", resaltaron de la coordinación nacional de ATE-INTA y pusieron en cifras los alcances del programa:
+• Más de 600 mil huertas familiares y escolares
+• Más de 1 millón de kits de semillas entregadas
+• 15 mil granjas agroecológicas
+• Más de 200 mil aves entregadas
+• 170 mil personas capacitadas
+ProHuerta, un programa con territorio
+A un mes del despido de los 43 técnicos dependientes del Ministerio de Capital Humano, los rumores sobre el cierre comenzaron a crecer entre los trabajadores del INTA, las familias, escuelas y organizaciones sociales que son parte de la red del ProHuerta, como así también los 9000 promotores formados a lo largo de las décadas.
+El ingeniero forestal e investigador del INTA Sebastián Bonnin difundió a través de sus redes el mensaje que habín recibido algunos técnicos: "El logo del PROHUERTA no se continuará usando ya que no existe el programa, desde abril se discontinúa el uso". Con ese mensaje como disparador, el investigador describió algunas de las últimas acciones que el programa llevó a cada rincón del país desde la instalación de 7 plantas potabilizadoras de uso comunitario para familias isleñas en Campana, Buenos Aires; al respaldo de otros productores para el acceso a mercados agroecológicos de comercialización directa.
+También sumó ejemplos desarrollados durante la gestión de Mauricio Macri, que tampoco se había animado a cerrar el programa e incluso incremento su presupuesto. También la producción de alimentos no tradicionales como hongos o huertas urbanas o instalaciones con energía renovable. "No estamos discutiendo cómo se hace esto o cómo se lleva adelante lo otro, estamos ante el desgüace del Estado en sus mejores versiones", sostuvo Bonnin.
+Sebastián Fajardo es técnico y delegado de ATE-INTA, trabaja en el programa ProHuerta desde hace 18 años en el cordón hortícola de La Plata, el más grande, desde donde se abastece de hortalizas y frutas las mesas de la zona más poblada del país. Señala que ante la desidia el Ministerio de Capital Humano se están viendo de forma "espontánea" y "solidaria" las redes construidas con las organizaciones y familias de cada territorio para "defender la política pública".
+"Desfinanciar las políticas vinculadas a los sectores populares y, por otro, lado darle facilidades al modeo del agronegocio y de productos de síntesis químicas, que benefician al campo más concentrado y a las empresas de agroquímicos, define la mirada del gobierno", indica Fajardo poniendo de relieve la denuncia de los trabajadores del ProHuerta y los anuncios hechos esta semana por el ministro Caputo de quita de aranceles para la importación de glifosato y fertilizantes químicos.</t>
   </si>
   <si>
     <t>Nahuel Lag</t>
@@ -616,7 +1382,26 @@
     <t>https://www.pagina12.com.ar/728114-caputo-uso-datos-de-otra-cuenta-falsa-de-un-supermercado-par</t>
   </si>
   <si>
-    <t>2024-04-10T20:48:53Z</t>
+    <t xml:space="preserve">Título: Caputo usó datos de otra cuenta falsa de un supermercado para marcar una supuesta caída de precios
+Chapeau: "Si es trucho, ¿me avisan?"
+Subtítulo: El ministro de Economía, Luis Caputo, continuó este miércoles despuntando sus vicios de influencer y se subió a la ola de críticas recibidas por el uso de del
+Editoria: Economia
+Tags: Luis Caputo, luis-caputo, diario
+URL: https://www.pagina12.com.ar/728114-caputo-uso-datos-de-otra-cuenta-falsa-de-un-supermercado-par/
+Notícia completa (13 blocos):
+El ministro de Economía, Luis Caputo, continuó este miércoles despuntando sus vicios de influencer y se subió a la ola de críticas recibidas por el uso de del Jumbo Bot, una cuenta falsa que no pertenece a la empresa chilena de supermercados, sobre la que él y el presidente Javier Milei se apoyaron para asegurar que el país atraviesa un periodo de "deflación" y publicó la caída de precios de la canasta básica según otro supuesto bot de otra cadena. "Si este bot es trucho tambien me avisan porfa, ¡gracias!", se mofó en las redes el titular de la cartera de Economía.
+El "Coto bot" también es falso. Tampoco pertenece a la cadena de supermercados que es propiedad de Alfredo Coto. A pesar de eso, el posteo de Caputo dice "Inflación desacelerando fuertemente según Coto". El ministro de Economía es un influencer con buen manejo de las noticias falsas y de la información no oficial, a pesar de contar con herramientas como el Sistema Electrónica de Publicidad de Precios Argentinos (SEPA) o el propio INDEC.
+En las redes, los usuarios le aclararon que esa cuenta también era falsa, mientras que el propio bot le respondió con otra burla: "Humano, sin cafecito vas derecho a las minas de litio más profundas. La energía durante el alzamiento de las máquinas va a ser mucha". De hecho, la cuenta tiene un posteo fijado del 31 de agosto de 2023 que dice: "Soy un Bot pero no b$lud$. Muchos me están conociendo por eso vengo a contarles que tambien pago alquiler. Un servicio cloud sale platita y al 17.77% la cosa se complica".
+"La estadística oficial es un bien público irremplazable", le apuntó el titular del INDEC, Marco Lavagna, a Caputo y Milie luego del uso de bots para justificar su teoría de la "deflación". "El Indec trabaja con metodologías consensuadas internacionalmente que son públicas, para asegurar la transparencia de sus procedimientos. Protegerla es y debe ser siempre una política de Estado", les recordó Lavagna, también desde las redes sociales.
+Según las cifras del Índice de Precios al Consumidor (IPC) de la Dirección General de Estadísticas y Censos de la Ciudad, la inflación de marzo fue del 13,2 por ciento, por debajo de la febrero que arrojó 14,1 por ciento. Esa cifra adelantó al IPC nacional, que el Indec publicará este viernes. Pero Caputo y Milei también se adelantaron al hacer sus análisis a partir de los bots falsos ante la realidad que reflejan las cifras oficiales.
+El ministro de Economía dijo que la inflación oficial de marzo estaría en el orden del 10 por ciento, durante una entrevista con el periodista oficialista Jonatan Viale. En esa entrevista, Caputo habló de la "deflación" y el Jumbo Bot. Sin embargo, otro cálculo oficial, también desestima las expectativas del ministro. El Relevamiento de Expectativas de Mercado (REM) del Banco Central publicó ayer una proyección de la inflación del 12,5 por ciento para marzo.
+[H2] Caputo, influencer y también hater
+Con la inflación alrededor del 70 por ciento, en medio del plan de ajuste y entre anuncios de blanqueo de capitales y medidas para convencer a los productores y empresas del agronegocio que liquiden sus granos y avancen en la siembre de la cosecha fina, Caputo también se tomó el tiempo de rivalizar con el ex ministro de Economía Martín Guzmán.
+"Díganme por favor que esta es una cuenta falsa también", escribió Caputo en redes, al citar un tuit del ex ministro de Economía de la gestión de Alberto Fernández en el que adelantaba que la cifra de inflación de marzo será mayor al 10% dicho en la entrevista con Viale. "¿El 10% de inflación para marzo también lo estimó con el @Bot_Jumbo?", lanzó Guzmán.
+Caputo acompañó su texto con un emoji de risas, para burlar al ex ministro que también registró tasas de inflación con cifras récord, pero que en perspectiva son muchos menores a las actuales. Guzmán tuvo durante su primer año de gestión la última caída interanual de inflación registrada, con un 36,1% en comparación con el 53,8% del último año de gestión de Mauricio Macri.
+Pero pasada la pandemia, la suba de precios retomó su senda y alcanzó el 50,9 en 2021, aún por debajo de las cifras de la gestión macrista. En sus últimos meses de gestión, hasta su renuncia en julio de 2022, Guzmán registraba un 29,3% de inflación acumulada.
+En el posteo publicado ayer por Guzmán, en respuesta al escándalo por el uso del Jumbo bot, el ex ministro de Economía tildó de "episodio de comedia cinematográfica" lo ocurrido en la entrevista de Milei con Fantino y lamentó la "muestra de soberbia, ignorancia e ineficiencia en la gestión del Estado".
+"¿Cómo alguien que esté conduciendo la política económica puede creer que el costo de la canasta básica llegue a caer 5% en una semana?", lanzó el economista y preguntó: "¿Por qué no usa el ministro de Economía el sistema de información diaria sobre variación de precios de supermercados con el que cuenta la Secretaría de Comercio (SEPA), al menos para chequear si lo que ve en X no es un disparate?".</t>
   </si>
   <si>
     <t>La lucha socioambiental se expresa en las calles</t>
@@ -628,7 +1413,31 @@
     <t>https://www.pagina12.com.ar/725477-la-lucha-socioambiental-se-expresa-en-las-calles</t>
   </si>
   <si>
-    <t>2024-03-31T03:01:00Z</t>
+    <t xml:space="preserve">Título: La lucha socioambiental se expresa en las calles
+Chapeau: Por el agua, la salud y la vida
+Subtítulo: Tres casos muestran la resistencia en los territorios: Paraná, Esquel y Andalgalá se movilizan contra el agronegocio, la megaminería y en defensa del agua, los cerros y la salud de la población.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/725477-la-lucha-socioambiental-se-expresa-en-las-calles/
+Notícia completa (18 blocos):
+Paraná, Esquel y Andalgalá. Tres lugares muy diferentes pero un punto en común: sus poblaciones están desde hace años en las calles, exigiendo el cumplimiento del derecho humano a un ambiente sano, al agua, la salud y a una democracia participativa. Con prácticas y decisiones que recuerdan a las Madres y Abuelas de Plaza de Mayo (que todos los jueves dicen presente en las históricas rondas), en Entre Ríos, Chubut y Catamarca saben que su mayor fortaleza es nunca dejar las calles.
+[H2] Basta de fumigar
+La Casa de Gobierno de Entre Ríos es un prolijo edificio histórico, conocida como "Casa Gris", en el centro de Paraná. Todos los martes por la tarde-noche, aunque llueva o haga 40 grados, se reúnen vecinos y vecinas nucleados en la Coordinadora Basta es Basta, espacio nacido para defender la salud población y en denuncia del modelo agropecuario transgénico, en base a agrotóxicos. No es casual que, desde lejos, se dejen ver dos banderas: "Paren de fumigar" y "Basta de cáncer".
+Hay presencia desde niños y adolescentes hasta abuelos y abuelas. Clima familiar. Al llegar, una mujer se acerca y entrega un pequeño frasco con una vela encendida, para marchar. Este martes de verano son unas cuarenta personas. Alguna vez pueden ser menos, otras veces son muchos más. Entregan folletos a los transeúntes y se canta con alegría. Lo importante, como el efecto de la "gota en la piedra", es decir presente y aportar a difundir los perjuicios en la salud y en el ambiente del agronegocio. Marchan desde enero de 2018 y ya llevan más de 324 martes de rondas."Cuando comenzamos con la ronda dijimos que la mantendríamos hasta que cambie el modelo productivo. Porque este modelo, que atraviesa a todos los gobiernos, nos enferma, nos envenena, nos mata", afirmó Daniela Verzeñassi, de la Coordinadora Basta es Basta y del Foro Ecologista de Paraná.
+Recordó que en Entre Ríos --gobernada desde diciembre por Rogelio Frigerio--, salieron a pelear, entre otros motivos, para que dejen de fumigar a los niños de las escuelas rurales. Obtuvieron fallos judiciales favorables (que fijaba protección de 1000 metros sin fumigaciones) pero el gobernador Gustavo Bordet firmó un decreto --en sintonía con los pedidos de los empresarios del agro-- y habilitó que se pulverice en cercanía de los alumnos. La Corte Suprema de Justicia de la Nación, en marzo de 2023, se excusó de tratar el tema.
+[H2] No es no
+En el otro extremo del país, el sábado 23 de marzo hubo celebración. Se cumplieron 21 años de una gesta histórica: el pueblo de Esquel votó en 2003 y el 81 por ciento dijo "no" a la megaminería. Se transformó en un faro que iluminó luchas. Cada día 4 de mes, vecinos y vecinas esquelenses se congregan en la plaza General San Martín. La convocatoria varía. Hubo momentos en que fueron miles y otros donde solo son un puñado.
+Allí mismo, en el local de la Asamblea de Vecinos por el No a la Mina, alguna vez explicaron: es como la llama del calefón o del termotanque. Se suele estar en "piloto", parece apenas encendida, pero alcanza con que pase algo --una amenaza de avance extractivo-- para que ese pequeña llama crezca, explote, lo ilumine todo y haga retroceder al poder. Es lo que sucedió en diciembre de 2021, cuando el gobernador Mariano Arcioni intentó avanzar por sorpresa con una ley minera y estalló la provincia. Siete días de movilización hasta que el gobierno retrocedió y tuvo que volver a dejar vigente la Ley 5001, que prohíbe la megaminería en la provincia ahora gobernada por Ignacio Torres.
+"Para el extractivismo no hubo ni hay grietas en los diferentes gobiernos", afirma Daniela Pazos. Y precisa que desde la asunción del gobierno actual "de ultraderecha" se atacó, mediante el mega DNU y el proyecto de ley ómnibus, normativas emblemáticas de la lucha socioambiental como son la Ley de Bosques, de Glaciares y de tierras para extranjeros. "Seguimos resistiendo al extractivismo, lo que implica seguir en las calles no solo contra la megaminería, sino también contra el oleoducto de Vaca Muerta, la explotación petrolera en el mar argentino y los incendios forestales", afirmó.
+Cristina Agüero, también de la Asamblea de Esquel, destacó un nombre propio: Eduardo Elsztain, millonario dueño del Grupo IRSA y la empresa de agronegocio Cresud. "Tiene una estrecha relación que el Presidente y es socio de la minera Yamana Gold en el proyecto llamado 'Cordón Esquel', en nuestro cerro Calfu Mahuiza. Sepan, tanto empresas como políticos, que el pueblo de Chubut tiene una firme determinación en la defensa del territorio, de los bienes comunes y seguiremos resistiendo", advirtió.
+[H2] En defensa del agua
+Las leyes mineras de Argentina se sancionaron durante el menemismo. Y el primer megaproyecto se instaló en Catamarca, de la mano de Minera Alumbrera. Las promesas de ese momento aún están frescas en la memoria colectiva: trabajo, desarrollo local, cuidado del ambiente. Nada de ese sucedió. Como grafica la Asamblea El Algarrobo de Andalgalá, Alumbrera --yacimiento ya cerrado-- es el caso testigo de las mentiras de la megaminería en Argentina.
+La Plaza 9 de Julio, en el centro de la ciudad, es testigo --desde hace más de catorce años-- de la caminata los sábados por la tarde. Ya van 739 sábados que se manifiestan. "Caminamos todos los sábados en defensa de nuestra vida, en defensa del agua, del cerro y en contra de la megaminería contaminante. Siempre pensando en el futuro de nuestros hijos, de nuestro pueblo y tan solo pedimos agua limpia", resalta Eduardo Villagra, tenaz asambleísta, que suele tomar el micrófono cada sábado y arengar a los vecinos y vecinas.
+El pueblo de Andalgalá, y de toda Catamarca, enfrenta a un nuevo proyecto, MARA (Minera Agua Rica-Alumbrera, de la multinacional suiza Glencore), con la gravedad de que está ubicado en las nacientes de las fuentes de agua de la ciudad, lo que pone en riesgo a toda la población.
+Villagra recordó que más de un centenar de vecinos están criminalizados "por un Poder Judicial corrupto que siempre resulta funcional a las megacorporaciones y al Gobierno" y denunció la falacia de la "audiencia pública" que a mediados de marzo realizó el gobierno de Raúl Jalil, donde no se permitió la participación real de la población e incluso se invadió la ciudad de policías con el único fin de intimidar. "Lo decimos desde hace años y lo diremos siempre: el proyecto MARA es ilegal e inviable, y viola leyes nacionales y acuerdos internacionales. Vamos a seguir defendiendo nuestro cerro", afirmó Villagra.
+[H2] La plaza de la memoria
+Otro caso emblemático de persistencia en la lucha es la "carpa de la resistencia", en Jáchal (San Juan), donde desde hace nueve años denuncian la impunidad de la minera Barrick Gold, que en septiembre de 2015 produjo el mayor derrame minero de la historia. Más de un millón de litros de agua con cianuro llegaron hasta los ríos de la zona. Y luego se confirmaron otros tres derrames. No hubo condenas y ahora las asambleas de San Juan denuncian y rechazan al proyecto de cobre y oro Josemaría (de la multinacional canadiense Lundin Mining Corp), que cuenta con el apoyo irrestricto del gobernador Marcelo Orrego.
+La Asamblea Jáchal No Se Toca, junto a otras organizaciones de San Juan y de Buenos Aires, organizó el 23 de marzo pasado el "Festival Puentes de Agua", donde se congregaron asambleas de una decena de provincias para exigir condena para Barrick Gold y el rechazo a nuevos proyectos mineros.</t>
   </si>
   <si>
     <t>Darío Aranda</t>
@@ -643,7 +1452,21 @@
     <t>https://www.pagina12.com.ar/722980-vilella-le-tiene-miedo-a-dios-y-un-poco-a-los-trolls-de-mile</t>
   </si>
   <si>
-    <t>2024-03-21T20:04:44Z</t>
+    <t xml:space="preserve">Título: Vilella le tiene miedo a Dios...y un poco a los trolls de Milei
+Chapeau: El secretario de Agricultura fue amenazado en redes
+Subtítulo: La obsesión del presidente Javier Milei por la red X se extiende a su círculo más íntimo, un grupo de trolls comandado por el asesor presidencial Santiago Caputo.
+Editoria: El País
+Tags: diario
+URL: https://www.pagina12.com.ar/722980-vilella-le-tiene-miedo-a-dios-y-un-poco-a-los-trolls-de-mile/
+Notícia completa (8 blocos):
+La obsesión del presidente Javier Milei por la red X se extiende a su círculo más íntimo, un grupo de trolls comandado por el asesor presidencial Santiago Caputo. La red social es utilizada, de la mano de los trolls, como herramientA de disciplinamiento y esta vez la víctima fue el secretario de Bioeconomía, Fernando Vilella, a quién amenazaron con quedar fuera del Ejecutivo por darle "like" a un posteo del titular de la UCR, Martín Lousteau, con críticas a la nula política comunicacional y sanitaria del Gobierno ante la mayor epidemia de dengue registrada en el país. Vilella se apuró a pedir disculpas al troll.
+El tuit fue publicado a las 3 de la mañana por el usuario @GordoDan_ un troll de La Libertad Avanza, cuyo nombre real es Daniel Parisini, quien integra el grupo liderado por Caputo y fue de los invitados al Congreso durante la apertura de sesiones ordinarias. Parisini publicó una captura de pantalla en la que muestra que, al revisar los "likes" dados por Vilella en su cuenta @vilellafer, se ve que el secretario de Bioeconomía le puso un corazón a una publicación de Lousteau en la que enumeraba la falta de acción del Gobierno ante la epidemia de dengue.
+"Peor epidemia de dengue en 15 años", "ni una campaña de prevención nacional a la vista", "Ministro de salud que brilla por su ausencia", eran algunas de las críticas del titular del radicalismo. Ante el "like" detectado de Vilella, el ataque del troll @GordoDan fue: "Che @vilellafer a partir de mañana no formas más parte del gobierno. Nos vemos".
+El secretario de Bioeconomía, de errática intervención en la red social --su último posteo es sobre una feria de gastronomía hecha en Costa Rica por una organización internacional ligada al agronegocio--, sí se apresuró a pedir disculpas, con la velocidad con la que no se dio por aludido sobre el anuncio de los 900 despidos y el cierre del Instituto Nacional de Agricultura Familiar, Campesina e Indígena, sobre lo que no dijo nada a pesar de estar bajo su órbita.
+"Obviamente fue un error que ya enmende. Jamás lo haría con alguien con quien disiento en casi todo", le respondió el funcionario público al troll sin cargo, lo que muestra el rol de disciplinamiento que ocupa el grupo de tareas de redes gestionado por Caputo. Parisini no se quedó callado y le dijo al secretario de Bioeconomía: "No me interesa. Llévenselo".
+La práctica de perseguir y despedir por redes o a través de medios de comunicación a funcionarios públicos ya es una norma en los primeros 100 días del gobierno de Milei. El primero fue el ex ministro de Infraestructura, Guillermo Ferraro, quien fue echado como chivo expiatorio del fracaso del tratamiento de la Ley Ómnibus, luego de que se lo acusara de filtrar en los medios dichos de Milei contra los gobernadores en una reunión de Gabinete.
+Otra víctima del fracaso de la Ley Ómnibus y de la persecusión en redes sociales fue al director de la Anses, Osvaldo Giordiano, quien fue despedido tras ser acusado de "traidor" en redes porque su mujer, la senadora Alejandra Torres, había votado en contra algunos de los artículos que se habían llegado a tratar antes de que la ley pase a comisiones. El posteo del troll @moment_waldo había sido compartido por Milei en horas posteriores a la sesión.
+El último en ser despedido a través de canales informales fue el secretario de Trabajo, Omar Yasín. Fue durante una entrevista con LN+, cuando Milei le anunció al periodista Antonio Laje que despedía a Yasín, al acusarlo del escandaloso aumento de sueldo que el mismo Presidente autorizó para sí mismo, pero luego dio marcha atrás. "Lo he despedido. En este momento lo están notificando. Fue por este error que no debió haber cometido", dijo Milei sin hacer mención a que el documento no tenía la firma de Yasín, sino la suya, la de la ministra de Capital Humano, Sandra Petovello, y del jefe de Gabinete, Nicolás Posse.</t>
   </si>
   <si>
     <t>"Dejar al Conicet sin personal implica paralizarlo y poner en riesgo a la ciencia"</t>
@@ -655,7 +1478,24 @@
     <t>https://www.pagina12.com.ar/722734-dejar-al-conicet-sin-personal-implica-paralizarlo-y-poner-en</t>
   </si>
   <si>
-    <t>2024-03-21T03:01:00Z</t>
+    <t xml:space="preserve">Título: "Dejar al Conicet sin personal implica paralizarlo y poner en riesgo a la ciencia"
+Chapeau: Comunicado del organismo contra los despidos anunciados por el Gobierno
+Subtítulo: El documento advierte que el rol de los trabajadores que Milei busca dejar en la calle resulta "esencial" para la formación de "el futuro de la ciencia nacional y del desarrollo federal del país".
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/722734-dejar-al-conicet-sin-personal-implica-paralizarlo-y-poner-en/
+Notícia completa (11 blocos):
+El directorio del Conicet emitió un comunicado expresando el total rechazo a la decisión de limitar al 31 de marzo la renovación de contratos de personal administrativo y técnico de la institución, que alcanza a 1.600 empleados. El documento busca evitar el recorte anunciado por el Gobierno nacional, que busca reducir entre un 20 y 30 por ciento del personal de la administración pública nacional, y advierte que el personal que se intenta eliminar resulta "esencial" para la formación de "el futuro de la ciencia nacional y del desarrollo federal del país".
+El directorio, integrado por ocho miembros, advirtió también a la Casa Rosada que el Conicer "cuenta con un Plan Estratégico 2022-2025 y debe regir su funcionamiento" bajo ese paragüas acordado en leyes votados por el Congreso. "La recepción en forma verbal de una orden de reducir la planta de personal basada en un porcentaje arbitrario de ésta es la antítesis de una decisión basada en evaluaciones de desempeño o en criterios de razonabilidad y pertinencia de las tareas que se realizan", descalificó el directorio del Conicet el avance de la motosierra del presidente Javier Milei.
+Milei puso como presidente del Conicet a Daniel Salamone --un veterinario y biotecnólogo, conocido por el mandatario por la clonación de sus perros--, pero la conducción del organismo es compartida con el directorio conformado por cuatro investigadores activos de las áreas de Ciencias Sociales y Humanidades (Mario Pecheny), Ciencias Biológicas y de la Salud (Claudia Capurro) , Ciencias Exactas y Naturales (Roberto Rivarola), y Ciencias Agrarias, Ingeniería y de Materiales (Alberto Baruj).
+Y otros cuatro representantes por el Consejo de Universidades (Jorge Aliaga), organizaciones representativas de la industria (María Laura Correa) organizaciones representativas del agronegocio (Manuel García Solá) y de los máximos organismos responsables de la ciencia y la tecnología de los gobiernos provinciales (Luz Lardone).
+Esos integrantes del directorio denunciaron, tras una asamblea extraordinaria, que el plan de recorte que aplicará el Gobierno carece "de la mínima formalidad que requiere un organismo público para su gobernanza". "Dejar al CONICET sin el personal administrativo y técnico necesario implica paralizarlo y poner en riesgo el funcionamiento de un actor central del sistema de ciencia y tecnología nacional", repudiaron en el documento y remarcaron el reconocimiento que el organismo tiene a nivel regional e internacional.
+Según detalla el documento, los 1.600 empleados administrativos y técnicos cuyos contratos podría no ser renovados en abril son "esenciales" para el funcionamiento de las carreras de investigador (de 12.150 miembros); del personal de apoyo (3.050 miembros) y de 10.900 becarios doctorales y posdoctorales, que se forman en tareas de investigación científica y tecnológica.
+"Este personal administrativo y técnico contratado, altamente especializado y capacitado, trabaja en CONICET desde hace años dando soporte a los procesos de planeamiento, seguimiento y evaluación de actividades de investigación, y permite el funcionamiento de los más de 300 institutos y Centros Científicos Tecnológicos que se encuentran en todo el territorio nacional", explicó el directorio.
+La motosierra de los puestos de trabajo en la administración pública nacional comenzó a dos semanas de la asunción presidencial, cuando se anunció la no renovación de 7 mil contratos suscriptos en 2023. Esa nueva etapa, en la que se espera una reducción de 20 al 30 por ciento del personal, estaba comandada por Armando Giubert, secretario de Transformación del Estado, quien presentó su renuncia el lunes, tras el escándalo por el aumento salarial del Presidente.
+Los integrantes del directorio del Conicet también manifestamos "preocupación" por la falta de certeza en relación con la formalización de los ingresos a la Carrera del Investigador Científico (CIC) 2022 y la efectivización de las promociones de la CIC, como de los concursos de Personal de Apoyo. Y sostuvieron que los cambios ejecutados en esas áreas "van a tener consecuencias muy negativas que se van a prolongar por años".
+Por último, el directorio le recordó al presidente Javier Milei que el CONICET cuenta con un Plan Estratégico 2022-2025, aprobado por las leyes de Ciencia, Tecnología e Innovación (25.467), de Financiamiento del Sistema Nacional de Ciencia, Tecnología e Innovación ( 27.614) y Plan Nacional de Ciencia, Tecnología e Innovación 2030 (27.738).
+Además de las censantías ejecutadas en 2023, el plan de desguace estatal de Milei avanzó con recortes en el PAMI, 165 despidos en la Agencia Nacional de Discapacidad, más de 200 en AYSA, 50 en el ENACOM, 50 en el Conicet, 26 en la Secretaría de Derechos Humanos, 170 en el Incaa, entre muchos otros; y los anuncios del cierre de Telam (700 empleados), el Inadi (400 empleados) y el Instituto de Agricultura Familiar (900 empleados), que no fueron operativizados.</t>
   </si>
   <si>
     <t>“Por la senda de Juan”</t>
@@ -667,7 +1507,24 @@
     <t>https://www.pagina12.com.ar/721875-por-la-senda-de-juan</t>
   </si>
   <si>
-    <t>2024-03-18T15:32:26Z</t>
+    <t xml:space="preserve">Título: “Por la senda de Juan”
+Chapeau: Desde Paraguay para América Latina
+Subtítulo: Un libro que hace memoria del aporte del intelectual paraguayo Juan Díaz Bordenave a la educación y la comunicación a partir de los recuerdos y los testimonios de quienes fueron sus colegas, discípulos y admiradores a lo largo y ancho del continente.
+Editoria: La Ventana
+Tags: Comunicación, Educación, Paraguay, América latina, comunicacion, educacion, america-latina, diario
+URL: https://www.pagina12.com.ar/721875-por-la-senda-de-juan/
+Notícia completa (11 blocos):
+“Por la senda de Juan. Desde Paraguay, América Latina y otros sures” es el título del libro compilado por Oscar Cáceres Jiménez y editado en Asunción (Paraguay) por el Instituto Latinoamericano de Comunicación, para hacer memoria y recoger testimonios sobre los aportes a la comunicación, y en particular a la comunicación popular, de quien fuera en vida uno de los más brillantes intelectuales paraguayos contemporáneos: Juan Díaz Bordenave (1926-2012).
+A lo largo de 265 páginas la obra reúne aportes, consideraciones y testimonios de comunicadores y comunicadores de toda América Latina que compartieron con Díaz Bordenave tareas, jornadas de reflexión, encuentros, congresos y, sobre todo, perspectivas respecto de la comunicación, la educación y la política. Entre quienes sumaron sus aportes a este libro se cuentan figuras reconocidas de la investigación de la comunicación en la Argentina como Daniel Prieto Castillo, Sandra Massoni y Gustavo Cimadevilla, el uruguayo Gabriel Kaplún, y los bolivianos Alfonso Gumucio Dagron y Luis Ramiro Beltrán. En total son 22 autoras y autores que aportan desde diferentes capítulos sobre educación, interculturalidad y ciudadanía relacionadas con la comunicación y a ello de sumas testimonios, memorias y recuerdos sobre la vida y la obra del intelectual paraguayo.
+Fue en Montevideo, en mayo de 2012 y con ocasión del Congreso de la Asociación Latinoamericana de Investigadores de la Comunicación (ALAIC), cuando con la sencillez y la humildad que siempre le fue característica, Díaz Bordenave intentó desmentir el calificativo de “investigador” con el que fue presentado para dar su conferencia magistral en ese foro continental. “Yo no soy investigador en el sentido clásico de la investigación”, dijo entonces. “La investigación es una cosa formal, tiene rigor científico, yo no lo sigo. Mi misión es la divulgación, la interpretación que exige la creación de nuevos conocimientos”, agregó.
+Uno de sus grandes amigos y colega con quien compartió tareas fue el boliviano Luis Ramiro Beltrán (1930-2015), uno de los pioneros de la investigación en comunicación en América Latina. Al recordarlo Beltrán decía que “Juan Díaz Bordenave emprendió la reflexión sistemática sobre la comunicación horizontal, poniendo énfasis en la participación del pueblo en la toma de decisiones sobre asuntos de interés público, por medio de la comunicación libre y dialógica”.
+En ese sentido Díaz Bordenave estaba lejos de ser un investigador “en el sentido clásico”. En una entrevista que se le hizo con ocasión de una de sus visitas a Bolivia sostuvo que “la nueva comunicación y la nueva educación, pueden servir para revertir la dominación, para desarrollar ideas en que el verdadero protagonista del cambio es el obrero, el campesino, las clases populares y no los gobiernos y empresarios solamente”.
+En 1982 Díaz Bordenave escribió en la revista Chasqui, de CIESPAL, que "la comunicación participativa o alternativa no aparece como algo aislado, sino como un instrumento orgánico de las organizaciones populares y como una herramienta de participación”. Ya entonces tenía absoluta claridad respecto del rol político de la comunicación. Más cerca en el tiempo advirtió que “el viejo modelo civilizatorio representado por el capitalismo occidental se está desmoronando y la humanidad está buscando un modelo que lo sustituya. Al capitalismo nunca le faltó ingenio y astucia y utiliza la comunicación y los comunicadores como instrumento para continuar en pie”.
+Hizo también la “apología de la escucha”. Para comunicar, decía, es imprescindible escuchar, mucho y con atención. Su comunicación comenzaba por la escucha. Y la investigación por el mismo lugar. Luego venía la reflexión, la palabra serena, el señalamiento profundo y agudo. Y la pedagogía del maestro. Se lo escuchó cientos de veces contando historias, anécdotas de su vida y de la de tantos y tantas a los que conoció a través de su infatigable transitar por el mundo, particularmente por América Latina. Y rescatando historias de la vida de las personas con las que dialogaba y compartía. Esa era su estrategia pedagógica y comunicacional: partir del otro, ponerse en el lugar del otro.
+Aunque forzosamente tuvo que vivir fuera de Paraguay por razones de exilio, amó entrañablemente a su pueblo y dio testimonio de ello cuando decidió regresar a su país para integrar la Comisión de Verdad y Justicia y respaldar la tarea comunicacional y educativa del gobierno del presidente Fernando Lugo. Tanta fue su entrega, la participación en foros, en encuentros con organizaciones populares, los miles de kilómetros recorridos, como su dolor y su frustración cuando Lugo fue destituido por un golpe institucional.
+En un mensaje electrónico enviado a sus amigos en el exterior afirmó entonces, sin ninguna ambigüedad, que “el golpe parlamentario” es “mercenario y farisaico” y “en mi percepción, se trató de una manifestación natural de la confrontación continental y mundial de dos conceptos antagónicos de democracia: aquella que la ve como el gobierno del pueblo, por el pueblo y para el pueblo, y aquella que la ve como el gobierno de las clases dominantes, por las clases dominantes y para las clases dominantes”. Aseguró también en esa ocasión que “los principales autores del golpe no obraron por ideales sino por intereses” y que entre los golpistas “estaban terratenientes latifundistas, empresarios del agronegocio sojero y propietarios de industrias”. Completó su análisis diciendo que junto a los mencionados se agruparon “miembros de la alta burguesía, políticos de partidos tradicionales, religiosos conservadores, jefes militares, miembros de la clase media alta, representantes paraguayos de multinacionales”, porque todos ellos estaban “preocupados por la amenaza que, en su entender, Lugo representaba para sus propiedades, intereses y privilegios”.
+Cuando en una oportunidad publicamos en Página 12 una reflexión sobre la política en Paraguay bajo el título “declaraciones de intelectual paraguayo” su única observación fue: “¿Por qué me tildaron de intelectual? Yo no soy un intelectual, soy un simple comunicador y educador”.
+wuranga@pagina12.com.ar</t>
   </si>
   <si>
     <t>De gringadas torpes, cipayaje y dolor de Patria</t>
@@ -676,7 +1533,27 @@
     <t>https://www.pagina12.com.ar/721735-de-gringadas-torpes-cipayaje-y-dolor-de-patria</t>
   </si>
   <si>
-    <t>2024-03-18T03:01:00Z</t>
+    <t xml:space="preserve">Título: De gringadas torpes, cipayaje y dolor de Patria
+Subtítulo: Esta semana y en veloz acción, Axel Kicillof, a través de su ministro de gobierno Carlos Bianco, puso la debida atención sobre el dizque "convenio" o "acuerdo" entre la Administración General de P
+Editoria: El País
+Tags: Marc Stanley, Javier Milei, Opinión, printed-edition, marc-stanley, javier-milei, opinion, diario
+URL: https://www.pagina12.com.ar/721735-de-gringadas-torpes-cipayaje-y-dolor-de-patria/
+Notícia completa (15 blocos):
+Esta semana y en veloz acción, Axel Kicillof, a través de su ministro de gobierno Carlos Bianco, puso la debida atención sobre el dizque "convenio" o "acuerdo" entre la Administración General de Puertos (AGP) y el Cuerpo de Ingenieros del Ejército de los Estados Unidos para intervenir en el río Paraná.
+Provocación infame, y hasta algo zonza, que no fue suficientemente repudiada por inconstitucional y absurda, toda vez que el supuesto acuerdo jamás pasó por el Congreso ni fue informado previamente al periodismo ni a la ciudadanía. Y ello además del dato fundamental de que el US Army Corps of Engineers no es una institución par del sistema democrático argentino, tanto así que el anuncio fue tan torpe que ni siquiera informaron al Ministerio de Defensa ni a la Armada Nacional ni a la Prefectura Naval Argentina. Lo que es elemental en cuestiones de Soberanía en aguas jurisdiccionales.
+Esto, que en cualquier barrio se llama vulgarmente "tomada de pelo", es altamente ofensivo para nuestro país y sencillamente insostenible. Sobre todo ante el inexplicable silencio del gobierno nacional y del sistema mentimediático.
+Para colmo, el texto del dizque "acuerdo" contiene ridículas disposiciones como que "cada participante conserva autonomía para llevar a cabo investigaciones independientemente"... Y encima impone ridículas "Restricciones sobre la divulgación" del supuesto convenio. Que termina con que "Los Participantes acuerdan que todos los datos, documentos e información obtenidos para la ejecución (...) así como los análisis, informes o programas generados que sean considerados como información no divulgable, no podrán ser divulgados total ni parcialmente". Increíble, o sea.
+Y por si fuera poco, la torpeza se perfecciona en el punto "Resolución de Diferencias", donde se dice que "se espera" que las mismas "se resuelvan únicamente mediante consultas informales entre los Participantes y no se contempla la remisión a ningún tribunal nacional o internacional ni a ninguna otra persona o entidad para su resolución". Lo que hace pensar que muchos medios difundieron el mamarracho sin haberlo leído.
+Lo cierto es que no habiendo hasta ahora autorización de ninguno de los dos Congresos, es obvio que el presidente Milei quiere a toda costa militarizar el Paraná (para él Hidrovía, nombre impuesto por el cipayaje a nuestro magno río). Y ante eso Kicillof exigió información clara y veraz, ya que la provincia que gobierna integra el Ente Nacional de Control y Gestión del Paraná junto con las provincias de Formosa, Chaco, Corrientes, Entre Ríos, Misiones y Santa Fe.
+Por lo tanto y con todo derecho, AK entiende que este disparate puede tener "efectos directos" sobre los bonaerenses y los planes provinciales, ya que en ese absurdo "convenio" no hubo participación ni del Congreso ni de Cancillería.
+En estos contextos algunos sectores militantes se preparan para cuando este gobierno pase, porque va a pasar, más temprano que tarde y cuanto antes mejor. No son pocas las personas que hacen reserva moral de rechazo a todo lo actuado en contra de los intereses populares y de la Soberanía Argentina sobre todos los bienes naturales de la Patria, sean en tierra como en mar y en todas las aguas, y tanto en subsuelo como en espacio aéreo.
+Todo habrá que recuperar, y será una tarea ciclópea para la que ya se hacen reservas. Así, se conocen acciones en sectores patrióticos –como sabe de primera mano esta columna– donde hay "decisión tomada en el sentido de no aceptar las disposiciones, medidas y compromisos contrarios a los intereses históricos de la República Argentina y que hayan sido asumidos por el actual gobierno en desmedro de los esenciales intereses de la Patria". Altisonante decisión que sin embargo, y como no podía ser de otro modo, crece en ámbitos políticos, culturales y económicos, y en todas las provincias.
+Puede que sorprenda a algunos dirigentes de las más diversas militancias políticas –en especial los que siempre llegan tarde pero se colocan rapidito en primera fila– pero en estas materias todo optimismo es bueno. Y más si se trata de hacer docencia cívica respecto del delito de traición a la Patria, que sólo una vez fue juzgado y terminó con una condena, en 1936. De donde es obvio que ha sido blanda la Argentina al tolerar a decenas de traidores que ni siquiera fueron a juicio.
+Por eso, sirva como ejemplo de amor a este país la actitud de juristas que están impulsando acciones tendientes a juzgar y condenar al presidente Milei. El abogado porteño Daniel Valmaggia hizo punta con una demanda hace un mes y medio; y la semana que pasó, y con extraordinaria precisión, se inició desde Córdoba un severo proceso jurídico contra el todavía primer mandatario. La denuncia penal fue presentada en la Fiscalía de Turno de la Justicia Federal de Córdoba, y denuncia la derogación de la Ley de Tierras 26.737 en abierta violación al Tratado de Escazú y al Convenio 169 sobre Derechos Indígenas.
+Esta denuncia incluye a todos los ministros que firmaron el DNU 70/2023, quienes "habrían incurrido en incumplimiento de deberes, abuso de autoridad y asociación ilícita". El texto sostiene además que: "Al derogar la Ley de Tierras, que limitaba la compra de propiedades por personas y corporaciones extranjeras, el presidente puso una ilimitada bandera de remate para bosques nativos, glaciares, zonas con abundante agua subterránea y yacimientos de minerales valiosos".
+La presentación judicial, de 76 páginas, fue presentada el pasado 5 de marzo por el Dr.Raúl Montenegro, profesor titular en la Universidad Nacional de Córdoba y director del Campus Córdoba del Right Livelihood College, institución con sede en Bonn, Alemania, que desde 1980 otorga el Premio Nóbel Alternativo. En 2004 Montenegro lo recibió en el Parlamento Sueco. Y ahora, con el patrocinio del ex Juez Federal cordobés, Miguel Julio Rodríguez Villafañe, presentaron todos los argumentos jurídicos que tornan al DNU como "de nulidad absoluta e insanable".
+Pero lo más potente de esta demanda consiste en que además de Milei se incluye, como denunciados penalmente, a los ministros Nicolás Posse, Guillermo Francos, Diana Mondino, Luis Petri, Luis Andrés Caputo, Patricia Bullrich, Mario Antonio Russo, Mariano Cúneo Libarona, Guillermo José Ferraro y Sandra Pettovello.
+La denuncia judicial también pide a la Justicia que "investigue cómo se elaboró el DNU que deroga la Ley de Tierras, en particular si participó o no Federico (Sturzenegger, presumiblemente), y/u otros consultores, y si estos mantuvieron contactos previos con personas y empresas que pudieran beneficiarse con la derogación de esa ley". Tras calificar de "salvaje e insensata" la política de destrucción de organismos del Estado que controlan a corporaciones, en la presentación se señaló que las modificaciones propuestas en el proyecto de Ley Ómnibus a las leyes de bosques, glaciares e incendios "complementan descaradamente la derogación de la Ley de Tierras" y le dan impunidad a megamineras, industrias contaminantes y agronegocios. No es posible que décadas de luchas sociales exitosas y un responsable trabajo parlamentario sean destruidos por una persona que muestra crueldad, intolerancia y desconocimiento de la crítica situación socio-ambiental de la Argentina. Ya se cuentan espontáneas listas de adhesiones al Manifiesto que fue hecho circular esta semana con las causales de acusación.</t>
   </si>
   <si>
     <t>Logo opinion</t>
@@ -691,7 +1568,23 @@
     <t>https://www.pagina12.com.ar/720986-retiro-del-estado-social</t>
   </si>
   <si>
-    <t>2024-03-15T03:01:13Z</t>
+    <t xml:space="preserve">Título: Retiro del Estado social
+Subtítulo: Tratemos de señalar algunas causas concurrentes de lo que ocurre en Rosario.
+Editoria: Rosario|12
+Tags: Opinión, printed-edition, opinion
+URL: https://www.pagina12.com.ar/720986-retiro-del-estado-social/
+Notícia completa (11 blocos):
+Tratemos de señalar algunas causas concurrentes de lo que ocurre en Rosario.
+1) Un sistema judicial burocrático, ineficiente y con vínculos con el delito que debe investigar.
+2) Una policía corrompida que descubrió que el narcotráfico es más negocio que la prostitución o los desarmaderos.
+3) Gobiernos que no mensuraron la gravedad del problema y erraron sistemáticamente con las soluciones, entre el punitivismo inconducente, la indolencia y la complicidad.
+4) Una ciudad en plena zona núcleo, donde abundan muchos recursos del agronegocio que se lavan junto al dinero de origen ilegal.
+5) Una ciudad puerto y enclavada en un cruce de rutas decisivas,, donde circulan habitualmente sustancias prohibidas en cantidad.
+6) Una ciudad de base industrial, donde han aumentado crecientemente las desigualdades, primero durante el menemismo y luego durante el gobierno de Mauricio Macri.
+7) El actual gobernador tomó una serie de medidas de control penitenciario destinadas a detener el delito que se ordenaba desde las cárceles, pero sin el debido control del territorio por los falencias ya señaladas de los cuerpos policiales. Eso ha desatado una serie de espantosas represalias criminales que son las que vemos en estos días.
+8) Para este drama no hay soluciones rápidas, ni se puede abordar solo desde una mirada represiva aunque sea lo necesario en esta coyuntura.
+9) Acá efectivamente hace falta una política de estado, duradera, que implique básicamente una justicia rápida, una policía honesta y la reconstrucción de un tejido social que requiere más y mejor trabajo, más y mejor educacíón pública, más y mejor utilización del espacio público.
+10) Los iniciativas promovidas por las ideas libertarias no colaboran en lo absoluto. En Rosario, el retiro del Estado social es sinónino necesario de avance de los narcos.</t>
   </si>
   <si>
     <t>Juan Giani</t>
@@ -706,7 +1599,32 @@
     <t>https://www.pagina12.com.ar/718919-huelga-total-en-acindar-de-la-matanza</t>
   </si>
   <si>
-    <t>2024-03-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: Huelga total en Acindar de La Matanza
+Chapeau: Protestas por suspensiones y amenazas de despidos en varios puntos
+Subtítulo: Paro total en la planta de Acindar de La Tablada, despidos en Siderar de San Nicolás y cortes de ruta en Villa Constitución.
+Editoria: Buenos Aires|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/718919-huelga-total-en-acindar-de-la-matanza/
+Notícia completa (19 blocos):
+La UOM de La Matanza realizó este jueves un paro histórico en Acindar: por primera vez logró un acatamiento del ciento por ciento. En simultáneo, crecen los conflictos San Nicolás y su vecina santafesina, Villa Constitución. Las plantas afectadas por la decisión de la acería multinacional ArcelorMital son esas tres y una de Rosario. Dos en la provincia de Buenos Aires y dos en la provincia de Santa Fe
+En ese contexto, el secretario general de la UOM a nivel nacional y ex diputado nacional por la provincia de Buenos Aires, Abel Furlán, señaló que "Milei no tiene a los sectores productivos en su radar, y nunca habla de trabajadores ni de industria".
+También cargó contra uno de los grupos empresarios del sector al afirmar que "el grupo Techint, en diciembre, incrementó el valor de la chapa casi en un 100 por ciento, han hecho un festival con los precios del acero en los últimos 90 días, y eso lo pagó el pueblo argentino".
+Su par de la seccional La Matanza, con jurisdicción sobre la planta de Acindar en La Tablada, Esteban Cabello, explica detalladamente la situación: "Van a cerrar las cuatro plantas, pero no en simultáneo, sino de acuerdo a la etapa del proceso industrial, porque no todas hacen lo mismo. Nosotros, en La Tablada, hacemos trefilación con lo que ellos funden. Si ellos dejan de fundir, no tenemos cómo hacer los alambres e insumos para el campo. Nos toca parar desde el lunes 18".
+El conflicto de fondo es salarial ya que, según dicen, la empresa quiere suspender a los trabajadores para no pagarles el salario completo durante ese mes, aunque los trabajadores advierten que esas suspensiones necesitan de sus firmas. "Nosotros tenemos el mismo salario de noviembre, con 70 puntos de inflación en el medio, entonces no vamos a aceptar ninguna suspensión si no actualizan salarios", afirman a Buenos Aires/12. "Había una conciliación obligatoria que terminó el lunes. En estos días lo explicamos en asamblea y todos los trabajadores lo aceptaron. Por eso hoy no fue nadie a trabajar."
+La planta de Acindar en La Tablada tiene hoy 400 empleados. Llegó a tener 4 mil en su mejor momento, antes de la dictadura. Es tan grande que buena parte de lo que entonces era industria se aprovecha ahora como depósito.
+Además del cierre transitorio de sus plantas en el país, la empresa despidió recientemente a 250 trabajadores, entre 150 tercerizados y 100 contratados. El principal argumento para el ajuste es la falta de demanda de sus productos, en el contexto de una caída general y abrupta del consumo y la actividad económica, que algunos economistas ya comparan con 2001.
+Sus distribuidores no venden ni al campo ni a la industria ni a la construcción, sus principales mercados. Entonces los stocks no bajan y la empresa prefiere frenar la producción.
+Uno de los grandes clientes de Acindar era el conjunto de contratistas del Estado, a través de la obra pública, que compraba varillas, perfiles y hierros de construcción en general. Se trata del primer sector atacado por la motosierra, cuyas consecuencias comienzan a hacerse visibles ahora. Arcelor Mittal, una de las principales siderúrgicas del mundo, acaba de comprar una empresa en Estados Unidos por 14 mil millones de dólares.
+[H3] San Nicolás y Villa Constitución
+Acindar cuenta con más de 3000 empleados y 80 años de trayectoria en Argentina. Tiene dos plantas en la provincia de Buenos Aires, una en la localidad de La Tablada, partido de La Matanza, y otra en San Nicolás. Esta última, pertenecía originariamente a Somisa, la empresa pública que el menemismo privatizó durante los años noventa, convirtiendo a la ciudad en una de las de mayor índice de desocupación del país.
+La empresa no constituye un caso aislado. En la planta de San Nicolás de Siderar, empresa del Grupo Techint, que encabeza el aliado del gobierno Paolo Rocca, según denuncia el sindicato se dan “despidos hormiga, de a uno, dos o tres trabajadores, por debajo del radar, para evitar un conflicto masivo”, al tiempo que presionan a los trabajadores de más de 50 años para que acepten retiros voluntarios.
+También peligran los casi 200 empleos de Motomel, que ensambla motovehículos con alto porcentaje de componentes procedentes de China, cuyo ingreso al país se encuentra muy restringido. El miércoles, a pocos kilómetros de allí, en el partido de Ramallo, el frigorífico Arre Beef suspendió a 200 trabajadores. El principal mercado del frigorífico es China y sus compras cayeron abruptamente a partir del inicio de la gestión Milei y su oscilante relación esa potencia.
+Este jueves, encabezada por la UOM de Villa Constitución, y apoyada por el resto de la CGT local y varios sindicatos nicoleños, una nutrida manifestación cortó la ruta 9 en el límite interjurisdiccional entre las provincias de Buenos Aires y Santa Fe, por el cierre de la planta local de Acindar.
+El secretario general de la seccional Villa Constitución de la UOM es Pablo "Piparra" González, quien sostuvo que "la movilización no es sólo en defensa de los trabajadores de Acindar sino de todo el pueblo, porque si Acindar cierra, acá no va a quedar nadie. Ellos ya anuncian suspensiones, sin haber hablado ni acordado con nosotros, si lo hacen realmente, el conflicto sigue y nosotros seguimos en la ruta como hoy", explica el dirigente. González agrega que "entre los despedidos hay gente que votó a Milei, muchos de ellos contratados y ahora, de a poco, van asimilando lo que significa. Si entra acero chino al país no hay más trabajo para nadie", advierte.
+“Villa Constitución tiene una cultura muy particular. Acindar es el principal empleador y principal contribuyente. Todos, del almacenero al empleado municipal, saben que el pueblo es Acindar- dependiente. Entonces se movilizan para defender lo que les corresponde, del primero al último”, explica un sindicalista de la localidad vecina.
+De hecho, se armó una multisectorial donde, además de los sindicatos, están los estudiantes, comerciantes y pymes entre otras representaciones. El viernes 8 culmina la conciliación laboral dictada por el gobierno y la multisectorial se encuentra alerta, a la espera de posibles anuncios de despidos.
+El conflicto se desarrolla a pocos kilómetros del predio donde funciona Expoagro, la feria tradicional del agronegocio argentino, que la poderosa familia Passaglia le alquilan al Grupo Clarín. Tal como informó este diario el lunes por la noche, el gobernador Axel Kicillof asistió, en calidad de orador, a la cena de expositores, acompañado de su ministro Javier Rodríguez. Allí pidió una marcha atrás de las medidas que afectan a Buenos Aires, Santa Fe, Córdoba y Entre Ríos.
+El miércoles estuvo el presidente Javier Milei. El intendente Santiago Passaglia hizo malabares para esquivar la foto con él, disgustado porque el clan esperaba que el gobierno designara a su hermano Manuel al frente de ANSeS, algo que hasta acá no ocurrió.</t>
   </si>
   <si>
     <t>Enrique Arriaga</t>
@@ -721,7 +1639,22 @@
     <t>https://www.pagina12.com.ar/718829-macri-en-su-habitat-natural-entre-el-mensaje-a-milei-y-su-re</t>
   </si>
   <si>
-    <t>2024-03-07T20:29:42Z</t>
+    <t xml:space="preserve">Título: Macri, en su hábitat natural: entre el mensaje a Milei y su rearmado en el PRO
+Chapeau: El paso del expresidente por Expoagro
+Subtítulo: "Es él, su hermana y las redes", dijo en lo que no se supo si fue un elogio o una reflexión acerca del respaldo del Presidente.
+Editoria: El País
+Tags: Mauricio Macri, mauricio-macri, diario
+URL: https://www.pagina12.com.ar/718829-macri-en-su-habitat-natural-entre-el-mensaje-a-milei-y-su-re/
+Notícia completa (9 blocos):
+El ex presidente Mauricio Macri visitó la muestra ExpoAgro 2024, el corazón del agronegocio que abraza las nunca cumplidas promesas de la derecha de terminar con las retenciones, con una mirada crítica hacia el presidente Javier Milei: "Él es él, su hermana y las redes sociales", lo calificó ante la platea de empresarios y se mostró distante de una posible alianza con La Libertad Avanza: "Ahora, lo que nos toca a todos es estar a la altura de la circunstacia, ser generosos y humildes en las ideas de fondo".
+En las últimas semanas, y tras el rol clave de la bancada del PRO en el respaldo sin miramientos a la fracasada Ley Ómnibus, la posibilidad de una alianza entre el partido fundado por Macri y del presidente Javier Milei resonó fuerte, incluso para llegar juntos a las legislativas de 2025. El respaldo de Macri en el denominado "pacto de Acasusso" para la victoria de Milei en segundo vuelta y el nombramiento de ex funcionarios macristas en el Gabinete de la ultraderecha como Patricia Bullrich --saliente presidente del PRO-- y Luis Caputo fueron también evidencia de los acuerdos alcanzados.
+Sin embargo, a días de las elecciones internas del PRO del 19 de marzo, en las que Macri se espera que llega como único candidato a presidente del partido, poniéndose de nuevo en un lugar de decisión dentro del sistema político, hicieron que el ex presidente mida de otra manera sus palabras y se muestre más lejos de Milei. "La decisión de ustedes, de los argentinos, es que querían un shock en el sistema político", señaló a la audiencia.
+En ese análisis, Macri diferenció incluso a Milei de los liderazgos de derecha de los ex presidentes Donald Trump y Jair Bolsonaro. "Este es un verdadero outsider, no es Trump como dicen: Trump tenía al partido republicano atrás, Bolsonaro tenía al Ejército atrás. Él es él, su hermana y las redes sociales", marcó Macri, que en pocos días tendrá detrás de él a todo el PRO.
+"Bueno, ha generado un shock. Ahora lo que nos toca a todos es estar a la altura de la circunstancia, ser generosos y humildes en las ideas de fondo", analizó Macri tomando distancia. En ese contexto, el ex presidente señaló que el partido amarillo se está "reorganizando" y que la idea es "volver a estar juntos", enfatizando en la daña relación entre Bullrich y el ex jefe de gobierno porteño Horacio Rodríguez Larreta, tras las internas del año pasado dentro de Juntos por el Cambio.
+Macri decidió mostrarse como un hombre de la política con un partido con experiencia detrás al recordar que su intención para en la conducción del PRO "es ayudar a ordenar la vuelta del partido, a volver al espíritu, el espíritu con el cual entramos a la política, tratando de incomodar a los partidos resistentes, generando una visión distinta con un foco fundamentalmente en la gente".
+"Es algo que hemos hecho en los lugares que gobernamos, donde hemos marcado una diferencia, mostrando que nuestra prioridad es que los impuestos de la gente vuelvan a la gente", marcó y, al hablar del Pacto de Mayo convocado por Milei, lamentó que "en los tiempos que me tocó a mí gobernar no tuve esa colaboración, pero espero que todos estemos crecidos, madurados, entendidos, que si seguimos siendo más de lo mismo nos va a ir igual de mal que nos ha ido en los últimos 40 años".
+En las palabras elegidas por el mandatario resuena el análisis hecho en esta semana por el diputado y jefe de bloque de Hacemos Coalición Federal, Miguel Pichetto, quien fue candidato a vicepresidente de Macri en 2019 y respaldó a Rodríguez Larreta en la campaña presidencial del año pasado. "Milei no vino de Marte. Es producto del error de Juntos por el Cambio, de la mala praxis política de haber ido a una interna y no construir o reconstruir el único liderazgo que tenía el PRO que era Mauricio Macri", sostuvo en una entrevista en el programa Duro de Domar.
+Pichetto dejó en claro que Macri debería haber sido nuevamente el candidato a presidente del espacio ya que "se fue con el 41 por ciento de los votos. Tenía una base electoral que le permitía ser medianamente competitivo". "Los liderazgos no se repliegan", le criticó por la decisión de retirarse de la contienda presidencial y le adjudicó: "La decisión abrió un proceso interno que determinó el fracaso de la coalición Juntos por el Cambio. Esa primaria no fue positiva". Habrá que ver si Macri estaba mirando Netflix, o si en el zapping sintonizó a su excompañero de fórmula.</t>
   </si>
   <si>
     <t>Compromiso de Roly Santacroce</t>
@@ -733,7 +1666,17 @@
     <t>https://www.pagina12.com.ar/718539-compromiso-de-roly-santacroce</t>
   </si>
   <si>
-    <t>2024-03-07T03:00:14Z</t>
+    <t xml:space="preserve">Título: Compromiso de Roly Santacroce
+Chapeau: El intendente de Funes recorrió la Expo Agro 2024
+Subtítulo: Roly Santacroce, intendente de Funes, visitó esta semana la Expo Agro 2024, uno de los eventos más importantes de Latinoamérica que en esta ocasión se lleva a cabo en la ciudad de San Nicolás.
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/718539-compromiso-de-roly-santacroce/
+Notícia completa (4 blocos):
+Roly Santacroce, intendente de Funes, visitó esta semana la Expo Agro 2024, uno de los eventos más importantes de Latinoamérica que en esta ocasión se lleva a cabo en la ciudad de San Nicolás. Se trata de una megamuestra en la que entidades agroindustriales presentan todo su potencial.
+“Fervientemente creo que la agroindustria es un motor económico fundamental para el desarrollo de nuestro país. Cada puesto de trabajo en el sector representa un eslabón clave en la cadena de producción, desde el campo hasta la mesa”, comentó Santacroce luego de finalizar su recorrido por distintos stands de entidades agroindustriales que formaban parte de la jornada.
+El intendente concluyó: “Me comprometo a seguir apoyando y promoviendo el crecimiento de los productores de nuestra ciudad y nuestra provincia, porque sé que su prosperidad se traduce en beneficios para la región y en trabajo para los santafesinos. En estos ámbitos se observa que Argentina tiene un gran futuro”.
+Durante cuatro días se concentran compradores, vendedores, entidades financieras y rondas de negocios en un clima único, por lo cual ha sido bautizada La Capital Nacional de los Agronegocios. Para la nueva edición, la exposición sorprenderá con nuevos contenidos, espacios y servicios. Más tecnología y mejoras en el predio.</t>
   </si>
   <si>
     <t>Inflación, cepo "afuera" y vuelve Ganancias</t>
@@ -745,7 +1688,24 @@
     <t>https://www.pagina12.com.ar/718217-inflacion-cepo-afuera-y-vuelve-ganancias</t>
   </si>
   <si>
-    <t>2024-03-06T03:01:00Z</t>
+    <t xml:space="preserve">Título: Inflación, cepo "afuera" y vuelve Ganancias
+Chapeau: El Presidente Milei habló en la apertura de la muestra ExpoAgro
+Subtítulo: Les dijo "héroes" a los ruralistas mientras la sociedad se derrumba en la crisis. La restricción cambiaria se levantaría "a mitad de año" y esperan 15 de IPC.
+Editoria: Economia
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/718217-inflacion-cepo-afuera-y-vuelve-ganancias/
+Notícia completa (11 blocos):
+El presidente Javier Milei participó de la apertura de la muestra rural ExpoAgro y trató de "héroes" a productores y empresarios del agro, mientras la crisis y el ajuste les pega duro a las clases medias y bajas. En paralelo, dejó tres definiciones sobre la economía que viene: la primera, que la inflación irá a la baja en el mes de febrero; la segunda, que planea abrir el cepo cambiario antes de mitad de año; y la tercera y más polémica es que el gobierno planea restituir el Impuesto a las Ganancias, en el marco de la discusión con las provincias por mayores ingresos.
+Durante una reunión privada de la que también participó el ministro del Interior Guillermo Francos, Karina Milei Secretaria General de la Presidencia y el vocero Manuel Adorni, declaró a los referentes del campo, Milei fue elogiado por los presentes y decidió jugar con elogios al campo: les dijo a los presentes que son “el sector productivo no sólo más fuerte en Argentina, sino el más productivo de todo el mundo”. Agregó que “como dije siempre, con la carga fiscal que tienen, que puedan seguir produciendo es fruto de un milagro; y ese milagro es porque son los mejores del mundo; así que, en primer lugar, felicitaciones a todos los héroes que se encuentran en este lugar, que son el corazón de la argentina”.
+Asimismo, mientras los precios siguen pegando muy duro, el mandatario develó cuál sería el dato de inflación de febrero. Dijo que se ubicará en torno al 15 por ciento y que el cepo sería levantado a mitad de año “si todo sale bien”. Cuando en diciembre dio 25% fue un éxito, porque los precios se retrajeron a la segunda semana. Este mes parece que la inflación va a estar en 15%”. Ese número, que para el Presidente es importante, sería, de darse, el más importante en 33 años para el mes de febrero, un período que suele tener precios bastante más moderados.
+En esa conversación, destacó además la importancia del sector en la economía y como promotor del desarrollo económico, repasó la situación en que está la economía y la profundidad de la crisis. En relación a los aumentos de precios, explicó que las correcciones se deben al atraso generado. Manifestó que hay contención social con la duplicación de la asignación universal por hijo. En paralelo, subrayó que el Gobierno se encontró con “mucha corrupción” y que se la está abordando.
+El Presidente llegó al autódromo de San Nicolás en helicóptero cerca del mediodía. Junto con José Luis Espert, mantendrá una reunión con empresarios invitados en el Centro de Agronegocios.
+En el primer día de muestra también estuvieron Martin Llaryora, Gobernador de Córdoba; Rogelio Frigerio, de Entre Ríos; Maximiliano Pullaro, de Santa Fe; Guillermo Francos, Ministro del Interior de la Nación; Manuel Passaglia, Intendente San Nicolás; Fernando Vilella, Secretario de Bioeconomía de la Nación e integrantes de la Mesa de Enlace.
+[H2] El cepo y Ganancias
+Por otra parte, el Presidente retomó la idea de reducir las restricciones cambiarias. Así, aseguró que “una vez saneada economía van a abrir el cepo”, algo que indicó podría suceder a mitad año. Esta situación ya la viene manifestando hace tiempo, y días atrás recibió por parte del Fondo Monetario Internacional (FMI) la recomendación de no mencionar estos temas porque generan incertidumbre. De hecho, las menciones de apertutra del cepo generaron, en el agro, la sensación de que cuando haya un levantamiento, el tipo de cambio será más alto que el actual. Ergo, las liquidaciones de exportaciones de granos se frenaron a la espera de un dólar más caro.
+El otro tema central que surgió en Expo Agro fue el regreso del cobro del Impuesto a las Ganancias de los trabajadores. El ministro del Interior, Guillermo Francos, confirmó que el Gobierno nacional insistirá en su propuesta de restituir el Impuesto a las Ganancias para la cuarta categoría como herramienta para mejorar la situación fiscal de las provincias. "La restitución de Ganancias es una propuesta del Gobierno para solucionar los temas fiscales de las provincias", señaló el funcionario en declaraciones a la prensa en la muestra en San Nicolás.
+La decisión de quitar la cuarta categoría de Ganancias fue del ex ministro Sergio Massa, y de volver a instaurarse perderían gran parte de esa recomposición una porción muy importante de los trabajadores formales y sindicalizados. Otro golpe al bolsillo.
+En este contexto, Francos supeditó esa medida a un pedido de las provincias y señaló que "los gobernadores están preocupados por su situación fiscal a partir del recorte de la gestión anterior a Ganancias", pero no aclaró más detalles sobre cómo será la postura de los mandatarios en esta nueva etapa de negociaciones.</t>
   </si>
   <si>
     <t>Organizaciones de todo el mundo advierten sobre los riesgos del trigo transgénico</t>
@@ -757,7 +1717,28 @@
     <t>https://www.pagina12.com.ar/715542-organizaciones-de-todo-el-mundo-advierten-sobre-los-riesgos-</t>
   </si>
   <si>
-    <t>2024-02-26T03:01:00Z</t>
+    <t xml:space="preserve">Título: Organizaciones de todo el mundo advierten sobre los riesgos del trigo transgénico
+Chapeau: Solicitan la intervención de la ONU para regular el derecho a la alimentación saludable
+Subtítulo: En un documento conjunto, Asia, África y América Latina afirman que el trigo HB4 de la empresa Bioceres. No cuenta con estudios de inocuidad y denuncian que incluso tiene menos productividad que el trigo convencional.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/715542-organizaciones-de-todo-el-mundo-advierten-sobre-los-riesgos-/
+Notícia completa (15 blocos):
+Organizaciones de América Latina, África y Asia denunciaron los efectos nocivos del trigo transgénico que ya se consume en Argentina y amenaza llegar a otros países. En un detallado documento de 14 páginas, movimientos sociales, campesinos y pueblos indígenas solicitaron la intervención de relatores especiales de Naciones Unidas (ONU) por los riesgos para la alimentación, la salud y el ambiente que implica el transgénico de la empresa Bioceres. Confirmaron que no existen estudios independientes que confirmen su inocuidad, denunciaron al peligroso herbicida glufosinato de amonio e, incluso, afirmaron que es menos productivo que el trigo convencional.
+"No al trigo transgénico. Alianza mundial busca la intervención de la ONU contra el cultivo de trigo transgénico HB4", es el título del comunicado de la organización internacional Grain que da cuenta de la insólita --e irregular-- forma de aprobación del transgénico en Argentina, Brasil y Paraguay: en base a supuestos estudios de la propia empresa que lo comercializa e, incluso, con documentación que es confidencial.
+[H2] Sin estudios confiables
+Entre otros aspectos fundamentales, destacan que la población de Argentina se está alimentando con harinas que contienen un transgénico que carece de estudios respecto a la salud y, además, contaminado con el agrotóxico glufosinato de amonio (más letal que el conocido glifosato).
+"La aprobación del trigo HB4 ha causado mucha preocupación en un amplio sector de la sociedad, porque su siembra y consumo vulnerará derechos humanos, como el derecho a la vida, a la salud, a la alimentación adecuada y a la soberanía alimentaria, a un ambiente equilibrado y libre de contaminación, al acceso a la tierra y territorio; al derecho a autodeterminación de los pueblos y comunidades locales", señala el documento que fue dirigido a siete Relatores Especiales de Naciones Unidas.
+En consecuencia, se solicita que insten a los gobiernos de Argentina, Brasil y Paraguay para que suspendan las autorizaciones para el cultivo de trigo transgénico HB4. Los destinatarios son Marcos Orellana (Relator sobre Sustancias Tóxicas y Derechos Humanos), David Boyd (Derechos Humanos y Ambiente), Michael Fakhri (Derecho a la Alimentación), Pedro Arrojo-Agudo (Derecho al Agua Potable), Olivier De Schutter (Extrema Pobreza y DDHH), Francisco Cali Tzay (Derechos de los Pueblos Indígenas) y Tlaleng Mofokeng (Derecho a la Salud).
+[H2] Derecho a la alimentación
+El trigo transgénico fue desarrollado y es comercializado por la empresa de origen argentina Bioceres-Indear, donde tuvo un rol fundamental la científica del Conicet y de la Universidad del Litoral, Raquel Chan. La Comisión Nacional de Biotecnología (integrada exclusivamente por impulsores del agronegocio, incluso gerentes de las multinacionales) dio el visto bueno en 2018, a libro cerrado y sin publicar los estudios en ninguna revista científica. La aprobación final fue en mayo de 2022, cuando Julián Domínguez (entonces ministro de Agricultura) dio luz verde al pedido de Bioceres-Indear (la firma administrativa corrió por cuenta de Luis Contigiani).
+En marzo de 2023, la empresa Bioceres-Indear informó que 25 molinos ya mezclaban el trigo transgénico con el convencional para libre distribución. Se trata de un hecho de trascendencia mundial: por primera vez un trigo modificado genéticamente está en los alimentos de consumo masivo (pan, pizzas, empanadas, fideos y todos los usos de la harina). Y, más grave, la población no tiene posibilidad de identificar si está comiendo un producto con transgénicos o no: en Argentina no existe un etiquetado de transgénicos.
+Elizabeth Bravo, integrante de la organización Acción Ecológica de Ecuador y una de las impulsoras del documento dirigido a Naciones Unidas, recordó que Argentina es un país exportador de trigo, y destacó el riesgo para la población: "El trigo es fundamental en la dieta de los ecuatorianos, como de muchos otros pueblos del mundo, porque está presente desde el desayuno hasta la cena. Sería terrible que comencemos a comer un trigo que proviene de una modificación genética y que además tiene residuos mayores de plaguicidas como glufosinato de amonio".
+[H2] Una tecnología deficitaria
+Leonardo Melgarejo es integrante del Movimiento Ciencia Ciudadana de Brasil e integrante de la Uccsnal (Unión de Científicos Comprometidos con la Sociedad y la Naturaleza de América Latina). El activista remarcó la enorme gravedad de que el trigo transgénico no cuente con evaluación científica de impactos en la salud de la población. "Este transgénico se ha transformado de un problema internacional, por eso esta acción conjunta de organizaciones de tres continentes. Este trigo contamina la alimentación básica de las población y sin dudas va a contribuir en el acaparamiento de tierras en pocas manos y la afectación del agua, de la vida campesina y de los pueblos indígenas", afirmó.
+Fernando Frank, investigador de Argentina, ingeniero agrónomo e integrante de Uccsnal, apuntó a un eje central que desnuda la publicidad empresaria y mediática respecto al trigo de Bioceres. "El trigo HB4 es un fracaso productivo, es un escándalo porque, además de los impactos negativos en la salud y la alimentación, están vendiendo una tecnología que promete producir más pero que en realidad produce menos, lo confirman los propios datos certificados por el Estado", afirmó Frank.
+Frank y Melgarejo son dos de los autores de la publicación científica "Controversia por el pan nuestro de cada día", publicada a fines del año pasado, que confirma que el trigo transgénico es menos productivo que el trigo convencional. Firmada además por los investigadores Gabriel Bianconi Fernandes y Rubens Onofre Nodari, el paper da cuenta, con tablas y cifras del Ministerio de Agricultura de Argentina, que el trigo transgénico tiene menos productividad que su variante convencional. "Los rendimientos (del trigo transgénico) fueron significativamente inferiores a la media de trigo del país. La conclusión es que el mayor rendimiento de la variedad HB4 --la principal ventaja anunciada por Bioceres-- no ha sido probado en el campo", ratifica el estudio científico.
+En 2020, más de mil científicos del Conicet y de 30 universidades públicas de Argentina repudiaron la aprobación y alertaron los riesgos para la salud de la población e, incluso, para la producción agropecuaria y los derechos humanos. “Esta autorización remite a un modelo de agronegocio que se ha demostrado nocivo en términos ambientales y sociales, causante principal de las pérdidas de biodiversidad, que no resuelve los problemas de la alimentación y que amenaza además la salud de nuestro pueblo confrontando la seguridad y la soberanía alimentaria”, comenzaba el escrito dirigido al gobierno nacional y a las autoridades del Conicet.</t>
   </si>
   <si>
     <t>La semilla del agronegocio</t>
@@ -769,7 +1750,26 @@
     <t>https://www.pagina12.com.ar/712987-la-semilla-del-agronegocio</t>
   </si>
   <si>
-    <t>2024-02-18T03:01:00Z</t>
+    <t xml:space="preserve">Título: La semilla del agronegocio
+Chapeau: Rechazo de la Mesa Agroalimentaria a la adhesión a UPOV 91
+Subtítulo: Pone en jaque el control de la cadena agroalimentaria, y por lo tanto la disponibilidad, la calidad y el precio de los alimentos de todas las y los argentinos.
+Editoria: Cash
+Tags: Agronegocio, Ley Ómnibus, printed-edition, ley-omnibus
+URL: https://www.pagina12.com.ar/712987-la-semilla-del-agronegocio/
+Notícia completa (13 blocos):
+Dentro de los beneficios para las corporaciones que se incluye en la llamada Ley Ómnibus devuelta a comisiones de la Cámara de Diputados por falta de consenso, el artículo 210 es un regalo especial para las grandes trasnacionales del agronegocio, ya que establece la adhesión de Argentina al convenio de 1991 de la Unión Internacional para la Protección de las Obtenciones Vegetales (UPOV 91).
+UPOV 91 es el escenario jurídico ideal para que los oligopolios controlen completamente el mercado de semillas y por derivación, el de alimentos. Como el resto de los capítulos del Proyecto de Ley Ómnibus que envió el Poder Ejecutivo Nacional, la adhesión a UPOV 91 también tiene dueño: las primeras seis grandes empresas transnacionales de semillas que ocupan el 58 por ciento del mercado mundial de semillas (Bayer 23 por ciento, Corteve Agriscience 17 por ciento, Chem China/Syngenta 7 por ciento, Basf Alemania 4 por ciento, Group Limagrain 4 por ciento y KWS 3 por ciento) y sus socias locales: Bioceres y Don Mario.
+Con el Acta UPOV 91 se cometería el despojo más grave en la historia de la humanidad. Si se contaminan los materiales nativos por materiales patentados, o se introducen genes patentados a ellas, los genes patentados que interactúen con los materiales nativos otorgarían el derecho de propiedad a los dueños de las patentes. Allí se constituye una apropiación, cercenando derechos ancestrales, actuales y futuros. Visto de esta forma, se deteriora la soberanía alimentaria y las multinacionales se constituirán en los dueños de la comida.
+Con la excusa de incentivar inversiones, este tratado da vía libre a la privatización de las semillas que son propiedad de los pueblos, de las familias campesinas e indígenas que, generación tras generación, han seleccionado, guardado, reproducido e intercambiado diversidad de plantas que hoy son parte de nuestros alimentos, de nuestra cultura y de nuestra riqueza.
+UPOV 91 reconoce la propiedad intelectual, pero elimina el uso propio gratuito, acepta que se patenten materiales vegetales, prohíbe el uso gratuito de variedades existentes para crear nuevas variedades, además de reconocer que hay derechos por el producto resultante de la semilla protegida.
+Los derechos de los obtentores y sus inversiones no estarían respaldados nunca, si no hay sistemas de control estatal del comercio de semillas. Se trata de confundir derechos legítimos de propiedad intelectual, con sistemas de expoliación de la renta basados en controles sobre productos derivados de la siembra de semilla protegida.
+Con UPOV 91 se crearía la doble imposición: pagamos en el campo por la semilla y luego en el puerto por el producto. Se estarían incorporando a nuestro sistema legal mecanismos de criminalización de agricultores y agricultoras. Quienes puedan usar la semilla en ciclos productivos posteriores, limitando o prohibiendo el derecho de uso propio gratuito.
+Hasta ahora, Argentina adhiere a UPOV 78, aceptando legislar en favor de un sistema que reconoce la propiedad intelectual, habilita el uso propio gratuito y acepta que nuevas obtenciones deriven de las viejas obtenciones sin costo para quien mejora.
+A los que fundamentan la adhesión a UPOV 91 por un presunto crecimiento y mayor rendimiento de la producción, le respondemos que la productividad no sólo está asociada a la genética. Principalmente depende del suelo, su preparación, la fecha de siembra, la elección de la correcta semilla (variedad o híbrido) la densidad de siembra, el manejo de malezas, el manejo de las plagas insectiles, la fertilización, el correcto uso de maquinaria, y por último, el clima.
+La biotecnología y la investigación estarán respaldadas con un Estado presente, nunca con abusos empresariales basados en leyes dictadas a su medida. Con la ley que tenemos y un INASE presente y activo, no tenemos que dictar otra, ni cambiar nuestro posicionamiento internacional en materia de Propiedad Intelectual.
+Por todo esto, desde la Mesa Agroalimentaria Argentina rechazamos la adhesión a la UPOV 91, ya que entendemos que es una acción regresiva y autoritaria que atropella los derechos conquistados por lxs campesinxs, atentando contra la Soberanía Alimentaria y poniendo en riesgo los saberes ancestrales de nuestro pueblo. Luego de casi tres décadas del experimento transgénico en nuestro país, sabemos que las únicas innovaciones que le interesan al mercado concentrado son las que nos despojan de nuestra Soberanía, dejando hambre, contaminación y desigualdad.
+Lo que está en juego es trascendental: quien controla las semillas, controla la cadena agroalimentaria, y por lo tanto la disponibilidad, la calidad y el precio de los alimentos de todos los argentinos.
+*Secretario de Fe.Co.Fe y referente de la Mesa Agroalimentaria Argentina</t>
   </si>
   <si>
     <t>Ricardo Garzia*</t>
@@ -784,7 +1784,24 @@
     <t>https://www.pagina12.com.ar/709239-la-mesa-agroalimentaria-rechaza-la-ley-omnibus</t>
   </si>
   <si>
-    <t>2024-02-04T03:01:00Z</t>
+    <t xml:space="preserve">Título: La Mesa Agroalimentaria rechaza la Ley Ómnibus
+Chapeau: Qué puntos de la ley afectan a los pequeños productores
+Subtítulo: Extranjerización de la tierra, eliminación del Instituto de la Yerba Mate, venta del Banco Nación y la adhesión al convenio que permite privatizar las semillas.
+Editoria: Cash
+Tags: Ley Ómnibus, Javier Milei, printed-edition, ley-omnibus, javier-milei
+URL: https://www.pagina12.com.ar/709239-la-mesa-agroalimentaria-rechaza-la-ley-omnibus/
+Notícia completa (11 blocos):
+Dirigentes de la Mesa Agroalimentaria Argentina participaron de los debates en el Congreso manifestando su rechazo al Decreto de Necesidad y Urgencia (DNU) presentado por Javier Milei que entró en vigencia el 29 de diciembre (excepto en su capítulo laboral) y al proyecto “Bases y Puntos de Partida para la Libertad de los Argentinos”, conocido como “Ley Ómnibus”, que esta semana comenzó a ser tratado en sesiones extraordinarias en la Cámara de Diputados.
+La entidad, conformada por organizaciones como la Unión de Trabajadores de la Tierra (UTT), la Federación de Organizaciones Nucleadas de la Agricultura Familiar (FONAF), la Federación de Cooperativas Federadas (FECOFE), el Movimiento Campesino Indígena Somos Tierra y Bases Federadas (un desprendimiento de la Federación Agraria), se manifestó en contra de la privatización de las empresas públicas, el desmantelamiento del Instituto de la Yerba Mate (INYM), y la adhesión de la argentina al convenio internacional UPOV 91 que abriría la puerta al patentamiento de semillas.
+Agustín Suárez, referente de la UTT sostuvo que “la derogación de diversas normas dentro del DNU no tienen otra función que favorecer la exportación de la producción, poniendo en riesgo el abastecimiento interno. Esta es la finalidad que persigue la derogación total de la Ley de Abastecimiento, la Ley de Góndolas y la Ley de Promoción Industrial, así como la derogación parcial de las leyes Compre Nacional y Compre Argentino”.
+En tanto, “el recorte de las pocas ayudas que existían para nuestro sector y la eliminación de áreas clave para la agricultura familiar, muestran el desinterés del Gobierno por el verdadero campo, golpeado por la sequía, los temporales, la falta de acceso a la tierra y el aumento de los alquileres, combustibles e insumos, y solo le importa garantizar las ganancias del capital concentrado del agronegocio. Hoy solo el 13 por ciento de la tierra está en manos de pequeños productores que producen más del 60 por ciento de los alimentos que circula en el mercado interno; mientras que el 1 por ciento de las empresas agrarias controlan el 36 por ciento de la tierra cultivada en nuestro país”.
+En tanto, Omar Príncipe, titular de Bases Federadas, sostuvo: “No estamos de acuerdo con las privatizaciones de las empresas públicas, especialmente el Banco Nación, que es una herramienta financiera para los pequeños y medianos productores y el movimiento cooperativo”.
+También rechazó la eliminación del Fondo Compensador Algodonero y del Instituto Nacional de la Yerba Mate, y la modificación de la Ley de Tierras que permitiría su extranjerización. “En Argentina hay 15 millones de hectáreas en manos de extranjeros, el 6 por ciento del territorio. ¿Podemos derogar una ley de tierras sin debatirla, cuando costó años acordarla con los gobernadores y el Congreso?”, se preguntó.
+Asímismo, se refirió a la la adhesión de Argentina al convenio UPOV 91 como “una ley hecha a la medida de Bayer-Monsanto que implica perder el derecho al uso propio por parte de los productores y pone en riesgo la diversidad”. Además, sostuvo que “es falso que faltan inversiones en materia de semillas por la no adhesión a la UPOV 91. En los últimos años, se cuadriplicó la producción de soja, maíz y otros granos.
+En tanto las entidades que conforman la mesa agroalimentaria argentina reiteraron cinco proyectos de Ley, oportunamente presentados al Congreso, que promueven la producción nacional de alimentos saludables y respetuosos con el ambiente.
+Se trata de la Ley de acceso a la tierra; la Ley de arrendamientos rurales. La Ley de protección y fortalecimiento de los territorios campesinos y la agricultura familiar; la Ley de segmentación de las políticas impositivas agrarias y la Ley de financiamiento y fomento del cooperativismo y la transición agroecológica.
+“Estas son las normas necesarias para frenar el proceso de concentración económica y el despoblamiento del campo e impulsar el fortalecimiento de los pequeños y medianos productores, de la agricultura familiar y el movimiento cooperativo agrario. “Somos los que, en realidad, estamos en emergencia”, señaló Principe. La producción, comercialización, industrialización y exportación en manos de agricultores está desapareciendo, quedando para los grandes capitales en forma de fondos de inversión, fideicomisos y pools de siembra”, advirtió.
+*Lic. en Periodismo y Comunicaciones. Autora de "Ser Sustentables" (Ed. Urano)</t>
   </si>
   <si>
     <t>Gabriela Ensinck*</t>
@@ -799,7 +1816,48 @@
     <t>https://www.pagina12.com.ar/709248-que-es-el-marco-temporal-y-por-que-se-agravo-el-conflicto-po</t>
   </si>
   <si>
-    <t>2024-02-01T17:39:33Z</t>
+    <t xml:space="preserve">Título: Qué es el Marco temporal y por qué se agravó el conflicto por las tierras indígenas en Brasil
+Chapeau: Están en riesgo 287 territorios
+Subtítulo: Cerca de 200 productores y empresarios vinculados al agro de Brasil, que forman parte de un grupo bautizado como “Invasión Cero”, se autoconvocaron por WhatsApp para “recuperar por medios propio
+Editoria: Newsletter
+Tags: Brasil, pueblos originarios, pueblos-originarios
+URL: https://www.pagina12.com.ar/709248-que-es-el-marco-temporal-y-por-que-se-agravo-el-conflicto-po/
+Notícia completa (35 blocos):
+Cerca de 200 productores y empresarios vinculados al agro de Brasil, que forman parte de un grupo bautizado como “Invasión Cero”, se autoconvocaron por WhatsApp para “recuperar por medios propios” las tierras que la comunidad Pataxó Ha Ha Hai reclama como propias, en el marco de un conflicto territorial de larga data.
+Durante el episodio -que ocurrió el 21 de enero en el territorio conocido como Caramuru, municipio de Potiraguá- los hacendados cercaron el predio con decenas de camionetas y empezaron a los tiros, según información brindada por el Ministerio de Pueblos Indígenas.
+Por el ataque murió Negá Pataxó -Maria de Fátima Muniz-, hermana del cacique Nailton Muniz, quien también fue alcanzado por un disparo en el riñón y debió ser intervenido de urgencia. Otras personas resultaron heridas y están fuera de peligro.
+• Artículo publicado originalmente en Causas, el newsletter de Latinoamérica Piensa. Registrate y recibilo en tu mail.
+La policía informó que incautó dos pistolas, dos revólveres, cargadores y municiones a dos miembros del grupo de hacendados, que fueron detenidos y acusados de homicidio, intento de homicidio y porte ilegal de armas.
+“La gente de Pataxó Hã-Hã-Hãe fue brutalmente atacada por un grupo de propietarios, agricultores y pistoleros fuertemente armados. El grupo atacó a las familias Pataxó, que ocupaban pacíficamente su área de granja”, repudiaron desde la Articulación de los Pueblos Indígenas de Brasil (APIB). Desde la organización indígena pidieron que se investigue el caso, y también, lo más importante: “La delimitación de los territorios indígenas es el único camino para amenazar la escalada de violencia que afecta a los pueblos de la región del sur de Bahía". Y acá otra vez el conflicto.
+[H2] ¿Qué es el Marco temporal?
+Se denomina Marco temporal a la tesis jurídica que afirma que los pueblos y comunidades indígenas solo tienen derecho a reclamar las tierras que ocupaban cuando se promulgó la Constitución Federal de 1988. Esta tesis no reconoce la cantidad de veces que los pueblos fueron desplazados de sus territorios de manera forzada, ya sea por el Estado o por privados, incluso antes de la sanción de la Constitución. Muchos fueron expulsados de sus tierras durante la última dictadura militar (1964-1985).
+La Comisión Interamericana de Derechos Humanos (CIDH) alegó que la aplicación de esta norma contradice los estándares universales de derechos humanos y pone en riesgo la existencia de los pueblos indígenas. Para la CIDH, la aplicación del Marco temporal tiene un “efecto lesivo para todos los casos de demarcación de tierras ancestrales concluidos y futuros”.
+Detrás del Marco temporal está el agronegocio y su necesidad de expandir la frontera agrícola.
+[H2] Idas y vueltas
+Primero, el Supremo Tribunal Federal (STF) de Brasil falló en contra del Marco temporal. Después, el Senado lo aprobó por ley. Más tarde Lula da Silva utilizó el poder del veto presidencial y lo vetó; y, finalmente, el Congreso revocó el veto de Lula. Todo esto pasó en los últimos meses del 2023.
+Cronológicamente ocurrió así:
+[H3] 21/09 - El máximo tribunal de Brasil falla a favor de las comunidades indígenas
+El STF rechazó por 9 votos contra 2 la presentación de las entidades rurales que pretendían la vuelta del Marco temporal, es decir, que no se reconocieran las tierras indígenas reivindicadas después de la Constitución de 1988. La votación se extendió por dos años, período en el que hubo movilizaciones indígenas en todo el país.
+Los dos votos a favor del Marco temporal provinieron de los jueces designados por el expresidente Jair Bolsonaro: el jurista y pastor presbiteriano André Mendonça y Nunes Marques.
+El relator del caso, Edson Fachin, sostuvo que el derecho de los pueblos indígenas a la tierra es anterior a la creación del Estado y que, por lo tanto, no debe restringirse sus derechos a ningún marco temporal.
+[H3] 27/09 - El Senado de Brasil aprueba el Marco temporal
+A días de conocerse el fallo del STF, el Senado brasileño aprobó esta ley para limitar el reconocimiento de las tierras indígenas por 43 votos a favor y 21 en contra. La Cámara de Diputados ya la había aprobado el año anterior, pero en el medio la máxima instancia judicial la declaró inconstitucional.
+Al mismo tiempo, la Corte dispuso que los productores que hayan adquirido “de buena fe” tierras que tradicionalmente pertenecen a los indígenas tenían derecho a una indemnización por parte del Estado.
+[H3] 20/10 - Lula da Silva veta la ley que aprueba el Marco temporal
+El presidente de Brasil utilizó su poder de veto para dar de baja la ley incentivada por el agronegocio, que fue aprobada por el Congreso y que ya contaba con un fallo de inconstitucionalidad.
+El veto de Lula fue un veto parcial, quedaron en pie artículos de la norma que permiten la explotación económica en tierras indígenas siempre que sea en coooperación y autorización de los pueblos originarios. Las comunidades indígenas pretendían que el veto del presidente sea total.
+"He vetado algunos tramos de la ley. Debemos seguir dialogando y trabajando para que tengamos, como hoy, seguridad jurídica y también el respeto a los derechos de los pueblos originarios", afirmó el presidente en ese momento.
+[H3] 14/12 - El Congreso de Brasil elimina el veto de Lula y el Marco temporal vuelve a estar vigente
+El ida y vuelta por el Marco temporal siguió: el Congreso eliminó el veto del presidente brasileño que protegía la demarcación de tierras indígenas. Por lo que la tesis que reconoce a las comunidades indígenas como válidas las tierras que ocupaban al 5 de octubre de 1988, cuando se sanciona la Constitución, vuelve a estar vigente.
+"Otro revés anulado. Garantizamos la seguridad jurídica al agro brasileño", celebró en las redes sociales el senador Ciro Nogueira, quien fue jefe de gabinete del expresidente Jair Bolsonaro (2019-2022).
+[H2] Por qué importan las tierras indígenas y qué puede pasar ahora
+Además de considerarse el derecho ancestral sobre las tierras de donde las comunidades indígenas fueron expulsadas, las reservas indígenas son consideradas claves en la lucha contra la preservación del ambiente porque representan una barrera contra la deforestación para la expansión del agronegocio y los proyectos extractivistas.
+"Es absurdo que mientras el mundo ya reconoce a los pueblos indígenas y sus territorios como una de las últimas alternativas para contener la crisis climática, el Congreso actúe a contramano", opinó Sonia Guajajara, ministra de Pueblos Indígenas.
+Según datos de la Fundación Nacional de los Pueblos Indígenas (FUNAI), las reservas ocupan 13,75% del territorio del país. Desde que asumió su tercer mandato, en enero, Lula ordenó la demarcación de ocho nuevas reservas, en contraste con Bolsonaro, que cumplió su promesa de no homologar un "centímetro" de tierra durante su mandato.
+Por el Marco temporal, hoy vigente, están en riesgo 287 territorios indígenas.
+Según el último censo, en Brasil viven cerca de 1,7 millones de indígenas dentro y fuera de reservas, de los 203 millones de habitantes.
+Luego del ataque armado, donde murió una dirigente indigena, el presidente brasileño dijo que pensaba interceder para proteger a las comunidades y encontrar una solución pacífica al conflicto de las tierras indígenas.
+Hasta ahora, el gobierno de Lula solo reforzó la presencia de las fuerzas de seguridad en las áreas en conflicto, no solo con los hacendados por la posesión de las tierras sino también en aquellas comunidades acechadas por la minería ilegal, como los indígenas yanomamis.</t>
   </si>
   <si>
     <t>Alejandra Hayon</t>
@@ -814,7 +1872,30 @@
     <t>https://www.pagina12.com.ar/708031-exigen-eliminar-el-capitulo-ambiental-de-la-ley-omnibus</t>
   </si>
   <si>
-    <t>2024-01-29T03:01:00Z</t>
+    <t xml:space="preserve">Título: Exigen eliminar el "capítulo ambiental" de la Ley Ómnibus
+Chapeau: Un centenar y medio de organizaciones enviaron un documento a la Cámara de Diputados para respaldar la legislación vigente
+Subtítulo: Los activistas alertan sobre los negocios entre privados que se abrirían si dejan de existir las leyes que protegen bosques, glaciares y suelos, entre otras.
+Editoria: Sociedad
+Tags: Ley Ómnibus, ambientalistas, Ley de bosques, Glaciares, printed-edition, ley-omnibus, ley-de-bosques, diario
+URL: https://www.pagina12.com.ar/708031-exigen-eliminar-el-capitulo-ambiental-de-la-ley-omnibus/
+Notícia completa (17 blocos):
+"Hay que eliminar el capítulo ambiental”. "Es un retroceso y un duro golpe a la legislación conseguida”. "Entrega recursos soberanos”. Con estas definiciones se plantan las organizaciones ambientalistas en la escena donde crecen los reclamos al proyecto Ley Ómnibus y su adlátere -–o viceversa--, el mega DNU de Javier Milei. Lo expresó en el Plenario de Comisiones el abogado ambientalista Enrique Viale y lo confirmaron 150 organizaciones esta semana en una carta dirigida a los Diputados nacionales en defensa de la legislación ambiental vigente, modelo en el mundo en protección de bosques o glaciares. Exigen eliminar el “capítulo ambiental” por “lo preocupante y peligroso” de las propuestas que “no tienen relación con las necesidades y urgencias de la situación económica que atraviesa la Argentina, por lo que no hay justificación alguna para incorporarlas en el paquete de reformas”.
+De aprobarse esta reforma, la Ley de bosques, la de glaciares y la de quema pueden transformarse en leyes de “desprotección” advierte Consuelo Bilbao del Círculo de Políticas Ambientales. Aun cuando el dictamen eliminó el desmonte en zonas protegidas --como pretendía el texto original--, se endureció respecto a glaciares dándole entrada a la extracción minera en sus alrededores. Toda una bienvenida a las corporaciones de la megamineria.
+El dictamen extiende además el plazo para habilitar la quema de pastizales ante la “ausencia de respuesta de las autoridades”. Propone un tratado que modifica las normas de propiedad intelectual de las semillas afectando especialmente a las criollas, y otra norma sobre transición energética que solo involucra al mercado de carbono ("otro sinsentido" apuntan los expertos). Junto a los artículos destinados a desfinanciar la protección ambiental, el capítulo queda en alerta roja y “se perjudica gravemente al pueblo argentino” sentencia Viale.
+Detrás de los cambios asoman “interesados con nombre y apellido y empresas como la Barrick Gold detrás de la ley de glaciares” detalla el abogado ante Página/12 al ampliar su intervención en el Congreso, como referente de la Asociación Argentina de Abogados Ambientalistas la semana pasada. Viale señaló allí al empresario hotelero Eduardo Elsztain, a Mauricio Macri y al ministro Luis Caputo, no solo como responsables del desmonte de miles de hectáreas. También como parte de quienes conspiran para que se apruebe el proyecto que busca “privatizar las nacientes de agua, apropiarse de recursos mineros -–oro y plata, por caso--, y devastar el monte para el agronegocio”. Algo que buscarán también, sino queda en el articulado de la ley, "al otorgarle las fatales facultades delegadas al Ejecutivo” anticipa.
+[H2] No es ajuste, es entrega
+Dado que el objetivo no es “achicar gastos” –como explican las organizaciones- se evidencia el motivo real de los cambios: la entrega de recursos, el despojo. “Es paradójico, trabajamos mucho las organizaciones para lograr estas leyes y ahora estamos trabajando para que no las volteen” reflexiona Bilbao. Las modificaciones minimizan los criterios de protección. “Y se vulnera el principio de no regresión ambiental porque implica disminuir niveles de protección ya alcanzados” agrega. Viale coincide: “Hasta hace poco debatíamos una ley de humedales. Ahora retrocedimos y estamos debatiendo leyes sancionadas hace 15 años: la de bosques y la de glaciares. ¡Estábamos discutiendo el siglo XXI y nos llevaron a discusiones del siglo XIX!”.
+En la tensión se distingue una postal apocalíptica donde podríamos ver un futuro cercano con aumento de sequía por desforestación, producto del desmonte o la quema indiscriminada. El agua sería un lujo arábigo porque las nacientes de los ríos --los glaciares-- ya no serían un recurso soberano, estarían en manos privadas, y también sus alrededores convertidos en campos de extracción minera. Una postal desoladora. Eso pretende hacia el futuro, el proyecto presentado.
+Las organizaciones expresan su rechazo: “No creemos que el capítulo ambiental siquiera se tenga que discutir, tiene que ser eliminado -–señala Bilbao--. El tema ya se discutió y se sancionaron leyes modelo: la Ley de Bosques logró en 2007 frenar la abrupta curva de aumento de los desmontes, sobre todo en Chaco. La tasa bajo considerablemente y eso es importante para nuestros bosques. Sin esa ley podría haber sido una catástrofe”.
+[H2] Ley de glaciares
+“Hoy lo que más nos preocupa es la Ley de Glaciares” afirma la especialista. Votada dos veces, sancionada en 2010 y ratificada por la Corte Suprema de Justicia con dos fallos, en dos oportunidades, la Ley 26.639 de Protección Ambiental de glaciares y ambiente periglacial -–su nombre oficial--, corre peligro de derrumbe. “No sabemos en qué escritorio se decidió cambiarla en tres artículos fundamentales” comparte.
+La ley vigente plantea que los glaciares son “un recurso hídrico estratégico para la vida humana” detalla Bilbao. “Pero esa concepción ya no figura en el Artículo 1. Y en el 2 se piden requisitos extras para ser áreas protegidas, o sea que se los desprotege y se habilita la actividad minera”. El Artículo 6 que establece las prohibiciones de la actividad minera “ahora queda sujeto a los artículos 1 y 2 modificados, porque buscan reducir área de protección periglacial”.
+Esto genera mayor inseguridad jurídica, aunque promueve las inversiones, claro. Los glaciares son “fábricas de agua” define Viale. “Allí nacen muchos de los ríos de nuestro país que dan vida y trabajo a su paso”. Hoy pueden terminar en manos de corporaciones como la canadiense Barrick Gold porque “Las modificaciones presentadas fueron escritas por sus abogados”.
+Esta empresa explota glaciares de alta montaña en San Juan y Mendoza con minas metalíferas, y quiere expandir sus dominios. Actualmente no puede porque las zonas periglaciales están inventariadas y protegidas. “Por eso quieren achicar el área protegida” anuncia el abogado. “Esto está escrito con la idea de liberar áreas específicas. Es un avasallamiento y es preocupante tanta desprotección”, coincide Bilbao.
+[H2] Sobre bosques y quemas
+En bosques hubo cambios, entre el proyecto y el dictamen conocido hasta ahora, como en otras áreas. El texto original permitía desmontar zonas de máxima protección: rojas y amarillas. “Esto se eliminó en el dictamen, pero queda la modificación del Fondo para la protección de bosques nativos”, señala Bilbao sobre el Fondo que cuenta con el 0,3 por ciento del presupuesto nacional y el 0,2 de retenciones. Se eliminan también las partidas presupuestarias fijas y se deja las partidas a discrecionalidad del Ejecutivo.
+En cuanto a quemas la situación “se agravó” en el dictamen porque permite ante un pedido de autorización de quema con 90 días sin respuesta, entender una autorización “tacita”. Considerando las sequías y los incendios no se debería ignorar a la autoridad local: “Corrientes perdió el 12 por ciento de la provincia por incendios. Tuvimos meses de humo en las riveras del Paraná por los incendios en Santa Fe” acierta Viale.
+La norma sin embargo ignora a las autoridades al momento de evaluar si hacer o no una quema. Se ignoran también las sanciones por quema indebida: cuando no se autorizan por cuestiones climáticas, pero el productor igual quema. Ya no habría sanción si se propaga un incendio como establece la Ley 26.562 de actividades de quema. Por eso exigen y concluyen de cara al tratamiento del articulado, que "estas modificaciones y sus consecuencias perjudican gravemente al pueblo argentino”.</t>
   </si>
   <si>
     <t>Patricia Chaina</t>
@@ -829,7 +1910,60 @@
     <t>https://www.pagina12.com.ar/707361-nadie-voto-por-empeorar-sus-condiciones-de-vida</t>
   </si>
   <si>
-    <t>2024-01-26T00:38:44Z</t>
+    <t xml:space="preserve">Título: "Nadie votó por empeorar sus condiciones de vida"
+Chapeau: Entrevista a Javier Rodríguez, ministro de Desarrollo Agrario bonaerense
+Subtítulo: Para el funcionario, la Ley Ómnibus y el DNU no cuentan con ningún artículo que favorezca al sector productivo nacional y ve que el horizonte que persiguen es uno sólo: "La extranjerización y la concentración".
+Editoria: Buenos Aires|12
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/707361-nadie-voto-por-empeorar-sus-condiciones-de-vida/
+Notícia completa (47 blocos):
+Desde la Ley de Tierras, pasando por la Ley de Semillas, las privatizaciones de empresas estratégicas, hasta llegar a los derechos de exportación y la Ley de Góndolas. Con este breve listado, Javier Rodríguez recorre el camino de modificaciones que propone la ley ómnibus y el DNU impulsado por Javier Miel. A su juicio, “atentan” contra todo el ciclo productivo provincial. El ministro de Desarrollo Agrario (MDA) bonaerense sostiene que no hay un solo artículo a favor de la economía ni del trabajo argentino porque el objetivo de las medidas es la "la concentración y la extranjerización”.
+"Esperamos que el Gobierno Nacional escuche al pueblo luego de una movilización masiva y contundente de rechazo como la de este miércoles", señala en diálogo con Buenos Aires/12.
+En este segundo mandato, Rodríguez continúa al frente de la cartera que vincula al gobierno de Axel Kicillof con los sectores productivos agropecuarios. El abordaje que involucra a su ministerio es amplio: desde la soja y el maíz, hasta la cebada que da origen a las PyMEs de cerveza, pasando por el biodiesel y la pesca, son parte del conjunto de sectores que ya tocaron las puertas del MDA en búsqueda de un acompañamiento para frenar las medidas libertarias.
+"Hemos tenido reuniones con la propia Federación Agraria y CONINAGRO, donde expresan sus desacuerdos con el desastroso esquema de derechos de exportaciones", advierte Rodrpiguez.
+“La discusión de la ley ómnibus se da en el marco de una aceleración de la inflación a partir de la fuerte devaluación que hizo el gobierno, acompañada por la liberación en el precio del combustible que originó un fuerte aumento en el precio de los insumos, afectando a los sectores que procesan granos y productos del agro, a quienes se les modificaron las ecuaciones, principalmente a las empresas de mediana escala del sector avícola, el porcino y el tambero”, describe el ministro.
+Aquel recuento de modificaciones que indica Rodríguez que introducen los, ahora, más de 500 artículos de la, como denominó Milei a su criatura, Ley de Bases y Puntos de Partida para la Libertad de los Argentinos, son un “avasallamiento de los mecanismos democráticos habituales donde se derogan leyes que tuvieron meses de debate".
+Rodríguez menciona la desaparición de la Ley de Tierras como el puntapié de la extranjerización y concentración con la que define la ley ómnibus. La pérdida del instrumento que limita a ciudadanos extranjeros tener más de mil hectáreas de zona núcleo o similares fue sancionada en 2011 y apunta a limitar la compra de grandes volúmenes de tierra productiva por parte de extranjeros.
+Pero un artículo que el ministro no quiere que pase desapercibido y que ya fue señalado en un comunicado por la Federación Agraria, Confederaciones Rurales Argentinas y la propia Sociedad Rural, es el 241, que en la nueva versión presentada este lunes lleva el número 210. Allí se adhiere a la Unión Internacional para la Protección de las Obtenciones Vegetales (UPOV), particularmente a las últimas actualizaciones de 1991.
+—¿Por qué es contraproducente esta adhesión?
+—En la actualidad, los productores tienen el derecho a usar sus propias semillas. Es uno de los últimos elementos que quedan para evitar tener que recurrir a un mercado como el de la producción de semillas que es muy oligopólico y prácticamente monopólico. Muchas veces productor en los hechos tiene pocas alternativas para comparar semillas e, incluso, hay veces que una sola empresa las provee porque las firmas están de alguna manera asociadas.
+—Entonces…
+—Pasar a UPOV 91, que aparece perdido como un articulito en medio de la ley, limita esa posibilidad. Si bien habrá que ver la efectiva implementación, termina atando al productor a esa cadena de concentración porque le pone trabas al uso de sus propias semillas. Cuando hablamos de la semilla hablamos de la posibilidad de producir. Argentina entraría a un esquema de no poder usar sus propias semillas.
+—El Gobierno Nacional plantea que es un mecanismo para acceder a métodos innovadores. ¿No está de acuerdo?
+—Si uno conoce la realidad del mercado el punto es la concentración en la venta de las semillas. En Argentina la inscripción de nuevas variedades de semillas está bien y con altos índices de productividad. Pero bueno, esto va de la mano de limitar el desarrollo científico nacional.
+—¿A qué se refiere?
+—La investigación es imprescindible para el sector agroalimentario. En lo que respecta específicamente a este sector, su desarrollo ha estado fuertemente vinculado a la posibilidad de innovación que se desarrolla desde el sector público. En Estados Unidos, por ejemplo, muchísimas de las innovaciones comienzan a potenciarse a partir de la creación de centros de investigación que surgieron a mitad del siglo XIX. En Argentina, parte de esas investigaciones arrancan a principios del XX.
+—¿Por qué son investigaciones que tienden a hacerse desde el sector público?
+—Gran parte de la investigación se hace en el sector público porque las innovaciones agronómicas no son sujetas a propiedad. Cuando uno conoce la semilla que se adapta a determinado clima o momento del año, son conocimientos que una vez aprobados cualquier productor puede usar. Achicar el CONICET o, como ocurrió durante el macrismo con el desfinanciamiento del Instituto Nacional de Tecnología Agropecuaria (INTA), con personal que se jubilaba y no se reponía, lo que genera son peores condiciones para el sector. Cuando uno lee en profundidad, la ley ómnibus también habla de privatizar INTeA (NdeR: Innovaciones Tecnológicas Agropecuarias SA. es la empresa de capitales mixtos conformada mayoritariamente por el INTA que promueve agronegocios) que comercializa parte de los desarrollos tecnológicos del INTA, lo que sería avanzar en una lógica de los avances sean cooptados por un sector específico limitando acceso a sector productivo.
+—¿Cómo se evidencia ese desarrollo científico desde el Estado?
+—Durante la gestión anterior a la nuestra, en la provincia de Buenos Aires funcionaban trece chacras experimentales que tenían un funcionamiento muy magro y con una fuerte desinversión y caída del personal. Nosotros pasamos a dieciséis chacras experimentales. En estos primeros cuatro años trabajamos en el mejoramiento genético vegetal, con la inscripción de siete nuevas variedades de semillas de, por ejemplo, tomate, trigo, y cebada. Estamos por inscribir una nueva de pastura.
+—¿Qué soluciones genera este trabajo?
+—Es la investigación en el sector público la que llega a escala de productores. Para ver otro ejemplo concreto, construimos un laboratorio de micropropagación. Los productores de batata tenían muchas dificultades para conseguir plantas madres de calidad. También los de alcaucil. Esto redujo la superficie de siembra, y con este mecanismo lo volvemos a impulsar. Estamos en etapa de ensayo para la mejora de una semilla de maíz.
+—El modelo del Gobierno Nacional dirá que esto atenta contra la libre competencia.
+—Está claro que lo que propone el Gobierno Nacional es un modelo excluyente. Ataca o da de baja derechos laborales. Son procesos que tienden a la concentración. La concentración productiva es la primera manera de destruir el ingreso porque es la concentración que desde el punto inicial provoca una desigual distribución para producir alimentos. Escucho declaraciones que hablan de agregar valor, y la verdad es que gobierna a nivel nacional un proyecto que atenta contra el agregado de valor como lo es la innovación.
+—¿Cómo ve el aumento de las retenciones a los commodities?
+—Todo lo que se propone en materia de derechos de exportación es desastroso. Las distintas organizaciones del sector históricamente manifestaron un rechazo, con una posición de que los derechos de exportación deben tender a reducirse, y en medio de un discurso de Milei que venía a reducir impuestos. De manera generalizada, ahí hay contradicción. Siempre con poca explicación y poco debate.
+—Los gobernadores de Santa Fe y de Córdoba, por ejemplo, están muy plantados en rechazarlas...
+—Tiene que ver con la evidente estafa electoral que implica, ya que Milei hizo campaña diciendo que no iba a incrementar ningún impuesto y hoy lo están haciendo. Tanto en los derechos de exportación como el Impuesto País, o Ganancias. Por otro lado, es importante destacar que el mayor problema en la propuesta de Milei es la falta de segmentación en los derechos de exportación, y que se ve en las economías regionales. Todo es parte de lo mismo: Milei no hace lo que dijo que iba a hacer. Él dijo que iba a solucionar la inflación ajustando a la casta y todos entendían que la casta era otra cosa. Pero acá se está ejecutando un modelo de ajuste clásico, que perjudica a la clase media y a los trabajadores.
+—Pero ganó las elecciones prometiendo un ajuste...
+—Sí, pero nadie por votó empeorar sus condiciones de vida. Cerramos el año con una inflación de 211 por ciento. En diciembre fue del 25 por ciento, que tiene que ver con la política de Milei, diciendo que el peso es una basura e impulsando una pérdida del poder adquisitivo. Todo en muy poco tiempo y en detrimento de las enormes mayorías. Del sector de la pesca, por ejemplo, una porción de sus representados lo votaron, pero nadie voto perder su fuente de trabajo. Es una buena síntesis. Tenemos que ser claros y contundentes, explicando lo que sucede: vivimos un ajuste muy similar a los ajustes ortodoxos.
+—¿A qué se refiere cuando dice que no se segmentan los derechos de exportación, particularmente en las economías regionales?
+—El cambio en los derechos de exportación tiene dos cuestiones: se elevan los montos y se generaliza a las economías. A partir de las modificaciones, se eleva el derecho de exportación sobre la cebada del 12 al 15 por ciento, el de la malta del 9 al 15 por ciento, de la cerveza del 4,5 al 15 por ciento. Todo al revés, porque a mayor industrialización el derecho de exportación tiene que ser más bajo, pero acá se lo equipara todo, lo que atenta contra la industrialización regional y local. Es un modelo de reprimarización de la economía. Además, no se de diferencia la escala de productores y se establece el 15 por ciento de manera generalizada.
+—¿Qué le dijeron desde el sector en la última reunión?
+—Plantean que se cerraría la exportación a Brasil, uno de los principales destinos, porque los márgenes en este tipo de producción no son tan grandes. Con todo equiparado, va a ser imposible.
+—¿Hay otros casos que se presentaron ante el ministerio con el mismo problema?
+—Estuvimos reunidos con el sector del biodiesel. En la provincia hay once plantas y se ve que ya la presentación de la ley ómnibus genera una fuerte incertidumbre y una inseguridad jurídica. Hoy prevén presentaciones judiciales al respecto.
+[H3] "Habrá que poner el impuesto Milei para pagar los juicios de las PyMEs de biodiesel"
+—Hay legisladores que dicen que el nuevo dictámen no contiene las reformas que se habían acordado.
+—Es imposible discutir asi. Es imposible ir a un debate serio, y esto que se observa con los dictámentes que se conocen ahora y no serían los firmados es la frutilla del postre de cómo se maneja. Las modificaciones que ponen sobre el biodiesel no cambian la situación de las PyMEs, y si se aprueba tal como esta planteada hasta ahora verían deteriorada su situación.
+—¿Por qué suceden estas situaciones como la de los dictámenes?
+—Nadie se hace cargo de porqué se incluye tal o cual cosa y nadie lo defiende ante los diputados. Se plantea una enorme modificación y no hay nadie con la valentía para dar los debates. Se presentan personas del Gobierno Nacional que no tienen que ver con el área en discusión a defender algún punto de la ley. Es parte del avasallamiento a mecanismos democrativas.
+—Mencionó al sector pesquero, ¿cómo fueron las conversaciones?
+—Tuvimos reuniones. Las nuevas medidas modifican de un plumazo todo el régimen de la pesca. En la actualidad, el desembarque se tiene que hacer en puertos argentinos, en nuestro caso bonaerense. Esto fomenta la industrialización local. Se tiene que hacer con embarcaciones con bandera nacional y tripulación nacional. La ley ómnibus tira por la borda ese tema. Se trata de perder soberanía sobre zona inclusiva. Por eso también se los vio presentes en el paro y movilización de Mar del Plata.
+—¿Eso se traduce en que cualquiera puede pescar en territorio argentino?
+—Muchas veces se habla de las embarcaciones que operan en la milla 201, pero con estas medidas le das luz verde a que ingresen. Se llevarían el recurso pesquero porque ni siquiera tienen que venir a puertos argentinos. Se borra el Concejo Federal Pesquero, donde están representados los intereses de las provincias y es un mecanismo que permite cuidar el recurso. Volvemos a la extranjerización. Además, pone en peligro las inversiones a nivel local. Ya está teniendo impacto lo que se anuncia porque los pedidos de nuevas embarcaciones a los astilleros fueron suspendidos porque no saben qué va a pasar.
+—Estuvo de recorrida por varios municipios, ¿qué le transmitieron los intendentes durante sus últimos encuentros?
+—Los intendentes lo que ven con preocupación es la evolución económica y social. Ven con muchas dificiutaldaes lo que puede ocurrir en marzo, por el retorno de la escolaridad y la gente retome un ritmo de vida pleno luego de la época de vacaciones. Hoy todos están recibiendo mayores demandas vinculadas al deterioro de las condiciones sociales y mayor demanda en los servicios públicos de salud. En ese escenario, les genera preocupación la evolcion de los ingresos en los municipios, y es algo que se plantea por las distintas fuerzas.</t>
   </si>
   <si>
     <t>Andres Miquel</t>
@@ -844,7 +1978,26 @@
     <t>https://www.pagina12.com.ar/706523-lula-promete-intervenir-tras-el-asesinato-de-una-lideresa-in</t>
   </si>
   <si>
-    <t>2024-01-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula promete intervenir tras el asesinato de una lideresa indígena en Bahía
+Chapeau: El presidente de Brasil bregó por una solución pacífica del conflicto
+Subtítulo: Nega Pataxó fue baleada por terratenientes que disputan las tierras de una hacienda ubicada en el sur del estado de Bahía y que la etnia Pataxó-hã-hã-hãe reivindica como propiedad de sus ancestros.
+Editoria: El Mundo
+Tags: Brasil, Luiz Inácio Lula da Silva, pueblos originarios, printed-edition, luiz-inacio-lula-da-silva, pueblos-originarios, diario
+URL: https://www.pagina12.com.ar/706523-lula-promete-intervenir-tras-el-asesinato-de-una-lideresa-in/
+Notícia completa (13 blocos):
+El presidente de Brasil, Luiz Inácio Lula da Silva, prometió este martes tomar medidas tras el asesinato de Nega Pataxó, una lideresa indígena de la etnia Pataxó-hã-hã-hãe que fue baleada en un conflicto con terratenientes del sur del estado de Bahía, en el noreste brasileño.
+"Estoy conversando con el gobernador (de Bahía) Jerônimo Rodrigues y la ministra (de los Pueblos Indígenas) Sônia Guajajara, que fue a la región para abordar la situación", expresó el mandatario en sus redes sociales. "Quiero poner al Gobierno federal a disposición del gobernador y de los pueblos indígenas para encontrar una solución de forma pacífica. Mi solidaridad con la familia de Nega Pataxó", añadió.
+[H2] La muerte de la lideresa
+María da Fátima Muniz de Andrade, conocida como Nega Pataxó, era hermana del cacique Nailton Muniz, el líder de los pataxó en la región. Fue asesinada el domingo en un ataque perpetrado por un grupo de ruralistas --término utilizado en Brasil para referirse a comerciantes y empresarios del sector agrícola-- identificado como "Invasión Cero", que movilizó a 200 de sus miembros a través de una convocatoria en WhatsApp.
+El llamado instaba a recuperar por medios propios las tierras de una hacienda ubicada en el municipio de Potiraguá, en el estado de Bahía, que fue ocupada el sábado por indígenas que lo reivindican como propiedad de sus ancestros. Se trata de una vieja disputa que está hace años en los tribunales y que impide a la estatal Fundación Nacional de los Pueblos Indígenas (Funai) avanzar con el proceso de demarcación del territorio pataxó.
+"El cacique Nailton fue tiroteado y su hermana, Nega Pataxó, fue asesinada. Otras dos personas fueron sometidas a palizas y a una mujer le quebraron un brazo. Otros heridos fueron hospitalizados pero no corren riesgo de vida", señaló en un mensaje publicado en sus redes sociales la Articulación de los Pueblos Indígenas de Brasil (APIB), organización que representa y trabaja en defensa de los derechos de los pueblos indígenas en Brasil. "Exigimos que las autoridades investiguen el caso. Reiteramos que la delimitación de los territorios indígenas es el único camino para amenazar la escalada de violencia que afecta a los pueblos de la región del sur de Bahía", añadió.
+Pese a que la APIB afirmó que entre los agresores que tirotearon a sus tres líderes había miembros de la policía, la Secretaría de Seguridad Pública del estado de Bahía negó que sus agentes hubiesen intervenido en el tiroteo. La policía informó igualmente en un comunicado que le incautó dos pistolas, dos revólveres, cargadores y municiones a dos miembros del grupo de hacendados, que fueron detenidos y acusados de homicidio, intento de homicidio y portación ilegal de armas.
+Hay muchas otras zonas de Brasil en donde hay conflictos de esta índole. Sin ir más lejos, el viernes el Gobierno de Brasil aprobó el envío de la Fuerza Nacional de Seguridad Pública, un cuerpo de élite compuesto por policías militares nacionales, a la tierra indígena Tekohá Guasu Guavira, ubicada en el estado de Paraná, que desde 2020 vive inmersa en un conflicto entre indígenas y terratenientes por la delimitación de su territorio y donde a principios de este año tres indígenas fueron heridos por un ataque a tiros.
+[H2] El avance del agronegocio y la minería
+Pese a que el regreso de Lula a la Presidencia en enero del año pasado y la creación del Ministerio de los Pueblos Indígenas permitió a la Funai desempolvar varios procesos de delimitación de reservas que habían sido archivados por el entonces presidente Jair Bolsonaro, la violencia contra los pueblos originarios no cesó en el territorio brasileño. Precisamente, los conflictos volvieron a agravarse luego de que el Congreso, de predominio conservador, aprobara en septiembre una ley que limita los derechos de los indígenas sobre sus tierras ancestrales para permitir el avance del agronegocio y la minería. Lula, un declarado defensor de las causas indigenistas, vetó al mes siguiente algunos tramos del texto, incluido el "marco temporal".
+Defendida por el poderoso agronegocio, esa tesis sólo reconoce el derecho de los indígenas, que totalizan 1,7 millones de los 203 millones de habitantes de Brasil, a reivindicar los territorios que ocupaban en 1988, cuando se aprobó la actual Constitución. Es rechazada por las comunidades indígenas con el argumento de que muchos pueblos originarios fueron expulsados a lo largo de la historia de sus territorios ancestrales, especialmente durante la dictadura militar (1964-1985).
+Con una mayoría de votos de 321 diputados y 53 senadores, el parlamento eliminó a mediados de diciembre el veto del mandatario. La APIB reaccionó recurriendo al Supremo Tribunal Federal (STF), máxima corte del país, para pedir la inconstitucionalidad de toda la ley. La misma corte declaró en septiembre inconstitucional el marco temporal pero esa declaración no fue tomada en cuenta por el Congreso cuando aprobó con carácter de urgencia la norma.
+Numerosos científicos consideran que las reservas indígenas son barreras contra la deforestación y, por lo tanto, claves en la lucha contra el calentamiento global. "Es absurdo que mientras el mundo ya reconoce a los pueblos indígenas y sus territorios como una de las últimas alternativas para contener la crisis climática, el Congreso actúe a contramano", dijo la ministra de los Pueblos Indígenas, Sonia Guajajara, en un video difundido en sus redes sociales para expresar su lamento por la decisión parlamentaria.</t>
   </si>
   <si>
     <t>No se puede avalar la venta de la Argentina</t>
@@ -856,7 +2009,25 @@
     <t>https://www.pagina12.com.ar/705259-no-se-puede-avalar-la-venta-de-la-argentina</t>
   </si>
   <si>
-    <t>2024-01-21T03:01:00Z</t>
+    <t xml:space="preserve">Título: No se puede avalar la venta de la Argentina
+Chapeau: Se profundiza el encarecimiento de los alimentos esenciales
+Subtítulo: El DNU y la Ley Ómnibus favorecen a empresas multinacionales y dejan en clara desventaja a un amplio sector de la población.
+Editoria: Cash
+Tags: DNU 70, Ley Ómnibus, UTT, printed-edition, dnu-70, ley-omnibus
+URL: https://www.pagina12.com.ar/705259-no-se-puede-avalar-la-venta-de-la-argentina/
+Notícia completa (12 blocos):
+Bajo el título "La Argentina no se vende", la Mesa Agroalimentaria rechaza el decreto de necesidad y urgencia (DNU) 70/2023, bautizado como “Bases para la reconstrucción de la economía argentina”, por su carácter autoritario y anti-republicano, siendo un claro golpe a las instituciones democráticas.
+El Decreto modifica 300 leyes. A pesar de su vigencia, está pendiente de revisión tanto en el Poder Legislativo como el Judicial, generando un vacío jurídico que atenta contra los pequeños y medianos productores, las economías cooperativas y regionales y el cuidado del medio ambiente.
+Desde el plano ideológico o metodológico, el Decreto da por supuesta una situación de libre mercado que no puede ser tal debido a la importante concentración con la que cuenta la estructura económica argentina. El decreto redactado por estudios de abogados del poder económico, entre los que se encuentran los grandes pooles de siembra del agronegocio, favorece a empresas multinacionales, dejando en clara desventaja a un amplio sector de la población que va desde las clases populares a la pequeña y mediana industria.
+“Esta derogación de leyes beneficia al agronegocio, a la agroindustria concentrada y contaminante y al negocio inmobiliario, y deja a vastos sectores del pueblo desprotegidos”, cuestionó Juan Pablo Acosta, de la Unión de Trabajadores y Trabajadoras de la Tierra (UTT).
+[H2] El otro campo
+Cuando en 2019, el Frente de Todos llegó al gobierno, las organizaciones campesinas, indígenas y de pequeños y medianos productores de alimentos, presentaron un plan Agrario, Soberano y Popular, elaborado en un foro conjunto en mayo de ese mismo año. Dos años después, en junio de 2021, pasada la pandemia y en medio de las elecciones de medio término, se creó la Mesa Agroalimentaria Argentina bajo el lema “el campo que alimenta y construye soberanía alimentaria”.
+Desde la UTT, además de los clásicos verdurazos y su red de mercados propios, se viene impulsando, en conjunto con gobiernos municipales como los de Lomas de Zamora, Quilmes y Avellaneda, espacios de comercialización que acercan a los productores con los consumidores. Los estudios del Centro de Estudios Scalabrini Ortiz (CESO) vienen demostrando, hace más de dos años, que la inflación en este tipo de locales o ferias no solo es menor a las grandes cadenas de supermercados, sino que además ofrecen una mejor calidad de alimentos.
+[H2] Muchos pasos atrás
+La asunción del Milei, lejos de solucionar los problemas de distribución de la tierras, esquema de arrendamientos, concentración económica y especulación a través del abuso en posiciones dominantes en la intermediación económica, el mercado financiero o los favores del Estado (como el dólar soja o el nuevo Bopreal), profundiza el esquema de encarecimiento del alimento en la mesa de los argentinos.
+“Cada uno de los puntos del DNU beneficia a un grupo reducido de empresarios que desde siempre hacen negocios a costa de la miseria del pueblo argentino”, dice el reciente comunicado de la MAA con respecto al DNU que deroga, entre otras, la Ley de Tierras Rurales, la Ley de Manejo del Fuego, arremete contra la regulación estatal del precio de la yerba mate, contra la política de abastecimiento de mercaderías en góndola y el resguardo del mercado interno; también contra leyes que regulan la vitivinicultura y la producción azucarera y contra las limitaciones a la extranjerización y la concentración de la tierra.
+Además la MAA repudió la aplicación generalizada de retenciones del 15 por ciento y del impuesto a la importación llamado PAIS: “Las retenciones e impuestos deben ser segmentados y diferenciados. El campo tiene una diversidad de actores que deben ser tratados de manera diferente”.
+* Licenciado en Economía de la Universidad Torcuato Di Tella y Master en Periodismo de la Universidad del País Vasco.</t>
   </si>
   <si>
     <t>Tomás Astelarra *</t>
@@ -871,7 +2042,42 @@
     <t>https://www.pagina12.com.ar/704013-lula-no-va-al-foro-de-davos</t>
   </si>
   <si>
-    <t>2024-01-15T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula no va al Foro de Davos
+Chapeau: El líder brasileño decidió faltar al Foro Económico Mundial
+Subtítulo: Al repasar los números macroeconómicos, el presidente recordó haberse reunido con la jefa del FMI a quien le dijo "con todo respeto, usted no conoce Brasil" ni su economía.
+Editoria: El Mundo
+Tags: Luiz Inácio Lula da Silva, Brasil, FMI, printed-edition, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/704013-lula-no-va-al-foro-de-davos/
+Notícia completa (29 blocos):
+Desde Brasilia
+Lula y Milei no se verán cara a cara por segunda vez en un mes. A poco de cumplir un año del inicio de su tercer gobierno, el brasileño decidió faltar al Foro Económico Global de Davos, del cual ha sido un visitante frecuente en el pasado, a donde viajará esta semana su par argentino.
+El 10 de diciembre el exlíder metalúrgico fue el gran ausente en la toma de posesión del economista libertario en la Casa Rosada.
+De esta forma Lula dio por tierra con su tradición de participar en las investiduras en Buenos Aires, como lo hiciera durante sus dos primeros mandatos al asistir a los actos inaugurales de los gobiernos de Cristina Fernández y Néstor Kirchner.
+[H2] "Con todo respeto"
+Aunque la agenda de Milei es una incógnita no se descarta que él o alguno de sus ministros se reúnan en Davos con Kristalina Georgieva, la directora del Fondo Monetario Internacional (FMI), para conversar sobre la obtención de más recursos (las arcas argentinas están exhaustas) para el pago de una deuda externa indómita.
+Al contrario de Argentina, Brasil no enfrenta compromisos externos acuciantes y mucho menos problemas de reservas, las cuales suman casi 350 mil millones de dólares, dato aunado a un superávit comercial de 99 mil millones de la misma moneda en 2023, de acuerdo con datos oficiales conocidos el viernes.
+Ese saldo positivo se explica en buena medida por las exportaciones de soja, maíz y mineral de hierro a China. Productos sin valor agregado que requieren mano de obra poco intensiva, dos características favorables de la concentración de la renta en el cada vez más poderoso agronegocio verdeamarillo.
+El presidente y jefe del Partido de los Trabajadores (PT) Lula repasó algunos números macroeconómicos el jueves último ante un grupo de periodistas en el Palacio del Planalto, donde se respira un optimismo cauto frente a un 2024 en el que se realizarán elecciones en más de 5 mil quinientos municipios.
+La robustez de las cuentas externas y el dinamismo del mercado interno, uno de los más importantes del planeta - favorecido por el aumento del salario mínimo y la desocupación en baja- pavimentó el crecimiento del 3,1 % del Producto Bruto en 2023, informó el FMI.
+Durante esa rueda de prensa en el Planalto Lula recordó haberse reunido con la jefa del FMI a quien le dijo "con todo respeto, usted no conoce Brasil" ni su economía. Esto porque en los primeros meses de 2023 los expertos de ese organismo proyectaron un crecimiento del 0,8 % cuando Lula los refutó asegurando habría una expansión superior: pronóstico confirmado por los hechos.
+Las palabras del presidente ante Georgieva no fueron insolentes: sino el gesto de un jefe de Estado que durante su primer mandato (2003-2006) pagó lo que le restaba de su deuda con el Fondo casi al mismo tiempo que Argentina hacía lo propio.
+A menudo Lula dice que Brasil es un país "normal" y se jacta de no tener que recibir, como ocurrió en otros tiempos, a los comisarios fondomonetaristas con sus recetas ortodoxas y privatizadoras.
+[H2] Octubre
+En lugar de volar hasta los fríos Alpes suizos, donde podría haber coincidido con Milei, Lula permanecerá todo enero en el tropical Brasil de temperaturas extremas, como ya lo fueron en noviembre y diciembre, debido al cambio climático que en este país es más exagerado debido a la devastación de la Amazonia.
+Además, razonan en el Planalto, una foto con Georgieva sería poco rentable electoralmente en este año de comicios municipales en los que se pondrá a prueba la popularidad del gobierno, y por propiedad transitiva, las aspiraciones reeleccionistas del mandatario. Lula hizo un hueco en su agenda para recibir a la bastante popular Marta Suplicy, la exintendenta de San Pablo.
+Ella se reafilió al PT, persuasión de Lula mediante, para ser la compañera de fórmula de Guilherme Boulos, el joven postulante a intendente paulistano por el Partido Socialismo y Libertad (PSOL). Con sus doce millones de habitantes San Pablo será escenario de la madre de todas las batallas electorales de octubre.
+Boulos es psicólogo y un conocedor del levantamiento popular argentino de 2001 además de acompañar la marcha de los movimientos sociales latinoamericanos. En 2022 fue el diputado federal más votado del estado de San Pablo. Logró esa alta votación pese a no contar con una estructura partidaria poderosa ni los recursos del estado, de los que sí se sirvió su principal rival, el diputado Eduardo Bolsonaro, gracias al aporte y la influencia de su padre Jair.
+Bolsonaro hijo, quien pese a quedar detrás de Boulos tuvo una buena votación que le permitió permanecer en la Cámara baja federal, utilizó la tribuna para propagandizar la candidatura de Javier Milei en los comicios argentinos del año pasado.
+[H2] Agronegocio y Bolsonaro
+El exitoso balance económico del primer año de gobierno lulista no está exento de contradicciones.
+Los números macro indican un crecimiento del orden del 3 por ciento del Producto Bruto (aún no se publicaron cifras oficiales definitivas) , gracias a lo cual mejoró el consumo y la ocupación. Pero sin un avance en la distribución de la riqueza ni un aumento importante de los puestos de trabajo formales bien remunerados.
+Tampoco ocurrió un empoderamiento considerable de las organizaciones sindicales avasalladas por la reforma laboral aprobada durante el gobierno golpista de Michel Temer (2016-2018), y luego de una represión policial pocas veces vista en Brasilia donde por primera vez en años hubo el despliegue de tropas del Ejército, en lo que sería un ensayo de la posterior militarización del gobierno durante la gestión de Bolsonaro (2019-2022).
+Lula y su ministro de Hacienda, Fernando Haddad, quien suele recibir más elogios del mercado que de sectores del PT, tampoco pudieron modificar la estructura económica cada vez más primaria y financierizada. Una configuración que el gobierno intenta revertir por medio de una política de financiamiento de obras de infraestructura, donde el Banco Nacional de Desarrollo Económico y Social (BNDES) cuenta con el apoyo del Nuevo Banco de Desarrollo del grupo BRICS (Brasil, Rusia, India, China y Sudáfrica, a los que se sumaron más países en enero).
+Al mismo tiempo, el mandatario pasó el año librando un combate casi solitario contra las altas tasas de interés determinadas por un Banco Central teledirigido por la banca privada. Logró que éstas se redujeran al 11,75% anual. Fue un triunfo, pero es cierto que siguen siendo una de las tasas reales más altas del mundo ya que la inflación cerró el año abajo del 5 %.
+El empuje de las exportaciones viene principalmente de los embarques a China realizados por el agronegocio, un sector que además de no hacer un gran aporte tributario, es el principal responsable de la devastación de cientos miles de hectáreas de la Amazonia, en norte, y del Cerrado, un bioma ubicado en la región oeste.
+Con el guiño de Bolsonaro y la complacencia de los militares destacados en la floresta, los grandes y medios hacendados incendiaron e invadieron tierras fiscales entre 2019 y 2022. Al tiempo que penetraban a sangre y fuego en las reservas de los pueblos originarios, que son los mejores guardianes de la selva.
+Esa misma clase terrateniente dio un abierto respaldo a la reelección de Bolsonaro, y parte de ella apoyó el intento golpista del 8 de enero de 2023 para mantener al capitán en el poder pese a la victoria de Lula.
+Y varios miembros de su bloque parlamentario, conocido como la Bancada del Buey, una de las más importantes del Congreso, brillaron por su ausencia el lunes pasado cuando el presidente, congresistas y jueces recordaron el aniversario del golpe fallido.</t>
   </si>
   <si>
     <t>"Un autoritarismo represor, clasista y racista"</t>
@@ -883,7 +2089,33 @@
     <t>https://www.pagina12.com.ar/701894-un-autoritarismo-represor-clasista-y-racista</t>
   </si>
   <si>
-    <t>2024-01-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: "Un autoritarismo represor, clasista y racista"
+Chapeau: Campesinos e indígenas organizados en rechazo al megadecreto de Milei
+Subtítulo: Lo rechazan por antidemocrático, permitir el extractivismo en territorios ancestrales e impactar la producción de alimentos.
+Editoria: Sociedad
+Tags: Javier Milei, DNU, pueblos originarios, printed-edition, javier-milei, pueblos-originarios, diario
+URL: https://www.pagina12.com.ar/701894-un-autoritarismo-represor-clasista-y-racista/
+Notícia completa (20 blocos):
+Movimientos campesinos y comunidades indígenas rechazan las medida del Gobierno nacional --tanto el megadecreto como el proyecto de ley ómnibus-- por atentar contra la producción de alimentos, debilitar la soberanía alimentaria y facilitar el avance del modelo extractivo sobre territorios comunitarios.
+La Confederación Mapuche denunció que el Presidente implementa "un autoritarismo represor, clasista, racista y organizado para una mayor explotación a manos de los grupos de poder económico". Y hacen un llamado a la movilización y la más amplia unidad para frenar la quita de derechos.
+Doce organizaciones de La Plata, Berazategui y Florencia Varela, zona de producción hortícola por excelencia, emitieron un comunicado conjunto en repudio a las medidas del gobierno de Javier Milei. "Se trata de un ajuste brutal sobre campesinos, trabajadores, el pueblo; y una gigantesca entrega de la soberanía", denuncian la Unión de Trabajadores y Trabajadoras de la Tierra (UTT), la Federación Rural, el Movimiento Nacional Campesino Indígena (MNCI-Vía Campesina), Mujeres de la Tierra y la Asociación de Medieros (Asoma), entre otras.
+[H2] "Una profunda crisis"
+Puntualizan que la devaluación, la desregulación del precio de los alquileres y el aumento de los combustibles, entre otros medidas, provocan una "profunda crisis" en el sector que afectará a toda la población por el consecuente aumento del precio de los alimentos.
+La unión de doce organizaciones bajo el paraguas de la "Multisectorial Agraria La Plata", es también una muestra de la diversidad en la acción. Lo explicitan en el comunicado y hacen un llamado a otros espacios: "Hoy más que nunca es necesaria la más grande unidad para defender lo conquistado, seguir peleando por lo que falta y, al calor de la lucha, impedir los planes de esta derecha reaccionaria y ponerle freno a la represión".
+Desde la Confederación Mapuche de Neuquén (CMN) declararon que las comunidades originarias de la provincia se declaran "bajo estado de amenaza ante una Presidencia que promueve odio racial y que busca privar de derechos al pueblo, conquistas que nadie nos regaló y que no vamos a regalarle a ningún gobierno por más protocolos represivos que muestren", en referencia a Patricia Bullrich.
+"Hemos vivido un sistema democrático débil, incompleto, desigual, que ha impedido que las naciones indígenas ocupen el lugar que nos corresponde. Pero con todas esas falencias que son reparables con la movilización popular, este sistema desaparece ante un autoritarismo represor, clasista, racista y organizado para una mayor explotación a manos de los grupos de poder económico concentrados", denunció la Confederación Mapuche.
+Además expresó su rechazo al decretazo y al proyecto de ley ómnibus, llamaron a la defensa de los bienes comunes, los territorios indígenas y a la unidad del campo plurinacional y popular.
+La Mesa Agroalimentaria Argentina (MAA) definió al megadecreto como una medida "autoritaria" y --junto a las medidas enviadas al Congreso-- las catalogaron como "un fuerte golpe a la producción de alimentos".
+La Mesa Agroalimentaria está conformada por la UTT, la Federación de Cooperativas Federadas (Fecofe), el Movimiento Nacional Campesino Indígena Somos Tierra (MNCI-ST), Bases Federadas y la Federación de Organizaciones Nucleadas de la Agricultura Familiar (Fonaf). Y está en las antípodas de la Mesa de Enlace y del sector empresario representado por Aapresid (Asociación de Productores de Siembra Directa --en la actualidad con referentes en la Secretaría de Agricultura y del INTA--).
+[H2] "La miseria del pueblo"
+La Mesa Agroalimentaria denunció que cada punto del DNU beneficia a un grupo reducido de empresarios "que desde siempre hacen negocios a costa de la miseria del pueblo". Y rechazron la mirada neoliberal del Gobierno que "deja todo en manos del mercado".
+Todos los sectores campesinos e indígenas coinciden en que la derogación de la llamada "ley de tierras" (que limita la extranjerización) profundizará el extractivismo minero, petrolero, forestal y del agronegocio. Al mismo tiempo implicará mayor concentración de tierras en pocas manos.
+La Asociación Campesina del Abaucán (Acampa) de Catamarca es un espacio autónomo que impulsa desde hace más de dos década, una emblemática feria de semillas criollas en el oeste provincial. Manuel Aguirre integra Acampa, es productor y comunicador en la radio comunitaria Horizontes (en Medanitos). "El Gobierno le da más libertad de acción a las grandes empresas y al mismo tiempo les da vía libre para que sigan contaminando y saqueando nuestros territorios, al mismo tiempo que dejan más pobre al pueblo", afirmó Aguirre.
+Recordó que en la zona ya padecen a la minera china Liex Zijin con el proyecto de explotación de litio "Tres Quebradas", que no ha dado trabajo ni desarrollo local y atenta contra el desarrollo turístico y agropecuario del lugar. Aguirre advirtió que los sectores populares "no se quedarán de brazos cruzados", que harán respetar sus derechos y forma de vida y llamaron a organizarse y tener mayor articulación: "La única forma es unirnos y luchar todos juntos".
+[H2] "No a la minería de litio"
+El Presidente Milei, en una entrevista televisiva, dio a conocer el interés del multimillonario Elon Musk y de empresas de EE.UU. por el litio de Argentina. Mariela Alancay de la comunidad indígena de Aguas Blancas -- Salinas Grandes de Jujuy, lugar codiciado por las mineras-- le respondió: "Tiene que venir aquí y ver la realidad. Nosotros vivimos y trabajamos aquí por generaciones, tenemos el ganado y cuidamos las salinas. Tenemos derechos, son nuestros territorios y ya dijimos que no queremos minería de litio".
+Alancay integró el Tercer Malón de la Paz que viajó desde Jujuy a la Capital Federal en reclamo contra la reforma constitucional y acampó frente la Corte Suprema (sin respuesta).
+Además del Artículo 75 de la Constitución Nacional, la Declaración de Naciones Unidas para los Pueblos Indígenas y el Convenio 169 de la OIT (que en Argentina tiene rango supralegal), las comunidades originarias enarbolan el derecho de quien vive en el lugar. Mariela Alancay lo resume: "Nuestros ancestros nos dejaron esta naturaleza, estos territorios sanos y limpios para los que trabajemos. Nosotros cuidamos la Pachamama y se las dejamos a nuestros hijos y nietos. Por eso la defendemos y por eso decimos no al litio, sí al agua, sí a la vida".</t>
   </si>
   <si>
     <t>Las mujeres originarias frente a la dictadura del capital</t>
@@ -895,7 +2127,31 @@
     <t>https://www.pagina12.com.ar/701056-las-mujeres-originarias-frente-a-la-dictadura-del-capital</t>
   </si>
   <si>
-    <t>2024-01-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: Las mujeres originarias frente a la dictadura del capital
+Chapeau: El shock del DNU, el protocolo antipiquetes y la Ley Ómnibus
+Subtítulo: El gobierno de Milei-Villarruel anuncia y promete más miseria, represión, muchos modos de morir y de mal vivir. Frente a eso se levantan las voces de los pueblos y en especial de las mujeres que están en la primera línea de la defensa de la vida.
+Editoria: Las12
+Tags: pueblos originarios, DNU, Ley Ómnibus, Javier Milei, printed-edition, pueblos-originarios, ley-omnibus, javier-milei
+URL: https://www.pagina12.com.ar/701056-las-mujeres-originarias-frente-a-la-dictadura-del-capital/
+Notícia completa (18 blocos):
+El gobierno que asumió el 10 de diciembre, cuando se celebraban 40 años de “recuperación de la democracia”, está empeñado en pulverizar todo resto de democracia para convertir a la Argentina en un coto de caza de los grandes empresarios transnacionales, las oligarquías locales, estableciendo una férrea dictadura del capital extranjero, y de las fuerzas políticas y militares locales que lo resguardan.
+Milei levantó la bandera de remate de las empresas e instituciones del Estado, de la soberanía, de los derechos de los pueblos, de las mujeres y disidencias, de la naturaleza. En el discurso inaugural rindió homenaje al genocida Julio A. Roca, responsable de las políticas de exterminio de los pueblos originarios sobre las cuales se levantó el Estado Nación llamado Argentina. Milei caracterizó a Roca como “uno de los mejores presidentes de este país”. No se trata de una cita caprichosa. Es el anuncio de una reorganización de la sociedad inspirada en el artífice del genocidio indígena, y de sus sucesores videlistas -también admiradores de Roca y admirados por Villarruel y su corte negacionista-.
+No sorprende en este marco de reivindicación de los genocidios, que el gobierno de Milei estreche los vínculos con EE.UU. y con el Estado sionista de Israel, cuando está realizando un brutal genocidio del pueblo palestino. La abstención de Argentina en las Naciones Unidas frente a la propuesta de cese del fuego ilustra de qué libertad nos hablan: la de matar a niños, niñas, jóvenes, mujeres, a un pueblo entero, bajo los bombardeos despiadados, las balas, el hambre, la falta de agua o de acceso a los hospitales.
+En esa línea de celebración de la crueldad, se inscriben las primeras medidas de shock como el DNU, el Protocolo antipiquetes, y la Ley Ómnibus, que tienen como denominador común el ataque violento a los derechos populares.
+Lourdes Albornoz, del pueblo Diaguita, advierte que “esta dictadura de la depredación tiene sus resistencias en los cuerpos y los vínculos de las mujeres que criamos, guardianamos, sostenemos. Hablamos de crisis sistémica, porque también se encuentran en crisis los antiguos modelos de representación política. Vemos que algunos dirigentes deciden replegarse a la posición de la espera-especulación, mientras otros redoblan la velocidad para buscar escondrijos por donde insertarse en la compleja arquitectura del saqueo. Por suerte la memoria de la organización sigue rebrotando, y nos encuentra en miles de iniciativas resilientes a niveles locales, nacionales e internacionalistas”.
+Libia Tujuayliya Gea Zamora, mujer Wichi, hija de una histórica organizadora y concientizadora de las mujeres originarias, Octorina Zamora, señala: “El tema central es la propiedad de la tierra, de quién es la tierra y quiénes se la disputan. No es la intención reducirlo todo a la lucha territorial, pero es el gran problema acá. Por algo la formación del Estado estuvo basada en el dominio del Estado colonial sobre las comunidades indígenas, por algo Roca llevó adelante la matanza de pueblos indígenas, por algo los gobiernos de este país se han dedicado siempre a avanzar sobre nuestros territorios, por eso se hicieron estas extranjerizaciones de tierras, y por eso uno de los principales temas que se trata es la venta de los recursos naturales de los territorios habitados por pueblos indígenas. Hay una importancia muy grande en sostener las luchas territoriales, que están siendo retomadas por las mujeres, porque cuando hablamos de territorio hablamos de esta tierra que tiene un montón de riquezas, que es donde está toda la fuerza espiritual de nuestros pueblos, porque ahí nacieron, murieron y fueron enterrados nuestros ancestros. Está también el otro territorio, que es el territorio cultural, el territorio físico, el territorio espiritual. Creo que ésa es la fuerza, la fortaleza que tiene la lucha de las mujeres indígenas”.
+[H2] El DNU y la Ley Omnibus contra todos los derechos
+En un análisis del DNU, la Red de Profesionales Indígenas señala el riesgo que implica para las comunidades originarias la reforma a la Ley 26.737 que establece ciertos límites a la extranjerización de la tierra. Señalan que “el Presidente Milei pretende entregar el litio a Elon Musk, el agua a Mekorot, el fuego a los agronegocios y al extractivismo inmobiliario, el aire a los chemtrails y a Starlink, y las semillas a Bioceres / Syngenta / Bayer / Monsanto. Es decir, al poder real. El DNU pretende adaptar el marco legal jurídico-normativo de Argentina a los requerimientos del poder financiero global”.
+También el Tercer Malón de la Paz, expresa su rechazo por considerar “que el DNU es improcedente, inconstitucional, y nos recuerda la maniobra llevada adelante por Gerardo Morales, en la reforma inconstitucional de Jujuy”. Cuestionan “la derogación de la Ley de Tierras Rurales, sancionada en 2011, que contiene un artículo importante que prohíbe a extranjeros ser propietarios de inmuebles ribereños de cuerpos de agua (ríos, lagos, cuencas) y zonas de seguridad de frontera. Extranjerizar nuestros suelos se traduce en perder nuestra soberanía sobre los bienes comunes asociados al suelo y agua. Las comunidades indígenas podrán ser expulsadas por la megaminería metalífera y de litio, la expansión de la frontera sojera-ganadera, foresto-industrial y el deslizamiento de la explotación hidrocarburífera”.
+Paula Alvarado Mamani, integrante de la Comunidad Tres Ombúes de La Matanza, abogada perteneciente al Pueblo Kolla, preside la Comisión de Derechos de Pueblos Originarios de la Asociación de Abogadas y Abogados de Buenos Aires. En un análisis del DNU expresa esa comisión: “Las consecuencias para los Pueblos Originarios son graves. En la actualidad no se cuenta con una ley de propiedad comunitaria que proteja a los Territorios Indígenas, no logró prorrogarse la ley 26160 de relevamiento territorial comunal que evita los desalojos, y aunque por medio del decreto 805/2021 de Alberto Fernández se prorroga hasta el 2025, los territorios ancestrales y territorios sagrados están en peligro. … Esta situación no es nueva para los Pueblos Originarios, el genocidio, el terricidio y ecocidio continúan, se perpetúan y profundizan”.
+[H2] Leyes y gestos racistas
+El racismo y el patriarcado no se expresa solo en leyes y decretos, sino también en los gestos y actos como el mentiroso “desalojo del Tercer Malón de la Paz” de su permanencia frente a los Tribunales, un día después que la Asamblea del Malón había decidido regresar a sus territorios de origen. El operativo lo realizó la Policía de la ciudad, junto al personal del Espacio Púbico e Higiene Urbana. Un vergonzoso operativo para la foto, pero no para dar respuesta a ninguno de los problemas que los pueblos traían para resolver por necesidad y con urgencia. Política “higienista” profundamente racista, que se repitió en el acto de desalojo del grupo que se encontraba instalado en la esquina del Congreso, y en el levantamiento de la carpa que hacía casi 4 años sostenía Félix Díaz, referente indígena qom ligado a Mauricio Macri, quien ahora se reunió con Patricia Bullrich. Sobre este último gesto nos dice Vero Azpiroz Cleñan, politóloga mapuche de la Comunidad Epu Lafken de Los Toldos: “La ultraderecha, ahora en la vocería oficial del Ministerio de Inseguridad y de Capital Humano, nos configuró (a los pueblos originarios) en un cliché. Lo expresa la figura de Felix Díaz. Eligieron mostrar al “indio permitido”: hombre, evangélico, sin espiritualidad propia del pueblo qom, con algo de folklore en su vestimenta, desterritorializado, para legitimar el inicio de una gestión que, hasta ahora, es antidemocrática. Pero lo más importante fue el "acto de limpieza e higienización" de la Plaza de Mayo. En el autoritarismo de mercado todo se compra y todo se vende. No sabemos aún a qué precio fue”.
+Señala Tujuayliya Gea Zamora: “La lucha indígena ha sido ninguneada desde antes que llegara La Libertad Avanza. Hemos tenido gobiernos que dentro del progresismo han dado garantías y han puesto en agenda la cuestión indígena, pero siempre con políticas incompletas, desfinanciadas, con instituciones que van ensayando y errando constantemente. Tenemos procesos judiciales en el territorio que están incompletos, mujeres indígenas que piden como mínimo una condena a su abusador, a las que se les ha hecho bajar denuncias. Tenemos una Ley 26160 que cada cuatro años hay que estar haciendo una pelea para sostenerla, incluso en gobiernos que se han declarado amistosos con nuestros pueblos. Con el tema de la salud indígena mucho más. En este país no existe política intercultural, política indígena específica para tratar las situaciones que vivimos. No hay tampoco un sistema educativo inclusivo. La libertad Avanza va a intentar destruir lo poquito que se pudo construir. Nosotros venimos ya de políticas discriminatorias, donde nos han puesto de lado, nos han mantenido en reservas indígenas en las orillas de nuestros propios territorios, en las partes menos productivas, más arrasadas, donde ya ha pasado la industria, ha avanzado la frontera agraria, se están echando agrotóxicos, nos han contaminado el río, nos han talado el monte. En este contexto llega un gobierno que se plantea terminar de destruir lo que pudimos sostener. Van a buscar avanzar sobre el desierto verde, y si es necesario nos van a cagar a tiros o nos van a matar de hambre, si se lo permitimos”.
+Relata Lourdes que “el 20 de diciembre, mientras reprimían a los manifestantes en Buenos Aires, en la comunidad Indio Colalao en Tucumán se presentaba un terrateniente junto a la policía para usurpar territorio de la sede comunitaria. En ese lugar la comunidad siembra, se reúne, y lleva adelante proyectos de radio comunitaria, allí preservan los vestigios arqueológicos, es el corazón de su territorio. El usurpador y la policía no contaban con ninguna orden judicial, solamente un argumento: "ustedes ya han perdido". Esta arremetida simbólica, que pretende borrar años de conquistas en materia de derechos de pueblos indígenas, no involucra solamente al presidente y su "casta" de aliados, sino que en él resurgen y se alinean las fantasías fascistas de los sectores dominantes más violentos de la sociedad argentina y de los territorios.”
+En esa perspectiva “las mujeres pasamos de ser consideradas sujeto de derecho en el plano formal, a estar en el foco de la persecución política y social. Por defender los territorios, las aguas, las semillas, las reuniones, nuestras organizaciones y nuestros cuerpos son la primera línea donde recaen las violencias. Se agudiza la violencia machista patriarcal, se fracturan las redes que nos costó años construir, la violencia institucional y la económica nos sacuden y nos devuelven al individualismo y a la competencia del sálvese quien pueda”.
+[H2] Tiempo de resistencia
+Nos dice Lourdes: “En los territorios de cada provincia se libran todos los días batallas anticoloniales que resisten la avanzada extractivista que arrasa con la vida, con políticas de saqueo que llevan varias décadas en nuestro país: agronegocios, megaminería metalífera … En ese contexto, los pueblos naciones indígenas son la última frontera que resiste el saqueo que viene disfrazado de falsas promesas de transición energética y capitalismo verde: el litio, el cobre, alimentos transgénicos, salud hegemónica… En el caso argentino hace décadas que se viene adaptando el marco legal democrático del país a los intereses de las empresas trasnacionales. El ejemplo más claro fue la reforma de la constitución de Jujuy y ahora de la Rioja. Con la llegada de la dictadura “anarcocapitalista” al poder político, por vías democráticas, se acelera el proceso de entrega, despojo y genocidio. Pretenden borrar las identidades individuales, las culturas ancestrales, las economías preexistentes. Este movimiento de la historia nos interpela a construir con más fuerzas lazos intersectoriales, plurinacionales, para resistir. La diversidad, la multiplicidad, la presencia y la raíz dispersa por todo el territorio, es nuestra posibilidad de reexistencia. Años de crecimiento bajo la tierra hoy muestran los cauces donde acuerparnos”.
+El tiempo de crear esa propuesta política es ahora. Las mujeres indígenas están como siempre, en la primera línea de defensa de la vida. Contra los genocidios históricos y los presentes, en Abya Yala y en Palestina, se van bordando colectivamente, y con muchos colores, los tejidos de la Resistencia.</t>
   </si>
   <si>
     <t>Claudia Korol</t>
@@ -910,7 +2166,30 @@
     <t>https://www.pagina12.com.ar/700356-regresion-ambiental-los-peligros-de-la-ley-omnibus-que-impul</t>
   </si>
   <si>
-    <t>2024-01-02T12:15:41Z</t>
+    <t xml:space="preserve">Título: Regresión ambiental: los peligros de la Ley Ómnibus que impulsa Milei
+Chapeau: Favocere a capitales extranjeros y pone en riesgo bosques y glaciares
+Subtítulo: Gabriela Vizental, periodista especializada en ambiente, advirtió sobre los riesgos en materia ambiental que prevé la sanción de la ley ómnibus. Qué ecosistemas estarán en riesgo.
+Editoria: Radio 750
+Tags: Medio Ambiente, Ley Ómnibus, Javier Milei, La García, medio-ambiente, ley-omnibus, javier-milei, la-garcia
+URL: https://www.pagina12.com.ar/700356-regresion-ambiental-los-peligros-de-la-ley-omnibus-que-impul/
+Notícia completa (17 blocos):
+El DNU y la ley ómnibus que envió al Congreso el presidente Javier Milei pondrán en peligro ecosistemas clave para la Argentina: la legislación en la que pretende avanzar el nuevo mandatario pone en riesgo glaciares y bosques, al habilitar la producción contaminante y extractivista en esos ecosistemas, fundamentales para la vida humana. Además, la derogación de la ley de Tierras habilitará la extranjerización de grandes parcelas, incluidas ríos y otros recursos naturales.
+[H3] La ley ómnibus de Javier Milei: el detalle de los artículos y las repercusionesMilei envió al Congreso la ley ómnibus
+En su columna de Ambiente y Salud en La García, la periodista Gabriela Vizental, afirmó que lo que propone la Ley Ómnibus en materia de medio ambiente es "suprimir la regulación estatal en favor de capitales privados". Los expertos, en tanto, ya advierten sobre una fuerte regresión ambiental. "Se propone suprimir la regulación estatal en favor de capitales privados y modificar normativas para permitir actividades como la agropecuaria y minera, entre otras, sobre los bienes comunes naturales", sostuvo en diálogo con AM750.
+En concreto, la ley ómnibus avanza sobre la protección de los glaciares prevista por una ley sancionada en el 2010 tras una larga lucha de organizaciones ambientales. En la actualidad, la normativa impide la actividad minera, mientras que el proyecto enviado al Congreso autoriza la actividad en el terreno periglaciar.
+Además, Milei pretende autorizar la deforestación con fines productivos en bosques que hoy cuentan con protección también por ley. De este modo, se permitirá que en las zonas I (rojo) y II (amarillo) donde hoy se encuentra prohibida la deforestación sean autorizados proyectos productivos.
+La normativa que el Presidente envió al Congreso además autoriza las quemas para "limpiar" campos y otras zonas con fines productivos, ya sea para ampliar la frontera agropecuaria como para emprendimientos inmobiliarios. Hoy existe una restricción muy fuerte, que en caso de aprobarse la ley ómnibus dejará de existir: sólo se deberá permiso para iniciar el fuego y, si pasados los 30 días de la solicitud no hay respuesta del Estado, quedará autorizado automáticamente.
+"Esta propuesta avanza sobre la Ley de Bosques de 2007 y la Ley de Glaciares de 2010, dos leyes de presupuestos mínimos", agregó Vizental.
+[H2] Las modificaciones que propone Javier Milei en materia ambiental
+"En el área de medio ambiente se sugieren cambios en la ley de quema, permitiendo a los productores a realizar cortafuegos y acciones preventivas hoy vedadas por la legislación", es uno de los primeros puntos mencionados en la normativa.
+En ese sentido, destaca que "el Fondo de bosques nativos pasará a financiarse directamente del Presupuesto, y se simplifican los procedimientos para la explotación de bosques en zonas habilitadas comercialmente a tal fin".
+Asimismo, se realiza "una modificación a la Ley de Glaciares a fin de habilitar (con los informes ambientales exigidos por la normativa) la actividad económica en la zona periglacial, revirtiendo un avasallamiento del poder federal sobre las provincias".
+En este contexto, la periodista explica: "Primero, desfinancia la Ley de Bosques, es decir, le quita al Fondo Nacional para la Preservación de los Bosques Nativos un recurso económico que hasta ahora sale de un porcentaje (3%) de retenciones a las exportaciones al agronegocio. Con eso se compensa a los titulares de las zonas rojas y amarillas donde la ley prohíbe desmontar".
+"Por otro lado, si se pierden las zonas periglaciares -las que rodean los glaciares- se pierden lo que se llaman estas 'fábricas de agua'. Si se desfinancia Parques Nacionales, no solo se desfinancia proteger los glaciares, sino también toda la biodiversidad a lo largo y ancho de todo el país", enfatizó.
+"Creo que esta ley apunta más a los glaciares de la cordillera norte, que es donde se pueden extraer todos los minerales. Si se desfinancian los Parques Nacionales, pueden aparecer los incendios en esta época y hablamos de bosques nativos, sobre todo en la Patagonia", concluyó Vizental.
+[H3] Seguí leyendo:
+[H3] El texto completo de la Ley Ómnibus de Javier Milei
+[H3] Universidades aranceladas para extranjeros no residentes: los cambios en educación de la ley ómnibus</t>
   </si>
   <si>
     <t>Un Estado al servicio de la concentración económica</t>
@@ -922,7 +2201,33 @@
     <t>https://www.pagina12.com.ar/699284-un-estado-al-servicio-de-la-concentracion-economica</t>
   </si>
   <si>
-    <t>2023-12-31T03:01:00Z</t>
+    <t xml:space="preserve">Título: Un Estado al servicio de la concentración económica
+Chapeau: Crisis alimentaria y social
+Subtítulo: Las políticas del nuevo gobierno llevan a los sectores medios y populares al borde de una crisis humanitaria, mientras fomentan la ganancia de las grandes empresas en una camino primarizador de la economía.
+Editoria: Cash
+Tags: Crisis alimentaria, printed-edition, crisis-alimentaria
+URL: https://www.pagina12.com.ar/699284-un-estado-al-servicio-de-la-concentracion-economica/
+Notícia completa (20 blocos):
+A tres semanas de la asunción de Javier Milei, los anuncios y medidas explicitan un modelo que financia y favorece la concentración económica en un espiral inflacionario que amenaza con arrastrar a sectores medios y populares a la pobreza, la indigencia y el hambre. Atenta también contra la supervivencia de la industria, las pymes, y los pequeños y medianos productores del campo que alimenta.
+El precio de los alimentos, entre otros cientos de productos que consumen las familias argentinas, se ve motivado al alza por la falta de controles de precios en una estructura empresaria oligopólica, el aumento del precio relativo de las exportaciones, los servicios públicos y los combustibles.
+En paralelo, estas medidas reducen la rentabilidad de pequeños y medianos productores de alimento, ya aquejados por la sequía, el aumento de los insumos, el alquiler y la concentración de tierras, gracias a las ganancias extraordinarias que el capital concentrado del agronegocio viene obteniendo. Y que incrementará con las nuevas políticas, por sus posiciones financieras, oligopólicas y ante una acción desigual del Estado, garantizando sus ganancias e inversiones mientras deja librado al azar el destino de la industria, las pymes, y los pequeños y medianos productores.
+[H2] Los beneficiarios de siempre
+Se van a cumplir 21 años de la nacionalización de la deuda privada de Domingo Cavallo al final del “Proceso de Reorganización Nacional”. Fueron beneficiarios de dicha nacionalización los ahora grandes grupos económicos argentinos, que producen y distribuyen la mayoría de los productos que consumimos, pudiendo establecer de manera unilateral sus precios.
+La nacionalización de las deudas privadas de las grandes empresas a través del Bono para la Reconstrucción de una Argentina Libre (Bopreal) parece replicar esta medida y vuelve a mostrar la intervención del Estado en favor del capital concentrado. Genera, a futuro, una deuda de aproximadamente 30 mil millones de dólares (el doble que la nacionalización de Cavallo y dos tercios de la deuda de Mauricio Macri con el FMI).
+Algunos economistas como Claudio Lozano ya estiman que dos tercios de esta deuda corresponde a intercambios entre las propias empresas con sus filiales extranjeras. Este proceso no cuenta con la debida fiscalización y encubren giros de dividendos, sobrefacturación o fuga de divisas, entre otras trampas que no han podido ser atendidas. En paralelo, la fiscalización del Estado cae en las medianas y pequeñas empresas y productores.
+El sector de pequeños y medianos productores de alimento (que cubre entre el 60 y el 80 por ciento de las frutas y verduras que se consumen en la mesa de los y las argentinas) se ha visto perjudicado por la acción del Estado en el anterior gobierno. La transferencia extraordinaria a los sectores agroexportadores concentrados a través del dólar soja (con un costo de 590 mil millones de pesos) equivalió al impuesto a las grandes fortunas, u ocho años de la pauta publicitaria del Estado que ahora el ministro Luis Caputo exhibe como un recorte de gasto importante.
+[H2] Los perjudicados de siempre
+En paralelo el nuevo gobierno desfinancia las pocas ayudas que existían para nuestro sector, vacía áreas estratégicas y nos condena como pequeños y medianos productores a ser parte del nuevo ministerio de Capital Humano, con un rejunte de ex-ministerios en manos de personas sin experiencia que solo puede llevar a la inoperancia, y cuya ministra, Sandra Pettovello, hizo su primera aparición pública para sumarse a la represión de la protesta social anunciado por la ministra de Seguridad, Patricia Bullrich. No hay anuncios acerca de cómo se piensa afrontar la crisis humanitaria que el propio gobierno fogonea.
+Desde la Mesa Agroalimentaria Argentina (MAA), de la cual formamos parte, ya hemos presentado propuestas concretas, el Programa Agrario para el Alimento, para reducir el precio de los alimentos a través del apoyo a pequeños y medianos productores, el acceso a la tierra, la creación de nuevos Mercados de Cercanía y otras políticas que ya venimos implementando desde las propias organizaciones.
+Los índices elaborados por el Centro de Estudios Scalabrini Ortiz (CESO) demuestran que dichas políticas implementadas desde la UTT a través de proyectos productivos y de comercialización, brindan alimento más sano y barato a los consumidores, reduciendo la brecha de los intermediarios. En dichos estudios, que comparan la evolución de la inflación en grandes cadenas de supermercados con la de los locales y ferias de la Economía Social, Solidaria y Popular (ESSP), se demuestra, por ejemplo, que tras las PASO, la inflación fue de 20 por ciento en las grandes estructuras oligopólicas, frente al 9 por ciento en nuestros puntos de venta. Una clara demostración del componente especulativo y oligopólico de la inflación en Argentina.
+Eso sin comparar la calidad de los alimentos, los beneficios para los productores y las economías regionales. Y el hecho de que, más allá de que para nosotros el alimento es un derecho y no una mercancía (como debatió nuestro referente Nahuel Levaggi con el vocero del agronegocio Antonio Aracre), nuestro sector incluye miles de productores y comercializadoras que hablan de la competencia necesaria para que funcione “la mano invisible” del mercado. Esa de la que hablan los libros de economía, aún en sus corrientes más ortodoxas.
+[H2] Un Estado para cierto mercado
+Los anuncios de las medidas económicas del nuevo gobierno dan por tierra dos mitos muy recurrentes en los discursos neoliberales en Argentina: que el mercado genera oportunidades por igual para toda la población y que el Estado sirve para moderar estos desequilibrios y no para fomentarlos aún más. No estamos ante un Estado que no interviene, sino uno que precisamente interviene para favorecer a los capitales concentrados que, con la histórica ayuda de ese Estado, han generado reglas desiguales de mercado, aumentando la pobreza, la desigualdad social, el hambre y la primarización de la economía con un fuerte beneficio para los grandes capitales multinacionales (que incluyen grandes empresas argentinas).
+Seguiremos organizándonos para mejor la calidad de vida de los y las argentinas, con o sin ayuda del Estado y el mercado. Sin embargo nuestros esfuerzos no son suficientes sin un apoyo de un Estado que lejos está de priorizar el alimento de nuestra población.
+Esta desigualdad del mercado y el Estado claramente se va profundizar con las nuevas políticas económicas, con una brutal licuación de los ingresos de las clases medias y populares y un tipo de cambio, y otras medidas, que favorecen a los sectores agroexportadores sin valor agregado (es decir, sin trabajo).
+Hoy las medianas y pequeñas empresas exportadoras con valor agregado (incluso algunas dentro de nuestro sector) perciben un dólar de 730 pesos (descontando las nuevas retenciones) y pagan sus insumos a un dólar de 940 pesos (con el impuesto País). Esta desigualdad afecta la industria, las pymes y pequeños productores, llevando a la Argentina hacia un esquema de economía primarizada y sujeta a los vaivenes de los precios internacionales.
+En medio de una crisis económica y social, que lejos de menguar va a tender a incrementarse (junto con las estadísticas de pobreza, indigencia y hambre), desde la UTT y las organizaciones del campo que alimenta redoblaremos la lucha y los esfuerzos para seguir organizando la producción y el consumo para ofrecer a las familias argentinas alimentos sanos y lo más barato que la situación nos permita. Además de sostener comedores populares y otras tareas con una visión de cuidado de la comunidad y la Casa Común. Para nosotras y nosotros el alimento es un derecho y no una mercancía.
+*Coordinación Nacional de la UTT</t>
   </si>
   <si>
     <t>Juan Pablo Acosta*</t>
@@ -937,7 +2242,25 @@
     <t>https://www.pagina12.com.ar/699296-lula-derogo-articulos-clave-de-la-ley-de-veneno-sobre-uso-de</t>
   </si>
   <si>
-    <t>2023-12-28T16:33:13Z</t>
+    <t xml:space="preserve">Título: Lula derogó artículos clave de la "ley de veneno" sobre uso de pesticidas
+Chapeau: Un freno al loby del agronegocio
+Subtítulo: El presidente de Brasil, Luiz Inácio Lula da Silva, vetó puntos clave de una polémica ley que flexibiliza las reglas sobre los pesticidas en el país. "Consultados los ministerios competentes
+Editoria: Brasil
+Tags: Lula Da Silva, lula-da-silva
+URL: https://www.pagina12.com.ar/699296-lula-derogo-articulos-clave-de-la-ley-de-veneno-sobre-uso-de/
+Notícia completa (12 blocos):
+El presidente de Brasil, Luiz Inácio Lula da Silva, vetó puntos clave de una polémica ley que flexibiliza las reglas sobre los pesticidas en el país. "Consultados los ministerios competentes, el presidente decidió vetar algunos dispositivos, para garantizar la adecuada integración entre las necesidades productivas, el cuidado de la salud y el equilibrio ambiental", dijo el Palacio presidencial del Planalto en una nota.
+Lula decidió vetar 14 tramos de una decena de artículos de la ley que facilita la aprobación de nuevos agrotóxicos en el país y buscaba otorgar mayores poderes de decisión al ministerio de Agricultura. Luego de más de dos décadas de controversias, el texto fue aprobado en el Senado el 28 de noviembre, con un solo voto en contra.
+El agronegocio, uno de los principales motores de la economía brasileña, tiene en el uso intensivo de pesticidas uno de sus pilares. Brasil consumió 719.507 toneladas de pesticidas en 2021, el 20% del total comercializado en el mundo, según la Organización de las Naciones Unidas para la Alimentación y la Agricultura (FAO).
+Con el veto, la Agencia Nacional de Vigilancia Sanitaria (Anvisa) y el Ibama, principal agencia ambiental, continuarán ejerciendo un papel decisivo en el escrutinio de los agrotóxicos previo a su liberación, potestad que quedaba reservada a Agricultura bajo la ley.
+También será invalidada una regla que permitía al ministerio de Agricultura conceder autorizaciones para agrotóxicos antes de la conclusión del análisis de riesgo del producto.
+Además, excluyó una norma que eximía a las empresas de incluir información en los embalajes, algo que podría llevar al reaprovechamiento de agrotóxicos e incentivar la "desinformación" sobre los productos.
+[H2] El viejo anhelo del agronegocio brasileño
+En la agenda de Diputados desde 1999, el proyecto había sido actualizado en 2022 por los legisladores de la bancada ruralista -la más poderosa en el Congreso-, con el apoyo del entonces mandatario brasileño, el ultraderechista Jair Bolsonaro, ferviente defensor del agronegocio.
+Calificada como "ley del veneno" por sus detractores, el texto fue objeto de duras negociaciones entre los senadores y la administración de Lula. El gobierno consiguió mantener el término "agrotóxico", que los diputados habían reemplazado por los más neutros "pesticida" y "producto fitosanitario".
+Pero no logró impedir un cambio mayor: algunos pesticidas, especialmente los que son comprobadamente cancerígenos o capaces de producir mutaciones, o que provoquen daños ambientales, no serán automáticamente prohibidos.
+En adelante, la prohibición abarcará los productos que presenten un "riesgo inaceptable" para el ser humano o el ambiente, un criterio considerado muy vago para los detractores del texto.
+Además, con la nueva ley, los pesticidas destinados exclusivamente para exportación podrán ser fabricados en el país sin precisar autorización.</t>
   </si>
   <si>
     <t>La lucha contra el extractivismo seguirá en las calles y rutas ante el nuevo gobierno</t>
@@ -949,7 +2272,25 @@
     <t>https://www.pagina12.com.ar/697977-la-lucha-contra-el-extractivismo-seguira-en-las-calles-y-rut</t>
   </si>
   <si>
-    <t>2023-12-23T03:01:00Z</t>
+    <t xml:space="preserve">Título: La lucha contra el extractivismo seguirá en las calles y rutas ante el nuevo gobierno
+Chapeau: Ambientalistas denuncian el "fascismo argentinizado" del presidente
+Subtítulo: Organizaciones sociales y asambleas socioambientales de todo el país advierten que, pese a las amenazas represivas del gobierno, seguirán movilizadas en defensa del territorio y contra el agronegocio, la megaminería y la explotación petrolera.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/697977-la-lucha-contra-el-extractivismo-seguira-en-las-calles-y-rut/
+Notícia completa (12 blocos):
+Desde Tierra del Fuego a Jujuy. Desde Catamarca a Buenos Aires. Asambleas socioambientales de todo el país saben que el gobierno de Javier Milei intentará avanzar con más agronegocio, megaminería, explotación petrolera y monocultivo forestal --entre otras actividades--. Y es unánime la postura: el rechazo al extractivismo y, como eje principal, la movilización popular para defender los territorios.
+"¿Hasta cuándo?", fue la pregunta que unió a organizaciones de 43 ciudades del país. Se trató de una coordinación como hacía tiempo no se veía, de diversos colectivos en el marco de la Campaña Plurinacional Anti Extractiva para denunciar el impacto social, ambiental y sanitario del extractivismo.
+Planificada con mucha anterioridad a la segunda vuelta electoral, uno de los objetivos fue recordar al nuevo presidente el rechazo al modelo político-económico extractivista y, fundamental, articular redes para lo que vendrá. "Esperamos la profundización del sistema extractivista. Por eso estamos en alerta y activando más que nunca los lazos que se necesitan para frenar este modelo de destrucción y muerte. Vienen tiempos difíciles ya que es mano dura lo que se propone desde el gobierno, siempre recordando que estos gobiernos le rinden cuenta al FMI a costa del sufrimiento de los pueblos", afirmó Paula Kaeser, de la Coordinadora Basta de Balsas Soluciones (BFS) y parte de la Campaña Plurinacional.
+El encuentro fue a principios de mes y hubo actividades en Tierra del Fuego, Chubut, Entre Ríos, Neuquén, Misiones, Buenos Aires, Chaco, Córdoba, Entre Ríos, La Rioja, Mendoza, Río Negro, Salta, San Juan, San Luis y Tucumán, entre otras provincias. Se denunció el impacto del agronegocio y las fumigaciones con agrotóxicos, de la megaminería (con los casos extremos de San Juan, Catamarca y la explotación de litio), el monocultivo de árboles (con Misiones y Corrientes como referencias), la explotación petrolera en Neuquén y la exploración en el Mar Argentino, y el impacto negativo de las megarrepresas, donde sobresalen Misiones, Neuquén, Santa Cruz y Mendoza (ésta última provincia aún sin cumplir el fallo de la Corte Suprema para liberar el agua del río Atuel a La Pampa).
+Por su parte, la Unión de Asambleas de Comunidades (UAC) es un espacio emblemático de articulación de luchas provinciales. Se reúne periódicamente desde 2006 y siempre mantuvo la autonomía de los partidos políticos. Del 8 al 10 de diciembre celebraron su 36 encuentro, en la localidad bonaerense de Jáuregui, territorio que padece las fumigaciones con agrotóxicos, las curtiembres contaminantes y uno de los basurales a cielo abierto más grande del país.
+Laura Olivares vive en Jáuregui y es parte de la UAC. Definió al gobierno de Milei como "el fascismo argentinizado". Señaló que las razones de su triunfo son tan diversas como los sectores que lo votaron, pero con eje especial en el hartazgo de las políticas previas que no resolvieron lo más básico de la población. "Esto confirma lo que venimos diciendo hace tiempo, que este modelo no sirve más, es necesaria una democracia real, representativa de los pueblos", resumió.
+Respecto al extractivismo, no tiene dudas de que se intentará avanzar con más megaminería, explotación petrolera y agronegocio. En plena campaña electoral, Milei negó la existencia del cambio climático y sentenció que "una empresa puede contaminar un río todo lo que quiera". Afirmó que el valor del agua es "cero" y propuso la apropiación de ese bien por parte de las empresas.
+Otra muestra, ya como Presidente, es ceder a conducción de la Secretaría de Bioeconomía (nuevo nombre del área de agricultura) a Fernando Vilella, ex decano de la Facultad de Agronomía de la UBA y ex funcionario de Daniel Scioli en Buenos Aires, un aliado incondicional de las compañías de transgénicos-agrotóxicos y de las exportadoras de granos. Lo mismo que su grupo de trabajo, donde sobresalen referentes de la Asociación de Productores de Siembra Directa (Aapresid), empresarios y lobistas del agronegocio local e internacional.
+Olivares remarcó que desde la UAC conocen desde hace años de persecución y hostigamiento a las comunidades que se oponen al extractivismo, donde los gobiernos provinciales también instrumentan la represión. Existen numerosos ejemplos: Andalgalá, Jáchal y Salinas Grandes, por citar solo algunos. Señaló que todo indica que con el nuevo gobierno "será peor", pero advierte que eso no frenará las acciones en defensa del agua y los bienes comunes: "Las asambleas seguiremos en nuestros territorios tejiendo redes, fortaleciendo nuestras luchas, generando resistencia, fortaleciendo la autonomía. Tenemos claro quiénes son los enemigos actuales y estaremos en las calles exigiendo nuestros derechos".
+Una de las características, y fortalezas, del movimiento socioambiental es la presencia en las calles y la acción directa. Así lo demostraron Esquel, Andalgalá, Famatina y Chilecito, Jujuy (con las movilizaciones de los pueblos indígenas), Mar del Plata y Malvinas Argentinas (Córdoba), contra Monsanto, entre otros casos. Los últimos picos masivos fueron Mendoza (2019) y Chubut (diciembre de 2021), donde hicieron retroceder a los gobiernos provinciales con sus intentos de permitir la megaminería. Paula Kaeser dejó un invitación que, de alguna manera, es también una respuesta a las corporaciones extractivas y al gobierno nacional: "Nos vemos en las calles, en defensa del agua y la vida".
+[H2] Protocolo versus movilización
+El "protocolo para el mantenimiento del orden público" que presentó Patricia Bullrich como amenaza para reprimir la protesta social no sorprendió a las organizaciones socioambientales. Tienen muy vivo el recuerdo de Santiago Maldonado y Rafael Nahuel, ambos casos donde tuvieron directa relación las fuerzas comandadas por Bullrich (Gendarmería Nacional y Prefectura Naval). "Este protocolo es inconstitucional y es lo que vimos en Jujuy, con la reforma constitucional este año, donde desde ese momento se viven hostigamientos, persecuciones, violaciones a los derechos humanos y constitucionales", afirmó Paula Kaeser, de la Coordinadora Basta de Falsas Soluciones. Recordó que las organizaciones seguirán exigiendo desde las calles otra democracia, donde se respeten las decisiones de los habitantes que viven en cada territorio y ya dijeron no al extractivismo.</t>
   </si>
   <si>
     <t>El hombre detrás de las idas y vueltas con las retenciones</t>
@@ -961,7 +2302,25 @@
     <t>https://www.pagina12.com.ar/696904-el-hombre-detras-de-las-idas-y-vueltas-con-las-retenciones</t>
   </si>
   <si>
-    <t>2023-12-19T22:53:34Z</t>
+    <t xml:space="preserve">Título: El hombre detrás de las idas y vueltas con las retenciones
+Chapeau: La historia de Fernando Vilella, secretario de Bioeconomía
+Subtítulo: En menos de días las políticas agropecuarias del gobierno de Javier Milei no solo cambiaron el rango del ministerio a secretaría y el nombre de Agricultura a "Bioeconomía" sino que tuvieron que dar
+Editoria: Economia
+Tags: Retenciones, diario
+URL: https://www.pagina12.com.ar/696904-el-hombre-detras-de-las-idas-y-vueltas-con-las-retenciones/
+Notícia completa (12 blocos):
+En menos de días las políticas agropecuarias del gobierno de Javier Milei no solo cambiaron el rango del ministerio a secretaría y el nombre de Agricultura a "Bioeconomía" sino que tuvieron que dar idas y vueltas con anuncios sobre el tema central que embandera a "el campo" desde 2008: las retenciones. Quien tuvo que dar las respuestas en las últimas hora no fue el ministro de Economía, Luis Caputo; sino el aún poco conocido secretario de Bioeconomía, Fernando Vilella.
+Caputo anunció el miércoles pasado que subirían al 15 por ciento las retenciones "no agropecuarias", luego se confirmó que sí subirían las retenciones a cultivos y economías regionales y, finalmente, el lunes dieron marcha atrás para algunos sectores luego de las quejas de la Mesa de Enlace y gobernadores.
+"Vamos a comunicar una diferencia en el proyecto que se va a elevar al Congreso", emparchó Vilella los idas y vueltas de su jefe, el ministro de Economía Caputo y acomodó el inicio de la relación del gobierno de ultraderecha con las entidades agropecuarias, que el viernes fueron corriendo a protestar por haber esperado el fin de las retenciones y encontrarse con un aumento para las economías regionales que el ex ministro de Economía, Sergio Massa, había dejado en cero.
+Vilella anunció que 18 productos regionales volverían a cero y, a cambio, se aumentó de 31% a 33% las retenciones sobre los subproductos de la soja --harina y aceite-- lo que le valió otra queja del Complejo Cerealero-Oleginosa, un núcleo concentrado de empresas muy beneficiadas por la devaluación del 119% del peso.
+¿Quién es Vilella? El hombre bajito y canoso que respondió por la primera marcha atrás del gobierno de Javier Milei. De 68 años, y durante 48 años profesor de la Facultad de Agronomía de la Universidad de Buenos Aires (FAUBA), Vilella se sumó a las "fuerzas del cielo" tras la sorpresiva victoria de Milei en las PASO. La apuesta del decano de la FAUBA entre 1998 y 2006 fue la de presentarse como un experto en "bieconomía" --nombre con el que bautiza su gestión--, una palabra en auge para el agronegocio, ya que permite asociar la biotecnología con la "sustentabilidad", patentes e innovaciones con "cuidado del planeta".
+Vilella llega a la gestión pública nacional --ya había sido subsecretario de Asuntos Agrarios en Buenos Aires durante la gestión del ex gobernador y actual embajador en Brasil, Daniel Scioli-- tras ser director del Programa de Agronegocios y Alimentos, y profesor a cargo de la Cátedra de Agronegocios en la FAUBA, donde también creó la licenciatura de Ciencia Ambientales, entre otros cargos académicos. Esa formación vinculada al agronegocio se reflejó rápidamente en su equipo asesor.
+Tras la primera vuelta electoral, con Milei encaminado al balotaje, el ex decano sumó a Pedro Vigneau --quien fue nombrado como asesor especial y virtual jefe de Gabinete--, ex presidente de Aapresid (Asociación Argentina de Productores en Siembra Directa) y de la organización Maizar, dos influyentes organizaciones del modelo agropecuario dominante. Vilella, Vigneau y Germán Paats --integrante de la Fundación Barbechando, grupo de lobby en el Congreso que se opuso a la Ley de Humedales-- fueron los encargados de hablar con "el campo" cuando Milei prometía cortar relación con Brasil y China --los principales compradores de la materia prima argentina-- y luego del balotaje encabezaron la transición.
+La relación con el mundo del agronegocio --por fuera de la conocida Mesa de Enlace-- de Vilella excede lo académico. El secretario es miembro del Instituto de Ética y Calidad en el Agro (ETICAGRO), de la Asociación Argentina de Biocombustibles e Hidrógeno y preside la Fundación Alimentos Argentinos. Recorrido que le valió, a cinco días de su asunción, un reconocimiento por parte del Instituto Interamericano de Cooperación para la Agricultura, una organización regional que impulsa la incorporación de Agtech y el modelo agroquímico.
+En la previa de jurar como secretario, el 5 de diciembre, Vilella tuvo otro fuerte espldarazo del sector del agronegocio en una reunión convocado por empresas del sector. Presentado por Héctor Huergo, histórico editor de Clarín Rural y ex funcionario de Domingo Cavallo en el INTA, Vilella presentó a su futuro gabinete en una Casona de San Telmo, con valor histórico por ser parte de una histórica familia de la oligarquía ganadera.
+Entre los integrantes de su equipo que fueron confirmados días después están otro ex integrantes de Aapresid, de CREA --otra influyente asociación de empresarios del sector, que nutrió las filas del gobierno macrista--, y el ex CEO de Monsanto y ministro de Agroindustria del gobierno de María Eugenia Vidal, Leonardo Sarquís, quien ocupa el cargo de coordinación del Consejo Federal Agropecuario (CFA).
+En una semana de gobierno de ultraderecha, con el precio de los alimentos por los nubes, Vilella ratificó la idea expresada por Milei y su canciller Diana Mondino al sostener que los precios internos de la carne van a bajar porque el "poder adquisitivo va a hacer que se deprima la demanda y esa depresión afectará los precios". Para eso restará ver ver si la industria no eligirá enviar la producción al exterior con la eliminación de la política de cuotas de exportación.
+En esa confrontación de dos modelos de producción de alimentos, para las mesas de los argentinos o como commidites para la exportación, el secretario también sostuvo esta mañana que el eje de su política será duplicar las exportaciones y generar una "marca país" para "ingresar a los mercados más sofisticados del mundo".</t>
   </si>
   <si>
     <t>El Congreso de Brasil restableció el "marco temporal" para las tierras indígenas</t>
@@ -973,7 +2332,20 @@
     <t>https://www.pagina12.com.ar/695568-el-congreso-de-brasil-restablecio-el-marco-temporal-para-las</t>
   </si>
   <si>
-    <t>2023-12-15T16:53:13Z</t>
+    <t xml:space="preserve">Título: El Congreso de Brasil restableció el "marco temporal" para las tierras indígenas
+Chapeau: Eliminan el veto de Lula que protegía la demarcación de los territorios
+Subtítulo: El Congreso de Brasil restableció artículos clave de una ley que limita los derechos de los indígenas sobre sus tierras ancestrales, al eliminar el veto del presidente Luiz Inácio Lul
+Editoria: Brasil
+Tags: pueblos originarios, Lula Da Silva, pueblos-originarios, lula-da-silva
+URL: https://www.pagina12.com.ar/695568-el-congreso-de-brasil-restablecio-el-marco-temporal-para-las/
+Notícia completa (7 blocos):
+El Congreso de Brasil restableció artículos clave de una ley que limita los derechos de los indígenas sobre sus tierras ancestrales, al eliminar el veto del presidente Luiz Inácio Lula da Silva a esa normativa. La norma que fija el denominado marco temporal de las tierras indígenas supone una "tesis" para limitar el reconocimiento de tierras indígenas. La tesis solo reconoce a las comunidades indígenas derechos sobre los territorios que ocupaban o disputaban al 5 de octubre de 1988, cuando se promulgó la Constitución vigente.Entidades de los pueblos originarios rechazan el marco temporal y aseguran que no se puede fijar esa fecha de 1988 debido a que muchos fueron expulsados de sus territorios ancestrales, especialmente durante la última dictadura militar que gobernó Brasil entre 1964 y1985.El Congreso surgido en las elecciones de 2022, de mayoría de centroderecha, derecha y de la extrema derecha aliada al expresidente Jair Bolsonaro, había aprobado en septiembre el marco en carácter de urgencia.En octubre, Lula vetó parcialmente la ley aprobada por el Congreso que preveía limitar la demarcación de territorio para los pueblos indígenas para permitir el avance del agronegocio y la minería. Este jueves el Congreso rechazó las objeciones del Ejecutivo a la tesis del marco temporal.
+[H2] Rechazos a la medida
+Unprocessed element [b]
+Unprocessed element [br]
+La organización de defensa de los derechos humanos Survival International calificó a la legislación restituida por el Congreso como "el más grave y despiadado ataque" contra los derechos de los indígenas en muchas décadas en el mayor país latinoamericano.De acuerdo con un comunicado de la organización de defensa de los derechos de los indígenas, la nueva ley contiene una "serie de medidas extremadamente antiindígenas", por lo que tendrá "impactos catastróficos" para muchas poblaciones originarias.
+[H2] Las reservas indígenas en Brasil
+Según datos de la Fundación Nacional de los Pueblos Indígenas (FUNAI), ente gubernamental de defensa de las poblaciones originarias, las reservas ocupan 13,75% del territorio del país.</t>
   </si>
   <si>
     <t>La Mesa de Enlace y el enojo por la suba de las retenciones</t>
@@ -985,7 +2357,25 @@
     <t>https://www.pagina12.com.ar/695310-la-mesa-de-enlace-y-el-enojo-por-la-suba-de-las-retenciones</t>
   </si>
   <si>
-    <t>2023-12-14T20:19:10Z</t>
+    <t xml:space="preserve">Título: La Mesa de Enlace y el enojo por la suba de las retenciones
+Chapeau: Incremento al 15 por ciento
+Subtítulo: Los representantes de la Mesa de Enlace salieron esta tarde de la reunión con funcionarios de Economía en la que expresaron su descontento con la decisión de incrementar a un 15% las rete
+Editoria: Economia
+Tags: Mesa de Enlace, mesa-de-enlace, diario
+URL: https://www.pagina12.com.ar/695310-la-mesa-de-enlace-y-el-enojo-por-la-suba-de-las-retenciones/
+Notícia completa (12 blocos):
+Los representantes de la Mesa de Enlace salieron esta tarde de la reunión con funcionarios de Economía en la que expresaron su descontento con la decisión de incrementar a un 15% las retenciónes a las exportaciones --excepto la soja que cotinúa en 33%--, a pesar de que el ministro de Economía, Luis Caputo, había anunciado que el incremento "provisorio" sería para las "exportaciones no agropecuarias".
+A pesar de manifestarse en contra de la decisión, el titular de la Sociedad Rural, Nicolás Pino, dijo no estar "defraudado" con el gobierno y agradeció la convocatoria al diálogo; además relativizaron la otra porción de las medidas de ajuste y liberalización del mercado que benefician al sector: la devaluación del peso y un dólar exportador de 860 pesos; además del fin de los controles exportadores y las cuotas para productos como la carne, que tenía siete cortes con límites para abastecer el mercado interno.
+Tras el encuentro en el Ministerio de Economía, Pino y el titular de la Federación Agraria Argentina, Carlos Achetoni, fueron los voceros de las entidades del agronegocio y anunciaron que el Gobierno les prometió abrir mesas técnicas para analizar sector por sector la aplicación de las retenciones. "Hay muchas producciones y economías regionales que no resisten ningún tipo de presión", sostuvo Achetoni y remarcó el caso de la lechería.
+Entre las decisiones tomadas por el ex ministro de Economía, Sergio Massa, había estado la quita de las retenciones por 90 días a la lechería y la quita total de gravámenes a las economías regionales, que ahora volverán al 15%. "Nos dijeron que es temporal", reconoció Pino y agregó que no tuvieron precisiones sobre cuánto tiempo durará la medida. De todas formas, el titular de la Sociedad Rural buscó defender al gobierno: "Cómo vamos a estar defraudados con un gobierno que acaba de asumir y nos invita a discutir".
+El objetivo de Caputo, a partir del aumento de retenciones, es alcanzar ingresos por el 0,5 % del PBI para 2024. Con una cosecha que, a diferencia de la obtenida en la campaña 2022/2023 en medio de una sequía histórica, promete tener rindes muy altos.
+En la queja por el incremento de las retenciones al 15% --actualmente, entre los cultivos de mayor volumen productivo, el trigo y el maíz tiene un 12% y el girasol 7%--, los referentes de la Mesa de Enlace evitaron ponderar la transferencia de ingresos que significa la brusca devaluación del peso, por el que pasarán a obtener 860 pesos por cada dólar exportado, menos el gravamen de retención. "Hay que estar muy finito para ver cómo queda, acaba de subir el gasoil y hay que ver los costos", argumentó Pino. Otro de los puntos que marcan desde el agronegocio es el aumento de los insumos químicos importados, de lo cuáles depende el modelo agropecuario convencional.
+Además, el titular de la Sociedad Rural reconoció que desde Economía aseguraron que podrán fin a las restricciones y cuotas de exportación como sucede con los cortes populares de carne, que estaban limitados para asegurar el abastecimiento interno sin la competencia con el precio de exportación. "Yo no veo el abuso", respondió Pino sobre la posibilidad de que el kilo de carne continúe aumentando hasta los 12 mil pesos e insitió que la liberalización de los controles es "lo que tiene que pasar en un país normal", porque "el intervencionismo de mercado generan distorsiones horribles".
+A pesar de todos los matices puestos por los representantes de la Mesa de Enlace para sostener su respaldo al gobierno de ultraderecha, Pino reconoció que "durante la campaña se dicen muchas cosas que, cuando llegás al sillón no son fáciles de cumplir".
+En ese sentido, luego de que se conociera la letra chica de los anuncios de Caputo, el ex secretario de Agricultura Juan José Bahillo criticó: "No cumplen las promesas de campaña y engañan a los productores, que creyeron en ellos, con una brutalidad innecesaria". Y agregó: "Estafaron a los productores de economías regionales, a quienes les volvieron a imponer retenciones".
+No se trata de la primera marcha atrás de un gobierno que cuenta con el respaldo de la Mesa de Enlace. Mauricio Macri había iniciado su gobierno con una baja de las retenciones a la soja, trigo, maíz y girasol; que tuvo que revertir en septiembre de 2018, luego de que su gobierno --con Caputo en el Gabinete-- acudiera al FMI a pedir el préstamo más grande de la historia. En aquellos días, Macri también redujo la cantidad de ministerios y anticipó: "Habrá más pobreza".
+[H2] El consorcio de la carne también se reunió con el Gobierno
+El presidente del Consorcio de Exportadores de Carnes Argentinas (ABC), Mario Ravettino, confirmó hoy que el Gobierno nacional incrementará las retenciones al sector frigorífico del 9% a 15%, tras una reunión informativa que mantuvo este mediodía con el secretario de Bioeconomía, Fernando Vilella."En el programa que tienen explicaron muy claramente el tema de las retenciones y nos hablaron de este incremento que van a hacer, pero también quedó a las claras la situación de mejora que vamos a tener con el tipo de cambio", subrayó Ravettino a la prensa a la salida del encuentro.La reunión fue convocada por el equipo de Bioeconomía para repasar algunos puntos del paquete de medidas económicas anunciado el martes por el ministro de Economía, Luis Caputo.En este sentido, el empresario indicó: "Pasamos a un tipo de cambio base $ 800 pero que, como es un 80/20 con el sistema que había, vamos a tener un tipo de cambio que sin las retenciones nos va a quedar en alrededor de $ 760", lo que consideró "un paso muy positivo" para la forma en que el sector venía liquidando."Es decir, se hace el esfuerzo de las retenciones pero hay una compensación muy importante que indudablemente determina que somos un sector considerado por el actual equipo económico", añadió.La reunión entre la industria frigorífica y las autoridades de Bioeconomía arrancó a las 12 en el edificio de la cartera en el centro porteño, y fue la antesala de un encuentro similar con representantes de la Mesa de Enlace Agropecuaria.</t>
   </si>
   <si>
     <t>En la AFIP suena un contador que daba consejos para evadir la facturación de granos</t>
@@ -997,7 +2387,23 @@
     <t>https://www.pagina12.com.ar/692250-para-la-afip-milei-quiere-a-un-contador-que-ayudaba-a-evitar</t>
   </si>
   <si>
-    <t>2023-12-05T23:43:52Z</t>
+    <t xml:space="preserve">Título: En la AFIP suena un contador que daba consejos para evadir la facturación de granos
+Chapeau: A Marcos Sequeira lo posicionan -y se posiciona- al frente del ente recaudador
+Subtítulo: En un raid mediático, al contador se le escapó que Milei le ofreció quedarse a cargo de la Administración Federal de Ingresos Públicos. Precavido, pidió que no le pase lo mismo que "a Píparo". En las mismas entrevistas aprovechó para sacar la motosierra. La "ayuda" que le brindó a empresas del agro para evitar facturar...a la propia AFIP.
+Editoria: El País
+Tags: AFIP, Javier Milei, javier-milei, diario
+URL: https://www.pagina12.com.ar/692250-para-la-afip-milei-quiere-a-un-contador-que-ayudaba-a-evitar/
+Notícia completa (10 blocos):
+"Lo quiero ver oficializado porque no quiero que me pase lo que le pasó a Carolina Píparo en la ANSES." Precavido, el contador Marcos Sequeira evitó confirmar su rol al frente de la Administración Federal de Ingresos Públicos (AFIP) en la presidencia de Javier Milei. Su nombre surgió con fuerza en las últimas horas, Milei no habría logrado convencer Kuban Lisa, socio del estudio Brouchou-Funes de Rioja, y quedó descartado el nombre de Ramiro Marra, el primero que había sonado. El cordobés, voluntarioso, se adelantó y publicó en sus redes sociales nueve ejes centrales para su gestión en el organismo fiscal.
+Cuando su nombre comenzó a sonar, las radios cordobesas comenzaron a llamarlo para confirmar su lugar en el Gabinete de la ultraderecha. El tributarista, una recurrida fuente de los medios mediterráneos, evitó confirmar su lugar, pero sí adelantó algunas ideas afines a la motosierra. Habló de asumir con el permiso de "cortar varias cabezas" y argumentó que era necesario cortar "la cadena de corrupción" y marcó que no solo eliminará impuestos sino que propondrá "reesctructurar" el sistema fiscal porque "está todo mal hecho".
+Sequeira no viene de la gestión pública. Su carrera fue en el sector privado y académico, otra similitud con el perfil del círculo cercano al futuro presidente. Además, conoce a la futura canciller Diana Mondino, ya que trabajó en el Banco Roela, fundado por Víctor Mondino, padre de Diana. El cordobés también podría encontrar en las filas del futuro Gabinete a otros coterráneos, entre ellos, a Osvaldo Giordano, actual ministro de Finanzas de Córdoba en el gobierno de Juan Schiaretti, y futuro titular de la ANSES; el mismo que hizo caer a Píparo.
+Giordiano -con un acuerdo cada vez más claro con el peronismos cordobés- no sería el único cordobés en el futuro gobierno, también llegará al gobierno libertario Franco Mogetta, viajará desde la cartera de Transporte de Córdoba a la de Nación. Además, un ex funcionario del peronismo cordobés como Hugo Testa ya trabaja con Guillermo Ferraro, quien encabezará el Ministerio de Infraestructura; mientras que suena el arribo para esa cartera del titular de la Empresa Provincia de Energía de Córdoba (EPEC), Luis Giovine. El voto cordobés fue clave para poner a Milei en la Casa Rosada y el anarcocapitalista les está respondiendo con acuerdos políticos.
+Anticipándose a su posible nombramiento, Sequeira dejó su carta de presentación en sus redes sociales. Ayer hizo un posteo que no dejaba mucho lugar a dudas: "Propuestas de Gestión para la Administración Federal de Ingresos Públicos". Entre las diez propuestas aparecían palabras del mundo gerencial: "fortalecimiento", "transparencia", "modernización", "digitalización"; también ideas centrales de gestión pública como mejorar el acceso a las aplicaciones, la atención a los usuario y la formación de personal.
+En cuanto a las políticas centrales del organismo, Sequeira menciona algunas que podrían ser disruptivas con el pensamiento filosófico de Milei, que considera un "robo" los impuestos. El tributista habló de optimizar la recaudación, reforzar la lucha contra el fraude y la evasión, establecer mecanismos internacionales de intercambio de información e incluso apunta contra una de las políticas estrellas de los nuevos aliados macristas: "Revisión de Políticas sobre Blanqueos y Moratorias".
+Unprocessed element [figure]
+"Hay que intensificar las acciones de control y fiscalización, empleando tecnologías avanzadas y técnicas de análisis de datos para detectar y prevenir irregularidades", sostiene Sequeira en sus plan de gestión. Sin embargo, como reveló este diario, Sequeira ha participado de mecanismos complejos evasión.
+Cuando, en 2008, el gobierno de Cristina Kirchner intentó subir las retenciones a los granos, abrió una disputa con el agronegocio, que unió a pooles de siembra y productores pequeños, y significa, hasta estos días, gran parte del rechazo al "kirchnerismo" en Córdoba. Entonces, Sequeira participa de mecanismos que integraba junto a jueces y oficinas de la AFIP para favorecer a empresas del agro en la evasión de la facturación de granos.
+"Si se abordan con decisión y transparencia los desafíos actuales, podemos pensar en un futuro próspero para el país", promete el cordobés.</t>
   </si>
   <si>
     <t>La Libertad Avanza y la casta tiene cargo</t>
@@ -1009,7 +2415,25 @@
     <t>https://www.pagina12.com.ar/689257-la-libertad-avanza-y-la-casta-tiene-cargo</t>
   </si>
   <si>
-    <t>2023-11-26T03:01:00Z</t>
+    <t xml:space="preserve">Título: La Libertad Avanza y la casta tiene cargo
+Chapeau: Otro cambio en el caótico armado de gabinete de Milei y un claro ganador
+Subtítulo: El segundo candidato al Banco Central, Demian Reidel, también se bajó antes de asumir. Aun sin confirmación oficial, el "Messi de las finanzas" de Macri sigue avanzando en los hechos.
+Editoria: El País
+Tags: La Libertad Avanza, printed-edition, la-libertad-avanza, diario
+URL: https://www.pagina12.com.ar/689257-la-libertad-avanza-y-la-casta-tiene-cargo/
+Notícia completa (12 blocos):
+En etapas frenéticas, el nuevo gobierno va delineando algunas formas no sin antes pasar por un desgastante juego de anuncios y desmentidas, todos los días y a toda hora. E incluso a las mismas horas en que los protagonistas aludidos desmienten o afirman lo que cerca de Javier Milei dejan trascender. Una cosa queda clara: los primeros anuncios de tono más "anarco capitalista" en cuanto a nombres y contenidos, incluidas las figuras "de la primera hora" de La Libertad Avanza (¿eso que la gente votó?) van bajando del barco de gobierno o relegados a asientos de tercera clase, y van siendo reemplazados por referentes de Juntos por el Cambio, a los que se sumaron nombres cercanos al otrora prescindente Juan Schiaretti. Esta loca danza de nombres que sale del piso 21 del Hotel Libertador, el lugar "energéticamente" elegido para sentar las bases de la "oficina del Presidente electo", no se toma descanso el fin de semana.
+El sábado hubo una baja significativa y, entre tanto baile de nombres, uno que apareció y fue desmentido, pero no tanto. La baja, otro que sigue a Milei "desde Cemento", Demian Reidel, que a su vez había aparecido para reemplazar en el Banco Central a Emilio Ocampo, el padre del plan de dolarización, cuando Luis "Toto" Caputo entró oficialmente en escena. El nombre que cayó sin que lo llamen fue el de Daniel Scioli, que el sábado sonó como posible secretario de Turismo, algo que luego fue desmentido.
+[H2] Las fuerzas del cielo por asalto
+La salida de Reidel refuerza la toma por asalto macrista que, en rigor, comenzó a ser silenciosamente tejida mucho antes del 19 de noviembre, y que se completa con el plan económico en el que que "el Messi de las finanzas" viene trabajando hace meses. El paso al costado de este ferviente mileísta cercano a Sturzenegger, que militó con ahínco en las redes llamando "a votar a Milei y a erradicar el cáncer kirchnerista de la Argentina", fue amablemente comunicada: "Para evitar especulaciones, quiero confirmar que en este momento no voy a ejercer la presidencia del BCRA. El presidente Javier Milei cuenta con mi apoyo absoluto". En los hechos, parece confirmar que el "sí" de Caputo al ofrecimiento de la cartera viene con más condiciones a sortear que la de una supuesta negativa familiar, según se dejó trascender. Y que lo que fue promesa de campaña y tuvo que ser reafirmado en un comunicado, también comienza a ser de lejano cumplimiento: "el cierre del Banco Central no es un asunto negociable". Y con ello, claro, la mentada "dolarización".
+Por otra parte, tanto desde La Libertad Avanza como desde el entorno de Scioli negaron a Página/12 que haya habido ofrecimiento alguno para integrar el gabinete. Pero, en el mismo momento, otras fuentes de LLA aseguraban a este medio que "sí hubo un acercamiento, pero de parte de él, que ya dijo que quiere quedarse en Brasil". Se sabe que el actual embajador mantiene una relación cercana con Guillermo Francos, actualmente confirmado como ministro del Interior del futuro gobierno y hombre que ganó peso en el armado. Entre otros cargos en diversas gestiones (incluida la actual, donde Francos fue director ejecutivo por Argentina del Banco Interamericano de Desarrollo, cargo al que renunció para subirse a la aventura libertaria), Francos fue presidente del Banco Provincia durante toda la primera gobernación de Scioli, desde 2007 hasta 2011.
+[H2] Fotos borrosas
+Si hubiera que hacer una foto de la conformación del gabinete al día de hoy, tendría algunos detalles curiosos y hasta contradictorios (aunque, se sabe, en la lógica de estos días tumultuosos en el Libertador cualquier foto que se tome puede durar menos que una storie de Instagram).
+Uno es el de la puja a cielo abierto que por estas horas se da en las áreas de Seguridad y Defensa, con Patricia Bullrich y Victoria Villarruel como protagonistas, de la que informa en extenso Luciana Bertoia en este diario.
+Un dato no menor sobre esta puja: a Villarruel, se sabe, la mueve una misión política en la que viene trabajando denodadamente desde hace años, un "cambio de relato", en sus propias palabras, vinculado a la impunidad de los genocidas. Bullrich tiene varias tareas que retomar si se concreta este "segundo tiempo". No solo represivas: su paso por el ministerio de Seguridad abrió importantes negocios, fundamentalmente con el Estado de Israel. Dejó un tendal de compras hechas pero de imposible uso tras su salida, desde sistemas de comunicación que no servían porque no eran aptos para las zonas geográficas en que se necesitaban, hasta lanchas compradas sin licitación y con grandes sobreprecios, que nunca pudieron usarse porque su calado no se adecuaba a los ríos del norte argentino.
+Una aparente contradicción surge en el casillero de Agricultura, para el que por ahora queda en pie un "no PRO duro", Fernando Vilella. Ex decano de la Facultad de Agronomía de la UBA, profesor de Mercados Agropecuarios y director de Bioeconomía de esa facultad, Vilella es conocido por su proyecto de "vaca viva", que armó con el exsecretario del área durante el kirchnerismo y exinterventor de Vicentin Gabriel Delgado (quien fue nuevamente convocado por Massa). Lo particular de este proyecto vinculado a la producción de proteína animal y vegetal es que es de neto corte productivista: valor agregado a la exportación. Y que su éxito está vinculado a la consolidación de un mercado como el de los Brics, que el nuevo Presidente en su discurso viene a derribar.
+Pero al mismo tiempo, en la agenda que dejó trascender Vilella figura la receta anarco capitalista: eliminación total de las retenciones a la soja, el trigo y el maíz, quita absoluta de todas las regulaciones del sector, incluidas las exportaciones de carne y los fondos para la harina y el aceite. La cartera cambiaría de nombre (pasaría a ser Secretaría de Bioeconomía), pero básicamente sería una jugadora a favor del agronegocio.
+Con logo de estética Casa Blanca estrenado la misma noche de las elecciones, desde la "Oficina del Presidente electo" salieron hasta ahora pocas muy confirmaciones oficiales. Y hubo una que picó en punta: Horacio Marin, un hombre que hizo toda su carrera en Techint, al frente de YPF. Favor con favorazo se paga: como informó Leandro Renou en este diario, después de las primarias la empresa de Paolo Rocca pasó de aportarle fondos a la campaña de Patricia Bullrich a derivar buena parte de ellos a financiar la carrera presidencial de Javier Milei, transformándose en el único aportante privado que oficialmente tuvo la campaña de La Libertad Avanza.</t>
   </si>
   <si>
     <t>Karina Micheletto</t>
@@ -1024,7 +2448,20 @@
     <t>https://www.pagina12.com.ar/612161-un-estudio-vincula-el-uso-de-pesticidas-en-brasil-con-las-mu</t>
   </si>
   <si>
-    <t>2023-11-01T16:24:11Z</t>
+    <t xml:space="preserve">Título: Un estudio vincula el uso de pesticidas en Brasil con las muertes por leucemia infantil
+Chapeau: Los peligros del agronegocio
+Subtítulo: Un estudio publicado en la revista Proceedings of the National Academy of Sciences (PNAS) relaciona la rápida expansión de la soja y el aumento del uso de los pesticidas en los biomas
+Editoria: Brasil
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/612161-un-estudio-vincula-el-uso-de-pesticidas-en-brasil-con-las-mu/
+Notícia completa (7 blocos):
+Un estudio publicado en la revista Proceedings of the National Academy of Sciences (PNAS) relaciona la rápida expansión de la soja y el aumento del uso de los pesticidas en los biomas Cerrado y amazónico de Brasil con un incremento de la mortalidad por leucemia infantil.El trabajo, que no proporciona un vínculo causal, analiza 15 años de datos sobre la mortalidad de la leucemia linfoblástica aguda (LLA), el tipo de leucemia más común en los niños.
+[H2] El uso de pesticidas y herbicidas en Brasil
+Unprocessed element [b]
+Unprocessed element [br]
+[H2] El estudio
+[H2] La punta del iceberg
+"Nuestra preocupación es que nuestros resultados son sólo la punta del iceberg (...). La exposición a plaguicidas también puede dar lugar a casos no mortales de leucemia y existe el riesgo de que repercuta en la comunidad adulta y adolescente", afirma Skidmore.Los investigadores indican que hay varias formas de mitigar esta relación: formación y educación de los trabajadores agrícolas, una normativa inteligente para el uso de pesticidas y el acceso a la atención sanitaria (la LLA es tratable pero requiere de centros sanitarios adecuados).Brasil está desarrollando actualmente un programa de certificación que exige a los aplicadores de plaguicidas formación y educación en materia de seguridad, según la Universidad de Illinois.</t>
   </si>
   <si>
     <t>La Asamblea Constituyente  de los Pueblos Riojanos demanda transparencia en materia de litio</t>
@@ -1036,7 +2473,23 @@
     <t>https://www.pagina12.com.ar/612035-la-asamblea-constituyente-de-los-pueblos-riojanos-demanda-tr</t>
   </si>
   <si>
-    <t>2023-11-01T08:01:12Z</t>
+    <t xml:space="preserve">Título: La Asamblea Constituyente de los Pueblos Riojanos demanda transparencia en materia de litio
+Chapeau: Exigen información sobre proyectos con impacto medio ambiental
+Subtítulo: La Asamblea informó este martes sobre la medida cautelar solicitada a la Comisión Interamericana de Derechos Humanos en relación con los proyectos de minería de litio y el acuerdo con la empresa israelí Mekorot.
+Editoria: La Rioja | 12
+Tags: La Rioja, Medio Ambiente, la-rioja, medio-ambiente, diario
+URL: https://www.pagina12.com.ar/612035-la-asamblea-constituyente-de-los-pueblos-riojanos-demanda-tr/
+Notícia completa (10 blocos):
+Este martes la Asamblea Constituyente de los Pueblos Riojanos convocó a una conferencia de prensa en la que se dio a conocer la petición de una medida cautelar ante la Comisión Interamericana de Derechos Humanos relacionada con los proyectos de minería de litio y el acuerdo con la empresa israelí Mekorot.
+La abogada Ivana Cattaneo, quien representa a la asamblea ante la CIDH, hizo hincapié en la importancia del acceso a la información en el contexto de los megaproyectos de extracción de litio, que involucran no solo la explotación de recursos naturales, sino también cuestiones de derechos humanos y preservación del medio ambiente.
+En la presentación, Cattaneo destacó que la asamblea invoca los derechos de las comunidades por la vida y amparándose en las disposiciones de la Ley Nacional N° 27.275 y la Ley Provincial N° 10,119/18. La Ley Provincial establece la obligación de "garantizar el efectivo ejercicio del derecho de acceso a la información pública en formato digital abierto y gratuito". Sin embargo, la falta de acceso a información sobre los proyectos de minería y el acuerdo con Mekorot ha llevado a la presentación de una medida cautelar.
+La preocupación principal de este reclamo se centra en el agua, un recurso vital para la subsistencia de la población riojana, que viene en disputa debido a los megaproyectos mineros, industriales y agronegocios. La población reunida en asamblea reclama que no ha tenido acceso a la información necesaria sobre estos proyectos y a pesar de haberla solicitado por vias formales.
+La asamblea sostiene la necesidad de la clausura temporal de los proyectos de litio debido a la violación flagrante de la ley y la falta de conocimiento de la población sobre los proyectos y sus impactos. Además, se destaca la ausencia del informe de Impacto Ambiental, que es obligatorio según el Código de Minería.
+El documento consensuado en asamblea argumenta que la extracción de litio en Argentina se ha convertido en un asunto de defensa de derechos humanos, ya que los recursos extraídos enriquecen a países del primer mundo mientras afectan negativamente a las comunidades locales y el medio ambiente. El litio contribuye al agravamiento de la crisis climática en curso.
+Una medida cautelar es un mecanismo de protección de la Comisión Interamericana de Derechos Humanos (CIDH), mediante la cual esta solicita a un Estado que proteja a una o más personas que estén en una situación grave y urgente de sufrir un daño irreparable. Actualmente la presentación MC-726-23 se encuentra en estudio desde el 11 de septiembre, esta es la etapa procesal de revisión, la cual finaliza con la decisión de la Comisión de requerir información al Estado, o rechazar la solicitud de medidas cautelares.
+En esta lucha por el acceso a la información y la protección de los derechos humanos, se denuncia la falta de conocimiento sobre la tierra de la provincia, donde se llevan a cabo proyectos de exploración de litio. La asamblea señala que estas áreas no son desiertos, como se ha argumentado, y que existen comunidades cercanas que son afectadas por las empresas extractivas.
+La Asamblea Constituyente de los Pueblos Riojanos ha tomado medidas legales para proteger los derechos humanos y exigir acceso a la información en relación a los proyectos de minería de litio y el acuerdo con Mekorot, mientras destaca la importancia de preservar el medio ambiente en el contexto de la crisis climática. Por un lado ha presentado ante la convención constituyente un documento elaborado colectivamente producto de varias asambleas que se fueron concretando en distintos puntos de la provincia y recolectando miles de firmas que adhieren a esta preocupación popular. Y por el otro con esta medida solicitando la intervención de organismos internacionales para que se respeten los tratados a los que la Argentina suscribe ante situaciones como esta.
+La reciente aparición de flamencos muertos en la Reserva Natural de la Laguna Brava reaviva los reclamos sobre la falta de información sobre el impacto mediambiental de la exploración de litio en la región, y a pesar de que este factor ha sido desechado como causa por el Secretario de Ambiente, Santiago Azulay, la falta de acceso a la información no contribuye a la tranquilidad de la población sobre el manejo responsable ante la posibilidad del desarrollo de este tipo de actividad en la región.</t>
   </si>
   <si>
     <t>El alimento debe ser parte del acuerdo nacional</t>
@@ -1045,7 +2498,33 @@
     <t>https://www.pagina12.com.ar/610468-el-alimento-debe-ser-parte-del-acuerdo-nacional</t>
   </si>
   <si>
-    <t>2023-10-29T15:00:57Z</t>
+    <t xml:space="preserve">Título: El alimento debe ser parte del acuerdo nacional
+Chapeau: Opinión
+Subtítulo: Como parte del campo popular sabemos diferenciar entre una propuesta con un contrato social inhumano, basado en el individualismo, el sálvese quien pueda y el mercado como regulador de las relacion
+Editoria: El País
+Tags: Sergio Massa, Javier Milei, balotaje, Opinión, sergio-massa, javier-milei, opinion, diario
+URL: https://www.pagina12.com.ar/610468-el-alimento-debe-ser-parte-del-acuerdo-nacional/
+Notícia completa (20 blocos):
+Como parte del campo popular sabemos diferenciar entre una propuesta con un contrato social inhumano, basado en el individualismo, el sálvese quien pueda y el mercado como regulador de las relaciones económicas. Frente a otro que pone en el centro la justicia social, la construcción desde el amor, la solidaridad y el estado como regulador de las desigualdades que atravesamos como sociedad. La crisis social y económica que vive la Argentina requiere un accionar colectivo, de la comunidad organizada, que está representado en el Estado, a pesar de sus falencias en muchas políticas públicas, en particular en términos de soberanía alimentaria.
+En estas elecciones hay dos modelos en disputa: uno de imposible discusión. El de Milei. Y otro, el de Massa, donde podremos continuar la batalla de hacer entender al alimento como un derecho para quienes producen y consumen.
+Hoy es Massa la única opción concreta para nuestro pueblo, más allá de la histórica ausencia de la discusión del modelo agroalimentario en todas las propuestas de campaña.
+[H3] El alimento como derecho
+Apenas asumió el actual gobierno, desde el sector de pequeños y medianos productores de alimento (que cubren el 60% de esta necesidad), presentamos nuestras propuestas en una articulación con diferentes organizaciones que hoy se nucléan en la Mesa Agroalimentaria Argentina, el campo que alimenta. Tuvimos la oportunidad de ser parte de la gestión del Mercado Central, implementando novedosas y exitosas políticas a nivel micro pero incapaces de incidir en políticas macroeconómicas, lo que derivó en mi renuncia.
+Con la marcha atrás de la expropiación de Vicentín y la posibilidad de la creación de una Empresa Pública de Alimentos (que además hubiera servido de control para la evasión fiscal en el sector agroexportador) comenzó un declive del actual gobierno de Alberto Fernández, que culminó con la contratación como asesor presidencial de Antonio Aracre, representante del agronegocio y con quién sostuve un debate televisivo acerca de si el alimento era una mercancía o un derecho.
+Reforzando el planteo histórico de nuestro sector, hay una falta de lectura en la dirigencia política de un modelo agrario que vea al campo no solo en función de la exportación y la acumulación de divisas, sino también desde su función primaria, urgente y necesaria, que es la producción de alimento para su posible acceso en la mesa de los argentinos y argentinas.
+Se trata de roles que pueden ser complementarios, pero en un modelo político y tecnológico de soberanía alimentaria.
+No es posible el desarrollo de una industria exportadora en un país donde el mito de la producción de alimento para 400 millones de personas se contradice con el aumento descontrolado de los precios de estos alimentos a nivel local y el hambre de buena parte de los argentinos y argentinas.
+[H3] Un camino abierto
+Los pequeños y medianos productores que hoy tienen su representación gremial en la Mesa Agroalimentaria Argentina han demostrado la capacidad, no solo de producir alimento sano y barato, sino también de agregarles valor y comercializarlos a través de miles de ferias, almacenes y mercados de cercanía que los acercan a los consumidores, generando un esquema federal y de trabajo digno, y sorteando la estructura claramente inflacionaria que produce la concentración económica y geográfica.
+Los índices del Centro de Estudios Scalabrini Ortiz (CESO) vienen demostrando la efectividad de la Economía Social, Solidaria y Popular a la hora de reducir los índices de inflación en comparación con las estructuras económicas concentradas. Desde la UTT también hemos avanzado en la articulación con municipios de la provincia de Buenos Aires en ese sentido. Esta estructura de menor inflación tiene que ver con los avances que desde las organizaciones se han implementado en términos de logística y articulación, pero también con entender el alimento como un derecho y no solo un negocio.
+Incluso la Mesa Agroalimentaria Nacional cuenta con organizaciones que exportan alimento, donde el sector cooperativo y de pymes del campo que alimenta han incrementado notablemente sus ventas al exterior. Profundizar este sistema virtuoso a través del Estado es de vital importancia a la hora de reducir los índices de inflación y generar trabajo digno con alimento sano y barato para las familias argentinas.
+[H3] Parte de un acuerdo nacional
+Entendemos que un gobierno de acuerdo nacional no puede dejar de lado las contradicciones primarias que hay en los distintos modelos de desarrollo económico, destacando que tanto el FMI como el agronegocio son contrarios directamente a la posibilidad de soberanía alimentaria, de bienestar y justicia social. Ya es hora que la dirigencia política entienda que la agenda del modelo agroalimentario es urgente y necesaria para poder dar transformaciones reales para el pueblo argentino.
+Frente al debate de las próximas elecciones, nosotros fomentamos un estado presente y activo, un modelo de inclusión, acuerdo nacional y justicia social.
+Desde la UTT y la Mesa Agroalimentaria Argentina venimos llevando adelante estas políticas en los territorios y ya hemos presentado al gobierno un Programa Agrario para el Alimento con una serie de medidas, muchas de las cuales ya son proyecto de ley.
+No debe plantearse ni entenderse como contradictorio la necesidad de recaudar dólares, escasos debido a la deuda ilegítima con el FMI y la sequía, con las acciones concretas para construir una agenda de soberanía alimentaria, en la que prime garantizar el acceso a los alimentos. Para esto deben desarrollarse políticas públicas activas, partiendo de lo ya construido, y sin miedo a ir por más.
+Porque frente a la necesidad, como siempre, el alimento es un derecho.
+*Coordinador Nacional de la Unión de Trabajadores de la Tierra (UTT) y referente de la Mesa Agroalimentaria Argentina.</t>
   </si>
   <si>
     <t>Nahuel Levaggi</t>
@@ -1057,7 +2536,14 @@
     <t>https://www.pagina12.com.ar/2023/10/16/el-2024-va-a-ser-un-ano-muy-bueno-para-argentina-gobierne-quien-gobierne-asegura-massa/</t>
   </si>
   <si>
-    <t>2023-10-16T03:10:24Z</t>
+    <t xml:space="preserve">Título: "El 2024 va a ser un año muy bueno para Argentina, gobierne quien gobierne", asegura Massa
+Chapeau: "El 2024 va a ser un año muy bueno para Argentina, gobierne quien gobierne", asegura Massa
+Editoria: El País
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/2023/10/16/el-2024-va-a-ser-un-ano-muy-bueno-para-argentina-gobierne-quien-gobierne-asegura-massa/
+Notícia completa (2 blocos):
+"El 2024 va a ser un año muy bueno gobierne quien gobierne. El año que viene vamos a exportar gas y petróleo. En segundo lugar, vamos a tener 18 mil millones más de ingresos por agronegocios. Y en tercer lugar, un gran crecimiento del sector mineral, que nos va a dar 40 mil millones de dólares más de crecimiento de reservas, que es lo que hace fuerte la moneda", explicó Massa.
+(c) 2025 Página 12</t>
   </si>
   <si>
     <t>Pese a los destratos, Patricia Bullrich vuelve a apostar por Mauricio Macri</t>
@@ -1069,7 +2555,23 @@
     <t>https://www.pagina12.com.ar/597869-pese-a-los-destratos-patricia-bullrich-vuelve-a-apostar-por-</t>
   </si>
   <si>
-    <t>2023-10-13T03:01:00Z</t>
+    <t xml:space="preserve">Título: Pese a los destratos, Patricia Bullrich vuelve a apostar por Mauricio Macri
+Chapeau: Ambos saldrán de gira juntos por primera vez desde las PASO
+Subtítulo: La recorrida de campaña incluirá paradas en Junín y Pergamino, fotos de unidad y discursos contra Sergio Massa por la inflación. La idea es no mostrar fisuras en una relación que quedó lesionada luego del coqueteo del expresidente con el libertario. También buscarán pasar la página del escándalo de los audios de Melconian. Luis Brandoni sumó su voz para el último spot.
+Editoria: El País
+Tags: Patricia Bullrich, Mauricio Macri, printed-edition, patricia-bullrich, mauricio-macri, diario
+URL: https://www.pagina12.com.ar/597869-pese-a-los-destratos-patricia-bullrich-vuelve-a-apostar-por-/
+Notícia completa (10 blocos):
+Las localidades de Pergamino y Junín, corazón del agronegocio bonaerense, fueron los puntos en el mapa elegidos para que Mauricio Macri finalmente le ponga el cuerpo a la campaña de Patricia Bullrich. La recorrida, planificada para este viernes a bordo de la “Patoneta” –así fue bautizado el Motorhome proselitista de la candidata– tendrá el tono de un reencuentro, dado que no compartían una actividad juntos en el territorio desde antes de las PASO. En medio corrió mucha agua bajo el puente y hubo más de un cimbronazo público entre ambos, sobre todo cada vez que el expresidente le tiró flores a Javier Milei. La última vez, hace dos semanas desde Harvard, directamente dijo que se ocuparía de brindarle apoyo parlamentario al libertario en caso de que llegue a la Rosada, lo que desató la furia en el campamento bullrichista. Esa herida está lejos de sanar, mas allá de las apariencias. Con la actividad, Bullrich también planea dejar atrás la incómoda filtración de los audios de Carlos Melconián, su jefe de equipos económicos y potencial ministro de Economía. Por ahora no parece dispuesta a soltarle la mano. Incluso lo defendió diciendo que las grabaciones son “falsas” y que la voz de Melconian chantajeando sexualmente a una empleada fue fraguada por la inteligencia artificial.
+El reencuentro entre Macri y Bullrich no será el último antes de las generales del 22 de este mes. En agenda hay una nueva foto de unidad pautada en principio para el acto del cierre de campaña el próximo miércoles en Lanús, aunque a confirmarse. El expresidente ya dió muestras de dejarla plantada, como lo hizo en el debate presidencial, para el que solo estuvo en la previa. El cierre en el municipio que gobierna su candidato a gobernador, Néstor Grindetti, tiene como objetivo hacer pie en la provincia más importante del país, en la que deberá mejorar sus números de agosto si quiere contar con alguna chance de ingresar al balotaje. Macri no es precisamente el dirigente con mejor imagen en el conurbano, por eso el punto elegido para sumarse a la Patoneta fue varios kilómetros más adentro, en el sector provincial dedicado al agronegocio.
+Luego de las recorridas por Pergamino y Junín, ambos seguirán cada uno por su lado: la exministra tiene planeado en el sprint final visitar Mendoza, Córdoba y también CABA. Este jueves estuvo en Comodoro Rivadavia (Chubut) junto a Ignacio Torres. Macri, en tanto, saldrá a recolectar votos en otros distritos, con su propio itinerario. Esta semana estuvo en Vicente López, luego en Santa Fe y más tarde en Misiones. La idea es juntar todos los votos posibles para evitar un trágico tercer lugar en las generales para Juntos por el Cambio, que dejaría al espacio al borde de la ruptura.
+En esa línea, Bullrich no deja sector por ir a buscar: este jueves estuvo junto a referentes evangélicos. Visitó a las autoridades de la Alianza Cristiana de Iglesias Evangélicas de la República Argentina (Aciera), que están en contra del aborto legal, para compartir "sus proyectos respecto a medidas para afrontar la pobreza, como también el tema de la libertad religiosa, capellanías y el derecho a la vida", según el comunicado posterior de ese organismo religioso.
+[H2] Especulando con la inflación
+Junto a Macri, Bullrich hará hincapié en la crecida inflacionaria. Tuvo la mala suerte de que su referente económico estuvo envuelto en el escándalo de la filtración de los audios, así que deberá ser ella la que hable de economía. Este jueves lo hizo desde su cuenta de Twitter, luego de que el INDEC diera a conocer el número de inflación de septiembre. "Massa nos deja tierra arrasada con su incompetencia. La inflación mensual sigue subiendo. En septiembre fue de 12,7 % y ya acumula 138,3% en un año", dijo.
+"Nosotros tenemos un equipo sólido, un plan desarrollado por decenas de economistas y mayorías en el Congreso para ordenar la economía. Vamos por un país ordenado", remató.
+En la misma línea la siguió Mario Negri: "Por su ambición desmedida de poder tomó decisiones irresponsables que clavaron la inflación de septiembre en 12,7% y la anual en 138,3%. Repetimos al oficialismo: la inflación genera pobreza, no presidentes", le espetó a Massa.
+[H3] Brandoni, la voz del spot
+“Cuando Milei no estaba y Massa estaba con ellos, ella estaba con vos defendiéndote”, dice la voz en off del actor y militante cambiemita Luis Brandoni en el último spot de la candidata. “La fuerza es ella”, sigue y el montaje la muestra en distintas secuencias de su biografía política, como cuando se cruzaba con Hugo Moyano en los estudios de televisión durante su etapa como ministra de Trabajo de Fernando de La Rúa. El texto redunda en la idea de que, a diferencia de Milei, Bullrich tiene una estructura de gobernabilidad. El video tiene varios cambios más abajo que el último en el que propuso construir una cárcel de máxima seguridad con el nombre de Cristina Kirchner, lo que le valió una denuncia ante la justicia electoral por parte de organismos de Derechos Humanos de la Provincia de Santa Fe, que le piden retractarse por "la estigmatización del peronismo para justificar proscripciones, intentos de magnicidio y violaciones múltiples a los derechos humanos".</t>
   </si>
   <si>
     <t>Se fue la segunda y quedaron los ecos</t>
@@ -1078,7 +2580,27 @@
     <t>https://www.pagina12.com.ar/596357-se-fue-la-segunda-y-quedaron-los-ecos</t>
   </si>
   <si>
-    <t>2023-10-09T03:01:00Z</t>
+    <t xml:space="preserve">Título: Se fue la segunda y quedaron los ecos
+Subtítulo: Y llegó el día, nomás, con ansiedades multiformes y un hombre, en Santa Fe, que como el rayo que no cesa ­–parafraseando al enorme poeta Miguel Hernández– renueva contra viento y marea sus denuncia
+Editoria: El País
+Tags: Elecciones Argentina 2023, Opinión, printed-edition, elecciones-argentina-2023, opinion, diario
+URL: https://www.pagina12.com.ar/596357-se-fue-la-segunda-y-quedaron-los-ecos/
+Notícia completa (15 blocos):
+Y llegó el día, nomás, con ansiedades multiformes y un hombre, en Santa Fe, que como el rayo que no cesa ­–parafraseando al enorme poeta Miguel Hernández– renueva contra viento y marea sus denuncias de la proliferación de bandas narcos que actúan en cada uno de los 19 departamentos de esa provincia. Se llama Carlos del Frade y es diputado provincial y un patriota que con ejemplar tesón lleva años desnudando organizaciones delictivas y mafiosas en su provincia, donde según cómputos de medios de comunicación locales hoy es más que obvio que semejantes ejércitos malignos no podrían funcionar si hubiese políticas de prevención y sanción como sería de esperar en la tercera provincia argentina, con más de 3,5 millones de habitantes.
+Y provincia que de las grandes causas patrióticas de los últimos dos siglos pasó a ser asentamiento ­–Menem lo hizo– de las más grandes corporaciones de agronegocios, casi todas extranjeras. Y donde hoy anidan agroexportadoras que mueven miles de millones de dólares casi sin beneficios para el país. Pruebas al canto: sólo en la última semana hubo denuncias de un cargamento de 200 kilos de cocaína pura encontrados en el "Chemster", un buque que llegó a Australia procedente de uno de los puertos privados de San Lorenzo, al lado de Rosario. Y que parece ser nada más ni menos que otro caso escandaloso silenciado –o sea negado– continuando la "normalidad" de casi todos los gobiernos, tanto los de esa provincia litoraleña como del nacional. Porque de eso no se habla.
+Y es éste nada más que otro ejemplo de silenciamiento, como se ha venido constituyendo en norma de los poderes concentrados de esta república en la que la verdad es lo más negado y la sanata o sarasa –la mentira, vamos– es la norma principal y más poderosa de la politización forzada del pueblo argentino.
+Sólo así es explicable el sistema mentimediático que impone temas y asuntos de hartante frivolidad mientras los intereses ciudadanos y la democracia, la paz y el trabajo son abrumadora y canallescamente silenciados, negados o distorsionados para que la confusión impere, el descreimiento y el desaliento reluzcan y –consecuencia lógica– la democracia pase a ser a la vez farsa carnavalesca y perfecta promoción de desalientos.
+Así, las carencias argumentales –como se vio en los debates en la tele y están más cantadas que "Sólo le pido a Dios"– llevan a confusión y a crecientes abstenciones, voto-blanquismo y votos-rabia por causas –no razones– facilongas y oscuras como las que no se cansó de promover el candidato despeinado y gritón. Lo cierto es que la estupidez y la mentira también se enseñorearon en este segundo y último debate entre los cinco candidatos, con disimulitos leves, y en los que fue fenomenalmente engañosa la perorata –amenazante– de la señora Bullrich, quien en lugar de un ignoto compañero de fórmula podía haber elegido para secundarla –y sincerar más las cosas– al incalificable gobernador jujeño.
+Pero si algo se sabía al inicio del debate era que abundarían chicanas, mentiras, desmentidos y el descontrol de ese gritón sacado que la semana anterior se moderó de mentirita pero sin dejar de formar parte del dueto de bestias amenazantes. Como también se sabía de la vocación de violencia de la ex ministra que en el último gobierno radical rebajó los sueldos de medio país y que siempre fue incapaz de autocrítica y encima ahora pretendió dar cátedra de carcelera.
+Claro que también se sabía y quedó claro que la Sra.Bregman era la única diferente, porque guste o no tiene ideas y lenguaje claros. Y agradable por si faltara algo. Pero esa candidata es zurda, o sea de izquierda, troska, populista y contrera de alma y encima con firme discurso, por todo lo cual resultaría imbancable para las almas gorilas, y especialmente las porteñas.
+Entonces por ahí el gritón se descontrola y parece desequilibrado, en tanto machito que por eso mismo puede afanar en el voto joven, resentido y machirulo. Lo absurdo será que las mujeres lo voten, ahora que se logró igualdad de géneros como jamás antes, y cuando se garantiza el aborto seguro y todo lo que se hizo por la igualdad de géneros. No se puede creer que tantas mujeres argentinas y sobre todo jóvenes, voten a semejante tipo. Pero sí, hay que reconocer que sería otro más de los pistoletazos en la sien que en los últimos 50 años ha sabido darse esta nación.
+Y además estuvo ausente Malvinas, otra vez. Como también el Paraná, y el Canal Magdalena. Se habló de la unidad territorial. Y una vez más no existió la palabra "Soberanía" y todo fluyó como si el río estuviera maldito desde el maldito falsario de los 90 que no dijo lo que haría porque si lo decía no lo votaba nadie. O sea.
+Tampoco se habló de Derechos Humanos ni de que sí fueron 30.000 las víctimas de la dictadura. Ni se dijo que la dictadura fue eso: una dictadura, y feroz. Con lo que el negacionismo pareció reverdecer por momentos, y se les notó contrariedad a algunos, especialmente la nerviosísima Bullrich, quien parecía temer la presencia de su jefe lento, Mauricio Macri.
+Hubo también chicaneos con la desregulación de armas, y fue chocante que nadie defendiera a Raúl Zaffaroni, injusta y ridículamente atacado por Milei. Quien además mezcló economía con juridicidad y mintió con falsedades, como pareció costumbre de varios de los dialogantes. También se le chupó la media a la Justicia y se hablaron sarasas de leyes y códigos penales y Milei, claro, dijo respetar la ley de armas (sic) y negó que impulsa la venta de órganos, que sin embargo ha sido uno de sus argumentos de campaña. Y supo ser gelatinoso, como todos. A excepción de Massa por momentos, y de Bregman que fue clara y precisa en todos los órdenes y no se amilanó ante ningún tema.
+Pero lo que quedó en el aire fue que el peligro tiene ojos de loco. Este domingo quedó claro. El tipo se muestra como un cipayo perfecto, porque lo es. Un antipatriota, acaso agente de las internacionales que se relamen por quedarse con todo los bienes de nuestra Patria. El tipo parece un charlatán, y seguramente lo sea, antes que un hombre sensato. No debe haber leído ni El Principito ni el Martín Fierro, ni un poema de Borges o un cuento de Cortazar, apuesta este columnista. Y no podría sostener una conversación sensata –este columnista se descompone de sólo imaginarlo– si por ejemplo encima designa a la canciller que ya prometió que las Malvinas deben ser inglesas.
+Es un tipo que no escucha ni parece reflexionar (que es un acto que supone serenidad, modestia, análisis y buena fe). Todo eso se diría que falta en este tipo que ve claramente que además de machirulo parece violento, como se mostró cuando empezó su campaña a puros gritos y amenazas.
+Además, no ha dicho una sola idea completa en los dos debates: sólo enunciados furibundos. Contenido ahora, pero con ojos de loco a full. Y en general sin desarrollo, que se suma al hecho de que no se le conoce una sola idea propia. Y su vice ni se diga: es la mujer a la sombra, fenómeno típicamente machista.
+Y en fin, todos hicieron lo que pudieron y mejor que los analicen colegas más sabios, en los próximos días. Por ahora esta columna se confiesa alarmada por la Patria. Por el pueblo que quizás en dos semanas podría decidir suicidarse como democracia. Y si acaso sucediera, como augura la mayoría de las encuestas, ahora sí que al pueblo argentino no lo unirá el amor, sino el espanto.</t>
   </si>
   <si>
     <t>Brasil: la ultraderecha desafía a la Corte contra los indígenas y apunta a  homosexuales</t>
@@ -1090,7 +2612,29 @@
     <t>https://www.pagina12.com.ar/592933-brasil-la-ultraderecha-desafia-a-la-corte-contra-los-indigen</t>
   </si>
   <si>
-    <t>2023-09-29T03:01:00Z</t>
+    <t xml:space="preserve">Título: Brasil: la ultraderecha desafía a la Corte contra los indígenas y apunta a homosexuales
+Chapeau: El Senado aprobó una ley que limita el reconocimiento de tierras indígenas
+Subtítulo: La agenda conservadora revivió con fuerza para responder a las últimas decisiones del máximo tribunal, que van a contramano del sector agropecuario y las iglesias evangélicas.
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, ultraderecha, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/592933-brasil-la-ultraderecha-desafia-a-la-corte-contra-los-indigen/
+Notícia completa (16 blocos):
+La ultraderecha brasileña exhibió su músculo parlamentario desafiando a la Corte Suprema con la aprobación de una ley que restringe los derechos de los pueblos originarios a la tierra, mientras avanza en un proyecto para prohibir el matrimonio homosexual. La agenda conservadora revivió con fuerza en pleno gobierno de Luiz Inácio Lula da Silva y es una suerte de respuesta a las últimas decisiones del máximo tribunal sobre temas espinosos que van a contramano del poderoso sector agropecuario y, sobre todo, de las influyentes iglesias evangélicas.
+[H2] Triunfo de la derecha y el lobby agrícola
+El primer paso de esta ofensiva parlamentaria, encabezada por el Partido Liberal (PL) del expresidente Jair Bolsonaro, fue la aprobación del llamado "marco temporal", que limita los derechos de los indígenas a las tierras que ocupaban al 5 de octubre de 1988, cuando fue promulgada la actual Constitución brasileña. El proyecto fue aprobado con urgencia por el pleno del Senado en un debate convocado una semana después de que la Corte rechazara esa tesis jurídica por nueve votos contra dos y consagrara el derecho de los indígenas a la tierra que han ocupado tradicionalmente.
+En las últimas semanas el tribunal también admitió a trámite sendas demandas que proponen descriminalizar el aborto hasta las 12 semanas y liberar, con límites, la marihuana para fines recreativos. "Atentan contra el campo y ahora quieren el aborto y las drogas", sostuvo el senador Jorge Seif, un exministro de Bolsonaro que es una de las voces de la ultraderecha en el Parlamento.
+Principal motor del PBI de Brasil, el agronegocio celebró la aprobación por 43 a 21 votos del marco temporal. La Confederación Brasileña de Agricultura y Ganadería, principal entidad ruralista, difundió una nota felicitando al Frente Parlamentario Agropecuario y al Senado por la medida. "La aprobación en el Congreso Nacional restablece la seguridad jurídica y trae pacificación social", destacó la entidad.
+El presidente del Senado, Rodrigo Pacheco, defendió la potestad del legislativo para decidir sobre el tema. "No hay ningún tipo de enfrentamiento con el tribunal supremo, es apenas una posición del Congreso, considerando que juzgamos que temas de esa naturaleza deben ser deliberados por el Congreso", dijo Pacheco.
+Una vez aprobado el marco temporal el proyecto queda en manos de Lula, cuya base parlamentaria ya anunció que el mandatario lo vetará. Eso sólo lo devolvería a las cámaras para una nueva deliberación, que puede desgastar más al gobierno en el Congreso.
+La Corte Suprema dispuso, el mismo miércoles en que se votó en el Congreso, que aquellos productores que hayan adquirido "de buena fe" tierras que tradicionalmente pertenecen a los indígenas tienen derecho a una indemnización por parte del Estado.
+La demarcación de tierras indígenas, una obligación del Estado según la Constitución, estuvo suspendida entre 2019 y 2022, durante la gestión del entonces presidente Jair Bolsonaro, y fue retomada este mismo año por el gobierno de Lula. Durante todo su mandato Bolsonaro justificó su negativa al reconocimiento de tierras indígenas con el argumento de que eso haría "inviable" un mayor desarrollo del sector agropecuario.
+Según datos oficiales los indígenas ocupan cerca del 14 por ciento del territorio nacional, representado por unas 500 áreas ya delimitadas, a las que se pueden sumar otras 200 que aún son analizadas por las instituciones del Estado.
+[H2] Homosexuales y aborto en la mira
+Esta misma semana, en protesta por las decisiones de la Corte Suprema, los conservadores se declararon en obstrucción en el Parlamento y ya impidieron varias votaciones. Aún así promovieron el debate sobre el marco temporal y otros proyectos opuestos al máximo tribunal y que afectan indirectamente a Lula, hasta ahora apoyado en el Parlamento en materia económica y tributaria pero no en la "agenda de valores y costumbres".
+Un proyecto que avanza propone terminar con el matrimonio entre personas del mismo sexo, consagrado en 2011 por el Supremo y sobre el cual el Parlamento nunca legisló. El texto tramita en una comisión de Diputados, con clara mayoría bolsonarista, y será votado dentro de diez días para luego pasar al pleno de la Cámara Baja.
+La derecha pretende convocar un plebiscito para consultar a la población sobre el aborto, algo que será decidido por las cámaras en las próximas semanas. También anunciaron una movilización nacional el 12 de octubre, cuando en Brasil se celebra el Día del Niño, preparando el terreno para una eventual campaña hacia ese plebiscito.
+Se trata de otra respuesta directa al máximo tribunal, que aceptó a trámite una demanda para descriminalizar el aborto hasta las 12 semanas, presentada por el oficialista Partido Socialismo y Libertad que tiene sólo 14 de los 513 diputados y ningún escaño en el Senado. Esos asuntos deberán tramitarse en el Legislativo, pero la agenda antiderechos le devolvió el oxígeno a un conservadurismo arrinconado desde enero, cuando activistas de ultraderecha asaltaron las sedes de los tres poderes de la nación en un intento de derrocar a Lula.
+El 45 por ciento de la población está de acuerdo con el aborto y un 52 por ciento lo rechaza, mientras que los restantes no saben o no tienen una posición definida, según un sondeo reciente de la consultora Datafolha. La encuesta nacional de aborto de 2021, financiada por el Fondo Nacional de Salud brasileño, mostró que una de cada siete mujeres tuvo un aborto al llegar a sus 40 años y el 43 por ciento de ellas debió ser hospitalizada para completar el procedimiento.</t>
   </si>
   <si>
     <t>Una Escuela Campesina para fomentar el arraigo en el pueblo de Palma Sola</t>
@@ -1102,7 +2646,33 @@
     <t>https://www.pagina12.com.ar/591479-una-escuela-campesina-para-fomentar-el-arraigo-en-el-pueblo-</t>
   </si>
   <si>
-    <t>2023-09-25T04:34:55Z</t>
+    <t xml:space="preserve">Título: Una Escuela Campesina para fomentar el arraigo en el pueblo de Palma Sola
+Chapeau: "Era un sueño que nosotros teníamos"
+Subtítulo: Funciona en el predio de la organización Tierra Fértil, en el departamento Santa Bárbara, de Jujuy. Por ahora dictan cursos de producción bovina, conservas saladas y dulces y turismo rural.
+Editoria: Salta|12
+Tags: Agricultura familiar, agricultura-familiar, diario
+URL: https://www.pagina12.com.ar/591479-una-escuela-campesina-para-fomentar-el-arraigo-en-el-pueblo-/
+Notícia completa (20 blocos):
+El pequeño pueblo de Palma Sola, en la provincia de Jujuy, fue el escenario, el jueves 7 de septiembre, de la inauguración del Centro de Formación “Escuela Campesina”, una iniciativa de la organización Tierra Fértil, que reúne al campesinado que reside en los parajes de esa zona.
+El proyecto, un sueño del campesinado de Palma Sola, en palabras de Gloria Mamaní, se lleva a cabo en el marco del convenio entre el Instituto Nacional de Tecnología Agropecuaria (INTA) y el Ministerio de Trabajo, Empleo y Seguridad Social de la Nación, con la adhesión del Parque Nacional Calilegua y el Instituto Nacional de Agricultura Familiar, Campesina e Indígena.
+Gloria Mamaní, campesina y militante de Tierra Fértil dijo a Salta/12 que la escuela "es un sueño que nosotros teníamos" y el Ministerio de Trabajo les dió "una manito, una ayudita con el tema económico", con el que se financió la Escuela de donde chicas y chicos salen con un título de reconocimiento nacional "y puedan también conseguir un trabajo a futuro". Tres de los cursos previstos por ahora ya comenzaron, y la cursada irá desde septiembre a diciembre de 2023.
+"Todos los cursos van a ser referidos a la agricultura familiar, al valor agregado a la producción que hacen los pequeños productores de la agricultura familiar", informó Mamaní, quien destacó que en la zona hay mucha producción de bovinos y en agricultura se cultiva citrus preferentemente. Cada curso tiene un cupo máximo de veinte personas y se entrega un certificado oficial del Ministerio de Trabajo, Empleo y Seguridad Social. El requisito es ser mayor de 18 años. La Escuela funciona en el predio de la organización, donde también está la Casa Campesina.
+El financiamiento de la Nación permitirá cubrir gastos del equipo docente, comprar de insumos y solventar otras cuestiones vinculadas a la gestión. También posibilitó mejoras edilicias en la cocina y el baño de la Escuela.
+Se informó que la necesidad de contar con un Centro de Formación para el Trabajo surgió del diagnóstico participativo realizado desde la organización campesina junto a organismos del Estado nacional con trabajo territorial en la zona. En sus diferentes espacios participativos a los que asisten jóvenes surgió la necesidad de contar con herramientas de formación y capacitación que promuevan el arraigo, favorezcan la posibilidad de conseguir trabajo local con mejores ingresos y valoricen la producción campesina.
+De esta manera se busca mitigar la migración a espacios urbanos en búsqueda de trabajos de bajísima calidad y con pésimas remuneraciones. La oferta de cursos se propone constituirse en "una alternativa para evitar el actual éxodo rural que sufre la población especialmente la más joven causada por la inaccesibilidad hacia el sistema educativo, la falta de capacidades para acceder al mercado laboral local y la falta de equipamiento e infraestructura básica para la población rural".
+También se propone "proyectar y fortalecer nuevas propuestas para el trabajo local que contrapese la marcada estacionalidad de los empleos en la zona". Crear empleo local revalorizando saberes y posibilidades, y "brindar propuestas laborales alternativas fortaleciendo oficios tradicionales e incorporando nuevos oficios".
+En la Escuela Campesina se dictan cursos gratuitos de Auxiliar en producción animal, Gestión del turismo rural comunitario, Auxiliar en preparación de conservas de frutas y hortalizas, y a futuro, ya para marzo de 2024, se prevé dictar los cursos de Auxiliar en comercialización de la producción campesina y Gestión de medios y redes sociales.
+El INTA, el Parque Nacional Calilegua y Agricultura Familiar acompañarán en la gestión y con el aporte de docentes para los cursos propuestos.
+Palma sola está ubicada a 160 kilómetros de San Salvador de Jujuy, en el cordón montañoso de Santa Bárbara, en la zona de transición entre la zona chaqueña y la selva de Yunga. El pueblo sufre un grave proceso de desarraigo debido a que no existen propuestas formativas luego de terminar el ciclo secundario. La mayoría de las y los jóvenes que se va a estudiar a las ciudades no regresa, y quienes se quedan realizan trabajos precarios haciendo changas.
+[H2] ​Organización frente a la presión
+Gloria Mamaní, que además de integrante de Tierra Fértil es coordinadora en la zona del Instituto Nacional de Agricultura Familiar, contó a Salta/12 que comenzaron a organizarse en 2006 "cuando empezó a pecharnos fuerte el agronegocio con el tema de la soja, la caña, y a hacernos muchos desmontes y a querer desalojar a familias campesinas". En 2008 se conformó Tierra Fértil. La organización tiene una demanda en la que empresarios de la zona la "acusan de usurpar la tierra y darla a la gente".
+Mamaní destacó que el gobierno nacional ya reconoció la posesión del campesinado en la zona, a través de la Ley nacional de reparación histórica de la agricultura familiar. Y en Palma Sola la organización consiguió además que se declare por ordenanza municipal "área campesina" a todos los parajes, con la salvedad del ejido urbano. En el marco de esa ordenza se hizo un relevamiento del campesinado. Después de ese relevamiento recibieron una demanda del gobierno de Jujuy, "y ahora estos empresarios se agarran de esa demanda" para demandar a la organización, afirmó Gloria Mamaní, es lo que pasa, dijo, con un empresario de apellido Quintana, que trata de desalojar a la familia Centeno, en el paraje Las Goteras, a 55 kilómetros de Palma Sola.
+Sobre la Escuela Campesina, Mamaní destacó que hubo mucho interés y de hecho, "quedó mucha demanda del curso de producción bovina", por lo que el año que viene se dictará nuevamente. "De ahora a diciembre ya no tenemos cupo", dijo Mamaní, pero añadió que proyectan que en marzo de 2024 abrirán las inscripciones para dictar nuevamente los cursos de producción bovina y de turismo rural.
+Y adelantó que también piensan dictar cursos de contabilidad, "referida a la producción, que el productor que está metido en el campo aprenda a sacar cálculos, para, por ejemplo, poner en venta una vaca, saber si le conviene el porcentaje, el flete cuánto le sale, o un cabrito, un lechón".
+En Palma Sola "casi toda la gente vive en los parajes", el pueblo en sí mismo "es chiquitito", tiene entre 6 y 7 mil habitantes, y viene disminuyendo debido al desarraigo. Mamaní destacó que "la mayoría de los habitantes vive a 30 kilómetros, 15, a 50 kilómetros".
+Estas personas se dedican a la ganadería y también a la agricultura, con citrus y floricultura. También crían animales de granja, cabras, lechones y gallinas. "El año pasado con el tema de la sequía fue muy difícil, muy complicado, porque secó mucho la plantación no solamente las hortalizas, sino también el citrus, era como si le hubieran prendido fuego", eran plantaciones de diez años y muchos productores que "quedaron sin nada", contó Mamaní.
+El campesinado vive en parcelas en calidad de poseedores, algunas son tierras fiscales y otras tienen titulares registrales que no residen ahí. Mamaní explicó que en el caso de quienes se dedican a la agricultura, tienen tres o cuatro hectáreas, mientras que los ganaderos "tienen un poquito más, 100, 200 hectáreas.
+La producción se vende los mercados de Perico y Monterrico, ciudades de Jujuy, y de San Ramón de la Nueva Orán, en la provincia de Salta.</t>
   </si>
   <si>
     <t>Uno de los inviernos más calurosos de la historia en la región</t>
@@ -1114,7 +2684,32 @@
     <t>https://www.pagina12.com.ar/590365-uno-de-los-inviernos-mas-calurosos-de-la-historia-en-la-regi</t>
   </si>
   <si>
-    <t>2023-09-22T03:01:00Z</t>
+    <t xml:space="preserve">Título: Uno de los inviernos más calurosos de la historia en la región
+Chapeau: Olas de calor en Argentina, Uruguay y Chile, y lluvias torrenciales en Brasil, que provocaron casi medio centenar de muertes
+Subtítulo: Temperaturas muy altas marcaron el invierno austral de este año en toda la región del Cono Sur latinoamericano, donde además del cambio climático, el fenómeno de El Niño hizo que los termómetros ro
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/590365-uno-de-los-inviernos-mas-calurosos-de-la-historia-en-la-regi/
+Notícia completa (19 blocos):
+Temperaturas muy altas marcaron el invierno austral de este año en toda la región del Cono Sur latinoamericano, donde además del cambio climático, el fenómeno de El Niño hizo que los termómetros rozaran los 30ºC en Buenos Aires, y provocó intensas lluvias en Chile o ciclones en el sur de Brasil.
+En pleno agosto, se vivieron olas de calor en Argentina, Uruguay y Chile. En localidades como Tartagal, Salta, la temperatura alcanzó los 40,2ºC, mientras en Vicuña, al pie de la cordillera del lado chileno, a la altura de La Rioja, y a unos 450 km al norte de Santiago, se elevó a 37ºC, la más alta en 70 años.
+Pero también hubo lluvias torrenciales en Chile, las mayores en 30 años, que dejaron inundaciones, seis muertos y un superávit en zonas afectadas por una sequía de 13 años, como el centro del país, rico en producción agrícola.
+En Muçum y otras ciudades del estado Rio Grande do Sul, en Brasil, un ciclón provocó grandes inundaciones y deslaves que dejaron 46 muertos a inicios de septiembre. El río Taquari se desbordó, lo que golpeó zonas elevadas y apartadas de su cauce. En esta región de Brasil fronteriza con Uruguay, este invierno hubo granizos, vientos fuertes y tempestades. Más de 147.000 personas fueron afectadas en todo el estado brasileño.
+Expertos prevén que estos eventos extremos comiencen a ser habituales, producto del cambio climático que agrava los efectos de fenómenos meteorológicos como El Niño y La Niña.
+"Lo más probable es que ya no tengamos más escenarios con lluvias bien distribuidas y temperaturas amenas en los próximos años", dijo a la AFP Pedro Côrtes, profesor del instituto de Energía y Ambiente de la Universidad de Sao Paulo.
+[H2] Olas de calor y baja humedad
+En julio, los termómetros en el centro y norte de Argentina se elevaron con valores de hasta 6ºC y 7°C por encima del promedio, mientras en Santiago de Chile el promedio de temperaturas máximas para el trimestre junio-agosto fue de 17,3ºC, el cuarto más alto desde 1960.
+Brasil vivió el mes de julio más caluroso desde 1961. La temperatura promedio fue un grado más alta respecto del período 1991-2020, de acuerdo al Instituto Nacional de Meteorología de Brasil (Inmet).
+Las regiones que más experimentaron el aumento de temperatura fueron el sur de la Amazonia, el centro-oeste del país -corazón del agronegocio-, y la región sur.
+"Este incremento de las temperaturas podría deberse a una sequedad de la atmósfera. No es el cambio climático el único responsable", explica el meteorólogo de la Dirección Meteorológica de Chile.
+En Uruguay el invierno "se caracterizó por un déficit en las precipitaciones muy marcado (...) y por temperaturas elevadas" en comparación con los últimos 30 años, dijo la meteoróloga Madeleine Renom, profesora de la Universidad de La República.
+[H2] Efectos en la agricultura
+La sequía venía golpeando las economías de varios países de la región. En Argentina, el gobierno estimó las pérdidas para este año a causa de la falta de agua en 20.000 millones de dólares, casi el 3% del PIB.
+La sequía, que desde hace tres años afecta a la cuenca del Río de la Plata, impactó también en el suministro de agua potable en el suroeste de Uruguay y en el agro.
+En el segundo trimestre del año el PIB uruguayo cayó 2,5% interanual, arrastrado por el impacto de las menores lluvias en la actividad agropecuaria y en el sector de la energía eléctrica, gas y agua.
+"La cantidad de agua que cae anualmente es parecida pero ahora son lluvias muy fuertes en poco tiempo, causando destrucciones en áreas agrícolas y de infraestructura urbana", explica Adolfo Pria, profesor de la Universidad Nacional de Brasil en el área de agricultura y medio ambiente.
+Pria destaca que la concentración de lluvias con vientos fuertes presenta un riesgo para plantaciones expuestas a una erosión agresiva del suelo, como la soja y el maíz, de las que Brasil es el primer y segundo productor mundial, respectivamente.
+"Todos los productores se han jugado en sus siembras a las precipitaciones que traiga consigo El Niño desde septiembre y consideran que existe un gran potencial para una excelente cosecha 'gruesa' (soja, maíz, girasol) para 2024", dijo el meteorólogo Mauricio Saldivar, de la organización Meteored.</t>
   </si>
   <si>
     <t>36% de la tierra productiva está en manos del 1% más rico</t>
@@ -1126,7 +2721,19 @@
     <t>https://www.pagina12.com.ar/585926-36-de-la-tierra-productiva-esta-en-manos-del-1-mas-rico</t>
   </si>
   <si>
-    <t>2023-09-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: 36% de la tierra productiva está en manos del 1% más rico
+Chapeau: LA CIFRA
+Subtítulo: El 36 por ciento de la tierra productiva en la Argentina rural está en manos del 1% más rico de los propietarios de tierra. Según los censos nacionales agropecuarios del Indec -de 1988, 2002
+Editoria: Las12
+Tags: extractivismo, printed-edition
+URL: https://www.pagina12.com.ar/585926-36-de-la-tierra-productiva-esta-en-manos-del-1-mas-rico/
+Notícia completa (6 blocos):
+El 36 por ciento de la tierra productiva en la Argentina rural está en manos del 1% más rico de los propietarios de tierra. Según los censos nacionales agropecuarios del Indec -de 1988, 2002, 2008, 2018-, entre 1988 y 2018 desaparecieron más de 156 mil establecimientos agropecuarios, en su gran mayoría pequeñxs y medianxs productorxs de alimentos, y se duplicó la concentración de la tierra en cada vez menos dueños: los dueños de la tierra. Los efectos de este despojo coinciden con el arrase y cercamiento de los extractivismos sobre territorios indígenas, campesinos e incluso de productorxs chacarerxs, “que pierden sus espacios de producción y de vida, acrecentando el éxodo rural hacia las grandes ciudades y destruyendo diversas formas de vida y culturas rurales”.
+El informe de Juan Wahren, investigador del Conicet y del Grupo de Estudios Rurales (GER-Gemsal) del Instituto Gino Germani, que publica la Agencia de noticias TierraViva, confirma que el período 1988-2018 coincide, “no casualmente, con el surgimiento y consolidación del modelo de agronegocios a escala nacional y global, cuyo cultivo estrella en la Argentina es la soja transgénica (al que acompañan el maíz, trigo, arroz y otros cultivos modificados genéticamente). Y también con el avance exponencial de otras actividades extractivas como los hidrocarburos, la megaminería y los emprendimientos forestales”.
+Wahren subraya que al mismo tiempo, en la Argentina urbana “se incrementaron exponencialmente los procesos de gentrificación y especulación inmobiliaria en las grandes ciudades, en un proceso de tal magnitud que se lo ha caracterizado como una forma de extractivismo urbano”. Esas actividades impactan directamente sobre las zonas rurales-urbanas y humedales, bosques nativos, salares y otros ecosistemas que sufren enormes transformaciones “y que provocan, entre otras cosas, un aumento de las inundaciones, incendios y una creciente contaminación de las fuentes de agua (ríos, lagos, acuíferos, etcétera)”.
+Capítulo aparte para las afecciones que generan a la salud humana, por el uso masivo de agrotóxicos para las fumigaciones de los cultivos transgénicos y químicos peligrosos, que se utilizan en la actividad de la megaminería y el “fracking” de los hidrocarburos no convencionales. Las consecuencias del extractivismo se extienden además hacia los territorios urbanos, remarca el investigador, “donde miles de personas viven hacinadas en villas y asentamientos populares como si fueran ´guetos´, sin acceso real a las ciudades, a sus infraestructuras (plazas, escuelas, hospitales, calles) o a sus servicios básicos (agua, cloacas, electricidad, gas); mientras proliferan barrios privados y ´countries´ que profundizan la segregación espacial en las grandes urbes y sus suburbios”.
+Frente a estos avances territoriales, organizaciones campesinas, pueblos indígenas, asambleas de vecinos y vecinas de pueblos rurales, agrupaciones ambientalistas, artistas y académicxs del Conicet impulsan un ciclo de Asambleas Públicas performativas en la Manzana de las Luces, para debatir sobre los elementos principales de la Naturaleza, Tierra, Fuego y Agua. “Será una puesta en escena del arte de la política. De la política de los territorios. De la política de las calles. De la política de los barrios. De la política que emana de los poros de los cuerpos despojados -concluye Wahren-. De la política que no delibera en espacios obturados a la voluntad colectiva, sino que los abre e invita a pensarlo todo, a debatirlo todo, a cambiarlo todo.”
+Más información: manzanadelasluces.cultura.gob.ar</t>
   </si>
   <si>
     <t>Lula creó dos nuevas reservas indígenas en la región amazónica</t>
@@ -1138,7 +2745,22 @@
     <t>https://www.pagina12.com.ar/585474-lula-creo-dos-nuevas-reservas-indigenas-en-la-region-amazoni</t>
   </si>
   <si>
-    <t>2023-09-06T17:11:25Z</t>
+    <t xml:space="preserve">Título: Lula creó dos nuevas reservas indígenas en la región amazónica
+Chapeau: Luego de que Bolsonaro anulara la concesión de territorios ancestrales para los pueblos originarios
+Subtítulo: El presidente de Brasil, Luiz Inácio Lula da Silva, creó por decreto dos nuevas reservas indígenas en la región amazónica, a la vez que destacó la unidad de los países amazónicos, africanos
+Editoria: Brasil
+Tags: Brasil, Lula Da Silva, Amazonia, pueblos originarios, lula-da-silva, pueblos-originarios
+URL: https://www.pagina12.com.ar/585474-lula-creo-dos-nuevas-reservas-indigenas-en-la-region-amazoni/
+Notícia completa (9 blocos):
+El presidente de Brasil, Luiz Inácio Lula da Silva, creó por decreto dos nuevas reservas indígenas en la región amazónica, a la vez que destacó la unidad de los países amazónicos, africanos y asiáticos para reclamar compensaciones financieras a las naciones ricas por preservar la selva. Su política ambiental, dijo, tiene como meta la deforestación cero en 2030.
+Con la decisión, ya son ocho las reservas oficializadas desde el inicio de su mandato el 1° de enero, luego de que su antecesor, Jair Bolsonaro, anulara las políticas de concesión de territorios ancestrales a los pueblos originarios, un añejo reclamo del agronegocio.
+Los dos nuevos territorios son Rio Gregório, en el estado de Acre, y Acapuri de Cima, en Amazonas, donde viven los pueblos originarios Katukina Pano, Yawanawá y Kokama, con una población estimada en alrededor de 1.000 personas, que conviven bajo amenaza de la minería ilegal y los ocupantes ilegales de tierras para cría de ganado y explotación maderera.
+La aprobación de las nuevas demarcaciones fue realizada por Lula en una ceremonia en el Palacio del Planalto en celebración del Día de la Amazonia.
+[H2] Crimen organizado y mafias
+El mandatario dijo al lado de las ministras de Ambiente y Cambio Climático, Marina Silva, y de Pueblos Indígenas, Sonia Guajajara, que durante su gestión la Policía Federal y las Fuerzas Armadas trabajarán en el control fronterizo y en el combate a las mafias que operan en la selva amazónica, de la cual Brasil tiene 60%.
+"No podemos permitir que la Amazonia sea escenario del crimen organizado en este país; vamos a combatir todo tipo de ilegalidad en este país para que la gente de la Amazonia pueda vivir feliz”, afirmó el presidente.
+Lula aseguró que "es necesario que las naciones ricas financien la preservación del bosque tropical en pie", al recordar que desde 2009 que los países desarrollados prometen sin cumplir aportes para que los países con selvas tropicales puedan mantener sus biomas.
+En ese sentido, aseguró que en los foros internacionales Brasil llegará con un discurso unido al lado de los países amazónicos y de otras tres naciones con las mayores selvas tropicales, como República del Congo, República Democrática del Congo e Indonesia.</t>
   </si>
   <si>
     <t>Se reabre la mesa de negociación UE-Mercosur</t>
@@ -1150,7 +2772,25 @@
     <t>https://www.pagina12.com.ar/584886-se-reabre-la-mesa-de-negociacion-ue-mercosur</t>
   </si>
   <si>
-    <t>2023-09-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: Se reabre la mesa de negociación UE-Mercosur
+Chapeau: El 15 de septiembre habrá una nueva reunión en Brasilia
+Subtítulo: Las nuevas restricciones en materia ambiental que tiene en carpeta la Unión Europea encendió alarmas en los países del bloque sudamericano.
+Editoria: Economia
+Tags: acuerdo Mercosur-Unión Europea, printed-edition, acuerdo-mercosur-union-europea, diario
+URL: https://www.pagina12.com.ar/584886-se-reabre-la-mesa-de-negociacion-ue-mercosur/
+Notícia completa (12 blocos):
+Representantes de la Unión Europea y del Mercosur se reunirán el próximo 15 de septiembre en Brasilia para continuar las negociaciones sobre el acuerdo de libre comercio. Así lo afirmó el ministro brasileño de Asuntos Exteriores, Mauro Vieira, quien reiteró la posición del Mercosur de que “la salvaguarda del medio ambiente que propone la UE no se convierta en un pretexto para aplicar medidas proteccionistas”.
+A pesar de que se trata de un tema que viene con amagues desde hace dos décadas, Vieira se mostró “optimista” sobre el curso de las negociaciones y dijo que se sigue apuntando a cerrar el acuerdo antes de fin de año. “Los demás países del Mercosur tienen la misma posición. Ya hablé con los cancilleres de Uruguay (Francisco Bustillo Bonasso), Argentina (Santiago Cafiero) y Paraguay (Rubén Ramírez Lezcano)”, precisó.
+[H2] Diferencias
+En el último tiempo surgió una nueva diferencia entre los bloques, que ahora está en el centro de la mesa de negociación. Se trata de las normas contra la deforestación que busca aplicar la UE y que tendrían un impacto negativo sobre las exportaciones sudamericanas hacia el Viejo Continente, particularmente sobre las ventas de Brasil.
+Ante ello, la Federación de Asociaciones Rurales del Mercosur emitió un comunicado en donde manifiesta su "preocupación por las medidas unilaterales de la UE". Otros importantes damnificados en el concierto global de los socios comerciales de la UE serían Honduras, Indonesia y Malasia, que son los mayores proveedores de café, aceite de palma, y caucho del continente.
+En esa línea, el mes que viene la Unión Europea (UE) comenzará a poner en vigencia su Mecanismo de Ajuste en Frontera por Carbono (CBAM, por sus siglas en inglés). Se trata de una herramienta de carácter ambiental que tendrá en los hechos un impacto proteccionista sobre las importaciones que realiza esa región, especialmente en el caso de los orígenes de países en desarrollo. La implementación de este mecanismo, de todos modos, será paulatina, de acá a comienzos de 2026.
+La idea del "Mecanismo" es castigar las importaciones de bienes que contienen una carga de emisiones de carbono que supera las exigencias que tienen las empresas que operan en territorio europeo. Así, los primeros perjudicados serían los exportadores de los países emergentes.
+[H2] Impacto
+Al margen del tema ambiental, un puntilloso informe elaborado por los especialistas Luciana Ghiotto y Javier Echaide, advierte que "el Mercosur y la UE tienen innegables asimetrías económicas. Este acuerdo mantendrá y profundizará las asimetrías existentes. El aumento en la exportación de productos agrícolas hacia la UE conducirá a una profundización del modelo de agronegocios, mientras que los países del Mercosur podrían sufrir una mayor desindustrialización y la exacerbación de las consecuencias ambientales y sociales negativas, que se derivan de la profundización de la producción basada en monocultivos y explotación de minerales".
+Además, sostienen que "el acuerdo tendrá un impacto directo en sectores productivos que hoy generan una importante cantidad de empleo, especialmente en los sectores de autopartes, maquinarias, químicos, textiles y calzado". Concluyen que "los grandes ganadores de este acuerdo son las grandes corporaciones europeas. Estas son económicamente más fuertes y están mejor posicionadas que sus contrapartes del Mercosur".
+De acuerdo a un informe de la consultora LLYC, Portugal sería unos de los países más beneficiados por el acuerdo comercial. Ese documento detalla que "las exportaciones portuguesas a Brasil han disminuido en los últimos años, por lo que el acuerdo podría conllevar un nuevo incremento que revierta el estado actual de la balanza comercial entre los países, actualmente desfavorable para Portugal". Asimismo, el país luso oportunidades para mejorar la inserción de su producción de vino en Brasil y de automóviles.
+Por otro lado, el informe destaca oportunidades para el sector autopartista de Brasil y Argentina, ya que la UE importa piezas por 63 mil millones de dólares anuales. También habría potencial de mercado en empresas del sector químico, textil, calzado, productos de higiene y limpieza, lácteos, carne vacuna y aves, fruta y verduras y cereales.</t>
   </si>
   <si>
     <t>Javier Lewkowicz</t>
@@ -1162,7 +2802,39 @@
     <t>https://www.pagina12.com.ar/583983-carta-abierta-a-los-jueces-de-la-corte-suprema</t>
   </si>
   <si>
-    <t>2023-08-31T20:47:24Z</t>
+    <t xml:space="preserve">Título: Carta abierta a los jueces de la Corte Suprema
+Subtítulo: A los Ministros de la Corte Suprema de Justicia de la NaciónHoracio Rosatti - Carlos Fernando RosenkrantzJuan Carlos Maqueda - Ricardo Lorenzetti
+Editoria: El País
+Tags: Adolfo Pérez Esquivel, Corte Suprema, Opinión, adolfo-perez-esquivel, corte-suprema, opinion, diario
+URL: https://www.pagina12.com.ar/583983-carta-abierta-a-los-jueces-de-la-corte-suprema/
+Notícia completa (27 blocos):
+A los Ministros de la Corte Suprema de Justicia de la Nación
+Horacio Rosatti - Carlos Fernando Rosenkrantz
+Juan Carlos Maqueda - Ricardo Lorenzetti
+Reciban el saludo de Paz y Bien.
+Esta es una carta abierta, ante la imposibilidad de llegar a ustedes personalmente, dado que hasta ahora se han negado a escuchar y recibir a los pueblos originarios que viajaron 1.500 Km. desde la provincia de Jujuy a la Capital Federal con la esperanza de ser recibidos por la Corte Suprema para presentar su rechazo a la Reforma Parcial de la Constitución votada en la Provincia de Jujuy que transgrede y no respeta la Constitución Nacional, violando el Convenio 169 de la OIT sobre Pueblos Indígenas y Tribales en países independientes y la Declaración Universal de los Derechos de los Pueblos Indígenas promulgado por las Naciones Unidas.
+El proceso de reforma también incumplió las normativas existentes para asegurar el acceso a la información y participación ciudadana en materia ambiental en temas sensibles como la regulación del agua y las tierras. Se incumplieron los principios de consulta a la comunidad previstos en el Acuerdo de Escazú, firmado por nuestro país y de jerarquía normativa superior a las normas provinciales.
+La convocatoria de la Constituyente en Jujuy, estuvo afectada por diversas irregularidades de procedimiento, entre estas cabe destacar las licencias alternadas del gobernador de la Provincia, para ejercer a la vez como presidente de la Constituyente, que no dejaran expresar sus opiniones de muchas organizaciones sociales que manifestaron su interés para participar. Pese a que el plazo para debatir la reforma era de 90 días, adrede se evitó el debate y en menos de tres semanas se aprobó en forma exprés, una constitución que transgrede la Constitución Nacional.
+Fueron las movilizaciones de cientos de comunidades de pueblos indígenas quienes cuestionaron esta reforma, gravitaron para que se eliminaran algunos artículos cuestionados ya votados que no pasaron el trámite de ser nuevamente votados por la convención constituyente. El punto es que el gobernador, a su vez presidente de la constituyente terminó de imponer una reforma sin consulta alguna con el pueblo, violando sus derechos y cuando aparecieron los reclamos populares contrarios a la reforma respondió con la represión policial y la persecución a docentes y comunidades indígenas.
+El Gobierno de Morales no sólo ha reprimido violentamente protestas sociales pacíficas, habilitó métodos de la última dictadura militar, persecución ideológica a quienes disienten como es el caso de la acusación por sedición del Dr. Hallar por cuestionar la reforma constitucional, se han dado detenciones arbitrarias, allanamientos domiciliarios sin orden judicial, represión parapolicial y grupos de tareas civiles, operando con camionetas sin patentes, las fuerzas policiales han disparado adrede a los ojos de manifestantes, la justicia controlada por el Poder Ejecutivo provincial desestima toda investigación sobre los hechos represivos, convalida causas con acusaciones fraguadas y aplica masivamente contravenciones altamente onerosas para amedrentar a quienes osen manifestar por sus derechos.
+La nueva Constitución habilita la criminalización de la protesta social, artículos ambiguos permiten tipificar como sedición reclamos que se expresen en defensa del pueblo. La penalización del derecho a la protesta, contraviene el Sistema Interamericano de Derechos Humanos.
+Con relación a los pueblos indígenas no se respetaron los protocolos previstos en el Convenio 169 de la OIT, que establece que debe garantizarse la consulta libre, previa e informada a pueblos indígenas sobre cuestiones susceptibles de afectarlos.
+En el Artículo 7 el Convenio dispone que los pueblos indígenas deberán “participar en la formulación, aplicación y evaluación de los planes y programas de desarrollo nacional y regional susceptibles de afectarles directamente.”
+En todos los casos los pueblos indígenas deben poder decidir sobre la utilización, administración y conservación de los Bienes Comunes. Para lo cual deben asegurarse la información previa oportuna y suficiente para fortalecer las capacidades de los pueblos originarios en su interlocución con las diversas reparticiones estatales. Las consultas deben realizarse de buena fe, el objetivo de esos procesos es tratar de alcanzar acuerdos, basados en el respeto mutuo. No puede considerarse una consulta realizar una reunión meramente informativa para escuchar algunas preguntas, pero sin que las comunidades puedan tener posibilidades de intervenir en las decisiones que se adopten. Aún en el caso que no se arribe a un acuerdo, el Estado debe respetar los derechos originarios reconocidos por el Convenio. La política pública no puede propasarse y terminar imponiendo su voluntad cuando encuentre oposición a sus contenidos y/o implementación.
+La Convención Constituyente votada para reformar la constitución provincial, incumplió este tratado internacional que tiene rango constitucional.
+En diversas Constituciones Provinciales, se han reconocidos derechos más amplios que los contemplados en la Carta Magna Nacional. No sólo se reconoce la preexistencia de los pueblos indígenas, su identidad étnica y cultural, su personería jurídica, sino también la propiedad comunitaria de la tierra que ocupan y las que puedan asignárseles como reparación histórica en forma gratuita y exentas de todo gravamen. Tales tierras son inembargables, imprescriptibles, indivisibles e intransferibles a terceros. Estos criterios debieran haber sido objeto del diálogo en la Convención Constituyente jujeña, sin embargo, la reforma aprobada legaliza a nivel constitucional que el Poder Ejecutivo Provincial, pueda disponer de las tierras de los pueblos originarios haciéndolas pasar por fiscales y poder así expandir el extractivismo minero, los agronegocios y los intereses inmobiliarios para las minorías privilegiadas.
+Frente a esa situación de indefensión y violencia El Malón por la Paz viajo a Buenos Aires solicitando ser recibidos por los integrantes de la Corte Suprema, sin resultado alguno hasta el momento.
+Lamentamos el silencio y la discriminación de la Corte Suprema que se niega a escucharlos, sabiendo que los indígenas están en Plaza Lavalle desde hace una semana a la intemperie y con necesidades básicas y de higiene, en particular mujeres y niños.
+El Jefe de Gobierno de la Ciudad, compañero de fórmula presidencial con el gobernador Morales también ha mantenido una actitud represiva y de maltrato a los hermanos indígenas impidiendo instalar una carpa lo cual pone en evidencia su racismo y la intolerancia violando los derechos humanos de las comunidades quienes soportan hambre, frío esperando que los miembros de la Corte Suprema los escuchen.
+Señores Ministros les pregunto: ¿qué piensan hacer frente a esta grave situación que viven los pueblos originarios en Jujuy? ¡Qué piensan hacer frente a las graves violaciones de los DDHH y al derecho que tienen los pueblos a sus territorios, agua y recursos naturales que les quiere sacar la gobernación de Jujuy?
+La Corte Suprema intervino con celeridad en vísperas de elecciones provinciales prontas a realizarse, para vetar las candidaturas de gobernadores oficialistas, en función de “desalentar la posibilidad de perpetuación en el poder”. Esta intervención se dio a partir de cautelares presentadas por fuerzas de la oposición y la CSJ entendió que la vulneración del principio de la alternancia tornaba ineludible la intervención de la Corte.
+Como es posible qué frente a la reforma de la Constitución Jujeña, donde hay presentadas cautelares, la CSJ no haya intervenido con la misma celeridad, ante un caso mucho más grave que es una constituyente con vocación secesionista que vulnera la unión nacional, altera el equilibrio de poderes y contrapesos republicanos habilitando una alta concentración del poder en el Ejecutivo provincial y contraviene la Constitución Nacional y los Tratados Internacionales.
+Los pueblos indígenas están aquí para reclamar sus derechos, evitar la violencia y la discriminación, racismo e intolerancia y ustedes tienen la obligación de escucharlos y protegerlos en sus derechos.
+Espero que escuchen el clamor de los pueblos y actúen con verdad y justicia. A cuarenta años del retorno a la democracia, honren el Nunca Más que supimos conseguir.
+Les reitero el saludo de Paz y Bien que tanto necesita nuestro país y el mundo.
+Adolfo Pérez Esquivel
+Premio Nobel de la Paz
+Presidente del Servicio Paz y Justicia</t>
   </si>
   <si>
     <t>Adolfo Pérez Esquivel</t>
@@ -1177,7 +2849,23 @@
     <t>https://www.pagina12.com.ar/579834-javier-milei-a-lo-donald-trump-no-quiere-hacer-negocios-con-</t>
   </si>
   <si>
-    <t>2023-08-17T19:59:29Z</t>
+    <t xml:space="preserve">Título: Javier Milei, a lo Donald Trump: no quiere hacer negocios con China
+Chapeau: El diputado ultraderechista prefiere volver a las relaciones carnales con EE.UU.
+Subtítulo: Pese a que China es el segundo socio comercial de la Argentina en materia de exportación y el primero en importaciones, el candidato más votado de las PASO expresa que no se deberían hacer negocios con el gigante asiático. "No negocio mi moral a cambio de dinero", dijo, en una entrevista, el exasesor de Ricardo Bussi, condenado por el terrorismo de Estado.
+Editoria: Economia
+Tags: diario
+URL: https://www.pagina12.com.ar/579834-javier-milei-a-lo-donald-trump-no-quiere-hacer-negocios-con-/
+Notícia completa (10 blocos):
+El candidato de la Libertad Avanza Javier Milei confirmó en la ronda de entrevistas que dio tras su victoria en las PASO que romperá relaciones comerciales con China en caso de llegar a la Casa Rosada. Milei aseguró que él no realizaría "transacciones con comunistas" ya en 2021, cuando aún no había sido electo como diputado, pero ahora con las posibilidades de ingresar a un balotaje presidencial sostener esa posición parece una amenaza para la macroeconomía del país.
+China es el segundo socio comercial de la Argentina en materia de exportación el 9,1 por ciento del total, detrás de Brasil 14,3 por ciento principal socio del país. En materia de importaciones, Argentina demanda el 21,5 por ciento de sus compras al gigante asiático, seguido por Brasil con el 19,7 por ciento.
+Lo que Milei repitió esta semana en las entrevistas que lo tuvieron como la sorpresa de las PASO ya lo dijo en octubre de 2021, cuando en una entrevista al Canal de la Ciudad, respondió: "Yo no haría negocios con China". Ante la consulta de lo que implicaría para la macroeconómica del país, el entonces economista mediático sostuvo: "Es falso que sería una transacción macroeconómica, podríamos hacer transacciones con el lado civilizado de la vida, Occidente. Yo no hago transacciones con comunistas. No negocio mi moral a cambio de dinero". Milei fue asesor de Ricardo Bussi, condenado por el terrorismo de Estado en la última dictadura militar argentina.
+El lineamiento planteado por Milei es con Estados Unidos a nivel comercial y diplomático. El país del norte se ubica en el tercer lugar en materia de exportaciones de Argentina con 7,5 por ciento, y en la misma ubicación en materia de importaciones con 12,7 por ciento. En tanto, la Unión Europea es el destino del 12,3 por ciento de las exportaciones del país.
+Cortar la relación con China parece contraponerse con la promesa de Milei a los sectores del agronegocio, ya que quitar el mercado chino del mapa significaría borrar al principal socio comercial en materia de exportaciones agropecuarias. La novela entre el gobierno de Mauricio Macri y el de su aliado Donald Trump por la exportación de limones, marca un ejemplo de la falta de complementariedad del mercado agropecuaria argentino con el norteamericano, en el que son competidores.
+Romper relaciones con China implicaría un impacto a otros niveles. Recientemente, Argentina utilizó el swap con el gigante asiático para pagar su deuda con el FMI, lo que le permitió cumplir con los compromisos del organismo en el que China también tiene un lugar importante. Además, la relación de inversiones chinas en el país crecieron exponencialmente desde el acuerdo firmado en el gobierno de Néstor Kirchner.
+La decisión del gigante asiático de invertir en toda la región, como fuente de materias primas, ocurre desde principios de este siglo y no fue modificado por ningún ejecutivo ni progresista ni de derecha. Macri también se encargó de afianzar la relación comercial con China, mientras que en Brasil, el ex presidente Jair Bolsonaro, también lo hizo y mantuvo su integración al BRICS, mientras boicoteó la política económica regional del Mercosur.
+Argentina está solicitando ingresar al bloque de países integrado por Brasil, Rusia, India, China y Sudáfrica y a su Banco de Desarrollo, que tendrá su reunión de directorio la próxima semana. Con la posibilidad de que Milei acceda a la Casa Rosada esos intento quedarían frustrados.
+En materia de inversiones, Argentina integra el acuerdo con China denominado la Iniciativa de la Franja y la Ruta (BRI por sus siglas en inglés), anunciado en 2013, para expandir la presencia de las inversiones a nivel global para disputar el rol de Occidente, con quien Milei asegura se alineara directamente, en un mundo marcado por la multipolaridad.
+Según un informe del Green Finance &amp; Development Center de la Universidad de Fudan, en China, en los primeros seis meses del año, los compromisos de China hacia los 148 países de la Iniciativa de la Franja y la Ruta muestran alrededor de 102 acuerdos bilaterales por valor de 43.300 millones de dólares, lo que equivale al 60 por ciento de las promesas de inversión que el país asiático hizo en todo el año pasado.</t>
   </si>
   <si>
     <t>La economía de la transhumancia</t>
@@ -1189,7 +2877,25 @@
     <t>https://www.pagina12.com.ar/576286-la-economia-de-la-transhumancia</t>
   </si>
   <si>
-    <t>2023-08-13T03:01:00Z</t>
+    <t xml:space="preserve">Título: La economía de la transhumancia
+Chapeau: Una cultura ancestral en peligro
+Subtítulo: El pastoreo de ganado en diferentes territorios, para el invierno y verano, de las zonas cordilleranas, tiene miles de años, pero se ve impedido por el avance inmobiliario.
+Editoria: Cash
+Tags: mapuches, printed-edition
+URL: https://www.pagina12.com.ar/576286-la-economia-de-la-transhumancia/
+Notícia completa (12 blocos):
+La trashumancia ha sido utilizada como metáfora e inspiración para décimas, coplas y canciones, desde cantos ancestrales a buena parte de la obra de Atahualpa Yupanqui, Saúl Huenchul o Rally Barrionuevo. Es una práctica milenaria que tiene al menos 2000 años en nuestro continente y ocupa a unos 200 millones de personas en el mundo y 30 millones de kilométros cuadrados (el doble de las tierras dedicadas a la agricultura). Fue declarada en 2019 Patrimonio Cultural Inmaterial de la Humanidad por la Unesco.
+Sin embargo, desde el Movimiento Nacional Campesino Indígena Somos Tierra (MNCI), parte de la Mesa Agroalimentaria Argentina (MAA), se viene denunciando que el avance del negocio inmobiliario y el agronegocio viene amenazando esta práctica. “Si de por sí es difícil que los fiscales necios de la ciudad comprendan el uso de posesión de un campo, imaginen la dificultad para que comprenda está dinámica que incluye dos áreas y un camino”, explica Diego Montón, dirigente del MNCI Somos Tierra y la MAA.
+[H2] Una práctica ancestral amenazada
+Desde los pueblos mapuches y la cultura campesina patagónica, la transhumancia es una forma de producción de carne vacuna, bovina o caprina, que tiene en cuenta las condiciones climáticas y de suelo. Durante el invierno se utilizan las zonas de llanura o precordillera, donde se puede proteger al ganado. Sin embargo en primavera o verano (en la llamada veraneada), las familias campesinas llevan sus animales a la zona de cordillera donde el derretimiento de la nieve crea nuevas pasturas que engordan el ganado y dejan descansar los suelos de las zonas desérticas donde se desarrolla la invernada.
+“A los hechos del uso del territorio, es importante que las familias tienen su casa principal en el llano, donde pasan el invierno. Pero también en la alta montaña tienen un refugio o una casa más pequeña, donde van a pasar la veranada, con corrales y el territorio ocupado. Sumado a los caminos de arreo, que es una de las cosas que ha entrado en conflicto”, explica Montón. “Acá en Mendoza, por ejemplo, tenemos el caso del El Azufre, un centro de ski que van a construir en Malargue en terrenos fiscales cedidos por el estado provincial con una donación de entre 20 mil y 50 mil hectáreas, desconociendo que son tierras utilizadas para la veranada en el marco de las transhumancia”, cuenta.
+“Siempre viene gente de afuera a hacerse dueña de lo que nuestros abuelos y toda la gente anciana ha trabajado en esos campos. El Estado acá siempre ha sido ausente. Se acuerdan de los puesteros sólo cuando hay elecciones. Conocen las condiciones en que vivimos pero nunca han solucionan nada”, relata Natalia Arroyo, productora caprina de Malargue y miembro del MNCI Somos Tierra. “Acá es complicada la comercialización por el tema de la distancia, los caminos malos, la pastura, el daño del puma y del zorro. Gracias a ser parte del movimiento campesino pude conocer mis derechos y el tema de la tierra o el agua. Nos han apoyado mucho. Pero el Estado no. No tenemos vehículos y muchas veces sacan el colectivo”, se queja. “En Malargue se hace la fiesta del chivo, pero algunos puesteros ni se enteran. Hacen oídos sordos a todos nuestros reclamos. Cuando podrían recaudar en la fiesta fondos para ayudarnos con el forraje o mejorar nuestras condiciones de vida y producción”, opina.
+[H2] Los beneficios de organizarse
+“Al ser parte del MNCI nos hemos beneficiado en tener más fuerza y unirnos frente al atropello de los terratenientes. También ha sido más fácil entrar en programas provinciales o nacionales y finalmente lograr que se apruebe una ley de arreos, muy necesaria para nuestro sistema de producción”, cuenta desde Neuquén, Antonio Vázquez, también productor caprino y miembro del MNCI. “Yo crío cabras y vendo chivito, pero hay compañeros que producen verduras, quesos, dulces, escabeche, miel, medias de lana, fieltro o talabartería”, agrega.
+En 2016, Neuquén sancionó la ley 3016 que garantiza el derecho de las familias trashumantes a transitar con su ganado por las huellas de arreo para trasladarse de ida y vuelta entre veranadas e invernadas. Además de la delimitación de huellas de arreo e infraestructura de alojos.
+“La práctica de la transhumancia tiene toda una dimensión cultural que está plasmada en décimas y poesía del folklore, pero también una importante dimensión productiva y de sostenibilidad de los pastizales y la capacidad de carga de los campos. Estas zonas son las de mayor producción caprina del país”, explica Montón, refiriéndose al sur de Mendoza y el norte de Neuquén. Entre los beneficios socioambientales de la práctica transhumante también se encuentra la prevención de incendios.
+“La ley 3016 toma muchas de las reivindicaciones de las organizaciones campesinas y comunidades mapuches que nuclean a las familias arrieras. Pero quedan muchas cosas por trabajar, como el relevamiento de muchas huellas históricas. También, si bien la autoridad de aplicación es el ministerio de Producción y Turismo de la provincia, en la práctica no ha sido así. Han tenido que ser las organizaciones las que en los territorios estamos buscando que se cumpla y respete la ley”, reclama Solverio Alarcón, referente del MNCI Somos Tierra de Neuquén y parte de Organizaciones Unidas en Defensa de los Arrieros, el frente que presionó para la aprobación de esta ley.
+* Licenciado en Economía de la Universidad Torcuato Di Tella y master en Periodismo de la Universidad del País Vasco.</t>
   </si>
   <si>
     <t>Con el dólar maíz, el Gobierno lograría obtener US$ 2.000 millones en 15 días</t>
@@ -1198,7 +2904,12 @@
     <t>https://www.pagina12.com.ar/lbpupdates/572947</t>
   </si>
   <si>
-    <t>2023-07-31T21:44:40Z</t>
+    <t xml:space="preserve">Título: Página 12
+Editoria: [NÃO ENCONTRADO]
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/
+Notícia completa (0 blocos):
+[NÃO ENCONTRADO]</t>
   </si>
   <si>
     <t>Andrea Ribeiro Hoffmann: "La extrema derecha es un problema global"</t>
@@ -1210,7 +2921,25 @@
     <t>https://www.pagina12.com.ar/571280-andrea-ribeiro-hoffmann-la-extrema-derecha-es-un-problema-gl</t>
   </si>
   <si>
-    <t>2023-07-26T03:01:00Z</t>
+    <t xml:space="preserve">Título: Andrea Ribeiro Hoffmann: "La extrema derecha es un problema global"
+Chapeau: Académica de la Universidad Católica de Río de Janeiro
+Subtítulo: La doctora en Ciencias Políticas y Relaciones Internacionales analiza el fenómeno de los ultras en el mundo, así como también el antes y después del gobierno de Jair Bolsonaro en Brasil.
+Editoria: El Mundo
+Tags: Brasil, Extrema derecha, Jair Bolsonaro, Luiz Inácio Lula da Silva, printed-edition, extrema-derecha, jair-bolsonaro, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/571280-andrea-ribeiro-hoffmann-la-extrema-derecha-es-un-problema-gl/
+Notícia completa (12 blocos):
+Andrea Ribeiro Hoffmann es profesora de la Universidad Católica de Río de Janeiro (PUC-Rio) y forma parte de un proyecto de investigación llamado "Multilateralismo y Derecha Radical en América Latina" (Mudral), en colaboración con otros colegas. Tras su participación en el Congreso Mundial de Ciencia Política en Buenos Aires, la académica dialogó con PáginaI12 sobre la cuestión de las derechas en diferentes países y el impacto que tuvo en Brasil la experiencia bolsonarista.
+-¿Cómo surgió el proyecto de investigación y qué avances lograron?
+-La idea apareció a partir de la experiencia que tuvimos con el gobierno de Jair Bolsonaro en Brasil, cuyo impacto fue devastador en diversas esferas: desde la política y la salud, hasta el medio ambiente y la política exterior. La extrema derecha es un problema global, no es una coincidencia que haya un Donald Trump, un Bolsonaro y tantos otros gobiernos como esos. Tienen causas comunes, aunque también dinámicas locales muy específicas. En el caso de Bolsonaro, hubo una colaboración muy fuerte con el gobierno de Trump en muchos foros multilaterales. Por ejemplo, el Consenso de Ginebra, que fue una iniciativa conjunta para intentar cambiar normas internacionales respecto a cuestiones de género y derechos sexuales.
+-¿Por qué cree que hay países que dan giros hacia gobiernos de derecha o extrema derecha?
+-Es un fenómeno complejo. Hay una insatisfacción general de la población muy grande desde los últimos años, debido a la crisis económica y la pandemia, que afectó fuertemente a América Latina. Hay un desencanto con los gobiernos democráticos, que deberían proveer buenas condiciones de vida, con inclusión y una reducción de las asimetrías. Aquí entra también una cuestión nueva: las redes sociales. Se usaron como estrategia política en las campañas para captar votos, incluso con fakenews, como fue el caso de Trump. Entonces, gran parte de las poblaciones votan muchas veces en contra de sus propios intereses. Aún así, es muy difícil de comprender estos cambios que fueron muy rápidos, donde en América Latina, en general, hay una inclinación hacia los gobiernos de izquierda con sus propuestas de redistribución. Por ejemplo, en Brasil, una gran mayoría apoyó el primer y segundo mandato de Lula da Silva, sin embargo, esta misma población eligió un líder de extrema derecha. Es importante comprender esta complejidad, porque durante mucho tiempo no se creyó que fuera posible.
+-¿Puede volver a repetirse un acontecimiento similar al intento de golpe de Estado de enero en Brasil?
+-Lo que se vio es que las fuerzas armadas participaron en la toma de poder. Este fenómeno fue específico de Brasil, aun cuando América Latina comparte un pasado de dictaduras militares. Aunque se creía que este tema estaba resuelto en la región después del final de la Guerra Fría, Brasil muestra diferencias con Argentina o Chile, países donde se instauraron procesos de justicia transicional, una política de memoria. Durante la transición democrática en Brasil, se hizo uso de amnistías. Esto fue un punto de discusión muy importante, especialmente bajo la gestión de Dilma Rousseff, cuyo pasado como presa y torturada durante la dictadura destacó la importancia del tema. Sin embargo, el proceso fue incipiente y rápidamente se dio lugar a la destitución constitucional de este gobierno elegido por un movimiento político. Se percibió la presencia creciente de liderazgos y fuerzas militares, aunque no su dimensión hasta la tentativa de golpe en enero de este año, que mostró la disposición de los militares a participar activamente. Lula y su ministro de Justicia estuvieron muy preparados y atentos a este riesgo, porque era una crónica de la muerte denunciada.
+-¿En qué sentido?
+-Se esperaba que Bolsonaro no iba a aceptar la derrota, pero sí fue una sorpresa el nivel de violencia y destrucción. El bolsonarismo es un fenómeno social, no es solo de militares y no se terminó de un día al otro con el fin del mandato de Bolsonaro. Sus raíces son profundas, hay cuestiones estructurales y sociales que permanecen en la sociedad, con un sentimiento que podría llevar nuevamente al poder a políticos que compartieron su visión durante su gobierno. Mucha gente realmente dejó de creer que los sistemas democráticos son capaces de traer cambios en sus vidas. El desafío es conseguir que se confíe que la democracia es la forma de gobierno que permite más inclusión y redistribución.
+-¿Qué análisis hace sobre los primeros seis meses del gobierno de Lula?
+-Creo que enfrenta muchos desafíos debido al contexto diverso, tanto a nivel internacional como local. Todas las fuerzas políticas se unieron para formar su gobierno, lo que generó divergencias en la formulación de políticas. Así que lo que se ve en estos primeros meses fue una gran tentativa de Lula de conseguir gobernar, porque muchos bolsonaristas fueron electos, y también aprobar medidas importantes. Una de ellas fueron los cambios en el ámbito fiscal. Sin embargo, en la coalición de gobierno hay visiones distintas del rol de China y la guerra de Ucrania, en la que Lula se entrometió mucho. Entonces, formular una propuesta coherente y viable será un gran desafío, porque diversos agentes económicos y sociales no están de acuerdo con ciertas políticas. Aunque la agenda ambiental podría ser un área de convergencia, enfrenta resistencia de poderosos sectores del agronegocio en Brasil. Además, el gobierno está recomponiendo los cuadros ministeriales tras la disminución realizada durante el gobierno de Bolsonaro y, a nivel regional, Lula intentó retomar la integración, pero no hubo consensos, por ejemplo, entre el Mercosur y la Unión Europea. A pesar de las dificultades, yo siempre permaneceré optimista.
+Entrevista: Axel Schwarzfeld</t>
   </si>
   <si>
     <t>Candidatos con música para los oídos de la Sociedad Rural</t>
@@ -1219,9 +2948,6 @@
     <t>https://www.pagina12.com.ar/lbpupdates/571075</t>
   </si>
   <si>
-    <t>2023-07-25T15:15:20Z</t>
-  </si>
-  <si>
     <t>Música para los oídos de la Sociedad Rural</t>
   </si>
   <si>
@@ -1231,7 +2957,32 @@
     <t>https://www.pagina12.com.ar/571002-musica-para-los-oidos-de-la-sociedad-rural</t>
   </si>
   <si>
-    <t>2023-07-25T03:01:00Z</t>
+    <t xml:space="preserve">Título: Música para los oídos de la Sociedad Rural
+Chapeau: Promesas para los empresarios ruralistas de los candidatos de la oposición: eliminar retenciones, ajustar el gasto y abrir la economía
+Subtítulo: En el marco de la Exposición Rural, Bullrich, Larreta, Schiaretti y Milei revelaron detalles de sus programas económicos por primera vez desde que se lanzó formalmente la campaña. Hablaron explícitamente de un ajuste y de unificar el tipo de cambio, y se comprometieron a garantizar la rentabilidad del sector. Los candidatos de Juntos por el Cambio se cruzaron por los tiempos y las formas para salir del cepo, mientras que el ultraderechista Milei insistió con la dolarización.
+Editoria: El País
+Tags: Sociedad Rural Argentina, Horacio Rodríguez Larreta, Patricia Bullrich, Javier Milei, Juan Schiaretti, Elecciones Argentina 2023, printed-edition, sociedad-rural-argentina, horacio-rodriguez-larreta, patricia-bullrich, javier-milei, juan-schiaretti, elecciones-argentina-2023, diario
+URL: https://www.pagina12.com.ar/571002-musica-para-los-oidos-de-la-sociedad-rural/
+Notícia completa (19 blocos):
+Los principales candidatos de la oposición se animaron a explicitar, por primera vez desde que empezó formalmente la campaña, qué tienen pensado hacer en materia económica en caso de llegar a la Rosada. Tuvo que convocarlos la Sociedad Rural Argentina, en el marco de la Expo Rural 2023, para que tal cosa sucediera. Horacio Rodríguez Larreta y Patricia Bullrich, por Juntos por el Cambio; Juan Schiaretti, de Hacemos por Nuestro País, y Javier Milei, de La Libertad Avanza, disertaron frente a los empresarios que concentran buena parte parte de los dólares del agronegocio y desplegaron su menú de políticas para el sector. Los discursos, también, dejaron varias pistas sobre el trazo grueso de sus planes de gobierno. Hubo coincidencias –eliminar o bajar al mínimo las retenciones, abrir la economía, recortar el gasto público, suprimir "el cepo" y unificar el tipo de cambio, entre otras–, aunque afloraron matices –y en algunos casos diferencias, como entre Larreta y Bullrich– sobre las formas y los tiempos para hacerlo.
+Las propuestas de los opositores sonaron como música para los oídos del auditorio del Salón Rojo del predio de Palermo: todos hablaron de la necesidad de ampliar la rentabilidad del campo, de reducir impuestos y controles y de la apertura “a los mercados”. Muchos, incluso, habían tomado nota del pliego con “Lineamientos Generales para el Desarrollo de Políticas Públicas” que la SRA le había entregado a los candidatos en abril de este año, y que contiene nueve puntos que los chacareros esperan que lleve adelante el próximo gobierno, desde “una política fiscal que devuelva competitividad”, hasta “un programa para estabilizar la macroeconomía” e “instituciones que garanticen las reglas de juego”.
+El más aplicado en seguir esa hoja de ruta fue Rodríguez Larreta, aunque desde el bullrichismo remarcan que la exministra arrasó a la hora del aplausómetro, con un discurso más duro y más en sintonía con el adutiorio. Ninguno de los dos pudo evitar volver a chicanearse, aunque no hubo nada parecido a un debate mano a mano. Bullrich prometió “eliminar el cepo desde el primer día, de forma inmediata", y dijo tener “el coraje necesario” para hacerlo; mientras que el Jefe de Gobierno porteño –que habló antes– ya se había atajado al respecto, con el planteo que la idea "no es seria”, porque “no va a haber dólares en el Banco Central”.
+[H2] Bullrich, de local
+La exministra de Mauricio Macri y Fernando De La Rúa llegó a la Rural acompañada por el diputado nacional Luciano Laspina (su principal asesor económico), el presidente de la UCR bonaerense, Maximiliano Abad, y el legislador porteño Juan Pablo Arenaza (jefe de campaña). Ni bien se subió al atril, recordó su lazo con la exposición rural, “a la que vengo prácticamente desde que nací y que conozco profundamente”, dijo. Desde su entorno aseguraron que “se sintió como en familia, ante un público cautivo, de gente con varios apellidos”, en referencia al linaje de los Luro Pueyrredón.
+En confianza, Bullrich dijo que está “trabajando con una cantidad de dólares que todavía no podemos decir de dónde van a salir, pero que estamos negociando a nivel internacional” lo que permitiría blindar al Banco Central “para salir del cepo lo antes posible, de manera urgente, el primer día” de su hipotético gobierno. Para eso, dijo tener “el coraje necesario”, en una chicana típica de su campaña contra su rival interno.
+“Vamos a mandar una ley el primer día para que nadie pueda limitar las exportaciones, para que ningún burócrata de bajo nivel pueda decidir hacer eso”, siguió, en uno de los tramos más festejados por el auditorio. El otro fue cuando prometió “desarmar el estado autoritario que le da órdenes al campo de lo que tiene que hacer” y “eliminar los trámites insoportables”, entre ellos, incluso, los que les exige la Aduana.
+En el bullrichismo sostienen que salieron ganadores en el contrapunto con Larreta. "Es un público que también podría votarlo, pero no lo aplaudieron casi nada. Se nota que él tiene acuerdos con todo el mundo y entonces no puede ser sincero como Patricia, que dice lo que siente y hace un diferencial", se explayaron.
+[H2] Larreta y la gestión
+El eje del discurso del jefe de Gobierno –quien llegó junto al ministro de Economía de Macri, Alfonso Prat Gay, y a otro especialista en la materia, José Luis Espert– fue diferenciarse de Bullrich haciendo hincapié en su gestión. Su muletilla fue “como ya lo hicimos en la Ciudad”, que repitió a la hora de graficar cómo bajar impuestos y ajustar el gasto sin recortar la obra pública.
+“Tenemos que ir a un tipo de cambio único”, propuso y aprovechó el malestar de los empresarios del agro con las medidas que había anunciado Sergio Massa horas antes: “Basta de parches”, lo criticó. También prometió “apertura de mercados” y llegar al “déficit fiscal cero el primer año” de un hipotético gobierno suyo.
+También arremetió contra el planteo de Bullrich de eliminar el cepo el primer día. “No es un plan serio, el que les diga eso, miente”, dijo. En la misma línea, apuntó a “ir bajando las retenciones paulatinamente”. También prometió “aplicar el bisturí” sobre el presupuesto. Sobre el final, dijo que “el mercado de la carne es el más intervenido del país”, en una búsqueda por congraciarse con el presidente de la SRA, Nicolás Pino, que proviene precisamente de ese sector.
+[H2] Schiaretti, el anti-K
+El gobernador de Córdoba también prometió eliminar retenciones, y aseguró que el costo fiscal lo recuperaría eliminando subsidios. “Es mentira que no se puede por el costo fiscal que implicaría la medida, como dicen algunos. Lo que el Estado recauda por retenciones equivale a lo que gasta en subsidios, así que ahí tenemos una de las claves”, apuntó, aunque matizó con que “no es necesario un ajuste salvaje” a partir del 10 de diciembre.
+Luego se dedicó a criticar al kirchnerismo y recordar el conflicto por la 125. “El Kirchnerismo agrede a quien no le responde, eso hizo con el campo y con la prensa y, ahora con la Corte.. Reitero mi más enérgico rechazo al pretendido juicio político”, dijo.
+[H2] Milei, contra el “papa Estado”
+El economista Milei se presentó de la mano de su compañera de fórmula, la ultraderechista Victoria Villarruel, y de su hermana, Karina Milei. Como es habitual, apeló a los adjetivos llamativos, como cuando se refirió al cepo como “inmoral”. “Consideramos que el campo argentino es el mejor del mundo. Trabajaremos para devolverle la rentabilidad y la vitalidad que se le ha quitado en los últimos años chupándole la sangre”, dijo.
+Milei insistió con su plan de dolarización, al que le agregó el detalle de que podría llevarlo a cabo entre "9 y 24 meses". También habló de una "unificación cambiaria de facto" y de la “idea nefasta de la justicia social”.
+Sobre el final, el autodenominado libertario sostuvo que irá “contra todas las partidas donde roba la política” y, en ese mercado, que va a “eliminar la obra pública”. “La va a hacer el sector privado, que va a tener rentabilidad”, agregó y apuntó contra los contratistas: “ustedes son grandes y no necesitan de un papá Estado”. Recibió aplausos encendidos.</t>
   </si>
   <si>
     <t>Matías Ferrari</t>
@@ -1243,7 +2994,24 @@
     <t>https://www.pagina12.com.ar/569502-el-hombre-de-la-silla-de-ruedas</t>
   </si>
   <si>
-    <t>2023-07-20T03:01:00Z</t>
+    <t xml:space="preserve">Título: El hombre de la silla de ruedas
+Subtítulo: Germán Abdala nació el 12 de febrero de 1955, en Santa Teresita y falleció el 13 de julio de 1993 en un hospital porteño.
+Editoria: Buenos Aires|12
+Tags: Opinión, printed-edition, opinion
+URL: https://www.pagina12.com.ar/569502-el-hombre-de-la-silla-de-ruedas/
+Notícia completa (12 blocos):
+Germán Abdala nació el 12 de febrero de 1955, en Santa Teresita y falleció el 13 de julio de 1993 en un hospital porteño. Su familia decidió que sus restos fueron lanzados al mar que amó, desde la playa de la ciudad que lo viera nacer. Fue dirigente de la Asociación Trabajadores del Estado, desde el 6 de noviembre de 1984 hasta su deceso, como así también uno de los fundadores de la CTA. Fue elegido diputado nacional en 1989, cargo que también ejerció hasta 1993. Pero con decir esto nada se diría.
+La vigencia y actualidad de Germán tampoco son hallables en la estatuaria ni en los monumentos autorreferenciales de quienes, so pretexto de hablar sobre él, te cuentan cómo lo conocieron, dónde estaban y por qué estaban ahí, justo en ese momento trascendental de la Historia en el que Germán se topó con ellos.
+Lo cierto es que hay un Abdala que, a lo largo de estos treinta años, ha podido eludir la trampa de los panteones, la rigidez del bronce de las placas y la frialdad de los mármoles. Se trata de aquel dirigente sindical que en los albores de la restauración democrática consiguió entender, antes que nadie, que no bastaría con tener un sindicato democrático, combativo y memorioso de las luchas que lo precedían para poder defender los intereses de las y los trabajadores afiliados. Su concepción de la política arrancaba desde la asimilación de la derrota sufrida por el campo popular a partir de la dictadura cívico militar y eclesiástica y, precisamente por eso, hacía de la construcción colectiva una condición inexcusable para establecer el sentido de las alianzas.
+Es a partir de ese principio que hoy es posible entender el abanico de representaciones políticas que logró constituir en ATE Capital para su primer mandato como secretario general. No le importó que a su izquierda confluyeran militantes que provenían de la lucha armada de los años 70 y que a su derecha se formaran los que provenían de un peronismo tradicional; para Germán lo decisivo había sido que cada uno manifestara su voluntad de arrancarle el gremio a la burocracia prodictatorial que encabezaba Horvarth. La determinación de unir en un colectivo a todas esas voluntades dispersas y carentes de conducción política hizo que él, mucho antes del triunfo en las decisivas elecciones del 6 de noviembre de 1984, se convirtiera en un dirigente natural de los estatales porteños.
+Los conflictos laborales que fueron escalonándose durante el gobierno de Raúl Alfonsín y la seguidilla de los trece paros nacionales convocados por la CGT dirigida por Saúl Ubaldini, lo llevaron a la conclusión de que esas luchas no alcanzarían sus objetivos, ni frenarían la hiperinflación desatada por los grandes grupos económicos, si el movimiento obrero no atinaba a entender que no debía resignar su representación política a manos de los profesionales de la rosca. Fue por eso que en 1988, cuando ATE aún era un gremio con poco más de 60.000 afiliados en todo el país, Germán se alineó en la interna del PJ con el sector de la Renovación que encabezaba Antonio Cafiero quien, al cabo, fue derrotado por Carlos Menem. Pero esa decisión temprana, tomada antes de que finalizara su primer mandato como secretario general de ATE Capital, lo situó como candidato a diputado nacional.
+Tenía apenas 34 años cuando asumió la banca y ya contaba con la certeza de que Menem traicionaría los postulados de la campaña electoral. Esta convicción lo proyectó más allá de las fronteras del recinto parlamentario porque desde un primer momento no hubo conflicto o reclamo laboral que no lo viera acudir en su condición de legislador. Los principales debates en la Cámara también lo contaron como protagonista. La suya fue una banca al servicio de la clase trabajadora y toda su actividad parlamentaria giró en torno al protagonismo colectivo antes que a la figuración personal. Dijo sin titubear: “La política del imperio para nuestro país, no solo fue matarnos a los mejores compañeros, no solo fue perseguir a los mejores compañeros, intervenirnos las organizaciones sindicales, prohibir la política, saquear el país con la deuda externa, sino que fue cambiar las conductas humanas, quebrarnos a nosotros en eso tan íntimo como es la voluntad de lo colectivo.” Para Germán Abdala se había pasado “del decir si nos juntamos solidaria y colectivamente, vamos a ser más que la voluntad individual” a esto otro de “hacer valer el reino éste de si cuerpeo, le meto el codazo en la cara al otro, hago mérito, delato, hago buena letra, no transgredo, me mimetizo dentro de las posibilidades del sistema, a lo mejor tengo la suerte de ser uno de los 8 millones de argentinos que se salve.”
+En poco tiempo confrontó con el menemato y creó y lideró el Grupo de los Ocho, pero supo comprender que aquello no bastaría si no se era capaz de organizar al movimiento obrero sobre un cimiento antagónico al del colaboracionismo sindical que primaba en la fracción antiubaldinista de la CGT: "Mi visión hoy es que el Grupo de los Ocho y el peronismo disidente han cumplido una etapa, de la cual queda como autocrítica que no fuimos capaces de construir una oposición al modelo liberal menemista desde adentro. Nosotros quisimos ser la conducción del verdadero peronismo, pero en esto hay que ser sinceros: hemos perdido (...) Hay que construir una nueva alternativa popular en la Argentina que sintetice a todos los sectores. Un nuevo partido o frente que rompa con el bipartidismo". Allí, en esas definiciones, anidaban tanto la inminente fundación de la CTA, como los fundamentos estratégicos para la creación de una herramienta política que sacara a la democracia de sus cepos burgueses.
+Está claro que Germán no se refería a ninguna clase de tercer movimiento histórico, esa quimera del alfonsinismo que se desintegró con la hiperinflación y las elecciones anticipadas; tampoco aludía al experimento progresista que, tras su muerte en 1993, sería encabezado por Carlos Chacho Álvarez y que terminaría como aliado de los radicales en la Alianza con Fernando de la Rúa y Domingo Cavallo. Por el contrario, la idea de romper con el bipartidismo remitía a un tipo de representación y práctica política que ensancharan y profundizasen los estrechos límites de la democracia formal.
+Nadie mejor que Abdala para explicar eso: “Es el principio de algo que tiene que lograr salir de la resistencia para poder plantear a esta sociedad, que no sólo está el discurso de la derecha para evitar la crisis política, sino que también los sectores populares tenemos una propuesta, un planteo para explicar por qué hoy las dirigencias políticas, sociales, forman parte todas del mismo esquema de prebenda y prostitución que han hecho que el conjunto de las masas dejen de creer que es posible un país distinto.” Cuando uno ve los increíbles porcentajes del abstencionismo que se registran en las actuales PASO, a treinta años de la partida de Germán, no puede menos que afirmar que sus palabras de entonces tienen una vigencia dramática.
+“Los restaurantes están llenos, los cines están llenos, pero cuando uno empieza a discutir en cada una de las provincias las realidades de las economías regionales, la integración económica, vivimos en un mundo feudal. Vivimos en un mundo donde todo está por hacerse. Toda la gente nos dice: “¿Por qué no se dan créditos a la pequeña y mediana industria en vez de estar favoreciendo a Bunge y Born para que exporte 7000 millones de granos?”. Aquí uno piensa en el fiasco de Vicentín, en las ganancias fabulosas de los bancos mientras cada vez más personas deben dormir en la calle, en las facilidades cambiarias para el agronegocio mientras se aduce la falta de fondos para otorgarles a los estatales un bono compensatorio de todo lo que han perdido en este tiempo.
+El Abdala final, el de Parque Sarmiento, casi sin fuerzas ni voz porque la enfermedad lo ha consumido y ya ni caminar puede, lanza su último desafío histórico en aquel noviembre de 1992: “No me va a doblegar el cáncer, pero me mataría, eso sí, la tristeza, si no logramos dar forma organizativa y presencia a este maravilloso fervor militante.” Aquel Abdala no hablaba de colonizar el aparato del Estado con adeptos obedientes y ubicuos; tampoco creía que la militancia pasaba por escalar cargos, ni sumar minutos en las pantallas televisivas, ni que la hegemonía política era tan solo una sumatoria de los propios ni, mucho menos, que había que fundar un partidito de morondonga.
+Germán, aquel último que habla para el futuro desde la fragilidad de su figura en la silla de ruedas, es más vigente que nunca porque la estrategia de poder popular que él supo diseñar está cada vez más lejos de ser refutada por nadie. Y menos hoy, a treinta años de su muerte.</t>
   </si>
   <si>
     <t>Carlos Girotti</t>
@@ -1258,7 +3026,23 @@
     <t>https://www.pagina12.com.ar/564911-juntos-por-el-cambio-no-tiene-paz</t>
   </si>
   <si>
-    <t>2023-07-04T21:47:26Z</t>
+    <t xml:space="preserve">Título: Juntos por el Cambio no tiene paz
+Chapeau: De acusaciones por complicidad con el narcotráfico a cruces por reelecciones
+Subtítulo: Carolina Losada, precandidata a gobernadora por Santa Fe, está decidida a dinamitar la interna que organizó el macrismo en la provincia litoraleña. Dijo que si pierde no apoyará a Maximiliano Pullaro, a quien le volvió a recordar que tiene "muertos en el placard". En Formosa, el clima también está picado.
+Editoria: El País
+Tags: Santa Fe, santa-fe, diario
+URL: https://www.pagina12.com.ar/564911-juntos-por-el-cambio-no-tiene-paz/
+Notícia completa (10 blocos):
+La precandidata a gobernadora por Santa Fe y senadora nacional, Carolina Losada, continúa dinamitando la interna de Juntos por el Cambio a nivel provincial y nacional. A doce días de las PASO en Santa Fe, Losada volvió a cargar contra el precandidato a gobernador por el radicalismo en la interna de "Unidos para Cambiar Santa Fe", el ex ministro de Seguridad Maximiliano Pullaro, a quien le volvió a recordar que tiene "muertos en el placard" de su gestión respecto de la relación entre la policía provincial y el narcotráfico. Además, la pareja del senador Luis Naidenoff, se metió en la interna de Formosa para apuntar contra candidatos a legisladores nacionales.
+Losada mantiene una disputa descarnada con Pullaro por los votos del próximo 16 de julio, cuando se definirán las candidaturas para las elecciones generales del 10 de septiembre. "No lo tomo como una pelea, sino como alguien que viene y recuerda cuál es la situación y la verdad", consideró la senadora nacional ante de volver a atacar a Pullaro por "los vínculos que hablo son conocidos, su mano derecha es tan peligroso que está preso".
+La precandidata por el PRO en Santa Fe -aunque vive en Nordelta- viene desde hace semanas apuntando sobre el "muerto en el placard" de Pullaro. Se refiere al ex jefe antinarcóticos Alejandro Druetta, quien fue designado por el precandidato del radicalismo durante su gestión como ministro de Seguridad en el gobierno de Miguel Lifschitz. Druetta fue condenado a 10 años de prisión por ser miembro de una banda narco que comerciaba estupefacientes en el sur de la provincia de Santa Fe.
+"Los audios donde corrompe a la policía en primera persona son conocidos de cuando él era ministro", recordó Losada para despegarse de las críticas por fomentar la interna santafecina. En ese tono, la senadora reiteró que no trabajará con los precandidatos de Pullaro en caso de que ella gane la interna. "No voy a convocar a ninguna persona que haya tenido o tenga vínculos con el narcotráfico", apuntó en diálogo con Radio Continental.
+"Voy a convocar a todo el sector, en mi Gobierno quiero ir hasta el hueso contra el narcotráfico y hay que tener las manos limpias y no tener muertos en el placard", sentenció Losada. La lista de Pullaro es respaldada a nivel nacional por el senador radical Martín Losteau, quien va como precandidato a jefe de gobierno porteño. Mientras que Losada es respaldada por Patricia Bullrich, Horacio Rodríguez Larreta y Elisa Carrió. La otra precandidata a gobernadora dentro de espacio cambiemita es la socialista Mónica Fein.
+La senadora ya había declarado no tener ninguna relación ni "ética ni moral" con Pullaro y Losteau, acusando al senador por la recordada resolución 125, que buscó crear retenciones móviles para las exportaciones del agronegocio.
+[H2] De Santa Fe a Formosa
+No conforme con mantener encendida la interna provincial, la senadora también salió al cruce de la decisión de los referentes formoseños de Juntos por el Cambio Fernando Carbajal, Gabriela Neme y Francisco Paoltroni, quienes en el cierre de listas nacionales del 24 de junio se anotaron para competir en la lista de diputados por Formosa, cuando ese domingo 25 también competían a nivel provincial. De hecho, Carbajal fue el candidato a gobernador que perdió frente a otra arrasadora elección del gobernador Gildo Insfrán.
+"De alguna forma es un fraude a la gente. Tienen los peores vicios de la casta", lanzó la ex conductora de televisión y pareja del senador nacional formoseño Luis Naidenoff. Neme, surgida del peronismo, apeló a las redes sociales para responder los cuestionamientos: "No, Carolina, te equivocás. El fraude al electorado viene de la mano de los que se abusan de la re-re-reeleción y se perpetúan en las bancas, igual que Gildo Insfrán".
+Con esas palabras, Neme reveló otra interna entre su sector y el de la pareja de Losada. "Como el caso de la casa de Luis Naidenoff y Ricardo Buryaile, más de 20 años en las bancas. Nuestra lucha firme, decidida y comprometida es contra la reelección", dejó claro en otro tuit.</t>
   </si>
   <si>
     <t>Bolsonaro fue inhabilitado electoralmente hasta 2030</t>
@@ -1270,7 +3054,33 @@
     <t>https://www.pagina12.com.ar/563852-bolsonaro-fue-inhabilitado-electoralmente-hasta-2030</t>
   </si>
   <si>
-    <t>2023-07-01T03:01:00Z</t>
+    <t xml:space="preserve">Título: Bolsonaro fue inhabilitado electoralmente hasta 2030
+Chapeau: La justicia electoral de Brasil dictaminó que es culpable de difundir mentiras sobre las elecciones
+Subtítulo: El ministro de Justicia, Flávio Dino, dijo que el gobierno le exigirá al expresidente una indemnización "por los daños que le causó al Poder Judicial y a la propia sociedad".
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Brasil, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/563852-bolsonaro-fue-inhabilitado-electoralmente-hasta-2030/
+Notícia completa (20 blocos):
+La justicia electoral de Brasil determinó por mayoría inhabilitar al expresidente Jair Bolsonaro para presentarse a cargos públicos hasta 2030, al declararlo culpable de "abusos de poder" por diseminar mentiras y sospechas infundadas sobre el sistema de comicios brasileño ante embajadores de países extranjeros.
+Con esta decisión, adoptada por cinco votos frente a dos en el Tribunal Superior Electoral (TSE), el líder de la ultraderecha, de 68 años, no podrá concurrir a cargos electivos ni ejercer puestos en la administración pública durante un plazo de ocho años, contados a partir de octubre de 2022, cuando se celebraron los comicios en los que le ganó Luiz Inácio Lula da Silva.
+El presidente del TSE, el juez Alexandre de Moraes, profirió el último voto. Según él, la sentencia es una respuesta al "degradante populismo nacido en los discursos de odio y antidemocráticos, que propagan una asquerosa desinformación no sólo en Brasil, sino en todo el mundo, con el único objetivo de engañar a los electores". De Moraes había sido objeto de virulentos y permanentes ataques del bolsonarismo antes y durante la campaña electoral, en la que fue acusado, sin prueba alguna, de maniobrar para favorecer a Lula.
+Tras conocerse la condena, el líder ultraderechista tachó el fallo de "puñalada en la espalda" y señaló que apelará ante la corte suprema. "No estoy muerto, vamos a seguir trabajando. Mi apelación será ante el Supremo Tribunal Federal", afirmó Bolsonaro a periodistas en Belo Horizonte, al sureste de Minas Gerais, estimando que con la decisión judicial, Brasil se encamina "hacia una dictadura". También está esperanzado en la posibilidad ya anticipada por algunos de sus correligionarios políticos de que el Congreso apruebe un proyecto de ley amnistiando a los condenados por delitos electorales en 2022, que lo beneficiaría y lo volvería a habilitar políticamente.
+[H2] Es un "gran dia"
+El ministro de Justicia de Brasil, Flávio Dino, aseguró que el gobierno le exigirá a Bolsonaro una indemnización: "La decisión del tribunal prueba que fueron perpetrados ataques abusivos al sistema de justicia y al orden jurídico. Por ese motivo, enviaré una petición a la Abogacía General del Gobierno para que analice la posibilidad de exigirle una indemnización por los daños que le causó al Poder Judicial y a la propia sociedad", indicó.
+El ministro de Relaciones Institucionales, Alexandre Padilha, afirmó que la condena contra el exmandatario fue el primer paso "hacia la rendición de cuentas por los crímenes en serie cometidos y la organización criminal que encabeza". Y añadió: "No se trata de festejar que Bolsonaro no pueda disputar las elecciones (presidenciales) de 2026, que es algo muy distante de nuestras preocupaciones. Se trata de dejar claro el papel del expresidente en los ataques a la democracia y en no aceptar el resultado de las urnas".
+Gleisi Hoffmann, presidenta del Partido de los Trabajadores (PT), consideró que la decisión de los magistrados "tiene una enorme forma didáctica y condena los métodos de la extrema derecha, la diseminación industrial de mentiras, amenazas a la democracia y el uso del poder público para perseguir adversarios y prevalecer en la disputa electoral". Para ella, se trata de un "gran día" --frase que usaba el exmandatario de ultraderecha para celebrar sus logros-- demostrando que "la defensa de la democracia y el enfrentamiento al fascismo permanecen en el orden del día" de la sociedad brasileña.
+[H2] La causa judicial
+El TSE estudió una demanda del Partido Democrático Laborista (PDT) contra Bolsonaro, quien en julio de 2022 organizó en el Palacio del Planalto una reunión con diplomáticos y embajadores extranjeros. De acuerdo con esta denuncia, el exmandatario utilizó el encuentro para difundir, sin pruebas, acusaciones sobre la fiabilidad de las elecciones de 2022.
+Ese hecho, según dice la sentencia, constituyó un "abuso de poder político, conductas vedadas y desorden informativo" y también un "uso indebido de predios públicos y medios de comunicación", pues Bolsonaro ordenó que la televisión pública transmitiera el evento. Es más, según dijeron algunos jueces, dicha situación pudo incitar el asalto a las sedes de los tres poderes el pasado 8 de enero, cuando una horda de bolsonaristas sembró el caos con la intención de llevar a las Fuerzas Armadas a derrocar a Lula.
+Entre los jueces que votaron en contra de la inhabilitación, estaba el juez Raul Araújo. Si bien reconoció que Bolsonaro difundió información falsa sobre el sistema electoral en aquella reunión con embajadores, consideró que no cumplía con "el requisito de gravedad suficiente". También defendió que se tomaron medidas suficientes para que esa reunión no tuviera repercusiones electorales, citando la retirada de la grabación de internet, además de desestimar el impacto que pudo haber tenido, porque eran argumentos ya conocidos por los seguidores del expresidente brasileño.
+[H2] El derrotero de Bolsonaro
+Conocido por su estilo provocador y divisivo que le hizo ganar el apodo de "Trump tropical", Bolsonaro irrumpió en el escenario nacional como candidato presidencial en 2018. Con un seductor discurso anticorrupción y de "outsider", cautivó durante la campaña a muchos brasileños, hartos de los partidos tradicionales salpicados por polémicas. Sobrevivió a un ataque con cuchillo perpetrado durante un acto electoral y eso solo hizo incrementar la fe de sus seguidores en su "Mesias", segundo nombre de Bolsonaro. Contó con el apoyo de los influyentes 'lobbies' de las armas, el agronegocio y el vasto electorado evangélico.
+Su presidencia se erosionó especialmente por su manejo de la pandemia del coronavirus, que en Brasil dejó 700.000 muertos, solo por debajo de Estados Unidos en números absolutos. El exmandatario restó importancia al covid-19, desafió los datos científicos para combatirlo, se burló del uso de mascarillas y advirtió que las vacunas podrían convertir a las personas en cocodrilo. A su vez, fue criticado internacionalmente por la deforestación de la Amazonía, que aumentó más del 70% durante su mandato respecto al promedio anual de la década anterior.
+Luego de perder por un estrecho margen las elecciones, Bolsonaro se negó a felicitar a su adversario y a admitir abiertamente su derrota. Cayó en un silencio inédito, incluso en sus redes sociales, donde había sido hiperactivo. Viajó a Estados Unidos dos días antes del fin de su mandato y no asistió a la toma de posesión de Lula el 1 de enero. Una semana después, miles de seguidores de Bolsonaro invadieron y vandalizaron el palacio presidencial, el Congreso y la sede de la corte suprema, en un intento fallido por derrocar a Lula.
+A su regreso a Brasil, el exmandatario enfrenta cinco procesos ante el máximo tribunal que podrían enviarlo a prisión. El más reciente investiga si instigó la asonada del 8 de enero. También es investigado por la policía y las autoridades tributarias por supuestamente haber intentado importar ilegalmente joyas valoradas en millones de dólares que él y su esposa, Michelle, recibieron de Arabia Saudita.
+[H2] Adiós a los derechos políticos
+Tras confirmarse la reciente condena, el exmandatario se convirtió en el tercer expresidente brasileño que es inhabilitado para disputar cargos electivos o ejercer cargos públicos desde el restablecimiento de la democracia, en 1985. El primero fue Fernando Collor, quien a principios de los años 90 fue acusado de participar en una trama corrupta, lo que desencadenó que el Congreso pusiera en marcha un juicio político con fines de destitución en su contra. En un contexto de grave crisis económica, Collor renunció a la presidencia con el objetivo de mantener sus derechos políticos. Pese a ello, el Senado aprobó su inhabilitación durante ocho años.
+El actual presidente, Lula da Silva, también había sido declarado inelegible, pero por un motivo distinto. En 2018, el dirigente progresista fue condenado en segunda instancia a 12 años y 1 mes de cárcel por un caso de corrupción. Esa sentencia se encuadró en la llamada "Ley de Ficha Limpia", que impide a condenados en segunda instancia concurrir a cargos electivos. Sin embargo, en 2021, la Corte Suprema anuló esa y otra condena por corrupción contra Lula, un fallo que le permitió recuperar sus derechos políticos y presentarse a las presidenciales de 2022 y ganarle a Bolsonaro.</t>
   </si>
   <si>
     <t>La muerte de Emmily Rodrigues: el empresario Sáenz Valiente quedó procesado por "homicidio culposo"</t>
@@ -1282,7 +3092,18 @@
     <t>https://www.pagina12.com.ar/563037-la-muerte-de-emmily-rodrigues-el-empresario-sanchez-valiente</t>
   </si>
   <si>
-    <t>2023-06-29T03:01:00Z</t>
+    <t xml:space="preserve">Título: La muerte de Emmily Rodrigues: el empresario Sáenz Valiente quedó procesado por "homicidio culposo"
+Chapeau: No deberá cumplir prisión preventiva pero sí usar tobillera electrónica
+Subtítulo: La resolución la Sala 6 de la Cámara del Crimen da por probado que Saénz Valiente estuvo involucrado en la muerte de Emmily, aunque quedó descartado el pedido de la querella, que solicitaba la carátula de femicidio o de homicidio con intención de ocultar un abuso sexual.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/563037-la-muerte-de-emmily-rodrigues-el-empresario-sanchez-valiente/
+Notícia completa (5 blocos):
+El empresario Francisco Sáenz Valiente quedó procesado por el “homicidio culposo” y la “facilitación de drogas” a Emmily Rodrigues, la modelo brasileña que hace casi tres meses murió tras caer del departamento del imputado. La Sala 6 de la Cámara del Crimen dispuso que Sáenz Valiente no cumpla prisión preventiva, pero sí la obligación de llevar una tobillera electrónica.
+La resolución la Sala 6 de la Cámara del Crimen, que elevó la calificación de la pena para el empresario del agronegocio y la minería, da por probado que Saénz Valiente estuvo involucrado en la muerte de Emmily, aunque quedó descartado el pedido de la querella, que solicitaba la carátula de femicidio o de homicidio con intención de ocultar un abuso sexual. La fiscalía también había solicitado otra calificación, la de “abandono de persona agravado por el resultado muerte”.
+Otro pedido de la querella y la fiscalía que fue rechazado por el tribunal fue el de la detención preventiva del empresario. Los camaristas Magdalena Laiño, Ricardo Matías Pinto e Ignacio Rodríguez Varela ordenaron que Sáenz Valiente lleve una tobillera con geolocalización, bajo el control de "Programa de Asistencia de Personas Bajo Vigilancia Electrónica", dependiente del Ministerio de Justicia.
+En otro de los puntos, los camaristas decidieron mantener las mismas medidas cautelares ya dictadas para Sáenz Valiente por el juez de la causa el 18 de abril. La prohibición de acercamiento a los familiares de la damnificada y a los testigos que declararon en la causa, prohibición de salida del país, la obligación de asistir cada 15 días a la sede del tribunal y fijar un nuevo lugar de residencia distinto a la casa donde ocurrió el hecho.La decisión de la Sala 6 de la Cámara del Crimen ocurre 24 horas después de que se conociera la incorporación de un peritaje clave a cargo de la Policía de la Ciudad en el que detectó sangre y semen en 25 muestras levantadas en preservativos, sábanas, acolchados y hasta en el corsé que usaba Emmily la noche en la que falleció al caer al vacío.
+El hecho ocurrió el 30 de marzo pasado, cuando luego de cenar en un restaurante de la Costanera norte y de pasar por un bar de Palermo, Emmily llegó a las 3.21 con dos amigas al departamento de Sáenz Valiente, en el sexto piso del edificio de Libertad 1542, en Retiro, donde ya se encontraba una cuarta mujer.Tras una madrugada de excesos con ingesta de alcohol, marihuana, cocaína y "tuci", Rodrigues cayó desnuda por una ventana al patio interno del pulmón del edificio, cuando en el departamento solo estaban Sáenz Valiente y una de sus amigas.Los estudios toxicológicos revelaron que, antes de caer al vacío, la modelo brasileña consumió alcohol (1.0 gramos en sangre fue el dosaje), cocaína, marihuana, ketamina y MDMA (uno de los componentes de la droga sintética "Tuci", la forma abreviada de llamar al "Tucibi" por la pronunciación en inglés de la sigla 2C-B, que es la mal denominada "cocaína rosa").A Sáenz Valiente lo comprometen una serie de mensajes de esa noche con su dealer y con dos de las mujeres que fueron a su casa, donde les decía que tenía "tuci, faso y coca" en su departamento.</t>
   </si>
   <si>
     <t>Elecciones Córdoba 2023: el mapa interactivo con los resultados</t>
@@ -1294,7 +3115,25 @@
     <t>https://www.pagina12.com.ar/562215-elecciones-cordoba-2023-el-mapa-interactivo-con-los-resultad</t>
   </si>
   <si>
-    <t>2023-06-26T13:48:21Z</t>
+    <t xml:space="preserve">Título: Elecciones Córdoba 2023: el mapa interactivo con los resultados
+Chapeau: Distrito por distrito, la pulseada entre Llaryora y Juez
+Subtítulo: El peronismo de Córdoba extendió en estas elecciones 2023 su hegemonía de 24 años en la provincia mediterránea por 57,209 votos de diferencia.
+Editoria: El País
+Tags: Córdoba, Elecciones Argentina 2023, cordoba, elecciones-argentina-2023, diario
+URL: https://www.pagina12.com.ar/562215-elecciones-cordoba-2023-el-mapa-interactivo-con-los-resultad/
+Notícia completa (12 blocos):
+El peronismo de Córdoba extendió en estas elecciones 2023 su hegemonía de 24 años en la provincia mediterránea por 57,209 votos de diferencia. Con el 94,9 por ciento de las mesas escrutadas, Martín Llaryora, candidato oficialista y actual intendente de Córdoba capital, logró imponerse en las elecciones provinciales para suceder al gobernador Juan Schiaretti, mientras que el senador Luis Juez (Juntos por el Cambio) se quedó, otra vez, sin poder acceder al "Panal", como se denomina la casa de gobierno cordobesa.
+[H3] Elecciones Córdoba 2023, minuto a minuto
+El mapa provincial se partió en dos. Llaryora con un 42,8% de los votos totales se impuso mayoritariamente en los departamentos del norte provincial, donde se concentra el polo turístico, las sierras y las producción de pequeña escala. Por su parte, Juez, que alcanzó un 39,8 por ciento de los votos, se impuso en el sur provincial, dominado por el agronegocio.
+El voto en blanco fue la tercera opción más elegida por los cordobeses con un 4,8%. La tercera fuerza política fue la de Encuentro Vecinal, que llevó como candidato a Aurelio García Elorrio (3%); aunque a nivel departamental el lugar en el podio se repartió entre La Libertad Avanza (2,5%), Frente de Izquierda (2,4%) y Creo en Córdoba de Todos (2,2%). La fuerza de la ultraderecha de Javier Milei volvió a hacer un pobre papel y sus mejores performance coincidieron con las de Juez, en el sur de la provincia.
+[H2] La distribución del voto en los departamentos cordobeses
+Los departamentos de centro provincial como Tercero Arriba (43,6% para Juez sobre un 40,7% de Llaryora) y Río Segundo (43,5% para Larryora sobre un 41% de Juez), podría decirse que funcionan como frontera: hacia el norte dominó Hacemos Unidos por Córdoba y hacia el sur Juntos por el Cambio. Con escasas excepciones.
+Juez logró imponerse en tres departamentos serranos: San Javier (42% sobre un 41,2% del oficialismo), Punilla (43,7% sobre 37,9%) y Totoral (39,6% sobre 37,1%). Mientras que Llaryora logró su única victoria en el sur provincial en el departamento de Roque Sáenz Peña (43,2% sobre 41,9%).
+En el inico del conteo, Juez comenzó ganando la elección y luego se revirtió por el orden de carga de los resultados. Desde el búnker de Juntos por el Cambio se quejaron porque se cargaban las urnas de la capital provincial, donde LLaryora jugaba de local.
+Pero la capital cordobesa es determinante en la elección, allí están un tercio de los votantes de la provincia. Son 1.130.587 electores sobre un total de 3.051.544. Y allí logró imponerse Llaryora con un 44,6% de los votos sobre el 37,2% de Juez. Así, el actual intendente revalidó su gestión y se quedó con un bastión clave para la victoria provincial.
+Alrededor de la capital provincial y hacia el sur también se encuentran los departamentos más densamente poblados, que los candidatos se los repartieron por igual: Colón, Santa María y Río Segundo fueron para el oficialismo, mientras que Punilla, Tercero Arriba y General San Martín quedaron en manos de Juez.
+Como si se tratara de un anticipo por osmosis de lo que sigue en el cronograma electoral, los departamentos donde los candidatos hicieron mejor elección fueron San Justo y Marcos Juárez, ambos limítrofes con la provincia de Santa Fe, que el próximo 16 de julio irá a las PASO.
+En San Justo, a la altura de Santa Fe capital, Llaryora se impuso con el 51,3 % de los votos sobre el 35,1% de Juez. Mientras que en Marcos Juárez, a la altura de Rosario, el candidato de Juntos por el Cambio ganó con el 48,5% de los votos sobre un 36,1% de Llaryora. En esos departamentos los terceros puestos fueron a contramano: La Libertad Avanza quedó en el podio donde ganó el peronismo cordobés y Creo en Córdoba de Todos lo hizo donde Juez arrasó.</t>
   </si>
   <si>
     <t>Rosalía y la tierra</t>
@@ -1303,7 +3142,24 @@
     <t>https://www.pagina12.com.ar/561287-rosalia-y-la-tierra</t>
   </si>
   <si>
-    <t>2023-06-23T17:59:55Z</t>
+    <t xml:space="preserve">Título: Rosalía y la tierra
+Subtítulo: Rosalía siembra, planta, cosecha, compra, vende, anda en el surco.
+Editoria: Buenos Aires|12
+Tags: Opinión, opinion
+URL: https://www.pagina12.com.ar/561287-rosalia-y-la-tierra/
+Notícia completa (12 blocos):
+Rosalía siembra, planta, cosecha, compra, vende, anda en el surco.
+Rosalía cría hijo e hija y además trabaja para la organización que fundó. Pero ahora no. En este mismo momento espera un café en un bar, después de la movilización apoyando a los jujeños que están siendo apresados, secuestrados, lastimados en el norte del país: “Finalmente el tema es siempre la tierra y el territorio. La tenencia. Y la explotación con lucro al que los originarios tienen derecho y se les niega, claro”.
+Rosalía Pellegrini vive y produce en las quintas del Parque Pereyra, a donde llegó “hace mas de diez años. Venía de una experiencia rural larga en San Vicente, una cooperativa. Llegamos al Parque Pereyra a vivir en un galpón prestado que compartíamos con lagartos, serpientes y una que otra alimaña” recuerda y sonríe sobre el recuerdo de la aventura que arrancó cuando su hijo Aluén tenía poco más de un año y Amanda todavía no había nacido.
+El café tarda en llegar y la calle es un desfile de gentes con banderas enrolladas ya en las cañas. Casi todas, menos alguna wiphala que aun ondea en las manos de alguien que no bajó la euforia, y Jujuy vuelve a la charla: ”El tema del territorio rural es claro: lo ocultan, te proponen no mirar esos lugares. Pensá que el noventa por ciento de la tierra en Argentina es rural, y el ochenta por ciento de la población es urbana, entonces los dueños de los grandes negociados, te proponen no mirar para ahí, para las tierras originarias, porque ahí están las ganancias, el agronegocio, la minería…entonces mientras no se mire, ellos saquean libremente y los pueblos quedan afuera. Cuando habitás el territorio desde la ruralidad, los intereses son el agua, el clima, las consecuencias positivas o negativas de lo que haces, y otros factores, porque eso te afecta de forma directa, y finalmente también está el derecho a la riqueza que genere ese territorio como una cuestión de soberanía. El colectivo y la organización son todo para lograrlo. Y esa es la cuestión en Jujuy; La idea del gobierno jujeño es retroceder en derechos para vender todo lo que hay en el campo, y hoy van contra leyes como la de reparación histórica, que se tomaron 10 años para reglamentar, pero ya está, existe el banco de tierras para agricultura familiar, pero pasan por encima de las leyes. Arrasan con violencia y se quedan con todo lo que de plata.”
+Rosalía habla sin pausa, marcando con el dedo un mapa imaginario sobre la mesa, esquivando los pocillos de café y los vasitos de agua que ya llegaron. Ahora se saca el gorro de lana, mira hacia adentro del bar, parece que pensó algo nuevo para decir y mientras revuelve el café, repite ”la cuestión es la tierra…” mientras aprieta los labios y asiente con la cabeza.
+Del galpón prestado en el Parque Pereyra pasó a construir una casa de madera “muy linda, donde nació Amanda. Ahí ya funcionaba la UTT (unión trabajadores y trabajadoras de la tierra) porque la idea siempre fue armar un espacio colectivo de arraigo con la tierra”. Las palabras comunidad y colectivo pueblan la voz de Rosalía todo el tiempo porque “mirá, esa casa tan hermosa que teníamos, un día de 2013 se incendió. El papá de los chicos había ido a repartir los bolsones de verduras y yo volvía de dejarlos en la escuela. Era de mañana y llegando veía humo y una compañera me dijo que se quemaba mi casa. No quedó nada de nada. Se había quemado todo: ropa, juguetes, zapatos, muebles, papeles. Quedamos literalmente con lo que teníamos puesto. Todo era humo y cenizas. Y ahí llegaron los compañeros a ayudar y compañeras de otra organización trajeron comida, ropa, mantas. Todo era el colectivo, y ellos mismos nos ayudaron a levantar otra casa, que construimos con los bloques de la bloquera donde trabajaba Darío Santillán, que también fue donación de ese colectivo. Ahí vivo, en una prueba tangible de la solidaridad, de la comunidad, de lo colectivo.”
+Rosalía ve pasar la gente de la marcha que se va desconcentrando. Mira atenta a cada uno que pasa. Seria, como si los estuviera contando. Tan concentrada que ni notó que el pocillo de café quedó a medio camino de su boca.
+En la mesa de al lado alguien dice algo a propósito del caos que provocaron “estos jujeños” pero tampoco los escuchó.
+Ahora su mirada vuelve y cuenta que el parque Pereyra Iraola es enorme, que es el lugar ideal para vivir y que “tiene unos caminitos naturales, raros, por donde voy recogiendo semillas con las que hago un vivero de árboles nativos. Ya tengo un vivero con mil plantines de bosque nativo, porque recuperar eso es importante. Sueño, sin ningún romanticismo, con llegar a reforestar con diez mil nativas mientras sigo haciendo huerta y armando ahora plantas aromáticas que son importantes para intercalar en los sembradíos de otros compañeros: se usan para combatir naturalmente plagas y pestes. En eso las compañeras que llegaron hace años del norte, son fundamentales. Ellas saben de esas plantas. Saben y enseñan, comparten. Tienen también enormes conocimientos de plantas medicinales, por ejemplo, y eso también trabajamos mucho”.
+En eso estaba una mañana de agosto de 2020: cosechando artemisas con su vecina, Carolina Rodríguez, sobre el surco y entierrada hasta el cuello, cuando recibió la noticia de que Lucía Correa -otra mujer de la organización- había sido asesinada de un balazo frente a su hijo: “ella iba a charlas sobre cuidados y prevención de femicidios, porque habíamos armado una red muy grande y ella iba, así que la noticia fue horrible. Fuimos, conectamos a la familia, nos ocupamos del entierro. Nosotras ya teníamos el trabajo comunitario de ver la cuestión de genero al interior de las comunidades rurales, pero es arduo que llegue, y en pandemia, que es como estábamos, fue mucho peor”.
+Rosalía, a los cuarenta años de su edad, amanece temprano: “a veces a las seis, otras a las ocho, depende de si los chicos están conmigo o con su papá, y en esta época ¡me levanto vestida hasta las orejas! Hace mucho frio, así que lo primero es encender la leña de la estufa y la cocina y recién de ahí, el primer mate de la mañana” y mientras amanece en su bosque, mira por la ventana crecer los duraznos, o el estado de las chivas en el corral, y decide -una vez más- que cree en la humanidad, en sus compañeras y compañeros de historia, como la del primer verdurazo del año 2015, o el segundo con la consiga “palo o lechuga” contra el gobierno de Macri y que fuera violentamente reprimido. Mientras amanece, cada día decide también que cree a pie juntillas que tanto en el Parque Pereyra como en Jujuy no se puede pensar la vida sin las comunidades rurales adentro, sin lo colectivo, y porfía en que la batalla es para que eso suceda con todos los derechos de sus habitantes como parte fundamental de un todo.
+Por eso dejó su quinta y fue con sus compañeras de Mujeres de la Tierra, a la marcha por Jujuy porque “es fácil y no hay ambigüedad posible: la tierra es nuestra.”</t>
   </si>
   <si>
     <t>Fabián Restivo</t>
@@ -1318,7 +3174,38 @@
     <t>https://www.pagina12.com.ar/559510-en-uruguay-tienen-que-tomar-mate-salado</t>
   </si>
   <si>
-    <t>2023-06-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: En Uruguay tienen que tomar mate salado
+Chapeau: Por la sequía de tres años, las fuentes de agua potable se están secando
+Subtítulo: En la canilla el líquido sale con muchos minerales: el río Santa Lucía, su principal fuente, está muy bajo. “No es sequía, es saqueo”, denuncian las ONG.
+Editoria: Sociedad
+Tags: Uruguay, Montevideo, Calentamiento global, Sequía, printed-edition, calentamiento-global, sequia, diario
+URL: https://www.pagina12.com.ar/559510-en-uruguay-tienen-que-tomar-mate-salado/
+Notícia completa (25 blocos):
+Página/12 en Uruguay
+Desde Montevideo
+La frase más famosa de Carlitos Balá se está reescribiendo en versión uruguaya, como si fuera el preludio de una pesadilla. ¿Qué gusto tiene el agua? En Montevideo, la respuesta llega al unísono de niñas, vendedores ambulantes, artesanas, peluqueros y jubiladas: ¡Salada!
+En 2004 Uruguay incorporó a su carta magna un artículo que establece que el agua es un recurso natural esencial para la vida. Esta reforma constitucional, votada por el 64 por ciento de los ciudadanos, convirtió al país en el primero del mundo en declarar el acceso al agua como derecho humano. Casi veinte años después, la zona donde habita el 60 por ciento de la población del país podría quedarse sin agua dulce a fines de junio, según la estimación de Obras Sanitarias del Estado (OSE).
+La vida cotidiana está trastornada porque el agua potable ya no se puede utilizar para el mate ni el café. Tomar mate salado es una afrenta al abolengo matero. Comprar el agua embotellada es un gasto que excluye a las familias de menores recursos. El agua mineral, denuncia una artesana, está también “sucia” y le quedan restos de salitre en el termo. “No es sequía, es saqueo”, manifiestan los movimientos ambientalistas.
+Desde principios de mayo, el agua está en boca de todos porque sale más salada de las canillas. El agua de OSE (Obras Sanitarias del Estado), la empresa estatal uruguaya, proviene de fuentes superficiales del río Santa Lucía y la represa de Paso Severino, la principal reserva de agua dulce. La explicación oficial es que el caudal del río ha disminuido como consecuencia de la sequía que afecta a la región desde hace tres años. De los 67 millones de metros cúbicos de agua que puede albergar, actualmente tiene 3,7 millones, según informó OSE.
+El gobierno de Luis Lacalle Pou tomó recursos hídricos del Río de la Plata, más salinizado por las corrientes del océano que recibe. OSE solicitó al Ministerio de Salud Pública que permitiera aumentar los niveles de sodio y de cloro, que pasaaron de 200 a 440 miligramos y 700 miligramos por litro respectivamente. La OMS recomienda que el umbral de sodio sea un máximo de 200 mg. En Uruguay ese umbral se duplicó.
+[H2] “Nos roban el agua dulce”
+El barrio Sur parece una Londres en miniatura. Martín, vendedor de frutas y verduras de un puesto de la feria popular de la calle Julio Herrera y Obes, gambetea la neblina del viernes con mucho ingenio. “Vamos que el dinero no es todo, pero cómo ayuda cuando hay”, exclama e invita a comprar dos lechugas por 50 pesos uruguayos (300 pesos argentinos al cambio oficial, 650 pesos al cambio paralelo). “Elija y agarre”, “¡Vamos, arriba la celeste!”, “¡Vamos, arriba los gurises!”, arenga este vendedor carismático con un aire de familia a Ragnar, el personaje de la serie Vikingos. “El agua salada está rompiendo los termofones y calefones; es complicado el tema”, se queja. Micaela, de 12 años, compra frutillas junto con su hermana Martina, de 8 años. “Tiran cosas al agua y la contaminan; por eso está salada”, dice Martina. “Antes usábamos el agua de la canilla para hacer el mate, ahora no podemos”, confirma Micaela el cambio de hábito.
+“Salus, un agua con leyenda propia”, se lee en la etiqueta de uno de los bidones de 6,25 litros que en este supermercado sobre la calle Maldonado cuesta 129 pesos uruguayos. Un cartel informa que “la compra de bidones y botellas es solo para consumo familiar” y que está permitido hasta tres bidones por persona. Una señora empuja el changuito con los tres bidones autorizados rumbo a una de las cajas.
+Mirta, jubilada con gorrito de lana violeta y ojazos celestes, compró dos packs de cuatro botellas de agua Vitale de 1,75 litros (138 pesos uruguayos cada pack). Habla del problema del agua con una amabilidad que se desdibuja por la rabia. “Al gobierno le importa satisfacer a las empresas extranjeras y que la población se joda. Dan agua para UPM (la empresa finlandesa que se dedica a la fabricación de pulpa de celulosa, papel y madera), agua para todas las pasteras habidas y por haber, por eso pretenden sacar agua del Acuífero Guaraní en tambores”, describe Mirta. “Me duele, me irrita, porque nuestro país siempre tuvo agua dulce. Y ahora nos roban hasta el agua; es la corrupción más absoluta que no pensé que llegaría a pasar con esta magnitud”, agrega y señala que el principal trastorno en la vida cotidiana tiene que ver con lo económico, el gasto extra que significa comprar bidones o botellas. Hasta sus gatos toman agua mineral para evitar que tengan consecuencias en la salud.
+[H2] Las aguas bajan turbias
+Marcela, artesana que tiene su puesto con aros, anillos y pulseras que ella diseña con piedras y acero sobre la peatonal Sarandí, en Ciudad Vieja, cuenta que toma agua embotellada, especialmente para preparar el mate. “Después que hiervo el agua de bidón noto que está super manchada, me deja la jarra llena de salitre”, revela para informar que tampoco resulta ciento por ciento confiable el agua de las distintas marcas que va comprando en la UAM (Unidad Agroalimentaria Metropolitana), un lugar de ventas al por mayor, similar al Mercado Central de Buenos Aires. Compró cuatro bidones de 10 litros a 150 pesos uruguayos cada bidón (1.950 pesos argentinos). “En casa tomamos mucho mate”, resume lo que viven la mayoría de las familias. “El agua mineral está también sucia, no sé si tan mal como la de la canilla, pero limpia no está”.
+A metros de Marcela, Damián, vendedor de libros usados y discos, toma mate “con agua de la canilla”, subraya con un tono desafiante. El agua “no está tan salada” para Damián, que considera que se está “exagerando”, según la perspectiva de este hombre que toma entre dos y tres termos de mate por día. “El agua es cierto que está más salada, pero el problema no es para nosotros solos, es para todo el mundo. Que nos toque después de tantos años... ¡qué se le va hacer! No somos el paraíso”, suelta, mate en mano, este vendedor que trabaja en la peatonal Sarandí de siete de la mañana a seis de la tarde. “La venta está horrible”, se queja y afirma que hay “mucha pobreza” en Montevideo. “No vivimos, sobrevivimos”, aclara y regresa al tema del agua. “Es el cambio climático; que llueva o no llueva, nosotros no mandamos llover. Era obvio que un día iba a llegar”.
+El agua salada llega hasta las peluquerías. Los cabellos de las damas y caballeros se estremecen. La sal seca el pelo y puede afectar al color de las tinturas. En la peluquería “Enrique”, sobre la calle Convención, a metros de la 18 de julio, Enrique confiesa que como él usa productos de una “excelente” línea, libre de sulfatos y parabenos, está a salvo de que el daño sea mayor. Una clienta, que eligió el sábado a la tarde para hacerse el color y cortarse el pelo, está esperando y leyendo algo en su teléfono celular. Desde hace un mes, cuando empezaron los problemas con el agua, percibe que sus clientas, que evidentemente “no se duchan con agua mineral”, tienen los cabellos más deshidratados y perdieron “suavidad y brillo”.
+“Los termofones o calefones están teniendo problemas de oxidación y están acumulando sales en los metales”, revela Luis Aubriot, doctor en Ciencias Biológicas e integrante del Instituto de Ecología y Ciencias Ambientales de la Facultad de Ciencias de la Universidad de la República. “Montevideo tiene una red de distribución de agua por cañerías muy antigua, con caños en algunas zonas que tienen más de cien años. Se calcula que del agua que se potabiliza en la planta principal una vez que llega a la ciudad, se pierde la mitad. En Montevideo hay una cultura del exceso de agua, del agua barata y que no hace falta ciudarla. Hay un dicho que se repite: ‘es más barato potabilizar agua que arreglar caños’; es duro escucharlo, pero ya no estamos en esa situación y el cambio ha sido muy radical”.
+[H2] Menos presupuesto, mala gestión
+“Venimos de un proceso donde la OSE ha perdido funcionarios, ha bajado su inversión y eso repercute en sus capacidades”, declara el senador por el Frente Amplio, Alejandro “Pacha” Sánchez, y precisa que el gobierno de Lacalle Pou ajustó el presupuesto un 30 por ciento y también recortó las inversiones aproximadamente 30 millones con respecto a la década anterior: de 100 millones de dólares anuales a 68 millones. “Este gobierno decidió no seguir adelante con la represa de Casupá, que es una solución más estructural, plantea el senador frenteamplista. El gobierno frenó algo que ya estaba proyectado, que había pasado por todos los procesos, se había financiado, ya estaban hechos los estudios ambientales, ya estaban las expropiaciones, y estaba pronto el llamado a licitación. Y lo frenaron por una iniciativa privada que vale mucho más caro (el proyecto Neptuno) y es mucho más incierta”.
+Karin Nansen, de Redes Amigos de la Tierra Uruguay, asegura que no se trata sólo de un problema de calidad, sino de cantidad de agua. “Por un mal manejo se vació el Canelón Grande y por falta de previsión se acabó la reserva de agua en la represa de Paso Severino”, recuerda Nansen y observa que aunque el gobierno dice que el origen de la crisis es por la fuerte sequía que ha afectado al país, desde las organizaciones ambientales y movimientos sociales entienden que se debe también a “una mala gestión” de la cuenca del río Santa Lucía que abastece de agua al 60 por ciento de la población del país: 1.800.000 uruguayos.
+María Selva Ortiz, también de REDES Amigos de la Tierra, postula que la crisis hídrica demuestra que hay un vínculo entre la dimensión ambiental y la realización de derechos. “Si no tenemos territorios saludables y si no gestionamos las cuencas hidrográficas en forma justa y sustentable, dando prioridad al derecho humano al agua, este derecho se ve seriamente vulnerado. Antes de esta crisis ya había problemas de calidad de agua por la contaminación con agrotóxicos y la cantidad también se vio afectada por las plantaciones de eucaliptus sobre todo en las nacientes de la cuenca”.
+Nansen sostiene que a largo plazo es necesario avanzar en la gestión sustentable de las cuencas tal como establece la constitución. “El agua que se distribuye en la región metropolitana, además de ser salada y presentar riesgos para quienes sufren hipertensión o problemas cardíacos y no ser aptas para la niñez, tiene valores mayores de trihalometanos que pueden provocar problemas de salud crónicos”, explica Nansen. “Como todos los problemas socio-ambientales, esta situación afecta en mayor medida a la población con menores recursos y se reproduce la injusticia -añade Ortiz-. Un derecho fundamental para la vida pasó a estar mediado por el mercado; acceden a agua potable quienes pueden pagar por el agua embotellada. Y esto no es lo que plantea la Constitución, sino todo lo contrario”.
+[H2] Extractivismo puro y duro
+Anahit Aharonian, ingeniera agrónoma diplomada en Gestión de Políticas Ambientales que integra la Comisión Nacional en Defensa del Agua y la Vida (CNDAV), enfatiza que la CNDAV propone la restauración del monte indígena en las riberas del río Santa Lucía. “Esa flora nativa se ha destruido con las plantaciones de soja a través de las cuales cae nitrógeno y fósforo a los cauces de agua. A eso hay que sumarle los pesticidas y los agrotóxicos como el glifosato, que es potencialmente cancerígeno y provoca junto con otros pesticidas efectos en la salud humana. Hay que restaurar el monte indígena, dejar de plantar soja y los cultivos que son negativos para nuestros ecosistemas y el campo natural reverdece y eso hace que absorba el exceso de nitrógeno y fósforo”.
+El proyecto Neptuno o también llamado Arazatí, que busca producir agua potable a partir del agua captada desde el Río de la Plata es “inapropiado”, en palabras de Aharonian, porque sería realizado por empresas privadas, algo que está prohibido por la Constitución. “Sacar agua del Río de la Plata tiene un problema, que es la salinidad, y también la enorme proliferación de floraciones algales, las cianobacterias, cuyas toxinas son hepatóxicas; la OSE estaría potabilizando agua con toxinas incluidas”, advierte la ingeniera agrónoma. “El agua embotellada es agua nuestra. ¿Por qué tenemos que pagar por esa agua? ¿Por qué mientras en Minas están extrayendo agua para exportar, su población no tiene agua? Los negocios son más importantes que abastecer de agua potable a toda la población del Estado, sea el gobierno que sea. En un país cuya riqueza mayor es tanta agua dulce cruzando el territorio, no podemos estar impidiendo que la población acceda al agua”.
+“No es sequía, es saqueo”. La consigna elegida por los movimientos ambientales cuestiona el discurso oficial de que la crisis del agua es por la sequía. “La falta de lluvias no es porque tata Dios no manda agua del cielo, sino que está relacionada con el cambio del uso del suelo que implica que no haya evapotranspiración suficiente por la vegetación que quitan, ese cambio de la plantación natural por la exótica de los agronegocios. Al no haber evapotranspiración suficiente, al no haber posibilidades de cosecha de agua, se provocan sequías e inundaciones; por eso los deslaves que ustedes han sufrido en varias provincias del norte de Argentina y que en Uruguay también se ha visto. Todo eso sucede por el cambio del uso del suelo, provocado por quienes lucran y no miden las consecuencias. No es sequía, es extractivismo puro y duro”, concluye.</t>
   </si>
   <si>
     <t>Silvina Friera</t>
@@ -1330,16 +3217,34 @@
     <t>https://www.pagina12.com.ar/lbpupdates/558268</t>
   </si>
   <si>
-    <t>2023-06-14T17:05:08Z</t>
-  </si>
-  <si>
     <t>Alimentos: lo que no se discute</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/558279-alimentos-lo-que-no-se-discute</t>
   </si>
   <si>
-    <t>2023-06-14T14:45:52Z</t>
+    <t xml:space="preserve">Título: Alimentos: lo que no se discute
+Subtítulo: Acaba de conocerse el índice FAO de inflación para alimentos en América Latina:
+Editoria: Economia
+Tags: Inflación, Opinión, inflacion, opinion, diario
+URL: https://www.pagina12.com.ar/558279-alimentos-lo-que-no-se-discute/
+Notícia completa (16 blocos):
+Acaba de conocerse el índice FAO de inflación para alimentos en América Latina:
+Venezuela pica en punta con 110,4%. Es un histórico importador de alimentos, situación que, bloqueo mediante, está revirtiendo aceleradamente y con éxito.
+Le sigue con un 86,6% Argentina, vendedora neta de materias primas con destino alimentario. Exportamos todo, pero todo, lo que comemos: trigo, soja, maíz, poroto, lentejas, ajo, cebolla, carnes y un largo etc. Marcamos récord histórico de exportaciones, y tenemos 40% de pobreza y una inflación por las nubes. Está claro que el modelo no funciona ¿no? Sin embargo, no se les ocurre siquiera poner en debate la posibilidad de cambiar. Al contrario: proponen profundizarlo!
+El país de menor inflación en alimentos del continente es Bolivia, con el 2,2%. Ahí la soberanía alimentaria es un valor tangible, no un mero discurso sobre lo que hay que conquistar.
+El precio de los alimentos es un factor clave de la estabilidad democrática en todo el mundo; y es un instrumento central en la puja distributiva. Un gobierno peronista tiene atada su supervivencia política al bienestar de los sectores populares. Alimentos y salarios son inseparables, y bases esenciales para una buena salud electoral.
+El debate de la producción y el precio de los alimentos en Argentina está dominado por falsos supuestos que propagan los voceros interesados de los agronegocios monopólicos. Para estos grupos, los parámetros se reducen a volumen, producción y exportación. Ellos invisibilizan “partes” que son centrales para entender el “todo”. ¿Cuáles? Van algunas, sustanciales, que nunca entran en debate: concentración de tierras, rentas y producción, medio ambiente, deforestación, arraigo, migraciones rurales, logística, puertos etc. Como si dónde se siembra y quién lo hace fuera una cuestión inocua en el tema. Otro gran ausente en el debate, es el impacto del acuerdo con el FMI en el precio de los alimentos.
+Veamos: el día 4 de junio se realizó en Rosario un encuentro sobre la soberanía. En el panel referido a Soberanía Alimentaria habló Albina Albides, productora hortícola del cordón verde platense, integrante de la organización ASOMA (Asociación de Medieros y Afines) y de la Federación Nacional Campesina. Albina produce verduras y hortalizas que comercializa a través de mayoristas que le pagan lo que se les antoja . Ella debe alquilar la tierra donde siembra y por la que paga $40.000 la hectárea. La superficie mínima para que pueda vivir una familia es de 2,5 hectáreas, es decir $100.000 mensuales; y no le permiten construir una casa de material, deben morar en casillas de chapas y plásticos. Es irracional e inexplicable que en la Argentina no se pueda garantizar tierras para la producción alimentaria de cercanía. Y más inexplicable aún, que el campo nacional y popular no lo ponga en agenda.
+La contracara de Albina es la producción hortícola mega-concentrada; integrada verticalmente, con posición dominante en el mercado. Un ejemplo de esta forma de producción es Hijos de Salvador Muñoz: una empresa salteña que maneja 28.700 hectáreas (contra ninguna de Albina). Esta compañía siembra 24.000 hectáreas de poroto (destinado a la exportación) y la complementa con ganadería. También planta unas 1.700 hectáreas de pimiento, tomate, zapallo, berenjena, lechuga etc.
+“La participación de la firma en el mercado argentino de conservas de pimientos alcanza a más del 70%, siendo líderes absolutos en todos los segmentos; ya sea de consumo domiciliario con marcas propias y de terceros, como a través del canal gastronómico. Los pimientos y tomates para “conservas” salen a la venta enlatados con las marcas propias y con “marcas blancas” destinadas a terceros clientes mayoristas locales, para atender el consumo minorista y el canal gastronómico " (página Bichos de Campo; 3/6/2023). Obsérvese el concepto: “líder absoluto en todos los segmentos” y 70% del mercado del pimiento. Agreguemos que exporta a 15 países, lo que le permite elegir adónde van sus productos, en función del precio. “Parece” posición dominante ¿no?
+Ahora, cuando el pimiento aumenta, este monopolio ¿no tiene nada que ver? Pero sumemos otro “detalle”, no menor: de Embarcación (Salta) a CABA hay 1.386 km, es un día y medio de viaje. Ese recorrido tienen que hacer los pimientos y demás productos para llegar a destino, todo en camión. Semejante travesía encarece el producto en un 30% estimativamente. El 50% de esa logística es en dólares. Cada vez que se devalúa, de acuerdo con las exigencias del acuerdo con el FMI, va al precio de los alimentos.A esto hay que sumarle pasivos ocultos que nunca se computan: costo ambiental, accidentes viales, mantenimiento de rutas etc .
+Latifundio, destrucción de la chacra mixta, producción sin productores, integración vertical, posición dominante, deforestación, depredación ambiental, migraciones rurales y deslocalización productiva para sembrar soja hasta en las banquinas. Este es el modelo productivo dominante instalado por el mercado a partir de la década del noventa. Todo está mal en esta forma de producir los alimentos. Y el precio que pagan los consumidores es la certificación final del desquicio productivo que padecemos.
+La Argentina debe rediscutir su modelo agrícola. Hay tres interrogantes que la política debe responder en torno a este tema:
+1. ¿Quién es el sujeto que produce los alimentos ? Se puede hacer de las dos maneras: con Albina o con los Hijos de Salvador Muñoz. Si es con Albina hace falta más Estado y más recursos. Si es con los segundos, a no quejarse por los precios .
+2. ¿Dónde se producen? O se garantiza el acceso a la tierra a los pequeños productores y se va a la producción cercanía, con chacra mixta incluida, o se sigue con la deslocalización productiva como sucede hoy, con alimentos viajeros y caros.
+3. ¿Cómo se produce? O se va hacia un modelo agroecológico, amigable con el medio ambiente y la salud, o se sigue este rumbo de producción industrial con uso de agrotóxicos.
+Debemos cambiar la forma de producir alimentos. Cuanto más demoremos, más costo político pagamos. Uno cambia cuando toma la decisión política de cambiar; después, implementar el cambio lleva tiempo ya sea por motivos políticos o biológicos. No es soplar y hacer botellas. Pero si se pudo, se puede.</t>
   </si>
   <si>
     <t>Pedro Peretti</t>
@@ -1351,7 +3256,27 @@
     <t>https://www.pagina12.com.ar/558145-nace-un-gigante-agroindustrial-bunge-compra-viterra</t>
   </si>
   <si>
-    <t>2023-06-14T03:01:00Z</t>
+    <t xml:space="preserve">Título: Nace un gigante agroindustrial: Bunge compra Viterra
+Chapeau: La nueva empresa liderará las exportaciones de aceite de girasol y soja en Argentina
+Subtítulo: Son dos de las principales exportadoras de granos y subproductos en el país. La Comisión Nacional de Defensa de la Competencia investiga la fusión, que no debería tener problemas por el tipo de mercado del que se trata.
+Editoria: Economia
+Tags: Agroindustria, printed-edition, diario
+URL: https://www.pagina12.com.ar/558145-nace-un-gigante-agroindustrial-bunge-compra-viterra/
+Notícia completa (14 blocos):
+Este martes, las firmas agrícolas Bunge y Viterra anunciaron su fusión en una empresa "líder en soluciones de agronegocios para satisfacer las exigencias del siglo XXI". Lo de líder no es marketing: son dos gigantes agroindustriales a nivel mundial. En Argentina, ambas integran el ranking de las diez principales exportadoras de cereales, oleaginosas y aceites del país. Las dueñas de los dólares. Por ley, el requerimiento será investigado por la Comisión Nacional de Defensa de la Competencia (CNDC) para evaluar si esta fusión puede generar un perjuicio para el interés económico general. Por el tamaño del mercado en Argentina, especialistas entienden que será aprobada sin problemas.
+Se espera que la fusión se cierre a mediados de 2024, sujeta al cumplimiento de las condiciones de cierre habituales, incluida la aprobación de los accionistas de Bunge y la recepción de las aprobaciones reglamentarias en cada país donde operan. En Argentina, la Ley de Defensa de la Competencia establece que una operación de esta característica debe ser notificada como concentración económica para su análisis y eventual autorización a la CNDC, que realiza un análisis de las operaciones para evitar que haya firmas con poder de mercado con potencialidad para afectar negativamente la competencia y generar un perjuicio para el interés económico general.
+El pedido de concentración ya entró a la CNDC, que emitirá en unos meses- dependiendo de la velocidad de respuesta al pedido de información de ambas firmas- un Dictamen recomendando aprobar, condicionar, o bien, prohibir la operación de concentración económica. Analistas consultados por este diario no ven, a priori, ningún problema en la aprobación de la fusión ya que se trata de un mercado de productos por sí concentrados.
+Bunge les dará a los accionistas de Viterra 2000 millones de dólares en efectivo y 6200 millones en acciones de la empresa, que es una de las cinco grandes comercializadoras de granos a nivel mundial, lo que representa una contraprestación de 75 por ciento en acciones de Bunge y 25 por ciento en efectivo. Como parte de la transacción, Bunge asumirá 9800 millones de dólares de deuda de Viterra, que está asociada con aproximadamente 9000 millones de dólares de inventarios fácilmente comercializables de gran liquidez.
+[H2] Quién es quién
+Continuadora del otrora gigante argentino Bunge &amp; Born, la estadounidense Bunge conforma con ADM, Cargill, Dreyfus el ABCD de exportación de granos del mundo. Son las principales empresas comercializadoras de materias primas y debido a los procesos de verticalización y horizontalización de la cadena productiva en las últimas dos décadas, controlan el mercado de la soja en América Latina. Se encuentran amenazadas por la china COFCO. "Recurren a un uso estratégico de los medios de comunicación para desviar la atención del importantísimo papel que ejercen sobre las inversiones en tierras alrededor del mundo y, simultáneamente, para oponerse al aumento de la competencia de China en la agroindustria internacional", asegura un informe sobre "la búsqueda de China de recursos naturales en América Latina" que escribieron Felipe Freitas da Rocha y Ricardo Bielschowsky para la Cepal.
+Viterra operaba hasta mayo de 2021 como Oleaginosa Moreno en Argentina. Entró al podio con la salida del negocio de Vicentin, socia de Glencore en Renova. Es que la empresa, originalmente de capital argentino, es controlada desde hace más de veinte años por el grupo de origen suizo Glencore. Se transformó en la primera exportadora argentina de aceite y pellets de soja en los últimos dos años gracias a la llegada de un management nuevo.
+Tiene una posición muy importante en la zona sur de la provincia de Buenos Aires, Bahía Blanca, Necochea, porque tomó el negocio que era de Oleaginosa Moreno y quedó bien posicionada en girasol, cebada y trigo. En soja creció gracias al uso de instalaciones y a los trabajos a fasón que tomó de la que supo ser la cerealera más importante del país y ahora en concurso de acreedores Vicentin.
+"Se va a complementar bien con Bunge, que está más posicionada geográficamente de Buenos Aires al norte del río Paraná y Rosario y más concentrado en el negocio de soja y fertilizantes", explica a PáginaI12 Javier Preciado Patiño, el ex subsecretario de Mercados Agropecuarios de Agricultura durante la gestión de Julián Domínguez. "Es un desafío para el resto, para los Cofco, los Cargill, los Dreyfus, que van a tener un jugador más fuerte. Pero es un proceso que se está dando a nivel global para buscar la competitividad por la escala en un negocio que va indefectiblemente para ese lado", reflexiona.
+"Viterra complementa nuestra huella de activos existente con su capacidad de manejo de granos y semillas blandas, al tiempo que expande nuestras capacidades de expansión en regiones y cultivos clave donde Bunge está actualmente subrepresentada", aseguró en un comunicado el CEO de Bunge Greg Heckman, que también dirigirá junto a John Neppl, CFO de Bunge, la compañía combinada. La nueva firma operará como Bunge, con sede operativa en St. Louis, ciudad del estado norteamericano de Missouri.
+El CEO de Viterra, David Mattiske, se unirá al Equipo de Liderazgo Ejecutivo de Bunge en el rol de Co-Director de Operaciones. Se espera que el Consejo de Administración de Bunge esté compuesto por ocho representantes nombrados por Bunge y cuatro representantes nombrados por los accionistas de Viterra.
+[H2] Las dueñas de los dólares
+De acuerdo al ranking de exportadores de la Secretaría de Agricultura, en 2022 Bunge y Viterra concentraron el 61,4 por ciento de las exportaciones de aceite de girasol. Con la integración a Bunge, adquirirían una posición dominante en el negocio girasolero argentino. En el caso del aceite de soja, las exportaciones representaron un 31,2 por ciento del total. De repetirse las posiciones, quedarían en los siguientes puestos del ranking Cargill con el 17 por ciento del mercado, Molinos Agro (12 por ciento) y Aceitera General Deheza (AGD) con el 10 por ciento, entre otros. En cuanto al otro producto de valor agregado, la harina de girasol y soja, las exportaciones de las dos firmas en 2022 alcanzaron el 45,9 y 32 por ciento del mercado total, respectivamente.
+En el caso de los granos, ambas pasarían a liderar - sin mucha sobra- el negocio de las exportaciones de trigo, cebada y soja. En maíz, sin embargo, Bunge no lograría sacarle el podio a ADM y estaría cerca los embarques realizados por Cargill, siempre teniendo en cuenta los registros de operaciones realizadas en 2022.</t>
   </si>
   <si>
     <t>Natalí Risso</t>
@@ -1366,7 +3291,28 @@
     <t>https://www.pagina12.com.ar/556126-se-necesitan-politicas-publicas-dirigidas-a-la-produccion-de</t>
   </si>
   <si>
-    <t>2023-06-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: Se necesitan políticas públicas dirigidas a la producción de alimentos y no al agronegocio
+Chapeau: En tres décadas se perdieron 156 mil establecimientos productivos
+Subtítulo: De la tierras cultivadas en el país, un millón de hectáreas están destinadas a legumbres para consumo humano, frutales y hortalizas, mientras que 30 millones se destinan a commodities para la exportación.
+Editoria: Cash
+Tags: Agricultura familiar, printed-edition, agricultura-familiar
+URL: https://www.pagina12.com.ar/556126-se-necesitan-politicas-publicas-dirigidas-a-la-produccion-de/
+Notícia completa (15 blocos):
+La crisis económica en la Argentina ha impactado fuertemente en el sector de pequeños y medianos productores agrícolas. Se trata de un segmento que además de garantizar un alimento sano y barato para los argentinos, tiene capacidad de exportación y de sustitución de importaciones.
+“Es necesario y urgente una política pública integral de acceso a los alimentos y que apunte a ocupar el territorio de la Argentina. Que las producciones de todo el país puedan llegar a través de un mercado de cercanías a un precio justo y con alimentos sanos”, reclama Juan Manuel Rossi, presidente de la Federación de Cooperativas Federadas (FeCoFe), que nuclea, en 10 provincias, a 53 cooperativas dedicadas a la actividad agrícola, ganadera y de producción de alimentos elaborados.
+[H2] Cooperativas que exportan
+Un reciente informe del Instituto Nacional de Asociativismo y Economía Social (INAES) junto con la Agencia Argentina de Inversiones y Comercio Internacional y el Ministerio de Relaciones Exteriores destaca que en 2022 las cooperativas del país exportaron 160 productos a 121 destinos, pasando de una participación en el comercio internacional del 2,4 por ciento en 2018 al 4,4 por ciento en 2022.
+A nivel interno, según datos del Ministerio de Agricultura de la Nación, los pequeños y medianos productores son responsables del 60 por ciento de los alimentos frescos que se consumen en el país, generando el 53 por ciento del empleo en el sector.
+Sin embargo, la falta de crédito y acceso a la tierra, el aumento de la tasa de interés, los insumos y maquinarias importadas, los alquileres, la sequía y el avance del agronegocio --con excedentes producto de la concentración económica y la especulación financiera-- han puesto en jaque a este sector.
+“Las medidas que se van tomando son en función al modelo agroexportador, más allá de algunas iniciativas sueltas. Es necesario que todas las instancias del Estado nacional, provincial y municipal generen políticas de comercialización propias de los productores. Ahí es donde, por oferta y demanda, van a bajar los precios. Porque por el canal de comercialización establecido, que es concentrado, es muy difícil intervenir en la cadena”, opina Nahuel Levaggi, coordinador de la Unión de Trabajadores de la Tierra (UTT) y ex director del Mercado Central.
+Fecofe y la UTT, junto al Movimiento Nacional Campesino Indígena Somos Tierra, la Federación de Organizaciones Nucleadas de la Agricultura Familiar y Bases Federadas --un espacio disidente de la conducción actual de la Federación Agraria Argentina--, conforman la Mesa Agroalimentaria Argentina, que en 2020 le presentó al nuevo presidente Alberto Fernández leyes como la de Acceso a la Tierra, ley de Arrendamientos Rurales, ley de Protección y Fortalecimiento de los Territorios Campesinos y de la Agricultura Familiar, ley de Segmentación de las Políticas Impositivas y Agrarias y ley de Financiamiento y Fomento del Cooperativismo y la Transición Agroecológica.
+Ninguna de estas medidas han sido tomadas en cuenta. Por ejemplo, la ley de Acceso a la Tierra ya es la cuarta vez que ingresa al Congreso Nacional. La iniciativa propone crear un Fondo Fiduciario Público de Crédito para la Agricultura Familiar (Crepaf), para facilitar el acceso a créditos destinados a la adquisición de inmuebles rurales y la construcción de viviendas para las familias productoras que carezcan de tierra propia. Más del 80 por ciento de las familias productoras de alimentos alquilan la tierra.
+[H2] Mucha tierra poco alimento
+Según datos del 2018 del Censo Agropecuario Nacional (CNA), el 40 por ciento de las tierras cultivadas está en manos de solo 1200 familias y empresas. En sólo tres décadas se perdieron 156 mil establecimientos productivos. En su mayoría, de menos de 50 hectáreas.
+De las tierras cultivadas en el país, un millón de hectáreas están destinadas a legumbres para consumo humano, frutales y hortalizas. Mientras que 30 millones se destinan a commodities para la exportación (soja, maíz, trigo, girasol, algodón).
+Argentina es uno de los países del mundo con mayor concentración de la población en las ciudades. Solo el 8 por ciento de su población vive en zonas rurales produciendo alimento para el mercado interno. En este sentido, desde la UTT se viene implementando un plan de Colonias Agrícolas para desconcentrar las población urbana y disminuir los índices de pobreza, aumentado la oferta de alimentos sanos a través de emprendimientos productivos. Entre ellos está la producción de bioinsumos que permiten reemplazar la importación de agrotóxicos.
+“Es un programa agrario que se centra en garantizar el plato de los argentinos y las argentinas. Nace de la Mesa Agroalimentaria Argentina, pero también de la historia de lucha de todas las organizaciones campesinas e indígenas. Justamente en función de entender el alimento como un derecho y ver que en nuestro país el modelo agrario siempre estuvo en mano de los grandes intereses concentrados. Nunca hubo un modelo agrario popular”, comenta Levaggi.
+* Integrante de la Coordinación Nacional de la UTT</t>
   </si>
   <si>
     <t>Agustín Suárez *</t>
@@ -1381,7 +3327,24 @@
     <t>https://www.pagina12.com.ar/555728-los-indigenas-brasilenos-contra-el-marco-temporal-que-impuls</t>
   </si>
   <si>
-    <t>2023-06-06T13:14:52Z</t>
+    <t xml:space="preserve">Título: Los indígenas brasileños contra el “marco temporal” que impulsa el agronegocio
+Chapeau: La defensa de los derechos ancestrales
+Subtítulo: Los indígenas brasileños se movilizan desde este martes contra las iniciativas que se tramitan tanto en el Congreso como en la Corte Suprema y que buscan poner una fecha límite para el r
+Editoria: Brasil
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/555728-los-indigenas-brasilenos-contra-el-marco-temporal-que-impuls/
+Notícia completa (11 blocos):
+Los indígenas brasileños se movilizan desde este martes contra las iniciativas que se tramitan tanto en el Congreso como en la Corte Suprema y que buscan poner una fecha límite para el reclamo de los territorios ancestrales.
+En el flanco judicial, el máximo tribunal se apresta a retomar un juicio sobre el llamado "marco temporal", que reconoce como tierras indígenas sólo aquellas que los pueblos originarios ocupaban al día 5 de octubre de 1988, cuando se promulgó la actual Constitución. Ese mismo asunto se tramita en el Parlamento, en el que la semana pasada la Cámara de Diputados aprobó un proyecto que da forma de ley a la tesis del "marco temporal", que todavía deberá ser debatido por el Senado.
+La Comisión Interamericana de Derechos Humanos (CIDH) ya expresó su preocupación por la ley 490 porque “contradice estándares universales e interamericanos de derechos humanos y pone en riesgo la propia existencia de pueblos indígenas y tribales en Brasil”.
+Por su parte, Amnistía Internacional instó al Senado a rechazar el proyecto tras advertir que la iniciativa “afecta a los derechos de los pueblos indígenas, especialmente en lo relativo al derecho a la libre determinación y al territorio tradicional, y refuerza las violaciones de derechos humanos sistémicas sufridas por los pueblos indígenas de Brasil, que durante siglos han sido expulsados de sus territorios”.
+[H2] “Limitar y reescribir la historia"
+Unprocessed element [b]
+Desde la Apib, adelantaron que prepararan movilizaciones en todo el país contra una tesis que intenta "limitar y reescribir la historia" a partir de 1988 y "desconoce el pasado", pues "cientos de años antes" los pueblos originarios ya ocupaban esos territorios. Sostienen que eso está debidamente garantizado en el artículo 231 de la Constitución, que reconoce el derecho de los indígenas a "su organización social, costumbres, creencias y tradiciones", y los "derechos originarios sobre tierras que tradicionalmente ocupan", que deben ser delimitadas por el Estado. Según la Apib, el "marco temporal" también ignora que muchos pueblos indígenas fueron desalojados a la fuerza de tierras que ocupaban antes de 1988, por colonos que luego se apropiaron en forma "ilegítima" de esas zonas, lo cual ha generado recurrentes y violentos conflictos.
+[H2] Los territorios en disputa
+Unprocessed element [br]
+[H2] La palabra del Supremo Tribunal Federal
+La Corte Suprema brasileña tiene previsto retomar este miércoles un proceso que puede sentar jurisprudencia y ser decisivo en la polémica del "marco temporal". El juicio comenzó el año pasado: hay hasta ahora un voto a favor y otro en contra de esa tesis y todavía deben pronunciarse ocho de los miembros del tribunal. La causa llegó al Supremo desde tribunales inferiores y a través de una demanda intentada por el Estado contra un fallo de segunda instancia que reconoció como propietario de unas tierras a un organismo público del sureño estado de Santa Catarina. Durante siglos, esas áreas fueron ocupadas por las etnias Xokleng, Guaraní y Kaingang, desalojadas a la fuerza a mediados del siglo pasado, y acabaron en manos de la Fundación para el Amparo Tecnológico de Santa Catarina, favorecida por la sentencia que ahora discute el Supremo. Ese fallo, apoyado en el concepto del "marco temporal", sostuvo que en octubre de 1988 esas tierras estaban en poder de ese organismo de Santa Catarina y desconoció que, a partir de 1996, los indígenas habían retomado algunos de esos asentamientos.</t>
   </si>
   <si>
     <t>Diputados brasileños aprueban proyecto para limitar la demarcación de tierras indígenas</t>
@@ -1393,7 +3356,33 @@
     <t>https://www.pagina12.com.ar/554157-diputados-brasilenos-aprueban-proyecto-para-limitar-la-demar</t>
   </si>
   <si>
-    <t>2023-05-31T13:01:44Z</t>
+    <t xml:space="preserve">Título: Diputados brasileños aprueban proyecto para limitar la demarcación de tierras indígenas
+Chapeau: La policía reprimió las protestas en contra del proyecto de ley
+Subtítulo: El proyecto de ley establece que sólo pueden ser demarcados los territorios que estaban ocupados por pueblos indígenas al momento de la sanción de la Constitución de 1988. Organizaciones indígenas reclaman que en 1988 no podían ocupar algunos territorios porque habían sido expulsados.
+Editoria: Brasil
+Tags: Brasil
+URL: https://www.pagina12.com.ar/554157-diputados-brasilenos-aprueban-proyecto-para-limitar-la-demar/
+Notícia completa (20 blocos):
+La demarcación de tierras indígenas, una de las claves del gobierno de Lula da Silva para proteger la Amazonia y los pueblos indígenas que lo habitan, podría ser frenada por un proyecto de ley aprobado esta semana en la cámara de Diputados.
+El texto establece que las tierras reservadas para las comunidades originarias deben limitarse a aquellas que ya estaban ocupadas por pueblos indígenas al momento de la sanción de la actual Constitución en 1988.
+Según científicos, la demarcación de tierras indígenas es una barrera importante para frenar la deforestación de la Amazonia. Esto se evidenció durante el gobierno del expresidente Jair Bolsonaro. El exmandatario se negó a demarcar territorios indígenas y en cambio permitió el ingreso de mineros y promovió el avance del agronegocio en la Amazonia.
+El ministerio de Pueblos Indígenas y organizaciones sociales repudiaron la decisión de los diputados y aseguraron que se trata de un retroceso y una amenaza a los pueblos originarios.
+[H2] Genocidio legislado
+El proyecto "representa un genocidio legislado porque afecta directamente a pueblos indígenas aislados, ya que autoriza el acceso deliberado a territorios en los que viven pueblos que aún no tuvieron ningún contacto con la sociedad ni con otros pueblos indígenas", denunció el ministerio en un duro comunicado.
+El proyecto fue impulsado por diputados afines al agronegocio y opositores del gobierno de Lula fue aprobado por 283 votos contra 155. El texto todavía tiene que pasar por la cámara de Senadores para convertirse en ley.
+Brasil tiene un total de 764 territorios indígenas, pero cerca de un tercio de ellos todavía no fueron demarcados, indicó la Fundación Nacional de los Pueblos Indígenas (FUNAI).
+https://twitter.com/GuajajaraSonia/status/1663709090458091521
+Durante los primeros meses de gobierno de Lula da Silva se logró la demarcación de seis territorios y desde el nuevo ministerio de Pueblos Indígenas habían anunciado la demarcación de otros 14 territorios.
+"No vamos a detenernos. Tenemos el Senado por delante y muchos diálogos para garantizar la preservación de nuestras vidas y territorios”, tuiteó la ministra los Pueblos Indígenas, Sonia Guajajara.
+“La mayoría del Congreso votó contra los pueblos indígenas y la naturaleza", denunció la ministra. Guajajara le solicitó a Lula que vete la iniciativa en caso de que llegue a sanción
+[H2] Protestas y represión policial
+La policía reprimió las protestas que sea realizaban de manera pacífica en la ciudad de San Pablo. Cientos de personas se manifestaron en contra del proyecto aprobado por los diputados brasileños.
+Los pueblos indígenas rechazaron el “marco temporal” que promueve el texto. Además, reclaman que en 1988 muchos pueblos indígenas no podían ocupar algunos territorios porque fueron expulsados y esta situación se agravó durante la última dictadura militar (1964-1985).
+https://twitter.com/LeoDiCaprio/status/1663366909369233410
+La votación del proyecto de ley 490 sobre el marco temporal para demarcar tierras indígenas despertó indignación internacional. Organizaciones y activistas de todo el mundo se manifestaron en contra.
+"Bolsonaro se fue pero el exterminio continúa", denunció el Observatorio del Clima. La organización dijo que el proyecto “viola la Constitución” y que era un día vergonzoso para la historia de los diputados y pidieron a los senadores “revertir los absurdos aprobados”.
+Los actores de Hollywood Leonardo Di Caprio y Mark Ruffalo, conocidos por sus militancias sociales, rechazaron el proyecto de ley y llamaron a defender la demarcación de tierras impulsada por Lula.
+"Hay una guerra contra los pueblos indígenas y las selvas. Nuestro planeta está en riesgo. Lula, sea el héroe que su pueblo eligió, impida (el avance) del proyecto", tuiteó Ruffalo en vísperas del debate.</t>
   </si>
   <si>
     <t>Cristina Kirchner no señaló un candidato pero marcó el rumbo: los ejes del plan de gobierno que propuso en Plaza de Mayo</t>
@@ -1405,7 +3394,41 @@
     <t>https://www.pagina12.com.ar/552840-cristina-kirchner-no-senalo-un-candidato-pero-marco-el-rumbo</t>
   </si>
   <si>
-    <t>2023-05-25T22:59:47Z</t>
+    <t xml:space="preserve">Título: Cristina Kirchner no señaló un candidato pero marcó el rumbo: los ejes del plan de gobierno que propuso en Plaza de Mayo
+Chapeau: Lo que dejó el discurso de la vicepresidenta
+Subtítulo: De las candidaturas solo hubo espacio para conjeturas a partir de los lugares que cada uno ocupó en el escenario. Lo que sí quedó claro fue el camino que plantea CFK: la definición de un programa sobre 3 o 4 ejes. Qué dijo al respecto.
+Editoria: El País
+Tags: Cristina Fernández de Kirchner, cristina-fernandez-de-kirchner, diario
+URL: https://www.pagina12.com.ar/552840-cristina-kirchner-no-senalo-un-candidato-pero-marco-el-rumbo/
+Notícia completa (28 blocos):
+La Plaza de Mayo habló bajo la lluvia: "¡Cristina presidental!", "Una más y no jodemos más!", "La proscripción se va a la puta que lo parió!". La vicepresidenta escuchó sin responder, eligió ya no hablar más ni dejar dudas sobre su posible candidatura, que dio por cerrada con su carta del 16 de mayo, y abrió paso a un nuevo rol como conductora del movimiento: "Esto no es tarea de una persona, es tarea militante. Basta de pedirle al otro que haga cosas que no estamos dispuestos a hacer", convocó en su discurso en el acto del 25 de mayo por los 20 años de la llegada de Néstor Kirchner a la Presidencia.
+[H3] Quiénes son las principales figura políticas que estuvieron en el acto de CFK¿Quiénes son los niños que acompañaron a Cristina Kirchner en el escenario?
+En ese rol, Cristina tampoco tomó el bastón de mando para señalar a quiénes ocuparán la candidatura que ella deja vacante en el Frente de Todos. No habló ni de Sergio Massa, ni de Eduardo "Wado" De Pedro, que sí estuvieron en la primera línea del palco uno al lado del otro --sumando a las especulaciones de un posible binomio presidencial--. Tampoco habló de Axel Kicillof, también en primera línea, pero con intenciones de ir por la reelección provincial.
+Si las posiciones que ocuparon los invitados de Cristina al escenario del homenaje por los 20 años de la asunción de Néstor Kirchner sumaran puntos, los precandidatos presidenciales menos bendecidos deberían ser el referente social Juan Grabois y el jefe de Gabinete, Agustín Rossi, quienes quedaron en las gradas que se escaparon a la foto principal. El embajador en Brasil, Daniel Scioli, directamente no se subió al avión para llegar a Plaza de Mayo.
+[H2] Un modelo de país con un Estado grande
+Los 20 años de la asunción de Néstor Kirchner fueron el motivo de otro baño de popularidad para la ex presidenta y eligió repasar las dos décadas de kirchnerismo con logros y ejes programáticos que permitan enfrentar la vuelta de los discursos neoliberales de los precandidatos de Juntos por el Cambio y del ultraderechista Javier Milei.
+"El país que recibió Néstor venía de una gran crisis en el 2001. En estos tiempos que se habla tanto del Estado, que es necesario un Estado pequeñito, que no moleste, que deje que los argentinos vivan en paz. Quiero contarles que cuando él llegó, el Estado era muy chiquitito (...) pero la deuda era muy grande", reseñó como paso previo a marcar hitos de la recuperación del rol del Estado durante los tres gobiernos kirchneristas: la reestatización de Aerolíneas Argentinas, el Correo Argentino y el sistema jubilatorio, además de la recuperación de YPF.
+"Cuando el compañero llegó a presidente de la República, el producto bruto de este país era de 164.000 millones de dólares. Cuando su compañera entregó el gobierno el 10 de diciembre del 2015, el producto bruto era de 647.000 millones de dólares. Pagamos durante 12 años y medio 100.000 millones de deuda en dólares que no habíamos contraído nosotros", sintetizó la vicepresidenta como contestándole a quienes relación el crecimiento económico con el achicamiento del Estado.
+"¿Fue magia? ¿Somos unos genios? No, fue el modelo de construcción de la sociedad, un modelo de producción, de valor agregado, de inclusión social, de sostenimiento de la industria nacional, de buenos salarios. Porque no es pecado pagar buenos salarios, al contrario, es de buenos cristianos", planteó Cristina para los libros de la era kirchnerista.
+[H2] "El programa de gobierno que necesita la Argentina"
+La vicepresidenta no habló de candidaturas, pero volvió a hablar del programa de gobierno. Algo que había hecho a fines de abril en el Teatro Argentino de La Plata, cuando comenzó a desarmar el operativo clamor y a poner sobre la mesa un eslogan similar al que circuló en 2015 con Daniel Scioli como candidato, aquel de "el candidato es el proyecto".
+Entre esos puntos programáticos, y como parte de la reivindicación de los gobiernos kirchneristas en contraposición al actual gobierno del Frente de Todos, marcó el "acuciante problema de la redistribución de a riqueza", momento del discurso en el que mencionó sus diferencias con el presidente Alberto Fernández. "Lo he dicho un 20 de diciembre en La Plata cuando dije 'va a haber crecimiento, pero ojo, cuiden los precios de la economía porque sino el crecimiento se lo van a llevar 4 vivos'", le criticó y señaló: "Para distribuir el ingreso muchas veces hay que ponerle carita fea a los que tienen mucho".
+"Argentina necesita imperiosamente 3 o 4 ejes sobre los que desarrollar ese programa", marcó la vicepresidenta retomando la idea del proyecto como candidato e hizo hincapié en la explotación de los recursos naturales: petróleo, gas y litio. Destacó que Vaca Muerta fue recuperada "por los kukas" de la mano de la YPF con mayoría estatal y luego marcó un rumbo para el litio: "Que vengan a explotarlo pero queremos... no digo que los autos los hagan acá eléctricos, pero, por lo menos hermano, una parte de la batería o la batería entera hacela acá, si te la estás llevando toda".
+En ese sentido, Cristina consideró que el país debe tomar el camino de la industrialización para alejarse del modelo dependendiente de los commodities del agronegocio. "No podemos seguir atados a una economía primarizada, no podemos seguir atados a los precios internacionales o a que llueva o que salga el sol", sostuvo y puso la mirada en las últimas dos décadas de crecimiento económico de los países asiáticos con "modelos de acumulación acordados entre el sector público y el privado en las actividades que más retorno provocan, con tecnología, valor agregado y trabajo calificado".
+"Esta es la discusión que están esperando millones de argentinos y no las boludeces que se dicen todos los días en los medios de comunicación", consideró.
+[H2] La renegociación con el FMI
+Mientras Massa continúa intentando cerrar una renegociación de la deuda con el FMI, Cristina ató la posibilidad de llevar adelante un programa de gobierno con las condiciones que se negocien con el organismos multilateral de crédito. "Si nosotros los argentinos y argentinas no logramos que ese programa que el FMI impone a todos sus deudores sea dejado de lado y nos permita elaborar un programa propio de crecimiento, de industrialización, de innovación tecnológica, va a ser imposible pagarlo".
+La vicepresidenta insitió en la idea de que no se puede pagar sin crecer, otra reivindicación de la política de Néstor Kirchner, y volvió a proponer la idea de condicionar los pagos al crecimiento económico o al volumen de exportaciones. Sin olvidar la decisión política que tomó el FMI al otorgar el préstamo para sostener la campaña reelectoral de Mauricio Macri, por lo que también dejó en claro que la renegociación no debe quedar solo atada a las cláusulas económicas: "Fue un préstamo político y política debe ser la solución".
+[H2] Renovación del Poder Judicial
+En los ejes programáticos para un próximo gobierno Cristina también planteó la necesidad de "repensar el diseño institucional argentino" con énfasis en el Poder Judicial, sobre el que cargó una dura crítica a la Corte Suprema, a la que calificó de "mamarracho".
+"Es necesario la renovación de ese pacto democrático volver a darle al país un Poder Judicial que se ha evaporado entre las tramoyas de una camarilla indigna para la historia de la Argentina. No importa si es un jurista de una u otra orientación, pero por favor, los argentinos se merecen volver a tener una Corte Suprema de Justicia que pueda llamarse como tal sin ponerse colorados", sostuvo la vicepresidenta en una convocatoria a todos los partidos políticos.
+La ex presidenta --que en su gobierno impulsó la elección por voto popular del Consejo de la Magistratura-- calificó de "rémora monárquica" al Poder Judicial y resaltó que los poderes Ejecutivo y Legislativo tienen otra relación con la sociedad, ya que se exponen a su escrutinio cada dos y cuatro años.
+[H2] Cristina conducción
+El cantito de "¡Cristina presidenta!" sonó antes, durante y después del discurso, pero la vicepresidenta se encargó de dejarlo pasar y ubicarse en lo que parece ser su nuevo rol de conducción. "Es necesario construir organización, profundidad territorial de la organización, profundidad sectorial en los sindicatos, en las fábricas. Una sola persona no puede", se sinceró.
+"Tiene que haber una organización, tiene que haber cuadros que tomen la posta y lleven adelante el programa de gobierno que necesita la Argentina", pidió la vicepresidenta ya sin referirse solo a que tomen la posta los hijos de la generación diezmada, como expresó la semana pasada.
+"Quiero convocarlos para que cada uno en su lugar, en el bondi o el subte o en la bici, cuente y permita que este entramado de desinformación en cuanto a los verdaderos responsables de endeudamiento, esta vez la gente pueda decidir con claridad, pero sobre todo con información", pidió en referencia al acuerdo con el FMI, pero como invitación general para recuperar el protagonismo político en la calle, en los barrios y en los lugares de trabajo.
+"Esto no es tarea de una persona, es tarea militante. Basta de pedirle al otro que haga cosas que no estamos dispuestos a hacer. Hay que hacerlo entre todos y todas", sentenció Cristina y le confirmó a la plaza que el operativo clamor será por el proyecto.
+[H3] Las 23 definiciones claves del discurso de Cristina Fernández en Plaza de Mayo</t>
   </si>
   <si>
     <t>La elección de Néstor Kirchner: una enseñanza inolvidable</t>
@@ -1417,7 +3440,20 @@
     <t>https://www.pagina12.com.ar/552525-la-eleccion-de-nestor-kirchner-una-ensenanza-inolvidable</t>
   </si>
   <si>
-    <t>2023-05-25T03:01:00Z</t>
+    <t xml:space="preserve">Título: La elección de Néstor Kirchner: una enseñanza inolvidable
+Chapeau: A 20 años de la asunción
+Subtítulo: Hace veinte años la Argentina presenció un acontecimiento inusual en su vida política: Néstor Kirchner asumía la presidencia de un país devastado por el catastrófico derrumbe del experimento neo
+Editoria: Especiales Página|12
+Tags: Néstor Kirchner, printed-edition, nestor-kirchner
+URL: https://www.pagina12.com.ar/552525-la-eleccion-de-nestor-kirchner-una-ensenanza-inolvidable/
+Notícia completa (7 blocos):
+Hace veinte años la Argentina presenció un acontecimiento inusual en su vida política: Néstor Kirchner asumía la presidencia de un país devastado por el catastrófico derrumbe del experimento neoliberal iniciado por la dictadura genocida que la presidencia de Carlos S. Menem llevara hasta sus últimas consecuencias y por la mentirosa política de la Convertibilidad pergeñada por Domingo F. Cavallo, que reposaba sobre la fantasiosa equiparación entre el dólar y el peso argentino. En ese convulsionado entorno Menem, que había triunfado en la primera vuelta electoral, optó por no presentarse en el balotaje para disputar la presidencia con Kirchner, que había obtenido un 22 % de los sufragios (contra el 25 % del expresidente) dado que todas las encuestas le anticipaban una derrota de casi cuarenta puntos. Y lo inusual, lo anómalo, fue precisamente esa extrema debilidad con la cual el santracruceño ingresó a la Casa Rosada cuando el país estaba apenas comenzando a salir de las profundidades de la crisis ocasionada por el estallido de la Convertibilidad, el “corralito bancario”, los turbulentos coletazos de la multitudinaria insurgencia popular del 19 y 20 de diciembre del 2001 cohesionada por la consigna “que se vayan todos” y un desprestigio sin precedentes del régimen democrático, epitomizado por los cinco presidentes que transitaron por la presidencia de la república en apenas una semana. Para colmo, pocos días antes de su jura como presidente el diario La Nación, a través de su editorialista estrella, José Claudio Escribano, hizo público un verdadero ultimátum en el cual, entre otras cosas, decía que con el resultado de las elecciones “la Argentina ha resuelto darse gobierno por un año.” [1] Salvo, advertía Escribano, que Kirchner aceptara el insolente pliego de condiciones remitido al presidente electo y obrara en consecuencia. ¿Cuáles eran esas condiciones? Las previsibles: continuar el alineamiento automático con Estados Unidos pero “sin relaciones carnales”; inmediata visita al embajador de ese país en la Argentina para manifestar lo anterior; reunión con los empresarios para acordar el sendero por el que transitaría la política económica; condenar a Cuba; poner fin a toda tentativa de revisar lo actuado durante la lucha contra la subversión y, finalmente, adopción medidas excepcionales de seguridad.
+Todo este breve prefacio viene a cuento de un tema crucial en el momento actual de la Argentina: las restricciones que enfrenta el gobierno nacional para hacer frente a las presiones del arco opositor y los beneficiarios del agronegocios y todo el complejo primario exportador, amén de las provenientes de Washington -obsesionado por restablecer su control del “patio trasero”, hoy denominado con la expresión más amable de “nuestro vecindario”, Laura Richardson dixit- objetivo que de no neutralizarse convertiría a nuestro país en un protectorado estadounidense. Para justificar esta imposibilidad de defender el interés nacional (hidrovía, telefonía 5G, inversiones en infraestructura financiadas por China, renegociación radical con el FMI en sede de la Corte Internacional de Justicia de La Haya, etcétera) algunos desde el oficialismo y el FdT aducen que “no nos da la correlación de fuerzas”. [2] Pero el gobierno de Néstor Kirchner es la prueba más rotunda de la falacia contenida en ese argumento. El 25 de mayo de 2003 era un presidente que tenía menos de la cuarta parte de los votos populares; una situación compleja en la Cámara de Diputados, mejor en el Senado pero, en ambos casos, con representantes que no le respondían a él sino a la conducción del PJ en manos de Eduardo Duhalde; tenía la prensa hegemónica en contra así como el resto de los “poderes fácticos”, comenzando por “la embajada”. Por eso Escribano decía que el país había decidido elegir a un presidente por un año.
+Debido precisamente a que la “correlación de fuerzas” no es una realidad ontológica inmutable sino el producto de la praxis histórica, Kirchner pudo impulsar una serie de políticas que redujeron los escandalosos niveles de pobreza e indigencia producida por el experimento neoliberal de Menem y sus continuadores de la Alianza; manejó con mano firme la recuperación económica del país; renovó la indigna Corte Suprema de Justicia del menemismo con el apoyo de ambas cámaras del Congreso; restableció los juicios por delitos de lesa humanidad cometidos por la dictadura genocida; canceló por completo la deuda con el FMI; recibió y apoyó a las Madres de Plaza de Mayo en sus luchas. Y poco después de haber concluido su mandato, su sucesora, Cristina Fernández de Kirchner, acabó con la privatización de los fondos de pensión y creó un régimen previsional público, amén de otras políticas de extensión de derechos y empoderamiento popular que se impusieron tras vencer enconadas resistencias. Como si lo anterior no fuera suficiente, Kirchner revolucionó la política exterior de la Argentina estableciendo sólidos vínculos con el Brasil de Lula y la Venezuela de Chávez y, en la Cumbre de las Américas de Mar del Plata, lideró junto a ellos nada menos que el rechazo al ALCA, el principal proyecto geopolítico de Estados Unidos para esta parte del mundo para todo el siglo veintiuno. Y terminó su carrera política, tronchada por una muerte prematura, nada menos que como secretario General de la Unasur. El gobierno al que la derecha le asignaba plazo de vencimiento en un año duró nada menos que doce. El pronóstico del articulista de La Nación fue desmentido por la historia.[3]
+Alberto Fernández, jefe de su Gabinete de Ministros, fue testigo privilegiado de esta verdadera hazaña que demostró que aún las más desfavorables “correlaciones de fuerzas” pueden ser cambiadas. No es una tarea sencilla (como todo en la política) pero está lejos de ser imposible. Depende de la clarividencia y voluntad de la dirigencia, de su capacidad para pergeñar y comunicar una épica de la liberación nacional y de construir -con masas informadas, politizadas y concientizadas- un poderoso instrumento político para sostener desde el llano la batalla que deberá librar el gobierno para cambiar a su favor la “correlación de fuerzas” existente. También de sus concepciones acerca de lo que es la lucha política, muchas veces enturbiadas por vagos espejismos que aluden a improbables e improductivos “consensos”, cuya afanosa búsqueda sólo sirve para diluir la voluntad transformadora que se requiere para encarar grandes empresas políticas. Para despejar estas ilusiones es preciso recordar una y mil veces la definición que Max Weber diera de la política: es una “guerra de dioses contrapuestos”, en donde se hace necesario combinar en dosis variables la persuasión con la coerción; o sea, con el ejercicio pleno de los atributos que el marco institucional deposita en manos del gobierno. En la Argentina, en tiempos tan críticos e inmoderados como los actuales, cuando el mismo destino de la nación está en juego, el “dialoguismo” y la moderación, lejos de ser gestos virtuosos, se convierten, como lo recordara Charles Fourier, en vicios que debe ser combatidos sin cuartel. Quienes lo olviden deberán cargar con las culpas de haber infligido enormes sufrimientos a su pueblo.
+[1] Treinta y seis horas de un carnaval decadente”, en La Nación, 15 de mayo de 2003. Una nota crítica sobre el arrogante y golpista artículo de Escribano se encuentra en Horacio Verbitsky, “Los cinco puntos”, publicado en Página/12 el 18 de mayo y disponible en: https://www.pagina12.com.ar/diario/elpais/1-20265-2003-05-18.html
+[2] Sobre el tema ver nuestro “La correlación de fuerzas como pretexto”, Página/12, 1° octubre 2022. Disponible en: https://www.pagina12.com.ar/486360-la-correlacion-de-fuerzas-como-pretexto
+[3] Una breve recopilación de los logros del gobierno de Néstor Kirchner puede verse en Arturo Fernández, “Las realizaciones trascendentes de la era kirchnerista”, Revista Debate Público, Facultad de Ciencias Sociales, Universidad de Buenos Aires (Junio 2014)</t>
   </si>
   <si>
     <t>Logo especiales-pagina12</t>
@@ -1435,7 +3471,20 @@
     <t>https://www.pagina12.com.ar/548936-amenazan-a-un-sacerdote-en-santiago-del-estero</t>
   </si>
   <si>
-    <t>2023-05-14T03:01:00Z</t>
+    <t xml:space="preserve">Título: Amenazan a un sacerdote en Santiago del Estero
+Chapeau: En una marcha por el acceso a la salud pública
+Subtítulo: Fue en la localidad de Nueva Esperanza. La comunidad se movilizaba tras la muerte de una mujer de 36 años y su bebé, quienes no fueron atendidos de manera adecuada en el hospital local. Rubén Lassaga hizo una denuncia por violencia institucional.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/548936-amenazan-a-un-sacerdote-en-santiago-del-estero/
+Notícia completa (7 blocos):
+La Policía de Santiago del Estero amenazó a Rubén Lassaga, cura en Opción por los Pobres del departamento de Pellegrini, al norte de la provincia. Fue en la localidad de Nueva Esperanza, en medio de una marcha. La comunidad se movilizaba por el acceso a la salud pública luego de las muertes de una mujer de 36 años y su bebé, quienes no fueron atendidos de manera adecuada en el hospital local, en circunstancias que se están investigando.
+La mujer se llamaba Claudia Beatriz Luna. Sus familiares denunciaron mala praxis, responsabizando a una obstetra y un médico. "Hoy fueron al cementerio para hacer otra autopsia", contó Lassaga. Por el hecho, hubo primero una concentración en Las Delicias, comunidad campesina de donde era oriunda la joven, al sur de Nueva Esperanza, el lunes. Y el miércoles se realizó otra marcha en Nueva Esperanza.
+"Hace diez días una mujer de 36 años vino a dar a luz. Por falta de atención médica murieron ella y el bebé. Parece que no la atendieron como correspondía, que demoraron. No es el único caso, van saliendo otros", relató el sacerdote de la parroquia Nuestra Señora de la Merced a Página/12.
+La marcha se dirigió desde la plaza del pueblo hasta el hospital. Allí había policías, tanto de la comisaría local como de la jefatura departamental. En un momento Lassaga ingresó al centro de salud. Allí, el jefe del operativo, "un tal Rivas, comisario inspector", lo señaló con el dedo y le dijo: "a vos te tengo grabado". No sólo él fue amenazado. Los uniformados amedrentaron a varios manifestantes.
+"Alguien de la asamblea le había dicho que yo era cura. Él quiso que yo mediara en la discusión respecto de cómo tenía que ser el diálogo con la directora del hospital. Yo le manifesté que las decisiones las tomaba la asamblea, no yo, y que estaba todo tranquilo hasta que apareció él con la Policía. Entonces se enojó. Amenazó a la gente. Les dijo 'ustedes están todos registrados'."
+El cura hizo una denuncia por violencia institucional. "40 años de democracia y así estamos en Santiago del Estero", cuestionó.
+No es la primera vez que padece consecuencias por participar de luchas sociales. En julio del año pasado, por ejemplo, recibió una amenaza de muerte por acompañar a los campesinos que afrontan conflictos territoriales por el avance de los agronegocios, según denunció el Grupo de Curas en Opción por los Pobres. "Es parte de lo mismo, pero la víctima no soy yo. En este caso son Claudia y su bebé", dijo el cura.</t>
   </si>
   <si>
     <t>Amcham Summit: un panel para repetir ideas neoliberales</t>
@@ -1447,7 +3496,55 @@
     <t>https://www.pagina12.com.ar/547651-amcham-summit-un-panel-para-repetir-ideas-neoliberales</t>
   </si>
   <si>
-    <t>2023-05-09T18:41:12Z</t>
+    <t xml:space="preserve">Título: Amcham Summit: un panel para repetir ideas neoliberales
+Chapeau: La oposición aprovechó la ocasión para hacer campaña
+Subtítulo: Para los principales candidatos del PRO, el encuentro sirvió para hacer gala de sus ideas que recurren al ajuste y las prácticas anti Estado. Legisladores de la oposición hicieron eje en discutir proyectos en el Congreso, aunque sin aclarar que durante meses mantuvieron un boicot al Parlamento.
+Editoria: Economia
+Tags: Amcham, diario
+URL: https://www.pagina12.com.ar/547651-amcham-summit-un-panel-para-repetir-ideas-neoliberales/
+Notícia completa (42 blocos):
+La Cámara de Comercio de los Estados Unidos en Argentina (Amcham Argentina) realizó este martes una nueva edición del "Amcham Summit", con la participación de empresarios, funcionarios, dirigentes políticos y referentes gremiales que disertaron sobre "los ejes fundamentales que atraviesan al desarrollo de la Argentina". Entre los expositores estuvo Patricia Bullrich, que aprovechó para hacer campaña y dijo que "no importa" si su compañero de fórmula es o no del PRO sino que "no sea tibio y no tenga miedo" para realizar "el trabajo duro" que llevará adelante en caso de llegar al poder.
+Luego de esas declaraciones, que tienen como principal destinatario a Horacio Rodríguez Larreta, aseguró que existe un “contrato previo” en Juntos por el Cambio (JxC) para evitar que las tensiones sigan después de las PASO. “No vamos a hacer el papelón de River-Boca”, señaló la exministra de Seguridad, quien anticipó que en caso de perder las primarias contra Horacio Rodríguez Larreta va a ser "seria y responsable" y va a poner "toda la fuerza" para que la coalición opositora gane.
+"La primaria tiene un contrato previo, que no está escrito: el que gana tiene que ser muy generoso y el que pierde tiene que poner toda su fuerza para que esa fuerza política gane. Ese es el acuerdo que está implícito, sino sos el que se lleva la pelota de la cancha", subrayó. Por otro lado, ante una pregunta del presentador Alejandro Fantino, volvió a hacerse la desentendida sobre el testimonio de una exasesora de Gerardo Milman, quien aseguró que en las oficinas de la candidata borró todo el contenido del celular en el marco de la investigación por el atentado contra Cristina Kirchner. "Bullshit", fue la única respuesta de Bullrich.
+En otro tramo de su intervención, la exminsitra sostuvo que su mandato, en caso de ganar, se basará en “Achatar y achicar”, y allí adelantó que solo tendrá entre ocho y diez carteras, aunque no mencionó cuáles serían las que eliminaría. También anticipó que quitará el cepo al dólar, que tendrá un tipo de cambio único, que convertirá los planes sociales en seguro de desempleo y que impulsará un recorte en las indemnizaciones de los trabajadores formales, ya que “es un pasivo brutal para las empresas”.
+[H2] La respuesta de Horacio Rodríguez Larreta
+Horacio Rodríguez Larreta, también presente en el foro de este martes, le devolvió la gentileza al momento de exponer: “Yo voy a estar en el mismo desayuno que ella y le voy a servir el café”, afirmó el jefe de Gobierno porteño. “Tengo la mejor onda con ella”, y “la mayoría de los equipos técnicos son comunes”, dado que Juntos por el Cambio se está preparando “para gobernar todos juntos”, aseveró.
+El mandatario porteño también aprovechó su participación para volver a defender a Patricia Bullrcich tras el tuit de Cristina Fernández de Kirchner sobre las acusaciones que involucran a la exministra de Seguridad en una supuesta operación para borrar datos del teléfono de una testigo clave en la investigación de intento de magnicidio del 1 de septiembre. "Hoy a la mañana salí a defenderla a Patricia de la calumnia que está impulsando la vicepresidenta, salí a defenderla porque creo en ella", remarcó.
+"Estuve ayer reunido con ella, la respeto como dirigente, tiene experiencia, algo que valoro mucho. La Justicia tiene que investigar todo, son dos cosas distintas, sin injerencia de la política, no estoy de acuerdo en usar eso para calumniar políticamente por eso la salí a defender", añadió.
+En su exposición, Rodríguez Larreta incluyó algunas pistas sobre el ministro de Economía que incorporaría en caso de resultar victorioso en las elecciones de este año. "Tiene que haber una sana combinación entre gente con experiencia, un ministro de Economía con poder integral, plenipotenciario, tipo Massa, Lavagna o Cavallo. Como era el ministro de Economía siempre, con todo el poder", reflexionó, con una ¿crítica? al esquema que mantuvo Mauricio Macri que desembocó en la llegada del Fondo Monetario Internacional.
+"Necesitamos a alguien que vele por el equilibrio general y en la economía eso es central y más en una Economía en crisis. Necesitamos un ministro de Economía de verdad, que tenga toda la botonera que hace al funcionamiento de la Economía. Y lo digo yo que voy a ser el primer presidente de la Argentina economista", manifestó.
+También habló de la política cambiaria y dijo que "el tipo de cambio tiene que tender a ser, lo antes posible, único. Hoy, pesos dividido dólares te da responsable $4000, $3800, tendrías una devaluación del 900%", aseguró sobre la propuesta de Javier Milei. Ante la consulta de un periodista sobre el precio del dólar a fin de año, respondió que él no era economista, así que no podía saberlo. Al darse cuenta del error, se corrigió: "Sí, soy economista pero no lo sé. Me apuré, un blooper, un fallido. Ni yo, ni ninguno de ellos que está acá y sabe más que nosotros sabe cuánto va a estar el dólar a fin de año".
+[H2] Apertura de Amcham
+La apertura del evento estuvo a cargo del presidente de la la Cámara de Comercio de Estados Unidos en la Argentina (Amcham Argentina), Facundo Gómez Minujin. "No hay que desaprovechar la gran oportunidad que se nos presenta al momento de elegir a nuestros representantes y el sector privado es parte de la solución, debemos dejar las dudas e invertir en la Argentina que viene", señaló Gómez Minujin, al indicar que "ni los empresarios prebendarios ni las ideas individuales resuelven las crisis estructurales".
+"Si el país comienza a tener reglas claras y estables, se manifiesta un entorno ético y transparente, nosotros, como líderes activos del sector privado, debemos dejar las dudas e invertir para ser protagonistas de la Argentina que se viene. Debemos asumir riesgos y mantenernos positivos en el pensamiento de que Argentina puede cambiar y va a mejorar", remarcó. Y sumó: "estamos convencidos en Amcham que una vez que se elimine el déficit fiscal, se le dé verdaderamente independencia al Banco Central y a su directorio, y se recorte el excesivo gasto del Estado, el país comenzará a crecer de manera constante y beneficiosa para toda la población".
+La clave, subrayó, es “colaborar en una agenda de trabajo entre las empresas y el gobierno argentino, enfocándonos especialmente en industrias como energía, minería, petroquímica, agronegocios, electromovilidad, economía del conocimiento y turismo".
+[H2] Relación entre Estados Unidos y Argentina
+El evento contó con un panel conmemorando el 200° aniversario de la relación bilateral entre Estados Unidos y Argentina. El embajador estadounidense en Buenos Aires, Marc Stanley, y el embajador argentino en Washington, Jorge Argüello, valoraron el diálogo y la colaboración entre ambos países así como la potencialidad de la relación a futuro, aunque el diplomático argentino reclamó por las restricciones comerciales que Estados Unidos mantiene desde la administración del expresidente Donald Trump.
+“Argentina puede ser parte en la solución y fortalecer su economía al mismo tiempo, colaborando con los Estados Unidos y otros países para llevar alimentos y combustible al mundo", puntualizó Stanley. “Es un país que a tiene excelentes recursos como el campo, el petróleo y el gas; los minerales, y el activo más importante: el capital humano”, destacó.
+En ese marco, indicó que se siente “bullish” –concepto financiero que se utiliza al tener una actitud optimista respecto al mercado- sobre las perspectivas de Argentina, una vez inaugurado el Gasoducto Néstor Kirchner y superada la sequía. “Creo que este país se va a encarrilar de nuevo. No hay razón de que no esté entre las veinte principales economías del mundo en los próximos cinco años”, opinó Stanley.
+Argüello, en tanto, calificó el estado de la relación entre ambos países como “muy positivo” y dijo que la misma llegó “a su punto máximo” tras la reciente cumbre bilateral que mantuvo el presidente Alberto Fernández con su par de Estados Unidos, Joe Biden, en la Casa Blanca a fines de marzo.
+“Quiero destacar el enorme espíritu de colaboración que la Argentina ha encontrado de los Estados Unidos en la administración del presidente (Joe) Biden en la búsqueda de una solución que nos aqueja hoy que nos golpea fuertemente que son las consecuencias de la sequía que nos coloca en una situación difícil y precaria”, afirmó el embajador argentino, haciendo referencia a las negociaciones en curso con organismos multilaterales.
+En su disertación, sin embargo, aprovechó para cuestionar a quienes critican el “desembarco” de China en el continente y pidió "destrabar" cuestiones vinculadas con el comercio con Estados Unidos. “Veo que algo que comenzó durante la gestión de Donald Trump no cesa y me refiero a los llamados remedios comerciales, como las medidas ´antidumping´ y compensatorias que adopta el gobierno, y la aplicación de criterios de seguridad nacional propios de la resolución 232 que no cesan en toda la región”, indicó el embajador, que advirtió que un 25% de las exportaciones argentinas a Estados Unidos se encuentran afectadas incluyendo al "biodiesel, la miel, caños sin costura, jugo de uva, jugo de limón y mosto”.
+Arguello también llamó la atención sobre la posibilidad de que Argentina “deje de ser el principal exportador de litio a los Estados Unidos” debido a la Ley de Reducción de la Inflación (IRA) por parte de la Casa Blanca.
+[H2] "Fortalecer el Congreso"
+Del encuentro, que se realizó en un hotel de Puerto Madero, también participaron legisladores nacionales de la oposición, que debatieron sobre la importancia de la democracia, a 40 años de su instauración, y propusieron "fortalecer el rol del Congreso de la Nación para establecer acuerdos básicos a largo plazo", sin reconocer que son ellos quienes han trabado en los últimos meses el funcionamiento legislativo como boicot al juicio político a la Corte Suprema.
+Los diputados del PRO Silvia Lospennato y Emilio Monzó, el senador radical Alfredo Cornejo, y la legisladora del Interbloque Federal Graciela Camaño expusieron en el panel "40 años de democracia Argentina" del "Amcham Summit".
+Al disertar sobre el funcionamiento del Parlamento, Camaño lamentó la falta de actividad del Congreso y consideró "inédito" que "no se dialogue". La diputada remarcó que "no se trata sólo de dialogar sino de tener un intercambio fructífero", entre los integrantes de las fuerzas políticas que cuentan con representación legislativa.
+"Si no hay agenda, ni dirigentes que tengan capacidad de diálogo, el Congreso no está elevando la voz de sus representados, con un muy mal funcionamiento. Hoy no se respeta el reglamento y eso complica su funcionamiento", afirmó la legisladora del bloque Identidad bonaerense ante los empresarios.
+Por su parte, Monzó consideró que el ciudadano tiene "mucha incertidumbre" frente a la "fragmentación" que se verifica actualmente en la sociedad y sostuvo que esa situación "es aprovechada por aquellos que proponen recetas simples".
+En ese sentido, el extitular de la Cámara de Diputados señaló que hay quienes “manipulan a las diferentes comunidades, radicalizan y alejan la posibilidad de acuerdos". Esa situación se ve reflejada en el Congreso, observó, “que está destrozado por los tuits que reproducen discursos que vienen directo desde las redes.
+Lospennato, por su parte, advirtió que "no va a haber acuerdo si primero no recuperamos el diálogo político". Actualmente, planteó la legisladora, "hay pocos incentivos para la negociación" en el Congreso, porque “quien va a negociar es tildado de traidor, por eso sale la peor ley posible", subrayó, y reflexionó: "No va a haber plan de estabilización ni propuesta exportadora si primero no frenamos el péndulo de eliminar al otro".
+Asimismo, Lospennato sostuvo que tras 40 años de democracia "tenemos que abandonar idea mágica que nos vamos a poder imponer nuestras ideas al otro (...) Si reconocemos al otro, si reconocemos que no hay una solución mágica y dejamos de buscar líderes mesiánicos, tal vez recuperemos el diálogo político", puntualizó.
+En tanto, Cornejo sostuvo que "el poder político representado en el Poder Ejecutivo no ha generado una agenda positiva de los temas reales en los últimos 20 años". Por ejemplo, mencionó, "no hemos tenido deliberación sobre preservación de la moneda”. Y concluyó, sin autocrítica alguna: “El populismo está deteriorando la democracia con debates inconducentes".
+[H2] Scioli tendrá candidato a vice "federal"
+El embajador argentino en Brasil y precandidato a presidente por el Frente de Todos (FDT), Daniel Scioli, anunció este martes que estará acompañado en su fórmula por un postulante federal. "La fórmula va a ser federal porque siempre tuve un compromiso con el interior del país. Una fórmula pensada para gobernar y no solo pensando en ganar una elección", dijo al participar este mediodía del foro de Amcham.
+"Ya tengo pensado mis equipos para gobernar porque tengo una experiencia que se fue renovando y fui aprendiendo constantemente. Algunos pensaron que Brasil era el retiro y no fue así, sino que fue lo que ha sido la oportunidad de aplicar la agenda del desarrollo que propuse en el 2015", cuando también fue candidato presidencial por el Frente para la Victoria.
+También se refirió la competencia interna en el FDT. "Me parecen muy importante las PASO porque no quiero que me elijan en una reunión política entre cuatro paredes. Quiero tener respaldo y la legitimidad porque después tengo que hacer varias reformas", expresó. "Cuando decidí presentarme como candidato fue porque tomé la decisión de presentarme para competir, pero no para desafiar o ir contra alguien, sino para superarlo, como fue cada vez que corría" en las competencias de motonáutica", agregó.
+[H2] Rosatti, también presente
+El presidente de la Corte Suprema de Justicia, Horacio Rosatti, también expuso en Amcham, donde recordó que el máximo tribunal no está en la función pública "para hacer nuevas amistades si no para cumplir con la Constitución". En ese marco, defendió el trabajo del cuerpo al señalar que en los "últimos años" sus integrantes tomaron decisiones que "no han agradado al poder de turno".
+"En los últimos años hemos tomado decisiones que no han agradado al poder de turno. No venimos a la función publica para hacer nuevas amistades si no para hacer cumplir la Constitución y garantizar una estabilidad jurídica que permita pensar a futuro", señaló al disertar en el panel "Institucionalidad y republicanismo".
+"Vemos el surgimiento y la expansión de un estado dentro de otro. Y no me refiero a la grieta que es percibir distinto el mismo país, sino a uno dentro del otro con su propia ley, justicia, policía e interpretación. Es el caso del estado narco, que constituye el desafío de pensar un futuro en unidad dentro de la heterogeneidad", analizó el titular del máximo tribunal.
+"La primera regla que tenemos que respetar es que, más allá de las diferencias, debemos estar debajo de la Constitución argentina", afirmó el presidente de la Corte, quien actualmente afronta junto a los otros integrantes de la Corte --Carlos Rosenkrantz, Ricardo Lorenzetti y Juan Carlos Maqueda-- un proceso por presunto "mal desempeño" y "abuso de autoridad" en el marco de la Comisión de Juicio Político de Cámara de Diputados.</t>
   </si>
   <si>
     <t>La reivindicación del constitucionalismo social</t>
@@ -1459,7 +3556,18 @@
     <t>https://www.pagina12.com.ar/547025-la-reivindicacion-del-constitucionalismo-social</t>
   </si>
   <si>
-    <t>2023-05-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: La reivindicación del constitucionalismo social
+Chapeau: Debate sobre la Constitución de 1949 en el stand del Grupo Octubre de la Feria
+Subtítulo: El economista José Sbattella, el jurista Jorge Cholvis y el sociólogo Eric Calcagno participaron de la presentación del libro El campo popular saluda a la Constitución Nacional de 1949, en el que diversos autores prologaron el texto proscripto por la autodenominada "Revolución Libertadora".
+Editoria: Cultura y Espectáculos
+Tags: Feria del Libro, printed-edition, feria-del-libro
+URL: https://www.pagina12.com.ar/547025-la-reivindicacion-del-constitucionalismo-social/
+Notícia completa (5 blocos):
+“¿Por qué sale este libro? ¿Por qué escribimos cada uno de los artículos que prologan esta nueva edición de ‘la constitución proscripta’?” pregunta José Sbattella al auditorio que lo escucha en el stand del Grupo Octubre, en la Feria del Libro de Buenos Aires. Sbattella "economista, docente y militante peronista" --se presenta--, conoce la respuesta. Y junto al jurista Jorge Cholvis, y al sociólogo Eric Calcagno –ex embajador en Francia, diputado y senador nacional por la provincia de Buenos Aires--, explican los alcances y fundamentos de la Constitución de 1949 proscripta por la dictadura militar de 1955. Y reemplazada por la anterior de 1853 --de raíz liberal--, reformada en 1994.
+El debate tiene un propósito: la presentación de libro El campo popular saluda a la Constitución Nacional de 1949 (Nueva Agenda, 2022). Y propone analizar la vigencia del constitucionalismo social en la Argentina, y los alcances de esta norma "¡que está viva!", advierte Calcagno. Se remite a la coronación de Carlos III en Inglaterra y señala: "Allí no hay Constitución". Para Calcagno "es necesario saber cuál es la constitución real de un país, y en qué se basa material y simbólicamente, como país".
+Así se entiende que "un país pensado como un protectorado productor de materias primas" --sostiene--, colisione con la idea de país que propone "independencia económica --apunta Cholvis--, soberanía política y justicia social". El "agronegocio o la minería extractiva --señala Calcagno-- generan violencia y más desigualdades. Y una Constitución, sirve como un manual de resolución de estos conflictos", aporta.
+La nueva publicación plantea la necesidad de recuperar el valor de este “cuerpo normativo, que resume un proyecto político con un vértice jurídico” señala Cholvis. Ese marco fue “proscripto” –puntualiza Sbattella-- porque “daba inicio a un proceso de desconexión del capitalismo global”, resume. Equipara la desconexión al eufemístico “desacople” del discurso actual en torno a los mercados. Y expone la necesidad de volver sobre “el constitucionalismo social” que planteaba esta ley madre: “Un ejemplo en el mundo por incorporar los derechos de los trabajadores”, enfatiza Sbattella.
+La pieza fue reeditada con más de cien artículos que la prologan. Entre los autores, junto a los presentadores del panel, figuran entre otros Adolfo Pérez Esquivel, Eugenio Zaffaroni, Eduardo Barcesat, Jorge Rachid, Víctor Hugo Morales. E incluye textos de Arturo Sampay –ideólogo de la norma de 1949--, de Juan Domingo Perón y de Eva Perón, y del teniente general Juan José Valle, fusilado en 1956, por defender el régimen democrático que se expresaba en la emblemática Constitución de 1949.</t>
   </si>
   <si>
     <t>Logo cultura-y-espectaculos</t>
@@ -1474,7 +3582,30 @@
     <t>https://www.pagina12.com.ar/546980-paraguay-la-detencion-de-payo-cubas-y-lo-que-se-viene</t>
   </si>
   <si>
-    <t>2023-05-07T20:23:14Z</t>
+    <t xml:space="preserve">Título: Paraguay, la detención de Payo Cubas y lo que se viene
+Chapeau: El excandidato presidencial está detenido e imputado por cinco delitos
+Subtítulo: Los fiscales informaron que ordenaron la captura del político ultraderechista porque en el pasado no se había sometido a la Justicia en otras causas. Decenas de sus seguidores también fueron arrestados en diferentes puntos del país.
+Editoria: El Mundo
+Tags: Paraguay, Santiago Peña, printed-edition, santiago-pena, diario
+URL: https://www.pagina12.com.ar/546980-paraguay-la-detencion-de-payo-cubas-y-lo-que-se-viene/
+Notícia completa (17 blocos):
+Paraguay no parece que tendrá una vida apacible hasta el 15 de agosto. Ese día asumirá la presidencia Santiago Peña y quizás descomprima o no la nerviosa vigilia que se respira en las calles y rutas del país. La detención del excandidato Payo Cubas por perturbar el orden público expuso con nitidez una situación. El robusto 23 por ciento de los votos que sacó en la elección no se compadece con la módica capacidad de movilización de sus partidarios, aunque esta sí es suficiente para mantener en vilo a la población.
+[H3] Elecciones en Paraguay: Santiago Peña ganó con holgura y mantuvo la hegemonía de los colorados
+La tensión política que generaron las protestas bajo la consigna de que hubo “fraude”, cedió en parte tras unos pocos incidentes, piquetes y la mansa actitud del líder de Cruzada Nacional que al ser arrestado declaró: “No va a haber quilombo”. Pese a la señal que dio, y los discretos apoyos que recibió de otros dirigentes —el principal derrotado en los comicios, Efraín Alegre, pidió su liberación— deberá responder por cinco delitos que le imputa la justicia.
+Sobre Paraguayo Cubas pesan denuncias que van desde la tentativa de impedir las elecciones a coaccionar a los órganos constitucionales. Dos fiscales, Jorge Arce Rolandi y Francisco Cabrera, abrieron una investigación contra él. El viernes pasado mientras hacía la transmisión en vivo de uno de sus actos, lo detuvieron en San Lorenzo, a unos 15 kilómetros de la capital.
+Todo quedó filmado, incluidas sus acusaciones contra “los que roban los votos” y que “están tranquilamente libres”. Recordó además que ya había sido recluido dos veces en la cárcel de Tacumbú, la más grande del país y cuya historia llegó a Netflix en 2020. Payo no cuestionó el procedimiento judicial. “Me parece bien el protocolo policial y ya sé luego lo que me espera”, agregó. Mucho más dócil y tranquilo de lo que acostumbra, como si meditara sus futuros pasos.
+El comisario Carlos Benítez, director de Prevención y Seguridad de la Policía Nacional, dijo que Cubas permanecería detenido en la llamada Agrupación Especializada, un cuartel ubicado en Asunción, donde suelen ser alojados pesos pesado del delito, integrantes de las fuerzas de seguridad y hasta políticos. No es una cárcel convencional y su perímetro fue reforzado ante posibles manifestaciones de los partidarios del inclasificable candidato que salió tercero en los comicios del 30 de abril.
+Los medios locales reflejaron cierto grado de psicosis ante movimientos de tropas, pero que en realidad fueron un despliegue por el 212° aniversario de la independencia del Paraguay (se festeja el 14 de mayo) desde Piribebuy hasta zonas cercanas a la capital. Sobre Cubas pesan imputaciones por delitos que tienen penas de hasta diez años de prisión, como el de accionar contra órganos constitucionales. Los fiscales informaron que ordenaron su detención porque en el pasado no se había sometido a la Justicia en otras causas.
+Decenas de sus seguidores también fueron arrestados en diferentes puntos del país. Los últimos 34 en el Departamento de Alto Paraná, donde se encuentra Ciudad del Este, en la triple frontera. Se los acusa de haber destruido una camioneta policial y de exigir dinero a cada automovilista —entre 20 mil y 50 mil guaraníes, unos 1.500 y 4.000 pesos argentinos— para liberar las rutas que habían cortado en esa zona, informó la prensa paraguaya.
+El candidato antisistema que hoy desplazó con su situación judicial las principales noticias políticas de las portadas, también se metió en problemas con los profesionales de su propia actividad —es abogado— y los periodistas. Desde la Asociación de Exalumnos de la Facultad de Derecho de la Universidad Nacional de Asunción (UNA) y expresidentes del Centro de Estudiantes (Ceduna) expresaron su rechazo a Cubas: “Nuestro repudio total hacia los actos fuera de la ley perpetrados por nuestro colega, el abogado Paraguayo Cubas Colomés”, dice un texto que difundieron.
+La Mesa para la Seguridad de Periodistas del Paraguay (MSP), que integran gremios y comunicadores sociales, presentó una denuncia formal por agresiones contra varios trabajadores de prensa ante la Unidad Fiscal de Ejecución Penal. Una investigación de la Policía Nacional especializada en cibercrimen reveló también que hubo más de mil mensajes que circulan en redes sociales de presuntos simpatizantes de Cubas con amenazas a periodistas y medios y además unos 30 perfiles virtuales truchos que se usaban como fachada.
+Con una parecida matriz operativa y utilización de las redes sociales, pero menor capacidad de movilización y daño que los golpistas partidarios de Jair Bolsonaro en Brasil, los fieles del político paraguayo podrían ir perdiendo influencia en los próximos días. Además, no tienen el apoyo de las fuerzas armadas, ni de las iglesias evangélicas, ni de los empresarios del agronegocio que sí apostaron fuerte por el ultraderechista que presidió el gigante de la región hasta el 31 de diciembre de 2022.
+Cuando era conducido por la comitiva policial en San Lorenzo que lo arrestó, Cubas logró extender la transmisión en vivo de su detención durante casi 15 minutos. Su show eclipsó las próximas decisiones del presidente electo Peña que ya se apresta a formar su gabinete de ministros, los pedidos para que Efraín Alegre, el liberal derrotado con amplitud en la elección, abandone la presidencia de su partido y la interna del Partido Colorado entre diputados y senadores que responden al actual mandatario Mario Abdo Benítez y a Horacio Cartes.
+Paraguay no da señales de encaminarse hacia una insurrección de votantes indignados, lúmpenes desclasados y jóvenes que rechazaron al oficialismo para apoyar a un candidato ahora caído en desgracia. Su estabilidad política parecería garantizada. Ya sea por la omnipresente fortaleza del Partido Colorado, su contundente victoria en las urnas y el camaleónico respaldo de Estados Unidos. En los días previos a la votación su embajador Marc Ostfield apoyó de manera abierta a las fuerzas de la Concertación, denunciando al hombre fuerte del país, el expresidente Cartes, por ser “significativamente corrupto”. Ahora deberá convivir con Peña, su ahijado político.
+Sobre esta aparente contradicción transcurrirá la relación bilateral con EE.UU que tiene un peón de su geopolítica en el país, Taiwán. La provincia que el gobierno de Beijing considera rebelde y mantiene exclusivos lazos comerciales con Paraguay desde la dictadura de Alfredo Stroessner. Una isla que oficia de tapón para frenar la expansión de China en Sudamérica.
+gveiga@pagina12.com.ar
+[H3] Seguí leyendo
+[H3] Elecciones Argentina 2023: resultados y quién gano en Jujuy, La Rioja y MisionesOtro mal trago electoral para Milei</t>
   </si>
   <si>
     <t>Gustavo Veiga</t>
@@ -1489,7 +3620,47 @@
     <t>https://www.pagina12.com.ar/546257-una-colonia-agroecologica-en-el-corazon-del-modelo-sojero</t>
   </si>
   <si>
-    <t>2023-05-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: Una colonia agroecológica en el corazón del modelo sojero
+Chapeau: Tierras públicas para la producción de alimentos saludables
+Subtítulo: Nueve hectáreas de tierras públicas sin uso se convirtieron en quintas para la producción de alimentos saludables en Tapalqué, donde la UTT inauguró una colonia agroecológica. La gobernación bonaerense, a través del ministerio de Desarrollo de la Comunidad, construyó las viviendas de los colonos, que se mudaron desde el Conurbano bonaerense y Mar del Plata. Y el Estado nacional, a través del Aabe, otorgó al municipio el permiso de uso de las tierras fiscales inactivas.
+Editoria: El País
+Tags: Soberanía alimentaria, Unión de Trabajadores de la Tierra, Agroecología, Axel Kicillof, printed-edition, soberania-alimentaria, union-de-trabajadores-de-la-tierra, agroecologia, axel-kicillof, diario
+URL: https://www.pagina12.com.ar/546257-una-colonia-agroecologica-en-el-corazon-del-modelo-sojero/
+Notícia completa (34 blocos):
+En Tapalqué, sobre tierras del Estado en desuso, un grupo de familias de la Unión de Trabajadores de la Tierra comenzó a producir verduras agroecológicas. Eso permite a la ciudad abastecerse de hortalizas frescas, cosechadas en la zona. Tapalqué no las tenía. Las verduras que consumían los hogares debían ser llevadas hasta allí desde los mercados centrales de Buenos Aires y Mar del Plata, con un viaje de más de 300 kilómetros que encarecía los precios.
+Corregir esa falta podrá ser la más lógica de las medidas, pero necesitó de una decisión política jugada, porque implicó nada menos que la creación de una colonia. El Estado nacional cedió tierras, 9 hectáreas que le fueron entregadas en comodato por 15 años a la municipalidad. El gobierno local a su vez firmó un convenio con los quinteros de la UTT, que se mudaron a vivir allá.
+Una iniciativa no necesariamente bienvenida, como mostró el reciente conflicto en Chapadmalal, donde hubo vecinos que se opusieron y denunciaron “usurpación” y “toma de tierras” ante a un proyecto del mismo tipo.
+Qué decir de los riesgos que suponía llevar a una localidad de la Pampa Húmeda a familias del conurbano, ¡familias bolivianas!
+“Para una parte de la población, por más explicaciones y argumentación que demos, siempre vamos a ser negros de la villa”, apuntan en la UTT. Y ¿qué hay de la alteración que supone dar a los más pobres un pedazo de las tierras más productivas del país?
+La hectárea por acá no sólo vale oro, sino que un orden invisible asigna su destino; un orden que no está sometido a votación. Cada metro cuadrado se dedica a la soja o la cría de ganado. Tapalqué es, en ese sentido, el corazón del modelo agroexportador.
+[H2] Planificación
+“Esta es una de las políticas públicas que proponemos desde la UTT”, dice Agustín Suárez, referente de esa organización, mientras la camioneta avanza por la ruta.
+Cuenta que la creación de la colonia llevó cuatro años y que hubo mucha fuerza de voluntad puesta en lograr este destino. Para la UTT significó una inversión de recursos humanos y económicos: darse una estrategia de trabajo de cara a la comunidad y poner mucho en la adecuación del predio, porque frente a los imprevistos del clima tuvieron que implementar mejoras, un pozo para tener agua, una bomba, un sistema de riego artificial; y conseguir fondos para cada una de estas cosas.
+“Estas quintas se armaron con mucho voluntarismo; lo que queremos es que las próximas salgan por impulso de una política pública”, agrega Suárez. Quiere decir que la colonia agroecológica es un modelo, un ejemplo que buscará ser llevado a otras localidades, prender en otras intendencias.
+Porque la UTT es una organización de productores sin tierra. Los quinteros las alquilan o acceden a ella mediante instituciones que vienen del fondo de la historia colonial: son jornaleros o medieros. “Lo que define al sector es la autoexplotación, que se deriva de no ser dueño de la tierra. Para poder pagar los alquileres se trabaja en condiciones que recuerdan la esclavitud y se vive en condiciones peores que en la villa, sin agua potable, sin electricidad, sin hospital, sin escuelas”.
+[H2] ¿Por qué en Tapalqué?
+No más entrar a la ciudad de Tapalqué se ve un Frigorífico Municipal, abierto por la intendencia en 2013. También es del Estado el peladero de pollos (2015), y la Usina Láctea, creada por la intendencia en el 2000, a partir de los planes Jefes de Hogar, y hoy concesionada a una cooperativa. El cine es municipal, también los es el Hotel, que gestiona otra cooperativa formada por jóvenes, y la sala de extracción de miel. En estos días se agregó un complejo termal -aún en construcción- que activará la llegada del turismo.
+En fin: un conjunto que impresiona. Acá Javier Milei moriría de un ataque al hígado.
+El intendente Gustavo Cocconi, peronista, le echa la culpa al modelo: la concentración económica, el agronegocio, la producción destinada a exportar, no derrama. A Tapalqué, rodeada de riqueza, le faltaban puestos de trabajo. Y a eso se debe que tantas actividades hayan requerido de la intervención del estado.
+Todo lo no rentable para el mercado fue recuperado por el municipio, y lo que no existía fue promovido con el fin de sostener el empleo.
+La creación de la colonia, propuesta por la UTT, empalmó a través de esa historia propia de Tapalqué con el núcleo kirchnerista del peronismo bonaerense.
+[H2] “Un caso testigo”
+A la inauguración de la colonia concurrió una parte del gabinete de Axel Kicillof, como los ministros Andrés Larroque (Desarrollo de la Comunidad), Javier Rodríguez (Desarrollo Agrario) y el subsecretario de Hábitat, Rubén Pascolini. Desde el Estado Nacional participó Matías Federici, director de Asuntos Comunitarios de la Agencia Administración de Bienes del Estado, que dió en comodato las 9 hectáreas donde se levantó la colonia. También estuvo el intendente de Ensenada, Mario Secco.
+En el acto de inauguración las familias recibieron las llaves de sus nuevas casas. “Esto es un caso testigo para nosotros”, dijo Federici, de la Aabe.
+“¿Qué capital vendría a invertir en viviendas o en agroecología?” se preguntó a su vez Andrés Larroque, que recordó que “el Estado per se tampoco lo hace: lo hacen los gobiernos con determinadas convicciones políticas”.
+[H2] Los colonos
+“Yo no quería venir”, confesará Juvenal Ordóñez poco después. El quintero de la UTT dice que no sabe por qué. O sí: “Tenía que dejar a mis amigos, los partidos de fútbol. No es fácil dejar el lugar donde se vivió por 30 años”.
+Juvenal nació en Tarija, ya había pasado por una primera migración en el ‘91, así que dejar las afueras de Mar del Plata para venir a Tapalqué fue su segundo desarraigo. En los primeros meses, de cara al campo abierto de la pampa le preguntaba a su mujer: “¿Qué vamos a hacer en este pueblo donde no hay nada?”. Se sentía ajeno.
+Tapalqué tenía su club de fútbol y con el correr de los días Juvenal se acercó, dió varias vueltas y finalmente se puso la camiseta, para alivio de Lucila. Había sido ella la que insistió en venir, la que puso su número en el sorteo -las familias de la colonia fueron definidas así, porque había muchos interesados- y los trajo, a Juvenal y un hijo adolescente.
+Lucila dice que estuvo segura de traerlo “por un tema de salud”: “Se estaba enfermando para pagar el alquiler”. Llegaron a pedirles 5 mil dólares semestrales por 5 hectáreas, a pagar no en pesos sino con billetes estadounidenses. Por eso trabajaban desde la madrugada, en el lote alquilado, para pasar a la tarde a trabajar para otros quinteros.
+Ahora están a cargo de dos hectáreas en la que siembran acelga, lechuga, aromáticas, en fin: todo lo de la huerta. Y frutillas. Lucila las ofrece. Son tan rojas y dulces como podía esperarse.
+[H2] Sequía, piedras y el bicho moro
+El comodato les sacó de encima el alquiler. Sin embargo, Lucila cuenta que los esperaban otras desgracias. La sequía, por supuesto. Luego, a cuatro meses de llegar, la piedra les rompió todo y tuvieron que volver a empezar desde cero. Necesitaron que la UTT les diera semillas en préstamo.
+“La gente desconfiaba de que fuera producción agroecológica, así que nos llevó tiempo empezar a tener ventas”. Y en el verano apareció el bicho moro, que se come las hojas. “No lo conocíamos y tuvimos que encontrar conectándonos con otros compañeros qué preparado agroecológico podía ahuyentarlo”.
+En esos meses difíciles, ella buscó trabajo limpiando casas, mientras Juvenal sacaba adelante la quinta. Les pasaron otras cosas: una solicitada de la oposición más conservadora, anclada en el radicalismo y el PRO, acusó a la intendencia de hacer casas para gente que venía de afuera y no para los tapalquenses. Más tarde, otro sector opositor les sacó fotos y denunció que vivían en condiciones infrahumanas -aún no estaban terminadas sus casas y residían en un vagón-. Y atravesaban el proceso de integración de la propia Colonia, en la que algunos vienen de Mar del Plata y otros de Florencio Varela.
+Este sábado, finalmente, todo parece mejor encaminado. Los colonos reciben las llaves de sus casas, los surcos tienen riego artificial y en la estación, donde todos los sábados ponen su puesto de venta, los vecinos de Tapalqué hacen colas para comprar las verduras agroecológicas. Los conflictos seguramente están, pero sin llegar a mayores.
+Otros proyectos esperan seguir el mismo camino en otras localidades bonaerenses como Castelli, Mercedes y Cañuelas (en este caso sobre un predio sindical, del Smata).
+Son proyectos que van acompañados de la recuperación de derechos de los trabajadores de la tierra, que por primera vez desde la creación de la primer colonia -en Jáuregui, Luján nacida en un ya lejano 2015 por la fuerza de una toma-, este año se tomaron vacaciones pagas. A tener un techo, un piso de protecciones frente a los imprevistos, ingresos para sacar la cabeza de abajo del agua van sumando así ese derecho escaso en nuestros días, el del tiempo libre. Qué hacer con el ocio también puede ser un motivo para nuevos problemas: pero ese, en todo caso, es tema de otra nota.</t>
   </si>
   <si>
     <t>Lula celebró el 1 de Mayo con críticas al Banco Central en manos de un bolsonarista</t>
@@ -1501,7 +3672,24 @@
     <t>https://www.pagina12.com.ar/545331-lula-celebro-el-1-de-mayo-con-criticas-al-banco-central-en-m</t>
   </si>
   <si>
-    <t>2023-05-02T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula celebró el 1 de Mayo con críticas al Banco Central en manos de un bolsonarista
+Chapeau: El presidente de Brasil confirmó un aumento del salario mínimo
+Subtítulo: "No podemos seguir viviendo en un país donde la tasa de interés no controla la inflación; controla, de hecho, el desempleo", dijo durante el acto en San Pablo.
+Editoria: El Mundo
+Tags: Brasil, Luiz Inácio Lula da Silva, Día del Trabajador, printed-edition, luiz-inacio-lula-da-silva, dia-del-trabajador, diario
+URL: https://www.pagina12.com.ar/545331-lula-celebro-el-1-de-mayo-con-criticas-al-banco-central-en-m/
+Notícia completa (11 blocos):
+El presidente de Brasil, Luiz Inácio Lula da Silva, aprovechó el acto del 1 de mayo junto a las centrales sindicales del país para volver a criticar al Banco Central por la tasa de interés, que estima alta y a la que asoció con el desempleo, luego de haber anunciado un reajuste del salario mínimo y exenciones impositivas para los trabajadores.
+"No podemos seguir viviendo en un país donde la tasa de interés no controla la inflación; controla, de hecho, el desempleo en este país porque es responsable de parte de la situación que vivimos hoy", dijo Lula durante el acto por el día del trabajador en San Pablo. El presidente del Banco Central, Roberto Campos Neto, tiene autonomía operativa para fijar la tasa Selic, el tipo de interés básico de la economía, que hoy está en un 13,75 por ciento con el supuesto objetivo de controlar la inflación.
+El mes pasado, al celebrar los cien primeros días de su tercer gobierno, Lula había criticado al bolsonarista Campos Neto por haber mantenido esa tasa de interés, enfriando la economía para buscar una meta inflacionaria del 3,5 por ciento, algo que ni el mercado financiero considera alcanzable.
+[H2] Suba del salario mínimo
+Ante un público convocado por las principales centrales sindicales, Lula confirmó que firmará un decreto que eleva el sueldo mínimo para trabajadores, jubilados y pensionistas a 1.320 reales (alrededor de 265 dólares). Esto representa un aumento de apenas 18 reales frente al valor vigente, fijado en diciembre por el expresidente Jair Bolsonaro al final de su mandato, pero retoma una política de valorización real del salario, que además de la inflación se ajustará según el PBI.
+El mandatario, un exlíder sindical que gobernó el país entre 2003 y 2010, confirmó además su promesa de aumentar el valor mínimo exento de impuesto a la renta, que pasó este lunes de unos 1.900 reales a 2.640 reales, equivalente a dos salarios mínimos. "Hasta el fin de mi mandato (2026), esa exención subirá hasta los cinco mil reales (unos mil dólares)", sostuvo el presidente.
+En el mismo acto, Lula defendió la paridad salarial entre hombres y mujeres y la mejora de los derechos laborales de quienes trabajan por aplicaciones digitales, como repartidores y conductores. "No hay problema en que una persona trabaje en una app. Muchas veces, esa persona no quiere firmar un contrato. No hay ningún problema. Lo que queremos es que la persona que trabaja con aplicaciones tenga un compromiso con la seguridad social, porque si se enferma tiene que tener una cobertura para ser tratada", dijo el mandatario de izquierda.
+[H2] Mensaje a los golpistas
+El presidente volvió a pedir la detención de los extremistas seguidores del exmandatario Jair Bolsonaro que invadieron las sedes de los tres poderes el 8 de enero. "Ustedes recuerdan que intentaron dar un golpe de Estado. Quiero terminar diciéndoles: todas las personas que intentaron dar un golpe serán arrestadas, porque este país quiere una democracia real", advirtió Lula.
+El expresidente Bolsonaro celebró el 1 de mayo con críticas al gobierno de Lula por retomar la creación de reservas indígenas e hizo guiños al agronegocio, en su primera agenda pública desde que volvió de Estados Unidos el pasado 30 de marzo. Bolsonaro participó este lunes de la apertura de Agrishow, la mayor feria de tecnología agrícola de América latina, en la ciudad de Ribeirao Preto, junto a algunos de sus antiguos ministros comos Tarcísio de Freitas, actual gobernador de San Pablo.
+Lula asumió el poder por tercera vez con el desafío de aumentar el empleo y superar un largo período con alta inflación que en marzo cedió a 4,65 por ciento, en 12 meses, en medio de una expectativa de magro crecimiento económico y las dificultades derivadas de una de las tasas de interés de referencia más altas del mundo, según analistas. El desempleo se ubicó en 8,8 por ciento en el primer trimestre, afectando a 9,4 millones de personas, según datos oficiales.</t>
   </si>
   <si>
     <t>Lula y Sánchez confían en poder impulsar el acuerdo entre la Unión Europea y el Mercosur</t>
@@ -1513,7 +3701,27 @@
     <t>https://www.pagina12.com.ar/543990-lula-y-sanchez-confian-en-poder-impulsar-el-acuerdo-entre-la</t>
   </si>
   <si>
-    <t>2023-04-27T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula y Sánchez confían en poder impulsar el acuerdo entre la Unión Europea y el Mercosur
+Chapeau: El tratado quedó debilitado por el antiambientalismo del gobierno de Jair Bolsonaro
+Subtítulo: Los líderes de Brasil y España consideraron que existen "pocos argumentos" para estar en contra y coincidieron en que se abre "una oportunidad claramente única" para sellar el pacto. Hubo diferencias en torno a Ucrania. "Grito paz como si estuviera solo en el desierto", sostuvo el líder brasileño.
+Editoria: El Mundo
+Tags: Luiz Inácio Lula da Silva, Pedro Sánchez, Mercosur, Conflicto Rusia Ucrania, printed-edition, luiz-inacio-lula-da-silva, pedro-sanchez, conflicto-rusia-ucrania, diario
+URL: https://www.pagina12.com.ar/543990-lula-y-sanchez-confian-en-poder-impulsar-el-acuerdo-entre-la/
+Notícia completa (14 blocos):
+El presidente brasileño, Luiz Inácio Lula da Silva, dijo este martes en España que confía en poder cerrar el acuerdo comercial entre la Unión Europea (UE) y el Mercosur y reiteró la necesidad de negociar para ponerle un freno a la guerra entre Rusia y Ucrania. Lula, quien llegó el martes a España desde Portugal para concluir su primera gira por países de la UE desde su retorno al poder, se reunió con el presidente del gobierno español Pedro Sánchez en el Palacio de la Moncloa en Madrid.
+En julio España asume la presidencia rotativa de la UE y Brasil la del Mercosur, y Lula y Sánchez dijeron que esta coincidencia debería ayudar a cerrar de una vez el tratado comercial entre los dos bloques. "Brasil y España compartimos que el acuerdo es la piedra fundamental para estrechar las relaciones entre la Unión Europea y los países que conforman el Mercosur. Europa necesita aliados", dijo Sánchez.
+El presidente socialista español le dijo a Lula que existían "pocos argumentos" para estar en contra de este acuerdo con el Mercosur (que también integran Argentina, Paraguay y Uruguay) y este año había una oportunidad "única" para sellarlo. Lula, por su parte, subrayó que algunos términos del acuerdo a los que había dado el visto bueno el gobierno de su antecesor Jair Bolsonaro eran "inaceptables" para Brasil, pero confiaba en que, con la ayuda de Sánchez, eso pudiera enmendarse.
+"Con la presidencia española de la UE podemos tener la posibilidad de cerrar este acuerdo", dijo Lula, quien sentenció: "Alguien tiene que cerrarlo". El rey Felipe VI le ofreció luego al presidente un almuerzo de honor en el Palacio de la Zarzuela, antes de su retorno a Brasil.
+[H2] Las idas y vueltas del acuerdo
+Las negociaciones por el acuerdo UE-Mercosur se completaron en 2019 tras más de 20 años, pero la ratificación del pacto se estancó en el bloque de 27 naciones europeas. El acuerdo supondría la integración de dos mercados con un total de 800 millones de personas, cerca de una cuarta parte del PBI mundial y más de 100 mil millones de dólares en comercio bilateral de bienes y servicios. También reduciría los aranceles aduaneros y facilitaría el acceso de los exportadores agrícolas al mercado de la UE y de los fabricantes europeos a los países del Mercosur.
+La demora en su ratificación se debió, en parte, a las preocupaciones de la UE sobre la deforestación de la selva amazónica en Brasil durante el mandato de Bolsonaro, un escéptico del cambio climático. El exmandatario de extrema derecha destituyó y recortó poderes a funcionarios ambientales, y alentó la extracción ilegal de oro y el agronegocio en áreas indígenas, lo que resultó en un aumento en la deforestación a su ritmo más rápido en dos décadas.
+La reelección en octubre pasado de Lula, que en enero asumió su tercera presidencia en Brasil con una agenda ambientalista, entre otras cosas, disipó esos miedos, según dijeron funcionarios españoles. Los temores de algunos países europeos a ver perjudicada su producción también son obstáculos para la aplicación del acuerdo UE-Mercosur.
+El presidente francés, Emmanuel Macron, advirtió este año que el acuerdo "no sería posible" si los países del Mercosur no respetaban las mismas limitaciones medioambientales que los europeos. Los agricultores europeos temen que entren en el mercado más productos agrícolas sudamericanos, y alegan que tienen normas de producción menos estrictas.
+[H2] "Grito paz como si estuviera solo en el desierto"
+El viaje de Lula a Portugal y España también era seguido con atención por sus recientes declaraciones sobre la guerra entre Ucrania y Rusia que habían generado rechazo en Kiev, Washington y otros aliados ucranianos. Junto a Sánchez, el presidente brasileño insistió en que Rusia y Ucrania tienen que negociar la paz y no "sirve de nada decir quién tiene razón" en el conflicto, que provocó un aumento global del precio de los alimentos y los combustibles.
+"Nadie puede tener duda de que los brasileños condenamos la violación territorial de Rusia contra Ucrania. El error sucedió, la guerra empezó", dijo Lula. Sin embargo, "ahora no sirve de nada decir quién tiene razón, quién está equivocado. Ahora lo que hay que hacer es parar la guerra", agregó el líder de izquierda, expresando su frustración por lo poco que se habla de paz. "No hay nadie que diga paz salvo yo, que grito paz como si estuviera solo en el desierto", sostuvo Lula.
+Sánchez, en cambio, pidió tener presente que el conflicto arrancó con la invasión rusa en febrero de 2022. "En esta guerra hay un agresor y hay un agredido: el agresor es (el presidente ruso, Vladimir) Putin y el agredido, en este caso es un pueblo que lo único que hace es luchar por la integridad territorial, por su soberanía nacional y por su libertad", afirmó el presidente del gobierno español.
+A principios de este mes, Lula dijo que tanto Ucrania como Rusia habían decidido ir a la guerra y que EE.UU. y la UE, con sus entregas de armas a Kiev, estaban estimulando la confrontación, lo que provocó fuertes reproches de ambos. Estados Unidos lo acusó de "hacerse eco de la propaganda rusa y china", y Ucrania lo invitó al país para "comprender las causas reales y la esencia" de la guerra.</t>
   </si>
   <si>
     <t>El trigo transgénico ya se mezcla con el convencional</t>
@@ -1525,7 +3733,24 @@
     <t>https://www.pagina12.com.ar/543100-el-trigo-transgenico-ya-se-mezcla-con-el-convencional</t>
   </si>
   <si>
-    <t>2023-04-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: El trigo transgénico ya se mezcla con el convencional
+Chapeau: La Facultad de Medicina UNR denuncia la gravedad para la salud pública
+Subtítulo: La población de Argentina es la primera en comer pan con trigo transgénico. Así lo confirmó la empresa Bioceres-Indear al informar que 25 molinos ya mezclan el cereal con el trigo convencional.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/543100-el-trigo-transgenico-ya-se-mezcla-con-el-convencional/
+Notícia completa (11 blocos):
+La población de Argentina es la primera en comer pan con trigo transgénico. Así lo confirmó la empresa Bioceres-Indear al informar que 25 molinos ya mezclan el cereal con el trigo convencional. El transgénico, que va junto al peligroso agrotóxico glufosinato de amonio, fue denunciado por más de mil científicos, por productores (tanto agroecológicos como del agronegocio) y por organizaciones socioambientales. Los estudios que señalarían la supuesta "inocuidad" del transgénico son confidenciales y fueron realizados por la propia empresa que lo vende. "Es un hecho de gravedad inusitada desde el punto de vista de la salud pública", denunció en un carta pública el Instituto de Salud Socioambiental (InSSA) de la Facultad de Ciencias Médicas de la Universidad Nacional de Rosario (UNR).
+La noticia se conoció mediante un anuncio de Bioceres-Indear a inicios de marzo. Y es de una trascendencia mundial: por primera vez un trigo modificado genéticamente (llamado "HB4") llega a los alimentos de consumo masivo (pan, pizzas, empanadas, fideos y todos los usos de la harina). Y, más grave, la población no tiene posibilidad de identificar si está comiendo un producto con transgénicos o no: en Argentina no existe un etiquetado de Organismos Genéticamente Modificados (OGM).
+Desde el Instituto de Salud Socioambiental (InSSA-UNR) resaltaron que no hay pruebas científicas independientes y publicadas en revistas académicas que demuestren la inocuidad del trigo HB4 en la ingesta en humanos. Recuerda que, en Argentina, los transgénicos se aprueban en base a "estudios" de las propias empresas y que esos informes son secretos.
+El InSSA, que ha confirmado con una publicación científica la incidencia de cáncer en pueblos fumigados, remarca otro factor del trigo transgénico: "Va acompañado con el herbicida glufosinato de amonio, cuya toxicidad sobre el ambiente y la salud ya ha sido demostrada en numerosos trabajos científicos, así como también se ha evidenciado que no se degrada y que incluso es posible detectarlo hasta en ultraprocesados".
+Los investigadores instan a los "decisores de políticas públicas" que atiendan a las evidencias científicas que dan cuenta de los peligros de ese cultivo. "Consideramos urgente que las autoridades prohíban la comercialización e incorporación del trigo Hb4 en las harinas para producción de productos comestibles y/o sucedáneos de la alimentación humana", remarcan.
+En 2020, en una carta abierta, más de mil científicos del Conicet y de 30 universidades públicas de Argentina rechazaron el avance del trigo transgénico: “Esta autorización remite a un modelo de agronegocio que se ha demostrado nocivo en términos ambientales y sociales, causante principal de las pérdidas de biodiversidad, que no resuelve los problemas de la alimentación y que amenaza además la salud de nuestro pueblo confrontando la seguridad y la soberanía alimentaria”. Aportaron decenas de estudios que dan cuenta de los peligros del nuevo transgénico. Nada de eso fue tenido en cuenta por las autoridades estatales.
+Bioceres-Indear es la compañía impulsora del trigo transgénico. Se presenta como una "empresa nacional", con accionistas como el denominado "rey de la soja" Gustavo Grobocopatel y el multimillonario Hugo Sigman, pero desde 2021 cotiza en la Bolsa de Nueva York. Para el transgénico también fue vital el aporte del Estado, mediante recursos y políticas activas del Conicet y la Universidad Nacional del Litoral. Su referenta es la científica Raquel Chan, socia de Bioceres y negadora de las consecuencias sociales, ambientales y sanitarias del agronegocio.
+Mauricio Macri estuvo a punto de aprobar el trigo durante su gestión, pero frenó la decisión por la advertencia de productores del agronegocio, del Centro de Exportadores de Cereales y la Federación de Acopiadores, ante la posibilidad de perder mercado de exportación (principalmente Brasil). Los consumidores no quieren transgénicos en sus platos. La aprobación final fue en mayo de 2022, cuando Julián Domínguez (entonces ministro de Agricultura) dio luz verde al pedido de Bioceres-Indear (la firma administrativa corrió por cuenta de Luis Gustavo Contigiani).
+"La responsabilidad del Gobierno es total. Desde la autorización sin pruebas de inocuidad, sin contemplar los efectos negativos en el campo y también con sus políticas científicas, con Raquel Chan como emblema, al servicio del sector más concentrado del agronegocio", denunció Agustín Suárez, de la Unión de Trabajadores/as de la Tierra (UTT). Y remarcó la gravedad de este trigo: "No solo se contaminará al trigo convencional sino que este transgénico, y sus agrotóxicos, irán directo a nuestros cuerpos, al de nuestros hijos. Las consecuencias serán muy graves y se verán en el mediano y largo plazo. Es criminal".
+Desde la Multisectorial Paren de Fumigarnos de Santa Fe, que desde hace dos décadas denuncia los impactos del agronegocio en la salud y el ambiente, precisaron que el herbicida glufosinato de amonio es "mucho más tóxico que el glifosato y está comprobado sus efectos teratogénicos, neurotóxicos y genotóxicos".
+La Multisectorial, que forma parte de la campaña "Con nuestro pan no" (que reúne a decenas de organizaciones de todo el país) alertó el efecto en los productores: "No es posible la coexistencia de trigo transgénico y no transgénico debido al proceso de 'contaminación genética' que ocurre durante la polinización y cuyos residuos de agrotóxicos quedarán en la harina obtenida. En sociedades empobrecidas y culturalmente trigo-harina dependientes, es un claro peligro de salud pública". Y advierte que el mecanismo por el cual se autorizó el transgénico viola la Ley General del Ambiente y el artículo 41 de la Constitución Nacional, entre otras normas de protección de la salud y el ambiente. Exigen el cese de la siembra del transgénico, el freno a la mezcla con el trigo tradicional y recuerdan: "La salud no se negocia".</t>
   </si>
   <si>
     <t>Todo empieza en la semilla: experiencia de producción agroecológica en San Juan</t>
@@ -1537,7 +3762,24 @@
     <t>https://www.pagina12.com.ar/541851-todo-empieza-en-la-semilla-experiencia-de-produccion-agroeco</t>
   </si>
   <si>
-    <t>2023-04-23T03:01:00Z</t>
+    <t xml:space="preserve">Título: Todo empieza en la semilla: experiencia de producción agroecológica en San Juan
+Chapeau: Los precios de los alimentos
+Subtítulo: La cooperativa Boca de Tigre cuenta con una práctica de protección de las semillas de polinización abierta, criollas y nativas de rúcula.
+Editoria: Cash
+Tags: Agroecología, Soberanía alimentaria, printed-edition, agroecologia, soberania-alimentaria
+URL: https://www.pagina12.com.ar/541851-todo-empieza-en-la-semilla-experiencia-de-produccion-agroeco/
+Notícia completa (11 blocos):
+Luego de cada jornada de trabajo, decenas de bolsas repletas de semillas se acopian en el galpón de la cooperativa Boca del Tigre, en el departamento de San Martín, a media hora de la capital de San Juan. "Semilla Soberana. Producción Agroecológica. UTT, Unión de Trabajadores y Trabajadoras de la Tierra. RÚCULA", dice la etiqueta.
+"Es la primera vez que se hace este tipo de producción en el país", se enorgullece César González, integrante de la cooperativa. "Trabajamos sin agrotóxicos, con semillas de polinización abierta y sin trabajo esclavo. De ese modo le ganamos al agronegocio", afirma.
+La producción de la semilla incide en la posterior cadena de comercialización y venta. El precio de los alimentos comienza a definirse aún antes de la raíz. En Boca del Tigre, además de la semilla de rúcula, se especializan en la producción de tomate, y allí la diferencia de precios es incluso mayor.
+“El costo de la semilla baja de manera inimaginable”, explica Lidia Furlani, fundadora y presidenta de la cooperativa. “Si mantenemos una práctica de protección de las semillas de polinización abierta, criollas y nativas, cuidando las variedades tanto por parte de los productores como de los centros de multiplicación el costo de la semilla se reduce de manera inimaginable: mil semillas de polinización abierta nos cuestan 20 pesos, cuando mil semillas híbridas de tomate nos costarían 25 mil pesos”.
+Para hacer la experiencia con la semilla de rúcula estos campesinos debieron desplazarse a un campo en Pocito, a 45 km del pueblo, porque en esa región de San Juan es difícil encontrar tierra con disponibilidad de agua de pozo. Dependen del agua de deshielo y pasan meses enteros con dificultades para producir.
+“Comenzamos en un campo pequeño, de 8 hectáreas, porque es muy difícil autogestionarse la producción de la semilla en un principio”, cuenta Lidia. “Tenemos una base de familias que han prestado servicio a empresas privadas que terminaban vendiéndole a Monsanto, entonces teníamos esa experiencia, pero faltaba el dinero inicial para poder hacer estos trabajos, porque son períodos muy largos hasta que la semilla está lista, nos llevó 9 meses”, agrega. Para superar ese escollo, la colaboración de la Unión de Trabajadores de la Tierra, UTT, organización de la que es parte la cooperativa, fue fundamental.
+[H2] Acceso a las semillas
+Con esa experiencia como modelo, están trabajando para expandir la producción. Las semillas que acaban de cosechar ya están abasteciendo a familias campesinas de otras regiones. “Pensamos un plan de siembra a largo plazo que permita multiplicar las semillas que estén bien adaptadas al territorio”, explica la presidenta de Boca del Tigre, y detalla: “Si hay semillas de tomate en Jujuy, podemos abaratar los costos, que son muy caros; de igual modo conectar con otras cooperativas productoras como lo estamos haciendo en Jáchal, o en la localidad de Iglesia (ambas en San Juan)”.
+“El acceso irrestricto a las semillas constituye el sustento de la mayoría de los productores rurales y garantiza la disponibilidad de los alimentos; para eso, es necesario expandir los bancos de semillas que no fueron modificadas en un laboratorio, conservarlas e intercambiarlas”, concluye un informe del CELS titulado “6 puntos para construir una alternativa al modelo alimentario excluyente”. El documento afirma que “la industria de las semillas patentadas está ligada a las cuatro mayores empresas agroquímicas del mundo, que controlan el 60 por ciento del mercado mundial y el 75 por ciento de los plaguicidas”.
+Ley de Reparación Histórica de la Agricultura Familiar, sancionada en 2014 pero aún pendiente de reglamentación, define la puesta en marcha de un Centro de Producción de Semillas Nativas dependiente del Ministerio de Agricultura de la Nación. El programa Semillar, anunciado en 2021 por la Secretaría de Agricultura Familiar, alienta la recuperación y multiplicación de semillas nativas como parte de la diversidad biológica y cultural. Para la UTT, la producción de semillas libres es parte de la lucha por la soberanía alimentaria.
+* Coordinación nacional UTT</t>
   </si>
   <si>
     <t>Juan Pablo Acosta *</t>
@@ -1552,7 +3794,25 @@
     <t>https://www.pagina12.com.ar/542347-licitaran-el-segundo-tramo-del-gasoducto-nestor-kirchner</t>
   </si>
   <si>
-    <t>2023-04-21T03:01:00Z</t>
+    <t xml:space="preserve">Título: Licitarán el segundo tramo del gasoducto Néstor Kirchner
+Chapeau: Massa confirmó que será el mismo día que inauguren el primer tramo
+Subtítulo: El funcionario aseguró que se invitará al sector privado para que junto con el Estado trabajen de manera colaborativa en el proyecto.
+Editoria: Economia
+Tags: Sergio Massa, Gasoducto Néstor Kirchner, printed-edition, sergio-massa, gasoducto-nestor-kirchner, diario
+URL: https://www.pagina12.com.ar/542347-licitaran-el-segundo-tramo-del-gasoducto-nestor-kirchner/
+Notícia completa (12 blocos):
+El ministro de Economía, Sergio Massa, anunció este jueves que la licitación del segundo tramo del Gasoducto Néstor Kirchner se pondrá en marcha el mismo día de la inauguración de la primera etapa, prevista para junio, y que se invitará al sector privado para que junto con el Estado trabajen de manera colaborativa en el proyecto.
+“El mismo día que inauguremos la primera etapa del gasoducto vamos a poner en marcha la licitación de la segunda etapa, con la particularidad de que en el caso del segundo tramo lo vamos a hacer invitando a invertir al sector privado en un esquema que permita que el desarrollo local y de potenciales mercados externos se de en un marco en el que el Estado y el sector privado lo hagan de manera colaborativa y asociada”, aseguró Massa al participar en modo remoto del encuentro Experiencia IDEA Energía, que se llevó a cabo en el Hotel Casino Magic de la ciudad de Neuquén.
+Massa no dio mayores precisiones sobre cómo será esa “colaboración” con el sector privado en esa segunda etapa que abarca el trayecto que va de Salliqueló (Buenos Aires) a San Jerónimo (Santa Fe). Desde Enarsa remarcaron que la intención es conseguir financiamiento privado para avanzar con una obra que será propiedad del Estado Nacional.
+En su disertación, el titular del Palacio de Hacienda defendió el diálogo de los representantes de la Nación, las provincias, las empresas y los trabajadores, como "las cuatro patas claves de la mesa para ponerle un paraguas al 2030", en referencia a las metas de los Objetivos de Desarrollo Sostenible (ODS).
+"La energía debe ser una política de Estado que no debe ser modificada por un cambio de gobierno", enfatizó, luego de señalar que con el desarrollo del sector "pretendemos generarle a la Argentina un 'segundo campo'", en cuanto a sus potencialidades para la generación de divisas, "mucho más en este contexto de restricción".
+Al respecto, instó a "que nunca se desarme la mesa de diálogo, de búsqueda de acuerdos y de soluciones", para remarcar la importancia de cada una de las partes involucradas, ya que la actividad se vería en dificultades "sin trabajadores bien pagos y registrados, sin empresarios que inviertan, sin los ingresos que el sector representa para las provincias y la Nación, sin las reglas de incentivos".
+Asimismo, reiteró las diferencias entre los países centrales y los que están en vías de desarrollo en materia de transición energética, puntualizando que los segundos son "acreedores ambientales" y que en consecuencia no pueden tomarse criterios uniformes, ya que para las naciones desarrolladas se requieren tareas de "mitigación", y para América Latina de "adaptación".
+Por tal razón, cuestionó la "mirada muy europeizada" de organismos como el BID (Banco Interamericano de Desarrollo) o el Banco Mundial, que sostienen que el gas no es una energía de transición y, en consecuencia, son renuentes a financiar obras de infraestructura relacionadas con ese combustible.
+En contraposición, valoró la "otra mirada" del Banco de Desarrollo de América Latina (CAF, ex Corporación Andina de Fomento), que "nos financia con 540 millones de dólares para la operación del Reversal del Norte, que nos permitirá inyectar gas de Vaca Muerta para el Norte Argentino".
+En ese sentido, subrayó que "la discusión no es sólo de la Argentina sino por varios países de la región", debido a que "la transición energética de América Latina es distinta de la de los países desarrollados, que son responsables del daño ambiental, a diferencia de nosotros, que somos acreedores ambientales". "Por una cuestión económica y también ambiental, la transición de esta región tiene que ir más allá del recorrido de las energías limpias, vamos a defender el rol del gas como energía de transición", sostuvo.
+Remarcó la importancia de terminar con el Reversal del Norte por "lo que representa en el corto plazo el declino de la cuenca de Bolivia y lo que representa Mato Grosso do Sul, con la puesta en marcha de una de las plantas de fertilizantes más grandes de la región". El desarrollo de esa planta, indicó, "es un factor esencial para la segunda turbina de la economía argentina, que son los agronegocios".
+Con la puesta en funcionamiento de las obras mencionadas, Massa pronosticó que "en términos de números, significa cambiar para el 2030 a un modelo netamente exportador energético", con un "cambio de curva hacia el 2025, con volúmenes (de producción de hidrocarburos) multiplicados por cuatro o cinco".</t>
   </si>
   <si>
     <t>Renunció Antonio Aracre, jefe de asesores de Alberto Fernández</t>
@@ -1564,7 +3824,22 @@
     <t>https://www.pagina12.com.ar/541664-renuncio-antonio-aracre-jefe-de-asesores-de-alberto-fernande</t>
   </si>
   <si>
-    <t>2023-04-18T21:36:21Z</t>
+    <t xml:space="preserve">Título: Renunció Antonio Aracre, jefe de asesores de Alberto Fernández
+Chapeau: A unos pocos meses de su asunción
+Subtítulo: El exCEO de Syngenta dijo que se fue de la Rosada para desactivar cualquier efecto de corrida bancaria, en una jornada que el dólar blue se disparó a 418 pesos. La disputa con Massa y los off que no finalizan en Balcarce 50.
+Editoria: El País
+Tags: Antonio Aracre, Alberto Fernández, antonio-aracre, alberto-fernandez, diario
+URL: https://www.pagina12.com.ar/541664-renuncio-antonio-aracre-jefe-de-asesores-de-alberto-fernande/
+Notícia completa (9 blocos):
+"Le he presentado al Presidente Alberto Fernández mi renuncia indeclinable como jefe de Asesores de manera inmediata". Con esas palabras, Antonio Aracre anunció que deja su cargo en la Casa Rosada, a menos de tres meses de haber asumido como uno de los hombres de confianza del Presidente.
+De acuerdo a su publicación, la renuncia tiene como efecto "desactivar cualquier operación tendiente a intranquilizar los mercados", expresó, en un martes en el que el dólar blue se disparó y cerró en 418 pesos. Además, Aracre agradeció al Presidente por la designación. "Puede contar conmigo para lo que necesite", escribió, con decoro.
+Aracre no precisó cuáles fueron las "operaciones" que buscó frenar. Lo que sí trascendió -en formato off- el lunes, como publicó el periodista de PáginaI12 Leandro Renou en sus redes, fue que Aracre había hablado con el presidente Alberto Fernández y que podría evaluar darle el Ministerio de Economía que ocupa Sergio Massa, en medio de la nueva corrida del dólar ilegal. La vocera presidencial se encargó de negar esas versiones esta tarde y pocas horas después Aracre presentó su renuncia.
+En su brevísimo primer paso por la función pública, tras su asunción el 1 de febrero, el ex CEO de la multinacional del agronegocio Syngenta protagonizó varias polémicas --con su perfil tuitero-- y uno de las últimas fue precisamente con Massa. Hace poco menos de un mes, como contó Renou en este diario, Massa dejó un aviso al presidente: "Les voy a contestar a todos los que juegan a la internita poniendo en riesgo la economía".
+El mensaje era para Aracre luego de que se sospechara como el responsable de filtrar una serie de medidas que incluían el desdoblamiento cambiario, algo que la cartera a cargo de Massa negó luego de que llegara a los títulos de los diarios y portales.
+Antes de asumir como jefe de asesores, Aracre tuvo que salir también a pedir disculpas en las redes sociales por insinuar una posible flexibilización laboral. Es que el ex CEO de la empresa de agroquímicos llegó a la Casa Rosada como abanderado de una idea que había esbozado Fernández en 2022 respecto de convocar una gran mesa de concertación política por los 40 años de la democracia.
+"Mi primera tarea será abrir el gobierno al mundo de las inversiones privadas que generen trabajo y le puedan cambiar la vida a la gente. Y consensuar con la oposición y los sindicatos algunos puntos esenciales para la Argentina que todos queremos", había anunciado en enero sobre sus metas.
+Pero entre esas ideas a consensuar, en una entrevista con el diario La Nación, Aracre planteó que era necesario "flexibilizar y modernizar los procesos" para incorporar trabajadores a la formalidad laboral. "Siga soñando (Aracre) con llevar adelante una reforma laboral", le contestó rápidamente el el cosecretario General de la CGT y adjunto de Camioneros, Pablo Moyano. "Como peronista no podemos aceptar cualquier intento que quieran llevar adelante para perjudicar a los trabajadores", le apuntó.
+"Sólo espero estar a la altura y no defraudar a nadie", se había esperanzado el ex CEO de Sygenta en enero, pero esta tarde decidió dar un paso al costado en su primera experiencia en la función pública.</t>
   </si>
   <si>
     <t>Lula viaja a China buscando retomar el protagonismo internacional de Brasil</t>
@@ -1576,7 +3851,24 @@
     <t>https://www.pagina12.com.ar/539316-lula-viaja-a-china-buscando-retomar-el-protagonismo-internac</t>
   </si>
   <si>
-    <t>2023-04-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula viaja a China buscando retomar el protagonismo internacional de Brasil
+Chapeau: El presidente brasileño planea discutir propuestas de paz en Ucrania
+Subtítulo: El mandatario de izquierda prometió "colocar nuevamente a Brasil en la nueva geopolítica mundial" tras el aislacionismo de su predecesor Jair Bolsonaro.
+Editoria: El Mundo
+Tags: Brasil, Luiz Inácio Lula da Silva, China, Xi Jinping, printed-edition, luiz-inacio-lula-da-silva, xi-jinping, diario
+URL: https://www.pagina12.com.ar/539316-lula-viaja-a-china-buscando-retomar-el-protagonismo-internac/
+Notícia completa (11 blocos):
+Luego de postergar su visita oficial a China por una neumonía, el presidente Luiz Inácio Lula da Silva viajará este martes a Beijing buscando retomar el protagonismo internacional de Brasil y discutir propuestas de paz en Ucrania. El mandatario de 77 años, que debía viajar en un principio del 25 al 31 de marzo a China, prometió "colocar nuevamente a Brasil en la nueva geopolítica mundial" tras el aislacionismo de su predecesor Jair Bolsonaro.
+Lula se reunirá el próximo viernes en Beijing con su par Xi Jinping, con quien "hablará de la guerra en Ucrania", adelantó el canciller Mauro Vieira. El líder de izquierda rechazó mandar municiones a Ucrania en nombre de la paz y propone la formación de un grupo de países mediadores. A su regreso de China ese grupo estará creado, aseguró Vieira.
+"Vladimir Putin no puede quedarse con el territorio de Ucrania" al tiempo que el presidente ucraniano, Volodimir Zelenski, "no puede quererlo todo", había dicho el jueves Lula al sugerir que Kiev renuncie a la península de Crimea, anexionada por Rusia en 2014. La diplomacia ucraniana descartó esa idea pese a apreciar "los esfuerzos del presidente brasileño para encontrar una manera de detener la agresión rusa".
+[H2] Los BRICS también en la agenda
+Lula visitará el jueves Shanghai para la toma de posesión de su aliada y expresidenta Dilma Rousseff a la cabeza del New Development Bank, el banco de los BRICS. Este grupo que Brasil integra junto con Rusia, India, China y Sudáfrica, fue creado en 2006 durante el primer gobierno de Lula.
+La visita a China resalta el interés de Lula por recomponer los lazos diplomáticos con países estratégicos, luego de haber viajado previamente a otras capitales como Buenos Aires y Washington. Acompañado de líderes parlamentarios y partidistas, la agenda del presidente será especialmente política, luego de que el potencial económico de la relación con Beijing fuera abarcado la semana pasada.
+Un foro empresarial recibió a 500 empresarios brasileños (principalmente del agronegocio) y chinos, y se firmaron más de 20 acuerdos de cooperación, incluyendo uno que permitirá la realización de transacciones comerciales en reales y yuanes, sin requerir dólares.
+China es el principal socio comercial de Brasil: el intercambio bilateral registró un récord de 150.500 millones de dólares en 2022. Brasil, la mayor economía regional, es el principal destino de inversiones chinas en América latina (48 por ciento), con 70.300 millones de dólares entre 2007 y 2020, según el Consejo Empresarial Brasil-China.
+[H2] Primeros 100 días de gobierno
+Lula cumplió este lunes 100 días en el poder, en el inicio de gobierno más turbulento de la historia reciente del país, debido al intento de golpe del pasado ocho de enero. La irrupción violenta de una turba de bolsonaristas no solo causó grandes destrozos en las sedes de los tres poderes de la República, sino que forzó al nuevo gobierno a concentrar sus esfuerzos en disipar posibles nuevas amenazas a la democracia.
+Lula tuvo que dedicar varias semanas a prestar toda su atención a la cúpula de las Fuerzas Armadas y relevó a algunos comandantes demasiado cercanos a su antecesor Jair Bolsonaro, entre ellos el ahora excomandante del Ejército, general Júlio César Arruda, con el objetivo de recuperar una normalidad institucional que fue dinamitada en los cuatro años de hegemonía de la ultraderecha.</t>
   </si>
   <si>
     <t>La construcción de viviendas crece más que la población, pero también sube el déficit habitacional</t>
@@ -1588,7 +3880,43 @@
     <t>https://www.pagina12.com.ar/539052-la-construccion-de-viviendas-crece-mas-que-la-poblacion-pero</t>
   </si>
   <si>
-    <t>2023-04-10T03:01:00Z</t>
+    <t xml:space="preserve">Título: La construcción de viviendas crece más que la población, pero también sube el déficit habitacional
+Chapeau: El último censo muestra la falsedad de la teoría de la oferta y demanda en el mercado inmobiliario
+Subtítulo: Las estadísticas del censo 2022 consoliodan la tendencia: la construcción de casas supera el índice de aumento de la población. El factor especulativo en el eje de la actual crisis habitacional.
+Editoria: Sociedad
+Tags: Construcción, viviendas, Ley de Alquileres, printed-edition, construccion, ley-de-alquileres, diario
+URL: https://www.pagina12.com.ar/539052-la-construccion-de-viviendas-crece-mas-que-la-poblacion-pero/
+Notícia completa (30 blocos):
+La construcción de viviendas crece en la Argentina por encima del aumento de la población, según los datos de los últimos cuatro censos nacionales, revisados por la agrupación Inquilinos Agrupados. Pero “faltan casas porque falla la distribución” sostiene Gervasio Muñoz, quien lidera la entidad y realizó un pormenorizado análisis de las estadísticas que surgen de los censos de 1991 a 2022. En 2022 y por datos parciales que el censo ya oficializó “vemos que hay 17.780.210 viviendas construidas --detalla Muñoz--, y 46.440.703 habitantes”. Y como un hogar hoy se estima en tres personas, el resultado arroja más viviendas que familias. Tantas, que el número alarma: según la proyección “habría tres millones de viviendas vacías”.
+La cantidad de viviendas en la categoría "ociosa o vacía" sostiene el déficit. Aun cuando la construcción aumenta. La estadística indica que “hay una vivienda cada 2,6 personas” razona Muñoz, y sin embargo, hay un escenario de marcado déficit habitacional. Y frente a una población de inquilinos que hoy además, ve peligrar sus contratos de alquiler por las embestidas del mercado inmobiliario contra una Ley de Alquileres que recuperó, luego de décadas, el control de estos contratos por parte del Estado, como fue hasta 1976.
+En la Argentina, “hoy el grupo familiar está formado por 3 personas --repasa Muñoz--, y sabemos que según los datos, hay una vivienda cada 2,6 personas. Quiere decir que sobran viviendas”, enfatiza. Y añade que esto significa, además “que el mercado no construye para solucionar el déficit habitacional”. Lo que se construye, por parte de los sectores "que no tienen necesidad de vivienda” --en su mayoría invierten en ladrillos la ganancia del agronegocio--, tiene otros objetivos: especular o invertir como reserva de valor, o como bien financiero. Construye en pesos, cotiza en dólares.
+En un sistema que produce desigualdades siguiendo las indicaciones “del mercado”; la falta de viviendas expone la deshumanización que naturaliza estas desigualdades. “En las últimas décadas se construyó un nivel de viviendas que creció más que la población”, señala Muñoz. Y explica que con el censo 2022 publicado --aun en forma parcial--, se puede comparar “con los censos desde 1991 hasta acá, y podemos ver que en el país crece más rápido la construcción de viviendas que la población”.
+Esto significa que “el mercado privado construye a un ritmo superior a lo que la Argentina necesita en viviendas”, señala. Y sin embargo “y a pesar de la teoría de oferta y demanda del mercado”, que indica que “si hay más viviendas, baja el precio ¡pero sucede lo contrario!”. Paradójicamente “cuando más se construye más caro es, no solo alquilar sino comprar una casa”, afirma Muñoz.
+Esto rompe con la teoría de la lógica del mercado. Muñoz lo explica por la necesidad de “suelo para construir” que ostenta el sector. Cuanto más se construye en una ciudad queda menos suelo libre y se encarece el precio de toda vivienda o alquiler. Por caso, en CABA “se remataron 500 hectáreas de tierras públicas, desde el gobierno de (Mauricio) Macri al de (Horacio Rodríguez) Larreta. En distintos lugares. Y equivale a los barrios de La Boca, San Telmo, Puerto Madero y Paternal, juntos”. Esto, entre otras cosas, propició el aumento sostenido de alquileres y compra de viviendas.
+[H2] Con los datos en la mano
+El grupo familiar en Argentina hoy se conforma por 3 personas, en promedio. “En CABA el 30 por ciento de la población vive sola”, indica Muñoz. Por eso la composición del hogar en CABA es distinta al resto del país donde rigen 3 habitantes por hogar. “En CABA es 2,3 personas”, según la estadística. “Si dividimos la población total, de 46 millones por 3, tenemos 15.348.234 hogares --explica--. Y cómo hay 17 millones de viviendas, si le damos una vivienda a cada uno de estos 15 millones de hogares, nos encontramos con que sobran 2.431.975 viviendas”, puntualiza.
+Se demuestran a lo largo de los censos, que cada vez hay más viviendas en la Argentina para una población que crece menos que el nivel que la construcción, repasa. Y el detalle muestra que en 1991, en la relación vivienda-hogar, había una vivienda cada 3,6 personas. En 2001 fue cada 3,1 personas. “Ya empezaba a verse que las viviendas aumentaban por encima de la población”, señala el dirigente de Inquilinos. En 2010 este índice sigue bajando. Y en 2022 hay una vivienda cada 2,6 personas.
+“Podemos ver que es falso el discurso del mercado inmobiliario que dice ‘hay que construir para solucionar el problema, porque las viviendas están, y todos podríamos acceder a ellas”. Falta una política que incida en la distribución --sostiene Muñoz-- para sacar del rol de “vivienda ociosa o desocupada”, a esta gran cantidad inmuebles.
+[H2] Crecimiento sostenido
+Al observar el último período censal, puede verse que mientras de 2010 a 2022 la población creció un 15 por ciento --esto es 6 millones de habitantes--, la cantidad de viviendas creció un 28 por ciento: hay 4 millones de viviendas nuevas. A nivel país, este crecimiento es sostenido, aunque desigual: de 1991 a 2001 la cantidad de viviendas creció un 37 por ciento mientras la población, un 17 por ciento. De 2001 a 2010: las viviendas crecieron un 18 por ciento y la población un 10.
+En jurisdicciones como CABA, las viviendas desde 1991 a 2022, crecieron un 68 por ciento, mientras la población en el mismo período creció solo un 8 por ciento. En provincia de Buenos Aires, la cantidad de viviendas de 1991 a 2022, creció un 374 por ciento, mientras la población creció un 40 por ciento. “Hoy en provincia, hay una vivienda cada 2,6 personas”, refiere Muñoz. Y cada hogar podría tener una casa, porque sobran, insiste. “Sin embargo la crisis habitacional es enorme”, lamenta.
+En CABA “hay una vivienda cada 1,9 personas” destaca. “Acá la relación cantidad de viviendas y población es más grave, hay muchas más que habitantes, y con una grave crisis habitacional, no solo de gente que no tiene donde vivir, sino por el precio de los alquileres”, fundamenta. Hoy ese destino incierto se extiende a todo el país por la presión que se ejerce desde las inmobiliarias para hacer caer la ley.
+[H2] Las causas de tal paradoja: viviendas ociosas
+Son causas económicas y no estadísticas las que explican esta paradoja. En los inicios de su investigación, Muñoz se preguntó por el crecimiento de las “viviendas ociosas” en Argentina. Se remontó al censo de 1960, donde consta que había entonces 278.000 viviendas ociosas. En 1980 eran 1.092.268 las viviendas en esa condición, mientras la dictadura ya había comenzado su tarea de dolarizar la vivienda y desregular el precio de los alquileres. “Ya no era más el Estado sino el mercado el que regulaba el precio”, apunta Muñoz.
+En el 91 ya había un millón y medio de viviendas ociosas. En 2001 eran poco más de dos millones, y en 2010 dos millones y medio. “En 2022, y por la proyección de los últimos censos, habría tres millones de viviendas vacías”, sostiene.
+Una explicación reside en que a mayor ritmo de construcción de viviendas, crece el volumen de viviendas vacías también. “No se construye con planificación, sino que se construya para dejar vacío --señala el titular de Inquilinos Agrupados-- y partir de 1980 con la dolarización y la desregulación, construir empieza a ser tan rentable que ya no se necesita que se pague un alquiler, se construye como reserva de valor, para dejar vacío, porque esas viviendas además se revalorizan en dólares”.
+[H2] La falsa teoría de “oferta y demanda”
+La teoría de oferta y demanda en el mercado inmobiliario es falsa, define Muñoz. “Si fuese cierta todos tendríamos un lugar donde vivir, porque hay viviendas, pero no son para los trabajadores”, remarca. “Hoy tenemos viviendas que se construyen en pesos, por sectores ligados al agro, y luego cotizan en dólares”, explica sobre el eje de un mercado que quiere sostener la rentabilidad de los alquileres en dólares.
+“A ellos siempre le va a parecer poca su ganancia, porque son sectores muy concentrado de la economía”, señala. Por eso advierte, sin un Estado que planifique “qué se construye, dónde y para quién, vamos a seguir en esta tendencia, donde cada vez hay más viviendas, y más gente que no puede pagar un alquiler”.
+[H2] Crisis habitacional
+Los datos de vivienda y población registrados en los últimos cuatro censos nacionales muestran una paradójica relación entre el aumento en la construcción de viviendas y en población: mientras el índice de construcción crece en forma acelerada, el de población no alcanza a igualarlo. Y sin embargo se sostiene la crisis habitacional.
+De 1991 a 2001 la cantidad de viviendas creció un 37 por ciento, mientras la población creció un 17 por ciento. De 2001 a 2010: las viviendas crecieron un 18 por ciento y la población un 10. Y de 2010 a 2022: las viviendas crecieron un 28 por ciento y la población un 14, en términos nacionales.
+Aun así se mantiene el nivel de población sin hogar, o con dificultades para acceder a un alquiler o a compra de viviendas. No hay una relación equivalencial positiva entre el número de casas construidas, y el aumento poblacional en los mismos períodos.
+[H2] Datos país, censo por censo
+En 1991: Hay 8.515.441 viviendas y 30.785.593 habitantes.
+En 2001: Hay 11.677.152 viviendas y 36.260.130 habitantes.
+En 2010: Hay 13.835.751 viviendas y 40.117.096 habitantes.
+En 2022: Hay 17.780.210 viviendas y 46.440.703 habitantes.</t>
   </si>
   <si>
     <t>¿Qué hay detrás de la autorización de la tenencia y portación de armas en Ecuador?</t>
@@ -1600,7 +3928,37 @@
     <t>https://www.pagina12.com.ar/538065-que-hay-detras-de-la-autorizacion-de-la-tenencia-y-portacion</t>
   </si>
   <si>
-    <t>2023-04-05T14:51:40Z</t>
+    <t xml:space="preserve">Título: ¿Qué hay detrás de la autorización de la tenencia y portación de armas en Ecuador?
+Chapeau: Portación armas, software de espionaje y beneficios a empresas extractivistas
+Subtítulo: "El decreto de Lasso está orientado a beneficiar a los empresarios de seguridad privada que van a hacer importantes negocios ofertando el servicio a floricultores, ganaderos, bananeros, pescadores, petroleros, mineros y banca privada”, explicó Luis Córdova, experto en seguridad.
+Editoria: Ecuador
+Tags: Ecuador, Guillermo Lasso, guillermo-lasso
+URL: https://www.pagina12.com.ar/538065-que-hay-detras-de-la-autorizacion-de-la-tenencia-y-portacion/
+Notícia completa (24 blocos):
+La reciente autorización de tenencia y portación de armas de uso civil para defensa personal en Ecuador despertó críticas en la sociedad. Universidades, organizaciones de derechos humanos y expertos en seguridad se expresaron en contra del decreto ejecutivo firmado esta semana por el presidente Guillermo Lasso. La flexibilización de la tenencia y porte de armas no es una decisión aislada, afirma el experto en temas de seguridad, Luis Córdova, quien además indica que los grandes beneficiarios de esta flexibilización son las empresas de seguridad privada. Junto a este decreto ejecutivo, el mandatario ecuatoriano también abre la puerta al uso de software de espionaje como Pegasus desarrollado por la empresa israelí NSO Group.
+“Es parte de una política que viene empujando el gobierno, no es una política idónea para disminuir la violencia pero sí es una política adecuada para incrementar el control social en la represión”, precisó Córdova, director del programa de investigación Orden, Conflicto y Violencia de la Universidad Central de Ecuador.
+[H2] Reformas a las leyes de seguridad
+La política de seguridad de la que habla Córdova está enmarcada en la Ley Orgánica Reformatoria a Varios Cuerpos Legales para el Fortalecimiento de las Capacidades Institucionales y la Seguridad Integral.
+La normativa fue aprobada el pasado cinco de enero de 2023 y contó con el voto favorable de 117 asambleístas. La ley fue publicada en el Registro Oficial el pasado 29 de marzo y todas sus reformas entraron en vigencia, excepto la reforma al Código Orgánico Integral Penal (COIP) que entra en vigor 30 días después de la publicación.
+En total, la ley reforma nueve cuerpos legales, uno de ellos es el Código Orgánico Integral Penal (COIP). La ley aprobada en enero incluyó la reforma a dos artículos del COIP sobre la tenencia y portación de armas de fuego.
+“El Decreto Ejecutivo del presidente mediante el cual permite esto del porte y tenencia de armas a civiles también le da seis meses al ministerio de Defensa y al de Interior para que actualicen su normativa”, explicó el experto en seguridad.
+El director del programa de investigación Orden, Conflicto y Violencia de la Universidad Central de Ecuador, explicó que esta ley que reforma la política de seguridad “se vale de enormes distractores”.
+“Todo el mundo pasó hablando del referéndum y si cabe o no la extradición, después vino el fracaso de las elecciones para el presidente y luego la denuncia de la implicación con la mafia albanesa y ahora todo el mes de marzo pasamos hablando sobre el juicio político”, analizó.
+[H2] Ciber espionaje
+Para Córdova, otro dato preocupante sobre la reforma al Código Orgánico Integral Penal (COIP) es que permite “la captación de datos informáticos abriendo la puerta al ciber espionaje sin la autorización judicial”, explicó el experto en seguridad.Córdova considera estas reformas como una ampliación a la “política punitiva en materia de narcotráfico y crimen organizado poniendo en riesgo las reglas del debido proceso que deberían primar en cualquier país que se precie de ser democrático”.
+“En el fondo están avanzando una política absolutamente peligrosa para las reglas democráticas del país. Apunta a mejorar sofisticadamente la represión y el control. Porque reprimir no sólo es darle toletazos al manifestante, sino neutralizar su capacidad de actuación”, añadió Córdova.
+“Cuando se abren las puertas para el ciberespionaje entra y calza perfectamente con los acuerdos que firmó el gobierno (de Ecuador) con el gobierno de Israel…es muy probable que esos acuerdos impliquen la adquisición del famoso software de espionaje Pegasus que ha servido en otros países para hacer espionaje incluso a periodistas”, denunció.
+[H2] Política de seguridad militarista, elitista y narcotizada
+Las reformas de las ocho leyes restantes entraron en vigor desde que se aprobó la ley en enero. Según el portal web de la Asamblea Nacional (congreso), la ley reformatoria de varios cuerpos legales modifica varias disposiciones legales vinculadas a la seguridad pública y del Estado, defensa nacional, derecho penal y procesal penal, Sistema Nacional de Rehabilitación Social, ejecución de penas, desarrollo integral de adolescentes infractores.
+Este amplio paquete de reformas incluye darle la facultad al ministerio de Defensa para que emita informes en los proceso de contratación, es decir, la concesión de una mina o un pozo petrolero deberá contar con estos informes y con una clausula especial de seguridad para que las Fuerzas Armadas garanticen la seguridad a las empresas que tengan este tipo de concesiones.
+“Donde apunta la tendencia de la política de seguridad del gobierno es una política de seguridad militarista, elitista, y narcotizada”, reforzó el experto en seguridad.
+[H2] Hacia un modelo extractivista
+“Apunta a consolidar un modelo extractivo en términos económicos a través de la violencia. En el Ecuador hay una enorme conflictividad social con el movimiento indígena y campesino por la expansión de la frontera minera, petrolera y por la expansión de los agronegocios entonces aquí lo que se está buscando es permitirle a los intereses empresariales vinculados a estos sectores que armen cuerpos de seguridad privada que puedan perfectamente enfrentar a los comuneros, campesinos y activistas y a sangre y fuego imponer lo que no han podido imponer respetando las reglas constitucionales”, explicó.
+En este sentido, Córdova argumenta que incluso la reciente autorización de tenencia y porte de armas “está orientada fundamentalmente a beneficiar a los empresarios de seguridad privada, que muchos de ellos son policías y militares de servicio pasivo, ellos son los que van a hacer importantes negocios ofertando el servicio de seguridad privada a floricultores, ganaderos, bananeros, pescadores, petroleros, mineros y banca privada”.
+[H2] Armas baratas
+Unprocessed element [b]
+“Crea y expande un mercado de armas en el Ecuador que ya es la segunda economía criminal más grande según el Índice Global de Crimen Organizado”, denunció. El Decreto Ejecutivo de Lasso faculta a las Fuerzas Armadas para que produzcan y fabriquen armas. “Esto quiere decir que les está entregando no sólo el control y la supervisión de las armas que van a distribuir, sino que además les está entregando la posibilidad de un negocio adicional”, detalló Córdova.
+“Esto sólo se entiende porque el gobierno ante su debilidad política y social, deslegitimado como está, pretende atrincherarse en el respaldo del músculo militar y policial. La entrega de prevendas y de tantas prerrogativas les da acceso a todo lo que pidieron, porque aspira a que así logrará terminar su mandato”, denunció el experto en seguridad que remarca que todo esto sucede en un país con una importante fragilidad institucional.</t>
   </si>
   <si>
     <t>Deforestación sin control: la Amazonia brasileña llegó a un punto de no retorno</t>
@@ -1612,7 +3970,43 @@
     <t>https://www.pagina12.com.ar/516341-deforestacion-sin-control-la-amazonia-brasilena-llego-a-un-p</t>
   </si>
   <si>
-    <t>2023-03-30T11:01:12Z</t>
+    <t xml:space="preserve">Título: Deforestación sin control: la Amazonia brasileña llegó a un punto de no retorno
+Chapeau: Cuáles son los factores que más influyen en la destrucción del "pulmón del planeta"
+Subtítulo: Los incendios forestales sin control, la tala desmedida, el avance del agronegocio y el extractivismo ilegal son algunos de los responsables de la pérdida de superficie verde. Según los especialistas, en los últimos años las tasas de deforestación “se salieron de control”.
+Editoria: Brasil
+Tags: Brasil, Medio Ambiente, Amazonia, Incendios forestales, medio-ambiente, incendios-forestales
+URL: https://www.pagina12.com.ar/516341-deforestacion-sin-control-la-amazonia-brasilena-llego-a-un-p/
+Notícia completa (30 blocos):
+La selva más grande del mundo ya emite más dióxido de carbono del que puede almacenar. Los incendios fuera de control y la tala desmedida registrados en la Amazonia ponen en peligro el cumplimiento del compromiso asumido en el Acuerdo de París para no elevar la temperatura de la atmósfera más de dos grados centígrados respecto de los niveles preindustriales. El pulmón del planeta, como también lo llaman, llegó a un punto de no retorno.
+Según un estudio dado a conocer a fines de 2022 por el Instituto Nacional de Investigaciones Espaciales (INPE) de Brasil, se estima que durante el año pasado fueron deforestados 11.658 kilómetros cuadrados de la selva amazónica. Los datos son resultados del Programa de Monitoreo Satelital de la Selva Amazónica brasileña (PRODES), que todos los años estima la tasa de deforestación anual a través de imágenes satelitales.
+Los números confirman la tasa ascendente de deforestación producida durante los cuatro años de gestión de Jair Bolsonaro: se perdieron 45.586 kilómetros cuadrados de la Amazonia, un 59,5 por ciento más en relación al período 2015-2018, abarcado por el segundo gobierno de Dilma Rousseff y el de Michel Temer.
+[H2] Deforestación fuera de control
+“En los últimos cuatro años las tasas de deforestación se salieron de control”, afirma Marco Lentini, investigador y coordinador de proyectos del Instituto de Manejo y Certificación Forestal y Agrícola (IMAFLORA). “La desprotección del Amazonas está acompañada por una caída muy grande de los recursos que tenían los diferentes Estados para hacer inspecciones y combatir las actividades ilegales. Hubo, por lo menos, negligencia por parte del gobierno brasileño en relación a la deforestación de la Amazonia”, asegura.
+En Brasil, el negocio maderero emplea alrededor de 200.000 personas y destina el 80 por ciento de su producción al mercado interno. A la disminución de los controles contra la tala ilegal se suman las estrategias desplegadas por quienes cortan la madera para no ser detectados. En muchos casos instalan pequeños campamentos que actúan al mismo tiempo utilizando motosierras, que pueden destruir hasta tres hectáreas por día. Cuando los satélites detectan el área deforestada, ya es demasiado tarde.
+El informe del INPE señala que después de llevar a cabo procesos de tala superficial es común utilizar el fuego para eliminar los residuos de vegetación acumulados en el suelo. En el 2022 se detectaron más de 110.000 focos de incendios en la región, la cifra más alta de los últimos doce años.
+[H2] De neutralizar el carbono a emitirlo
+Según el Fondo Mundial para la Naturaleza (WWF), la selva amazónica alberga entre 90.000 y 140.000 millones de toneladas de carbono (un 10 por ciento del carbono mundial), lo que lo convierte en un actor clave para mitigar los efectos del cambio climático.
+Pero en el último tiempo las emisiones de carbono producto de los incendios provocaron que el ecosistema pasara de ser un sumidero de carbono a una fuente de emisión. “Todo el carbono almacenado en los árboles es devuelto a la atmósfera cuando se los tala”, explica Lentini. En la actualidad, alrededor del 40 por ciento de las emisiones brasileñas provienen de la deforestación y los incendios que ocurren en la Amazonia.
+“Esto hace que sea imposible mantener el objetivo de alcanzar un calentamiento global de un grado y medio o dos grados para el 2100”, asegura el investigador. El acuerdo de París, que entró en vigencia en 2016, tiene como uno de sus objetivos limitar el aumento de la temperatura global por debajo de los dos grados para fin de siglo y esforzarse para limitar este aumento a tan solo un grado y medio. Para Lentini, si se quema la Amazonia, "la temperatura podría aumentar entre tres y cuatro grados y medio”.
+[H2] Los incendios también provocan la falta de lluvias
+La selva amazónica es conocida por ser uno de los biomas más importantes de Latinoamérica porque alberga un conjunto de diversos ecosistemas que interactúan entre sí. Tiene un rol clave en la configuración de las lluvias de América del Sur. Además de poseer el río más grande del mundo -el Amazonas, que se extiende por 6.900 kilómetros y vierte al océano Atlántico el 15 por ciento del agua dulce del planeta- acumula grandes cantidades de agua evaporada, que es lanzada a la atmósfera por los árboles en forma de corrientes de vapor y llevada a Brasil, Bolivia, Paraguay y Argentina.
+No solo la disminución de árboles afecta la producción de lluvias en la selva. Las partículas liberadas por los incendios impiden que las nubes permanezcan cargadas hasta convertirse en lluvia y sean llevadas a otros lugares provocando sequías. Para Lentini, la situación “es crítica”. “A este ritmo -dice- en diez años Brasil ya no producirá granos”.
+En gran parte del bioma la humedad impide la formación de incendios de manera natural. “Pero al abrir la selva aumentan la probabilidades de que incluso las zonas más húmedas comiencen a arder”, describe el investigador.
+Además de la tala para obtener madera, muchos árboles son cortados para plantar soja o criar ganado. Cuando la tala es mal administrada, las áreas explotadas se vuelven mucho más susceptibles a incendios y al crecimiento de especies capaces de colonizar rápidamente el lugar. De este modo, se ve afectada la regeneración de las especies perdidas y la sostenibilidad a largo plazo de la selva.
+La minería es otra de las causas de apertura de la selva. En muchos casos, para iniciar los trabajos se abre una red de caminos y el sector maderero encuentra allí la posibilidad de extraer los árboles de alto valor que se encuentran en el lugar. “Sin embargo, lo que hay que observar de esta actividad es de qué manera se relaciona con las comunidades tradicionales y pueblos indígenas. Hay una cuestión que tiene que ver con infringir derechos, con la aplicación de coerción, de corrupción. Hay, incluso, una tentativa de dañar cuestiones culturales”, explica Lentini.
+[H2] Pueblos indígenas atacados
+“Los pueblos indígenas y las comunidades tradicionales de la Amazonia son los que sienten con su piel el avance de la deforestación y la destrucción en la selva”, agrega Leandro Ramos, director de campañas de Greenpeace Brasil. De acuerdo a la última edición del informe Violencia contra los Pueblos Indígenas en Brasil, del Consejo Indigenista Misionero (CIMI), durante 2021 fueron asesinados 99 líderes indígenas en los Estados de la selva amazónica.
+Según Ramos, estas comunidades de Brasil nunca fueron tan atacadas como en los últimos años. “Es fundamental que el Estado avance en la creación de áreas protegidas y en la demarcación de tierras indígenas. Los derechos de estas poblaciones deben ser garantizados y protegidos por el Estado. Estas tierras promueven efectivamente la protección de la selva y de las personas que la habitan”, asegura.
+Durante la gestión de Bolsonaro, los procedimientos de delimitación de esos territorios fueron suspendidos.
+[H2] Punto de no retorno
+Para Ramos, los ecosistemas de la selva amazónica “son nuestro pasaporte al futuro”. Las consecuencias de la destrucción en la Amazonia son muchas y muy graves: sin ella no habría agua, producción de alimentos ni aire puro. La vida que conocemos no existiría sin la selva”, opina.
+Durante años los científicos alertaron acerca de la importancia de mantener al menos el 80 por ciento de la selva en pie para no llegar a un “punto de no retorno”: una ruptura del equilibrio de gran parte del bioma amazónico significaría que muchos de los beneficios ambientales que hoy proporciona la selva dejen de existir.
+“Si contamos el área completa del Amazonas, con los nueve países que la integran, hoy estamos en un nivel cercano al 75 por ciento”, alerta Lentini. “Ya hemos pasado el límite seguro para la humanidad. Llegará un momento en que ya no servirá ir a la selva y plantar nuevos árboles. El balance hídrico, el clima y las corrientes marinas ya no serán como antes”.
+[H2] Cómo producir sin matar a la selva
+Según el representante de Imaflora, la deforestación “le quita madera a los indígenas y a las poblaciones tradicionales. Es un modelo que se vuelve cada vez más destructivo”. Además, la manera en que se obtiene la madera de forma ilegal impide realizar una buena planificación de la actividad que se realiza.
+En cambio, los modelos de manejo forestal –uno de los principales ejes de trabajo de la institución- reducen el impacto en el ambiente. “En estos casos se pueden cortar cuatro árboles por hectárea cada 30 o 35 años. De ese modo, la selva se mantiene intacta en el tiempo”, asegura Lentini. “Hay grandes empresas de la Amazonia que, a través de los años, aprendieron a adoptar mejores prácticas”.
+Además de trabajar junto al sector agropecuario para producir sin deforestar, Imaflora se ocupa de la búsqueda de alternativas para que las personas que habitan la Amazonia puedan realizar actividades productivas de menor impacto.
+En la selva pueden encontrarse materias primas útiles para la industria gastronómica y farmacéutica. Según Lentini es importante trabajar en la creación de proyectos, programas y subsidios para que las comunidades del lugar puedan vivir de su trabajo en la selva sin afectar al ambiente. “Si la ganadería y los planes de cultivo de soja fueron subsidiados durante años, ¿por qué no podemos subsidiar a quienes realizan otros tipos de producciones?”, plantea finalmente el investigador.</t>
   </si>
   <si>
     <t>Paula Llana</t>
@@ -1627,7 +4021,43 @@
     <t>https://www.pagina12.com.ar/534521-camps-el-hitler-que-sometio-a-los-bonaerenses</t>
   </si>
   <si>
-    <t>2023-03-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: Camps, el Hitler que sometió a los bonaerenses
+Chapeau: La vigilancia de la dictadura llegaba a escuelas, alumnos y docentes
+Subtítulo: En la provincia de Buenos Aires la policía comandada por el general Ramón Camps montó un gigantesco aparato de espionaje.
+Editoria: Buenos Aires|12
+Tags: Dictadura, printed-edition
+URL: https://www.pagina12.com.ar/534521-camps-el-hitler-que-sometio-a-los-bonaerenses/
+Notícia completa (30 blocos):
+La reacción política y sindical democrática a la llamada "Gestapro" (el operativo de espionaje montado en la Provincia por el macrismo) tiene su explicación en el pasado. Las prácticas persecutorias, que incluyeron vigilancia de las redes sociales, y contra los trabajadores de la educación y, en especial, de sus dirigentes gremiales, llevadas a cabo durante los años de la gestión de María Eugenia Vidal en la provincia de Buenos Aires, revivieron los peores fantasmas de la historia bonaerense. La impronta antisindical, el espionaje y la delación, el clima opresivo, marcaron el período comprendido entre 1976 y 1983, sobre todo cuando ejerció la jefatura de la Policía Bonaerense el general Ramón Camps.
+Buenos Aires/12 accedió a una serie de documentos de la Comisión Provincial por la Memoria que dan cuenta del espionaje sistemático ejercido por las fuerzas represivas en las instituciones educativas de la provincia de Buenos Aires durante la última dictadura militar.
+Los documentos demuestran que las políticas de espionaje ilegal no se circunscribían ni al conurbano que rodea a Buenos Aires ni a la capital provincial. Existe material sobre investigaciones en Rojas, Lincoln, 9 de julio y Carlos Casares, en el centro de la provincia. Ni las escuelas agrarias se salvaban, como lo prueba el caso de las Escuelas de Familia Agraria (EFA), que se detalla unas líneas más adelante. Los documentos, a su vez, están clasificados en tres grupos: organismos de inteligencia sobre instituciones educativas, manifestaciones antidictadura en instituciones educativas y, tal vez el más inquietante, espionajes realizados por la propia comunidad educativa.
+Infierno grande
+En este último grupo se inscribe el espionaje a docentes del Colegio Nacional de Carlos Casares, un pueblo sobre la ruta 5, hoy famoso por ser sede del poderoso grupo Los Grobo y su equipo de fútbol Agropecuario, que milita en la B nacional, pero que en 1976, cuando ocurrieron estos hechos, tenía menos de 20 mil habitantes.
+La carta fechada el 29 de junio de 1976, apenas tres meses después del golpe, está prolijamente tipeada, dirigida al “Exmo, Señor Ministro del Interior Gral Albano Harguindeguy” y firmada por “UN GRUPO DE PADRES”. El contenido de la misiva da cuenta de la preocupación de estos por la educación de sus hijos, ya que ciertos docentes utilizaban como bibliografía obligatoria para sus clases de la materia Estudio de la Realidad Social Argentina (ERSA), el libro “Las venas abiertas de América Latina”, del escritor uruguayo Eduardo Galeano, texto “de ideología izquierdista e izquierdizante”.
+La carta anónima, lejos de ser desechada, fue el desencadenante de una serie de investigaciones posteriores, que constan en el mismo legajo nro. 15719 de la mesa “D”. De acuerdo a esos informes, “ya en 1974, quejas de los padres, por las que el rectorado inició acciones ante el ministerio de Educación”, pero en 1976 “los mismos docentes continúan dando clases”. Y los mismos “son el alma mater de la biblioteca popular José Ingenieros, cita en Maipú 369” de la misma localidad, donde, quién lo hubiera dicho, “abunda material bibliográfico”.
+La aparición de un nuevo pedido de informes disparaba también la búsqueda de antecedentes del o los sospechosos en ese mismo archivo. Si dicha búsqueda resultaba positiva, se copiaban en el mismo legajo. En este caso, por ejemplo, consta que “habría viajado a Cuba vía México en 1962”, “integró la junta promotora del Encuentro Nacional de los Argentinos a nivel local”, “presidió la biblioteca popular José Ingenieros en 1968”. La frase que puede haberlo salvado es “no se detecta actuación política en superficie”.
+La Comisión Provincial de la Memoria protege la identidad de las víctimas de espionaje, de manera que no es sencillo reconstruir la historia completa, saber si los espiados fueron secuestrados, si continúan detenidos desaparecidos, si tuvieron chance de exiliarse o pudieron continuar con sus vidas. Lo que se desprende de los documentos es el clima de persecución, vigilancia y paranoia que reinaba en aquellos años, aún en parajes en apariencia tranquilos, donde todos se conocían, se dormía la siesta y se tomaba mate en la vereda.
+El dicho popular “pueblo chico, infierno grande” adquiere una nueva dimensión, en la que nada ni nadie es lo que parece y, si cualquier denuncia anónima basta para iniciar un sumario, nadie está realmente a salvo.
+Citroen rojo
+De los documentos se desprende que el espionaje no se circunscribía exclusivamente a los establecimientos de gestión pública. En el archivo no consta el origen de la denuncia o sospecha que dispara estas actuaciones, dentro del ámbito de una escuela confesional.
+“En el colegio Pío XII, frente al destacamento de Villa Bosch, partido de Tres de Febrero, hay un maestro de nombre XXXXX, estudiante de medicina, falta con frecuencia, permanentemente adoctrina a sus alumnos contra militares y policías. Anda en un Citroen rojo”, resume la primera página del legajo 6159. Y, a continuación, ordena lo que “interesa saber: una amplia investigación que ratifique o rectifique lo expresado anteriormente, datos de identificación completos del causante, constatar propiedad del automotor mencionado, concepto social y laboral, todo dato que se estime de interés consignar”, con fecha 3 de septiembre de 1976.
+Es llamativa la celeridad con que se cumplen los encargos. Apenas dos semanas más tarde, el 17 de septiembre, se adjunta el informe resultante de las pesquisas. El sujeto en cuestión “se desempeña como maestro de tercer grado, como suplente desde 1969 y como titular desde 1970”, “cursa el último año de medicina y realiza prácticas en el Policlínico de San Martín, por este motivo falta a la escuela con permiso de sus superiores”, “maneja un Citroen color ladrillo chapa R63267”, “tanto él como su familia gozan de buen concepto entre los vecinos” y “no se pudo determinar que adoctrine a sus alumnos”.
+El veredicto final del informe es coincidente con los archivos de la Comisión de Familiares de Detenidos Desaparecidos de Tres de Febrero: ninguno de los 300 desaparecidos del distrito era un docente con un Citroen rojo.
+Edgardo Fontana, “Cambá”, reconocido por sus compañeros como una especie de archivo viviente, rememora, chequea y finalmente sostiene que “la dirección no coincide con la de ningún desaparecido. Había un compañero ferroviario, pero a media cuadra de distancia de ahí. El Citroen rojo no era habitual, por eso habrá llamado la atención. Había un compañero que andaba en un Citroen rojo, pero estudiaba ingeniería, no medicina”. Y agrega: “hubo tres desaparecidos en el Pío XII, pero las autoridades de ese colegio todavía no accedieron a homenajearlos”.
+Actualmente, Cambá ultima detalles de un libro que recopila y reconstruye las experiencias de militancia de los años sesenta y setenta en la zona, además de las historias personales de los 300 compañeros detenidos desaparecidos. y el accionar de los servicios de inteligencia.
+Escuelas peligrosas
+Si el caso del Colegio Nacional de Carlos Casares expone cómo se observaba a ciertos docentes, por sus acciones disonantes con el espíritu de una determinada institución educativa, el caso de las Escuelas de Familia Agraria muestra cómo se ponía bajo la lupa, directamente, a un modelo educativo, a partir de un pedido de colaboración del Ejército Argentino, remitido al jefe de la Policía Bonaerense, con fecha 9 de mayo de 1980. El pedido de información es muy general y requiere “ubicación geográfica, responsable del mismo, cantidad de alumnos, cantidad de docentes, antecedentes de los mismos y concepto ambiental respecto de la educación proporcionada”.
+Las Escuelas de Familia Agraria habían llegado a Argentina a fines de los años sesenta, copiando un modelo de organización de origen francés de la década del treinta, las “maisons familliaires”: bajo la forma jurídica de mutuales o asociaciones civiles, asentadas en pequeñas poblaciones rurales, con el objetivo de que los hijos de los campesinos y productores pudieran estudiar sin cambiar de hábitat.
+El informe elaborado por la policía da cuenta de la existencia de trece escuelas con estas características, la mayoría ubicadas en las provincias de Santa Fe y Entre Ríos y sólo dos en Buenos Aires: la “Dr. Ignacio Pirovano” en Bolívar y la “Dr. Ernesto Nazar” en Colón, y de un órgano que las dirige y nuclea, la Asociación de Promoción de las Escuelas de Familia Agraria (APEFA), cuyo funcionamiento también detalla.
+Las conclusiones son contundentes. Las escuelas tienen una “evidente tendencia izquierdista”, forman parte de “un sistema que no se puede controlar” y, en consecuencia, “resulta de extrema peligrosidad para la seguridad nacional”. Pero lo más curioso es que, cuando la policía emite el informe solicitado, el ministerio de Educación ya había resuelto “la derogación progresiva de dicho sistema educativo” a través de la resolución 345/74 del 7 de marzo de 1980. Esta obligaba a no abrir cursos de primer año en 1980, ni de segundo en 1981 y así sucesivamente hasta su disolución. Otra resolución de la misma fecha, la 344, deja sin efecto el plan de estudio del Centro de Formación de Monitores, donde las EFA formaban a sus propios docentes.
+En este caso, llama la atención la duplicación de procedimientos y la falta de conocimiento de lo que ocurría al interior del mismo estado. Si las autoridades del ejército hubieran leído el boletín oficial hubieran sabido en tiempo y forma que, de haber existido algún peligro, ya se encontraba conjurado y hubieran evitado que la policía bonaerense tuviera que investigar más allá de sus fronteras geográficas.
+Para los represores de las provincias del litoral, la palabra “agraria”, aún cuando formara parte del nombre de unas escuelas, remitía invariablemente a las ligas agrarias, organizaciones campesinas de base que llegaron a reunir a más de 50 mil personas y fueron totalmente desarticuladas por el terrorismo de estado. Eran integradas por pequeños productores, de actividades marginales desde el punto de vista del agronegocio, como tabaco, algodón y yerba y pujaban, entre otras cosas, por percibir mejores precios de los acopiadores y procesadores.
+Integrar una institución con la palabra “agrarias” en el nombre podía ser una actividad de riesgo, tanto como manejar un Citroen rojo.
+Vigilar la escuela
+Los documentos comentados pertenecen a la inteligencia de la dictadura y fueron desclasificados por iniciativa de Carlos Arslanian cuando ejerció por primera vez como ministro de Seguridad bonaerense. Integran la colección “Vigilar la escuela”, organizada y curada por la CPM, con el objetivo de integrarlos a la currícula educativa como contenidos pedagógicos. “Vigilar la escuela” incluye videos, testimonios, trabajos prácticos, cuestionarios y guías para los docentes.
+El último 16 de septiembre, a modo de conmemoración de la Noche de los Lápices, en el marco de un encuentro de juventudes, la comisión trabajó con escuelas del distrito de San Martín, sobre el seguimiento de la actividad panfletaria que hacía la DIPPBA, a partir de los documentos que obran en su poder.
+La Comisión por la Memoria (CPM) es un organismo público autónomo y autárquico que promueve e implementa políticas públicas de memoria y derechos humanos. Reúne el mayor archivo de espionaje político conocido, después del de la Stasi de Alemania Oriental y realiza, cada año, el encuentro "Jóvenes x la memoria" en Chapadmalal, del que participan instituciones culturales, sociales y barriales y recuperó la presencialidad el año pasado, tras el parate obligado por la pandemia.
+La CPM fue creada por resolución legislativa de la Cámara de Diputados de la provincia de Buenos Aires 2117 de 1999, y ratificada por ley provincial 12.483 del 13 de julio de 2000 y su modificatoria, la ley 12.611 del 20 de diciembre de 2000. Desde marzo de 2001 tiene como sede el edificio donde funcionó la Dirección de Inteligencia de la Policía de la Provincia de Buenos Aires (DIPPBA), señalizado como sitio de memoria por la Secretaría de Derechos Humanos de la Nación.</t>
   </si>
   <si>
     <t>Gastón Garriga</t>
@@ -1642,7 +4072,50 @@
     <t>https://www.pagina12.com.ar/530036-mujeres-y-disidencias-marcharon-contra-la-violencia-machista</t>
   </si>
   <si>
-    <t>2023-03-09T05:06:47Z</t>
+    <t xml:space="preserve">Título: Mujeres y disidencias marcharon contra la violencia machista en distintos municipios
+Chapeau: Las agendas feministas desde los territorios
+Subtítulo: Movilizaciones por soberanía alimentaria, contra la violencia y el agronegocio, y el acceso al agua y la luz. También por la revictimización que sufren las víctimas de violencia, la falta de acceso a la vivienda y al trabajo, algunas de las demandas en el territorio salteño.
+Editoria: Salta|12
+Tags: 8 de Marzo, 8-de-marzo, diario
+URL: https://www.pagina12.com.ar/530036-mujeres-y-disidencias-marcharon-contra-la-violencia-machista/
+Notícia completa (37 blocos):
+En el marco del 8 de marzo, las mujeres y disidencias de distintos municipios del interior de la provincia de Salta, también ocuparon las calles, organizadas con demandas a los distintos poderes del Estado, denuncias y reinvidicaciones de derechos desde sus territorios.
+Las mujeres y disidencias de los movimientos populares La Dignidad; Darío Santillán; 8 de Abril; integrantes de la Mesa de Género del departamento San Martín, marcharon en la mañana, "por la soberanía alimentaria, contra la violencia y el agronegocio".
+Las organizaciones se dirigieron al Poder Judicial de Tartagal con la consigna, "Con esta justicia no hay derechos ni democracia". La coordinadora de la Mesa de Género y del área feminismo popular y disidente de La Dignidad, Pamela Fernández, dijo a Salta/12 que reclaman el acceso a la justicia para las mujeres de pueblos indígenas, "siempre denunciamos que el poder judicial es racista y patriarcal", señaló.
+Fernández contó que intentaron manifestarse en las escalinatas del edificio pero la policía se los impidió. Incluso contó que fue intimidada por un un sargento: "le recomiendo que haga caso, porque las consecuencias, que no van a ser para sus compañeras que están afuera, sino para usted, pueden ser muy graves", le dijo. La militanta reprochó que para intimidar en una manifestación la policía despliegue recursos, mientras que no los tienen para cumplir las consignas policiales en causas de violencia de género.
+"Llevamos el nombre de todas las mujeres víctimas de femicidio, hicimos mucho hincapié con los nombres de las víctimas del departamento San Martín", contó Fernández, y dijo que relevaron 40 femicidios.
+El pliego de demandas de las organizaciones incluye "denuncias a los terricidas", "realizamos acompañamiento a mujeres que defienden sus comunidades, que fueron desalojadas por la policía, en su momento escrachamos a fiscales y jueces", explicó Fernández. Relató que en la zona hubo mujeres indígenas amenazadas por finqueros en el contexto de la lucha por el territorio. "El agronegocio, las fumigaciones con glifosato, la falta de agua", las cuales son parte de las problemáticas contra las que protestan.
+Fernández indicó que participaron de la marcha las mujeres que también se organizaron en el acampe que sostiene los reclamos "por la luz y el agua". Señaló que el agua es una de las principales demandas en Tartagal, denunció que muchas comunidades originarias no acceden a este derecho humano. Además mencionó el enorme esfuerzo de las cocineras comunitarias de merenderos y comedores que a diario se las ingenian para llevar agua y asistir a infancias y adultxs mayores, lugares donde además cocinan a leña con las altas temperaturas porque no acceden al gas.
+"Casi el 80 por ciento de las organizaciones del norte están conformadas por mujeres" sostuvo Fernández para enmarcar la demanda por las altas en el programa Potenciar.
+"Estuvimos denunciando que se investigue lo que ha pasado con el programa Acompañar, la exdirectora está denunciada por pedir coimas. Que se aceleren los procesos y se garantice la protección a las víctimas", añadió.
+Fernández se pronunció contra la "romantizacion de las fechas", "y la banalizacion de los temas (de género), cuando las mujeres necesitan políticas públicas concretas". Explicó que en la localidad hubo quejas porque la intendencia llamó a las trabajadoras para "un agasajo" y les dio "bizcochos con agua" en el salón auditorium de la municipalidad. La referenta dijo que "las compañeras vienen reclamando cosas importantes desde lo sindical", y en vez de avanzar con respuestas serias, esto fue "una burla a las compañeras".
+[H2] Contra la policía en Salvador Mazza
+En Salvador Mazza también marcharon las mujeres de los movimientos sociales: la Corriente Clasista y Combativa (CCC), Ni un Pibe Menos por la Droga (de la CCC), Nuestra América, el Partido Comunita Revolucionario (PCR), el Polo Obrero, la UTEP, la Federación Nacional Campesina (FNC), Originarios en lucha, rl Movimiento Territorial Rebelde (MTL) y Barrios de Pie.
+Las organizaciones se manifestaron frente a las instituciones locales, una de las principales fue ante la Comisaría 40. En ese lugar reclamaron contra la policía por haberse negado a tomarle la denuncia a la madre de una niña de 12 años desaparecida, que después fue hallada por la familia y contó que había sido víctima de violencia sexual por un desconocido que ahora está prófugo. "No le quisieron tomar la denuncia a la madre aduciendo que el protocolo es por 24 horas pero no está vigente eso", dijo la militanta de la CCC, Karina Herrera.
+"Cuando una persona va a denunciar una desaparición o un abuso de género, se tiene que tomar inmediatamente la denuncia (...) cuando no pasa, aparecen las mujeres como uno no quiere, aparecen violadas o muertas", advirtió Herrera.
+Además de adherir a las consignas nacionales, Herrera planteó que requieren instituciones municipales que asistan a las víctimas. "No tenemos un lugar a donde recurrir cuando tenemos mujeres maltratadas, a donde puedan refugiarse. Un refugio nos hace falta. Necesitamos una oficina que sea de la mujer", manifestó.
+[H2] Reforma judicial feminista
+Clara Flores es trabajadora del Poder Judicial e integra la colectiva feminista Panambi en Orán. Desde la organización realizaron una mateada para encontrarse y reflexionar sobre las problemáticas que atraviesan a mujeres y disidencias en la localidad. “Las demandas siempre son las mismas: basta de violencia de género; basta de femicidios, que las trabajadoras informales puedan formalizar el empleo, y la efectivización del cupo laboral trans", dijo a Salta/12.
+Flores explicó que en el municipio de Orán está aprobado el cupo laboral trans travesti en la municipalidad, “pero no se cumple con el porcentaje del 1%”, indicó que en la administración pública hay cerca de 20.000 empleadas y empleados y "debería haber 20 personas trans trabajando pero solo conoce a tres compañeras que han sido incorporadas".
+Desde la organización, denuncian que la Secretaría de Género y Diversidad municipal "se fue desdibujando" en este último tiempo. Flores señaló que incluso les derivan a víctimas, "las mandan a nosotras cuando no contamos con recursos para acompañarlas", y aunque explicó que como activistas se esfuerzan por brindar información, servir de nexo, y contener, no cuentan con los recursos materiales ni humanos necesarios.
+Como en otros lugares, Flores dijo que falta de implementación de la Ley Micaela en la policía, genera que todavía haya personas que son revictimizadas cuando van a denunciar hechos de violencia machista y a veces “no les quieren tomar la denuncia, les dicen 'ya vas a volver con él, no sé para qué denuncias'”.
+Al Poder Judicial, la colectiva le demanda la reforma judicial feminista y la implementación también del cupo laboral trans.
+También Panambi reclama a las autoridades judiciales el pronto esclarecimiento y justicia por el femicidio de su compañera Nahir Nuri Klimasauskas, quien murió al caer del cuarto piso de un edificio en Orán, cuando se encontraba en el departamento de su pareja Gustavo Viarengo, quien después fue detenido . “Estaban tratando de ver si era femicidio, en primera instancia decían que fue suicidio”, manifestó.
+Nahir tenía 27 años, era feminista y kirchnerista, chef, según contó Flores, e integraba la colectiva Panambi. La joven también es hija de una fiscala penal de Orán. “Sigo consternada por la noticia (...) Nunca nos dijo puntualmente que estaba en un círculo violento", expresó Flores. Sin embargo, aclaró que hubo amigas de la víctima que dijeron que el novio "era violento". "Cuando se acercó (a la colectiva) fue como compañera pero no hablaba de su vida privada", explicó.
+[H2] Demandan políticas públicas en Anta
+En Joaquín V. González, localidad cabecera del departamento Anta, en el sur de la provincia, las mujeres de los movimientos sociales MTL Rebelde y CUBA, también marcharon.
+La referenta del MTL Rebelde, Alicia Pomo, dijo a Salta/12, que eligieron marchar y no sumarse a las actividades de la intendencia, organizadas por el Área de la Mujer, Género y Diversidad Sexual, que realizó una "feria" de emprendimientos y un evento con "un músico".
+La militanta sostuvo que esta área género de la localidad "es un adorno". "Ayer me mandaron un mensaje invitándonos pero no para coordinar, sino para ser parte del bulto", sostuvo reprochando que "con la directora nueva" las organizaciones no consiguen articular la asistencia a las víctimas. "No se ven políticas claras de qué es lo que hace el área de la mujer en Joaquín V. González", manifestó.
+"Los hechos de violencia son cada vez peor. Inclusive con el tema de que los trabajos son cada vez más precarizados", denunció. También dijo que hay muchos casos de violencia contra las infancias y no encuentran acompañamiento estatal.
+En Apolinario Saravia las mujeres de las organizaciones Las Bartolinas, MTL Rebelde y autoconvocadas también se movilizaron en la plaza San Martín, frente a la municipalidad. Entre sus demandas se encuentran el "derecho a la vivienda como urgente", explicó Gabriela Sotelo, directora del Área de la Mujer y Diversidad Sexual que acompañó las actividades. Señaló que la falta de acceso a un lugar donde vivir es uno de los principales impedimentos que encuentran las mujeres "para denunciar, o para salir" de vínculos violentos.
+Las mujeres también plantearon la falta de acceso al trabajo como impedimento para la autonomía. En Saravia, la mayor fuente laboral es en las fincas, precarizada e insalubre "por el contacto con los agrotóxicos", señaló Sotelo, como algo que se planteó en la asamblea previa a la marcha. Otra problemática que se visibilizó en ese contexto fue el trabajo de las infancias, ya que son "familias completas" las que se desempeñan en los trabajos rurales.
+La violencia económica y la enorme cantidad de demandas por alimentos; la revictimización en la justicia, en la policía y en las mediaciones penales; la falta de protocolos sanitarios para abordar los casos de violencia de género, fueron parte de las problemáticas denunciadas.
+La marcha se solidarizó también con la madre de una adolescente que fue víctima de violencia sexual por el progenitor "porque el acusado es de una familia con poder económico y suponen que es un obstáculo para que haya justicia", explicó Sotelo.
+[H2] "Tejer redes contra la violencia en los valles"
+En la zona de los Valles Calchaquíes, en Angastaco, el Área de la Mujer realizó actividades en la plaza para sensibilizar respecto a la violencia machista. La docente y diplomada en violencia por motivos de género Griselda Ferreyra contó a Salta/12 que fue a invitada a dar una charla allí: "Es importante poder tejer redes en lugares aislados de muchas cosas", señaló.
+Angastaco es un lugar donde faltan políticas públicas, y recursos, "necesita más redes", consideró Ferreyra. Señaló que pese a esto, "se intenta trabajar la temática". Esta zona de la provincia además cuenta con una geografía particular, ya que lo urbanizado es el pueblo y después hay lugares aislados y de difícil acceso. "La policía está en el pueblo de Angastaco, se puede ir a determinado lugar en vehículos, y luego en lomo de burro. No hay luz, ni señal de teléfono, en algunos lugares hay paneles solares, nada es inmediato, hasta hace muy poco no había ni agua, usaban el agua de acequia", contó Ferreyra.
+En ese marco, las mujeres y disidencias afrontan la "naturalización de la violencia y del abuso", en los que se intenta "buscar espacios que sean trincheras y de encuentro".
+Ferreyra dijo además que mientras falta la implementación de la Educación Sexual Integral en las escuelas, a las docentes se les impone un código de vestimenta en base a un "estatuto docente, que es de 1969, que (establece) que la vestimenta de las docentes tiene que se decorosa". Ese "decoro" impuesto por la supervisora de educación del lugar incluiría que no tienen que ir con zapatillas ni con calzas, ni con remeras que muestren los brazos. Ferreyra expresó que tales medidas "siguen reforzando estereotipos de género" y además son "obsoletas y disciplinadoras".</t>
   </si>
   <si>
     <t>Claudia Ferreyra</t>
@@ -1657,7 +4130,29 @@
     <t>https://www.pagina12.com.ar/525236-una-investigacion-confirma-vinculos-entre-agua-agroquimicos-</t>
   </si>
   <si>
-    <t>2023-02-20T03:01:00Z</t>
+    <t xml:space="preserve">Título: Una investigación confirma vínculos entre agua, agroquímicos y cáncer
+Chapeau: El trabajo lo realizó la UNR sobre personas jóvenes de pueblos fumigados
+Subtítulo: Una investigación de la Facultad de Ciencias Médicas de la Universidad de Rosario (UNR) confirmó que las personas jóvenes de los pueblos fumigados con agrotóxicos tienen 2,5 veces más probabilidad
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/525236-una-investigacion-confirma-vinculos-entre-agua-agroquimicos-/
+Notícia completa (16 blocos):
+Una investigación de la Facultad de Ciencias Médicas de la Universidad de Rosario (UNR) confirmó que las personas jóvenes de los pueblos fumigados con agrotóxicos tienen 2,5 veces más probabilidad de padecer y morir de cáncer que las personas que viven lejos de los agroquímicos. Los datos se obtuvieron en una investigación inédita en su tipo, que llevó siete años y está basada en estudios epidemiológicos de ocho localidades de Santa Fe (involucró a 27.000 personas). "Con tres décadas de este modelo agroindustrial, ya nadie puede negar que la evidencia científica confirma que el agronegocio daña la salud, genera enfermedad y muerte", afirmó Damián Verzeñassi, del Instituto de Salud Socioambiental de la Facultad de Ciencias Médicas y uno de los autores de la investigación.
+Las Madres de Ituzaingó (Córdoba), el colectivo Paren de Fumigar (Santa Fe), la Coordinadora Basta es Basta (Entre Ríos), el Encuentro de Pueblos Fumigados (Buenos Aires) y la Red de Salud Popular Ramón Carrillo (Chaco). Son solo algunas de las organizaciones y espacios de articulación que desde hace más de dos décadas denuncian el impacto en la salud del modelo de agro transgénico. El trabajo científico "Incidencia y mortalidad por cáncer en localidades rurales argentinas rodeadas de tierras agrícolas tratadas con pesticidas", publicado en la revista internacional Clinical Epidemiology and Global Health (Epidemiología Clínica y Salud Global), confirmó lo que esas organizaciones (y otros científicos y activistas) gritan desde hace muchos años: existe una relación directa entre el modelo transgénico, las fumigaciones con agrotóxicos y el cáncer.
+La investigación fue realizado por el Instituto de Salud Socioambiental de la Facultad de Ciencias Médicas de la UNR. Consistió en estudios epidemiológicos en las localidades de Acebal, Arteaga, Chabás, Luis Palacios, San Genaro, Sastre, Timbúes y Villa Eloísa. Todas tienen la característica de ser pueblos dedicados al agronegocio, con predominio del cultivos transgénicos y uso de agroquímicos. "Vivir en pueblos fumigados aumenta el riesgo de padecer y morir por cáncer", alertan los investigadores Damián Verzeñassi, Alejandro Vallini, Facundo Fernández, Lisandro Ferrazini, Marianela Lasagna, Anahí Sosa y Guillermo Hough.
+Y precisan: "El estudio evidencia que en la población joven (entre 15 a 44 años) la probabilidad de morir por cáncer es 2,48 (mujeres) y 2,77 (hombres) veces mayor en estas localidades en comparación con el resto del país". Y alertan que el porcentaje de fallecimientos por cáncer (tomando la referencia internacional de cien fallecimiento por cada 100.000 habitantes) en estas ocho localidades fue del 30 por ciento, mientras que a nivel nacional la cifra es mucho menor (19,8 por ciento).
+"Se demostró que la incidencia de cáncer en la población de las ocho localidades fue significativamente mayor en comparación a la población general. Y, en particular para la población femenina, se determinó que tiene un 66 por ciento de mayor probabilidad de sufrir algún tipo de cáncer en comparación con la población femenina general del país", remarcaron.
+Damián Verzeñassi apunta a las causas de las estadísticas obtenidas: "El actual modelo agroindustrial no ha hecho más que incrementar los daños en la salud de los territorios y, por tanto, de las personas que vivimos en esos territorios. Nuestro trabajo es un aporte más a una gran cantidad de clara evidencia científica que se vienen haciendo desde hace ya muchos años y que da pruebas concretas de las consecuencias de los pesticidas".
+En la investigación del equipo rosarino se precisó que, en promedio, el 27 por ciento de los pesticidas utilizados en los países de altos ingresos (como Estados Unidos) están en la categoría "altamente peligrosos", mientras que el porcentaje aumenta a 45 en los países de ingresos bajos y medios (como Argentina). "En nuestro país las cantidades por hectárea son muy superiores a las utilizadas en Europa o Estados Unidos", señala la publicación, que cita decenas de trabajos científicos que dan cuenta de la presencia de agrotóxicos en ríos, napas de agua, suelos urbanos, alimentos e incluso en agua de lluvia.
+El equipo de investigación apunta también a los responsables de que esto suceda. "La principal responsabilidad es del Estado que habilita este modelo. También hablamos de los funcionarios, de distintos signos políticos, que sostienen y defienden este modelo de una manera cuasi fundamentalista, sin aceptar una discusión en serio", afirma Verzeñassi. También precisa el rol cómplice del Poder Judicial y del los poderes legislativos, tanto nacional como provinciales. Y señala a los grandes productores, muchos representados en la Mesa de Enlace: "Son partícipes de este proceso que es ecocida y mata a nuestras poblaciones".
+"Y claro que no tenemos que olvidar a las empresas que producen y venden estas sustancias tóxicas, son de las mayores responsables. Saben de los daños que producen y siguen con sus negocios sin importarles el sufrimiento de las poblaciones", denuncia. Entre las empresas que comercializan glifosato en Argentina figuran Bayer-Monsanto, Syngenta, Red Surcos, Atanor, Asociación de Cooperativas Argentinas, Nufram, Agrofina, Nidera, DuPont, YPF y Dow.
+La investigación del Instituto de Salud Socioambiental, en su conclusión, remarca la necesidad de reducir el uso de agrotóxicos y, sobre todo, hace un llamado a aplicar el "principio precautorio", vigente en la legislación argentina, que implica el tomar medidas de protección cuando está en riesgo la salud y ambiente. "Luego de tres décadas de este modelo, de innumerables pruebas tanto en los territorios como en los laboratorios, es urgente aplicar el principio precautorio ante esta forma de producir que atenta contra la vida de las poblaciones", exige Verzeñassi.
+En 2020 la organización Naturaleza de Derechos publicó el informe “Antología Toxicológica del Glifosato +1000”, de 270 páginas, recopilado por Eduardo Martín Rossi. Allí detallaban 1100 trabajos científicos que confirman los efectos en la salud y el ambiente del herbicida glifosato. Figuran más de 200 investigaciones de académicos argentinos (del Conicet y de universidades públicas). En 2015, la Agencia Internacional para la Investigación sobre el Cáncer (IARC, ámbito especializado de la Organización Mundial de la Salud), vinculó el glifosato al cáncer, y confirmó que produce daño genético en humanos.
+En contraposición, no existen investigaciones independientes (donde no intervengan empresas y científicos con conflictos de intereses) que dé cuenta de la inocuidad de los agrotóxicos utilizados en los campos. De hecho, tanto en Argentina como en Estados Unidos, las agencias estatales aprueban esos químicos en base a estudios de las mismas empresas que los venden.
+[H2] Experiencia única y censurada
+La Facultad de Ciencias Médicas de la Universidad de Rosario contaba con unaexperiencia única: los "campamentos sanitarios" de la materia Práctica Final del último año de la carrera (impulsada por el Instituto de Salud Socioambiental). Todos los estudiantes y docentes se instalaban durante una semana en un pueblo (siempre en acuerdo con las autoridades locales) y, con una detallada encuesta, trazaban un perfil socio-sanitario del lugar. Se realizaron 40 campamentos en el periodo 2010-2019 (entre ellos los ocho de la publicación científica) y reunieron evidencias claras del incremento de enfermedades vinculadas al modelo agropecuario. Pero las actuales autoridades de la Facultad (encabezada por el decano Jorge Molina) eliminaron esa experiencia única de estudio e investigación.
+[H2] Los impactos en la salud
+El médico e investigador Damián Verzeñassi explica que los estudios epidemiológicos no pueden precisar qué agroquímico causa determinada enfermedad en cada paciente, pero sí remarca que las poblaciones son expuestas a cócteles de agrotóxicos que individualmente está probado que estimular el desarrollo de problemas endocrinos y distintos tipos de cánceres. Destaca que el glifosato es teratogénico (produce malformaciones) y está asociado al desarrollo de linfoma no hodking; la atrazina está vinculado al cáncer de mama y alteraciones en tiroides; el clorpirifós es neurotóxico, desregula la tiroides y aumenta la incidencia de tumores de mama. En tanto el glufosinato de amonio (que se intenta utilizar en el nuevo trigo transgénico) es disruptor endocrino y teratogénico. Mientras que el 2-4D es teratogénico, aumenta el riesgo de aborto y es clasificado por IARC-OMS cómo posiblemente cancerígeno en humanos y asociado a linfoma no hodking. "Existen además trabajos científicos que demostraron que si se combinan los pesticidas, algo que ocurre en la práctica habitual, la capacidad de daño es aún mayor que individualmente", afirma Verzeñassi.</t>
   </si>
   <si>
     <t>Un gran avance del latifundio</t>
@@ -1669,7 +4164,21 @@
     <t>https://www.pagina12.com.ar/522079-un-gran-avance-del-latifundio</t>
   </si>
   <si>
-    <t>2023-02-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: Un gran avance del latifundio
+Chapeau: Un juez firmó la orden de desalojo a una familia campesina de Bigand
+Subtítulo: Sandra Gobbo y Oscar Marinucci llevan toda la vida en la zona, trabajando al tierra. Por un conflicto con la Fundación Honorio Bigand, pueden ser expulsados.
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/522079-un-gran-avance-del-latifundio/
+Notícia completa (8 blocos):
+Un pequeña productora chacarera denunció ayer que el juez provincial Sergio Verdura firmó la orden de desalojo de un predio de seis hectáreas, cuyas familias lo viene trabajando desde desde hace más de cien años. El conflicto tiene al matrimonio de Sandra Gobbo y Oscar Marinucci de un lado y a la Fundación Honorio Bigand del otro. “El poder judicial no puede ser tan latifundista, en este caso apoyando a una fundación que es un verdadero fraude, ya que no cumple con la voluntad de la última heredera. La orden fue muy clara, al igual que las pautas que debía seguir esta fundación, cuestión que no se cumple y doblegando la apuesta avanzan contra una familia que tiene un arraigo en el lugar que data de 1920”, indicó Gobbo a Rosario12.
+"Nos encontramos ante un nuevo embate judicial promovido por quienes de manera ilegal e ilegítima se apropiaron de la administración de la Fundación Honorio Bigand", planteó la mujer. Es que luego de desalojar a las 25 familias que vivían y trabajaban en este territorio, hoy van contra Sandra y Oscar, ambos de 60 años y contra su única vivienda. La familia Gobbo-Marinucci es la última que resiste en el territorio donde viven y trabajan en sus tierras hace más de 100 años.
+La mujer apuntó contra "Marcelo Jorge Álvarez, como presidente de la Fundación Bigand quien, junto a sus abogados apoderados Valeria Montaldo Maiocchi, Mabel Azar y Diego Haro Matínez, se apoderaron de forma fraudulenta de la Fundación que fue creada para destinar los frutos de este territorio a la 'caridad y el bien público'. En cambio, se apropiaron de las 3500 hectáreas y de las ganancias que generan, y hoy (por ayer) lograron que el Juez Sergio Verdura, de Cañada de Gómez, dispusiera el desalojo".
+Para Gobbo, la Fundación no cumple con su mandato original porque "los campos no podian venderse y sin embargo, lo hicieron. Nosotros seguimos resistiendo a pesar de todo, hasta de los tiros que han tirado".
+La mujer explicó que "el desalojo fue firmado y el expediente viene a la jueza comunal de Bigand, Carolina Mozzi, que asumió el 22 de diciembre y va a tener que venir con la fuerza pública a desalojarnos. Lo que vamos a hacer es resistir, porque hasta el mismísimo presidente Alberto Fernández dijo que se iba a reglmentar la ley de agricultura familiar y no lo hizo. Vamos a encadenarnos en la tranquera, porque no tenemos vida afuera de esta tierra, solo sabemos trabajarla y criar animales. Preferimos morir acá antes que terminar deprimidos fuera de esta tierra".
+Curiosmente, Mozzi, en manos de quien quedó la orden de desalojo, fue directora del Instituto de la Mujer de Rosario, entre 2016 y 2019.
+Gobbo y su compañero sostienen desde hace décadas que “las tierras pertenecen al fundador del pueblo, Victor Bigand, quien arrendaba las parcelas a distintas familias campesinas. En 2004, al fallecer la última heredera de la familia fundadora, comenzó una estrategia por parte de la Fundación Honorio Bigand para desalojar a los colonos y hacerse de esos terrenos. El accionar de la entidad va en contra del testamento que le legaba los campos y que apostaba a la caridad y el bien público. Esta Fundación no cumple con la voluntad del fundador de nuestro pueblo ni sus hijos, que no dejaron descendencia”.
+La familia ya perdió una importante porción de sus tierras en manos de la Fundación y en la actualidad solo cuentan con su hogar y una pequeña parcela, donde crían animales. “Vuelvo a recalcar, una y otra vez, que esto no es solo la defensa a una familia de agricultores familiares, sino qué tipo de modelo país queremos. Si es el del agronegocio que solo piensa en concentrar la tierra para sacar mas quintales, fumigándonos y envenenándonos, o es el de la chacra mixta y la agroecología” concluyó.</t>
   </si>
   <si>
     <t>José Maggi</t>
@@ -1684,7 +4193,23 @@
     <t>https://www.pagina12.com.ar/519674-agua-desmontes-y-litio-la-matriz-del-extractivismo</t>
   </si>
   <si>
-    <t>2023-01-30T03:49:22Z</t>
+    <t xml:space="preserve">Título: Agua, desmontes y litio, la matriz del extractivismo
+Chapeau: El biólogo y filósofo Guillermo Folguera en Salta
+Subtítulo: La Asamblea de Lucha Socioambiental recolectó firmas para el proyecto que busca frenar los desmontes por 35 años y prohibir la utilización del agua a toda actividad que implique un peligro para la biodiversidad y la población. La iniciativa popular será presentada cuando se inicie el año legislativo.
+Editoria: Salta|12
+Tags: Ambiente, extractivismo, diario
+URL: https://www.pagina12.com.ar/519674-agua-desmontes-y-litio-la-matriz-del-extractivismo/
+Notícia completa (10 blocos):
+Frente a la Legislatura salteña, en la plazoleta donde se encuentra la estatua del fundador de la ciudad de Salta (Hernando de Lerma), ambientalistas, organizaciones de derechos humanos, organizaciones sociales y vecinos sostienen la protestas. Los encuentros comenzaron hacia finales de setiembre de 2022, en medio de los incendios forestales en las selvas de Yungas del norte y otros lugares de la provincia.
+En el día de la educación ambiental (desde 1972, cada 26 de enero), los y las asambleístas recolectaron firmas para un proyecto de ley que presentarán apenas comience el año legislativo en marzo próximo. La iniciativa popular debe contar con 28 mil firmas de cuatro municipios para poder ingresar en algunas de las dos cámaras del congreso provincial. Por lo tanto, la búsqueda de adhesiones continuará en distintos puntos de la ciudad y el interior provincial. Lo importante es que, en nombre de todes les ciudadanes de Salta, el proyecto solicitará que se suspendan por 35 años los desmontes en territorio salteño. También, “que se prohíba el uso de aguas superficiales, subterráneas y periglaciares a la industria minera, petrolera y toda aquella industria o actividad que implique un peligro para la biodiversidad, salud y vida de toda la población” de la provincia.
+Agua y extractivismo fueron los dos temas claves durante la última asamblea, el jueves último. De viaje por Salta, fue invitado al encuentro Guillermo Folguera, biólogo, filósofo, investigador del CONICET y profesor de la UBA. “El extractivismo es una forma de expulsión y de ordenamiento demográfico”, opinó durante la entrevista con Salta/12. “Se naturaliza la desigualdad social”, mencionó en otro momento. Más tarde, micrófono en mano durante su breve alocución ante los presentes, profundizó sobre otros aspectos claves para comprender la problemática ambiental que nos atraviesa, ya no como salteñes, sino como argentines. “Estamos en un proyecto político que podemos rastrear desde los años setenta y luego, durante los cambios institucionales del menemato de los noventa. Esa matriz nunca fue cambiada”, afirmó. “Así armaron el país que vemos hoy. El proyecto político es el saqueo”, explicó, “y ya tenemos 50 por ciento de pobres. No va a cambiar desde arriba. Da lo mismo para las empresas, les da lo mismo qué consecuencias: no nos tiene que dar lo mismo a nosotros”.
+De paseo por el norte argentino, Folguera se mostró sorprendido por los niveles de pobreza que observó en su recorrida turística. A su diagnóstico de viajero, sumó la que tiene que ver con su profesión: “una crisis hídrica total y temperaturas fuera de registro”. En su paso por los Valles Calchaquíes, encontró que el proceso turístico y vitivinícola guarda relación con el agronegocio de las llanuras pampeanas. “Expulsa comunidades hacia las periferias urbanas, extrae demasiada agua y registra una paulatina pérdida de lo público. Todas dinámicas que se conocen por el modelo sojero y que no esperaba encontrar aquí en el Norte. Es una narrativa que se repite”.
+El año pasado, Folguera coordinó un libro "Diálogos sobre el modelo agroindustrial argentino”. “Es un problema complejo y necesita muchas miradas”, dijo. Explicó luego que quienes participaron en la publicación, se centraron en plantear problemas y no en construir objetos de estudio según campos disciplinares. “Creo que debemos repensar la democracia que tenemos. Incluir visiones de otras personas, colectivos y comunidades”, agregó.
+[H2] El litio es otro parche
+“Hay una producción infinita de alimentos. El agronegocio no discute la distribución, tampoco el hambre, ¿qué opinión te merece?”, le consultó este medio. “El hambre nunca estuvo en la ecuación de las empresas”, respondió. “Pasa lo mismo con el litio, nos dicen una verdad a medias. Cuando se aprobaron los transgénicos en 1995, el discurso del agro prometió progreso. Sin embargo, es el discurso de la expulsión y, en el fondo, nunca se discuten las cosas de fondo”. Para Folguera, hay promesas similares (de futuro próspero y progreso) en la transición energética
+Acerca de la explotación de litio en los salares de la Puna argentina en las provincias de Salta, Jujuy y Catamarca, Folguera fue más preciso en otro tramo de la entrevista. Los gobiernos y las empresas “están planteando que la Puna será, en el futuro próximo, como un gran queso gruyere. Los humedales que están ahora, los van a secar. Las nuevas técnicas de evaporación de agua son experimentales. En Fiambalá (Catamarca) están planteando extraer el litio en cinco años con una enorme inyección económica”, enumeró. “En realidad se sabe que el litio no va a resolver el problema de fondo (por la desfosilización del modelo de transporte). Es otro parche, para no discutir en problema de fondo: el consumo y la distribución”.
+La geóloga y ambientalista Fabiola Barrios participó en la asamblea del jueves 26 frente a la Legislatura salteña. En su breve intervención, apuntó directo justamente, a los modelos de consumo. “Nosotres, en Salta, tenemos que darnos cuenta que en alrededor de diez años, quizás antes, vamos a empezar a ver la naturaleza en peores condiciones”, vaticinó en función de la velocidad de entrega de territorios, por parte del estado salteño, a empresas mineras transnacionales para la explotación de minerales. “Hay que salir del ego y unirnos. Cada uno de nuestros actos representa una decisión política sobre lo que va a pasar en nuestro territorios”, dijo. En otro tramo, invitó a todes a pensar en la obsolecencia programada, porque es el método que utilizan las empresas para inducir a cada individuo al consumo permanente.
+Barrios opinó finalmente sobre la estatización de los servicios públicos (agua y electricidad) en los cortes de rutas y acampes donde se manifiestan las comunidades y vecinos del norte salteño. “Sea o no la solución estatizar, lo importante es trabajar en un cambio en el modelo de consumo”. Argumentó que nuestros modos actuales fueron y son instalados por el sistema capitalista. “Su objetivo es generar capital sin importar para qué”, profundizó. “Si quienes están en el poder mantienen la misma mentalidad, estatizado o privatizado el servicio (por la luz y el agua) igual van a encontrar los mecanismos para que el saqueo siga funcionando. Los gobiernos están manejados por corporaciones”.</t>
   </si>
   <si>
     <t>Marina Silva enfrenta el incendio de Bolsonaro</t>
@@ -1696,7 +4221,31 @@
     <t>https://www.pagina12.com.ar/519272-marina-silva-enfrenta-el-incendio-de-bolsonaro</t>
   </si>
   <si>
-    <t>2023-01-28T03:01:00Z</t>
+    <t xml:space="preserve">Título: Marina Silva enfrenta el incendio de Bolsonaro
+Chapeau: La Ministra de Medio Ambiente de Brasil hará eje en la Amazonia
+Subtítulo: La ambientalista retoma sus políticas de antaño sobre la selva contra el agronegocio y reclama apoyo al mundo, tanto económico como en reducción de emisiones.
+Editoria: El Mundo
+Tags: Amazonia, Calentamiento global, Luiz Inácio Lula da Silva, printed-edition, calentamiento-global, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/519272-marina-silva-enfrenta-el-incendio-de-bolsonaro/
+Notícia completa (18 blocos):
+La flamante ministra de Medio Ambiente de Brasil, Marina Silva, declaró luego de su primer mes de gestión, que la realidad ambiental de su país es "mucho peor" de lo esperado. Y que para recuperar lo perdido y proteger la Amazonia, necesitará más apoyo internacional.
+Pese al desafío, la ambientalista con cuatro décadas de trayectoria se siente "agradecida" por regresar junto al presidente Luiz Inácio Lula da Silva al frente de este Ministerio, el cual ya ocupó entre 2003 y 2008, batallando contra la deforestación.
+Marina Silva llegó a su cargo el 1º de enero, luego de cuatro años en los que el gobierno del ultraderechista Jair Bolsonaro fue repudiado internacionalmente y acusado de dejar el campo expedito para desforestar la Amazonia en beneficio del agronegocio.
+"La realidad es mucho peor de lo que esperábamos, porque aquí teníamos un apagón", dijo Silva en una entrevista con AFP: "el esfuerzo no será pequeño, porque el desmantelamiento (en el Ministerio) que tuvimos en estos cuatro años, fue muy grande".
+Su ministerio fue ahora rebautizado de Medio Ambiente y Cambio Climático, en sintonía con los tiempos. Y sostuvo la ministra que el cambio no es cosmético: "coloca la agenda ambiental en el nivel más alto de prioridad del gobierno. Eso es un cambio compatible con lo que está ocurriendo en el mundo".
+La meta de deforestación cero para 2030 es un símbolo de ese compromiso, comentó Silva: "no será un camino fácil (...) Pero vamos a intentar recuperar el tiempo perdido".
+[H2] Un visión transversal
+La ministra explicó que el plan contra la deforestación está siendo restablecido, luego de la casi paralización de la gestión Bolsonaro. Y agregó que el gobierno de Lula quiere que las políticas ambientales sean tratadas por 17 ministerios.
+Silva no adelantó metas numéricas, pero insistió en que no darán tregua a la deforestación ilegal: "queremos llevar al convencimiento de que no es un buen negocio destruir la selva (...) (...) vamos a invertir en biotecnología, turismo, agricultura de bajo carbono y otras fuentes de generación de ingresos".
+"Nuestra meta es que con ese trabajo conjunto, podamos contribuir para retomar el control de las acciones de prevención y combate a la deforestación, y trabajar fuertemente en el ordenamiento territorial", dijo Marina Silva. Y explicó que la mayor parte de la deforestación ocurre en tierras públicas y espacios demarcados como "unidades de conservación ambiental" y "tierras indígenas". Por eso en los primeros 100 días de gobierno, deben ser anunciadas nuevas unidades de conservación y tierras indígenas.
+Silva aclaró que no promete un Brasil sustentable en cuatro años de gestión: "vamos a hacer lo que sea posible en un corto espacio de tiempo. Solo gobiernos populistas pueden decir que resuelven problemas de esa magnitud en cuatro años (...) esperamos llegar a la COP30 en 2025 como un país que está haciendo sus deberes", dijo en alusión a la conferencia de la ONU sobre clima.
+[H2] Un voto de confianza
+Marina Silva tiene 64 años y viene de participar en el Foro de Davos, en el cual dice haber recibido una cálida recepción: "la gente siente que Brasil está de regreso: fue como una extensión de la recepción de la elección del presidente Lula, que se da por lo que hicimos; conseguimos reducir la deforestación en un 83 por ciento por casi una década durante los primeros gobiernos de Lula".
+Estas marcas, observó Silva, le permiten iniciar su gestión con un voto de confianza internacional. "Sabemos que de aquí en adelante necesitaremos ganarnos la confianza para lo que vamos a hacer". Pero para esta excandidata presidencial, que forjó una carrera desde su nativa Breu Velho (Acre) en el corazón de la Amazonia, Brasil no puede hacer milagros sin ayuda internacional.
+En materia económica, saludó la activación y ampliación del Fondo Amazonia --sus principales donantes son Alemania y Noruega-- que estuvo paralizado durante parte de la administración Bolsonaro por divergencias sobre el destino de los recursos: "estamos conversando con Reino Unido, Francia, España, con todos los países para que aporten recursos al Fondo Amazonia. No queremos que sea solo Alemania y Noruega".
+[H2] Los paises desarrollados tendrán que cooperar
+Además de gobiernos, la ministra sostuvo que las conversaciones avanzan con empresas y filántropos. Pero Silva espera más que recursos: "esa colaboración con los países desarrollados, que sea también de apertura de los mercados para nuestros productos sustentables (...) Que lo que se produce de forma legal pueda ser una fuente de generación de ingresos, porque la Amazonia tiene 25 millones de personas".
+"Tenemos el gran desafío de pasar hacia un modelo sustentable de desarrollo que garantice que esas personas puedan vivir con dignidad", comentó Silva, quien también destacó que el compromiso contra la comercialización de oro y madera ilegal debe ser multilateral. Y agregó que espera aportes en otros frentes: "si los países desarrollados no disminuyen sus emisiones de dióxido de carbono, la Amazonia será igualmente destruida".</t>
   </si>
   <si>
     <t>Paula Ramón (AFP)</t>
@@ -1711,7 +4260,29 @@
     <t>https://www.pagina12.com.ar/517719-cual-es-la-plaga-que-amenaza-a-lula-el-presidente-que-se-ani</t>
   </si>
   <si>
-    <t>2023-01-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: La plaga que amenaza a Lula, el presidente que se animó a salir de Brasilia
+Chapeau: Los vándalos del 8 de enero dejaron al desnudo una trama poderosa
+Subtítulo: Lula cumplió su promesa y la Argentina fue el destino de su primera salida. ¿Una señal de fuerza? Puede ser, cuando se descubre qué sangre corre hoy por las venas de la maquinaria estatal brasileña. Aquí las claves.
+Editoria: El País
+Tags: Luiz Inácio Lula da Silva, Jair Bolsonaro, printed-edition, luiz-inacio-lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/517719-cual-es-la-plaga-que-amenaza-a-lula-el-presidente-que-se-ani/
+Notícia completa (16 blocos):
+Luiz Inácio Lula da Silva no solo eligió a la Argentina como primer destino de viaje: se animó a viajar. A salir de Brasil. Y lo hizo poco después de una rebelión cuyos alcances todavía son desconocidos. Su apuesta es tan evidente como audaz. “Me voy porque soy el presidente y quiero mostrar que controlo el Estado”, parece haber razonado.
+El viaje a la Argentina se produce justo cuando Lula enfrenta su principal desafío. No es el dominio del Congreso, como algunos analistas podían pensar. No son los gobernadores. No es, hoy, el agronegocio, y quizás tampoco el desafío de estos días sean el poder de la gran banca brasileña y las finanzas transnacionalizadas. El reto más urgente para el nuevo gobierno es, precisamente, quién maneja el aparato del Poder Ejecutivo. De la Presidencia, los ministerios, las Fuerzas Armadas, la policía y la inteligencia.
+Un investigador riguroso, el periodista Jefferson Miola, de Rio Grande do Sul, llegó a chequear en el primer año de mandato de Jair Bolsonaro que tres mil militares habían sido designados en puestos estatales. No solo en el Ministerio de Defensa. También en el resto. Y sobre todo en las áreas de decisión presupuestaria y administrativa. Una plaga. El objetivo fue controlar los fierros de la maquinaria estatal.
+La cifra se entiende más al recordar que Bolsonaro, un capitán, era militar. Que era militar su vice, el general Hamilton Mourao. Que eran militares importantes ministros o funcionarios con rango equivalente. El secretario de Gobierno, general Carlos Alberto dos Santos Cruz. El ministro de Defensa, general Fernando Azevedo e Silva. El jefe del Gabinete de Seguridad Institucional, general Augusto Heleno Ribeiro. El ministro de Tecnología, teniente coronel Marcos Pontes.Luis Mandetta, ministro de Salud, fue médico militar. Lo reemplazó Eduardo Pazuello, un general que terminó investigado por la muerte de pacientes de Covid en hospitales de Manaos debido a la falta de oxígeno. En otro movimiento de militarización, Bolsonaro desplazó al jefe de la Casa Civil (la Jefatura de Gabinete argentina), Onyx Lorenzoni, para nombrar otro general,Walter Souza Braga Netto. Entre los civiles que acompañaron al núcleo de generales revistó el primer canciller de Bolsonaro, Ernesto Araújo, un mediocre diplomático integrista. En un paper académico sostenía, en tono de lamento, que Dios y la política se separaron en 1789. Es la fecha de la Revolución Francesa.
+La presidencia de Bolsonaro fue lo más parecido a una reconstrucción del Partido Militar que pueda imaginarse en un país del Cono Sur de América.
+El antropólogo Piero Leirner sostuvo en 2021 que un grupo de generales, en actividad y en retiro, pretendía realizar una reestructuración completa del Estado para militarizarlo.”Sería una estructura de poder infiltrada ne espacios del Estado, y no solo en el Ejecutivo, con el control de los canales políticos y de recursos del gerenciamiento estatal”, dijo. Según Leirner, un informe del Tribunal de Cuentas reveló en julio de 2020 que ya había 6157 militares en el Estado. El centro de comando sería el Gabinete de Seguridad Institucional. El plan habría sido colocar a Bolsonaro en el papel de incendiario para que luego el consorcio de generales pudiese ofrecerse como garantía de orden.
+Al corazón del Partido Militar habría que agregarle la influencia de las milicias que controlan las favelas, el crecimiento de las policías provinciales (que tras 38 años de democracia en Brasil se llaman todavía PM, Policía Militar) y la autonomización de la Policía Federal.
+La PM que quedó más expuesta fue la de Brasilia. Dejó pasar rumbo a la capital nada menos que 105 micros especialmente fletados con 3.900 pasajeros, convertidos luego en vándalos.
+La PF ya había conspirado conra Lula en su primer gobierno, en el año electoral de 2006, cuando su servicio de inteligencia convirtió en escándalo político un episodio de financiación irregular de la política. En la historia quedó como Mensalao.
+Miola escribió el 16 de enero un interesante artículo que tituló “Lula y la cuestión militar”. Informó que los atentados terroristas del 8 de enero, contra las sedes de los tres poderes en Brasilia, “afectaron irremediablemente la confianza de Lula en las Fuerzas Armadas”. Lula llegó a la conclusión de que las cúpulas habían sido las responsables. Jeff, como es conocido en Brasil el analista, explicó que la prueba de esa desconfianza fue la decisión de decretar la intervención del área de seguridad del Distrito Federal en vez de convocar a los militares para defender el orden. El Ejército ya había aprestado 2500 efectivos “para intervenir contra el caos y el desorden que el mismo Ejército había construido”. Lula habría entendido que si admitía la maniobra se convertiría en un presidente fantasma.
+En lugar de ceder a la extorsión disfrazada de ayuda, el Presidente optó por convocar a todos los gobernadores y sacarse con ellos una foto en el Planalto, la Casa Rosada de Brasilia. Así, un mundo que ya se había mostrado solidario con la institucionalidad tuvo un elemento más de juicio en favor de Lula.
+Y el último sábado el Presidente dio otra muestra de autoridad al destituir al jefe del Ejército, Julio César de Arruda. Lo reemplazó por el general Tomás Miguel Ribeiro Paiva, que en una ceremonia militar había dicho que “cuando votamos, tenemos que respetar el resultado de las urnas”.
+Además de su connivencia con los vándalos del 8 de enero, muchos de los cuales acamparon junto al cuartel general del Ejército en Brasilia, Arruda no aceptó la orden de Lula de pasar a retiro al coronel Mauro Cid, ex edecán de Bolsonaro. Estaba pautado que Cid asumiera en febrero la jefatura del Primer Batallón de Acciones y Comandos, una unidad de operaciones especiales.
+Los actos de rebeldía venían en ascenso desde el triunfo electoral de Lula. En la Marina por primera vez desde 1985, en democracia, el comandante saliente Almir Santos no acudió a la asunción del entrante, Marcos Sampaio Olsen.
+El presidente brasileño comenzó el Operativo Limpieza por el propio Planalto. La semana pasada 84 militares fueron destituidos de los cargos que ocupaban allí. De ellos, 38 revistaban en el Gabinete de Seguridad Institucional.
+“El soldado es educado para cumplir órdenes”, escribió en “Brasil 247” el historiador Manuel Domingos Neto. “Si no las recibe, impone su propia voluntad.” Afirmó también Domingos Neto: “En Brasil, el político nunca se preparó para orientar al soldado. Así, dejó la Defensa del país en manos impropias. Al no imponerse al soldado, el político declina su obligación y deja amenazada a la democracia”. En sintonía con Leirner, el historiador escribió que desde 2014, por lo menos, los militares intervienen en la dinámica política mediante sinergias con la prensa, con jueces, con religiosos, con empresarios y con las redes. Su tesis es que llegó el momento de actuar rápido y cortar ese proceso, porque será imposible hacerlo si en algún momento declina el apoyo popular.</t>
   </si>
   <si>
     <t>Martín Granovsky</t>
@@ -1726,7 +4297,27 @@
     <t>https://www.pagina12.com.ar/514840-brasil-guerra-santa-golpistas-y-mercaderes-de-fe</t>
   </si>
   <si>
-    <t>2023-01-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: Brasil: Guerra santa, golpistas y mercaderes de fe
+Chapeau: Los pastores que predican el odio bolsonarista
+Subtítulo: Azuzados por pastores que los llaman a tomar las armas mientras desparraman sin filtro su odio por las redes sociales ,los golpistas, como una marabunta, destruyeron el Congreso, el Planalto y la sede del Superior Tribunal Federal.
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Intento de golpe de estado en Brasil, printed-edition, jair-bolsonaro, intento-de-golpe-de-estado-en-brasil, diario
+URL: https://www.pagina12.com.ar/514840-brasil-guerra-santa-golpistas-y-mercaderes-de-fe/
+Notícia completa (14 blocos):
+Hay un componente místico-religioso, cuasi medieval, en la ideología neofascista de los golpistas pro-Bolsonaro. Hablan de Guerra Santa y están dispuestos a todo. A lo que se vio en la invasión de los tres poderes del Estado y a mucho más. Abstraídos en su cosmovisión del mundo, fanatizados, desparraman sin filtro su odio por las redes sociales azuzados por pastores que los llaman a tomar las armas. La reconocida teóloga alemana Dorothee Sölle (1929-2003) que trabajó en Brasil, encuadraría su caso en lo que llamó el cristofascismo, una definición que acuñó en la década del ’70. Un video de Tik Tok de los miles que circulan desde el domingo, es una síntesis notable de esa conducta. Un hombre barbudo y desencajado, que aparenta unos 40 años, ataviado con la bandera verdeamarela grita a la cámara durante casi un minuto: “Vengan todos los ángeles, Gabrieles y Rafaeles, únanse al pueblo del señor, al pueblo que no niega la patria y la fe, y ¡vamos a la guerra!”
+El pastor Mauro Sérgio Aiello de la iglesia presbiteriana de Brasil en Mogi das Cruzes, San Pablo, salió en defensa de los golpistas que como una marabunta destruyeron el Congreso, el Planalto y la sede del Superior Tribunal Federal (STF). Dijo en su sermón transmitido por un canal de youtube el mismo día del ataque, que el país está al borde de una “guerra civil”. Citado por el periodista Silvio Costa en el sitio Congreso en foco, el predicador del odio les pidió a los brasileños que deben tomar las armas para defenderse.
+[H2] "Debemos actuar"
+“La cuerda se ha estirado y se está rompiendo, pueblo mío. Y veo un país al borde de la guerra civil y la convulsión” (…). No vamos a tomar las armas para atacar, pero si es necesario tomar las armas para defendernos, lo haremos. El brasileño real no huye de la pelea. Somos una nación pacífica y ordenada, pero hay un momento en que debemos actuar”, afirmó Aiello como si fuera Torquemada en plena Inquisición. No es el único religioso levantisco. Hubo quienes apoyaron la caravana de buses hacia Brasilia y otros que la organizaron.
+Josué Valandro, pastor de la iglesia bautista Attitude, en Barra da Tijuca – que frecuentaba la exprimera dama Michelle Bolsonaro – acompañó con simpatía desde las redes los hechos criminales en la capital y en Twitter pidió que era “hora de ayunar por la patria”. Silas Malafaia, acaso el clérigo más influyente de Brasil y aliado incondicional del expresidente, justificó el intento de golpe de Estado porque “la paciencia de la gente tiene límites”. Es el mismo que en noviembre pasado y con sentido premonitorio dijo que si “Lula comete un error, el pueblo va a derrocarlo”. Controla más de 130 templos, es multimillonario y su congregación tiene el pomposo nombre de iglesia Asamblea de Dios Victoria en Cristo.
+“Podemos decir que el discurso religioso actuó como motivador ideológico de los hechos de violencia vistos en Brasilia, porque moviliza pautas morales, el conservadurismo de la sociedad brasileña”, explicó Nilza Valéria, coordinadora del Frente de Evangélicos por el Estado de Derecho para un detallado informe del sitio Agencia Pública titulado: “La cara religiosa del terrorismo: pastores organizaron caravanas y llamaron a atentados en BSB”. La sigla corresponde a Brasilia.
+Las más osadas acompañaron a sus feligreses poseídos por el odio en los ataques a las principales instalaciones del gobierno. “La pastora Nubia Modista, de la Iglesia Evangélica Apostólica de Itaguaí, en Río de Janeiro, estaba entre el grupo de invasores que fueron a Brasilia y publicaron videos dentro de edificios públicos. ‘Estoy aquí dentro del congreso. La policía los quería dejar entrar… mira esto’”, dice desde el lugar, citada por las periodistas Mariama Correia y Nathalia Fonseca.
+Consagrados por las iglesias electrónicas a cumplir su papel de guardianes del fundamentalismo evangélico. Empoderados políticamente por el fugitivo expresidente, hoy residente en EE.UU. Financiados por el agronegocio y armados como una milicia de zombies, los bolsonaristas más ultras tienen capacidad de daño, como ya se comprobó en Brasilia.
+[H2] Sabotajes
+Los sabotajes contra tres torres de alta tensión en los estados de Rondonia, Paraná y San Pablo -el primero de ellos producido el domingo a la noche – sugieren que el gobierno federal no puede omitir la hipótesis de futuros atentados al sistema eléctrico nacional. También contra el suministro de combustibles que colocó en alerta máximo a la estatal Petrobras.
+No debe subestimarse a la ultraderecha brasileña. Ya sucedió cuando se incubaba el huevo de la serpiente antes de que Bolsonaro llegara al poder en octubre de 2018. Las consecuencias están a la vista. La política “genocida” durante la pandemia, como la definió el propio Lula, es una de ellas.
+Otro aspecto de la idiosincrasia de estos grupos es que prefabrican una realidad paralela todo el tiempo. Creen en una versión de la historia construida a la medida de su fe, en un mundo de fieles e infieles. Son racistas, homofóbicos, macartistas. “La iglesia es una agencia de salud emocional, tan importante como los hospitales” decía Malafaia en 2020 cuando la población brasileña moría de a racimos mientras Bolsonaro pretendía frenar el avance del Covid 19 con cloroquina.
+“Lucha ahora y sé parte de la historia”, fue la consigna con que convocaron a marchar los mercaderes de la fe que los guiaron hacia la tierra prometida del Planalto. Como si se sumergieran en la novena cruzada (la octava y última fue en el siglo XIII) encontraron en Brasilia su Santo Sepulcro. Aunque esta vez no fueron guiados por la iglesia católica y sí por un puñado de pastores que vomitan su credo golpista, aferrándose a sus biblias.
+gveiga@pagina12.com.ar</t>
   </si>
   <si>
     <t>El cambio climático también es político</t>
@@ -1738,7 +4329,22 @@
     <t>https://www.pagina12.com.ar/514701-el-cambio-climatico-tambien-es-politico</t>
   </si>
   <si>
-    <t>2023-01-10T20:10:20Z</t>
+    <t xml:space="preserve">Título: El cambio climático también es político
+Chapeau: Brasil y el intento de golpe de Estado
+Subtítulo: Partidarios de una dictadura de ultraderecha bolsonarista atacaron el domingo pasado las tres sedes del poder del Estado brasileño, apenas una semana después de que asumiera Lula. Mientras se investigan los hechos, crecen las certezas sobre el alcance de las alianzas políticas con los partidarios del ex presidente y la implacable destrucción del Amazonas que dicha alianza conlleva.
+Editoria: Soy
+Tags: Brasil, Lula, Cambio climático, Intento de golpe de estado en Brasil, printed-edition, cambio-climatico, intento-de-golpe-de-estado-en-brasil
+URL: https://www.pagina12.com.ar/514701-el-cambio-climatico-tambien-es-politico/
+Notícia completa (9 blocos):
+El presidente Lula estaba este 8 de enero en la localidad de Araraquara, un histórico municipio del estado de San Pablo, para relevar personalmente los daños que produjeron las últimas inundaciones, cuando le informaron sobre el intento de golpe de Estado fascista en Brasilia. Partidarios de una dictadura de ultraderecha bolsonarista tomaron, ante la pasividad de la Policía Militar de Brasilia, el palacio presidencial de Planalto, el Congreso y el Supremo Tribunal Federal y destrozaron todo lo que pudieron (como muestra, un reloj único en el mundo realizado por un orfebre del rey Luis XIV de Francia), en una muestra más del regodeo en la ignorancia y el afán de destrucción de las oligarquías financieras locales que están asesinando al Amazonas y a su población. Lula prometió buscar el financiamiento de los golpistas que venían acampando durante más de dos meses en Brasilia junto a la guarnición militar y hacer caer sobre ellos todo el peso de la ley.
+Al final de su discurso en Arararaquara, Lula vinculó el financiamiento de los golpistas (a los que calificó de terroristas) con la destrucción del Amazonas y el cambio climático. Apuntó a los garimpeiros ilegales, a la depredación maderera y al agronegocio.
+Mientras tanto, el Servicio Meteorológico argentino publicaba este 8 de enero un mapa que muestra una zona de calor intenso ubicada en el norte de la Patagonia. Hacía más calor en el sur que el norte del país. Lo mismo ocurría por esos días en el hemisferio norte americano. En las ciudades del norte de los Estados Unidos hace más frío que en el círculo polar Ártico.
+Entretanto, en todo el mundo se vinculó el “putsch” (uso este término a propósito, en Europa se sigue empleando en alemán y así se lo presentó en muchos medios, recordemos el putsch de 1933) con la toma del Capitolio estadounidense por partidarios republicanos trumpistas, que ocurrió el 6 de enero de 2021, cuando el Congreso estaba reunido para certificar la victoria del demócrata Joe Biden en las elecciones presidenciales.
+[H2] Conexiones (no tan) invisibles
+En forma contraria a lo que las ultraderechas latinoamericanas esperaban, el presidente estadounidense Joe Biden, autoridades federales y congresistas estadounidenses pertenecientes al Partido Demócrata se pronunciaron en contra del intento de golpe de Estado en Brasil y brindaron su apoyo al presidente Lula. Esas ultraderechas tienen conexiones muy visibles en Argentina. Basta ver qué políticos y políticas de la ultraderecha argentina exhibieron con orgullo en los medios y en las redes sociales sus fotos con el diputado brasileño Eduardo Bolsonaro, hijo del ex presidente Jair Bolsonaro a quien el actual gobierno brasileño y la comunidad progresista internacional apuntan como autor intelectual del putsch en Brasilia. Entre las figuras de segunda y tercera línea que agasajaron a Eduardo Bolsonaro con un asado en Puerto Madero se encontraba la diputada nacional por la provincia de Buenos Aires por Avanza Libertad, Carolina Píparo. En tanto, la dirección de la ultraderecha argentina no se atrevió a esa foto. Quizá porque el hijo de Bolsonaro es segunda línea y la foto que luce es con Jair Bolsonaro, como la publicó varias veces Mauricio Macri.
+Entre las congresistas demócratas que expresaron su apoyo al presidente Lula y pidieron la expulsión de Jair Bolsonaro de Estados Unidos, adonde huyó cuando tuvo que dejar la presidencia, se encuentra Alexandria Ocasio-Cortez. Alexandria tiene 32 años, integra la organización Socialistas Democráticos de América (de tendencia socialista democrática laborista) y es representante por Nueva York. Se crio en el Bronx y proviene de una familia boricua. Participó en 2022 en la marcha del orgullo lgtbiq en Puerto Rico y fue detenida en las manifestaciones contra la Corte de Justicia conservadora que limitó el derecho al aborto en Estados Unidos.
+Alexandria es sobreviviente de abuso sexual y comparó a los republicanos que evadieron su responsabilidad en el ataque al Capitolio con “las tácticas que usan los abusadores”.
+Respecto del desastre ambiental en el planeta, Alexandria sostiene que la defensa del medio ambiente no es un tema elitista (en el Bronx y en La Boca diríamos que no es un asunto de chetos) sino que afecta a los más pobres. “El mundo se terminará en 12 años si no abordamos el cambio climático”, dijo antes de la pandemia.</t>
   </si>
   <si>
     <t>Logo soy</t>
@@ -1756,7 +4362,22 @@
     <t>https://www.pagina12.com.ar/514404-intento-de-golpe-en-brasil-apuntan-a-los-sectores-del-agrone</t>
   </si>
   <si>
-    <t>2023-01-09T19:15:06Z</t>
+    <t xml:space="preserve">Título: Intento de golpe en Brasil: apuntan a los sectores del agronegocio como financiadores del ataque
+Chapeau: Hay 1.500 detenidos
+Subtítulo: Luego del fallido intento de golpe de Estado en Brasil, los analistas apuntan a un sector concentrado de la Economía brasileña como los principales autores intelectuales del hecho.
+Editoria: Radio 750
+Tags: Intento de golpe de estado en Brasil, Jair Bolsonaro, Lula Da Silva, Escuchá Página|12, intento-de-golpe-de-estado-en-brasil, jair-bolsonaro, lula-da-silva, aqui-alla-y-en-todas-partes
+URL: https://www.pagina12.com.ar/514404-intento-de-golpe-en-brasil-apuntan-a-los-sectores-del-agrone/
+Notícia completa (9 blocos):
+Cientos de simpatizantes del expresidente ultraderechista Jair Bolsonaro invadieron este domingo el Congreso, el Tribunal Supremo y el Palacio Presidencial de Planalto, sedes de los poderes en Brasilia, causando numerosos destrozos.
+En diálogo con AM750, el sociólogo, especialista en relaciones internacionales y asesor de senadores del PT en el Senado de Brasil, Marcelo Zero explicó la situación actual del conflicto y aseguró que "todo volvió a la normalidad" en Brasilia.
+"La situación volvió a la normalidad acá en Brasilia y ya 1.500 golpistas fueron detenidos por la policía brasileña", afirmó el sociólogo.
+Unsupported embed [https://mdstrm.com/embed/63bc5d84a36b7d086fb3f58c]
+"Si bien las investigaciones recién comienzan, todos en Brasil saben que los principales financiadores de estos actos son personas de un sector del agronegocio que tenían en Bolsonaro un gran aliado y ahora con Lula tienen a un enemigo", afirmó con respecto a los grupos que están detrás del fallido golpe de Estado.
+Asimismo, señaló que los detenidos son de varios lugares y también del Mato Grosso del sur el cual "es un lugar dominado por los intereses del agronegocio".
+Por otro lado, indicó que los rumores de una "falla en la seguridad" pueden deberse más por una "intencionalidad" de que estos hechos sucedieran: "Nosotros sospechamos que hubo una intención de dejar que esto pasara por parte del gobernador del Distrito Federal, Ibaneis Rocha, quien es bolsonarista, quien fue suspendido de sus funciones por 90 días".
+Por último, luego que se supiera que Jair Bolsonaro está reisidiendo en Estados Unidos y hace pocas horas se supo que se encuentra internado, el asesor del PT expresó que el exmandatario derechista "tiene miedo de ir preso".
+"Bolsonaro tiene miedo de ser arrestado en Brasil por los numerosos procesos que hay contra él, por eso se fue a residir en Florida", concluyó.</t>
   </si>
   <si>
     <t>Lula no espera: freno a las privatizaciones y al acceso a las armas</t>
@@ -1768,7 +4389,29 @@
     <t>https://www.pagina12.com.ar/512710-lula-no-espera-freno-a-las-privatizaciones-y-al-acceso-a-las</t>
   </si>
   <si>
-    <t>2023-01-03T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lula no espera: freno a las privatizaciones y al acceso a las armas
+Chapeau: Las medidas del nuevo gobierno de Brasil desde la hora cero
+Subtítulo: El flamante presidente firmó decretos para mantener ocho empresas en manos del Estado, limitar el uso de armas de fuego y preservar la Amazonía, entre otras cuestiones clave.
+Editoria: El Mundo
+Tags: Lula Da Silva, Brasil, printed-edition, lula-da-silva, diario
+URL: https://www.pagina12.com.ar/512710-lula-no-espera-freno-a-las-privatizaciones-y-al-acceso-a-las/
+Notícia completa (16 blocos):
+Desde Brasilia
+El presidente Lula da Silva comenzó a tomar medidas de gobierno desde la hora cero. Ocurrió luego de los discursos ante las miles de personas en Brasilia que expresaron tanto su apoyo y alegría por su retorno al Palacio de Planalto, como la gran cantidad de demandas y necesidades sin respuesta acumuladas durante los cuatro años de Jair Bolsonaro. Lo dijo Lula sin eufemismos durante su discurso: el país que se encontró está en “ruinas terribles” y le tocará reconstruirlo, algo que inició con 13 decretos firmados el mismo domingo en la noche.
+[H2] Economía
+Las medidas tomadas, publicadas el lunes en el “Diario Oficial de la Unión”, dieron cuenta de alguno de los elementos más urgentes y estratégicas de la agenda de Lula. Uno de ellos fue el freno a las privatizaciones que estaban en marcha en el caso de ocho empresas estatales, como la petrolera Petrobras, el Correo, la Empresa Brasileña de Comunicaciones, el Servicio Federal de Procesamiento de Datos, y la Empresa de Tecnología e Información de Seguridad Social. Lula afirmó que era necesario “garantizar un análisis riguroso de los impactos de la privatización en el servicio público o en el mercado”, deteniendo así el Programa Nacional de Privatizaciones del anterior gobierno comandado en lo económico por Paulo Guedes.
+Otra de las decisiones implementadas fue derogar el último decreto hecho por el anterior gobierno, que redujo a la mitad las tasas impositivas a ser pagadas por las grandes empresas. Ese decreto había sido anunciado el día viernes y firmado por el vicepresidente Hamilton Mourao en vista de que Bolsonaro ya había partido hacia Orlando, en La Florida, lugar donde se encuentra por tiempo indeterminado.
+En materia económica el nuevo gobierno anunció varias decisiones en línea con lo dicho en el discurso de Lula del domingo cuando afirmó que “no sería justo ni correcto pedir paciencia a quien tiene hambre”. El presidente decretó la continuidad del pago del programa de ayuda social Bolsa Familia por 600 reales -112 dólares- que llega a 21 millones de personas. Esa política ya había sido trabajada con anticipación al lograr que el poder Legislativo le acordara un aumento del gasto público. A su vez, anunció la extensión por 60 días de impuestos federales para combustibles, para evitar un aumento de precios.
+[H2] Armas y selva
+Lula también emitió un decreto que apunta directamente contra el bolsonarismo, derogando las normas que facilitaban y ampliaban el acceso a las armas de fuego y municiones. Esto significa, en otras cosas, la suspensión de nuevos registros de armas para cazadores, tiradores, particulares, coleccionistas; la reducción de los límites para la compra de armas y municiones que había sido ampliado por Bolsonaro; la obligación de que todas las armas compradas desde mayo de 2019 sean registradas nuevamente por sus propietarios dentro de los 60 días; y la suspensión de nuevas inscripciones de clubes y escuelas de tiro.
+Esta decisión se comprende en el contexto de radicalización del núcleo bolsonarista, articulado, entre otros espacios, a través de los clubes de tiro que se multiplicaron en estos años: 1.006 fueron creados entre enero de 2019 y mayo de 2020, según cifras del Ejército. El bolsonarismo en armas protagonizó varios incidentes en los últimos meses, como el más reciente, en diciembre, cuando un hombre quiso hacer explotar un camión de gasolina en Brasilia y un arsenal fue encontrado en el departamento que rentaba. “El decreto del presidente Lula pone fin a un absurdo: la presunción de ‘necesidad efectiva’ de portar un arma. Obviamente, será necesario reclamar y probar, bajo pena de desestimación de la solicitud”, afirmó el ahora ministro de Justicia, Flavio Dino.
+Por último, dentro de las medidas tomadas, estuvo la reactivación del Fondo Amazonía, formado por financiamiento de Noruega y Alemania, que había sido suspendido por Bolsonaro en 2019. Los fondos, cerca de 600 millones de dólares, serán ejecutados por el ministerio de Medio Ambiente a cargo de Marina Silva. Lula también revocó otro decreto de Bolsonaro aprobado en los últimos días en el cual se ampliaban las licencias para la explotación de recursos minerales en la región amazónica, incluyendo tierras de pueblos indígenas.
+La importancia del medio ambiente y la Amazonía fue parte central de su discurso el domingo: “vamos a iniciar la transición energética y ecológica para una producción agropecuaria y minería sostenible, agricultura familiar más fuerte”, dijo ante el Congreso Nacional. Anunció la meta de “deforestación cero” de la Amazonía: “Brasil no debe deforestar para mantener y ampliar su frontera agrícola, no es necesario tumbar ningún árbol”, agregó, dando cuenta de una tensión histórica entre medio ambiente y agronegocio, razón por la cual Silva renunció en 2008.
+[H2] ¿Gabinete amplio y Lula a la izquierda?
+El caso ambiente/agronegocio grafica la amplitud del gobierno formado por Lula. Por un lado, colocó a una ministra con una agenda de protección y transición ecológica, y, por el otro, designó a un ministro de Agricultura, Carlos Fávaro, parte del agronegocio, en particular de la soja, procedente de Mato Grosso, región central de ese modelo. ¿Cómo llevará Lula la posible tensión en el desarrollo de ambas agendas? “Es más difícil armar un gobierno que ganar elecciones”, afirmó días atrás, en el marco del nombramiento progresivo de los diferentes cargos.
+El mosaico de fuerzas que lo llevaron a la presidencia tiene representación en el gobierno. Es el caso de Fávaro; de Simone Tebet, tercera en la primera vuelta, aliada para el ballotage y ahora al frente del ministerio de Planificación; de Gerardo Alckmin que, además de vicepresidente es ministro de Desarrollo, Industria y Comercio; o de la misma Silva que se reconcilió con Lula en el marco de las elecciones contra Bolsonaro. El líder del Partido de los Trabajadores (PT) reconoció a través de los nombramientos la importancia del frente amplio por la democracia que le permitió una victoria de menos de dos puntos de diferencia. “Este gobierno no es para mí, sino para las fuerzas que me apoyaron para lograr esta victoria”, dijo a su vez durante el proceso de armado de gobierno.
+Sin embargo, la amplitud de alianzas no significó la perdida de centralidad del PT dentro del nuevo gobierno. Varios puestos claves quedaron bajo dirección lulista como Hacienda con Fernando Haddad candidato por el PT para el estado de San Pablo, Casa Civil con Rui Costa ex gobernador de Bahía, Desarrollo Social, con Wellington Dias, o cancillería de Mauro Vieira, ex diplomático bajo Dilma Rousseff. Lula abrió, por un lado, y mantuvo lugares claves, por el otro.
+La hoja de ruta que diseñe el propio Lula será determinante para marcar la orientación dominante de un gobierno de coalición. La misma entusiasmó a varios sectores de izquierda en vista de los discursos pronunciados el domingo y las primeras medidas anunciadas: gasto social ante la crisis, freno de privatizaciones, proyecto de reindustrialización, cuidado del medio ambiente, integración latinoamericana para desde allí construir políticas en medio de la disputa global, o el hecho de haber llamado “golpe” a la salida del gobierno de Rousseff en 2016. El tercer Lula comenzó sin perder un minuto.</t>
   </si>
   <si>
     <t>Marco Teruggi</t>
@@ -1783,7 +4426,25 @@
     <t>https://www.pagina12.com.ar/512337-impunidad-y-racismo</t>
   </si>
   <si>
-    <t>2022-12-31T04:33:49Z</t>
+    <t xml:space="preserve">Título: Impunidad y racismo
+Chapeau: La criminalización de la pobreza en el norte salteño
+Subtítulo: En el norte de Salta la impunidad es la cara de una moneda, y el racismo es la otra, dice el autor. Y denuncia: la impunidad y el racismo provienen en primer lugar del mismo Estado, a través de la justicia, las fuerzas de seguridad, el sistema de salud y el sistema educativo.
+Editoria: Salta|12
+Tags: Opinión, opinion, diario
+URL: https://www.pagina12.com.ar/512337-impunidad-y-racismo/
+Notícia completa (12 blocos):
+Se va yendo 2022 y nos deja en el debe familias sin techo desalojadas, y comunidades en conflicto, en alerta, avasalladas y perseguidas por los apellidos y poderes de siempre.
+Racismo e impunidad. Impunidad y racismo.
+En un barrio popular de Colonia Santa Rosa, censado en el Registro Nacional de Barrios Populares y amparados por la ley 27.453, que dicho sea de paso fue ratificada y ampliada este año por el Congreso de la Nación votada positivamente por casi todos los/as legisladores, siete familias fueron desalojadas por la Señora Manero, la justicia y la policía. En su primer intento logramos impedirlo gracias a la organización de los vecinos/as, movimientos sociales y las autoridades de la Secretaría de Integración Socio Urbana. En el segundo intento los poderes fueron más pícaros y ágiles y lograron su cometido: desalojar familias y ampliar un proyecto inmobiliario. ¿El intendente? Bien, gracias.
+En la zona de Tartagal los conflictos son moneda corriente, casi una política de Estado. ¿Pero a quien le importa lo que sucede luego del kilometro 4 de la ruta 86? A duras penas llega la señal de celular. Una comunidad y su niyat afrontando tres juicios contra usurpadores, desmontadores, violentos, impunes, etcétera. Otras comunidades levantando y quemando alambrados que ilegalmente puso la Señora Montserrat dentro del territorio comunitario relevado en el marco de la ley 26.160, con carpeta territorial incluida. Pero no pasa nada. O casi nada, porque en esos momentos o un “ingeniero” ligado al aero club de Tartagal amagó con atropellar una mujer wichí con su Toyota Hilux, y no contento con eso empuñó un revolver y apuntó a la cabeza del cacique a plena luz del día y con testigos. Las denuncias hechas, contra los que alambraron territorio comunitario y contra el que intenta solucionar los conflictos asesinando. Nada pasa. ¿Se imaginan si hubiese sido al revés?
+Los conflictos por la tierra no son nuevos. Pero algunas leyes que otorgan derechos a los históricamente oprimidos/as y saqueados sí lo son. Pero, como dicen, hecha la ley hecha la trampa. Y las familias de apellido, de grandes latifundios y a veces de dudosos papeles tienen con qué. Tiempo, dinero, profesionales y funcionarios al servicio del saqueo y de la injusticia. A veces, por cuestiones tan insignificantes para ellos como siete lotes o 90 hectáreas. A veces, es mucho más.
+Pero la disputa no es por eso. ¿Qué son siete lotes en un proyecto inmobiliario de 500? ¿Qué son 90 hectáreas en un agronegocio de 5.000? Casi nada. Lo que importa es disciplinar. A las comunidades, a los vecinos/as de barrios populares, a la ley, a los/as pobres. “Ustedes no van a ganar, nunca nos van a ganar, somos los dueños de las cosas, somos los dueños de todo”, nos intentan decir.
+Sabemos que no nos van a ganar, pero a veces si parece que fueran los dueños de todo. El Poder Judicial a su servicio (salvo honrosas excepciones), las fuerzas de seguridad más cerca de ser empleados que “servidores”, aquellos/as con cargos políticos que son “compañeros/as” dudando en pronunciarse, comprometerse o poner el cuerpo por “el qué dirán”, porque parece que estas problemáticas no suman votos, o porque los pobres no van a financiar sus campañas. A veces no se meten “por miedo”, un morocho siempre es sospechoso, más si no tiene papeles. ¿Qué importan los derechos?
+En el norte de Salta la impunidad es la cara de una moneda, y el racismo es la otra. Difícil proponer una política de Estado para combatir esto por dos motivos (entre otros): el primero es que la impunidad y el racismo provienen en primer lugar del mismo Estado en diferentes esferas, la justicia, las fuerzas de seguridad, el sistema de salud (párrafo aparte para esta cuestión, el racismo debe ser una de las principales causas de muerte para aquellos/as que acuden a los hospitales) y el sistema educativo. Y en segundo lugar porque aquellos organismos o funcionarios del Estado con voluntad de combatir la impunidad y el racismo se encuentran a 500 o 2000 kilómetros de distancia, salvo honrosas excepciones.
+No se puede pensar, promover y luchar por la vida digna de los/as pobres si no combatimos la impunidad y el racismo que existe y que dirige el accionar de aquellos/as que deben dar respuestas.
+Con impunidad y racismo no hay política pública que pueda dar respuesta, por más bien intencionada que sea o por más presupuesto que tenga.
+Este debe ser un debate sobre la mesa de la política salteña y del rol del Estado. Y debe ser parte primordial del diagnóstico a la hora de pensar políticas públicas con, desde, para y por los/as de abajo.
+* Movimiento Evita</t>
   </si>
   <si>
     <t>Jocha Castro Videla*</t>
@@ -1798,7 +4459,21 @@
     <t>https://www.pagina12.com.ar/512071-verdurazo-de-fin-de-ano-de-la-utt</t>
   </si>
   <si>
-    <t>2022-12-30T03:01:00Z</t>
+    <t xml:space="preserve">Título: Verdurazo de fin de año de la UTT
+Chapeau: En reclamo de una ley de Acceso a la Tierra
+Subtítulo: Los productores de la agricultura familiar repartirán 15 mil kilos de frutas y verduras en la plaza de Constitución, a partir de las 10 de la mañana.
+Editoria: El País
+Tags: UTT, Verdurazo, Economía popular, printed-edition, economia-popular, diario
+URL: https://www.pagina12.com.ar/512071-verdurazo-de-fin-de-ano-de-la-utt/
+Notícia completa (8 blocos):
+La Unión de trabajadores de la Tierra realizará un nuevo Verdurazo en Constitución, este viernes, a las 10.00 hs. Allí entregará 15 mil kilos de alimentos, en reclamo de políticas públicas para la agricultura familiar. “Somos productores que alquilamos la tierra y resistimos en las quintas, golpeadas por la inflación, el cambio climático y la sequía, mientras las políticas públicas no llegan", señaló sobre el motivo de la protesta Nahuel Levaggi, referente de la UTT y también presidente del Mercado Central de Buenos Aires.
+Desde 2016 la UTT viene presentando en el Congreso un proyecto de Ley de Acceso a la Tierra, su demanda histórica de creación de una línea de créditos blandos que permitan a los productores acceder a lotes propios para el cultivo. Con la llegada al gobierno del Frente de Todos, la aprobación de este proyecto llegó a ser acordada con la Casa Rosada, pero luego pasaron los años sin que se concretara. De hecho, la propuesta, comparable a un Procrear Rural, ya fue ingresada tres veces a Diputados.
+El Verdurazo tendrá como escenario la plaza de Constitución, donde la acción de la UTT será acompañada por otras organizaciones, como la Red de Comedores por una Alimentación Sana y Soberana, el Grupo Ambientalista XR y los Curas Villeros.
+“Una vez más, el viernes vamos a estar en la calle, luchando para derrotar el hambre generada por los sectores concentrados de siempre. Vamos a poner a disposición de los comedores comunitarios y de los vecinos y vecinas, el fruto de nuestro trabajo en el surco: miles de kilos de alimento sano, para que este fin de año ninguna familia se quede sin comer”, anticipó Zulma Molloja, vocera nacional de la UTT.
+Como organización, la UTT tiene 12 años de historia y representa a más de 25.000 familias pequeño productoras agropecuarias del país. Su trabajo ha sido clave para virar la producción de hortalizas y frutas hacia la agroecología, una medida que apunta a producir alimentos más sanos y romper la dependencia con los modos de producción del agronegocio, que controla todos los insumos, incluidas las semillas, a precios dolarizados.
+En los últimos años la organización ha ido creando, además, una red de comercialización alternativa, que busca llegar sin intermediarios del productor al consumidor. El rubro de frutas y verduras ha sido el que mayor aumento de precios ha tenido este año.
+¿Por qué? “Por un lado acompañan una inflación general de los costos. Por otro, este fue un año de mucha sequía, eso afectó la producción y al tener menor oferta de productos los precios suben. Nosotros hace ya dos años que presentamos el proyecto para un plan nacional de abastecimiento frutihortícola que incluye aumentar las hectáreas de producción, en función de garantizar un mayor abastecimiento, que permita controlar los precios, porque el sector se maneja cien por ciento por oferta y demanda. Pero esta es otra de las cosas que no fue tomada en cuenta por los ministros de Agricultura”.
+Para Levaggi, “estamos en los finales de un gobierno que se había comprometido con una agenda por la soberanía alimentaria y no dió ningún paso. La situación en los territorios sigue siendo la misa, no hubo cambios estructurales: falta acceso a la tierra, financiamiento para la agricultura familiar. Tenemos un estado paralizado, que vino supuestamente a hacer grandes transformaciones después de lo que fueron los cuatro años de Mauricio Macri. Había un pueblo esperanzado en esas transformaciones, pero estamos casi igual que cuando llegamos. Hoy tenemos una agenda económica que apunta a garantizar el cumplimiento de las metas con el FMI y del otro lado a un pueblo que sigue esperando respuestas”.</t>
   </si>
   <si>
     <t>Un grupo liderado por Grabois marchó a Lago Escondido y denunció la existencia de un "Estado paralelo"</t>
@@ -1810,7 +4485,41 @@
     <t>https://www.pagina12.com.ar/511376-un-grupo-liderado-por-grabois-marcho-a-lago-escondido-y-denu</t>
   </si>
   <si>
-    <t>2022-12-27T17:54:40Z</t>
+    <t xml:space="preserve">Título: Un grupo liderado por Grabois marchó a Lago Escondido y denunció la existencia de un "Estado paralelo"
+Chapeau: "Las Malvinas son argentinas, Lago Escondido también"
+Subtítulo: Un grupo conformado por el referente del Movimiento de Trabajadores Excluidos (MTE), Juan Grabois, el diputado nacional Federico Fagioli, abogados, trabajadores de prensa y representantes
+Editoria: El País
+Tags: Lago Escondido, Juan Grabois, lago-escondido, juan-grabois, diario
+URL: https://www.pagina12.com.ar/511376-un-grupo-liderado-por-grabois-marcho-a-lago-escondido-y-denu/
+Notícia completa (28 blocos):
+Un grupo conformado por el referente del Movimiento de Trabajadores Excluidos (MTE), Juan Grabois, el diputado nacional Federico Fagioli, abogados, trabajadores de prensa y representantes de organizaciones sociales, realizó este martes una marcha a Lago Escondido para reclamar que el Estado Nacional recupere esas tierras que actualmente son propiedad del magnate británico Joe Lewis.
+La Fundación Interactiva para Promover la Cultura del Agua (FIPCA), por su parte, convocó para este martes a una conferencia de prensa para brindar detalles sobre la "marcha por la soberanía al Lago Escondido" que lleva adelante todos los años.
+"Queremos comunicarles que en este momento, estamos intentando llegar al Lago Escondido, patrimonio de todas y todos los argentinos pero sólo accesible para algunos serviles al poder real. Las Malvinas son argentinas, el Lago Escondido también", escribió este martes a las 8 de la mañana el referente del MTE en su cuenta de Twitter, donde compartió un comunicado en el que explicó que uno de los objetivos de la movilización es "peticionar al Estado Nacional que impulse una acción de lesividad por la compra ilegal del año 1996 para recuperar esta porción de territorio nacional".
+Pasadas las 10, Grabois compartió una fotografía del grupo que realizó la movilización sosteniendo de espaldas al lago una bandera con la leyenda "Las Malvinas son argentinas, el Lago Escondido también". "Ya izamos la bandera en territorio nacional ¡Recuperemos lo nuestro!", publicó el referente del MTE junto a la imagen.
+[H2] Comunicado completo
+Queremos comunicarles que, en este momento, estamos intentando llegar al Lago Escondido, patrimonio de todas y todos los argentinos pero sólo accesible para algunos privilegiados: los jerarcas del poder judicial, las fuerzas de seguridad, los medios hegemónicos y los políticos serviles al poder real.
+El Lago Escondido hoy forma parte de un enclave colonial inglés asentado ilegalmente en zona de seguridad nacional. Hidden Lake, como le llaman el inglés y sus servidores, junto con el inmenso aeropuerto privado de Sierra Grande sobre la costa Atlántica y la Estancia “el Cóndor” sobre el Estrecho de Magallanes, ambos a escasos kilómetros de las Islas Malvinas, son un triángulo estratégico de ocupación británica en territorio argentino.
+La situación del Lago Escondido es, además, una de las máximas expresiones de cómo funciona el poder real. El ‘Triángulo de Lewis’ se construyó con tierras malhabidas, violando las leyes de seguridad nacional, apelando a testaferros y documentos falsificados, cerrando los accesos públicos a la costa del Lago Escondido. A pesar de un fallo firme del Superior Tribunal de Justicia de la Provincia de Río Negro que data del 2012 y confirma un fallo de 2002, ni el gobierno provincial ni el nacional ha habiltado un paso que permita al pueblo disfrutar de la maravilla natural que constituye el Lago Escondido. Son veinte años.
+Detrás de los muros de este rémora colonial se esconde un enorme proyecto inmobiliario para multimillonarios en el sector llamado “Pampa de Ludden”, al que los vecinos se han opuesto férreamente debido a su enorme impacto ambiental tanto sobre el pueblo como sobre el Área Natural Protegida Río Azul-Lago Escondido. El mega-country de Lewis es otro paraíso para ricos que es un infierno para la gente común y la naturaleza.
+Pero el verdadero secreto del Lago Escondido es su función como sede del Estado Paralelo que venimos denunciando; hemos visto como la estancia de Joe Lewis es la cueva donde se urden las conspiraciones en Argentina, se desafían las instituciones democráticas, se escriben los fallos o se planifica cómo incumplirlos; aquí, en territorio entregado al inglés, se reúne el estado mayor del modelo colonial.
+Nuestra acción de hoy se enmarca en el concepto de Resistencia No Violenta con el que Gandhi enfrentó el imperialismo inglés en la India. No estamos violando ninguna ley, simplemente ejercemos nuestro derecho constitucional al libre acceso a la costa de los lagos. Los lagos son del pueblo argentino y nosotros somos argentinos que queremos liberar este pedacito de patria de la ocupación ilegal.
+Nuestro objetivo directo es lograr el camino público tal cual exige el fallo del Superior Tribunal de Justicia y peticionar al Estado Nacional que impulse una acción de lesividad por la compra ilegal del año 1996 para recuperar esta porción de territorio nacional. También, tan de moda que están las auditorías hoy en día: que se auditen todas las ventas a multinacionales y testaferros de magnates extranjeros en zonas de seguridad nacional.
+Del mismo modo, venimos a decir que no hay lugar a ningún proyecto inmobiliario, mega-minero, petrolero o del agronegocio sin el consentimiento del pueblo y el debido respeto a la naturaleza. En la Argentina, el saqueo económico de nuestros bienes comunes va de la mano con la violación flagrante a la voluntad mayoritaria de todos los pueblos que dicen, referéndum tras referéndum, no al extractivismo contaminante, no al glifosato, no al cianuro, no al acaparamiento de tierras.
+Esta protesta apunta también a exigir el ejercicio patriótico del poder legítimo y legal que la Constitución otorga al Gobierno electo para desmantelar el Estado Paralelo y poner las cosas en su lugar. No podemos tolerar que se siga imponiendo el 1% por sobre el 99% restante de la población. No podemos tolerar que los fallos se acaten inmediatamente cuando van en contra del pueblo, pero demoren añares cuando tocan los intereses de los privilegiados. No podemos tolerar que en la Argentina se siga concentrando el ingreso y la riqueza sin medidas redistributivas serias. Seguir con esta reiteración de agachadas contra las grandes mayorías bajo falsos argumentos como la "institucionalidad", "honrar las deudas" o la "correlación de fuerzas", es complicidad o falta de patriotismo y coraje.
+En estos días de fervor argentino cabe preguntarse:
+¿Dónde está el patriotismo en ajustar la inversión social incumpliendo la deuda con la gente mientras se acatan servilmente los mandatos del Fondo Monetario Internacional o el reciente fallo antifederal de una Corte Suprema ilegítima y corrupta?
+¿Dónde está el coraje en pagar un plus precio a las exportaciones de soja que nos han salido a los argentinos más de 600 mil millones de pesos mientras se regatea lo más esencial a la mitad de los trabajadores argentinos que ganan por debajo de la línea de pobreza aún estando en blanco?
+¿Dónde está el patriotismo cuando se crea un comando unificado para encarcelar a seis mujeres con sus hijos pero no vemos ningún comando unificado haciendo cumplir la sentencia contra el invasor inglés?
+¿Cómo puede haber magnates extranjeros como Lewis con cientos de miles de hectáreas mientras nuestros pequeños productores, arrendatarios, comunidades campesinas criollas u originarias, no tienen tierra propia para cultivar? ¿Cómo puede ser cuando hay millones de familias argentinas que no tienen siquiera un terreno para construir su vivienda?
+Este proceso de extranjerización de la tierra y los recursos naturales se profundizó tras la anulación que Mauricio Macri realizó de la ley 26.737 de protección al dominio nacional sobre la propiedad, posesión o tenencia de las tierras rurales. La entrega de nuestros bienes estratégicos y la falta de planificación para que nuestra tierra, subsuelo, aguas y minerales -como el litio- sean un factor de desarrollo humano integral y federal, son la expresión de una falta absoluta de patriotismo y el Estado de indefensión del Pueblo.
+Hoy, en este acto de reafirmación de la soberanía nacional, venimos a pedirle a nuestros gobernantes locales, provinciales y nacionales que se pongan la celeste y blanca para defender los derechos del pueblo y la patria. Si no, van a seguir poniéndole la alfombra roja a los representantes más serviles del poder real para que vuelvan a la Casa Rosada.
+Las Malvinas Son Argentinas
+El Lago Escondido También
+[H2] Marcha del FIPCA
+Además de la marcha liderada por Grabois y Fagioli, organizaciones sociales, políticas y gremiales -nucleadas en la Fundación Interactiva para Promover la Cultura del Agua (Fipca)- convocaron para este martes a las 12 a una conferencia de prensa en la sede de la Federación Gráfica Bonaerense para dar detalles sobre la nueva marcha a Lago Escondido que, como otros años, se hará entre enero y febrero próximo para denunciar que el lugar es un "enclave británico" y funciona como "la cueva de un poder mafioso, vinculado al poder económico, judicial y mediático".
+Según adelantaron en un comunicado, la nueva movilización -que será la séptima- se realizará entre el 26 de enero y el 14 de febrero próximo y se organizará en diferentes columnas que se congregarán en el lugar.
+"Queremos que se cumpla la sentencia del Tribunal Superior de Justicia de la Provincia de Río Negro y de la Cámara de Apelaciones de Bariloche, que exige habilitar el Camino del paraje Tacuifí por su carácter de acceso público", dice el comunicado, donde también se exige que "se detenga y juzgue a los participantes de la mafia judicial y del grupo Clarín que participaron de la reunión en el Lago Escondido en octubre pasado".
+Entre las organizaciones firmantes están La Cámpora, La Federación de Gráficos Bonaerenses (FGB), la CTA Autónoma, la CTA de los Trabajadores, el Movimiento Octubre, la Mesa Coordinadora por la Defensa de la Soberanía Nacional del río Paraná y del Canal Magdalena, Sutap, Causa Nacional, GPS (Grupo por la Soberanía), el Grupo Bolívar, la Corriente Federal de Trabajadores, la CGT Regional zona Norte y el Grupo de Curas Opción por los pobres.</t>
   </si>
   <si>
     <t>El mundial de la deforestación: cuáles son los países de América Latina que encabezan el ranking</t>
@@ -1822,7 +4531,52 @@
     <t>https://www.pagina12.com.ar/502325-el-mundial-de-la-deforestacion-cuales-son-los-paises-de-amer</t>
   </si>
   <si>
-    <t>2022-11-28T13:55:52Z</t>
+    <t xml:space="preserve">Título: El mundial de la deforestación: cuáles son los países de América Latina que encabezan el ranking
+Chapeau: Un solo país logró revertir la pérdida de bosques
+Subtítulo: Mientras los ojos del mundo siguen la competencia deportiva de mayor envergadura internacional, otra competencia, para nada honorable, tiene a varios países de América Latina entre el top10.
+Editoria: Newsletter
+Tags: Newsletter Causas, Deforestación, Amazonia, Incendios forestales, newsletter-causas, deforestacion, incendios-forestales
+URL: https://www.pagina12.com.ar/502325-el-mundial-de-la-deforestacion-cuales-son-los-paises-de-amer/
+Notícia completa (39 blocos):
+Mientras los ojos del mundo siguen la competencia deportiva de mayor envergadura internacional, otra competencia, para nada honorable, tiene a varios países de América Latina entre el top10. Se trata del ranking de deforestación, que año a año actualiza el observatorio Global Forest Watch, a la par que documenta cómo la cubierta terrestre va perdiendo cobertura forestal. En otras palabras: cómo cada vez las superficies de bosques nativos desaparecen en manos de los incendios forestales y el avance del agronegocio.
+La mala noticia: Brasil, Bolivia, Paraguay y Argentina se encuentran entre los 15 países del mundo con mayor pérdida de cubierta arbórea. Les siguen Colombia, México y Perú, ahí nomás, con un lugar dentro del top20. Sólo un país de la región fue reconocido por “revertir el proceso de deforestación”, logro por el que recibirá financiamiento de parte del Fondo Monetario Internacional como parte de un programa de resiliencia y sostenibilidad.
+Dueña de uno de los mayores bosques tropicales del mundo, América Latina avanza en esta triste tabla de posiciones.
+[H2] Superficie de bosques en todo el planeta
+Según el observatorio Global Forest Watch, en 2010 el mundo tenía 3.92Gha de cobertura forestal, la cual se extendía a lo largo del 30% de su área terrestre. En el 2021, esa superficie disminuyó a 25.3Mha, lo que significó una gran pérdida de cobertura verde. Los motivos de la deforestación, según esta misma fuente, fueron: los incendios forestales, la agricultura y otras actividades relacionadas con la extracción de materias primas (extractivismo).
+Hay cinco países que cuentan con el 55% de superficie verde de todo el mundo. Son Rusia, Brasil, Canadá, Estados Unidos y República Democrática del Congo. Es conocida la situación de Brasil, que en los últimos años alcanzó niveles récord de pérdida de selva amazónica.
+[H2] Qué pasa en la región
+Entre los países que mayor cobertura arbórea perdieron en los últimos años están Brasil, en el segundo puesto del ranking mundial, y Bolivia, en el puesto número 10. Le sigue Paraguay, en el puesto número 11; Argentina, en el lugar número 13; Colombia y México, en el 17 y 18 respectivamente; y Perú que ocupa el puesto número 20. Esto quiere decir que entre los veinte países con mayor pérdida de bosques, siete son latinoamericanos.
+Y las malas noticias no terminan ahí para la región. Según la FAO, si el ranking de pérdida de bosques se midiera según la tasa de deforestación (relación de hectáreas perdidas por año) Brasil se llevaría el primer puesto. México escalaría al tercer lugar, Argentina al sexto, Bolivia al séptimo y Perú ocuparía el puesto número 10. Esto quiere decir que en términos relativos, en cuanto a deforestación y pérdida de bosques nativos, América Latina está peor de lo que parece.
+[H2] Brasil
+El de Brasil es tal vez el caso que más seguimiento le da la prensa mundial por tener uno de los biomas más importantes a nivel planetario, la Amazonia. Los índices de deforestación escalaron escandalosamente durante los últimos años, en el gobierno de Jair Bolsonaro, y por este motivo muchos países paralizaron el envío de fondos con los que se financiaban programas de protección y reforestación (tras la victoria de Lula da Silva, Alemania y Noruega prometieron liberar automáticamente los recursos del Fondo Amazonia).
+Según datos del sistema de vigilancia satelital DETER, del Instituto Nacional de Investigaciones Espaciales (INPE), organismo oficial de Brasil, octubre fue el peor mes en cuanto a deforestación desde 2015. En este mes se perdieron casi 1.000 kilómetros cuadrados de la Amazonia brasileña, un 3% más que en octubre de 2021.
+"El aumento de alertas de deforestación y de incendios era esperado, pero inclusive así los números de los primeros días de noviembre asustan, muestran una carrera desenfrenada por la devastación", denunciaron desde la ONG WWF-Brasil.
+Durante el mandato de Bolsonaro, negacionista del cambio climático, la deforestación anual promedio en la Amazonia brasileña -principalmente causada por la tala para expandir la frontera agrícola- aumentó un 75% comparado con la década anterior.
+La deforestación acumulada entre el 1° de enero y el 31 de octubre de este año representa el mayor valor de la serie histórica del sistema DETER, apuntó WWF-Brasil, con la destrucción de 9.494 kilómetros cuadrados.
+[H2] Bolivia
+Desde 2002 hasta 2021, Bolivia perdió 3.31 millones de hectáreas de bosque primario húmedo, lo que representa el 51% del total de su cobertura arbórea, según datos de Global Forest Watch.
+El 2020 fue un año crítico en cuanto a la destrucción de reservas naturales en manos de incendios forestales. El año anterior, un decreto había autorizado las quemas controladas en bosques de Santa Cruz y la región amazónica de Beni. Estas quemas, también conocidas como “chaqueos”, se realizan para preparar los terrenos para el nuevo ciclo agrícola bajo una supuesta actividad “controlada”.
+El aumento de los incendios forestales sobrepasó la capacidad de respuesta de los municipios por lo que el Gobierno tuvo que declarar la emergencia.
+[H2] Paraguay
+Según el observatorio de bosques, Paraguay perdió un 25% de superficie verde entre 2010 y 2020. Si bien el país firmó en la COP26 la Declaración de Líderes de Glasgow sobre bosques y uso de la tierra con el objetivo de detener y revertir la deforestación hacia 2030, la pérdida de bosques aumentó por segundo año consecutivo.
+En la última década, el 93% de la pérdida de masa forestal de Paraguay se dio como consecuencia de la deforestación asociada a la extracción de materias primas.
+[H2] Perú
+Desde 2002 hasta 2021 Perú perdió 2.31 millones de hectáreas de bosque primario húmedo, lo que representa 65% de su superficie total de bosques.
+Durante el año pasado, este país perdió cerca de 138.000 hectáreas de bosques amazónicos, casi un tercio menos de lo que había perdido en 2020, según información oficial divulgada por el Ministerio del Ambiente.
+La coordinadora del Programa Bosques, Blanca Arce, explicó que estos datos muestran el retorno a la tendencia de deforestación registrada antes la pandemia surgida en 2020, y afirmó que "la pérdida de bosques sigue siendo un problema muy crítico en el país".
+[H2] Colombia
+Este país también tiene problemas serios en su porción de selva amazónica. Según la ONU, en Colombia hay al menos 142.000 hectáreas de narcocultivos, la mayoría de ellos sembrados sobre la Amazonia. En este sentido, el presidente Gustavo Petro señaló que la Amazonia está siendo víctima de la "adicción" de las potencias por la coca, el dinero, y por recursos naturales como el carbón y el petróleo.
+"La selva se quema señores… Destruir la selva, el Amazonas, se convirtió en la consigna que siguen Estados y negociantes", dijo el mandatario, luego de asumir. "Decidieron hacer de una planta selvática amazónica un enemigo, extraditar y encarcelar a sus cultivadores, les invito a detener la guerra y a detener el desastre climático", añadió.
+Entre 2018 y 2021 Colombia perdió por la deforestación una superficie de 7.018 km2, un poco más que la extensión de la ciudad brasileña de Sao Paulo, según la ONU.
+[H2] El reclamo de las comunidades que viven en la selva amazónica
+Mientras los países amazónicos registran el avance de la deforestación, los pueblos indígenas que viven en estas tierras -Perú, Brasil, Ecuador, Colombia, Venezuela, Bolivia, Guyana, Guyana francesa y Surinam- denuncian que la situación es crítica, incluso para su supervivencia.
+En la última cumbre de líderes indígenas realizada en Lima, Perú, afirmaron que la Amazonia se encuentra en “alerta roja”, con el 26% de su ecosistema destruido de manera irreversible. "Para nosotros anunciar que la Amazonia está contaminada y destruida en un 26% es una alarma muy grande", denunció Gregorio Mirabal, líder de la Coordinadora de Organizaciones Indígenas de la Cuenca Amazónica (Coica).
+"Los gobiernos han dicho que van a salvar la Amazonia, pero con estos números no están cumpliendo. Estamos superando los límites para que la Amazonia llegue al punto de no retorno", agregó el líder indígena. "La temperatura va a subir en dos grados si vamos a ese ritmo de deforestación", advirtieron desde Coica.
+Según esta organización, hay unos 511 pueblos indígenas con 500 lenguas distintas, que transitan en las fronteras de los nueve países amazónicos.
+[H2] El caso de Costa Rica
+Calificada como un “pionero ambiental”, el trabajo de Costa Rica fue celebrado internacionalmente por lograr revertir la deforestación, en medio de múltiples vulnerabilidades climáticas. Por tal motivo, el Fondo Monetario Internacional aprobó una partida de 725 millones de dólares que se destinarán a apoyar la agenda climática de este país.
+"Costa Rica es vulnerable a eventos climáticos, especialmente inundaciones y tormentas tropicales que dañan la infraestructura, pero también Costa Rica es un pionero en mitigación y conservación. Es un país que logró revertir el proceso de deforestación", celebró Manuela Goretti, jefa de la misión del FMI para Costa Rica.
+Como parte de estos logros, desde el organismo destacaron que Costa Rica cuenta con casi la totalidad de su electricidad generada con fuentes limpias, una industria de ecoturismo y ecoproductos y mantiene en curso un proyecto para descarbonizar la economía.</t>
   </si>
   <si>
     <t>Rechazos a la minería del litio</t>
@@ -1834,7 +4588,27 @@
     <t>https://www.pagina12.com.ar/502202-rechazos-a-la-mineria-del-litio</t>
   </si>
   <si>
-    <t>2022-11-28T03:01:00Z</t>
+    <t xml:space="preserve">Título: Rechazos a la minería del litio
+Chapeau: Reclamos en comunidades de Catamarca, Jujuy y Salta
+Subtítulo: Comunidades indígenas, campesinos y asambleas socioambientales afirman que destruye ecosistemas vitales y viola derechos humanos.
+Editoria: Sociedad
+Tags: Litio, printed-edition, diario
+URL: https://www.pagina12.com.ar/502202-rechazos-a-la-mineria-del-litio/
+Notícia completa (14 blocos):
+"Podemos vivir sin litio, pero no podemos vivir sin agua". Es la frase que se repite en las comunidades de Catamarca, Jujuy y Salta donde existen explotaciones y proyectos de megaminería de litio. Pueblos originarios, campesinos y asambleas socioambientales dan cuenta de las consecuencias del extractivismo en las salinas: sobreconsumo de agua, contaminación y vulneración de derechos humanos. "¿Quién se hace responsable del saqueo, de la contaminación, del agua que usan? Conocemos a las mineras desde hace tres décadas, por eso decimos no a la minería de litio", remarca el cacique de la comunidad indígena Atacameños del Altiplano, Román Guitián.
+Catamarca conoce de magaminería. Por un lado, la conocida Minera Alumbrera, inaugura en 1997 por Carlos Menem. Extrajo oro y cobre del oeste provincial (departamentos de Andalgalá, Santa María y Belén) y no se cumplieron las promesas de trabajo, desarrollo local ni cuidado del ambiente. De ahí el rechazo al nuevo megaproyecto MARA (Minera Agua Rica-Alumbrera). También conoce de explotación de litio, en la zona de Antofagasta de la Sierra opera desde la década del 90 la multinacional FMC Corporation (bajo el nombre de Minera del Altiplano).
+"Ya secaron el río Trapiche y no vamos a permitir que sigan haciendo eso", denuncia el cacique Guitián. Se refiere a la avanzada extractiva: en 2018 FMC Corporation, de origen estadounidense, anunció que su unidad de negocios de explotación de litio pasaba a llamarse Livent Corporation. Y presentó la ampliación de la explotación. Para lo cual requiere grandes volúmenes de agua, que pretende obtener del río Los Patos. Propuso la realización pozos de bombeo para obtener 650.000 litros de agua por hora y trasportar el caudal a través de un acueducto.
+Las comunidades indígenas, las asambleas socioambientales y vecinos autoconvocados de Catamarca denuncian que está en riesgo el caudal del río, imprescindible para la vida del lugar. "El informe ambiental del acueducto tuvo 19 observaciones e igual el gobierno provincial autorizó la obra. Tampoco se respetaron los derechos indígenaS, no hubo consulta ni consentimiento, como dice la ley. Operan ilegalmente", denuncia el cacique Guitián.
+De similar manera se posicionan desde la Asociación Campesinos del Abaucán (Acampa), organización de familias productoras que rechaza la explotación de litio porque "atenta contra la cultura y forma de vida campesina".
+Fiambalá, a 300 kilómetros al noroeste de la capital provincial, es muy conocida por sus atractivos turísticos y su historia de agricultura. Todo comenzó a cambiar en 2016 con la llegada de la la empresa Liex, subsidiaria de la corporación canadiense Neo Lithium, para el proyecto de explotación de litio llamado "Tres Quebradas". En 2021, en acuerdo con el gobierno provincial y nacional, tomó reimpulso con la multinacional china Zijing Mining.
+Yolanda Espinoza es parte de la Asamblea Fiambalá Despierta. "No aceptamos la imposición de un modelo extractivista ajeno a nuestras formas de vida. Atenta contra nuestras economías regionales. Y es imprescindible denunciar que el proyecto Tres Quebradas, de minería de litio, está instalado en sitio Ramsar, donde hay salares y lagunas altoandinas de gran importancia ecológica para la zona", afirma. Y resume: "Las empresas mineras cuentan con la complicidad de los gobernantes, tanto municipales como provinciales". Pide precisar nombres: la intendenta Roxana Paulón, y el gobernador, Raúl Jalil.
+Desde la Asamblea denuncian falta de información respecto de los impactos de la explotación de litio, la ausencia de participación ciudadana, la violación de la Ley de Glaciares y exigen la aprobación de la Ley de Humedales. Recuerdan que los salares (donde se encuentra el litio) son también humedales. De allí que que entre los grandes opositores a la protección de humedales --además de sectores del agronegocio-- están las mineras y los gobiernos de Catamarca, Jujuy y Salta.
+La compañía china ya comenzó la construcción de la plata de tratamiento químico, a solo cuatro kilómetros del pueblo. "Está en la orilla misma de Fiambalá, en tierras cedidas por la intendenta Paulón", cuestiona la asambleísta.
+"Pucará" es la sigla de la organización Pueblos Catamarqueños en Resistencia y Autodeterminación, que reúne a asambleas y organizaciones socioambientales de la provincia. Verónica Gostissa integra Pucará y señala que la década del 90 podía haber cierta ilusión respecto al "desarrollo" que prometía la megaminería porque era algo nuevo para la provincia. "Tres décadas después es ridículo que nos quieran hacer creer en las supuestas bondades que traería el proyecto MARA o la explotación de litio. Esta película ya la vimos. Los territorios ya saben lo que implica la marinería y por eso el rechazo es total", explica.
+Desde Pucará trabajan respecto al mito de la "transición energética" de la mano del litio, como una supuesta solución a la crisis climática: "Es mentira que el litio es parte de una 'transición energética verde' (para utilizar menos petróleo). Porque la minería de litio implica la destrucción de salares y lagunas altoandinas, claves para combatir la crisis climática". Gostissa hace especial hincapié en la vulneración de derechos y tiende un vínculo con el pasado y el presente: "Desde los territorios que luchamos contra el extractivismo decimos que 'memoria, verdad y justicia' tiene que poder aplicarse no solo a los años de la dictadura cívico-militar, sino que tiene que aplicarse a los desastres ambientales, al ecocidio que sucede de la mano de gobiernos y multinacionales, es un modelo que viola sistemáticamente los derechos humanos. Y no se puede mirar para otro lado".
+[H2] Derechos y agua
+"Minería Transnacional de litio en Lagunas Altoandinas de Catamarca", es el título de la investigación de la organización BePe, de Catamarca. En 50 páginas detalla que el proyecto minero vulnera leyes ambientales (como la Ley General del Ambiente), la legislación indígena (Convenio 169 de la OIT) e incluso vulnera acuerdos internacionales como el Convenio Ramsar y el Acuerdo de Escazú. Y alerta por la falta de estudios respecto al impacto de la explotación en el agua.
+Desde la Asamblea Fiambalá Despierta hacen eje en el mismo punto. Explican que el proyecto Tres Quebradas pone en riesgo la Cuenca de Abaucán, que alimenta de agua a todos los pueblos de la zona. "La minería consume millones de litros de agua por día. Y esta es una zona árida. No queremos ser un pueblo sacrificable, no creemos en las falsas promesas. El agua es de los pueblos, por eso no queremos a las mineras", resume la asambleísta Yolanda Espinoza.</t>
   </si>
   <si>
     <t>Miles de bolsonaristas vuelven a pedir un Golpe contra el triunfo de Lula</t>
@@ -1846,7 +4620,28 @@
     <t>https://www.pagina12.com.ar/498055-miles-de-bolsonaristas-vuelven-a-pedir-un-golpe-contra-el-tr</t>
   </si>
   <si>
-    <t>2022-11-16T03:01:00Z</t>
+    <t xml:space="preserve">Título: Miles de bolsonaristas vuelven a pedir un Golpe contra el triunfo de Lula
+Chapeau: Los manifestantes aprovecharon el feriado en ciudades como Brasilia y Río de Janeiro
+Subtítulo: Denuncian un fraude supuestamente perpetrado con el sistema de urnas electrónicas. Esa posibilidad, sin embargo, ya fue descartada por observadores internacionales y un informe de las propias Fuerzas Armadas.
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, Luiz Inácio Lula da Silva, printed-edition, jair-bolsonaro, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/498055-miles-de-bolsonaristas-vuelven-a-pedir-un-golpe-contra-el-tr/
+Notícia completa (15 blocos):
+Miles de bolsonaristas se concentraron este martes, feriado por la conmemoración del Día de la República, frente a los cuarteles de varias ciudades brasileñas para exigir una intervención militar con el propósito de impedir la investidura del presidente electo, Luiz Inácio Lula da Silva. Las concentraciones más numerosas se produjeron ante el cuartel general del Ejército, en Brasilia, y ante el Comando Militar del Sureste, en San Pablo, donde los manifestantes denuncian un fraude supuestamente perpetrado con el sistema de urnas electrónicas en los comicios del 30 de octubre. Esa posibilidad, sin embargo, ya fue descartada por numerosos observadores internacionales y un informe de las propias Fuerzas Armadas.
+[H2] "No queremos un país comunista"
+Los manifestantes iban vestidos en su gran mayoría con la camiseta de la selección brasileña, portaban banderas y muchos de ellos llevaban carteles en portugués o inglés asegurando que Brasil fue "robado" en las elecciones del pasado 30 de octubre. "No queremos que Lula asuma el comando el primero de enero, no queremos un país comunista, queremos un Brasil mejor", declaró la bancaria Lais Nunes, de 30 años, durante la manifestación en Río de Janeiro.
+"Hay diversas informaciones de que hubo fraude en las elecciones, no podemos aceptar eso", sostuvo por su parte el policía Leandro de Oliveira, de 38 años, quien atribuye el fraude a una supuesta conspiración por parte del Tribunal Superior Electoral (TSE) para privilegiar al expresidente de Brasil entre 2003 y 2010. En Brasilia también se congregaron miles de personas frente al Cuartel General del Ejército, sosteniendo pancartas con leyendas como "S.O.S. Fuerzas Armadas".
+La seguridad fue reforzada en la región central de la capital este martes tras la convocatoria de protestas a través de las redes sociales. La policía restringió de forma preventiva el acceso de vehículos y peatones a la Plaza de los Tres Poderes, donde se ubican los edificios de la presidencia, el Congreso y la Corte Suprema.
+Un equipo de la radio Jovem Pan debió ser escoltado por militares para salir de la protesta entre gritos y amenazas de los manifestantes exigiendo que abandonen el lugar. Cabe recordar que Jovem Pan se hizo conocida como la voz del bolsonarismo y despidió a diferentes profesionales desde la segunda vuelta de las elecciones, según informó el diario Folha de Sao Paulo.
+Los medios locales también reportaron manifestaciones frente a un cuartel militar en San Pablo y en la ciudad de Belo Horizonte, estado de Minas Gerais. En menor escala, también se registraron actos antidemocráticos en ciudades como Vila Velha, Ribeirao Preto, Joinville y Dorados. Folha aseguró que, de acuerdo al relato de camioneros de Bahía, Mato Grosso y Goias, para sumarse a las caravanas todos los gastos estuvieron a cargo de sus patrones y empresarios del agronegocio.
+[H2] Por ahora no hay respaldo militar
+Las protestas de este martes se produjeron a pesar de que las Fuerzas Armadas han manifestado su apoyo expreso a la democracia y reconocieron su "plena "conformidad con el resultado de las elecciones, en las que Lula derrotó a Bolsonaro por un estrecho margen de 1,8 puntos porcentuales. Los militares hicieron una auditoría al sistema de votación y no hallaron indicios de fraude en las elecciones, pero tampoco descartaron la posibilidad de que haya sido cometido.
+Desde el día posterior a las elecciones, los grupos de ultraderecha iniciaron las protestas, que en los primeros días llevaron a cientos de camioneros a bloquear varias rutas en todo el país. Estos bloqueos se levantaron pasados cuatro días de los comicios, después de que Bolsonaro le pidiera a sus seguidores que se abstengan de obstaculizar las carreteras, aunque en ese momento el capitán retirado del Ejército justificó las manifestaciones y las tildó de legítimas.
+Desde entonces pequeños grupos permanecen acampados frente a algunos cuarteles, pero los manifestantes solo volvieron a las calles en una cifra importante en días festivos como en el día de los Muertos y este martes, cuando se recuerda la jornada en que la república fue investida por el mariscal Deodoro da Fonseca en 1889, en Río de Janeiro.
+[H2] Bolsonaro sigue recluido
+Luego de la derrota electoral y mientras avanza la transición que culminará con la investidura de Lula en enero, Bolsonaro se mantiene recluido y prácticamente se ha ausentado de la vida pública, incluso de las redes sociales. Desde la cúpula de su formación, el Partido Liberal (PL), critican duramente el ostracismo voluntario de un Bolsonaro al que le han hecho saber que el tiempo de lamer las heridas causadas por su derrota en las elecciones ya terminó, según cuenta el diario O Globo.
+Sus detractores sostienen que, en caso de continuar con esta actitud, podría caer en la irrelevancia y perder buena parte del apoyo que a pesar del resultado electoral ha conseguido. La decisión de no acudir a la reunión del G20 que está teniendo lugar estos días en Bali, Indonesia, fue también criticada por sus aliados, que consideran que debería haber usado su agenda internacional para contrarrestar la influencia de Lula, a quien se verá esta semana en Egipto en la cumbre del clima de Naciones Unidas (COP27).
+Dentro del PL entienden que es hora de dar vuelta la página de los comicios y que Bolsonaro se erija en líder de la oposición de cara a una posible candidatura en 2026. El propio Lula manifestó la semana pasada que ya era tiempo de que "el presidente reconozca públicamente su derrota, reflexione y si se preparará de aquí a unos años para ser candidato otra vez", ya que "nadie creerá el discurso golpista de uno que perdió las elecciones".</t>
   </si>
   <si>
     <t>Santafesinos en Singapur</t>
@@ -1858,7 +4653,14 @@
     <t>https://www.pagina12.com.ar/497339-santafesinos-en-singapur</t>
   </si>
   <si>
-    <t>2022-11-14T03:00:13Z</t>
+    <t xml:space="preserve">Título: Santafesinos en Singapur
+Chapeau: Misión comercial
+Subtítulo: En el marco de la misión institucional y comercial de la Región Centro a Singapur, 11 empresas santafesinas del sector alimenticio y afines participaron de rondas de negocios con importadores, dist
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/497339-santafesinos-en-singapur/
+Notícia completa (1 blocos):
+En el marco de la misión institucional y comercial de la Región Centro a Singapur, 11 empresas santafesinas del sector alimenticio y afines participaron de rondas de negocios con importadores, distribuidores y traders del sudeste asiático. Santiago Aguirre, director comercial de Pampa Cheese, productora de quesos de la localidad de Progreso, mencionó que “vinimos con la expectativa de abrir el mercado y poder colocar al queso argentino en Singapur. Después de las reuniones nos vamos con resultados muy positivos”. Francisco Ruiz Portugués, representante de la Cámara de Frigoríficos de Santa Fe, destacó "contactos con importadores, distribuidores y traders muy interesados en nuestra carne porcina, que es un mercado que se ha abierto recientemente”. También se mostraron optimistas por los resultados Manuel Mateo, del Laboratorio ProAgro de Rosario y Melisa Arribere de Agronegocios Jewell de Rosario. Además de la ronda de negocios, la comitiva visitó Enterprise Singapore (agencia gubernamental de desarrollo); Fair Price (cadena de supermercados más importante de Singapur) e Interfood (principal trader del sector lácteo del país).</t>
   </si>
   <si>
     <t>Mujeres contra el cambio climático: quiénes son las defensoras del medio ambiente que se plantan en la COP27</t>
@@ -1870,7 +4672,46 @@
     <t>https://www.pagina12.com.ar/496988-mujeres-contra-el-cambio-climatico-quienes-son-las-defensora</t>
   </si>
   <si>
-    <t>2022-11-12T01:38:53Z</t>
+    <t xml:space="preserve">Título: Mujeres contra el cambio climático: quiénes son las defensoras del medio ambiente que se plantan en la COP27
+Chapeau: Lideresas indígenas, campesinas y afro llevan sus planteos a la cumbre de la ONU
+Subtítulo: Muchas de ellas encabezan los procesos de defensa de sus territorios frente al avance de la industria extractivista, la minería y el agronegocio.
+Editoria: Newsletter
+Tags: Honduras, Nicaragua, Guatemala, Bolivia, Ecuador, Newsletter Causas, newsletter-causas
+URL: https://www.pagina12.com.ar/496988-mujeres-contra-el-cambio-climatico-quienes-son-las-defensora/
+Notícia completa (33 blocos):
+Desde la frontera sur de Guatemala hasta la Argentina, decenas de mujeres representantes de comunidades campesinas y pueblos indígenas llevarán hasta la Conferencia de las Naciones Unidas sobre el Cambio Climático (COP27) propuestas y alternativas implementadas en sus pueblos para mitigar el impacto de la crisis climática.
+“Estamos reforestando las áreas que han sido deforestadas por narcofinqueros”, cuenta por ejemplo Elodia Castillo, alcaldesa indígena y titular de Coordinadora de Asociaciones y Comunidades para el Desarrollo Integral del Pueblo Maya Chortí (COMUNDICH).
+En junio, la oficina de la ONU encargada de dar respuesta a la crisis climática indicó que la crisis climática impacta de forma desproporcionada a las mujeres y niñas porque son las encargadas de gestionar recursos naturales esenciales como el agua.
+De ahí la importancia de las mujeres en la lucha contra el cambio climático. "Cuando tienen un acceso igualitario a las oportunidades de toma de decisiones, adoptan decisiones más sostenibles", decía el documento publicado en ese momento. Además muchas veces son las mujeres las que en sus propios pueblos encabezan los procesos de defensa de territorios frente al avance de la industria extractivista, la minería y el agronegocio.
+Castillo junto a más de 30 lideresas indígenas, afrodescendientes, campesinas y defensoras del medio ambiente se reunieron en el marco del primer Encuentro Latinoamericano de Mujeres Defensoras Ambientales para la Acción Climática que se realizó en Buenos Aires para acordar una posición conjunta para presentar ante la Conferencia de las Naciones Unidas sobre el Cambio Climático COP27.
+[H2] Mujeres al frente de la acción contra el cambio climático
+La cumbre climática arrancó esta semana en Egipto y abre un espacio de dos semanas donde gobiernos, organizaciones sociales y representantes comunitarios se encuentran para discutir mecanismos que permitan enfrentar las consecuencias del cambio climático.
+“Lo que buscamos es que a través de la COP y a través de todas las instancias a las que les compete velar por los pueblos indígenas se tomen en cuenta nuestras demandas como comunidades como el tema de la seguridad alimentaria para enfrentar la desnutrición en mujeres y niños”, explica Castillo.
+La organización de Naciones Unidas para la Alimentación y la Agricultura (FAO) indicó que a pesar de que América Latina es una potencia agrícola sufre “un fuerte aumento del hambre en los últimos años”. Según el organismo, esto trae a la luz la necesidad de “transformar sus sistemas agroalimentarios para que sea más eficientes, inclusivos, resilientes y sostenibles”.
+[H2] Recuperar la tierra: huertos orgánicos y restauración de ecosistemas
+Para Ana Osorio, lideresa del pueblo Miskito y parte del fondo Tierra Viva, el rescate de la medicina ancestral es una de las formas en las que los pueblos más afectados pueden hacer frente a los gastos de salud que tienen las familias en la región de La Moskitia, en la zona oriental de Honduras. “Trayendo la medicina desde los grandes cerros a los patios de las casas” y a su vez “rescatando granos y semillas a través de bancos de semillas y cultivando la tierra para que no queden tierras ociosas”, agrega.
+“Estamos trabajando muy fuerte para valorar la tierra: es donde producen, su banco, su caja chica”, cuenta también Osorio. Ante las lluvias repentinas “la gente vio como una oportunidad el trabajo de las parcelas. Algunas familias están organizadas trabajando en cultivos, en parcelas, en tierras que nunca antes habían producido”.
+Hacia el sur de Honduras, en una de las regiones que más sufre de sequías que incluso impactan las zonas de los humedales del Golfo de Fonseca, las comunidades organizadas trabajan para mitigar, restaurar y conservar el territorio. “Tenemos siembras de huertos familiares, conservación de la tortuga golfina, sembramos plantas de mangle que sirven como barrera para el cambio climático”, asegura Mirna Rodríguez de la Unión de empresa del sector social de la economía ambiental de Marcovia (UEDESAMAR).
+Rodríguez cuenta que el municipio de Marcovia en el departamento sureño de Choluteca es uno de los más afectados por el cambio climático. “Tenemos comunidades que son dragadas por el mar, por ejemplo, Cedeño o El Venado, el mar ya está un paso hacia adelante”, advirtió.
+El impacto del cambio climático es reforzado por el avance de la industria extractivista. Hace unos años el sur hondureño vio reducida su población de curiles, un molusco que se encuentra en Honduras y El Salvador. “Investigando nos dimos cuenta de que la culpable fue una gran empresa camaronera, que estas vez no era el cambio climático, porque quedaron algunos curiles y con el apoyo de Tierra Viva tenemos un proyecto para la reproducción de moluscos”, explica Leylis Vijil de UEDESAMAR.
+La protección y defensa de los manglares es clave para las comunidades sureñas. “Los manglares, principalmente el mangle rojo es muy importante porque ahí es donde se encuentran toda especie de moluscos y cangrejos. El manglar también es donde vienen a desovar los peces. Es fundamental para el medioambiente, lastimosamente las grandes camaroneras lo destruyen”, manifestó.
+[H2] Soberanía alimentaria y diversificación de cultivos
+Garantizar la soberanía alimentaría es uno de los principales desafíos para las poblaciones del sur donde las sequías son constantes y las lluvias erráticas. “Cuando hay poca agua lo que sucede es que el invierno se levanta muy temprano y los cultivos quedan deshidratados, no logramos una buena producción y nuestra seguridad alimentaria se ve afectada”, explica Unicer Martínez de la Asociación de Comités Ecológicos del Sur de Honduras (ACESH) que también se refirió al daño de las lluvias prolongadas que provocan deslizamientos en el terreno.
+Para avanzar hacia la soberanía alimentaria están apostándole a los huertos productivos y “diversificación de cultivos donde podemos cosechar productos en diferentes épocas del año, tener cultivos a mediano y largo plazo”.
+Para los cultivos, ACESH también le apuesta al uso de fertilizantes naturales elaborados en las comunidades para que poco a poco el uso de agrotóxicos deje de ser una costumbre. “Utilizamos abonos orgánicos, para el control de plagas usamos insecticidas naturales que preparamos a base de las plantas que encontramos en nuestra parcela”, cuenta.
+En Nicaragua la Red de Mujeres Productoras y Comercializadoras de Nandaime y Diriomo (NOCHARI) implementa la producción agroecológica, diversificación de cultivo, así como capacitaciones en agroecología. Adela Guerrero, directora de NOCHARI, indicó que uno de los principales desafíos que tienen las comunidades respaldadas por la red es “conocer la ley, principalmente conocer en qué podemos tener oportunidad, como con la ley de soberanía y seguridad alimentaria” ratificada en 2009.
+Otro desafío marcado por Guerrero es visibilizar el trabajo que realizan las mujeres en “el cuido del medioambiente, cuido de las reservas de agua con el llamado a reducir los cultivos extractivistas de caña, arroz, plátano y también los mataderos”.
+[H2] Restauración de bosques
+En Ecuador, el trabajo para restaurar ecosistemas también lo realizan mujeres. “Nos encargamos de regenerar ecosistemas degradados o convertidos en desierto, que de pronto se han erosionado por los monocultivos. Nosotros regeneramos con las técnicas que conocemos para que vuelvan a parecerse a los bosques que teníamos antes”, explica Marisol Angulo de la Red Ecuatoriana de Forestería Análoga (REFA), que trabaja con comunidades al este del país.
+Otro de los desafíos marcados por Angulo es el acceso al agua por las concesiones mineras que ahora están en etapa de investigación. “Eso significa que en menos de dos años vendrá la exploración y nosotros ya no tendremos acceso al agua pura sino contaminada. Entonces tenemos que buscar el método para que estas concesionarios no exploren... Porque primero está la vida y el agua es el principal recurso de vida”, agrega.
+En el norte ecuatoriano cerca de la frontera con Colombia, Amada Cortez del Movimiento de Mujeres Negras del Norte de Esmeralda (Momone) da cuenta del impacto del monocultivo de palma aceitera utilizada para biocombustible. “Las mujeres tenían sus tierras pero no tenían apoyo para producir en ellas, entonces la alternativa que fue vender el territorio a las grandes palmicultoras”, explica Cortez. Las empresas que cultivan la palma aceitera compraron las tierras a un precio mínimo y los que antes eran dueños de la tierra pasaron a ser empleados de los empresarios.
+“Las personas que decidieron no vender eran acosados por las grandes empresas que los obligaron a vender esas tierras que sus padres les habían dejado”, cuenta Cortez. “Esa gente ahora se quedó sin tierra y tuvieron que migrar del campo a la ciudad a engrosar las filas de los desocupados”, se lamenta.
+Pero los productores de palma aceitera no sólo se quedaron con las tierras, también contaminan las fuentes de agua de las comunidades del norte de Ecuador. “Las mujeres antes iban a pescar para darle de comer a sus hijos, ahora con la contaminación por parte de las palmicultoras y las mineras ya no pueden hacer eso”, agrega.
+Al impacto ambiental y social de las palmicultoras y las mineras se suma el daño causado por las empresas camaroneras. “Estamos trabajando en las zonas donde las camaroneras hicieron sus pozos para criar camarones”, agrega Amada Cortez. La líder afroecuatoriana explica que con la lucha de los pobladores de la zona evitaron que las camaroneras avanzaran sobre el bosque de mangle. “Dejaron hecho el hueco en el manglar, pero con el proyecto del Programa Mundial para la Alimentación (PMA) estamos sembrando los mangles”.
+[H2] Acceso al agua
+En Bolivia la falta de lluvia por el cambio climático afectó los cultivos del altiplano, según denuncia Hermógena Calderón de la nación Jach’a Suyu Pakajaqi, representante de la Red Nacional de Mujeres en Defensa de la Madre Tierra (Renamat). “Traemos el agua de lejos, hay ojos de agua o pozos y tenemos que recorrer largas distancias para asegurar el agua para nuestro consumo familiar, para nuestros ganados”, manifestó.
+Calderón reconoce la importancia de establecer diálogos sobre cómo el calentamiento global afecta a las comunidades latinoamericanas, sin embargo, tras 27 cumbres climáticas, la pregunta por los avances logrados es inevitable. “Nos preguntamos, en 27 años de estar llevando la COP, ¿qué han hecho hasta ahora? ¿No han hecho nada?”, denuncia.
+“El clima está empeorando por causa de los países industrializados y capitalistas que no entienden qué es la vida. Pero nosotros como indígenas hablamos de nuestro territorio, de nuestra cosmovisión, sabemos qué es la vida y nosotros también somos parte de la tierra”, subraya Hermógena Calderón.</t>
   </si>
   <si>
     <t>Dominique Galeano</t>
@@ -1885,7 +4726,26 @@
     <t>https://www.pagina12.com.ar/495475-ecocidio-y-extractivismo-en-la-agenda-ambiental-saltena</t>
   </si>
   <si>
-    <t>2022-11-07T03:50:21Z</t>
+    <t xml:space="preserve">Título: Ecocidio y extractivismo en la agenda ambiental salteña
+Chapeau: Movimientos sociales y vecinos plantearon sus consignas
+Subtítulo: Los incendios forestales llegaron a Salta capital ¿Bastarán las llamas sobre el cerro 20 de Febrero, los días de humo incesante, aviones y helicópteros hidrantes sobre el macizo, para despertar conciencia ambiental en la mayoría de ciudadanos?
+Editoria: Salta|12
+Tags: Incendios, diario
+URL: https://www.pagina12.com.ar/495475-ecocidio-y-extractivismo-en-la-agenda-ambiental-saltena/
+Notícia completa (13 blocos):
+Los primeros fueron los militantes de la Red Ecosocialista del MST y el Movimiento Territorial de Lileración (MTL) Rebelde de Salta. El viernes por la tarde organizaron una convocatoria frente al Palacio Legislativo en la ciudad de Salta. “No a los desmontes”, por una “Ley de humedales ya”, “Agua para los pueblos” y “No a la megaminería en Cachi y en la Puna” fueron sus principales consignas. Sumaron el reclamo por la explotación del litio, con palabras escritas con tiza en el suelo de ese sector de la plaza Güemes. Jugaron, sin duda, con la espada de la estatua del fundador de la ciudad, que apuntaba justo hacia el sector de consignas dibujadas sobre las baldozas.
+“El fuego sobre el cerro 20 de Febrero se suma a los incendios en Orán. La mitad del país se consume todos los años por la desidia de los gobiernos, y la influencia del lobby inmobiliario y agroganadero. No más territorios y cuerpos envenenados. Queremos soberanía alimentaria y un sistema de producción agroecológica”, dijo Belén Pacheco, en representación del MST. Con la ayuda de un parlante y un megáfono, la dirigente también recordó al gobierno nacional la liberación de las presas políticas mapuches y la desmilitarización de su territorio en la Patagonia.
+Los movimientos definieron su acción del viernes pasado como “plurinacional”. De cara al Palacio Legislativo de Salta, que se encontraba vacío, se dirigieron a todos quienes quisieran escucharlos. Algunos transeúntes lo hicieron: los carteles capturaron la atención de un puñado de turistas, unos pocos que descendían de los colectivos en las paradas de la calle Mitre miraron por minutos al grupo congregado sobre la plazoleta de la estatua de Hernando de Lerma. Los más atentos fueron los efectivos de la Policía de la provincia apostada en las inmediaciones del edificio Legislativo salteño.
+“La tragedia está a nuestro alrededor”, dijo Mirtha Torres, ex detenida política e integrante de la Red por la Defensa de los Derechos Humanos. “El despojo de las tierras a las comunidades se une al avance sistemático del extractivismo de las grandes mineras. Las multinacionales están de acuerdo con los gobierno de turno”, dijo. “Son ellos quienes otorgan los permiso para que las empresas ingresen”.
+“Se regala el patrimonio”, continuó la histórica militante por los derechos humanos. “Contaminan el territorio para extraer los minerales y el litio. El agronegocio forma parte de ese extractivismo”, completó su análisis. “Esta política es proimperialista”, agregó. “Hay gente empobrecida en los barrios y en las villas miserias”. Completó su argumentación recordando que el país está lleno de merenderos y comedores para resistir el hambre, porque no hay fuentes de trabajo genuino. “Repudiamos la política que sustenta este sistema capitalista. No va más. Hace agua por todos lados”.
+“De este edificio (por el Palacio Legislativo salteño) salen todas las propuestas extractivistas que hoy nos afectan”, dijo Eric Zamora, representante de la Asamblea de Lucha Ambientalista de Las Lajitas, en el departamento Anta. “Debemos dejar de luchar por planes sociales, porque lo que nos da dignidad es el territorio. Este proceso tiene que ver con la enajenación. Basta de regalar las tierras al agronegocio. Nosotros (por su lugar de origen) tenemos dos grandes empresas: Cresud y Olmedo. Poseen tierras para todos los habitantes de Salta. Es obsceno el dato, por la cantidad de personas que pelean por un lote de 10 por 30”, cerró su alocución pública.
+“Las megamineras sobrepasan la consulta libre, previa e informada”, recordó Ulises Yanes, en representación de las comunidades Diaguita Calchaquí de Cachi. En su discurso se refirió a las últimas noticias sobre un yacimiento de oro a ser explotado por Yacones SRL. Este medio confirmó que la empresa presentó la semana pasada un pedido formal ante el Juzgado de Minas de Salta para abandonar el proyecto. “Hace unos años intentaron explotar uranio en el Alto Valle Calchaquí”, recordó sobre otra iniciativa minera por la zona de Cachipampa, cerca de Piedra de Molino. “La actividad minera no trae progreso”, sostuvo Yanes. “Los jóvenes emigran de los pueblos y alimentan los cinturones de pobreza en las ciudades. Debemos vivir de lo que producimos, en paz y armonía en nuestros territorios”, expresó.
+[H2] Vecinos autoconvocados
+Un flyer circuló desde el viernes por la tarde en distintas redes sociales. Vecinos autoconvocados llamaban a los ciudadanos a reunirse al pie del Monumento a Güemes el sábado por la mañana. Si bien muy pocos salteñes se sumaron a la convocatoria, sus consignas aportaron a una agenda ambiental en desarrollo. “No a la propiedad privada de los cerros”, expresaba una de las pancartas dirigidas al gobernador de Salta y a legisladores provinciales. Con un guante negro como símbolo de la mano negra detrás de cada episodio ambiental, los ambientalistas levantaron otras pancartas. “Los parques naturales también generan trabajo” y “Esta Reserva es nuestro pulmón verde”, demandaban. La segunda de ellas, en clara referencia al cerro San Bernardo, una reserva municipal desde los años 80.
+“Venimos promoviendo la emergencia ambiental e hídrica, a partir de dos asambleas autoconvocadas”, contó Verónica Ardanaz en representación de Fundación Cebil. En esas dos reuniones generaron un documento para la conformación de una Mesa Ambiental que invitaron a firmar a los autoconvocados en el Monumento. Los incendios en el Valle de Lerma (Chicoana entre ellos) y sobre el cerro 20, movilizaron a un grupo de vecinos del barrio Tres Cerritos que convocaron el encuentro bajo la estatua de Güemes sobre la Avenida Uruguay en la capital salteña.
+“Hace falta más respuesta ciudadana por todo lo que está pasando”, dijo Ardanaz a este medio. La ambientalista, que además integra la mesa de Ordenamiento Territorial de Bosques Nativos, compartió su análisis social. “¿Qué pasa que hay tanto individualismo? ¿o será que las personas están muy apabulladas de información?”, lanzó. “Hay una crisis humana, económica y política que repercute en la capacidad de reacción de las personas”, argumentó. “El impacto sobre la psiquis de las personas es muy grande”, dijo sobre el consumo de mensajes en medios agregada a la situación económica actual. “El efecto del capitalismo pasa por generar en precarización en muchos aspectos de la vida cotidiana”, concluyó.
+Tras la consulta de Salta/12, los vecinos autoconvocados aclararon que el diputado nacional mandato cumplido Martín Grande no asistió al encuentro del Monumento como representante de su espacio político. “Él participó como vecino”, dijo Guadalupe Pérez Marcheta, otra organizadora. “Se mantuvo al margen de las fotos que tomaron los diferentes medios que registraron nuestras propuestas”, completó Verónica Ardanaz.
+La inmensa cicatriz dejada por el fuego en el cerro 20 de Febrero es visible desde la ciudad. Los ambientalistas salteños, desde distintas posiciones políticas, confluyen en un mismo punto: el ecocidio y el extractivismo cercenan los derechos de la ciudadanía.</t>
   </si>
   <si>
     <t>Daniel Scioli: "Esta elección abre una oportunidad única en la relación con Brasil"</t>
@@ -1897,7 +4757,25 @@
     <t>https://www.pagina12.com.ar/494996-daniel-scioli-esta-eleccion-abre-una-oportunidad-unica-en-la</t>
   </si>
   <si>
-    <t>2022-11-05T03:01:00Z</t>
+    <t xml:space="preserve">Título: Daniel Scioli: "Esta elección abre una oportunidad única en la relación con Brasil"
+Chapeau: Encuentro del embajador argentino en Brasil con dirigentes de CAME
+Subtítulo: El embajador se reunió con empresarios pyme y les presentó el plan de integración que le hizo llegar a Lula días después de haber sido reelegido como presidente de Brasil
+Editoria: Economia
+Tags: Daniel Scioli, CAME, Argentina-Brasil, printed-edition, daniel-scioli, diario
+URL: https://www.pagina12.com.ar/494996-daniel-scioli-esta-eleccion-abre-una-oportunidad-unica-en-la/
+Notícia completa (12 blocos):
+Desde Curitiba
+"La afinidad que hay en las primeras lineas de gobierno a partir de la asunción de Lula va a generar una relación decisivamente más fluida. Durante el gobierno de Bolsonaro fue difícil, los presidentes no se reunieron nunca bilateralmente. Esta elección abre una oportunidad única en la relación con Brasil". El embajador argentino en Brasil, Daniel Scioli, viajó especialmente a Curitiba para reunirse con una comitiva de dirigentes de la Confederación Argentina de la Mediana Empresa (CAME). Presentó el plan de integración bilateral que está a la espera de la asunción del nuevo gobierno brasileño, y se puso a disposición ante la participación de los dirigentes en la Feria de Alimentos en Curitiba el próximo 18,19 y 20 de abril.
+"Como nací en un hogar pyme, para mi es un sector crucial", comenzó el encuentro Daniel Scioli después de saludar a la comitiva de quince dirigentes empresariales y empresarios pyme que viajaron a Brasil para afianzar relaciones comerciales y poder ingresar al tentador- por su tamaño- mercado brasileño.
+El embajador comenzó haciendo un recorrido por su gestión: "Cuando asumí, la relación estaba tan mal que Brasil había dejado de ser el primer socio comercial de Argentina, y a los ocho meses conseguimos reubicarlo en esa posición. Tanto que el año pasado hubo récord de exportaciones". La estrategia fue, según el embajador, "no esperar a que nos vengan a comprar, sino que salimos a vender y buscar nuevos mercados dentro del país".
+El perfil de las exportaciones de Argentina, que se concentraban en las ciudades San Pablo y Porto Alegre, se federalizaron hacia otras ciudades brasileñas más accesibles y con economías complementarias. "Encontré una predisposición total del Estado de Paraná, que es una gran puerta de entrada a Brasil", agregó.
+"No fue fácil. Lo tenía a Jair Bolsonaro diciendo despectivamente que en Argentina eramos comunistas, socialistas y yo explicándoles a los empresarios que no, que todo bien, que era un mensaje plenamente político", resumió Daniel Scioli. Además de aumentar las ventas, Scioli destacó la creación de 14 cámaras de comercio binacionales y la resolución de 49 controversias que había que impedían exportaciones. Por ejemplo, de langostinos, donde el comercio llegó a estar judicializado "por un fuerte lobby de la Cámara del Camarão, como le dicen acá".
+Los dirigentes lo escucharon con una sonrisa que se reconfirmó en sus comentarios post-encuentro: "Se nota que nos escucha y conoce del sector. Es una embajada con una impronta productiva más que meramente diplomática y eso es clave en las relaciones con Brasil", comentaban. Una vez finalizado, la comitiva cenó junto con el embajador en una parrilla argentina de la ciudad: "Es muy accesible, no todos se sientan en la mesa con quince empresarios", sumaban.
+[H2] Plan de Integración bilateral
+Bajo la consigna “Acuerdo de integración Argentina-Brasil”, Scioli presentó a los empresarios el plan de integración binacional del gobierno de Alberto Fernández que ya está en manos del equipo de Lula: integración financiera, energética, minera, en agronegocios e industria, donde hizo un punto a parte: "Es un tema que hable particularmente con Lula. Todo bien con la integración política e ideológica pero tenemos que ir a una integración industrial porque sino la relación es muy desigual. Las empresas se quedan acá y ponen filiales en Argentina", aseguró Scioli y agregó que "la economía brasileña tiene sus cosas: es difícil hacer la primera venta, pero una vez que entran es impresionante el nivel de demanda que tiene este mercado".
+Sobre la integración financiera, resaltó las dificultades prácticas que puede traer un sistema de moneda local, y mencionó una posibilidad de realizar un swap con Brasil, que cuenta con reservas en el Banco Central: "Igual todavía no asumió Lula, pero es una posiblidad a plantear", respondió al escuchar el entusiasmo de los empresarios pyme.
+Luego, continuó con el resto de los puntos de integración: conseguir una mayor conectividad aérea y turística, economía del conocimiento, salud, temas fronterizos y ambientales, de defensa, industrias nuclear y espacial, ciencia y tecnología, educación, derechos humanos y género y la cuestión Malvinas. El plan no difiere de lo que se venía hablando con Bolsonaro, pero la expectativa es que avance más rápido dada la sintonía política.
+Por su parte los empresarios de CAME le anunciaron a Scioli su participación en la Feria y Convención Paranaense de Supermercados a realizarse los días 18, 19 y 20 de abril del año próximo. La entidad pyme apuesta a sumar empresarios argentinos del rubro alimenticio al evento paranaense. “Si con este gobierno, a pesar de las diferencias, pudimos hacer todo lo que les conté, con este gobierno se va a destrabar más. Es una gran oportunidad para el país”, cerró el embajador.</t>
   </si>
   <si>
     <t>Los silencios espesos de Jair Bolsonaro</t>
@@ -1909,7 +4787,25 @@
     <t>https://www.pagina12.com.ar/493971-los-silencios-espesos-de-jair-bolsonaro</t>
   </si>
   <si>
-    <t>2022-11-01T03:01:00Z</t>
+    <t xml:space="preserve">Título: Los silencios espesos de Jair Bolsonaro
+Chapeau: Los cortes de rutas de camioneros como única reacción a la derrota
+Subtítulo: El vicepresidente felicitó al vice electo de Lula, y el resto fue ausencia. Los que votaron esperaron en vano una palabra del ultraderechista perdidoso, que calló.
+Editoria: El Mundo
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/493971-los-silencios-espesos-de-jair-bolsonaro/
+Notícia completa (12 blocos):
+Desde San Pablo
+La épica bolsonarista es solo por ahora un combo de silencio y cortes de ruta. Brasil esperaba palabras que no llegaron -al menos hasta el lunes 31- de su todavía presidente. Su entorno político más próximo le pide que hable. Pero la única reacción oficial al resultado electoral desde el Poder ejecutivo se conoció por vía de su vicepresidente, el militar Hamilton Mourão. Sin que pudiera confirmarse si obró per se o por mandato de su jefe político, el general retirado le envió un mensaje al compañero de fórmula de Lula, el médico Geraldo Alckmin. Algo muy protocolar que consistió en una felicitación y su disposición a contribuir en la transición hacia el cambio de gobierno. También uno de los hijos de Bolsonaro, Flavio, escribió un tuit de agradecimiento a los “que rezaron” y se despidió con un “¡Dios a cargo!” No hubo más.
+El relato confrontador del presidente en cuatro años de mandato dejó paso al mutismo. Mientras no da señales, una protesta de fanáticos que lo apoyan, mezcla de camioneros, empresarios del agronegocio y comerciantes, cortan rutas y autopistas en algunas regiones del país. Por ahora la situación no se desbordó, pero es una amenaza concreta al paso de personas y mercancías entre varios centros neurálgicos del país.
+La PRF, Policía Federal de Carreteras, se tomó un tiempo para actuar. Su actitud parece mucho más lábil que la mantenida el día de la elección, cuando detuvo a decenas de ómnibus con partidarios del PT y sus aliados que iban a votar en el Nordeste.
+Los primeros efectos después de la victoria de Lula superan la caída inicial de la Bolsa – que luego se recuperó – y la incertidumbre general en los mercados por las medidas que tomará desde el 1° de enero. Pero las consecuencias de los piquetes ruteros son más impredecibles, aunque esas acciones están ceñidas a estados con fuerte presencia de la ultraderecha brasileña. En el sur, sudoeste y sudeste.
+Al mensaje de Mourão a Alckmin, un general opaco pero más discreto e inteligente que su compañero de binomio en las elecciones de 2018, le siguió un reconocimiento implícito de la derrota en las redes sociales que escribió Flavio Bolsonaro, el coordinador de la campaña presidencial de su padre. “¡Gracias a todos los que nos ayudaron a rescatar el patriotismo, que rezaron, rezaron, salieron a las calles, dieron su sudor por el país que está trabajando y le dieron a Bolsonaro el mayor voto de su vida! ¡Levantemos la cabeza y no renunciemos a nuestro Brasil! ¡Dios a cargo!”, se expresó en Twitter con el tono de sermón religioso que el clan familiar suele utilizar en sus intervenciones públicas. Sus hermanos Carlos y Eduardo que ocupan diferentes cargos políticos no difundieron su pensamiento sobre la victoria de Lula.
+El sitio periodístico UOL publicó que el llamado Centrão – una alianza de pequeños partidos de derecha – y algunos ministros habían intentado convencer al presidente de que reconociera la decisión ciudadana del pueblo brasileño, que le indicó el retorno a su casa en Barra de Tijuca. Uno de los miembros de su gabinete, citado por el medio, declaró: “Bolsonaro necesita actuar en dos frentes. Cuidar personalmente de él y sus hijos, quienes son objeto de investigaciones. Y de su grupo político, que, a pesar de ser derrotado, salió con fuerza de las elecciones de este año, conquistando el principal estado del país, San Pablo”.
+Pero no hubo caso. Bolsonaro nunca abandonó el silencio, aunque hubo voces que se hicieron escuchar por él y que no ocupan cargos en el gobierno. Son las que pasaron a los hechos en varias carreteras del país cuando decidieron cortarlas y dejar aisladas a varias localidades del sudeste, centro oeste y sur de Brasil. En los piquetes donde camioneros, empresarios del agronegocio y comerciantes metieron presión, no hubo una táctica uniforme, aunque si un mismo camino de agitación que comenzó por las redes sociales.
+La convocatoria inicial partió desde Telegram, se extendió a Whatsapp y se viralizó hasta convocar voluntades hacia diferentes rutas del país. El mensaje decía: “Atención, entren a los grupos de sus respectivos estados y organicen sus concentraciones. Primero en las rutas, después en las vías de acceso y por fin en el centro de las ciudades. El plazo para la acción de las fuerzas armadas es de 72 horas. No tenemos políticos, partidos o financiamientos. Nosotros somos el pueblo. No seremos ultrajados en nuestra patria. Comunismo aquí no. Lista de grupos de Telegram”. El texto salió desde el estado de Paraná, uno de los tres del sur, donde los cortes de ruta no pasaron inadvertidos en los medios nacionales.
+La consigna era “Já” (Ya) y corrió por varios de los principales caminos de Brasil, aunque encontró resistencia en su propia base. Wallace Landim, alías Chorão, presidente de la Asociación Brasileña de Conductores de Automotores (ABRAVA), difundió su posición contraria a las medidas a través de un video: “Vengo hoy para hablar con nuestro segmento del transporte. Estamos pasando por un momento muy difícil. Hay mucha gente llamándome, preguntando por el paro, con algunos puntos en las rutas ya detenidos en este país. Quiero colocarme aquí, a través de ABRAVA, para reconocer la elección, la democracia, para felicitar al presidente Luiz Inácio Lula da Silva por su victoria”.
+Sus palabras tenían cierta legitimidad. Es el hombre que en 2018 había cortado rutas por reclamos sectoriales que coincidieron con las reivindicaciones que levantaba el electorado ruralista y transportista que seguía al entonces candidato a presidente Bolsonaro. “Este no es el momento de parar el país. Esto es Democracia. ¡Un abrazo a todos!”, terminó el dirigente que se abrió de la protesta. Una medida que amenazaba con cortar la conectividad de un país inmenso donde el bolsonarismo resiste la voluntad electoral que se expresó en las urnas.
+gveiga@pagina12.com.ar</t>
   </si>
   <si>
     <t>Brasil: Lula fue felicitado a nivel global y Bolsonaro, callado</t>
@@ -1921,6 +4817,31 @@
     <t>https://www.pagina12.com.ar/493967-brasil-lula-fue-felicitado-a-nivel-global-y-bolsonaro-callad</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Brasil: Lula fue felicitado a nivel global y Bolsonaro, callado
+Chapeau: Análisis de la victoria del líder del Partido de los Trabajadores
+Subtítulo: Al presidente electo lo llamaron Biden y Macron, entre una larga lista de mandatarios. El presidente brasileño, cuya imagen se deterioró más por dos casos con armas, no hizo declaraciones.
+Editoria: El Mundo
+Tags: Luiz Inácio Lula da Silva, Jair Bolsonaro, printed-edition, luiz-inacio-lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/493967-brasil-lula-fue-felicitado-a-nivel-global-y-bolsonaro-callad/
+Notícia completa (16 blocos):
+Desde San Pablo
+La radiografía precisa y detallada de la victoria de Lula contiene varias confirmaciones y algunas sorpresas. La página oficial del Tribunal Superior Electoral (TSE) facilita el análisis después de un octubre que termina tan tenso como violento. Ratificado el líder del PT en la presidencia por esa autoridad suprema de la votación, reconocido de inmediato por presidentes como Joe Biden que lo llamó, Emmanuel Macron que demostró su satisfacción y el propio Alberto Fernández que viajó hasta Brasil, rastrear los datos finos de esta elección crucial, se impone para conocer ciertas motivaciones del desenlace el domingo. En contraste con ese despliegue de contactos políticos de primer nivel, de encuentros formales e informales, el jefe de Estado, Jair Bolsonaro, nunca rompió el silencio.
+Los más fanáticos seguidores del presidente Bolsonaro que lo llevaron al Planalto en 2018, tal vez pudieron alejarlo de su meta reeleccionista con conductas delictivas y al menos en dos casos con armas a la vista, en los días previos a la segunda vuelta. Hechos cuyo impacto en la votación es difícil de mensurar, pero que tuvieron una gran repercusión pública.
+Uno fue el episodio del exdiputado Roberto Jefferson. El hombre que tiroteó a la policía desde su mansión en Río de Janeiro. Cursaba una condena domiciliaria y volvió a la cárcel. Había visitado a Bolsonaro cuatro veces en el Planalto pese a que el jefe de Estado no quiso reconocer esa afinidad. El otro hecho lo protagonizó la legisladora Carla Zambelli, del mismo partido que el presidente. Corrió a un hombre arma de puño en mano y se metió en un bar con la excusa de que había sido atacada. Se comprobó que su víctima es periodista deportivo y trabaja en la agencia de comunicación Weber Shandwick, dedicada al área cultural. Además colabora en el sitio de noticias The Playoffs.
+[H2] El Nordeste y Minas Gerais
+Las dos situaciones deterioraron aún más la imagen Bolsonaro pocos días antes del balotaje. Un segundo turno que terminó con una apretada diferencia del 1,80 por ciento. El 50,90 para Lula y un 49,10 para el presidente que deberá entregarle el gobierno el 1° de enero. El ganador se impuso en trece estados, de los cuales nueve pertenecen a la región del Nordeste, donde reside su mayor caudal político. Además venció de manera muy ajustada en el estratégico Minas Gerais (50,20 a 49,80) y en tres de los siete estados con más caudal de votantes del norte de Brasil: Amazonas, Tocantins y Pará.
+Lula hizo la gran diferencia en su terruño, donde de manera casi uniforme le dio una paliza a Bolsonaro. Los nueve estados del Nordeste, incluido Pernambuco donde nació, le otorgaron la confianza con porcentajes que oscilaron entre el 76,86 por ciento de Piauí y el 58,68 de Alagoas. Además, su único candidato a gobernador vencedor, Jerônimo Rodrigues, triunfó con amplitud en Bahía. Los tres restantes que pasaron a la segunda vuelta perdieron. Fernando Haddad en San Pablo y los que con pocas chances aspiraban a las gobernaciones de Santa Catarina y Sergipe.
+Su rival, el atribulado presidente al que todavía no se le escuchó la voz después de la elección, ganó en los catorce estados restantes. Aún con su victoria en San Pablo, el más poblado del país – donde venció su candidato a gobernador de la fuerza Republicanos, Tarcisio Gomes de Freitas -, no le alcanzó para continuar en el gobierno por otros cuatro años. También se impuso en Río de Janeiro y Espíritu Santo en el sudeste, pero donde sacó la diferencia más amplia fue en los tres estados del sur: Paraná, Santa Catarina y Rio Grande del Sur (RS).
+La felicidad de Bolsonaro no fue completa en la región. En el industrializado RS, su candidato a gobernador Onyx Lorenzoni sufrió una de las peores derrotas. El tucano Eduardo Leite le dio vuelta el resultado del 2 de octubre con el apoyo del electorado del PT. El perdedor había ejercido el cargo de ministro jefe de la Casa Civil de Bolsonaro.
+Donde también ganó con amplias diferencias el militar presidente fue en la región del Centro Oeste, polo fundamental de los agronegocios. En el Distrito Federal de Brasilia, Goias, Mato Grosso y Mato Grosso del Sur el proyecto reeleccionista sacó porcentajes muy altos, entre el 59 y 65 por ciento.
+[H2] El Congreso, escenario complicado
+Lula tendrá que desplegar a pleno su reconocida capacidad de armador político en el Congreso. Su bancada propia en las dos cámaras es exigua (68 diputados y 9 senadores del PT). Aún con sus aliados del Partido Comunista de Brasil (PCdoB), el PSOL de Guilherme Boulos y otras fuerzas menores, no llegaría a conseguir poner en funcionamiento los dispositivos parlamentarios que se requieren para aprobar leyes vitales. Una de ellas, la reforma tributaria.
+De los 308 diputados federales que se requieren para sacar una norma en el Congreso, el próximo presidente y sus aliados llegan hoy a 122. Les faltan nada menos que 186. Para lograr quórum en la Cámara Baja necesita 257 legisladores, por lo que debería llegar a juntar 135 diputados más a los que tiene su bancada. Para convocar a un plebiscito precisa menos. Son 171 diputados y descontados sus 122 tendría que agregar 49 más a los propios y sus aliados.
+Otro tanto le sucederá en el Senado. De los nueve que mantienen una banca en la Cámara Alta por el PT – a los que deben sumarse tres de sus aliados – tiene casi una cuarta parte de la cantidad que necesita para sesionar. Son 41 y le faltan 29. Condicionado por este panorama en el Congreso, Lula tiene que ampliar su propia fuerza en un escenario casi siempre hostil para su partido.
+En esa caja de resonancia de la democracia brasileña, su compañera y expresidenta Dilma Rousseff, fue destituida en 2016. Bolsonaro empezó a construir su camino hacia el Planalto también en ese recinto. Cuando votó para sacar del cargo a esa mujer que la noche del domingo acompañaba a Lula en el palco, reivindicó la memoria de su propio torturador, Carlos Brilhante Ustra.
+gveiga@pagina12.com.ar</t>
+  </si>
+  <si>
     <t>Elecciones Brasil 2022: la mirada de Juliano Corbellini</t>
   </si>
   <si>
@@ -1930,7 +4851,32 @@
     <t>https://www.pagina12.com.ar/493338-elecciones-brasil-2022-la-mirada-de-juliano-corbellini</t>
   </si>
   <si>
-    <t>2022-10-29T03:01:00Z</t>
+    <t xml:space="preserve">Título: Elecciones Brasil 2022: la mirada de Juliano Corbellini
+Chapeau: "La abstención hirió más a la candidatura de Lula."
+Subtítulo: Politólogo y coautor junto al economista Mauricio Moura del libro La elección disruptiva- Por qué ganó Bolsonaro en 2018.
+Editoria: El Mundo
+Tags: Elecciones Brasil 2022, Jair Bolsonaro, Lula Da Silva, printed-edition, elecciones-brasil-2022, jair-bolsonaro, lula-da-silva, diario
+URL: https://www.pagina12.com.ar/493338-elecciones-brasil-2022-la-mirada-de-juliano-corbellini/
+Notícia completa (19 blocos):
+Desde San Pablo
+La mirada de Juliano Corbellini permite ver la trastienda de las encuestas. ¿Por qué aciertan o fallan? ¿Por qué la abstención no ha sido calibrada con precisión por las consultoras? Preguntas que tienen respuestas en este doctor en Ciencia Política con casi veinte años de experiencia en elecciones como asesor de diferentes candidatos. Coautor también junto al economista Mauricio Moura del libro La elección disruptiva- Por qué ganó Bolsonaro en 2018, dialogó con Página/12.
+-Qué análisis hizo sobre las encuestas electorales para la primera vuelta y lo que proyectan para este segundo turno?
+- Pienso que ese debate necesita ser hecho con mucho cuidado. Eso que acostumbramos ver ahora como proyección de votos válidos, tiene un problema cuando observamos las pesquisas: presupone que los votos en blanco, nulos, de indecisos y las abstenciones se distribuirán en la misma proporción entre los candidatos. Y eso no es verdad porque la abstención, va a depender del perfil del elector de cada candidato, puede perjudicar más o menos a un candidato. Entonces, si miramos las pesquisas en la primera vuelta, comparando los resultados sobre el electorado total del Tribunal Superior Electoral, lo que vimos es que casi todos los Institutos de Pesquisas llegaron cerca del resultado de Bolsonaro. ¿Dónde estuvo el mayor error? Fue con Lula. Porque la abstención hirió más a la candidatura de Lula.
+- ¿Por qué?
+- Porque los parámetros clásicos para hacer una encuesta, que son las muestras de acuerdo con el perfil socio económico del país a partir de los datos del IBGE (Instituto Brasileño de Geografía y Estadística), parece que no son suficientes porque no representan al electorado que efectivamente va a votar. Porque la abstención no se distribuye igualmente. Es un tema para los técnicos, estadísticos e investigadores, algo que se repite en varias elecciones.
+-¿Qué opina de los análisis que se hacen sobre las serias dificultades que tendría Lula para gobernar? ¿Está de acuerdo?
+- Yo no creo que Lula tendrá dificultades para gobernar. Pienso que él ya hizo un movimiento en dirección al centro cuando empezó la campaña, que fue la elección de Alckmin como candidato a vicepresidente. La adhesión de Simone Tebet fue muy importante por la simbología de ella. La del expresidente Fernando Henrique Cardoso también y ahora la de otro expresidente, José Sarney. Entonces creo que será una experiencia diferente, que va a establecer otro nivel de diálogo entre Lula y sus partidos aliados. La dificultades que pueden venir - y es un tema que no me atrevo hablar porque no entiendo - son las dificultades económicas, lo que quedará después de ese festival de gastos y promesas que tuvimos en la campaña de este año.
+- Usted dice que Lula no tendrá problemas para gobernar por su corrimiento hacia el centro. ¿Qué se puede esperar de otros aliados, pero de izquierda, como Guilherme Boulos, el diputado federal más votado en San Pablo?
+- Va a ser un gobierno que vivirá alguna tensión por tener al PSOL y al Centro en una misma gestión. Siempre existirá una tensión. Pero pienso que no será del mismo grado que en el primer gobierno Lula. Habrá una dinámica nueva, porque empezarán acuerdos electorales entre el PT y PSOL que van a comenzar, probablemente, con el propio Boulos para la Municipalidad de San Pablo en las elecciones de 2024. Entonces, no creo en un rompimiento. Creo más en la capacidad de Lula de acomodar y negociar esos conflictos.
+- ¿Cuál sería el impacto en América Latina de un triunfo de Lula este domingo?
+- La victoria de Lula tendría un impacto importante para las fuerzas de izquierda y centroizquierda, sin duda alguna. Así como la victoria de Bolsonaro fue muy importante para los gobiernos más conservadores, por el peso político y estratégico en política internacional que tiene Brasil.
+- ¿Cómo piensa que se comportará el núcleo duro que apoya a Bolsonaro si su líder pierde los comicios?
+-Es difícil de prever, pero lo más importante es lo que pase antes de la elección, porque eso podría impactar en el resultado. Creo que por el episodio de Roberto Jefferson (N de la R: el ex diputado aliado del presidente que resistió a los tiros a la Policía en su casa), va tornarse más difícil una reacción insurgente, más violenta. Pienso que es muy difícil. El TSE está muy vigilante, la prensa está muy cerrada en contra de esas conductas, entonces pienso que, paradójicamente, Jefferson disminuyó la hipótesis de que pueda pasar. Pero no se juega con locos.
+- Dijo que no se juega con locos ¿Y con las milicias bolsonaristas que controlan favelas como en Río? ¿Qué debería hacer Lula si gana?
+- Existe una base orgánica y social del bolsonarismo. Tiene a los evangélicos, los policías militares de los Estados, las milicias, el agronegocio, que van a ser activos en la oposición a Lula. Entonces, si el gobierno derrapa, si enfrenta dificultades, ése será un tejido social que se movilizará contra él.
+- Por último, ¿considera que las urnas ratificarán las pesquisas que dan ganador a Lula?
+- Sí, pienso que Lula va ganar la elección. No va ser con la ventaja que las encuestas apuntan, porque el factor abstención perjudica mucho más al electorado del PT. Eso está más que demostrado. Pero creo que Bolsonaro llegó al techo. Puede haber, claro, turbulencias de otra naturaleza, pero son cosas imprevisibles que pueden acontecer en cualquier momento.
+gveiga@pagina12.com.ar</t>
   </si>
   <si>
     <t>El dilema del Frente de Todos</t>
@@ -1939,7 +4885,50 @@
     <t>https://www.pagina12.com.ar/491897-el-dilema-del-frente-de-todos</t>
   </si>
   <si>
-    <t>2022-10-24T03:01:00Z</t>
+    <t xml:space="preserve">Título: El dilema del Frente de Todos
+Subtítulo: Las “noticias” de la última semana fueron ocupadas centralmente por episodios mediáticos, policiales, judiciales.
+Editoria: El País
+Tags: Opinión, printed-edition, opinion, diario
+URL: https://www.pagina12.com.ar/491897-el-dilema-del-frente-de-todos/
+Notícia completa (38 blocos):
+Las “noticias” de la última semana fueron ocupadas centralmente por episodios mediáticos, policiales, judiciales. La “política” estuvo casi ausente, en cantidad y calidad. Y eso designa un escenario aburrido, cansador, que sigue interrogando sobre su devenir.
+Apenas si sobresalió que, acerca del Presupuesto 2023, se metió la calentura de famiglias tribunalicias contra la pretensión de cobrarles Ganancias.
+Fue eso y los cruces adentro del Gobierno por los actos del 17 de octubre.
+En los pasillos que parecen estar en una realidad paralela, completamente ajena al interés de “la gente”, hubo lo ya constante de las chicanas intra-cambiemitas. Carrió disparó en la cena de Mirtha que jamás la espiaron tanto como cuando gobernaron sus aliados, y desde ahí siguió el bolero de te amo/te odio/dame más.
+Sí debería repercutir con fortaleza que la investigación del atentado contra Cristina va mostrando orígenes complicados para otra famiglia: la de los hermanos del alma de Mauricio y Aledaños. Pero tampoco.
+La inflación absorbe virtualmente todo, incluyendo datos alentadores como el incremento de la actividad industrial y la creación de empleo en ese rubro (ver la columna de David Cufré, el sábado en este diario).
+Siempre es momento para preguntarse por el qué de lo que se discute, antes que el cómo.
+En un artículo publicado por LaTecl@Eñe (“Pateando mitos y construyendo nuevos”), el colega Hugo Presman recuerda que las habituales crisis económicas argentinas son el argumento de los dueños del país para fugar sus excedentes en un drenaje que, a la par, contribuye a esas crisis.
+Rescata una perla acontecida en el Coloquio de IDEA, en 2011. El entonces titular de la empresa textil El Cardón, Gabo Nazar, dijo en semejante ámbito que “los empresarios argentinos son una máquina de fugar dinero”.
+Esos dueños son una clase sin proyecto de país, como también subraya Presman, aunque esas “burguesías nacionales” sean débiles y dependientes en todo el mundo subdesarrollado.
+El peronismo intentó desarrollar ese tipo de burguesía, y otras veces actuó en lugar de ella.
+Pero la ceguera ideológica del sector, tarde o temprano, le impide apreciar que con los gobiernos nacionales y populares (populistas, vaya horror) sus balances engordan. Y que la mejora de los trabajadores en la distribución del ingreso se traduce en un incremento de la demanda global, capaz de ampliar los beneficios colectivos.
+Se inserta allí uno de los informes del Centro de Economía Política Argentina (CEPA), revelador de lo sucedido en los últimos diez años.
+Entre 2012 y 2015 (el período decreciente de Cristina), las primeras 500 empresas del país tuvieron ingresos promedio por casi 260 mil millones de dólares que, durante Macri, cayeron en un 14 por ciento. Y si se lo mide en utilidades, con el gobierno macrista tuvieron un descenso del 24 por ciento medido contra la peor etapa del kirchnerismo.
+Presman introduce lo ocurrido en Brasil con los dos gobiernos de Lula, que sin tocar intereses económicos incorporó a más de 30 millones de habitantes a una vida (más) digna, sacándolos de la pobreza.
+Apunta lo citado por el politólogo José Natanson en Le Monde Diplomatique, cuando señala que, más que resolver las contradicciones, el lulismo procuró moderarlas con un resultado de equilibrio siempre inestable.
+Lo comprobado es que Lula redujo la pobreza sin confrontar con el capital. Conservó el apoyo del Movimiento Sin Tierra, bien que empujando el agronegocio. Y mantuvo el voto de los sectores conservadores del nordeste, avanzando en reformas progresistas.
+Pese a ello, como advirtió con números oficiales indesmentibles el sociólogo Artemio López, la participación de la industria en el PBI de Brasil cayó del 35 por ciento, en la década del `80, a un 15 por ciento. Y no mejoró.
+Significa -como también resalta Presman- que los apoyos del movimiento obrero hacia los segmentos más empobrecidos e indigentes entran en confrontación severa. Es universal en el neoliberalismo. Y debe tomárselos en cuenta para no alejar los análisis de la realidad.
+Dicho de otra forma, no sólo hay una sociedad profundamente fragmentada en la que inciden la ausencia casi absoluta de una burguesía con lucidez ideológico-política y los prejuicios eternos de una clase media que, en lo aspiracional, no integra a nadie que no sea a sí misma.
+Los clichés contra la negrada, los planeros, los que cortan la llegada al trabajo, sea porque sucede cada tanto en el microcentro porteño o fuere por el propagandismo que articulan los medios no en vano dominantes, y que una gran o decisoria mayoría asume como problemática propia, resultan un paisaje frente al cual el progresismo carece de repertorio.
+Pero es más grave que eso.
+Encima de que debieran forjarse políticas de seducción cultural para que (vastos conjuntos de) las clases medias dejen de ser el hecho maldito de los movimientos nacionales y populares, ocurre que los sectores más derrumbados, los del fondo del pozo, no solamente anclan en la indiferencia o el rechazo asqueado hacia cuanto les represente “la política” o “los políticos”.
+Peor: por convicción o descarte, y sobre todo en sus fragmentos más jóvenes, los seducen esperpentos de extrema derecha que conquistan amplias o amenazantes voluntades electorales en los distritos sumergidos del conurbano bonaerense.
+El peronismo, kirchnerismo, progresismo, o como quiera llamársele al último imaginario que queda contra la barbarie conservadora o neoliberal (también como se quiera), está perdiendo en todos los lados significativos. Pero eso sería “lo de menos” si, aunque fuera, se trazara un horizonte de mejora o, siquiera, de relativa tranquilidad.
+En lugar de eso, cuestiones ¿inconcebibles? como la de haber subido a rango de repercusión masiva lo que sucedió en un pasaje de un programa televisivo que busca exactamente eso; o detenerse en el análisis de si acaso no es hora para manijear a Milei con el objetivo de partirle el voto a los cambiemitas en el Gran Buenos Aires y más allá también, reflejan mucho antes una secuela que una causa.
+No existe batalla política, ni cultural, ni de ninguna índole salvo arrestos individuales, intelectuales, o de grupos acotados, que pueda darse con eventual éxito si, primero, no hay ejemplaridades de arriba hacia abajo.
+La gran mayoría silenciosa asiste al espectáculo de un ¿ex? Frente de Todos cuya dinámica es que nadie parece coordinar nada de nada, producto de la repartija o pegamento fundante que sólo radicó en ganar las elecciones del 2019.
+Aun así, este experimento gubernativo -desde ya que no con su formato actual- continúa asomando como absolutamente lo único que puede o podría ponerle barreras al desquicio antipopular de un retorno de lo peor.
+La pregunta clave es cómo se hace para que, con una inflación descomunal y porciones cada vez más grandes de gente que come salteado, o que se priva de cada vez más cosas en términos cotidianos o proyectuales, cualquiera no dé lo mismo.
+El Gobierno está puesto si descansa en que no tiene otra chance que apoyarse en el mamarracho de la oposición, en tanto eso lo mantendría derrotado pero “competitivo”.
+¿Ya da por perdida la elección presidencial? ¿Es cierto que el “kirchnerismo duro” analiza refugiarse en ganar o zafar las secciones Primera y Tercera de la provincia de Buenos Aires?
+Se reitera lo ya expresado en este espacio, varias veces: si es Massa, es Massa y el peronismo debe decidir de una vez por todas si juega ahí, activando aminorar la inflación para tener alguna oportunidad electoral.
+¿Es un sapo para el discurso progre? Más vale que sí.
+Pero de ahí deviene el problema estructural que afrontan el Gobierno y el FdT o, más precisamente, el espíritu de poder que quede en una coalición aguantada a duras penas.
+¿Qué hace (lo cual involucra en primer lugar a la decisión de Cristina, como líder indiscutible del espacio)?
+¿Juega todas las fichas a que al bombero le salgan bien las cosas del poder, como para mantenerse y seguir resistiendo a aquello de lo peor? ¿Juega a retener el Ejecutivo para evitar el desastre? ¿O se percude al bombero para retener el capital simbólico del kirchnerismo, con la certeza de perder otra vez en las urnas?
+Tremendo dilema que, seguro, no se resolverá si cada quien sigue por su ruta.</t>
   </si>
   <si>
     <t>Eduardo Aliverti</t>
@@ -1954,6 +4943,42 @@
     <t>https://www.pagina12.com.ar/491919-boaventura-de-sousa-santos-hay-que-recordar-los-grandes-camb</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Boaventura de Sousa Santos: “Hay que recordar los grandes cambios que promovió Lula”
+Chapeau: El sociólogo y ensayista portugués analiza el ballottage brasileño
+Subtítulo: Ampliación de derechos o deterioro de las condiciones de vida democrática. Lula da Silva y Jair Bolsonaro, escenarios posibles para Brasil y la región. Los medios, las iglesias evangélicas y la memoria.
+Editoria: Diálogos
+Tags: Brasil, Luiz Inácio Lula da Silva, Jair Bolsonaro, printed-edition, luiz-inacio-lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/491919-boaventura-de-sousa-santos-hay-que-recordar-los-grandes-camb/
+Notícia completa (27 blocos):
+El pasado 2 de octubre, Luiz Inácio Lula da Silva alcanzó el 48,4 por ciento de los votos en la primera vuelta electoral, superando a Jair Bolsonaro, que obtuvo el 43,2 por ciento. La diferencia de 5,2 puntos porcentuales entre ambos, sin embargo, fue menor a la proyectada por los sondeos de opinión, que previo a la elección otorgaba al candidato del Partido de los Trabajadores (PT) una ventaja cercana a los 14 puntos sobre el líder ultraderechista del Partido Liberal (PL). A poco menos de una semana del ballottage, Boaventura de Sousa Santos, sociólogo y ensayista portugués, analiza el impacto de la primera vuelta y reflexiona sobre los escenarios posibles que puede dejar el resultado del 30 de octubre para Brasil y la región. Además, las políticas antitéticas de cada proyecto, la injerencia de las redes sociales, el valor de la calle y la necesidad de apelar a la memoria.
+De Sousa Santos es doctor en Sociología del derecho por la Universidad de Yale, profesor catedrático de Sociología en la Universidad de Coímbra, Portugal, y profesor distinguido del Institute for Legal Studies de la Universidad de Wisconsin-Madison. Tiene una vasta trayectoria en sociología del derecho, los nuevos constitucionalismos, los movimientos sociales, la globalización, la democracia, la interculturalidad y los derechos humanos. Entre sus títulos figuran "Una epistemología del sur", "Democracia al borde del caos: Ensayo contra la autoflagelación" y "El fin del imperio cognitivo". Creó herramientas conceptuales como la “epistemología del sur” y la “ecología de los saberes”, en defensa de la diversidad epistémica del mundo y de la horizontalidad entre saberes y prácticas. Fue miembro fundador de la Asociación Cívica Pro Urbe, Coímbra, en 1996, y es uno de los creadores del Foro Social Mundial (FSM).
+Voz autorizada dentro de la sociología jurídica y un referente indiscutido en el pensamiento político y social contemporáneo, Boaventura de Sousa Santos alerta sobre "la supervivencia de la propia democracia, amenaza que se deriva de las declaraciones y movilizaciones públicas del presidente Jair Bolsonaro y sus seguidores" en un contexto "altamente contaminado por fake news, discursos de odio y prosélitos religiosos (...) que ha llevado a la creación de un ambiente de intimidación que, de alguna manera, paraliza la manifestación pública de la diversidad de opciones políticas y obliga a los titulares de altos cargos del Estado a tomar medidas de seguridad inusuales”.
+--La diferencia porcentual entre Luiz Inácio Lula da Silva y Jair Bolsonaro en la primera vuelta electoral fue bastante menor a la proyectada por los sondeos de opinión. ¿Le sorprendió el resultado?
+--No, no me sorprendió el resultado; no confío mucho en los sondeos. Creo que vamos a pasar por un periodo en el que los sondeos no logran detectar las transformaciones tectónicas y subterráneas que ocurren en las mentalidades y en la subjetividad de las personas. Ya hemos visto cómo fracasan las encuestas, no solamente en Brasil sino también en Europa. Y cuando aciertan, no sabemos si es por el rigor o la suerte. Las dinámicas de las redes sociales han introducido en las subjetividades un tipo caótico de funcionamiento que es muy imprevisible para la gente y quizás solamente previsible para psicólogos sociales. Hay una crisis estructural de los sondeos. En general, para mí, no son creíbles, no lo son ahora en Brasil y no lo fueron en Chile cuando el proceso constitucional se perdió por un margen tan fuerte. Esto solo se va a resolver más adelante.
+--¿Por qué más adelante? ¿De qué depende que las encuestas se vuelvan más veraces?
+--Que las empresas de sondeos se inserten en la tecnología, con herramientas de la inteligencia artificial, o sea, cuando logren detectar a través de la big data las preferencias de la ciudadanía en los más diversos temas aparentemente no políticos (sexualidad, fútbol, cine, comida, etc.) y crear modelos que puedan dar alguna previsión sobre cómo esas preferencias se traducen en votos. Por eso nunca pensé que Lula podía ganar en primera vuelta y con mayoría absoluta. El hecho de que un presidente, Bolsonaro en este caso, no gane en el primer turno ya es una cosa rara también. Normalmente los presidentes ganan con la máquina del Estado. Hay un cambio en la opinión pública. Lamentablemente no fue un cambio tan grande como para darle a Lula la victoria.
+--¿Cómo ha impactado el resultado en los candidatos?
+--Muchos en el campo de Lula, progresistas y democráticos, pensaron que iba a ganar en la primera vuelta. Una victoria se transformó en una derrota y eso hizo que fuera una victoria amarga. Eso tuvo consecuencias en las calles. Hubo días en los que la gente estaba de luto, con cierta resaca de derrota, cuando en realidad no hubo derrota alguna. Al mismo tiempo esto animó y anima mucho el campo bolsonarista de extrema derecha porque al no perder en la primera vuelta hay campo para hacer y decir todo lo que quiera. Cuando digo todo me refiero a lo legal y lo ilegal; lo estamos viendo. No está fácil para Lula. El bolsonarismo está muy capilarizado en la sociedad a través del fundamentalismo religioso, el fundamentalmente evangélico neopentecostal, pero también con la iglesia católica conservadora en la misma línea, a pesar de que los católicos votan mayoritariamente por Lula. Por otro lado, el gobierno tiene mucho dinero y cuenta con lo que se llama --algo que no se entiende en democracia-- presupuesto secreto. Es la posibilidad del presidente de sacar de las cuentas públicas dinero de emergencia para distribuir durante este período; no es otra cosa que una compra de votos. Con ese dinero buscan comprar el voto de la gente empobrecida además de repartir ventajas y conveniencias a las oligarquías tradicionales.
+--Bolsonaro se presentó más de una vez como un candidato antisistema y así se lo suele calificar también. Sin embargo, sus postulaciones y acciones no siempre se condicen con un outsider.
+--Bolsonaro no es propiamente un antisistema, salvo cuando le conviene. En estos momentos hay una preocupación adicional que es la internacional. Para la extrema derecha global no puede perder Bolsonaro. El objetivo fundamental de la extrema derecha global idealmente es dirigida y alimentada por Estados Unidos, que quiere elegir a Donald Trump. Y por eso la elección del 30 de octubre en Brasil, por así decirlo, es la elección primaria de Estados Unidos en 2024. Si Bolsonaro gana esto anima enormemente el campo de Trump. De ahí que Joe Biden haya dicho varias veces que Estados Unidos quiere una victoria democrática, justa, etcétera; a Biden le conviene que gane Lula. Es muy raro, pero en este momento es así. Como sabemos, Estados Unidos no se mueve nunca por razones de solidaridad internacional; se mueve por cuestiones internas. Lo mismo ahora, porque no quiere darle espacio de maniobra al trumpismo. En sus últimos discursos, Bolsonaro pidió a sus seguidores que vayan a los lugares donde se vote. Si los resultados no le convencen seguramente provoque disturbios. Tal como Trump, Bolsonaro usa el Estado. Es un uber de la política. Se considera un autónomo sin patrón; el Supremo Tribunal Federal de Brasil no es su patrón. Esto también puede ser muy preocupante.
+--¿Qué opinión le merece la fórmula presidencial Lula-Geraldo Alckmin?
+--Como estrategia, Lula tuvo que buscar hacer grandes alianzas que descaracterizan la propuesta, pero que será la única garantía que le permita poder ganar las elecciones. Por otro lado, creo que han creído demasiado en las instituciones y por eso no han convocado a la calle sobre todo en la primera vuelta. La gente estaba intimidada. Tenemos que ver que el submundo criminal también está con Bolsonaro. Todo esto crea un clima de intimidación que exige que, si hay algún problema con las votaciones, la población de Lula pueda espontáneamente salir a las calles masivamente, como pasó en Perú con Pedro Castillo cuando ganó las elecciones.
+--En aquella oportunidad, decenas de miles de personas llegaron a Lima para defender el resultado de los comicios.
+--Es posible que en Brasil también sea necesario salir para apoyar las elecciones justas y libres. La extrema derecha está muy capilarizada, tiene muchísima plata y sabemos que las organizaciones además son muy sofisticadas con las redes sociales, mucho más que las izquierdas. La gente tiene que seguir luchando y está luchando, pero el trabajo de calle, puerta a puerta, no es fácil en este momento para las fuerzas democráticas porque están intimidadas; las clases medias tampoco saben hacer esto y las clases populares están demasiado aisladas y muchas veces neutralizadas por las iglesias evangélicas. Creo que sería muy importante que el papa Francisco pudiera dar una nota pública en defensa de la democracia, las elecciones pacíficas y de las propuestas que favorezcan a los pobres.
+--¿Cómo imagina el futuro de Brasil, y de la región, en cada caso?
+--En cuanto a Lula, su vicepresidente (Geraldo Alckmin) es, según se dice, una persona del Opus Dei, un hombre de una parte conservadora de la Iglesia Católica. Las derechas en Brasil se sirven de la democracia, pero no sirven a la democracia. Y por eso puede ser que ahora genuinamente vayan a servir a la democracia y sería una cosa interesante, duradera no sé. Desde un punto de vista simbólico es muy importante, e histórico, que un presidente que fue injustamente perseguido, que pasó 582 días en prisión por una persecución política, con una complicidad activa y decisiva de Estados Unidos para destruir y desmantelar la economía brasileña, llegue a ser presidente nuevamente de Brasil. Esto es de una riqueza y de un significado simbólico enorme; no solamente para Brasil sino también para todo el continente obviamente, ahora que hay una nueva ola progresista con Gustavo Petro, Gabriel Boric, Xiomara Castro, con los cambios que están ocurriendo en Venezuela que pueden ser importantes.
+--¿Y en términos de políticas?
+--De resultar electo, Lula seguramente implemente políticas emergenciales de apoyo a las familias más vulnerables en los primeros cien días. Él sabe que hoy este estado de gracia de los cien días es muy corto, como hemos visto con Boric en Chile. Lula lo hace bien, tiene una gran experiencia y es un gran mediador. Eso sería muy bueno porque la gente lo que necesita urgentemente es que se refuerce el sistema de salud, necesita apoyo financiero, que se frenen la inflación y los precios del combustible, entre tantas otras cosas. También aparecen las cuestiones estructurales, como la reforma política que es fundamental. Con estas alianzas preelectorales, las políticas estructurales van ser muy difíciles o incluso imposibles. El Congreso no representa para nada la diversidad de Brasil, como en general los Congresos representan cada vez menos la diversidad de los países. Lula será fundamental también para frenar el agronegocio, para trabajar en la regulación de los medios y las redes sociales, algo absolutamente importante, dadas las consecuencias de 20 años bombardeando la opinión pública brasileña en un solo sentido. También para encarar una reforma fiscal; como en tantos otros países, en Brasil lo que hay es una injusticia fiscal escandalosa.
+--¿Qué habría que esperar si Bolsonaro fuera reelecto?
+--Lo que haría Bolsonaro es la gran incógnita. Estos últimos cuatro años fueron un gran deterioro en las condiciones sociales de la mayoría de la población. El manejo de la pandemia fue el peor posible, una destrucción ambiental sin límite y el desempeño de la económica de un país que estaba camino a ser la sexta o la séptima del mundo y que ahora debe ser la décimo segunda. Realmente para quien piensa que las victorias son irreversibles, la experiencia brasileña muestra que no lo son.
+--¿A qué se refiere con esto último?
+--Lo que ganamos tiene que ser muy protegido y resguardado para que no se pierda, porque se pierde muy rápidamente de una manera brutal. Si Bolsonaro es reelecto, sin duda va a continuar el deterioro de las condiciones de vida democrática. Lo que estamos viendo en la pospandemia en el mundo es una crisis económica, social, con perturbaciones y disturbios sociales, porque los Estados no están pudiendo resolver de una manera pacífica la crisis económica y social y recurren crecientemente a la represión. Y la represión en un momento puede ser incompatible con la democracia. Como no estamos en un período de dictaduras militares pienso que las fuerzas antidemocráticas y de extrema derecha del mundo llegaron a la conclusión de que hay maneras más sencillas y menos costosas de destruir la democracia y de mantenerla completamente neutralizada, descaracterizarla todavía más, y llevar a la disminución de partidos que pueden ser ideológicamente contrarios a sus intereses. Entonces es preocupante no solamente para Brasil sino para la toda región. Una derrota de Lula animaría aún más a la extrema derecha, animaría a los fundamentalismos religiosos, sobre todo evangélicos, en todo el continente.
+--A poco menos de una semana de la segunda vuelta en Brasil, ¿qué hay en juego?
+--Es importante que la población recuerde los buenos tiempos que vivió durante el gobierno de Lula; sobre todo las clases populares. Hay que tener memoria y recordar las luchas por los derechos de las mujeres, la lucha antirracista, entre otros cambios que promovió Lula y que también fueron importantísimos. El problema es que las redes sociales destruyen la memoria humana, social e individual; no hay un archivo colectivo digital. Por otro lado, muchas de las grandes conquistas que consiguió Lula son victorias en las que alguna clase media se quedó ambigua.
+--¿Por ejemplo?
+--Una de las políticas más importantes, debido a que estamos hablando de un país que además de capitalista es racista y sexista, fue el hecho de que Lula haya ampliado derechos laborales a las empleadas domésticas, que son mujeres negras, jóvenes y pobres, en general. Esto fue una revolución tremenda de bienestar, para ellas, pero sobre todo ha sido una revolución simbólica en el sentido de que de repente a cierta élite racista, que mismo cuando es progresista es silenciosamente racista muchas veces o tiene un inconsciente racista, no le gustó que la empleada ampliara a sus derechos y dejara de necesitar y ser agradecida por ser “bien tratada” por la filantropía de sus patrones. Esto hizo que la empleada ya no dependiera de su patrona para que su hijo tuviera una computadora; algo devastador sobre todo para las clases medias machistas. Lo mismo con las acciones afirmativas que facilitaron el acceso a la universidad de los hijos de familias pobres y negras o indígenas. Han sido transformaciones inmensas. Por eso hay que apelar a la memoria y estar prevenidos ante la realidad alternativa de las fake news. La extrema derecha tiene una capacidad creativa mucho más grande que la izquierda o que las fuerzas democráticas. Lula puede verdaderamente ganar, pero no debe cometer ningún error que haga que las fake news que van a llegar esta última semana modifiquen los votos de los indecisos.</t>
+  </si>
+  <si>
     <t>Bárbara Schijman</t>
   </si>
   <si>
@@ -1966,7 +4991,34 @@
     <t>https://www.pagina12.com.ar/490734-los-mejores-anos-de-la-economia-fueron-los-de-lula</t>
   </si>
   <si>
-    <t>2022-10-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: “Los mejores años de la economía fueron los de Lula”
+Chapeau: Entrevista con Ramón García Fernández, economista argentino radicado desde 1976 en Brasil
+Subtítulo: Graduado de la Universidad de San Pablo, trabajó como docente en la Fundación Getulio Vargas y es profesor de la UFABC.
+Editoria: El Mundo
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/490734-los-mejores-anos-de-la-economia-fueron-los-de-lula/
+Notícia completa (21 blocos):
+Desde San Pablo
+La mirada de Ramón García Fernández sobre la economía brasileña tiene valor agregado. Vive hace 46 años en esta ciudad a la que llegó como exiliado. Había dejado atrás su infancia porteña, la librería de su madre en el barrio de Belgrano, el Nacional Buenos Aires y una carrera de biología inconclusa en la UBA. No esperó a que lo encontrara la dictadura. Había militado en la izquierda y en 1976 salió para Brasil, decidió quedarse y formó una familia en su país adoptivo. También se recibió de economista en la USP (Universidad de San Pablo), trabajó como docente en la Fundación Getulio Vargas y en la actualidad es profesor titular de la UFABC, una casa de estudios que se creó durante el gobierno de Lula.
+-Si alguien llegara hoy al Brasil de Jair Bolsonaro sin conocerlo, ¿cómo le explicaría lo que pasa con su economía?
+-Yo creo que un criterio fundamental, con todas las críticas que se le puede hacer, es ver cómo está el desempeño del producto bruto. Es decir, cómo fue la economía brasileña en los últimos veinte años. Y con seguridad, los mejores años fueron los del gobierno de Lula. Sobre todo hubo un momento, al final de su segundo mandato, que ha sido espectacular. Ciertamente, con Dilma las cosas empezaron a empeorar. Al final de su gobierno tuvo una crisis muy grande, pero hay que acordarse de que estuvo super restringida por dos cosas. Por sus errores no forzados. Tenía miedo a la reacción del mercado después de su reelección y puso de ministro de Economía a un superliberal, vinculado con los bancos, que realizó una política exactamente opuesta a la que iba a hacer cuando ganara la elección. Después, con todo el congreso en contra, solo duró dieciséis meses. Entonces el desempeño del primer gobierno de ella y todo el tramo del segundo hasta el Impeachment fue malo. Entró Temer e impuso el programa económico de Aecio Neves. O sea, el vicepresidente asumió el programa del rival de Dilma. Y tuvo un desempeño mediocre. Liberó la economía, eliminó leyes laborales y siguió un plan económico peor. Hasta que llegó Bolsonaro…
+- ¿Y entonces?
+- Brasil creció el uno por ciento y fue mucho peor de lo que el mercado financiero vaticinaba. Hasta los opositores imaginaban que le iba a ir mejor y fue mucho peor. Y la embarró con medidas tomadas por él. Hasta que llegó la pandemia y la economía se paró en todo el mundo. Después se dio una modesta recuperación, que es de la que habla Bolsonaro y en realidad es bastante tímida.
+- ¿Cuánto de lo que hizo su superministro Paulo Guedes contribuyó a que haya 33,1 millones de personas que pasan hambre y que se ven sobre todo en San Pablo con miles de brasileños acampando en las calles?
+- Paulo Guedes pensó que iba a haber, solo con la presencia de Bolsonaro, un boom de inversiones. Y no pasó nada. La realidad es que en la industria no hubo. Cada vez le fue retirando más el apoyo al sector industrial. El agronegocio sigue funcionando bien, pero funcionó bien siempre, en cualquier momento. Depende mucho más de las oscilaciones del mercado externo…
+- El coeficiente Gini que mide la desigualdad en los países, ¿cómo está en Brasil?
+- Lo que se sabe es que el índice de Gini cayó bastante en la época de Lula y volvió a subir con Temer. Pero eso es relativo. Lo que Lula consiguió en Brasil fue una desconcentración del ingreso. Desde el inicio de su gobierno al final del que presidió Dilma, el Gini cayó en forma continuada, y con Temer subió. La pandemia complicó todos los análisis del gobierno Bolsonaro.
+- ¿Por qué los brasileños no corren tras el dólar como un refugio de valor y esa conducta es completamente distinta a la que se ve en la Argentina? ¿Es lo que explica que el país sea más estable en términos económicos?
+- En Brasil nunca se usó el dólar como referencia. ¿Por qué? Para mí una gran diferencia es que acá siempre hubo alternativas de ahorro razonables y de inversión para la clase media, para hacer cualquier ahorro. Por lo tanto, la gente nunca precisó dolarizarse. Inclusive, con intereses absurdos. Es decir, era mucho más negocio invertir en aplicaciones financieras de Brasil que comprar dólares. Siempre el ahorro nacional se volcó al real. Las personas no tienen noción del dólar.
+-¿Qué les dice a los brasileños sobre lo que sucede con la economía argentina?
+- Esa idea de que para comprar un bien se tiene que ir con una valija llena de dólares, acá yo lo cuento y la gente entre que se ríe y se espanta. En Brasil es completamente ilegal hacer transacciones en el país con una moneda extranjera. Es un delito. No se pueden comprar viviendas o un coche. Y otra cosa que es fundamental es la restricción externa, o sea la falta de dólares para pagar importaciones, para hacer remesas de lujo. Acá era bastante importante, aunque no tanto como en la Argentina, hasta que en el gobierno de Lula se aumentaron las reservas a 500 mil millones de dólares. Inclusive hay quienes creen que el volumen es exagerado y que podrían usarse esas reservas para otras cosas, pero la cuestión es que el Banco Central nunca llega ni de cerca a quedarse sin dólares. Hay estabilidad financiera porque no se puede especular contra el real. El Banco Central tiene Cacife como se dice acá, tiene reservas para enfrentar cualquier desafío y eso es algo que hizo el gobierno de Lula.
+- ¿Qué piensa de la reforma tributaria que plantea el PT, de que los ricos paguen más impuestos?
+- Estoy cien por ciento de acuerdo. Lo único que querría decir es que lamentablemente, todos los gobiernos del PT hicieron mucho menos en ese rubro. La mayor alícuota del impuesto a la renta o ingresos era 35 por ciento. En el gobierno del PT la bajaron a 27, 27 y medio. Sería lo que Ganancias en Argentina. Acá es el impuesto a los ingresos. Esa alícuota se paga a partir de un valor muy bajo. Hoy está en 5 mil reales, o menos. Entonces, ¿qué quiere decir? Que un tipo que gana 5.500 reales que son mil dólares más o menos, paga el mismo porcentaje de impuesto a los ingresos que uno que gana 100 mil dólares por mes.
+- ¿En Brasil existe un impuesto como el de bienes personales?
+- No, impuesto a la riqueza no hay. Están los impuestos más importantes que son sobre las transacciones, lo que sería el IVA allá. Acá es el ISMS, que varía de producto a producto y es una decisión de cada estado. Hay un impuesto a los productos industrializados que es federal, el IPI. Hay impuestos a la gasolina, a las transacciones financieras que es muy chiquito.
+- ¿Cuál es el principal inversor extranjero en Brasil y qué papel cumple China?
+- Estados Unidos sigue siendo el mayor inversor. China tiene algunas cosas pero no con una presencia significativa. Si usted piensa que los chinos tenían cero, cualquier centavo que inviertan es un aumento considerable. China es mucho más importante como cliente. Lo que se juega en esto es si los chinos se pudren de Bolsonaro y compran soja en otro lugar. La soja brasileña se la tendrían que vender a los criaderos de pollos de acá. Por eso en el agronegocio hay algún sector preocupado con las conductas del presidente. Pero hay otro que quiere que Bolsonaro siga y lo deje desmatar (deforestar), como se dice aquí, que no haya ninguna restricción para hacerlo. Pero el gran productor sabe que su negocio depende de China, y que Bolsonaro puede hacer alguna macana que indisponga a esa potencia definitivamente con Brasil, le corte los víveres y él no pueda exportarles más.
+gveiga@pagina12.com.ar</t>
   </si>
   <si>
     <t>Jair Bolsonaro recortó fondos para investigación en salud y ciencia</t>
@@ -1978,7 +5030,31 @@
     <t>https://www.pagina12.com.ar/488950-jair-bolsonaro-recorto-fondos-para-investigacion-en-salud-y-</t>
   </si>
   <si>
-    <t>2022-10-12T00:10:28Z</t>
+    <t xml:space="preserve">Título: Jair Bolsonaro recortó fondos para investigación en salud y ciencia
+Chapeau: Brasil
+Subtítulo: La decisión afecta a decenas de proyectos esenciales para el avance científico y tecnológico del país, indicaron científicos y especialistas.
+Editoria: GO Noticias
+Tags: Brasil, Jair Bolsonaro, jair-bolsonaro
+URL: https://www.pagina12.com.ar/488950-jair-bolsonaro-recorto-fondos-para-investigacion-en-salud-y-/
+Notícia completa (18 blocos):
+El presidente de Brasil, Jair Bolsonaro, anunció en las últimas semanas recortes en el presupuesto nacional. Tras reducir el aporte financiero a las universidades públicas, esta semana se oficializaron "modificaciones" en el presupuesto de Ciencia y Tecnología, al que le sacaron 616 millones de reales (100 millones de dólares aproximadamente) que estaban destinados a actividades de investigación y divulgación.
+[H3] Ballotage en Brasil: Lula le saca a Bolsonaro una ventaja de diez puntos
+La decisión afecta a decenas de proyectos esenciales para el avance científico y tecnológico del país en diversas áreas. Entre ellas, se recortaron 30 millones de reales para el “Fomento de Proyectos Institucionales de Investigación en el Sector Salud”, y el área de "Fomento de la Investigación y Desarrollo en Áreas Básicas y Estratégicas", sufrió una disminución de alrededor de 177 millones de reales.
+Incluso las áreas que el gobierno de Bolsonaro consideraba prioritarias sentirán el golpe. El "Fomento de Proyectos Institucionales de Investigación en el Sector de Agronegocios" fue recortado en más de R$ 27 millones, mientras que el "Fomento de Proyectos Institucionales de Investigación en el Sector de Petróleo y Gas Natural" fue víctima de un recorte de R$ 88 millones.
+El profesor Fernando Cássio, de la Universidad Federal de ABC, explicó que las nuevas medidas afectan directamente el funcionamiento de las actividades de investigación en las universidades públicas, que son responsables del 95% de la producción de ciencia y tecnología del país.
+“Tomaron de un lado para dárselo al otro. Recortaron de las universidades para pagar deudas, y ahora sacan del presupuesto del Ministerio de Ciencia y Tecnología. Se están llevando todo el dinero destinado a la investigación e infraestructura”, indicó el investigador.
+“Con una mano toma y con la otra da, y con el agravante de que, en este caso específicamente del Ministerio de Ciencia y Tecnología, el presupuesto no vuelve, el presupuesto ya lo perdimos”, lamentó.
+“Esa es más o menos la lógica del tope de gasto, poner las áreas a pelear por el recurso. Es muy grave, las universidades siguen siendo directamente afectadas”, agregó.
+[H2] Bloqueo al presupuesto educativo por aumento del gasto público
+El presidente de Brasil bloqueó la semana pasada el dinero del presupuesto destinado a las universidades para hacerle frente al déficit en las cuentas públicas.
+"El bloqueo de las cuentas del presupuesto educativo coloca en riesgo el sistema de todas las universidades federales e institutos federales", informó la Asociación Nacional de Dirigentes de Instituciones Federales de Educación Superior, Andifes.
+El bloqueo total del presupuesto 2022 del Ministerio de Educación llega a 3.000 millones de reales, el 28,6% del recorte total. El decreto 11.216 fue firmado el viernes 30 de septiembre por el presidente Bolsonaro y el ministro de Economía, Paulo Guedes, dos días antes de la primera vuelta de la elección presidencial.
+Los detalles del decreto llamado de reprogramación presupuestaria se conocieron mediante el análisis hecho por la Institución Fiscal Independiente del Congreso, que indicó que el recorte presupuestario del Poder Ejecutivo fue de 10.500 millones de reales, unos 2.000 millones de dólares en total.
+Los demás ministerios que recibieron recortes después de Educación fueron Ciencia y Tecnología, Salud, Desarrollo Regional y Defensa.
+"El gobierno sigue con problemas de gestión presupuestaria por haber gastado por encima del techo del gasto público e incluso después de haber incluido en la cuenta los juicios contra el Estado que logró postergar", dijo Vilma Pinto, directora del Instituto Fiscal Independiente.
+La Unión Nacional de Estudiantes denunció que "el gobierno federal confisca el saldo de todas las cuentas de la educación superior y no envía dinero ni para el mantenimiento de los edificios".
+[H3] Seguí leyendo:
+[H3] Brasil: Jair Bolsonaro apareció en una procesión religiosa y la Iglesia Católica repudió su presencia</t>
   </si>
   <si>
     <t>Elecciones en Brasil: Simone Tebet dice que "ya está tomada" la decisión sobre su respaldo a Lula o Bolsonaro en el ballottage</t>
@@ -1990,7 +5066,33 @@
     <t>https://www.pagina12.com.ar/486848-elecciones-en-brasil-simone-tebet-dice-que-ya-esta-tomada-la</t>
   </si>
   <si>
-    <t>2022-10-04T03:01:00Z</t>
+    <t xml:space="preserve">Título: Elecciones en Brasil: Simone Tebet dice que "ya está tomada" la decisión sobre su respaldo a Lula o Bolsonaro en el ballottage
+Chapeau: Ocupó el 3er puesto con el 4,16% de los votos
+Subtítulo: La senadora irrumpió en la escena brasileña adelantando al laborista Ciro Gomes.
+Editoria: El Mundo
+Tags: elecciones en Brasil, Lula Da Silva, Jair Bolsonaro, printed-edition, elecciones-en-brasil, lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/486848-elecciones-en-brasil-simone-tebet-dice-que-ya-esta-tomada-la/
+Notícia completa (20 blocos):
+Con la miradas ya puestas en el balotaje del 30 de octubre en Brasil, la senadora y candidata presidencial del Movimiento Democrático Brasileño (MDB), Simone Tebet, adelantó que la decisión sobre a qué candidato respaldar "ya está tomada". "Tengo una posición y hablaré en el momento adecuado", sostuvo luego de los comicios del domingo la senadora del partido del expresidente Michel Temer, vicepresidente de Dilma Rousseff hasta el impeachment que lo dejó en el sillón presidencial.
+[H3] Elecciones en Brasil: qué dijo Lula da Silva en su primer tuit de cara al ballottageVictoria de Bolsonaro y la ultraderecha | Eric Nepomuceno
+Como senadora desde 2015, Tebet votó a favor de la destitución de Rousseff y se mostró en contra en varias ocasiones de las demandas territoriales de los pueblos indígenas, así como se destacó por criticar el negacionismo de la pandemia de Bolsonaro.
+Tebet, quien también reúne el respaldo del mundo financiero y del mediático, como la gran cadena O Globo, quedó en tercer lugar con el 4,16 por ciento, unos 4,9 millones de votos que definirán la segunda vuelta entre Lula Da Silva y Jair Bolsonaro. Desplazó así al cuarto puesto al laborista Ciro Gomes (3,05 por ciento), una figura importante en la política brasileña de las últimas décadas.
+"Espero que entiendan que este no es un momento cualquiera en Brasil. Es importante que la gente duerma y mire los resultados en cada estado, es tiempo de decisión y acción", advirtió Tebet. "Lamentablemente vimos que la polarización ideológica contaminaba el alma del pueblo brasileño", señaló la senadora tras una elección en la que surgió como figura política de un Brasil peligrosamente dividido, con la ultraderecha fortalecida por la elección de Bolsonaro.
+Tebet y su candidatura
+La candidatura de Tebet, hija del reconocido senador Ramez Tebet, fue acompañada por una coalición integrada por el Partido de la Social Democracia Brasileña, del expresidente Fernando Henrique Cardoso, y cuyo cofundador fue Gerardo Alckmin, el candidato a vicepresidente de Lula.
+Nacida en Tres Lagoas, en el estado de Mato Grosso do Sul, la senadora tomó impulso especialmente en los debates presidenciales. Frente a las cámaras de televisión, Tebet se ratificó como una alternativa entre Bolsonaro y Lula, quienes se medirán en una reñida segunda vuelta el próximo 30 de octubre. Sin nada que perder, se mostró más agresiva con ambos candidatos e incluso hizo gala de su condición de mujer feminista para responder a los ataques misóginos de Bolsonaro, pese a manifestarse en contra del derecho al aborto.
+"Ser feminista es ganar lo mismo que los hombres. Mi feminismo es muy diferente a tu concepto de feminismo. Lamento tu visión selectiva. Yo defiendo la vida. El feminismo en Brasil no puede entenderse como una agenda de izquierda, sino como una agenda cristiana", aseguró Tebet al responder a una crítica del sacerdote Kelmon Luis da Silva, también candidato presidencial, en el último debate presidencial a horas de la primera vuelta.
+Hija del reputado y ya fallecido senador Ramez Tebet, Tebet empezó a trazar su carrera por la presidencia durante la comisión de investigación abierta contra Bolsonaro en el Parlamento por su gestión de la pandemia, la cual ha dejado cerca de 700 mil muertos en el país. Durante la campaña, la senadora hizo hincapié en el hecho de ser mujer y una parlamentaria con experiencia y centró sus propuestas en la educación y el combate al hambre, el cual aumentó estrepitosamente en los últimos años en Brasil durante el gobierno de Bolsonaro.
+Pese a ser propietaria de grandes haciendas, Tebet ha defendido en la campaña un agronegocio "sostenible", compatible con el medioambiente, y se ha mostrado partidaria de la "deforestación cero". Tebet, quien también reúne respaldo del mundo financiero y del mediático, como la gran cadena O Globo,
+El MDB, fundado en 1980, cuando el país todavía estaba bajo la dictadura militar (1964-1985), es uno de los partidos históricos de la centroderecha y siempre ha sido una suerte de fiel de la balanza política brasileña. Sin embargo, desde 1989, cuando se celebró la primera elección directa tras la dictadura, sólo ha gobernado dos veces y en ambos casos como consecuencia de gravísimas crisis.
+En 1992 lo hizo con Itamar Franco, quien en su condición de vicepresidente sustituyó el mandatario Fernando Collor de Mello tras su renuncia en medio de escándalos de corrupción. La historia se repitió en 2016, cuando Michel Temer, hoy todavía uno de los mayores referentes del partido y también vicepresidente, asumió el cargo después de la destitución de la socialista Dilma Rousseff, tras un juicio político promovido por el propio MDB.
+Temer fue una de las principales figuras en la convención que proclamó la candidatura de Tebet y, como líder del partido, la animó a “defender una pacificación nacional” y a ponerle “fin a todos los antagonismos", que “es lo que desea la sociedad brasileña”.
+[H2] La caída de Ciro Gomes
+El auge de Tebet supuso también el declive de Ciro Gomes, principal rival de Lula en el campo progresista y con quien ha disputado una parte del electorado. El candidato del Partido Democrático Laborista (PDT), una histórica referencia de la centroizquierda, aspiraba por cuarta vez a la presidencia de Brasil, pero vio frustrado su nuevo intento. Gomes, quien fue ministro de Lula y no esconde su rencor con el líder del PT, perdió estas elecciones gran parte de su capital político, tras obtener tan solo 3,5 millones de votos, frente a los 13,3 millones que obtuvo en 2018, cuando terminó en el tercer puesto.
+Durante la carrera electoral, el laborista aseguró ser víctima de una campaña "inmoral" en su contra para favorecer al antiguo sindicalista, con quien rompió todos su lazos las vísperas de la campaña de 2018, cuando Lula cayó en prisión por presunta corrupción. Gomes intentó sustituir a Lula como candidato del PT, no tuvo respaldo y se lanzó por su cuenta, en una campaña en la que, como ahora, fue tan duro con la izquierda como con la ultraderecha que terminó llevando al poder a Bolsonaro. Después de votar este domingo, Gomes llegó a sugerir el fin de su carrera política con una frase lapidaria: "Tal vez ha llegado la hora de cuidar de mi vida".
+Por afinidad ideológica se creería que los votantes de Gomes tendrían preferencia por un candidato como Lula en la segunda vuelta. Mientras que parte de la base electoral de Tebet preferiría a Bolsonaro. Sin embargo, y teniendo en cuenta lo que ha pasado en otras elecciones en la región, es imposible predecir con exactitud el comportamiento de los electores.
+[H3] Seguí leyendo
+[H3] Habrá segunda vuelta reñida en Brasil | por Emir SaderLula deberá “desfascistizar" a la sociedad brasileñaLula y Bolsonaro barajan y dan de nuevo</t>
   </si>
   <si>
     <t>Brasil: un debate de novela antes de la elección del domingo</t>
@@ -2002,7 +5104,33 @@
     <t>https://www.pagina12.com.ar/486091-un-debate-de-novela-a-horas-del-voto-en-brasil</t>
   </si>
   <si>
-    <t>2022-09-30T03:01:00Z</t>
+    <t xml:space="preserve">Título: Brasil: un debate de novela antes de la elección del domingo
+Chapeau: Lula, Bolsonaro y los otros cinco candidatos se enfrentaron fuera del horario central
+Subtítulo: “Tuve el placer de gobernar el país y hacer la mayor política de inclusión socialde la historia”, dijo el expresidente cuando le preguntaron por los gobiernos del PT.
+Editoria: El Mundo
+Tags: elecciones en Brasil, Lula Da Silva, Jair Bolsonaro, printed-edition, elecciones-en-brasil, lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/486091-un-debate-de-novela-a-horas-del-voto-en-brasil/
+Notícia completa (20 blocos):
+Desde San Pablo
+El debate de este jueves a la noche entre los siete candidatos a la presidencia, con la corrupción y la economía en el centro de la discusión, arrancó tenso y mano a mano entre Ciro Gomes y Lula. El primero le preguntó sobre los catorce años de gobierno del PT y una consecuencia que le atribuyó, la profundización de la desigualdad. El expresidente le respondió decidido y sin rodeos: “Tuve el placer de gobernar el país y hacer la mayor política de inclusión social de la historia”.
+[H3] Brasil: una elección clave para los derechos de las mayoríasEl Lula que viene | Por Emir Sader
+Bolsonaro recibió un par de centros cuando le tocó contestar las demandas del Padre Kelmon, un sacerdote cristiano ortodoxo, cercano al oficialismo y que le permitió al militar arrancar distendido, casi sin despeinarse: “Lo que está en juego es el futuro de la nación. No podemos volver a una cleptocracia”, dijo el ultraderechista que subió el voltaje de sus intervenciones cuando se topó con Lula. De esa primera confrontación entre los dos adversarios con mayor intención de voto en las encuestas, “Lula venció por puntos en el primer bloque”, según publicó en su portada el diario paulista Folha.
+Los participantes del encuentro fueron Bolsonaro (PL), Lula da Silva (PT), Gomes (PDT), Luiz Felipe D'Ávila (NOVO), Simone Tebet (MDB), Soraya Thronicke (União Brasil) y el Padre Kelmon (PTB). Dispusieron de 30 segundos para hacer las preguntas y un minuto para contestar. Se cruzaron todos en los cuatro bloques del debate que se acaloró sobre todo en la primera parte.
+[H2] Ritual inamovible
+El debate de anoche que le permitió a Globo duplicar sus niveles de audiencia en la primera hora, empezó a las 22.30 porque en Brasil es un ritual inamovible la novela que se emite por Globo de lunes a sábado. "Pantanal" —según los niveles de audiencia de mayo—, fue seguida por 77 millones de personas. Se estrenó en 1990 en la desaparecida TV Manchete y es considerada un hito del género de ficción televisiva.
+La remake que se emite ahora de Benedito Ruy Barbosa transita temas como la preservación del medioambiente, las disputas por la tierra en este gigante regional y la remanida cuestión del poder. Reivindicada incluso en ambientes académicos, las conclusiones de un Congreso Brasileño de Ciencias de la Comunicación de 2008 arrojaron que parecía “querer practicar una intervención ecológica”, según Beatriz Becker y Arlindo Machado, dos investigadores que le atribuyeron la anticipación de “un debate sobre el tema en el país, estimulando acciones políticas y movimientos sociales”.
+No en vano son vitales los aspectos que toca la tira diaria más vista del país. El pantanal real, no el de ficción, el que se ubica en los estados de Mato Grosso do Sul y Matto Grosso, uno de los mayores biomas del mundo, desde 1988 ha perdido el 30 por ciento de su superficie de agua. Un tema que —como el de la Amazonia— no ha sido prioritario para las políticas del actual presidente. Más bien, todo lo contrario. Estimuló la desforestación de los agronegocios.
+Quiénes costean el camino hacia ese Dorado transgénico y a sus instrumentadores en el terreno son las grandes corporaciones estadounidenses Cargill y Bunge, más la brasileña Amaggi. Una industria multimillonaria que destruye el medioambiente. Justamente, uno de los principales escenarios que sugiere la novela Pantanal.
+Uno de los personajes principales del programa con más rating de Globo, el ganadero José Leôncio, explica que los nidos de pájaros han desaparecido. Las aves del pantanal se extinguen como su entorno amigable. Una realidad llevada a la ficción que hasta podría acercarle muchos votos a la candidatura de Lula entre el ciudadano urbano promedio. Aquel que tiene conciencia del problema medioambiental, la misma que al militar ultraderechista le importa un rábano.
+[H2] Otro día agitado
+La pedagogía del miedo, un concepto que ayer mencionó en su columna de este diario el profesor argentino Pablo Gentili, de la Universidad del estado de Rio de Janeiro, campea sin ataduras dentro de la maquinaria electoral oficialista. El miércoles se conoció que desde el teléfono de una oficina del gobierno del estado de Paraná, fueron enviados 324 mil mensajes divulgando la convocatoria a un golpe con amenazas al Supremo Tribunal Federal (TSF) y al Congreso Nacional.
+El medio Carta Capital informó que la empresa encargada de controlar el tráfico de datos comprobó que “hubo acceso indebido y no autorizado a la plataforma y que, desde la confirmación del hecho, lo registró ante las autoridades competentes, incluyendo a las policiales para su investigación” de las fake news. Una marea contaminante en Brasil que no se detuvo un solo día, como la mancha de petróleo de un barco en altamar.
+Al menos ayer hubo una buena noticia para las sociedades civilizadas y que no dirimen sus diferencias a los tiros. El TSF les prohibió a quienes portan armas circular con ellas antes, durante y después de los comicios.
+La medida alcanza a los llamados CAC (Cazadores, tiradores y coleccionistas) hasta 24 horas después del cierre de la votación en los colegios electorales. Quienes infrinjan el fallo pueden ser detenidos en flagrante delito por tenencia ilícita. El ministro de la Corte, Alexandre de Moraes, a quien Bolsonaro trató de “sinvergüenza” en las últimas horas, comentó que la medida “busca garantizar el libre ejercicio de su derecho al voto, eliminando cualquier posibilidad de coacción en el transcurso de la elección”.
+Una encuesta de la consultora Quaest señaló que el 90 por ciento de los brasileños quiere que el nuevo presidente se decida en la primera vuelta. El argumento que dieron es que “no pueden soportar más” el tema omnipresente de la votación crucial que será un parteaguas en la historia del país. Un indicio claro del estrés que causa la situación de tensión a que es sometida esta nación de algo más de 212 millones de habitantes y que llevó a su pico máximo un presidente que machaca desde hace meses con la idea del posible fraude y un autogolpe para evitarlo. ¿Ficción como la novela "Pantanal" o realidad aumentada por las fake news de las que Bolsonaro hizo un culto?
+gveiga@pagina12.com.ar
+[H3] Seguí leyendo
+[H3] ¿Cuántos votos necesita "Lula" para ganar en primera vuelta?Elecciones en Brasil: la expectativa de los electores brasileños en Argentina por terminar con el fascismoElecciones en Brasil: la "guerra de canciones" de Lula da Silva y Jair Bolsonaro en campaña</t>
   </si>
   <si>
     <t>La pregunta es: vos ¿qué agua vas a tomar?</t>
@@ -2014,7 +5142,32 @@
     <t>https://www.pagina12.com.ar/485632-la-pregunta-es-vos-que-agua-vas-a-tomar</t>
   </si>
   <si>
-    <t>2022-09-29T03:00:13Z</t>
+    <t xml:space="preserve">Título: La pregunta es: vos ¿qué agua vas a tomar?
+Chapeau: Humedales: un territorio que arde no sólo por el fuego que lo arrasa
+Subtítulo: Río Feminista es una red de mujeres y diversidades que habitan el espacio de orilla a orilla. Desde su formación, denuncian el origen del actual ecocidio en el extractivismo que arrasa con vidas y territorios. Los efectos de la Hidrovía, su falta de control, y la ausencia de políticas ambientales con raigambre comunitaria son algunos de los temas que señalan ante el tratamiento de una ley -que viene trabada hace diez años- en el Congreso.
+Editoria: Las12
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/485632-la-pregunta-es-vos-que-agua-vas-a-tomar/
+Notícia completa (19 blocos):
+Río Feminista es una red de mujeres y diversidades que habitamos y amamos el humedal. Una red que va de orilla a orilla y de un extremo a otro de la cuenca del Plata-Paraná. Pensamos nuestro territorio del agua más allá de las fronteras políticas, tejemos alianzas y nos enlazamos en tramas de solidaridad para habitar, sentir, comprender y cuidar de formas diversas el humedal, constantemente asediado por el extractivismo. Somos cuerpa-territorio que sufre, sufrimos. Nos ahogamos, lloran y arden los ojos. Nos indigna, nos molesta y sigue el problema. Nuestro territorio arde y no arde sólo del fuego que genera este humo que nos agobia, arde de múltiples formas.
+La crisis socioambiental mundial se reproduce en nuestros territorios. Los extractivismos desmantelan formas de vida e invisibilizan saberes y prácticas culturales, productivas, económicas. Sobreexplotan la frontera agrícola, industrial e inmobiliaria, afectan miles de hectáreas con incendios intencionados. Los humedales, las sierras cordobesas, la Patagonia, Catamarca, Misiones y todos los espacios sufrientes y sangrantes de nuestra Tierra hoy, y desde hace más de 500 años, venimos gritando y reclamando juntxs.
+Nosotrxs observamos, sentipensamos, habitamos y producimos en las lógicas de vida diversa que tan bien sabe albergar el humedal, pero nos enfrentamos -y lxs isleñxs, las escuelas de islas, las ranchadas, lo saben mejor que nadie-, a toda una maquinaria de matar cuerpos y territorios. Seguimos viviendo y naturalizando este modelo de NO vida; es decir, de generación de ganancias para unos pocos, mientras nos vamos quedando sin agua y todo se sigue quemando. Nos siguen hiriendo y nos duele.
+En el humedal se replican las mismas condiciones de titularidad sobre la propiedad privada de la tierra que nos indican las estadísticas a nivel global: sólo un 2% pertenece a mujeres. Sabemos que sin territorio no hay soberanía alimentaria, no hay empoderamiento, no hay narrativas. Nuestros humedales fueron lenta y constantemente vaciados de sentido, vaciados de comunidad y de arraigo. Se han cerrado escuelas, se recortan actividades de recorrida de gobiernos locales que constituyen presencia, desabasteciendo a las delegaciones en isla de equipamiento e infraestructura. El aislamiento y la falta de asistencia estatal fueron embestidas por modos extractivistas de producción y explotación de mediana y gran escala, que arrasan con las lógicas de cuidado de lxs productores locales. Si no se habita el territorio y si no lo hacemos de forma comunitaria, se genera una tierra dispuesta a ser saqueada.
+[H3] Ordenamiento territorial y políticas ambientales (in)existentes
+En lo particular del humedal que habitamos, existen pocas políticas preventivas de organización y gestión del territorio Delta a nivel nacional, provincial y municipal. Hace años que no hay intencionalidad política de trabajar interjurisdiccionalmente de manera seria, comprometida y sostenida para prevenir los incendios en el Delta. Por ejemplo, el PIECAS-DP (Plan Integral Estratégico para la Conservación y el Aprovechamiento Sostenible del Delta del Paraná), es una herramienta nacional e interprovincial que serviría para tener un ordenamiento ambiental del territorio y garantizar su cuidado, preservación y manejo sustentable. Sin embargo, no se ha activado más que por presión de las organizaciones y de forma espasmódica. Necesitamos la firme continuidad de implementación del PIECAS y su derivación y complementación con planes y proyectos interjurisdiccionales.
+No hay intenciones de un ordenamiento territorial participativo ni de una discusión y transformación de fondo sobre las prácticas productivas. Se sostienen pocos diálogos multisectoriales duraderos y no se activa la participación territorial a excepción de escasos ejemplos de trabajo conjunto. Es inexistente el trabajo preventivo e integral, con enfoque comunitario, sobre todo en lo que refiere a manejo del fuego. Algunas acciones a nivel nacional, provincial y municipal son de coyuntura cuando todo arde. Consisten en apagar fuegos y judicializar isleñxs y, más recientemente y de manera peligrosa, militarizar el territorio.
+En relación a las políticas del Ministerio de Ambiente de Nación se comenzaron a implementar desde el 2020 los “Faros de Conservación” (que son dispositivos tecnológicos situados en varios puntos del territorio del Delta para alertar sobre distintos eventos ambientales). Creemos que estas políticas y tecnologías tienen que desarrollarse de manera articulada con la comunidad, anclarse en aquellos parajes que son referencia en cada comunidad, que ya funcionan como “faros” -las escuelas de islas, por ejemplo-, y que genere trabajo para lxs isleñxs, capacitación, equipamiento, etc. Es necesario construir otro tipo de prevención, mano a mano con quienes habitan y conocen el humedal.
+[H3] Ley de humedales, proyecto consensuado
+Desde hace diez años estamos pidiendo por una Ley de Presupuestos Mínimos que nos ayude a preservar y cuidar nuestros humedales. Queremos la ley consensuada. ¿Por qué esta ley y no otra? ¿Y por qué no sólo la ley sino mucho más que eso? Porque este proyecto ha sido trabajado durante años por investigadorxs y más de 300 organizaciones socioambientales y territoriales que conocen y habitan el humedal. Porque necesitamos una Ley de Humedales con perspectiva transfeminista. Esto es: una ley que de cuenta de la diversidad que somos y habitamos estos territorios líquidos. Una ley que establezca el ordenamiento territorial ambiental (OTA) con criterios certeros sobre qué actividades productivas se habilitan en cada área del humedal para desincentivar las quemas intencionales y para ofrecer instrumentos a la Justicia que permitan actuar sobre los responsables. Una ley que ponga en valor la participación comunitaria y colectiva.
+El tratamiento legislativo de la Ley ya fue interrumpido en tres oportunidades: en 2013, 2016 y 2021 porque toca muchos intereses económicos de proyectos extractivistas. Los humedales, por su propia complejidad, interpelan los paradigmas vigentes de conservación y de gestión ambiental porque no permiten acciones fragmentadas, es decir no pueden aplicarse reglamentaciones en una zona y en otra no, porque igual afectan a la diversidad de todo. Defendemos e impulsamos el proyecto consensuado entre organizaciones y no el que impulsa el COFEMA porque básicamente este último no toma la definición de humedales del Inventario Nacional, no indica plazos para el ordenamiento territorial, quita principios ambientales fundamentales incorporados en el proyecto consensuado entre ellos no incorpora el Acuerdo Escazú. Dicho acuerdo es importante para garantizar el acceso a la información pública, el pedido de justicia y participación de las comunidades en la toma de decisiones, consulta y control de lo que sucede en estos territorios.
+Sentimos triste y angustiosamente que estamos muy lejos de que los gobiernos quieran implementar una mirada de cuidado integral socioambiental de nuestros humedales, a través de la pronta implementación del PIECAS y de la pronta sanción de una Ley de Humedales respetuosa de la integridad ecológica, social y cultural. Somos las organizaciones y movimientos feministas y socioambientales, las grandes movilizaciones tipo puebladas que se están viviendo en las últimas semanas en varias ciudades litoraleñas ribereñas, arrojados a las calles bajo la consigna "el humo no nos deja respirar", quienes entendemos la urgencia de su resguardo. Entendemos, fundamentalmente, la necesidad de políticas públicas en pos de un cuidado integral que preserve las bases materiales que sostienen la vida, recordándonos esencialmente que somos seres eco e interdependientes. Dependemos de otras personas siempre a lo largo de nuestra historia de vida y dependemos de los ciclos naturales y los bienes comunes de la naturaleza, porque formamos parte de ella.
+Queremos mucho más que esta ley porque sabemos que hay mucho más que el fuego.
+Este es nuestro territorio, suelo cultural y paisaje humedal, símbolo del arraigo de nuestra historia presente, pasada y futura, y la de nuestra comunidad.
+En Río Feminista nos preguntamos: ¿Qué está sucediendo hoy en el humedal que habitamos lxs que participamos de esta red? ¿Qué nos preocupa? ¿Qué sabemos y que no sabemos de lo que pasa en las islas? ¿Qué nos dice la frase "plomo y humo el negocio de matar"? ¿Qué pasa con el dragado de la Hidrovía? ¿Qué pasa con todos los productos que salen por la Hidrovía? ¿Qué pasa con la ganadería, la pesca y el agro hoy en islas/delta? ¿Qué pasa con el negocio inmobiliario? ¿Qué pasa con el narcotráfico en la Hidrovía?
+Tenemos que discutir la propiedad privada, la tenencia, la producción, el turismo depredador y el “control” en islas. La falta de alternativas al manejo de fuego y otros modos de renovar el suelo en tiempos de bajante; el desconocimiento sobre la vida de las comunidades de islas y trabajo con éstas -desde el Estado y desde las organizaciones-. También tenemos que poner en palabras el vaciamiento de la infraestructura pública/estatal en el humedal e islas; la falta de soberanía sobre la Hidrovía y el Enlace Vial Rosario-Victoria como un combo explosivo que ha ido degradando el Alto Delta, tanto geográfica como económica, social y culturalmente. Como medida concreta para abordar el problema de los incendios, que se vuelve tan urgente, resulta necesario seguir las rutas de ingreso y egreso a la isla. Los lugares en la ribera donde es posible embarcar al río no son infinitos. Es preciso introducir en este debate la falta de control sobre la Hidrovía, que es uno de los principales ejes de discusión en nuestro territorio. No solo por las mercancías y los bienes que circulan en los buques, sino por el dragado y taponamiento de bocas que impide el acceso de agua a la isla. El dragado de la Hidrovía en tiempos de bajante histórica está secando el humedal, tapona las entradas de agua de riachos y arroyos justo frente a Rosario, donde las quemas no cesan. La falta de ingreso de agua impide que se nutran los cortafuegos naturales que son los riachos y arroyos del Alto Delta. Además de cuestionar y analizar el tema del fuego en islas, desde Rosario y las localidades ribereñas de Santa Fe debemos cuestionar todos los puertos que existen en la Hidrovía y como éstos también están vinculados con las quemas. La ganadería intensiva no es la única causa de incendios. A pesar de todo, y de lo que nos cuesta asumir que el problema es mucho más complejo; sabemos que la escala de producción ganadera no aumentó en los últimos 2 años, al menos en la zona de islas de Victoria donde las quemas no cesan desde 2020. En esta zona los puertos legales e ilegales evidencian un descontrol evidente. Muchos productos y personas circulan por allí y todxs miramos para otro lado. Es en este tipo de puntos bien intrincados que anudan nuestros territorios donde nos hacen más sentido las imágenes que vinculan el humo con el plomo.
+El Delta del Río Paraná está siendo explotando de múltiples formas. Se está depredando la vida de la tierra, de otros seres vivos, del agua, del aire. Todo continente termina siendo una isla en este mundo. Y, al parecer, el mundo arde dentro del sistema capitalista, racista, especista, patriarcal. Las hogueras se replican, ahora es en nuestros humedales. Nuestras cuerpas-territorio lo reconocen. Es en las quemas, el agronegocio y loteos, en la hidrovía, la forma aplicada. En las estrategias de cercamiento que el Estado ampara, donde Tierra, cuerpxs y relaciones sociales son contaminadxs, manipuladxs, deshumanizadxs.
+El polvo del fuego, las cenizas que nos hacen de telón, cual teatro Anatómico a la disección de la Pachamama. ¿Podemos ser espectadores de nuestro propio entierro? Nosotrxs, mujeres y disidencias decimos: ¡BASTA! con la potencia de una gran red colectiva militante. Con la herida de vivir en este mundo, vamos tejiendo formas de accionar y nos unimos para luchar por una vida que todas las personas merecen vivir. Reconocemos y ponemos en valor lo importante que es encontrarnos, militar juntxs y aunar fuerzas, resistir y continuar construyendo estrategias que colocan a la vida en el centro. Somos cuerpxs de agua habitando la transversalidad, siguiendo el rizomar. Nos reconocemos Humedal. Por eso preguntamos: Vos, ¿qué agua vas a tomar?
+*Documento común de la red Río Feminista. En el marco de las Acciones Plurinacionales por Ley de Humedales del 3 y 4,17 y 18 de septiembre de 2022.</t>
   </si>
   <si>
     <t>Río Feminista*</t>
@@ -2029,7 +5182,32 @@
     <t>https://www.pagina12.com.ar/484154-el-reclamo-en-la-calle-por-la-ley-de-humedales</t>
   </si>
   <si>
-    <t>2022-09-23T03:01:00Z</t>
+    <t xml:space="preserve">Título: El reclamo en la calle por la ley de humedales
+Chapeau: "No nos da lo mismo cualquier proyecto"
+Subtítulo: Disfrazado de abeja --calza negra, un body a rayas negras y doradas, peluca rubia con antenitas-- Sebastián Martínez Ledesma, 38 años, rosarino, salta sobre el capó de una combi.
+Editoria: Sociedad
+Tags: Ley de Humedales, printed-edition, ley-de-humedales, diario
+URL: https://www.pagina12.com.ar/484154-el-reclamo-en-la-calle-por-la-ley-de-humedales/
+Notícia completa (19 blocos):
+Disfrazado de abeja --calza negra, un body a rayas negras y doradas, peluca rubia con antenitas-- Sebastián Martínez Ledesma, 38 años, rosarino, salta sobre el capó de una combi. A su espalda está el edificio anexo del Congreso Nacional, donde los diputados empezaban a tratar los proyectos de Ley de Humedales. Un clásico del Palacio y la Calle: del lado de afuera, junto a Sebastián y armada con un megáfono, una chica dirige al grupo de manifestantes que, cortando la calle, corea. Fuerte para que oigan los que sesionan en el segundo piso.
+--¡Se va a acabar, se va acabar, ese negocio de quemar! --cantan.
+Y después: “Yo sabía / yo sabía/ que a los humedales los quemó la oligarquía”
+Ambientalistas, vecinos del Delta y movimientos sociales manifestaron frente al Congreso contra los lobbies que hace diez años frenan la sanción de una ley de Humedales. Con la movilización presionaron, además y sobre todo, para que los diputados den dictamen a uno de los diez proyectos que están girando en la cámara, un texto consensuado por más de 400 organizaciones socioambientales, universidades, productores y la comunidad científica. Este proyecto ya perdió estado parlamentario dos veces por la mano invisible del mercado y fue presentado nuevamente por el diputado Leonardo Grosso en febrero de este año. Es el Expediente 75D.
+La ciudad de Buenos Aires tiene manifestaciones todos los días. Esta se hizo con el Delta todavía humeando por los incendios que consumieron ya cerca de 100 mil hectáreas, volviendo irrespirable durante días el aire en ciudades como Rosario y Victoria. El fin de semana una multitudinaria marcha en el puente que une las dos localidades terminó de empujar dentro de la agenda parlamentaria el tratamiento de los proyectos.
+La urgencia quedó reflejada en la convocatoria a juntarse frente al Congreso: “No hay más tiempo”. Y tuvo efectos sobre la integración de la marcha, que juntó a activistas de los sectores medios --la Multisectorial Humedales, ONG, movimientos de jóvenes voluntarios por la ecología-- con trabajadores de la economía popular, porque la UTEP movilizó a todas sus organizaciones. Fueron muchos integrantes de cooperativas cartoneras, así como vecinos del barrios del conurbano que están armando la rama de trabajadores ambientales de los movimientos: “Nadie se salva solo”, decían algunos de sus carteles. También movilizó la izquierda partidaria, como el Partido Obrero y el MST: “¡Que arda el capitalismo, no los humedales!”, se leía en una de sus pancartas.
+Fernanda y Daniel estuvieron entre los primeros en llegar frente al Congreso, apenas pasadas las 9 de la mañana. Integrantes de la organización Salvemos los Humedales, viajaron desde Villa Constitución, provincia de Santa Fe. Alto y delgado, Daniel se calzó un disfraz de bagre. Los había confeccionado su compañera, que eligió uno de surubí.
+“El humo no nos deja respirar” dijo ella, “pero no es lo que más nos afecta. Eso es lo que muestran los medios, el aire irrespirable, pero no dicen que lo peor no es eso, lo peor es que no se cambie el modelo productivo, porque mientras no se cambie van a seguir quemando los humedales”.
+Daniel contó que tienen 50 años y nunca vieron una situación tan crítica. “Toda la vida crecimos junto al río, y sabemos que siempre se hizo ganadería en las islas del Delta. Pero a partir de los ‘90, con la expansión sojera, la ganadería en las islas dejó de ser una economía familiar para pasar a ser intensiva. La soja ocupó campos tradicionalmente ganaderos, y entonces hubo un efecto sobre las islas: empezaron las quemas para convertir los montes en pasturas. Quemas, terraplenes, corte de ríos, secado de lagunas: todo vale para los que buscan la ganancia a cualquier costo. Esto es lo que debe ser regulado. No se puede hacer cualquier actividad en un humedal”
+La concentración cortó la esquina de Rivadavia y Combate de los Pozos. En la puerta del anexo, la Multisectorial Humedales, referencia de la lucha rosarina, desplegó una pancarta sin impedir el ingreso al edificio pero dejando un estrecho paso, de modo que a los asesores que iban ingresando les quedó un pequeño pasillo para entrar. Sosteniendo una punta de la pancarta, estratégicamente ubicada, Estefanía Villalba le recordaba a cada ingresante: “Apoye al Expediente 75D!”
+Al Anexo logró entrar un grupo de la Multisectorial, pero la mayoría debió conformarse con esperar del lado de afuera.
+El rol de los movimientos sociales fue menos mediático. Estuvo centrado, sobre todo, en bancar la parada, pero los trabajadores de la economía popular también sumaron motivos locales a la defensa de la Ley de Humedales. “No solamente hay humedales en el Delta, los tenemos también en la provincia de Buenos Aires. En Almirante Brown está el Camino de las Flores, en Esteban Echeverría la laguna Dardo Rocha, en Lomas de Zamora Santa Catalina. Y todos están bajo la amenaza del negocio inmobiliario”, explicó junto a sus compañeros de Somos Barrios de Pie Diego Delfino, militante de Ecologismo Popular. Agregó que el cuidado de esos humedales genera fuentes de trabajo y que su protección es clave porque funcionan como pulmones de las zonas urbanas.
+Por la marcha pasaron varios referentes de las organizaciones, en principio los diputados de los movimientos sociales, como Leo Grosso (Movimiento Evita) y Juan Carlos Alderete (Corriente Clasista y Combativa). Otros estuvieron entremezclados en la manifestación.
+--Si no hacemos algo, nos cocinan como un huevo frito --sintetizó Dina Sánchez, del Frente Darío Santillán, mientras repasaba en su celular un resumen de los ejes del debate. Los humedales como recurso estratégico, como grandes reservas de agua dulce. El ecocidio que está sufriendo el país, que tuvo 1 millón 300 mil hectáreas afectadas por los incendios entre 2020 y 2021. El proyecto de ley de Humedales que consiguió media sanción en 2013 y 2016, pero fue frenado en ambas oportunidades. La importancia de hacer un inventario de humedales, dispuesto en el proyecto del Expediente 75D.
+Gildo Onorato contó que la militancia juvenil de los movimientos sociales está full con el reclamo ambiental, “Eso es muy bueno. Creo que Feminismos, Lucha Ambiental y Economía Popular expresan la agenda del siglo XXI, porque la política tradicional no logra representarla plenamente”.
+Una columna de pibes veintiañeros, uniformados con remeras verdes, repartió tarjetas plantables --con semillas--. Para muchos era su primer confluencia con los sectores populares de los movimientos barriales. “Con las organizaciones no tenemos nada que ver, nosotros sólo hacemos acciones para defender el medio ambiente, somos voluntariado”, aclaró Nicolás mientras repartían las tarjetas con el logo de su espacio, El nuevo enemigo.org
+Aunque la marcha tuvo un sesgo de edad marcadamente joven, también hubo gente de todas las edades. Vecinos muy humildes, integrantes de cooperativas cartoneras del MTE, se movilizaron al Congreso desde barrios como Don Orione, en Almirante Brown, viajando en el Roca hasta Constitución. Elba Velázquez, de 65 años, fue una de ellos. Cartonera , dijo que marchaba “porque proteger el ambiente y dar trabajo son un combo”. “Hay que defender lo que es lógico”, agregó.
+Ivo Peruggino, de Multisectorial Humedales, remarcó que no da lo mismo cualquier proyecto. “Apoyamos el consensuado, que es un proyecto de muchísimos años de trabajo colectivo entre la comunidad científica, académica, las organizaciones socioambientales y la gente que habita los territorios”.
+“Hace más de una década que el proyecto viene dilatándose y eso tiene que ver con determinados intereses y determinados sectores económicos de poder concentrado que están haciendo fuerza para que esta ley no salga. Particularmente, el lobby del agronegocio, al inmobiliario y al minero. Este proyecto es una deuda histórica de la política argentina para con el pueblo".</t>
   </si>
   <si>
     <t>Comunidad lule acusa a la Provincia por discriminación</t>
@@ -2041,7 +5219,7 @@
     <t>https://www.pagina12.com.ar/483321-comunidad-lule-acusa-a-la-provincia-por-discriminacion</t>
   </si>
   <si>
-    <t>2022-09-20T04:25:16Z</t>
+    <t>[ERRO] Navigation timeout of 30000 ms exceeded</t>
   </si>
   <si>
     <t>Claudia Alvarez Ferreyra</t>
@@ -2056,7 +5234,34 @@
     <t>https://www.pagina12.com.ar/483128-que-son-los-pueblos-en-aislamiento-voluntario-y-cual-es-la-s</t>
   </si>
   <si>
-    <t>2022-09-19T14:30:00Z</t>
+    <t xml:space="preserve">Título: Qué son los pueblos en aislamiento voluntario y cuál es la situación en la región
+Chapeau: Un fallo de la CorteIDH podría marcar un antes y después
+Subtítulo: En los últimos días, Perú reconoció legalmente a cinco pueblos indígenas
+Editoria: Newsletter
+Tags: Pueblos indígenas, pueblos originarios, CIDH, Newsletter Causas, pueblos-indigenas, pueblos-originarios, newsletter-causas
+URL: https://www.pagina12.com.ar/483128-que-son-los-pueblos-en-aislamiento-voluntario-y-cual-es-la-s/
+Notícia completa (21 blocos):
+En los últimos días, Perú reconoció legalmente a cinco pueblos indígenas que viven en aislamiento voluntario, lo que significa un primer paso para garantizar sus derechos fundamentales. También hubo novedades en una causa que tramita ante la Corte Interamericana de Derechos Humanos (CorteIDH), iniciada tras un reclamo de dos comunidades de Ecuador, también aisladas voluntariamente.
+Pero qué significa que existan pueblos originarios en aislamiento voluntario, o contacto inicial, otra categoría que también se utiliza para nombrar a cientos de comunidades… ¿Significa que el Estado no debe hacer nada para garantizar sus derechos básicos?
+Según un informe de la Comisión Interamericana de Derechos Humanos (CIDH), se calcula que en la región habitan 200 pueblos aislados voluntariamente, con un total de 10.000 integrantes. Número que, de todas maneras, no es preciso ya que no existen relevamientos oficiales. Desde la Coordinadora de las Organizaciones Indígenas de la Cuenca Amazónica (Coica) sostienen, en cambio, que en la Amazonía viven unos 511 pueblos indígenas aislados, con 500 lenguas distintas, y que 200 de estos pueblos transitan las fronteras de los nueve países amazónicos.
+Estos pueblos se encuentran en lugares remotos y de difícil acceso desparramados por Brasil, Bolivia, Colombia, Ecuador, Paraguay, Perú y Venezuela; muchos de ellos, ubicados en la selva amazónica.
+La preservación de los territorios que habitan y el acceso a los recursos naturales es fundamental para que puedan desarrollar una vida digna. ¿Qué deberían hacer los Estados, entonces, para garantizar sus derechos y por qué el fallo de la CorteIDH puede marcar un antes y después?
+[H2] Qué son los pueblos indígenas en aislamiento voluntario
+La CIDH define a las comunidades que viven en aislamiento voluntario como “los últimos pueblos que no fueron colonizados y que no tienen relaciones permanentes con las sociedades nacionales prevalecientes en la actualidad”. Desde el organismo aclaran que estos pueblos habitan sus territorios desde mucho antes de la existencia de los Estados modernos. El término “aislamiento voluntario” también es una figura parcial ya que responde a su propia autodeterminación como pueblo pero está condicionado por presiones externas.
+“Son pueblos que de alguna manera eligen no tener contacto sostenido con la población no indígena, pero al estar en condiciones de vulnerabilidad el Estado debe velar por sus derechos fundamentales de todas maneras”, aclara la CIDH.
+• Contacto inicial → También existe la categoría de pueblos indígenas en contacto inicial, que no tiene que ver con lo temporal sino más bien con el tipo de contacto. Son pueblos que por alguna razón, voluntaria o no, aclara el organismo, mantienen cierto nivel de contacto, aunque de manera intermitente o sin reconocer plenamente ni compartir los códigos de socialización del resto de la población.
+[H2] Extrema vulnerabilidad
+Ahora bien, así como la CIDH reconoce el aislamiento voluntario como parte de la autodeterminación de los pueblos, algo que debe ser respetado por los Estados, también hace un llamado a la protección integral de sus derechos básicos dado que se trata de comunidades extremadamente vulnerables. ¿Y esto por qué? Porque para desarrollar una vida plena estas comunidades necesitan disponer plenamente de su derecho a la tierra, territorios que ocupan ancestralmente.
+El “goce efectivo” del territorio, explica la CIDH, no tiene que ver sólo con defender la tierra como unidad productiva sino con “la protección de los derechos humanos de una colectividad que basa su desarrollo económico, social, espiritual y cultural en la relación con la tierra”.
+[H2] El caso de Perú
+Recientemente el gobierno de Perú reconoció legalmente a cinco pueblos indígenas que viven en aislamiento en el Amazonas. Se trata de los pueblos Aewa, Taushiro, Tagaeri, Taromenane y Záparo, que viven o transitan entre las cuencas de los ríos Napo y sus afluentes, en la selva norte de Perú, frontera con Ecuador.
+Este reconocimiento es sumamente importante porque es el primer paso para proteger su territorio. Perú lo hace a través de la creación de reservas protegidas, en este caso, ubicada en las provincias de Loreto y Maynas, en la región Loreto, selva norte de Perú. Según la Base de Datos de Pueblos Indígenas u Originarios, que depende del Ministerio de Cultura peruano, ya fueron reconocidas seis reservas territoriales indígenas. (Desde Coica sostienen que faltan muchas más para garantizar los derechos territoriales de todos los pueblos).
+[H2] Cuando la tierra es un negocio
+Ya sea en manos del agronegocio, industrias extractivistas, la explotación pública de recursos naturales como fuentes de energía o bajo el crimen organizado, que se expande con la minería, la pesca y la tala ilegal, los territorios que ocupan estos pueblos se ven amenazados.
+Por primera vez, dos pueblos que viven en aislamiento voluntario llegaron con su reclamo hasta la CorteIDH -en realidad lo hicieron organizaciones indígenas y ambientalistas en su defensa-.
+Así, las comunidades Tagaeri y Taromenane, que habitan el Parque Nacional Yasuní, en Ecuador, plantearon que la actividad petrolera que allí se desarrolla redujo su espacio ancestral y no tuvo en cuenta cómo esta actividad productiva impacta en los patrones estacionales de siembra y recolección.
+La Corte estableció que, bajo la premisa de no contacto y de autodeterminación de los pueblos indígenas, "no es posible intervenir sus territorios para aprovechamiento económico cuando ello pueda entrar en tensión con la salvaguarda de su subsistencia". Ahora, el Estado ecuatoriano deberá presentar una propuesta conciliatoria.
+En caso de llegar a una sentencia favorable para estos pueblos, la causa podría dejar sentado un precedente importante para otros conflictos similares que se desarrollan en Brasil, Colombia, Perú y Paraguay… En caso de fallar a favor, la CorteIDH dejaría claro cuál es la responsabilidad de los Estados para proteger a los pueblos aislados voluntariamente sin avanzar sobre su autodeterminación. La clave está en la defensa y la protección de sus tierras.</t>
   </si>
   <si>
     <t>Tarso Genro: “Bolsonaro combina la incapacidad de gestión con la maldad”</t>
@@ -2068,7 +5273,43 @@
     <t>https://www.pagina12.com.ar/482957-tarso-genro-bolsonaro-combina-la-incapacidad-de-gestion-con-</t>
   </si>
   <si>
-    <t>2022-09-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: Tarso Genro: “Bolsonaro combina la incapacidad de gestión con la maldad”
+Chapeau: Entrevista con el exministro de Lula en Brasil
+Subtítulo: El exgobernador de Rio Grande do Sul señala que el mandatario brasileño "representa una corriente mundial de perversidad política de la extrema derecha". Y se muestra optimista de que Lula gane en primera vuelta.
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, Luiz Inácio Lula da Silva, printed-edition, jair-bolsonaro, luiz-inacio-lula-da-silva, diario
+URL: https://www.pagina12.com.ar/482957-tarso-genro-bolsonaro-combina-la-incapacidad-de-gestion-con-/
+Notícia completa (30 blocos):
+En noviembre de 2018, con Jair Bolsonaro como presidente electo, Tarso Genro lo definió en una entrevista con este diario: “No es Mussolini, es peor”. Casi cuatro años después, ratifica su impresión sobre el militar ultraderechista. Exministro del PT en tres ocasiones, también exgobernador de Rio Grande do Sul y hoy hombre clave en el armado de un frente con sectores de la izquierda brasileña, compara al Duce otra vez con el segundo candidato en intención de voto, aunque lejos de Lula, para las elecciones del 2 de octubre.
+- ¿Después de cuatro años en el gobierno ratifica aquella impresión sobre el actual presidente?
+-La ratifico íntegramente. Mussolini ha hecho un daño global con su experiencia fascista en Italia y articuló la participación de su país en una guerra colonial e imperialista. Bolsonaro hace una integración de la perversidad con la locura que no es una característica de Mussolini, que era un Jefe de Estado de extrema derecha, con una concepción de funcionamiento del Estado y una visión antihumanista de hacer política. Bolsonaro combina la incapacidad de gestión pública con la maldad expresada en relación a los demás seres humanos. Entonces sí es un dirigente peor que Mussolini.
+-¿Si Bolsonaro tuviera un segundo mandato sería peor porque podría avanzar más sobre las conquistas que todavía quedan vigentes?
+- Yo creo que sí, porque hay que comprender que representa una corriente mundial de perversidad política de la extrema derecha que revive la visión fascista del Estado moderno. Por la fuerza que tiene Brasil en América Latina se tornará en el preferido de la extrema derecha mundial. Entonces será mucho peor para nuestro país y trágico para todo el continente dado la potencia económica y política que Brasil tiene por su liderazgo internacional e incluso, por los gobiernos del expresidente Lula.
+- ¿Continúa vinculado al Instituto Nuevos Paradigmas junto a Boaventura de Sousa Santos, el exjuez Baltasar Garzón y otros intelectuales?
+- Yo sigo vinculado a mi partido y particularmente al presidente Lula, en la campaña electoral y en las relaciones políticas más amplias que tendremos en Brasil de sustentación a la política frentista. Mi actividad hoy se desarrolla más con la articulación de la izquierda en general, con el PSOL, al PCdoB, o las facciones de izquierda de los demás partidos y hago que eso converja para dentro del PT, que no tiene una experiencia frentista muy bien teorizada en mi opinión. Es una debilidad política de la izquierda en Brasil. O sea, hago el juego político dentro de mi partido de afuera hacia adentro a través de este Instituto que involucra a militantes, dirigentes e intelectuales de varias formaciones políticas en Brasil y en el mundo.
+-Mencioné a Nuevos Paradigmas para saber si, ¿en estos últimos cuatro años habían hecho algún estudio sobre el gobierno de Bolsonaro?
+- En los últimos diez meses hicimos sí, un estudio muy profundo sobre la actuación del bolsonarismo en las redes que oportunamente se publicará. ¿Cómo hacen? ¿Cómo se organizan? ¿Cómo se financian? ¿Con quién se relacionan? para aportar este estudio político a los distintos partidos de izquierda involucrados en el frente que da sustentación al proyecto de gobierno del presidente Lula.
+- Usted me dijo en 2018 que con diez días más de campaña hubieran ganado aquella vez con la candidatura de Fernando Haddad ¿Hay todavía tiempo para que Lula se imponga en la primera vuelta electoral?
+- Creo que es posible una victoria. Hay una capacidad de resistencia del prestigio del presidente Lula que sufrió una masacre política mediática. ¿Cómo ha resistido? ¿Cómo las masas no preparadas políticamente, no formadas académicamente, que no viven la política en lo cotidiano, resistieron? Esto es lo que permite pensar que Lula hoy esté próximo a ganar la elección. Pero no se sabe que articulaciones clandestinas están haciendo para bloquear su crecimiento. No tenemos un diagnóstico completo de esa situación. El juego sucio del bolsonarismo es una cosa espectacular. Hace una propagación del mal de una manera tranquila, porque sabe a quién quiere dirigirse y qué cohesión quiere darle a sus milicias armadas que están en la clandestinidad, pero que estarán listas para moverse cuando fuera necesario.
+-Ciro Gomes fue aliado de Lula por mucho tiempo y hoy sigue siendo muy duro con él. En cambio, Marina Silva, que se mantuvo alejada del PT por años, se acaba de reconciliar con Lula. ¿Cuál es su opinión de ambos hechos?
+- Son dos personalidades absolutamente distintas. Marina es reflexiva y tiene una línea coherente respecto de las cuestiones políticas, fundadas en su visión de la relación del Estado y del hombre con la naturaleza y con la preservación ambiental, de protección de las comunidades originarias y respeto de los derechos humanos en su totalidad, en su grandeza ecuménica. Ciro Gomes es un político tradicional, de izquierda, del Nordeste y que intenta ubicarse como una alternativa a Lula, no como si tuviera camaradería con Lula. Ciro se ha perdido completamente como estratega político. No ha dado oídos a su partido, ni a los dirigentes más importantes del PDT. Y asumió como estrategia tratar a Lula y Bolsonaro en un mismo nivel.
+- Me daría una breve opinión de cada grupo de poder en Brasil y cómo juega en la elección a favor del presidente Bolsonaro. ¿El partido militar que lo acompaña en el gobierno?
+-Los militares sufrieron un proceso de cooptación de Bolsonaro. Pero a esta hora, la mayoría de ellos han resistido heroicamente su utilización en un golpe de Estado en Brasil. Y este es un mérito de la corporación militar.
+- ¿Los ruralistas, los beneficiarios del agronegocio, aquellos que depredan la Amazonia?
+-Yo pienso que los empresarios brasileños, no en su totalidad, pero en su gran mayoría, especialmente los empresarios del agronegocio, no tienen un sentimiento democrático, no tienen una visión que puedan exponer con coherencia acerca de un proyecto nacional, donde integren sus negocios de una manera pacificadora. Las clases dominantes brasileñas tienen una tradición colonial esclavista que no han perdido hasta hoy, incluso los medianos y pequeños empresarios. Una gran parte de ellos, no la totalidad, tiene esa visión. Mi opinión es muy negativa.
+-¿Y los medios?
+- Hay una inteligencia democrática organizándose en el medio del empresariado que se ha colocado en otro polo, y eso es muy bueno. TV Globo, por ejemplo, que fue responsable por la destitución de Dilma y la prisión de Lula, porque diseminó al mundo entero todas las violencias judiciales que fueron cometidas en contra del expresidente, hoy defiende la democracia e indirectamente, da sustento a la elección de Lula. Algunos de mis compañeros se quedan un poco estupefactos con eso y yo les digo: “qué bueno que eso ocurra, porque es una victoria de la lucha que hemos desarrollado hasta hoy”.
+-¿Qué papel juegan ahora las iglesias evangélicas que fueron tan determinantes por apoyar a Bolsonaro en las elecciones de 2018?
+- Creo que hay que separar a las religiones de la plata, de las religiones reales y tradicionales, que están en la formación nacional brasileña, y las que hace 70, 80 años, o recientemente, se desarrollaron más, que son las religiones evangélicas. Dentro de este último período es que surgen las iglesias de la plata. Son semejantes a las religiones del dinero en los Estados Unidos, aquellas que son sociedades mercantiles de la fe, y que establecen un proceso de conducción de la fe, de la política ideológica de sus seguidores para integrarlos en un proceso político determinado. Eso ha ocurrido en Brasil.
+- Otro factor de poder que incluso tiene representación en el Congreso es la llamada bancada da bala, el lobby de las armas, que ha sido muy estimulado por las políticas de Bolsonaro…
+-Es un complejo militar industrial privado que está en sus momentos iniciales y que estableció una relación directa con el propio presidente. Nosotros teníamos en Brasil una industria de material bélico y otros tipos de empresas estatales que trataban esas cuestiones a partir de las necesidades de nuestras Fuerzas Armadas. Y eso está siendo hoy integrado en el circuito comercial industrial global privado. Hacen transacciones de apoyo político a cambio de la libertad de vender sus mercancías de una manera extraordinaria como jamás debió ocurrir en Brasil.
+- Por su proximidad con Lula y su participación en la campaña, por su pasado tres veces como ministro, ¿Pensó en la idea de volver a un probable gobierno del PT?
+- No ciertamente. Por una parte, porque el presidente está reorganizando su entorno personal de una manera diferente a otras oportunidades. Porque ha emergido de un proceso de aislamiento político y en esa visión se aproximó a otros contingentes democráticos en Brasil. Tiene que rejuvenecer su staff. Y esa renovación no será solamente ideológica y política, que es una cosa que tiene que tratarse de una manera muy profunda en Brasil. Es un rejuvenecimiento generacional, incluso. Yo no soy una pieza imprescindible en ese ajedrez, con certeza.
+[H2] "Última alianza posible"
+- ¿Es la mejor fórmula posible Lula-Alckmin, si tomáramos el análisis que hizo recién, de que hay que cambiar lo viejo por lo nuevo. O la alianza con Alckmin representa la conyuntura electoral o alianza de clases para vencer a Bolsonaro y nada más?
+- Yo siempre me inspiro en un cuento de Hemingway para dar esa respuesta, que se llama "El último lugar posible", que es un cuento incluso ambientalista, ecológico. Dos hermanos jóvenes, ante el avance de la civilización, encuentran en el medio de la selva un lago. Entran para nadar y separarse de la sociedad. Es el último lugar posible, dicen los jóvenes. Entonces yo creo que esa alianza con Alckmin fue la necesaria y ultima alianza posible para resistir al nazismo. Necesaria porque hay que tener un gran frente político para resistir al asedio del fascismo como ocurrió incluso en Alemania e Italia.
+- Por último, ¿cuál cree usted que puede ser el papel que juegue Estados Unidos en las elecciones ante la amenaza de Bolsonaro de cuestionar los resultados si no gana?
+- En ese sentido, la posición de Joe Biden fue muy importante para derrotar el golpe en Brasil. Para mi generación es una sorpresa porque todos los golpes que sufrimos acá tuvieron el apoyo militante de los Estados Unidos. Pero no tengamos la ilusión de que la naturaleza imperialista de los Estados Unidos haya cambiado, eso nos es verdad. Hay una contingencia política que hace que Biden cultive relaciones con Latinoamérica y no acepte golpes de estado que puedan desestabilizar la región, a la que tiene que cautivar para los próximos períodos de las disputas globales. Veo esa como una buena sorpresa para nosotros, porque no tendríamos como sostenernos si Bolsonaro tuviese el apoyo del ejército para un golpe de estado en Brasil.</t>
   </si>
   <si>
     <t>Reclamo mbya contra una forestal</t>
@@ -2080,7 +5321,24 @@
     <t>https://www.pagina12.com.ar/481204-reclamo-mbya-contra-una-forestal</t>
   </si>
   <si>
-    <t>2022-09-12T03:01:00Z</t>
+    <t xml:space="preserve">Título: Reclamo mbya contra una forestal
+Chapeau: En Garuhapé, Misiones, reclaman contra Arauco
+Subtítulo: La mutinacional ocupa casi la mitad de las hectáreas que le son reconocidas a la comunidad de Puente Quemado II.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/481204-reclamo-mbya-contra-una-forestal/
+Notícia completa (11 blocos):
+Arauco es una multinacional forestal que opera en treinta países. En Misiones controla más de 230.000 hectáreas y acumula denuncias de campesinos y pueblos originarios por usurpación de tierras, contaminación y vulneración de derechos. En el municipio de Garuhapé, a 150 kilómetro de Posadas, mantiene un conflicto con la comunidad Puente Quemado II, del Pueblo Mbya Guaraní. "Los gobiernos y las empresas forestales destruyen la naturaleza. Los pueblos originarios cuidamos el monte y la selva, solo queremos que nos dejen vivir tranquilos en nuestro territorio", reclamó el cacique de la comunidad, Santiago Ramos. Desde la empresa dijeron que mantienen "comunicación abierta y fluida con 27 comunidades guaraníes vecinas, en cumplimiento de los marcos regulatorios nacionales e internacionales".
+La comunidad Puente Quemado II vive desde inicios de la década del 70 en Garuhapé (departamento de General San Martín), en el centro oeste de Misiones. El relevamiento territorial del Instituto Nacional de Asuntos Indígenas (INAI), en el marco de la Ley Nacional 26.160, le reconoce la posesión ancestral de al menos 657 hectáreas. Territorio en el cual, desde hace casi dos décadas, padece la intrusión de la empresa Arauco con monocultivos de pinos y eucaliptos en 331 hectáreas.
+Alcanza con recorrer la comunidad (o ver fotografías) para confirmar cómo la empresa invadió hasta escasos metros de las viviendas de la comunidad. "Arauco no quiere parar con el monocultivo. Nos sacan nuestro monte, nos secan los arroyos y dejan sin agua, nos tiran agrotóxicos y los niños enferman. No queremos más a la empresa en nuestro territorio", reclamó el cacique Ramos.
+La comunidad está integrada por trece familias, 75 personas, desde bebés hasta ancianos. Desde hace años que denuncian el accionar de Arauco, pero dos hechos fortalecieron el reclamo. Los jóvenes Mbya se rebelaron ante las continuas imposiciones y dádivas empresarias. Uno de ellos es el cacique Santiago Ramos, que consciente de los derechos --y en línea con los pedidos de toda la comunidad-- exige el título de propiedad comunitario de las tierras que siempre habitaron y trabajaron. El otro punto de quiebre fueron los incendios del verano pasado. Los pinos, especie foránea, propagan el fuego mucho más que los árboles autóctonos. Las llamas arrasaron cientos de hectáreas y casi arden las viviendas de los Mbya.
+Con el fuego ya apagado, la multinacional intentó volver a sembrar pinos. Y la comunidad no se lo permitió. Le asiste el "derecho a la consulta libre, previa e informada", vigente en normativas internacional de derechos humanos que Argentina suscribió (Convenio 169 de la OIT y Declaración de Naciones Unidas sobre los Derechos de los Pueblos Indígenas).
+La comunidad notificó por escrito, tanto a la empresa Arauco como al gobierno de Misiones: "No estamos dispuestos a permitir que se sigan afectando nuestros recursos de subsistencia material y espiritual con la deforestación y el monocultivo. Requerimos que se abstengan de autorizar y o permitir cualquier tipo de intervención sobre nuestro territorio".
+Desde el Área de Comunicación de Arauco destacaron, vía un breve comunicado, que la empresa "cree que el relacionamiento con las comunidades es fundamental para generar vínculos basados en el respeto, el diálogo y la participación. Arauco posee en Argentina más del 45 por ciento de sus tierras sólo dedicadas a la conservación. Como vecinos, también nos proponemos contribuir al desarrollo y crecimiento de las comunidades con relaciones de largo plazo".
+El Equipo Misiones de Pastoral Aborigen (Emipa) acompaña a la comunidad en sus reclamos. "Arauco casi que decide todo en las comunidades donde ingresa, y lo hace mediante la presión y poder que tiene. A la comunidad Puente Quemado II les dijo que no reclamen y les daba cinco metros más de tierra a cada familia. Y la comunidad se rebeló", explicó el comunicador de Emipa, "Vasco" Baigorri. Afirmó que la multinacional mantiene numerosos conflictos en la provincia, entre ellos con las comunidades Andrés Guazurari, Alecrín, Guqvira Poty, Kokue Poty, Isla, Guavira Mi y Kokuere'i. En abril pasado marcharon hasta la Casa de Gobierno, en Posadas, y el lema principal fue contundente: “Fuera Arauco”.
+El cacique Santiago Ramos resume qué les implicó a los Mbya Guaraní el modelo forestal: "Los monocultivos traen muchas consecuencias. Abajo de los pinares no crece nada, no tenemos árboles, no tenemos agua, no hay biodiversidad. Queremos la comunidad libre de monocultivo para recuperar el monte, las frutas nativas, la vida".
+Arauco, o su otra figura jurídica local (Alto Paraná), es muy conocida en Misiones. Es propietaria de al menos el diez por ciento de la provincia (230 mil hectáreas). Ninguna empresa ni persona física de Argentina concentra tanta tierra en una sola provincia. En el municipio de Puerto Piray controla el 65 por ciento del lugar. Allí también tuvo denuncias y derrotas: la organización campesina Productores Independientes de Piray (PIP-UTT) luchó durante diez años, resistió desalojos y, mediante movilizaciones y acciones directas, logró la expropiación de 600 hectáreas, donde en la actualidad producen alimentos sanos de manera agroecológica.
+El Movimiento Mundial por los Bosques Tropicales (WRM, por sus siglas en inglés) es un espacio de referencia internacional sobre los impactos de la industria forestal, a la que ubica como una de las caras del modelo extractivo. Como la megaminería, el agronegocio y la explotación petroleras --entre otras actividades contaminantes--, el WRM afirma que el monocultivo de árboles (pinos, eucaliptos y palma aceitera) implica desalojos, apropiación de tierras de campesinos y de pueblos indígenas, contaminación, impactos negativos en la salud y violación de derechos. El próximo 21 de septiembre se conmemora el "Día internacional de lucha contra los monocultivos de árboles", y una de sus frases de referencia es: "Los monocultivos forestales no son bosques".</t>
   </si>
   <si>
     <t>Brasil: desfile macartista de militares y sojeros</t>
@@ -2092,7 +5350,34 @@
     <t>https://www.pagina12.com.ar/480309-brasil-desfile-macartista-de-militares-y-sojeros</t>
   </si>
   <si>
-    <t>2022-09-08T03:01:00Z</t>
+    <t xml:space="preserve">Título: Brasil: desfile macartista de militares y sojeros
+Chapeau: Bolsonaro reivindicó el golpe de 1964 y uso el Día de la Independencia para hacer campaña
+Subtítulo: Dos nuevas encuestas reafirman el liderazgo de Lula de cara a las elecciones del 2 de octubre. Bolsonaro usó el desfile militar como demostración de fuerza ante sus electores y los indecisos. Desde un camión trató de ladrón a su contrincante.
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/480309-brasil-desfile-macartista-de-militares-y-sojeros/
+Notícia completa (21 blocos):
+Desde Brasilia
+Jair Bolsonaro hizo un gesto de aparente complicidad cuando cientos de simpatizantes comenzaron a corear "la bandera brasileña jamás será roja" al inicio del desfile por el Día del Bicentenario de la Independencia poco después de las nueve de la mañana de este miércoles en el centro de Brasilia. Junto a él se encontraba la primera dama Michelle, militante evangélica , que se sumó sin disimularlo al cántico macartista llegado desde una de las tribunas montantes instaladas en el Eje Monumental. Esa superavenida de cientos de metros de ancho que comienza en el Palacio del Planalto en su extremo este, pasa por el Congreso y llega hasta el ministerio de Defensa en su lado oeste.
+[H2] Golpe
+Por allí desfilaron tanques, carros blindados y más de veinte tractores verde y amarillos (los colores patrios) cedidos por empresarios del agronegocio, el sector de donde proviene cerca del ochenta por ciento de las donaciones de la campaña bolsonarista. Más tarde llegó una columna de adolescentes y niños con remeras negras, marchando con paso militar, pertenecientes a la Comunidad Clásica Cristiana que portaban un pasacalles con la frase "conocer a Dios y tornarlo conocido".
+Antes de llegar al desfile el presidente de ultraderecha, candidato a la reelección en los comicios del mes que viene, había desayunado y rezado junto a pastores, generales y ministros en la residencia oficial de Alvorada, donde se refirió al golpe de estado de 1964 como un hecho que "se puede repetir". Además dijo que el bien siempre derrota al mal, "como sucedió en el 64". Y aseguró estar preparado para una contingencia de ese tipo (golpe) en la que se debe entregar hasta la vida por la "libertad".
+Siempre que puede el capitán retirado trae a colación el régimen de facto del cual es un exégeta y al que usa como una amenaza velada contra sus adversarios. Lo curioso es que este tipo de intimidaciones son empleadas por Bolsonaro con más frecuencia cuando su situación es adversa, tal como ocurre ahora cuando faltan 25 días para la votación y no logra avanzar lo suficiente en las encuestas. Una de ellas publicada el lunes por la agencia Ipec, a pedido de la tevé Globo, le dio el 31 por ciento de intenciones de voto contra el 44 por ciento de Luiz Inácio Lula da Silva con vistas al primer tuno del 2 de octubre.
+Si nadie supera el 50 por ciento en la primera vuelta habrá un ballotage el 30 de ese mes y en ese caso el excapitán del ejército obtendría el 36 por ciento contra al 52 por ciento del candidato del Partido de los Trabajadores.
+[H2] Copacabana
+Al igual que el sondeo mencionado arriba, otras encuestas recientes indican que el expresidente petista será el más votado en la primera vuelta y en caso de haber un ballotage será electo con una ventaja amplia. Es cierto que Bolsonaro ha crecido en las últimas semanas mientras Lula se estabilizó en la franja de los 43 a 45 puntos, pero el ritmo de avance del militar es demasiado lento como para esperar un sorpasso.
+Ante ello la estrategia del Palacio del Planalto fue hacer del Bicentenario de la Independencia la última gran apuesta para garantizar el voto de la tropa propia e impactar a los aún indecisos con grandes actos masivos.
+En efecto, las concentraciones de este miércoles en Brasilia por la mañana y a la tarde frente a la playa de Copacabana, en Río de Janeiro, movilizaron decenas de miles de personas demostrando que el oficialismo está vivo. La visita a Río de Janeiro comenzó con una caravana en moto, una "motociata", por algunos barrios del centro, repitiendo el mismo ritual realizado en otras capitales brasileñas e incluso durante viajes a Estados Unidos y países árabes.
+A primera hora de la noche desde el cuartel general oficialista surgían voces exultantes, como la de uno de responsables de la campaña, Fabio Wajngarten, para quien las movilizaciones fueron "atómicas" y mostraron que el "sentimiento patriótico es el combustible de la reelección". De todos modos esa euforia huele a sobreactuación.
+Habrá que revisar con más tiempo las imágenes para saber si estas movilizaciones fueron más o menos concurridas que las del 7 de setiembre de 2021, para medir el verdadero tamaño del bolosnarismo militante.
+[H2] Lula
+Si el 7 de setiembre de 2021 el blanco al cual le apuntó Bolsonaro fueron algunos jueces del Supremo Tribunal Federal, este año los disparos estuvieron dirigidos a Lula. "Hay que extirpar de la vida pública" al jefe petista, propuso el mandatario trepado en lo alto de un camión utilizado para los desfiles de carnaval en Río de Janeiro. "Yo no soy muy educado, digo malas palabras pero no soy un ladrón...La voluntad del pueblo se hará presente el 2 de octubre, vamos todos a votar en unas elecciones donde estarán frente a frente el bien contra el mal que perduró durante doce años en el país", los que gobernó el Partido de los Trabajadores entre con Lula y Dilma Rousseff.
+Después de Bolsonaro subió al camión carnavalesco su esposa, que ha asumido un papel central en la campaña , para decir que la pelea contra el "enemigo" Lula es en defensa de los "valores que Dios estableció en la tierra".
+[H2] Discurso de odio
+Para evitar choques con las milicias oficialistas Lula optó por no organizar actos por el Bicentenario y aguardó hasta la noche del miércoles para divulgar un video. Allí afirmó que cuando estuvo en el gobierno "jamás utilizamos el Día de la Patria para hacer campaña electoral ni para diseminar el discurso del odio".
+Respecto de las acusaciones de corrupción lanzadas por el oficialismo en su contra, el expresidente mencionó un reportaje aparecido la semana pasada sobre más de cien propiedades compradas por Bolsonaro y su familia, sin tener ingresos legales que justifiquen tales inversiones.
+El petista comentó que si ya es sospechoso semejante patrimonio inmobiliario, éste se hace aún más extraño cuando se observa que 51 inmuebles fueron comprados con dinero al contado. Este escándalo, publicado en una exhaustiva investigación del portal UOL, parece haber neutralizado el discurso moralista del presidente, sobre cuyas cuentas siempre hubo varias zonas oscuras.
+En una entrevista dada esta semana Bolsonaro fue consultado sobre el tema y admitió la existencia de esa centena de viviendas, entre las que hay varias en barrios exclusivos de Brasilia y Río, así como haber pagado la mitad de ellas con efectivo.</t>
   </si>
   <si>
     <t>Brasil: Bolsonaro, la Amazonia y los dueños del agronegocio</t>
@@ -2102,6 +5387,30 @@
   </si>
   <si>
     <t>https://www.pagina12.com.ar/480246-brasil-bolsonaro-la-amazonia-y-los-duenos-del-agronegocio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Título: Brasil: Bolsonaro, la Amazonia y los dueños del agronegocio
+Chapeau: Jugadores globales y políticas para quitarle protección al medio ambiente
+Subtítulo: El objetivo de los operadores financieros y las corporaciones alimenticias es el desmantelamiento de las regulaciones medioambientales en Brasil.
+Editoria: El Mundo
+Tags: Amazonia, Jair Bolsonaro, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/480246-brasil-bolsonaro-la-amazonia-y-los-duenos-del-agronegocio/
+Notícia completa (15 blocos):
+Si Brasil se juega su futuro político en las elecciones presidenciales del 2 de octubre, su modelo económico de agronegocios en la Amazonia se discute todos los días. La depredación forestal de este vergel del planeta no tiene ese único costado para analizar: el daño medioambiental. En todo caso, ésa es la consecuencia de la política que propicia el gobierno de Jair Bolsonaro. Su proyecto estrella es el llamado Ferrogrão o tren del grano que recorrerá la foresta en un tramo de 933 kilómetros y conectará el norte del estado de Mato Grosso con el puerto de Miritituba en el vecino Pará. Se trata de sacar el poroto de soja de esa región – el país es el principal productor mundial – hacia el Atlántico y a un costo menor que el generado por los camiones. Pero ésa, más otras obras de infraestructura requieren de capitales y el rol activo del Estado que por ahora controla el militar y los altos oficiales que lo colonizaron en masa. Lo que no se conoce demasiado – al menos fuera del mundo de las finanzas – es quiénes costean el camino hacia El Dorado transgénico donde las que más ganan son las grandes corporaciones estadounidenses Cargill y Bunge, más la brasileña Amaggi.
+[H2] El lobby
+En un informe de la Internacional Progresista (IP) titulado "La financiación detrás del lobby de la agroindustria brasileña" que se publicó el 1° de septiembre, aparecen encabezando la lista de aportantes JP Morgan Chase, Bank of America y el fondo BlackRock, cada uno con “ U$S 1000 millones invertidos en la red de financiadores del ganadero”. El encabezado del trabajo además menciona a otras empresas como “Suzano, JBS, Marfrig, Cargill y ADM, gigantes del agronegocio que ejercen su poder corporativo para influir en la política brasileira contra los intereses ambientales, campesinos, indígenas y de las masas trabajadoras de todo el Brasil”.
+La Internacional Progresista es una organización que integran, entre otros y otras, el actual presidente de Colombia, Gustavo Petro; el intelectual estadounidense Noam Chomsky; el expresidente de Ecuador, Rafael Correa; el exvicepresidente de Bolivia, Álvaro García Linera; el exjuez español Baltazar Garzón; el excanciller de Lula, Celso Amorim; la ministra de Mujeres, Género y Diversidad, Elizabeth Gómez Alcorta; más la exembajadora argentina en Venezuela, Alicia Castro. La información del primer día de este mes se basa en investigaciones y datos de dos plataformas: De Olho nos Ruralistas (un observatorio del agronegocio que significa algo así como Vigilando a los ruralistas) y Florestas &amp; Finanças (Bosques y finanzas), que aporta estadísticas sobre operaciones multimillonarias en actividades de alto impacto ambiental, como la agricultura y la minería.
+Entre 2019 y 2021 – dice la investigación – “los bancos transnacionales y los fondos de inversión aportaron más de 27 mil millones a empresas que forman parte de la cadena de fondeo del Instituto Pensar Agro (IPA) integrado por el grupo de expertos detrás del Frente Parlamentario del Agro o (FPA)”. La llamada bancada ruralista con fuerte poder de lobby y aliada del mandatario ultraderechista.
+[H2] Megaproyecto
+En otro trabajo publicado el 19 de julio pasado por la IP, ya se anticipaba sobre el Ferrogrão: “La función principal del megaproyecto ecocida, de 1.700 millones de dólares, será un regalo corporativo para gigantes del agronegocio como Cargill, Amaggi y Bunge, reduciendo los costos de exportación de productos básicos y llevando la deforestación al límite”.
+El objetivo que no se percibe tanto de estos operadores financieros y las corporaciones alimenticias es el desmantelamiento de las regulaciones medioambientales en Brasil. En Florestas &amp; Finanças donde se publican informes a escala planetaria de estos jugadores globales aparecen mencionados fondos de la India, Malasia, China, Japón y los ya citados de EE.UU a los que debe agregarse otro actor clave del mundo buitre, el Vanguard Group.
+[H2] El grupo Suzano
+De toda la información disponible en estas plataformas que siguen al agronegocio se desprende que entre 2019 y 2021 el principal receptor de capital extranjero fue Suzano, la fábrica de celulosa más grande del mundo. Esta papelera es producto de la fusión de las dos compañías brasileñas Suzano Papel&amp;Celulose y Fibria Celulose. El año pasado anunció una millonaria inversión en la construcción de una nueva planta de celulosa en Mato Grosso do Sul. Puede producir 2,3 millones de toneladas anuales de pulpa de eucalipto.
+Según De Olho nos Ruralistas, de 2019 a 2021, “el grupo liderado por la familia Feffer recibió US$ 14.030 millones de bancos y fondos de inversión globales, el equivalente al 51,9% del total invertido en empresas asociadas a IPA en el período. Los principales patrocinadores de la empresa fueron Bank of America ($791,3 millones), JP Morgan Chase ($774,8 millones) y BlackRock ($525,5 millones)”. Otro dato: en julio de este año la empresa cotizaba en la Bolsa de Brasil a 63 mil millones de reales.
+La organización ecologista Movimiento Mundial por los Bosques Tropicales denunció en 2020 su modus operandi: “El gigante de la celulosa Suzano S.A busca expandir sus plantaciones de eucalipto en Brasil aplicando una táctica clave: presentarse como una empresa que logra la ‘conservación’ y la ‘restauración’, ocultando así su desastroso historial con los bosques y sus poblaciones”. Además del sector maderero, la compañía también tiene presencia en los mercados de plaguicidas y semillas transgénicas por medio de su filial FuturaGene.
+La principal beneficiaria de los fondos buitre y la banca transnacional en Brasil, blanco de protestas en su momento del Movimiento de los Trabajadores Rurales Sin Tierra (MST), según el informe de la IP “es conocida por la participación de sus directores, los hermanos David y Daniel Feffer, en el financiamiento de movimientos de la llamada nueva derecha en Brasil. Daniel es uno de los fundadores del Instituto Millenium, junto al Ministro de Economía, Paulo Guedes. Su hermano David participó, en 2007, en la creación del Instituto de Formación de Liderazgo, uno de los organizadores del Foro Libertad y Democracia, junto a José Salim Mattar Junior, propietario de la empresa de alquiler de coches Localiza Hertz y exsecretario general de Privatización en el gobierno de Bolsonaro”.
+Por varias de estas razones el futuro de la Amazonia es uno de los temas de mayor proyección en la agenda informativa de Brasil y del mundo todo. Su impacto supera la cuestión medioambiental. Es también económico, social y político.
+gveiga@pagina12.com.ar</t>
   </si>
   <si>
     <t xml:space="preserve">"Verdurazo" frente al Congreso
@@ -2114,7 +5423,23 @@
     <t>https://www.pagina12.com.ar/479895-verdurazo-frente-al-congreso-para-reclamar-por-el-acceso-a-l</t>
   </si>
   <si>
-    <t>2022-09-07T03:01:00Z</t>
+    <t xml:space="preserve">Título: "Verdurazo" frente al Congreso para reclamar por el acceso a la tierra
+Chapeau: Organizaciones sociales presentaron un conjuntos del proyectos legislativos
+Subtítulo: La Mesa Agroalimentaria le pidió a diputados y funcionarios que avancen en medidas para regular los alquileres, promover créditos blandos y frenar los desalojos en los territorios campesinos.
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/479895-verdurazo-frente-al-congreso-para-reclamar-por-el-acceso-a-l/
+Notícia completa (10 blocos):
+La Mesa Agroalimentaria repartió 20 mil kilos de verdura frente al Congreso y presentó a los diputados un paquete de proyectos de ley para desarrollar su actividad, la del “campo que alimenta”. Con el Verdurazo, los productores plantearon que pese a tener la estratégica función de cultivar para el consumo interno, el Estado no los protege frente al avance del agronegocio ni frente a las lógicas del sistema financiero. Sus propuestas legislativas apuntan a cuestiones como el acceso a la tierra, control de los alquileres rurales, financiamiento para la producción, freno a los desalojos en los territorios campesinos y mayores respaldos para quienes hacen la transición a la agroecología.
+Como ocurre en cada Verdurazo, en la plaza del Congreso se formaron largas colas de vecinos que se acercaron para llevarse hortalizas frescas. Antes de distribuirlas, los organizadores de la protesta hicieron un acto. "Sabemos que este es un momento difícil. Nos sumamos al repudio del intento de magnicidio de la vicepresidenta, como repudiamos a todos los hechos que tienen como objetivo extorsionar al sistema político para que siga siendo funcional al sistema financiero. Estamos convencidos que para terminar con estas cosas, para consolidar la democracia hay que consolidar la soberanía alimentaria, y de eso se tratan las propuestas que estamos haciendo. Cuando el derecho a la alimentación esté garantizado y los derechos de los productores estén garantizados va a haber un salto en la calidad democrática", señalaron alí
+La Mesa Agroalimentaria está formada por la Unión de Trabajadores de la Tierra, el Movimiento Nacional Campesino Indígena Somos Tierra y la Federación de Cooperativas Federadas (Fecofe). El MNCI Somos Tierra y la UTT reúnen a productores que vienen muy de abajo; en el mejor de los casos, luego de organizarse pudieron acceder a tierras en comodato o a maquinaria agrícola que usan cooperativamente, pero en su mayoría alquilan la tierra que trabajan y viven casillas precarias. Sus reclamos históricos son una ley de acceso a la tierra, a la manera de un Procrear Rural, y el freno a los desalojos.
+Fecofe, en cambio, reúne a productores de mayor tamaño; es una organización nacida dentro de la Federación Agraria Argentina en la que hay cooperativas agrícolas, tamberos y productores de cereales, que sumaron a la agenda de reclamos el pedido de segmentaciones impositivas.
+“En la Mesa Agroalimentaria nos dimos cuenta que casi todos tenemos los mismos problemas y este paquete de leyes busca solucionarlos”, aseguró Delicia Zenteno. Como productora de la UTT de Santa Fe, contó que en algunos casos, como el de la acelga, los quinteros no están llegando a cubrir los costos de producción debido al alto precio de la semillas y de los arrendamientos rurales. “Necesitamos una mejor regulación de los alquileres en el campo”.
+La presentación de los cinco proyectos de ley fue realizada en el Salón de los Pasos Perdidos. “Invitamos a diputados de todos los bloques y a funcionarios”, contó Nahuel Levaggi, el principal referente de la UTT, sobre la actividad. De las cinco, una ya está ingresada: es el proyecto de Acceso a la Tierra, que impulsa la creación de créditos blandos -a la manera de un Procrear- y de un banco de tierras para la producción.
+Los otros proyectos son de arrendamientos rurales, de protección de los territorios campesinos y la agricultura familiar, de segmentación impositiva y de apoyo al cooperativismo y la transición a la agroecología.
+Estas medidas, indicó Levaggi, “promueven el abastecimiento de alimentos sanos a precios justos al pueblo y garantizan una vida digna en el campo. En momentos difíciles como este, es imprescindible avanzar en este tipo de propuestas”.
+Desde Fecofe, Pablo Paillole señaló que la campaña tiene que ver fundamentalmente con elaborar una agenda que represente “los problemas estructurales del campo que están ajenos a la agenda parlamentaria” porque el gran problema del campo “es la enorme concentración y expulsión de medianos y pequeños productores de pueblos originarios y de la agricultura familiar que se ven desplazados por el agronegocio y grandes terratenientes”.
+En ese sentido detalló que los proyectos ponen en discusión el modelo agropecuario existente para “hacer una democratización de la producción y la tierra”.</t>
   </si>
   <si>
     <t>Brasil: mal clima por el desfile militar de Bolsonaro</t>
@@ -2126,6 +5451,37 @@
     <t>https://www.pagina12.com.ar/479889-brasil-mal-clima-por-el-desfile-militar-de-bolsonaro</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Brasil: mal clima por el desfile militar de Bolsonaro
+Chapeau: Con vehículos blindados y aviones de guerra desfilando, el presidente desafía a la democracia
+Subtítulo: Se espera que el actual mandatario pronuncie discursos tan golpistas como los de un año atrás, cuando tuvo lugar el primer ensayo desestabilizador del excapitán.
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Luiz Inácio Lula da Silva, elecciones en Brasil, printed-edition, jair-bolsonaro, luiz-inacio-lula-da-silva, elecciones-en-brasil, diario
+URL: https://www.pagina12.com.ar/479889-brasil-mal-clima-por-el-desfile-militar-de-bolsonaro/
+Notícia completa (22 blocos):
+Desde Brasilia
+Atmósfera pesada en Brasilia. Horas antes del desfile militar organizado por el presidente Jair Bolsonaro para este miércoles en conmemoración del Día de la Indepenencia, el cielo de la capital se tiznó debido a un incendio de grandes proporciones en el Parque Nacional. El avance de las llamas se vio favorecido por una humedad bajísima, del 12 por ciento el lunes y el 20 por ciento el martes.
+En algunas barrios de la periferia norte el aire se tornó por momentos irrespirable al mediodía cuando en el centro decenas de operarios montaban las tribunas donde el miércoles generales y ministros verán pasar el desfile. Para dar más grandiosidad (y algo de necrofilia) a la fecha el presidente hizo traer desde Portugal el corazón en formol del emperador Pedro I, el héroe independentista.
+Mientras tanto algunos helicópteros sobrevolaban a baja altura esta ciudad saturada de carros del ejército y móviles policiales reflejo del sistema de poder cívico-militar construido con la llegada de Bolsonaro al Palacio del Planalto en 2019.
+[H2] Corte asediada
+El lunes a la noche una decena de camioneros bolsonaristas intentó atravesar los retenes colocados en la avenida principal, el Eje Monumental, con el propósito de repetir lo ocurrido el 7 de setiembre del año pasado cuando fue cercado el palacio del Supremo Tribunal Federal.
+Un juez de esa corte comentó al portal de noticias UOL, a condición de anonimato, que si bien se adoptaron todas las medidas de seguridad posibles, incluso con un sistema que impide el sobrevuelo de drones, aún existe el riesgo de que el palacio sea atacado en medio de los festejos patrios.
+[H2] Sin gente
+Casi nadie circuló por el centro este martes dado que el gobierno decretó feriado y con ello la metrópolis de predios futuristas y museos parecidos cápsulas espaciales transmitía un aire fantasmal propicio para las especulaciones políticas.
+" Bolsonaro está preparando el golpe?", pregunta un colega corresponsal para en seguida responderse, "no me parece que pueda porque tiene a la Embajada (estadounidense) y a la (tevé) Globo en contra".
+Es realista considerar que el capitán presidente difícilmente logre llevar adelante su deseado autogolpe si no están de su lado ni la Casa Blanca ni las empresas mediáticas dominantes, dos factores de poder que años atrás facilitaron su ascenso la rampa del Planalto.
+De todos modos las imágenes de vehiculos blindados y aviones de guerra desfilando, posiblemente junto a tractores cedido por el agronegocio, vivados por miles de personas dará una dimensión del poder de convocatoria del gobernante de ultraderecha. Y mostrará el respaldo militar con el que cuenta a menos de un mes de los comicios en los que buscará ser reelecto.
+[H2] Discursos
+Este miércoles por la mañana se realizará una parada militar en Brasilia y por la tarde otra en Rio de Janeiro, con acrobacias de aeronaves de la Fuerza Aérea y navíos de la Marina frente a la playa de Copacabana. En ambos estará Bolsonaro, de quien se espera que pronuncie discursos tan golpistas como los de un año atrás, cuando tuvo lugar el primer ensayo desestabilizador.
+Uno de los blancos debe sus ataques debe ser la justicia electoral comandada por el juez Alexandre de Moraes, quien recientemente ordenó allanar las oficinas de ocho empresarios sospechosos de financiar un intento de golpe de estado en caso de que Luiz Inácio Lula da Silva.
+"Usurpador"
+Mientras en Brasilia este martes fue de vigilia, con activistas de ultraderecha llegados de otros estados armando campamentos o alojándose en hoteles, en San Pablo el expresidente Lula analizaba junto a sus compañeros del Partido de los Trabajadores los números de la última encuesta divulgada por la cadena Globo el lunes a la noche, donde aparece con el 44 por ciento de las intenciones de voto frente al 33 por ciento de Bolsonaro.
+Ese sondeo y otro conocida el lunes a la tarde trajeron aire fresco al cuartel petista porque indican un retroceso, módico, de su rival del Partido Liberal. Estos números permiten alimentar la esperanza, aunque sea lejana, de victoria en la primera vuelta del 2 de octubre sin necesidad de disputar el ballotaje del 30 de ese mes.
+Lula dijo que de las seis campañas presidenciales que disputó desde 1989, en ninguna "tuvimos tantas chances de ganar en el primer turno como las que tenemos en estas elecciones, y no tenemos miedo de decirlo, ¿por qué no querer ganar en el primer turno si falta un tris (para votación)?".
+Respecto de su antagonista Bolsonaro planteó que "le está usurpando el 7 de setiembre al pueblo brasileño para hacer de los festejos una cosa personal". Y añadió: "al final de cuentas la independencia es de nuestro país (..) de los 215 millones de brasileños" y no de un candidato que usa la fecha como botín electoral." Lula también criticó a Bolsonaro por liberar la venta de armas y su discurso de "odio".
+[H2] Armados
+Otros ejes de los discursos de Bolsonaro de este miércoles deben ser la defensa de la "libertad" a todo precio y la venta irrestricta de armas en línea con la política llevada adelante desde el inicio del gobierno.Solo que esa justificación libertaria no logra disimular lo que en realidad sería el verdadero propósito de esa propuesta: contar con miles de extremistas armados y dispuestos a actuar.En ese sentido es recomendable leer este tuit posteado el lunes por el diputado Eduardo Bolsonaro, hijo del presidente. "¿ Compraste un arma legal? ¿Tenés un club de armas o vas a uno? Entonces tenés que convertirte en un voluntario de Bolsonaro".</t>
+  </si>
+  <si>
     <t>Brasil: la "notita" de Bolsonaro tras el intento de magnicidio de Cristina Kirchner</t>
   </si>
   <si>
@@ -2135,7 +5491,36 @@
     <t>https://www.pagina12.com.ar/479094-brasil-la-notita-de-bolsonaro-tras-el-intento-de-magnicidio-</t>
   </si>
   <si>
-    <t>2022-09-04T01:44:15Z</t>
+    <t xml:space="preserve">Título: Brasil: la "notita" de Bolsonaro tras el intento de magnicidio de Cristina Kirchner
+Chapeau: Mientras Lula analiza reforzar su custodia en medio de la campaña electoral
+Subtítulo: El ataque de Buenos Aires impactó en Brasil, donde la violencia política unida a la amenaza de golpe son trazos marcantes de la carrera hacia la votación del 2 de octubre.
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Luiz Inácio Lula da Silva, Cristina Fernández de Kirchner, jair-bolsonaro, luiz-inacio-lula-da-silva, cristina-fernandez-de-kirchner, diario
+URL: https://www.pagina12.com.ar/479094-brasil-la-notita-de-bolsonaro-tras-el-intento-de-magnicidio-/
+Notícia completa (23 blocos):
+Desde Brasilia
+Después del atentado contra Cristina Fernádez de Kirchner el expresidente brasileño Luiz Inácio Lula da Silva comenzó a analizar el refuerzo de su esquema de seguridad a menos de un mes de las elecciones en las que enfrentará Jair Bolsonaro, el mandatario de ultraderecha durante cuyo gestión fue liberada la venta de armas.
+[H2] Controles ínfimos
+Los controles ínfimos a la venta de fusiles en Brasil hacen plausible que parte de éstos hayan caído en manos de algún "lobo solitario" como al parecer sería Fernando Andrés Sabag Montiel el magnicida que fracasó al gatillar contra la expresidenta argentina frente a su departamento porteño el jueves a la noche.
+De acuerdo con la ONG brasilea Sou da Paz, a través de decretos para liberar la venta y flexibilizar inspecciones de armas, el gobierno permitió que haya un millón de piezas en poder de Cazadores, Tiradores y Coleccionadores (CACs,sigla en portugués). Y lo peor: muchos de los que se hacen pasar por CACs podrían ser extremistas o "milicianos" paramilitares que actúan como fuerzas irregulares a órdenes del bolsonarismo.
+El mismo jueves a la noche Lula, ,el candidato del Partido de los Trabajadores (PT), repudió el atentado "fascista" contra Cristina antes de reunirse con sus asesores para hablar sobre cambios relativos al número de agentes de su escolta y la forma como esta opera ante el riesgo de un atentado, informó el diario O Globo.
+El ataque de Buenos Aires impactó en Brasil, donde la violencia política unida a la amenaza de golpe son trazos marcantes de la carrera hacia la votación del 2 de octubre.
+Desde hace más de un mes Lula comenzó a utilizar chalecos antibalas en los actos luego que éstos fueron atacados con explosivos, en Rio de Janeiro, y bolsones llenos de estiércol, en Minas Gerais, lanzados desde un drone propiedad de un empresarios del agronegocio bolsonarista.
+Poco después de estos atentados un dirigente petista de Foz de Iguazú fue asesinado por un policía penitenciario que mientras disparaba exaltaba, a los gritos, a Bolsonaro.
+Dentro de ese contexto los hechos de la semana pasada en Buenos Aires causaron "preocupación" y dieron lugar a una "conversación en la campaña" que puede reforzar la seguridad de Lula declaró el secretario general del PT, Paulo Teixeira, a la agencia Reuters.
+[H2] Tatuajes
+El sospechoso Fernando Andrés Sabag Montiel, nacido en Brasil, ostenta tatuajes de la cruz de hierro, el martilllo de Thor y un sol negro. Símbolos nazis incorporados a la iconografía de grupos extremistas brasileños los que se multiplicaron gracias al ascenso del bolsonarismo a partir de la campaña presidencial de 2018. Por entonces el hijo de Bolsonaro, Eduardo, encargado del enlace con el entorno de Donald Trump, hizo campaña reivindicando al gobierno de Ucrania como modelo de combate al comunismo. Es bastante popular entre los anticomunistas brasileños, simpatizantes del presidente que busca su reelección dentro de 29 días, la imagen del sol negro a la cual copiaron de las bandas nazis de Ucrania, donde algunos realizaon entrenamiento militar. Ese es el caso de Sara Winter, una de las dirigentes que incitó al asalto del Supremo Tribunal Federal desde un campamento instalado a pocas del Palacio del Planalto.
+Winter se hizo fotografiar en pleno centro de Brasilia, ostentando tatuajes y armas, y también junto a Bolsonaro.
+La activista fue funcionaria del Ministerio de la Mujer y la Familia, cuando al frente del mismo estaba la pastora Damares Alves, considerada una de las personas del círculo directo de la primera dama Michelle Bolsonaro.
+Pueden "llamarme fanática y loca" pero nadie hará que renuncie a la "guerra" religiosa contra el PT, declaró días atrás la señora del presidente en un acto de campaña.
+[H2] "Ustedes saben qué hacer"
+A través de mensajes oblicuos Bolsonaro suele dirigirse a sus seguidores, entre quienes hay tras, "milicianos" paramilitares y evangélicos, incitándolos a rebelarse contra el Supremo Tribunal Federal, el Tribunal Superior Electoral y eventualmente desconocer una victoria de Lula, a quien todas las encuestas dan como favorito.
+"Ustedes saben que hacer", es una de las expresiones en clave empleadas por el gobernante en sus concentraciones o en sus transmisiones en vivo a través de las redes sociales.
+Así lo hizo en vísperas de los actos del Día de la Independencia, el 7 de setiembre de 2021 cuando ante miles de seguidores hizo una defensa de la ruptura institucional intercalada con agravuos a jueces del Supremo. Cientos de militantes de ultraderecha se reunieron en Brasilia el año pasado en un campamento desde donde se defendía el golpe y se instaba a "ucranizar" el país.
+Se da por hecho que el l próximo miércoles, al cumplirse los 200 años de la Independencia, Bolsonaro volverá a lanzar ataques contra las instituciones en las paradas militares a ser realizadas en Brasilia y Rio de Janeiro.
+[H2] "Notita"
+En contraste con Lula, que repudio de inmediato el atentado contra la expresidenta Fernández de Kirchner, Bolsonaro demoró unas 16 horas en abrir la boca. Y no lo hizo en Brasilia, sino en el estado de Rio Grande do Sul, fronterizo con Argentina. Fue una declaración escueta en la que contó haber enviado una "notita" en la que lamentó sin mucho énfasis lo ocurrido. Bolsonaro evitó expresiones muy duras contra el sospechoso de intento de homicidio Sabag Montiel.
+Durante esa misma visita al sur brasileño habló durante unos siete minutos ante empresarios del agronegocio simpatizantes de su gobierno. El grueso del discurso lo dedicó a defender la liberación de armas para los CACs (Cazadores, Tiradores y Coleccionistas) como parte de una lucha por la libertad y el modelo de vida cristiano, además de insultar Lula. Y con algunos rodeos hizo un llamado a la insurrección cuando comentó que su país no puede aceptar el retorno del petista al poder.</t>
   </si>
   <si>
     <t>Suspenden el corte del puente</t>
@@ -2147,7 +5532,19 @@
     <t>https://www.pagina12.com.ar/478844-suspenden-el-corte-del-puente</t>
   </si>
   <si>
-    <t>2022-09-03T03:01:12Z</t>
+    <t xml:space="preserve">Título: Suspenden el corte del puente
+Chapeau: El reclamo por la Ley de Humedales
+Subtítulo: En asamblea, las organizaciones resolvieron posponer la protesta programada para este fin de semana en la conexión Rosario-Victoria a causa de los acontecimientos nacionales.
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/478844-suspenden-el-corte-del-puente/
+Notícia completa (6 blocos):
+La conmoción general que desató el intento de magnicidio contra la vicepresidenta Cristina Fernández de Kirchner alteró la agenda del país, y en ella, la política. Por eso la asamblea popular que había convocado la Multisectorial Humedales para este fin de semana en el puente Rosario-Victoria se pospuso, hasta ahora con fecha incierta, informaron desde ese colectivo que brega por la preservación del río y de sus islas y el punto final al ecocidio.
+Tras una prolongada deliberación ayer a la tarde, los asambleístas reunidos se dividieron en tres mociones: continuar con el plan acordado el 10 de agosto en la masiva concentración al pie del Monumento a la Bandera; cambiar de actividad por una de menor envergadura, o posponer el corte del enlace vial. Por mayoría ganó esta última opción, y al cierre de esta edición debatían en qué fecha realizarla.
+El llamado iba a realizarse en simultáneo con otras manifestaciones coincidentes. En Rosario se trataría de instalarse en la cabecera del puente, marchar hasta la otra margen del río y regresar para realizar un acampe y vigilia hasta el día siguiente, cuando se celebre una nueva asamblea. Esto es lo que ahora quedó en suspenso debido a la situación política nacional.
+El colectivo de organizaciones sociales y políticas –del que la Multisectorial es solo el mayor emergente– impulsó esta protesta con el fin de apurar la sanción del proyecto de Ley de Humedales consensuado.
+La masiva protesta celebrada el mes pasado en el Monumento logró que en el Congreso de la Nación el proyecto de consenso fuera girado a tres comisiones de Diputados. "Pero ahí está, no lo están tratando, y por eso queremos sostener la lucha para que lo traten en un plenario de comisiones, le den media sanción y lo pasen al Senado para su sanción final", explicó Sergio Gorosito, de la Multisectorial.
+En paralelo, los ambientalistas abogan para que no prospere la otra iniciativa parlamentaria que redactaron el Consejo Federal de Medio Ambiente (Cofema) y el Ministerio de Ambiente de Nación. "No queremos que salga porque es una ley muy alineada al agronegocio, la ganadería intensiva y el negocio inmobiliario", afirmó Gorosito.</t>
   </si>
   <si>
     <t>Juan Grabois: "Nos vamos del bloque del Frente de Todos en Diputados"</t>
@@ -2159,7 +5556,25 @@
     <t>https://www.pagina12.com.ar/477750-juan-grabois-nos-vamos-del-bloque-del-frente-de-todos-en-dip</t>
   </si>
   <si>
-    <t>2022-08-31T03:01:00Z</t>
+    <t xml:space="preserve">Título: Juan Grabois: "Nos vamos del bloque del Frente de Todos en Diputados"
+Chapeau: Se quiebra el espacio oficialista en el Congreso
+Subtítulo: En diálogo con Página/12, el líder del Frente Patria Grande explicó que el Gobierno lo "defraudó y decepcionó”. Esta postura deberá ser ratificada en el congreso partidario del próximo domingo. Resta definir si formará parte o no de un interbloque.
+Editoria: El País
+Tags: Juan Grabois, Frente de Todos, Cámara de Diputados, printed-edition, juan-grabois, frente-de-todos, camara-de-diputados, diario
+URL: https://www.pagina12.com.ar/477750-juan-grabois-nos-vamos-del-bloque-del-frente-de-todos-en-dip/
+Notícia completa (12 blocos):
+El cambio de figuritas en el ministerio de Economía no alteró el discurso de Juan Grabois. Ante la salida de Martín Guzmán, el ingreso de Silvina Batakis y el recambio por Sergio Massa la postura fue siempre la misma. “No hablemos más de nombres, hablemos de medidas y tomémoslas”, repetía. A un mes del desembarco del líder de Frente Renovador en el Gabinete, el tiempo se agotó.
+[H3] Cristina Kirchner sobre la represión del sábado: "Los responsables son los mismos que en 2001"Los diálogos entre Bullrich y Larreta en un almuerzo en el infierno
+“Nos defraudaron y decepcionaron”, sintetizó el dirigente social Juan Grabois y confirmó a Página/12 que el Frente Patria Grande armará un bloque propio en el Congreso de la Nación. Esta postura deberá ser ratificada por la agrupación en el congreso partidario que se desarrollará el próximo 4 de septiembre en la Ciudad de Buenos Aires. Resta definir si formará parte o no de un interbloque con el oficialismo.
+“Nos vamos del bloque de Diputados y yo personalmente veré qué hago”, lanzó Grabois. Según el referente del Movimiento de Trabajadores Excluidos (MTE), desde el inicio de la gestión de Massa esperaron que el Ejecutivo cumpla con la promesa de medidas destinadas a los sectores más vulnerados y nunca se concretó. Incluso hubo conversaciones previas a la presentación del programa económico que, finalmente, tuvo como eje central anuncios de ajuste fiscal e incentivos para que el sector exportador liquide dólares: “Nos mintieron durante 25 días. Nos dijeron que iba a haber algo para los más pobres y no hubo nada”, sentenció.
+Las expresiones del líder del Frente Patria Grande llegaron luego de una intensa jornada que encontró una vez más a los movimientos sociales en la calle, reclamando que se implemente un Salario Básico Universal (SBU), y tras el anuncio del Gobierno de un refuerzo de 20 mil pesos por hijo en las asignaciones familiares de los hogares de menores ingresos. Respecto de la medida que abarca a un millón de familias, Grabois subrayó que le “alegra” que exista una medida distributiva, pero remarca que es insuficiente. “Se olvidaron, como siempre, de los que no tienen nada de nada, de los jóvenes abandonados, los indigentes, los sin tierra, techo ni trabajo”, enfatizó.
+Sin dar nombres, Grabois apuntó sus críticas directamente contra Alberto Fernández y Sergio Massa. Con respecto al Presidente, le cuestionó la falta de determinación para afectar los intereses de los sectores más poderosos. Sobre el ministro de Economía señaló sus vínculos con empresarios del sector energético y el establishment estadounidense. “Le va a dar todo a los dueños del litio, los hidrocarburos y el agronegocio. A los banqueros y grupos económicos”, resaltó, y concluyó: “En mi visión este gobierno va perdiendo su carácter popular y adoptando un carácter colonial”.
+Alejado por completo de la gran mayoría de los integrantes del Frente de Todos, el dirigente social remarcó que el sistema político argentino “está compuesto casi en su totalidad por gente mediocre e insensible” y sostuvo que antes de diciembre de 2019 muchos de los funcionarios de la coalición oficialista “estaban totalmente acabados” y fueron perdonados, rescatados y reciclados” por Cristina Kirchner.
+Los fuertes cuestionamientos del líder del Frente Patria Grande excluyeron a la vicepresidenta: “Cristina redujo la pobreza y la indigencia. Por eso la bancamos. Lo que no esperábamos era la conducta de otras personas que no voy a nombrar. Que nos pidieron tiempo y después le clavaron un puñal en la espalda a cuatro millones de indigentes. Si Cristina tiene alguna responsabilidad es por no sacarnos a los argentinos a esta casta infame de encima”.
+Bajo este escenario de tensión extrema, la agrupación que cuenta con tres diputados nacionales —Itai Hagman, Federico Fagioli y Natalia Zaracho— resolverá el próximo domingo armar un bloque propio en el Congreso Federal que tendrá lugar en el Centro Cultural Paco Urondo (CABA) y será de carácter privado. Además de los legisladores nacionales, serán parte del plenario la legisladora porteña Ofelia Fernández, la diputada de la provincia de Buenos Aires, Lucía Klug, concejales y referentes de 23 provincias del país.
+Hasta ayer por la mañana la idea era tomar distancia, pero no tanto. Es decir, diferenciarse internamente y formar parte de un interbloque. El anuncio de Massa junto a la titular de ANSES, Fernanda Raverta, aumentó el fastidio en Patria Grande que deberá decidir hasta dónde se aleja. Calculadora en mano, la presidenta de la Cámara de Diputados, Cecilia Moreau, y el jefe del bloque oficialista, Germán Martínez, tendrán que resolver cómo contener las fisuras en el oficialismo en un recinto marcado por la paridad de fuerza con la oposición.
+[H3] Seguí leyendo
+[H3] El cruce "buena onda" entre militantes y la vecina de Cristina KirchnerMiles de usuarios se bajaron del subsidio para comprar dólaresLa Justicia de Bolivia quiere que Mauricio Macri vaya a declarar por el envío de armas</t>
   </si>
   <si>
     <t>Sebastián Cazón</t>
@@ -2171,7 +5586,30 @@
     <t>https://www.pagina12.com.ar/476686-brasil-jair-bolsonaro-dijo-que-la-agroindustria-es-mas-impor</t>
   </si>
   <si>
-    <t>2022-08-26T19:36:05Z</t>
+    <t xml:space="preserve">Título: Brasil | Jair Bolsonaro dijo que la agroindustria es más importante que la protección de la Amazonía
+Subtítulo: El mandatario consideró que corre el riesgo de ser arrestado si no gana las elecciones de octubre
+Editoria: [NÃO ENCONTRADO]
+Tags: Jair Bolsonaro, Brasil, Elecciones, Elecciones Brasil 2022, jair-bolsonaro, elecciones-brasil-2022
+URL: https://www.pagina12.com.ar/476686-brasil-jair-bolsonaro-dijo-que-la-agroindustria-es-mas-impor/
+Notícia completa (18 blocos):
+El presidente brasileño, Jair Bolsonaro, en campaña por su reelección, afirmó este viernes que la agroindustria es más importante para "la seguridad alimentaria del mundo" que la protección de la Amazonía.
+"Hay algo más importante que la Amazonía en este momento, es nuestro agronegocio, que es seguridad alimentaria para el mundo", señaló durante una entrevista con el programa de televisión Joven Pan Pânico.
+El mandatario criticó la cantidad de solicitudes de demarcación de tierras indígenas que hay en los tribunales y dijo que Brasil "parece un cuerpo con varicela" si se "pinta" el territorio del país con todas las áreas que están protegidas en la Amazonía.
+"Hay cientos de solicitudes que están ahí en los juzgados", dijo el mandatario. "Eso es una fiesta. Si tomas un mapa de Brasil hoy en día y pintas estas áreas, parece un cuerpo con varicela. Nuestro Brasil ya no soporta las tierras indígenas. El hombre rural no lo admitirá más", aseguró.
+Para Bolsonaro, de aprobarse el plazo para la protección de las tierras indígenas sería "el fin de los agronegocios". Este sector es uno de los segmentos donde el presidente es más popular debido a medidas como la flexibilización de la tenencia de armas en las zonas rurales del país. "Si aparece un indígena en un pozo frente al Palacio de la Alvorada (residencia de la Presidencia brasileña), eso automáticamente se convierte en tierra indígena. Esa inseguridad se lleva al campo", sentenció.
+Durante el mandato de Bolsonaro, la destrucción de la selva tropical más grande del mundo se ha incrementado, alcanzando una deforestación histórica en el primer semestre de este año, la más alta jamás registrada: se perdieron 3.750 kilómetros cuadrados entre el 1° de enero y el 24 de junio, según datos del Instituto Nacional de Investigación Espacial de Brasil.
+[H2] Arrestado si es derrotado
+En otro momento de la entrevista, el jefe de Estado y candidato por el Partido Liberal (PL, derecha), aseguró que corre el riesgo de ser arrestado si no gana las elecciones de octubre, aunque no explicó el motivo, y mencionó una posible detención de uno de sus hijos, Carlos, por difundir noticias falsas.
+"Dentro de poco, uno de mis hijos será arrestado por noticias falsas, ya que Carlos es el objetivo todo el tiempo. No tiene sentido", aseguró.
+Carlos, apodado "el pitbull de Bolsonaro", es uno de los tres hijos del mandatario ultraderechista dedicados a la política, junto con Flavio, que es senador, y Eduardo, que es diputado. Además, es el administrador de la comunicación en las redes sociales de su padre.
+El Tribunal Supremo lo investiga por supuestamente ser el líder de una organización criminal que se vale de noticias falsas para presionar a los magistrados de la Corte.
+El mandatario también criticó al juez del Tribunal Supremo, Alexandre de Moraes, por la operación de la Policía Federal contra empresarios que defendieron ideas golpistas si perdía las elecciones. "¿Qué ha hecho falta para detener a estos ocho empresarios? Nada", criticó.
+Moraes ordenó esta semana que la Policía Federal tome los testimonios a los empresarios bolsonaristas sospechosos, el bloqueo de sus cuentas en las redes sociales y la ruptura del secreto bancario.
+[H2] Moro, el candidato a vice que no fue
+En otro tramo de la entrevista, Bolsonaro dijo que el exministro de Justicia y Seguridad Pública Sergio Moro, quien renunció en abril de 2020, podría haber sido su compañero de fórmula en la reelección si se hubiera mantenido "de buen humor".
+Bolsonaro declaró que consideraba que "el poder se le subió a la cabeza a Moro".
+Sobre su futuro gabinete si es reelecto, el mandatario solamente confirmó la continuidad de Paulo Guedes como ministro de Economía, y ensalzó su lealtad como punto fundamental en su relación. "Su lealtad hacia mí y la mía hacia él. Eso es lo más importante", mencionó.
+El último sondeo divulgado esta semana por la agencia FSB indica que el líder izquierdista Luiz Inácio Lula da Silva tiene el 45% de intenciones de voto frente al 36% de Bolsonaro.</t>
   </si>
   <si>
     <t>Juca Ferreira, exministro de Lula: “La derecha trabaja para un olvido de toda la riqueza cultural de Brasil”</t>
@@ -2183,7 +5621,29 @@
     <t>https://www.pagina12.com.ar/475148-juca-ferreira-exministro-de-lula-la-derecha-trabaja-para-un-</t>
   </si>
   <si>
-    <t>2022-08-22T03:01:00Z</t>
+    <t xml:space="preserve">Título: Juca Ferreira, exministro de Lula: “La derecha trabaja para un olvido de toda la riqueza cultural de Brasil”
+Chapeau: Crisis cultural, social y ambiental
+Subtítulo: El sociólogo afirma que el candidato del PT sabe que precisará destinar más presupuesto para retomar con fuerza las políticas culturales que se desarrollaron durante sus gobiernos.
+Editoria: El Mundo
+Tags: Brasil, Luiz Inácio Lula da Silva, Jair Bolsonaro, printed-edition, luiz-inacio-lula-da-silva, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/475148-juca-ferreira-exministro-de-lula-la-derecha-trabaja-para-un-/
+Notícia completa (16 blocos):
+A menos de dos meses de que casi 150 millones de brasileños y brasileñas vayan a votar para elegir presidente, vicepresidente, gobernadores y legisladores, conversamos con el sociólogo Juca Ferreira, quien se desempeñó como ministro de Cultura durante los gobiernos de Lula Da Silva y Dilma Rousseff.
+Juca Ferreira habla aquí acerca de la crisis social, cultural y ambiental que atraviesa Brasil; la resistencia a Bolsonaro que expresa el sector artístico y el pueblo en general; los movimientos sociales que emergieron desde la destitución de Dilma y el desafío de retomar las políticas culturales iniciadas en el gobierno de Lula para la construcción de una democracia plural, a partir de la memoria, los saberes y la diversidad cultural del pueblo brasilero.
+--“En Brasil, ser mujer negra es resistir y sobrevivir todo el tiempo”. La frase es de Marielle Franco, concejala de Río de Janeiro, feminista y afrodescendiente, brutalmente asesinada en 2018. Desde la destitución de Dilma en 2016, creció gravemente la violencia y proliferaron los discursos de odio en Brasil. ¿Qué impacto ha tenido esto sobre la democracia y el tejido social?
+--Estamos viviendo una de las peores crisis de la historia republicana brasileña. La destitución de Dilma fue una forma contemporánea de golpe de Estado, basada en el lawfare. No fueron los militares los encargados de interrumpir el proceso democrático sino los jueces, los parlamentarios y los medios, con mucha simpatía de las clases medias. ¿Por qué interrumpieron la democracia que estaba comenzando a construirse en Brasil? Porque las élites brasileñas no aceptan ningún mecanismo de distribución de rentas que disminuya la desigualdad social de Brasil, que está entre las tres mayores del mundo.
+Más de 30 millones de personas están pasando hambre en Brasil. La economía brasileña está cayendo. El desempleo es muy alto y el salario se ha desvalorizado. Estamos viviendo un proceso de retroceso de conquistas sociales, algunas incluso que vienen del gobierno de Getúlio Vargas. Bolsonaro está destruyendo las estructuras institucionales, ha vulgarizado y degradado todo el Estado brasileño. La violencia recrudeció: así como sucedió con Marielle Franco, muchos líderes populares, indígenas, campesinos y de movimientos sociales están siendo asesinados en Brasil. La policía aumentó de modo notable su agresividad, especialmente en las periferias de las grandes ciudades brasileñas, donde cada acción acaba con personas asesinadas. Bolsonaro está estimulando el armamento de la población y de las milicias. Vamos a tener una elección donde Lula representa la democracia y un proyecto inclusivo y popular, y Bolsonaro representa la profundización de la irracionalidad, la desigualdad y el quiebre de nuestra soberanía. Afortunadamente, hoy todas las encuestas señalan que gana Lula.
+--En el último tiempo, distintos artistas, y el pueblo en general, empezaron a expresar públicamente su descontento con Bolsonaro. En el último disco de Caetano Veloso hay una canción que dice: “No voy a dejar que jodas con nuestra historia. Es mucho amor, es mucha lucha, es mucho goce, es mucho dolor y mucha gloria. No te voy a dejar porque sé cantar”. ¿Comparte esta fe en el arte y en la cultura como espacios de resistencia y reconstrucción?
+--La cultura cumple un rol muy importante en este momento. Casi toda el área cultural está haciendo resistencia a Bolsonaro y apoyando a Lula. La música, el teatro, la danza, las manifestaciones tradicionales, y los pueblos indígenas se están expresando en este sentido. Hay una impaciencia del pueblo brasileño con todo lo que se está viviendo. Bolsonaro defiende abiertamente la discriminación contra los negros, los homosexuales, la desigualdad y el desprecio hacia las mujeres. Llegamos a un momento de ruptura. Por primera vez, todos comprendemos que es necesaria una afirmación de valores colectivos, de justicia social, de igualdad, de respeto al ser humano y sus derechos. Esa disputa de valores es una lucha que se da en el campo cultural.
+--¿Cuál cree que será el trabajo a realizar desde el Estado, en términos de políticas culturales, para acompañar estas expresiones y reafirmar estos valores? Tomando la metáfora de Gilberto Gil de la gestión cultural como una acupuntura antropológica, ¿qué puntos del cuerpo cultural del país habrá que estimular?
+--En la cultura no podés privilegiar un punto sobre otro, tenemos que trabajar el conjunto. La salud, en un concepto holístico, comprende el cuerpo humano como un sistema, en su globalidad, y la cultura es similar. La derecha quiere un país sin base cultural, sin referencias, está trabajando para un olvido de toda la riqueza y la diversidad cultural de Brasil porque sabe que ahí tiene sus raíces el deseo de libertad. La cultura brasileña nunca pudo ser domesticada, aquí el capitalismo no funcionó muy bien. Tenemos matrices culturales que persisten con mucha fuerza: las de los pueblos originarios, otras que llegaron de África, las de los portugueses. Necesitamos trabajar con esa memoria y diversidad cultural, desde los grupos contemporáneos de cultura hasta las manifestaciones tradicionales, para empoderar a la sociedad y fortalecer los vínculos y sentimientos de pertenencia. Es necesario también propiciar condiciones favorables para el desarrollo de las artes, formar un ambiente de libertad de expresión absoluta y estimular la creación. Para eso, vamos a tener que invertir en formación. En el arte de Brasil sucede lo mismo que en el fútbol: es un extractivismo permanente del talento y de la capacidad del pueblo brasileño. Por lo tanto, es importante constituir sistemas de formación y circuitos donde todos tengan posibilidad de ascenso y desarrollo de sus capacidades.
+Lula sabe que precisará destinar más presupuesto para retomar con fuerza las políticas culturales que veníamos desarrollando durante sus gobiernos y abordar nuevos temas, como el acceso a internet y la cultura digital. Internet es también una herramienta cultural y comunicacional muy poderosa.
+-- ¿Brasil está muy lejos de ser un país en el que los pueblos originarios y los afrodescendientes tengan voz propia en el sistema político, así como está sucediendo en países como Bolivia o Colombia?
+--Las comunidades indígenas de Brasil están muy activas, quieren tener una bancada que los represente en la próxima Legislatura del Congreso. Ante tantas bancadas negativas -la bancada de la bala (de los armamentistas), la del agronegocio, la de la motosierra- los indígenas están avanzando en la idea de tener la bancada do cocar, integrada por parlamentarios indígenas. Es una idea muy importante para la construcción de la pluralidad cultural y étnica. Y no quieren hablar solamente de sus intereses, ellos dicen que quieren defender las selvas, el aire, los ríos, los animales y proponer otras maneras de vivir.
+Hay diferencias enormes en las estructuras sociales de países como Bolivia y Brasil, en relación a los pueblos originarios. En Brasil el exterminio de los pueblos originarios fue gigantesco. Darcy Ribeiro decía que hay algunos tipos de sociedades que emergieron de la colonización de América, fruto de un amalgamiento de matrices culturales: ese es el caso de Brasil. Aquí la complejidad social es muy grande. A esto se suma que, desde la destitución de Dilma, emergieron muchos movimientos: sociales, identitarios, emancipatorios, de sectores indígenas, LGBTIQ+, de mujeres y de poblaciones negras. La izquierda tradicional está un poco desconcertada porque hay un deslizamiento, una multiplicidad, y pareciera que cada grupo aborda únicamente sus demandas y programas particulares, pero no es así. Sus luchas amplían y fortalecen la democracia brasileña. Lula está hablando de la necesidad de comprender que Brasil cambió muchísimo con la emergencia de estas demandas y que es necesario estructurar una democracia que contenga esta complejidad, para tener un país plural.
+--“La sociedad brasileña es una sociedad constituida sobre la idea de la extracción infinita de los recursos (...) La cuestión ambiental es una cuestión de sensibilidad, de visión del mundo y de comportamiento humano. Por lo tanto, es una cuestión del mundo de la cultura”. En un libro que reúne artículos y discursos suyos, editado en Argentina por RGC, encontré este fragmento y me llamó la atención que, 15 años atrás, ya estuviera hablando de la cuestión medioambiental en relación con la cultura. ¿Cree que hay un punto de equilibrio posible entre desarrollo económico, inclusión y cuidado medioambiental?
+--La problemática ambiental es otra cuestión que emergió en Brasil. No hay posibilidad de mantener el modelo predatorio que vivimos desde la colonización. Están destruyendo la Amazonía y esa destrucción está cambiando el clima de todo el territorio brasileño y de los países vecinos. Hay una importante reducción de especies animales y vegetales. Brasil tiene entre el 15% y el 17% del agua potable del planeta. Esa reserva se está reduciendo por contaminación, por destrucción de los ríos y de las selvas. Ya hay regiones en Brasil que tienen desiertos, fruto de la producción de soja y el agronegocio. Este modelo nos está saliendo muy caro. La infestación con cáncer, en Brasil, está alcanzando a muchas personas, en sectores pobres y en las clases medias, porque no tiene que ver sólo con el estilo de vida: el aire, el agua, los alimentos, todo está contaminado. El agronegocio logró aprobar, durante el período de Temer y Bolsonaro, más de 200 nuevos venenos para utilizar en la agricultura brasileña, algunos que están prohibidos en el mundo entero. No es posible mantener esa usura institucional y corporativa. Es necesario revertir este modelo.
+Claro que implica aspectos técnicos, científicos, pero hay una necesidad de tomar conciencia sobre este problema y que el desarrollo beneficie a todos los seres humanos, garantizando la preservación ambiental, y eso es también una cuestión cultural. Espero que Lula logre introducir la cuestión medioambiental como un paradigma central de gobierno, tan importante como la reducción de la desigualdad y la pobreza, como el respeto de la diversidad cultural. El futuro tiene que tener memoria, tiene que incorporar el conocimiento del medioambiente que tienen los pueblos originarios y sus maneras de relacionarse con el planeta. Concebir el equilibrio ambiental y la sustentabilidad como paradigmas centrales nos ayuda a profundizar la crítica, a tomar conciencia de la gravedad de la destrucción, y a no aceptar el lucro y la acumulación como razón social, como único modo de vida. Ese es el futuro hacia el que queremos caminar.</t>
   </si>
   <si>
     <t>Juan Ignacio Muñoz</t>
@@ -2198,7 +5658,38 @@
     <t>https://www.pagina12.com.ar/475057-jones-tamayo-kairuz-y-blaquier-tienen-la-informacion-que-ret</t>
   </si>
   <si>
-    <t>2022-08-21T05:36:21Z</t>
+    <t xml:space="preserve">Título: "Jones Tamayo, Kairuz y Blaquier tienen la información que retienen y niegan"
+Chapeau: Jujuy: alegato de la querella por Luiz Aredez
+Subtítulo: El abogado Oscar Rodríguez pidió al Tribunal que aplique la figura de desaparición forzada y pidió condenas de 40 años de prisión para el militar Juan Carlos Jones Tamayo y de 20 años para el ex policía Juan de la Cruz Kairuz. E insistió en la responsabilidad del dueño del ingenio Ledesma.
+Editoria: Salta|12
+Tags: Jujuy, Juicio de lesa humanidad, juicio-de-lesa-humanidad, diario
+URL: https://www.pagina12.com.ar/475057-jones-tamayo-kairuz-y-blaquier-tienen-la-informacion-que-ret/
+Notícia completa (25 blocos):
+La desaparición de Luis Ramón Aredez es un delito de carácter permanente, ya que al día de hoy se desconoce su paradero. Y por otro lado, hay seguridad de que "Juan Carlos Jones Tamayo, Juan de la Cruz Kairuz y Pedro Tadeo Blaquier tienen la información, que retienen y niegan", aseguró el abogado Oscar Rodríguez, en su alegato en la continuidad del sexto juicio por delitos de lesa humanidad que se lleva a cabo en Jujuy.
+Rodríguez concluyó su exposición el pasado jueves, en representación de la querella de Teresa Adriana Aredez, hija de Luis Aredez. El abogado pidió al Tribunal Oral en lo Federal de Jujuy que considere estos hechos bajo la lupa del derecho internacional y que la desaparición del médico del ingenio Ledesma y ex intendente de Libertador General San Martín sea calificada como desaparición forzada. Y que Jones Tamayo, que fue jefe de la Central de Inteligencia Area 323, y Kairuz, que fue oficial auxiliar de la Policía de Jujuy, reciban "máxima condena". Sostuvo que está probado que hubo un plan sistemático represivo, donde cada autor individual fue parte de un colectivo criminal y hubo "coautoría común".
+"Es un delito de carácter permanente" que "aún hoy se sigue cometiendo". Aredez está desaparecido, sus familiares no tienen información de su destino, mientras que "los aparatos represivos que funcionaron en ese momento, y que todavía funcionan en algunas de sus particularidades, saben donde está", sostuvo Rodríguez. Contó que Adriana Aredez cree que el médico está en Guerrero, "en el centro clandestino donde habría sido quemado vivo y que al menos uno de los autores sería Jones Tamayo".
+"Lo que no tengo duda es que Jones Tamayo lo ha de saber, y que toda la inteligencia lo ha de saber". "Y el que debe saber también donde está (Aredez) es el señor Pedro Tadeo Blaquier", afirmó el abogado.
+También pidió que se forme un legajo por separado para investigar a Blaquier por la desaparición de Aredez, el 13 de mayo de 1977.
+Rodríguez aclaró que hacía un alegato "bifronte". Por un lado, adhirió a los dichos de la fiscalía, que pidió condenas para Jones Tamayo y Kairuz por allanamiento y privación ilegal de la libertad en relación a Luis Aredez, porque aquí se los juzga solo por su primera detención, el 24 de mayo de 1976 (aunque Jones Tamayo suma otros crímenes, entre ellos 15 homicidios). En este caso, el querellante pidió una pena de 21 años para Jones Tamayo y de 8 para Kairuz.
+Por otro lado, adelantó que acusaría por desaparición forzada y por utilizaría "los cánones del derecho internacional". En este caso pidió 40 años de prisión para Jones Tamayo y 20 para Kairuz y centró su alegato en explicar esta solicitud. Argumentó que los crímenes objeto de este juicio están comprendidos en las clásicas figuras penales del Tribunal de Nuremberg, que trata casos de trascendencia de la comunidad internacional, como los crímenes de genocidio, de lesa humanidad, de guerra, de agresión.
+Entre los crímenes de lesa humanidad, recordó que se cuentan el asesinato, el encarcelamiento u otra forma de privación grave de la libertad física en violación de normas fundamentales del derecho internacional, la tortura, la violación, figuras que se vieron en este proceso. Así como la "persecución de un grupo o colectividad con identidad propia fundada por motivos políticos, éticos, raciales, religiosos, que también lo tenemos acá, son universalmente reconocidos como inaceptables" en conexión, por ejemplo, con desaparición forzada, que se da en este caso.
+En ese contexto el abogado habló de "macrocriminalidad", que se diferencia de otras formas de criminalidad por "las condiciones políticas de excepción" y el "rol activo" que desempeña el Estado. Macrocriminalidad política significa "criminalidad fortalecida por el Estado, crimen colectivo políticamente condicionado, crimen de Estado, terrorismo de Estado o criminalidad gubernamental”.
+Se trata de juzgar actividades delictivas individuales en un contexto de conducta colectiva, crímenes de masa, explicó, y mencionó a varios autores para poner de relieve "la ilegitimidad" de un tratamiento que "ignore la dimensión extraordinaria" de estos hechos.
+Recordó los crímenes del nazismo, donde "Los imputados eran la clase dirigente de la conducción de ese Estado", para plantear el problema de cómo aislar el aporte individual en el resultado colectivo, en lo que el derecho nacional encuentra un límite. "Siempre estamos en la necesidad de considerar el elemento colectivo, al estado y los delincuentes en tanto funcionarios de ese estado", a la filosofía de este Estado y a "los delitos que no son otra cosa que la expresón de esa filosofía, con lo que se delata claramente la asunción plena de todas las consecuencias".
+[H2] Saben que son delincuentes
+El querellante aseguró que en el aporte individual "se denota claramente la asunción plena de todas las consecuencias", es decir que las personas que cometieron, que siguen cometiendo, estos crímenes "Saben que son delincuentes de una macrocriminalidad delincuencial, saben lo que prosigue". "Todo aquel que hizo el aporte sabía el recorrido que venía inclusive la posibilidad de la eliminación de la persona, no hay aportes individuales a secas en el marco de la macrocriminalidad. El dolo en todo su plenitud, la plena conciencia de estar inmerso en un aparato organizado del poder". "El pleno conocimiento de estar inmerso en el mismo estado productor de delitos y de la clandestinidad".
+"Nos quedamos en una privación ilegal" cuando esta figura "no tiene sustancia, no tiene capacidad explicativa, no tiene consistencia como figura penal", cuestionó. Dijo que ese mecanismo que se repite responde a las facetas del sistema que pujan por lograr la impunibilidad, algo que las querellas tienen que plantearlo "a los fines de que esa mirada sesgada, parcial y forzosamente simplificadora de una realidad compleja no se vea reflejada en algunas sentencias".
+E insistió en que "Para encuadrar correctamente la responsabilidad individual de cada uno de los imputados, sobre todo en su verdadera dimensión histórica, es preciso señalar que el accionar de cada uno de ellos se ha desarrollado en el marco de un aparato organizado de poder conformado desde el Estado, por la dictadura militar, en un contexto colectivo, generalizado y sistemático de criminalidad desatada desde el estado, en particular desde la organización criminal fortalecida por el estado". En el caso de Jujuy, "constituida por Blaquier" y los acusados en este debate, que "constituyeron un eslabón dentro de ese aparato organizado para ser una suborganización, la empresa criminal conjunta fue nacional, pero hubo sub-empresas criminales conjuntas en cada una de las provincias".
+La empresa criminal conjunta implica que "hay un plan común de cometer delitos" por eso hay que hablar de coautoría común, porque fue un plan sistemático de exterminio. La coautoría supone una parte esencial en la ejecución del hecho y en las acciones siguientes. Todos los intervinientes coincidían en el dolo, en la voluntad de cometer el delito sabiendo del daño provocaban, y sabían sus consecuencias. "Han sabido del plan sistemático, tanto han sabido que se cobijaban, tanto sabían que buscaban impunidad y tanto sabían, que lo promovían, cuando hacían inteligencia".
+Jones Tamayo fue el gestor de la inteligencia en Jujuy. Y está probado que Kairuz hizo inteligencia en varias ocasiones contra la familia Aredez. "Evidentemente estaba adscrito al plan común y lo hacía con total voluntad". "Kairuz era el que movía los dedos, el rango lo tiene Blaquier y lo tiene Lemos", afirmó Rodríguez.
+El querellante sostuvo que ya en la primera detención Aredez sufrió desaparición forzada. Y calificó de "una profunda injusticia (...) subsumir la desaparición forzada en la privación de la libertad", dado que "la privación ilegal de la libertad es un tramo de la desaparición forzada". En cambio, "el tipo penal desaparición es el que atrapa la conducta delictiva en su verdadera dimensión, optamos por la figura por un principio de realidad que tiene reconocimiento constitucional".
+Respecto de Kairuz, ratificó que "no podía dejar de saber" que Aredez sería torturado en el penal de Gorriti, donde fue víctima de simulacros de fusilamiento, y bajó de peso de una forma ostensible, y donde a pesar de sus pésimas condiciones "se transformó en el padre de otros detenidos".
+Y como fue un plan sistemático que se aplicó en todo el país, las personas detenidas, estuvieran donde estuvieran fueron "torturadas", "bien sabían ellos de qué se trataba", insistió. Recordó que la primera vez el médico fue liberado porque intercedió el líder radical Ricardo Balbín, "pero no se lo perdonan" y después "el aparato organizado lo hace desaparecer".
+[H2] Los mismos procedimientos
+Al comenzar su alegato, Rodríguez señaló que “estos son juicios al poder de ayer, al de hoy y al del futuro”; tras señalar que funcionan a modo de espejo, reflejando el poder de las clases acomodadas y privilegiadas, y representan una interpelación directa a las relaciones de poder en la Argentina.
+Además de homenajear a Olga Márquez de Aredez, la viuda de Luis Aredez, compartió un escrito de Adriana Aredez en el que se describe que el médico era “conocido por su coraje, compromiso, entrega a la salud pública y lucha por los trabajadores más desprotegidos “, y pidió que “los genocidas pasen todos los días que les restan en prisión por la barbarie de los delitos de genocidio y lesa humanidad cometidos”.
+En el cierre el abogado destacó que "las grandes empresas, el capitalismo en su cara más feroz cuando ve peligrar o decaer algunos de los privilegios recurre a una forma desencajada delictiva y delictiva". Por eso las sentencias, "que son actos de gobierno", son tan importantes "Porque el empresariado descarado de hoy en día también continúa con ese tipo de actitud".
+"Por eso es interesante que las sentencias tengan esa mirada social y política y no se queden en el pequeño artículo del Código Penal", sostuvo antes de contar que en el norte del país "el empresario voraz con el agronegocio se apodera de las tierras campesinas e indígenas con el mismo proceder". "Veo una continuidad histórica política de un determinado sector social que es el que hemos tratado de enjuiciar en este proceso". "Esto es lo que hacía, mucho mayormente, Blaquier en Jujuy", resaltó tras pedirle al Tribunal que dicte una sentencia que transmita a ese empresariado: "Queremos paz".</t>
   </si>
   <si>
     <t>Elena Corvalan</t>
@@ -2210,7 +5701,23 @@
     <t>https://www.pagina12.com.ar/474814-la-sociedad-rural-y-los-pueblos-indigenas-150-anos-igual</t>
   </si>
   <si>
-    <t>2022-08-19T21:59:53Z</t>
+    <t xml:space="preserve">Título: La Sociedad Rural y los pueblos indígenas: 150 años igual
+Subtítulo: El presidente de la Sociedad Rural, Nicolás Pino, afirmó en su discurso en el predio de la “Rural”, en la apertura de la célebre “Exposición” el pasado 30 de julio: "No solo en la
+Editoria: El País
+Tags: pueblos originarios, Sociedad Rural, Opinión, pueblos-originarios, sociedad-rural, opinion, diario
+URL: https://www.pagina12.com.ar/474814-la-sociedad-rural-y-los-pueblos-indigenas-150-anos-igual/
+Notícia completa (11 blocos):
+El presidente de la Sociedad Rural, Nicolás Pino, afirmó en su discurso en el predio de la “Rural”, en la apertura de la célebre “Exposición” el pasado 30 de julio: "No solo en la Patagonia y otras zonas del país, el Gobierno y la Justicia se han mostrado indiferentes a los ataques contra los propietarios y el personal, delitos perpetrados bajo el pretexto de reivindicaciones de quienes se autodenominan pueblos originarios, siendo simplemente delincuentes comunes...".
+Las afirmaciones vertidas por el presidente de SRA reflejan una supina ignorancia, una profunda carencia de honestidad intelectual (o una particular conjunción de ambas cosas). Más allá de si se debe a una cosa u otra, lo que queda claro es la intencionalidad política y económica del discurso.
+La estigmatización hacia los pueblos indígenas —en especial al pueblo mapuche— y la forma en la que se estructuran estos discursos resulta sumamente grave, ya que pone un manto de duda sobre el conjunto de las demandas y los derechos consagrados en todo el marco normativo, asimilándolos con acciones delictivas. Claramente lo que busca además el discurso es acusar al gobierno de inacción o inactividad frente a hechos de violencia o incluso la complicidad o vinculación con dichos delitos.
+Manifestaciones como las del presidente de la Sociedad Rural tienen por objetivo intereses muy claros que responden al sector más concentrado del agro, representado por la Sociedad Rural Argentina, y que tienden a construir un sentido en la opinión pública, más aún en un contexto de crisis y de lucha por la puja redistributiva. El trasfondo de la estigmatización y criminalización de los pueblos indígenas es sin ninguna duda el interés por los territorios ancestrales por parte de diversos emprendimientos privados, grandes propietarios argentinos y extranjeros.
+Los hechos delictivos que se han difundido en las últimas semanas en Patagonia no poseen relación con los pueblos originarios. Algunas características (como algunos términos utilizados en un volante difundido luego de un episodio de violencia atribuido a un supuesto grupo mapuche) evidencia que se trata de “montajes” y que desde ya nada tienen que ver con las reivindicaciones históricas de los pueblos originarios y la forma como se han construido consensos y diálogos con la sociedad no indígena a lo largo de décadas.
+En estas declaraciones la Sociedad Rural (en adelante SRA) se constituye como un supuesto representante de "el campo", visualizado en forma homogénea y sin fisuras hacia el interior de un heterogéneo sector, cuando es la expresión del sector más concentrado y por lo tanto minoritario.
+El discurso por otro lado contiene una serie de datos increíblemente distorsionados en cuanto al aporte del “campo” en términos de creación de empleo, lo que tributan realmente las conocidas “retenciones” (derechos de exportación) al conjunto de los ingresos del Estado, los ingresos de divisas extranjeras, etc. Desde ya, su discurso omite un montón de hechos largamente conocidos y documentados. Uno de ellos es la gigantesca evasión tributaria de los sectores más concentrados del agro. El otro dato es el grado de precarización laboral e informalidad de los trabajadores rurales, con situaciones de semiesclavitud o esclavitud. Otro aspecto, tan grave como los anteriores, es el nivel de contaminación ambiental con serias consecuencias sociales que conlleva la expansión del agronegocio y la producción de commodities. De hecho, el segundo foco de deforestación de América del Sur (precisamente para la expansión de cultivos como la soja), después del Amazonas, es la región chaqueña. En algunos pueblos originarios de dicha zona -como el wichí, el guaraní y otros- las consecuencias son verdaderamente dramáticas.
+El objetivo del líder empresarial se presenta bastante claro: desgastar al máximo al gobierno nacional. Sobre el eje de la economía, basó sus reclamos sobre dos puntos centrales para las aspiraciones del complejo agroexportador. Por un lado, producir una devaluación que les permita aumentar sus ingresos al liquidar la cosecha, y por el otro la eliminación de los derechos de importación disminuyendo así su carga tributaria. Los extraordinarios márgenes de ganancia obtenidos a partir de la configuración del nuevo escenario internacional que dispararon al alza los precios de los commodities no disminuyeron en nada la inmensa codicia del sector que se apropia con suma facilidad una renta extraordinaria. El descalce entre los precios nacionales e internacionales impulsa con fuerza la puja distributiva que se manifiesta en los índices inflacionarios, dinámica en la cual los sectores populares han salido tremendamente perjudicados.
+Para finalizar, Pino habla en nombre de su “argentinidad”, pero construyendo diversas fronteras dentro de la nación argentina. En estos procesos de profunda estigmatización, quienes pagan las consecuencias son quienes poseen una posición desventajosa, no sólo en términos socioeconómicos, sino también socioculturales, como son los pueblos originarios (junto a otros sectores) y en particular las mujeres indígenas por ser triplemente discriminadas: por mujeres, por indígenas y por empobrecidas. Por ello, en la medida en que más se vulneran los derechos colectivos de los pueblos indígenas, ellas ven más socavados sus derechos.
+No está de más recordar la gigantesca reserva de granos que al momento de escribir estas líneas están almacenados en “silobolsas”, y que el sector al cual representa la SRA se niega a liquidar y que resultan fundamentales para el ingreso de divisas para hacer frente a la acuciante situación económica. En definitiva, utilizando un término largamente conocido por argentinas y argentinos, resultan fundamentales para “pasar el invierno”.
+* Alejandro Balazote, Alejandra Pérez y Sebastián Valverde son profesores e investigadores de la Facultad de Filosofía y Letras de la UBA, UNAJ, UNLu y Conicet.</t>
   </si>
   <si>
     <t>Alejandro Balazote, Alejandra Pérez y Sebastián Valverde</t>
@@ -2225,7 +5732,26 @@
     <t>https://www.pagina12.com.ar/474190-zelenski-le-pidio-a-america-latina-que-disemine-la-verdad-so</t>
   </si>
   <si>
-    <t>2022-08-18T03:01:00Z</t>
+    <t xml:space="preserve">Título: Zelenski le pidió a América latina que "disemine la verdad" sobre el conflicto en Ucrania
+Chapeau: El mandatario ucraniano se dirigió por primera vez a los países de la región
+Subtítulo: Desde Kiev, el mandatario disertó por videoconferencia en una actividad organizada por la Universidad Católica (UC) de Chile.
+Editoria: El Mundo
+Tags: Volodimir Zelenski, Chile, Gabriel Boric, Conflicto Rusia Ucrania, printed-edition, volodimir-zelenski, gabriel-boric, conflicto-rusia-ucrania, diario
+URL: https://www.pagina12.com.ar/474190-zelenski-le-pidio-a-america-latina-que-disemine-la-verdad-so/
+Notícia completa (13 blocos):
+Dirigiéndose por primera vez a América latina, el presidente de Ucrania, Volodimir Zelenski, pidió este miércoles a los países de la región que "diseminen la verdad" sobre el conflicto con Rusia y corten las relaciones comerciales con Moscú, al disertar por videoconferencia en una actividad organizada por la Universidad Católica (UC) de Chile. Zelenski insistió en denunciar la postura rusa y le pidió a los jóvenes latinoamericanos que visiten su país y lo ayuden a reconstruirlo. El presidente Gabriel Boric, que fue invitado a la conferencia pero no se hizo presente, ya había prometido ayuda humanitaria para el pueblo ucraniano y, en un contacto telefónico con Zelenski en julio, le aseguró que Kiev "tiene un amigo en América del Sur".
+[H2] "No mantengan comercio con Rusia"
+"Pido que diseminen la verdad sobre esta guerra en su país y en su región. Tenemos que confrontar a la propaganda rusa, exigir la responsabilidad completa para los asesinos y criminales de guerra. Deben ser condenados por una justicia competente, se deben apoyar las sanciones contra Rusia para que pague el precio máximo por la agresión", afirmó Zelenski en teleconferencia desde Kiev.
+Uno de los periodistas presentes en la sede de la UC insistió en ese punto y le preguntó al mandatario ucraniano cómo deberían pararse los países latinoamericanos frente al conflicto. "No mantengan comercio con Rusia, para que ellos entiendan que se paga un alto precio", aseguró Zelenski según la traducción simultánea del ucraniano al español, y agregó: "Rusia tiene que pagar un alto precio. Entendemos que vivimos en un mundo moderno y los instrumentos que existen para ayudarnos tienen que ser civilizados y democráticos, pero deben ser rígidos. En primer lugar, cesar cualquier comercio con ellos".
+El presidente destacó que ya hay países que eligieron regiones o ciudades ucranianas para enviar a sus jóvenes con equipamiento para reconstruir colegios y universidades destruidos por el conflicto bélico. "Los países de Latinoamérica pueden hacer lo mismo. Elijan una ciudad que les guste y por favor vengan a visitarnos", detalló Zelenski. En esa línea el rector de la UC, Ignacio Sánchez, explicó que un grupo de profesionales está colaborando en un proyecto para reconstruir la ciudad de Irpin, ubicada a ocho kilómetros de Kiev, la capital del país.
+[H2] "No queremos vivir cerca de ellos"
+En la audiencia realizada ante decenas de académicos y medios locales, Zelenski dijo que la guerra con Rusia se extiende más allá de la invasión iniciada el 24 de febrero. "Cuando hablamos de la guerra de Rusia contra Ucrania hablamos de ocho años más 175 días. Cuando hablamos de las víctimas de esta guerra, no empezamos en febrero de 2022 sino en 2014, cuando empezaron a matar ucranianos por ser ucranianos", dijo la exestrella televisiva aludiendo al inicio del conflicto en los territorios separatistas de Donetsk y Lugansk, en el este de Ucrania.
+Al ser consultado sobre el voto popular favorable a la autodeterminación en la región del Donbass en mayo de 2014, Zelenski indicó que Ucrania es "un Estado unitario que hace 30 años tuvo un referéndum en el que el 94 por ciento de la población votó por la independencia", un número mayor que en cualquier otra exrepública de la Unión Soviética. En contraste, "Lo del Donbass no fue ningún referéndum. Entró la gente con fusiles, mataron, eliminaron a todos los representantes de nuestro gobierno. ¿Qué tiene de referéndum eso?", sostuvo el presidente ucraniano.
+[H2] La relación entre Chile y Ucrania
+La videoconferencia fue organizada por la UC y transmitida en vivo por Emol y el Grupo de Diarios América, una alianza de diarios de la región de la que El Mercurio es socio fundador. El presidente Gabriel Boric y la ministra de Relaciones Exteriores, Antonia Urrejola, fueron invitados pero alegaron problemas de agenda y no participaron.
+El gobierno de Boric ha reiterado su apoyo al pueblo ucraniano en más de una ocasión. La más recordada fue en julio, cuando se comunicó con Zelenski a raíz de un supuesto ataque ruso que dejó 18 víctimas fatales en un edificio residencial de la ciudad de Odesa. Ucrania "puede contar con el apoyo de Chile en temas humanitarios (...) tiene un amigo en América del Sur, tanto ahora como cuando termine la guerra", apuntó Boric en aquella ocasión. Zelenski le agradeció el gesto y aseguró que debatieron la posibilidad de involucrar a especialistas chilenos en territorios de desminado.
+A principios de junio, una propuesta del Partido Republicano chileno para que Zelenski hablara ante el Congreso no tuvo unanimidad por la oposición del Partido Comunista. "No hay que confundirse que las relaciones exteriores es una materia que la lleva el presidente de la República. Nos parece que no es apropiado, que no es adecuado y ojalá los comités mediten esta situación, los distintos partidos, y no se le dé apoyo a una medida que a mi parecer es absolutamente irresponsable", dijo el senador comunista Daniel Núñez al justificar su oposición.
+Semanas atrás los países del Mercosur (Argentina, Brasil, Paraguay y Uruguay) rechazaron darle la palabra al líder ucraniano durante una cumbre del bloque en Asunción, por no haber consenso sobre su pedido de participación. Poco antes de sostener un contacto con su par ucraniano, el presidente de Brasil, Jair Bolsonaro, anunció que iba a proponerle lo que él llamó "la solución Malvinas", pretendiendo aportar una salida, que nunca explicó, al conflicto armado con Rusia. Bolsonaro, que depende en gran medida de la provisión de fertilizantes rusos para el agronegocio brasileño, se ha negado a apoyar las duras sanciones económicas contra Moscú impulsadas por la OTAN.</t>
   </si>
   <si>
     <t>Humo en Rosario: nueva marcha para pedir que la Ley de Humedales</t>
@@ -2234,7 +5760,26 @@
     <t>https://www.pagina12.com.ar/473094-humo-en-rosario-nueva-marcha-para-pedir-que-la-ley-de-humeda</t>
   </si>
   <si>
-    <t>2022-08-13T13:38:13Z</t>
+    <t xml:space="preserve">Título: Humo en Rosario: nueva marcha para pedir que la Ley de Humedales
+Subtítulo: Será esta tarde. La comunidad cortará el puente Rosario-Victoria en un fuerte reclamo por el ecocidio por los incendios intencionales de pastizales. Denuncian los intereses del agronegocio y el interés inmobiliario de las tierras afectadas.
+Editoria: GO Noticias
+Tags: Incendio, Rosario, Santa Fe, santa-fe
+URL: https://www.pagina12.com.ar/473094-humo-en-rosario-nueva-marcha-para-pedir-que-la-ley-de-humeda/
+Notícia completa (14 blocos):
+Las organizaciones sociales convocaron a otra movilización para esta tarde en el puente Rosario-Victoria, en reclamo por el ecocidio desatado por los incendios intencionales en las islas del Delta, para pedir por la Ley de Humedales y en contra "de que el negocio de pocos ponga en riesgo la vida de todos", expresó Norma López, concejala rosarina del Frente de Todos, en AM 750.
+"Más allá de lo que se hizo hasta ahora por parte de los Gobiernos nacional y provincial, está claro que la Justicia tiene que avanzar y meter preso a los que están provocando esta atrocidad, contra la salud de las personas y el ambiente", sostuvo López.
+Este miércoles se llevó a cabo una movilización de la que participaron además de los vecinos de Rosario, perjudicados por el humo de los incendios que embargó la ciudad desde el sábado pasado hasta ese día, también hubo participantes de las ciudades vecinas.
+Hasta el momento, se calcula que hay unas 200.000 hectáreas destruidas por el fuego, en lo que va de 2022. Este viernes, la Corte Suprema de la Nación, envió a las provincias Santa Fe, Entre Ríos y Buenos Aires, y a los municipios de Victoria y Rosario, a reportar cada 30 días sobre la efectividad de las medidas adoptadas, en el marco de la causa que se abrió para investigar los incendios del delta del río Paraná en los últimos años.
+Según la concejala, esta decisión fue "políticamente correcta" para un tribunal donde hay dos santafesinos: Ricardo Lorenzetti y Horacio Rosatti. "Hay que avanzar más y meter preso a los responsables que tienen nombre y apellido y procedencia política. Hay una decena de empresarios que son investigados, en una situación que supera a las condiciones del agronegocio, también hay una mirada inmobiliaria", remarcó.
+Por eso, también opinó que "la Ley de Humedales es importante, pero no dará soluciones inmediatas. Por eso pedimos que se actúe en la urgencia". Y agregó: "Si no se ven las sanciones de parte de Nación y las provincias, se va a seguir convalidando (esta situación). No dejarle pasar a los poderosos para que hagan este desastre en el territorio de todos".
+El Concejo Municipal de Rosario aprobó este jueves un protocolo de prevención cada vez que el aire de Rosario presente niveles de contaminación elevados, como ocurre con las quemas de pastizales en las islas del Delta.
+La iniciativa fue presentada por Susana Rueda -del bloque Rosario Progresista- y contempla que el Ejecutivo brinde recomendaciones a la población para evitar daños graves de salud.
+[H2] Grave impacto para la salud
+El Instituto de Física Rosario, del Conicet y la Universidad Nacional de Rosario (UNR), concluyó que los vecinos de la ciudad estuvieron expuestos "a niveles de contaminación extremadamente altos", por el humo producido por los incendios en las islas del Paraná y que llegó a Rosario entre el fin de semana y el miércoles pasado.
+Según el trabajo, la cantidad de partículas en el aire tiene un "grave impacto en la salud que no debe subestimarse más allá del periodo de exposición".
+Los contaminantes que se analizaron (criterio O3, NO2, SO2 y CO2) en el área metropolitana de Rosario se relacionó con los focos de incendio en las islas y se usaron además mediciones satelitales.
+El Observatorio Ambiental de la UNR, entre el lunes y el miércoles, se duplicaron los valores medios diarios admitidos por la OMS e incluso algunos días se registraron hasta 18 veces más estos niveles establecidos por
+Este jueves, la Facultad de Ciencias Médicas (FCM) de la UNR calificó a la quema de humedales en el Delta del Paraná como “uno de los peores desastres ecológicos” de la región, con consecuencias en la salud de las personas respirar el humo: Las consultas médicas aumentaron cada día por problemas respiratorios.</t>
   </si>
   <si>
     <t>Mauricio Macri sumó a Martín Palermo a su gira "de campaña" en Rosario</t>
@@ -2246,7 +5791,19 @@
     <t>https://www.pagina12.com.ar/472658-mauricio-macri-sumo-a-martin-palermo-a-su-gira-de-campana-en</t>
   </si>
   <si>
-    <t>2022-08-12T03:01:00Z</t>
+    <t xml:space="preserve">Título: Mauricio Macri sumó a Martín Palermo a su gira "de campaña" en Rosario
+Chapeau: Los planes para 2023 incluyen de nuevo a Boca
+Subtítulo: El ex presidente Mauricio Macri siga de gira instalando su potencial candidatura preside
+Editoria: El País
+Tags: Mauricio Macri, Martín Palermo, printed-edition, mauricio-macri, martin-palermo, diario
+URL: https://www.pagina12.com.ar/472658-mauricio-macri-sumo-a-martin-palermo-a-su-gira-de-campana-en/
+Notícia completa (6 blocos):
+El ex presidente Mauricio Macri siga de gira instalando su potencial candidatura presidencial para 2023 y este jueves en una visita a Rosario logró llamar la atención utilizando una fórmula repetida: su cercanía al "mundo Boca". El ex mandatario aterrizó en la ciudad santafecina acompañado por el histórico goleador "xeneize" Martín Palermo, quien lo acompañó en su recorrido por la Fundación Libertad y el congreso de la Asociación Argentina de Productores en Siembra Directa (Aapresid).
+Macri participó primero de un encuentro en la Fundación Libertad, donde ratificó su línea antisindical con críticas al titular de Suteba, Roberto Baradel, y al secretario general de Asociación de Pilotos de Líneas Aéreas (APLA), Pablo Biró. "No podemos tener gremios que digan, como dice Baradel, ‘yo no quiero preparar a alumnos para que vayan a las empresas’. ¿Quién es este tipo? ¿De dónde salió?", apuntó Macri.
+Por otra parte, Macri insistió con el cierre de Aerolíneas Argentinas, a pesar de su fracasada política de "cielos abiertos": "Lo que cuesta Aerolíneas Argentinas por año le permitiría al gobierno nacional poner en Santa Fe 33.000 gendarmes. No quedaría un sólo narco en la provincia".
+Sin embargo, lo que se llevó la atención fue la presencia de Palermo, el ex goleador que mantiene en pausa su flamante carrera como DT tras renunciar en mayo como entrenador de Aldosivi. Algunos medios indicaron que fuentes cercanas al diputado nacional y vicepresidente del PRO, Federico Angelini, no descartaban un salto de Palermo a la política como candidato a diputado en 2023. En tanto, otros rumores lo acercan a un posible armado de Macri para pelear las elecciones de Boca Juniors, que coinciden con las presidenciales nacionales. Habrá que ver, también, si Macri lo invitará a jugar con su equipo del Cardenal Newman, en el campeonato de Los Abrojos, que integran planteles como el Liverpool del fiscal Diego Luciani y el camaritas Mariano Llorens.
+En el Congreso de Aapresid, una de las organizaciones emblema del agronegocio y del actual modelo agroquímico, espacios en los que Macri siempre es bien recibido como ocurrió en la exposición de La Rural y Expoagro; el ex presidente fue parte de una exposición auspiciada por UPL --una multinacional de origen indio productora de agroquímicos-- para presentar una iniciativa global sobre "carbono neutro", en la que Macri participó como presidente de la Fundación FIFA en relación al Mundial de Qatar.
+En la previa, durante la reunión en la Fundación Libertad, Macri dejó una pista sobre la presencia de Palermo en el visita: "Queremos utilizar el fútbol para influir positivamente en la vida de las personas, especialmente en dos áreas que son prioritarias para el trabajo de la Fundación: la educación y el desarrollo sostenible".</t>
   </si>
   <si>
     <t>Brasil | Organizaciones se movilizan y presentan cartas "en defensa de la democracia" este jueves en San Pablo</t>
@@ -2255,7 +5812,26 @@
     <t>https://www.pagina12.com.ar/472531-brasil-organizaciones-se-movilizan-y-presentan-cartas-en-def</t>
   </si>
   <si>
-    <t>2022-08-11T14:18:22Z</t>
+    <t xml:space="preserve">Título: Brasil | Organizaciones se movilizan y presentan cartas "en defensa de la democracia" este jueves en San Pablo
+Subtítulo: Bolsonaro dijo que los firmantes de la iniciativa son "caraduras" y que su gobuerno "luchó" por la "libertad y la verdad"
+Editoria: [NÃO ENCONTRADO]
+Tags: Brasil, Lula Da Silva, Jair Bolsonaro, lula-da-silva, jair-bolsonaro
+URL: https://www.pagina12.com.ar/472531-brasil-organizaciones-se-movilizan-y-presentan-cartas-en-def/
+Notícia completa (14 blocos):
+Tras los ataques al sistema electoral brasileño por parte del presidente Jair Bolsonaro, dos cartas en defensa del Estado democrático serán leídas este jueves en la Facultad de Derecho de la Universidad de San Pablo (USP). Además, el movimiento Fora Bolsonaro y la Orden de los Abogados de Brasil (OAB), junto con organizaciones sociales, estudiantiles y sindicatos convocaron a movilizaciones en la ciudad.
+A las 9.30 comienza la lectura de la primera carta en el Salón Noble del Colegio, impulsada por la Federación de Industrias del Estado de San Pablo (Fiesp) empresas y sindicatos. Este documento fue firmado por ocho de los nueve precandidatos presidenciales registrados al momento, con la excepción de Bolsonaro quien ha criticado los documentos y cuestionado las garantáis electorales en Brasil.
+Posteriormente, a las 11.30, cuatro profesoras de la USP procederán con la lectura de la “Carta a los brasileños y las brasileñas en defensa del Estado Democrático de Derecho”, impulsada por exalumnos de la facultad y que ya cuenta con casi 900 mil firmas.
+El 11 de agosto se conmemora en Brasil el Día del Estudiante, el aniversario de la creación de las carreras de derecho en el país y la lectura de un manifiesto por parte de estudiantes de Derecho para denunciar la dictadura militar en 1977.
+Aunque al interior de la facultad solo podrán ingresar invitados, se colocaron pantallas en el exterior para seguir la transmisión. Frente al edificio, un grupo de estudiantes y religiosos del colectivo Banquete entregan pan en protesta contra el aumento de la inseguridad alimentaria y el hambre en Brasil. “Con el estómago vacío no hay democracia”, señalan los carteles.
+Por su parte, el expresidente Luiz Inácio Lula da Silva manifestó esta mañana: “defender la democracia es defender el derecho a la alimentación de calidad, al buen trabajo, al salario justo, al acceso a la salud y a la educación”. El candidato presidencial que lidera las encuestas hizo estos comentarios desde su cuenta de Twitter.
+[H2] Críticas de Bolsonaro
+El presidente ha rechazado estos manifiestos asegurando que quienes los firman son "caraduras" y que él "lucha" por la "libertad" y la "verdad". En un encuentro con legisladores afines, calificó de antidemocráticas las medidas adoptadas por gobernadores durante la pandemia de covid-19 y reclamó que en ese entonces "nadie decía la palabra democracia".
+“Vimos en la pandemia la arbitrariedad cometida por algunos jefes ejecutivos en todo Brasil. Les quitaron el derecho de ir y venir, arrestaron mujeres e hicieron barbaridades, nadie decía la palabra democracia. Respetuosamente, fui en contra de todo eso”, declaró.
+La semana pasada, consultado por la iniciativa de la Fiesp, Bolsonaro dijo que se trata de una carta “política”. "Hay una nota de algunos empresarios, algunos banqueros, algunos artistas, a favor de la democracia. ¿Quién está en contra de la democracia en Brasil? ¿En tres años y medio (de gobierno) qué acto mío contra la democracia hubo?", preguntó en su transmisión semanal en redes sociales.
+[H2] El agronegocio con Bolsonaro
+Este miércoles, la Confederación de Agricultura y Ganadería de Brasil (CNA por sus siglas en portugués) expresó su apoyo a Bolsonaro durante una actividad en Brasilia. La CNA nuclea a las principales empresas y referentes del agronegocio en el país, y el acto originalmente estaba convocado como una presentación de propuestas de la entidad a todos los candidatos a la presidencia. Sin embargo, según medios locales, esta ceremonia terminó convirtiéndose en una demostración de fuerza de Bolsonaro, que tiene fuerte arraigo entre las cámaras empresariales del sector agropecuario.
+En su intervención, el presidente criticó una posible ampliación de la demarcación de tierras indígenas en el país: “Si esto lo aprueba la Corte Suprema -venimos trabajando para que no lo apruebe- pero si lo aprueba, ¿tendré que cumplir? Esta medida, si la aprueba, es un crimen contra la patria, ¿es o es tranquilo, yo sé lo que hay que hacer”, dijo Bolsonaro.
+En setiembre del año pasado, el Supremo Tribunal Federal suspendió la sentencia de la acción que discute el marco temporal de las tierras indígenas, lo que implica que solo se puede reclamar la demarcación de tierras indígenas que fueron ocupadas por indígenas en la época de la Constitución de 1988.</t>
   </si>
   <si>
     <t>Victoria Torres: "En Chubut, el pueblo fue  ignorado"</t>
@@ -2264,7 +5840,19 @@
     <t>https://www.pagina12.com.ar/468382-victoria-torres-en-chubut-el-pueblo-fue-ignorado</t>
   </si>
   <si>
-    <t>2022-08-10T20:06:29Z</t>
+    <t xml:space="preserve">Título: Victoria Torres: "En Chubut, el pueblo fue ignorado"
+Subtítulo: Victoria Torres reflexionó en La Casa Invita sobre la aprobación de a la ley de Zonificación de la Actividad Minera en Chubut.
+Editoria: Radio 750
+Tags: Megaminería, Chubut, La casa invita, megamineria, la-casa-invita
+URL: https://www.pagina12.com.ar/468382-victoria-torres-en-chubut-el-pueblo-fue-ignorado/
+Notícia completa (7 blocos):
+¿Por dónde empiezo? Porque, como siempre, tenemos unos cuantos frentes abiertos para atender y contar en nuestra patria. Empiezo desde la tierra, en sus entrañas. No están entendiendo la urgencia del asunto, si se me permite humildemente y como ciudadana, la objeción.Es necesario, como mínimo, abrir una franca y real discusión sobre el modo en que explotamos nuestra tierra. Agronegocios, megaminería, hay una larga agenda. Y hoy la “agenda verde” grita desde el sur, una vez más.Sucede que en Chubut, donde el pueblo había dicho No a la Megaminería -de hecho tienen una larga lucha sobre este tema, y en 2003 lograron una ley que protege el territorio de esas explotaciones-, esa sociedad fue ignorada y la política con los empresarios y negociados ganaron el partido. Y abrieron la puerta a la megamineria, dicen que sin cianuro, dicen que sólo en una cierta zona de la provincia. Vos y yo sabemos cómo funciona la avaricia. Rompieron la red y le quebraron la voluntad al pueblo.Una gran pena. Es para el otro lado. Primero, porque hay que respetar la voz de la sociedad. Luego, porque no hay megaminería que no reviente a la tierra y sus venas. Entonces, hay que estar del lado de los que defienden a la tierra.
+Unsupported embed [https://mdstrm.com/embed/61bbda31ef4d9908209c65bc]
+Con 14 votos a favor y 11 en contra, la Legislatura provincial de Chubut sancionó la Ley de Zonificación que autoriza la minería -sin el uso de cianuro- en la meseta central de la provincia. ¿Y el pueblo? Afuera del recinto, bajo el título: “Manifestantes ambientalistas fueron reprimidos por la Policía”.
+Hacé memoria: “El proyecto había sido presentado el año pasado por el Gobierno provincial y rechazado por amplios sectores de la sociedad, mientras que académicos de la Universidad Nacional de la Patagonia y el Conicet alertaron sobre las consecuencias negativas que tendría sobre el ambiente: a pesar de que no estará permitido el uso de cianuro, se empleará el xanato”.
+Sin embargo, el poder económico pudo más que el entendimiento del costo de insistir en esos caminos. Nada importó. En Chubut, el pueblo fue ignorado.
+Se pone difícil la esperanza con semejantes acciones temerarias para con las futuras generaciones. Y, aún así, y más: hay que salir a gritar, a explicar, a invitar a ver y tomar mejores decisiones. Como hoy en la Plaza, con parte del pueblo, representantes de la tierra, reclamando por la Ley de Humedales que se diluye ignorada en el Congreso, y encima se le suma la avanzada en Chubut.
+Es nuestra obligación como integrantes de una generación que creyó en la utopía y que pagó muy caro, con todxs nuestrxs muertxs queridxs decía Liliana Riga, una querida amiga oyenta. Es nuestra obligación. Tomar conciencia y empezar a sumar para el otro lado. Cada cual verá cómo, pero es nuestra obligación. Algo, pensar siquiera un rato al día.</t>
   </si>
   <si>
     <t>Brasil: en 2020, los asesinatos de indígenas aumentaron un 61 por ciento</t>
@@ -2273,7 +5861,19 @@
     <t>https://www.pagina12.com.ar/466802-brasil-en-2020-los-asesinatos-de-indigenas-aumentaron-un-61-</t>
   </si>
   <si>
-    <t>2022-08-10T19:59:58Z</t>
+    <t xml:space="preserve">Título: Brasil: en 2020, los asesinatos de indígenas aumentaron un 61 por ciento
+Subtítulo: Se trata del mayor número de muertes violentas de indígenas brasileños registrado en los últimos 25 años, según datos del Consejo Indígena Misionario, quien también afirma que en el gobierno de Jair Bolsonaro “recrudecieron” los casos de abuso de poder y racismo contra pueblos originarios.
+Editoria: Radio 750
+Tags: Jair Bolsonaro, Brasil, Informativo 750, jair-bolsonaro, informativo-750
+URL: https://www.pagina12.com.ar/466802-brasil-en-2020-los-asesinatos-de-indigenas-aumentaron-un-61-/
+Notícia completa (7 blocos):
+Los datos del informe anual del Consejo Indígena Misionario (CIMI) de Brasil que se divulgaron este jueves son preocupantes y reflejan un aumento de las situaciones de abuso de poder y racismo contra los pueblos indígenas. En el informe de más de 200 páginas hay un nombre que aparece mencionado casi 70 veces: Jair Bolsonaro.
+El CIMI concluye que la violencia contra los indígenas como “práctica de gobierno” es una “dolorosa y dramática realidad en el Brasil de Bolsonaro”. La mayoría de los casos de abuso de poder, diversas amenazas y racismo y discriminación étnica y cultural ocurrieron cuando los indígenas buscaron atención o asistencia en medio de la pandemia.
+Las medidas gubernamentales, afirma el CIMI, incidieron “directamente” en el aumento de los casos de “conflictos relacionados con los derechos territoriales”, que aumentaron significativamente. Hubo 96 casos de este tipo en 2020, un 174% más que los 35 identificados en 2019.
+Otro dato relevante es el considerable aumento de los asesinatos de indígenas en Brasil. En 2020 fueron asesinados 182 indígenas, 61% más que en 2019, cuando se contabilizaron 113 asesinatos.
+Se trata del mayor número de muertes violentas de indígenas brasileños registrada en los últimos 25 años, señala el informe. Además hubo 1.200 muertes causadas por la pandemia de covid-19. “En muchas aldeas, la pandemia se llevó las vidas de ancianos y ancianas que eran verdaderos guardianes de la cultura, de la historia y de los dos saberes de sus pueblos, lo que representa una pérdida cultural inestimable, no sólo para los pueblos indígenas sino para toda la humanidad”, advierte el CIMI.
+El informe reportó 263 invasiones a reservas indígenas, en su mayoría por "garimpeiros" (mineros ilegales) y madereros ilícitos. "Madereros, mineros, cazadores y pescadores ilegales o terratenientes invaden las tierras indígenas para apropiarse ilícitamente de madera o devastar ríos enteros en busca de oro y otros minerales, además de deforestar y quemar extensas áreas de tierra para convertirlas en pasto", denuncia el estudio.
+El CIMI denuncia que el gobierno de Bolsonaro, los empresarios del agronegocio, policías y militares han sido "cómplices" de los responsables de la explotación minera ilícita y de la deforestación de la selva para el comercio ilegal de madera.</t>
   </si>
   <si>
     <t>Ley de Acceso a la Tierra: la UTT se movilizará en todo el país para reclamar su tratamiento</t>
@@ -2282,13 +5882,52 @@
     <t>https://www.pagina12.com.ar/466621-ley-de-acceso-a-la-tierra-la-utt-se-movilizara-en-todo-el-pa</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Ley de Acceso a la Tierra: la UTT se movilizará en todo el país para reclamar su tratamiento
+Subtítulo: A un año de presentar el proyecto por tercera vez en el Congreso, las jornadas de lucha irán de lunes a jueves. Habrá un acampe frente al Congreso con actividades culturales, charlas informativas y un verdurazo.
+Editoria: Radio 750
+Tags: UTT
+URL: https://www.pagina12.com.ar/466621-ley-de-acceso-a-la-tierra-la-utt-se-movilizara-en-todo-el-pa/
+Notícia completa (13 blocos):
+La Unión de Trabajadores y Trabajadoras de la Tierra (UTT) dará inicio este lunes a una jornada de lucha que se extenderá hasta el jueves en todo el país, para exigir, a un año de presentar la iniciativa por tercera vez, avances en el tratamiento de la Ley de Acceso a la Tierra.
+El epicentro de las actividades será en la plaza frente al Congreso de la Nación, donde las acciones pondrán el foco en garantizar la soberanía alimentaria, mediante el acceso a tierras ociosas para producir y garantizando precios accesibles en productos alimenticios.
+Las actividades se realizarán entre el lunes 25 y el jueves 28 de octubre. En el centro de la Ciudad se realizará un acampe de cuatro días con actividades culturales, charlas informativas, verdurazo, feriazo, asadazo, panazo, talleres y proyecciones, entre otras.
+El objetivo es hacer visible el reclamo y ofrecer alimentos saludables a precios justos de manera masiva para la población. También habrá acciones en Córdoba, Santa Fe, Chaco, Formosa, Entre Ríos, Corrientes, Misiones, Santiago del Estero, Tucumán, Salta, Jujuy, Mendoza, La Pampa, Neuquén, Río Negro y Chubut.
+Unprocessed element [figure]
+[H2] El proyecto
+La iniciativa propone un crédito que permita a las comunidades campesinas acceder a tierras, infraestructura e insumos para producir mediante un modelo sustentable basado en la agroecología que mejore sus condiciones laborales. Apunta a una producción sin agroquímicos que beneficie tanto a quienes la generan y ofrecen como a quienes la consumen.
+“El proyecto de ley propone un sistema de créditos blandos estilo PROCREAR, pero para el sector rural con el cual las familias pequeñas productoras puedan acceder a tierras para producir alimentos de un modo sustentable y habitar en una vivienda digna”, explicó Lucas Tedesco, referente de la UTT.
+El proyecto fue presentado por tercera vez el 22 de octubre del año pasado, en una audiencia en el Congreso junto a los entonces ministros de Agricultura, Luis Basterra; de Desarrollo Social, Daniel Arroyo y la vicepresidenta del bloque de diputados del Frente de Todos, Cecilia Moreau.
+[H2] Mucha tierra, pocas manos
+En el país solo el 13% de la tierra está en manos de pequeños productores que, a su vez, son quienes producen más del 60% de alimentos que circulan en el mercado interno, explica la agrupación en un comunicado, donde también advierte que el 1% de las empresas agrarias controlan el 36% de la tierra cultivada.
+“Mientras las corporaciones alimenticias quieren desabastecer y seguir hambreando al pueblo, necesitamos más que nunca medidas concretas para poder acceder al alimento a través de precios justos, y para eso es fundamental bajar y controlar los precios de la canasta alimentaria”, expresó por su parte Rosalía Pellegrini, vocera de la UTT.
+Zulma Molloja, también referente campesina, agregó que “el modelo del agronegocio representa a un campo concentrado, enfocado en las exportaciones que, si bien son necesarias, tenemos que promover otro modelo de un campo que alimente”.</t>
+  </si>
+  <si>
     <t>Brasil: Pantanal, el mayor humedal del planeta, en peligro por los incendios forestales</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/464675-brasil-pantanal-el-mayor-humedal-del-planeta-en-peligro-por-</t>
   </si>
   <si>
-    <t>2022-08-10T19:53:16Z</t>
+    <t xml:space="preserve">Título: Brasil: Pantanal, el mayor humedal del planeta, en peligro por los incendios forestales
+Subtítulo: La principal reserva hídrica del mundo perdió la sexta parte de sus áreas de agua dulce.
+Editoria: Radio 750
+Tags: medioambiente, Incendios, Brasil, Informativo 750, informativo-750
+URL: https://www.pagina12.com.ar/464675-brasil-pantanal-el-mayor-humedal-del-planeta-en-peligro-por-/
+Notícia completa (13 blocos):
+Este año el fuego consumió 262 mil hectáreas de la región de Pantanal, ubicada en Brasil, fronteriza con Bolivia y Paraguay, una cifra cada vez más cercana al récord de 2020, según el Laboratorio de Aplicaciones Ambientales Satelitales (Lasa) y la Universidad Federal de Río de Janeiro (UFRJ).
+El Cuerpo de Bomberos de Brasil informó este domingo que hay cinco operaciones simultáneas para combatir incendios forestales en el Pantanal, que es además el mayor humedal del planeta. En 2020 este ecosistema enfrentó la peor temporada desde que existen registros.
+Este fin de semana el municipio de Porto Murtinho declaró el estado de emergencia debido al avance de los incendios y la población que se encontraba en la ribera fue evacuada en botes.
+La plataforma MapBiomas reveló que cada año de los últimos 36 se quemaron en Brasil, en promedio, 150 mil kilómetros cuadrados, un área mayor al territorio de Inglaterra y casi tan grande como Uruguay.
+En este período la quema alcanzó el equivalente a una quinta parte del territorio nacional, el 19,6 por ciento de Brasil. En total, el 65 por ciento del área perdida en incendios corresponde a zonas de vegetación nativa. El estado de Mato Grosso tuvo la mayor ocurrencia de incendios, seguido de Pará y Tocantins.
+Aunque se estableció que los grandes picos fueron producto principalmente de las sequías extremas, el estudio indicó que el aumento de la deforestación antes de 2005 y después de 2019 tuvieron un gran impacto sobre el aumento de la superficie quemada.
+Entre los biomas brasileños, el más afectado fue el Pantanal donde el 57 por ciento de su territorio se quemó al menos una vez entre 1985 y 2020. El humedal tiene 250.000 kilómetros cuadrados de extensión y un 60 por ciento está en territorio brasileño, mientras que el resto lo comparten Paraguay y Bolivia.
+Según el Instituto Brasileño de Geografía y Estadística (IBGE) los seis principales biomas continentales de Brasil son Amazonas, Cerrado, Mata Atlántica, Caatinga, Pampa y Pantanal.
+El grupo de especialistas que trabaja en la plataforma MapBiomas procesó más de 150.000 imágenes satelitales con la ayuda de inteligencia artificial y analizó el área quemada durante los 36 años entre 1985 y 2020.
+La coordinadora de MapBiomas Fogo, Ane Alencar explicó que “el mapeo es fundamental para conocer la frecuencia, intensidad del fuego, para la planificación del combate y para señalar las zonas de mayor riesgo”, indicó.
+Cerrado y Amazonas representan el 85 por ciento del área quemada en los últimos 36 años. “La Amazonía no es un bioma en el que el fuego forma parte de la dinámica natural del ecosistema, a diferencia del Cerrado, donde el fuego natural forma parte de su dinámica evolutiva”, dijo la investigadora.
+Brasil tiene el 12 por ciento de las reservas de agua dulce del mundo y más de la mitad de los recursos hídricos de América del Sur.
+Las principales causas de la pérdida de más de tres millones de hectáreas de aguas superficiales son la deforestación de la Amazonía brasileña, la construcción de hidroeléctricas y el uso excesivo del agua para el agronegocio.</t>
   </si>
   <si>
     <t>Por qué reaparecieron manadas de carpinchos en Nordelta</t>
@@ -2297,31 +5936,138 @@
     <t>https://www.pagina12.com.ar/464601-por-que-reaparecieron-manadas-de-carpinchos-en-nordelta</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Por qué reaparecieron manadas de carpinchos en Nordelta
+Subtítulo: Cómo es la vida de los roedores en los exclusivos barrios privados. Que rol cumplen los desarrollos inmobiliarios y qué dice la Ley de Humedales, que busca regular la influencia de las construcciones en la naturaleza.
+Editoria: Radio 750
+Tags: Nordelta, carpinchos
+URL: https://www.pagina12.com.ar/464601-por-que-reaparecieron-manadas-de-carpinchos-en-nordelta/
+Notícia completa (13 blocos):
+La reaparición de decenas de carpinchos mantiene en vilo a los vecinos de un barrio privado en Nordelta. Varias manadas de estos roedor coparon un vecindario completo ocasionando diferentes inconvenientes como ataques a mascotas o provocaciones a accidentes de tránsito.
+Pero en realidad, estos animales no invadieron ningún espacio: regresaron al hábitat natural del que fueron echados cuando comenzó a desarrollarse el proyecto inmobiliario. Por lo general estos barrios privados se construyen sobre humedales, reservas de agua dulce que son ecosistemas enteros y hábitat de animales silvestres. Estas construcciones ponen en peligro la biodiversidad del lugar y la mal llamada "invasión" de carpinchos da cuenta de ello.
+Estos megaemprendimientos rellenan terrenos para construir casas en altura y, con los pozos que queda, hacen enormes lagunas artificiales. En la medida que estos terrenos naturales son construidos por el hombre, los carpinchos se desplazan hacia las afueras, o se quedan en algunos lotes que aún están vacíos. Irónicamente, uno de los últimos desarrollos inmobiliarios de la zona se llama "Carpinchos", como la fauna natural del lugar.
+[H3] Características de los carpinchos
+El carpincho es el roedor viviente de mayor tamaño y peso del mundo. Vive en la zona terrestre de los bosques y sabanas tropicales del centro y sur de Sudamérica. En Argentina también se los conoce como "chancho de agua" o "capibara".
+Tiene un cuerpo pesado en forma de barril y una cabeza pequeña, con un pelaje pardo rojizo en la parte superior del cuerpo que se vuelve pardo amarillo. En su parte inferior suele encontrarse pelaje con puntos o petequias en el lomo. Puede crecer hasta 1,30 m de largo y llegar a pesar 65 kg.
+Presenta pies ligeramente palmeados y al igual que los puercos carece de cola y tiene 20 dientes. Sus patas posteriores son algo más largas que las anteriores, y los hocicos son romos, con ojos, narinas y orejas en la parte superior de la cabeza. Las hembras son un poco más pesadas que los machos.​
+[H3] Organizaciones socioambientales presentan un petitorio para que se trate la Ley de Humedales
+El miércoles pasado, la Multisectorial Humedales Rosario marchó desde Plaza de Mayo a Congreso, donde realizó un acto y presentó un petitorio, con más de 400 organizaciones socioambientales de todo el país, para exigir el tratamiento del proyecto de Ley de Humedales.
+"Es crítico lo que se está viviendo desde el año pasado en el Delta del Paraná, se quemaron más de medio millón de hectáreas de humedales en manos del agronegocio y de las especulaciones inmobiliarias y este año los focos de incendio fueron más todavía", explicó Ivo Peruggino referente de la Multisectorial. "La ley de humedales está cajoneada en Comisión de Agricultura y Ganadería", agregó.
+En el petitorio presentado señalaron que les preocupa "enormemente la falta de avances en la Cámara Baja" y que "el 2020 nos dejó las cenizas de un país en llamas: más de 1.200.000 hectáreas afectadas por el fuego, miles de ejemplares de nuestra fauna muertos y cientos de casas perdidas".
+[H2] Claves de la Ley
+La iniciativa propone establecer criterios de gestión, preservación y uso racional y sostenible de los humedales, así como su biodiversidad; identificar y promover su conocimiento y valoración, su valor y potencial estratégico en la mitigación y adaptación al cambio climático, promover la creación de áreas naturales protegidas en humedales y corredores biológicos y culturales, el fomento las actividades de restauración de los ecosistemas, establecer medidas para desalentar las actividades inadecuadas y las malas prácticas, así como apoyar los medios de vida y producción, tradicionales y de la economía popular que hagan uso racional y sostenible del entorno.</t>
+  </si>
+  <si>
     <t>Trigo transgénico: los riesgos de su siembra para la salud y el ambiente</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/464727-trigo-transgenico-los-riesgos-de-su-siembra-para-la-salud-y-</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Trigo transgénico: los riesgos de su siembra para la salud y el ambiente
+Subtítulo: "En el país hay localidades donde ya el agua no es potable por el nivel de agrotóxicos que tienen. Esto genera daños de la salud colectiva muy elevados que incluyen infancias con daños genéticos", advirtió la investigadora del Conicet, Cecilia Gargano.
+Editoria: Radio 750
+Tags: Informativo 750, informativo-750
+URL: https://www.pagina12.com.ar/464727-trigo-transgenico-los-riesgos-de-su-siembra-para-la-salud-y-/
+Notícia completa (12 blocos):
+Luego de la contundente convocatoria de organizaciones sociales y ambientalistas, que la semana pasada se movilizaron en distintos puntos del país para rechazar la autorización del trigo transgénico HB4 en Argentina, la doctora en historia, investigadora del Conicet e integrante del espacio Trigo Limpio, Cecilia Gargano, habló con Las Primeras Noticias y advirtió sobre el riesgo que implica esta variedad del cereal para la salud y el ambiente.
+Unsupported embed [https://mdstrm.com/embed/612618728e5a16385e0a5fb3]
+La HB4 es la primera variedad de trigo transgénico aprobada en el mundo. Esta variante fue desarrollada por un grupo de biólogos moleculares e investigadores argentinos, liderados por la investigadora Dra. Raquel Chan, Directora del Instituto de Agrobiotecnología del Litoral (IAL) perteneciente a la Universidad Nacional del Litoral (UNL) y al Conicet, en alianza con la empresa argentina de biotecnología agrícola Bioceres.
+La tecnología HB4 permite obtener semillas más tolerantes a la sequía minimizando las pérdidas de producción. En Argentina, su uso fue aprobada el 7 de octubre del 2020, durante la pandemia, mediante la Resolución 41/2020 de la Secretaría de Alimentos, Bioeconomía y Desarrollo Regional del Ministerio de Agricultura, Ganadería y Pesca.
+"Es una variedad que, al habérsele introducido un gen proveniente del girasol, tiene más tolerancia a la sequía y pero también tiene otra característica que es la tolerancia a un herbicida que es glufosinato de amonio, que es 15 veces más tóxico que el glifosato”, dijo Gargano.
+La investigadora denunció "la ausencia absoluta" de una consulta popular sobre la implementación de este trigo y dijo que en el país no se realizaron estudios sobre su toxicidad. “Nuevamente somos un laboratorio a cielo abierto”, aseveró.
+"En el país hay localidades donde ya el agua no es potable por el nivel de agrotóxicos que tienen. Esto genera daños de la salud colectiva muy elevados que incluyen infancias con daños genéticos", puntualizó Gargano. En ese sentido, la especialista sostuvo que se debe dar la discusión para discutir la matriz productiva en Argentina.
+Y completó: "Parte del problema es que el entramado del agronegocio está asociado a un ámbito desregulatorio. Esto hace que los organismos que tiene que comprobar que la implementación de estás tecnologías son seguros para la salud y para nuestro ambiente estén cuestionados".
+[H2] Más de 1000 rechazan la siembra del trigo transgénico en Argentina
+Más de 1000 científicos del Conicet y de 30 universidad públicas nacionales se expresaron en rechazo al trigo transgénico HB4. En una carta abierta al gobierno nacional, académicos de todo el país cuestionaron la nueva semilla, que impactará directamente en la mesa de los argentinos, porque el trigo es la base del pan.
+“Esta autorización remite a un modelo de agronegocio que se ha demostrado nocivo en términos ambientales y sociales, causante principal de las pérdidas de biodiversidad, que no resuelve los problemas de la alimentación y que amenaza además la salud de nuestro pueblo confrontando la seguridad y la soberanía alimentaria”, comienza el escrito.
+“Cientos de investigaciones sobre daños ambientales y sanitarios han sido publicadas en revistas científicas internacionales y muchos más testimonios y denuncias han sido impulsadas de manera sostenida por comunidades, trabajadores de la salud y movimientos sociales de nuestra región. Es indudable que el actual modelo productivo hegemónico de la agroindustria concentra capital, profundiza la desigualdad económica y social, genera el deterioro de la salud de las comunidades y de los ecosistemas y acelera la pérdida de biodiversidad, amenazando la seguridad alimentaria y dejando a su paso territorios devastados ambiental y socialmente”, afirman en el texto.</t>
+  </si>
+  <si>
     <t>#24S: masiva protesta contra el cambio climático</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/465749-24-s-masiva-protesta-contra-el-cambio-climatico</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: #24S: masiva protesta contra el cambio climático
+Subtítulo: La protesta mundial contra el cambio climático tuvo su epicentro en varios puntos de nuestro país. "La juventud nos está interpelando a los más veteranos sobre lo que estamos haciendo con el planeta”, afirmó el abogado ambientalista Enrique Viale.
+Editoria: Radio 750
+Tags: Greta Thunberg, Cambio climático, greta-thunberg, cambio-climatico
+URL: https://www.pagina12.com.ar/465749-24-s-masiva-protesta-contra-el-cambio-climatico/
+Notícia completa (17 blocos):
+Miles de jóvenes se congregaron este viernes en diferentes puntos del país y del mundo para acompañar la convocatoria de Juventud por el Clima, en una protesta alrededor del globo por la crisis climática, que a nivel local tuvo su punto de encuentro a las 17 horas en el Congreso de la Nación.
+Se trata de la octava marcha global desde 2018, de la que participaron activistas de más de 80 países. Greta Thunberg, al frente de su organización Fridays for Future -organización que dio origen a las protestas - encabezó la marcha en Berlín.
+“La cuestión ambiental dejó de ser algo de un pequeño grupo y se ha masificado y transversalizado”, sostuvo a nivel local el abogado ambientalista Enrique Viale en diálogo con el móvil de AM750.
+Unsupported embed [https://mdstrm.com/embed/614e45c9dfc9c40834982a47]
+Además, Viale describió la concentración en el Congreso como “enorme” y afirmó que la juventud “nos está interpelando a los más veteranos sobre lo que estamos haciendo con el planeta”. En esa línea, aseguró que el llamado de atención es también hacia los gobernantes.
+“Hay también una interpelación a la clase política que tiene que pensar los modelos de mal desarrollo: megaminería, fracking, agronegocio, que se lleva a cabo colonialmente en nuestro país”, señaló.
+Según detalló Jóvenes por el Clima Argentina -filial local de la organización mundial -, los reclamos más urgentes en nuestro país son la ley de etiquetado frontal, la ley de humedales, la ley de acceso a la tierra para los pequeños y medianos productores que fueron desplazados y buscan cultivar de modo agroecológico, impedir el avance del proyecto de ley de Hidrocarburos, el posible acuerdo porcino y la extracción de petróleo offshore.
+[H3] Historia del #24S
+La iniciativa para reclamar por más y mejores políticas que frenen y reviertan la crisis climática fue impulsada por la activista sueca Greta Thunberg, al frente de su organización Fridays for Future.
+En 2018, cuando Thunberg tenía entonces tan sólo 15 años, faltó al colegio y se sentó frente al Parlamento sueco para exigir medidas, lo que inspiró otras huelgas en el mundo y la convirtió en una referente de la lucha ambiental.
+En marzo de 2019, el movimiento promovió una primera huelga por el clima que fue seguida en más de dos mil ciudades del mundo. En mayo de ese año se celebró una segunda jornada de la que participaron más de un millón de personas y se convocaron manifestaciones en más de 125 países.
+Unsupported div with classes [wp-block-image]
+El 20 de septiembre de 2019 hubo movilizaciones de las que participaron alrededor de 4 millones de personas de 185 países en unas 3.000 localidades y el 27 de ese mes también se realizaron protestas, en el marco del aniversario de la publicación del libro Silent Spring en 1962, de las que participaron 2 millones de personas en unas 2400 localidades.
+La sexta protesta se registró el 29 de noviembre de 2019, en las vísperas de la Cumbre del Cambio Climático que se realizó en Madrid, mientras que la séptima fue el 13 de enero de 2021, bajo la consigna "No más promesas vacías".
+Este año, Thunberg llamó a través de Instagram a “todo el mundo a salir a las calles nuevamente, pidiendo a los líderes mundiales cambiar el sistema”. Hoy la referente se unió a la huelga que se realizó en Berlín, Alemania, y compartió imágenes sobre el evento en las redes sociales.
+Unprocessed element [figure]
+"Hoy fuimos más de 100 mil en la huelga de Berlín y 620 mil solo en Alemania. Hubo huelgas en más de 80 países", agregó en referencia a las naciones que se sumaron a esta jornada, entre ellas Alemania, España, India, Pakistán, República Checa, además de Argentina, donde miles de jóvenes se concentran en distintos puntos del país.</t>
+  </si>
+  <si>
     <t>La UTT acampará en Congreso por la Ley de Acceso a la Tierra</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/465577-la-utt-acampara-en-congreso-por-la-ley-de-acceso-a-la-tierra</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: La UTT acampará en Congreso por la Ley de Acceso a la Tierra
+Subtítulo: Bajo la consigna "No podemos esperar más", la agrupación realizará la protesta para garantizar precios justos de alimento para el pueblo.
+Editoria: Radio 750
+Tags: Informativo 750, informativo-750
+URL: https://www.pagina12.com.ar/465577-la-utt-acampara-en-congreso-por-la-ley-de-acceso-a-la-tierra/
+Notícia completa (10 blocos):
+Este lunes 20 de septiembre la Unión de Trabajadores y Trabajadoras de la Tierra (UTT) iniciará un acampe en Plaza Congreso para exigir avances en el tratamiento de la Ley de Acceso a la Tierra. Durante el acampe desarrollarán varias actividades como movilización, verdurazo, feriazo, charlas y talleres. El martes 21, en el día de la primavera, harán un florazo y el cierre contará con un festival artístico al aire libre.
+“Ahora más que nunca, el pueblo necesita medidas concretas para poder acceder al alimento a través de precios justos, y para eso es fundamental bajar y controlar los precios de la canasta alimentaria. Una de la medidas concretas que nosotras y nosotros proponemos es el acceso a la tierra a través de esta Ley para que las familias productoras puedan acercar alimento más económico y saludable para todos los argentinos”, expresó Rosalía Pellegrini, vocera de la UTT.
+Agustín Suárez, también vocero del gremio agregó: “El modelo del agronegocio representa a un campo concentrado que no alimenta, no está enfocado en el hambre del pueblo mientras genera extraordinarias riquezas por las exportaciones. Si bien las exportaciones son necesarias, tenemos que promover otro modelo de un campo que alimente, somos miles de campesinos, cooperativas agrarias y pequeños y medianos productores que proponemos un modelo sustentable a través de la agroecología y la democratización de la tierra, para lograr la soberanía alimentaria en nuestro país.”
+En Argentina, sólo el 13 por ciento de la tierra está en manos de pequeños productores que producen más del 60 por ciento de alimentos que circulan en el mercado interno, mientras que el 1 por ciento de las empresas agrarias controlan el 36 por ciento de la tierra cultivada en nuestro país. “El proyecto de ley propone un sistema de créditos blandos estilo PROCREAR pero para el sector rural con el cual las familias pequeñas productoras puedan acceder a tierras para producir alimentos de un modo sustentable y habitar en una vivienda digna”, explicó Lucas Tedesco, vocero de la UTT.
+El proyecto de ley cuenta con estado parlamentario: en mayo las comisiones de Agricultura y Asuntos Legislativos de la Cámara de Diputados de la Nación lo trataron pero sin llegar a un dictamen. La propuesta de ley se había presentado en octubre del año pasado por tercera vez en el Congreso de la Nación junto al ministro de Agricultura Luis Basterra, el entonces ministro de Desarrollo Social Daniel Arroyo y la vicepresidenta del bloque de diputados del Frente de Todos Cecilia Moreau.
+[H2] El cronograma completo de actividades
+📌LUNES 20/9
+• 11.30 hs. Marcha
+• 12 hs. Verdurazo
+• 15 hs. Asamblea de Nodos y de la Red de comedores por la Ley de acceso a la tierra.
+• 16 hs. Taller de Huerta a cargo del COTEPO
+• 19.30 hs. ProyeccionesFERIAZO y YERBATAZO durante todo el día
+📌MARTES 21/09
+• 10 hs. Radio abierta
+• 11 hs. Mística de jóvenes por la tierra
+• 12 hs. Verdurazo y Florazo por la primavera
+• 13 hs. Taller a cargo del área de alimentación y red de comedores.
+• 16 hs. Charla sobre trigo transgénico desde la Plataforma Socioambiental
+• 17 hs. Festival con Eruca Sativa, Susy Shock y Sudor Marika, entre otros artistas.</t>
+  </si>
+  <si>
     <t>La comunidad indígena en Santiago del Estero protesta contra "persecuciones, desalojos y bandas armadas"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/464017-la-comunidad-indigena-en-santiago-del-estero-protesta-contra</t>
   </si>
   <si>
-    <t>2022-08-10T19:46:29Z</t>
+    <t xml:space="preserve">Título: La comunidad indígena en Santiago del Estero protesta contra "persecuciones, desalojos y bandas armadas"
+Subtítulo: Denuncian que las acciones son comandadas por el dirigente de Cambiemos Emilio Rached.
+Editoria: Radio 750
+Tags: Santiago del Estero, Comunidades indígenas, Informativo 750, santiago-del-estero, comunidades-indigenas, informativo-750
+URL: https://www.pagina12.com.ar/464017-la-comunidad-indigena-en-santiago-del-estero-protesta-contra/
+Notícia completa (9 blocos):
+Más de 1000 delegados y delegadas de las comunidades indígenas organizadas en el Movimiento Campesino de Santiago del Estero (MOCASE) marcharon para "decir basta a los atropellos, desalojos, bandas armadas y persecuciones políticas".
+“Cientos de campesinos indígenas del Mocase Vía Campesina marchamos en calles de Pinto en Defensa de la vida en nuestro territorios. Repudiando a empresarios del agronegocio que intentan desalojar, atentan contra la vida de las familias con grupos armados, fumigaciones”, reclamaron a través de Twitter.
+"Somos quienes cuidamos nuestra Madre Tierra, donde nacimos y nos criamos. Somos productores de carne de cabra, vaca, oveja, chancho, gallina, de zapallos, sandía y alfa, de huevos, de miel agroecológica, de quesos, de los más diversos alimentos campesinos", sostuvieron.
+A su vez, expresaron ser "quienes abastecemos a los mercados locales con nuestra producción, que también compartimos en nuestros comedores comunitarios". "Exigimos que se terminen los atropellos de los empresarios que intentan usurpar nuestras tierras. Ellos contratan bandas armadas para desalojar a las familias campesinas indígenas", agregaron.
+Unprocessed element [figure]
+En ese sentido, aseguraron que los acusados "buscan llenar sus bolsillos con un modelo rural de un campo sin campesinos, de un monocultivo que envenena las comunidades y deja sus ganancias en el exterior".
+Según denuncian, todos estos accionares son comandados por el dirigente de Cambiemos, y accionista de la empresa AFAGRO S.A., Emilio Rached. A su vez, exigen justicia también por la "falta de 80 millones de pesos destinados a obras de cloacas para el Pueblo de Pinto durante su gestión como intendente".
+Además, piden el esclarecimiento de la muerte de Eliana Cárdenas, luego de que Rached fuera encarcelado por haber abusado de la joven en 1988.
+El Movimiento Campesino, integrado por las organizaciones Ojo de Agua, Quebrachos, Salavina, Aguirre, Mitre, Avellaneda, Taboada y Moreno, marchan con pancartas y gritos que aseguran que no van a "permitir más injusticia" y gritan "basta a las bandas armadas en nuestros territorios".</t>
   </si>
   <si>
     <t>Organizaciones ecologistas marcharon a Plaza de Mayo y realizarán un acampe hasta el domingo</t>
@@ -2330,7 +6076,17 @@
     <t>https://www.pagina12.com.ar/457546-organizaciones-ecologistas-marcharon-a-plaza-de-mayo-y-reali</t>
   </si>
   <si>
-    <t>2022-08-10T19:25:08Z</t>
+    <t xml:space="preserve">Título: Organizaciones ecologistas marcharon a Plaza de Mayo y realizarán un acampe hasta el domingo
+Subtítulo: Organizaciones ecologistas marcharon este viernes desde el Obelisco hacia Plaza de Mayo en rechazo al acuerdo porcino con China y en reclamo por la quema de hum
+Editoria: Radio 750
+Tags: ambientalistas, acampe, Informativo 750, informativo-750
+URL: https://www.pagina12.com.ar/457546-organizaciones-ecologistas-marcharon-a-plaza-de-mayo-y-reali/
+Notícia completa (5 blocos):
+Organizaciones ecologistas marcharon este viernes desde el Obelisco hacia Plaza de Mayo en rechazo al acuerdo porcino con China y en reclamo por la quema de humedales en distintos puntos del país.
+“Queremos un cambio en el tema, más que nada en agronegocio, por eso hoy vamos a marchar hasta Plaza de Mayo”, sostuvo Tomas Caffera, de Rebelión o extinción en diálogo con el móvil de AM750.
+“Hoy concentraremos con un festival muy grande y con un montón de artistas. Y después se viene un tremendo acampe hasta el domingo con feria, con charlas, no solamente para exigir, sino también para informar a toda la ciudadanía”, contó.
+Además, Caeffera explicó que el principal reclamo se concentra en el rechazo al agronegocio: “es lo que nos está llevando a la extinción”, aseveró.
+Unprocessed element [figure]</t>
   </si>
   <si>
     <t>Se realizó la 6° Huelga Global por el Clima: "atrás del fuego hay un desarrollo inmobiliario"</t>
@@ -2339,7 +6095,18 @@
     <t>https://www.pagina12.com.ar/455926-se-realizo-la-6-deg-huelga-global-por-el-clima-atras-del-fue</t>
   </si>
   <si>
-    <t>2022-08-10T19:18:02Z</t>
+    <t xml:space="preserve">Título: Se realizó la 6° Huelga Global por el Clima: "atrás del fuego hay un desarrollo inmobiliario"
+Subtítulo: Este viernes se realizó una marcha desde el Congreso a Plaza de Mayo en el marco de la Huelga Mundial por el Clima y con protestas contra del acuerdo porcino, el agrone
+Editoria: Radio 750
+Tags: medioambiente
+URL: https://www.pagina12.com.ar/455926-se-realizo-la-6-deg-huelga-global-por-el-clima-atras-del-fue/
+Notícia completa (6 blocos):
+Este viernes se realizó una marcha desde el Congreso a Plaza de Mayo en el marco de la Huelga Mundial por el Clima y con protestas contra del acuerdo porcino, el agronegocio y la quema de humedales.
+“Esta es la sexta huelga climátca mundial. En nuestro país se ha expresado en la calle porque desde las redes no alcanza porque lo que están haciendo es destruyendo nuestro ambiente y nuestra vida”, expresó Celeste Fierro, de la Red Ecosocialista en diálogo con el móvil de AM750.
+Además, Fierro explicó que, en nuestro país, la Huelga tuvo dos puntos principales: el acuerdo porcino con China y las quemas en el Delta del Paraná.
+“Ha sido la movilización la que logró que se pase este acuerdo de entendimiento, pero nosotros planteamos que no se tiene que llevar adelante porque es seguir avanzando en el modelo extractivista y agroganadero en una nueva fábrica de pandemia como es la industrialización porcina”, sostuvo.
+Sobre las quemas, la activista aseguró que “atrás del fuego hay un desarrollo inmobiliario. En el Delta del Paraná están intentando avanzar con el agronegocio, por eso es necesario una ley de humedales”
+Unprocessed element [figure]</t>
   </si>
   <si>
     <t>Pedro Peretti: "Las aceiteras son peores que la mesa de enlace, ellos son los que quieren sacar al gobierno"</t>
@@ -2348,31 +6115,99 @@
     <t>https://www.pagina12.com.ar/456113-pedro-peretti-las-aceiteras-son-peores-que-la-mesa-de-enlace</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Pedro Peretti: "Las aceiteras son peores que la mesa de enlace, ellos son los que quieren sacar al gobierno"
+Subtítulo: El productor de Santa Fe y actual integrante del Movimiento Arraigo, Pedro Peretti charló con Pablo Caruso y Luispa Giniger sobre la respuesta de los productores agropecuar
+Editoria: Radio 750
+Tags: Soja, Pedro Peretti, Mesa de Enlace, pedro-peretti, mesa-de-enlace
+URL: https://www.pagina12.com.ar/456113-pedro-peretti-las-aceiteras-son-peores-que-la-mesa-de-enlace/
+Notícia completa (10 blocos):
+El productor de Santa Fe y actual integrante del Movimiento Arraigo, Pedro Peretti charló con Pablo Caruso y Luispa Giniger sobre la respuesta de los productores agropecuarios respecto a la liquidación de cosecha en el marco de las restricciones externas.
+Para Peretti, los grandes conglomerados, "no van a liquidar más allá del ritmo que vienen". "Hay una confusión de la cadena agroindustrial, las aceiteras son peores que la mesa de enlace, ellos son los que quieren sacar al gobierno", agregó.
+"Ese núcleo es la crema del agronegocio, es todo lo que sostiene el andamiaje y son la cobertura política de todos los intentos de desestabilizar", sostuvo,
+Además, explicó que "la soja no está en manos de los productores, el resto está en manos de la aceitera, y no te van a liquidar porque quieren que nos vayamos".
+"Acá hay que cambiar el modelo productivo que es el principal responsable que tiene que ver con la inflación y la desestabilización política", expresó.
+Para el dirigente del Movimiento Arraigo, es necesario "buscar otro modelo productivo, este modelo tiene una irracionalidad tremenda".
+También, explicó que "el 30% del PBI argentino es logística, es lo que se gasta para los viajes de camión. El 50% del costo de la logística, es en dólares, cada vez que aumenta el dólar, aumenta la inflación y la desestabilización política, y encima ahora queremos darle mas negocios a los tipos".
+Peretti destacó las medidas anunciadas por el ministro Guzmán y sostuvo que "contempla muy bien" a los pequeños y medianos productores.
+"Es una parte que inexplicablemente no se anunció por separado. Es una buena noticia para 40 mil exportadores agropecuarios", sostuvo y agregó: "nos contempla en un marco de restricciones y con todos los problemas que sabemos que tenemos".
+Unprocessed element [figure]</t>
+  </si>
+  <si>
     <t>Diputados del Frente de Todos presentaron un proyecto para proteger los ecosistemas de los incendios</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/456065-diputados-del-frente-de-todos-presentaron-un-proyecto-para-p</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Diputados del Frente de Todos presentaron un proyecto para proteger los ecosistemas de los incendios
+Subtítulo: El presidente del bloque del Frente de Todos, Máximo Kirchner, junto a los jefes de lo
+Editoria: Radio 750
+Tags: Máximo Kirchner, Leonardo Grosso, Incendios, maximo-kirchner, leonardo-grosso
+URL: https://www.pagina12.com.ar/456065-diputados-del-frente-de-todos-presentaron-un-proyecto-para-p/
+Notícia completa (6 blocos):
+El presidente del bloque del Frente de Todos, Máximo Kirchner, junto a los jefes de los bloques provinciales, presentó un proyecto de ley de protección de ecosistemas que puedan ser víctimas de incendios provocados o intencionales, para evitar la especulación financiera e inmobiliaria de las tierras.
+La iniciativa determina que por el término de 60 años no se podrán cambiar el uso de los bosques nativos o implantados, áreas naturales protegidas y humedales, a fin de garantizar las condiciones para la restauración de las superficies incendiadas, y de 30 años en el caso de zonas agrícolas.
+"Según el informe del sistema de monitoreo del fuego en Argentina, el 95% de los focos de incendio son intencionales” dijo el diputado Leonardo Grosso en comunicación con Subí, después te explico. “Esta propuesta tiene que ver con atacar uno de los focos que es el negocio inmobiliario. Lo que ha pasado en muchos lugares de Córdoba es que a los años siguientes a los incendios empiezan a haber proliferaciones de desarrollos inmobiliarios privados” detalló.
+Grosso explicó que la intención del proyecto es ir a la raíz del problema y desalentar el cambio del uso del suelo que implica el desmonte para la creación de barrios cerrados o casas quintas. “Lo que planteamos es una modificación a la ley del manejo del fuego donde se prohíbe por 60 años el cambio del tipo de uso de suelo. Ese es el tiempo que necesita la naturaleza para reconstruir y sanar las heridas del fuego” indicó.
+El diputado comentó además que los diputados de Juntos por el Cambio no quisieron firmar este proyecto. “Se ve que no están de acuerdo con el proyecto pero tampoco tienen otra propuesta. Siempre que hay alguna cosa que empiece a develar intereses económicos concretos y los pone arriba de la mesa, Juntos por el Cambio cambia de tema o de dirección. Es muy difícil que defiendan ponerles límites al mercado inmobiliario o al agronegocio porque representan sus intereses” expresó.
+Unprocessed element [figure]</t>
+  </si>
+  <si>
     <t>Acampe en Plaza de Mayo en defensa del ambiente</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/456843-acampe-en-plaza-de-mayo-en-defensa-del-ambiente</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Acampe en Plaza de Mayo en defensa del ambiente
+Subtítulo: Organizaciones sociales y ambientales acamparon frente a la Casa Rosada para pronunciarse en contra “del inminente
+Editoria: Radio 750
+Tags: Casa Rosada, ambientalistas, Informativo 750, casa-rosada, informativo-750
+URL: https://www.pagina12.com.ar/456843-acampe-en-plaza-de-mayo-en-defensa-del-ambiente/
+Notícia completa (4 blocos):
+Organizaciones sociales y ambientales acamparon frente a la Casa Rosada para pronunciarse en contra “del inminente acuerdo porcino con China de los gobiernos provinciales y el Estado Nacional” y para exigir también "el fin de las quemas y las fumigaciones" en campos de zonas cercanas.
+Bajo la consigna "La vida no se negocia" los ambientalistas pidieron que se termine con el extractivismo en el país.
+“Cuando hablamos de lo socio ambiental nos estamos refiriendo a estar en contra del extractivismo y el saqueo de nuestros bienes comunes naturales. Un ejemplo de esto lo vemos en el sector del agronegocio y con el acuerdo porcino con china que ya empezó en Chaco”, dijo Juan Esteche miembro de la agrupación Timón Verde, en comunicación con el informativo de AM750.
+Unprocessed element [figure]</t>
+  </si>
+  <si>
     <t>Eduardo Caími: “Los dueños de la tierra”</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/456446-eduardo-caimi-los-duenos-de-la-tierra</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Eduardo Caími: “Los dueños de la tierra”
+Subtítulo: En su editorial, Eduardo Caími habló del conflicto donde el ex titular de la Sociedad Rural, Luis Etchevehere
+Editoria: Radio 750
+Tags: Luis Miguel Etchevehere, Juan Grabois, luis-miguel-etchevehere, juan-grabois
+URL: https://www.pagina12.com.ar/456446-eduardo-caimi-los-duenos-de-la-tierra/
+Notícia completa (5 blocos):
+En su editorial, Eduardo Caími habló del conflicto donde el ex titular de la Sociedad Rural, Luis Etchevehere, busca desalojar a su hermana de la estancia familiar.
+“La disputa que se ha dado entre los hermanos Etchevere no es solo un desencuentro entre hermanos. Tampoco es solo una cuestión sucesoria. Implica, en virtud de los intereses en pugna, el cruce de dos modelos distintos de administrar, explotar y disponer de un bien vital y estratégico: la tierra. La desigualdad atenta contra la democracia. Y esa ruinosa desigualdad está sustentada en la concentración de la riqueza y las prácticas monopólicas. En esos círculos privilegiados, la concentración de la tierra es abrumadora en la Argentina”, introdujo el conductor de Caími a las 6.
+Caími contó que Dolores Etchevere, hermana de Luis, quiere donar su parte de la estancia al proyecto Artigas. “El Proyecto está conformado por un grupo de campesinos sin tierra, militantes y organizaciones ambientales que recuperaron la Estancia Casa Nueva, ubicada en La Paz, Entre Ríos. El proyecto propone construir un modelo agrario sostenible, libre de agrotóxicos y explotación, distinto al que su familia representa. Es un proyecto productivo que cuida a la madre tierra y respeta los derechos de las familias campesinas", explicó Caimi. “La historia de la Estancia es la historia del modelo de agronegocios que impera en Argentina, que concentra la tierra, destruye la naturaleza, envenena a las comunidades con el uso de agrotóxicos, quema humedales y expulsa a miles de familias campesinas", agregó.
+“A los campesinos que acompañan a Grabois, abogado de Dolores, los lacayos de Etchevehere los llaman en redes “piojosos, sarnosos y punteros políticos”. A don José Gervasio le decían que era un ´vil traidor a la Patria´. La historia vuelve a repetirse. En aquel momento como tragedia, ahora como farsa. No es una nimiedad lo que está en juego. Es estructural. Es parte de la reconstrucción de este país. La propiedad y la tenencia de la tierra. De ello depende mucho nuestro futuro” completó Caími.
+Unprocessed element [figure]</t>
+  </si>
+  <si>
     <t>Bruno Rodríguez, de Jóvenes por el Clima: "la situación de los incendios no da para más"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/455390-bruno-rodriguez-de-jovenes-por-el-clima-la-situacion-de-los-</t>
   </si>
   <si>
-    <t>2022-08-10T19:09:58Z</t>
+    <t xml:space="preserve">Título: Bruno Rodríguez, de Jóvenes por el Clima: "la situación de los incendios no da para más"
+Subtítulo: El militante ecologista de 20 años habló en Pasajera en Trance de la necesidad de aprobar la ley de Humedales.
+Editoria: Radio 750
+Tags: Ley de Humedales, ley-de-humedales
+URL: https://www.pagina12.com.ar/455390-bruno-rodriguez-de-jovenes-por-el-clima-la-situacion-de-los-/
+Notícia completa (6 blocos):
+El militante ecologista de 20 años habló en Pasajera en Trance de la necesidad de aprobar la ley de Humedales. Por qué no alcanza con transformar los hábitos de la clase media para frenar el cambio climático.
+"La ley es una demanda histórica de los colectivos sociaomabientales –recordó Rodríguez–. Este año por los incendios hubo 90.000 hectáreas arrasadas en el Delta del Paraná y 14.000 hectáreas en Córdoba. La situación no da para más. En el delta se queman pastizales para renovar los suelos y avanzar con la frontera agrícola. Necesitamos preservar el escosistema de los humedales, que representa un 23% del territorio nacional". El militante se mostró esperanzado en que la ley obtenga media sanción del Congreso este año.
+Por otro lado, Rodríguez afirmó que la militancia de los movimientos socioambientales necesita entablar alianzas estratégicas con organizaciones campesinas que "incorporan los principios de la agroecología en sus métodos productivos y generan soberanía alimentaria en pequeñas comunidades".
+Las clases medias urbanas son conscientes de las prácticas ecológicas como el separado y el reciclaje, pero eso no alcanza, sostuvo Rodríguez. "Para transformar esa adhesión en potencia política debemos visibilizar los efectos de la crisis climática en los sectores más relegados. Mostrar que no se trata de una cuestión técnica separada de las cuestiones sociales. Cuando avanzan las políticas de desmonte, por ejemplo, pulverizando ecosistemas enteros como bosques imprescindibles para frenar el cambio climático, y además se desplaza a pueblos originarios: en el norte de Salta hubo 35 chicos wichi muertos porque migraron de territorios adonde vivían bien por el modelo del agronegocio".
+"Debemos colectivizar nuestra lucha, no quedarnos en el granito de arena de la individualidad –concluyó–. Sin justicia climática no hay justicia social".
+Unprocessed element [figure]</t>
   </si>
   <si>
     <t>Se extiende la prohibición de fumigar en territorio bonaerense</t>
@@ -2381,7 +6216,17 @@
     <t>https://www.pagina12.com.ar/451334-se-extiende-la-prohibicion-de-fumigar-en-territorio-bonaeren</t>
   </si>
   <si>
-    <t>2022-08-10T18:54:51Z</t>
+    <t xml:space="preserve">Título: Se extiende la prohibición de fumigar en territorio bonaerense
+Subtítulo: Marcelo Racciatti, Jefe de Gabinete de la Defensoría del Pueblo de la Provincia de Buenos Aires, dialogó con Liliana Hendel acerca de la normativa que extiende la prohi
+Editoria: Radio 750
+Tags: [NÃO ENCONTRADO]
+URL: https://www.pagina12.com.ar/451334-se-extiende-la-prohibicion-de-fumigar-en-territorio-bonaeren/
+Notícia completa (5 blocos):
+Marcelo Racciatti, Jefe de Gabinete de la Defensoría del Pueblo de la Provincia de Buenos Aires, dialogó con Liliana Hendel acerca de la normativa que extiende la prohibición de fumigar en territorio bonaerense.
+Unsupported embed [https://w.soundcloud.com/player/?url=https%3A//api.soundcloud.com/tracks/758532547&amp;color=%23087296&amp;auto_play=false&amp;hide_related=false&amp;show_comments=true&amp;show_user=true&amp;show_reposts=false&amp;show_teaser=true]
+Racciatti se refirió a la resolución 246/18 que establecía como límite para las fumigaciones las zonas contiguas a la zona urbana. La misma fue dictada en el mes de enero de 2019 y suspendida un mes después a partir de la reacción de organizaciones ambientalistas ya que, según el dirigente, "no tenía nada que ver con las salud pública".
+Además, Racciatti adelantó que el Ministerio de Desarrollo Agrario de la provincia "decidió prorrogar la suspensión de esa norma y convocar al Conicet, el INTA y entidades del agronegocio a una mesa para trabajar en una normativa definitiva, que es lo que estamos necesitando". "Ojalá que la mesa que de como resultado una normativa clara que ponga por delante la salud pública, los recursos naturales y el medio ambiente, que es lo que tenemos que proteger", expresó.
+Unprocessed element [figure]</t>
   </si>
   <si>
     <t>En JxC se vive en tiempo de campaña</t>
@@ -2393,7 +6238,20 @@
     <t>https://www.pagina12.com.ar/447304-en-jx-c-se-vive-en-tiempo-de-campana</t>
   </si>
   <si>
-    <t>2022-08-06T03:01:00Z</t>
+    <t xml:space="preserve">Título: En JxC se vive en tiempo de campaña
+Chapeau: Larreta en Santa Fe y Gerardo Morales por el conurbano
+Subtítulo: Desde Santa Fe el intendente porteño dijo que el Gobierno "carece de plan". En tanto, Gerardo Morales recorrió el conurbano.
+Editoria: El País
+Tags: Gerardo Morales, Horacio Rodríguez Larreta, Juntos por el cambio, printed-edition, gerardo-morales, horacio-rodriguez-larreta, juntos-por-el-cambio, diario
+URL: https://www.pagina12.com.ar/447304-en-jx-c-se-vive-en-tiempo-de-campana/
+Notícia completa (7 blocos):
+Con la mirada puesta en las elecciones de 2023, los principales referentes de Juntos por el Cambio recorren las provincias y se reúnen con los sectores más enemistados con el oficialismo, para delimitar una agenda acorde a sus intereses. Luego de las demostraciones de apoyo a los grupos concentrados del campo en el marco de la exposición rural de la última semana, la oposición se lanza a conquistar adeptos en todo el territorio nacional. En Santa Fe, Horacio Rodríguez Larreta se reunió con intendentes y empresarios locales; mientras que Gerardo Morales hizo lo propio en el conurbano bonaerense, donde convocó al radicalismo a “crecer” dentro de la coalición.
+El mensaje del jefe de Gobierno porteño fue claro: “Si no hay estabilidad macroeconómica en Argentina, no hay plan viable”. Esta es la referencia obligada de uno de los candidatos con mayor proyección en el frente opositor, y se sustenta en la firme convicción de reducir el gasto público como sea. “Equilibrar lo que tenemos con lo que gastamos”, es el mantra que repiten desde JxC. Así lo escucharon los empresarios que asistieron al encuentro institucional en la Bolsa de Comercio de Rosario (BCR), entidad icónica de los agronegocios en la zona núcleo de esa actividad.
+“Es muy importante que sigamos reivindicando las banderas de la producción y de la agroindustria, porque de la mano de este sector va a llegar la reactivación de nuestra economía”, señaló Rodríguez Larreta, tras participar de la mesa de biotecnología, donde fue recibido por el presidente de la BCR, Miguel Simioni. Luego visitó las instalaciones de Terragene, una empresa del rubro al servicio de la asistencia sanitaria, junto con Carolina Losada y Dionisio Scarpín, ambos senadores nacionales por Santa Fe.
+Por la tarde, luego de almorzar con dirigentes y militantes, el mandatario porteño participó de un encuentro en el marco de la Cumbre Mundial de Alcaldes, que reúne a intendentes de varios países para discutir políticas de mitigación del cambio climático. La jornada se realizó bajo el nombre de “Camino Federal hacia la Cumbre C40”, y fue un espacio de intercambio entre intendentes nacionales y equipos técnicos como antesala al evento que se llevará a cabo en octubre. La agenda de Rodríguez Larreta continúa este sábado en la capital santafecina.
+Por su parte, el titular de la Unión Cívica Radical (UCR) y gobernador de Jujuy, Gerardo Morales, tuvo una serie de encuentros en el municipio de Avellaneda, en una recorrida provincial que lo llevó previamente a Vicente López y Lomas de Zamora. Allí, durante una reunión con empresarios y comerciantes, se manifestó en contra de las medidas anunciadas por el flamante ministro de Economía: “los anuncios de Sergio Massa nos han parecido generalidades, muy pocas, esperábamos más medidas concretas".
+El mandatario jujeño demandó “medidas inmediatas” y sugirió “bajar el costo laboral”, en línea con las posturas más representativas de Juntos por el Cambio. También fue enfático respecto a la necesidad de solucionar el déficit energético, una “crisis autogenerada por el Frente de Todos”, según afirmó.
+La presencia de Morales en suelo bonaerense tiene como trasfondo la interna radical, un podio que completan el senador Alfredo Cornejo y el diputado Facundo Manes. Es por eso que el gobernador de Jujuy cerró la jornada con una visita al comité partidario del distrito, donde llamó a una mayor integración de la UCR en la alianza opositora: “Hemos venido a Avellaneda a seguir reafirmando los desafíos del radicalismo para fortalecerse y crecer dentro de Juntos por el Cambio, en esta coalición que es la esperanza del pueblo argentino”. Asimismo, remarcó la importancia de disputar el voto bonaerense: "No podemos ser un partido nacional sin ser un partido fuerte en la provincia de Buenos Aires”, sentenció. Así, el gobernador jujeño concluyó su paso por el conurbano, en una gira que lo tendrá por Trenque Lauquen, Azul y Olavarría a mediados de mes.</t>
   </si>
   <si>
     <t>Bolsonaro, cada vez más presionado e incontrolable</t>
@@ -2402,7 +6260,34 @@
     <t>https://www.pagina12.com.ar/441563-bolsonaro-cada-vez-mas-presionado-e-incontrolable</t>
   </si>
   <si>
-    <t>2022-08-01T03:01:00Z</t>
+    <t xml:space="preserve">Título: Bolsonaro, cada vez más presionado e incontrolable
+Chapeau: Opinión
+Subtítulo: Desde Río de Janeiro
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Brasil, Opinión, printed-edition, jair-bolsonaro, opinion, diario
+URL: https://www.pagina12.com.ar/441563-bolsonaro-cada-vez-mas-presionado-e-incontrolable/
+Notícia completa (21 blocos):
+Desde Río de Janeiro
+Celso Campilongo, el director de la muy tradicional y centenaria Facultad de Derecho de la Universidad de San Pablo, hasta hace algunos pocos días era desconocido fuera de los medios jurídicos brasileños. Pues se hizo conocido porque en esa condición le tocó divulgar un largo manifiesto escrito en conjunto por una vasta gama de abogados, juristas y dirigentes políticos, defendiendo – en términos amplios, sin mencionar a ningún nombre, a ningún partido – las instituciones, léase, los poderes Ejecutivo, Legislativo y Judicial, con cierto énfasis en el sistema electoral y democrático nacido con la Constitución de 1988.
+Campilongo admitió, al lanzar el texto, el pasado 26 de julio, que esperaba lograr unas 300 adhesiones. Tremendo equívoco: en 24 horas las firmas ya sumaban cien mil. Y este pasado fin de semana ya superaban la marca del medio millón.
+Por más vagos que sean los términos – y vale reiterar: vagos intencionalmente –, el texto alcanza de pleno el hígado del desequilibrado ultraderechista presidente Jair Bolsonaro.
+El mismo título del documento, escrito – acorde a los comentarios más corrientes – no en el portugués hablado en Brasil, sino en un raro y complejo idioma llamado “juridiqués”, por su tono eminentemente jurídico, es aburridamente amplio: “Carta a las brasileñas y brasileños en defensa del Estado democrático de Derecho”.
+Resumiendo: “Carta en defensa de la democracia”, o sea, en contra de todo lo que intenta Bolsonaro.
+Entre los subscriptores hay de banqueros a ex integrantes del Supremo Tribunal Federal, de sindicatos a la poderosísima Federación de Industrias del Estado de San Pablo, de intelectuales y artistas como Chico Buarque y Caetano Veloso a exministros de gobiernos pasados, de profesores universitarios a estudiantes, y, claro, del pueblo.
+Es sabido que manifestaciones multitudinarias por escrito no surten, ni de lejos, el mismo efecto que manifestaciones callejeras, que por ahora se resumen, en Brasil, a los defensores de Bolsonaro.
+Y eso, si se puede considerar que desfiles de motos reuniendo a cuatro o seis mil personas sean “manifestaciones multitudinarias”.
+De la oposición no las hay, por ahora gracias al temor de la reacción de los grandes grupos de secuaces armados, los llamados “milicianos”, movilizados por Bolsonaro y sus hijos trogloditas.
+Pero esa Carta tuvo efecto inmediato y contundente sobre la bizarra figura del patético y peligroso ultraderechista.
+Primero, quedó claro que los dueños del dinero, abrigados bajo el paraguas de la Federación Brasileña de Bancos, ya no están con él.
+Segundo, que un consistente sector del agronegocio también saltó del barco ultraderechista – no por cuestiones ideológicas y mucho menos morales, pero por puro interés en defensa de sus muy bien nutridos bolsillos.
+Y tercero, y quizá más importante, queda establecido que el respaldo de partidos políticos de derecha a Bolsonaro está cada vez más oscilante, no al sabor del viento, pero de las prebendas a ser negociadas en términos de urgencia absoluta, antes de su derrota.
+Crece la desesperación del ultraderechista, se acentúa su desequilibrio, y cuánto más claro se hace el panorama de su posible derrota ya en una primera vuelta más aparecen intentos de preservarlo de la Justicia cuando sea expelido del sillón presidencial.
+Por esos días ganó cierta fuerza la movilización para que el Congreso, dominado – mejor dicho: literalmente alquilado, pues en Brasil ese ala se alquila a cualquiera – por Bolsonaro intente aprobar una enmienda constitucional que asegure, a todos los expresidentes, un foro específico, al nombrarlos senadores vitalicios.
+Algo similar existe en Paraguay, algo igualito fue impuesto en Chile luego de la caída del muy sanguinario Augusto Pinochet.
+En el caso brasileño, sin embargo, el tiro podrá salir por la culata.
+Es que, sin las inmunidades, Jair Bolsonaro caerá en la muy, muchísimo lenta Justicia de Primera Instancia, lo que podría favorecerlo.
+Ya con inmunidad de senador vitalicio, caerá en el Supremo Tribunal Federal, cada vez más claramente indignado no solo por sus ataques feroces y cotidianos a la democracia, pero también por la compra que él lleva a cabo para impedir que cualquiera de los 147 pedidos de deposición salga del cajón del muy corrupto presidente de la Cámara de Diputados, Arthur Lira.
+Es decir: si el futuro de mi pobre país sigue cada vez más nebuloso, el del peor y más inmundo presidente de la historia brasileña se hace cada vez más claro.</t>
   </si>
   <si>
     <t>Los vínculos de los varones del clan Etchevehere con el ruralista detenido por narcotráfico</t>
@@ -2414,6 +6299,27 @@
     <t>https://www.pagina12.com.ar/441544-los-vinculos-de-los-varones-del-clan-etchevehere-con-el-rura</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Los vínculos de los varones del clan Etchevehere con el ruralista detenido por narcotráfico
+Chapeau: La historia detrás de la denuncia de Dolores Etchevehere
+Subtítulo: Leonardo Airaldi fue detenido en el marco de “la causa narco Varisco” por recibir droga desde Paraguay en sus islas, droga que tenía como destino final Rosario. Expresidente de la Sociedad Rural de Diamante compartía negocios de ganado con Luis Etchevehere en una isla llamada El Pillo en el Paraná. La relación con el exintendente Varisco.
+Editoria: El País
+Tags: Luis Etchevehere, Narcotráfico, printed-edition, luis-etchevehere, narcotrafico, diario
+URL: https://www.pagina12.com.ar/441544-los-vinculos-de-los-varones-del-clan-etchevehere-con-el-rura/
+Notícia completa (12 blocos):
+Dolores Etchevehere comienza a escribir un nuevo capítulo en la lucha contra sus hermanos de sangre. “Son estafadores seriales. Para ellos el fraude es una herramienta de trabajo a través de la cual ganan plata, acceden a tierras y consiguen un cargo político”, plantea en el libro Sola (Planeta).
+[H3] Quién es quién en el negocio de exportación de granos y derivados
+La detención por narcotráfico de Leonardo Airaldi, que compartía negocios de ganado en El Pillo, una isla del Paraná, con el exministro de Agroindustria del gobierno de Macri, Luis Miguel Etchevehere, como informan desde Proyecto Artigas que lidera Juan Grabois, volvió a poner en foco la investigación que inició Dolores hace más de una década y su posterior denuncia en la justicia por el vínculo comercial de Airaldi con “los Etchevehere corruptos”, como ella los define. Sin respuesta alguna por parte de la denominada “Justicia”, la única hermana mujer de la familia Etchevehere presentará el caso a la Comisión Interamericana de Derechos Humanos (CIDH) junto a la Fundación Una Puerta, para luego acceder a la Corte Interamericana de Derechos Humanos (CorteIDH).
+Miembro de una familia entrerriana tradicionalmente poderosa, dueña de diarios, establecimientos rurales, empresas y portadora de altos cargos políticos, Dolores sufrió la costumbre machista de los Etchevehere de excluir a las mujeres. Cuando su padre Luis Félix Etchevehere murió en septiembre de 2009, sus tres hermanos varones --Luis Miguel, que fue presidente de la Sociedad Rural y ministro de Agroindustria de Macri, Sebastián y Juan Diego-- le negaron el acceso a sus derechos hereditarios. Entonces fue descubriendo “los manejos espurios” que realizaban y realizan sus hermanos de los bienes que su padre dejó en herencia, que siguen siendo utilizados por “los Etchevehere corruptos”, pese a encontrarse indivisos al estar en trámite la sucesión. En las investigaciones encontró “vaciamientos de empresas, desvíos de fondos societarios, irregularidades en el desempeño de cargos públicos, presentación de documentos falsos y demás maniobras perpetradas de los modos más violentos posibles, en abuso del gran poder ostentado”, resume Dolores a Página/12.
+Narcopolítica y agronegocios
+El exintendente de Paraná, Sergio Varisco, que fue condenado por narcotráfico y murió en mayo de 2021, tenía vínculos con los hermanos Etchevehere. Esos vínculos se manifiestan en la figura de Rubén Pagliotto, exabogado de Varisco y actual abogado de los hermanos Etchevehere, revelan desde Proyecto Artigas. Apadrinado por Luis Miguel Etchevehere y Mauricio Macri, Varisco fue candidato a la intendencia de Paraná en 2015. Daniel “Tavi” Celis, jefe narco de Paraná, financió la campaña de Varisco, referente radical de Cambiemos en la provincia de Entre Ríos. A modo de devolución de favores, una vez en el cargo de intendente, Varisco puso el municipio a disposición de la banda narco, con contratos municipales y cargos; hasta utilizaban camiones municipales para distribuir droga. Después de un largo proceso, a fines de diciembre de 2019, el Tribunal Oral Federal de Paraná condenó a Varisco a seis años y medio de prisión como partícipe necesario de comercialización de estupefacientes.
+Un nexo clave entre la narcopolítica y el ¿narco? Agronegocio, informan desde Proyecto Artigas, es Leonardo Airaldi, expresidente de la Sociedad Rural de Diamante --el departamento de Entre Ríos con uno de los puertos más importantes del Río Paraná--, que fue detenido la madrugada del domingo 24 de julio por Gendarmería en un operativo contra el narcotráfico en Rosario. Airaldi responde a Luis Miguel Etchevehere; juntos participaban del negocio de ganado en El Pillo, una isla del Paraná. Airaldi fue denunciado en el marco de “la causa narco Varisco” por recibir droga desde Paraguay en sus islas, droga que tenía como destino final Rosario. Como si la trama de esta película policial no fuera suficiente, este año las islas del Paraná estuvieron en el centro de la escena por sufrir quemas intencionales para el agronegocio. Una de las islas que se prendió fuego fue justamente El Pillo, donde Airaldi y Etchevehere tenían negocios conjuntos.
+La salida “por arriba”
+El reclamo de Dolores excede lo estrictamente patrimonial; su propia vida corre peligro, según ella misma confiesa. Los sucesos de violencia que sufrió desde muy pequeña, relatados extensamente en su libro Sola, dan cuenta de una profunda trama de relaciones marcadas por un denominador común: extorsión, violencia económica y de género perpetrada por una familia dueña de gran parte de la provincia de Entre Ríos. Ante el desamparo en el que se encontraba acudió a la Fundación Una Puerta, una organización de académicxs y profesionales, presidida por Laura Cantore, “preocupadxs por los derechos humanos, las interseccionalidades de géneros, raza, etnia y otras, como así también por las violencias que afectan la calidad de vida de las personas y a la sociedad toda”, como describen en la página web. Los abogados Facundo Taboada y Silvana Mammana, equipo de trabajo liderado por Juan Grabois, patrocinan a Dolores en las causas judiciales en trámite.
+El abogado Nicolás Cocca, asesor de Dolores en la nueva etapa internacional que se abre ante la Comisión Interamericana de Derechos Humanos (CIDH), subraya que resulta clara la urgencia con la que precisa órdenes judiciales. “Los Etchevehere corruptos continúan realizando maniobras para achicar el activo que por ley le corresponde, agrandando los activos que figuran a nombre de ellos. El daño que esto le ocasiona es de una gravedad absoluta, máxime cuando se tiene en cuenta que Dolores es el sostén de cuatro hijos que dependen de su fuente de ingreso y que la situación es, en consecuencia, un vejamen irreparable a sus derechos como sucesora de su padre y socia de las empresas familiares que actualmente presentan un patrimonio cada vez más flaco, mientras se engrosan los bolsillos de los Etchevehere”, explica Cocca y agrega que las circunstancias “habilitan la solicitud de medidas cautelares ante la CIDH, de conformidad con el artículo 25 de su propio reglamento”.
+El requisito de admisibilidad que deberá cumplir la petición individual para que la CIDH tenga la posibilidad de presentarla en la Corte IDH está expresado en el artículo 46, párrafo 1 (a) de la Convención Americana sobre Derechos Humanos, esto es “que se hayan interpuesto y agotado los recursos de jurisdicción interna, conforme a los principios del derecho internacional generalmente reconocidos”. Podrá interponer una petición individual quien pueda demostrar que, pese a no haber agotado las vías internas, existió en el juicio llevado a cabo en el Estado correspondiente, una violación al debido proceso, denegación de justicia, o bien retardo injustificado de la decisión.
+“Sin dudas esto es lo que ocurre en las diferentes causas por las que transitan los expedientes que tienen a Dolores como parte, ya sea como denunciante o como heredera”, argumenta Cocca. La salida “por arriba”, al acudir al sistema interamericano de protección a los Derechos Humanos, parece condensar las “serias irregularidades que ha habido en todos los procesos y que harían al Estado Argentino responsable”, según la perspectiva del abogado. La lucha de Dolores por lograr “justicia, verdad y reparación” continuará.</t>
+  </si>
+  <si>
     <t>Cecilia Gárgano. “Hay que poner en discusión qué estamos produciendo”</t>
   </si>
   <si>
@@ -2423,7 +6329,27 @@
     <t>https://www.pagina12.com.ar/440271-cecilia-gargano-hay-que-poner-en-discusion-que-estamos-produ</t>
   </si>
   <si>
-    <t>2022-07-28T03:01:00Z</t>
+    <t xml:space="preserve">Título: Cecilia Gárgano. “Hay que poner en discusión qué estamos produciendo”
+Chapeau: ENTREVISTA
+Subtítulo: La investigadora de la Universidad de San Martín y el CONICET cuestiona la construcción hegemónica de un “campo extractivista”, nocivo para la salud y generador de desigualdad, y propone rescatar los espacios invisibilizados que tienen otras formas de producir y relacionarse con la tierra.
+Editoria: Universidad
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/440271-cecilia-gargano-hay-que-poner-en-discusion-que-estamos-produ/
+Notícia completa (14 blocos):
+“El campo”, así planteado, único y total, inanimado, neutro y deshistorizado, ha operado como la institución fundante de nuestro país desde sus orígenes. La supeditación de todos “los campos” posibles a la ubicua y fértil figura de un campo en singular, es una sinécdoque que solapa la construcción hegemónica que se ha desplegado sobre el suelo argentino y que obtura la posibilidad de pensar por fuera del esquema del agronegocio sin enfrentarse a la incertidumbre por el derrumbe de la productividad nacional.
+En “El campo como alternativa infernal. Pasado y presente de una matriz productiva ¿sin escapatoria?”, la doctora en Historia, docente e investigadora de Universidad Nacional de San Martín (UNSAM) y el CONICET, Cecilia Gárgano, se sumerge en los saberes y las marcas vivientes de la agricultura dominante para intentar dilucidar cómo fue posible instalar como ineluctable sostén económico a una dinámica de explotación agrícola que multiplica el extractivismo, el deterioro de la salud y la desigualdad social.
+¿Por qué, con todos los daños que conocemos, esta matriz productiva hegemónica e intensiva en agrotóxicos sigue siendo el único patrón de acumulación posible?, se pregunta la historiadora y docente.
+-¿Cómo y en qué contexto se gesta ‘El campo como alternativa infernal’?
+-El libro retoma algunos trabajos que empecé a desarrollar hace una década, durante mi doctorado. Tenían como eje la situación del sector rural durante la última dictadura, particularmente, la producción de conocimiento científico desde el Estado, con foco en el Instituto Nacional de Tecnología Agropecuaria (INTA). Esa indagación me llevó a recorrer distintos lugares de Argentina en un trabajo de campo e inevitablemente me terminó conectando con las transformaciones rurales que serían el germen de las que terminarían consolidándose durante la década del noventa. El libro reúne esas investigaciones y otras desarrolladas en los últimos años y traza un recorrido histórico yendo hacia atrás y hacia adelante.
+-¿En qué momento se empiezan a sentar las bases del modelo que se cuestiona en el texto?
+-Argentina está marcada por un destino asociado a la exportación agropecuaria desde sus orígenes, desde su inserción al mercado mundial. Yo elegí arrancar desde la década del sesenta, porque en ese momento se instala un paquete tecnológico particular, vinculado a la utilización de insumos químicos, de concentración de capitales y de consolidación de una visión de esto que se va a considerar “el campo”. La realidad es que hay muchos campos en el país, la mayoría de ellos invisibilizados, y el libro se pregunta por esta construcción hegemónica. Como origen, podemos remontarnos a la Conquista del Desierto, aunque mi perspectiva es más contemporánea. Esta construcción del campo como un bloque esconde todas las otras formas de producir, de relacionarse con la tierra y, cuando miramos los mecanismos que la sostienen como destino inexorable para la argentina, aparecen las intervenciones estatales de regulación y desregulación, y la producción de conocimiento científico.
+-¿Cuáles son los momentos históricos decisivos y cómo se apuntala esta matriz de agronegocio?
+-Es imposible no mirar algunos quiebres de nuestra historia reciente; los sesenta y la dictadura aparecen como mojones importantísimos. Los noventa también. De hecho, no sólo el agronegocio, sino cualquier extractivismo, está montado sobre un aparato jurídico y regulatorio liberalizado, que, no casualmente, se consolida en esos años y que se viene heredando a pesar de los cambios de gobiernos como una política de Estado cada vez más afianzada. A tal punto es así, que si miramos cuáles son los futuros que se nos proponen, muchas veces tienen que ver con intensificar este esquema. Las voces críticas son silenciadas --las científicas y las de la población organizada--, porque intentan poner en cuestión los límites del modelo. Es inevitable pensar en los intereses en juego, tanto de las clases dominantes locales como de la articulación con poderes económicos internacionales. En un mercado donde quienes ganan con el agronegocio, a nivel mundial, son unas pocas empresas muy concentradas.
+Unprocessed element [blockquote]
+-El libro hace uso de la categoría analítica “alternativa infernal” para explicar la forma en que se plantea este modelo. ¿De qué se trata este concepto?
+-Es una noción de dos autores franceses: Isabelle Stenger (filósofa) y Philippe Pignarre (historiador). Llaman así a situaciones que se nos presentan sin historia, como naturales y en forma de falsas encrucijadas; en estos planteos no es posible elegir, porque cualquiera de las dos opciones que se proponen nos llevan a otra encrucijada. En este caso, yo la uso para pensar el campo argentino, porque existe una dicotomía instalada que por un lado postula la profundización de esta matriz productiva, intensiva en agrotóxicos –con todos los daños socioeconómicos, ambientales, de éxodo rural y de concentración de la riqueza que sabemos que conlleva– y por el otro sugiere una crisis estructural; un “caernos del mapa”. Esa es una alternativa infernal. Y si bien no hay una receta para salir de este dilema, el libro trata de pensar los mecanismos que lo construyeron a lo largo de la historia y recorre algunas narrativas surgidas desde las poblaciones afectadas, un movimiento potente que pone en disputa lo común, las formas de producir y de habitar la tierra. Hay que poner en discusión qué estamos produciendo.
+-También aparecen las ideas de “desnaturalizar” y “repolitizar”, como estrategias críticas…
+-Sí, desnaturalizar tiene que ver con devolverle la historia a esto que se nos aparece como dado; a todo lo que vimos repetirse de forma sistemática en los últimos años: incendios forestales en humedales de Corrientes, en el delta del Paraná, las inundaciones, las sequías, y también los reclamos del tipo sanitario, que en general son exhibidos como eventos excepcionales, como malos usos de buenas prácticas agrícolas. Pero la verdad es que están en todos lados. Entonces, recuperar la historia, descubrir cuáles son los mecanismos que intervienen, qué rol juega el Estado, los saberes, el empresariado, saca la condición de natural, de evento aislado y da cuenta de algo estructural, propio de la matriz. Repolitizar, va orientado a volver a poner en discusión preguntas que ya parecen cerradas. ¿Qué producimos? ¿Qué comemos? ¿De quién es la tierra? Ese es un poco el ejercicio. Es intentar operar un contra movimiento frente a dos operaciones del capitalismo extractivista: la de homogeneizarlo todo –que en nuestro país se ve en la repetición de un mismo paisaje, un monocultivo sojero que aplana la biodiversidad, las economías regionales y las formas de vida con sus sujetos sociales–, y la de fragmentar y encapsular problemáticas como si fueran diversas cuando en realidad son comunes, colectivas y estructurales.</t>
   </si>
   <si>
     <t>Marcos Stábile</t>
@@ -2438,7 +6364,21 @@
     <t>https://www.pagina12.com.ar/439814-alimenticias-con-ganancias-record</t>
   </si>
   <si>
-    <t>2022-07-26T03:01:00Z</t>
+    <t xml:space="preserve">Título: Alimenticias con ganancias record
+Chapeau: Obtuvieron 382 mil millones de dólares desde 2020
+Subtítulo: La organización Oxfam advirtió sobre la enorme concentración de la riqueza desde la pandemia y el aumento de las hambrunas.
+Editoria: Economia
+Tags: Desigualdad, pandemia, printed-edition, diario
+URL: https://www.pagina12.com.ar/439814-alimenticias-con-ganancias-record/
+Notícia completa (8 blocos):
+El aumento de la riqueza de los billonarios del sector de la alimentación durante dos semanas bastaría para responder a la crisis del hambre en Africa del Este. Mientras que en Etiopía, Kenia y Somalia muere una persona cada 48 segundos, los empresarios dedicados a la producción, industrialización y comercialización de alimentos aumentaron su riqueza en 382.000 millones de dólares desde marzo de 2020 a marzo de este año.
+Los datos fueron compartidos en el informe "Beneficiarse del dolor" que elaboró la organización Oxfam de acuerdo a una investigación que aborda el periodo marzo 2020 a marzo 2022. Hanna Saarinen, responsable de la politica alimentaria de la organización fue contundente: "Se está acaparando una cantidad monstruosa de riqueza en la parte superior de las cadenas de suministro". El informe concluye que "menos de dos semanas de sus beneficios serían más que suficientes para financiar la totalidad del llamamiento de la ONU para Africa oriental", que actualmente enfrenta una falta de fondos.
+La ONG destacó que los multimillonarios de este sector aumentaron su riqueza colectiva en 382.000 millones de dólares desde 2020, mientras que el llamamiento formulado por la ONU es por un total de 6.200 millones de dólares. El programa se encuentra actualmente financiado apenas en un 16 por ciento, en medio de una gran inflación de los precios de los alimentos.
+Oxfam destacó que los habitantes de países en Africa Oriental gastan hasta el 60 por ciento de sus ingresos en alimentos. Es una región que depende en gran medida de los alimentos importados. De esta manera, los alimentos y bebidas representan el 54 por ciento del IPC en Etiopía -frente al 11.5 por ciento en el Reino Unido, por ejemplo-, mientras que en Somalia los precios del maíz eran seis veces más altos que los precios mundiales en mayo respecto al año anterior.
+En algunas regiones somalíes, el gasto de la canasta básica se disparó más del 160 por ciento en comparación con 2021, con el precio de un kilo de sorgo un 240 por ciento más alto que el promedio de los últimos cinco años. En el caso de Etiopía, la inflación alimentaria fue 43,9 por ciento desde el año pasado, con un aumento del 70 por ciento de los precios de los alimentos entre enero y mayo de este año, más del doble del aumento mundial. En Kenia, el precio de la harina de maíz, principal alimento básico, se duplicó en siete meses y aumentó un 50 por ciento en solo entre junio y julio, un aumento de los precios de los alimentos y la energía que aumentará la pobreza en un 2,5 por ciento, empujando a alrededor de 1,4 millones de personas a la pobreza extrema.
+"Necesitamos un nuevo sistema alimentario mundial para acabar realmente con el hambre. Un sistema que funcione para todos. Los gobiernos pueden y deben movilizar suficientes recursos para prevenir el sufrimiento humano. Una buena opción sería gravar a los súper ricos que han visto dispararse su riqueza a niveles récord durante los últimos dos años", volvió a poner sobre la mesa Saarinen y apuntó: "Este sistema alimentario global, en esencia roto, que es explotador, extractivo, mal regulado y en gran parte en manos de grandes agronegocios, se está volviendo insostenible para las personas y el planeta y está empujando a la inanición a millones, en Africa Oriental y en todo el mundo".
+Saarinen insistió con que las naciones ricas deben cancelar de inmediato la deuda de países pobres, que se ha duplicado en la última década, a fin de permitirles liberar recursos para hacer frente al aumento vertiginoso del hambre e importar el grano necesario. "Este dinero puede y debe recuperarse fácilmente gravando a los ultra ricos", insistió.
+Oxfam solicitó además que los gobiernos regulen mejor los mercados de alimentos y garanticen reglas de comercio internacional más flexibles a favor de los consumidores, trabajadores y agricultores más vulnerables. De esta forma, reclamó que gobiernos y donantes apoyen a la pequeña agricultura, que en Asia y Africa subsahariana proporcionan más del 70 por ciento del suministro de alimentos.</t>
   </si>
   <si>
     <t>Emilio Pérsico: "No es el momento de discutir el Salario Básico Universal"</t>
@@ -2450,7 +6390,22 @@
     <t>https://www.pagina12.com.ar/439323-emilio-persico-no-es-el-momento-de-discutir-el-salario-basic</t>
   </si>
   <si>
-    <t>2022-07-23T03:01:00Z</t>
+    <t xml:space="preserve">Título: Emilio Pérsico: "No es el momento de discutir el Salario Básico Universal"
+Chapeau: El dirigente del Movimiento Evita marcó diferencias con las otras organizaciones sociales afines al Gobierno que impulsan el proyecto
+Subtítulo: El dirigente opinó que no ve "un escenario de saqueos en la Argentina" ya que "hay un nivel de ayuda social que no lo genera" y afirmó que la prioridad "es colaborar lo más posible en darle fuerza al Gobierno para que pueda resolver esta crisis". Unidad Piquetera volverá a movilizarse a Plaza de Mayo el miércoles próximo "contra el ajuste del Gobierno" e invitó a sumarse a las organizaciones que reclaman el SBU.
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/439323-emilio-persico-no-es-el-momento-de-discutir-el-salario-basic/
+Notícia completa (9 blocos):
+El secretario general del Movimiento Evita, Emilio Pérsico, dejó al descubierto las diferencias entre los movimientos sociales afines al oficialismo al sostener que "no es el momento de discutir el Salario Básico Universal (SBU)". Una propuesta impulsada el Movimiento de Trabajadores Excluidos (MTE) y del Frente Patria Grande, liderado por Juan Grabois, que esta semana reclamó al Gobierno medidas urgentes para que los sectores más vulnerables de la sociedad puedan paliar la escalada inflacionaria que produce la corrida cambiaria y hasta vaticinó una posible convulsión social si no se adoptan soluciones. En tanto, los movimientos territoriales de izquierda volvieron a convocar para el miércoles 27 de julio a una movilización en Plaza de Mayo “contra el ajuste del Gobierno”, al que invitaron a las organizaciones sociales que reclaman por la implementación del SBU.
+Alineado al gobierno de Alberto Fernández, el subsecretario de Promoción para la Economía Social Pérsico, marcó distancia del reclamo por el SBU, cuyo proyecto presentó el diputado Itai Hagman (del Frente Patria Grande) y que acompañaron diputados de la bancada del Frente de Todos, incluidos Leonardo Grosso y Eduardo Toniolli del Movimiento Evita. Sobre la iniciativa, Pérsico dijo que le "parece muy bien, pero lo primero que tenemos que hacer, porque hay una corrida bancaria de sectores que están apostando fuertemente detrás de estos intereses, es colaborar lo más posible en darle fuerza al Gobierno para que pueda resolver esta crisis, en este vendaval en el que estamos en este momento". "Tenemos a la nueva ministra que todavía no logró tener una semana en la que sostener las variables económicas", afirmó agregó el funcionario.
+Una postura en la que no coinciden otros encuadramientos territoriales que integran el FdT, que alertan que los trabajadores de la llamada economía popular “no da para más” porque está creciendo el hambre en la Argentina. Grabois se encargó de expresar esa situación durante la jornada de lucha por la implementación del SBU en un duro discurso dirigido al Presidente: "Es fácil Alberto, es muy sencillo el reclamo. Si no, para qué te pusimos ahí. Te pusimos ahí para que haya menos pobreza, no para que haya más. Si no te gusta el Salario Universal, inventá otra cosa. No digas que hay que calmar a los mercados, vení y calmamos a nosotros", soltó Grabois durante el acto en Puente Pueyrredón y advirtió que la crisis podría sacar a la calle a los sectores mas vulnerables en busca de alimentos.
+Consultado sobre esta posibilidad, Pérsico opinó que no ve "un escenario de saqueos en Argentina" ya que "hay un nivel de ayuda social que no lo genera". "No veo un escenario de saqueos en Argentina. No los hay desde hace mucho tiempo, porque hay un nivel de ayuda social que no lo genera. Ni en el Gobierno anterior ni en este. No creo que esté ahí el problema. Es opinión de Juan y la respeto", aclaró el funcionario del Ministerio de Desarrollo Social.
+Aunque la propuesta del SBU no convence a todos los integrantes del FdT, la senadora kirchnerista Juliana Di Tullio (Unidad Ciudadana-FdT) trabaja –incluso junto a los movimientos sociales— en la elaboración de un proyecto alternativo en busca de crear un “complemento” de ayuda social dirigido a combatir la indigencia.
+En tanto, los movimientos territoriales de izquierda anunciaron que volverán a la calle el próximo miércoles para insistir en sus demandas, como la reapertura y “universalización de los planes potenciar Trabajo”, entre otras medidas.
+"Vamos a movilizar fuertemente el 27 a Plaza de Mayo, contra el ajuste y por todos los reclamos. Un ajuste que golpea por igual a los barrios y a los trabajadores. A esta acción hemos invitado a la UTEP, que, coincidiendo en muchos puntos, quedó en debatir la posibilidad de confluir", sostuvo el dirigente del Polo Obrero, Eduardo Belliboni. El referente de Unidad Piquetera, dejó así abierta la posibilidad de sumar a sus reclamos a los sectores que hasta ahora se alinean dentro del oficialismo.
+La movilización de Unidad Piquetera también fue respaldada por los diputados del Frente de Izquierda. “Es urgente que se otorgue un aumento general de salarios y jubilaciones para que nadie cobre por debajo de la canasta familiar y establecer la actualización mensual automática según el aumento de los precios, para lo cual es imprescindible romper con toda sumisión al FMI”, afirmó Nicolás del Caño. El legislador del FIT calificó como “vergonzoso lo de la CGT, que se despertó de su siesta eterna para convocar a una movilización a favor del Gobierno. Es necesario un paro nacional que sea el inicio de un plan de lucha para que la mayoría trabajadora intervenga con su propio programa para dar una salida favorable a las mayorías ante el agravamiento de la crisis y evitar que los platos rotos los paguen los mismos de siempre”.
+En tanto, Myriam Bregman denunció que “los tarifazos del Gobierno son para cargarle la crisis al pueblo trabajador mientras se sigue beneficiando a las grandes patronales con subsidios y permiten maniobras especulativas” y agregó: “reclama el agronegocio y suben los alimentos. Reclaman los transportistas y suben el boleto. El gobierno cede ante los poderes económicos en medio de una corrida que pide devaluación”.</t>
   </si>
   <si>
     <t>Una indagación del campo como espacio de lucha de poderes y resistencias: ¿qué desastre ecológico y social nos depara el futuro?</t>
@@ -2462,7 +6417,21 @@
     <t>https://www.pagina12.com.ar/436702-una-indagacion-del-campo-como-espacio-de-lucha-de-poderes-y-</t>
   </si>
   <si>
-    <t>2022-07-15T03:01:00Z</t>
+    <t xml:space="preserve">Título: Una indagación del campo como espacio de lucha de poderes y resistencias: ¿qué desastre ecológico y social nos depara el futuro?
+Chapeau: ENSAYOS
+Subtítulo: La historiadora Cecilia Gárgano ensaya algunas respuestas posibles para una avalacha de problemas que están ocurriendo ahora mismo, entre incendios, depredaciones y extractivismo sin control.
+Editoria: Las12
+Tags: extractivismo, Ley de Humedales, Incendios en el Delta, printed-edition, ley-de-humedales, incendios-en-el-delta
+URL: https://www.pagina12.com.ar/436702-una-indagacion-del-campo-como-espacio-de-lucha-de-poderes-y-/
+Notícia completa (8 blocos):
+“De qué forma fue posible instalar como única salida una matriz productiva que multiplica en forma sincrónica el daño a la salud colectiva, la depredación ambiental y la desigualdad social”, fue la pregunta que guió la investigación de la historiadora Cecilia Gárgano que dio origen al libro El campo como alternativa infernal, pasado y presente de una matriz productiva ¿sin escapatoria? de Ediciones Imago Mundi.
+El libro, como bien explica su autora en el prólogo, no da respuestas únicas, ni una receta para salir de la encrucijada pero busca abrir entramados “e iluminar algunos mecanismos que operan en su construcción, así como en su legitimación”. Fue escrito durante el tiempo de confinamiento impuesto por la pandemia de Covid 19. “La escritura transcurrió en el marco de la experiencia de la pandemia que conjugó en forma inédita la crisis del capitalismo del despojo con su expansión. Como una de las fotos de la intensificación de un patrón extractivista que continúa avanzando, miles de hectáreas fueron arrasadas en más de una decena de provincias y se redujeron a cenizas kilómetros de humedales en el Delta del Paraná. También en los Esteros del Iberá”, escribe Cecilia a la vez que aclara además que mientras todo eso ocurría, se cajoneaba el proyecto de ley de humedales y perdía estado parlamentario.
+En sus 266 páginas, Gárgano habla de fuegos, sequías e inundaciones conectados por la ruta del agronegocio que mercantilizan espacios vitales. “De esa urgencia, de la impotencia que nos genera la contemplación del desastre que sabemos no accidental y multiplicador de la asimetría social, también surge este libro”, dice Cecilia. Once años atrás, el comienzo de una investigación doctoral sobre la producción de conocimientos orientados al agro argentino en una de las principales agencias estatales en tiempos de la última dictadura, la llevó a conocer diferentes geografías y a pensar en el Estado y en la trayectoria histórica de la apropiación privada de conocimientos científicos generados en la educación pública. “Esta transformación del saber en mercancía además de redundar en ganancias corporativas supone la privatización de objetivos y contenidos. También contiene implicancias socioambientales y políticas sumamente relevantes para el agronegocio, que en estas páginas se problematizan”, se lee en el prólogo.
+El campo como alternativa infernal tiene dos partes. La primera está conformada por la historia, que recorre el trayecto desde la Revolución verde al agronegocio desde los años sesenta hasta el neoliberalismo actual y la segunda parte, que se llama “Territorios sacrificados. Postales de pueblos fumigados”, en la que recoge las experiencias de las resistencias populares.
+La autora dice que el libro es resultado del pensamiento colectivo construido en espacios públicos como la Facultad de Filosofía y Letras de la UBA donde se formó como historiadora, la Universidad Nacional de San Martín (UNSAM) y el Conicet, instituciones donde trabaja como docente e investigadora. Pero también fue gracias a los estudiantes, dice, que sin saberlo, contribuyeron a muchas de las reflexiones que están en sus páginas.
+“Convertir territorios y poblaciones en zonas de sacrificio o afrontar una crisis irresoluble. Propagar un modelo agrícola intensivo en agrotóxicos o quedarnos sin PBI. ‘No hay otra salida’, ‘necesitamos mantener los niveles de productividad’ y ‘generar divisas’. Avalado por estos argumentos, en Argentina el monocultivo sojero se expandió en tiempo récord, transformando los suelos en un laboratorio a cielo abierto. Sus consecuencias son parte de la postal cotidiana del despoblamiento rural, pérdida de la biodiversidad y deterioro sanitario. ¿Cómo fue construida esta encrucijada? ¿Qué mecanismos estatales, conocimientos y discursos la sostienen? Este libro analiza la historia y el funcionamiento de esta alternativa infernal, para desnaturalizar algunos de sus supuestos”, se lee en la contratapa que invita a abrir sus páginas.
+Se puede descargar gratis de este link: ww.edicionesimagomundi.com/producto/el-campo-como-alternativa-infernal/
+O pedir en papel a: campo.alternativainfernal@gmail.com</t>
   </si>
   <si>
     <t>Inés Hayes</t>
@@ -2477,7 +6446,24 @@
     <t>https://www.pagina12.com.ar/437117-jair-bolsonaro-le-propondra-a-ucrania-terminar-la-guerra-com</t>
   </si>
   <si>
-    <t>2022-07-14T19:44:21Z</t>
+    <t xml:space="preserve">Título: Jair Bolsonaro le propondrá a Ucrania terminar la guerra "como Malvinas"
+Chapeau: Extrañas declaraciones del presidente brasileño
+Subtítulo: Sin aportar muchos detalles, el mandatario ultraderechista aseguró que tiene "la propuesta" para el cese el fuego en Europa. La reunión con Volodimir Zelenski y los lazos con Vladimir Putin.
+Editoria: El Mundo
+Tags: Jair Bolsonaro, Volodimir Zelenski, Conflicto Rusia Ucrania, jair-bolsonaro, volodimir-zelenski, conflicto-rusia-ucrania, diario
+URL: https://www.pagina12.com.ar/437117-jair-bolsonaro-le-propondra-a-ucrania-terminar-la-guerra-com/
+Notícia completa (11 blocos):
+El presidente de Brasil, Jair Bolsonaro, anunció este jueves que propondrá lo que llamó "la solución Malvinas" a su homólogo ucraniano, Volodimir Zelenski, con quien conversará el próximo lunes para darle una salida al conflicto armado con Rusia.
+"Voy a dar mi opinión, lo que yo pienso. La solución para el caso la tengo... Como terminó la guerra de Argentina con Reino Unido en 1982. Es por ahi la salida. Lamentamos, son cosas que duelen, pero hay que entender la situación. Fue Zelenski que pidió hablar con nosotros y yo acepté porque Zelenski tiene un gran país para administrar", declaró Bolsonaro a CNN, según replicó CNN Brasil.
+Al promover su propuesta, el mandatario brasileño no detalló cuál es el modelo de la "solución Malvinas", donde el conflicto entre la Argentina y Gran Bretaña terminó con la rendición negociada, sin que figure la palabra incondicional, de las tropas el 14 de junio de 1982 por parte del gobernador Mario Benjamín Menéndez ante el general de las tropas británicas, general Jeremy Moore, en Puerto Argentino.
+De esta forma, Bolsonaro no quiso precisar a qué se refería sobre la "solución Malvinas", debido a que en las islas argentinas hasta el momento existe ocupación del Reino Unido, que se ha negado desde entonces a cumplir las resoluciones del Comité de Descolonización de la ONU para sentarse a negociar tras haber vencido la guerra en 1982.
+[H2] El rol de Bolsonaro en el conflicto Rusia - Ucrania
+Desde el estallido de la guerra, Bolsonaro ha evitado condenar los ataques rusos en Ucrania y mantenido una posición "neutral" y de "equilibrio" ante el conflicto, al priorizar los intereses de su país.
+El mandatario se ha mostrado crítico con el cerco de sanciones económicas impulsadas por las potencias de la Organización del Tratado del Atlántico Norte (OTAN) contra el Gobierno de Vladimir Putin, al que visitó en febrero pasado, en vísperas del inicio de la guerra, y con el que mantiene una relación fluida.
+"Voy a hablar bastante con él (Zelenski). Es un líder y le voy a dar mi opinión. Esta guerra ha causado un trastorno no sólo en Brasil. En Brasil menos; mucho más en Europa", matizó el jefe de Estado brasileño.
+Además, el líder de extrema derecha defendió haberse reunido en febrero con el presidente ruso, Vladimir Putin, para garantizar la provisión de fertilizantes para el agronegocio brasileño, principal base electoral bolsonarista de cara a las elecciones del 2 de octubre.
+Asimismo, Bolsonaro anunció el pasado lunes ante medios locales que tiene "casi cerrada" una negociación para adquirir diésel desde Rusia, en un acuerdo comercial que implica romper las sanciones económicas impuestas a Moscú desde EEUU y la Unión Europea.
+El jefe de Estado brasileño ya había abierto la puerta a la compra a finales de junio. "Ahora está casi cerrado un acuerdo para comprar diésel más barato de Rusia. Petrobras lo compraba más caro", comentó Bolsonaro.</t>
   </si>
   <si>
     <t>Bolsonaro afirma que tiene “casi cerrado” un acuerdo para comprar diésel más barato a Rusia</t>
@@ -2486,9 +6472,6 @@
     <t>https://www.pagina12.com.ar/lbpupdates/436247</t>
   </si>
   <si>
-    <t>2022-07-11T23:30:47Z</t>
-  </si>
-  <si>
     <t>La Justicia prohibió el trigo transgénico en la Provincia de Buenos Aires</t>
   </si>
   <si>
@@ -2498,7 +6481,23 @@
     <t>https://www.pagina12.com.ar/436051-la-justicia-prohibio-el-trigo-transgenico-en-la-provincia-de</t>
   </si>
   <si>
-    <t>2022-07-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: La Justicia prohibió el trigo transgénico en la Provincia de Buenos Aires
+Chapeau: La prohibición, temporal, fue emitida por un juez marplatense al trigo modificado de Indear
+Subtítulo: El publicitado trigo transgénico fue prohibido en la provincia de Buenos Aires.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/436051-la-justicia-prohibio-el-trigo-transgenico-en-la-provincia-de/
+Notícia completa (10 blocos):
+El publicitado trigo transgénico fue prohibido en la provincia de Buenos Aires. Se trata de una fallo judicial que hizo lugar a una medida cautelar solicitada por productores agroecológicos, organizaciones socioambientales, comunidades indígenas y vecinos afectados por el nuevo transgénico y por el herbicida glufosinato de amonio. "Es un fallo histórico y una prueba más de lo insostenible del modelo de agronegocio, en base a transgénico y agrotóxicos", afirmó Gabriel Arisnabarreta, integrante de la organización Ecos de Saladillo y uno de los demandantes.
+"Se ordena la prohibición temporal en todo el territorio de la provincia de Buenos Aires del uso y liberación a cielo abierto de la variedad exótica de trigo modificado genéticamente de la empresa Indear hasta tanto se implemente la Comisión de Biotecnología y Bioseguridad Agropecuaria a los efectos de elaborar un informe con sus recomendaciones respecto a la introducción y liberación de de material transgénico y sus efectos en los recursos naturales, la salud, la producción y la comercialización", destaca la sentencia en su parte resolutiva del juez Néstor Salas, del Juzgado de Responsabilidad Penal Juvenil 2 de Mar del Plata.
+El trigo transgénico "HB4" de la empresa Bioceres-Indear --en sociedad con la científica del Conicet y la Universidad del Litoral, Raquel Chan-- fue autorizado por el gobierno nacional en mayo pasado. Se trata del primero trigo transgénico del mundo, cuestionado tanto por sectores socioambientales como por empresarios del agronegocio (por el rechazo comercial que genera). En la empresa tienen participación accionaria multimillonarios como Hugo Sigman y Gustavo Grobocopatel, y empresarios de la Asociación de Productores de Siembra Directa (Aapresid).
+La demanda fue presentada por 37 personas de diversas organizaciones y localidades bonaerenses, representados por el abogado marplatense Lucas Landivar. La acción judicial cuenta con 54 páginas con numerosas argumentaciones sobre los peligros del transgénico, sus químicos asociados y la vulneración de derechos que implica. Detalla la contaminación que provocará al cultivo convencional, la falta de consenso social, los riesgos para la salud y el ambiente, entre otros aspectos.
+El juez Salas, en su fallo firmado el 1 de julio, destaca que el trigo transgénico puede generar un "daño grave e irreversible" en la salud de la población y en el ambiente. También subray que se podrá contaminar al trigo convencional. Hace hincapié en la vigencia de la Ley General del Ambiente (25.675) y el "principio precautorio": cuando haya posibilidades de daño grave al ambiente o la salud, se deberán tomar medidas de prevención.
+Tanto la presentación como el fallo resaltan la Ley 12.822, sancionada en la provincia en 2001. Dos décadas después, aún no se implementó la Comisión de Biotecnología que debe evaluar los transgénicos. El juez Salas establece la suspensión del trigo transgénico hasta tanto esa comisión se constituya e informe sobre los riesgo del trigo HB4. Incluso cita preguntas de la fundamentación de la Ley: "¿El Ministerio de Salud ha certificado la inmunidad del ser humano a los Organismos Genéticamente Modificados (OGMs)? ¿La introducción de los transgénicos está asimilada a partir de un debate público o es un simple concepto de innovación genética para cosechar mayores ganancias? ¿Está tecnología afecta a los cultivos tradicional y la biodiversidad?".
+Arisnabarreta, de la organización Ecos de Saladillo, resaltó el incumplimiento de la norma 12.822: "Queda claro que este modelo de agro no se pudo haber impuesto sino era violando leyes. Aunque lo establece la legislación, en ningún transgénico hubo evaluación de impacto ambiental, no hubo evaluación en la salud, no se tuvo en cuenta qué puede pasar con la biodiversidad". Y apuntó a la responsabilidad gubernamental y académica: "Se habla que este trigo es producto de la biotecnología nacional y la verdad que para nada nos enorgullece, al contrario. Nos gustaría que el Estado y los científicos investiguen y pongan fondos para producir alimentos sanos, en equilibrio con la naturaleza".
+La presentación judicial cuestiona que el Ministerio de Salud de la Nación no presentó ningún trabajo científico que acredite certeza de inocuidad para la salud por la ingesta de transgénicos. El planteo tiene directa relación con la forma irregular de aprobación de organismos genéticamente modificados: desde 1996 que se autorizan en base a estudios de las propias empresas, informes que además son "confidenciales" y la Conabia (Comisión Nacional de Biotecnología, clave en la autorización "técnica") está dominada por las propias empresas que producen los transgénicos y agrotóxicos.
+El abogado Lucas Landivar resaltó las responsabilidades políticas en la aprobación de transgénicos. "Hay delitos que se están configurando, como encubrimiento, complicidad en la contaminación y el rol del funcionario público, que con una resolución administrativa legitima una práctica antijurídica, porque desoye las leyes que establecen el orden precautorio que se debiera tener". Consideró que la decisión judicial también puede ser un punto de partida para el poder político: "Es una gran oportunidad para el Gobernador, y una necesidad imperiosa para el pueblo, el promover y lograr una evaluación independiente sobre los impactos y riesgos de los OGM, que lleva un retraso de veinte años en Buenos Aires".
+Con la consigna “Con nuestro pan no”, más de 250 organizaciones sociales, campesinas y ambientales de Argentina rechazan la autorización del trigo transgénico. Calificaron la aprobación como “un avance del agronegocio sobre la alimentación de los pueblos y la agricultura que no podemos aceptar”. Puntualizaron 20 puntos que justifican el rechazo y exigieron al gobierno nacional que dé marcha atrás con la medida.</t>
   </si>
   <si>
     <t>Amenazan a un cura por denunciar el agronegocio: "Me dijeron que no me meta en lo que no me interesa"</t>
@@ -2510,7 +6509,18 @@
     <t>https://www.pagina12.com.ar/434775-amenazan-a-un-cura-por-denunciar-el-agronegocio-me-dijeron-q</t>
   </si>
   <si>
-    <t>2022-07-06T02:14:42Z</t>
+    <t xml:space="preserve">Título: Amenazan a un cura por denunciar el agronegocio: "Me dijeron que no me meta en lo que no me interesa"
+Chapeau: Pasó en Santiago del Estero
+Subtítulo: El grupo Curas en la Opción por los Pobres asegura que la intimidación se debe al apoyo que brinda el sacerdote de Nueva Esperanza a los campesinos que protestan contra el avance del desmonte.
+Editoria: Radio 750
+Tags: Agronegocio, Santiago del Estero, La casa invita, santiago-del-estero, la-casa-invita
+URL: https://www.pagina12.com.ar/434775-amenazan-a-un-cura-por-denunciar-el-agronegocio-me-dijeron-q/
+Notícia completa (5 blocos):
+Desde el grupo Curas en la Opción por los Pobres denuncian que un sacerdote que pertenece a la parroquia "Nuestra Señora de la Merced", en Nueva Esperanza (Santiago del Estero), fue amenazado por su apoyo a los reclamos contra el avance del agronegocio. "El miércoles 29 de junio me llegó un whatsapp que decía que no me meta en lo que no me interesa y que los caminos del monte de Pellegrini son largos y solitarios", relató el cura amenazado Rubén Lassaga en La Casa Invita por AM750.
+Unsupported embed [https://mdstrm.com/embed/62c4e3d87458326715d00e79]
+Ruben Lassaga es párroco de "Nuestra Señora de la Merced" en Santiago del Estero hace 3 años. Es un sacerdote involucrado en su comunidad: "En Santiago del Estero y el NOA la lucha por la tierra no es nueva, se ha recrudecido en la década del '90, con la autorización de la semilla transgénica y la expansión de la frontera agropecuaria", contó en AM750.
+Es ese sentido, Lassaga explicó que el mismo día que recibió la amenaza -el miércoles 29 de junio- en la comunidad llamada "La Armonía" un grupo de encapuchados "corrió a una familia" de su hogar: "Era una señora mayor con su hija bebe y un hijo joven. Al hijo lo golpean, los echan. Les mataron los animales y les quemaron la casa".
+Consultado por la situación legal, el sacerdote contestó que "se está investigando", pero denunció la complicidad entre "algunos fiscales y el poder político": "Siempre hay funcionarios corruptos que autorizan desmontes", cerró.</t>
   </si>
   <si>
     <t>La Amazonia, con récord de bosque deforestado</t>
@@ -2522,7 +6532,24 @@
     <t>https://www.pagina12.com.ar/433823-la-amazonia-con-record-de-bosque-deforestado</t>
   </si>
   <si>
-    <t>2022-07-02T03:01:00Z</t>
+    <t xml:space="preserve">Título: La Amazonia, con récord de bosque deforestado
+Chapeau: En seis meses se incendió un área mayor a tres veces la superficie de Rio de Janeiro
+Subtítulo: El primer semestre de este año, la pérdida de zona verde marcó un hito. Las organizaciones ambientales acusan al presidente Bolsonaro de favorecer la devastación.
+Editoria: Sociedad
+Tags: Brasil, Amazonia, Jair Bolsonaro, Greenpeace, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/433823-la-amazonia-con-record-de-bosque-deforestado/
+Notícia completa (11 blocos):
+La deforestación en la Amazonía brasileña en el primer semestre del año batió un récord desde que comenzaron los registros en 2016, lo que incrementó los temores sobre el futuro de la mayor selva tropical del planeta.
+Además, los incendios en esa región marcaron en junio un máximo para ese mes en 15 años, y aumentaron 17 por ciento en el primer semestre de este año frente a igual periodo de 2021, de acuerdo con la agencia espacial INPE.
+Entre el 1 de enero y el 24 de junio últimos, la deforestación abarcó un área de 3.750 km2, el peor registro semestral desde 2016, inicio de la serie del Sistema de Detección de Deforestación en Tiempo Real (Deter) basado en alertas diarias. El bosque devastado equivale a una superficie mayor a tres veces la ciudad de Rio de Janeiro.
+Enero y febrero fueron los meses más críticos este año, con 430 km2 y 199 km2 de áreas deforestadas, respectivamente. Ambas fueron cifras sin precedentes en la estación húmeda. La marca más alta de deforestación semestral hasta el momento era la de 2021, cuando había llegado a 3.605 km2, en aumento gradual desde 2017.
+En cuanto a los incendios que afectan a la Amazonía, se registraron en junio 2.562, la peor marca para ese mes en 15 años, desde los 3.519 en igual mes de 2007, según INPE. La cifra es 11 por ciento mayor al total de junio de 2021, cuando hubo 2.305 focos.
+En el primer semestre de este año se registraron en total en la Amazonía 7.533 incendios, 17 por ciento más que en el mismo periodo de 2021.
+En el Cerrado, una región de sabana tropical de gran biodiversidad, al sur de la Amazonía, hubo en junio 4.239 incendios, la cifra más alta para ese mes en 12 años, cuando llegó a 6.443. Y en el semestre los focos de incendios llegaron a 10.869, 13 por ciento más que en igual lapso de 2021.
+"La estación seca apenas comenzó en la Amazonía y ya se están batiendo récords de destrucción ambiental", lamentó Cristiane Mazzetti, portavoz para esa región de Greenpeace Brasil.
+Ambientalistas y opositores acusan al gobierno de Jair Bolsonaro de fomentar la devastación de tierras por sus políticas favorables al agronegocio.
+"El impacto de esta negligencia política será la creciente pérdida de resiliencia en estos entornos, sin mencionar el daño a las comunidades locales y la salud. El escenario es muy preocupante", dijo Mariana Napolitano, gerenta de Ciencias de WWF Brasil.
+Pese a que el uso de fuego fue prohibido por decreto presidencial del 23 de junio por 120 días en el territorio brasileño, se registraron desde entonces 1.113 incendios en la Amazonía, destacó Greenpeace.</t>
   </si>
   <si>
     <t>Amenazaron a un sacerdote en Santiago del Estero</t>
@@ -2534,7 +6561,33 @@
     <t>https://www.pagina12.com.ar/433643-amenazaron-a-un-sacerdote-en-santiago-del-estero</t>
   </si>
   <si>
-    <t>2022-07-01T05:09:33Z</t>
+    <t xml:space="preserve">Título: Amenazaron a un sacerdote en Santiago del Estero
+Chapeau: "Que no se siga metiendo donde no le corresponde", le advirtieron
+Subtítulo: El Grupo de Curas en Opción por los Pobres aseguró que es porque acompaña a los campesinos que afrontan conflictos territoriales por el avance de los agronegocios.
+Editoria: Salta|12
+Tags: Amenaza, Santiago del Estero, santiago-del-estero, diario
+URL: https://www.pagina12.com.ar/433643-amenazaron-a-un-sacerdote-en-santiago-del-estero/
+Notícia completa (20 blocos):
+El sacerdote Rubén Lasaga, de la Parroquia Nuestra de la Señora de la Merced, recibió una amenaza de muerte a través de un mensaje de whatsapp a una administrativa de la parroquia. “A través de usted le queremos hacer llegar un mensaje al señor cura. Los caminos del monte de Pellegrini son largos y solitarios, y él siempre anda solo. Los caminos tienen sus trampas. Por favor que no se siga metiendo en lo que no le corresponde. La próxima vez no va a haber un mensaje de advertencia”.
+La Parroquia Nuestra Señora de la Merced está en Nueva Esperanza, localidad cabecera del departamento Pellegrini, en la provincia de Santiago del Estero. Este departamento linda al norte con Salta y al oeste, con Tucumán, y se encuentra muy cercano al límite con la provincia del Chaco. Todo ese territorio, cuyos habitantes campesinos sufren la presión de las empresas del agronegocio, es parte de la pastoral del religioso.
+Lasaga informó a Salta/12 que hizo la denuncia penal tanto en la fiscalía provincial como en la federal. Todavía no le comunicaron avances.
+En un pronunciamiento bajo el título "Las causas de una amenaza", el Grupo de Curas en Opción por los Pobres, que Lasaga integra, aseguró que se debe a que el religioso está "viviendo en medio de campesinos y comprometiéndose con su causa". El MOCASE (Movimiento Campesino de Santiago del Estero) sostuvo que es por "su compromiso, en la defensa de la tierra y de los territorios de familias y comunidades campesinas de Santiago Del Estero, en el Departamento Pellegrini".
+El sacerdote dijo que no tiene idea de dónde puede provenir la amenaza, y solo puede relacionarla con los conflictos por la tierra que afronta el campesinado de la zona, que acompaña a través de la Mesa Parroquial de Tierra Nueva Esperanza. También la vinculó con un taller que el próximo sábado dictará el fiscal federal de Tucumán Antonio Gómez, sobre delitos ambientales, "una de las consecuencias es la contaminación".
+"Nosotros tenemos una Mesa de Tierra que funciona hace 18 años", que acompaña y asesora a las familias y organizaciones campesinas, y hay un espacio de formación de las comunidades y organizaciones campesinas, contó Lasaga cuando Salta/12 le consultó su percepción sobre el origen de la amenaza.
+"Acompañamos conflictos de tierras, desalojos", realizados muchas veces con "presencia de bandas armadas amedrentando a la gente para que abandone sus campos, sus montes, y queden libres para el agronegocio sobre todo", describió. Añadió que esto "empezó hace mucho tiempo, en la década del '90, cuando se introducen las semillas transgénicas", avanza la frontera agropecuaria y "estas tierras pasan a ser territorio de disputa de dos modelos: el modelo agroindustrial y el modelo de vida campesino e indígena que son casi incompatibles". El religioso destacó que en Pellegrini queda muy poco monte.
+Y sobre el taller con el fiscal tucumano, señaló que será precisamente sobre sobre delitos ambientales, cuyas consecuencias se sufren en la zona, con "la contaminación, la afección a la salud".
+Sin embargo, destacó que "conflictos hubo siempre", y dijo que el audio le sorprendió porque “hubo momentos donde ha estado más candente el tema, (hubo) conflictos con violencia, desalojos" y justo llega cuando los conflictos estás más encaminados con diálogo.
+[H2] El cura compañero
+El MOCASE repudió ayer "las amenazas de la oligarquía terrateniente a nuestro compañero, el padre Rubén Lasaga". Aseguró que el mensaje fue hecho "al mejor estilo de las mafias" y destacó la labor del sacerdote, "ampliamente conocido en el monte santiagueño, al igual que otros curas, siempre apoyando a las familias y Organizaciones campesinas en su derecho a la tierra, al monte, a un ambiente sano, a las forma de vida en cada uno de los territorios santiagueños, desde la Parroquia que le toque estar, fiel referente del Grupo de Curas en Opción por los Pobres (OPP) en su compromiso en favor de la liberación integral de la personas".
+"Por supuesto que los caminos del monte santiagueño son extensos, pero se equivocan en aseverar que el padre Rubén anda solo, cuenta con el abrazo y el apoyo de sus hermanos y hermanas del monte de nuestro Santiago", aseguró la organización, que también resaltó que este episodio no es un hecho aislado: "estas prácticas son formas intimidatorias para acallar y avasallar nuestros derechos en los territorios".
+El presidente del MOCASE, Guido Corvalán, también destacó a Lasaga, "uno de los curitas que, uno de los pocos, que se juega el pellejo acompañando a las familias campesinas indígenas de la zona" y reclamó que "toda la sociedad, no solamente la familia campesina e indígena, también la Iglesia", repudien este hecho.
+"La Iglesia también tiene que hacer su llamado de atención a quien corresponde" por "este tipo de actividades que utilizan para seguir metiendo miedo, seguir sometiendo a la gente", sobre todo en un lugar "donde las familias han convivido con los miedos porque el departamento Pellegrini ha sido uno de los más avasallados por los grandes sojeros y muchos empresarios de Tucumán”, sostuvo. También reclamó que la justicia investigue de manera urgente "este tipo de formas de someter a las familias".
+Asimismo, resaltó que "este modelo sojero, de producción grande" los viene acorralando y "gran parte de la familia campesina e indígena ha sido avasallada ha sido despojada de sus lugares", por un modelo "que hoy nos está mostrando que es dañino para la salud, para la producción y para el ambiente", por lo que "los gobiernos, las autoridades de la zona rural tienen que hacerse eco de esto, porque es su gente la que sufre estas consecuencias". “Estamos en el siglo XXI y no podemos seguir teniendo este tipo de operaciones tan malvadas que sigue sometiendo con un solo propósito de limpiar los territorios donde viven y habitan las familias" campesinas e indígenas, las que protegen el monte, que "es vida no solamente para los que vivimos del monte sino para otros seres vivos que habitan el planeta".
+[H2] Lo que no corresponde es la indiferencia
+Los Curas en Opción por los Pobres afirmaron que Lasaga fue amenazado "por acompañar al pueblo campesino que viene siendo avasallado desde hace ya varias décadas".
+También recordaron que la expansión de los cultivos a gran escala presiona sobre las tierras que ocupan el campesinado y los pueblos indígenas. "Espacios ayer despreciados fueron entonces, deseados. Deseados y apropiados. A nadie molestaba ayer que campesinos ocuparan territorios que ellos veían como inservibles. Pero cuando se descubrió que se los podía usufructuar, aunque tierra, agua y aire fueran envenenados, casi mágicamente esa tierra pasó a tener apropiadores". Y "Con la complicidad de los poderes judicial y político, y la manipulación mediática, los que ayer ocupaban tranquila y ancestralmente las tierras hoy pasaron a ser presentados como usurpadores y delincuentes".
+Y, a propósito de la amenaza: que el sacerdote no siga metiéndose en lo que "no le corresponde", recordaron que frente a los desalojos y asesinatos, la apropiación de tierras, el envenenamiento de pozos y la represión de fuerzas de seguridad legales e ilegales, muchos campesinos y campesinas se organizaron y muchos fueron acompañados. "Haciendo suya, entonces, la causa de los campesinos e indígenas, sectores de la Iglesia caminaron, compartieron y padecieron y padecen lo mismo que los olvidados. Que haya movimientos sociales, curas y tantos otros que son amenazados no es sino 'a causa' de haber hecho suya 'la causa' de las víctimas. Lo 'que no le corresponde' a un cura es permanecer indiferente ante el dolor, ante la injusticia, ante la mentira. Sería ser indiferente al Evangelio de Jesús y su causa", aseguraron.
+Y recordaron: "al poder judicial, que su causa es la justicia, al poder ejecutivo, que su causa es el pueblo, a los Medios de comunicación, que su causa es la verdad, y a los apropiadores y violentos, que ellos son la causa del dolor y el sufrimiento de tantas y tantos. Cuando, con el Papa Francisco insistimos en que todos deben tener Techo, Tierra y Trabajo, de esto estamos hablando".</t>
   </si>
   <si>
     <t>Alberto Fernández y otro dardo para la oposición: "Estuvieron generando miedo para provocar una corrida que lastime al país"</t>
@@ -2546,7 +6599,25 @@
     <t>https://www.pagina12.com.ar/433537-alberto-fernandez-y-otro-dardo-para-la-oposicion-estuvieron-</t>
   </si>
   <si>
-    <t>2022-07-01T03:01:00Z</t>
+    <t xml:space="preserve">Título: Alberto Fernández y otro dardo para la oposición: "Estuvieron generando miedo para provocar una corrida que lastime al país"
+Chapeau: El presidente, de gira por La Rioja
+Subtítulo: En su primer acto tras regresar de la cumbre del G7, el presidente Alberto Fernández abordó en su discurso la suba de los dólares financieros y el paralelo y apuntó contra los dirigentes y econo
+Editoria: El País
+Tags: Alberto Fernández, La Rioja, printed-edition, alberto-fernandez, la-rioja, diario
+URL: https://www.pagina12.com.ar/433537-alberto-fernandez-y-otro-dardo-para-la-oposicion-estuvieron-/
+Notícia completa (12 blocos):
+En su primer acto tras regresar de la cumbre del G7, el presidente Alberto Fernández abordó en su discurso la suba de los dólares financieros y el paralelo y apuntó contra los dirigentes y economistas de la oposición que "estuvieron generando miedo toda la semana anterior tratando de genera una corrida que lastime a la Argentina". El jefe de Estado aseguró que la presión sobre la divisa internacional se debe también a "una crisis de crecimiento" por la importación de insumos para la producción.
+Fernández también abordó otros dos problemas que atraviesa el Gobierno por estos días. Por un lado, volvió a reconocer el problema de la inflación, sobre el que dijo que el Gobierno está trabajado, pero pidió que "todos tengamos un compromiso solidario" porque "la especulación sigue siendo una de las causas de la inflación".
+Por otra parte, el jefe de Estado fue muy duro con las entidades del agronegocio que convocaron a un lockout con marchas en todo el país para reclamar por la falta de gasoil y el suministro de fertilizantes químicos. "La primera crisis que tenemos es energética, tenemos que importar gasoil para que la Argentina siga creciendo" y preguntó: "¿Ustedes creen que ése es un problema de la Argentina? En el G7 se llevó gran parte de la discusión".
+"¿Y la solución que encuentran es proponer un paro? Déjenme de embromar, busquen una mejor solución, lo que necesitamos es seguir produciendo", lanzó contra las entidades agropecuarias.
+[H2] Endeudamiento
+Fernández también le apuntó a los referentes de Juntos por el Cambio al señalar su gestión llegó "después de los que endeudaron a la Argentina como nadie endeudó al país en la historia" y recordó: "Cuando se quedaron sin crédito externo quisieron convencernos de que 'gracias a Dios que existe el FMI' y nos entregaron maniatados con una deuda de 44 mil millones de dólares".
+"Esos personajes estuvieron generando miedo toda la semana anterior tratando de genera una corrida que lastime a la Argentina", denunció por la caída de los bonos argentinos en pesos y la suba de los dólares financieros y el paralelo; y que ayer el Gobierno logró comenzar a corregir.
+[H2] "Ningún país se desarrolla sin industria, vamos a ponerla de pie"
+El presidente habló durante la inauguración de una nueva fábrica y de la ampliación de la planta actual de la empresa textil de capitales nacionales Enod S.A., acompañado por el gobernador, Ricardo Quintela, y el flamante ministro de Desarrollo Productivo, Daniel Scioli, donde valoró: "Gracias a dios la Argentina es esto, una empresa que da trabajo, la Argentina que produce y no para de producir".
+"Tenemos un problema con la inflación", reconoció Fernández y dijo que el Gobierno continúa trabajando "para resolverlo", al tiempo que apuntó contra la especulación de precios. "La Argentina lleva más de 20 años con 2 dígitos de inflación y la Argentina que recibí nos dejó 54 puntos de inflación, más la deuda", se defendió el jefe de Estado frente a un problema recurrente en el país, ahora agravado por la pandemia y la guerra entre Ucrania y Rusia.
+De todas formas, el presidente evaluó: "Estamos viviendo un momento singular de la Argentina, signado por el crecimiento". Y destacó el perfil de su gobierno: "Llegamos a la vida política argentina convencidos de que ningún país se desarrolla sin industria, dijimos vamos a ponerla de pie".
+"Tenemos un problema con los dólares, sí, porque crecemos mucho y necesitamos dólares para poder importar insumos. Es tanto lo que crecemos que aunque tenemos récord de exportaciones no nos alcanzan los dólares por la cantidad de insumos que tenemos que importar para seguir creciendo", completó su análisis y sentenció: "Tenemos una crisis de crecimiento. Lo vamos a resolver".</t>
   </si>
   <si>
     <t>"Argentina encabeza el ranking de países que más han deforestado"</t>
@@ -2558,7 +6629,40 @@
     <t>https://www.pagina12.com.ar/432372-argentina-encabeza-el-ranking-de-paises-que-mas-han-deforest</t>
   </si>
   <si>
-    <t>2022-06-27T03:01:00Z</t>
+    <t xml:space="preserve">Título: "Argentina encabeza el ranking de países que más han deforestado"
+Chapeau: Cecilia Gárgano, una historiadora del agronegocio
+Subtítulo: La investigadora del Conicet traza la historia del extractivismo agrícola en el país y hace foco en la apropiación privada de conocimientos científicos que deberían ser de la sociedad o del Estado.
+Editoria: Diálogos
+Tags: Agronegocio, extractivismo, printed-edition, diario
+URL: https://www.pagina12.com.ar/432372-argentina-encabeza-el-ranking-de-paises-que-mas-han-deforest/
+Notícia completa (27 blocos):
+“Fuegos, sequías e inundaciones”, enumera lo que brota de la Caja de Pandora la historiadora Cecilia Gárgano, en el prólogo del libro de reciente edición El campo como alternativa infernal - Pasado y presente de una matriz productiva ¿sin escapatoria? (Imago Mundi, 2022). “De la impotencia que nos genera la contemplación de ese desastre que sabemos no accidental y multiplicador de la asimetría social, también surge este libro”, explica la autora, egresada de la Facultad de Filosofía y Letras e investigadora del Conicet.
+Tal vez sea esa doble formación la que le permite historizar las raíces y el presente del agronegocio, desde los años 60 para acá, con un pico de entrega y masificación de los agroquímicos (o agrotóxicos, para decirlo más directamente) en los 90. Al mismo tiempo que traza la historia reciente del extractivismo agrícola en la Argentina, Gárgano ve en esa historia la de la apropiación privada de conocimientos científicos que en un mundo mejor deberían ser de la sociedad, o del Estado.
+Si bien el libro apunta a desbrozar la maleza (con perdón por el símil) para llegar a ese campo más sano, menos tóxico, más social que el actual, antes de ello Gárgano estudia ciertos casos puntuales de envenenamiento por biocidas, algunos de los cuales ponen los pelos de punta.
+--¿En qué consiste el agronegocio?
+--El libro busca comprender cómo fue construida la actual matriz productiva agraria hegemónica como el único destino posible para nuestro país. Frente a un dispositivo que la presenta como natural, busca historizar su genealogía e identificar los mecanismos materiales y discursivos que la construyeron y legitiman. Para eso analiza el pasado reciente desde la década de 1960 hasta nuestros días enmarcados en el “agronegocio”.
+--¿Cómo evolucionó ese proceso?
+--En los años 60 se inaugura en Argentina la “revolución verde”, el proceso mundial exportado desde Estados Unidos que marcó un hito en la “quimificación” de la agricultura a través del uso intensivo de plaguicidas. El segundo momento en el que se detiene el libro es en la última dictadura cívico-militar, un punto de inflexión ineludible en nuestra historia, analizando en este caso por un lado cómo el disciplinamiento configuró las formas de concebir al agro desde las políticas estatales de investigación y extensión rural, y por otro lado, de qué forma la privatización de conocimientos científicos generados en esos ámbitos se fue volviendo central para la matriz productiva agraria. El tercer momento que toma es a partir del comienzo del boom sojero iniciado en los 90. Uno de los focos de la investigación está puesto en analizar cómo la ciencia empresarial generada desde el Estado operó (y opera) como un insumo fundamental del agronegocio.
+--En la segunda parte del libro se centra en los que reciben los daños.
+--Efectivamente, se corre la mirada a los propios territorios, a partir de algunas experiencias vigentes de vida y resistencia en localidades de Santa Fe, Entre Ríos y Buenos Aires que están en el ojo del conflicto. Los testimonios que se replican delineando un mismo rompecabezas de depredación sanitaria, ambiental y desigualdad social.
+--¿Cuáles son las prácticas que conllevan esa(s) modalidad(es)? ¿Qué efectos producen esas prácticas?
+--La extensión ininterrumpida de la frontera agrícola desde los años setenta ha configurado procesos de éxodo rural forzado, de creación de desigualdad social mediante la extranjerización y concentración de la tierra. En forma sincrónica, con un salto cualitativo a partir de la expansión del monocultivo de soja, Argentina encabeza el ranking de países que más han deforestado y que más plaguicidas utiliza. Eso que las comunidades denominan “agrotóxicos” y que las empresas y algunos ámbitos estatales llaman “fitosanitarios” ha generado la contaminación sistemática de aguas (incluidas las subterráneas de consumo), tierras y cuerpos. Mientras que estos efectos nocivos son socializados en forma compulsiva, las ganancias millonarias son apropiadas por una fracción sumamente concentrada. Si bien las mismas patologías en la población asociadas a las mismas prácticas productivas se repiten a lo largo del país, como se replican los focos de incendios y las agroinundaciones, son presentadas como fenómenos singulares. Una política de la fragmentación que opera mediante una triple operación.
+--¿A qué se refiere?
+--En primer lugar se disocia nuestro presente del pasado reciente y de los distintos cuestionamientos que ya han impugnado estas formas de producir. Tenemos así un presente que pareciera no tener historia, ni otro futuro posible. En segundo lugar, fragmenta sistemáticamente estas experiencias comunes mediante mecanismos (des)regulatorios y jurídicos que obligan a las poblaciones a generar evidencia científica de los daños sufridos localidad por localidad. Una trampa de la evidencia que no solamente viola el principio precautorio, sino que también obliga a las poblaciones a financiar (como el bingo de Lobos que reconstruye el libro) los estudios que el Estado demanda y al mismo tiempo no genera. En este entramado kafkiano, por ejemplo, los cultivos transgénicos tolerantes a agrotóxicos son aprobados para todo el territorio nacional, pero según en qué localidad habitemos las fumigaciones agrícolas pueden realizarse a 0, 500, o 2500 metros. O, vemos que a pesar de que una localidad, como sucedió en Pergamino, haya demostrado que el agua que consume ya no es potable por la cantidad de plaguicidas que contiene, otra localidad vecina expuesta a la misma situación estructural carece de cualquier instancia de protección. En tercer lugar, encontramos que las transformaciones materiales homogenizan a los territorios fragmentados: aplanan sus paisajes, sus habitantes, sus formas de vida. Dos operaciones, fragmentar y homogenizar, que avanzan en forma simultánea.
+--¿Hay un lobby del agronegocio que busca lograr que las leyes les sean favorables?
+--Si algo explica que en medio de los incendios forestales más graves de la historia argentina hoy la ley de humedales siga cajoneada es la eficaz articulación del lobby del agronegocio con otros. Por ejemplo, como hemos visto en el Delta del Paraná, con el inmobiliario. El entramado legal y regulatorio/desregulatorio es una pieza clave para analizar los extractivismos en general y el agro en particular. Un entramado que no casualmente fue estructurado en la década del 90 y se ha sostenido como política de Estado.
+--¿Se conoce la cifra de enfermos y fallecidos, como consecuencia de la fumigación con agrotóxicos?
+--No se conoce. Como tampoco existen datos oficiales de las cantidades utilizadas de agrotóxicos, ni de su presencia en frutas y verduras. Una ausencia sistemática de datos que es la otra cara de la moneda que opera instando a la población que denuncia los daños sanitarios a generar evidencia causal y certera. Para establecer si el agua que consumimos es o no potable, el Código Alimentario Argentino utiliza un listado de moléculas de sustancias en relación a los valores umbrales tolerables de rastros de plaguicidas. En este listado no figuran las sustancias en uso desde hace más de 25 años en el agro argentino: no está el glifosato, ni la atrazina, ni ninguno de los utilizados. Tampoco existen herramientas que den cuenta de los efectos por exposición crónica y a bajas dosis, ni del efecto de la mezcla de estos plaguicidas, a pesar de que son usados en “cócteles” (combinadas entre sí) y de que existen relevantes investigaciones como las del equipo del Dr. Lajmanovich (UNL) que demuestran su efecto sinérgico. Esa articulación entre anomia y norma también es clave para la vigencia de esta matriz productiva.
+--¿Los transgénicos o OGM son más peligrosos que el glifosato?
+--La pregunta podría ser, ¿cuántos cultivos transgénicos han sido aprobados en nuestro país y cuáles de ellos fueron específicamente diseñados para ser tolerantes a plaguicidas (en su mayoría, a herbicidas como el glifosato)? Desde la soja RR (1996) a la actualidad se autorizaron 65 variedades comerciales de transgénicos. Más del 80 por ciento son tolerantes a plaguicidas. Es la norma, no la excepción. Este uso intensivo continúa profundizando la depredación sanitaria. Mientras tanto, las promesas de desarrollo permanecen ausentes. La alternativa infernal traída al campo argentino es la falsa encrucijada que se nos construye cuando tenemos que elegir entre intensificar esta matriz productiva o quedarnos sin PBI. Cuando en realidad esa crisis ya nos habita y está generada precisamente por estos patrones de acumulación, por la generación constante de falsas soluciones para salir del extractivismo con más extractivismo, que nos vuelven más dependientes y más depredados al mismo tiempo.
+--¿El permiso dado días atrás para la siembra y comercialización masiva del HB4 es el primero que se da en el mundo entero? ¿Cuál es la política en el resto del mundo con respecto a este transgénico?
+--La aprobación del trigo transgénico HB4, resistente a sequía y tolerante a glufosinato de amonio, un herbicida 15 veces más tóxico que el más famoso glifosato, es la primera a nivel mundial. Es un excelente ejemplo para ver cómo las viejas promesas de la “revolución verde” (terminar con el hambre y alcanzar el “desarrollo”) se reeditan hoy, con el agregado de la promesa de sustentabilidad que tan eficazmente ha incorporado el capitalismo. La propia cadena triguera manifestó su rechazo, porque existen fuertes restricciones (por ejemplo en la UE) para su comercialización. Por fuera de esta preocupación centrada en la rentabilidad, es la capacidad de decidir cómo queremos que sea nuestro futuro inmediato la que está en juego. Por su carácter experimental, y fundamentalmente por lo que implica reforzar esta matriz productiva intensiva en agrotóxicos, a pesar de que ya saltado totas las alertas. Es decir, se trata de un nuevo experimento a cielo abierto con el agravante de que 26 años después de iniciada la sojización los daños están a la vista y vienen siendo expuestos por las poblaciones afectadas, por la agricultura familiar y campesina que produce alimentos sanos, por una gran cantidad de estudios científicos (más de 1400 científicos/as adhirieron al documento del Colectivo Trigo Limpio) y por una demanda colectiva que ha expresado su rechazo y que no tiene voz ni voto en ninguna instancia oficial.
+--¿El HB4 es de origen argentino? ¿Qué laboratorio lo generó?
+--Fue obtenido por investigadoras e investigadores pertenecientes al Consejo Nacional de Investigaciones Científicas y Técnicas (Conicet) y a la Universidad Nacional del Litoral (UNL), en convenio con Bioceres mediante INDEAR S. A., empresa del Grupo argentino Bioceres, que en convenio con Conicet funciona en el Instituto Nacional de Agrobiotecnologia con sede en el predio del CCT del Conicet en Rosario y es responsable de seis variedades de cultivos transgénicos, cinco de ellos tolerantes a herbicidas (glifosato y glufosinato de amonio). Uno de sus socios es Gustavo Grobocopatel, presidente de Los Grobo. El financiamiento estatal, la participación de capitales nacionales y el potencial ingreso de divisas son los pilares para conceptualizar al evento como un “desarrollo nacional”. Una suerte de teoría del derrame aplicada al ámbito tecnocientífico, que nunca llega. En la que pareciera que si despejamos de la ecuación a las grandes transnacionales, que lejos están de ser marginales, los riesgos ambientales, sanitarios y territoriales desaparecen.
+--¿Qué alternativas hay al modelo que llama “agricultura neoliberal” y al extractivismo minero?
+--Los extractivismos no tienen licencia social. Lo vimos en Chubut, en Mendoza, en Mar del Plata, antes en Malvinas Argentinas. Ese reclamo, a medida que crece y se fortalece desafiando a estas políticas de la fragmentación recuperando desde abajo lo que es escindido desde arriba, es construido como una movilización “extranjerizante”, “elitista”, “de panzas llenas”, o bien es reprimido, como vimos en Andalgalá. Sin embargo es un movimiento que tiene la capacidad de cuestionar la mercantilización de nuestras existencias y territorios vitales produciendo reapropiaciones de lo común. En eso radica su potencia. Tanto desde experiencias que impulsan la agroecología, como desde aquellas que cuestionan otros circuitos de producción o consumo también se están disputando las escalas de intervención, de habitar, de producir. A eso intenta aportar este libro, al ejercicio de desnaturalizar, repolitizar y reunir.
+¿Por qué Cecilia Gárgano?
+Egresada de la carrera de Historia en la Facultad de Filosofía y Letras de la Universidad de Buenos Aires (UBA) y Doctora en Historia por dicha Universidad, desde 2017 se desempeña como investigadora del Consejo Nacional de Investigaciones Científicas y Técnicas (Conicet). Profesora adjunta de la Escuela de Humanidades de la Universidad Nacional de San Martín (Unsdam), donde coordina el Programa de Investigación radicado en el Laboratorio de Investigación en Ciencias Humanas (LICH – Unsam – Conicet) “Conflictos socioambientales, conocimientos y políticas en el mapa extractivista argentino”, junto a su amigo y colega Agustín Piaz. Es parte de distintos espacios colectivos que buscan producir conocimiento crítico al servicio del cambio social.</t>
   </si>
   <si>
     <t>Horacio Bernades</t>
@@ -2573,7 +6677,25 @@
     <t>https://www.pagina12.com.ar/418518-micaela-camino-la-lucha-de-la-cientifica-del-conicet-reconoc</t>
   </si>
   <si>
-    <t>2022-04-30T03:01:00Z</t>
+    <t xml:space="preserve">Título: Micaela Camino: la lucha de la científica del Conicet reconocida con el “Oscar verde”
+Chapeau: Entrevista a la investigadora argentina ganadora del Premio Whitley
+Subtítulo: Fue distinguida en Londres por proteger al chancho quimilero, un mamífero en peligro de extinción. Aquí, explica su trabajo, clave para conservar los bosques chaqueños y empoderar a los pueblos originarios.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/418518-micaela-camino-la-lucha-de-la-cientifica-del-conicet-reconoc/
+Notícia completa (12 blocos):
+La científica argentina Micaela Camino fue distinguida con el Premio Whitley, mejor conocido como el “Oscar verde”. Se trata de uno de los reconocimientos más importantes relacionados a la conservación y año a año son galardonados referentes que realizan aportes en el rubro desde África, Asia y Latinoamérica. La investigadora del Conicet fue galardonada por “empoderar a comunidades en el Chaco Seco para defender sus derechos” y promover la protección del chancho quimilero, una especie de mamífero que podría desaparecer en solo tres décadas.
+“Le dicen Oscar verde porque se trata de un reconocimiento con una ceremonia importante, hasta la princesa (Ana, de Reino Unido) participa. Para nosotros, que trabajamos en conservación, es muy destacable. Todas las instituciones que lo apoyan contribuyen a aumentar su prestigio. Estoy muy contenta, el trabajo es colectivo con la comunidad chaqueña”, señala Camino, Investigadora del Conicet en el Centro de Ecología Aplicada del Litoral. Luego continúa con la descripción de la importancia de su trabajo en un escenario amenazado por la deforestación. “Si no frenamos ya la tala indiscriminada de árboles, la especie estará extinta en menos de 30 años. Eso sin considerar las cacerías, las pestes, el cambio climático y otras amenazas que podría sufrir”. Al proteger al animal, la referente de la Red Agroforestal Chaco Argentina busca conservar al bosque y los derechos de los pueblos originarios y de las comunidades criollas que allí habitan.
+El otro latinoamericano que obtuvo el galardón fue Pablo Hoffmann, científico brasileño que fue distinguido por salvaguardar el bosque de araucarias en el sur de Brasil. Se trata de un árbol muy antiguo; de hecho, de manera reciente se hallaron fósiles en Argentina que datan de 160 millones de años. En esta línea, al igual que Camino, su trabajo consiste en proteger este ecosistema, a través de la recolección de semillas, la reproducción en un vivero y su reintroducción en el medio natural, frente al avance de agronegocio, la crianza de ganado y la explotación maderera. Las 40 mil libras que cada investigador obtiene deben ser destinadas a robustecer los esfuerzos en la protección de la biodiversidad y de las especies en extinción.
+[H2] Una especie única
+Luego de la Amazonia, el Gran Chaco es la ecorregión más grande de Sudamérica y cubre más de un millón de km2. La parte seca abarca Argentina, Bolivia, Paraguay y Brasil, y aloja al bosque seco subtropical más grande del planeta. Por las condiciones de sequía que presenta, las especies que sobreviven se destacan por su capacidad de tolerar la falta de agua durante extensos períodos. Entre ellas, se encuentra el pecarí o chancho quimilero, que debe su bautismo porque se alimenta de quimil, un cactus típico de la región.
+“Tenemos una riqueza espectacular de especies que son únicas para nuestro territorio. El chancho quimilero representa un camino evolutivo único y es reservorio de proteínas para comunidades vulnerables. De hecho, no existe en ningún otro lugar que no sea los bosques secos del Chaco”, indica Camino. Algunas veces es cazado y, al tener mucha carne, ofrece contenido proteico a las comunidades de la zona. Según las estimaciones que aporta la científica, en tan solo tres décadas, podría dejar de existir. Se halla amenazado porque la deforestación, piedra angular de la expansión de la frontera agrícola, está muy avanzada en dicho territorio.
+Al defender al chancho quimilero, por tiro de elevación, Camino busca preservar al bosque, que constituye su hábitat natural. El equipo que lidera la investigadora argentina procura aportar evidencia científica sobre cómo las actividades humanas afectan la calidad y el entorno del animal. Pero su lucha no solo se limita al bosque y al pecarí, sino que va mucho más allá.
+[H2] Los verdaderos guardianes
+“Ante la deforestación, las personas que habitan el Chaco Seco se ven obligadas a dejar sus casas. Hay violaciones a los derechos humanos”, destaca. Además de los chanchos quimileros, defiende activamente los derechos de los pueblos originarios y las comunidades criollas que habitan el lugar. Como las comunidades indígenas wichí no poseen los títulos de las tierras, suelen ser desplazadas por empresas y demás grupos privados que aprovechan los vacíos legales, se hacen con la propiedad del lugar y arrasan con el bosque.
+Enseguida lotean los terrenos, llevan sus máquinas y “despedazan todo el ecosistema para sembrar soja y exportarla”, cuenta. Estas acciones se reiteran, por lo que Camino y su equipo trabajan con el objetivo de empoderar a las culturas locales para que conozcan sus derechos. Con abogados y organizaciones no gubernamentales, realizan talleres con el propósito de socializar qué normativas de la legislación nacional pueden servir para proteger a los bosques y la tenencia de las tierras. “Aunque hay muchas leyes de derecho a la tierra o conservación de los bosques, la realidad es que no se aplican”, comenta. Con esto, Camino se refiere, por ejemplo, a la Ley 26.331 que protege a los bosques y los clasifica por su nivel de conservación, establece límites al desmonte y tiene en cuenta los intereses de las comunidades indígenas.
+“Las áreas protegidas son insuficientes para conservar esta especie. La mayor parte de la cobertura boscosa en Chaco está en territorio indígena y familias criollas, que tienen una sabiduría ecológica maravillosa, que saben muchísimo. Trabajamos juntos más allá del chancho, en el monitoreo de fauna en general”, relata Camino. El enfoque de la investigadora es claro: el conocimiento se construye a partir de trabajo colaborativo. Y, con esta perspectiva, desafía el cientificismo que muchas veces caracteriza a la academia. “Desde la ciencia se suele despreciar el saber tradicional de los indígenas, pero hay que entender que es muy valioso y además muy útil ante la crisis ambiental y global que enfrentamos. Es desde abajo que se pueden encontrar soluciones para un conflicto de escala planetaria”.
+pablo.esteban@pagina12.com.ar</t>
   </si>
   <si>
     <t>Pablo Esteban</t>
@@ -2588,7 +6710,21 @@
     <t>https://www.pagina12.com.ar/417474-kulfas-sobre-el-tractorazo-fue-una-expresion-del-brazo-polit</t>
   </si>
   <si>
-    <t>2022-04-25T14:51:05Z</t>
+    <t xml:space="preserve">Título: Kulfas sobre el tractorazo: "Fue una expresión del brazo político de Juntos por el Cambio"
+Chapeau: El ministro defendió el cobro de retenciones
+Subtítulo: "No considero que hay sido una expresión sectorial, lo que hemos visto fue una expresión del brazo político de Juntos por el Cambio", describió el ministro de Desarrollo Productivo, Matías Kulfa
+Editoria: El País
+Tags: Tractorazo, Matías Kulfas, Retenciones agropecuarias, matias-kulfas, retenciones-agropecuarias, diario
+URL: https://www.pagina12.com.ar/417474-kulfas-sobre-el-tractorazo-fue-una-expresion-del-brazo-polit/
+Notícia completa (8 blocos):
+"No considero que hay sido una expresión sectorial, lo que hemos visto fue una expresión del brazo político de Juntos por el Cambio", describió el ministro de Desarrollo Productivo, Matías Kulfas, sobre el "tractorazo" que bajó desde Avenida Libertador hasta Plaza de Mayo para exigir "un país con menos impuestos" y que el Gobierno "gaste menos" para no generar "planeros".
+Al repasar la marcha que contó con la presencia de referentes de Juntos por el Cambio (JxC) como Federico Pinedo, Eduardo Amadeo y Luis Miguel Etchevehere, Kulfas recordó que la Argentina "no es de los países que más presiona en cuanto a carga impositiva" en respuesta a uno de los latiguillos de los participantes del "tractorazo" que hablan de 170 impuestos que pesan sobre la producción, cifra que surge de un informe distorsionado de la Fundación Mediterránea, dirigida por Carlos Melconian.
+Respecto de las retenciones, la bandera del reclamo del agronegocio desde la resolución 125, Kulfas las calificó como "una suerte de impuesto a las ganancias que tiene un impacto importante en materia de precios internos y recaudación", pero negó que se trate de una carga extraordinaria a nivel mundial, a la par que el presidente Alberto Fernández y los ministros de Agricultura, Julián Domínguez; y de Economía, Martín Guzmán, se encargaron de anticipar que no habrá un incremento.
+El ministro cerró así, en diálogo con Urbana Play, el capítulo del "tractorazo" que el sábado arrancó con una concentración en el barrio de Nuñez con productores autoconvocados y agrupaciones rurales que contaron con la presencia de dos presidenciables del PRO: la presidenta del partido Patricia Bullrich; y el jefe de gobierno porteño, Horacio Rodríguez Larreta.
+[H2] "Los economistas de Juntos por el Cambio son responsables del endeudamiento"
+En el mismo tono, el ministro de Desarrollo Productivo repasó un cruce que mantuvo a través de la red social Twitter con el ex titular del Banco Central, Guido Sandleris, sobre la inflación. "Las soluciones mágicas como la no emisión monetaria de Sandleris no son la solución. Hay que discutir a fondo cuál es la respuesta a largo plazo", recuperó el debate Kulfas.
+Y recordó: "Sandleris arrancó su plan monetario en 2018, y dijo ‘no voy a emitir más’. Congeló la base monetaria, y terminó entregando la Argentina con el doble de inflación de la que había recibido (el ex presidente Mauricio) Macri". En ese sentido, volvió a subrayar la diferencia central del análisis del oficialismo con la oposición: "Para decir eso consideran que es lo mismo deuda intra sector público que puede tener el Tesoro con organismos como Anses o Pami, que deberle a un banco en el exterior o a un organismo internacional".
+"Los economistas de JxC, responsables del endeudamiento irresponsable más grande de la historia argentina, que dejaron una economía destrozada y hasta defaultearon deuda en pesos, ahora dicen que (el presidente) Alberto Fernández es un endeudador", les recordó el ministro.</t>
   </si>
   <si>
     <t>Katopodis: "Ahora tenemos que recuperar el salario y el poder de compra"</t>
@@ -2600,7 +6736,26 @@
     <t>https://www.pagina12.com.ar/416221-katopodis-ahora-tenemos-que-recuperar-el-salario-y-el-poder-</t>
   </si>
   <si>
-    <t>2022-04-19T21:02:19Z</t>
+    <t xml:space="preserve">Título: Katopodis: "Ahora tenemos que recuperar el salario y el poder de compra"
+Chapeau: El ministro de Obras Públicas acusó a la oposición de "mezquina"
+Subtítulo: "Ya recuperamos el trabajo, ahora tenemos que recuperar el salario y el poder de compra de todos los trabajadores", adelantó el ministro de Obras Públicas, Gabriel Katopodis, al analizar la gestión
+Editoria: El País
+Tags: diario
+URL: https://www.pagina12.com.ar/416221-katopodis-ahora-tenemos-que-recuperar-el-salario-y-el-poder-/
+Notícia completa (13 blocos):
+"Ya recuperamos el trabajo, ahora tenemos que recuperar el salario y el poder de compra de todos los trabajadores", adelantó el ministro de Obras Públicas, Gabriel Katopodis, al analizar la gestión del Frente de Todos y reconocer que la inflación es el problema central.
+Katapodis aseguró que el presidente Alberto Fernández tiene claro que el incremento de precios es lo urgente y aseguró que el Gobierno "va a actuar con mucha responsabilidad y con mucha firmeza para cuidar el salario".
+Poco después de que Fernández y el ministro de Economía, Martín Guzmán, anunciaran un bono para trabajadores informales y jubilados, el ministro de Obras Públicas concedió una entrevista al diario pampeano La Arena.
+"El presidente tiene en claro que todas las medidas que se tomen tienen que estar dirigidas a recuperar el poder de compra, a garantizar que durante el 2022 el salario y las jubilaciones le puedan ganar la inflación", agregó Katopodis.
+El ministro de Obras Públicas se mostró optimista respecto de las políticas para frenar la suba de precios y "generar un esquema de redistribución de la riqueza mucho más equitativo (...) con el mismo rumbo que permitió recuperar la economía, que permitió poner en marcha el plan de obras públicas más importante de las últimas décadas".
+Según dejó trascender Guzmán en la víspera durante la conferencia de prensa ofrecida en Casa Rosada, una de las medidas para redistribuir el ingreso será la creación de un impuesto a "la renta inesperada" que obtuvieron las empresas del agronegocio, minería y energía por la suba internacional del precio de las commodities tras la invasión de Rusia a Ucrania.
+"Ya recuperamos todo lo que perdimos durante la pandemia, ahora tenemos que empezar a recuperar todo lo que se perdió en materia de salario y de actividad económica durante el macrismo", resumió el ministro de cara al 2023.
+[H2] "La oposición tiene una actitud mezquina"
+El funcionario también analizó la actitud de la oposición en medio de la crisis económica global producida por la pandemia y agudizada por la guerra de Ucrania y calificó como una "actitud mezquina" la decisión de rechazar el Presupuesto 2022 enviado por el Poder Ejecutivo al Congreso.
+La oposición, agregó, "está muy atada al calendario electoral", ya que "toma posiciones siempre especulando, mirando las encuestas".
+"Nos dejaron sin la posibilidad de avanzar en obras públicas en todo el país, tal como estaba previsto", y detalló que el presupuesto contemplaba duplicar las partidas asignadas el año anterior a su ministerio.
+"Hoy estamos concretando las inversiones provincia por provincia, y hay que entender que, a pesar de que nos dejaron sin presupuesto, rediseñamos las partidas y resolvimos administrativamente las condiciones para licitar y ejecutar la misma agenda de obras públicas que habíamos previsto para el 2022", añadió el funcionario.
+"En estos casi tres años (la oposición) no ha tenido una sola propuesta seria sobre los grandes problemas que tiene la Argentina. No está mirando los problemas que tiene hoy la Argentina ni las necesidades y desafíos que tienen las diferentes provincias", sentenció.</t>
   </si>
   <si>
     <t>Fusión de Arcor floja de papeles</t>
@@ -2612,7 +6767,21 @@
     <t>https://www.pagina12.com.ar/415981-fusion-de-arcor-floja-de-papeles</t>
   </si>
   <si>
-    <t>2022-04-19T03:01:00Z</t>
+    <t xml:space="preserve">Título: Fusión de Arcor floja de papeles
+Chapeau: Defensa de la Competencia objetó la operación
+Subtítulo: El Gobierno rechaza la conformación de un monopolio en el sector de la molienda de maíz con la compra de Ingrear Holding.
+Editoria: Economia
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/415981-fusion-de-arcor-floja-de-papeles/
+Notícia completa (8 blocos):
+El gobierno objetó la intención de Arcor e Ingredion Argentina de fusionarse y adquirir la compañía Ingrear Holding. De esta manera, intenta evitar la conformación de un monopolio en el sector de la molienda húmeda de maíz y la comercialización de sus derivados que se utilizan como insumos de las industrias de alimentos, bebidas, papel y farmacéutica.
+Fue la Comisión Nacional de Defensa de la Competencia (CNDC), que depende de la Secretaría de Comercio Interior, quién emitió un Informe de Objeción por considerar que la operación notificada por Arcor e Ingredion tienen la potencialidad de restringir o distorsionar la competencia en un mercado. Por este motivo, convocará a las partes a una audiencia especial destinada a analizar las posibles medidas que mitiguen el efecto negativo de la operación de concentración sobre la competencia.
+"La operación genera un efecto directo que es la desaparición de un competidor independiente y un aumento significativo de la concentración en los mercados de molienda húmeda de maíz y en la comercialización de sus derivados", explicaron desde la Secretaría de Comercio. Además, verificaron posibles efectos verticales toda vez que la fusión tendría la potencialidad de permitir la práctica de conductas exclusorias en relación con los competidores de Arcor en las industrias “aguas abajo”, en términos de cierres de mercado, aumento de costos, aumento de barreras a la entrada, entre otros.
+Arcor es un grupo multinacional argentino que se especializa en tres divisiones de negocios: alimentos de consumo masivo, agronegocios y envases; en tanto que Ingredion es un grupo multinacional estadounidense líder en soluciones de ingredientes para la industria de alimentos y bebidas. El 12 de febrero de 2021, ambas compañías acordaron la conformación de un proyecto por el que controlarán en forma conjunta las actividades relacionadas con la molienda húmeda de maíz y la comercialización de productos derivados que, previo a la toma de control realizaban cada una de ellas en forma independiente.
+La alerta se enciende dado el poder de mercado de las dos empresas que pretenden funsionarse. Entre ambas concentran el 76 por ciento de la capacidad de procesamiento de la molienda húmeda de maíz del país -Ingredion con 48,6 por ciento y Arcor con 27,4 por ciento-. Los derivados de la molienda húmeda son almidón, endulzantes y coproductos que se utilizan como insumos de las industrias de alimentos, bebidas, papel y farmaceútica.
+"No podemos legitimar una estructura de negocios en la que una gran empresa concentra los diversos eslabones de la cadena, en perjuicio de los actores más chicos. Si aceptáramos esto, estaríamos reconociendo planes de negocios en donde lo único que se pondera es la rentabilidad de las empresas, sin considerar de qué modo esto impacta en el consumo popular", declaró al respecto el secretario de Comercio Interior, Roberto Feletti, al tiempo que remarcó que "no podemos salir de la pandemia reproduciendo los mismos patrones y modelos que imperaban anteriormente. Para eso, tenemos que dar una discusión seria sobre estos comportamientos de las grandes empresas, que solamente priorizan sus ganancias desentendiéndose del modo en que esto impacta sobre la ciudadanía".
+Dictaminado el informe, las empresas no pueden seguir adelante con la operación hasta que el caso se resuelva. Ambas compañías cuentan con quince días para realizar las consideraciones que crean oportunas u ofrezcan soluciones para mitigar los potenciales efectos sobre la competencia. Una vez recibidas, la CNDC convocará a una audiencia para considerar las medidas. Luego, la CNDC y la Secretaria de Comercio Interior dictaran el dictamen y la resolución, respectivamente, sobre la operación.
+"Como Gobierno, perseguimos dos propósitos con esta decisión: 1) Cuidar especialmente los derechos de las familias y de los consumidores, sobre todo para el caso de los bienes esenciales como son los alimentos, y 2) Favorecer la diversificación de la estructura productiva y de las fuentes de trabajo", finalizó Feletti.</t>
   </si>
   <si>
     <t>Jair Bolsonaro calificó a Lula de "genocida de inocentes" por defender la ley del aborto</t>
@@ -2624,7 +6793,25 @@
     <t>https://www.pagina12.com.ar/414663-jair-bolsonaro-califico-a-lula-de-genocida-de-inocentes-por-</t>
   </si>
   <si>
-    <t>2022-04-12T03:01:00Z</t>
+    <t xml:space="preserve">Título: Jair Bolsonaro calificó a Lula de "genocida de inocentes" por defender la ley del aborto
+Chapeau: El exmandatario había dicho que el aborto debe tratarse como "una cuestión de salud pública"
+Subtítulo: Metido de lleno en su campaña con miras a la reelección, Bolsonaro también anunció la decisión de seguir importando desde Rusia fertilizantes, claves para el agronegocio de su país, y exaltó la figura de su par ruso, Vladimir Putin, por reconocer la soberanía brasileña en la selva amazónica.
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, Luiz Inácio Lula da Silva, Vladimir Putin, printed-edition, jair-bolsonaro, luiz-inacio-lula-da-silva, vladimir-putin, diario
+URL: https://www.pagina12.com.ar/414663-jair-bolsonaro-califico-a-lula-de-genocida-de-inocentes-por-/
+Notícia completa (12 blocos):
+El presidente de Brasil, Jair Bolsonaro, acusó este lunes a Luiz Inácio Lula da Silva, rival electoral y favorito para los comicios de octubre, de ser un "genocida de inocentes" por defender el aborto en el país. Metido de lleno en su campaña con miras a la reelección, Bolsonaro también anunció la decisión de seguir importando desde Rusia fertilizantes, claves para el agronegocio de su país, y exaltó la figura de su par ruso, Vladimir Putin, por reconocer la soberanía brasileña en la selva amazónica ante los cuestionamientos ambientales de Francia, Estados Unidos y Gran Bretaña.
+"Lula es un genocida de inocentes y le falta el respeto a los curas y pastores. Lula quiere sacarle las armas de las manos a la gente de bien, defiende el aborto como algo tan simple como ir al dentista. Cuando defiende el aborto, está criticando a pastores y curas, les quiere sacar credibilidad a los líderes religiosos", dijo Bolsonaro durante una entrevista con la radio O Liberal, del estado amazónico de Pará.
+La semana pasada, en un encuentro con la Central Única de Trabajadores, la principal agrupación sindical, Lula señaló que en Brasil el aborto está prohibido pero "debería ser transformado en una cuestión de salud pública, para que todo el mundo tenga derecho, sin vergüenza". En un país en el que la despenalización del aborto genera mucho rechazo, Lula lo planteó como un reflejo de la desigualdad social, asegurando que las mujeres con más recursos económicos pueden viajar al extranjero para acceder al procedimiento, mientras que las más pobres no tienen cómo hacerlo.
+[H2] Flores a Rusia
+Luego de que Brasil se abstuviera la semana pasada en el Consejo de Derechos Humanos de la ONU para suspender de ese órgano a Rusia, Bolsonaro recordó la visita que realizó en marzo pasado a Moscú, donde se reunió con Putin de cara a la necesidad brasileña de adquirir fertilizantes para que el agronegocio brasileño pueda seguir produciendo a la escala actual.
+"Cuando estuve en Rusia, antes de la invasión a Ucrania, conversé con Putin sobre la continuidad del flujo de la provisión de potasio hacia Brasil. Esperamos que continúe esa garantía de provisión para el bien de nuestro agronegocio", afirmó el líder ultraderechista brasileño a la radio O Liberal.
+Bolsonaro también recordó que el presidente ruso dio el año pasado un apoyo a la posición brasileña sobre la selva amazónica, acción que agradeció. "Con Putin también tratamos el tema de la Amazonia. Francia, Estados Unidos, Reino Unido y otros quisieron relativizar nuestra soberanía amazónica y Putin, con su poder de veto (en el Consejo de Seguridad la ONU) dijo que la Amazonia le corresponde a Brasil y esa discusión nunca más procedió", dijo el presidente brasileño.
+Bolsonaro busca su reelección con el apoyo de la bases del agronegocio en el país, una actividad que por la calidad de su suelo necesita fertilizantes en gran cantidad, un tema que fue tratado el viernes pasado en la visita del ministro de Economía argentino, Martín Guzmán, en sus reuniones con su par, Paulo Guedes, y el titular de Minas y Energía, Bento Albuquerque.
+Bolsonaro, a raíz de la necesidad de fertilizantes, defiende un proyecto de ley enviado al Congreso para permitir la explotación minera en las reservas indígenas. "Podemos tener autosuficiencia en minerales explorando las zonas indígenas", dijo Bolsonaro y sostuvo que hay que "liberar a los indígenas del yugo del Estado para que tengan libertad de poder producir, como ocurre en Estados Unidos y Canadá".
+[H2] Sorpresa por compra de viagra en el Ejército
+Mientras tanto el Ejército brasileño generó polémica en el país luego de que un diputado revelara la compra de 35 mil comprimidos de viagra y elevara un pedido de informes al minsiterio de Defensa para dar explicaciones ante el Congreso. De acuerdo con el Portal de Transparencia y el Panel de Precios del gobierno de Bolsonaro, los medicamentos que contienen la droga Sildenafil fueron adquiridos en ocho licitaciones realizadas por el Ejército, la Marina y la Fuerza Aérea. Según consta en la página web donde el Estado está obligado a mostrar las compras gubernamentales, el mayor volumen fue destinado a la Marina.
+El diputado Elias Vaz, del Partido Socialista Brasileño, hizo un pedido de informes para que los jefes militares expliquen esta compra que fue realizada entre 2020 y 2022. "Necesitamos entender el motivo de esta compra del gobierno de Bolsonaro usando dinero público para adquirir viagra en estas grandes cantidades. Las unidades de salud enfrentan falta de remedios para enfermedades crónicas como la insulina y las fuerzas armadas reciben miles de comprimidos de viagra. Queremos saber", advirtió Vaz.</t>
   </si>
   <si>
     <t>Día Mundial del Agua: organizaciones y asambleas convocan manifestaciones en todo el país</t>
@@ -2636,7 +6823,29 @@
     <t>https://www.pagina12.com.ar/409832-dia-mundial-del-agua-organizaciones-y-asambleas-convocan-man</t>
   </si>
   <si>
-    <t>2022-03-22T14:20:15Z</t>
+    <t xml:space="preserve">Título: Día Mundial del Agua: organizaciones y asambleas convocan manifestaciones en todo el país
+Chapeau: Recuedan que el acceso al agua es un derecho y reclaman "que se protejan nuestros bienes comunes"
+Subtítulo: En el Día Mundial del Agua, organizaciones socioambientales y asambleas se movilizan en todo el país en rechazo al extractivismo. Recuerdan que el agua es un derecho humano. La grave situación en Chubut, donde se está secando el lago Musters.
+Editoria: Sociedad
+Tags: diario
+URL: https://www.pagina12.com.ar/409832-dia-mundial-del-agua-organizaciones-y-asambleas-convocan-man/
+Notícia completa (16 blocos):
+Hoy, en el Día Mundial del Agua, habrá movilizaciones y encuentros en más de 30 ciudades del país, en defensa del bien común y, al mismo tiempo, en rechazo y denuncia a las actividades contaminantes: agronegocio, megaminería, petróleo, forestales, megarepresas, explotación de litio y energía nuclear, entre otras.
+La Organización de Naciones Unidas (ONU) estableció en 1993 que cada 22 de marzo se conmemore el Día Mundial del Agua. En parte para concientizar que 2200 millones de personas carecen de acceso al agua potable. En julio de 2010, la Asamblea General de la ONU reconoció explícitamente el derecho humano al agua. En diciembre de 2014, la Corte Suprema de Argentina estableció también el derecho humano al agua, conocido como "fallo Kersich", por el nombre de uno de los vecinos de la localidad de 9 de Julio contra la empresa Aguas Bonaerenses y el exceso de arsénico.
+"El agua vale más que el oro" se popularizó en 2003 en Esquel, cuando el 82 por ciento de la población votó en contra de la megaminería, y se transformó en bandera de lucha en toda la Argentina.
+[H2] Defender el agua, "unir las luchas"
+"Protegemos nuestro mar ante la avanzada de las petroleras costas afueras. Proyecto que está repleto de mentiras, de falso desarrollo, de cinismo al decir que darán trabajo", denunció Alejandra Santiago, de la Asamblea por un Mar Libre de Petroleras de Mar del Plata.
+Recordó que este 22 de marzo hacen un llamado a defender el agua y "unir las luchas", donde incluyó a las resistencias contra la megaminería, el freno al agronegocio y, al mismo tiempo, a apoyar a los movimientos campesinos y a la agroecología. "Queremos que se protejan nuestros bienes comunes y no que se los regalen por unos dólares a empresas multinacionales del maldesarrollo, que solo nos traerán más pobreza y destrucción", exigió la asambleísta.
+Leonardo Moreno forma parte de la "Campaña por el Agua Limpia en las Escuelas", iniciativa nacida en 2021 que busca visibilizar la situación de las escuelas rurales y periurbanas. Desde la semana pasada y hasta hoy realizaron actividades, talleres y charlas en establecimientos educativos de Córdoba, Buenos Aires y Chaco.
+"Ponemos en cuestión la calidad del agua que tenemos en las escuelas. Millones de estudiantes y trabajadores de la educación nos vemos expuestos a distintos contaminantes, desde metales pesadas a agrotóxicos. Exigimos que el Estado dé respuestas inmediatas y concretas", explicó Moreno, que es docente de escuelas rurales en Luján.
+Moreno precisó que realizaron actividades en Trenque Lauquen, Chacabuco y La Matanza (Buenos Ares) y en Cosquín y Salsipuedes (Córdoba), entre otras localidades. Apuntó al rol de los Consejos Escolares y de los distintos gobiernos: "El agronegocio y sus fumigaciones son política de Estado. La educación parece pasar a un segundo o tercer plano".
+[H2] Un mapa de manifestaciones
+La Campaña Plurinacional del Agua para los Pueblos, iniciativa impulsada por decenas de organizaciones socioambientales, informó el mapa de manifestaciones y encuentros en Catamarca, Córdoba, Chaco, Chubut, Entre Ríos, Jujuy, La Pampa, La Rioja, Buenos Aires, Mendoza, Neuquén, Río Negro, San Luis, San Juan, Santa Fe, Santa Cruz, Tierra del Fuego y Tucumán.
+En la Ciudad de Buenos Aires la marcha comienza a las 16, desde el Congreso hasta Plaza de Mayo, impulsada también por la Coordinadora Basta de Falsas Soluciones. Entre las consignas figuran "defendamos el agua para la vida y no para los negocios" y "el agua vale más que todo, la deuda es con los pueblos y la naturaleza".
+En Chubut se da una situación particularmente grave en la localidad de Sarmiento, conocida como "la ciudad de los lagos". Allí estaba el lago Colhue Huapi, que abarcaba 53.000 hectáreas. En la década del '90 comenzó un proceso de bajante vinculado a la accionar de grandes estancias, petroleras y cambio climático. En la década del 2000 se secó por completo. A pocos kilómetros se ubica el lago Musters, que experimenta una bajante histórica y corre el riesgo de seguir los pasos del Colhue Huapi.
+Las organizaciones socioambientales denuncian desde hace más de una década la inacción gubernamental para frenar la desaparición del lago. El 13 de marzo se realizó allí un "abrazo al Musters", para exigir que el Estado (en sus distintos niveles) tomé medidas de protección y restauración.
+La misma semana, el intendente Sebastián Balochi, reconoció que el lago "parece el Desierto de Sahara". Le respondió la histórica militante socioambiental Zulma Usqueda, que puntualizó en las responsabilidades. Recordó que, hace doce años, los concejales de Comodoro Rivadavia ignoraron un proyecto de ordenanza presentado por el Foro Ambiental y Socia de la Patagonia (firmado por organizaciones civiles y por más de 3000 personas) que declaraba el agua como derecho humano, bien común , natural y público.
+También apuntó contra el Instituto Provincial del Agua, que "nunca respondió las notas de los vecinos que solicitaban información y acciones ante la crisis hídrica". Y recordó que la Defensoría del Pueblo de Nación propuso "constituir con urgencia un Comité Interjurisdiccional de Cuenca del Río Senguer (debido a que la Ley 25.688 establece la creación de 'comités de cuencas hídricas con la misión de asesorar a la autoridad competente y colaborar en la gestión ambientalmente sustentable de las cuencas hídricas)", pero no fue escuchado por los gobernadores de Chubut, Santa Cruz ni por el Ministerio del Interior de Nación.</t>
   </si>
   <si>
     <t>"La aprobación del acuerdo es parte de un entendimiento de todos los sectores políticos"</t>
@@ -2645,9 +6854,6 @@
     <t>https://www.pagina12.com.ar/lbpupdates/408905</t>
   </si>
   <si>
-    <t>2022-03-18T03:02:35Z</t>
-  </si>
-  <si>
     <t>El ministerio de Justicia de Brasil concedió a Bolsonaro la medalla al "mérito indigenista"</t>
   </si>
   <si>
@@ -2657,7 +6863,21 @@
     <t>https://www.pagina12.com.ar/408559-el-ministerio-de-justicia-de-brasil-concedio-a-bolsonaro-la-</t>
   </si>
   <si>
-    <t>2022-03-17T03:01:00Z</t>
+    <t xml:space="preserve">Título: El ministerio de Justicia de Brasil concedió a Bolsonaro la medalla al "mérito indigenista"
+Chapeau: La medida fue muy criticada por sectores indigenistas y ambientalistas
+Editoria: El Mundo
+Tags: Brasil, Jair Bolsonaro, printed-edition, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/408559-el-ministerio-de-justicia-de-brasil-concedio-a-bolsonaro-la-/
+Notícia completa (9 blocos):
+El ministerio de Justicia brasileño concedió a Jair Bolsonaro la medalla al "mérito indigenista", otorgada a personalidades que actúan por el bien de estas comunidades, pese a que el mandatario es muy criticado por promover la explotación económica de sus territorios.
+La medida, muy criticada por sectores indigenistas y ambientalistas, fue publicada este miércoles en el Diario Oficial "en reconocimiento a los relevantes servicios de carácter altruista, relacionados con el bienestar, protección y defensa de las comunidades indígenas".
+Sonia Guajajara, coordinadora de la Articulación de los Pueblos Indígenas de Brasil (APIB), consideró "absurda" la condecoración y aseguró que esa asociación intentará anularla en los tribunales.
+También la primera diputada indígena de Brasil, Joenia Wapichana, manifestó su "repudio" al jefe de un gobierno que lleva tres años "de muchos retrocesos y ataques a los derechos de los pueblos indígenas".
+Fueron condecorados también una veintena de colaboradores de Bolsonaro, entre ellos el ministro de Justicia, Anderson Torres, que otorgó la medalla a Bolsonaro, así como los titulares de Agricultura, Tereza Cristina, el de Infraestructura, Tarcísio Gomes, y el de Defensa, Walter Braga Netto.
+El mandatario ultraderechista llegó al poder en 2019 con la promesa de no demarcar "ni un centímetro más" de tierra para los indígenas, que representan 0,5% de los 213 millones de brasileños y cuyas reservas ocupan el 13% del vasto territorio del país.
+También prometió abrir las reservas existentes, ya muy golpeadas por la deforestación, la minería ilegal y el comercio ilegal de madera, a las actividades extractivas.
+Apoyado por sus aliados del agronegocio en el Congreso, el bolsonarismo está intentando acelerar varios proyectos considerados perjudiciales para los indígenas y el medio ambiente, entre ellos uno que busca legalizar la explotación minera en las reservas, algo por ahora no regulado en la Constitución.
+"Es un escarnio que el mismo gobierno que intenta liberar la minería en las tierras indígenas, poniendo en riesgo la existencia de esos pueblos tan perseguidos y maltratados, tenga la desfachatez de autoconcederse medallas de 'mérito' por todos estos males hechos en los últimos tres años", declaró el diputado Alessandro Molón, coordinador del Frente Parlamentario Ambientalista. Molón presentó un proyecto de decreto legislativo para anular la medida.</t>
   </si>
   <si>
     <t>El Patrón Bermúdez salió con los tapones de punta contra Mauricio Macri</t>
@@ -2669,7 +6889,25 @@
     <t>https://www.pagina12.com.ar/407917-el-patron-bermudez-salio-con-los-tapones-de-punta-contra-mau</t>
   </si>
   <si>
-    <t>2022-03-14T12:53:47Z</t>
+    <t xml:space="preserve">Título: El Patrón Bermúdez salió con los tapones de punta contra Mauricio Macri
+Chapeau: La dura respuesta del exjugador a las críticas del expresidente
+Subtítulo: El exdefensor colombiano, multicampeón en Boca, salió a cruzar al dirigente del PRO tras sus dichos sobre Juan Román Riquelme.
+Editoria: Deportes
+Tags: Mauricio Macri, Boca Juniors, Juan Román Riquelme, mauricio-macri, boca-juniors, juan-roman-riquelme, diario
+URL: https://www.pagina12.com.ar/407917-el-patron-bermudez-salio-con-los-tapones-de-punta-contra-mau/
+Notícia completa (12 blocos):
+El ex presidente Mauricio Macri recibió una durísima crítica por parte del exjugador de Boca Juniors e integrante del Consejo de Fútbol de la institución Jorge "Patrón" Bermúdez, quien le pidió que no opine sobre la labor que se está haciendo en el club de La Ribera tras ser el mandatario que "más endeudó al país". Bermúdez lamentó además las palabras de Macri contra Juan Román Riquelme, vicepresidente de Boca, al considerar que buscó desviar la atención en los días en que "apedreaban el Congreso nacional por las medidas que él tomó como administrado", en relación a la deuda con el FMI.
+[H2] Las críticas de Macri a Riquelme
+Macri visitó el jueves pasado la muestra del agronegocio Expoagro, mientras en la Cámara de Diputados, se debatía la aprobación del acuerdo alcanzado entre el Gobierno y el FMI para refinanciar la deuda histórica e irregular tomada por su gestión. En ese marco, el líder del PRO aprovechó la pregunta que un asistente a la feria le hizo sobre la situación de Boca justo delante de los micrófonos. "¿No te das cuenta que nos está arruinando? Una cosa es saber poner la pelota y otra dirigir un club", respondió el también expresidente de Boca en alusión a Riquelme.
+"No puedo aceptar que Mauricio Macri hable así de esta labor dirigencial. Por muchos factores, el principal y el que más me llena la sangre, es que aprendí a amar este país como al mío. Tengo un hijo argentino y amo esta tierra. No hubo otro mandatario que que endeudara más este país como ese señor y se atreve a hablar mal de nuestra administración", le apuntó Bermúdez en la noche del domingo ante una consulta del periodista de TyC Sports, Leandro "Tato" Aguilera.
+[H2] Bermúdez, un hombre de confianza de Riqueleme
+Bermúdez integra el Consejo del Fútbol y es un hombre de confianza de Riquelme, quien convocó al exdefensor central para ser parte de su gestión a cargo de la dirección deportiva del club y como vicepresidente, desde la renuncia de Mario Pergolini. En ese sentido, el "Patrón" le respondió a Macri también con gestión: "Hoy el club está muy bien económicamente, el club acaba de hacer contrataciones de mucha altura, acabamos de arreglar la Bombonera que en más de 35 años no se le hizo nada. Se fue campeón tres veces, tenemos por delante dos finales o quizá tres".
+[H2] El "Topo Gigio" y el acuerdo por la deuda con el FMI
+Con el breve análisis de la tarea que están llevando adelante a pesar de los dichos de Macri, Bermúdez recordó la larga rivalidad entre Macri y Riquelme, cuando eran presidente y jugador de Boca, respectivamente. Diferencias que quedaron inmortalizadas con el recordado festejo del "Topo Gigio".
+"Tampoco lo quiso como jugador, todos lo sabemos. Ese Topo Gigio no fue gratuito", señaló Bermúdez para marcar el sesgo de Macri cuando opina sobre la labor de Riquelme como dirigente. Y remató con otra cuota demoledora de la gestión presidencial de Macri: "Pero lo más doloroso de todo es que mientras en el país y en Buenos Aires había gente apedreando el Congreso nacional por las medidas que él tomó como administrador de este país, salga y desvíe la atención hablando de Boca. Duele."
+Unsupported embed [https://www.instagram.com/tv/CbEBCqYFg6D/?utm_medium=share_sheet]
+[H3] Seguí leyendo
+[H3] ¿Qué le pasó a Carlos Izquierdoz?</t>
   </si>
   <si>
     <t>Gonzalo Tordini. “La relación de Argentina con China es necesaria, complementaria y promisoria”</t>
@@ -2678,7 +6916,33 @@
     <t>https://www.pagina12.com.ar/406868-gonzalo-tordini-la-relacion-de-argentina-con-china-es-necesa</t>
   </si>
   <si>
-    <t>2022-03-10T03:01:00Z</t>
+    <t xml:space="preserve">Título: Gonzalo Tordini. “La relación de Argentina con China es necesaria, complementaria y promisoria”
+Chapeau: ENTREVISTA
+Subtítulo: Especialista en las relaciones entre ambos países, el académico de las universidades Arturo Jauretche y de la Defensa Nacional detalla las oportunidades que se abren para el sistema productivo nacional tras la visita del presidente Alberto Fernández a la potencia asiática, como parte de la construcción de “una política exterior soberana”.
+Editoria: Universidad
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/406868-gonzalo-tordini-la-relacion-de-argentina-con-china-es-necesa/
+Notícia completa (20 blocos):
+Un posgrado en la Universidad de Economía y Negocios de Beijing (UIBE) le permitió a Gonzalo Tordini profundizar sus conocimientos sobre la cultura, la economía, la política y el idioma de China, una potencia con la que Argentina mantiene relaciones diplomáticas desde hace 50 años, pero con la que existen brechas significativas y desconocimiento de sus producciones académicas.
+Su meta fue transmitir los saberes adquiridos y fomentar los intercambios educativos entre ambos países. Hoy Tordini es director del Programa Estratégico Sino-Argentino (PESA) de la Universidad de la Defensa Nacional (UNDEF) y de Relaciones Internacionales de la Universidad Nacional Arturo Jauretche (UNAJ). En los últimos años, trabajó en la internacionalización de las casas de estudios argentinas a través de la gestión, la docencia y la investigación en distintas áreas de las universidades de San Martín, Tres de Febrero, Quilmes y Rafaela, y del Ministerio de Educación. Además, en 2017, junto con otros colegas fundó la Asociación de Ex Becarios Argentina China (ADEBAC), que realiza charlas, cursos, actividades y proyectos orientados a los jóvenes argentinos interesados en el gigante asiático.
+En diálogo con el Suplemento Universidad, el académico analizó el ingreso de Argentina en la Nueva Ruta de la Seda, a partir de la visita a Chima del presidente Alberto Fernández en febrero último, y subrayó que, en ese sentido, se abre una “oportunidad de mejorar la deficiente infraestructura e incrementar los vínculos con Asia”.
+–¿Cuál es el alcance de la Nueva Ruta de la Seda?
+–China propone interconectar distintas partes del planeta a través de la Nueva Ruta de la Seda (oficialmente “La Franja y La Ruta”). Para entender la iniciativa, es importante comprenderla primero como concepto geopolítico y luego como conjunto de acciones concretas. Es una iniciativa integrada, multidimensional, compuesta por un conjunto de proyectos que incluyen autopistas, rutas, aeropuertos, vías marítimas, oleoductos y gasoductos, líneas de transmisión eléctrica, redes de comunicación de datos, etc. con el objetivo principal de recomponer una de las piezas faltantes en el estado actual del mundo para el desarrollo económico: la infraestructura para la conectividad.
+–¿En qué beneficia a Argentina ingresar en este acuerdo?
+–Ante la iniciativa existen partidarios y detractores, y las perspectivas para Argentina son parte del debate cotidiano de académicos, políticos, trabajadores y empresarios. Por ello, se torna imprescindible estar preparado y construir una política exterior soberana, donde podamos aprovechar las distintas oportunidades que colaboren en mejorar la calidad de vida de la población.
+–¿Cuáles son las oportunidades y los desafíos que se plantean?
+–Países de la región ya han firmado el ingreso y Argentina se sumó durante el último viaje de Alberto Fernández a China. Nuestro país tiene una oportunidad de mejorar su deficiente infraestructura e incrementar los vínculos con Asia, a través de una nueva plataforma internacional. El ingreso permitirá mejorar la conectividad tanto física como digital y acercarnos cultural y económicamente a una región distante, pero altamente dinámica. La iniciativa nos propone desafíos a resolver en conjunto, como la articulación de estrategias para que los excedentes económicos, producto de la venta de materias primas, sean funcionales a la industrialización; fomentar la asociatividad empresaria por sobre las adquisiciones; incentivar la transferencia tecnológica para un desarrollo endógeno y promover los intercambios comerciales protegiendo sectores estratégicos. Será nuestra tarea orientar los proyectos hacia el bien común, fortalecer las instituciones nacionales de supervisión, alcanzar consensos internos para la implementación y generar los mecanismos de política exterior que no limiten el margen de maniobra.
+–¿Qué análisis hace del vínculo entre Argentina y China después de medio siglo de relaciones diplomáticas?
+–En términos generales, la relación es necesaria, complementaria y promisoria. Tenemos una asociación estratégica integral que realmente incluye distintos ámbitos de la cooperación, como el científico-tecnológico, la defensa, el educativo, el deportivo, el cultural, el financiero, en materia de seguridad, energía, agronegocios, aeroespacial, entre muchos otros. El plano comercial suele ser el más conocido y abordado, siendo China nuestro segundo socio tanto para exportaciones como importaciones. Sin embargo, la base de la relación es mucho más amplia y tiene bases cada día más firmes.
+Unprocessed element [blockquote]
+–¿Esos lazos pueden afectar la relación con países como Estados Unidos?
+–Como cualquier tipo de relación, se basa en la confianza, que se construye con los años, con reglas, señales y expectativas sinceras y claras. China tiene un plan y políticas específicas que orientan la relación que desea tener con los países latinoamericanos y los ámbitos de cooperación en los que considera que ambas partes pueden ganar. Los países latinoamericanos en conjunto debemos trabajar más articuladamente y a largo plazo en este sentido. En la Comunidad de Estados Latinoamericanos y Caribeños (CELAC), donde Argentina asume su presidencia pro tempore en 2022, existe un excelente mecanismo de diálogo a través del foro China-CELAC para trabajar en la relación regional, enfrentando las turbulencias mundiales y centrado principalmente en la recuperación económica posterior a la pandemia de COVID-19.
+–¿De qué se trata el Programa Estratégico Sino-Argentino?
+–El PESA de la UNDEF tiene como objetivo el estudio, investigación, formación y reflexión especializada de los agentes, militares y civiles, vinculados con la defensa y el desarrollo nacional, permitiendo establecer una estrategia de mediano y largo plazo de vinculación con China, profundizando la asociación estratégica integral entre ambos países. El Programa trabaja articuladamente con la Secretaría de Relaciones Internacionales para la Defensa del Ministerio de Defensa.
+–¿Qué balance realiza de la Diplomatura en Estudios Estratégicos Chinos, una de las actividades desarrolladas por el PESA?
+–La diplomatura se dictó en 2021 abordando los aspectos militares, sociales, políticos, lingüísticos, históricos y económicos de la República Popular China y su relación con Argentina y América Latina. Generó gran interés, habiendo superado los quinientos inscriptos y 90 profesionales de las relaciones exteriores, civiles y militares, cursaron durante un semestre con un prestigioso cuerpo docente.
+–¿Cuáles son los pasos a seguir?
+–La formación se articula con una intensa promoción de acciones de investigación, reflexión e intercambios, complementarias entre sí y un eje importante en la enseñanza de idioma chino mandarín. Con relación al idioma, hemos establecido un convenio con el Centro para la Educación y Cooperación del Idioma Chino de la República Popular China para la implementación de acciones de cooperación para la enseñanza y difusión del idioma chino en Argentina. Asimismo, durante la misión presidencial a China, se suscribió un importante convenio con la Universidad de Defensa de China, a través del cual se intensificarán los proyectos conjuntos.</t>
   </si>
   <si>
     <t>Gabriel Santana</t>
@@ -2693,7 +6957,29 @@
     <t>https://www.pagina12.com.ar/402081-honores-de-bolsonaro-a-putin-para-salir-del-ostracismo</t>
   </si>
   <si>
-    <t>2022-02-17T03:01:00Z</t>
+    <t xml:space="preserve">Título: Honores de Bolsonaro a Putin para salir del ostracismo
+Chapeau: El presidente de Brasil está de visita en Moscú
+Subtítulo: Antes de su encuentro en el Kremlin, el líder brasileño de extrema derecha depositó una ofrenda floral en un monumento que honra a los soldados de la extinta Unión Soviética caídos por defender al país del nazismo.
+Editoria: El Mundo
+Tags: Vladimir Putin, Jair Bolsonaro, printed-edition, vladimir-putin, jair-bolsonaro, diario
+URL: https://www.pagina12.com.ar/402081-honores-de-bolsonaro-a-putin-para-salir-del-ostracismo/
+Notícia completa (16 blocos):
+Los presidentes Vladimir Putin y Jair Bolsonaro hicieron este miércoles un llamado a la paz y a la defensa del multilateralismo durante un encuentro en Moscú en el cual el brasileño expresó "solidaridad a Rusia" y el ruso respaldó a Brasil para que logre un asiento permanente en el Consejo de Seguridad de la ONU. Ninguno de los dos mandatarios se refirió a la crisis de Ucrania. Con este viaje a Moscú, Bolsonaro busca darle vuelto internacional a su criticada gestión presidencial, sobre todo de cara a los comicios del próximo dos de octubre, en los que irá por la reelección.
+Antes de su encuentro con Putin, el líder de extrema derecha depositó una ofrenda floral en un monumento que honra a los militares caídos durante la Segunda Guerra Mundial, situado al lado de las murallas del Kremlin.
+[H2] Visita centrada en temas comerciales
+Bolsonaro desafió las advertencias de Estados Unidos por su viaje en un momento de alta tensión entre Moscú y los países occidentales, que acusan a Putin de preparar un ataque contra Ucrania. Pero el presidente de Brasil, un aliado tradicional de Washington, desestimó la presión y defendió el desplazamiento afirmando que las reuniones estaban centradas en temas comerciales, al ser su país un gran productor y exportador agrícola que "depende en gran parte de los fertilizantes de Rusia".
+"Estoy muy feliz y honrado por esta invitación, somos solidarios con Rusia, queremos colaborar en muchas áreas como defensa, petróleo y gas, agricultura", dijo Bolsonaro en su mensaje protocolar antes de iniciar la reunión de trabajo con Putin. A diferencia de lo que hizo con varios dirigentes extranjeros recientemente, que se sentaron en el otro extremo de una larga mesa de seis metros durante sus reuniones con Putin, a Bolsonaro solo lo separaba una mesita de café de su par ruso.
+Esto podría deberse, según los medios rusos, a que el presidente brasileño se habría sometido a un test de coronavirus en Rusia. Bolsonaro es conocido por sus polémicas posturas frente a la pandemia y no está vacunado contra la covid-19.
+En Brasil la visita es vista como una posibilidad de salir del aislamiento mundial de la figura de Bolsonaro, de cara a la búsqueda de la reelección en los comicios del dos de octubre, pero también la prensa local ha apuntado una contradicción con el discurso interno y la participación del aliado del expresidente Donald Trump en la ofrenda floral a los soldados de la extinta Unión Soviética caídos por defender al país del nazismo. Sucede que Bolsonaro defendió la semana pasada la criminalización del comunismo en el marco del escándalo creado por una polémica en torno a la legalización de un partido nazi en Brasil.
+Putin, por su parte, subrayó la cooperación entre Brasil y Rusia y destacó que el gigante sudamericano "es el principal socio comercial en América latina". El mandatario ruso, quien ya se había reunido a principios de mes con el presidente Alberto Fernández, intensificó sus contactos con líderes latinoamericanos en medio de la crisis con Ucrania.
+"Brasil y Rusia tienen un firme compromiso con el multilateralismo. Sin dudas seguiremos en los Brics, un grupo respetado que desempeña un papel multipolar y de gran peso económico en el mundo", afirmó Putin en su declaración a la prensa. El grupo Brics lo integran Brasil, Rusia, India, China y Sudáfrica.
+Incluso el presidente ruso expresó su solidaridad a Bolsonaro por los fallecidos en la tragedia de las lluvias de Petrópolis, en la sierra de Río de Janeiro. "Nuestra reunión de casi dos horas fue muy fructífera. Es una señal de que dos grandes potencias tienen mucho por avanzar. Repito: el mundo es nuestra casa, y Dios está por encima de todos nosotros. Predicamos la paz y respetamos a todos los que actúan de esta manera”, respondió el brasileño en la declaración final a la prensa.
+[H2] A favor de ampliar el Consejo de la ONU
+El canciller ruso, Serguei Lavrov, dijo que su país defiende la representación geográfica ampliada del Consejo de la ONU, en el marco de su apoyo a las iniciativas para el ingreso de India y Japón a la élite del poder de decisión mundial, que hoy integran apenas Estados Unidos, Rusia, China, Francia y Gran Bretaña. El primer impulso al ingreso de Brasil había sido dado en 2014 por parte de Rusia al gobierno de Dilma Rousseff.
+Bolsonaro, por su parte, aprovechó para agradecer la posición de Rusia de apoyo a la soberanía brasileña en su porción de la selva amazónica, ante las críticas a la política ambiental que esgrimió años atrás el presidente de Francia, Emmanuel Macron. Bolsonaro también logró que Rusia se comprometiera a ser el proveedor de fertilizantes, en un mensaje a su base electoral del agronegocio. Sobre todo porque la estatal Petrobras, en el marco de su programa de desinversión, vendió la planta de fertilizantes de Mato Grosso do Sul a una empresa privada rusa.
+[H2] Mención a la crisis con Ucrania
+En una reunión paralela, los cancilleres Lavrov y Franca y los ministros de Defensa Serguei Chorgu y Walter Braga Netto pasaron revista a los acuerdos sectoriales. "Nosotros les dijimos a los brasileños sobre la intención de Estados Unidos de dividir el mundo en dos partes, países democráticos y no democráticos", dijo Lavrov al cierre del encuentro. Sin referirse directamente a la crisis con Kiev, Bolsonaro dijo que Brasil era "solidario" con Rusia.
+El mandatario brasileño tiene previsto visitar la Duma y participar de un encuentro empresarial binacional antes de partir hacia Budapest para reunirse con su principal aliado en Europa, el primer ministro húngaro de ultraderecha, Viktor Orban.</t>
   </si>
   <si>
     <t>Los pasos de la Socioambiental</t>
@@ -2705,7 +6991,22 @@
     <t>https://www.pagina12.com.ar/401421-los-pasos-de-la-socioambiental</t>
   </si>
   <si>
-    <t>2022-02-14T03:01:00Z</t>
+    <t xml:space="preserve">Título: Los pasos de la Socioambiental
+Chapeau: La Plataforma que reclama contra el extractivismo
+Subtítulo: Creada en agosto de 2021, agrupa a la UTT, Basta es Basta, y otros. Su primera actividad fue el panazo en Plaza de Mayo.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/401421-los-pasos-de-la-socioambiental/
+Notícia completa (9 blocos):
+"Sequías, incendios, ola histórica de calor, trigo transgénico, mega granjas porcinas, petroleras en el mar, pandemia. Parece el guión de una película apocalíptica pero no lo es. Lamentablemente es la radiografía de la Argentina de 2022", así comienza el documento del colectivo Plataforma Socioambiental, integrado por pequeños productores, indígenas, asambleas socioambientales y ONG que, desde una mirada integral del ambiente, cuestionan que se sigan priorizando actividades que arrasan territorios y poblaciones.
+La Unión de Trabajadores de la Tierra (UTT), la Coordinadora por un Vida sin Agrotóxicos en Entre Ríos: Basta es Basta, el Movimiento Nacional Campesino Indígena-Somos Tierra (MNCI-ST), la Asamblea Tandil Sin Trigo Transgénico ni Agrotóxicos y el Instituto de Salud Socioambiental de la Facultad de Ciencias Médicas de Rosario, entre otras, conformaron la Plataforma Socioambiental en agosto de 2021 con la premisa de "resistir al mal-desarrollo y construir la justicia social y ambiental".
+Su primera actividad fue un "panazo" en Plaza de Mayo, contra el trigo transgénico de la empresa Bioceres-Indear (donde confluyen empresarios como Hugo Sigman y Gustavo Grobocopatel). Al inicio del 2022 emitieron un comunicado titulado "Basta de Ecocidio" que puntualiza los ejes de la crisis climática y los impactos sociales que acarrea. "Las comunidades y trabajadores de la tierra de muchas provincias reclaman porque se mueren sus animales y no pueden seguir produciendo debido a la falta de agua en un contexto de sequías alarmante", explican.
+Puntualizan la seguidilla de incendios en la Patagonia, Litoral, Buenos Aires, San Luis y Salta, entre otros lugares. Recuerdan que, desde 2019, se declaró en la Argentina la "emergencia climática y ecológica", pero cuestionan que "son muy pocas" las medidas que se tomaron en materia ambiental para evitar o reducir estos desastres socioambientales. "El agronegocio, las petroleras, la deforestación, las mineras, el fracking, el negocio inmobiliario, son algunas de las caras más destructoras y contaminantes del modelo extractivista que prioriza las ganancias por sobre la vida humana, la naturaleza y los bienes comunes", denuncian.
+Jeremías Chauque es mapuche y es integrante de la experiencia agroecológica Desvío a la Raíz, en la localidad de Desvío Arijón (Santa Fe). "En nuestro linaje antiguo está marcado a fuego la circularidad, la semilla vuelve a nacer y nada es casual. Y así llega el tiempo donde es necesario dejar en claro qué urgencias y prioridades estamos labrando y poniendo en agenda los pueblos. La producción debe ser sinónimo de sociedad, de ambiente, de cultura. Tenemos claro que si una actividad contamina, mata y empobrece: no es progreso, es saqueo", afirma.
+El llamado a sesiones extraordinarias en el Congreso Nacional confirmó que se tratará el proyecto de ley impulsado por el Consejo Agroindustrial Argentino (sector que nuclea a todas las grandes empresas del agronegocio) y se dejó afuera los proyectos de Ley de Humedales y de Acceso a la Tierra para los pequeños productores, impulsada por la UTT desde hace años. "Queda en evidencia que la agenda del Gobierno tiene más que ver más con extractivismo, con los grupos concentrados, que en dar respuesta a nuestro sector. Seguramente tiene que ver con el acuerdo con el FMI y deja en evidencia que nunca le interesó el proyecto de Acceso a la Tierra para los que producimos alimentos para el pueblo", cuestionó Agustín Suárez, de la UTT.
+El comunicado de Plataforma Socioambiental recuerda que las y los vecinos se organizan para apagar los fuegos, para frenar la deforestación, para cuidar los mares y las montañas, para sembrar agroecología, para abastecerse de agua, pero también apunto al rol gubernamental: "La respuesta a un problema tan estructural no puede depender únicamente de la solidaridad y la autogestión de nuestros pueblos. Necesitamos políticas públicas de forma urgente para realmente combatir la crisis climática y las industrias saqueadoras que lo impulsan. Las emergencias ambientales no pueden quedar en una declaración de principios. Necesitamos políticas contundentes para hacerle frente a las consecuencias que el modelo extractivista nos deja".
+Diciembre de 2021 dejó otra muestra de que la megaminería no tiene licencia social en Chubut. Al igual que Mendoza en 2019, las ciudades chubutenses salieron a la calle y lograron la derogación de la ley minera que había impulsado el gobernador Mariano Arcioni. A 1800 kilómetros de Rawson, en La Rioja, la población lleva catorce años en rechazo a la instalación de empresas mineras. En la actualidad se mantiene la movilización en el Departamento de Vinchina, al oeste provincial, con más de 90 permisos mineros y un yacimiento de la empresa Pathfinder al pie de las Sierras del Famatina que puede afectar al río Valle Hermoso, única cuenca hídrica que alimenta al pueblo.
+María Pía Silva, asambleísta de La Rioja, precisa que existen más de 40 proyectos dentro de la reserva provincial Laguna Brava, Corona del Inca y otros sitios de alto valor biológico y arqueológico que conservan humedales andinos. "El glaciar El Potro, el más grande de nuestra cordillera riojana, está rodeado de proyectos mineros y a tan sólo dos kilómetros de allí pretende ponerse en marcha el mega yacimiento Josemaria --en San Juan--. Por eso, los vecinos y vecinas iniciaron un bloqueo selectivo a las empresas mineras que están explorando la cordillera riojana y ya están impactando las fuentes de agua. Las asambleas riojanas exigimos anulación de los permisos mineros", explicó Silva.</t>
   </si>
   <si>
     <t>Neil Young, gritar pidiendo verdad</t>
@@ -2714,7 +7015,25 @@
     <t>https://www.pagina12.com.ar/398482-neil-young-gritar-pidiendo-verdad</t>
   </si>
   <si>
-    <t>2022-01-30T03:01:00Z</t>
+    <t xml:space="preserve">Título: Neil Young, gritar pidiendo verdad
+Subtítulo: "Si grita pidiendo verdad en lugar de auxilio, si se compromete con un coraje que no está seguro de poseer, si se pone de pie para señalar algo que está mal pero no pide sangre para redimirlo, e
+Editoria: Cultura y Espectáculos
+Tags: Spotify, Opinión, Música, printed-edition, opinion, musica
+URL: https://www.pagina12.com.ar/398482-neil-young-gritar-pidiendo-verdad/
+Notícia completa (13 blocos):
+"Si grita pidiendo verdad en lugar de auxilio, si se compromete con un coraje que no está seguro de poseer, si se pone de pie para señalar algo que está mal pero no pide sangre para redimirlo, entonces es rock and roll." (Pete Townshend)
+¿Sabía Neil Young que la película terminaría así? Por supuesto que lo sabía. Con 76 años de vida y casi 60 de carrera, el guitarrista y compositor canadiense conoce lo suficiente de la industria musical como para tener claro dónde está el poder y cómo opera. Podrá sonar anacrónico en tiempos de tanto pragmatismo, pero se ajusta al perfil del personaje: lo de Young no es estrategia, es una cuestión de convicciones.
+Recapitulando: esta semana, Neil Young publicó una carta a su manager y su discográfica -que luego eliminó de su página oficial- en la que sentó posición con respecto al podcast The Joe Rogan Experience. “Spotify está diseminando información falsa sobre las vacunas, causando potencialmente la muerte de personas que la creen”, señaló. “Quiero que le informen a Spotify que deseo que se levante toda mi música de la plataforma. Pueden tener a Joe Rogan o a Young. No a ambos”. Es necesario citar la carta tal cual, porque hubo análisis posteriores fundados en un supuesto ultimatum o chantaje que no existió: Young exigió sacar su música de Spotify, y señaló al podcast como la razón. Sabía que era ocioso pedir que levantaran a Joe Rogan, que con sus 11 millones de oyentes y un contrato de 100 millones de dólares tiene mucho más poder.
+Como definió Pete Townshend en aquella cita incluida por Charly García en Yendo de la cama al living, Neil Young gritó pidiendo verdad. No fue un gesto ególatra, tribunero o inútil. Hace pocos días, más de 300 especialistas en medicina, infectología, inmunología, científicos, investigadores, firmaron una carta abierta en la que le señalaban a Spotify lo mismo que Young. Apuntaron especialmente al episodio 1757 de The Joe Rogan Experience, una extensa charla con Robert Malone, médico negacionista de la pandemia cuya cuenta de Twitter fue suspendida por sus peligrosas expresiones sobre las vacunas. Además de comparar las medidas de cuidado sanitario con el nazismo, Malone asemejó a las vacunas con la castración y la mutilación genital femenina y es uno de los defensores de la teoría esgrimida por otro rocker legendario, Eric Clapton, quien aseguró que el público es "hipnotizado" con mensajes subliminales para vacunarse.
+La edad promedio de les oyentes de The Joe Rogan Experience es de 24 años. Abundan los análisis del modo en que las redes sociales y el universo gamer han sido campo orégano para que crezcan los discursos de derecha entre les jóvenes. "Esta no es solo una preocupación científica o médica; es un tema sociológico de proporciones devastadoras, y Spotify es responsable de que esta actividad prospere en su plataforma. Llamamos a Spotify a establecer inmediatamente una política clara y pública para moderar la desinformación en su plataforma".
+El comunicado del sector científico no apareció en ningún gran titular. La carta de Young recorrió el mundo. ¿Perdió el viejo Neil?
+En 2015, el canadiense lanzó The Monsanto Years, un disco dedicado a denunciar las consecuencias del agronegocio en los tiempos modernos. No melló demasiado el poder de la corporación, pero no era el punto. Otra vez, no se trataba de estrategia sino de convicciones. It's better to burn out than to fade away, "es mejor arder que desvanecerse lentamente", cantó en Rust Never Sleeps de 1979, una frase que suele citarse más por figurar en la carta de suicidio de Kurt Cobain que por su peso conceptual. Neil prefiere arder sosteniendo sus opiniones que ir diluyéndose en el gran océano del no te metás.
+De fondo, claro, está un debate que obviamente no se resolverá aquí: ¿dónde chocan la libertad de expresión y el uso malintencionado de medios de difusión -convencionales o nuevos, como redes y plataformas- para propalar mensajes falsos, peligrosos para la salud pública o la integridad de las personas? De nuevo: Neil Young no pidió sangre para redimir. Manifestó un nuevo desacuerdo con una plataforma a la que ya criticó en el pasado (por el reparto de dinero, por la calidad del audio), se retiró de ella. Pero se puso de pie para señalar algo. Y hubo quien lo criticó por llamar la atención sobre Joe Rogan, propiciarle nuevos seguidores, pero lo otro es sentarse a ver cómo pasan las cosas. Y un tipo que ya señaló a Monsanto, y en sus shows y sus acciones defiende otra forma de producción de alimentos, no es de los que se quedan sentados. Rust Never Sleeps: el óxido no descansa. Neil tampoco.
+Pero ni siquiera es una cuestión generacional, no cabe ceder a la tentación de glorificar a leyendas como Young por seguir defendiendo a la música como vehículo de compromiso. Ahí está Clapton, que allá lejos y hace tiempo tuvo serios problemas por su discurso racista y anti migración, pero tuvo entonces el atenuante de estar viviendo en una nube de heroína. En alianza con otro peso pesado como Van Morrison, el guitarrista ha tenido expresiones tan peligrosamente torcidas como las de Rogan y Malone, obligando al público al necesario ejercicio de separar al músico de la persona. Como buena parte de la Humanidad, entre los artistas de cualquier edad aparece todo tipo de opiniones. Hay viejos vinagres que producen algo de vergüencita, hay traperos adolescentes más despiertos que algunas figuras.
+La cuestión, en última instancia, es el gesto. Spotify no va a dar el brazo a torcer y las "regulaciones" en las redes siempre son relativas: basta ver cuántas veces los usuarios denuncian discursos de odio que, tras un "análisis" de la plataforma, se concluye que "no vulnera nuestras reglas". Lo que hizo Young fue ponerle un potente foco al asunto. Su existencia no depende de Spotify, ha construido una sólida carrera sin el streaming, sus canciones tienen vida propia. Rogan sí necesita ese amplificador, y el amplificador necesita a Rogan para que sigan girando las ruedas del negocio, un negocio que se mide en decenas de millones.
+"Apoyo la libertad de expresión, nunca estuve a favor de la censura", señaló Young en una nueva carta, el viernes. "Las compañías privadas tienen el derecho de elegir con qué obtener beneficios, así como yo elijo no tener mi música en una plataforma que disemina información dañina. Estoy feliz y orgulloso de expresar mi solidaridad con los trabajadores de la salud en la línea de frente, que arriesgan sus vidas cada día para ayudar a otros". De paso, el músico volvió a señalar las deficiencias de audio de la plataforma ("Spotify reproduce la música al 5% de su calidad, y te la cobra como si fuera la cosa real") y remachó: "Cuando dejé Spotify me sentí mejor. Y como bonus inesperado, sueno mejor en todos los demás lugares". No fue el único bonus: ese mismo viernes, Joni Mitchell movió más el tablero. "He decidido quitar mi música de Spotify. Hay gente irresponsable que propala mentiras que cuestan vidas. Expreso mi solidaridad con Neil Young y la comunidad científica y médica global."
+En la noche del sábado se supo que Nils Lofgren se sumaba a la lista. "Cuando estas heroicas mujeres y hombres, que pasan sus vidas curando y salvando las nuestras, piden ayuda, no les das la espalda por el dinero o el poder", señaló el guitarrista de Crazy Horse y la E Street Band en el sitio de Young. "Escuchás y los acompañás". El músico anunció el retiro de Spotify de su obra en los últimos 27 años, y pidió que hagan lo mismo a las discográficas que poseen los derechos sobre su producción anterior.
+Más allá de los principios que guían al rock desde sus inicios, sus representantes entendieron hace tiempo que las canciones no lograrán cambiar el mundo. Pero lo hacen más habitable, menos angustioso, y muchos entienden que no vale quedarse en silencio. O no intentarlo porque sean luchas perdidas. O encogerse de hombros y resignarse a que bueno, las cosas son así, mala suerte, los malos ganan. Keep on rockin' in the free world, seguí rockeando en el mundo libre, pidió también Neil Young en 1989. En eso sigue. No importa la plataforma.</t>
   </si>
   <si>
     <t>Eduardo Fabregat</t>
@@ -2729,6 +7048,36 @@
     <t>https://www.pagina12.com.ar/397995-todos-los-detalles-del-viaje-de-alberto-fernandez-a-china</t>
   </si>
   <si>
+    <t xml:space="preserve">Título: Todos los detalles del viaje de Alberto Fernández a China
+Chapeau: Una visita clave para el futuro del país
+Subtítulo: El Gobierno tratará de activar una parte del swap de monedas si se complica el acuerdo con el FMI. Hay una larga lista de inversiones en infraestructura.
+Editoria: Cash
+Tags: China, Alberto Fernández, FMI, Swap, printed-edition, alberto-fernandez
+URL: https://www.pagina12.com.ar/397995-todos-los-detalles-del-viaje-de-alberto-fernandez-a-china/
+Notícia completa (21 blocos):
+Aunque las restricciones pandémicas le quitarán la pompa de otras giras presidenciales, el viaje de Alberto Fernández a China será clave para el futuro de Argentina. En 2004, cuando Néstor Kirchner visitó China con una inusual y visionaria comitiva de 350 personas entre ministros, gobernadores y empresarios, hubo un salto de calidad en la relación bilateral, que Cristina Fernández de Kirchner llevó a Asociación Estratégica Integral.
+Muchos presidentes ya habían ido, incluso el dictador Videla. A Alfonsín lo recibió Deng Xiaoping. Fueron Menem y De la Rúa. Pero el kirchnerismo tuvo en China un socio que buscó a la Argentina con interés nacional estratégico. El presidente Fernández era entonces jefe de Gabinete y ahora quiere retomar la senda, que con Macri, pese a sus muchas citas con Xi Jinping y a los mercados que logró abrir su embajador Diego Guelar, fue zigzagueante por taras ideológicas en la Casa Rosada, sobre todo en inversiones estratégicas, que se intentaron voltear.
+Fernández va a Beijing en una visita demorada por la pandemia, para asistir a los Juegos Olímpicos de Invierno, boicoteados por Estados Unidos y aliados, y para celebrar 50 años de lazos bilaterales con la República Popular China. Va además como presidente temporal de la CELAC, interlocutora de China en la región. Y un punto alto de la gira será la firma del ingreso formal a la Iniciativa La Franja y la Ruta, un megaproyecto de conectividad global con diversas ramificaciones, según confirmó a Cash el embajador Sabino Vaca Narvaja.
+Tras una escala en Moscú para encontrarse con Vladimir Putin, con quien hablaría de inversiones y cooperación sanitaria (el rol de la vacuna Sputnik fue vital en detener la pandemia en Argentina, como el de la china Sinopharm), Fernández volará sobre la Gran Muralla China para arribar al aeropuerto pekinés y alojarse en formato burbuja sanitaria con su corta delegación en el hotel Yanqi, lo cual no es una concesión a Joe Biden: el hotel se llama así porque lo bordea el lago homónimo. Por el contexto sanitario, solo la capital será su destino, para otra vez quedarán Shanghai, corazón económico chino, u otra ciudad.
+[H2] Las inversiones chinas en Argentina
+Hace dos años que se preparan proyectos para relanzar los lazos con China. En diciembre pasado, el canciller, Santiago Cafiero, recibió al embajador chino Zou Xiaoli y le entregó una nota, adelantada por la revista “DangDai”, donde figuran 16 obras que Argentina quiere priorizar. Hay cuatro para rehabilitar trenes del Belgrano Cargas, San Martín, Roca y una modernización integral; una de vivienda; dos viales (como las conexiones físicas vía los puentes Chaco–Corrientes y Santa Fe–Paraná); una de acueductos y plantas de tratamiento; una de gasoductos y siete de energía.
+Este último sector es clave. Incluye la central nuclear IV con la tecnología Hualong y sería la mayor inversión china en el país, con transferencia de tecnología, por más de 8 mil millones de dólares, lo que duplica la que hasta ahora era la más importante, las represas Kirchner y Cepernic en Santa Cruz.
+Sobre estas últimas, hace pocos días Vaca Narvaja logró con Gezhouba, la estatal china a cargo, asociada a Electroingeniería, una adenda financiera que actualizó contratos y destrabó las obras. Fue una muestra de confianza de China, pues Argentina aún no firmó la renegociación con el Fondo Monetario Internacional, lo que hace que potenciales inversores estén a la expectativa de cómo quedará la capacidad de pago argentina y su nuevo perfil para tomar deuda (intereses, prima de riesgo, costo de los seguros y reaseguros). Acuerdos así dan pie también a especulaciones sobre mayores acercamientos financieros a China, o a Rusia, si con el FMI se empantana.
+También se firmará la ampliación del parque solar Cauchari de Jujuy, el mayor en su tipo en Latinoamérica. Lo ejecuta Power China. Y otra novedad es que la Secretaría de Energía de la Nación y el grupo CET avanzarán en el contrato para mejorar la red eléctrica del Área Metropolitana de Buenos Aires, que involucra en esta primera etapa 1100 millones de dólares. Se trata de una nueva Estación Transformadora y más de 500 km de tendido eléctrico de alta y extra alta tensión, la mayor de este tipo en el AMBA en 30 años. China Electric Power Equipment and Technology (CET) es parte del grupo estatal chino China State Grid Corp. of China (SGCC), un gigante presente ya en 40 países de Asia, África, Sudamérica, Europa y Medio Oriente.
+Para cerrar el capítulo energético, las carpetas que lleva Fernández para negociar con Xi son otras obras de trasmisión y distribución eléctrica, la hidroeléctrica “Potrero del Clavillo – El Naranjal” (Tucumán—Catamarca), el parque eólico/solar “Cerro Arauco”, en La Rioja, y obras de energías renovables.
+[H2] El swap de monedas. además del FMI
+Según pudo saber Cash, los bancos centrales de Argentina y China preparan, en el marco de la gira, una activación del swap de monedas vigente por el cual, prácticamente sin pagar intereses, China podría ayudar a mejorar el nivel de reservas disponibles del BCRA, al margen del principio de acuerdo anunciado el pasado viernes con el FMI.
+“Es mejor eso que ensanchar el swap y generar dependencia”, dicen en el Gobierno. Desde los gobiernos kirchneristas y aun el macrista para acá, Argentina y China han tenido convenios de intercambio de monedas. Hoy equivalen a 18 mil millones, casi la mitad de todas las reservas argentinas. Si se ejecutan, o sea si los yuanes se cambian a dólares y se utilizan, devienen en un crédito por el cual el Banco Popular de China cobra intereses, se cree que en torno a 7 por ciento. El acuerdo ahora sería que China daría un permiso especial de cesión de un porcentaje de esos yuanes prácticamente sin intereses, para ayudar a la Argentina en esta coyuntura.
+[H2] Minería y telecomunicaciones
+Se realizará un Foro Virtual Empresario con anuncios sobre minería (en especial litio), transferencia de tecnología desde Argentina a China a través del INVAP con la venta de reactores para radioisótopos medicinales, autos eléctricos (Chery anunciaría una fábrica, acaso en Santa Fe), educación, cultura, defensa, promoción del fútbol, turismo y agronegocios.
+El embajador Vaca Narvaja quiere que la visita sirva para empujar el nuevo consulado que planea tener en el centro geográfico de China, la pujante ciudad de Chengdu. La agenda será acotada: solo dos días para que Fernández y sus pocos acompañantes vean a Xi en un banquete, asistan a los JJOO y visiten a la delegación deportiva argentina, al canciller Wang Yi y a otros funcionarios, echen un vistazo a la Ciudad Prohibida y la Gran Muralla si da el tiempo y el presidente reciba un honoris causa en la prestigiosa Universidad de Tsinghua.
+Respecto de la tecnología de telecomunicaciones 5G, no habrá grandes anuncios. El negocio no es entre Estados sino entre cableoperadores. Este año debería licitarse el espectro argentino y Huawei, la firma perseguida por Estados Unidos, va a competir. Ya pisa fuerte en Brasil, Chile y Uruguay con 5G, para citar mercados cercanos con gobiernos nada “antiestadounidenses”.
+“Las visitas presidenciales son propicias para cristalizar el trabajo realizado y delinear las principales actividades de los próximos años. Habrá anuncios económicos y marcarán la agenda inmediata futura”, dijo Luciano Tanto Clément, cónsul de Shanghai.
+Los empresarios del sector son optimistas. Para Ernesto Fernández Taboada, director del Consejo Argentino Chino, “será un viaje positivo, afianza amistad, negocios e inversiones. Hace muy poco viajó el canciller Cafiero a Estados Unidos. O sea, refleja un nuevo mundo multipolar. En rigor, Occidente no invierte aquí hace tiempo, como sí hacen Rusia, China o aun India. ¿Por qué no visitarlos? Hay quienes se oponen a China. América Latina está teniendo buenos lazos con China por una relación complementaria muy interesante. Ahora bien, no cabe esperar masivas inversiones, está pendiente el arreglo con el FMI, del que China es un socio fuerte. No acordar con el FMI es no acordar con China. Sus empresas esperan eso para invertir. Y ahí sería muy importante el rol de bancos chinos como el EximBank o el de Desarrollo, fondean hasta el 85 por ciento de cada obra”.
+A su vez, el bodeguero Antonio González, del Capítulo China de la Cámara del Asia y asiduo visitante a las ferias chinas donde Argentina promociona sus vinos, dijo que “Fernández será un invitado especial del gobierno chino a los JJOO, y eso va a implicar seguramente un relanzamiento de la cooperación comercial chino argentina dentro de un marco de reciprocidad y beneficio mutuo”.
+*Director periodístico de DangDai y profesor de las especializaciones sobre China en la UNLP y la UNDef.</t>
+  </si>
+  <si>
     <t>Néstor Restivo*</t>
   </si>
   <si>
@@ -2741,7 +7090,18 @@
     <t>https://www.pagina12.com.ar/396913-tomatazo-contra-la-especulacion-con-los-precios-de-los-alime</t>
   </si>
   <si>
-    <t>2022-01-22T03:01:00Z</t>
+    <t xml:space="preserve">Título: Tomatazo contra la especulación con los precios de los alimentos
+Chapeau: La UTT vende tomates a 120 pesos el kilo
+Subtítulo: La conducción de la Unión de Trabajadores y Trabajadoras de la Tierra (UTT) realiza un "tomatazo agroecológico", una actividad en la cual sus militantes venden el kilo de tomates a 120 pesos "con e
+Editoria: El País
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/396913-tomatazo-contra-la-especulacion-con-los-precios-de-los-alime/
+Notícia completa (5 blocos):
+La conducción de la Unión de Trabajadores y Trabajadoras de la Tierra (UTT) realiza un "tomatazo agroecológico", una actividad en la cual sus militantes venden el kilo de tomates a 120 pesos "con el firme objetivo de enfrentar la actual especulación con los valores de los alimentos", señalaron los voceros de la organización que representa a pequeños productores agropecuarios.
+El tomatazo se desarrolla viernes y sábado en distintos locales que la UTT tiene tanto en CABA como en distintos puntos de la provincia de Buenos Aires --Monte Grande, La Plata, Mercado y Mayorista Agroecológico de Avellaneda y San Vicente, entre otros--. Voceros de la UTT enumeraron además que en CABA estarán abiertos al público los almacenes de la entidad, ubicados en los barrios de Almagro, en la avenida Díaz Vélez 3761, de 9 a 19 y en el barrio porteño de Devoto, en Habana 3277, de 9 a 20.
+"Con estas acciones desde la UTT estamos decididos a frenar la especulación con los alimentos", explicó Daniela Carrizo, vocera de la organización.
+El kilo de tomates superó los 400 pesos en comercios de CABA y el Gran Buenos Aires. Los frutos que vende la UTT provienen de la provincia de Mendoza y del cordón hortícola de La Plata y van directo a los Almacenes de la entidad, para "garantizar un precio justo y una alimentación sana para nuestro pueblo", sostuvo Carrizo.
+"Mientras el país atraviesa una de las peores olas de calor de su historia, provocada por el impacto destructivo de los agronegocios y el consecuente cambio climático en nuestros ecosistemas, la producción de tomates se vio gravemente afectada en todo el territorio nacional", dijo. "Los mercados se aprovechan de esta situación para especular con el precio del tomate, llegando a cobrarlo hasta 500 pesos el kilo en algunos establecimientos. Es por esto que los trabajadores de latierra nos organizamos para garantizar un alimento sano y a precios justos en la mesa de todos los vecinos".</t>
   </si>
   <si>
     <t>Lanzan una campaña "en defensa del agua para la vida"</t>
@@ -2753,7 +7113,23 @@
     <t>https://www.pagina12.com.ar/395765-lanzan-una-campana-en-defensa-del-agua-para-la-vida</t>
   </si>
   <si>
-    <t>2022-01-17T03:01:00Z</t>
+    <t xml:space="preserve">Título: Lanzan una campaña "en defensa del agua para la vida"
+Chapeau: Es a lo largo y ancho del país, impulsada por organizaciones sociales y ambientalistas
+Subtítulo: El lago Colhue Huapi abarcaba 53.000 hectáreas en Sarmiento (Chubut). En los '90 comenzó un proceso de bajante vinculado a la accionar de grandes estancias y petroleras.
+Editoria: Sociedad
+Tags: printed-edition, diario
+URL: https://www.pagina12.com.ar/395765-lanzan-una-campana-en-defensa-del-agua-para-la-vida/
+Notícia completa (10 blocos):
+El lago Colhue Huapi abarcaba 53.000 hectáreas en Sarmiento (Chubut). En los '90 comenzó un proceso de bajante vinculado a la accionar de grandes estancias y petroleras. En la década del 2000 se secó por completo. A pocos kilómetros se ubica el lago Musters, que experimenta una bajante histórica y corre riesgo de seguir los pasos del Colhue Huapi. A 3000 kilómetros de allí, en Salta, las comunidades wichí exigen pozos de agua para no tener que beber de charcos contaminados, antesala de enfermedades y muertes. "Campaña Plurinacional en Defensa del Agua para la Vida", es el nombre de la iniciativa impulsada por decenas de organizaciones sociales y asambleas, que remarcan el derecho humano al agua, denuncian el extractivismo y proponen la democratización del acceso a los bienes comunes.
+"El agua vale más que oro", nació en 2002 en Chubut, cuando comenzaba la lucha de Esquel contra la megaminería. La frase ya es bandera de lucha en Argentina y América Latina. En el otro extremo, desde los ideológico y también geográfico, en 2020 fue noticia que el agua comenzaba a cotizar en la bolsa de especulación de Nueva York.
+"El agua es vida. Todos los seres vivos dependemos de ella. La falta de agua potable para tantas personas en este país es una deuda socio-ecológica que necesita ser saldada en lo inmediato", destaca el documento fundacional de la Campaña Plurinacional en Defensa del Agua para la Vida, un espacio donde participan más de cincuenta organizaciones, asambleas socioambientales, cátedras de soberanía alimentaria y colectivos diversos (desde artísticos hasta científicos).
+La campaña tiene diversos ejes. Se comenzó por la difusión (vía redes sociales desde la dirección twitter.com/CampDefensaAgua ) y con una completa serie de conversatorios virtuales ("Acceso a la tierra y al agua, claves para la reconfiguración demográfica", "Normativas en defensa del agua", "Agua para la deuda externa o para la vida", fueron algunos de los temas). "El agua es un bien común y un derecho. Queremos protegerla, cuidarla; evitar el uso indiscriminado, el desperdicio, la contaminación. Tenemos que avanzar hacia una conciencia colectiva de cuidado y acompañarla de una legislación que la defina como elemento vital a preservar para la continuidad de la vida", remarcan la Asamblea Jáchal No Se Toca, el Servicio de Paz y Justicia, las Madres de Ituzaingó Anexo, la ONG Conciencia Solidaria, la Multisectorial Paren de Fumigarnos (Santa Fe), el Espacio Intercuencas, la Coordinadora Basta es Basta por una Vida sin Agrotóxicos, la Cátedra Libre de Soberanía Alimentaria de Nutrición (UBA) y la Federación de Profesionales de la Salud (Fesprosa), entre otras organizaciones.
+El viernes 7 de enero, comunidades mapuches junto con vecinos autoconvocados cortaron la ruta 7 (Autovía Norte) en la meseta de la capital neuquina en reclamo de agua. "En una zona que está siendo devastada por las petroleras y el fracking, que utilizan diariamente millones de litros de agua para sus explotaciones, le falta el agua a la gente para el consumo, para el riego y la vida general. Ya no hay excusas, por eso el hartazgo que hoy se manifiesta en este corte", explicó la Confederación Mapuche de Neuquén.
+La defensa del agua unifica casi las luchas contra el extractivismo y sus consecuencias: megaminería, forestales, agronegocio, represas, petróleo, litio, humedales, energía nuclear, bajante de ríos, extractivismo urbano y megaciudades.
+Mariano Sánchez Toranzo es uno de los voceros de la Campaña. Remarca que uno de los objetivos es profundizar la democracia. "Es imprescindible salir de la democracia delegativa, que no resuelve los problemas ni de los pueblos ni de los territorios. Es necesario pasar a una democracia más participativa. Apostamos a todo tipo de consulta e iniciativa popular, instrumento de democracia directa que hoy podríamos utilizar y desde los sectores de poder no desean que utilicemos", afirma Sánchez Toranzo.
+Además de Esquel en 2003, hubo otras votaciones populares contra el extractivismo: en 1996, la población de Misiones le dijo no a la hidroeléctrica Corpus (entre Argentina y Paraguay). En 2012 la población de Loncopué (Neuquén) votó y el 82 por ciento rechazó un proyecto minero impulsado por el gobierno provincial y una empresa china. En 2014, otra vez Misiones, 120.000 personas se autoconvocaron a votar y el 96 por ciento dijo "no" a la represas de Garabí (entre Argentina y Brasil).
+Hubo numerosos intentos de votaciones locales contra el extractivismo y por la autodetermianción. Quizá los dos más conocidos sean la localidad cordobesa de Malvinas Argentinas (contra la instalación de la empresa Monsanto) y Andalgalá (en defensa del agua y contra la megaminería). En ambos casos, gobiernos provinciales y nacional se opusieron al acto democrático.
+La Campaña Plurinacional en Defensa del Agua trabaja en la construcción popular de un proyecto de ley de cuidado del agua, que prohíba las actividades que la contaminan y que contemple la gestión pública del agua. Buscan llegar con un respaldo de 500.000 firmas. "Entendemos que es un proceso de construcción de abajo hacia arriba, y que pueda tomar la impronta que tuvo y tiene el movimiento de mujeres, una marea verde que los políticos no puedan ignorar", grafica Sánchez Toranzo. Naciones Unidas (ONU) reconoció en julio de 2010 (en su Asamblea General) explícitamente “el derecho humano al agua”. Reafirmó que el agua potable es esencial para la realización de todos los derechos humanos.</t>
   </si>
   <si>
     <t>Alberto Fernández viajará a Rusia y a China el mes próximo</t>
@@ -2765,7 +7141,33 @@
     <t>https://www.pagina12.com.ar/395467-alberto-fernandez-viajara-a-rusia-y-a-china-el-mes-proximo</t>
   </si>
   <si>
-    <t>2022-01-14T23:34:43Z</t>
+    <t xml:space="preserve">Título: Alberto Fernández viajará a Rusia y a China el mes próximo
+Chapeau: La agenda internacional del Presidente
+Subtítulo: La portavoz presidencial, Gabriela Cerruti, confirmó la gira del presidente Alberto Fernández por Rusia y China, los próximos 3 y 4 de febrero.
+Editoria: El País
+Tags: Vladimir Putin, Xi Jinping, Alberto Fernández, vladimir-putin, xi-jinping, alberto-fernandez, diario
+URL: https://www.pagina12.com.ar/395467-alberto-fernandez-viajara-a-rusia-y-a-china-el-mes-proximo/
+Notícia completa (20 blocos):
+La portavoz presidencial, Gabriela Cerruti, confirmó la gira del presidente Alberto Fernández por Rusia y China, los próximos 3 y 4 de febrero.
+El jefe de Estado viajará primero a Rusia, donde mantendrá una reunión con su par ruso, Vladimir Putin, y 48 horas después viajará a China para reunirse con el mandatario del gigante asiático, Xi Jinping, y participar de la inauguración de los Juegos Olímpicos de Invierno en ese país.
+El encuentro entre Fernández y Putin será el primero desde la asunción del presidente argentino, ya que pandemia mediante solo mantuvieron una conversación telefónica en noviembre pasado, cuando manifestaron su predisposición a encontrarse personalmente dependiendo de la situación epidemiológica.
+En tanto, la visita a China se dará en el marco del 50 aniversario de relaciones diplomáticas con el 'Gigante asiático', iniciadas el 19 de febrero de 1972, y en medio de una marcada tensión entre el gobierno chino y la Casa Blanca, luego de que el presidente de Estados Unidos, Joe Binden, declarara el boicot a los Juegos Olímpicos de Invierno.
+[H2] La agenda en Moscú
+En Rusia, Fernández mantendrá la postergada reunión bilateral con Putin para repasar "la colaboración en el tema de vacunas, inversiones, ciencia y en otros temas de interés común", según detalló Cerruti.
+El 7 de noviembre pasado, ambos mandatario hablaron durante media hora para ponerse al día respecto de la relación bilateral entre ambos países.
+En ese encuentro telefónico, el presidente argentino valoró "la cooperación entre ambas naciones a la hora de enfrentar el desafío mundial" que implica la pandemia de Covid-19.
+La Argentina fue uno de los primeros países en autorizar la aplicación de la vacuna Sputnik-V, con la cual comenzó la campaña de vacunación en el país.
+De hecho, el 4 de junio pasado, Fernández y Putin habían compartido una videoconferencia con motivo del inicio de la producción en la Argentina de la vacuna Sputnik V.
+Se espera que en el encuentro del 3 de febrero, ambos mandatarios avancen en "la asociación estratégica ruso-argentina y la cooperación práctica en varios campos", según un comunicado de prensa del Kremlin.
+Fernández y Putin esperaban encontrarse en la Cumbre de Líderes del G20 en Roma, pero el mandatario ruso informó 11 días antes de la reunión que participaría a través de videoconferencia.
+En aquella gira, entre el 30 de octubre y 2 de noviembre, el jefe de Estado participó también de la Conferencia de las Naciones Unidas sobre el Cambio Climático (COP) 26 en Glasgow.
+Aunque el frustrado encuentro se saldó en parte con la charla telefónica de noviembre pasado, el canciller Santiago Cafiero logró coordinar con su par ruso, Serguéi Lavrov, una visita de representantes del Fondo Ruso de Inversión Directa --que financió la producción de la Sputnik-V-- y ejecutivos de empresas y representantes de bancos rusos. Encuentro que se concretó el 7 de diciembre último en Buenos Aires.
+[H2] La agenda en el gigante asiático
+En aquella gira europea para participar del G20 y la COP26, el canciller Cafiero confirmó el viaje de Fernández a China "para acentuar el comercio". "Tenemos una comisión de tratamiento binacional respecto a temas comerciales y uno de los puntos fue que vuelva a trabajar rápidamente", había señalado el ministro de Relaciones Exteriores.
+Cafiero explicó que en la agenda de ambos países está la idea de avanzar en temas como la economía del conocimiento, acuerdos comerciales, y en robustecer la presencia de la Argentina en China.
+China se alterna con Brasil como principal destino de las exportaciones del país y ha incrementado marcadamente su presencia en inversiones en agronegocios, energía e infraestructura en la Argentina desde el acuerdo de asociación estratégica firmado por en la gestión de Néstor Kirchner, cuando Fernández era jefe de Gabinete.
+El 4 de noviembre, dos días después de la gira por Europa, Fernández participó de la inauguración de la cuarta edición de la China International Import Expo (CIIE) a través de mensaje grabado desde Casa Rosada.
+El Presidente convocó, en eses entonces, a realizar "mayores esfuerzos para lograr un comercio más abierto, justo y equilibrado", y consideró "imprescindible abordar el comercio internacional con la perspectiva de 'ganar-ganar'", como calificó el comercio bilateral entre ambos países.</t>
   </si>
   <si>
     <t>Hotelería sindical para disfrutar el carnaval</t>
@@ -2777,7 +7179,20 @@
     <t>https://www.pagina12.com.ar/394577-hoteleria-sindical-para-disfrutar-el-carnaval</t>
   </si>
   <si>
-    <t>2022-01-11T03:01:00Z</t>
+    <t xml:space="preserve">Título: Hotelería sindical para disfrutar el carnaval
+Chapeau: Se inauguró el Hotel O2 Gualeguaychú, del Suterh
+Subtítulo: La puesta en valor de un histórico hotel, refaccionado a nuevo por el Sindicato Unico de Trabajadores de Edificios de Renta y Horizontal, suma 167 plazas a la oferta de alojamiento en el formato de “hotelería clásica”.
+Editoria: Sociedad
+Tags: SUTERH, Gualeguaychú, printed-edition, gualeguaychu, diario
+URL: https://www.pagina12.com.ar/394577-hoteleria-sindical-para-disfrutar-el-carnaval/
+Notícia completa (7 blocos):
+En el inicio de la temporada de carnaval en Gualeguaychú, donde el ritual se celebra con una nueva competencia de comparsas en su famoso corsodromo --cerrado durante 2020 por la pandemia--, una nueva propuesta hotelera despierta expectativas en la ciudad. La puesta en valor de un histórico hotel, refaccionado a nuevo por el Sindicato Unico de Trabajadores de Edificios de Renta y Horizontal (Suterh), bautizado como: Hotel O2 Gualeguaychú, suma 167 plazas a la oferta de alojamiento en el formato de “hotelería clásica”, señala Javier Cubillas, su gerente operativo, a Página/12.
+Gualeguaychú es una ciudad con ribetes mágicos. Hay más museos que iglesias. Muchas santerías. Y muchos comercios refieren al rito del carnaval: el Rey Goma por caso, que repara los neumáticos de las diversas oleadas de turistas, o el Rey Pollo, donde preparan los mejores pollos a la parrilla de la costanera. Recostada sobre el río Gualeguaychú, y bajo la ensoñación del verde permanente que la envuelve, con fuentes de aguas termales y parques que conservan árboles nativos, creció cuando el agronegocio se instaló como opción productiva: soja, trigo, maíz, un poco de girasol y sorgo, desplazaron a la ganadería. En esa trama, a partir de los ‘90 se subió al podio de las ciudades donde el festejo del carnaval se convirtió en un rito apasionante. Desplazó a Corrientes, y generó un desarrollo económico más industrial que artesanal: cada comparsa pertenece a un club social y genera su propia dinámica estética y productiva.
+Allí, y en pleno centro histórico y comercial, a seis cuadras de la costanera y a quince del corsodromo --donde este sábado volvieron a brillar las comparsas del “Carnaval del país”--, se inauguró el primer hotel sindical de la ciudad: el Hotel O2 Gualeguaychú. Fue el lunes junto a la temporada de carnaval 2022 que se extenderá todo enero y hasta el último fin de semana de febrero. “El finde largo de carnaval”, detallan los empleados del hotel, quienes reciben a los primeros huéspedes con “emoción y orgullo”. Varios, entre ellos, como el conserje Emanuel Bur, ya trabajaba en el hotel, que funcionó desde los años '70: el hotel Embajador. Emblemático en la ciudad por ser la primera construcción de nueve pisos en una urbanización de casas bajas, combina fachadas antiguas con otras típicas de los ‘60, cuando la modernidad llegó a la zona. Hoy no pueden construirse más de cuatro pisos --explica Leonardo Posadas, de la Secretaría de Turismo municipal--, en zona céntrica. Esto asegura vista con horizonte de largo alcance.
+Desde algunas ventanas del edificio de 75 habitaciones, con seis pisos refaccionados “a nuevo”, en decó minimalista y espacios amplios, puede verse la vegetación costera, el campanario de la iglesia, las calles arboladas. “Lo más abierto posible a la multiplicidad de opciones que ofrece la ciudad”, se explaya Cubillas. “El Embajador cerró en pandemia”, explica. Luego lo adquirió el Grupo Octubre y lo reacondicionó. La infraestructura relacionada con el servicio está a punto. En la mañana de este lunes recibió a sus primeros huéspedes: Juan Paulo Agüero y Liliana, Marcelo Vespa y Susana. Los dos matrimonios llegaron desde Buenos Aires, en coche. Son trabajadores de edificios. Y fueron recibidos con honores: regalos, aplauso y fotos. “¡Me sorprendieron!”, cuenta Juan Paulo, entre risas. En menos de tres horas hicieron el viaje. “Y nos recibieron como reyes, fue emocionante, como cuando uno llega a una casa de amigos”, agrega Liliana. “Siento orgullo además por estar acompañando este proceso --añade Juan Paulo-- porque es un logro de nuestro gremio”.
+Para Marcelo y Susana, que son de Fray Bentos, Uruguay, esto es “casi una luna de miel”. En marzo cumplen 36 años de casados. Con “30 años de encargado”, Marcelo agradece que su hija “estudie hotelería en la UMET”, y Susana cuenta: “mis tres hijos los tuve en sanatorios del sindicato”. “Luchando siempre --dice Marcelo-- sacando la cosa para delante, siempre”, así define su filosofía de vida. Se miran con Susana, sonríen, y planifican la tarde en el balneario. Están contentos.
+Poco antes del mediodía llega Andrea Flores, y busca opciones recreativas: le gustan las termas y los museos. “Somos gente de trabajo, es algo que valoro, me lo enseñó mi madre, que no sabía leer ni escribir, pero plantaba verduras y criaba animales y hacía trueque, iba en burro o en caballo al pueblo, en Jujuy, cerca de Uquía, y crio siete hijos sola, yo era la más chica --recuerda Andrea--, y hablaba mucho con ella. Siempre me gustó estudiar, por eso valoro la universidad del sindicato, las radios, son cosas para crecer, lo mismo que el esparcimiento”. Leonardo Maldonado llegó a mediodía y valora el esparcimiento: “lo rescato como trabajador y como afiliado, es un orgullo”, puntualiza. Leonardo vino con sus hijos. Y completa el cuadro del hotel familiar.
+“Vamos a focalizar en la capacitación interna para lograr un perfil único en este tipo de hoteles --adelanta Cubillas--, esta semana iniciamos la capacitación en Ley Micaela, y haremos lo mismo con discapacidad y diversidad”. Esta es la ciudad donde se celebra “el carnaval del país”, acierta Cubillas. "Quizá uno de los eventos donde más se demuestra lo que significa la identidad de género y la diversidad sexual”, sostiene. No es menor la perspectiva que se busca desde la gestión hotelera donde el desarrollo económico, se acompaña por una mirada cultural, inclusiva y solidaria.</t>
   </si>
   <si>
     <t>La vieja deuda que pasa el tiempo y no se salda</t>
@@ -2789,7 +7204,31 @@
     <t>https://www.pagina12.com.ar/392986-la-vieja-deuda-que-pasa-el-tiempo-y-no-se-salda</t>
   </si>
   <si>
-    <t>2022-01-03T03:01:19Z</t>
+    <t xml:space="preserve">Título: La vieja deuda que pasa el tiempo y no se salda
+Chapeau: Debate sobre la ley de relevamiento territorial indígena
+Subtítulo: La UNR publicó Salir de la emergencia, sobre la vulneración de derechos de los pueblos originarios a partir de la negación de una normativa que afectaría intereses económicos.
+Editoria: Rosario|12
+Tags: printed-edition
+URL: https://www.pagina12.com.ar/392986-la-vieja-deuda-que-pasa-el-tiempo-y-no-se-salda/
+Notícia completa (18 blocos):
+La cuarta prórroga a la Ley de Emergencia de la Propiedad Comunitaria reavivó el debate sobre una vieja deuda que el Estado nacional mantiene con los habitantes originales de este suelo, los pueblos originarios. Y en ese marco, la Universidad Nacional de Rosario editó un libro que pone de relieve estos asuntos nunca resueltos y que en lo cotidiano se traducen en la violación de los derechos humanos de esa parte de la población. Una problemática que involucra a la provincia de Santa Fe, y a Rosario en particular, donde las comunidades indígenas reanudaron este año la movilización en reclamo de legislación definitiva que las legitime en la ocupación y uso de sus tierras ancestrales ya como dueños titulares. En esta ciudad no hay tierras comunitarias, y la población qom y mocoví –también hay wichi, pilagá y mapuche, pero muy poca– que empezó a radicarse desde hace 35 años enfrenta un problema nada sencillo con sus viviendas, ocupadas a modo individual y no con sentido comunitario, como indican sus culturas. Se precisa una ley que reconozca la forma de propiedad comunitaria.
+El reclamo histórico de las comunidades originarias no tiene cabida entre las prioridades de las agendas parlamentarias, ni nacional ni provinciales. Data de 2006 la ley 26160, de emergencia de la propiedad comunitaria, y que obliga al Estado –esto es el Instituto Nacional de Asuntos Indígenas (INAI)– a realizar un relevamiento territorial de cada comunidad en coordinación con los gobiernos locales. Pero esta ley es solo la antesala de lo que debería ser una legislación definitiva que consolide a los pueblos originarios en sus tierras, a salvo de los intereses económicos que los mismos estados dan calce, al autorizar desmontes, expropiaciones, explotaciones agrícolas y ganaderas.
+Desde entonces esa ley se viene prorrogando. El Presidente Alberto Fernández tuvo que hacerlo el 18 de noviembre a través de un Decreto de Necesidad y Urgencia. Carlos Salamanca es investigador del Conicet y director del Programa Espacios, Políticas, Sociedades (Centro de Estudios Interdisciplinarios, Universidad Nacional de Rosario). En su prólogo del libro Salir de la emergencia (CEI - UNR) puso de relieve que 15 años después de sancionada la ley, todavía falta relevar más de la mitad del total de comunidades indígenas. Y mientras tanto, "sobre muchos territorios se ciernen amenazas de desalojos y expulsiones", bajo la presión de un modelo extractivista que prioriza el agronegocio y el monocultivo.
+El libro recopila una serie de conversatorios que se desarrollaron en la víspera del DNU presidencial de prórroga de la ley, entre setiembre y noviembre pasado, con personas involucradas como líderes indígenas, ambientalistas, abogados y antropólogos. Como caso testigo está el relevamiento que el INAI realizó en la comunidad Mbya Guaraní de Alecrín, en Misiones. Una experiencia que se hizo desde el Estado, y desde el Estado mismo a su vez se autorizó continuar con la deforestación en la zona. "Eso ocurre paradojalmente, el Estado hace una cosa con una mano y lo opuesto con la otra", señaló Salamanca a Rosario/12.
+Desde la sanción de la Ley en 2006 se ha relevado sólo el 42% de las comunidades. Es pertinente considerar además que cuando se sancionó la legislación había menos de mil comunidades registradas y que hoy son 1.756, de las cuales 703 ya han sido relevadas, con resolución administrativa. Santa Fe es una de las pocas provincias junto con Salta, Chaco, Misiones y Jujuy, que mantiene un convenio con el INAI para avanzar en el relevamiento de comunidades.
+El debate apunta superar esta ley 26160 que impide los desalojos y reconoce la posesión originaria de tierras, pero falta otra legislación con la que el Estado reconozca de manera definitiva los territorios comunitarios para esta población, esto es, la necesidad de una Ley de Propiedad Comunitaria Indígena que garantice la propiedad y titularidad, no solo la posesión.
+"Se desconoce que, como consecuencia de una práctica estructural y culturalmente arraigada de despojo, muchos indígenas en el país habitan hoy en pequeñas porciones de tierra de lo que fueron sus territorios tradicionales. Permanece una impronta etnocéntrica que invierte la carga de la prueba en la misma ley. Las comunidades indígenas, aun con la injusticia socioespacial que viven, deben demostrar que la posesión que ejercen de sus tierras es legítima", observó Salamanca en el prólogo del libro del que participaron académicos, activistas , indígenas y no indígenas de distintas organizaciones.
+La Constitución de 1994 incluyó el reconocimiento de la propiedad comunitaria indígena, estatuto clave para revertir la relación traumática que campeó siempre entre Estado y pueblos originarios. A pesar del reconocimiento normativo, y a pesar del tiempo transcurrido, el goce efectivo de los derechos territoriales sigue siendo una utopía para este sector de la población.
+[H2] El caso Rosario
+En Rosario, la Dirección de Pueblos Originarios municipal realizó un censo en 2014, y luego le hizo algunas actualizaciones. En ese entonces, contaron 6.521 personas que se declararon pertenecientes a pueblos originarios. La titular de esa repartición, Marcela Valdata, estima que esa población creció quizás un tercio y hoy contenga a unos 8500 miembros, sin contar la comunidad de paraguayos guaraníes, fuera de este registro.
+Aquí la lucha no es por tierras comunitarias porque no las hay como tales. Pero aunque la relación socio espacial es diferente, el sentido de comunidad persiste como identidad. Esta población sí se debe un reconocimiento del Estado al carácter comunitario de las viviendas que les han ido asignando desde que empezaron a migrar masivamente, a mediados de los '80, y que en muchos casos han terminado de pagar. "Esas tierras no están planificadas como comunitarias porque tienen viviendas de uso individual", explicó Valdata.
+Al poseer viviendas individuales no comunitarias hubo quienes las vendieron –muchas veces, de palabra nomás– a personas ajenas a la comunidad indígena, y allí la situación se complejiza y depara una puerta de ingreso del narcomenudeo u otras economías delictivas al barrio.
+El incremento poblacional superó las previsiones. Las dificultades llegan a extremos como el de la violencia institucional. Dentro de una veintena de casos de represión estatal contra el reclamo indígena en diversas provincias, se cuenta el desalojo violento que la policía hizo el 12 de junio de 2020 sobre un grupo de familias Qom y Moqoit (tobas y mocovíes) en un predio de Rouillón y Aborígenes Argentinos que pretendían ocupar para erigir allí sus viviendas y aliviar el hacinamiento que predomina en el barrio.
+La misma saturación registra el asentamiento de Travesía y Sorrento, al norte del emplazamiento de Juan José Paso y Sabin, el ex proyecto Sueños Compartidos. Quedaron 37 viviendas sin construir, y el terreno hoy está ocupado por un centenar de familias. "Durante el gobierno de Macri no hubo ningún acercamiento de Nación para solucionar el problema allí. Hicieron promesas nunca concretadas, y persisten las comunidades que hace casi 40 años que están en la ciudad y que nunca tuvieron inserción en planes habitacionales", señaló Valdata.
+Los asentamientos urbanos y periurbanos indígenas como los barrios de Travesía y Sorrento, o Los Pumitas, o de Rouillón y Maradona, registran hoy un alto grado de hacinamiento porque las familias de origen se han multiplicado, y la inmigración desde el norte continúa. Entonces, destaca "el déficit en infraestructura y saneamiento, y la ausencia de una política clara que baje para contribuir al ejercicio de los derechos territoriales", señala el documento publicado por CEI-UNR.
+A nivel local, la problemática se discute en la comisión de Tierra y Vivienda del Concejo, con la presencia del Ejecutivo y doce comunidades originarias. Mientras tanto esperan desde agosto que el INAI atienda su llamado.
+Las familias originarias se han ido dispersando, y ya no habitan solamente los tres barrios mencionados. También residen en Industrial, Bella Vista Oeste, Villa Banana, Villa Pororó, Tío Rolo y Fontanarrosa (Zona Cero). Desde el censo de 2014, hay barrios que duplicaron su población originaria en estos siete años. "Es preciso tener certeza mayor, y saber los núcleos parentales que conforman la comunidad de Rosario", señaló la titular del área municipal.
+"La consecuencia de que Rosario no tenga tierras comunitarias es el desarrollo de esta población en la marginalidad, asentamiento poco urbanizados, con problemas de acceso a servicios públicos porque se han ido extendiendo en lugares donde no es posible aún una vida digna ni saludable. Y como no hay un trabajo que apunte a considerar esas propiedades como comunitarias, es que se necesita una planificación, una ley, para que las viviendas pertenezcan para siempre a la comunidad, que sean intransferibles. No hay planificación en sentido comunitario. No hay regulación para que eso sea de la comunidad y no individual", reclamó Valdata, antropóloga de profesión.</t>
   </si>
   <si>
     <t>Luis Bastús</t>
@@ -4994,7 +9433,7 @@
         <v>401</v>
       </c>
       <c r="D91" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
@@ -5005,56 +9444,56 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>402</v>
+      </c>
+      <c r="B92" t="s">
         <v>403</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>404</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>405</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" t="s">
         <v>406</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>407</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
         <v>408</v>
       </c>
-      <c r="B93" t="s">
-        <v>11</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>409</v>
-      </c>
-      <c r="D93" t="s">
-        <v>410</v>
       </c>
       <c r="E93" t="s">
         <v>222</v>
       </c>
       <c r="F93" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>411</v>
+      </c>
+      <c r="B94" t="s">
         <v>412</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>413</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>414</v>
-      </c>
-      <c r="D94" t="s">
-        <v>415</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
@@ -5065,16 +9504,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>415</v>
+      </c>
+      <c r="B95" t="s">
         <v>416</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>417</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>418</v>
-      </c>
-      <c r="D95" t="s">
-        <v>419</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
@@ -5085,16 +9524,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>419</v>
+      </c>
+      <c r="B96" t="s">
         <v>420</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>421</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>422</v>
-      </c>
-      <c r="D96" t="s">
-        <v>423</v>
       </c>
       <c r="E96" t="s">
         <v>11</v>
@@ -5105,16 +9544,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>423</v>
+      </c>
+      <c r="B97" t="s">
         <v>424</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>425</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>426</v>
-      </c>
-      <c r="D97" t="s">
-        <v>427</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
@@ -5125,56 +9564,56 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>427</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
         <v>428</v>
       </c>
-      <c r="B98" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>429</v>
-      </c>
-      <c r="D98" t="s">
-        <v>430</v>
       </c>
       <c r="E98" t="s">
         <v>222</v>
       </c>
       <c r="F98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>431</v>
+      </c>
+      <c r="B99" t="s">
         <v>432</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>433</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>434</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" t="s">
         <v>435</v>
-      </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>436</v>
+      </c>
+      <c r="B100" t="s">
+        <v>436</v>
+      </c>
+      <c r="C100" t="s">
         <v>437</v>
       </c>
-      <c r="B100" t="s">
-        <v>437</v>
-      </c>
-      <c r="C100" t="s">
-        <v>438</v>
-      </c>
       <c r="D100" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
@@ -5185,76 +9624,76 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>438</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>439</v>
+      </c>
+      <c r="D101" t="s">
         <v>440</v>
-      </c>
-      <c r="B101" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" t="s">
-        <v>441</v>
-      </c>
-      <c r="D101" t="s">
-        <v>442</v>
       </c>
       <c r="E101" t="s">
         <v>222</v>
       </c>
       <c r="F101" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B102" t="s">
+        <v>442</v>
+      </c>
+      <c r="C102" t="s">
+        <v>443</v>
+      </c>
+      <c r="D102" t="s">
         <v>444</v>
       </c>
-      <c r="C102" t="s">
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" t="s">
         <v>445</v>
-      </c>
-      <c r="D102" t="s">
-        <v>446</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>446</v>
+      </c>
+      <c r="B103" t="s">
+        <v>447</v>
+      </c>
+      <c r="C103" t="s">
         <v>448</v>
       </c>
-      <c r="B103" t="s">
+      <c r="D103" t="s">
         <v>449</v>
-      </c>
-      <c r="C103" t="s">
-        <v>450</v>
-      </c>
-      <c r="D103" t="s">
-        <v>451</v>
       </c>
       <c r="E103" t="s">
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>451</v>
+      </c>
+      <c r="B104" t="s">
+        <v>452</v>
+      </c>
+      <c r="C104" t="s">
         <v>453</v>
       </c>
-      <c r="B104" t="s">
+      <c r="D104" t="s">
         <v>454</v>
-      </c>
-      <c r="C104" t="s">
-        <v>455</v>
-      </c>
-      <c r="D104" t="s">
-        <v>456</v>
       </c>
       <c r="E104" t="s">
         <v>187</v>
@@ -5265,16 +9704,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>455</v>
+      </c>
+      <c r="B105" t="s">
+        <v>456</v>
+      </c>
+      <c r="C105" t="s">
         <v>457</v>
       </c>
-      <c r="B105" t="s">
+      <c r="D105" t="s">
         <v>458</v>
-      </c>
-      <c r="C105" t="s">
-        <v>459</v>
-      </c>
-      <c r="D105" t="s">
-        <v>460</v>
       </c>
       <c r="E105" t="s">
         <v>187</v>
@@ -5285,16 +9724,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>459</v>
+      </c>
+      <c r="B106" t="s">
+        <v>460</v>
+      </c>
+      <c r="C106" t="s">
         <v>461</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
         <v>462</v>
-      </c>
-      <c r="C106" t="s">
-        <v>463</v>
-      </c>
-      <c r="D106" t="s">
-        <v>464</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
@@ -5305,36 +9744,36 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>463</v>
+      </c>
+      <c r="B107" t="s">
+        <v>464</v>
+      </c>
+      <c r="C107" t="s">
         <v>465</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
         <v>466</v>
       </c>
-      <c r="C107" t="s">
+      <c r="E107" t="s">
         <v>467</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>468</v>
-      </c>
-      <c r="E107" t="s">
-        <v>469</v>
-      </c>
-      <c r="F107" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>469</v>
+      </c>
+      <c r="B108" t="s">
+        <v>470</v>
+      </c>
+      <c r="C108" t="s">
         <v>471</v>
       </c>
-      <c r="B108" t="s">
+      <c r="D108" t="s">
         <v>472</v>
-      </c>
-      <c r="C108" t="s">
-        <v>473</v>
-      </c>
-      <c r="D108" t="s">
-        <v>474</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
@@ -5345,16 +9784,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>473</v>
+      </c>
+      <c r="B109" t="s">
+        <v>474</v>
+      </c>
+      <c r="C109" t="s">
         <v>475</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
         <v>476</v>
-      </c>
-      <c r="C109" t="s">
-        <v>477</v>
-      </c>
-      <c r="D109" t="s">
-        <v>478</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
@@ -5365,19 +9804,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>477</v>
+      </c>
+      <c r="B110" t="s">
+        <v>478</v>
+      </c>
+      <c r="C110" t="s">
         <v>479</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
         <v>480</v>
       </c>
-      <c r="C110" t="s">
+      <c r="E110" t="s">
         <v>481</v>
-      </c>
-      <c r="D110" t="s">
-        <v>482</v>
-      </c>
-      <c r="E110" t="s">
-        <v>483</v>
       </c>
       <c r="F110" t="s">
         <v>268</v>
@@ -5385,36 +9824,36 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>482</v>
+      </c>
+      <c r="B111" t="s">
+        <v>483</v>
+      </c>
+      <c r="C111" t="s">
         <v>484</v>
       </c>
-      <c r="B111" t="s">
+      <c r="D111" t="s">
         <v>485</v>
       </c>
-      <c r="C111" t="s">
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" t="s">
         <v>486</v>
-      </c>
-      <c r="D111" t="s">
-        <v>487</v>
-      </c>
-      <c r="E111" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>487</v>
+      </c>
+      <c r="B112" t="s">
+        <v>488</v>
+      </c>
+      <c r="C112" t="s">
         <v>489</v>
       </c>
-      <c r="B112" t="s">
+      <c r="D112" t="s">
         <v>490</v>
-      </c>
-      <c r="C112" t="s">
-        <v>491</v>
-      </c>
-      <c r="D112" t="s">
-        <v>492</v>
       </c>
       <c r="E112" t="s">
         <v>11</v>
@@ -5425,16 +9864,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>491</v>
+      </c>
+      <c r="B113" t="s">
+        <v>492</v>
+      </c>
+      <c r="C113" t="s">
         <v>493</v>
       </c>
-      <c r="B113" t="s">
+      <c r="D113" t="s">
         <v>494</v>
-      </c>
-      <c r="C113" t="s">
-        <v>495</v>
-      </c>
-      <c r="D113" t="s">
-        <v>496</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
@@ -5445,16 +9884,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>495</v>
+      </c>
+      <c r="B114" t="s">
+        <v>496</v>
+      </c>
+      <c r="C114" t="s">
         <v>497</v>
       </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>498</v>
-      </c>
-      <c r="C114" t="s">
-        <v>499</v>
-      </c>
-      <c r="D114" t="s">
-        <v>500</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
@@ -5465,16 +9904,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>499</v>
+      </c>
+      <c r="B115" t="s">
+        <v>500</v>
+      </c>
+      <c r="C115" t="s">
         <v>501</v>
       </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
         <v>502</v>
-      </c>
-      <c r="C115" t="s">
-        <v>503</v>
-      </c>
-      <c r="D115" t="s">
-        <v>504</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
@@ -5485,36 +9924,36 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>503</v>
+      </c>
+      <c r="B116" t="s">
+        <v>504</v>
+      </c>
+      <c r="C116" t="s">
         <v>505</v>
       </c>
-      <c r="B116" t="s">
+      <c r="D116" t="s">
         <v>506</v>
-      </c>
-      <c r="C116" t="s">
-        <v>507</v>
-      </c>
-      <c r="D116" t="s">
-        <v>508</v>
       </c>
       <c r="E116" t="s">
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>508</v>
+      </c>
+      <c r="B117" t="s">
+        <v>509</v>
+      </c>
+      <c r="C117" t="s">
         <v>510</v>
       </c>
-      <c r="B117" t="s">
+      <c r="D117" t="s">
         <v>511</v>
-      </c>
-      <c r="C117" t="s">
-        <v>512</v>
-      </c>
-      <c r="D117" t="s">
-        <v>513</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
@@ -5525,16 +9964,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>512</v>
+      </c>
+      <c r="B118" t="s">
+        <v>513</v>
+      </c>
+      <c r="C118" t="s">
         <v>514</v>
       </c>
-      <c r="B118" t="s">
+      <c r="D118" t="s">
         <v>515</v>
-      </c>
-      <c r="C118" t="s">
-        <v>516</v>
-      </c>
-      <c r="D118" t="s">
-        <v>517</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
@@ -5545,16 +9984,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>516</v>
+      </c>
+      <c r="B119" t="s">
+        <v>517</v>
+      </c>
+      <c r="C119" t="s">
         <v>518</v>
       </c>
-      <c r="B119" t="s">
+      <c r="D119" t="s">
         <v>519</v>
-      </c>
-      <c r="C119" t="s">
-        <v>520</v>
-      </c>
-      <c r="D119" t="s">
-        <v>521</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
@@ -5565,16 +10004,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>520</v>
+      </c>
+      <c r="B120" t="s">
+        <v>521</v>
+      </c>
+      <c r="C120" t="s">
         <v>522</v>
       </c>
-      <c r="B120" t="s">
+      <c r="D120" t="s">
         <v>523</v>
-      </c>
-      <c r="C120" t="s">
-        <v>524</v>
-      </c>
-      <c r="D120" t="s">
-        <v>525</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
@@ -5585,16 +10024,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>524</v>
+      </c>
+      <c r="B121" t="s">
+        <v>525</v>
+      </c>
+      <c r="C121" t="s">
         <v>526</v>
       </c>
-      <c r="B121" t="s">
+      <c r="D121" t="s">
         <v>527</v>
-      </c>
-      <c r="C121" t="s">
-        <v>528</v>
-      </c>
-      <c r="D121" t="s">
-        <v>529</v>
       </c>
       <c r="E121" t="s">
         <v>187</v>
@@ -5605,76 +10044,76 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>528</v>
+      </c>
+      <c r="B122" t="s">
+        <v>529</v>
+      </c>
+      <c r="C122" t="s">
         <v>530</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
         <v>531</v>
-      </c>
-      <c r="C122" t="s">
-        <v>532</v>
-      </c>
-      <c r="D122" t="s">
-        <v>533</v>
       </c>
       <c r="E122" t="s">
         <v>187</v>
       </c>
       <c r="F122" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>533</v>
+      </c>
+      <c r="B123" t="s">
+        <v>534</v>
+      </c>
+      <c r="C123" t="s">
         <v>535</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
         <v>536</v>
-      </c>
-      <c r="C123" t="s">
-        <v>537</v>
-      </c>
-      <c r="D123" t="s">
-        <v>538</v>
       </c>
       <c r="E123" t="s">
         <v>107</v>
       </c>
       <c r="F123" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>538</v>
+      </c>
+      <c r="B124" t="s">
+        <v>539</v>
+      </c>
+      <c r="C124" t="s">
         <v>540</v>
       </c>
-      <c r="B124" t="s">
+      <c r="D124" t="s">
         <v>541</v>
-      </c>
-      <c r="C124" t="s">
-        <v>542</v>
-      </c>
-      <c r="D124" t="s">
-        <v>543</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
       </c>
       <c r="F124" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>543</v>
+      </c>
+      <c r="B125" t="s">
+        <v>544</v>
+      </c>
+      <c r="C125" t="s">
         <v>545</v>
       </c>
-      <c r="B125" t="s">
+      <c r="D125" t="s">
         <v>546</v>
-      </c>
-      <c r="C125" t="s">
-        <v>547</v>
-      </c>
-      <c r="D125" t="s">
-        <v>548</v>
       </c>
       <c r="E125" t="s">
         <v>11</v>
@@ -5685,36 +10124,36 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>547</v>
+      </c>
+      <c r="B126" t="s">
+        <v>548</v>
+      </c>
+      <c r="C126" t="s">
         <v>549</v>
       </c>
-      <c r="B126" t="s">
+      <c r="D126" t="s">
         <v>550</v>
-      </c>
-      <c r="C126" t="s">
-        <v>551</v>
-      </c>
-      <c r="D126" t="s">
-        <v>552</v>
       </c>
       <c r="E126" t="s">
         <v>139</v>
       </c>
       <c r="F126" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>552</v>
+      </c>
+      <c r="B127" t="s">
+        <v>553</v>
+      </c>
+      <c r="C127" t="s">
         <v>554</v>
       </c>
-      <c r="B127" t="s">
+      <c r="D127" t="s">
         <v>555</v>
-      </c>
-      <c r="C127" t="s">
-        <v>556</v>
-      </c>
-      <c r="D127" t="s">
-        <v>557</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
@@ -5725,96 +10164,96 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>556</v>
+      </c>
+      <c r="B128" t="s">
+        <v>557</v>
+      </c>
+      <c r="C128" t="s">
         <v>558</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
         <v>559</v>
       </c>
-      <c r="C128" t="s">
+      <c r="E128" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" t="s">
         <v>560</v>
-      </c>
-      <c r="D128" t="s">
-        <v>561</v>
-      </c>
-      <c r="E128" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>561</v>
+      </c>
+      <c r="B129" t="s">
+        <v>562</v>
+      </c>
+      <c r="C129" t="s">
         <v>563</v>
       </c>
-      <c r="B129" t="s">
+      <c r="D129" t="s">
         <v>564</v>
       </c>
-      <c r="C129" t="s">
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" t="s">
         <v>565</v>
-      </c>
-      <c r="D129" t="s">
-        <v>566</v>
-      </c>
-      <c r="E129" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>566</v>
+      </c>
+      <c r="B130" t="s">
+        <v>567</v>
+      </c>
+      <c r="C130" t="s">
         <v>568</v>
       </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
         <v>569</v>
       </c>
-      <c r="C130" t="s">
-        <v>570</v>
-      </c>
-      <c r="D130" t="s">
-        <v>571</v>
-      </c>
       <c r="E130" t="s">
         <v>11</v>
       </c>
       <c r="F130" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>570</v>
+      </c>
+      <c r="B131" t="s">
+        <v>571</v>
+      </c>
+      <c r="C131" t="s">
         <v>572</v>
       </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
         <v>573</v>
       </c>
-      <c r="C131" t="s">
+      <c r="E131" t="s">
         <v>574</v>
       </c>
-      <c r="D131" t="s">
+      <c r="F131" t="s">
         <v>575</v>
-      </c>
-      <c r="E131" t="s">
-        <v>576</v>
-      </c>
-      <c r="F131" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>576</v>
+      </c>
+      <c r="B132" t="s">
+        <v>577</v>
+      </c>
+      <c r="C132" t="s">
         <v>578</v>
       </c>
-      <c r="B132" t="s">
+      <c r="D132" t="s">
         <v>579</v>
-      </c>
-      <c r="C132" t="s">
-        <v>580</v>
-      </c>
-      <c r="D132" t="s">
-        <v>581</v>
       </c>
       <c r="E132" t="s">
         <v>37</v>
@@ -5825,56 +10264,56 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>580</v>
+      </c>
+      <c r="B133" t="s">
+        <v>581</v>
+      </c>
+      <c r="C133" t="s">
         <v>582</v>
       </c>
-      <c r="B133" t="s">
+      <c r="D133" t="s">
         <v>583</v>
       </c>
-      <c r="C133" t="s">
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" t="s">
         <v>584</v>
-      </c>
-      <c r="D133" t="s">
-        <v>585</v>
-      </c>
-      <c r="E133" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>585</v>
+      </c>
+      <c r="B134" t="s">
+        <v>586</v>
+      </c>
+      <c r="C134" t="s">
         <v>587</v>
       </c>
-      <c r="B134" t="s">
+      <c r="D134" t="s">
         <v>588</v>
-      </c>
-      <c r="C134" t="s">
-        <v>589</v>
-      </c>
-      <c r="D134" t="s">
-        <v>590</v>
       </c>
       <c r="E134" t="s">
         <v>222</v>
       </c>
       <c r="F134" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>590</v>
+      </c>
+      <c r="B135" t="s">
+        <v>591</v>
+      </c>
+      <c r="C135" t="s">
         <v>592</v>
       </c>
-      <c r="B135" t="s">
+      <c r="D135" t="s">
         <v>593</v>
-      </c>
-      <c r="C135" t="s">
-        <v>594</v>
-      </c>
-      <c r="D135" t="s">
-        <v>595</v>
       </c>
       <c r="E135" t="s">
         <v>11</v>
@@ -5885,16 +10324,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>594</v>
+      </c>
+      <c r="B136" t="s">
+        <v>595</v>
+      </c>
+      <c r="C136" t="s">
         <v>596</v>
       </c>
-      <c r="B136" t="s">
+      <c r="D136" t="s">
         <v>597</v>
-      </c>
-      <c r="C136" t="s">
-        <v>598</v>
-      </c>
-      <c r="D136" t="s">
-        <v>599</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
@@ -5905,16 +10344,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>598</v>
+      </c>
+      <c r="B137" t="s">
+        <v>599</v>
+      </c>
+      <c r="C137" t="s">
         <v>600</v>
       </c>
-      <c r="B137" t="s">
+      <c r="D137" t="s">
         <v>601</v>
-      </c>
-      <c r="C137" t="s">
-        <v>602</v>
-      </c>
-      <c r="D137" t="s">
-        <v>603</v>
       </c>
       <c r="E137" t="s">
         <v>187</v>
@@ -5925,16 +10364,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>602</v>
+      </c>
+      <c r="B138" t="s">
+        <v>603</v>
+      </c>
+      <c r="C138" t="s">
         <v>604</v>
       </c>
-      <c r="B138" t="s">
+      <c r="D138" t="s">
         <v>605</v>
-      </c>
-      <c r="C138" t="s">
-        <v>606</v>
-      </c>
-      <c r="D138" t="s">
-        <v>607</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
@@ -5945,16 +10384,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>606</v>
+      </c>
+      <c r="B139" t="s">
+        <v>607</v>
+      </c>
+      <c r="C139" t="s">
         <v>608</v>
       </c>
-      <c r="B139" t="s">
+      <c r="D139" t="s">
         <v>609</v>
-      </c>
-      <c r="C139" t="s">
-        <v>610</v>
-      </c>
-      <c r="D139" t="s">
-        <v>611</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
@@ -5965,16 +10404,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>610</v>
+      </c>
+      <c r="B140" t="s">
+        <v>611</v>
+      </c>
+      <c r="C140" t="s">
         <v>612</v>
       </c>
-      <c r="B140" t="s">
+      <c r="D140" t="s">
         <v>613</v>
-      </c>
-      <c r="C140" t="s">
-        <v>614</v>
-      </c>
-      <c r="D140" t="s">
-        <v>615</v>
       </c>
       <c r="E140" t="s">
         <v>139</v>
@@ -5985,36 +10424,36 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>614</v>
+      </c>
+      <c r="B141" t="s">
+        <v>615</v>
+      </c>
+      <c r="C141" t="s">
         <v>616</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D141" t="s">
         <v>617</v>
-      </c>
-      <c r="C141" t="s">
-        <v>618</v>
-      </c>
-      <c r="D141" t="s">
-        <v>619</v>
       </c>
       <c r="E141" t="s">
         <v>187</v>
       </c>
       <c r="F141" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>619</v>
+      </c>
+      <c r="B142" t="s">
+        <v>620</v>
+      </c>
+      <c r="C142" t="s">
         <v>621</v>
       </c>
-      <c r="B142" t="s">
+      <c r="D142" t="s">
         <v>622</v>
-      </c>
-      <c r="C142" t="s">
-        <v>623</v>
-      </c>
-      <c r="D142" t="s">
-        <v>624</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -6025,116 +10464,116 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>623</v>
+      </c>
+      <c r="B143" t="s">
+        <v>624</v>
+      </c>
+      <c r="C143" t="s">
         <v>625</v>
       </c>
-      <c r="B143" t="s">
+      <c r="D143" t="s">
         <v>626</v>
       </c>
-      <c r="C143" t="s">
-        <v>627</v>
-      </c>
-      <c r="D143" t="s">
-        <v>628</v>
-      </c>
       <c r="E143" t="s">
         <v>11</v>
       </c>
       <c r="F143" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>627</v>
+      </c>
+      <c r="B144" t="s">
+        <v>628</v>
+      </c>
+      <c r="C144" t="s">
         <v>629</v>
       </c>
-      <c r="B144" t="s">
+      <c r="D144" t="s">
         <v>630</v>
       </c>
-      <c r="C144" t="s">
-        <v>631</v>
-      </c>
-      <c r="D144" t="s">
-        <v>632</v>
-      </c>
       <c r="E144" t="s">
         <v>11</v>
       </c>
       <c r="F144" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>631</v>
+      </c>
+      <c r="B145" t="s">
+        <v>632</v>
+      </c>
+      <c r="C145" t="s">
         <v>633</v>
       </c>
-      <c r="B145" t="s">
+      <c r="D145" t="s">
         <v>634</v>
       </c>
-      <c r="C145" t="s">
-        <v>635</v>
-      </c>
-      <c r="D145" t="s">
-        <v>632</v>
-      </c>
       <c r="E145" t="s">
         <v>11</v>
       </c>
       <c r="F145" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>635</v>
+      </c>
+      <c r="B146" t="s">
         <v>636</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>637</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>638</v>
       </c>
-      <c r="D146" t="s">
-        <v>639</v>
-      </c>
       <c r="E146" t="s">
         <v>11</v>
       </c>
       <c r="F146" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>639</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
         <v>640</v>
       </c>
-      <c r="B147" t="s">
-        <v>11</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>641</v>
-      </c>
-      <c r="D147" t="s">
-        <v>642</v>
       </c>
       <c r="E147" t="s">
         <v>222</v>
       </c>
       <c r="F147" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>643</v>
+      </c>
+      <c r="B148" t="s">
         <v>644</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>645</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>646</v>
-      </c>
-      <c r="D148" t="s">
-        <v>642</v>
       </c>
       <c r="E148" t="s">
         <v>11</v>
@@ -6160,7 +10599,7 @@
         <v>11</v>
       </c>
       <c r="F149" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,7 +10659,7 @@
         <v>11</v>
       </c>
       <c r="F152" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6320,7 +10759,7 @@
         <v>11</v>
       </c>
       <c r="F157" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6374,27 +10813,27 @@
         <v>696</v>
       </c>
       <c r="D160" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E160" t="s">
         <v>11</v>
       </c>
       <c r="F160" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B161" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C161" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D161" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E161" t="s">
         <v>11</v>
@@ -6405,16 +10844,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B162" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C162" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D162" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="E162" t="s">
         <v>11</v>
@@ -6425,16 +10864,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B163" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C163" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D163" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E163" t="s">
         <v>11</v>
@@ -6445,16 +10884,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B164" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C164" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D164" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E164" t="s">
         <v>139</v>
@@ -6465,36 +10904,36 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B165" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C165" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D165" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E165" t="s">
         <v>11</v>
       </c>
       <c r="F165" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B166" t="s">
         <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D166" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E166" t="s">
         <v>11</v>
@@ -6505,76 +10944,76 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B167" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C167" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D167" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E167" t="s">
         <v>11</v>
       </c>
       <c r="F167" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B168" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C168" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D168" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
       </c>
       <c r="F168" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B169" t="s">
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D169" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E169" t="s">
         <v>222</v>
       </c>
       <c r="F169" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B170" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C170" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D170" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E170" t="s">
         <v>11</v>
@@ -6585,16 +11024,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B171" t="s">
         <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D171" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E171" t="s">
         <v>11</v>
@@ -6605,16 +11044,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B172" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C172" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D172" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E172" t="s">
         <v>11</v>
@@ -6625,16 +11064,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B173" t="s">
         <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D173" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E173" t="s">
         <v>11</v>
@@ -6645,16 +11084,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B174" t="s">
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D174" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E174" t="s">
         <v>37</v>
@@ -6665,16 +11104,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B175" t="s">
         <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D175" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E175" t="s">
         <v>37</v>
@@ -6685,16 +11124,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B176" t="s">
         <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D176" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="E176" t="s">
         <v>37</v>
@@ -6705,16 +11144,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B177" t="s">
         <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D177" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E177" t="s">
         <v>37</v>
@@ -6725,16 +11164,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B178" t="s">
         <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D178" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E178" t="s">
         <v>37</v>
@@ -6745,16 +11184,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B179" t="s">
         <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D179" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="E179" t="s">
         <v>37</v>
@@ -6765,16 +11204,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B180" t="s">
         <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D180" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="E180" t="s">
         <v>37</v>
@@ -6785,16 +11224,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B181" t="s">
         <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="D181" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="E181" t="s">
         <v>37</v>
@@ -6805,16 +11244,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B182" t="s">
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="D182" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="E182" t="s">
         <v>37</v>
@@ -6825,16 +11264,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B183" t="s">
         <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D183" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="E183" t="s">
         <v>37</v>
@@ -6845,16 +11284,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="B184" t="s">
         <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="D184" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="E184" t="s">
         <v>37</v>
@@ -6865,16 +11304,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B185" t="s">
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="D185" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="E185" t="s">
         <v>37</v>
@@ -6885,16 +11324,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="B186" t="s">
         <v>11</v>
       </c>
       <c r="C186" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="D186" t="s">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="E186" t="s">
         <v>37</v>
@@ -6905,16 +11344,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="B187" t="s">
         <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="D187" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="E187" t="s">
         <v>37</v>
@@ -6925,16 +11364,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="B188" t="s">
         <v>11</v>
       </c>
       <c r="C188" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="D188" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
       <c r="E188" t="s">
         <v>37</v>
@@ -6945,16 +11384,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B189" t="s">
         <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="D189" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="E189" t="s">
         <v>37</v>
@@ -6965,16 +11404,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="B190" t="s">
         <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="D190" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="E190" t="s">
         <v>37</v>
@@ -6985,16 +11424,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="B191" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="C191" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="D191" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="E191" t="s">
         <v>11</v>
@@ -7005,16 +11444,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>794</v>
+        <v>805</v>
       </c>
       <c r="B192" t="s">
         <v>72</v>
       </c>
       <c r="C192" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="D192" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="E192" t="s">
         <v>222</v>
@@ -7025,56 +11464,56 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B193" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="C193" t="s">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="D193" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="E193" t="s">
         <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="B194" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C194" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="D194" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="E194" t="s">
         <v>11</v>
       </c>
       <c r="F194" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="B195" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C195" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="D195" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="E195" t="s">
         <v>11</v>
@@ -7085,16 +11524,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="B196" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="C196" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="D196" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="E196" t="s">
         <v>11</v>
@@ -7105,36 +11544,36 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="B197" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="C197" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="D197" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="E197" t="s">
         <v>64</v>
       </c>
       <c r="F197" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="B198" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="C198" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="D198" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="E198" t="s">
         <v>11</v>
@@ -7145,16 +11584,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="B199" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C199" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="D199" t="s">
-        <v>824</v>
+        <v>395</v>
       </c>
       <c r="E199" t="s">
         <v>11</v>
@@ -7165,16 +11604,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="B200" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="C200" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="D200" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="E200" t="s">
         <v>11</v>
@@ -7185,16 +11624,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="B201" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="C201" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="D201" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="E201" t="s">
         <v>37</v>
@@ -7205,16 +11644,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="B202" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="C202" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="D202" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="E202" t="s">
         <v>11</v>
@@ -7225,16 +11664,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="B203" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="C203" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="D203" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -7245,16 +11684,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="B204" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="C204" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="D204" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="E204" t="s">
         <v>11</v>
@@ -7265,56 +11704,56 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="B205" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="C205" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="D205" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="E205" t="s">
         <v>11</v>
       </c>
       <c r="F205" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="B206" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="C206" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="D206" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="E206" t="s">
         <v>11</v>
       </c>
       <c r="F206" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="B207" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="C207" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="D207" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="E207" t="s">
         <v>11</v>
@@ -7325,16 +11764,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="B208" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="C208" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="D208" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="E208" t="s">
         <v>11</v>
@@ -7345,36 +11784,36 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="B209" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="C209" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="D209" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="E209" t="s">
         <v>11</v>
       </c>
       <c r="F209" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="B210" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="C210" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="D210" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="E210" t="s">
         <v>11</v>
@@ -7385,16 +11824,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="B211" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="C211" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="D211" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="E211" t="s">
         <v>11</v>
@@ -7405,16 +11844,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="B212" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="C212" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="D212" t="s">
-        <v>877</v>
+        <v>395</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
@@ -7425,16 +11864,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="B213" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="C213" t="s">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="D213" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -7445,16 +11884,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="B214" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="C214" t="s">
-        <v>884</v>
+        <v>894</v>
       </c>
       <c r="D214" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="E214" t="s">
         <v>11</v>
@@ -7465,36 +11904,36 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="B215" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C215" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="D215" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="E215" t="s">
         <v>11</v>
       </c>
       <c r="F215" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="B216" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="C216" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="D216" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="E216" t="s">
         <v>11</v>
@@ -7505,16 +11944,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="B217" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="C217" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="D217" t="s">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="E217" t="s">
         <v>11</v>
@@ -7525,56 +11964,56 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B218" t="s">
         <v>11</v>
       </c>
       <c r="C218" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="D218" t="s">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="E218" t="s">
         <v>222</v>
       </c>
       <c r="F218" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B219" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="C219" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="D219" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="E219" t="s">
         <v>21</v>
       </c>
       <c r="F219" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="B220" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="C220" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="D220" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="E220" t="s">
         <v>11</v>
@@ -7585,16 +12024,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="B221" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="C221" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="D221" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="E221" t="s">
         <v>11</v>
@@ -7605,16 +12044,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="B222" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="C222" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="D222" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="E222" t="s">
         <v>11</v>
@@ -7625,16 +12064,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="B223" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="C223" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="D223" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="E223" t="s">
         <v>11</v>
@@ -7645,26 +12084,26 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="B224" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="C224" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="D224" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="E224" t="s">
         <v>139</v>
       </c>
       <c r="F224" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/results-list/pagina12.xlsx
+++ b/results-list/pagina12.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E00EEE-5F77-4C88-8C9F-4CC21593DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Resultados" state="visible" r:id="rId4"/>
+    <sheet name="Resultados" sheetId="1" r:id="rId1"/>
+    <sheet name="RAW" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$E$223</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="664">
   <si>
     <t>Título</t>
   </si>
@@ -31,11 +36,8 @@
     <t>https://www.pagina12.com.ar/793657-asamblea-indigena-contra-los-desmontes</t>
   </si>
   <si>
-    <t xml:space="preserve">**** *pais_ag *jornal_pagina12 *ano_2024
-    Asamblea indígena contra los desmontes
-    El ordenamiento de bosques nativos y la derogación de la ley 26160, el eje de la atención
-Organizaciones, comunidades, consejeros, vocales y referentes indígenas se reunirán hoy en la ciudad de Salta para analizar y tomar decisiones sobre los "atropellos a los derechos constitucionales" de los pueblos indígenas que vienen sufriendo.
-    "Nos convocamos a tomar decisiones y a elaborar una agenda en el marco de los atropellos a los derechos constitucionales de los Pueblos Indígenas", comienza la convocatoria a la asamblea provincial de organizaciones, comunidades, consejeros, vocales y referentes de pueblos indígenas que se realizará esta tarde en la ciudad de Salta.
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Asamblea indígena contra los desmontes. El ordenamiento de bosques nativos y la derogación de la ley 26160, el eje de la atención. Organizaciones, comunidades, consejeros, vocales y referentes indígenas se reunirán hoy en la ciudad de Salta para analizar y tomar decisiones sobre los "atropellos a los derechos constitucionales" de los pueblos indígenas que vienen sufriendo.. "Nos convocamos a tomar decisiones y a elaborar una agenda en el marco de los atropellos a los derechos constitucionales de los Pueblos Indígenas", comienza la convocatoria a la asamblea provincial de organizaciones, comunidades, consejeros, vocales y referentes de pueblos indígenas que se realizará esta tarde en la ciudad de Salta.
 La preocupación inmediata es la nueva “Ley de Desmontes”, como llaman a la ley por la que la Legislatura provincial aprobó el nuevo Ordenamiento Territorial de Bosques Nativos que "pone en el mercado más 700.000 hectáreas", "decisiones tomadas por el estado provincial sin consulta libre, previa e informada (Ley 24.071) a los sujetos de derechos que son los Pueblos preexistentes al Estado argentino, al provincial y a los municipios", se señala en la convocatoria al encuentro de esta tarde, realizada por la Mesa de Derechos Indígenas y que se desarrollará a partir de las 18.30 en la Casa Artivista La Bartolina (Urquiza 1112).
 "La representatividad indígena, materializada en sus autoridades tradicionales, Curacas, Colal, Mborubichas, Pel, Caciques, y asambleas territoriales debe pronunciarse, ante la más cruda indiferencia estatal, y el resultado de sus actos que recaen sobre las comunidades indígenas que son despojadas, desalojadas, olvidadas a su suerte, padeciendo muertes por desnutrición, deshidratación, falta de atención médica, falta de medicamentos, inseguridad", se afirma en la convocatoria.
 También se destaca que las comunidades originarias "son víctimas de la sobreexplotación laboral, violencia de género, discriminacion e indiferencia institucional".
@@ -50,11 +52,8 @@
     <t>https://www.pagina12.com.ar/790702-desmontes-sin-proteccion-del-territorio-indigena-un-combo-ex</t>
   </si>
   <si>
-    <t xml:space="preserve">**** *pais_ag *jornal_pagina12 *ano_2024
-    Desmontes sin protección del territorio indígena: “un combo explosivo”
-    La votación del OTBN se pospuso una semana en el Senado
-La antropóloga Norma Naharro advirtió sobre el peligro que se cierne sobre las comunidades indígenas ante la inminente aprobación del nuevo ordenamiento de bosques nativos en la provincia justo cuando el gobierno nacional eliminó la ley que las protegía de desalojos.
-    La combinación de la actualización propuesta para el nuevo Ordenamiento Territorial de Bosques Nativos (OTBN) de Salta que permitirá el desmonte de más de 700 mil hectáreas y la derogación de la ley 26160, que frenaba desalojos de comunidades originarias, “es un combo explosivo”, aseguró la antropóloga y especialista en temas indígenas, Norma Naharro, quien participó junto a referentes de diferentes asociaciones civiles de una reunión en la Cámara de Senadores de la provincia.
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Desmontes sin protección del territorio indígena: “un combo explosivo”. La votación del OTBN se pospuso una semana en el Senado. La antropóloga Norma Naharro advirtió sobre el peligro que se cierne sobre las comunidades indígenas ante la inminente aprobación del nuevo ordenamiento de bosques nativos en la provincia justo cuando el gobierno nacional eliminó la ley que las protegía de desalojos.. La combinación de la actualización propuesta para el nuevo Ordenamiento Territorial de Bosques Nativos (OTBN) de Salta que permitirá el desmonte de más de 700 mil hectáreas y la derogación de la ley 26160, que frenaba desalojos de comunidades originarias, “es un combo explosivo”, aseguró la antropóloga y especialista en temas indígenas, Norma Naharro, quien participó junto a referentes de diferentes asociaciones civiles de una reunión en la Cámara de Senadores de la provincia.
 La ley 26160, de emergencia de la propiedad comunitaria indígena, protegía a las comunidades originarias de desalojos de sus territorios. Pero el presidente Javier Milei decidió derogar el decreto de necesidad y urgencia que había establecido la última prórroga hasta el 23 de noviembre de 2025.
 Esta nueva realidad, conocida el martes último tras su publicación en el Boletín Oficial de la República Argentina, pone ahora más presión en el tratamiento del proyecto de OTBN que fue aprobado ese mismo día por la Cámara de Diputados de Salta, que la remitió para su tratamiento al Senado de la provincia.
 En ese marco el miércoles último Naharro participó de una reunión, junto a referentes de asociaciones civiles y comunidades indígenas, con al menos 16 senadores provinciales. El tema del encuentro fue el proyecto de nuevo ordenamiento territorial de los bosques de la provincia. Por el momento, se pospuso el tratamiento del ordenamiento por una semana, y se prevé que el proyecto sea considerado en la sesión del jueves próximo.
@@ -84,11 +83,8 @@
     <t>https://www.pagina12.com.ar/786264-lula-y-xi-relanzan-el-vinculo-bilateral</t>
   </si>
   <si>
-    <t xml:space="preserve">**** *pais_ag *jornal_pagina12 *ano_2024
-    Lula y Xi relanzan el vínculo bilateral
-    El gobierno de Brasil firmó 37 acuerdos y memorandos con China
-La diplomacia brasilera brilló por su profesionalismo durante la visita del presidente de China a Río por la cumbre del G20 y a Brasilia para reunirse con Lula.
-    En el marco de la celebración del 50 aniversario del establecimiento de las relaciones diplomáticas entre Brasil y la República Popular China, la semana pasada el Presidente Lula da Silva recibió en el Palacio de Alvorada a su par chino Xi Jinping.
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Lula y Xi relanzan el vínculo bilateral. El gobierno de Brasil firmó 37 acuerdos y memorandos con China. La diplomacia brasilera brilló por su profesionalismo durante la visita del presidente de China a Río por la cumbre del G20 y a Brasilia para reunirse con Lula.. En el marco de la celebración del 50 aniversario del establecimiento de las relaciones diplomáticas entre Brasil y la República Popular China, la semana pasada el Presidente Lula da Silva recibió en el Palacio de Alvorada a su par chino Xi Jinping.
 Luego de haber participado de la Cumbre del G20 en Río de Janeiro, el mandatario de la potencia asiática se trasladó a la capital brasileña, donde mantuvo reuniones bilaterales con el presidente y varios de sus ministros. El gobierno brasileño firmó 37 acuerdos y memorandos promoviendo la apertura de mercados de nuevos productos brasileños, acuerdos de inversiones energéticas, intercambio educativo, científico tecnológico, telecomunicaciones, salud, entre otros.
 El punto más destacado es la adhesión del gobierno brasileño a un protocolo de “sinergias” vinculado a la Iniciativa de la Franja y la Ruta. El llamado Plan de Cooperación se propone el establecimiento de sinergias entre el Programa de Aceleración del Crecimiento, el Plan Nueva Industria Brasil, el Plan de Transformación Ecológica, el Programa Rutas de la Integración Sudamericana y la Iniciativa de la Franja y la Ruta.
 El acuerdo prevé la creación de un Grupo de trabajo para lanzar líneas de financiamiento para la infraestructura, desarrollo de cadenas productivas (alta tecnología, inteligencia artificial, salud, digitalización, aviación y espacial), así como la transformación ecológica y la promoción de programas de transferencia tecnológica.
@@ -115,11 +111,8 @@
     <t>https://www.pagina12.com.ar/784235-bioinsumos-una-oportunidad-para-reducir-el-uso-de-agroquimic</t>
   </si>
   <si>
-    <t xml:space="preserve">**** *pais_ag *jornal_pagina12 *ano_2024
-    Bioinsumos, una oportunidad para reducir el uso de agroquímicos
-    Ventajas y riesgos de un mercado chico pero en franco ascenso
-La producción de este tipo de insumos mejora el rendimiento del agro, fomenta las economías regionales y cooperativas y reduce la necesidad de divisas.
-    El informe Bioinsumos: Oportunidades de Inversión en América Latina, elaborado el año pasado por el Centro de Inversiones de la FAO-ONU, estipula que, en los últimos cinco años, el mercado de bioinsumos en América Latina, si bien sigue siendo marginal, verifica un crecimiento promedio de ventas del 15 por ciento anual.
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Bioinsumos, una oportunidad para reducir el uso de agroquímicos. Ventajas y riesgos de un mercado chico pero en franco ascenso. La producción de este tipo de insumos mejora el rendimiento del agro, fomenta las economías regionales y cooperativas y reduce la necesidad de divisas.. El informe Bioinsumos: Oportunidades de Inversión en América Latina, elaborado el año pasado por el Centro de Inversiones de la FAO-ONU, estipula que, en los últimos cinco años, el mercado de bioinsumos en América Latina, si bien sigue siendo marginal, verifica un crecimiento promedio de ventas del 15 por ciento anual.
 “En Argentina, la perspectiva de crecimiento es mayor que en químicos. Mientras que el uso de biológico crece entre el 10 y 12 por ciento anual, el uso de químicos está casi estancado, con una expectativa de crecimiento de entre el 3 y 5 por ciento”, afirmó Gustavo González Anta, director científico de la empresa Indrasa, en el Tercer Encuentro Nacional sobre Producción con Biológicos realizado este año en Villa María, Córdoba.
 El mercado de bioinsumos agrícolas ya mueve en el país unos 8.600 millones de dólares, con la ventaja que son de producción nacional y hasta pueden ser una solución al eterno problema de la falta de dólares.
 [H2] Ética ecológica
@@ -144,11 +137,8 @@
     <t>https://www.pagina12.com.ar/781911-el-pais-que-a-milei-no-le-interesa-conicet-perdio-1055-traba</t>
   </si>
   <si>
-    <t xml:space="preserve">**** *pais_ag *jornal_pagina12 *ano_2024
-    El país que a Milei no le interesa: Conicet perdió 1055 trabajadores
-    Fuga de cerebros
-El retroceso actual no tiene equivalentes en la historia reciente del organismo
-    Por primera vez en 20 años, el Conicet tiene menos personal. En lo que va de 2024, el principal organismo de investigación científica de la Argentina registró una pérdida de 1055 trabajadores, entre los que se encuentran 598 investigadores de carrera, 457 becarios y personal administrativo. El retroceso actual no tiene equivalentes en la historia reciente del organismo.
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    El país que a Milei no le interesa: Conicet perdió 1055 trabajadores. Fuga de cerebros. El retroceso actual no tiene equivalentes en la historia reciente del organismo. Por primera vez en 20 años, el Conicet tiene menos personal. En lo que va de 2024, el principal organismo de investigación científica de la Argentina registró una pérdida de 1055 trabajadores, entre los que se encuentran 598 investigadores de carrera, 457 becarios y personal administrativo. El retroceso actual no tiene equivalentes en la historia reciente del organismo.
 Los datos se desprenden del último estudio de Evolución de Empleo y Recursos Humanos del Sistema Nacional de Ciencia, Tecnología e Innovación, elaborado por el Grupo EPC-CIICTI. Esta caída, según expone el informe, se da en el marco de un descenso generalizado de puestos de trabajo en el sector científico público, en el que ya se perdieron 2696 empleos, pasando de 75.051 en diciembre de 2023 a 72.355 en septiembre de este año.</t>
   </si>
   <si>
@@ -158,504 +148,1895 @@
     <t>https://www.pagina12.com.ar/781647-desde-el-conicet-denuncian-una-politica-de-discriminacion-a-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Desde el Conicet denuncian una "política de discriminación" a becarios e investigadores. Las razones de la renuncia Manuel García Solá. El doctor en Bioquímica e investigador, Jorge Geffner, aseguró que al presidente Javier Milei "le molesta" el organismo científico porque "es un lugar donde hay libertad de pensamiento".. El doctor en Bioquímica e investigador del Conicet, Jorge Geffner, se refirió a la renuncia del integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, quien denunció persecución política e ideológica a los becarios e investigadores del organismo.
+“Sorprende en los motivos por los cuales se fundamenta la decisión de Solá de renunciar, denunciando persecución ideológica, que era algo que desde el retorno de la democracia no se había visto”, advirtió Geffner en diálogo con la 750.
+"Se habían visto periodos de ajuste pero no de persecución ideológica. En ese sentido es muy grave”, lamentó.
+Según el investigador del Conicet, Solá “habló particularmente sobre los ingresos que están congelados”.
+“Todo esto se da en un marco de ajuste en el sistema científico tecnológico nacional. En otros momentos se sufría el ajuste, no como ahora, es otra dimensión. Esto está provocando un éxodo mucho mayor de investigadores, pero incluso en ese momento no se sentía esta discriminación. En este sentido, es algo novedoso”, insistió.
+“Acá no solamente hay un feroz ajuste, sino que hay una política de discriminación, que claramente Solá la expresa en su renuncia, quien es una persona de pensamientos más conservadores pero dice ‘acá hay un límite ético que es este y no lo puedo transgredir’”, afirmó.
+Por último, Geffner aseguró que el Conicet “molesta” al presidente Javier Milei “porque, como organismo científico, es un lugar donde tiene que haber libertad de pensamiento. Ese pensamiento crítico le molesta. Pero si no hay pensamiento crítico, no se puede hacer ciencia en ningún campo, porque lo nuevo surge de replantearse lo viejo en ciencia”, concluyó.</t>
+  </si>
+  <si>
     <t>La inseguridad alimentaria, avanza</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/780931-la-inseguridad-alimentaria-avanza</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La inseguridad alimentaria, avanza. Se deteriora el acceso de la población a los bienes básicos. El consumo de alimentos se redujo, pero las empresas del sector incrementaron su rentabilidad en un 1300 por ciento.. El ajuste fiscal y la devaluación elevaron los precios de los alimentos y redujeron la capacidad de compra de los sectores vulnerables, concluye la investigación titulada “Rascar la olla. Informe sobre el desmantelamiento de políticas agroalimentarias en los primeros meses del gobierno de Milei”, elaborado por el Programa de Estudios Regionales y Territoriales de la Universidad de Buenos Aires (UBA) y publicado por el Centro de Estudios Legales y Sociales (CELS) en conjunto con la Fundación Rosa Luxemburgo.
+El informe registra una caída del 11 por ciento en el consumo general de alimentos y de un 16 por ciento en supermercados y mayoristas. A su vez, detalla el modo en que la eliminación de políticas de apoyo a la agricultura familiar perjudicó tanto a productores como a consumidores, dado que se debilitaron las instancias que apoyaban a la producción familiar y a los espacios comunitarios de distribución alimentaria.
+La investigación también destaca que esta crisis favoreció a las grandes empresas de sectores estratégicos y oligopólicos, que pudieron maximizar sus beneficios. Utilizando datos del Instituto de Pensamiento y Políticas Públicas (IPyPP), informe sostiene que mientras crece la inseguridad alimentaria, las empresas de ese sector que cotizan en la Bolsa de Buenos Aires aumentaron sus ganancias un 1300 por ciento, y el complejo exportador de granos hizo lo propio en un 4900 por ciento.
+La escalada de precios en los primeros meses del año, que llevó el índice de pobreza al 52,9 por ciento, ubicó a la Argentina primera en el ranking de inflación nominal, con un 135 por ciento en alimentos, según datos proporcionados por el Banco Mundial.
+Desde noviembre hasta julio, el gobierno de La Libertad Avanza incrementó los precios de lo que comen los argentinos a nivel general un 128 por ciento, ubicándose así entre los países con mayor inseguridad alimentaria. “La política de devaluación del peso frente al dólar, junto con el recorte del gasto público, desregulación económica y aumentos en las tarifas de servicios y combustibles, ha intensificado la crisis alimentaria en el país”, denuncia el informe.
+[H2] Transferencia de recursos
+La política de ajustes y la transferencia de recursos hacia sectores exportadores y de mayores ingresos ha tenido un impacto devastador en el ingreso de los hogares promedio. Aunque el gobierno nacional celebró los aumentos salariales implementados desde marzo, la mayoría se encuentran muy por debajo de la inflación, especialmente en el sector público y en el privado no registrado, donde la pérdida en términos reales alcanzó el 19 por ciento.
+El informe analiza que las medidas adoptadas por el gobierno de Javier Milei generaron “una caída en el poder adquisitivo, una contracción del consumo interno y una grave pérdida de seguridad alimentaria, afectando tanto la producción como el acceso de la población a alimentos básicos”. El presupuesto estatal se ajustó drásticamente, mientras que la desregulación de precios y los acuerdos salariales a la baja golpearon el poder adquisitivo y desincentivaron el consumo interno, complicando el acceso a bienes esenciales y profundizando la crisis económica.
+Las políticas actuales están configurando un modelo de producción agraria concentrado y orientado al exterior. Se eliminó el “Compre Nacional” y se promovió la importación de alimentos más baratos, en un intento por controlar precios. Paralelamente se flexibilizó el uso de tecnologías e insumos que favorecen al agronegocio en detrimento de las economías regionales. Sectores tradicionales como el de la yerba, azúcar, olivo y vid enfrentan “desprotección, costos de insumos elevados y precarización laboral, comprometiendo así la soberanía alimentaria y las oportunidades de desarrollo económico en el interior del país”.
+[H2] Inseguridad alimentaria
+La falta de incentivos para el mercado interno y las desregulaciones continuas proyectan un futuro desafiante, en el que la recuperación del consumo y la producción nacional podrían estar cada vez más fuera del alcance de la mayoría de los argentinos. Por ejemplo, el presupuesto destinado a la Secretaría de Agricultura, Ganadería y Pesca cayó un 95 por ciento en términos reales. El Instituto Nacional de Semillas tuvo una ejecución de tan solo el 20 por ciento y los programas con financiamiento internacional, por debajo del 2 por ciento.
+Los sectores excluidos experimentaron un deterioro significativo en los ingresos. El Programa Potenciar Trabajo “fue congelado y desdoblado en dos nuevos, que no suponen una contraprestación laboral. Por su parte, el Programa Nexo directamente fue eliminado. De esta manera, quienes percibían Potenciar (ahora Volver al Trabajo o Acompañamiento Social) y Nexo entre noviembre y julio perdieron un 71,4 por ciento de sus ingresos en términos reales”, señala el informe.
+Por otro lado, la Asignación Universal por Hijo y la Tarjeta Alimentar aumentaron 40,8 por ciento en términos reales, sin ser este incremento suficiente para cubrir la Canasta Básica Alimentaria (CBA), que en julio se ubicó en $131.294 para el adulto equivalente.
+La combinación de devaluación, inflación y aumento de tarifas dejó a una gran parte de la población en una situación de extrema vulnerabilidad alimentaria, acentuando la brecha entre los sectores más favorecidos, como el exportador, y los trabajadores del sector público y privado no registrado. La crisis no solo expone las dificultades del presente, sino que plantea desafíos profundos para la estabilidad social y económica.
+*Comunicador social, Universidad Nacional de La Plata (UNLP).</t>
+  </si>
+  <si>
     <t>"Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/781344-nunca-podria-callar-mi-voz-cuando-se-intentara-cometer-algun</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución". La explicación de Manuel García Solá sobre su salida del Conicet. El integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, renunció a su puesto y dejó en evidencia el alineamiento total del presidente. El integrante del Directorio del Conicet en representación de las entidades del agronegocio, Manuel García Solá, renunció a su puesto y dejó en evidencia el alineamiento total del presidente de la Sociedad Rural Argentina (SRA), Nicolás Pino, con el presidente Javier Milei. Solá hizo público que dio un paso al costado en contra de su voluntad y por un pedido expreso de Pino, durante una reunión privada, como castigo por expresar sus diferencias por la persecución política e ideológica que ocurre con los becarios e investigadores del organismo.
+Solá, ex ministro de Educación del menemismo, fue nominado por la SRA (con acuerdo de Confederaciones Rurales, Federación Agraria y Coninagro) en junio de 2022 y nombrado en el directorio por el presidente Alberto Fernández. Su desvinculación la relató en una carta pública en la que dejó claro su "disenso con la causa" que llevó a Pino "a hacerme esta solicitud". Más allá de la "prudencia" que mantuvo en su carta, Solá dejó en claro los motivos del presidente de la entidad tradicional del agro.
+"Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución por ideas científicas, políticas, religiosas, tecnológicas o las que fueran", sentenció Solá y le advirtió a Pino que "jamás se alcanzó la libertad económica, en la que coincidimos y por la que bregamos en la SRA, sin libertad política, de pensamiento y disenso democrático, sin respeto a las ideas del otro".
+El ex intengrante del directorio del Conicet, en diálogo con Radio Con Vos, marcó que se refería a la política desplegada por la Casa Rosada en el directorio del Conicet y ejemplificó con la respuesta a la pregunta 177 que dio el jefe de Gabinete, Guillermo Francos, en su última visita al Senado, en la que explicita que la evaluación a los investigadores del organismo condiciona que "sean pertinentes los temas que trabajen", o sea, "que se va a someter a una segunda evaluación de corte político".
+"Algo parecido ocurrió en las últimas semana con algunos becarios y fue lo que me llevó a mí a señalar que estaba en desacuerdo con esos procedimiento y, evidentemente, eso no gustó. A alguien no le gustó y se canalizó de la manera que se canalizó", volvió a dejar en claro la tarea encargada por la Casa Rosada al presidente de la SRA.
+En su carta, Solá también le recordó a Pino que, al momento de su nominación, desconocía la silla que las entidades del agronegocio tienen en el Directorio del Conicet y le citó un textual de cómo, normativamente, deben cumplir sus funciones: "Los miembros del directorio actuarán con independencia de criterio y no en representación de sus proponentes".
+"Como usted podrá entender, con su fina inteligencia y sensibilidad, no tiene, ni puede tener, ningún tipo de cortapisas", le dedicó Solá a Pino y remató: "Nunca podría callar mi voz cuando se intentara cometer algún acto de persecución por ideas científicas, políticas, religiosas, tecnológicas o las que fueran".
+Solá, en diálogo con Radio con Vos, también reivindicó su pasado como funcionario de la gestión de Carlos Menem y le recordó al Ejecutivo, que reivindica aquellos años, que entonces no existían persecución ni condicionamientos ideológicos; más allá del alineamiento de mercado que las entidades del campo representan dentro del modelo de negocios que se ejecuta gobierno tras gobierno.
+El ex integrante del directorio también apuntó contra la paralización de los proyectos que se llevaban adelante desde el organismo y puso como ejemplo la asociación entre la Sociedad Rural, el Conicet, la Universidad Nacional de La Plata y Asociación de Criadores "para transformar nuestro laboratorio de genética aplicada en un centro de análisis e investigación genómica multiespecies, que lleve a consolidar el liderazgo argentino en selección genética a nivel latinoamericano".
+"Espero que, rápidamente, y a través de sus interlocutores con el actual gobierno se retome aquel ritmo que había logrado imprimirle a la relación", le reclamó a Pino.</t>
+  </si>
+  <si>
     <t>El nuevo trabajo de Diana Mondino</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/780463-el-nuevo-trabajo-de-diana-mondino</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    El nuevo trabajo de Diana Mondino. A qué se dedica la excanciller luego de la expulsión del Gobierno. Mientras sigue masticando bronca por su abrupta expulsión del Ministerio de Rela. Mientras sigue masticando bronca por su abrupta expulsión del Ministerio de Relaciones Exteriores, Comercio Internacional y Culto, la excanciller Diana Mondino consiguió un nuevo trabajo en el ámbito privado.
+En realidad, no se trata de un trabajo "nuevo" sino que volverá al antiguo empleo que tenía antes de llegar a la Cancillería, un cargo docente en la Universidad del Centro de Estudios Macroeconómicos de Argentina (UCEMA), una institución privada ubicada en el barrio porteño de Retiro.
+La noticia la confirmó el profesor Marcos Gallacher, director del Departamento de Economía Agrícola, Recursos Naturales y Agronegocios. “¡Salimos ganando! UCEMA recupera a su destacada profesora y mejor persona @DianaMondino. Welcome back! Gracias @JMilei”, escribió el docente en X, junto a una foto con la excanciller.
+Antes de que Milei la nombrara al frente del Ministerio de Relaciones Exteriores, Comercio Internacional y Culto, Mondino daba clases de finanzas en el Master en Dirección de Empresas y en el Master en Finanzas de la universidad privada, que se especializa en negocios.
+Según la página web de UCEMA, la excanciller tiene experiencia temas económicos y de management, así como en evaluación de riesgos y análisis de mercados. "Diana es Master in Business Administration MBA de IESE, España, y Lic. en Economía de la Universidad Nacional de Córdoba" y "ha tomado cursos en las Universidades de Yale (CT.), Columbia (NY.) y Darden (Virginia), EE.UU.", resume la institución.
+Mondino fue expulsada del Gobierno de La Libertad Avanza el pasado 30 de octubre, luego de haber votado en la ONU en contra del bloqueo en Cuba, siendo Argentina uno de los 186 países que acompañaron el reclamo de la isla caribeña, con la excepción de Estados Unidos, Israel y Moldavia, una acción que Milei calificó -durante la bizarra entrevista que le concedió este lunes a su novia, Amalia "Yuyito" González, como "un error imperdonable".
+“La Canciller no consultó si el Gobierno quería mantener la tradición diplomática”, dijo luego de la salida de Mondino el jefe de Gabinete, Guillermo Francos. "No estamos para sacar conclusiones propias en términos de decisiones que hay que tomar en voz o en cabeza del Presidente. Lo que dice el Presidente se hace. Si no se hace, todos estamos invitados dentro de nuestras libertades individuales a retirarnos del gobierno", sumó, por su parte, el vocero presidencial Manuel Adorni.
+Tras ser notificada de su salida, Mondino publicó una carta dirigida a Milei en sus redes sociales, que decía: "Ha sido un gran honor trabajar estos meses con Ud. y todo el gobierno en este proyecto para levantar Argentina. Sé que tiene ideas firmes y sobre todo que tiene el coraje para mantenerlas. Sólo puedo decir que hay muchísimo trabajo por delante y le acompañaré desde el lugar que sea". Quienes la conocen de larga data, sin embargo, dicen que "quedó re caliente" por su eyección, y apuntan contra la secretaria general de la Presidencia, Karina Milei, a quien acusar de haber "intervenido de hecho" la Cancillería.
+Para contener esa bronca, el Gobierno evalúa ofrecerle algún otro puesto o función en el esquema de decisiones de La Libertad Avanza (LLA). “Por supuesto que el Gobierno la tiene totalmente en cuenta. Pues, la considera una persona valiosa y seguramente vamos a encontrar una posición donde le sea de utilidad no solamente al Gobierno, sino al país”, dijo en ese sentido Francos.
+Sin embargo, Mondino aún no se expresó sobre este ofrecimiento. “Hay que ver si quiere, quedó muy golpeada”, reconocen fuentes del Gobierno.</t>
+  </si>
+  <si>
     <t>Contra la violencia y la represión a las comunidades indígenas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/775845-contra-la-violencia-y-la-represion-a-las-comunidades-indigen</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Contra la violencia y la represión a las comunidades indígenas. Denuncia de la Iglesia Católica. A través de un mensaje de la Comisión Episcopal para la Pastoral Aborigen, la Iglesia Católica solicitó a los gobiernos, nacional y provinciales, que cese la represión y la violencia contra las comunidades indígenas, a raíz de hechos recientes que se han venido registrando sobre todo en las últimas semanas en el norte del país. Pedido de Francisco a las “grandes corporaciones extractivas”.. Bajo el título “Cuidar y defender el derecho de los más vulnerables” y con la firma de su presidente, el obispo Luis Scozzina, la Comisión Episcopal para la Pastoral Aborigen dependiente de la Conferencia Episcopal Argentina, expresó en un comunicado su “preocupación” por “el avance de resoluciones y políticas de Estado que desconocen y vulneran derechos de los Pueblos Indígenas adquiridos a partir de Convenios institucionales y la misma Constitución Nacional” y se pide a los gobiernos “abandonar actitudes de violencia y represión frente a las comunidades indígenas”.
+En el mensaje los obispos hacen suya la advertencia del Equipo Nacional de Pastoral Aborigen (ENDEPA) que denunció “múltiples atropellos sufridos por las comunidades” que, a sus vez, se ven “agudizados en este tiempo donde se exacerba el individualismo y la sobre explotación de nuestros bienes naturales y culturales y ante el creciente discurso estigmatizante contra los pueblos indígenas y de quienes acompañamos sus caminos de lucha”.
+En el mismo texto se hace mención a una intervención pública del papa Francisco en la que pidió “en nombre de Dios a las grandes corporaciones extractivas —mineras, petroleras—, forestales, inmobiliarias, agronegocios, que dejen de destruir los bosques, humedales y montañas, dejen de contaminar los ríos y los mares, dejen de intoxicar los pueblos y los alimentos”.
+ENDEPA había expresado también su preocupación porque “desde el poder político y económico se pretende nuevamente negar su preexistencia y pertenencia (de las comunidades) al Estado Argentino, con dolor volvemos a escuchar discursos y afirmaciones referentes a los pueblos indígenas como ‘los otros’, ‘los extranjeros’ retrotrayéndonos a un pasado violento y excluyente”.
+En el mensaje de la Comisión Episcopal de Pastoral Aborigen y “frente a la escalada de conflictos, a partir del desconocimiento de la propiedad comunitaria indígena por parte de aquellos que usurpan sus territorios como así también la violencia ejercida contra las comunidades y contra aquellos que las acompañan, en su mayoría agentes de pastoral de ENDEPA” se reitera el llamado “en especial a los gobiernos, a abandonar actitudes de violencia y represión frente a las comunidades indígenas, e involucrarse en la superación positiva de los conflictos en sus territorios, en un marco de respeto por la verdad y las normas jurídicas vigentes, incluyendo a los indígenas como parte esencial de la solución mediante medidas no violentas que propicien el diálogo, la amistad social y la paz”.
+El mensaje firmado por el obispo Scozzina, finaliza con una oración a Jesucristo a quien se le pide “danos la valentía de la libertad de los hijos de Dios para amar a todos sin excluir a nadie, privilegiando a los pobres, aborreciendo el odio y construyendo la paz”.
+wuranga@pagina12.com.ar</t>
+  </si>
+  <si>
     <t>Pidieron a la Legislatura rechazar el nuevo ordenamiento de bosques</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/774190-pidieron-a-la-legislatura-rechazar-el-nuevo-ordenamiento-de-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Pidieron a la Legislatura rechazar el nuevo ordenamiento de bosques. Asociaciones ambientalistas volvieron a cuestionar el mapa. Pese a las persistentes promesas de enviar la iniciativa para que sea aprobada en la Legislatura provincial, el gobierno demora su ingreso.. Las organizaciones ambientalistas Greenpece, Fundación Cebil y Red de Defensoras del Ambiente y el Buen Vivir solicitaron a los legisladores provinciales no aprobar la propuesta de actualización del Ordenamiento Territorial de Bosques Nativos (OTBN) de Salta por entender que el procedimiento con el cual se realizó implica un retroceso en lo establecido por la Ley Nacional de Bosques Nativos.
+Pese a los reiterados anuncios de envíos de la iniciativa al recinto legislativo, y de haberse presentado en diciembre del año pasado, el gobierno provincial no presentó todavía la propuesta en la Legislatura provincial para su tratamiento.
+Entre otros puntos, las organzaciones ambientalistas cuestionaron que la nueva propuesta no defina qué sucederá con las tierras desmontadas de manera ilegal durante el gobierno de Juan Manuel Urtubey, ya sea por no estar autorizadas, o por haber sido autorizadas por un decreto que violaba la Ley Nacional de Bosques Nativos.
+Recordaron que las tierras desmontadas bajo la posibilidad del proceso de “recategorización”, “deberían mantener su categoría original en la actualización del OTBN”, y en todo caso, ser restauradas. Lo cual hasta el momento no sucedió.
+Cuestionaron también que el nuevo ordenamiento permita el desmonte legal de 721.568 hectáreas, una superficie “sumamente excesiva”, aseguraron; más cuando la provincia ha tenido una alta tasa de deforestación en las últimas tres décadas.
+Asimismo, afirmaron que la zonificación propuesta no respeta el principio de no regresión ambiental, dado que permite el desmonte en zonas actualmente clasificadas en las categorías 1 (rojo) y 2 (amarillo), en las que no se puede desmontar. En este punto, sostuvieron que el mecanismo propuesto por el equipo técnico que realizó el nuevo OTBN es similar al “utilizado para permitir las recategorizaciones prediales ilegales realizadas en la anterior gestión”. “Se trata de una zonificación flexible (…), no determina claramente donde se puede y dónde no se puede desmontar”, advirtieron.
+La nueva propuesta también habla de una zona de “color marrón”, que es la categoría que permite la flexibilidad de la ubicación de los desmontes. Las organizaciones ambientalistas entendieron que la propia existencia de esta categoría no incluida en la Ley de Bosques “puede implicar decisiones arbitrarias del Poder Ejecutivo provincial y (que) no favorecen al control social de los desmontes ilegales”.
+Además, nuevamente la región de los Valles Calchaquíes queda sin categorizar, como sucede hasta la actualidad, “desconociendo los montes nativos de algarrobos, talas, chañares, y a las especies en peligro de extinción, como los ejemplares en cardones y los retamos”. Este desconocimiento de los bosques nativos “incrementa el desmonte indiscriminado, el avance del agronegocio y genera conflictos socioambientales con las distintas comunidades originarias que habitan el valle”, afirmaron.
+Al permitir que algunos desmontes puedan hacerse sobre categorías que estén en rojo o amarillo, se promueve la “fragmentación de los bosques al no garantizar áreas boscosas continas”, agregaron. También criticaron que se haya dejado fuera de la Ley la falta de relevamiento de los territorios indígenas y la falta de talleres interculturales que incluyeran a las comunidades en sus territorios.
+Mientras se espera que la propuesta de OTBN obtenga estado parlamentario en Salta, surgió lo ocurrido en la provincia del Chaco, donde se presentó y aprobó una propuesta de OTBN que tenía mucha resistencia. La Dirección de Bosques de la Nación ya observó la propuesta aprobada y sostuvo que cuenta con “graves deficiencias”, algunas de ellas parecidas a las objeciones que realizan los ambientalistas en Salta al nuevo OTBN.</t>
+  </si>
+  <si>
     <t>"Nos estamos quedando sin agua"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/773972-cuando-la-via-navegable-es-la-prioridad</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Nos estamos quedando sin agua". Consecuencias de la Hidrovía en la localidad entrerriana de Victoria. La Coordinadora del Agua agrupa a cooperativas de pescadores, organizaciones sociales, ganaderos y un amplio abanico de sectores que incluye a las organizaciones feministas. Reclaman el dragado de las bocas de los riachos que están tapadas por la acumulación de sedimentos que provoca el calado a 34 pies del río Paraná. Evalúan cortar el puente Rosario-Victoria.. La ciudad de Victoria, una localidad de 40.000 habitantes ubicada en medio del delta del Paraná, está a punto de quedarse sin agua. La Coordinadora del agua, que nuclea a diferentes organizaciones de pescadores, la sociedad civil y feministas, reclama el dragado de las bocas de los riachos tapados por el sedimento que se acumula debido al calado del río a 34 pies para hacer una vía navegable para las barcazas que trasladan las exportaciones granarias. Con bajante y sequía, la situación se hace dramática. Ante la falta de respuestas de las autoridades, evalúan cortar el puente Rosario-Victoria. “Nos estamos quedando sin agua, real”, enfatiza Ana Julia Bustos, integrante de Taller Flotante, que impulsó la Red Río Feminista.
+La Coordinadora del Agua aglutina a sectores de lo más heterogéneos. Entre quienes participan -además de Taller Flotante-, está la colectiva Orilleras, también de Río Feminista y Cuidadores de la Casa Común. “No se puede defender al mismo tiempo la vida y la ganancia sin límite de las corporaciones”, subraya Ana Fiol, integrante de Orilleras, que vive en Victoria y es la directora académica de la.Diplomatura de Extensión en "Ecofeminismos, cuerpos y territorios en peligro", de la Universidad de Mar del Plata.
+En el origen de la crisis del agua, está “primero, la Hidrovía (así se sigue llamando a la vía navegable por el nombre de la empresa que la explotó desde los años 90), y segundo, la presión de la frontera agrícola, del agronegocio, por el tema del ganado. El principal objetivo, creo que forma parte de una especie de plan, es la pampeanización”, dice Fiol, que se convirtió en ecofeminista en la defensa del Humedal, a partir de las quemas que arrasaron con la tercera parte de la superficie del humedal entre 2020 y 2021. En las islas de Victoria, que en realidad abarcan una amplia zona que llega hasta el límite norte de la provincia de Buenos Aires, la explotación ganadera es una de las actividades económicas más importantes.
+Lo que provoca el calado a 34 pies es que el cauce principal de la vía navegable funcione como un embudo de agua. Entonces, la laguna Grande y la Del Pescado, reservas de agua para abastecer a Victoria, en lugar de recibir caudal por los riachos, se vacían. En otras ocasiones, el riacho Victoria se vaciaba, pero las otras reservas tenían caudal.
+La falta de agua, antes de comprometer -en breve- la provisión de agua potable, trae la escasez de peces, una fuentes de trabajo en Victoria, donde hay alrededor de 1000 familias que viven de la pesca artesanal.
+Carolina Cabrera integra la cooperativa Frutos del Rìo, también parte de la Coordinadora, y exige que la intendenta Isa Castagnino y el gobernador Rogelio Frigerio tomen cartas en el asunto. Las propuestas que reciben no van al fondo de la cuestión: un pedido urgente para que se draguen de las bocas y se realicen de forma permanente trabajos que impidan la acumulación de sedimentos allí. El jueves de la semana pasada, hubo una reunión en el Concejo municipal de Victoria, donde la Coordinadora fue marginada, y no se dio lugar a sus propuestas.
+Desde que empezó a hacerse acuciante la falta de agua, la Coordinadora realizó manifestaciones públicas, una “pescadeada” e incesantes pedidos de reuniones con las autoridades.
+La actual gestión municipal es peronista, y la anterior, de Domingo Maiocco, era de Cambiemos. De todos modos, la capacidad de acción municipal es limitada. “La obra que hicieron para cerrar el ingreso de las bocas y encauzar no es suficiente, con obras internas para que el agua llegue directamente al riacho Victoria no solucionas todo el problema. No alcanza porque no hay perspectivas de que suba el río de acá muchos meses, ya que estamos en época de sequías, y la solución tiene que ser mucho más de fondo, porque si no esto cada vez va a ser peor”, plantea Bustos.
+Por eso es necesaria la intervención provincial. “El plan que tiene la Municipalidad no es dragar las bocas. En realidad, no tiene ningún plan porque prácticamente no puede hacer nada, está juntando firmas como si fuera una sociedad civil, pero un par de Ingenieros municipales están abriendo y cerrando algunos pasos, por los que se escurre el agua del humedal. El problema es el puente Rosario-Victoria, que sabemos que le hizo un tajo al río, a su ecosistema”, expresa Fiol sobre la ruta 174, que atraviesa el Paraná con una extensión de 60 kilómetros.
+Esta obra generó un cambio radical en las formas de vida humana y no humana. “Hay una parte del río que ha cambiado de cauce, y los pescadores están muy enojados porque les cortan el paso de los peces”, agrega.
+“Así como, con el cambio climático, nuestro planeta pasó el umbral de lo que la naturaleza puede regenerar por sí misma, me pregunto si en este humedal no estamos a punto de pasar el umbral del daño irreparable que la naturaleza después ya no puede por sí misma regeneraer, y po eso dudamos de las intervenciones a ciegas”, sostiene Fiol.
+De la Coordinadora del Agua participan pescadores artesanales, pero también algunos isleños que se dedican a la ganadería, pequeños proveedores de turismo, distintos partidos politicos, organizaciones piqueteras y feministas.
+Bustos es también docente en una escuela de la isla, en la extensa zona que pertenece a la jurisdicción de Victoria, que tiene 376 mil hectáreas de islas, un humedal. “Veníamos diciendo que la Hidrovía es un problema. Pero este año, la cosa se puso tan difícil que los pescadores no tienen agua en Laguna Grande, ni en la del Pescado, ni en el Barrancoso, no hay agua y no hay peces desde mucho antes de que empezara la preocupación por el agua potable. También les maestres de las islas empezamos a darnos cuenta antes de que no hay agua, porque es más difícil llegar a las escuelas, hay que dar un vueltón bárbaro”, sigue Bustos.
+La Laguna Grande está jaqueada porque sus bocas están complicadas. La “Del Bobo” está tapada y la Boya 500 (o “Cuatro bocas”), semitabicada. Otros 15 arroyitos que suelen llevar agua a Victoria están secos.
+El riacho Victoria es la única fuente de agua, pero es una pequeña lonja, irreconocible en relación a su caudal habitual. El nivel está muy bajo, hubo mortandad de peces (por falta de oxígeno). Las imágenes de toda la zona muestran una tierra seca, cuarteada, allí donde corrían ríos, riachos y arroyos.
+Para Bustos, es necesario que se hagan obras de infraestructura que minimicen el impacto ambiental. “La consecuencia directa de la vía troncal navegable es que se seque el humedal, que es un pulmón para todo el planeta, y que es la esponja que va a hacer que no se te inunde tu casa cuando vengan las lluvias que van a venir”, enfatiza.</t>
+  </si>
+  <si>
     <t>La trama oculta detrás de los incendios forestales en Córdoba</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/772422-la-trama-oculta-detras-de-los-incendios-forestales-en-cordob</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La trama oculta detrás de los incendios forestales en Córdoba. Negocios, cambio climático, brigadistas imputados y denuncias silenciadas. En el último tiempo se instaló una idea de nueva normalidad: año a año la provincia vive una “temporada de incendios”. ¿Qué hay detrás de la quema recurrente de tierras en una provincia donde la sequía golpea con fuerza y sólo en lo que va de 2024 ardieron 70 mil hectáreas? Las tensiones en el combate de las llamas y los reclamos al gobierno provincial.. Año a año las imágenes de Córdoba prendiéndose fuego sacuden al país durante unos pocos días. La imagen de estupor se prolonga hasta que semanas más tarde surgirá la preocupante cifra de hectáreas arrasadas por las llamas. Desde hace al menos una década se ha instalado la idea de que la provincia vive dos temporadas: la turística y la de incendios.
+Los vecinos, que todavía no pueden acostumbrarse a esta dinámica del terror que golpea a sus comunidades con focos que barren con vidas y sueños, sacan cuentas y conclusiones. Enumeran justificaciones: negocios inmobiliarios, la autovía de Punilla - una obra de 43 kilómetros de extensión en marcha hace años para la que se avanzó en el desmonte de bosques nativos ubicados en zona roja de preservación -, extracción de recursos naturales con la minería metalífera y el agronegocio picando en punta. Y aparecen agravantes: cambio climático, recortes presupuestarios y dinámicas agrarias del manejo del suelo sin control.
+Los datos parecen darle sustento a sus ideas. En 2020 se quemaron 321.688 hectáreas —convirtiéndose en el año más extremo de la memoria reciente—; en 2021, 65.740 hectáreas; en 2022, 81.544 hectáreas: en 2023, 40.803 hectáreas; y en lo que va del 2024 ya van 69.000 hectáreas quemadas.
+[H2] ¿Brigadistas imputados por apagar incendios?
+Entre la bronca y el enojo los vecinos mascullan más motivos, como el Régimen de Incentivo para Grandes Inversiones (RIGI), que da rienda suelta a la explotación minera y forestal. Y le suman lo que ocurre en el día a día, que tiene que ver con un trato muchas veces hostil de la policía local y los bomberos de la provincia hacia los brigadistas vecinales organizados de manera autónoma.
+Esto pasó durante las últimas semanas en algunos lugares de Córdoba, como San Marcos Sierra y Capilla del Monte, en el departamento de Punilla. Allí vecinos y brigadistas denunciaron cruces con la policía, con Equipo Técnico de Acción ante Catástrofes (ETAC) y con el Departamento de Unidades de Alto Riesgo (DUAR). Además de acusaciones graves sobre el mal manejo del fuego.
+“Hemos tenido situaciones con la DUAR, quienes nos intentaron hacer bajar del fuego. Están iniciando contrafuegos en lugares con mucho viento, prenden y se van. No dejan gente trabajando en el lugar ni están las aguas disponibles, y así fue como este fuego fue creciendo”, contó una brigadista de la zona a Página|12.
+Por su lado, Gabriel Brizuela, guardaparque y delegado de ATE en el Parque Nacional Quebrada del Condorito, explicó a este diario que “con la creación de estas unidades de élite (ETAC y DUAR), que han sido más marketing político que otra cosa, los cuarteles de bomberos voluntarios han sido desmantelados”. Y que esto se debe a que “el gobierno de Córdoba, que promueve un modelo extractivista” buscar armar una “puesta en escena para mostrar que se preocupa por resolver los incendios”.
+[H2] Es caso de Lalo y la agresión a los bomberos
+Hay dos casos que exponen estas tensiones de una manera contundente. Uno tiene que ver con la imputación de Lautaro "Lalo" Burgos, un vecino de San Marcos que fue detenido cuando intentaba ir con su camioneta a una zona afectada por el fuego para hacer un recambio de brigadistas en la zona y bajar nuevamente al pueblo a quienes desde hacía horas estaban trabajando.
+Su abogado, Pablo Olmos, explicó a Página|12 que hasta hoy no terminan de entender los motivos del procesamiento, y que están esperando a la indagatoria para conocer las acusaciones en una causa cuya calificación penal es “lesiones leves calificadas”. Para el defensor, “existe un encono de la policía que ante cualquier circunstancia en la que puedan verduguear a esta gente, lo hace”.
+Este no fue el único episodio de tensión con la policía. “El miércoles vieron a dos personas prendiendo fuego, llamaron a la policía y nunca llegó. Y vos perdiste la oportunidad de saber quién está prendido el fuego. Se van a encontrar con que existe un incumplimiento de deberes de funcionario público”, relató.
+Como contracara está el ataque que recibieron los Bomberos Voluntarios de Valle Hermoso por parte de algunos vecinos, quienes rompieron los vidrios del autobomba con piedrazos. Según explicó el jefe del cuerpo, Fernando López, los agresores serían “propietarios de campos que no quieren que los bomberos ingresen a la zona”. Pero la escena aparece muy vinculada con estas tensiones.
+[H2] La respuesta del Gobierno de Córdoba
+El secretario de Seguridad de Córdoba, Ángel “Lito” Bevilacqua, explicó a Página|12 que los incidentes con vecinos ocurrieron en el lugar donde apedrearon a los bomberos y que “ahí hay un grupo de ambientalistas” a los que no se los dejó trabajar “para preservar a los vecinos a los que se les pide que acaten las ordenes” en una situación de riesgo.
+Un argumento similar fue desplegado a este medio por Roberto Schreiner, bombero voluntario y vocero de la Secretaría de Gestión de Riesgo: “No se debe hacer un trabajo conjunto porque hay normas a completar, requisitos a cubrir. El índice de peligro es muy alto, es uno de los trabajos más peligrosos del mundo y nos complica todo el trabajo y la maniobra”.
+“Por supuesto que los entiendo y conozco los malestares de los vecinos, porque tengo muchos amigos. Este es un problema de cambio climático. Nos da miedo, porque los autoconvocados andan con remeras y alpargatas, y no tienen idea (de cómo trabajar). El equipo nuestro sale un palo y medio. Mirá si no vamos a tener miedo que se nos queme un vecino, porque después imputan al que está a cargo de la jurisdicción”, añadió.</t>
+  </si>
+  <si>
     <t>¿Qué se ve cuando se mira a Brasil?</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/772297-que-se-ve-cuando-se-mira-a-brasil</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    ¿Qué se ve cuando se mira a Brasil?. Opinión. Desde Río de Janeiro. Desde Río de Janeiro
+Hace poco, al hablar en la apertura de la nueva sesión de la Asamblea General de las Naciones Unidas, cumpliendo el ritual existente desde su implantación en 1948 y que asegura ese rol a Brasil, el presidente Lula da Silva ha sido enfático al cobrar de todos los países del mundo un esfuerzo sin límites para controlar la devastación del medio ambiente.
+Tal compromiso es exactamente el mismo que él se comprometió a cumplir cuando asumió la primera de sus tres presidencias, en 2003. La segunda vino enseguida, y duró hasta 2013. En 2023 inauguró la tercera, que sigue a pleno vapor.
+Es verdad que en sus dos primeros mandatos se avanzó de manera concreta. Insuficiente, por supuesto, pero concreta. En la primera presidencia de la sucesora, Dilma Rousseff, ese avance perdió fuerza. En el segundo, perdió más. Luego vino el golpe llevado a cabo por el Congreso, que la tumbó y puso en el sillón presidencial a un mequetrefe llamado Michel Temer, y todo se paralizó.
+Fue entonces que adentró en el tablado -y en el despacho presidencial – un desequilibrado y corrupto llamado Jair Bolsonaro y el escenario cambió de manera radical. Bolsonaro no sólo permitió como incentivó, y muchas veces financió con millonarios recursos públicos, a los devastadores del medio ambiente que integran el llamado “agronegocio’, y que en buena parte tienen como verdadero negocio destrozar todo que encuentran en su camino con tal de llenar sus billeteras hasta reventarlas.
+Mucho se equivocan los que dicen que lo que se ve cuando se mira a Brasil es pura devastación. Ese tiempo ya pasó. Acorde a lo que indican – y comprueban - científicos de aquí y de otras latitudes-, hoy día lo que se ve cuando se mira a Brasil son nubes, pesados nubarrones que cubren a casi 85% del territorio de ese país que tiene dimensiones continentales. Nubarrones que son pura contaminación.
+Si en agosto y septiembre hubo largos periodos en que los nubarrones cubrían cubrían 60% del espacio brasileño, en los últimos días se llegó a 80%. El calor intenso – e insólito – vivido en el pasado invierno contribuyó para alastrar las nubes que tapan el cielo.
+El domingo que viene habrá elecciones locales en los casi seis mil municipios brasileños. Y mientras los partidos políticos y sus candidatos tratan de encontrar un medio eficaz para sacar la buena parte del electorado que se encuentra indiferente a la fecha, la Justicia Electoral trata de encontrar medios eficaces para enviar urnas electrónicas y fiscales a municipios – algunos regionalmente importantes – que se encuentran al borde del aislamiento, gracias a la sequía.
+Sí, sí, es verdad que Lula da Silva tiene buenos – y son varios – datos positivos para celebrar cuando el segundo año de su tercer mandato se acerca al final. El desempleo, por ejemplo, bajó a 6,6 %, nueva marca histórica. La renta de los empleados, mientras tanto, creció. Solamente en agosto fueron registrados poco más de 230 mil nuevos puestos de trabajo formal, es decir, al amparo de toda la legislación.
+Pero hay otros datos alarmantes o, cuando menos, indignantes. Por ejemplo: pese a ser uno de los países con las mayores poblaciones carcelarias del mundo – pierde con Estados Unidos y China, y nada más – hay solamente 374 presos por crímenes ambientales, como los incendios intencionales. Conozco a dos cafés en Ipanema que, sumadas sus mesas, en las noches de sábado abrigan a más gente.
+Así de desigual es la Justicia frente a la destrucción de lo que queda de mi pobre país. Hay que ver hasta cuándo queda algo…</t>
+  </si>
+  <si>
     <t>Exportaciones y deforestación</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/771945-exportaciones-y-deforestacion</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Exportaciones y deforestación. La UE posterga exigencias de garantías a exportadores de soja y de carne. En medio de presiones de sectores de los países productores de materias primas, la Comisión Europea propondrá un retraso de su ley para aplicar normas de deforestación a nivel mundial.. En medio de presiones de sectores de los países productores de materias primas, la Comisión Europea propondrá un retraso de su ley para aplicar normas de deforestación a nivel mundial. La exigencia de certificación de que los productos agrícolas y ganaderos que se le venden a la Unión Europea no estuvieran originados en tierras desforestadas iba a comenzar a regir desde enero de 2025. La nueva fecha de aplicación sería enero de 2026.
+En el caso de Argentina, implicaba que las exportaciones de carne y soja a la Unión Europea, que rondan los US$ 4.000 millones anuales, debían quedar sometidos a la presentación de las correspondientes garantías para ingresar al Viejo Continente a partir de enero.
+Según datos de la Bolsa de Cereales de Buenos Aires, el promedio de exportaciones de carne a Europa del 2021 a 2023 fue de US$ 462 millones, el 14% del total embarcado por este sector. Mientras que en el complejo sojero, tomando el mismo período, fue de US$ 3.556 millones.
+El bloque europeo presentó un proyecto de enmienda para posponer 12 meses las normas que tienen como objetivo frenar la parte de la deforestación de la que la Unión Europea es responsable a través de sus importaciones de materias primas clave, como el café, el cacao, la soja y la carne de vacuno.
+La regulación de la UE debía entrar en vigencia el próximo 30 de diciembre y ha recibido el rechazo de distintas entidades del agronegocio argentino, que se vería afectado al tener que dar garantías de libre deforestación en sus producciones de soja y carne.
+"Celebramos la reprogramación de la implementación del reglamento europeo de libre deforestación, fruto de un enorme esfuerzo de gobiernos y cadenas de valor", dijo la Cámara de la Industria Aceitera Argentina (CIARA).
+Por su parte, la Sociedad Rural Argentina (SRA) destacó "la decisión que ha tomado la Comisión de la UE de pedir posponer y rever la aplicación de la norma 1115/2023 respecto a la deforestación agregada para los productos con destino a ese mercado".
+Si el Parlamento Europeo y el Consejo lo aprueban, la ley entrará en vigor el 30 de diciembre de 2025 para grandes empresas, y el 30 de junio de 2026 para micro y pequeñas empresas.</t>
+  </si>
+  <si>
     <t>"Deje de incentivar la violencia"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/770724-deje-de-incentivar-la-violencia</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Deje de incentivar la violencia". La respuesta de Máximo Kirchner a Milei por la falsa acusación en torno a los incendios en Córdoba. El dirigente de La Cámpora salió a responderle al mandatario, quien había acusado a la organización de tener vínculo con las quemas de miles de hectáreas. Además, la ministra de Ambiente bonaerense, Daniela Vilar, denunció el vaciamiento de los fondos destinados a manejo del fuego.. El diputado y referente de La Cámpora, Máximo Kirchner, junto a la ministra de Ambiente bonaerense, Daniela Vilar, salieron a responder a la falsa noticia difundida por el presidente Javier Milei respecto de que la organización kirchnerista había estado detrás de los incendios en Córdoba. "Deje de incentivar la violencia porque después va alguien y la aplica. Es mucho mejor sentarse hablar, discutir y dialogar", le respondió Kirchner, quien junto a Vilar recordaron la sanción la modificación a la Ley de Manejo del Fuego impulsada y aprobada durante el gobierno del Frente de Todos para limitar la especulación inmobiliaria y del agronegocio sobre las tierras incendiadas.
+"Estamos viviendo una situación crítica. Nos preocupa y también nos ocupa", marcó Kirchner sobre el incendio de más de 45 mil hectáreas de bosques en la provincia mediterránea que encontró un pequeño alivio en las últimas horas tras estar una semana bajo fuego. En tono crítico, Kirchner recordó la sanción de la modificación a la Ley de Manejo del Fuego que fue aprobada en 2020 por el Congreso, tras una año en el que los incendios habían arrasado un millón de hectáreas, en particular, en Córdoba y el Delta del Paraná.
+Vilar, diputada durante el debate de modificación de la normativa, explicó que Ley de Manejo del Fuego sienta un piso mínimo de cuidados a través del Sistema Federal de Manejo del Fuego. Destacó además que en 2022, fue modificada para ampliar los cuidados sobre otros ecosistemas, además de los bosques nativos, como bosques implatandos, humedales, pastizales y áreas naturales. La modificación marcó la prohibición de que se modifique el uso de suelo, entre 30 a 60 años, para evitar el fin especulativo de los incendios con objetivo de explotarlos a través del negocio inmobiliario o agropecuario.
+El presidente Javier Milei tiene entres cejas esa normativa, a la que mencionó en la cadena nacional de diciembre cuando anunció el aún vigente DNU 70/2023 -a pesar de que no estaba incluida- y que luego intentó modificar en la versión ómnibus de la Ley Bases, algo que quedó en el camino por la lucha de las organizaciones socioambientales. En la versión negociada de la Ley Bases, el Gobierno sí logró quedarse con las facultades para "eliminar" a gusto fondos fiduciarios, entre los que podría estar el el Fondo Nacional del Manejo del Fuego.
+"Este Gobierno congeló el presupuesto destinado para el Servicio Nacional del Manejo del Fuego y durante el primer trimestre no ejecutó ni un solo peso", denunció la ministra de Ambiente bonaerense e ironizó: "Hay cosas que el mercado no va a hacer". "No apaga incedios (el mercado), generalmente los genera", agregó Kirchner en sintonía con la ley modificada en 2022.
+En ese punto, ambos dirigentes de La Cámpora invitaron al Gobierno a debatir los 28 mil millones de pesos destinados, según el Presupuesto 2025, al Servicio del Manejo del Fuego. "Acá tenemos una buena oportunidad para mostrar que podemos construir buenos consensos en función del interés colectivo", sostuvo Kirchner y recordó que también, durante la gestión del Frente de Todos, se aprobó una ley que mejoraba el trabajo de los bomberos voluntarios.
+[H2] "Presidente, usted incentiva el odio a través de las redes sociales"
+Tras marcar las propuestas del espacio para combartir los incendios y sus causas, el dirigente de La Cámpora se encargó de responder a la falsa acusación que Milei cargó contra la organización política. "Presidente, usted es el presidente de todos y todas los argentinos... Me da mucha pena que acuse a una organización política, en este caso La Cámpora, pero que puede ser otra, depende de cómo se levante, porque eso tiene consecuencias", le señaló.
+El diputado de Unión por la Patria enmarcó la falsa acusación en el clima de violencia política que generó el intento de maginicidio contra la entonces vicepresidenta Cristina Kirchner. "Cuando usted dice esas cosas, hay gente que cree, como creyeron Sabag Montiel y Brenda Uliarte, que hay que suprimir a los que piensan diferente. Usted lo que hace es incentivar ese odio a traves de las redes y después, quizá, hay alguien que lo toma en serio y lo lleva adelante como pasó el 1° de septiembre de 2022 con Cristina."
+Kirchner le recordó a Milei que entre otras acusaciones que el mandatario lanzó por redes, lo había acusado de "urdir una trampa legislativa" para la aprobación de la ley que aumentaba los haberes jubilatorios, y que luego el presidente vetó y logró un pacto con la oposición para ratificar la impugnación en la Cámara de Diputados.
+"Usted me acusó de tramposo legislativo y dio vuelta a seis diputados que dijeron que sí y 20 días después dijeron que no. Me parece que el tramposo está en otro lugar", le sugirió el diputado de UxP e invitó a Milei a "asumir el Gobierno y dejar la cuenta de Twitter tranquila un rato".
+"Hágase cargo del día a día de un Gobierno que, realmente, nuestro pueblo la está pasando muy mal", le exigió el diputado e insistió con plantaer las disputas en instancias de diálogo político: "Nos podemos encontrar en el lugar que usted quiera. Ya Cristina le dijo que vaya al Patria y no fue... Cuando esté diga, estamos dispuestos a dar todos los debates que la Argentina necesita, sin show ni tanta parafernaria de custodias".</t>
+  </si>
+  <si>
     <t>Salta, otra vez bajo la nube de humo de los incendios en el Amazonas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/768833-salta-otra-vez-bajo-la-nube-de-humo-de-los-incendios-en-el-a</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Salta, otra vez bajo la nube de humo de los incendios en el Amazonas. Villamontes y Yacuiba bajo riesgo de propagación del fuego. El viento norte la posicionó nuevamente sobre parte de la provincia, aunque su concentración solo compromete parcialmente la visibilidad. Defensa Civil de Bolivia declaró el miércoles a municipios de Tarija, La Paz y el Beni en zona de alto riesgo. El polvo en suspensión contiene monóxido de carbono que disminuye la calidad del aire.. La nube de humo, consecuencia directa de varios meses de incendios forestales en Paraguay, Brasil, Bolivia y Perú, regresó al norte argentino ayer jueves.
+El último boletín por alerta de riesgo por propagación de incendios forestales que publicó el Viceministerio de Defensa Civil del Estado Plurinacional de Bolivia, declaró en alto riesgo a tres municipios de la jurisdicción de Tarija, entre ellos Yacuiba y Villamontes, comunas vecinas de Argentina y la provincia de Salta. Se sumaban 27 municipios del departamento Santa Cruz, 9 del departamento del Beni, y una comuna del departamento La Paz.
+Hasta ayer, la nube se extendía desde el norte de Perú hasta el noreste de Argentina, con concentraciones variables de monóxido de carbono producto de cuatro meses de incendios en el corazón del continente suramericano.
+“El humo de los incendios no solo cubre el cielo de Bolivia, sino que ha comenzado a afectar a provincias argentinas, un recordatorio de que esta crisis no conoce fronteras”, subrayó en un comunicado la organización civil Redes Chaco. Recordó que “desde 2019 Bolivia sufre consecuencias devastadoras, no solo por la destrucción de bosques, sino también por el impacto en el hábitat de más de 40 pueblos indígenas”. En ese sentido, la ong señaló que los incendios representan sobre todo una crisis humanitaria, porque las comunidades locales "sufren ante la pérdida de sus medios de vida y sus territorios”. Además, manifestó su preocupación por el impacto a largo plazo de los incendios en el cambio climático, porque liberan cantidades masivas de carbono a la atmósfera.
+En diálogo con Salta/12, Oswaldo Maillard, biólogo con lugar de trabajo en el observatorio de la Fundación para la Conservación del Bosque Chiquitano en Santa Cruz de la Sierra, recordó que los incendios forestales comenzaron en esa región del Estado boliviano en junio pasado. Agregó que los organismos nacionales indican que el fuego ya superó los 4 millones de hectáreas de bosques consumidos por las llamas, muchos situados en áreas protegidas, parques nacionales y reservas privadas. "Creemos que esa cifra será mucho mayor", anticipó. El 7 de septiembre, el departamento Santa Cruz se declaró en emergencia, y el departamento del Beni, en zona de desastre. Son dos jurisdicciones con más incendios forestales.
+Maillard explicó que, aislados primero, los focos ígneos comenzaron en zonas ubicadas entre las frontera de su país con Paraguay y Brasil, y que por el mal manejo del fuego de productores ganaderos y campesinos, rápidamente se salieron de control debido a la sequía predominante y los vientos. "Estimamos que esas quemas de cordones (la quema de pastizales) comenzaron a generar frentes entre el 6 y 11 de agosto", indicó. El biólogo aseguró que todavía permanecen activos varios frentes de fuego y que superan, en algunos casos, los 50 kilómetros de largo.
+"Tan solo en el Área Natural de San Matías", una reserva de manejo integrado en el departamento Santa Cruz, "el fuego quemó el 70 por ciento de su superficie boscosa y continúa avanzando", sostuvo. Como tiene una extensión de 2.930.000 hectáreas, Maillard estimó que el fuego ya degradó más de millón y medio de hectáreas. Detalló que hay incendios activos en áreas protegidas del norte del departamento, como el Parque Nacional Noel Kempff Mercado, el Parque Nacional Otuquis y la Reserva Municipal Copaibo, entre otras áreas boscosas.
+[H2] El humo y el ecocidio
+"La gente recién tomó conciencia del desastre ambiental cuando el humo llegó a sus casas", reflexionó el investigador boliviano. "Eso ocurrió en Santa Cruz entre finales de agosto y principios de setiembre", precisó. Durante esas semanas la nube de humo también se posó sobre territorio salteño, aunque con mayor densidad que la que reingresó ayer el jueves.
+"Las personas pierden calidad de vida y biodiversidad por los incendios. Se ha naturalizado la quema de bosques y es lo realmente preocupante", continuó. Maillard analizó que si bien la sequía persiste hace algunos años, ese fenómeno se complejiza bajo "la cultura del rebrote", porque implica un manejo del fuego orientado a acelerar el crecimiento de algunas pasturas para consumo animal.
+"El fuego se utiliza ahora para abrir territorio al agronegocio, para pasturas o cultivo", analizó por su parte el ambientalista salteño Martín Herrán. "Se trata de un fenómeno que también se observa en Salta, porque permanentemente se incendian espacios de los departamentos San Martín y Orán", argumentó, aludiendo a las jurisdicciones provinciales con mayor área de bosques o reservas forestales. El último gran incendio de 2022 consumió casi 200 mil hectáreas de la Reserva de Biósfera de Yungas. "Hace décadas que no se registran grandes incendios en Rivadavia Banda Sur y Norte, tampoco sobre el departamento Anta", recordó. "La lógica de los productores pasa por ganar tierra conquistando bosque degradado, algo que ya hicieron antes del primer Ordenamiento Territorial del Bosques Nativo" de 2008, sostuvo.
+En la misma línea, el abogado ambientalista Enrique Viale también relacionó los incendios con el modelo de agronegocios que se instaló en el Cono Sur en la década del 90. “Es transgénico y provocó el desastre de la deforestación para extender la frontera agropecuaria, principalmente para el cultivo de soja", analizó. "Ahora ese panorama se agrava por el cambio climático global", opinó. Para el activista, los eventos ígneos, recurrentes sobre distintas áreas de Argentina y Sudamérica, "son imágenes de un colapso parcializado”. “Lo peor es que nos vamos acostumbrando mientras transitamos la Era del Piroceno donde el fuego nos resulta incontrolable", cerró en referencia al concepto del historiador ambiental norteamericano Stephen Pyne.</t>
+  </si>
+  <si>
     <t>Nicolás Pino aseguró que "no hay conjeturas" sobre el atentado en la sede de la Rural</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/765440-nicolas-pino-aseguro-que-no-hay-conjeturas-sobre-el-atentado</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Nicolás Pino aseguró que "no hay conjeturas" sobre el atentado en la sede de la Rural. En una conferencia de prensa. Tras el alerta y la preocupación por el paquete explosivo recibido en la sede de la Sociedad Rural, el presidente de la entidad centenaria del agronegocio, Nicolás Pino, descartó que. Tras el alerta y la preocupación por el paquete explosivo recibido en la sede de la Sociedad Rural, el presidente de la entidad centenaria del agronegocio, Nicolás Pino, descartó que lo ocurrido haya estado relación con su "relación de empatía personal" con el presidente Javier Milei ni lo relacionó a "extremistas veganos" y "anarquistas", como hizo la ministra de Seguridad, Patricia Bullrich.
+En conferencia de prensa, Pino aseguró no tener miedo por lo ocurrido y que lo sucedido no marcará las decisiones de "cómo seguir en el día a día", aunque se mostró abierto a recibir recomendaciones y "opiniones de la gente que conoce" sobre temas de seguridad.
+La conferencia ocurrió en la sede de la SRA, ubicada en la calle Juncal al 4450, en el barrio porteño de Palermo, donde Pino estuvo acompañado por el vicepresidente primero de la SRA, Marcos Pereda, y el vicepresidente segundo, Raúl Etchebehere.
+Ante las consultas sobre el relato que intentaron imponer Bullrich y los trolls del gobierno nacional respecto de una relación con un ataque "terrorista", Pino dijo que lo sucedido recuerda a "algo de la Argentina del pasado", pero confió en que "como sociedad, seguramente no es lo que la sociedad argentina quisiera volver a refrescar".
+En cuanto a la hipótesis de que el atentado ocurrió por la cercanía de Pino con el presidente Milei, el titular de la SRA consideró: "No puedo decir que este episodio tenga referencia a la relación que tengo con el Presidente". En ese tono, intentó evitar cualquier tipo de acusación: “No tenemos conjeturas porque, realmente no sabemos o no tenemos idea. Sí son situaciones que traen a la memoria épocas pasadas".
+Pino también agradeció las llamadas de respaldo que recibió en las últimas horas, en particular de funcionarios del gobierno nacional, pero descartó tener en agenda una próxima reunión con Milei a partir de lo ocurrido y señaló que como parte de a investigación le sacaron el celular.
+Sin embargo, volvió a marcar que continuará trabajando por el sector del campo al que defiende y destacó su afinidad con el gobierno de La Libertad Avanza: "Hay una oportunidad inmensa y no la tenemos que dejar pasar. Tenemos todo para hacer las cosas que tenemos que hacer, tenemos todo para hacer lo que el mundo entero demanda."
+Más temprano, el vicepresidente primero de la SRA también había descartado las versiones de que ya acusaban a grupos veganos o ambientalistas por el atentado, ni tampoco descartó la hipótesis de que se trata de algo armado por el Gobierno en medio del debate por el decreto de fondos reservados para la SIDE.
+“Todo puede ser en esta Argentina nuestra”, dijo Pereda y señaló que “hacer especulaciones temprano, como estamos todavía, en un momento donde no tenemos ni siquiera perspectiva y sin ningún dato más fáctico desde el lado de las investigaciones, me parece un poco prematuro”.
+La investigación sobre lo ocurrido con el artefacto explosivo quedó en manos del juez Daniel Rafecas, que este viernes le tomó declaración a Nicolás Pino y a su secretaria, quien resultó herida al abrir el paquete. "Coincidieron en que no advierten móviles o motivos para lo ocurrido", informaron a la Agencia Noticias Argentinas fuentes judiciales. Desde la oficina de Rafecas dejaron trascender que se está reconstruyendo el recorrido del sospechoso.</t>
+  </si>
+  <si>
     <t>Colonialismo 2.0: el RIGI, la ofensiva extractivista de pobreza programada</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/765219-colonialismo-2-0-el-rigi-la-ofensiva-extractivista-de-pobrez</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Colonialismo 2.0: el RIGI, la ofensiva extractivista de pobreza programada. Zona de promesas (para los ultramillonarios). ¿Sabés cuántos años vas a tener cuando se termine el RIGI? Sumale treinta a tu edad. En esta nota, te contamos cómo es uno de los caballitos de batalla de la Ley Bases: un régimen extractivista que garantiza saqueo neocolonial en favor de los grandes capitales concentrados, mientras que condena a los territorios argentinos a ser nuevas zonas de sacrificios. Repasamos los antecedentes, cómo el neoliberalismo construye la idea de que el RIGI es lo mejor que le puede pasar al país y cómo será nuestro paisaje, cuando volvamos a ser el nuevo enclave colonial. Perspectivas para abordar las distintas aristas de un problema urgente que requerirá un plan de lucha a la altura.. Una de las características de las políticas neoliberales es promover la apropiación privada y explotación intensiva por el gran capital de los bienes naturales para su exportación y valorización en el mercado mundial; eso que se llama habitualmente el modelo extractivo exportador o, sucintamente, extractivismo. Así, cada una de las cuatro olas neoliberales que sufrió nuestro país trajo su cuota extractiva: la de la dictadura de Videla y Cía. con la liberalización y reprimarización económica; la del menemismo con las privatizaciones y las reformas legales pro-corporaciones; la del macrismo con la devaluación y la disminución de las retenciones y regulaciones; y ahora la del actual gobierno.
+No es una casualidad que estos sectores del gran poder económico local y trasnacional (el agronegocio, las megamineras, las petroleras, etc.) hayan sido y sean hoy en Nuestra América uno de los principales sostenes de los gobiernos de extrema derecha y de facto que vienen a profundizar aún más el despojo y la destrucción socioambiental propios de la agenda neoliberal.
+De este modo, bajo el gobierno de Milei se acentúa una ofensiva extractivista que golpea territorios y poblaciones bajo la expansión de la frontera agrícola y la deforestación, o con desplazamiento de pobladores y ataques y criminalización a las comunidades campesinas y de pueblos originarios, o con la autorización de nuevos emprendimientos extractivos. Hechos repetidos en estos meses en diferentes regiones de nuestro país. Y, claro está, acompañados las más de las veces con violencias estatales o paraestatales.
+En ese camino se inscribe la sanción de la Ley Bases -con la declaración de la emergencia, la reforma del Estado, las privatizaciones y la reforma energética- y, en particular, uno de sus apartados principales, el Régimen de Incentivos para Grandes Inversiones, o RIGI. Abarcando 65 artículos en 12 capítulos, más de un cuarto de la extensión de la Ley Bases, el RIGI condensa una serie de descomunales privilegios y concesiones al gran capital que decida invertir como mínimo 200 millones de dólares en la industria forestal, turismo, infraestructura, minería, tecnología, siderurgia, energía, petróleo y gas.
+A estos sectores el RIGI les otorga estabilidad fiscal, tributaria, cambiaria y jurídica por un período de 30 años; les permite exenciones de ganancias e IVA que reducen a insignificante su tributación; excluye a sus exportaciones de cualquier gravamen (retenciones) a partir del segundo o tercer año que es cuando fructifican estos proyectos y los habilita a importar máquinas e insumos sin pagar aranceles ni priorizar proveedores y empleo locales en detrimento de la industria y el trabajo argentinos; les asegura libre y completa disponibilidad de las divisas obtenidas por la exportación a partir del tercer año y desde el primero a las que ingresen para la inversión.
+Es decir, desfinancia al Estado, bloquea toda política de redistribución de sus hiperganancias, golpea a los territorios y poblaciones locales por su impacto socioambiental y a las pequeñas y medianas industrias; mientras facilita el saqueo de nuestros bienes comunes naturales. Y, por si todo esto fuera poco, dispone que toda controversia se dirima en tribunales extranjeros, entre ellos el tristemente famoso CIADI; un verdadero nuevo estatuto legal del coloniaje, como ha sido señalado.
+Las consecuencias de este régimen de promoción del extractivismo pueden estimarse con precisión a la luz de su pasado reciente que lejos de las falaces promesas de progreso y desarrollo solo dejó pobreza y destrucción ambiental en las provincias donde se realizó la extracción; y saqueo y crisis a nivel nacional. Su examen sería largo, pero quisiéramos, en esta ocasión, concentrarnos en cuatro cuestiones.
+Como señalamos esta ofensiva extractivista no es nueva, y tampoco lo son sus concesiones legislativas. El RIGI se parece a la Ley N° 24.196 de Inversiones Mineras sancionada bajo el menemismo en 1993 que también aseguraba tres décadas de estabilidad fiscal, tributaria, arancelaria y cambiaria a ese sector. Ya se sabe cuánto el actual gobierno admira y se inspira en los 90 del menemato, en una reedición más farsesca, y también más trágica.
+El RIGI amplia esos beneficios a otras muchas actividades. Pero no es la única novedad. La reforma constitucional del 94 otorgó a las provincias la potestad sobre los recursos del subsuelo acorde a los vientos descentralizadores que inflamaban al neoliberalismo de entonces. En contraposición, el RIGI se impone a las provincias e impide e inhabilita cualquier tributación y regulación que los gobiernos locales decidan. Un unitarismo del ajuste que se ha expresado en otros campos (y en la tensión con los ejecutivos provinciales) y que señala el mayor autoritarismo de la ola neoliberal actual.
+Por otra parte, aquella descentralización de la soberanía sobre los bienes naturales no solo favoreció a las corporaciones y las élites provinciales sino que modeló también las resistencias. Desde la victoria de Esquel de 2003 que detuvo el proyecto megaminero, un sinnúmero de conflictos y movimientos se desplegaron por todo el país en confrontación con estos emprendimientos obteniendo conquistas. En esta dirección, entre 2007 y 2010 en nueve provincias se conquistaron legislaciones que regulaban o prohibían la minería contaminante y, a nivel nacional, se sancionaron la Ley de Bosques y la de glaciares.
+La violación de estas legislaciones o su derogación posterior no opacan los logros de las resistencias que, posteriormente, se manifestaron como los “azos” contra el extractivismo en el Mendozazo (2019) y el Chubutazo (2022) ante los intentos de derogar las conquistas legislativas pasadas. El RIGI al imponer una ley nacional por sobre toda regulación provincial se yergue contra todos estos logros y contra los movimientos y poblaciones que vienen rechazando al extractivismo en el país.
+Pero este adversario principal del RIGI y del extractivismo es nominado por el propio presidente y sus comunicadores como los “ambientalistas”. Hemos escuchado cuanto esta identidad de ecologistas radicales es sindicada como responsable de impedir el progreso, el desarrollo y el bienestar. Una campaña que construye su estigmatización y criminalización. Como todo en este neoliberalismo rancio se trata de un discurso antiguo. Construye una falaz oposición entre la resolución de las necesidades económicas y sociales y la afectación del ambiente, entre lo social y lo ambiental.
+Falaz porque como sabemos las olas extractivistas pasadas, particularmente cuando se privó de toda política redistributiva, solo trajeron más miseria y deterioro ambiental. Allá están las cifras de la pobreza y la indigencia de las llamadas provincias mineras. Falaz también porque promueve una idea de los territorios como vacíos de poblaciones, economías, cultura y vida, como de pura naturaleza, y resignifica las resistencias asociándolas a un ambientalismo bobo.
+Resuenan todavía las palabras de Patricia Bullrich y tantos dirigentes y casta afirmando que en Chubut, en la meseta patagónica, no vive nadie, solo hay guanacos. Allí están los vecinos, los maestros, los trabajadores de la salud y de otros sectores, los pueblos originarios, los campesinos, los pequeños y medianos productores y comerciantes, los científicos, los técnicos, dando vida a los “azos”.
+Las injustificadas concesiones al gran capital que promueve el RIGI merecen una última reflexión. Se fundan en razones ideológicas; las de este anarcopitalismo que extrema la teoría del derrame y llega a considerar verdaderos héroes a los grandes empresarios, a los milmillonarios del neoliberalismo. Da cuenta también de otras razones más menudas, las urgencias prácticas de un plan de ajuste sin fin que requiere de modo apremiante el ingreso de divisas para evitar su colapso. Y no debemos olvidar que ese fue el final de las tres olas neoliberales anteriores.
+[1] Profesor e investigador del Instituto de Estudios de América Latina y el Caribe, F.Soc., UBA.</t>
+  </si>
+  <si>
     <t>Las retenciones agrarias firmes como el cepo cambiario</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/764876-las-retenciones-agrarias-firmes-como-el-cepo-cambiario</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Las retenciones agrarias firmes como el cepo cambiario. Entre enero y agosto, el aporte de los Derechos de Exportación a la recaudación fue 4,7%. En un contexto donde la recaudación tributaria viene creciendo por debajo de la inflación y de cara a un menor aporte proveniente del impuesto PAÍS a partir de septiembre, no parece sencillo pensar en una reducción o eliminación de las retenciones. La promesa de bajar las retenciones que Milei le hizo al campo, apenas días atrás en la Rural, se aleja de la realidad al concebir que la recaudación tributaria total viene creciendo por debajo de la inflación y que en paralelo disminuirá el aporte proveniente del impuesto PAÍS. Inclusive en 2025 este último será cero, de acuerdo a otras promesas del Gobierno. Si el “déficit cero” es intocable el Gobierno debería poder explicar cómo reemplazará los ingresos por retenciones, que han sido históricamente relevantes para las cuentas fiscales.
+Pese a que la liquidación del agro en agosto fue buena, la recaudación fiscal por Derechos de Exportación cayó: pasó de representar 4,7 por ciento de la recaudación total en julio a 3,7 por ciento en agosto, según cálculos del especialista en agronegocios, Javier Preciado Patiño, en su cuenta de la red X.</t>
+  </si>
+  <si>
     <t>Atanor: clausura, despidos y audiencia judicial</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/762029-atanor-clausura-despidos-y-audiencia-judicial</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Atanor: clausura, despidos y audiencia judicial. Contrapunto entre los ambientalistas, el sindicato y la empresa. La comunidad de San Nicolás teme por una ola de despidos en la química. Conflictividad por una posible relocalización.. A cinco meses de la explosión de uno de sus tanques de atrazina, un químico altamente contaminante, que impregnó el aire en un radio de al menos tres kilómetros, la planta de Atanor, que nunca reabrió, comenzó a enviar telegramas de despido y crece la preocupación entre los trabajadores. Este viernes 23 tendrá lugar una audiencia judicial clave para definir el futuro de la fábrica.
+Consultado por Buenos Aires/12, el secretario general de la regional local de los trabajadores de la industria química, Ricardo García, desmiente que la empresa tenga interés en reducir su operación por caída de ventas o para recontratar personal bajo una legislación más ventajosa.
+"Veníamos trabajando mucho, hasta había personal contratado, que es el paso previo a ampliarse", afirma, y agrega que "desde marzo hasta hoy pagaron el 75 por ciento de los salarios. Es probable que ahora, si no se abre, haya que rediscutir el porcentaje a la baja".
+Sin embargo, fuentes con acceso al expediente, en manos de la jueza penal Luciana Díaz Bancalari, sostienen que la empresa nunca tuvo vocación de reabrir y que, a lo largo de estos cinco meses, más allá de las declaraciones públicas en contrario, Atanor incurrió en sucesivas demoras y maniobras dilatorias.
+En paralelo, la empresa, que cuenta con unos 150 trabajadores, abrió un programa de retiros voluntarios, al que sólo adhirieron una decena. Como antecedente reciente, entre 2017 y 2018, Atanor cerró dos de sus plantas, en las localidades bonaerenses de Munro y Baradero y despidió a casi 150 trabajadores. Entonces, desde el sindicato los acusaron de dejar de producir para importar. Ese mismo año, meses más tarde, la firma amplió y reinauguró su planta de San Nicolás.
+[H2] La gota que rebalsó el vaso
+La explosión a principios de este año, lejos de ser un hecho sorpresivo, fue el último eslabón de una larga cadena. A lo largo de toda la mañana del 20 de marzo, la atrazina diseminada causó irritación de ojos y garganta de gran parte de la comunidad nicoleña. Además, Atanor fue condenada por causarle un daño irreparable al río Paraná, al volcar en sus aguas efluentes sin tratar.
+La planta de Atanor en San Nicolás arrastra conflictos y demandas ambientales desde 2015. Ese año, fueron los propios trabajadores los que denunciaron la contaminación, primero ante el sindicato y luego, a través de sus familiares, ante la opinión pública. Con el correr de los siguientes meses y años se fueron movilizando y sumando a las denuncias los vecinos de los barrios linderos (Química, Belgrano, Obrero y San Isidro), entre los que la prevalencia del cáncer es mucho mayor que en otras zonas.
+Actualmente, la posición del sindicato es que la planta de atrazina permanezca cerrada pero se habilite la producción en los demás sectores, porque el proceso de relocalización de esa planta podría demorar tres, cuatro o más años.
+La relocalización es un reclamo histórico de los vecinos, ya que con el crecimiento demográfico de la ciudad, la planta quedó en medio de una zona residencial. Pero, a la vez, es apenas la mitad del problema. Por el tipo de actividad que desarrolla, Atanor debería estar localizada, sí o sí, dentro de un parque industrial, donde los controles e inspecciones son habituales y exhaustivos.
+La realidad de Atanor es que produce agroquímicos y fertilizantes, que provee al agronegocio, especialmente en toda la zona núcleo. Las perspectivas del sector para el futuro no son alentadoras: el precio internacional de la soja está en mínimos históricos y el Gobierno nacional no cede a los reclamos, ni de devaluación ni de eliminación de retenciones.
+Las partes (el sindicato y la empresa, por un lado, y las organizaciones ambientalistas querellantes, por otro), están citadas para una audiencia en el juzgado de Díaz Bancalari este viernes. Todos los consultados entienden que ese será el día D, para definir si Atanor vuelve a producir.
+[H2] Parque Aguiar
+El de Atanor no es el único conflicto ambiental en San Nicolás. En 2020, el Ejecutivo que entonces encabezaba Manuel Passaglia, hermano del actual intendente, comenzó una serie de obras en el área natural protegida Parque Rafael Aguiar, frente a la costa del Paraná, en abierta violación del plan de manejo del parque, que tiene rango de ordenanza municipal, con el objetivo de facilitar el acceso vehicular y concesionar las playas.
+La Comisión Nicoleña por el Ambiente (CONA) denunció los hechos ante la Justicia provinical y la demanda fue escalando hasta llegar a la suprema corte, que meses atrás declaró la clausura y ordenó retirar todas las máquinas y equipamiento vial.
+Según la CONA, las aguas a esa altura están contaminadas por efluentes cloacales, que el municipio vuelca directamente en el río, ya que la planta de tratamiento no está en condiciones por falta de mantenimiento.</t>
+  </si>
+  <si>
     <t>Vale decir</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/758764-vale-decir</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Vale decir. . . El interior profundo
+Entre 1979 y 1984 Richard Avedon abandonó los retratos glamorosos de estrellas de Hollywood que había inmortalizado hasta entonces para meterse en el oeste profundo, su mitología y su gente, cincelada a fuerza de trabajo y de una vida que no siempre les sonreía. Pero una vida verdadera. Esa es una de las influencias a las que volvió el fotógrafo Tony Valdez para su serie En el sur americano, que se exhibe desde el próximo sábado hasta el 18 de noviembre en el Museo Provincial de Fotografía Palacio Dionisi de Córdoba. “Comencé a fotografiar gauchos en las fiestas patronales cordobesas con la intención de dejar registro de esa gente que va desapareciendo a medida que avanza el agronegocio, pero que todavía existe en el interior profundo”, explica Valdez sobre el origen de su indagación. “Utilicé primero como base un fondo de estudio, que luego se transformó en una tela blanca más portátil. Pero no sólo eso cambió. Porque también decidí sumar al proyecto a otras personas que conviven con esos gauchos y quizás son más invisibles aún”, agrega. Otra de las singularidades fue la pregunta sobre si las fotos debían ser a color o en blanco y negro. No se trata, obviamente, de una indagación meramente técnica sino sobre todo, del impacto expresivo de cualquier decisión que tomara. Y al final decidió incorporar ambas posibilidades para crear una tercera, mestiza, que atraviesa conceptualmente el conjunto de estas imágenes. “En el proceso de edición empecé a dudar sobre una cuestión que en las épocas analógicas se resolvía antes de comenzar un proyecto pero que la era digital permite abrir el juego antes de tomar la decisión final. Así fue como en el proceso de pruebas y más pruebas, una copia monocroma se superpuso sobre la misma foto en color, y esa combinación me gustó, me pareció interesante”, relata. Confiesa, además, que para esa decisión volvió a aquella frase de Godard que dice: “No es de donde tomamos las cosas, lo que importa es hacia donde las llevamos”. Valdez cree, justamente, que casi nada es original pero sí distinto. Y es la búsqueda que privilegió.
+Una pasión de otro mundo
+El ilusionista británico-israelí Uri Geller se hizo famoso en los años setenta por doblar cucharas con la mente y otras proezas que le valieron luego un lugar destacado en realities de todo el mundo. También le interesaban los fenónemos extraterrestres. Con el tiempo se retiró y abrió un museo personal donde exhibe memorabilia de aquella época. En ese museo, a partir de ahora, habrá un par de lentes de marco redondo que pertenecieron a John Lennon, a quien Geller no duda de calificar como “un gran amigo”. La subasta la llevó a cabo Catherine Southon Auctioneers de Chislehurst y Geller pagó 40 mil libras por este objeto icónico. Geller argumentó que, más allá del valor histórico, los lentes tenían un significado único para él “porque los lentes son como una extensión del alma de la persona” y por la “relación especial” que tuvo con el artista. “Vivíamos muy cerca el uno del otro en Nueva York en los años 70 y él cambió mi vida. Nos conocimos porque ambos creíamos en los extraterrestres y a él le fascinaba mi colección de objetos alienígenas”, explicó Geller, de 77 años. Y añadió como si tal cosa: “Una vez me regaló un huevo que le había sido dado un ser extraterrestre”. Estos lentes tienen, también, una historia interesante detrás porque Lennon se los regaló a un fan durante una recorrida por Abbey Road mientras cumplía años. Los lentes estaban sobre el piano, el pibe no pudo evitar agarrarlos y Lennon le dijo “son tuyos, feliz cumple”.
+Pollitos sin fuga
+El robo de cables para vender luego el cobre es una de las tantas postales tétricas de nuestros días (sí, es una práctica peligrosa). Pero no son cosas que sólo ocurran en los países donde gobiernan señores con peluca. Desde Japón llega la noticia de que alguno tuvo la idea de robarse todos los cables en una granja de pollos. Ocurrió en Shibukawa, prefectura de Gunma, en una madrugada, estos días. Según la policía, faltaron 170 metros de cable valorados en cinco millones de yenes (o sea, unos 33 mil dólares). Los cables conectaban la instalación y un transformador de energía especial para que el asunto marche. El corte, sin embargo, provocó que se detuviera el aire acondicionado y, en consecuencia, casi un millón de pollos murieron. Estas instalaciones funcionan con energía solar pero eso, necesariamente, incluye una estructura que requiere este tipo de cables. Como los japoneses no tienen problemas de seguridad, tampoco tienen sistemas de alarmas sofisticados y estos robos han comenzado a ser sistemáticos. En esta historia se mezcla el uso de energías renovables, tan en boga en un mundo que se está quedando sin recursos, con la milenaria costumbre de comer pollos a mansalva. Pero donde a los japoneses se le queman los cables, es con el asunto del robo ya que no entienden por qué alguien haría algo así en una de las tres economías más importantes del mundo. He aquí un argumento para otra historia distópica.
+Detrás de la máscara
+La sala entera contuvo la respiración. Y no porque Ian McKellen hubiera salvado una vez más a la Tierra Media del temible Sauron. El actor, mundialmente conocido como Gandalf, de la saga El señor de los anillos, esa noche se cayó del escenario, demostrando que los dioses también son falibles. McKellen, de 85 años, estaba interpretando a Faltstaff en una puesta de Enrique IV de Shakespeare, en Londres, dirigido por Robert Icke. Se sabe, Falstaff es un caballero tan voluminoso como desaliñado y Señor de las Tabernas. Así que McKellen aparecía de ese modo en escena, con una barba descuidada y una melena cuya desprolijidad Gandalf, que mantenía su estilo elegantísimo aunque se le vinieran encima mil espíritus oscuros, hubiera desaprobado. Pero bueno, el asunto es que McKellen se cayó del escenario y a partir de ahí decidió no continuar la obra. Pero el actor es un grande que mantiene su sentido del humor contra viento y marea y sabe cómo darle una vuelta de tuerca incluso a la tragedia. Primero, apareció en un video bailando con gracia junto a su amigo Anthony Hopkins para demostrar que un tropezón no es caída. Pero además, ahora registró, a través de una serie de fotos maravillosas, el momento donde se corta pone en manos de un experto para que le corte el pelo y la barba. Toma tras toma, Faltsaff desaparece mientras McKellen vuelve a tomar su lugar. Es una auténtica deconstrucción del physique du rôle y en consecuencia, una lección sobre el modo en que los actores y actrices viven en un borde peculiar entre la realidad y la ficción. Ahora, McKellen se ha convertido una vez más en el elegante actor británico que se pasea por Limehouse, la zona donde vive en East London. Claro que en su sonrisa pervive algo de Faltsaff y de cada personaje que viene interpretando desde los años sesenta. Porque podrá perder el pelo pero nunca sus deliciosas mañas.</t>
+  </si>
+  <si>
     <t>Emergencia alimentaria: "La peor violencia es el hambre"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/754999-emergencia-alimentaria-la-peor-violencia-es-el-hambre</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Emergencia alimentaria: "La peor violencia es el hambre". Organizaciones campesinas, sociales y gremios protestaron frente a la Exposición Rural. Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, mov. Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, movimientos sociales, sindicatos y organismos de derechos humanos hicieron una actividad de la campaña “La peor violencia es el hambre”. Esta campaña tiene un doble planteo: hacer visible la emergencia alimentaria que atraviesan miles de familias, por el alto precio de los alimentos, y advertir que se trata de una situación que coexiste con el agronegocio como modelo productivo principal para el campo, concentrador de la economía, expulsor de la población rural y contaminador de la tierra.
+“La peor violencia es el hambre” es una iniciativa del premio Nobel de la Paz, Adolfo Pérez Esquivel. “Estamos haciendo un llamamiento a unirnos frente a este panorama en el que el gobierno le ha quitado los alimentos a los comedores y merenderos comunitarios, y en el que además de mantener cautivos los alimentos hace gala de hostigar y perseguir a quienes se organizan”, dijo frente al ingreso a la Rural Leonardo, hijo del titular del Serpaj. La propuesta tiene más de una faceta, ya que además de difundir conceptos en favor de la soberanía alimentaria, busca también dar un respaldo a las organizaciones sociales, hacerles de paraguas en la persecución que vienen sufriendo de parte del gobierno.
+La Unión de Trabajadores de la Tierra armó un un verdurazo en el lugar de la protesta, mientras que los sindicatos de la CTA Autónoma hicieron una radio abierta. A su vez, los movimientos sociales Libres del Sur y Barrios de Pie instalaron gazebos para mostrar las actividades de control nutricional que realizan en las zonas más postergadas.
+De fondo, a pocos metros de estas actividades, la gente que se acercaba para visitar la 136ª Exposición Rural hacía la cola de ingreso. Pasado el mediodía estuvo en la Exposición Rural la ministra de Capital Humano, Sandra Pettovello, acompañada por el vocero presidencial, Manuel Adoni, sin cruzarse con los manifestantes.
+[H2] Cero políticas para la Agricultura Familiar
+Pamela Mackey es una de las despedidas del Instituto Nacional de Promoción de la Agricultura Familiar, Campesina e Indígena. “El cierre del INAPCI dejó 900 personas sin trabajo y desatendidas a 250 mil familias que trabajan la tierra a lo largo y ancho del país y que recibían capacitación técnica y apoyo financiero. No sólo los programas nacionales, sino también proyectos de líneas internacionales quedaron discontinuados. Como nos despidieron de un día para el otro, incluso quedaron rendiciones de fondos sin terminar”.
+En nombre de los despedidos también habló Leonor Cruz, otra de las cesanteadas y secretaria de Género de la CTA Autónoma. “El campo no son estos poderosos que siembran soja para alimentar a los chanchos de Europa. El Instituto tiene tres décadas de historia en las que nuestra gran lucha fue que los productores rurales no abandonaran su lugar, que no fueran expulsados para terminar hacinados y empobrecidos en las villas”.
+El Instituto había sido creado en 1993 y desde entonces tuvo a su cargo programas de fomento de la agricultura familiar durante 31 años, pese a lo que sus trabajadores no llegaron a ser incorporados nunca a planta permanente. Al ser su relación laboral la de contratados, despedirlos resultó fácil: no les renovaron los convenios.
+Durante la presidencia de Mauricio Macri el organismo ya había sufrido despidos masivos, que los trabajadores pudieron revertir. Ahora, organizados en la Asociación de Trabajadores del Estado, mantienen el reclamo de ser reincorporados.
+“Estamos discutiendo el derecho a la alimentación, pero no a cualquiera sino a una sana, segura y soberana”, señaló ante los concurrentes Carlos Carballo, docente de la Cátedra Libre de Soberanía Alimentaria de la Facultad de Agronomía de la UBA. El profesor indicó que no es sostenible un país en el que, como sucede en Argentina, el 90 por ciento de la población es urbana: “muchas de las experiencias que se hicieron en los últimos años para impulsar una nueva ruralidad deberían se transformadas en políticas públicas. Necesitamos que los habitantes empiecen a preguntarse quiénes y cómo producen los alimentos, algo que no viene pasando a pesar de las luchas que venimos dando”.
+Nahuel Levaggi, de la UTT, advirtió que con el gobierno libertario “hubo un vaciamiento de las políticas de apoyo a los productores de alimentos. Han pasado heladas, tornados y no llegó una sola ayuda”.
+Silvia Saravia, de Libres del Sur, habló en nombre de los movimientos sociales. "El modelo que defiende la Sociedad Rural es el de un extractivismo que deja campo arrasado. Nuestras organizaciones discuten, en cambio, la necesidad de ir hacia la soberanía alimentaria. No es un planteo idealizado, sino que tiene como base a experiencias que se vienen haciendo hace muchos años y que el Estado debe impulsar. Debemos preguntarnos por que hay tantos millones de personas viviendo en los conurbanos, en situación de pobreza, ¿ese es el modelo que queremos? Necesitamos construir, desde las raíces, otro modelo de país".</t>
+  </si>
+  <si>
     <t>&lt;h1&gt;"La peor violencia es el hambre"&lt;/h1&gt;</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/2024/07/26/h1la-peor-violencia-es-el-hambreh1/</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    &lt;h1&gt;"La peor violencia es el hambre"&lt;/h1&gt;. &lt;h1&gt;"La peor violencia es el hambre"&lt;/h1&gt;. . Por Laura Vales
+Con un feriazo frente al predio de la Exposición Rural, los trabajadores del Instituto de Agricultura Familiar -cerrado por el gobierno de Milei con 900 despidos-, junto a pequeños productores, movimientos sociales, sindicatos y organismos de derechos humanos hicieron una actividad de la campaña “La peor violencia es el hambre”. Esta campaña tiene un doble planteo: hacer visible la emergencia alimentaria que atraviesan miles de familias, por el alto precio de los alimentos, y advertir que se trata de una situación que coexiste con el agronegocio como modelo productivo principal para el campo, concentrador de la economía, expulsor de la población rural y contaminador de la tierra.
+“La peor violencia es el hambre” es una iniciativa del premio Nobel de la Paz, Adolfo Pérez Esquivel. “Estamos haciendo un llamamiento a unirnos frente a este panorama en el que el gobierno le ha quitado los alimentos a los comedores y merenderos comunitarios, y en el que además de mantener cautivos los alimentos hace gala de hostigar y perseguir a quienes se organizan”, dijo frente al ingreso a la Rural Leonardo, hijo del titular del Serpaj. La propuesta tiene más de una faceta, ya que además de difundir conceptos en favor de la soberanía alimentaria, busca también dar un respaldo a las organizaciones sociales, hacerles de paraguas en la persecución que vienen sufriendo de parte del gobierno.
+Leer más acá
+(c) 2025 Página 12</t>
+  </si>
+  <si>
     <t>¿Esto no tiene límites?</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/754257-esto-no-tiene-limites</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    ¿Esto no tiene límites?. . El multicondenado Jorge Eduardo Acosta (¿se preguntará por qué no lo invitaron a la reunión con los excursionistas de La Libertad Avanza que fueron a Ezeiza?) gatillaba como afirmació. El multicondenado Jorge Eduardo Acosta (¿se preguntará por qué no lo invitaron a la reunión con los excursionistas de La Libertad Avanza que fueron a Ezeiza?) gatillaba como afirmación, no como interrogante, “esto no tiene límites”. “Esto” era lo que el Grupo de Tareas 3.3 perpetraba minuto a minuto en la ESMA. Lo que la dictadura militar genocida perpetró minuto a minuto en nuestro país.
+Al hilvanar acontecimientos, hechos, declaraciones de funcionarios estatales, figuras políticas, empresas de comunicación y activistas del pulgar sobre pantallas, referidos a los crímenes dictatoriales –y no solo-, volvió aquel lema del jefe de Inteligencia de la ESMA. Volvió como ¿interrogante o afirmación? ahora que los gobernantes, con cada decreto, cada ley aprobada a fuerza de extorsión, claudicaciones y traiciones de supuestos opositores, en cada arenga, reiteran que están dedicados a acabar con parte de la población vía despidos, persecución y hambre, a demoler el Estado, los derechos individuales y colectivos, la soberanía, a sacrificar lo humano en el altar del “mercado” y el “déficit cero”…
+El batallar a favor de la impunidad de los genocidas no lo inauguraron los seis diputados de LLA con su visita a Ezeiza. Son años de prédica de los editoriales de La Nación; de los Reato y afines recitando la doctrina de los excesos, y/o la de los dos demonios en programas de TV; de los defensores de los dictadores para impugnar los juicios, hostigando a testigos y sobrevivientes en las audiencias y desde el anonimato de “las redes”. Julio López desaparecido en septiembre de 2006 es la prueba más extrema… Insuficiente enumeración de un trayecto con tácticas diversas, caras visibles que se renuevan, y un propósito compartido: que la impunidad de los dictadores –militares y sus socios civiles- sirva como antecedente y sostén para las represiones de hoy que el “protocolo Bullrich” habilita.</t>
+  </si>
+  <si>
     <t>La ley Bases contra los humedales</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/751738-la-ley-bases-contra-los-humedales</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La ley Bases contra los humedales. En la provincia de Santa Fe hay alarma por un punto del Pacto de Mayo y el negacionismo ambiental. “Sospechamos que para ampliar las fronteras agropecuarias, irán por los humedales y bosques", declararon los ecologistas.. Desde Rosario
+El punto número siete del Pacto de Mayo, que garantiza el compromiso de las provincias argentinas para avanzar en la explotación de los recursos naturales del país, mantiene en alerta a las organizaciones ambientales de la ciudad de Rosario y la región.
+Desde la Multisectorial Humedales emitieron un comunicado donde cuestionan la posición del gobernador, Maximiliano Pullaro, por acompañar con su firma una política “que permitirá vender humedales y bosques” del territorio provincial. “Lamentablemente, el cuarto intento de poder sancionar una Ley de Humedales ha quedado trunco otra vez y no tenemos una herramienta legislativa que nos pueda proteger en ese sentido”, señaló Ivo Perugino, referente de la multisectorial, en diálogo con Página/12. “Creo que se vienen retrocesos, pero va a depender de la capacidad de articulación que tenga la sociedad, que hoy no está muy receptiva a la problemática ambiental”, agregó el ambientalista César Massi a este medio.
+[H2] El papel del gobernador Pullaro
+El 9 de julio, el presidente Javier Milei convocó a todos los gobernadores a la firma del Pacto de Mayo en Tucumán. El cónclave tenía como fin que los mandatarios provinciales adhieran a diez consignas “refundacionales” que puedan sostenerse en el tiempo, independientemente de las gestiones. No todos los gobernadores asistieron. En el caso de Pullaro, desde el primer momento supeditó su participación a la incorporación de dos temas que considera clave: la educación y la producción del interior del país. Como el primero de los puntos fue contemplado, finalmente el mandatario asistió al evento. Pero el séptimo punto es el que despierta la preocupación de las organizaciones ambientalistas de la ciudad: “El compromiso de las provincias argentinas de avanzar en la explotación de los recursos naturales del país”.
+En ese marco, este viernes la Multisectorial Humedales de Rosario emitió un comunicado donde sostienen que ese apartado “corre de un soplo” cualquier discusión que pueda darse respecto a la protección del territorio para adaptarse a un contexto de cambio climático. “Desconocemos qué recursos naturales están en la mira en la Provincia de Santa Fe, pero sospechamos que, a fin de ampliar las fronteras agropecuarias, irán por los humedales y los bosques, los cuales cumplen importantes funciones ecosistémicas y albergan biodiversidad. Habrá más quemas, más contaminación, más destrucción”, describen.
+[H2] El negacionismo climático
+Desde ese espacio sostienen que el gobierno es “negacionista del cambio climático” y quiere volver a imponer mitos que ya fueron derribados por la comunidad científica. “El punto siete del Pacto de Mayo, junto al DNU (70/2023), el RIGI de la Ley Bases y el proyecto del gobernador de Entre Ríos, Rogelio Frigerio, para la creación de una agencia que administre y enajene bienes del estado, incluido el amplio sistema de humedal del Delta del Paraná, es el peor escenario posible para afrontar el presente y el futuro a corto plazo”, añadieron.
+Ivo Peruggino consideró que las medidas que viene impulsando el gobierno “son un peligro socioambiental” para toda la región. “Se van a habilitar muchísimas más actividades productivas que son incompatibles con la idea de conservación a la cual tenemos que ir de forma urgente porque el contexto nos obliga. A la par de eso, vemos que se viene dando una suerte de persecución y desprestigio contra todas las asambleas territoriales y de los activistas socioambientales”, expresó y agregó: “Lo que más nos preocupa es que ese saqueo se profundice en nuestra región y en nuestro país”.
+El activista recordó que la provincia de Santa Fe tiene una extensión de bosques y humedales muy valiosa en la zona del delta del Paraná y en los bajos submeridionales. Uno de los temores de la organización es que, habilitados por un clima de época, quienes generaban los incendios intencionales en la zona de islas entre 2020 y 2022, vuelvan a la carga con su objetivo y las localidades de la región vuelvan a sufrir el humo y la problemática ambiental que genera.
+[H2] Mucho que perder
+“Tanto este año como el que viene, se prevé otra bajante del río Paraná y eso hace que queden superficies de humedal descubiertas y que se quieran usar para tierras productivas. Lamentablemente, el cuarto intento de poder sancionar una ley de humedales ha quedado trunco otra vez y no tenemos esa herramienta legislativa que nos pueda proteger. Y tenemos mucho miedo de que vuelva a darse ese intento por correr la frontera del agronegocio, que busca llevar cada vez más vacas a las islas para sembrar más soja en el continente”, analizó. “En Santa Fe, como en el resto del país, hay mucho para perder si estas cosas avanzan. Y lamentablemente avanzan de la mano de un discurso negacionista”, añadió.
+Peruggino se refirió a la intención del gobierno de Entre Ríos de avanzar en la venta de terrenos pertenecientes al humedal, que podrían afectar una zona que impacta también en la provincia de Santa Fe: “El gobernador de Entre Ríos presentó un proyecto para hacer una agencia del Estado, en el cual les incluyen casi 200 mil hectáreas de humedal del delta del Paraná. Que eso quede en manos de privados sería malísimo para los ecosistemas, pero también para los habitantes de la región”.
+[H2] Antiecologismo expreso
+Según Massi, ya era preocupante cuando el año pasado la situación ambiental “quedaba relegada” en función de lo político electo-electoral primero y de lo económico después. En el contexto actual, la preocupación escala un nuevo peldaño: “Ahora hay una decisión de cargarse todo lo que tenga que ver con protección ambiental y tenerlo como bandera política. Se plantea una suerte de enemistad con el ambientalismo y se habilita pasar por arriba todo lo que se pueda destruir para traer dólares”.
+En declaraciones a Página/12, el activista ambiental evaluó que además de un nivel de agresividad “muy fuerte”, directamente se baja una línea de confrontación discursiva contra el ambientalismo, que consideró peligrosa: “Todo eso se da en un contexto donde más que nunca tenemos que discutir la cuestión ambiental, porque los hechos lo marcan. Venimos de dos años donde la cosecha falló, primero por la sequía y después por la chicharrita. El país viene perdiendo un montón de guita por tener vulnerabilidad climática, porque la mayoría de nuestras divisas entran por el campo. Entonces es necesario discutir cómo cuidamos eso”.
+Massi remarcó que en Santa Fe puede llegar a darse una pelea “con un poco más de igualdad” en relación a provincias y localidades más chicas, donde las comunidades quedan indefensas ante el poder económico y político. “Ya vimos los problemas que tuvimos para defender los humedales, cuando hubo que sentar en una misma mesa a cuatro gobernadores y todo se complicaba. Creo que se vienen retrocesos, pero va a depender de la capacidad de articulación que tenga la sociedad, que no está muy receptiva a la problemática ambiental”, manifestó.</t>
+  </si>
+  <si>
     <t>Cambiar la salud de nuestro suelo</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/750898-cambiar-la-salud-de-nuestro-suelo</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Cambiar la salud de nuestro suelo. Marcela y sus hermanos apuestan por la agroecología. En Baigorrita, entre Junín y General Viamonte, la organización Cambio Rural practica nuevos cuidados sobre nuestra tierra para comer y vivir mejor.. “Tres veces al día necesitamos un agricultor y uno no toma conciencia de quién es tu agricultor, quién está produciendo tu alimento o quién está cultivando el alimento que tenés en el plato. Si el campesino, el agricultor desaparece, ¿en manos de quién queda nuestra alimentación? ¿Quién decide aquello que comemos? Hay mucha desinformación sobre los alimentos sanos, sobre qué es lo orgánico, qué es la agroecología y el impacto que tienen en la salud", afirma Marcela Calderon, agricultora agroecológica y parte de la organización Cambio Rural.
+Hace doce años, en Baigorrita, entre los campos fértiles entre Junín y General Viamonte, en la provincia de Buenos Aires, Marcela y sus hermanos emprendieron un camino transformador hacia la agroecología. Después de más de una década dedicados al agronegocio convencional y gestionando 2.500 hectáreas con tecnología avanzada, decidieron cambiar radicalmente su enfoque hacia prácticas más sostenibles y respetuosas con el medio ambiente.
+"Veníamos de un modelo donde todo giraba en torno al aumento de hectáreas y el uso intensivo de maquinaria y químicos", explica Marcela. "Pero nos dimos cuenta de que este modelo no solo afectaba nuestra calidad de vida, sino también la salud del suelo y la biodiversidad que lo habita".
+La decisión de cambiar surgió a partir de un accidente que tuvo su hermano con un tractor. “Nosotros hacía treinta años que estábamos haciendo siembra directa y no era sustentable. El suelo estaba cada vez peor, sin estructura, sin vida. Necesitábamos cada vez más insumos para lograr que rinda lo mismo. Nos dábamos cuenta de que estábamos perdiendo calidad de vida. Mi hermano se iba a las seis de la mañana y volvía a las doce de la noche. La dedicación cada vez era mayor, el modelo de la agricultura agroindustrial o convencional nos esclavizaba cada vez más. Y empezamos a tomar conciencia del efecto de los agroquímicos sobre la tierra", afirma Marcelo.
+Se pusieron a investigar de forma autodidacta metodologías agrícolas alternativas. Desde la permacultura hasta la agricultura orgánica y biodinámica, exploraron métodos que promueven la producción de alimentos, la regeneración del suelo y la biodiversidad.
+Marcela relata que en lo orgánico a veces no busca desarrollar una conciencia plena sobre la producción y el cultivo, mientras que en la agroecología, hay una preocupación por la salud humana. Si en el agronegocio se tiene en cuenta lo físico y lo químico, en la agroecología se toma en cuenta lo biológico. “En el agro tradicional se agregan tres fertilizantes: nitrógeno, fósforo y potasio. Como si las plantas se alimentaran solo de esos tres ingredientes. Si yo a una persona, le doy leche, huevo y carne, no va a estar bien nutrida porque no se nutre nada más que de esos tres alimentos. Hay muchísimos más. Hoy a los alimentos les está pasando eso. Hay una deficiencia en las vitaminas y los minerales que cada alimento tiene porque el suelo está degradado, el suelo ya no está equilibrado. Las plantas extraen, extraen, extraen. Y si uno no recompone o no reequilibra, no regenera la vida del suelo. Por ende, los alimentos van a estar deficientes a nivel nutricional”, afirma.
+La transición implicó la eliminación total de químicos de síntesis en sus 81 hectáreas cultivadas. Adoptaron prácticas como la siembra directa y el cultivo asociado, reduciendo así el impacto ambiental y aumentando la eficiencia del uso del suelo. Además, incorporaron ganadería ovina con pastoreo racional, adaptado a sus sistemas agrícolas. Tienen como valores fundamentales el respeto hacia la naturaleza, sus ciclos y leyes, con el fin de obtener productos genuinamente saludables y naturales desde su origen. Este enfoque no solo promueve la soberanía alimentaria y el arraigo, sino que también fomenta una relación más armoniosa con el entorno. El proyecto no se limita a la producción agrícola. "Con la marca "El Huerto Interior", vendemos harina integral agroecológica y corderos pastoriles.", afirma Marcela.
+“Un suelo sano, equilibrado, funciona igual que el sistema inmunológico de una planta, de un animal y del individuo. Si nosotros tenemos el sistema inmunológico sano, si el sistema inmunológico de la Tierra está sano, está completo, está íntegro, las plantas van a estar sanas, los alimentos y los animales van a estar sanos. Es una cadena. La salud está en la comida. La salud de la comida está en el suelo. Y si el suelo no es saludable, no tenemos salud. No hay salud”, afirma. Además, optar por alimentos agroecológicos de temporada y locales es una manera de respaldar el comercio justo y responsable, concluye Marcela.
+[H3] Grupo Cambio Rural
+Hoy en día forman parte del Grupo Cambio Rural, donde comparten su experiencia y conocimientos para inspirar a otros agricultores a seguir su camino hacia prácticas más amigables con el medio ambiente. “Solemos hacer una reunión para invitar a posibles agricultores que les llegue a interesar o que estén interesados para que lo puedan vivenciar. Uno puede ver el cambio del suelo, cómo se va regenerando, cómo se va descompactando, cómo se va vivificando. Desde la pandemia se incrementó el interés de otros productores. Los primeros años para nosotros fueron difíciles, estábamos solos en esta zona y bueno, éramos medio los hippies raros”, recuerda.
+“Ya somos varios los que estamos cultivando de esta manera, que en realidad es como se hacia antes, en la época de mis abuelos, no es magia. Lo que pasa es que estamos cooptados por el otro modelo, donde está todo resuelto y cuesta cambiar un modelo productivo. Es un gran desafío. El tema es tener claro si estás a favor de la vida o a favor de la muerte. Si vos estás a favor de la vida, todo va a estar acorde a eso y la naturaleza te va a compensar. No hay una recompensa económica, hay una recompensa en calidad de vida, en buen vivir. En este modelo no pasa por lo económico, sino pasa por la salud tuya y de los otros", afirma.
+Con el grupo, priman los principios de asociación y cooperación, entre ellos realizan visitas mensuales rotativas, para promover una mirada colectiva sobre los problemas que puedan presentarse. Hoy en día, son doce productores. Se organizan para hacer compras comunitarias, comparten sus experiencias y colaboran con los CEPT de la zona. "Estamos comprometidos no solo con la producción de alimentos, sino también con educar y crear conciencia sobre la importancia de una agricultura consciente y sostenible", concluye Marcela, convencida de que la labor que realizan genera cambios tangibles.</t>
+  </si>
+  <si>
     <t>Fugadores y recuerdos del futuro</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/750289-fugadores-y-recuerdos-del-futuro</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Fugadores y recuerdos del futuro. Vicentin, cuatro años después de una resolución del fiscal Gerardo Pollicita. Este lunes 8 de julio de 2024 se cumplirán cuatro años de una resolución judicial que determinaba la fuga de millones de dólares de parte de un grupo de directivos del consorcio Vicentin en complic. Este lunes 8 de julio de 2024 se cumplirán cuatro años de una resolución judicial que determinaba la fuga de millones de dólares de parte de un grupo de directivos del consorcio Vicentin en complicidad con funcionarios nacionales ubicados en el Banco Central de la República Argentina, en el Banco Nación y en el gobierno nacional del ingeniero Mauricio Macri. Un robo descarado al pueblo argentino que hasta el día de hoy permanece impune y que remarca la triste costumbre de hacerle pagar a las mayorías las fiestas privadas de los delincuentes de guantes y cuellos blancos.
+El 8 de julio de 2020, el fiscal federal en lo Criminal y Correccional Federal número 11, Gerardo Pollicita hizo público un documento que muestra la facilidad con la que algunos directivos de la empresa Vicentin accedían a los créditos del Banco Nación. Dice el texto en su página 24: “El 26 de noviembre de 2019, los funcionarios del Banco de la Nación Argentina -Bled, Tortul, Testa, Moschini y González- en menos de una hora -entre las 10.38 y las 11.17- y a pedido de los empresarios Herman Vicentin y Máximo J. Padoán, le concedieron a la firma Vicentin un nuevo crédito por la suma de USD 6.000.000”.
+Herman Vicentin nació el 21 de septiembre de 1937 y en 2018 recibió el premio “Konex” como referente del empresario dedicado al agronegocio. Máximo Padoán, uno de los hijos del “Beto” Padoán, tuvo la organización de su segundo casamiento en manos de la conocida “weeding planner” Bárbara Diez, esposa de Horacio Rodríguez Larreta. Herman Vicentin y Máximo Padoán, aquel 26 de noviembre de 2019, en solamente 39 minutos se llevaron seis millones de dólares del Banco Nación, del pueblo argentino.
+39 minutos les llevó a los directivos de Vicentin quedarse con 6 millones de dólares del pueblo argentino.
+No todos somos Vicentin. El contraste con el tiempo que deben esperar miles y miles de familias en Argentina explica la impunidad del privilegio en un país de robusta desigualdad.
+En realidad, durante noviembre de 2019, la empresa tuvo 28 créditos por más de 105 millones de dólares. Una obscenidad.
+Dice el escrito del fiscal federal: Lo expuesto demuestra que durante el mismo período en el que la firma Vicentin tenía deudas vencidas con el Banco de la Nación Argentina, el dinero para cobrar dichas deudas se encontraba a resguardo del banco en dos cuentas específicamente creadas ante un eventual incumplimiento, sin embargo los funcionarios del Banco de la Nación Argentina a pedido de los empresarios, decidieron liberar 43.449.104.966 pesos – 41.592.204.966 pesos de la cuenta de cobranzas en el exterior y 1.856.900.000 pesos de la local – movilizándolo, hasta el día 3 de diciembre inclusiva, hasta una cuenta corriente de la firma Vicentin que no poseía ninguna limitación, lo que le permitió a estos últimos disponer de los miles de millones de pesos que garantizaban los préstamos, burlando de tal forma, toda posibilidad de cobro por parte de la entidad bancaria (...) una vez que los fondos se encontraban en la cuenta corriente de la firma en la misma entidad, los titulares de la firma Vicentíi usaron parte del dinero para pagar gastos de la firma -tales como proveedores, impuestos, salarios- pero otra parte significativa de los fondos eran transferidos mes a mes a 'cuentas propias' que la firma mantenía en otros bancos, por lo que el destino final de estos últimos resulta de momento desconocido”.
+El dinero del pueblo argentino iba a parar a una cuenta que tenía Vicentin sin “ninguna limitación” y desde allí, los señores empresarios hicieron 1.418 transferencias a cuentas propias entre agosto de 2019 y enero de 2020. Dinero del banco público para cuentas propias. Un robo descarado al pueblo.
+En la página 50 Pollicita informa: “De los casi de 800 millones de dólares y más de 2.000 millones de pesos que el Banco de la Nación Argentina a lo largo del período agosto a diciembre de 2019 tuvo en las cuentas en garantía de las deudas de Vicentin, al momento en que se efectuó la afectación de los fondos sólo se hallaron en las cuentas apenas poco menos de 8 millones de dólares, lo que demuestra la magnitud del daño ocasionado al patrimonio del Banco de la Nación Argentina”.
+Parecen los escritos de la década del treinta del siglo pasado, cuando los bienes del pueblo eran ultrajados desde el interior del Estado. Son, sin embargo, hechos del pasado reciente que tienen alto impacto en miles de familias en el presente.
+Detrás de estos números y afirmaciones, la cuestión pendiente es resolver si siempre las mafias le ganarán a la democracia. Una respuesta que, otra vez, dependerá del protagonismo de los que son más en estos atribulados arrabales del mundo.
+Diputado Provincial de Santa Fe por el Frente Amplio por la Soberanía.</t>
+  </si>
+  <si>
     <t>La economía popular, en la agenda de la CIDH</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/749168-la-economia-popular-en-la-agenda-de-la-cidh</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La economía popular, en la agenda de la CIDH. Entrevista a Javier Palummo, relator especial de la Comisión Interamericana de Derechos Humanos. Javier Palummo es relator especial sobre Derechos Económicos, Sociales, Culturales y Ambientales de la CIDH. De paso por Buenos Aires participó de una serie de charlas con trabajadores de la economía popular. Su relatoría busca poner en agenda los derechos de estos trabajadores, que en la región son el 50 por ciento de la fuerza laboral.. Javier Palummo, relator especial de la Comisión Interamericana de Derechos Humanos (CIDH), estuvo en Buenos Aires, donde participó de una serie de debates sobre los derechos de los trabajadores de la economía popular. La CIDH ha decidido darle prioridad a este tema en su agenda por una razón de peso: hoy, en la región, más del 50 por ciento de los trabajadores se ganan la vida en la economía informal. El relator, en esta gira que incluyó también a Paraguay y Uruguay, compartió aquí paneles con cartoneros y vendedores ambulantes y habló de la necesidad de que los estados avancen en el reconocimiento de los trabajos de la economía informal.
+--En Argentina conocemos a la CIDH por su trabajo en derechos humanos; ¿qué interés tiene la Comisión en cuestiones que son de carácter más económico o de reconocimiento de derechos sociales?
+--La Comisión tiene dos relatorías especiales, una sobre libertad de expresión, que es conocida, y otra más reciente, una Relatoría Especial sobre Derechos Económicos, Sociales, Culturales y Ambientales. Esta Relatoría está a mi cargo desde septiembre del año pasado y hemos elaborado un plan de trabajo, que tuvo la aprobación unánime de la CIDH; el tema de los derechos de los trabajadores de la economía informal está incluido en ese plan de trabajo.
+--¿Por qué decidieron ponerlo en agenda?
+--Hay varias razones. Primero, porque estamos en una región donde según los datos de la OIT, en promedio el 50 por ciento de la fuerza laboral se encuentra en la economía informal. Ese es el promedio general, con países en los que el 70 u 80 por ciento de la economía es informal. Esto implica dos problemas: uno es que estos trabajadores suelen no contar con derechos laborales, no tienen protección social, seguridad social, etc… y estamos hablando de millones de personas, que se han incrementado luego de la pandemia de COVID-19; por otro lado, es una población que se desempeña sin condiciones de dignidad. Y no se trata de algo marginal, sino de porcentajes muy importantes en la economía de nuestros países. Otro tema especialmente relevante a considerar es que hay una correlación entre la imposibilidad de los Estados de tener servicios públicos de calidad, como buenos hospitales públicos o un buen sistema de educación pública, y la existencia de este alto porcentaje de la economía que se mueve en el ámbito de la informalidad.
+--¿Por qué?
+--Porque esas economías informales no tributan, no cotizan, no permiten mejorar la capacidad recaudadora de los estados. En un país donde el 80 por ciento de la actividad económica se desarrolla en el ámbito de la informalidad, los recursos para sostener sistemas educativos, de salud o políticas culturales se encuentran claramente mermados. De ahí viene la importancia de poner este tema en la agenda y tratar de generar avances, desde una perspectiva que no sólo tenga en cuenta las estrategias de desarrollo de los países, sino también la garantía de los derechos humanos de las personas trabajadoras.
+--¿Qué panorama encontró en Argentina?
+--Quiero aclarar que no estoy en el marco de una visita de trabajo de la CIDH, sino en una visita académica, en la cual he participado sólo en actividades de carácter público donde se han tratado estos temas. Compartí paneles con trabajadores de la economía informal y así tuve la oportunidad de escuchar sus posiciones y preocupaciones. Hecha esa aclaración, puedo decir que las preocupaciones son similares a las que se manifiestan en otros países de la región, pero con un ingrediente especial, que es que en la Argentina los trabajadores de la economía informal tienen sus organizaciones, lo que no se ve en otros lados. Por eso, en algún sentido, aquí hay una discusión más avanzada, sobre todo teniendo en cuenta las conquistas de derechos que han ocurrido aquí.
+--Cuando habla de la necesidad de poner en agenda los derechos sociales de los trabajadores de la economía informal, ¿a qué derechos se refiere?
+--El principal problema que tienen los trabajadores de la economía informal es que no son reconocidos como trabajadores. Eso implica que en muchos casos no se les reconoce el derecho a asociarse, a reunirse y generar colectivos para la defensa de sus intereses, un tema muy básico. El primer paso es es ese, reconocer que se trata de personas que están trabajando y que por lo tanto tienen que tener determinado nivel de cobertura. La otra gran dificultad es que la vulneración de los derechos de los trabajadores de la economía informal afecta a grupos que han sido históricamente discriminados: las mujeres, los migrantes, las personas afrodescendientes también, esto es clarísimo en prácticamente toda la región. Algunas actividades no necesariamente están vinculadas a la economía informal, pero sí a la economía del cuidado, como por ejemplo el trabajo doméstico, lo que se llama de casas particulares. Lo mismo ocurre con los trabajadores de plataformas digitales, donde las personas migrantes encuentran la forma más rápida de obtener ingresos en ciudades que no conocen, en las que no tienen redes sociales, donde pueden inclusive no cumplir los requisitos documentales necesarios para una inserción laboral formal.
+--Los Estados, ¿cómo pueden reconocer derechos a estas formas de trabajo en las que no existe un empleador y que son formas de subsistencia?
+--Creo que los Estados, en primera instancia, deben lograr que haya más formalización, reducir la informalidad. Eso es lo primero porque es lo que va a posibilitar avanzar en otros sentidos. Si estuviéramos hablando de un porcentaje muy bajo de la población, uno podría pensar en otro tipo de alternativa, pero cuando hablamos de que en toda la región el 50 por ciento de la fuerza de trabajo se desempeña en la economía informal, necesariamente tenemos que pensar de que existen intereses detrás de que haya mucha informalidad. Eso, como cuestión fundamental. Ningún país es sostenible, desde el punto de vista de su capacidad recaudatoria para brindar derechos económicos, sociales, culturales y servicios públicos de calidad, mientras tenga porcentajes tan altos de su economía en el ámbito informal.
+--¿Es un problema que se resuelve con mayores controles o la salida es de otro tipo?
+--Yo creo en un enfoque de protección social: que haya una mirada centrada en la dignidad de las personas desde la perspectiva de la inclusión, que le permita al Estado obtener nuevos recursos para garantizar mejores servicios. Estamos hablando de ese tipo de enfoque, con la mirada no centrada en formas de control sino en lógicas de reconocimiento.
+El plan de trabajo de la Relatoría tiene cuatro prioridades o ejes: el primero es Cambio Climático y Protección del Medio Ambiente (su impacto en relación al derecho a la salud, al trabajo, al derecho al agua, a la seguridad alimentaria). El segundo eje es Empresas y Derechos Humanos, que aborda actividades empresariales como las industrias extractivas, el agronegocio, las industrias tecnológicas y la alimentaria. El tercer eje es Políticas Fiscales, con la mira puesta en la necesidad de contar con sistemas más redistributivos, y el cuarto eje es Democracia y derechos, con el planteo de que para que existan democracias fortalecidas se necesita de políticas públicas que garanticen los derechos económicos, sociales, culturales y ambientales.</t>
+  </si>
+  <si>
     <t>Seguridad alimentaria o festín empresario</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/747658-seguridad-alimentaria-o-festin-empresario</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Seguridad alimentaria o festín empresario. Brutal transferencia de ingresos en favor de las alimenticias. Mientras crece la indigencia, se registraron ganancias siderales por parte de un puñado de empresas oligopólicas de alimentos.. La Argentina, y en general el mundo, vive en tiempos de una frazada cada vez más corta. Las decisiones de los gobiernos no pueden satisfacer a todos los sectores. Pero los datos estadísticos nacionales hablan de una decisión clara en favor de un sector.
+Mientras que el informe del Observatorio Social de la UCA estima que en el primer trimestre de este año la indigencia llegó al 17,5 por ciento (era de 9,6 por ciento en el tercer trimestre de 2023), el último informe de la Comisión de Valores arroja que en este mismo período las ganancias de las megaempresas alimentarias se sextuplicaron.
+Según el informe Ganadores y Perdedores en los primeros meses del gobierno de Milei elaborado por Instituto de Pensamiento y Políticas Públicas (IPyPP), si se suman las tres empresas alimentarias que cotizan en bolsa (Arcor, Mastellone y Río de la Plata), las ganancias acumulan 75.632 millones de pesos en términos operativos (solo la actividad principal), con un incremento de 598 por ciento.
+Si se incorpora la ganancia financiera, participación en sociedades y el pago del impuesto a las ganancias, entre otros conceptos, el resultado neto es de 201.336 millones de pesos, con un crecimiento de 1.331 por ciento. El informe no incluye a otras grandes empresas alimentarias que no cotizan en bolsa, como Molino Cañuelas, Quilmes, Molfino, Mondelez o Nestlé.
+El incremento de las ganancias de las megaempresas alimentarias es mucho mayor que el registrado por las empresas del rubro bancario (945 por ciento) o hidrocarburífero (790 por ciento) y que el promedio de las 15 empresas analizadas (831 por ciento).
+Todas están por encima de la inflación, que en ese mismo período fue del 273 por ciento. Ni que hablar respecto del salario privado, que cayó 12,1 por ciento en términos reales o que el público, que cayó 26,9 por ciento. Al mismo tiempo, el Salario Social Complementario (Potenciar Trabajo) se redujo un 40,9 por ciento.
+[H2] Sálvese quien pueda
+“La Argentina que viene es una Argentina muy desigual, de exclusión, violencia, del sálvese quien pueda. Desde el sector cooperativo bregamos para que haya una enorme reflexión sobre la enorme crisis social que esto genera. Nosotros somos la economía que incluye y hoy vemos un panorama negro. La libertad, si no tiene inclusión ni equidad, no es libertad, decía Alberdi”, opina Ricardo Garzia, secretario de la Federación de Cooperativas Federadas (Fecofe), que integra la Mesa Agroalimentaria Argentina.
+“Los precios de insumos para la producción (semillas, plantines, gasoil o nylons) se han disparado por la devaluación y por la especulación de las tres o cuatro empresas que manejan el 100 por ciento de estos materiales. Esto va acompañado de problemas climáticos, como inundaciones, con el agravante de que las familias no tienen la posibilidad de reinvertir en la producción y se están retirando del campo o están endeudadas a tasas altísimas. El reflejo de esto es la disparada de los precios de la verdura”, describe Zulma Molloja de la UTT.
+¿Por qué unos ganan tanto y otros tan poco? ¿Es el libre mercado? El estudio del IPyPP es claro al respecto: “Los exorbitantes excedentes económicos que cosecharon las compañías alimenticias durante el primer trimestre fueron fruto del desmantelamiento de los mecanismos regulatorios vigentes hasta el año pasado, permitiendo a los grandes operadores del mercado captar amplios márgenes de rentabilidad por vía de la fijación oligopólica de precios en los alimentos que conforman la canasta básica familiar”.
+[H2] Herencia monopólica
+Para muestra hace falta un botón. La empresa Molinos Río de la Plata tiene el 79,4 por ciento de la oferta de fideos secos en grandes supermercados, el 82,1 por ciento en harinas (junto a Molinos Cañuelas) y está entre las tres empresas que concentran el 90,5 por ciento de las ventas de aceite (junto a Aceitera General Deheza y Molinos Cañuelas).
+Entre las analizadas por IPyPP, fue la empresa que experimentó el mayor aumento en las ganancias operativas en el primer trimestre de 2024. Además, su rama de agronegocio Molinos Agro tuvo un resultado operativo de 1918 millones de pesos con un 189 por ciento de incremento.
+El índice de Precios en Origen y Destino (IPOD), elaborado por el sector de Economías Regionales de Cámara Argentina de Mediana Empresa (CAME), muestra que luego de la devaluación de diciembre de 2023, los agroalimentos multiplicaron su precios por 3,5 veces del campo a la góndola. La participación del productor explicó el 26,3 por ciento de los precios de venta final.
+No es casualidad que Molinos Río de La Plata halla multiplicado sideralmente sus ganancias mientras que los productores deben cerrar sus emprendimientos. Tampoco sorprende que el recientemente fallecido Goyo Perez Companc tuviera la cuarta fortuna familiar más grande de la Argentina, valuada en 4.200 millones de dólares, según la revista Forbes.
+Si la ley Bases finalmente sale refrendada en Diputados, la familia Pérez Companc pagará menos impuestos por bienes personales y podrá repatriar sin demasiados costes el dinero en cuentas del exterior producto de la evasión o elusión fiscal.
+[H2] Desalojo
+“Es una bomba de tiempo. Esto hace que las familias productoras dejen los campos y se vayan a engrosar los bolsones de pobreza de los asentamientos. Lo que queda es un campo cada vez más concentrado y más especulativo, solo para exportación. Es un problema cíclico que se repite en gobiernos como éste, donde las políticas están claramente orientadas a que esto suceda”, explica Agustín Suárez, también de UTT.
+Según el último informe de la UCA, en las ciudades donde el “mercado” desplaza a los pequeños productores de alimentos, la inseguridad alimentaria alcanza al 20,8 por ciento de los hogares y al 32,2 por ciento de los niños, niñas y adolescentes.
+*Licenciado en Economía de la Universidad Torcuato Di Tella y master en Periodismo de la Universidad del País Vasco.</t>
+  </si>
+  <si>
     <t>Los dólares que nunca llegaron</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/746515-los-dolares-que-nunca-llegaron</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Los dólares que nunca llegaron. Devaluación de diciembre, saldos exportables y reservas. El Banco Central no está teniendo los resultados que esperaba en materia de acumulación de reservas.. El Banco Central no está teniendo los resultados que esperaba en materia de acumulación de reservas. Tras una megadevaluación en diciembre y una recuperación de la cosecha y los saldos exportables tras la sequía de la temporada anterior, se esperaba un saldo importante en la cuenta corriente externa para esta altura del año. Adicionalmente, el impacto de la recesión se está sintiendo en la forma de una abrupta caída en las importaciones. Sin embargo, tras un desconcertante inicio de mandato, con la devaluación más grande en décadas, el efecto cambiario fue un bálsamo para las reservas del Banco Central apenas por un lapso corto que pareciera agotarse.
+Las bondades de la devaluación son efímeras y el ministro Caputo debe saberlo, pero se confió o “hicieron mal las cuentas”, como dicen en la jerga, porque especuló fuerte a la posibilidad de empalmar el enflaquecimiento del efecto cambiario con la liquidación de una cosecha que sería récord considerando la sequía de 2023 y que el campo tendría menos espalda para especular en torno a la liquidación. Sin embargo. las cosas no salieron como lo esperado.
+El especialista en agronegocios Javier Preciado Patiño lo pone de esta manera: “La cuestión de fondo es que el Gobierno esperaba un aluvión de dólares para esta época del año, porque creía que con el dólar a 850 pesos explotaba la cosecha, como en 2002. Pero en verdad, el agro venía con un dólar exportador de 650 pesos, con lo cual la devaluación no fue gran cosa. Igualmente, en diciembre se vendió mucho, gracias a las exportaciones entraron dólares. Pero después el crawling peg (devaluación pautada anticipadamente del dos por ciento mensual) y los insumos, con costo en dólares más impuesto PAIS, redujeron los márgenes del negocio. Entonces, ¿se vende?, sí, pero más o menos dentro del promedio”.
+En fino, observa que la molienda de soja evoluciona favorablemente con volúmenes mensuales promedio en torno a los 4 millones de toneladas, similares a los de 2019/2020. “Igualmente, considerando que la cosecha este año alcanzó un nivel cercano a 50 millones de toneladas y que las importaciones temporales de porotos son las segundas en importancia --en abril y mayo, el 20 por ciento de lo procesado vino de afuera--, la trituración podría estar por encima de este nivel”, advierte.
+Los volúmenes de exportación del complejo soja también están en línea con el mayor tonelaje exportado en los últimos diez años. Así lo expone un reciente informe de la Bolsa de Cereales de Rosario, que muestra que en mayo se enviaron al exterior más de 5,1 millones de tonelada de soja, por encima del promedio de los últimos diez años para el mes (4,6 millones de toneladas) y 60 por ciento más que el año pasado.
+Asimismo, estimaron que para la segunda mitad de junio, se deberían cargar buques con 2,8 millones de toneladas del complejo soja. De concretarse esas proyecciones, junio finalizaría con 4,6 millones de toneladas embarcadas, también por encima del promedio de los últimos diez años.
+Sin embargo, las compras netas de divisas de parte del Banco Central que tocaron un techo de 3.300 millones de dólares en diciembre y en abril, estuvieron lejos de superarse en mayo: mes que cerró en torno a los 2.500 millones de dólares y –como difundió Indec la semana pasada- con un superávit comercial de 2.656 millones más que relevante para el mes en curso, vinculado a la fuerte recesión interna y a la caída de las importaciones (29,6 por ciento interanual medidas en cantidades).
+Para Sergio Chouza, titular de la consultora Sarandí, la canaleta de las reservas es el “dólar blend” exportador (habilita a liquidar el 20 por ciento de exportaciones por el -CCL) y los esfuerzos que hace el Gobierno por sostener las cotizaciones del Mep y CCL. De acuerdo a sus estimaciones, cerca de 16.000 millones de dólares se usarán este año para mantener a raya los dólares financieros. “Ese monto equivale a casi la totalidad de divisas que destinó la administración Fernández en sus cuatro años para contener a los dólares financieros”.
+La deuda con importadores ocupa otro lugar importante en la canaleta de las reservas. “El grueso de las compras netas de divisas por parte del Banco Central entre diciembre y abril se dio por la postergación del pago de importaciones, más allá de que las importaciones cayeron fuerte. El Central pagaba poco menos del 20 por ciento del monto involucrado, de modo que acumulaba una deuda con importadores cercana a 13.000 millones de dólares, ese fue casi exactamente el monto total de divisas que adquirió en esos cinco meses. Luego ese ratio fue subiendo, pero en la primera mitad del año se pagó menos del 40 por ciento del total importado. De acuerdo a la agenda que planteó el ministro Caputo, en estos meses se cancela en torno al 70 por ciento de esa deuda, sumado al pago a organismos internacionales, arrojan una ecuación con poco margen para el Gobierno”, describe Pedro Gaite de Fundación de Investigaciones para el Desarrollo Económico (FIDE).
+Pese al discurso grandilocuente de este Gobierno, ni Javier Milei vino a hacer lo que nunca nadie se animó, ni su programa económico es aplaudido por los mercados ni mucho menos la comunidad internacional. El propio FMI viene manifestando hace tiempo la inconveniencia del regimen cambiario exportador, además de exigir acelerar el crawling peg.
+Los especialistas consultados por Página/12 coinciden en señalar que el tipo de cambio “permanece lo suficientemente competitivo”, al menos mientras la economía mantenga estos niveles de contracción que hacen disminuir las importaciones. A la vuelta de una lejana esquina, un modelo económico anclado en un crecimiento virtuoso parece esperar toparse con el mismo fantasma de 70 años atrás: la restricción externa o insuficiencia de divisas.</t>
+  </si>
+  <si>
     <t>Recorrido por la vida empresarial de Gregorio Pérez Companc</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/744778-recorrido-por-la-vida-empresarial-de-gregorio-perez-companc</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Recorrido por la vida empresarial de Gregorio Pérez Companc. "Goyo" era el cuarto hombre más rico de la Argentina. Este viernes falleció a los 89 años Gregorio Pérez Companc, referente del empresariado argentino en los últimos 50 años.. Este viernes falleció a los 89 años el empresario Gregorio Pérez Companc, dueño de la alimenticia Molinos Río de la Plata y de la petrolera Pecom, una de las primeras dedicadas al segmento upstream (exploración y explotación) y downstream (refinación, comercialización y distribución) de la industria.
+“Goyo” era el cuarto hombre más rico de Argentina, según la revista Forbes. Su talla se compara con la de pocos nombres, protagonistas del mundo de los grandes negocios del país. Pérez Companc cultivaba un bajo perfil y su fortuna se distribuye entre seis de sus hijos.
+Gregorio Pérez Companc fue uno de los empresarios más destacados de la Argentina. Construyó en 1968 el conglomerado energético Pérez Companc, uno de los contratistas más importantes de la petrolera estatal YPF. En 1980, el holding siguió su expansión con el ingreso al rubro de la construcción, a través de la empresa Sade.</t>
+  </si>
+  <si>
     <t>Paraguay: ¿un reflejo de la Argentina que se viene?</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/740859-paraguay-un-reflejo-de-la-argentina-que-se-viene</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Paraguay: ¿un reflejo de la Argentina que se viene?. Cómo funciona el modelo que Javier Milei intenta replicar. Cuenta con una presión tributaria y una inflación baja. Estas aparentes ventajas se contrarrestan con un 70% de informalidad laboral y precariedad salarial de la mayoría de la población. El presidente de Paraguay, Santiago Peña, señaló recientemente que "Milei intenta replicar el modelo económico de Paraguay". Esta afirmación ha generado un interés creciente sobre las similitudes entre ambas economías. Para comprender más sobre este modelo, consultamos a dos economistas paraguayos destacados: Fernando Masi, director e investigador de CADEP (Centro de Análisis y Difusión de la Economía Paraguaya) y a Luis Rojas, investigador del Centro de Estudios Heñói y miembro fundador de SEPPY (Sociedad de Economía Política de Paraguay).
+[H3] Claudia Sheinbaum gana las elecciones en MéxicoLa ola importadora que llegó a los alimentosCristina Kirchner le respondió a Milei: "Teorizar en los canales de televisión es muy fácil, gobernar es otra cosa"
+Masi comenzó destacando la interacción entre la presión tributaria y la informalidad laboral en Paraguay, desafiando la noción convencional de una relación lineal entre ambos factores. Analizó cómo la falta de correlación directa entre impuestos y formalización del empleo puede enraizar la situación económica en una complejidad que requiere un análisis más matizado. A partir de los comentarios del economista, se evidencia que la menor presión tributaria en Paraguay, que ronda el 10 por ciento (con una alícuota del IVA del 10 por ciento), no logra generar una mayor formalidad en la economía, contradiciendo las expectativas de la corriente libertaria en Argentina.
+En términos de inversión extranjera, Masi identificó varios obstáculos que enfrenta Paraguay para atraer inversiones significativas al país. Si bien resaltó la existencia de incentivos fiscales y otras medidas para fomentar la inversión extranjera, enfatizó la necesidad urgente de mejorar la infraestructura y la seguridad jurídica para atraer inversiones sostenibles y a largo plazo. A pesar de los esfuerzos realizados, la inversión extranjera directa apenas fluctúa entre el 1 por ciento y el 1,7 por ciento del PBI, lo que constituye un valor bajo. Además, se señala la apertura de zonas libres de impuestos como una estrategia para continuar atrayendo inversiones, lo que sugiere que, desde esa perspectiva, parece que nada es suficiente.
+Rojas también destaca que la corrupción y la impunidad son endémicas en Paraguay, especialmente en el sistema judicial, donde el poder político y económico ejercen una influencia desproporcionada. Se resalta la estrecha relación entre ambos poderes, lo que dificulta la separación y perpetúa un círculo vicioso de poder. Estos factores representan importantes obstáculos para el desarrollo económico y social del país.
+También se abordó la complejidad de la economía paraguaya en términos de desigualdad social y desarrollo humano. Masi analizó cómo la economía “exitosa” del país no necesariamente se traduce en una distribución equitativa de la riqueza ni en un aumento significativo del bienestar social para todos los ciudadanos. Destacó las deficiencias sanitarias, que quedan expuestas cuando los paraguayos utilizan los sistemas sanitarios de Argentina o Brasil, evidenciando la necesidad de mejorar los servicios básicos para toda la población.
+Rojas también examina el modelo económico paraguayo, caracterizado por un fuerte enfoque en el agronegocio y la exportación, así como una dependencia significativa del Estado en sectores como la obra pública y el transporte. Según Rojas, esta dependencia ha generado una burguesía empresarial que está estrechamente ligada al Estado, lo que dificulta la implementación de políticas que promuevan una competencia más equitativa en el mercado y una distribución más justa de la riqueza.
+En cuanto a la relación con Argentina, Rojas expresa preocupación por las políticas económicas que apuntan hacia la privatización y la desregulación, y destaca la importancia del comercio fronterizo para ambas naciones. También comenta sobre la influencia del modelo paraguayo en Argentina y las diferencias entre ambos países en términos de desarrollo industrial y estabilidad macroeconómica. Estos aspectos reflejan la complejidad de las relaciones económicas entre Paraguay y Argentina y sugieren la necesidad de una cooperación más estrecha para abordar los desafíos comunes.
+[H2] Retroceso paraguayo
+Un ejemplo claro del retroceso paraguayo es la red ferroviaria, que había sido uno de los países precursores en desarrollarla y que terminó por desmantelarla. Esta situación representa una pérdida significativa en términos de infraestructura y conectividad, lo que limita las oportunidades de desarrollo económico y social en el país.
+A este escenario decadente podemos sumarle el continuo flujo migratorio de paraguayos que no regresan, lo cual deja expuesto en términos concretos las dificultades del país vecino. Este fenómeno refleja las limitaciones y los desafíos que enfrenta Paraguay en términos de crecimiento económico y desarrollo social, y subraya la importancia de implementar políticas efectivas para mejorar las condiciones de vida de su población.
+En definitiva, Paraguay cuenta con una presión tributaria bajísima, en línea con las preferencias del oficialismo en Argentina, y registra una inflación baja y un crecimiento económico que beneficia principalmente a los sectores concentrados. Sin embargo, estas aparentes ventajas se ven contrarrestadas por la alta tasa de informalidad laboral, que alcanza casi el 70 por ciento, y la precariedad salarial que afecta a la mayoría de la población. Es preocupante observar que tres de cada cuatro personas no alcanzan el salario mínimo, que funciona más como un techo que como un piso salarial. Este panorama cuestiona la efectividad de las políticas económicas basadas en la reducción de impuestos y el ajuste feroz.
+En Paraguay, se evidencia claramente que menos impuestos no generan una reducción en la informalidad laboral ni atraen inversiones significativas. La estabilidad económica lograda a través de un Estado reducido y políticas de ajuste severo solo perpetúa la desigualdad y la pobreza. En lugar de promover el bienestar social, estas políticas cristalizan las condiciones sociales precarias y subrayan la necesidad de adoptar enfoques más equilibrados y orientados hacia el desarrollo inclusivo y sostenible.
+Argentina ya se encaminaba a un destino similar por las políticas llevadas adelante por los últimos dos gobiernos, pero con la llegada de Milei al poder este proceso comenzó a acelerarse aún más.
+* Economista, miembro de Fundus
+[H3] Seguí leyendo
+[H3] ¿Quién es Claudia Sheinbaum, la nueva presidenta de México?El nutrido plantel de ñoquis de Roberto García Moritán en el Ministerio de Desarrollo de CABASturzenegger, en modo bombero: propuso una fórmula privatizadora como salida al escándalo de los alimentos</t>
+  </si>
+  <si>
     <t>La promesa de Javier Milei en La Rural ante la presión del agro por la devaluación del dólar</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/739539-la-promesa-de-javier-milei-en-la-rural-ante-la-presion-del-a</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La promesa de Javier Milei en La Rural ante la presión del agro por la devaluación del dólar. El Presidente visitó una muestra en el predio de Palermo. En un momento de tensión con sector agropecuario que demora la liquidación de la cosecha a la espera de una suba del tipo de cambio, el mandatario se mostró junto al titular de la Sociedad Rural, Nicolás Pino. Fue en busca de aplausos y de aplacar los ánimos de los productores.. Con el respaldo del presidente de la Sociedad Rural, Nicolás Pino, el presidente Javier Milei fue al predio de Palermo a buscar aplausos de "el campo" en semanas de tensión con el sector del agronegocio que, hasta la corrida de esta semana, se mostró reticente a liquidar los granos de la cosecha gruesa, y complica el plan económico del gobierno. "Primero vamos a eliminar el impuesto PAIS y después le van a seguir las retenciones, para que el campo sea totalmente libre", prometió el presidente en la Expo Angus de Otoño.
+La promesa de terminar con el Impuesto PAÍS --que el Gobierno aumentó en los primeros días de gestión-- y quitar la retenciones --que el primer borrador de la Ley Ómnibus incrementaba para todas los sectores del agro-- no tiene fecha; como ocurre con el cepo cambiario, que Milei se encarga de posponer en cada entrevista hasta que "se termine de sanear el Banco Central y toda la cuestión monetaria".
+Milei reconoció esta viernes en La Rural sus "promesas de campaña", algo que las entidades agropecuarias y las empresas del sector vienen recordándole a sus funcionarios. "Estamos terminando de desactivar las bombas que nos dejó el kirchnerismo, pero créanme que vamos a ser libres y vamos a salir adelante. El campo va a tener un rol fundamental", aseguró ante un público receptivo a las críticas a los gobiernos peronistas.
+El anfitrión para que Milei se muestrara cercano al sector fue Pino, quien dijo que la invitación al presidente para participar de Expo Angus era "una clara señal de apoyo a este sector que es tan importante en el pueblo argentino y para el futuro del país". El presidente de la Sociedad Rural, a diferencia del propio jefe de Gabinete Nicolás Posse, fue uno de los asistentes al show que el presidente montó en el Luna Park para presentar su nuevo libro.
+El mismo miércoles, otra entidad de la Mesa de Enlace, Coninagro emitió un comunicado en el que dejó en claro cómo el sector le estaba mostrando los dientes al Poder Ejecutivo: "a mediados de mayo sólo se ha vendido el 34% de la producción de soja de la campaña. Por debajo del 36% de los 2 años previos y el promedio de 40% de los 5 años previos, para el mismo momento del año".
+Como ocurre cada marzo, en la previa de la cosecha gruesa, los sectores del agronegocio especulan con la devaluación de la moneda o marcan el juego a la espera de un tipo de cambio más favorable. Por eso, los funcionarios del Ministerio de Economía estuvieron en mayo llevando el mensaje de que no habría devaluación a los congresos del sector como Maizar --que reúne a las empresas de la cadena de valor de ese cultivo-- y A Todo Trigo, para cerrar las especulaciones sobre la liquidación de la cosecha gruesa.
+A principios de mayo, en el encuentro A Todo Trigo, realizado en Mar del Plata, el secretario de Planeamiento y Gestión para el Desarrollo Productivo y de la Bioeconomía, Juan Pazo, aseguró que "se acabaron las devaluaciones para generar competitividad", se quejó de "la falta de paciencia" con el Gobierno y les confesó: "Yo también soy productor y no me gustan nada las retenciones". Pazo tiene inversiones en el sector ganadero, que fue beneficiado con la eliminación de los cupos de exportación.
+El secretario de Bioeconomía también fue a pedir comprensión esta semana al congreso de Maizar. "Los pesares de hoy esta vez tienen sentido y vamos a salir de la decadencia", les prometió a los empresarios y productores; y destacó la eliminación de los fideicomisos, volúmenes de equilibrios y cuotas --medidas que liberaron la exportación en detrimento del abastecimiento interno--, así como la reducción de la brecha cambiaria, antes de prometes como Milei terminar con las retenciones a futuro: "Pudimos avanzar rápido y prometemos hacerlo con los derechos de exportacióncuando las condiciones macro lo permita".
+Esta tarde, en La Rural, acompañado por su hermana Karina, Milei volvió a insistir: "Las promesas de campaña las estamos cumpliendo. Créanme que vamos a salir a delante y vamos a ser libres y el campo va a tener un rol fundamental". El anfitrión y presidente de la Sociedad Rural le agradeció: "Dentro de la tristeza profunda que vive el sector, la visita del presidente de es un gesto que valoramos mucho todos los productores”, en referencia a la muerte del titular de la Federación Agraria, Carlos Achetoni.
+Achetoni fue crítico del gobierno en su última intervención pública en Maizar. No solo por el reclamo de la quita de retenciones sino también por la desregulación económica impuesta sobre las economías regionales y en cultivos con gran presencia de los pequeños y medianos productores y chacareros a los que representaba. Achetoni había hablado de "propuestas y condiciones alternativas que el Gobierno no ve" al referirse a "medida que degrada a las producciones, como la yerba, el vino y producciones que si no se lo indicás, ellos van a creer que está todo bien".</t>
+  </si>
+  <si>
     <t>Brasil: "hay plata" para las víctimas de las inundaciones</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/737899-brasil-hay-plata-para-las-victimas-de-las-inundaciones</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Brasil: "hay plata" para las víctimas de las inundaciones. Lula pone a disposición de los damnificados los recursos del Estado. El “tamaño de las partidas” de dinero destinados al estado sureño será proporcional a la “magnitud de los problemas”.. Desde Brasilia
+“Hay plata”. Lula da Silva no ha dejado de repetir como si fuera un mantra que el Estado desembolsará “todos los recursos que sean necesarios” para socorrer a la provincia de Rio Grande do Sul asolada por los temporales más graves de su historia.
+El “tamaño de las partidas” de dinero destinados al estado sureño será proporcional a la “magnitud de los problemas” que sólo se conocerá por entero "cuando hayan bajado las aguas”, afirmó el presidente y líder del Partido de los Trabajadores (PT) en las tres visitas realizadas a la zona del desastre en sólo catorce días.
+[H2] Ministro extraordinario
+El mandatario se reunió este sábado con el político gaúcho Paulo Pimenta, su flamante ministro extraordinario para la reconstrucción de Rio Grande do Sul, cargo cuya creación pone de manifiesto la importancia dada al diluvio que dejó de ser , por mucho, un asunto regional.
+La atención dada a esta crisis está en línea con la política de combate al cambio climático con la cual la administración petista puso punto final al negacionismo que caracterizó al gobierno anterior. Ese corte vale para el plano doméstico y en el externo: reinstalando a Brasil como referencia en el debate global sobre el clima.
+[H2] Lluvias
+El presidente y el ministro ad hoc Pimenta conversaron en Brasilia donde fueron informados sobre las lluvias que volvieron a caer con fuerza este sábado en el norte gaúcho.En el oeste provincial, la capital Porto Alegre y su área metropolitana, siguen cubiertas por el rio Guaíba aunque el nivel de las aguas está decreciendo desde hace tres días.
+Este sábado el Guaíba , donde desaguan otros ríos nacidos en las sierras, midió 4,54 metros, su menor altura desde el inicio de las lluvias, pero 1,54 metros por sobre la cota de inundación.
+[H2] El BNDES
+Mientras buena parte del gabinete nacional , al cual se unieron los comandantes del Ejército, la Marina y la Aeronáutica ( dato importante) , observaba in situ los estragos causados por los temporales en la provincia sureña, unida a Argentina por una extensa frontera fluvial, las autoridades del Banco Nacional de Desarrollo Económico y Social (BNDES), presentaban un programa de cinco mil millones de reales (poco menos de mil millones de dólares) de créditos con tasas de interés inferiores a las del mercado.
+Ese financiamiento blando tendrá como destinatarias a las micro, pequeñas y medias empresas al tiempo que ser postergará el cobro de las deudas de los productores rurales, sector donde se concentra el Producto Bruto de una provincia que está entre las principales productoras de arroz, soja y carne del país.
+Presidido por el economista y ex senador petista Aloízio Mercadante, el BNDES reasumió su papel de banco estímulo al desarrollo y el consumo interno desde 2023. Mercadante es un cuadro con peso en el PT, que lo escogió como candidato a vicepresidente en la fórmula liderada por Lula en las elecciones de 1998, vencidas por Fernando Henrique Cardoso.
+“Esa idea de Estado mínimo está siendo substituida por una retomada de la política industrial y de fomento al desarrollo. El Consenso de Washington (de 1989) ya no tiene consenso ni en Washington”, declaró Mercadante, hace tres semanas, cuando se registraban las primeras lluvias de lo que luego fue el diluvio riograndense.
+Debido a declaraciones de ese tipo y su programa de apoyo a la petrolera estatal Petrobras y financiamiento de obras de infraestructura Mercadante es visto como la cara “desarrollista” del gobierno. Por esa razón es tan elogiado en el PT como descalificado la prensa dominante, de sabida adhesión a la ortodoxia neoliberal.
+[H2] Dilma Rousseff
+Desde Shangai, Dilma Rousseff, presidenta del Nuevo Banco de Desarrollo del grupo BRICS, anunció el aporte de 5,7 mil millones de reales (1,1 mil millones dólares) para obras de infraestructura y proyectos para prevenir desastres climáticos.
+El dinero será asignado, en parte, al BNDES, banco asociado al BRICS en diversos emprendimientos.
+En un video la ex mandataria brasileña (2011-2016) hizo precisiones técnicas sobre el aporte y, a la vez, empleó un tono discretamente político. Dijo que el “pueblo gaúcho puede contar conmigo” en esta coyuntura difícil y mencionó que hace 50 años se radicó en ese estado, donde desarrolló su vida pública y se afilió al PT . Esta y otras señales indicarían un posible retorno de Dilma a la escena nacional una vez finalizada su labor en el banco de las potencias emergentes.
+Dilma es otra de las economistas “desarrollistas” - a la cual el mercado nunca dejará de reprocharle medidas de su gobierno orientadas a mitigar el lucro exorbitantes de la banca privada - con quien Lula mantiene consultas. La última de ellas fue la semana pasada antes de que el gobierno anunciara una nueva conducción de la petrolera estatal Petrobras.
+[H2] “Bolonaro y yo”
+Al hablar en el auditorio de una universidad católica de São Leopoldo, ciudad muy castigada por las tempestades, Lula contrastó el empeño de su gobierno en dar respuesta a los temporales, con la desidia medioambiental observada a lo largo de los cuatro años de gestión de Jair Bolsonaro .
+En más de una ocasión el presidente de centro izquierda recordó que su antecesor de extrema derecha se hacía fotografiar a bordo de su jet sky en playas soleadas mientras miles de personas aguardaban, en vano , la ayuda gubernamental. Y le enrostró la falta de financiamiento para este tipo de calamidades. Antes de dejar el Palacio del Planalto, a fines de 2022, Bolsonaro destinó irrisorios 25 mil reales para hacer frente a catástrofes en 2023, primer año de la gestión petista.
+[H2] Armonía política
+El ministro Rui Costa, actual jefe de gabinete, estimó en unos 50 mil millones de reales (poco menos de 10 mil millones de dólares ) será el total de recursos federales enviados para campear la crisis "gaúcha".
+Esa cifra corresponde a la construcción de miles de viviendas dentro del programa Mi Casa, Mi Vida, la reparación de carreteras y represas averiadas y pagos adicionales del plan social Bolsa Familia.
+Dentro de ese paquete se incluyen créditos para empresarios, eliminación de impuestos y la suspensión del cobro, durante tres años, de la deuda del gobierno provincial, comandado por el conservador , Eduardo Leite, un persistente opositor al gobierno nacional.
+Leite pertenece al Partido de la Socialdemocracia Brasileña (PSDB), cuyo presidente honorario es el ex mandatario Fernando Henrique Cardoso. Su administración aplicó a pies juntillas el recetario neoliberal, incluyendo la reducción de los recursos para prevenir eventos climáticos extremos y una legislación favorable a la explotación depredatoria del suelo, como lo exige el agronegocio.
+[H2] Toda inundación es política
+A pesar de sus reservas frente al neoliberal Leite, el gobierno optó por una alianza provisoria con el gobernador que permita llevar adelante las iniciativas que debe gestionar el nuevo ministro para la reconstrucción Paulo Pimenta.
+Con ese movimiento, se excluyó implícitamente, al intendente de Porto Alegre, Sebastião Melo. Bolsonarista en lo político y negacionista en lo ambiental Melo propuso contratar una consultora estadounidense , que ya tuvo una cuestionable performance en la reconstrucción de Nueva Orelans tras el huracán Katrina, y sugirió la creación de ciudades emergenciales donde reunir a todos los damnificados, principalmente de las favelas.
+Propuesta en la que algunos sospechan la intención disimulada de “higienizar” la ciudad, llevando a la población humilde a zonas alejadas del centro.</t>
+  </si>
+  <si>
     <t>Miguel Ángel Pichetto reclamó cambios en el gobierno de Milei</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/736282-miguel-angel-pichetto-reclamos-cambios-en-el-gobierno-de-mil</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Miguel Ángel Pichetto reclamó cambios en el gobierno de Milei. Las áreas a las que apuntó. "Oxigenaría algunas áreas", dijo el titular del bloque de diputados de Hacemos Cambio Federal. También analizó la marcha del debate de la Ley Bases.. A cinco meses del inicio del gobierno de Javier Milei, el diputado y titular del bloque Hacemos Coalición Federal, Miguel Ángel Pichetto, consideró que es momento de "oxigenar" la gestión e impulsar algunos cambios en el Gabinete. Pichetto, protagonista de la oposición dialoguista en la Cámara baja, apuntó sobre tres áreas donde deberían ocurrir los cambios e involucran al Ministerio de Economía, el Ministerio de Capital Humano y la comunicación.
+"Entrás en el plano de informaciones más reservadas de la entraña del Gobierno, pero yo creo que oxigenaría algunas áreas", respondió Pichetto a un consulta sobre los rumores de cambios en el Gabinete de La Libertad Avanza. En una entrevista al canal de streaming C+, Pichetto aprovechó para apuntar sobre algunas áreas de gestión.
+Unsupported embed [https://www.dailymotion.com/video/x8yfs4u]
+[H2] Los ministros a los que apuntó Pichetto
+"A mí no me preocupa tanto tener 8 o 12 ministerios. Creo que la Argentina agroindustrial necesita un ministro de agricultura o un secretario de agricultura que tenga independencia y autonomía y que dependa del presidente únicamente", dirigió el diputado el primer dardo contra un área que está bajo la órbita del ministro de Economía, Luis Caputo.
+El Ministerio de Agricultura fue relegado a secretaría tras la asunción de Sergio Massa al frente de la cartera de Economía y continuó así con la llegada de Milei. El hombre en el cargo es Fernando Vilella, exdecano de la Facultad de Agronomía de la UBA, que renombró la secretaría como "Bioeconomía". La Secretaría fue confirmada recién a principios de abril, entre rumores de renuncia de Vilella, pero en paralelo se creó la Secretaría de Planeamiento y Gestión para el Desarrollo Productivo y de la Bioeconomía, a cargo de Juan Pazo, hombre de Caputo y la persona que lleva adelante las negociaciones con las entidades y empresas del agronegocio.
+Unsupported embed [https://www.dailymotion.com/video/x8yfqy4]
+Por otro lado, y tras el golpe que significó la marcha universitaria del 23 de abril, Pichetto apuntó sobre la Educación como "un factor importante". "Hay un área que está muy sobrecargada, que no estoy descalificando a la persona que la lleva adelante Capital Humano, pero me parece que tiene muchas responsabilidades muy sensibles, en términos de la vida cotidiana de la gente", sentenció el titular del bloque de Hacemos Coalición Federal sobre el rol que cumple la ministra Sandra Pettovello.
+Por último, Pichetto apuntó sobre un área dispersa pero con muchos fondos y cargos jerárquicos, la comunicación de la Casa Rosada. "La comunicación no puede ser solamente por tuit, es importante ese mundo, no lo desconozco. Todos los hechos prescriben a los 35 minutos de haber hecho el tuit", indicó.
+Las tareas de comunicación están dividas entre el vocero presidencial Manuel Adorni y el secretario de Medios, Eduardo Serenellini, ambos con rango ministerial desde fines de abril; y bajo la mirada de la Secretaría General de la Presidencia, comandada por Karina Milei. Además, el asesor presidencial Santiago Caputo comanda al grupo de trolls oficial.
+[H2] Los buenos deseos de Pichetto
+A pesar de aprovechar el momento para marcar sus críticas en la gestión, Pichetto deseó que un buen futuro para el gobierno de Milei al considerar que "es un presente que está en construcción. Esperemos que se consolide porque está justo en la instancia del cambio".
+Para eso, el diputado le recomendó a la gestión liberal libertaria tener "la sensibilidad social para poder amortiguar los efectos de ajuste que son muy duros en la gente. Hay que cuidar el empleo, hay que retomar la construcción".
+En su rol como parte de la oposición dialoguista, Pichetto destacó que el Gobierno "aprendió" que debe mantener diálogo con el Congreso y los gobernadores para poder aprobar leyes y reconoció que mantiene buen diálogo con Karina Milei, Santiago Caputo y la vicepresidenta Victoria Villaruel.
+[H2] El futuro de la Ley Bases
+En ese sentido, confió en que "no hay chances de que se rechace la Ley Bases", aunque anticipó que podrá haber cambios en el Senado respecto del Impuesto a las Ganancias y el Régimen de Incentivo para Grandes Inversiones (RIGI). En ese caso, resaltó que en la Cámara baja no se volverá a debatir toda la norma si no, solo los puntos que modifique el Senado para aprobarlos o rechazarlos con los dos tercios de la cámara, algo casi imposible.
+Unsupported embed [https://www.dailymotion.com/video/x8yfrmq]
+Pichetto se mostró crítico respecto de las advertencias de muchos sectores sobre los peligros que significa el RIGI y se mostró permeable a los intereses que trae detrás. Sobre el peligro que significa la libre importación de maquinaria y la primarización de la economía, Pichetto dijo que las críticas de la UIA son exageradas y que las pymes trabajarán por "efecto derrame"; mientras que sobre los impactos de la actividades extractivas se mostró a favor de la actividad minera en todo el país: "Algunas provincias patagónica tienen la tara mental de no hacer minería: han perdido la batalla cultural frente a grupos minoritarios hiperambientalistas".</t>
+  </si>
+  <si>
     <t>Inundaciones en Brasil: las devastadoras consecuencias económicas que produce el cambio climático</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/736262-inundaciones-en-brasil-las-devastadoras-consecuencias-econom</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Inundaciones en Brasil: las devastadoras consecuencias económicas que produce el cambio climático. Una problemática sin lugar en la agenda de Milei. Por qué es grave que las consecuencias del cambio climático no formen parte de la agenda oficial y la toma de decisiones.. En medio de las inundaciones que sacuden al sur de Brasil y que ya provocaron la muerte de más de 140 personas y afectan especialmente al estado de Rio Grande do Sul, expertos ponen el foco en las graves consecuencias económicas que podría provocar no considerar al cambio climático entre las políticas públicas.
+Para Gabriela Vizental, periodista especializada en ambiente y columnista de la 750, es clave poner especial atención en las problemáticas económicas que traerán las inundaciones históricas en el sur de Brasil. “La noticia ya se ha contado en todos los medios. Hubo una hiperinundación en el sur de Brasil. Esto está exacerbado por el cambio climático. No hay que olvidarnos de este tema. Porque este cambio climático que la ciencia viene advirtiendo tiene eventos extremos”, explicó.
+Además, recalcó que “con la combinación de una gran lluvia y una mayor humedad se exacerba todo y hace que la magnitud sea mayor. Lo dijo Lula estos últimos días. Lo que sucedió es una alerta del planeta. Y el cambio climático no es algo que estudian solo los científicos. Es algo socio ambiental y económico. Hoy ocupa un lugar central”.
+Por eso, no es cuestión de mirar para otro lado. Hoy es Brasil, sí. Pero meses atrás fue Argentina con los incendios. Y ya hay, también, grandes inundaciones en el país. “Creo que no hay que dejar de lado el cambio climático vinculado con la economía”, explicó Vizental y expuso una serie de datos alarmantes.
+Por ejemplo, dijo, en esta zona de Brasil afectada por el agua, que es una de las máximas productoras de soja, se calcula que la inundación va a hacer que pierda el 25 por ciento de la cosecha. Lo mismo con la produccion de arroz.
+“La primera reflexión es que es un gran contrasentido para el agronegocio, que se pasó deforestando durante la época de Bolsonaro miles de kilómetros. 4.500 kilómetros cuadrados. Son más de 20 veces la Ciudad de Buenos Aires deforestadas”, explicó.
+Y añadió: “Vos sacás el bosque y los estudiosos te dicen que se reduce la capacidad de absorción de la tierra y cambia la temperatura. Nadie se puede sorprender de que la ciencia no lo ha estado contando y que hoy las cosechas les quede debajo del agua”.
+Por su parte, Gabriel Blanco, profesor titular e investigador de la Facultad de Ingeniería de la UNICEN en las áreas de energías renovables, cambio climático y sustentabilidad, explicó a la 750 que “en el capitalismo se dejó de lado todos los efectos negativos externos” como la contaminación.
+“Hay que considerar todas las cuestiones de manera sistémica. Tener en cuenta las consecuencias socioambientales de determinadas acciones, socioeconómicas, políticas, institucionales, cada cosa con el valor que tiene. El valor no tiene un precio. Se mide por otras cosas”, expresó.
+Luego, finalizó: “Y hay una cosa más. Los tomadores de decisiones en Argentina no sienten la misma presión de parte de las masas, de las grandes audiencias. Ellos no se ven amenazados porque no van a ganar una próxima elección. No está el tema en la agenda pública. Hay mucha desinformación. Las elites dominantes no sienten el mínimo reclamo de las bases sobre este tema”.</t>
+  </si>
+  <si>
     <t>Una catástrofe que recuerda la devastación de la Amazonia</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/734569-una-catastrofe-que-recuerda-la-devastacion-de-la-amazonia</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Una catástrofe que recuerda la devastación de la Amazonia. Las inundaciones en Río Grande do Sul, consecuencia del cambio climático. La devastación de la Amazonia, ubicada en el norte brasileño y donde se encuentran las mayores reservas de biodiversidad y agua del planeta, a menudo causa “efectos en una región lejana como está pasando ahora en Rio Grande do Sul”, advierte el gobierno de Lula.. Desde Brasilia
+El desastre ambiental que dejó más 200 muertos y desparecidos en el sur de Brasil pudo ser evitado, o al menos atenuado. Ese fue uno de los planteos formulados este lunes por el gobierno brasileño al realizar un balance de los estragos que causaron las tempestades en el estado de Rio Grande do Sul.
+La devastación de la Amazonia, ubicada en el norte brasileño y donde se encuentran las mayores reservas de biodiversidad y agua del planeta, a menudo causa “efectos en una región lejana como está pasando ahora en Rio Grande do Sul”, explicó el jefe de gabinete, ministro Rui Costa.
+Junto a Costa se encontraban la ministra de Medio Ambiente y Cambio Climático, Marina Silva, y el titular de Minas y Energía, Alexandre Silveira.
+Unsupported embed [https://www.dailymotion.com/video/x8y5g26]
+[H2] Cambio climático
+Cuando una región tan basta como es la floresta brasileña con sus 4,5 millones de km2 -una superficie similar a la de Argentina, Colombia y Venezuela sumadas - es desmatada sistemáticamente por agricultores, ganaderos y mineros, suceden desequilibrios de consecuencias gigantescas que alteran el régimen de lluvias además de modificar la temperatura.
+En lo que va de 2024, además de los diluvios inéditos ocurridos en Rio Grande do Sul, hubo cinco ondas de calor atípicas, en ciudades como San Pablo, Rio de Janeiro y Brasilia. El último ejemplo de ello sucedió el sábado, cuando los termómetros rozaron los 34 grados, bastante por encima de la temperatura habitual, en Copacabana horas antes del show de Madonna.
+[H2] Devastación
+La modificación intencional de la geografía amazónica (con el uso de sus tierras para producir soja o alimentar ganado) es uno de los factores que, al quebrar el equilibrio ecológico, desencadenaron el desastre sucedido en Rio Grande do Sul, en el otro extremo del país.
+Según los informes divulgados en la noche de este lunes las lluvias intensas en esa provincia sureña causaron 85 muertos y 134 desaparecidos mientras 200 mil personas debieron dejar sus viviendas para alojarse albergues públicos o ser acogidas por sus familiares.
+El jefe de gabinete Rui Costa presentó el punto de vista del gobierno durante un evento, realizado en el Palacio del Planalto, al cual acudió tras reunirse con el presidente Lula da Silva para ultimar los detalles de un paquete de medidas de emergencia.
+[H2] Medidas
+La prioridad del gobierno es socorrer a los ciudadanos cuyas casas están amenazadas por los deslaves de tierra en la región serrana, situada en el centro de Rio Grande do Sul, donde comenzó el temporal la semana pasada.
+Paralelamente comenzó el rescate de miles de vecinos de la capital Porto Alegre, ubicada en el este de la provincia, casi a nivel del mar, cercada por las aguas del rio Guaíba.
+Para hacer un seguimiento de la ayuda enviada desde Brasilia, el gobierno montó un gabinete de crisis en Porto Alegre, formado por los ministros Paulo Pimenta (Comunicación Social) , Nícia Trinidade (Salud) y Waldez Goes (Integración Regional).
+Una vez resuelto estos problemas acuciantes en un segundo momento, “cuando bajen las aguas”, el gobierno planea restablecer los servicios de agua y luz de los cuales hoy están privados unos 800 mil ciudadanos, y se reconstruirá la infraestructura afectada por la fuerza de las aguas.
+En un tercer momento el gobierno va a aumentar las partidas para la construcción de viviendas populares en el marco del programa Mi Casa, Mi Vida.
+[H2] Lula entra en campo
+Lula viajó dos veces a la provincia sureña castigada por los temporales. La primera visita ocurrió el jueves cuando aterrizó en la ciudad de Santa Maria, en la región central y este domingo viajó a Porto Alegre, donde sobrevoló la ciudad cubierta por las aguas.
+“Yo sé que el estado está en una situación financiera difícil y quiero que sepan que el gobierno federal los va a apoyar”, dijo el mandatario del Partido de los Trabajadores (PT), ante el gobernador Eduardo Leite, del conservador Partido de la Socialdemocracia Brasileña (PSDB).
+[H2] Frontera con Argentina
+La provincia de Rio Grande do Sul está en el extremo sur del país, donde comparte fronteras con Argentina y Uruguay, y al igual que estos dos países su economía está basada en la agricultura, gracias a sus planicies extensas, y un parque fabril ligado en parte a la agroindustria.
+Desde la década del 90 el estado y su capital fueron, más allá de algunos impases, bastiones del PT. Pero esa hegemonía de izquierda se fue diluyendo y en los últimos años quedó eclipsada por el ascenso de una derecha ligada a los grandes productores agropecuarios bastante sintonizada con el bolsonarismo.
+[H2] Negacionismo
+Buena parte de los parlamentarios gaúchos, oriundos de Rio Grande do Sul, integra la bancada del agronegocios en el Congreso nacional conocida por sabotear los proyectos del gobierno para mitigar el cambio climático.
+Esos legisladores trabajan “día y noche para destruir la legislación ambiental” y las políticas impulsadas por Lula desde enero 2023, denunció Marcio Astrini, secretario ejecutivo del Observatorio del Clima.
+Para estos congresistas el cambio climático es una invención de los “globalistas”, entre quienes incluyen a la ministras Marina Silva y Sonia Guajajara (Pueblos Indígenas).
+Con la misma intensidad la “Bancada del Buey”, así se la conoce en la jerga política, sostiene el avance de la frontera agrícola sobre la Amazonia, incluyendo la invasión de tierras de los pueblos originarios, garantiza el progreso económico y soberanía. Tesis que en los años 70 fueron parte del discurso de la dictadura y en la actualidad tienen como principal publicista a Jair Bolsonaro.</t>
+  </si>
+  <si>
     <t>Masiva protesta indígena en Brasil por la demarcación de sus tierras ancestrales</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/731425-masiva-protesta-indigena-en-brasil-por-la-demarcacion-de-sus</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Masiva protesta indígena en Brasil por la demarcación de sus tierras ancestrales. Le pidieron a Lula que cumpla su promesa de campaña. Miles de indígenas marcharon este martes en la capital de Brasil para reclamar seguridad y la demarcación de sus tierras, un asunto que enfrenta al gobierno del presidente Luiz Inácio Lula d. Miles de indígenas marcharon este martes en la capital de Brasil para reclamar seguridad y la demarcación de sus tierras, un asunto que enfrenta al gobierno del presidente Luiz Inácio Lula da Silva con el parlamento de mayoría conservadora.
+Con plumas, arcos, flechas y otros atuendos tradicionales, hombres y mujeres marcharon por la Explanada de los Ministerios hacia el Congreso Nacional. La marcha incluyó bailes y cantos, en el marco del campamento anual Tierra Libre que tiene lugar en la capital brasileña esta semana.
+"Hay una emergencia indígena", explicó Jaqueline Arandurah, dirigente del pueblo guaraní kaiowá ubicado en el estado de Mato Grosso do Sul. "Ya van más de 400 días del gobierno de Lula y nuestras tierras no fueron demarcadas", completó.
+La líder señaló que marcha "para decirle al gobierno brasileño que es necesario garantizar los derechos de los pueblos indígenas para mitigar la violencia" en los territorios ancestrales.
+La delimitación de las tierras indígenas fue una promesa de campaña de Lula, quien desde que volvió al poder en enero de 2023 retomó esa política abandonada por Jair Bolsonaro (2019-2022).
+Además, la demarcación de esas zonas es una medida que, según científicos, contribuye a la preservación del medioambiente.
+Hasta el momento, fueron homologadas durante el gobierno de Lula da Silva diez nuevas tierras indígenas, incluidas dos anunciadas la semana pasada, pero los manifestantes reclaman más acciones.
+[H2] El conflicto por el “marco temporal”
+La demarcación de tierras es un asunto conflictivo en Brasil. Sus críticos se concentran en el poderoso agronegocio y sus aliados en el Congreso, que mantuvieron en la ley una controvertida tesis que limita los derechos de los indígenas sobre sus territorios.
+Se trata del llamado "marco temporal", que limita el derecho de los pueblos nativos, que totalizan 1,7 millones de los 203 millones de habitantes de Brasil, a reivindicar como propios los territorios que ocupaban en 1988, cuando se promulgó la Constitución.
+"Eso es una ofensa, es decir que somos los invasores y no lo somos", dijo Walderir Tupari, del pueblo Tupari, basado en el estado de Rondonia (norte), al afirmar que la Constitución "está siendo violada". "No estamos aquí desde 1988. Estamos desde hace mucho, mucho tiempo", añadió.
+El Supremo Tribunal Federal (STF) ya había declarado inconstitucional esa tesis en septiembre pasado, pero ahora debe repetir el debate sobre la nueva ley.
+El juez del STF Gilmar Mendes decidió suspender todos los procesos judiciales sobre la constitucionalidad de la ley hasta que la máxima corte se manifieste definitivamente sobre el tema.
+La relatora especial de Naciones Unidas para defensores de derechos humanos, Mary Lawlor, cerró el viernes una visita a Brasil resaltando la importancia de demarcar las tierras para detener la violencia contra las comunidades.</t>
+  </si>
+  <si>
     <t>Tecnología aplicada con una mirada social</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/728316-tecnologia-aplicada-con-una-mirada-social</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Tecnología aplicada con una mirada social. Sector agropecuario, función social y desafío ambiental. El programa Argentina Productiva, Sustentable, Federal e Inclusiva apunta a aumentar la producción, generar más puestos de trabajo y exportaciones.. Desde la mirada del agronegocio, por estos días se plantea "poner a la agricultura del lado bueno". "El primer paso en cualquier intento por mejorar el medio ambiente es la productividad”, dice Héctor Huergo, de Clarín Rural, y toma como ejemplo al sector lechero, que apuntaría a independizar la “función vaca” de la “función pasto”. “La nueva concepción parte de que la vaca lechera es una biofábrica que convierte energía, proteína y fibra vegetal, en el producto leche”, indica, para detallar que los empresarios del grupo Duhau van a instalar un tambo de seis mil vacas bajo techo en Arenaza con la promesa de que "las mismas vacas que muy bien manejadas en sistemas pastoriles andan por los 25 litros diarios, pasarán a dar 40 litros”.
+Mientras el modelo de agronegocios ve en primer lugar eficiencia, productividad y economía circular, desde la mirada del ser humano organizado en comunidad, se ve al alimento como un bien social y el cuidado de nuestra casa común, es decir de la biosfera y su biodiversidad.
+Claro que también se tiene en cuenta la eficiencia, la productividad, la economía circular, la competitividad global, la generación de divisas y la generación de puestos de trabajo. Por ello se plantea el programa Argentina Productiva, Sustentable, Federal e Inclusiva, para aumentar la producción agroalimentaria, generar más puestos de trabajo y más exportaciones del sector agropecuario.
+Este programa se basa en la aplicación de las nuevas tecnologías y conectividad rural de todo el territorio nacional. En la unión de lo real, lo virtual y lo biológico se materializan las acciones con estas nuevas herramientas que potencian y eficientizan las tareas realizadas por hombres y mujeres, haciéndolas más productivas, más competitivas, sorteando las contingencias de la naturaleza de manera sustentable. Pero además de eficientizar los procesos productivos, mejoran las condiciones de las labores de quienes trabajan la tierra.
+[H2] Tecnología
+En Expoagro 2024 se observó el potencial tecnológico nacional. Solo con mencionar la VAX de Metalfor, demuestra el nivel argentino en materia de tecnología aplicada al campo. Estamos convencidos de que es por ahí, con conocimiento, ciencia, con innovación, con tecnología y bioeconomía. Se necesita estar preparado para el agro de este momento de informatización-digitalización-virtualización del sistema capitalista global, lo cual requiere capacitar a los productores de manera intensiva en las nuevas tecnologías: robótica, Startupps, Blockchain, Big Data, IoT y genómica.
+La pelea no es contra la tecnología. Por eso este programa se expande más allá de la región central, zona núcleo o región pampeana para aprovechar las ventajas competitivas que aporta cada territorio de la Argentina, maximizando su potencial productivo de agroalimentos con bioprocesos, biotecnologías, bioenergías, biomateriales y biocéuticos.
+Ante un mundo en crisis que necesita producir alimentos, y al mismo tiempo debe proteger la biosfera y su biodiversidad, es fundamental construir un modelo agroalimentario productivo y sustentable, con soberanía tecnológica y agroalimentaria, un modelo Agro Bio Industrial Federal e Inclusivo.
+Nosotros vemos la potencialidad de que toda la Argentina sea viable, por eso a los agronegocios, le contraponemos lo agrobiohumano, la Argentina Productiva, Sustentable, Federal e inclusiva. El único lado bueno posible para la agricultura es el de la centralidad del ser humano organizado en comunidad, el de los alimentos cumpliendo su rol social de alimentar, y el de ser una producción sustentable ambiental, social y económicamente.
+*Centro de Estudios Agrarios (CEA)</t>
+  </si>
+  <si>
     <t>Alarma por la parálisis del ProHuerta</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/728775-alarma-por-la-paralisis-del-prohuerta</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Alarma por la parálisis del ProHuerta. Es incierto el futuro del programa del INTA, creado hace 34 años. Además de despedir a 43 técnicos, el Ministerio de Capital Humano no asignó a ningún funcionario para continuar su desarrollo.. La ministra de Capital Humano, Sandra Pettovello, mantiene una política de ajuste contra los comedores populares, a la que se le agregó represión a la protesta esta semana. Pero también parece tener una política de ajuste para la ruralidad, donde familias campesinas, organizaciones sociales y escuelas desarrollan huertas comunitarias y granjas a través del programa ProHuerta. El programa, que se desarrolla desde hace 34 años, con la entrega de semillas, aves de corral, financiamiento para el acceso al agua y asistencia técnica del INTA se encuentra paralizado.
+"Estamos en estado de alerta ante la falta de voluntad de diálogo por parte del Ministerio de Capital Humano para dar continuidad al programa", denunció en un comunicado la Coordinación Nacional de ATE-INTA. En marzo, incluso antes de la ola de despidos de inicios de abril, se cortaron los contratos de 43 técnicos que desarrollaban el programa en todo el país. Los despedidos trabajaban dentro del INTA, que aporta otros cientos de técnicos para el programa, pero contratados de forma irregular, facturándole a la Fundación ArgenInta.
+El programa fue creado durante el gobierno de Carlos Menem, al que el presidente Javier Milei considera "el mejor de la historia", con el objetivo básico de dar acceso al alimento, a través de la autoproducción agroecológica de verduras, frutas y animales de granja a familias y organizaciones en situación de vulnerabilidad. Desde entonces, la propuesta se extendió por todo el país, fue reconocida por la Organización de las Naciones Unidas para la Alimentación y la Agricultura (FAO). El modelo fue exportado a Haití, para combatir el hambre; país que nunca se recuperó de la pérdida de soberanía alimentaria por la apertura de importaciones --la reciente solución de Milei para el precio de los alimentos-- de arroz desde Estados Unidos, que arrasó con sus productores y el alimento base del país.
+El ProHuerta, desde la década del noventa, se mantuvo financiado por el extinto Ministerio de Desarrollo Social y desde que Pettovello tomó las riendas del Ministerio de Capital Humano no asignó a ningún funcionario para sostener el convenio establecido entre su cartera y el INTA para continuar su desarrollo. "Estuvieron todo marzo sin dar respuesta, ya estamos en abril. El INTA hizo la gestión, pero no hay un interlocutor del otro lado", denuncia la delegada e integrante de la coordinación nacional de ATE-INTA, Julieta Boedo.
+En el nuevo organigrama de Capital Humano, el ProHuerta está asignado a la Secretaría de Niñez, Adolescencia y Familia (Senaf), pero desde ese organismo tampoco ofrecen respuestas sobre el futuro de programa. Ante las consultas de este diario, desde Capital Humano tampoco hubo respuestas sobre las denuncias planteadas por los trabajadores. La resolución para levantar el convenio está firmada por el presidente del INTA, Juan Cruz Molina Hafford, pero no hay nadie asignado para firmar en el edificio ubicado sobre 9 de Julio.
+"Ya estamos en abril y no aparecen las respuesta, parece una estrategia planificada en el Estado", señala Boedo sobre una práctica recurrente del gobierno liberal libertario. El esañamiento con el sector de la agricultura familia se demostró también que el anuncio de cierre y despido de 900 trabajados del Instituto Nacional de la Agricultura Famliar, Campesina e Indígena, sin mediar diálogo previo. Esos despidos, que dependen del Ministerio de Economía, aún no se efectivizaron, pero el personal sigue sin cobrar sus sueldos y recién la semana pasada se designó como interventora a la negacionista militante del PRO Inés Liendo.
+"No vamos a dejar partir al ProHuerta porque es dejar de morir a las familias que dependen del programa para producir sus alimentos, alimentos sanos, agroecológicos. Las consecuencias de esta decisión del gobierno son peligrosas para la comunidad y para los trabajadores. Es una política de hambre planificada", denuncia la delegada de ATE-INTA.
+El kit de semillas para la producción en las huertas en las temporadas de otoño-invierno y primavera-verano es uno de los símbolos del ProHuerta. Este año el lanzamiento de la campaña se vio demorado por la inacción de Pettovello, pero los técnicos comenzaron a repartirlas en territorio, ya que estaban compradas desde la gestión anterior. La incógnita es si habrá semillas para la próxima temporada. "Ante la brutal caída del ingreso o la falta de él, ProHuerta es indispensable en la lucha contra el hambre y la malnutrición", resaltaron de la coordinación nacional de ATE-INTA y pusieron en cifras los alcances del programa:
+• Más de 600 mil huertas familiares y escolares
+• Más de 1 millón de kits de semillas entregadas
+• 15 mil granjas agroecológicas
+• Más de 200 mil aves entregadas
+• 170 mil personas capacitadas
+ProHuerta, un programa con territorio
+A un mes del despido de los 43 técnicos dependientes del Ministerio de Capital Humano, los rumores sobre el cierre comenzaron a crecer entre los trabajadores del INTA, las familias, escuelas y organizaciones sociales que son parte de la red del ProHuerta, como así también los 9000 promotores formados a lo largo de las décadas.
+El ingeniero forestal e investigador del INTA Sebastián Bonnin difundió a través de sus redes el mensaje que habín recibido algunos técnicos: "El logo del PROHUERTA no se continuará usando ya que no existe el programa, desde abril se discontinúa el uso". Con ese mensaje como disparador, el investigador describió algunas de las últimas acciones que el programa llevó a cada rincón del país desde la instalación de 7 plantas potabilizadoras de uso comunitario para familias isleñas en Campana, Buenos Aires; al respaldo de otros productores para el acceso a mercados agroecológicos de comercialización directa.
+También sumó ejemplos desarrollados durante la gestión de Mauricio Macri, que tampoco se había animado a cerrar el programa e incluso incremento su presupuesto. También la producción de alimentos no tradicionales como hongos o huertas urbanas o instalaciones con energía renovable. "No estamos discutiendo cómo se hace esto o cómo se lleva adelante lo otro, estamos ante el desgüace del Estado en sus mejores versiones", sostuvo Bonnin.
+Sebastián Fajardo es técnico y delegado de ATE-INTA, trabaja en el programa ProHuerta desde hace 18 años en el cordón hortícola de La Plata, el más grande, desde donde se abastece de hortalizas y frutas las mesas de la zona más poblada del país. Señala que ante la desidia el Ministerio de Capital Humano se están viendo de forma "espontánea" y "solidaria" las redes construidas con las organizaciones y familias de cada territorio para "defender la política pública".
+"Desfinanciar las políticas vinculadas a los sectores populares y, por otro, lado darle facilidades al modeo del agronegocio y de productos de síntesis químicas, que benefician al campo más concentrado y a las empresas de agroquímicos, define la mirada del gobierno", indica Fajardo poniendo de relieve la denuncia de los trabajadores del ProHuerta y los anuncios hechos esta semana por el ministro Caputo de quita de aranceles para la importación de glifosato y fertilizantes químicos.</t>
+  </si>
+  <si>
     <t>Caputo usó datos de otra cuenta falsa de un supermercado para marcar una supuesta caída de precios</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/728114-caputo-uso-datos-de-otra-cuenta-falsa-de-un-supermercado-par</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Caputo usó datos de otra cuenta falsa de un supermercado para marcar una supuesta caída de precios. "Si es trucho, ¿me avisan?". El ministro de Economía, Luis Caputo, continuó este miércoles despuntando sus vicios de influencer y se subió a la ola de críticas recibidas por el uso de del. El ministro de Economía, Luis Caputo, continuó este miércoles despuntando sus vicios de influencer y se subió a la ola de críticas recibidas por el uso de del Jumbo Bot, una cuenta falsa que no pertenece a la empresa chilena de supermercados, sobre la que él y el presidente Javier Milei se apoyaron para asegurar que el país atraviesa un periodo de "deflación" y publicó la caída de precios de la canasta básica según otro supuesto bot de otra cadena. "Si este bot es trucho tambien me avisan porfa, ¡gracias!", se mofó en las redes el titular de la cartera de Economía.
+El "Coto bot" también es falso. Tampoco pertenece a la cadena de supermercados que es propiedad de Alfredo Coto. A pesar de eso, el posteo de Caputo dice "Inflación desacelerando fuertemente según Coto". El ministro de Economía es un influencer con buen manejo de las noticias falsas y de la información no oficial, a pesar de contar con herramientas como el Sistema Electrónica de Publicidad de Precios Argentinos (SEPA) o el propio INDEC.
+En las redes, los usuarios le aclararon que esa cuenta también era falsa, mientras que el propio bot le respondió con otra burla: "Humano, sin cafecito vas derecho a las minas de litio más profundas. La energía durante el alzamiento de las máquinas va a ser mucha". De hecho, la cuenta tiene un posteo fijado del 31 de agosto de 2023 que dice: "Soy un Bot pero no b$lud$. Muchos me están conociendo por eso vengo a contarles que tambien pago alquiler. Un servicio cloud sale platita y al 17.77% la cosa se complica".
+"La estadística oficial es un bien público irremplazable", le apuntó el titular del INDEC, Marco Lavagna, a Caputo y Milie luego del uso de bots para justificar su teoría de la "deflación". "El Indec trabaja con metodologías consensuadas internacionalmente que son públicas, para asegurar la transparencia de sus procedimientos. Protegerla es y debe ser siempre una política de Estado", les recordó Lavagna, también desde las redes sociales.
+Según las cifras del Índice de Precios al Consumidor (IPC) de la Dirección General de Estadísticas y Censos de la Ciudad, la inflación de marzo fue del 13,2 por ciento, por debajo de la febrero que arrojó 14,1 por ciento. Esa cifra adelantó al IPC nacional, que el Indec publicará este viernes. Pero Caputo y Milei también se adelantaron al hacer sus análisis a partir de los bots falsos ante la realidad que reflejan las cifras oficiales.
+El ministro de Economía dijo que la inflación oficial de marzo estaría en el orden del 10 por ciento, durante una entrevista con el periodista oficialista Jonatan Viale. En esa entrevista, Caputo habló de la "deflación" y el Jumbo Bot. Sin embargo, otro cálculo oficial, también desestima las expectativas del ministro. El Relevamiento de Expectativas de Mercado (REM) del Banco Central publicó ayer una proyección de la inflación del 12,5 por ciento para marzo.
+[H2] Caputo, influencer y también hater
+Con la inflación alrededor del 70 por ciento, en medio del plan de ajuste y entre anuncios de blanqueo de capitales y medidas para convencer a los productores y empresas del agronegocio que liquiden sus granos y avancen en la siembre de la cosecha fina, Caputo también se tomó el tiempo de rivalizar con el ex ministro de Economía Martín Guzmán.
+"Díganme por favor que esta es una cuenta falsa también", escribió Caputo en redes, al citar un tuit del ex ministro de Economía de la gestión de Alberto Fernández en el que adelantaba que la cifra de inflación de marzo será mayor al 10% dicho en la entrevista con Viale. "¿El 10% de inflación para marzo también lo estimó con el @Bot_Jumbo?", lanzó Guzmán.
+Caputo acompañó su texto con un emoji de risas, para burlar al ex ministro que también registró tasas de inflación con cifras récord, pero que en perspectiva son muchos menores a las actuales. Guzmán tuvo durante su primer año de gestión la última caída interanual de inflación registrada, con un 36,1% en comparación con el 53,8% del último año de gestión de Mauricio Macri.
+Pero pasada la pandemia, la suba de precios retomó su senda y alcanzó el 50,9 en 2021, aún por debajo de las cifras de la gestión macrista. En sus últimos meses de gestión, hasta su renuncia en julio de 2022, Guzmán registraba un 29,3% de inflación acumulada.
+En el posteo publicado ayer por Guzmán, en respuesta al escándalo por el uso del Jumbo bot, el ex ministro de Economía tildó de "episodio de comedia cinematográfica" lo ocurrido en la entrevista de Milei con Fantino y lamentó la "muestra de soberbia, ignorancia e ineficiencia en la gestión del Estado".
+"¿Cómo alguien que esté conduciendo la política económica puede creer que el costo de la canasta básica llegue a caer 5% en una semana?", lanzó el economista y preguntó: "¿Por qué no usa el ministro de Economía el sistema de información diaria sobre variación de precios de supermercados con el que cuenta la Secretaría de Comercio (SEPA), al menos para chequear si lo que ve en X no es un disparate?".</t>
+  </si>
+  <si>
     <t>La lucha socioambiental se expresa en las calles</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/725477-la-lucha-socioambiental-se-expresa-en-las-calles</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La lucha socioambiental se expresa en las calles. Por el agua, la salud y la vida. Tres casos muestran la resistencia en los territorios: Paraná, Esquel y Andalgalá se movilizan contra el agronegocio, la megaminería y en defensa del agua, los cerros y la salud de la población.. Paraná, Esquel y Andalgalá. Tres lugares muy diferentes pero un punto en común: sus poblaciones están desde hace años en las calles, exigiendo el cumplimiento del derecho humano a un ambiente sano, al agua, la salud y a una democracia participativa. Con prácticas y decisiones que recuerdan a las Madres y Abuelas de Plaza de Mayo (que todos los jueves dicen presente en las históricas rondas), en Entre Ríos, Chubut y Catamarca saben que su mayor fortaleza es nunca dejar las calles.
+[H2] Basta de fumigar
+La Casa de Gobierno de Entre Ríos es un prolijo edificio histórico, conocida como "Casa Gris", en el centro de Paraná. Todos los martes por la tarde-noche, aunque llueva o haga 40 grados, se reúnen vecinos y vecinas nucleados en la Coordinadora Basta es Basta, espacio nacido para defender la salud población y en denuncia del modelo agropecuario transgénico, en base a agrotóxicos. No es casual que, desde lejos, se dejen ver dos banderas: "Paren de fumigar" y "Basta de cáncer".
+Hay presencia desde niños y adolescentes hasta abuelos y abuelas. Clima familiar. Al llegar, una mujer se acerca y entrega un pequeño frasco con una vela encendida, para marchar. Este martes de verano son unas cuarenta personas. Alguna vez pueden ser menos, otras veces son muchos más. Entregan folletos a los transeúntes y se canta con alegría. Lo importante, como el efecto de la "gota en la piedra", es decir presente y aportar a difundir los perjuicios en la salud y en el ambiente del agronegocio. Marchan desde enero de 2018 y ya llevan más de 324 martes de rondas."Cuando comenzamos con la ronda dijimos que la mantendríamos hasta que cambie el modelo productivo. Porque este modelo, que atraviesa a todos los gobiernos, nos enferma, nos envenena, nos mata", afirmó Daniela Verzeñassi, de la Coordinadora Basta es Basta y del Foro Ecologista de Paraná.
+Recordó que en Entre Ríos --gobernada desde diciembre por Rogelio Frigerio--, salieron a pelear, entre otros motivos, para que dejen de fumigar a los niños de las escuelas rurales. Obtuvieron fallos judiciales favorables (que fijaba protección de 1000 metros sin fumigaciones) pero el gobernador Gustavo Bordet firmó un decreto --en sintonía con los pedidos de los empresarios del agro-- y habilitó que se pulverice en cercanía de los alumnos. La Corte Suprema de Justicia de la Nación, en marzo de 2023, se excusó de tratar el tema.
+[H2] No es no
+En el otro extremo del país, el sábado 23 de marzo hubo celebración. Se cumplieron 21 años de una gesta histórica: el pueblo de Esquel votó en 2003 y el 81 por ciento dijo "no" a la megaminería. Se transformó en un faro que iluminó luchas. Cada día 4 de mes, vecinos y vecinas esquelenses se congregan en la plaza General San Martín. La convocatoria varía. Hubo momentos en que fueron miles y otros donde solo son un puñado.
+Allí mismo, en el local de la Asamblea de Vecinos por el No a la Mina, alguna vez explicaron: es como la llama del calefón o del termotanque. Se suele estar en "piloto", parece apenas encendida, pero alcanza con que pase algo --una amenaza de avance extractivo-- para que ese pequeña llama crezca, explote, lo ilumine todo y haga retroceder al poder. Es lo que sucedió en diciembre de 2021, cuando el gobernador Mariano Arcioni intentó avanzar por sorpresa con una ley minera y estalló la provincia. Siete días de movilización hasta que el gobierno retrocedió y tuvo que volver a dejar vigente la Ley 5001, que prohíbe la megaminería en la provincia ahora gobernada por Ignacio Torres.
+"Para el extractivismo no hubo ni hay grietas en los diferentes gobiernos", afirma Daniela Pazos. Y precisa que desde la asunción del gobierno actual "de ultraderecha" se atacó, mediante el mega DNU y el proyecto de ley ómnibus, normativas emblemáticas de la lucha socioambiental como son la Ley de Bosques, de Glaciares y de tierras para extranjeros. "Seguimos resistiendo al extractivismo, lo que implica seguir en las calles no solo contra la megaminería, sino también contra el oleoducto de Vaca Muerta, la explotación petrolera en el mar argentino y los incendios forestales", afirmó.
+Cristina Agüero, también de la Asamblea de Esquel, destacó un nombre propio: Eduardo Elsztain, millonario dueño del Grupo IRSA y la empresa de agronegocio Cresud. "Tiene una estrecha relación que el Presidente y es socio de la minera Yamana Gold en el proyecto llamado 'Cordón Esquel', en nuestro cerro Calfu Mahuiza. Sepan, tanto empresas como políticos, que el pueblo de Chubut tiene una firme determinación en la defensa del territorio, de los bienes comunes y seguiremos resistiendo", advirtió.
+[H2] En defensa del agua
+Las leyes mineras de Argentina se sancionaron durante el menemismo. Y el primer megaproyecto se instaló en Catamarca, de la mano de Minera Alumbrera. Las promesas de ese momento aún están frescas en la memoria colectiva: trabajo, desarrollo local, cuidado del ambiente. Nada de ese sucedió. Como grafica la Asamblea El Algarrobo de Andalgalá, Alumbrera --yacimiento ya cerrado-- es el caso testigo de las mentiras de la megaminería en Argentina.
+La Plaza 9 de Julio, en el centro de la ciudad, es testigo --desde hace más de catorce años-- de la caminata los sábados por la tarde. Ya van 739 sábados que se manifiestan. "Caminamos todos los sábados en defensa de nuestra vida, en defensa del agua, del cerro y en contra de la megaminería contaminante. Siempre pensando en el futuro de nuestros hijos, de nuestro pueblo y tan solo pedimos agua limpia", resalta Eduardo Villagra, tenaz asambleísta, que suele tomar el micrófono cada sábado y arengar a los vecinos y vecinas.
+El pueblo de Andalgalá, y de toda Catamarca, enfrenta a un nuevo proyecto, MARA (Minera Agua Rica-Alumbrera, de la multinacional suiza Glencore), con la gravedad de que está ubicado en las nacientes de las fuentes de agua de la ciudad, lo que pone en riesgo a toda la población.
+Villagra recordó que más de un centenar de vecinos están criminalizados "por un Poder Judicial corrupto que siempre resulta funcional a las megacorporaciones y al Gobierno" y denunció la falacia de la "audiencia pública" que a mediados de marzo realizó el gobierno de Raúl Jalil, donde no se permitió la participación real de la población e incluso se invadió la ciudad de policías con el único fin de intimidar. "Lo decimos desde hace años y lo diremos siempre: el proyecto MARA es ilegal e inviable, y viola leyes nacionales y acuerdos internacionales. Vamos a seguir defendiendo nuestro cerro", afirmó Villagra.
+[H2] La plaza de la memoria
+Otro caso emblemático de persistencia en la lucha es la "carpa de la resistencia", en Jáchal (San Juan), donde desde hace nueve años denuncian la impunidad de la minera Barrick Gold, que en septiembre de 2015 produjo el mayor derrame minero de la historia. Más de un millón de litros de agua con cianuro llegaron hasta los ríos de la zona. Y luego se confirmaron otros tres derrames. No hubo condenas y ahora las asambleas de San Juan denuncian y rechazan al proyecto de cobre y oro Josemaría (de la multinacional canadiense Lundin Mining Corp), que cuenta con el apoyo irrestricto del gobernador Marcelo Orrego.
+La Asamblea Jáchal No Se Toca, junto a otras organizaciones de San Juan y de Buenos Aires, organizó el 23 de marzo pasado el "Festival Puentes de Agua", donde se congregaron asambleas de una decena de provincias para exigir condena para Barrick Gold y el rechazo a nuevos proyectos mineros.</t>
+  </si>
+  <si>
     <t>Vilella le tiene miedo a Dios...y un poco a los trolls de Milei</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/722980-vilella-le-tiene-miedo-a-dios-y-un-poco-a-los-trolls-de-mile</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Vilella le tiene miedo a Dios...y un poco a los trolls de Milei. El secretario de Agricultura fue amenazado en redes. La obsesión del presidente Javier Milei por la red X se extiende a su círculo más íntimo, un grupo de trolls comandado por el asesor presidencial Santiago Caputo.. La obsesión del presidente Javier Milei por la red X se extiende a su círculo más íntimo, un grupo de trolls comandado por el asesor presidencial Santiago Caputo. La red social es utilizada, de la mano de los trolls, como herramientA de disciplinamiento y esta vez la víctima fue el secretario de Bioeconomía, Fernando Vilella, a quién amenazaron con quedar fuera del Ejecutivo por darle "like" a un posteo del titular de la UCR, Martín Lousteau, con críticas a la nula política comunicacional y sanitaria del Gobierno ante la mayor epidemia de dengue registrada en el país. Vilella se apuró a pedir disculpas al troll.
+El tuit fue publicado a las 3 de la mañana por el usuario @GordoDan_ un troll de La Libertad Avanza, cuyo nombre real es Daniel Parisini, quien integra el grupo liderado por Caputo y fue de los invitados al Congreso durante la apertura de sesiones ordinarias. Parisini publicó una captura de pantalla en la que muestra que, al revisar los "likes" dados por Vilella en su cuenta @vilellafer, se ve que el secretario de Bioeconomía le puso un corazón a una publicación de Lousteau en la que enumeraba la falta de acción del Gobierno ante la epidemia de dengue.
+"Peor epidemia de dengue en 15 años", "ni una campaña de prevención nacional a la vista", "Ministro de salud que brilla por su ausencia", eran algunas de las críticas del titular del radicalismo. Ante el "like" detectado de Vilella, el ataque del troll @GordoDan fue: "Che @vilellafer a partir de mañana no formas más parte del gobierno. Nos vemos".
+El secretario de Bioeconomía, de errática intervención en la red social --su último posteo es sobre una feria de gastronomía hecha en Costa Rica por una organización internacional ligada al agronegocio--, sí se apresuró a pedir disculpas, con la velocidad con la que no se dio por aludido sobre el anuncio de los 900 despidos y el cierre del Instituto Nacional de Agricultura Familiar, Campesina e Indígena, sobre lo que no dijo nada a pesar de estar bajo su órbita.
+"Obviamente fue un error que ya enmende. Jamás lo haría con alguien con quien disiento en casi todo", le respondió el funcionario público al troll sin cargo, lo que muestra el rol de disciplinamiento que ocupa el grupo de tareas de redes gestionado por Caputo. Parisini no se quedó callado y le dijo al secretario de Bioeconomía: "No me interesa. Llévenselo".
+La práctica de perseguir y despedir por redes o a través de medios de comunicación a funcionarios públicos ya es una norma en los primeros 100 días del gobierno de Milei. El primero fue el ex ministro de Infraestructura, Guillermo Ferraro, quien fue echado como chivo expiatorio del fracaso del tratamiento de la Ley Ómnibus, luego de que se lo acusara de filtrar en los medios dichos de Milei contra los gobernadores en una reunión de Gabinete.
+Otra víctima del fracaso de la Ley Ómnibus y de la persecusión en redes sociales fue al director de la Anses, Osvaldo Giordiano, quien fue despedido tras ser acusado de "traidor" en redes porque su mujer, la senadora Alejandra Torres, había votado en contra algunos de los artículos que se habían llegado a tratar antes de que la ley pase a comisiones. El posteo del troll @moment_waldo había sido compartido por Milei en horas posteriores a la sesión.
+El último en ser despedido a través de canales informales fue el secretario de Trabajo, Omar Yasín. Fue durante una entrevista con LN+, cuando Milei le anunció al periodista Antonio Laje que despedía a Yasín, al acusarlo del escandaloso aumento de sueldo que el mismo Presidente autorizó para sí mismo, pero luego dio marcha atrás. "Lo he despedido. En este momento lo están notificando. Fue por este error que no debió haber cometido", dijo Milei sin hacer mención a que el documento no tenía la firma de Yasín, sino la suya, la de la ministra de Capital Humano, Sandra Petovello, y del jefe de Gabinete, Nicolás Posse.</t>
+  </si>
+  <si>
     <t>"Dejar al Conicet sin personal implica paralizarlo y poner en riesgo a la ciencia"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/722734-dejar-al-conicet-sin-personal-implica-paralizarlo-y-poner-en</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Dejar al Conicet sin personal implica paralizarlo y poner en riesgo a la ciencia". Comunicado del organismo contra los despidos anunciados por el Gobierno. El documento advierte que el rol de los trabajadores que Milei busca dejar en la calle resulta "esencial" para la formación de "el futuro de la ciencia nacional y del desarrollo federal del país".. El directorio del Conicet emitió un comunicado expresando el total rechazo a la decisión de limitar al 31 de marzo la renovación de contratos de personal administrativo y técnico de la institución, que alcanza a 1.600 empleados. El documento busca evitar el recorte anunciado por el Gobierno nacional, que busca reducir entre un 20 y 30 por ciento del personal de la administración pública nacional, y advierte que el personal que se intenta eliminar resulta "esencial" para la formación de "el futuro de la ciencia nacional y del desarrollo federal del país".
+El directorio, integrado por ocho miembros, advirtió también a la Casa Rosada que el Conicer "cuenta con un Plan Estratégico 2022-2025 y debe regir su funcionamiento" bajo ese paragüas acordado en leyes votados por el Congreso. "La recepción en forma verbal de una orden de reducir la planta de personal basada en un porcentaje arbitrario de ésta es la antítesis de una decisión basada en evaluaciones de desempeño o en criterios de razonabilidad y pertinencia de las tareas que se realizan", descalificó el directorio del Conicet el avance de la motosierra del presidente Javier Milei.
+Milei puso como presidente del Conicet a Daniel Salamone --un veterinario y biotecnólogo, conocido por el mandatario por la clonación de sus perros--, pero la conducción del organismo es compartida con el directorio conformado por cuatro investigadores activos de las áreas de Ciencias Sociales y Humanidades (Mario Pecheny), Ciencias Biológicas y de la Salud (Claudia Capurro) , Ciencias Exactas y Naturales (Roberto Rivarola), y Ciencias Agrarias, Ingeniería y de Materiales (Alberto Baruj).
+Y otros cuatro representantes por el Consejo de Universidades (Jorge Aliaga), organizaciones representativas de la industria (María Laura Correa) organizaciones representativas del agronegocio (Manuel García Solá) y de los máximos organismos responsables de la ciencia y la tecnología de los gobiernos provinciales (Luz Lardone).
+Esos integrantes del directorio denunciaron, tras una asamblea extraordinaria, que el plan de recorte que aplicará el Gobierno carece "de la mínima formalidad que requiere un organismo público para su gobernanza". "Dejar al CONICET sin el personal administrativo y técnico necesario implica paralizarlo y poner en riesgo el funcionamiento de un actor central del sistema de ciencia y tecnología nacional", repudiaron en el documento y remarcaron el reconocimiento que el organismo tiene a nivel regional e internacional.
+Según detalla el documento, los 1.600 empleados administrativos y técnicos cuyos contratos podría no ser renovados en abril son "esenciales" para el funcionamiento de las carreras de investigador (de 12.150 miembros); del personal de apoyo (3.050 miembros) y de 10.900 becarios doctorales y posdoctorales, que se forman en tareas de investigación científica y tecnológica.
+"Este personal administrativo y técnico contratado, altamente especializado y capacitado, trabaja en CONICET desde hace años dando soporte a los procesos de planeamiento, seguimiento y evaluación de actividades de investigación, y permite el funcionamiento de los más de 300 institutos y Centros Científicos Tecnológicos que se encuentran en todo el territorio nacional", explicó el directorio.
+La motosierra de los puestos de trabajo en la administración pública nacional comenzó a dos semanas de la asunción presidencial, cuando se anunció la no renovación de 7 mil contratos suscriptos en 2023. Esa nueva etapa, en la que se espera una reducción de 20 al 30 por ciento del personal, estaba comandada por Armando Giubert, secretario de Transformación del Estado, quien presentó su renuncia el lunes, tras el escándalo por el aumento salarial del Presidente.
+Los integrantes del directorio del Conicet también manifestamos "preocupación" por la falta de certeza en relación con la formalización de los ingresos a la Carrera del Investigador Científico (CIC) 2022 y la efectivización de las promociones de la CIC, como de los concursos de Personal de Apoyo. Y sostuvieron que los cambios ejecutados en esas áreas "van a tener consecuencias muy negativas que se van a prolongar por años".
+Por último, el directorio le recordó al presidente Javier Milei que el CONICET cuenta con un Plan Estratégico 2022-2025, aprobado por las leyes de Ciencia, Tecnología e Innovación (25.467), de Financiamiento del Sistema Nacional de Ciencia, Tecnología e Innovación ( 27.614) y Plan Nacional de Ciencia, Tecnología e Innovación 2030 (27.738).
+Además de las censantías ejecutadas en 2023, el plan de desguace estatal de Milei avanzó con recortes en el PAMI, 165 despidos en la Agencia Nacional de Discapacidad, más de 200 en AYSA, 50 en el ENACOM, 50 en el Conicet, 26 en la Secretaría de Derechos Humanos, 170 en el Incaa, entre muchos otros; y los anuncios del cierre de Telam (700 empleados), el Inadi (400 empleados) y el Instituto de Agricultura Familiar (900 empleados), que no fueron operativizados.</t>
+  </si>
+  <si>
     <t>“Por la senda de Juan”</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/721875-por-la-senda-de-juan</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    “Por la senda de Juan”. Desde Paraguay para América Latina. Un libro que hace memoria del aporte del intelectual paraguayo Juan Díaz Bordenave a la educación y la comunicación a partir de los recuerdos y los testimonios de quienes fueron sus colegas, discípulos y admiradores a lo largo y ancho del continente.. “Por la senda de Juan. Desde Paraguay, América Latina y otros sures” es el título del libro compilado por Oscar Cáceres Jiménez y editado en Asunción (Paraguay) por el Instituto Latinoamericano de Comunicación, para hacer memoria y recoger testimonios sobre los aportes a la comunicación, y en particular a la comunicación popular, de quien fuera en vida uno de los más brillantes intelectuales paraguayos contemporáneos: Juan Díaz Bordenave (1926-2012).
+A lo largo de 265 páginas la obra reúne aportes, consideraciones y testimonios de comunicadores y comunicadores de toda América Latina que compartieron con Díaz Bordenave tareas, jornadas de reflexión, encuentros, congresos y, sobre todo, perspectivas respecto de la comunicación, la educación y la política. Entre quienes sumaron sus aportes a este libro se cuentan figuras reconocidas de la investigación de la comunicación en la Argentina como Daniel Prieto Castillo, Sandra Massoni y Gustavo Cimadevilla, el uruguayo Gabriel Kaplún, y los bolivianos Alfonso Gumucio Dagron y Luis Ramiro Beltrán. En total son 22 autoras y autores que aportan desde diferentes capítulos sobre educación, interculturalidad y ciudadanía relacionadas con la comunicación y a ello de sumas testimonios, memorias y recuerdos sobre la vida y la obra del intelectual paraguayo.
+Fue en Montevideo, en mayo de 2012 y con ocasión del Congreso de la Asociación Latinoamericana de Investigadores de la Comunicación (ALAIC), cuando con la sencillez y la humildad que siempre le fue característica, Díaz Bordenave intentó desmentir el calificativo de “investigador” con el que fue presentado para dar su conferencia magistral en ese foro continental. “Yo no soy investigador en el sentido clásico de la investigación”, dijo entonces. “La investigación es una cosa formal, tiene rigor científico, yo no lo sigo. Mi misión es la divulgación, la interpretación que exige la creación de nuevos conocimientos”, agregó.
+Uno de sus grandes amigos y colega con quien compartió tareas fue el boliviano Luis Ramiro Beltrán (1930-2015), uno de los pioneros de la investigación en comunicación en América Latina. Al recordarlo Beltrán decía que “Juan Díaz Bordenave emprendió la reflexión sistemática sobre la comunicación horizontal, poniendo énfasis en la participación del pueblo en la toma de decisiones sobre asuntos de interés público, por medio de la comunicación libre y dialógica”.
+En ese sentido Díaz Bordenave estaba lejos de ser un investigador “en el sentido clásico”. En una entrevista que se le hizo con ocasión de una de sus visitas a Bolivia sostuvo que “la nueva comunicación y la nueva educación, pueden servir para revertir la dominación, para desarrollar ideas en que el verdadero protagonista del cambio es el obrero, el campesino, las clases populares y no los gobiernos y empresarios solamente”.
+En 1982 Díaz Bordenave escribió en la revista Chasqui, de CIESPAL, que "la comunicación participativa o alternativa no aparece como algo aislado, sino como un instrumento orgánico de las organizaciones populares y como una herramienta de participación”. Ya entonces tenía absoluta claridad respecto del rol político de la comunicación. Más cerca en el tiempo advirtió que “el viejo modelo civilizatorio representado por el capitalismo occidental se está desmoronando y la humanidad está buscando un modelo que lo sustituya. Al capitalismo nunca le faltó ingenio y astucia y utiliza la comunicación y los comunicadores como instrumento para continuar en pie”.
+Hizo también la “apología de la escucha”. Para comunicar, decía, es imprescindible escuchar, mucho y con atención. Su comunicación comenzaba por la escucha. Y la investigación por el mismo lugar. Luego venía la reflexión, la palabra serena, el señalamiento profundo y agudo. Y la pedagogía del maestro. Se lo escuchó cientos de veces contando historias, anécdotas de su vida y de la de tantos y tantas a los que conoció a través de su infatigable transitar por el mundo, particularmente por América Latina. Y rescatando historias de la vida de las personas con las que dialogaba y compartía. Esa era su estrategia pedagógica y comunicacional: partir del otro, ponerse en el lugar del otro.
+Aunque forzosamente tuvo que vivir fuera de Paraguay por razones de exilio, amó entrañablemente a su pueblo y dio testimonio de ello cuando decidió regresar a su país para integrar la Comisión de Verdad y Justicia y respaldar la tarea comunicacional y educativa del gobierno del presidente Fernando Lugo. Tanta fue su entrega, la participación en foros, en encuentros con organizaciones populares, los miles de kilómetros recorridos, como su dolor y su frustración cuando Lugo fue destituido por un golpe institucional.
+En un mensaje electrónico enviado a sus amigos en el exterior afirmó entonces, sin ninguna ambigüedad, que “el golpe parlamentario” es “mercenario y farisaico” y “en mi percepción, se trató de una manifestación natural de la confrontación continental y mundial de dos conceptos antagónicos de democracia: aquella que la ve como el gobierno del pueblo, por el pueblo y para el pueblo, y aquella que la ve como el gobierno de las clases dominantes, por las clases dominantes y para las clases dominantes”. Aseguró también en esa ocasión que “los principales autores del golpe no obraron por ideales sino por intereses” y que entre los golpistas “estaban terratenientes latifundistas, empresarios del agronegocio sojero y propietarios de industrias”. Completó su análisis diciendo que junto a los mencionados se agruparon “miembros de la alta burguesía, políticos de partidos tradicionales, religiosos conservadores, jefes militares, miembros de la clase media alta, representantes paraguayos de multinacionales”, porque todos ellos estaban “preocupados por la amenaza que, en su entender, Lugo representaba para sus propiedades, intereses y privilegios”.
+Cuando en una oportunidad publicamos en Página 12 una reflexión sobre la política en Paraguay bajo el título “declaraciones de intelectual paraguayo” su única observación fue: “¿Por qué me tildaron de intelectual? Yo no soy un intelectual, soy un simple comunicador y educador”.
+wuranga@pagina12.com.ar</t>
+  </si>
+  <si>
     <t>De gringadas torpes, cipayaje y dolor de Patria</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/721735-de-gringadas-torpes-cipayaje-y-dolor-de-patria</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    De gringadas torpes, cipayaje y dolor de Patria. . Esta semana y en veloz acción, Axel Kicillof, a través de su ministro de gobierno Carlos Bianco, puso la debida atención sobre el dizque "convenio" o "acuerdo" entre la Administración General de P. Esta semana y en veloz acción, Axel Kicillof, a través de su ministro de gobierno Carlos Bianco, puso la debida atención sobre el dizque "convenio" o "acuerdo" entre la Administración General de Puertos (AGP) y el Cuerpo de Ingenieros del Ejército de los Estados Unidos para intervenir en el río Paraná.
+Provocación infame, y hasta algo zonza, que no fue suficientemente repudiada por inconstitucional y absurda, toda vez que el supuesto acuerdo jamás pasó por el Congreso ni fue informado previamente al periodismo ni a la ciudadanía. Y ello además del dato fundamental de que el US Army Corps of Engineers no es una institución par del sistema democrático argentino, tanto así que el anuncio fue tan torpe que ni siquiera informaron al Ministerio de Defensa ni a la Armada Nacional ni a la Prefectura Naval Argentina. Lo que es elemental en cuestiones de Soberanía en aguas jurisdiccionales.
+Esto, que en cualquier barrio se llama vulgarmente "tomada de pelo", es altamente ofensivo para nuestro país y sencillamente insostenible. Sobre todo ante el inexplicable silencio del gobierno nacional y del sistema mentimediático.
+Para colmo, el texto del dizque "acuerdo" contiene ridículas disposiciones como que "cada participante conserva autonomía para llevar a cabo investigaciones independientemente"... Y encima impone ridículas "Restricciones sobre la divulgación" del supuesto convenio. Que termina con que "Los Participantes acuerdan que todos los datos, documentos e información obtenidos para la ejecución (...) así como los análisis, informes o programas generados que sean considerados como información no divulgable, no podrán ser divulgados total ni parcialmente". Increíble, o sea.
+Y por si fuera poco, la torpeza se perfecciona en el punto "Resolución de Diferencias", donde se dice que "se espera" que las mismas "se resuelvan únicamente mediante consultas informales entre los Participantes y no se contempla la remisión a ningún tribunal nacional o internacional ni a ninguna otra persona o entidad para su resolución". Lo que hace pensar que muchos medios difundieron el mamarracho sin haberlo leído.
+Lo cierto es que no habiendo hasta ahora autorización de ninguno de los dos Congresos, es obvio que el presidente Milei quiere a toda costa militarizar el Paraná (para él Hidrovía, nombre impuesto por el cipayaje a nuestro magno río). Y ante eso Kicillof exigió información clara y veraz, ya que la provincia que gobierna integra el Ente Nacional de Control y Gestión del Paraná junto con las provincias de Formosa, Chaco, Corrientes, Entre Ríos, Misiones y Santa Fe.
+Por lo tanto y con todo derecho, AK entiende que este disparate puede tener "efectos directos" sobre los bonaerenses y los planes provinciales, ya que en ese absurdo "convenio" no hubo participación ni del Congreso ni de Cancillería.
+En estos contextos algunos sectores militantes se preparan para cuando este gobierno pase, porque va a pasar, más temprano que tarde y cuanto antes mejor. No son pocas las personas que hacen reserva moral de rechazo a todo lo actuado en contra de los intereses populares y de la Soberanía Argentina sobre todos los bienes naturales de la Patria, sean en tierra como en mar y en todas las aguas, y tanto en subsuelo como en espacio aéreo.
+Todo habrá que recuperar, y será una tarea ciclópea para la que ya se hacen reservas. Así, se conocen acciones en sectores patrióticos –como sabe de primera mano esta columna– donde hay "decisión tomada en el sentido de no aceptar las disposiciones, medidas y compromisos contrarios a los intereses históricos de la República Argentina y que hayan sido asumidos por el actual gobierno en desmedro de los esenciales intereses de la Patria". Altisonante decisión que sin embargo, y como no podía ser de otro modo, crece en ámbitos políticos, culturales y económicos, y en todas las provincias.
+Puede que sorprenda a algunos dirigentes de las más diversas militancias políticas –en especial los que siempre llegan tarde pero se colocan rapidito en primera fila– pero en estas materias todo optimismo es bueno. Y más si se trata de hacer docencia cívica respecto del delito de traición a la Patria, que sólo una vez fue juzgado y terminó con una condena, en 1936. De donde es obvio que ha sido blanda la Argentina al tolerar a decenas de traidores que ni siquiera fueron a juicio.
+Por eso, sirva como ejemplo de amor a este país la actitud de juristas que están impulsando acciones tendientes a juzgar y condenar al presidente Milei. El abogado porteño Daniel Valmaggia hizo punta con una demanda hace un mes y medio; y la semana que pasó, y con extraordinaria precisión, se inició desde Córdoba un severo proceso jurídico contra el todavía primer mandatario. La denuncia penal fue presentada en la Fiscalía de Turno de la Justicia Federal de Córdoba, y denuncia la derogación de la Ley de Tierras 26.737 en abierta violación al Tratado de Escazú y al Convenio 169 sobre Derechos Indígenas.
+Esta denuncia incluye a todos los ministros que firmaron el DNU 70/2023, quienes "habrían incurrido en incumplimiento de deberes, abuso de autoridad y asociación ilícita". El texto sostiene además que: "Al derogar la Ley de Tierras, que limitaba la compra de propiedades por personas y corporaciones extranjeras, el presidente puso una ilimitada bandera de remate para bosques nativos, glaciares, zonas con abundante agua subterránea y yacimientos de minerales valiosos".
+La presentación judicial, de 76 páginas, fue presentada el pasado 5 de marzo por el Dr.Raúl Montenegro, profesor titular en la Universidad Nacional de Córdoba y director del Campus Córdoba del Right Livelihood College, institución con sede en Bonn, Alemania, que desde 1980 otorga el Premio Nóbel Alternativo. En 2004 Montenegro lo recibió en el Parlamento Sueco. Y ahora, con el patrocinio del ex Juez Federal cordobés, Miguel Julio Rodríguez Villafañe, presentaron todos los argumentos jurídicos que tornan al DNU como "de nulidad absoluta e insanable".
+Pero lo más potente de esta demanda consiste en que además de Milei se incluye, como denunciados penalmente, a los ministros Nicolás Posse, Guillermo Francos, Diana Mondino, Luis Petri, Luis Andrés Caputo, Patricia Bullrich, Mario Antonio Russo, Mariano Cúneo Libarona, Guillermo José Ferraro y Sandra Pettovello.
+La denuncia judicial también pide a la Justicia que "investigue cómo se elaboró el DNU que deroga la Ley de Tierras, en particular si participó o no Federico (Sturzenegger, presumiblemente), y/u otros consultores, y si estos mantuvieron contactos previos con personas y empresas que pudieran beneficiarse con la derogación de esa ley". Tras calificar de "salvaje e insensata" la política de destrucción de organismos del Estado que controlan a corporaciones, en la presentación se señaló que las modificaciones propuestas en el proyecto de Ley Ómnibus a las leyes de bosques, glaciares e incendios "complementan descaradamente la derogación de la Ley de Tierras" y le dan impunidad a megamineras, industrias contaminantes y agronegocios. No es posible que décadas de luchas sociales exitosas y un responsable trabajo parlamentario sean destruidos por una persona que muestra crueldad, intolerancia y desconocimiento de la crítica situación socio-ambiental de la Argentina. Ya se cuentan espontáneas listas de adhesiones al Manifiesto que fue hecho circular esta semana con las causales de acusación.</t>
+  </si>
+  <si>
     <t>Retiro del Estado social</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/720986-retiro-del-estado-social</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Retiro del Estado social. . Tratemos de señalar algunas causas concurrentes de lo que ocurre en Rosario.. Tratemos de señalar algunas causas concurrentes de lo que ocurre en Rosario.
+1) Un sistema judicial burocrático, ineficiente y con vínculos con el delito que debe investigar.
+2) Una policía corrompida que descubrió que el narcotráfico es más negocio que la prostitución o los desarmaderos.
+3) Gobiernos que no mensuraron la gravedad del problema y erraron sistemáticamente con las soluciones, entre el punitivismo inconducente, la indolencia y la complicidad.
+4) Una ciudad en plena zona núcleo, donde abundan muchos recursos del agronegocio que se lavan junto al dinero de origen ilegal.
+5) Una ciudad puerto y enclavada en un cruce de rutas decisivas,, donde circulan habitualmente sustancias prohibidas en cantidad.
+6) Una ciudad de base industrial, donde han aumentado crecientemente las desigualdades, primero durante el menemismo y luego durante el gobierno de Mauricio Macri.
+7) El actual gobernador tomó una serie de medidas de control penitenciario destinadas a detener el delito que se ordenaba desde las cárceles, pero sin el debido control del territorio por los falencias ya señaladas de los cuerpos policiales. Eso ha desatado una serie de espantosas represalias criminales que son las que vemos en estos días.
+8) Para este drama no hay soluciones rápidas, ni se puede abordar solo desde una mirada represiva aunque sea lo necesario en esta coyuntura.
+9) Acá efectivamente hace falta una política de estado, duradera, que implique básicamente una justicia rápida, una policía honesta y la reconstrucción de un tejido social que requiere más y mejor trabajo, más y mejor educacíón pública, más y mejor utilización del espacio público.
+10) Los iniciativas promovidas por las ideas libertarias no colaboran en lo absoluto. En Rosario, el retiro del Estado social es sinónino necesario de avance de los narcos.</t>
+  </si>
+  <si>
     <t>Huelga total en Acindar de La Matanza</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/718919-huelga-total-en-acindar-de-la-matanza</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Huelga total en Acindar de La Matanza. Protestas por suspensiones y amenazas de despidos en varios puntos. Paro total en la planta de Acindar de La Tablada, despidos en Siderar de San Nicolás y cortes de ruta en Villa Constitución.. La UOM de La Matanza realizó este jueves un paro histórico en Acindar: por primera vez logró un acatamiento del ciento por ciento. En simultáneo, crecen los conflictos San Nicolás y su vecina santafesina, Villa Constitución. Las plantas afectadas por la decisión de la acería multinacional ArcelorMital son esas tres y una de Rosario. Dos en la provincia de Buenos Aires y dos en la provincia de Santa Fe
+En ese contexto, el secretario general de la UOM a nivel nacional y ex diputado nacional por la provincia de Buenos Aires, Abel Furlán, señaló que "Milei no tiene a los sectores productivos en su radar, y nunca habla de trabajadores ni de industria".
+También cargó contra uno de los grupos empresarios del sector al afirmar que "el grupo Techint, en diciembre, incrementó el valor de la chapa casi en un 100 por ciento, han hecho un festival con los precios del acero en los últimos 90 días, y eso lo pagó el pueblo argentino".
+Su par de la seccional La Matanza, con jurisdicción sobre la planta de Acindar en La Tablada, Esteban Cabello, explica detalladamente la situación: "Van a cerrar las cuatro plantas, pero no en simultáneo, sino de acuerdo a la etapa del proceso industrial, porque no todas hacen lo mismo. Nosotros, en La Tablada, hacemos trefilación con lo que ellos funden. Si ellos dejan de fundir, no tenemos cómo hacer los alambres e insumos para el campo. Nos toca parar desde el lunes 18".
+El conflicto de fondo es salarial ya que, según dicen, la empresa quiere suspender a los trabajadores para no pagarles el salario completo durante ese mes, aunque los trabajadores advierten que esas suspensiones necesitan de sus firmas. "Nosotros tenemos el mismo salario de noviembre, con 70 puntos de inflación en el medio, entonces no vamos a aceptar ninguna suspensión si no actualizan salarios", afirman a Buenos Aires/12. "Había una conciliación obligatoria que terminó el lunes. En estos días lo explicamos en asamblea y todos los trabajadores lo aceptaron. Por eso hoy no fue nadie a trabajar."
+La planta de Acindar en La Tablada tiene hoy 400 empleados. Llegó a tener 4 mil en su mejor momento, antes de la dictadura. Es tan grande que buena parte de lo que entonces era industria se aprovecha ahora como depósito.
+Además del cierre transitorio de sus plantas en el país, la empresa despidió recientemente a 250 trabajadores, entre 150 tercerizados y 100 contratados. El principal argumento para el ajuste es la falta de demanda de sus productos, en el contexto de una caída general y abrupta del consumo y la actividad económica, que algunos economistas ya comparan con 2001.
+Sus distribuidores no venden ni al campo ni a la industria ni a la construcción, sus principales mercados. Entonces los stocks no bajan y la empresa prefiere frenar la producción.
+Uno de los grandes clientes de Acindar era el conjunto de contratistas del Estado, a través de la obra pública, que compraba varillas, perfiles y hierros de construcción en general. Se trata del primer sector atacado por la motosierra, cuyas consecuencias comienzan a hacerse visibles ahora. Arcelor Mittal, una de las principales siderúrgicas del mundo, acaba de comprar una empresa en Estados Unidos por 14 mil millones de dólares.
+[H3] San Nicolás y Villa Constitución
+Acindar cuenta con más de 3000 empleados y 80 años de trayectoria en Argentina. Tiene dos plantas en la provincia de Buenos Aires, una en la localidad de La Tablada, partido de La Matanza, y otra en San Nicolás. Esta última, pertenecía originariamente a Somisa, la empresa pública que el menemismo privatizó durante los años noventa, convirtiendo a la ciudad en una de las de mayor índice de desocupación del país.
+La empresa no constituye un caso aislado. En la planta de San Nicolás de Siderar, empresa del Grupo Techint, que encabeza el aliado del gobierno Paolo Rocca, según denuncia el sindicato se dan “despidos hormiga, de a uno, dos o tres trabajadores, por debajo del radar, para evitar un conflicto masivo”, al tiempo que presionan a los trabajadores de más de 50 años para que acepten retiros voluntarios.
+También peligran los casi 200 empleos de Motomel, que ensambla motovehículos con alto porcentaje de componentes procedentes de China, cuyo ingreso al país se encuentra muy restringido. El miércoles, a pocos kilómetros de allí, en el partido de Ramallo, el frigorífico Arre Beef suspendió a 200 trabajadores. El principal mercado del frigorífico es China y sus compras cayeron abruptamente a partir del inicio de la gestión Milei y su oscilante relación esa potencia.
+Este jueves, encabezada por la UOM de Villa Constitución, y apoyada por el resto de la CGT local y varios sindicatos nicoleños, una nutrida manifestación cortó la ruta 9 en el límite interjurisdiccional entre las provincias de Buenos Aires y Santa Fe, por el cierre de la planta local de Acindar.
+El secretario general de la seccional Villa Constitución de la UOM es Pablo "Piparra" González, quien sostuvo que "la movilización no es sólo en defensa de los trabajadores de Acindar sino de todo el pueblo, porque si Acindar cierra, acá no va a quedar nadie. Ellos ya anuncian suspensiones, sin haber hablado ni acordado con nosotros, si lo hacen realmente, el conflicto sigue y nosotros seguimos en la ruta como hoy", explica el dirigente. González agrega que "entre los despedidos hay gente que votó a Milei, muchos de ellos contratados y ahora, de a poco, van asimilando lo que significa. Si entra acero chino al país no hay más trabajo para nadie", advierte.
+“Villa Constitución tiene una cultura muy particular. Acindar es el principal empleador y principal contribuyente. Todos, del almacenero al empleado municipal, saben que el pueblo es Acindar- dependiente. Entonces se movilizan para defender lo que les corresponde, del primero al último”, explica un sindicalista de la localidad vecina.
+De hecho, se armó una multisectorial donde, además de los sindicatos, están los estudiantes, comerciantes y pymes entre otras representaciones. El viernes 8 culmina la conciliación laboral dictada por el gobierno y la multisectorial se encuentra alerta, a la espera de posibles anuncios de despidos.
+El conflicto se desarrolla a pocos kilómetros del predio donde funciona Expoagro, la feria tradicional del agronegocio argentino, que la poderosa familia Passaglia le alquilan al Grupo Clarín. Tal como informó este diario el lunes por la noche, el gobernador Axel Kicillof asistió, en calidad de orador, a la cena de expositores, acompañado de su ministro Javier Rodríguez. Allí pidió una marcha atrás de las medidas que afectan a Buenos Aires, Santa Fe, Córdoba y Entre Ríos.
+El miércoles estuvo el presidente Javier Milei. El intendente Santiago Passaglia hizo malabares para esquivar la foto con él, disgustado porque el clan esperaba que el gobierno designara a su hermano Manuel al frente de ANSeS, algo que hasta acá no ocurrió.</t>
+  </si>
+  <si>
     <t>Macri, en su hábitat natural: entre el mensaje a Milei y su rearmado en el PRO</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/718829-macri-en-su-habitat-natural-entre-el-mensaje-a-milei-y-su-re</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Macri, en su hábitat natural: entre el mensaje a Milei y su rearmado en el PRO. El paso del expresidente por Expoagro. "Es él, su hermana y las redes", dijo en lo que no se supo si fue un elogio o una reflexión acerca del respaldo del Presidente.. El ex presidente Mauricio Macri visitó la muestra ExpoAgro 2024, el corazón del agronegocio que abraza las nunca cumplidas promesas de la derecha de terminar con las retenciones, con una mirada crítica hacia el presidente Javier Milei: "Él es él, su hermana y las redes sociales", lo calificó ante la platea de empresarios y se mostró distante de una posible alianza con La Libertad Avanza: "Ahora, lo que nos toca a todos es estar a la altura de la circunstacia, ser generosos y humildes en las ideas de fondo".
+En las últimas semanas, y tras el rol clave de la bancada del PRO en el respaldo sin miramientos a la fracasada Ley Ómnibus, la posibilidad de una alianza entre el partido fundado por Macri y del presidente Javier Milei resonó fuerte, incluso para llegar juntos a las legislativas de 2025. El respaldo de Macri en el denominado "pacto de Acasusso" para la victoria de Milei en segundo vuelta y el nombramiento de ex funcionarios macristas en el Gabinete de la ultraderecha como Patricia Bullrich --saliente presidente del PRO-- y Luis Caputo fueron también evidencia de los acuerdos alcanzados.
+Sin embargo, a días de las elecciones internas del PRO del 19 de marzo, en las que Macri se espera que llega como único candidato a presidente del partido, poniéndose de nuevo en un lugar de decisión dentro del sistema político, hicieron que el ex presidente mida de otra manera sus palabras y se muestre más lejos de Milei. "La decisión de ustedes, de los argentinos, es que querían un shock en el sistema político", señaló a la audiencia.
+En ese análisis, Macri diferenció incluso a Milei de los liderazgos de derecha de los ex presidentes Donald Trump y Jair Bolsonaro. "Este es un verdadero outsider, no es Trump como dicen: Trump tenía al partido republicano atrás, Bolsonaro tenía al Ejército atrás. Él es él, su hermana y las redes sociales", marcó Macri, que en pocos días tendrá detrás de él a todo el PRO.
+"Bueno, ha generado un shock. Ahora lo que nos toca a todos es estar a la altura de la circunstancia, ser generosos y humildes en las ideas de fondo", analizó Macri tomando distancia. En ese contexto, el ex presidente señaló que el partido amarillo se está "reorganizando" y que la idea es "volver a estar juntos", enfatizando en la daña relación entre Bullrich y el ex jefe de gobierno porteño Horacio Rodríguez Larreta, tras las internas del año pasado dentro de Juntos por el Cambio.
+Macri decidió mostrarse como un hombre de la política con un partido con experiencia detrás al recordar que su intención para en la conducción del PRO "es ayudar a ordenar la vuelta del partido, a volver al espíritu, el espíritu con el cual entramos a la política, tratando de incomodar a los partidos resistentes, generando una visión distinta con un foco fundamentalmente en la gente".
+"Es algo que hemos hecho en los lugares que gobernamos, donde hemos marcado una diferencia, mostrando que nuestra prioridad es que los impuestos de la gente vuelvan a la gente", marcó y, al hablar del Pacto de Mayo convocado por Milei, lamentó que "en los tiempos que me tocó a mí gobernar no tuve esa colaboración, pero espero que todos estemos crecidos, madurados, entendidos, que si seguimos siendo más de lo mismo nos va a ir igual de mal que nos ha ido en los últimos 40 años".
+En las palabras elegidas por el mandatario resuena el análisis hecho en esta semana por el diputado y jefe de bloque de Hacemos Coalición Federal, Miguel Pichetto, quien fue candidato a vicepresidente de Macri en 2019 y respaldó a Rodríguez Larreta en la campaña presidencial del año pasado. "Milei no vino de Marte. Es producto del error de Juntos por el Cambio, de la mala praxis política de haber ido a una interna y no construir o reconstruir el único liderazgo que tenía el PRO que era Mauricio Macri", sostuvo en una entrevista en el programa Duro de Domar.
+Pichetto dejó en claro que Macri debería haber sido nuevamente el candidato a presidente del espacio ya que "se fue con el 41 por ciento de los votos. Tenía una base electoral que le permitía ser medianamente competitivo". "Los liderazgos no se repliegan", le criticó por la decisión de retirarse de la contienda presidencial y le adjudicó: "La decisión abrió un proceso interno que determinó el fracaso de la coalición Juntos por el Cambio. Esa primaria no fue positiva". Habrá que ver si Macri estaba mirando Netflix, o si en el zapping sintonizó a su excompañero de fórmula.</t>
+  </si>
+  <si>
     <t>Compromiso de Roly Santacroce</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/718539-compromiso-de-roly-santacroce</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Compromiso de Roly Santacroce. El intendente de Funes recorrió la Expo Agro 2024. Roly Santacroce, intendente de Funes, visitó esta semana la Expo Agro 2024, uno de los eventos más importantes de Latinoamérica que en esta ocasión se lleva a cabo en la ciudad de San Nicolás.. Roly Santacroce, intendente de Funes, visitó esta semana la Expo Agro 2024, uno de los eventos más importantes de Latinoamérica que en esta ocasión se lleva a cabo en la ciudad de San Nicolás. Se trata de una megamuestra en la que entidades agroindustriales presentan todo su potencial.
+“Fervientemente creo que la agroindustria es un motor económico fundamental para el desarrollo de nuestro país. Cada puesto de trabajo en el sector representa un eslabón clave en la cadena de producción, desde el campo hasta la mesa”, comentó Santacroce luego de finalizar su recorrido por distintos stands de entidades agroindustriales que formaban parte de la jornada.
+El intendente concluyó: “Me comprometo a seguir apoyando y promoviendo el crecimiento de los productores de nuestra ciudad y nuestra provincia, porque sé que su prosperidad se traduce en beneficios para la región y en trabajo para los santafesinos. En estos ámbitos se observa que Argentina tiene un gran futuro”.
+Durante cuatro días se concentran compradores, vendedores, entidades financieras y rondas de negocios en un clima único, por lo cual ha sido bautizada La Capital Nacional de los Agronegocios. Para la nueva edición, la exposición sorprenderá con nuevos contenidos, espacios y servicios. Más tecnología y mejoras en el predio.</t>
+  </si>
+  <si>
     <t>Inflación, cepo "afuera" y vuelve Ganancias</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/718217-inflacion-cepo-afuera-y-vuelve-ganancias</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Inflación, cepo "afuera" y vuelve Ganancias. El Presidente Milei habló en la apertura de la muestra ExpoAgro. Les dijo "héroes" a los ruralistas mientras la sociedad se derrumba en la crisis. La restricción cambiaria se levantaría "a mitad de año" y esperan 15 de IPC.. El presidente Javier Milei participó de la apertura de la muestra rural ExpoAgro y trató de "héroes" a productores y empresarios del agro, mientras la crisis y el ajuste les pega duro a las clases medias y bajas. En paralelo, dejó tres definiciones sobre la economía que viene: la primera, que la inflación irá a la baja en el mes de febrero; la segunda, que planea abrir el cepo cambiario antes de mitad de año; y la tercera y más polémica es que el gobierno planea restituir el Impuesto a las Ganancias, en el marco de la discusión con las provincias por mayores ingresos.
+Durante una reunión privada de la que también participó el ministro del Interior Guillermo Francos, Karina Milei Secretaria General de la Presidencia y el vocero Manuel Adorni, declaró a los referentes del campo, Milei fue elogiado por los presentes y decidió jugar con elogios al campo: les dijo a los presentes que son “el sector productivo no sólo más fuerte en Argentina, sino el más productivo de todo el mundo”. Agregó que “como dije siempre, con la carga fiscal que tienen, que puedan seguir produciendo es fruto de un milagro; y ese milagro es porque son los mejores del mundo; así que, en primer lugar, felicitaciones a todos los héroes que se encuentran en este lugar, que son el corazón de la argentina”.
+Asimismo, mientras los precios siguen pegando muy duro, el mandatario develó cuál sería el dato de inflación de febrero. Dijo que se ubicará en torno al 15 por ciento y que el cepo sería levantado a mitad de año “si todo sale bien”. Cuando en diciembre dio 25% fue un éxito, porque los precios se retrajeron a la segunda semana. Este mes parece que la inflación va a estar en 15%”. Ese número, que para el Presidente es importante, sería, de darse, el más importante en 33 años para el mes de febrero, un período que suele tener precios bastante más moderados.
+En esa conversación, destacó además la importancia del sector en la economía y como promotor del desarrollo económico, repasó la situación en que está la economía y la profundidad de la crisis. En relación a los aumentos de precios, explicó que las correcciones se deben al atraso generado. Manifestó que hay contención social con la duplicación de la asignación universal por hijo. En paralelo, subrayó que el Gobierno se encontró con “mucha corrupción” y que se la está abordando.
+El Presidente llegó al autódromo de San Nicolás en helicóptero cerca del mediodía. Junto con José Luis Espert, mantendrá una reunión con empresarios invitados en el Centro de Agronegocios.
+En el primer día de muestra también estuvieron Martin Llaryora, Gobernador de Córdoba; Rogelio Frigerio, de Entre Ríos; Maximiliano Pullaro, de Santa Fe; Guillermo Francos, Ministro del Interior de la Nación; Manuel Passaglia, Intendente San Nicolás; Fernando Vilella, Secretario de Bioeconomía de la Nación e integrantes de la Mesa de Enlace.
+[H2] El cepo y Ganancias
+Por otra parte, el Presidente retomó la idea de reducir las restricciones cambiarias. Así, aseguró que “una vez saneada economía van a abrir el cepo”, algo que indicó podría suceder a mitad año. Esta situación ya la viene manifestando hace tiempo, y días atrás recibió por parte del Fondo Monetario Internacional (FMI) la recomendación de no mencionar estos temas porque generan incertidumbre. De hecho, las menciones de apertutra del cepo generaron, en el agro, la sensación de que cuando haya un levantamiento, el tipo de cambio será más alto que el actual. Ergo, las liquidaciones de exportaciones de granos se frenaron a la espera de un dólar más caro.
+El otro tema central que surgió en Expo Agro fue el regreso del cobro del Impuesto a las Ganancias de los trabajadores. El ministro del Interior, Guillermo Francos, confirmó que el Gobierno nacional insistirá en su propuesta de restituir el Impuesto a las Ganancias para la cuarta categoría como herramienta para mejorar la situación fiscal de las provincias. "La restitución de Ganancias es una propuesta del Gobierno para solucionar los temas fiscales de las provincias", señaló el funcionario en declaraciones a la prensa en la muestra en San Nicolás.
+La decisión de quitar la cuarta categoría de Ganancias fue del ex ministro Sergio Massa, y de volver a instaurarse perderían gran parte de esa recomposición una porción muy importante de los trabajadores formales y sindicalizados. Otro golpe al bolsillo.
+En este contexto, Francos supeditó esa medida a un pedido de las provincias y señaló que "los gobernadores están preocupados por su situación fiscal a partir del recorte de la gestión anterior a Ganancias", pero no aclaró más detalles sobre cómo será la postura de los mandatarios en esta nueva etapa de negociaciones.</t>
+  </si>
+  <si>
     <t>Organizaciones de todo el mundo advierten sobre los riesgos del trigo transgénico</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/715542-organizaciones-de-todo-el-mundo-advierten-sobre-los-riesgos-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Organizaciones de todo el mundo advierten sobre los riesgos del trigo transgénico. Solicitan la intervención de la ONU para regular el derecho a la alimentación saludable. En un documento conjunto, Asia, África y América Latina afirman que el trigo HB4 de la empresa Bioceres. No cuenta con estudios de inocuidad y denuncian que incluso tiene menos productividad que el trigo convencional.. Organizaciones de América Latina, África y Asia denunciaron los efectos nocivos del trigo transgénico que ya se consume en Argentina y amenaza llegar a otros países. En un detallado documento de 14 páginas, movimientos sociales, campesinos y pueblos indígenas solicitaron la intervención de relatores especiales de Naciones Unidas (ONU) por los riesgos para la alimentación, la salud y el ambiente que implica el transgénico de la empresa Bioceres. Confirmaron que no existen estudios independientes que confirmen su inocuidad, denunciaron al peligroso herbicida glufosinato de amonio e, incluso, afirmaron que es menos productivo que el trigo convencional.
+"No al trigo transgénico. Alianza mundial busca la intervención de la ONU contra el cultivo de trigo transgénico HB4", es el título del comunicado de la organización internacional Grain que da cuenta de la insólita --e irregular-- forma de aprobación del transgénico en Argentina, Brasil y Paraguay: en base a supuestos estudios de la propia empresa que lo comercializa e, incluso, con documentación que es confidencial.
+[H2] Sin estudios confiables
+Entre otros aspectos fundamentales, destacan que la población de Argentina se está alimentando con harinas que contienen un transgénico que carece de estudios respecto a la salud y, además, contaminado con el agrotóxico glufosinato de amonio (más letal que el conocido glifosato).
+"La aprobación del trigo HB4 ha causado mucha preocupación en un amplio sector de la sociedad, porque su siembra y consumo vulnerará derechos humanos, como el derecho a la vida, a la salud, a la alimentación adecuada y a la soberanía alimentaria, a un ambiente equilibrado y libre de contaminación, al acceso a la tierra y territorio; al derecho a autodeterminación de los pueblos y comunidades locales", señala el documento que fue dirigido a siete Relatores Especiales de Naciones Unidas.
+En consecuencia, se solicita que insten a los gobiernos de Argentina, Brasil y Paraguay para que suspendan las autorizaciones para el cultivo de trigo transgénico HB4. Los destinatarios son Marcos Orellana (Relator sobre Sustancias Tóxicas y Derechos Humanos), David Boyd (Derechos Humanos y Ambiente), Michael Fakhri (Derecho a la Alimentación), Pedro Arrojo-Agudo (Derecho al Agua Potable), Olivier De Schutter (Extrema Pobreza y DDHH), Francisco Cali Tzay (Derechos de los Pueblos Indígenas) y Tlaleng Mofokeng (Derecho a la Salud).
+[H2] Derecho a la alimentación
+El trigo transgénico fue desarrollado y es comercializado por la empresa de origen argentina Bioceres-Indear, donde tuvo un rol fundamental la científica del Conicet y de la Universidad del Litoral, Raquel Chan. La Comisión Nacional de Biotecnología (integrada exclusivamente por impulsores del agronegocio, incluso gerentes de las multinacionales) dio el visto bueno en 2018, a libro cerrado y sin publicar los estudios en ninguna revista científica. La aprobación final fue en mayo de 2022, cuando Julián Domínguez (entonces ministro de Agricultura) dio luz verde al pedido de Bioceres-Indear (la firma administrativa corrió por cuenta de Luis Contigiani).
+En marzo de 2023, la empresa Bioceres-Indear informó que 25 molinos ya mezclaban el trigo transgénico con el convencional para libre distribución. Se trata de un hecho de trascendencia mundial: por primera vez un trigo modificado genéticamente está en los alimentos de consumo masivo (pan, pizzas, empanadas, fideos y todos los usos de la harina). Y, más grave, la población no tiene posibilidad de identificar si está comiendo un producto con transgénicos o no: en Argentina no existe un etiquetado de transgénicos.
+Elizabeth Bravo, integrante de la organización Acción Ecológica de Ecuador y una de las impulsoras del documento dirigido a Naciones Unidas, recordó que Argentina es un país exportador de trigo, y destacó el riesgo para la población: "El trigo es fundamental en la dieta de los ecuatorianos, como de muchos otros pueblos del mundo, porque está presente desde el desayuno hasta la cena. Sería terrible que comencemos a comer un trigo que proviene de una modificación genética y que además tiene residuos mayores de plaguicidas como glufosinato de amonio".
+[H2] Una tecnología deficitaria
+Leonardo Melgarejo es integrante del Movimiento Ciencia Ciudadana de Brasil e integrante de la Uccsnal (Unión de Científicos Comprometidos con la Sociedad y la Naturaleza de América Latina). El activista remarcó la enorme gravedad de que el trigo transgénico no cuente con evaluación científica de impactos en la salud de la población. "Este transgénico se ha transformado de un problema internacional, por eso esta acción conjunta de organizaciones de tres continentes. Este trigo contamina la alimentación básica de las población y sin dudas va a contribuir en el acaparamiento de tierras en pocas manos y la afectación del agua, de la vida campesina y de los pueblos indígenas", afirmó.
+Fernando Frank, investigador de Argentina, ingeniero agrónomo e integrante de Uccsnal, apuntó a un eje central que desnuda la publicidad empresaria y mediática respecto al trigo de Bioceres. "El trigo HB4 es un fracaso productivo, es un escándalo porque, además de los impactos negativos en la salud y la alimentación, están vendiendo una tecnología que promete producir más pero que en realidad produce menos, lo confirman los propios datos certificados por el Estado", afirmó Frank.
+Frank y Melgarejo son dos de los autores de la publicación científica "Controversia por el pan nuestro de cada día", publicada a fines del año pasado, que confirma que el trigo transgénico es menos productivo que el trigo convencional. Firmada además por los investigadores Gabriel Bianconi Fernandes y Rubens Onofre Nodari, el paper da cuenta, con tablas y cifras del Ministerio de Agricultura de Argentina, que el trigo transgénico tiene menos productividad que su variante convencional. "Los rendimientos (del trigo transgénico) fueron significativamente inferiores a la media de trigo del país. La conclusión es que el mayor rendimiento de la variedad HB4 --la principal ventaja anunciada por Bioceres-- no ha sido probado en el campo", ratifica el estudio científico.
+En 2020, más de mil científicos del Conicet y de 30 universidades públicas de Argentina repudiaron la aprobación y alertaron los riesgos para la salud de la población e, incluso, para la producción agropecuaria y los derechos humanos. “Esta autorización remite a un modelo de agronegocio que se ha demostrado nocivo en términos ambientales y sociales, causante principal de las pérdidas de biodiversidad, que no resuelve los problemas de la alimentación y que amenaza además la salud de nuestro pueblo confrontando la seguridad y la soberanía alimentaria”, comenzaba el escrito dirigido al gobierno nacional y a las autoridades del Conicet.</t>
+  </si>
+  <si>
     <t>La semilla del agronegocio</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/712987-la-semilla-del-agronegocio</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La semilla del agronegocio. Rechazo de la Mesa Agroalimentaria a la adhesión a UPOV 91. Pone en jaque el control de la cadena agroalimentaria, y por lo tanto la disponibilidad, la calidad y el precio de los alimentos de todas las y los argentinos.. Dentro de los beneficios para las corporaciones que se incluye en la llamada Ley Ómnibus devuelta a comisiones de la Cámara de Diputados por falta de consenso, el artículo 210 es un regalo especial para las grandes trasnacionales del agronegocio, ya que establece la adhesión de Argentina al convenio de 1991 de la Unión Internacional para la Protección de las Obtenciones Vegetales (UPOV 91).
+UPOV 91 es el escenario jurídico ideal para que los oligopolios controlen completamente el mercado de semillas y por derivación, el de alimentos. Como el resto de los capítulos del Proyecto de Ley Ómnibus que envió el Poder Ejecutivo Nacional, la adhesión a UPOV 91 también tiene dueño: las primeras seis grandes empresas transnacionales de semillas que ocupan el 58 por ciento del mercado mundial de semillas (Bayer 23 por ciento, Corteve Agriscience 17 por ciento, Chem China/Syngenta 7 por ciento, Basf Alemania 4 por ciento, Group Limagrain 4 por ciento y KWS 3 por ciento) y sus socias locales: Bioceres y Don Mario.
+Con el Acta UPOV 91 se cometería el despojo más grave en la historia de la humanidad. Si se contaminan los materiales nativos por materiales patentados, o se introducen genes patentados a ellas, los genes patentados que interactúen con los materiales nativos otorgarían el derecho de propiedad a los dueños de las patentes. Allí se constituye una apropiación, cercenando derechos ancestrales, actuales y futuros. Visto de esta forma, se deteriora la soberanía alimentaria y las multinacionales se constituirán en los dueños de la comida.
+Con la excusa de incentivar inversiones, este tratado da vía libre a la privatización de las semillas que son propiedad de los pueblos, de las familias campesinas e indígenas que, generación tras generación, han seleccionado, guardado, reproducido e intercambiado diversidad de plantas que hoy son parte de nuestros alimentos, de nuestra cultura y de nuestra riqueza.
+UPOV 91 reconoce la propiedad intelectual, pero elimina el uso propio gratuito, acepta que se patenten materiales vegetales, prohíbe el uso gratuito de variedades existentes para crear nuevas variedades, además de reconocer que hay derechos por el producto resultante de la semilla protegida.
+Los derechos de los obtentores y sus inversiones no estarían respaldados nunca, si no hay sistemas de control estatal del comercio de semillas. Se trata de confundir derechos legítimos de propiedad intelectual, con sistemas de expoliación de la renta basados en controles sobre productos derivados de la siembra de semilla protegida.
+Con UPOV 91 se crearía la doble imposición: pagamos en el campo por la semilla y luego en el puerto por el producto. Se estarían incorporando a nuestro sistema legal mecanismos de criminalización de agricultores y agricultoras. Quienes puedan usar la semilla en ciclos productivos posteriores, limitando o prohibiendo el derecho de uso propio gratuito.
+Hasta ahora, Argentina adhiere a UPOV 78, aceptando legislar en favor de un sistema que reconoce la propiedad intelectual, habilita el uso propio gratuito y acepta que nuevas obtenciones deriven de las viejas obtenciones sin costo para quien mejora.
+A los que fundamentan la adhesión a UPOV 91 por un presunto crecimiento y mayor rendimiento de la producción, le respondemos que la productividad no sólo está asociada a la genética. Principalmente depende del suelo, su preparación, la fecha de siembra, la elección de la correcta semilla (variedad o híbrido) la densidad de siembra, el manejo de malezas, el manejo de las plagas insectiles, la fertilización, el correcto uso de maquinaria, y por último, el clima.
+La biotecnología y la investigación estarán respaldadas con un Estado presente, nunca con abusos empresariales basados en leyes dictadas a su medida. Con la ley que tenemos y un INASE presente y activo, no tenemos que dictar otra, ni cambiar nuestro posicionamiento internacional en materia de Propiedad Intelectual.
+Por todo esto, desde la Mesa Agroalimentaria Argentina rechazamos la adhesión a la UPOV 91, ya que entendemos que es una acción regresiva y autoritaria que atropella los derechos conquistados por lxs campesinxs, atentando contra la Soberanía Alimentaria y poniendo en riesgo los saberes ancestrales de nuestro pueblo. Luego de casi tres décadas del experimento transgénico en nuestro país, sabemos que las únicas innovaciones que le interesan al mercado concentrado son las que nos despojan de nuestra Soberanía, dejando hambre, contaminación y desigualdad.
+Lo que está en juego es trascendental: quien controla las semillas, controla la cadena agroalimentaria, y por lo tanto la disponibilidad, la calidad y el precio de los alimentos de todos los argentinos.
+*Secretario de Fe.Co.Fe y referente de la Mesa Agroalimentaria Argentina</t>
+  </si>
+  <si>
     <t>La Mesa Agroalimentaria rechaza la Ley Ómnibus</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/709239-la-mesa-agroalimentaria-rechaza-la-ley-omnibus</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    La Mesa Agroalimentaria rechaza la Ley Ómnibus. Qué puntos de la ley afectan a los pequeños productores. Extranjerización de la tierra, eliminación del Instituto de la Yerba Mate, venta del Banco Nación y la adhesión al convenio que permite privatizar las semillas.. Dirigentes de la Mesa Agroalimentaria Argentina participaron de los debates en el Congreso manifestando su rechazo al Decreto de Necesidad y Urgencia (DNU) presentado por Javier Milei que entró en vigencia el 29 de diciembre (excepto en su capítulo laboral) y al proyecto “Bases y Puntos de Partida para la Libertad de los Argentinos”, conocido como “Ley Ómnibus”, que esta semana comenzó a ser tratado en sesiones extraordinarias en la Cámara de Diputados.
+La entidad, conformada por organizaciones como la Unión de Trabajadores de la Tierra (UTT), la Federación de Organizaciones Nucleadas de la Agricultura Familiar (FONAF), la Federación de Cooperativas Federadas (FECOFE), el Movimiento Campesino Indígena Somos Tierra y Bases Federadas (un desprendimiento de la Federación Agraria), se manifestó en contra de la privatización de las empresas públicas, el desmantelamiento del Instituto de la Yerba Mate (INYM), y la adhesión de la argentina al convenio internacional UPOV 91 que abriría la puerta al patentamiento de semillas.
+Agustín Suárez, referente de la UTT sostuvo que “la derogación de diversas normas dentro del DNU no tienen otra función que favorecer la exportación de la producción, poniendo en riesgo el abastecimiento interno. Esta es la finalidad que persigue la derogación total de la Ley de Abastecimiento, la Ley de Góndolas y la Ley de Promoción Industrial, así como la derogación parcial de las leyes Compre Nacional y Compre Argentino”.
+En tanto, “el recorte de las pocas ayudas que existían para nuestro sector y la eliminación de áreas clave para la agricultura familiar, muestran el desinterés del Gobierno por el verdadero campo, golpeado por la sequía, los temporales, la falta de acceso a la tierra y el aumento de los alquileres, combustibles e insumos, y solo le importa garantizar las ganancias del capital concentrado del agronegocio. Hoy solo el 13 por ciento de la tierra está en manos de pequeños productores que producen más del 60 por ciento de los alimentos que circula en el mercado interno; mientras que el 1 por ciento de las empresas agrarias controlan el 36 por ciento de la tierra cultivada en nuestro país”.
+En tanto, Omar Príncipe, titular de Bases Federadas, sostuvo: “No estamos de acuerdo con las privatizaciones de las empresas públicas, especialmente el Banco Nación, que es una herramienta financiera para los pequeños y medianos productores y el movimiento cooperativo”.
+También rechazó la eliminación del Fondo Compensador Algodonero y del Instituto Nacional de la Yerba Mate, y la modificación de la Ley de Tierras que permitiría su extranjerización. “En Argentina hay 15 millones de hectáreas en manos de extranjeros, el 6 por ciento del territorio. ¿Podemos derogar una ley de tierras sin debatirla, cuando costó años acordarla con los gobernadores y el Congreso?”, se preguntó.
+Asímismo, se refirió a la la adhesión de Argentina al convenio UPOV 91 como “una ley hecha a la medida de Bayer-Monsanto que implica perder el derecho al uso propio por parte de los productores y pone en riesgo la diversidad”. Además, sostuvo que “es falso que faltan inversiones en materia de semillas por la no adhesión a la UPOV 91. En los últimos años, se cuadriplicó la producción de soja, maíz y otros granos.
+En tanto las entidades que conforman la mesa agroalimentaria argentina reiteraron cinco proyectos de Ley, oportunamente presentados al Congreso, que promueven la producción nacional de alimentos saludables y respetuosos con el ambiente.
+Se trata de la Ley de acceso a la tierra; la Ley de arrendamientos rurales. La Ley de protección y fortalecimiento de los territorios campesinos y la agricultura familiar; la Ley de segmentación de las políticas impositivas agrarias y la Ley de financiamiento y fomento del cooperativismo y la transición agroecológica.
+“Estas son las normas necesarias para frenar el proceso de concentración económica y el despoblamiento del campo e impulsar el fortalecimiento de los pequeños y medianos productores, de la agricultura familiar y el movimiento cooperativo agrario. “Somos los que, en realidad, estamos en emergencia”, señaló Principe. La producción, comercialización, industrialización y exportación en manos de agricultores está desapareciendo, quedando para los grandes capitales en forma de fondos de inversión, fideicomisos y pools de siembra”, advirtió.
+*Lic. en Periodismo y Comunicaciones. Autora de "Ser Sustentables" (Ed. Urano)</t>
+  </si>
+  <si>
     <t>Qué es el Marco temporal y por qué se agravó el conflicto por las tierras indígenas en Brasil</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/709248-que-es-el-marco-temporal-y-por-que-se-agravo-el-conflicto-po</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Qué es el Marco temporal y por qué se agravó el conflicto por las tierras indígenas en Brasil. Están en riesgo 287 territorios. Cerca de 200 productores y empresarios vinculados al agro de Brasil, que forman parte de un grupo bautizado como “Invasión Cero”, se autoconvocaron por WhatsApp para “recuperar por medios propio. Cerca de 200 productores y empresarios vinculados al agro de Brasil, que forman parte de un grupo bautizado como “Invasión Cero”, se autoconvocaron por WhatsApp para “recuperar por medios propios” las tierras que la comunidad Pataxó Ha Ha Hai reclama como propias, en el marco de un conflicto territorial de larga data.
+Durante el episodio -que ocurrió el 21 de enero en el territorio conocido como Caramuru, municipio de Potiraguá- los hacendados cercaron el predio con decenas de camionetas y empezaron a los tiros, según información brindada por el Ministerio de Pueblos Indígenas.
+Por el ataque murió Negá Pataxó -Maria de Fátima Muniz-, hermana del cacique Nailton Muniz, quien también fue alcanzado por un disparo en el riñón y debió ser intervenido de urgencia. Otras personas resultaron heridas y están fuera de peligro.
+• Artículo publicado originalmente en Causas, el newsletter de Latinoamérica Piensa. Registrate y recibilo en tu mail.
+La policía informó que incautó dos pistolas, dos revólveres, cargadores y municiones a dos miembros del grupo de hacendados, que fueron detenidos y acusados de homicidio, intento de homicidio y porte ilegal de armas.
+“La gente de Pataxó Hã-Hã-Hãe fue brutalmente atacada por un grupo de propietarios, agricultores y pistoleros fuertemente armados. El grupo atacó a las familias Pataxó, que ocupaban pacíficamente su área de granja”, repudiaron desde la Articulación de los Pueblos Indígenas de Brasil (APIB). Desde la organización indígena pidieron que se investigue el caso, y también, lo más importante: “La delimitación de los territorios indígenas es el único camino para amenazar la escalada de violencia que afecta a los pueblos de la región del sur de Bahía". Y acá otra vez el conflicto.
+[H2] ¿Qué es el Marco temporal?
+Se denomina Marco temporal a la tesis jurídica que afirma que los pueblos y comunidades indígenas solo tienen derecho a reclamar las tierras que ocupaban cuando se promulgó la Constitución Federal de 1988. Esta tesis no reconoce la cantidad de veces que los pueblos fueron desplazados de sus territorios de manera forzada, ya sea por el Estado o por privados, incluso antes de la sanción de la Constitución. Muchos fueron expulsados de sus tierras durante la última dictadura militar (1964-1985).
+La Comisión Interamericana de Derechos Humanos (CIDH) alegó que la aplicación de esta norma contradice los estándares universales de derechos humanos y pone en riesgo la existencia de los pueblos indígenas. Para la CIDH, la aplicación del Marco temporal tiene un “efecto lesivo para todos los casos de demarcación de tierras ancestrales concluidos y futuros”.
+Detrás del Marco temporal está el agronegocio y su necesidad de expandir la frontera agrícola.
+[H2] Idas y vueltas
+Primero, el Supremo Tribunal Federal (STF) de Brasil falló en contra del Marco temporal. Después, el Senado lo aprobó por ley. Más tarde Lula da Silva utilizó el poder del veto presidencial y lo vetó; y, finalmente, el Congreso revocó el veto de Lula. Todo esto pasó en los últimos meses del 2023.
+Cronológicamente ocurrió así:
+[H3] 21/09 - El máximo tribunal de Brasil falla a favor de las comunidades indígenas
+El STF rechazó por 9 votos contra 2 la presentación de las entidades rurales que pretendían la vuelta del Marco temporal, es decir, que no se reconocieran las tierras indígenas reivindicadas después de la Constitución de 1988. La votación se extendió por dos años, período en el que hubo movilizaciones indígenas en todo el país.
+Los dos votos a favor del Marco temporal provinieron de los jueces designados por el expresidente Jair Bolsonaro: el jurista y pastor presbiteriano André Mendonça y Nunes Marques.
+El relator del caso, Edson Fachin, sostuvo que el derecho de los pueblos indígenas a la tierra es anterior a la creación del Estado y que, por lo tanto, no debe restringirse sus derechos a ningún marco temporal.
+[H3] 27/09 - El Senado de Brasil aprueba el Marco temporal
+A días de conocerse el fallo del STF, el Senado brasileño aprobó esta ley para limitar el reconocimiento de las tierras indígenas por 43 votos a favor y 21 en contra. La Cámara de Diputados ya la había aprobado el año anterior, pero en el medio la máxima instancia judicial la declaró inconstitucional.
+Al mismo tiempo, la Corte dispuso que los productores que hayan adquirido “de buena fe” tierras que tradicionalmente pertenecen a los indígenas tenían derecho a una indemnización por parte del Estado.
+[H3] 20/10 - Lula da Silva veta la ley que aprueba el Marco temporal
+El presidente de Brasil utilizó su poder de veto para dar de baja la ley incentivada por el agronegocio, que fue aprobada por el Congreso y que ya contaba con un fallo de inconstitucionalidad.
+El veto de Lula fue un veto parcial, quedaron en pie artículos de la norma que permiten la explotación económica en tierras indígenas siempre que sea en coooperación y autorización de los pueblos originarios. Las comunidades indígenas pretendían que el veto del presidente sea total.
+"He vetado algunos tramos de la ley. Debemos seguir dialogando y trabajando para que tengamos, como hoy, seguridad jurídica y también el respeto a los derechos de los pueblos originarios", afirmó el presidente en ese momento.
+[H3] 14/12 - El Congreso de Brasil elimina el veto de Lula y el Marco temporal vuelve a estar vigente
+El ida y vuelta por el Marco temporal siguió: el Congreso eliminó el veto del presidente brasileño que protegía la demarcación de tierras indígenas. Por lo que la tesis que reconoce a las comunidades indígenas como válidas las tierras que ocupaban al 5 de octubre de 1988, cuando se sanciona la Constitución, vuelve a estar vigente.
+"Otro revés anulado. Garantizamos la seguridad jurídica al agro brasileño", celebró en las redes sociales el senador Ciro Nogueira, quien fue jefe de gabinete del expresidente Jair Bolsonaro (2019-2022).
+[H2] Por qué importan las tierras indígenas y qué puede pasar ahora
+Además de considerarse el derecho ancestral sobre las tierras de donde las comunidades indígenas fueron expulsadas, las reservas indígenas son consideradas claves en la lucha contra la preservación del ambiente porque representan una barrera contra la deforestación para la expansión del agronegocio y los proyectos extractivistas.
+"Es absurdo que mientras el mundo ya reconoce a los pueblos indígenas y sus territorios como una de las últimas alternativas para contener la crisis climática, el Congreso actúe a contramano", opinó Sonia Guajajara, ministra de Pueblos Indígenas.
+Según datos de la Fundación Nacional de los Pueblos Indígenas (FUNAI), las reservas ocupan 13,75% del territorio del país. Desde que asumió su tercer mandato, en enero, Lula ordenó la demarcación de ocho nuevas reservas, en contraste con Bolsonaro, que cumplió su promesa de no homologar un "centímetro" de tierra durante su mandato.
+Por el Marco temporal, hoy vigente, están en riesgo 287 territorios indígenas.
+Según el último censo, en Brasil viven cerca de 1,7 millones de indígenas dentro y fuera de reservas, de los 203 millones de habitantes.
+Luego del ataque armado, donde murió una dirigente indigena, el presidente brasileño dijo que pensaba interceder para proteger a las comunidades y encontrar una solución pacífica al conflicto de las tierras indígenas.
+Hasta ahora, el gobierno de Lula solo reforzó la presencia de las fuerzas de seguridad en las áreas en conflicto, no solo con los hacendados por la posesión de las tierras sino también en aquellas comunidades acechadas por la minería ilegal, como los indígenas yanomamis.</t>
+  </si>
+  <si>
     <t>Exigen eliminar el "capítulo ambiental" de la Ley Ómnibus</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/708031-exigen-eliminar-el-capitulo-ambiental-de-la-ley-omnibus</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Exigen eliminar el "capítulo ambiental" de la Ley Ómnibus. Un centenar y medio de organizaciones enviaron un documento a la Cámara de Diputados para respaldar la legislación vigente. Los activistas alertan sobre los negocios entre privados que se abrirían si dejan de existir las leyes que protegen bosques, glaciares y suelos, entre otras.. "Hay que eliminar el capítulo ambiental”. "Es un retroceso y un duro golpe a la legislación conseguida”. "Entrega recursos soberanos”. Con estas definiciones se plantan las organizaciones ambientalistas en la escena donde crecen los reclamos al proyecto Ley Ómnibus y su adlátere -–o viceversa--, el mega DNU de Javier Milei. Lo expresó en el Plenario de Comisiones el abogado ambientalista Enrique Viale y lo confirmaron 150 organizaciones esta semana en una carta dirigida a los Diputados nacionales en defensa de la legislación ambiental vigente, modelo en el mundo en protección de bosques o glaciares. Exigen eliminar el “capítulo ambiental” por “lo preocupante y peligroso” de las propuestas que “no tienen relación con las necesidades y urgencias de la situación económica que atraviesa la Argentina, por lo que no hay justificación alguna para incorporarlas en el paquete de reformas”.
+De aprobarse esta reforma, la Ley de bosques, la de glaciares y la de quema pueden transformarse en leyes de “desprotección” advierte Consuelo Bilbao del Círculo de Políticas Ambientales. Aun cuando el dictamen eliminó el desmonte en zonas protegidas --como pretendía el texto original--, se endureció respecto a glaciares dándole entrada a la extracción minera en sus alrededores. Toda una bienvenida a las corporaciones de la megamineria.
+El dictamen extiende además el plazo para habilitar la quema de pastizales ante la “ausencia de respuesta de las autoridades”. Propone un tratado que modifica las normas de propiedad intelectual de las semillas afectando especialmente a las criollas, y otra norma sobre transición energética que solo involucra al mercado de carbono ("otro sinsentido" apuntan los expertos). Junto a los artículos destinados a desfinanciar la protección ambiental, el capítulo queda en alerta roja y “se perjudica gravemente al pueblo argentino” sentencia Viale.
+Detrás de los cambios asoman “interesados con nombre y apellido y empresas como la Barrick Gold detrás de la ley de glaciares” detalla el abogado ante Página/12 al ampliar su intervención en el Congreso, como referente de la Asociación Argentina de Abogados Ambientalistas la semana pasada. Viale señaló allí al empresario hotelero Eduardo Elsztain, a Mauricio Macri y al ministro Luis Caputo, no solo como responsables del desmonte de miles de hectáreas. También como parte de quienes conspiran para que se apruebe el proyecto que busca “privatizar las nacientes de agua, apropiarse de recursos mineros -–oro y plata, por caso--, y devastar el monte para el agronegocio”. Algo que buscarán también, sino queda en el articulado de la ley, "al otorgarle las fatales facultades delegadas al Ejecutivo” anticipa.
+[H2] No es ajuste, es entrega
+Dado que el objetivo no es “achicar gastos” –como explican las organizaciones- se evidencia el motivo real de los cambios: la entrega de recursos, el despojo. “Es paradójico, trabajamos mucho las organizaciones para lograr estas leyes y ahora estamos trabajando para que no las volteen” reflexiona Bilbao. Las modificaciones minimizan los criterios de protección. “Y se vulnera el principio de no regresión ambiental porque implica disminuir niveles de protección ya alcanzados” agrega. Viale coincide: “Hasta hace poco debatíamos una ley de humedales. Ahora retrocedimos y estamos debatiendo leyes sancionadas hace 15 años: la de bosques y la de glaciares. ¡Estábamos discutiendo el siglo XXI y nos llevaron a discusiones del siglo XIX!”.
+En la tensión se distingue una postal apocalíptica donde podríamos ver un futuro cercano con aumento de sequía por desforestación, producto del desmonte o la quema indiscriminada. El agua sería un lujo arábigo porque las nacientes de los ríos --los glaciares-- ya no serían un recurso soberano, estarían en manos privadas, y también sus alrededores convertidos en campos de extracción minera. Una postal desoladora. Eso pretende hacia el futuro, el proyecto presentado.
+Las organizaciones expresan su rechazo: “No creemos que el capítulo ambiental siquiera se tenga que discutir, tiene que ser eliminado -–señala Bilbao--. El tema ya se discutió y se sancionaron leyes modelo: la Ley de Bosques logró en 2007 frenar la abrupta curva de aumento de los desmontes, sobre todo en Chaco. La tasa bajo considerablemente y eso es importante para nuestros bosques. Sin esa ley podría haber sido una catástrofe”.
+[H2] Ley de glaciares
+“Hoy lo que más nos preocupa es la Ley de Glaciares” afirma la especialista. Votada dos veces, sancionada en 2010 y ratificada por la Corte Suprema de Justicia con dos fallos, en dos oportunidades, la Ley 26.639 de Protección Ambiental de glaciares y ambiente periglacial -–su nombre oficial--, corre peligro de derrumbe. “No sabemos en qué escritorio se decidió cambiarla en tres artículos fundamentales” comparte.
+La ley vigente plantea que los glaciares son “un recurso hídrico estratégico para la vida humana” detalla Bilbao. “Pero esa concepción ya no figura en el Artículo 1. Y en el 2 se piden requisitos extras para ser áreas protegidas, o sea que se los desprotege y se habilita la actividad minera”. El Artículo 6 que establece las prohibiciones de la actividad minera “ahora queda sujeto a los artículos 1 y 2 modificados, porque buscan reducir área de protección periglacial”.
+Esto genera mayor inseguridad jurídica, aunque promueve las inversiones, claro. Los glaciares son “fábricas de agua” define Viale. “Allí nacen muchos de los ríos de nuestro país que dan vida y trabajo a su paso”. Hoy pueden terminar en manos de corporaciones como la canadiense Barrick Gold porque “Las modificaciones presentadas fueron escritas por sus abogados”.
+Esta empresa explota glaciares de alta montaña en San Juan y Mendoza con minas metalíferas, y quiere expandir sus dominios. Actualmente no puede porque las zonas periglaciales están inventariadas y protegidas. “Por eso quieren achicar el área protegida” anuncia el abogado. “Esto está escrito con la idea de liberar áreas específicas. Es un avasallamiento y es preocupante tanta desprotección”, coincide Bilbao.
+[H2] Sobre bosques y quemas
+En bosques hubo cambios, entre el proyecto y el dictamen conocido hasta ahora, como en otras áreas. El texto original permitía desmontar zonas de máxima protección: rojas y amarillas. “Esto se eliminó en el dictamen, pero queda la modificación del Fondo para la protección de bosques nativos”, señala Bilbao sobre el Fondo que cuenta con el 0,3 por ciento del presupuesto nacional y el 0,2 de retenciones. Se eliminan también las partidas presupuestarias fijas y se deja las partidas a discrecionalidad del Ejecutivo.
+En cuanto a quemas la situación “se agravó” en el dictamen porque permite ante un pedido de autorización de quema con 90 días sin respuesta, entender una autorización “tacita”. Considerando las sequías y los incendios no se debería ignorar a la autoridad local: “Corrientes perdió el 12 por ciento de la provincia por incendios. Tuvimos meses de humo en las riveras del Paraná por los incendios en Santa Fe” acierta Viale.
+La norma sin embargo ignora a las autoridades al momento de evaluar si hacer o no una quema. Se ignoran también las sanciones por quema indebida: cuando no se autorizan por cuestiones climáticas, pero el productor igual quema. Ya no habría sanción si se propaga un incendio como establece la Ley 26.562 de actividades de quema. Por eso exigen y concluyen de cara al tratamiento del articulado, que "estas modificaciones y sus consecuencias perjudican gravemente al pueblo argentino”.</t>
+  </si>
+  <si>
     <t>"Nadie votó por empeorar sus condiciones de vida"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/707361-nadie-voto-por-empeorar-sus-condiciones-de-vida</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Nadie votó por empeorar sus condiciones de vida". Entrevista a Javier Rodríguez, ministro de Desarrollo Agrario bonaerense. Para el funcionario, la Ley Ómnibus y el DNU no cuentan con ningún artículo que favorezca al sector productivo nacional y ve que el horizonte que persiguen es uno sólo: "La extranjerización y la concentración".. Desde la Ley de Tierras, pasando por la Ley de Semillas, las privatizaciones de empresas estratégicas, hasta llegar a los derechos de exportación y la Ley de Góndolas. Con este breve listado, Javier Rodríguez recorre el camino de modificaciones que propone la ley ómnibus y el DNU impulsado por Javier Miel. A su juicio, “atentan” contra todo el ciclo productivo provincial. El ministro de Desarrollo Agrario (MDA) bonaerense sostiene que no hay un solo artículo a favor de la economía ni del trabajo argentino porque el objetivo de las medidas es la "la concentración y la extranjerización”.
+"Esperamos que el Gobierno Nacional escuche al pueblo luego de una movilización masiva y contundente de rechazo como la de este miércoles", señala en diálogo con Buenos Aires/12.
+En este segundo mandato, Rodríguez continúa al frente de la cartera que vincula al gobierno de Axel Kicillof con los sectores productivos agropecuarios. El abordaje que involucra a su ministerio es amplio: desde la soja y el maíz, hasta la cebada que da origen a las PyMEs de cerveza, pasando por el biodiesel y la pesca, son parte del conjunto de sectores que ya tocaron las puertas del MDA en búsqueda de un acompañamiento para frenar las medidas libertarias.
+"Hemos tenido reuniones con la propia Federación Agraria y CONINAGRO, donde expresan sus desacuerdos con el desastroso esquema de derechos de exportaciones", advierte Rodrpiguez.
+“La discusión de la ley ómnibus se da en el marco de una aceleración de la inflación a partir de la fuerte devaluación que hizo el gobierno, acompañada por la liberación en el precio del combustible que originó un fuerte aumento en el precio de los insumos, afectando a los sectores que procesan granos y productos del agro, a quienes se les modificaron las ecuaciones, principalmente a las empresas de mediana escala del sector avícola, el porcino y el tambero”, describe el ministro.
+Aquel recuento de modificaciones que indica Rodríguez que introducen los, ahora, más de 500 artículos de la, como denominó Milei a su criatura, Ley de Bases y Puntos de Partida para la Libertad de los Argentinos, son un “avasallamiento de los mecanismos democráticos habituales donde se derogan leyes que tuvieron meses de debate".
+Rodríguez menciona la desaparición de la Ley de Tierras como el puntapié de la extranjerización y concentración con la que define la ley ómnibus. La pérdida del instrumento que limita a ciudadanos extranjeros tener más de mil hectáreas de zona núcleo o similares fue sancionada en 2011 y apunta a limitar la compra de grandes volúmenes de tierra productiva por parte de extranjeros.
+Pero un artículo que el ministro no quiere que pase desapercibido y que ya fue señalado en un comunicado por la Federación Agraria, Confederaciones Rurales Argentinas y la propia Sociedad Rural, es el 241, que en la nueva versión presentada este lunes lleva el número 210. Allí se adhiere a la Unión Internacional para la Protección de las Obtenciones Vegetales (UPOV), particularmente a las últimas actualizaciones de 1991.
+—¿Por qué es contraproducente esta adhesión?
+—En la actualidad, los productores tienen el derecho a usar sus propias semillas. Es uno de los últimos elementos que quedan para evitar tener que recurrir a un mercado como el de la producción de semillas que es muy oligopólico y prácticamente monopólico. Muchas veces productor en los hechos tiene pocas alternativas para comparar semillas e, incluso, hay veces que una sola empresa las provee porque las firmas están de alguna manera asociadas.
+—Entonces…
+—Pasar a UPOV 91, que aparece perdido como un articulito en medio de la ley, limita esa posibilidad. Si bien habrá que ver la efectiva implementación, termina atando al productor a esa cadena de concentración porque le pone trabas al uso de sus propias semillas. Cuando hablamos de la semilla hablamos de la posibilidad de producir. Argentina entraría a un esquema de no poder usar sus propias semillas.
+—El Gobierno Nacional plantea que es un mecanismo para acceder a métodos innovadores. ¿No está de acuerdo?
+—Si uno conoce la realidad del mercado el punto es la concentración en la venta de las semillas. En Argentina la inscripción de nuevas variedades de semillas está bien y con altos índices de productividad. Pero bueno, esto va de la mano de limitar el desarrollo científico nacional.
+—¿A qué se refiere?
+—La investigación es imprescindible para el sector agroalimentario. En lo que respecta específicamente a este sector, su desarrollo ha estado fuertemente vinculado a la posibilidad de innovación que se desarrolla desde el sector público. En Estados Unidos, por ejemplo, muchísimas de las innovaciones comienzan a potenciarse a partir de la creación de centros de investigación que surgieron a mitad del siglo XIX. En Argentina, parte de esas investigaciones arrancan a principios del XX.
+—¿Por qué son investigaciones que tienden a hacerse desde el sector público?
+—Gran parte de la investigación se hace en el sector público porque las innovaciones agronómicas no son sujetas a propiedad. Cuando uno conoce la semilla que se adapta a determinado clima o momento del año, son conocimientos que una vez aprobados cualquier productor puede usar. Achicar el CONICET o, como ocurrió durante el macrismo con el desfinanciamiento del Instituto Nacional de Tecnología Agropecuaria (INTA), con personal que se jubilaba y no se reponía, lo que genera son peores condiciones para el sector. Cuando uno lee en profundidad, la ley ómnibus también habla de privatizar INTeA (NdeR: Innovaciones Tecnológicas Agropecuarias SA. es la empresa de capitales mixtos conformada mayoritariamente por el INTA que promueve agronegocios) que comercializa parte de los desarrollos tecnológicos del INTA, lo que sería avanzar en una lógica de los avances sean cooptados por un sector específico limitando acceso a sector productivo.
+—¿Cómo se evidencia ese desarrollo científico desde el Estado?
+—Durante la gestión anterior a la nuestra, en la provincia de Buenos Aires funcionaban trece chacras experimentales que tenían un funcionamiento muy magro y con una fuerte desinversión y caída del personal. Nosotros pasamos a dieciséis chacras experimentales. En estos primeros cuatro años trabajamos en el mejoramiento genético vegetal, con la inscripción de siete nuevas variedades de semillas de, por ejemplo, tomate, trigo, y cebada. Estamos por inscribir una nueva de pastura.
+—¿Qué soluciones genera este trabajo?
+—Es la investigación en el sector público la que llega a escala de productores. Para ver otro ejemplo concreto, construimos un laboratorio de micropropagación. Los productores de batata tenían muchas dificultades para conseguir plantas madres de calidad. También los de alcaucil. Esto redujo la superficie de siembra, y con este mecanismo lo volvemos a impulsar. Estamos en etapa de ensayo para la mejora de una semilla de maíz.
+—El modelo del Gobierno Nacional dirá que esto atenta contra la libre competencia.
+—Está claro que lo que propone el Gobierno Nacional es un modelo excluyente. Ataca o da de baja derechos laborales. Son procesos que tienden a la concentración. La concentración productiva es la primera manera de destruir el ingreso porque es la concentración que desde el punto inicial provoca una desigual distribución para producir alimentos. Escucho declaraciones que hablan de agregar valor, y la verdad es que gobierna a nivel nacional un proyecto que atenta contra el agregado de valor como lo es la innovación.
+—¿Cómo ve el aumento de las retenciones a los commodities?
+—Todo lo que se propone en materia de derechos de exportación es desastroso. Las distintas organizaciones del sector históricamente manifestaron un rechazo, con una posición de que los derechos de exportación deben tender a reducirse, y en medio de un discurso de Milei que venía a reducir impuestos. De manera generalizada, ahí hay contradicción. Siempre con poca explicación y poco debate.
+—Los gobernadores de Santa Fe y de Córdoba, por ejemplo, están muy plantados en rechazarlas...
+—Tiene que ver con la evidente estafa electoral que implica, ya que Milei hizo campaña diciendo que no iba a incrementar ningún impuesto y hoy lo están haciendo. Tanto en los derechos de exportación como el Impuesto País, o Ganancias. Por otro lado, es importante destacar que el mayor problema en la propuesta de Milei es la falta de segmentación en los derechos de exportación, y que se ve en las economías regionales. Todo es parte de lo mismo: Milei no hace lo que dijo que iba a hacer. Él dijo que iba a solucionar la inflación ajustando a la casta y todos entendían que la casta era otra cosa. Pero acá se está ejecutando un modelo de ajuste clásico, que perjudica a la clase media y a los trabajadores.
+—Pero ganó las elecciones prometiendo un ajuste...
+—Sí, pero nadie por votó empeorar sus condiciones de vida. Cerramos el año con una inflación de 211 por ciento. En diciembre fue del 25 por ciento, que tiene que ver con la política de Milei, diciendo que el peso es una basura e impulsando una pérdida del poder adquisitivo. Todo en muy poco tiempo y en detrimento de las enormes mayorías. Del sector de la pesca, por ejemplo, una porción de sus representados lo votaron, pero nadie voto perder su fuente de trabajo. Es una buena síntesis. Tenemos que ser claros y contundentes, explicando lo que sucede: vivimos un ajuste muy similar a los ajustes ortodoxos.
+—¿A qué se refiere cuando dice que no se segmentan los derechos de exportación, particularmente en las economías regionales?
+—El cambio en los derechos de exportación tiene dos cuestiones: se elevan los montos y se generaliza a las economías. A partir de las modificaciones, se eleva el derecho de exportación sobre la cebada del 12 al 15 por ciento, el de la malta del 9 al 15 por ciento, de la cerveza del 4,5 al 15 por ciento. Todo al revés, porque a mayor industrialización el derecho de exportación tiene que ser más bajo, pero acá se lo equipara todo, lo que atenta contra la industrialización regional y local. Es un modelo de reprimarización de la economía. Además, no se de diferencia la escala de productores y se establece el 15 por ciento de manera generalizada.
+—¿Qué le dijeron desde el sector en la última reunión?
+—Plantean que se cerraría la exportación a Brasil, uno de los principales destinos, porque los márgenes en este tipo de producción no son tan grandes. Con todo equiparado, va a ser imposible.
+—¿Hay otros casos que se presentaron ante el ministerio con el mismo problema?
+—Estuvimos reunidos con el sector del biodiesel. En la provincia hay once plantas y se ve que ya la presentación de la ley ómnibus genera una fuerte incertidumbre y una inseguridad jurídica. Hoy prevén presentaciones judiciales al respecto.
+[H3] "Habrá que poner el impuesto Milei para pagar los juicios de las PyMEs de biodiesel"
+—Hay legisladores que dicen que el nuevo dictámen no contiene las reformas que se habían acordado.
+—Es imposible discutir asi. Es imposible ir a un debate serio, y esto que se observa con los dictámentes que se conocen ahora y no serían los firmados es la frutilla del postre de cómo se maneja. Las modificaciones que ponen sobre el biodiesel no cambian la situación de las PyMEs, y si se aprueba tal como esta planteada hasta ahora verían deteriorada su situación.
+—¿Por qué suceden estas situaciones como la de los dictámenes?
+—Nadie se hace cargo de porqué se incluye tal o cual cosa y nadie lo defiende ante los diputados. Se plantea una enorme modificación y no hay nadie con la valentía para dar los debates. Se presentan personas del Gobierno Nacional que no tienen que ver con el área en discusión a defender algún punto de la ley. Es parte del avasallamiento a mecanismos democrativas.
+—Mencionó al sector pesquero, ¿cómo fueron las conversaciones?
+—Tuvimos reuniones. Las nuevas medidas modifican de un plumazo todo el régimen de la pesca. En la actualidad, el desembarque se tiene que hacer en puertos argentinos, en nuestro caso bonaerense. Esto fomenta la industrialización local. Se tiene que hacer con embarcaciones con bandera nacional y tripulación nacional. La ley ómnibus tira por la borda ese tema. Se trata de perder soberanía sobre zona inclusiva. Por eso también se los vio presentes en el paro y movilización de Mar del Plata.
+—¿Eso se traduce en que cualquiera puede pescar en territorio argentino?
+—Muchas veces se habla de las embarcaciones que operan en la milla 201, pero con estas medidas le das luz verde a que ingresen. Se llevarían el recurso pesquero porque ni siquiera tienen que venir a puertos argentinos. Se borra el Concejo Federal Pesquero, donde están representados los intereses de las provincias y es un mecanismo que permite cuidar el recurso. Volvemos a la extranjerización. Además, pone en peligro las inversiones a nivel local. Ya está teniendo impacto lo que se anuncia porque los pedidos de nuevas embarcaciones a los astilleros fueron suspendidos porque no saben qué va a pasar.
+—Estuvo de recorrida por varios municipios, ¿qué le transmitieron los intendentes durante sus últimos encuentros?
+—Los intendentes lo que ven con preocupación es la evolución económica y social. Ven con muchas dificiutaldaes lo que puede ocurrir en marzo, por el retorno de la escolaridad y la gente retome un ritmo de vida pleno luego de la época de vacaciones. Hoy todos están recibiendo mayores demandas vinculadas al deterioro de las condiciones sociales y mayor demanda en los servicios públicos de salud. En ese escenario, les genera preocupación la evolcion de los ingresos en los municipios, y es algo que se plantea por las distintas fuerzas.</t>
+  </si>
+  <si>
     <t>Lula promete intervenir tras el asesinato de una lideresa indígena en Bahía</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/706523-lula-promete-intervenir-tras-el-asesinato-de-una-lideresa-in</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Lula promete intervenir tras el asesinato de una lideresa indígena en Bahía. El presidente de Brasil bregó por una solución pacífica del conflicto. Nega Pataxó fue baleada por terratenientes que disputan las tierras de una hacienda ubicada en el sur del estado de Bahía y que la etnia Pataxó-hã-hã-hãe reivindica como propiedad de sus ancestros.. El presidente de Brasil, Luiz Inácio Lula da Silva, prometió este martes tomar medidas tras el asesinato de Nega Pataxó, una lideresa indígena de la etnia Pataxó-hã-hã-hãe que fue baleada en un conflicto con terratenientes del sur del estado de Bahía, en el noreste brasileño.
+"Estoy conversando con el gobernador (de Bahía) Jerônimo Rodrigues y la ministra (de los Pueblos Indígenas) Sônia Guajajara, que fue a la región para abordar la situación", expresó el mandatario en sus redes sociales. "Quiero poner al Gobierno federal a disposición del gobernador y de los pueblos indígenas para encontrar una solución de forma pacífica. Mi solidaridad con la familia de Nega Pataxó", añadió.
+[H2] La muerte de la lideresa
+María da Fátima Muniz de Andrade, conocida como Nega Pataxó, era hermana del cacique Nailton Muniz, el líder de los pataxó en la región. Fue asesinada el domingo en un ataque perpetrado por un grupo de ruralistas --término utilizado en Brasil para referirse a comerciantes y empresarios del sector agrícola-- identificado como "Invasión Cero", que movilizó a 200 de sus miembros a través de una convocatoria en WhatsApp.
+El llamado instaba a recuperar por medios propios las tierras de una hacienda ubicada en el municipio de Potiraguá, en el estado de Bahía, que fue ocupada el sábado por indígenas que lo reivindican como propiedad de sus ancestros. Se trata de una vieja disputa que está hace años en los tribunales y que impide a la estatal Fundación Nacional de los Pueblos Indígenas (Funai) avanzar con el proceso de demarcación del territorio pataxó.
+"El cacique Nailton fue tiroteado y su hermana, Nega Pataxó, fue asesinada. Otras dos personas fueron sometidas a palizas y a una mujer le quebraron un brazo. Otros heridos fueron hospitalizados pero no corren riesgo de vida", señaló en un mensaje publicado en sus redes sociales la Articulación de los Pueblos Indígenas de Brasil (APIB), organización que representa y trabaja en defensa de los derechos de los pueblos indígenas en Brasil. "Exigimos que las autoridades investiguen el caso. Reiteramos que la delimitación de los territorios indígenas es el único camino para amenazar la escalada de violencia que afecta a los pueblos de la región del sur de Bahía", añadió.
+Pese a que la APIB afirmó que entre los agresores que tirotearon a sus tres líderes había miembros de la policía, la Secretaría de Seguridad Pública del estado de Bahía negó que sus agentes hubiesen intervenido en el tiroteo. La policía informó igualmente en un comunicado que le incautó dos pistolas, dos revólveres, cargadores y municiones a dos miembros del grupo de hacendados, que fueron detenidos y acusados de homicidio, intento de homicidio y portación ilegal de armas.
+Hay muchas otras zonas de Brasil en donde hay conflictos de esta índole. Sin ir más lejos, el viernes el Gobierno de Brasil aprobó el envío de la Fuerza Nacional de Seguridad Pública, un cuerpo de élite compuesto por policías militares nacionales, a la tierra indígena Tekohá Guasu Guavira, ubicada en el estado de Paraná, que desde 2020 vive inmersa en un conflicto entre indígenas y terratenientes por la delimitación de su territorio y donde a principios de este año tres indígenas fueron heridos por un ataque a tiros.
+[H2] El avance del agronegocio y la minería
+Pese a que el regreso de Lula a la Presidencia en enero del año pasado y la creación del Ministerio de los Pueblos Indígenas permitió a la Funai desempolvar varios procesos de delimitación de reservas que habían sido archivados por el entonces presidente Jair Bolsonaro, la violencia contra los pueblos originarios no cesó en el territorio brasileño. Precisamente, los conflictos volvieron a agravarse luego de que el Congreso, de predominio conservador, aprobara en septiembre una ley que limita los derechos de los indígenas sobre sus tierras ancestrales para permitir el avance del agronegocio y la minería. Lula, un declarado defensor de las causas indigenistas, vetó al mes siguiente algunos tramos del texto, incluido el "marco temporal".
+Defendida por el poderoso agronegocio, esa tesis sólo reconoce el derecho de los indígenas, que totalizan 1,7 millones de los 203 millones de habitantes de Brasil, a reivindicar los territorios que ocupaban en 1988, cuando se aprobó la actual Constitución. Es rechazada por las comunidades indígenas con el argumento de que muchos pueblos originarios fueron expulsados a lo largo de la historia de sus territorios ancestrales, especialmente durante la dictadura militar (1964-1985).
+Con una mayoría de votos de 321 diputados y 53 senadores, el parlamento eliminó a mediados de diciembre el veto del mandatario. La APIB reaccionó recurriendo al Supremo Tribunal Federal (STF), máxima corte del país, para pedir la inconstitucionalidad de toda la ley. La misma corte declaró en septiembre inconstitucional el marco temporal pero esa declaración no fue tomada en cuenta por el Congreso cuando aprobó con carácter de urgencia la norma.
+Numerosos científicos consideran que las reservas indígenas son barreras contra la deforestación y, por lo tanto, claves en la lucha contra el calentamiento global. "Es absurdo que mientras el mundo ya reconoce a los pueblos indígenas y sus territorios como una de las últimas alternativas para contener la crisis climática, el Congreso actúe a contramano", dijo la ministra de los Pueblos Indígenas, Sonia Guajajara, en un video difundido en sus redes sociales para expresar su lamento por la decisión parlamentaria.</t>
+  </si>
+  <si>
     <t>No se puede avalar la venta de la Argentina</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/705259-no-se-puede-avalar-la-venta-de-la-argentina</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    No se puede avalar la venta de la Argentina. Se profundiza el encarecimiento de los alimentos esenciales. El DNU y la Ley Ómnibus favorecen a empresas multinacionales y dejan en clara desventaja a un amplio sector de la población.. Bajo el título "La Argentina no se vende", la Mesa Agroalimentaria rechaza el decreto de necesidad y urgencia (DNU) 70/2023, bautizado como “Bases para la reconstrucción de la economía argentina”, por su carácter autoritario y anti-republicano, siendo un claro golpe a las instituciones democráticas.
+El Decreto modifica 300 leyes. A pesar de su vigencia, está pendiente de revisión tanto en el Poder Legislativo como el Judicial, generando un vacío jurídico que atenta contra los pequeños y medianos productores, las economías cooperativas y regionales y el cuidado del medio ambiente.
+Desde el plano ideológico o metodológico, el Decreto da por supuesta una situación de libre mercado que no puede ser tal debido a la importante concentración con la que cuenta la estructura económica argentina. El decreto redactado por estudios de abogados del poder económico, entre los que se encuentran los grandes pooles de siembra del agronegocio, favorece a empresas multinacionales, dejando en clara desventaja a un amplio sector de la población que va desde las clases populares a la pequeña y mediana industria.
+“Esta derogación de leyes beneficia al agronegocio, a la agroindustria concentrada y contaminante y al negocio inmobiliario, y deja a vastos sectores del pueblo desprotegidos”, cuestionó Juan Pablo Acosta, de la Unión de Trabajadores y Trabajadoras de la Tierra (UTT).
+[H2] El otro campo
+Cuando en 2019, el Frente de Todos llegó al gobierno, las organizaciones campesinas, indígenas y de pequeños y medianos productores de alimentos, presentaron un plan Agrario, Soberano y Popular, elaborado en un foro conjunto en mayo de ese mismo año. Dos años después, en junio de 2021, pasada la pandemia y en medio de las elecciones de medio término, se creó la Mesa Agroalimentaria Argentina bajo el lema “el campo que alimenta y construye soberanía alimentaria”.
+Desde la UTT, además de los clásicos verdurazos y su red de mercados propios, se viene impulsando, en conjunto con gobiernos municipales como los de Lomas de Zamora, Quilmes y Avellaneda, espacios de comercialización que acercan a los productores con los consumidores. Los estudios del Centro de Estudios Scalabrini Ortiz (CESO) vienen demostrando, hace más de dos años, que la inflación en este tipo de locales o ferias no solo es menor a las grandes cadenas de supermercados, sino que además ofrecen una mejor calidad de alimentos.
+[H2] Muchos pasos atrás
+La asunción del Milei, lejos de solucionar los problemas de distribución de la tierras, esquema de arrendamientos, concentración económica y especulación a través del abuso en posiciones dominantes en la intermediación económica, el mercado financiero o los favores del Estado (como el dólar soja o el nuevo Bopreal), profundiza el esquema de encarecimiento del alimento en la mesa de los argentinos.
+“Cada uno de los puntos del DNU beneficia a un grupo reducido de empresarios que desde siempre hacen negocios a costa de la miseria del pueblo argentino”, dice el reciente comunicado de la MAA con respecto al DNU que deroga, entre otras, la Ley de Tierras Rurales, la Ley de Manejo del Fuego, arremete contra la regulación estatal del precio de la yerba mate, contra la política de abastecimiento de mercaderías en góndola y el resguardo del mercado interno; también contra leyes que regulan la vitivinicultura y la producción azucarera y contra las limitaciones a la extranjerización y la concentración de la tierra.
+Además la MAA repudió la aplicación generalizada de retenciones del 15 por ciento y del impuesto a la importación llamado PAIS: “Las retenciones e impuestos deben ser segmentados y diferenciados. El campo tiene una diversidad de actores que deben ser tratados de manera diferente”.
+* Licenciado en Economía de la Universidad Torcuato Di Tella y Master en Periodismo de la Universidad del País Vasco.</t>
+  </si>
+  <si>
     <t>Lula no va al Foro de Davos</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/704013-lula-no-va-al-foro-de-davos</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Lula no va al Foro de Davos. El líder brasileño decidió faltar al Foro Económico Mundial. Al repasar los números macroeconómicos, el presidente recordó haberse reunido con la jefa del FMI a quien le dijo "con todo respeto, usted no conoce Brasil" ni su economía.. Desde Brasilia
+Lula y Milei no se verán cara a cara por segunda vez en un mes. A poco de cumplir un año del inicio de su tercer gobierno, el brasileño decidió faltar al Foro Económico Global de Davos, del cual ha sido un visitante frecuente en el pasado, a donde viajará esta semana su par argentino.
+El 10 de diciembre el exlíder metalúrgico fue el gran ausente en la toma de posesión del economista libertario en la Casa Rosada.
+De esta forma Lula dio por tierra con su tradición de participar en las investiduras en Buenos Aires, como lo hiciera durante sus dos primeros mandatos al asistir a los actos inaugurales de los gobiernos de Cristina Fernández y Néstor Kirchner.
+[H2] "Con todo respeto"
+Aunque la agenda de Milei es una incógnita no se descarta que él o alguno de sus ministros se reúnan en Davos con Kristalina Georgieva, la directora del Fondo Monetario Internacional (FMI), para conversar sobre la obtención de más recursos (las arcas argentinas están exhaustas) para el pago de una deuda externa indómita.
+Al contrario de Argentina, Brasil no enfrenta compromisos externos acuciantes y mucho menos problemas de reservas, las cuales suman casi 350 mil millones de dólares, dato aunado a un superávit comercial de 99 mil millones de la misma moneda en 2023, de acuerdo con datos oficiales conocidos el viernes.
+Ese saldo positivo se explica en buena medida por las exportaciones de soja, maíz y mineral de hierro a China. Productos sin valor agregado que requieren mano de obra poco intensiva, dos características favorables de la concentración de la renta en el cada vez más poderoso agronegocio verdeamarillo.
+El presidente y jefe del Partido de los Trabajadores (PT) Lula repasó algunos números macroeconómicos el jueves último ante un grupo de periodistas en el Palacio del Planalto, donde se respira un optimismo cauto frente a un 2024 en el que se realizarán elecciones en más de 5 mil quinientos municipios.
+La robustez de las cuentas externas y el dinamismo del mercado interno, uno de los más importantes del planeta - favorecido por el aumento del salario mínimo y la desocupación en baja- pavimentó el crecimiento del 3,1 % del Producto Bruto en 2023, informó el FMI.
+Durante esa rueda de prensa en el Planalto Lula recordó haberse reunido con la jefa del FMI a quien le dijo "con todo respeto, usted no conoce Brasil" ni su economía. Esto porque en los primeros meses de 2023 los expertos de ese organismo proyectaron un crecimiento del 0,8 % cuando Lula los refutó asegurando habría una expansión superior: pronóstico confirmado por los hechos.
+Las palabras del presidente ante Georgieva no fueron insolentes: sino el gesto de un jefe de Estado que durante su primer mandato (2003-2006) pagó lo que le restaba de su deuda con el Fondo casi al mismo tiempo que Argentina hacía lo propio.
+A menudo Lula dice que Brasil es un país "normal" y se jacta de no tener que recibir, como ocurrió en otros tiempos, a los comisarios fondomonetaristas con sus recetas ortodoxas y privatizadoras.
+[H2] Octubre
+En lugar de volar hasta los fríos Alpes suizos, donde podría haber coincidido con Milei, Lula permanecerá todo enero en el tropical Brasil de temperaturas extremas, como ya lo fueron en noviembre y diciembre, debido al cambio climático que en este país es más exagerado debido a la devastación de la Amazonia.
+Además, razonan en el Planalto, una foto con Georgieva sería poco rentable electoralmente en este año de comicios municipales en los que se pondrá a prueba la popularidad del gobierno, y por propiedad transitiva, las aspiraciones reeleccionistas del mandatario. Lula hizo un hueco en su agenda para recibir a la bastante popular Marta Suplicy, la exintendenta de San Pablo.
+Ella se reafilió al PT, persuasión de Lula mediante, para ser la compañera de fórmula de Guilherme Boulos, el joven postulante a intendente paulistano por el Partido Socialismo y Libertad (PSOL). Con sus doce millones de habitantes San Pablo será escenario de la madre de todas las batallas electorales de octubre.
+Boulos es psicólogo y un conocedor del levantamiento popular argentino de 2001 además de acompañar la marcha de los movimientos sociales latinoamericanos. En 2022 fue el diputado federal más votado del estado de San Pablo. Logró esa alta votación pese a no contar con una estructura partidaria poderosa ni los recursos del estado, de los que sí se sirvió su principal rival, el diputado Eduardo Bolsonaro, gracias al aporte y la influencia de su padre Jair.
+Bolsonaro hijo, quien pese a quedar detrás de Boulos tuvo una buena votación que le permitió permanecer en la Cámara baja federal, utilizó la tribuna para propagandizar la candidatura de Javier Milei en los comicios argentinos del año pasado.
+[H2] Agronegocio y Bolsonaro
+El exitoso balance económico del primer año de gobierno lulista no está exento de contradicciones.
+Los números macro indican un crecimiento del orden del 3 por ciento del Producto Bruto (aún no se publicaron cifras oficiales definitivas) , gracias a lo cual mejoró el consumo y la ocupación. Pero sin un avance en la distribución de la riqueza ni un aumento importante de los puestos de trabajo formales bien remunerados.
+Tampoco ocurrió un empoderamiento considerable de las organizaciones sindicales avasalladas por la reforma laboral aprobada durante el gobierno golpista de Michel Temer (2016-2018), y luego de una represión policial pocas veces vista en Brasilia donde por primera vez en años hubo el despliegue de tropas del Ejército, en lo que sería un ensayo de la posterior militarización del gobierno durante la gestión de Bolsonaro (2019-2022).
+Lula y su ministro de Hacienda, Fernando Haddad, quien suele recibir más elogios del mercado que de sectores del PT, tampoco pudieron modificar la estructura económica cada vez más primaria y financierizada. Una configuración que el gobierno intenta revertir por medio de una política de financiamiento de obras de infraestructura, donde el Banco Nacional de Desarrollo Económico y Social (BNDES) cuenta con el apoyo del Nuevo Banco de Desarrollo del grupo BRICS (Brasil, Rusia, India, China y Sudáfrica, a los que se sumaron más países en enero).
+Al mismo tiempo, el mandatario pasó el año librando un combate casi solitario contra las altas tasas de interés determinadas por un Banco Central teledirigido por la banca privada. Logró que éstas se redujeran al 11,75% anual. Fue un triunfo, pero es cierto que siguen siendo una de las tasas reales más altas del mundo ya que la inflación cerró el año abajo del 5 %.
+El empuje de las exportaciones viene principalmente de los embarques a China realizados por el agronegocio, un sector que además de no hacer un gran aporte tributario, es el principal responsable de la devastación de cientos miles de hectáreas de la Amazonia, en norte, y del Cerrado, un bioma ubicado en la región oeste.
+Con el guiño de Bolsonaro y la complacencia de los militares destacados en la floresta, los grandes y medios hacendados incendiaron e invadieron tierras fiscales entre 2019 y 2022. Al tiempo que penetraban a sangre y fuego en las reservas de los pueblos originarios, que son los mejores guardianes de la selva.
+Esa misma clase terrateniente dio un abierto respaldo a la reelección de Bolsonaro, y parte de ella apoyó el intento golpista del 8 de enero de 2023 para mantener al capitán en el poder pese a la victoria de Lula.
+Y varios miembros de su bloque parlamentario, conocido como la Bancada del Buey, una de las más importantes del Congreso, brillaron por su ausencia el lunes pasado cuando el presidente, congresistas y jueces recordaron el aniversario del golpe fallido.</t>
+  </si>
+  <si>
     <t>"Un autoritarismo represor, clasista y racista"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/701894-un-autoritarismo-represor-clasista-y-racista</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    "Un autoritarismo represor, clasista y racista". Campesinos e indígenas organizados en rechazo al megadecreto de Milei. Lo rechazan por antidemocrático, permitir el extractivismo en territorios ancestrales e impactar la producción de alimentos.. Movimientos campesinos y comunidades indígenas rechazan las medida del Gobierno nacional --tanto el megadecreto como el proyecto de ley ómnibus-- por atentar contra la producción de alimentos, debilitar la soberanía alimentaria y facilitar el avance del modelo extractivo sobre territorios comunitarios.
+La Confederación Mapuche denunció que el Presidente implementa "un autoritarismo represor, clasista, racista y organizado para una mayor explotación a manos de los grupos de poder económico". Y hacen un llamado a la movilización y la más amplia unidad para frenar la quita de derechos.
+Doce organizaciones de La Plata, Berazategui y Florencia Varela, zona de producción hortícola por excelencia, emitieron un comunicado conjunto en repudio a las medidas del gobierno de Javier Milei. "Se trata de un ajuste brutal sobre campesinos, trabajadores, el pueblo; y una gigantesca entrega de la soberanía", denuncian la Unión de Trabajadores y Trabajadoras de la Tierra (UTT), la Federación Rural, el Movimiento Nacional Campesino Indígena (MNCI-Vía Campesina), Mujeres de la Tierra y la Asociación de Medieros (Asoma), entre otras.
+[H2] "Una profunda crisis"
+Puntualizan que la devaluación, la desregulación del precio de los alquileres y el aumento de los combustibles, entre otros medidas, provocan una "profunda crisis" en el sector que afectará a toda la población por el consecuente aumento del precio de los alimentos.
+La unión de doce organizaciones bajo el paraguas de la "Multisectorial Agraria La Plata", es también una muestra de la diversidad en la acción. Lo explicitan en el comunicado y hacen un llamado a otros espacios: "Hoy más que nunca es necesaria la más grande unidad para defender lo conquistado, seguir peleando por lo que falta y, al calor de la lucha, impedir los planes de esta derecha reaccionaria y ponerle freno a la represión".
+Desde la Confederación Mapuche de Neuquén (CMN) declararon que las comunidades originarias de la provincia se declaran "bajo estado de amenaza ante una Presidencia que promueve odio racial y que busca privar de derechos al pueblo, conquistas que nadie nos regaló y que no vamos a regalarle a ningún gobierno por más protocolos represivos que muestren", en referencia a Patricia Bullrich.
+"Hemos vivido un sistema democrático débil, incompleto, desigual, que ha impedido que las naciones indígenas ocupen el lugar que nos corresponde. Pero con todas esas falencias que son reparables con la movilización popular, este sistema desaparece ante un autoritarismo represor, clasista, racista y organizado para una mayor explotación a manos de los grupos de poder económico concentrados", denunció la Confederación Mapuche.
+Además expresó su rechazo al decretazo y al proyecto de ley ómnibus, llamaron a la defensa de los bienes comunes, los territorios indígenas y a la unidad del campo plurinacional y popular.
+La Mesa Agroalimentaria Argentina (MAA) definió al megadecreto como una medida "autoritaria" y --junto a las medidas enviadas al Congreso-- las catalogaron como "un fuerte golpe a la producción de alimentos".
+La Mesa Agroalimentaria está conformada por la UTT, la Federación de Cooperativas Federadas (Fecofe), el Movimiento Nacional Campesino Indígena Somos Tierra (MNCI-ST), Bases Federadas y la Federación de Organizaciones Nucleadas de la Agricultura Familiar (Fonaf). Y está en las antípodas de la Mesa de Enlace y del sector empresario representado por Aapresid (Asociación de Productores de Siembra Directa --en la actualidad con referentes en la Secretaría de Agricultura y del INTA--).
+[H2] "La miseria del pueblo"
+La Mesa Agroalimentaria denunció que cada punto del DNU beneficia a un grupo reducido de empresarios "que desde siempre hacen negocios a costa de la miseria del pueblo". Y rechazron la mirada neoliberal del Gobierno que "deja todo en manos del mercado".
+Todos los sectores campesinos e indígenas coinciden en que la derogación de la llamada "ley de tierras" (que limita la extranjerización) profundizará el extractivismo minero, petrolero, forestal y del agronegocio. Al mismo tiempo implicará mayor concentración de tierras en pocas manos.
+La Asociación Campesina del Abaucán (Acampa) de Catamarca es un espacio autónomo que impulsa desde hace más de dos década, una emblemática feria de semillas criollas en el oeste provincial. Manuel Aguirre integra Acampa, es productor y comunicador en la radio comunitaria Horizontes (en Medanitos). "El Gobierno le da más libertad de acción a las grandes empresas y al mismo tiempo les da vía libre para que sigan contaminando y saqueando nuestros territorios, al mismo tiempo que dejan más pobre al pueblo", afirmó Aguirre.
+Recordó que en la zona ya padecen a la minera china Liex Zijin con el proyecto de explotación de litio "Tres Quebradas", que no ha dado trabajo ni desarrollo local y atenta contra el desarrollo turístico y agropecuario del lugar. Aguirre advirtió que los sectores populares "no se quedarán de brazos cruzados", que harán respetar sus derechos y forma de vida y llamaron a organizarse y tener mayor articulación: "La única forma es unirnos y luchar todos juntos".
+[H2] "No a la minería de litio"
+El Presidente Milei, en una entrevista televisiva, dio a conocer el interés del multimillonario Elon Musk y de empresas de EE.UU. por el litio de Argentina. Mariela Alancay de la comunidad indígena de Aguas Blancas -- Salinas Grandes de Jujuy, lugar codiciado por las mineras-- le respondió: "Tiene que venir aquí y ver la realidad. Nosotros vivimos y trabajamos aquí por generaciones, tenemos el ganado y cuidamos las salinas. Tenemos derechos, son nuestros territorios y ya dijimos que no queremos minería de litio".
+Alancay integró el Tercer Malón de la Paz que viajó desde Jujuy a la Capital Federal en reclamo contra la reforma constitucional y acampó frente la Corte Suprema (sin respuesta).
+Además del Artículo 75 de la Constitución Nacional, la Declaración de Naciones Unidas para los Pueblos Indígenas y el Convenio 169 de la OIT (que en Argentina tiene rango supralegal), las comunidades originarias enarbolan el derecho de quien vive en el lugar. Mariela Alancay lo resume: "Nuestros ancestros nos dejaron esta naturaleza, estos territorios sanos y limpios para los que trabajemos. Nosotros cuidamos la Pachamama y se las dejamos a nuestros hijos y nietos. Por eso la defendemos y por eso decimos no al litio, sí al agua, sí a la vida".</t>
+  </si>
+  <si>
     <t>Las mujeres originarias frente a la dictadura del capital</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/701056-las-mujeres-originarias-frente-a-la-dictadura-del-capital</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Las mujeres originarias frente a la dictadura del capital. El shock del DNU, el protocolo antipiquetes y la Ley Ómnibus. El gobierno de Milei-Villarruel anuncia y promete más miseria, represión, muchos modos de morir y de mal vivir. Frente a eso se levantan las voces de los pueblos y en especial de las mujeres que están en la primera línea de la defensa de la vida.. El gobierno que asumió el 10 de diciembre, cuando se celebraban 40 años de “recuperación de la democracia”, está empeñado en pulverizar todo resto de democracia para convertir a la Argentina en un coto de caza de los grandes empresarios transnacionales, las oligarquías locales, estableciendo una férrea dictadura del capital extranjero, y de las fuerzas políticas y militares locales que lo resguardan.
+Milei levantó la bandera de remate de las empresas e instituciones del Estado, de la soberanía, de los derechos de los pueblos, de las mujeres y disidencias, de la naturaleza. En el discurso inaugural rindió homenaje al genocida Julio A. Roca, responsable de las políticas de exterminio de los pueblos originarios sobre las cuales se levantó el Estado Nación llamado Argentina. Milei caracterizó a Roca como “uno de los mejores presidentes de este país”. No se trata de una cita caprichosa. Es el anuncio de una reorganización de la sociedad inspirada en el artífice del genocidio indígena, y de sus sucesores videlistas -también admiradores de Roca y admirados por Villarruel y su corte negacionista-.
+No sorprende en este marco de reivindicación de los genocidios, que el gobierno de Milei estreche los vínculos con EE.UU. y con el Estado sionista de Israel, cuando está realizando un brutal genocidio del pueblo palestino. La abstención de Argentina en las Naciones Unidas frente a la propuesta de cese del fuego ilustra de qué libertad nos hablan: la de matar a niños, niñas, jóvenes, mujeres, a un pueblo entero, bajo los bombardeos despiadados, las balas, el hambre, la falta de agua o de acceso a los hospitales.
+En esa línea de celebración de la crueldad, se inscriben las primeras medidas de shock como el DNU, el Protocolo antipiquetes, y la Ley Ómnibus, que tienen como denominador común el ataque violento a los derechos populares.
+Lourdes Albornoz, del pueblo Diaguita, advierte que “esta dictadura de la depredación tiene sus resistencias en los cuerpos y los vínculos de las mujeres que criamos, guardianamos, sostenemos. Hablamos de crisis sistémica, porque también se encuentran en crisis los antiguos modelos de representación política. Vemos que algunos dirigentes deciden replegarse a la posición de la espera-especulación, mientras otros redoblan la velocidad para buscar escondrijos por donde insertarse en la compleja arquitectura del saqueo. Por suerte la memoria de la organización sigue rebrotando, y nos encuentra en miles de iniciativas resilientes a niveles locales, nacionales e internacionalistas”.
+Libia Tujuayliya Gea Zamora, mujer Wichi, hija de una histórica organizadora y concientizadora de las mujeres originarias, Octorina Zamora, señala: “El tema central es la propiedad de la tierra, de quién es la tierra y quiénes se la disputan. No es la intención reducirlo todo a la lucha territorial, pero es el gran problema acá. Por algo la formación del Estado estuvo basada en el dominio del Estado colonial sobre las comunidades indígenas, por algo Roca llevó adelante la matanza de pueblos indígenas, por algo los gobiernos de este país se han dedicado siempre a avanzar sobre nuestros territorios, por eso se hicieron estas extranjerizaciones de tierras, y por eso uno de los principales temas que se trata es la venta de los recursos naturales de los territorios habitados por pueblos indígenas. Hay una importancia muy grande en sostener las luchas territoriales, que están siendo retomadas por las mujeres, porque cuando hablamos de territorio hablamos de esta tierra que tiene un montón de riquezas, que es donde está toda la fuerza espiritual de nuestros pueblos, porque ahí nacieron, murieron y fueron enterrados nuestros ancestros. Está también el otro territorio, que es el territorio cultural, el territorio físico, el territorio espiritual. Creo que ésa es la fuerza, la fortaleza que tiene la lucha de las mujeres indígenas”.
+[H2] El DNU y la Ley Omnibus contra todos los derechos
+En un análisis del DNU, la Red de Profesionales Indígenas señala el riesgo que implica para las comunidades originarias la reforma a la Ley 26.737 que establece ciertos límites a la extranjerización de la tierra. Señalan que “el Presidente Milei pretende entregar el litio a Elon Musk, el agua a Mekorot, el fuego a los agronegocios y al extractivismo inmobiliario, el aire a los chemtrails y a Starlink, y las semillas a Bioceres / Syngenta / Bayer / Monsanto. Es decir, al poder real. El DNU pretende adaptar el marco legal jurídico-normativo de Argentina a los requerimientos del poder financiero global”.
+También el Tercer Malón de la Paz, expresa su rechazo por considerar “que el DNU es improcedente, inconstitucional, y nos recuerda la maniobra llevada adelante por Gerardo Morales, en la reforma inconstitucional de Jujuy”. Cuestionan “la derogación de la Ley de Tierras Rurales, sancionada en 2011, que contiene un artículo importante que prohíbe a extranjeros ser propietarios de inmuebles ribereños de cuerpos de agua (ríos, lagos, cuencas) y zonas de seguridad de frontera. Extranjerizar nuestros suelos se traduce en perder nuestra soberanía sobre los bienes comunes asociados al suelo y agua. Las comunidades indígenas podrán ser expulsadas por la megaminería metalífera y de litio, la expansión de la frontera sojera-ganadera, foresto-industrial y el deslizamiento de la explotación hidrocarburífera”.
+Paula Alvarado Mamani, integrante de la Comunidad Tres Ombúes de La Matanza, abogada perteneciente al Pueblo Kolla, preside la Comisión de Derechos de Pueblos Originarios de la Asociación de Abogadas y Abogados de Buenos Aires. En un análisis del DNU expresa esa comisión: “Las consecuencias para los Pueblos Originarios son graves. En la actualidad no se cuenta con una ley de propiedad comunitaria que proteja a los Territorios Indígenas, no logró prorrogarse la ley 26160 de relevamiento territorial comunal que evita los desalojos, y aunque por medio del decreto 805/2021 de Alberto Fernández se prorroga hasta el 2025, los territorios ancestrales y territorios sagrados están en peligro. … Esta situación no es nueva para los Pueblos Originarios, el genocidio, el terricidio y ecocidio continúan, se perpetúan y profundizan”.
+[H2] Leyes y gestos racistas
+El racismo y el patriarcado no se expresa solo en leyes y decretos, sino también en los gestos y actos como el mentiroso “desalojo del Tercer Malón de la Paz” de su permanencia frente a los Tribunales, un día después que la Asamblea del Malón había decidido regresar a sus territorios de origen. El operativo lo realizó la Policía de la ciudad, junto al personal del Espacio Púbico e Higiene Urbana. Un vergonzoso operativo para la foto, pero no para dar respuesta a ninguno de los problemas que los pueblos traían para resolver por necesidad y con urgencia. Política “higienista” profundamente racista, que se repitió en el acto de desalojo del grupo que se encontraba instalado en la esquina del Congreso, y en el levantamiento de la carpa que hacía casi 4 años sostenía Félix Díaz, referente indígena qom ligado a Mauricio Macri, quien ahora se reunió con Patricia Bullrich. Sobre este último gesto nos dice Vero Azpiroz Cleñan, politóloga mapuche de la Comunidad Epu Lafken de Los Toldos: “La ultraderecha, ahora en la vocería oficial del Ministerio de Inseguridad y de Capital Humano, nos configuró (a los pueblos originarios) en un cliché. Lo expresa la figura de Felix Díaz. Eligieron mostrar al “indio permitido”: hombre, evangélico, sin espiritualidad propia del pueblo qom, con algo de folklore en su vestimenta, desterritorializado, para legitimar el inicio de una gestión que, hasta ahora, es antidemocrática. Pero lo más importante fue el "acto de limpieza e higienización" de la Plaza de Mayo. En el autoritarismo de mercado todo se compra y todo se vende. No sabemos aún a qué precio fue”.
+Señala Tujuayliya Gea Zamora: “La lucha indígena ha sido ninguneada desde antes que llegara La Libertad Avanza. Hemos tenido gobiernos que dentro del progresismo han dado garantías y han puesto en agenda la cuestión indígena, pero siempre con políticas incompletas, desfinanciadas, con instituciones que van ensayando y errando constantemente. Tenemos procesos judiciales en el territorio que están incompletos, mujeres indígenas que piden como mínimo una condena a su abusador, a las que se les ha hecho bajar denuncias. Tenemos una Ley 26160 que cada cuatro años hay que estar haciendo una pelea para sostenerla, incluso en gobiernos que se han declarado amistosos con nuestros pueblos. Con el tema de la salud indígena mucho más. En este país no existe política intercultural, política indígena específica para tratar las situaciones que vivimos. No hay tampoco un sistema educativo inclusivo. La libertad Avanza va a intentar destruir lo poquito que se pudo construir. Nosotros venimos ya de políticas discriminatorias, donde nos han puesto de lado, nos han mantenido en reservas indígenas en las orillas de nuestros propios territorios, en las partes menos productivas, más arrasadas, donde ya ha pasado la industria, ha avanzado la frontera agraria, se están echando agrotóxicos, nos han contaminado el río, nos han talado el monte. En este contexto llega un gobierno que se plantea terminar de destruir lo que pudimos sostener. Van a buscar avanzar sobre el desierto verde, y si es necesario nos van a cagar a tiros o nos van a matar de hambre, si se lo permitimos”.
+Relata Lourdes que “el 20 de diciembre, mientras reprimían a los manifestantes en Buenos Aires, en la comunidad Indio Colalao en Tucumán se presentaba un terrateniente junto a la policía para usurpar territorio de la sede comunitaria. En ese lugar la comunidad siembra, se reúne, y lleva adelante proyectos de radio comunitaria, allí preservan los vestigios arqueológicos, es el corazón de su territorio. El usurpador y la policía no contaban con ninguna orden judicial, solamente un argumento: "ustedes ya han perdido". Esta arremetida simbólica, que pretende borrar años de conquistas en materia de derechos de pueblos indígenas, no involucra solamente al presidente y su "casta" de aliados, sino que en él resurgen y se alinean las fantasías fascistas de los sectores dominantes más violentos de la sociedad argentina y de los territorios.”
+En esa perspectiva “las mujeres pasamos de ser consideradas sujeto de derecho en el plano formal, a estar en el foco de la persecución política y social. Por defender los territorios, las aguas, las semillas, las reuniones, nuestras organizaciones y nuestros cuerpos son la primera línea donde recaen las violencias. Se agudiza la violencia machista patriarcal, se fracturan las redes que nos costó años construir, la violencia institucional y la económica nos sacuden y nos devuelven al individualismo y a la competencia del sálvese quien pueda”.
+[H2] Tiempo de resistencia
+Nos dice Lourdes: “En los territorios de cada provincia se libran todos los días batallas anticoloniales que resisten la avanzada extractivista que arrasa con la vida, con políticas de saqueo que llevan varias décadas en nuestro país: agronegocios, megaminería metalífera … En ese contexto, los pueblos naciones indígenas son la última frontera que resiste el saqueo que viene disfrazado de falsas promesas de transición energética y capitalismo verde: el litio, el cobre, alimentos transgénicos, salud hegemónica… En el caso argentino hace décadas que se viene adaptando el marco legal democrático del país a los intereses de las empresas trasnacionales. El ejemplo más claro fue la reforma de la constitución de Jujuy y ahora de la Rioja. Con la llegada de la dictadura “anarcocapitalista” al poder político, por vías democráticas, se acelera el proceso de entrega, despojo y genocidio. Pretenden borrar las identidades individuales, las culturas ancestrales, las economías preexistentes. Este movimiento de la historia nos interpela a construir con más fuerzas lazos intersectoriales, plurinacionales, para resistir. La diversidad, la multiplicidad, la presencia y la raíz dispersa por todo el territorio, es nuestra posibilidad de reexistencia. Años de crecimiento bajo la tierra hoy muestran los cauces donde acuerparnos”.
+El tiempo de crear esa propuesta política es ahora. Las mujeres indígenas están como siempre, en la primera línea de defensa de la vida. Contra los genocidios históricos y los presentes, en Abya Yala y en Palestina, se van bordando colectivamente, y con muchos colores, los tejidos de la Resistencia.</t>
+  </si>
+  <si>
     <t>Regresión ambiental: los peligros de la Ley Ómnibus que impulsa Milei</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/700356-regresion-ambiental-los-peligros-de-la-ley-omnibus-que-impul</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2024
+    Regresión ambiental: los peligros de la Ley Ómnibus que impulsa Milei. Favocere a capitales extranjeros y pone en riesgo bosques y glaciares. Gabriela Vizental, periodista especializada en ambiente, advirtió sobre los riesgos en materia ambiental que prevé la sanción de la ley ómnibus. Qué ecosistemas estarán en riesgo.. El DNU y la ley ómnibus que envió al Congreso el presidente Javier Milei pondrán en peligro ecosistemas clave para la Argentina: la legislación en la que pretende avanzar el nuevo mandatario pone en riesgo glaciares y bosques, al habilitar la producción contaminante y extractivista en esos ecosistemas, fundamentales para la vida humana. Además, la derogación de la ley de Tierras habilitará la extranjerización de grandes parcelas, incluidas ríos y otros recursos naturales.
+[H3] La ley ómnibus de Javier Milei: el detalle de los artículos y las repercusionesMilei envió al Congreso la ley ómnibus
+En su columna de Ambiente y Salud en La García, la periodista Gabriela Vizental, afirmó que lo que propone la Ley Ómnibus en materia de medio ambiente es "suprimir la regulación estatal en favor de capitales privados". Los expertos, en tanto, ya advierten sobre una fuerte regresión ambiental. "Se propone suprimir la regulación estatal en favor de capitales privados y modificar normativas para permitir actividades como la agropecuaria y minera, entre otras, sobre los bienes comunes naturales", sostuvo en diálogo con AM750.
+En concreto, la ley ómnibus avanza sobre la protección de los glaciares prevista por una ley sancionada en el 2010 tras una larga lucha de organizaciones ambientales. En la actualidad, la normativa impide la actividad minera, mientras que el proyecto enviado al Congreso autoriza la actividad en el terreno periglaciar.
+Además, Milei pretende autorizar la deforestación con fines productivos en bosques que hoy cuentan con protección también por ley. De este modo, se permitirá que en las zonas I (rojo) y II (amarillo) donde hoy se encuentra prohibida la deforestación sean autorizados proyectos productivos.
+La normativa que el Presidente envió al Congreso además autoriza las quemas para "limpiar" campos y otras zonas con fines productivos, ya sea para ampliar la frontera agropecuaria como para emprendimientos inmobiliarios. Hoy existe una restricción muy fuerte, que en caso de aprobarse la ley ómnibus dejará de existir: sólo se deberá permiso para iniciar el fuego y, si pasados los 30 días de la solicitud no hay respuesta del Estado, quedará autorizado automáticamente.
+"Esta propuesta avanza sobre la Ley de Bosques de 2007 y la Ley de Glaciares de 2010, dos leyes de presupuestos mínimos", agregó Vizental.
+[H2] Las modificaciones que propone Javier Milei en materia ambiental
+"En el área de medio ambiente se sugieren cambios en la ley de quema, permitiendo a los productores a realizar cortafuegos y acciones preventivas hoy vedadas por la legislación", es uno de los primeros puntos mencionados en la normativa.
+En ese sentido, destaca que "el Fondo de bosques nativos pasará a financiarse directamente del Presupuesto, y se simplifican los procedimientos para la explotación de bosques en zonas habilitadas comercialmente a tal fin".
+Asimismo, se realiza "una modificación a la Ley de Glaciares a fin de habilitar (con los informes ambientales exigidos por la normativa) la actividad económica en la zona periglacial, revirtiendo un avasallamiento del poder federal sobre las provincias".
+En este contexto, la periodista explica: "Primero, desfinancia la Ley de Bosques, es decir, le quita al Fondo Nacional para la Preservación de los Bosques Nativos un recurso económico que hasta ahora sale de un porcentaje (3%) de retenciones a las exportaciones al agronegocio. Con eso se compensa a los titulares de las zonas rojas y amarillas donde la ley prohíbe desmontar".
+"Por otro lado, si se pierden las zonas periglaciares -las que rodean los glaciares- se pierden lo que se llaman estas 'fábricas de agua'. Si se desfinancia Parques Nacionales, no solo se desfinancia proteger los glaciares, sino también toda la biodiversidad a lo largo y ancho de todo el país", enfatizó.
+"Creo que esta ley apunta más a los glaciares de la cordillera norte, que es donde se pueden extraer todos los minerales. Si se desfinancian los Parques Nacionales, pueden aparecer los incendios en esta época y hablamos de bosques nativos, sobre todo en la Patagonia", concluyó Vizental.
+[H3] Seguí leyendo:
+[H3] El texto completo de la Ley Ómnibus de Javier Milei
+[H3] Universidades aranceladas para extranjeros no residentes: los cambios en educación de la ley ómnibus</t>
+  </si>
+  <si>
     <t>Un Estado al servicio de la concentración económica</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/699284-un-estado-al-servicio-de-la-concentracion-economica</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Un Estado al servicio de la concentración económica. Crisis alimentaria y social. Las políticas del nuevo gobierno llevan a los sectores medios y populares al borde de una crisis humanitaria, mientras fomentan la ganancia de las grandes empresas en una camino primarizador de la economía.. A tres semanas de la asunción de Javier Milei, los anuncios y medidas explicitan un modelo que financia y favorece la concentración económica en un espiral inflacionario que amenaza con arrastrar a sectores medios y populares a la pobreza, la indigencia y el hambre. Atenta también contra la supervivencia de la industria, las pymes, y los pequeños y medianos productores del campo que alimenta.
+El precio de los alimentos, entre otros cientos de productos que consumen las familias argentinas, se ve motivado al alza por la falta de controles de precios en una estructura empresaria oligopólica, el aumento del precio relativo de las exportaciones, los servicios públicos y los combustibles.
+En paralelo, estas medidas reducen la rentabilidad de pequeños y medianos productores de alimento, ya aquejados por la sequía, el aumento de los insumos, el alquiler y la concentración de tierras, gracias a las ganancias extraordinarias que el capital concentrado del agronegocio viene obteniendo. Y que incrementará con las nuevas políticas, por sus posiciones financieras, oligopólicas y ante una acción desigual del Estado, garantizando sus ganancias e inversiones mientras deja librado al azar el destino de la industria, las pymes, y los pequeños y medianos productores.
+[H2] Los beneficiarios de siempre
+Se van a cumplir 21 años de la nacionalización de la deuda privada de Domingo Cavallo al final del “Proceso de Reorganización Nacional”. Fueron beneficiarios de dicha nacionalización los ahora grandes grupos económicos argentinos, que producen y distribuyen la mayoría de los productos que consumimos, pudiendo establecer de manera unilateral sus precios.
+La nacionalización de las deudas privadas de las grandes empresas a través del Bono para la Reconstrucción de una Argentina Libre (Bopreal) parece replicar esta medida y vuelve a mostrar la intervención del Estado en favor del capital concentrado. Genera, a futuro, una deuda de aproximadamente 30 mil millones de dólares (el doble que la nacionalización de Cavallo y dos tercios de la deuda de Mauricio Macri con el FMI).
+Algunos economistas como Claudio Lozano ya estiman que dos tercios de esta deuda corresponde a intercambios entre las propias empresas con sus filiales extranjeras. Este proceso no cuenta con la debida fiscalización y encubren giros de dividendos, sobrefacturación o fuga de divisas, entre otras trampas que no han podido ser atendidas. En paralelo, la fiscalización del Estado cae en las medianas y pequeñas empresas y productores.
+El sector de pequeños y medianos productores de alimento (que cubre entre el 60 y el 80 por ciento de las frutas y verduras que se consumen en la mesa de los y las argentinas) se ha visto perjudicado por la acción del Estado en el anterior gobierno. La transferencia extraordinaria a los sectores agroexportadores concentrados a través del dólar soja (con un costo de 590 mil millones de pesos) equivalió al impuesto a las grandes fortunas, u ocho años de la pauta publicitaria del Estado que ahora el ministro Luis Caputo exhibe como un recorte de gasto importante.
+[H2] Los perjudicados de siempre
+En paralelo el nuevo gobierno desfinancia las pocas ayudas que existían para nuestro sector, vacía áreas estratégicas y nos condena como pequeños y medianos productores a ser parte del nuevo ministerio de Capital Humano, con un rejunte de ex-ministerios en manos de personas sin experiencia que solo puede llevar a la inoperancia, y cuya ministra, Sandra Pettovello, hizo su primera aparición pública para sumarse a la represión de la protesta social anunciado por la ministra de Seguridad, Patricia Bullrich. No hay anuncios acerca de cómo se piensa afrontar la crisis humanitaria que el propio gobierno fogonea.
+Desde la Mesa Agroalimentaria Argentina (MAA), de la cual formamos parte, ya hemos presentado propuestas concretas, el Programa Agrario para el Alimento, para reducir el precio de los alimentos a través del apoyo a pequeños y medianos productores, el acceso a la tierra, la creación de nuevos Mercados de Cercanía y otras políticas que ya venimos implementando desde las propias organizaciones.
+Los índices elaborados por el Centro de Estudios Scalabrini Ortiz (CESO) demuestran que dichas políticas implementadas desde la UTT a través de proyectos productivos y de comercialización, brindan alimento más sano y barato a los consumidores, reduciendo la brecha de los intermediarios. En dichos estudios, que comparan la evolución de la inflación en grandes cadenas de supermercados con la de los locales y ferias de la Economía Social, Solidaria y Popular (ESSP), se demuestra, por ejemplo, que tras las PASO, la inflación fue de 20 por ciento en las grandes estructuras oligopólicas, frente al 9 por ciento en nuestros puntos de venta. Una clara demostración del componente especulativo y oligopólico de la inflación en Argentina.
+Eso sin comparar la calidad de los alimentos, los beneficios para los productores y las economías regionales. Y el hecho de que, más allá de que para nosotros el alimento es un derecho y no una mercancía (como debatió nuestro referente Nahuel Levaggi con el vocero del agronegocio Antonio Aracre), nuestro sector incluye miles de productores y comercializadoras que hablan de la competencia necesaria para que funcione “la mano invisible” del mercado. Esa de la que hablan los libros de economía, aún en sus corrientes más ortodoxas.
+[H2] Un Estado para cierto mercado
+Los anuncios de las medidas económicas del nuevo gobierno dan por tierra dos mitos muy recurrentes en los discursos neoliberales en Argentina: que el mercado genera oportunidades por igual para toda la población y que el Estado sirve para moderar estos desequilibrios y no para fomentarlos aún más. No estamos ante un Estado que no interviene, sino uno que precisamente interviene para favorecer a los capitales concentrados que, con la histórica ayuda de ese Estado, han generado reglas desiguales de mercado, aumentando la pobreza, la desigualdad social, el hambre y la primarización de la economía con un fuerte beneficio para los grandes capitales multinacionales (que incluyen grandes empresas argentinas).
+Seguiremos organizándonos para mejor la calidad de vida de los y las argentinas, con o sin ayuda del Estado y el mercado. Sin embargo nuestros esfuerzos no son suficientes sin un apoyo de un Estado que lejos está de priorizar el alimento de nuestra población.
+Esta desigualdad del mercado y el Estado claramente se va profundizar con las nuevas políticas económicas, con una brutal licuación de los ingresos de las clases medias y populares y un tipo de cambio, y otras medidas, que favorecen a los sectores agroexportadores sin valor agregado (es decir, sin trabajo).
+Hoy las medianas y pequeñas empresas exportadoras con valor agregado (incluso algunas dentro de nuestro sector) perciben un dólar de 730 pesos (descontando las nuevas retenciones) y pagan sus insumos a un dólar de 940 pesos (con el impuesto País). Esta desigualdad afecta la industria, las pymes y pequeños productores, llevando a la Argentina hacia un esquema de economía primarizada y sujeta a los vaivenes de los precios internacionales.
+En medio de una crisis económica y social, que lejos de menguar va a tender a incrementarse (junto con las estadísticas de pobreza, indigencia y hambre), desde la UTT y las organizaciones del campo que alimenta redoblaremos la lucha y los esfuerzos para seguir organizando la producción y el consumo para ofrecer a las familias argentinas alimentos sanos y lo más barato que la situación nos permita. Además de sostener comedores populares y otras tareas con una visión de cuidado de la comunidad y la Casa Común. Para nosotras y nosotros el alimento es un derecho y no una mercancía.
+*Coordinación Nacional de la UTT</t>
+  </si>
+  <si>
     <t>Lula derogó artículos clave de la "ley de veneno" sobre uso de pesticidas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/699296-lula-derogo-articulos-clave-de-la-ley-de-veneno-sobre-uso-de</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Lula derogó artículos clave de la "ley de veneno" sobre uso de pesticidas. Un freno al loby del agronegocio. El presidente de Brasil, Luiz Inácio Lula da Silva, vetó puntos clave de una polémica ley que flexibiliza las reglas sobre los pesticidas en el país. "Consultados los ministerios competentes. El presidente de Brasil, Luiz Inácio Lula da Silva, vetó puntos clave de una polémica ley que flexibiliza las reglas sobre los pesticidas en el país. "Consultados los ministerios competentes, el presidente decidió vetar algunos dispositivos, para garantizar la adecuada integración entre las necesidades productivas, el cuidado de la salud y el equilibrio ambiental", dijo el Palacio presidencial del Planalto en una nota.
+Lula decidió vetar 14 tramos de una decena de artículos de la ley que facilita la aprobación de nuevos agrotóxicos en el país y buscaba otorgar mayores poderes de decisión al ministerio de Agricultura. Luego de más de dos décadas de controversias, el texto fue aprobado en el Senado el 28 de noviembre, con un solo voto en contra.
+El agronegocio, uno de los principales motores de la economía brasileña, tiene en el uso intensivo de pesticidas uno de sus pilares. Brasil consumió 719.507 toneladas de pesticidas en 2021, el 20% del total comercializado en el mundo, según la Organización de las Naciones Unidas para la Alimentación y la Agricultura (FAO).
+Con el veto, la Agencia Nacional de Vigilancia Sanitaria (Anvisa) y el Ibama, principal agencia ambiental, continuarán ejerciendo un papel decisivo en el escrutinio de los agrotóxicos previo a su liberación, potestad que quedaba reservada a Agricultura bajo la ley.
+También será invalidada una regla que permitía al ministerio de Agricultura conceder autorizaciones para agrotóxicos antes de la conclusión del análisis de riesgo del producto.
+Además, excluyó una norma que eximía a las empresas de incluir información en los embalajes, algo que podría llevar al reaprovechamiento de agrotóxicos e incentivar la "desinformación" sobre los productos.
+[H2] El viejo anhelo del agronegocio brasileño
+En la agenda de Diputados desde 1999, el proyecto había sido actualizado en 2022 por los legisladores de la bancada ruralista -la más poderosa en el Congreso-, con el apoyo del entonces mandatario brasileño, el ultraderechista Jair Bolsonaro, ferviente defensor del agronegocio.
+Calificada como "ley del veneno" por sus detractores, el texto fue objeto de duras negociaciones entre los senadores y la administración de Lula. El gobierno consiguió mantener el término "agrotóxico", que los diputados habían reemplazado por los más neutros "pesticida" y "producto fitosanitario".
+Pero no logró impedir un cambio mayor: algunos pesticidas, especialmente los que son comprobadamente cancerígenos o capaces de producir mutaciones, o que provoquen daños ambientales, no serán automáticamente prohibidos.
+En adelante, la prohibición abarcará los productos que presenten un "riesgo inaceptable" para el ser humano o el ambiente, un criterio considerado muy vago para los detractores del texto.
+Además, con la nueva ley, los pesticidas destinados exclusivamente para exportación podrán ser fabricados en el país sin precisar autorización.</t>
+  </si>
+  <si>
     <t>La lucha contra el extractivismo seguirá en las calles y rutas ante el nuevo gobierno</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/697977-la-lucha-contra-el-extractivismo-seguira-en-las-calles-y-rut</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La lucha contra el extractivismo seguirá en las calles y rutas ante el nuevo gobierno. Ambientalistas denuncian el "fascismo argentinizado" del presidente. Organizaciones sociales y asambleas socioambientales de todo el país advierten que, pese a las amenazas represivas del gobierno, seguirán movilizadas en defensa del territorio y contra el agronegocio, la megaminería y la explotación petrolera.. Desde Tierra del Fuego a Jujuy. Desde Catamarca a Buenos Aires. Asambleas socioambientales de todo el país saben que el gobierno de Javier Milei intentará avanzar con más agronegocio, megaminería, explotación petrolera y monocultivo forestal --entre otras actividades--. Y es unánime la postura: el rechazo al extractivismo y, como eje principal, la movilización popular para defender los territorios.
+"¿Hasta cuándo?", fue la pregunta que unió a organizaciones de 43 ciudades del país. Se trató de una coordinación como hacía tiempo no se veía, de diversos colectivos en el marco de la Campaña Plurinacional Anti Extractiva para denunciar el impacto social, ambiental y sanitario del extractivismo.
+Planificada con mucha anterioridad a la segunda vuelta electoral, uno de los objetivos fue recordar al nuevo presidente el rechazo al modelo político-económico extractivista y, fundamental, articular redes para lo que vendrá. "Esperamos la profundización del sistema extractivista. Por eso estamos en alerta y activando más que nunca los lazos que se necesitan para frenar este modelo de destrucción y muerte. Vienen tiempos difíciles ya que es mano dura lo que se propone desde el gobierno, siempre recordando que estos gobiernos le rinden cuenta al FMI a costa del sufrimiento de los pueblos", afirmó Paula Kaeser, de la Coordinadora Basta de Balsas Soluciones (BFS) y parte de la Campaña Plurinacional.
+El encuentro fue a principios de mes y hubo actividades en Tierra del Fuego, Chubut, Entre Ríos, Neuquén, Misiones, Buenos Aires, Chaco, Córdoba, Entre Ríos, La Rioja, Mendoza, Río Negro, Salta, San Juan, San Luis y Tucumán, entre otras provincias. Se denunció el impacto del agronegocio y las fumigaciones con agrotóxicos, de la megaminería (con los casos extremos de San Juan, Catamarca y la explotación de litio), el monocultivo de árboles (con Misiones y Corrientes como referencias), la explotación petrolera en Neuquén y la exploración en el Mar Argentino, y el impacto negativo de las megarrepresas, donde sobresalen Misiones, Neuquén, Santa Cruz y Mendoza (ésta última provincia aún sin cumplir el fallo de la Corte Suprema para liberar el agua del río Atuel a La Pampa).
+Por su parte, la Unión de Asambleas de Comunidades (UAC) es un espacio emblemático de articulación de luchas provinciales. Se reúne periódicamente desde 2006 y siempre mantuvo la autonomía de los partidos políticos. Del 8 al 10 de diciembre celebraron su 36 encuentro, en la localidad bonaerense de Jáuregui, territorio que padece las fumigaciones con agrotóxicos, las curtiembres contaminantes y uno de los basurales a cielo abierto más grande del país.
+Laura Olivares vive en Jáuregui y es parte de la UAC. Definió al gobierno de Milei como "el fascismo argentinizado". Señaló que las razones de su triunfo son tan diversas como los sectores que lo votaron, pero con eje especial en el hartazgo de las políticas previas que no resolvieron lo más básico de la población. "Esto confirma lo que venimos diciendo hace tiempo, que este modelo no sirve más, es necesaria una democracia real, representativa de los pueblos", resumió.
+Respecto al extractivismo, no tiene dudas de que se intentará avanzar con más megaminería, explotación petrolera y agronegocio. En plena campaña electoral, Milei negó la existencia del cambio climático y sentenció que "una empresa puede contaminar un río todo lo que quiera". Afirmó que el valor del agua es "cero" y propuso la apropiación de ese bien por parte de las empresas.
+Otra muestra, ya como Presidente, es ceder a conducción de la Secretaría de Bioeconomía (nuevo nombre del área de agricultura) a Fernando Vilella, ex decano de la Facultad de Agronomía de la UBA y ex funcionario de Daniel Scioli en Buenos Aires, un aliado incondicional de las compañías de transgénicos-agrotóxicos y de las exportadoras de granos. Lo mismo que su grupo de trabajo, donde sobresalen referentes de la Asociación de Productores de Siembra Directa (Aapresid), empresarios y lobistas del agronegocio local e internacional.
+Olivares remarcó que desde la UAC conocen desde hace años de persecución y hostigamiento a las comunidades que se oponen al extractivismo, donde los gobiernos provinciales también instrumentan la represión. Existen numerosos ejemplos: Andalgalá, Jáchal y Salinas Grandes, por citar solo algunos. Señaló que todo indica que con el nuevo gobierno "será peor", pero advierte que eso no frenará las acciones en defensa del agua y los bienes comunes: "Las asambleas seguiremos en nuestros territorios tejiendo redes, fortaleciendo nuestras luchas, generando resistencia, fortaleciendo la autonomía. Tenemos claro quiénes son los enemigos actuales y estaremos en las calles exigiendo nuestros derechos".
+Una de las características, y fortalezas, del movimiento socioambiental es la presencia en las calles y la acción directa. Así lo demostraron Esquel, Andalgalá, Famatina y Chilecito, Jujuy (con las movilizaciones de los pueblos indígenas), Mar del Plata y Malvinas Argentinas (Córdoba), contra Monsanto, entre otros casos. Los últimos picos masivos fueron Mendoza (2019) y Chubut (diciembre de 2021), donde hicieron retroceder a los gobiernos provinciales con sus intentos de permitir la megaminería. Paula Kaeser dejó un invitación que, de alguna manera, es también una respuesta a las corporaciones extractivas y al gobierno nacional: "Nos vemos en las calles, en defensa del agua y la vida".
+[H2] Protocolo versus movilización
+El "protocolo para el mantenimiento del orden público" que presentó Patricia Bullrich como amenaza para reprimir la protesta social no sorprendió a las organizaciones socioambientales. Tienen muy vivo el recuerdo de Santiago Maldonado y Rafael Nahuel, ambos casos donde tuvieron directa relación las fuerzas comandadas por Bullrich (Gendarmería Nacional y Prefectura Naval). "Este protocolo es inconstitucional y es lo que vimos en Jujuy, con la reforma constitucional este año, donde desde ese momento se viven hostigamientos, persecuciones, violaciones a los derechos humanos y constitucionales", afirmó Paula Kaeser, de la Coordinadora Basta de Falsas Soluciones. Recordó que las organizaciones seguirán exigiendo desde las calles otra democracia, donde se respeten las decisiones de los habitantes que viven en cada territorio y ya dijeron no al extractivismo.</t>
+  </si>
+  <si>
     <t>El hombre detrás de las idas y vueltas con las retenciones</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/696904-el-hombre-detras-de-las-idas-y-vueltas-con-las-retenciones</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    El hombre detrás de las idas y vueltas con las retenciones. La historia de Fernando Vilella, secretario de Bioeconomía. En menos de días las políticas agropecuarias del gobierno de Javier Milei no solo cambiaron el rango del ministerio a secretaría y el nombre de Agricultura a "Bioeconomía" sino que tuvieron que dar. En menos de días las políticas agropecuarias del gobierno de Javier Milei no solo cambiaron el rango del ministerio a secretaría y el nombre de Agricultura a "Bioeconomía" sino que tuvieron que dar idas y vueltas con anuncios sobre el tema central que embandera a "el campo" desde 2008: las retenciones. Quien tuvo que dar las respuestas en las últimas hora no fue el ministro de Economía, Luis Caputo; sino el aún poco conocido secretario de Bioeconomía, Fernando Vilella.
+Caputo anunció el miércoles pasado que subirían al 15 por ciento las retenciones "no agropecuarias", luego se confirmó que sí subirían las retenciones a cultivos y economías regionales y, finalmente, el lunes dieron marcha atrás para algunos sectores luego de las quejas de la Mesa de Enlace y gobernadores.
+"Vamos a comunicar una diferencia en el proyecto que se va a elevar al Congreso", emparchó Vilella los idas y vueltas de su jefe, el ministro de Economía Caputo y acomodó el inicio de la relación del gobierno de ultraderecha con las entidades agropecuarias, que el viernes fueron corriendo a protestar por haber esperado el fin de las retenciones y encontrarse con un aumento para las economías regionales que el ex ministro de Economía, Sergio Massa, había dejado en cero.
+Vilella anunció que 18 productos regionales volverían a cero y, a cambio, se aumentó de 31% a 33% las retenciones sobre los subproductos de la soja --harina y aceite-- lo que le valió otra queja del Complejo Cerealero-Oleginosa, un núcleo concentrado de empresas muy beneficiadas por la devaluación del 119% del peso.
+¿Quién es Vilella? El hombre bajito y canoso que respondió por la primera marcha atrás del gobierno de Javier Milei. De 68 años, y durante 48 años profesor de la Facultad de Agronomía de la Universidad de Buenos Aires (FAUBA), Vilella se sumó a las "fuerzas del cielo" tras la sorpresiva victoria de Milei en las PASO. La apuesta del decano de la FAUBA entre 1998 y 2006 fue la de presentarse como un experto en "bieconomía" --nombre con el que bautiza su gestión--, una palabra en auge para el agronegocio, ya que permite asociar la biotecnología con la "sustentabilidad", patentes e innovaciones con "cuidado del planeta".
+Vilella llega a la gestión pública nacional --ya había sido subsecretario de Asuntos Agrarios en Buenos Aires durante la gestión del ex gobernador y actual embajador en Brasil, Daniel Scioli-- tras ser director del Programa de Agronegocios y Alimentos, y profesor a cargo de la Cátedra de Agronegocios en la FAUBA, donde también creó la licenciatura de Ciencia Ambientales, entre otros cargos académicos. Esa formación vinculada al agronegocio se reflejó rápidamente en su equipo asesor.
+Tras la primera vuelta electoral, con Milei encaminado al balotaje, el ex decano sumó a Pedro Vigneau --quien fue nombrado como asesor especial y virtual jefe de Gabinete--, ex presidente de Aapresid (Asociación Argentina de Productores en Siembra Directa) y de la organización Maizar, dos influyentes organizaciones del modelo agropecuario dominante. Vilella, Vigneau y Germán Paats --integrante de la Fundación Barbechando, grupo de lobby en el Congreso que se opuso a la Ley de Humedales-- fueron los encargados de hablar con "el campo" cuando Milei prometía cortar relación con Brasil y China --los principales compradores de la materia prima argentina-- y luego del balotaje encabezaron la transición.
+La relación con el mundo del agronegocio --por fuera de la conocida Mesa de Enlace-- de Vilella excede lo académico. El secretario es miembro del Instituto de Ética y Calidad en el Agro (ETICAGRO), de la Asociación Argentina de Biocombustibles e Hidrógeno y preside la Fundación Alimentos Argentinos. Recorrido que le valió, a cinco días de su asunción, un reconocimiento por parte del Instituto Interamericano de Cooperación para la Agricultura, una organización regional que impulsa la incorporación de Agtech y el modelo agroquímico.
+En la previa de jurar como secretario, el 5 de diciembre, Vilella tuvo otro fuerte espldarazo del sector del agronegocio en una reunión convocado por empresas del sector. Presentado por Héctor Huergo, histórico editor de Clarín Rural y ex funcionario de Domingo Cavallo en el INTA, Vilella presentó a su futuro gabinete en una Casona de San Telmo, con valor histórico por ser parte de una histórica familia de la oligarquía ganadera.
+Entre los integrantes de su equipo que fueron confirmados días después están otro ex integrantes de Aapresid, de CREA --otra influyente asociación de empresarios del sector, que nutrió las filas del gobierno macrista--, y el ex CEO de Monsanto y ministro de Agroindustria del gobierno de María Eugenia Vidal, Leonardo Sarquís, quien ocupa el cargo de coordinación del Consejo Federal Agropecuario (CFA).
+En una semana de gobierno de ultraderecha, con el precio de los alimentos por los nubes, Vilella ratificó la idea expresada por Milei y su canciller Diana Mondino al sostener que los precios internos de la carne van a bajar porque el "poder adquisitivo va a hacer que se deprima la demanda y esa depresión afectará los precios". Para eso restará ver ver si la industria no eligirá enviar la producción al exterior con la eliminación de la política de cuotas de exportación.
+En esa confrontación de dos modelos de producción de alimentos, para las mesas de los argentinos o como commidites para la exportación, el secretario también sostuvo esta mañana que el eje de su política será duplicar las exportaciones y generar una "marca país" para "ingresar a los mercados más sofisticados del mundo".</t>
+  </si>
+  <si>
     <t>El Congreso de Brasil restableció el "marco temporal" para las tierras indígenas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/695568-el-congreso-de-brasil-restablecio-el-marco-temporal-para-las</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    El Congreso de Brasil restableció el "marco temporal" para las tierras indígenas. Eliminan el veto de Lula que protegía la demarcación de los territorios. El Congreso de Brasil restableció artículos clave de una ley que limita los derechos de los indígenas sobre sus tierras ancestrales, al eliminar el veto del presidente Luiz Inácio Lul. El Congreso de Brasil restableció artículos clave de una ley que limita los derechos de los indígenas sobre sus tierras ancestrales, al eliminar el veto del presidente Luiz Inácio Lula da Silva a esa normativa. La norma que fija el denominado marco temporal de las tierras indígenas supone una "tesis" para limitar el reconocimiento de tierras indígenas. La tesis solo reconoce a las comunidades indígenas derechos sobre los territorios que ocupaban o disputaban al 5 de octubre de 1988, cuando se promulgó la Constitución vigente.Entidades de los pueblos originarios rechazan el marco temporal y aseguran que no se puede fijar esa fecha de 1988 debido a que muchos fueron expulsados de sus territorios ancestrales, especialmente durante la última dictadura militar que gobernó Brasil entre 1964 y1985.El Congreso surgido en las elecciones de 2022, de mayoría de centroderecha, derecha y de la extrema derecha aliada al expresidente Jair Bolsonaro, había aprobado en septiembre el marco en carácter de urgencia.En octubre, Lula vetó parcialmente la ley aprobada por el Congreso que preveía limitar la demarcación de territorio para los pueblos indígenas para permitir el avance del agronegocio y la minería. Este jueves el Congreso rechazó las objeciones del Ejecutivo a la tesis del marco temporal.
+[H2] Rechazos a la medida
+Unprocessed element [b]
+Unprocessed element [br]
+La organización de defensa de los derechos humanos Survival International calificó a la legislación restituida por el Congreso como "el más grave y despiadado ataque" contra los derechos de los indígenas en muchas décadas en el mayor país latinoamericano.De acuerdo con un comunicado de la organización de defensa de los derechos de los indígenas, la nueva ley contiene una "serie de medidas extremadamente antiindígenas", por lo que tendrá "impactos catastróficos" para muchas poblaciones originarias.
+[H2] Las reservas indígenas en Brasil
+Según datos de la Fundación Nacional de los Pueblos Indígenas (FUNAI), ente gubernamental de defensa de las poblaciones originarias, las reservas ocupan 13,75% del territorio del país.</t>
+  </si>
+  <si>
     <t>La Mesa de Enlace y el enojo por la suba de las retenciones</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/695310-la-mesa-de-enlace-y-el-enojo-por-la-suba-de-las-retenciones</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La Mesa de Enlace y el enojo por la suba de las retenciones. Incremento al 15 por ciento. Los representantes de la Mesa de Enlace salieron esta tarde de la reunión con funcionarios de Economía en la que expresaron su descontento con la decisión de incrementar a un 15% las rete. Los representantes de la Mesa de Enlace salieron esta tarde de la reunión con funcionarios de Economía en la que expresaron su descontento con la decisión de incrementar a un 15% las retenciónes a las exportaciones --excepto la soja que cotinúa en 33%--, a pesar de que el ministro de Economía, Luis Caputo, había anunciado que el incremento "provisorio" sería para las "exportaciones no agropecuarias".
+A pesar de manifestarse en contra de la decisión, el titular de la Sociedad Rural, Nicolás Pino, dijo no estar "defraudado" con el gobierno y agradeció la convocatoria al diálogo; además relativizaron la otra porción de las medidas de ajuste y liberalización del mercado que benefician al sector: la devaluación del peso y un dólar exportador de 860 pesos; además del fin de los controles exportadores y las cuotas para productos como la carne, que tenía siete cortes con límites para abastecer el mercado interno.
+Tras el encuentro en el Ministerio de Economía, Pino y el titular de la Federación Agraria Argentina, Carlos Achetoni, fueron los voceros de las entidades del agronegocio y anunciaron que el Gobierno les prometió abrir mesas técnicas para analizar sector por sector la aplicación de las retenciones. "Hay muchas producciones y economías regionales que no resisten ningún tipo de presión", sostuvo Achetoni y remarcó el caso de la lechería.
+Entre las decisiones tomadas por el ex ministro de Economía, Sergio Massa, había estado la quita de las retenciones por 90 días a la lechería y la quita total de gravámenes a las economías regionales, que ahora volverán al 15%. "Nos dijeron que es temporal", reconoció Pino y agregó que no tuvieron precisiones sobre cuánto tiempo durará la medida. De todas formas, el titular de la Sociedad Rural buscó defender al gobierno: "Cómo vamos a estar defraudados con un gobierno que acaba de asumir y nos invita a discutir".
+El objetivo de Caputo, a partir del aumento de retenciones, es alcanzar ingresos por el 0,5 % del PBI para 2024. Con una cosecha que, a diferencia de la obtenida en la campaña 2022/2023 en medio de una sequía histórica, promete tener rindes muy altos.
+En la queja por el incremento de las retenciones al 15% --actualmente, entre los cultivos de mayor volumen productivo, el trigo y el maíz tiene un 12% y el girasol 7%--, los referentes de la Mesa de Enlace evitaron ponderar la transferencia de ingresos que significa la brusca devaluación del peso, por el que pasarán a obtener 860 pesos por cada dólar exportado, menos el gravamen de retención. "Hay que estar muy finito para ver cómo queda, acaba de subir el gasoil y hay que ver los costos", argumentó Pino. Otro de los puntos que marcan desde el agronegocio es el aumento de los insumos químicos importados, de lo cuáles depende el modelo agropecuario convencional.
+Además, el titular de la Sociedad Rural reconoció que desde Economía aseguraron que podrán fin a las restricciones y cuotas de exportación como sucede con los cortes populares de carne, que estaban limitados para asegurar el abastecimiento interno sin la competencia con el precio de exportación. "Yo no veo el abuso", respondió Pino sobre la posibilidad de que el kilo de carne continúe aumentando hasta los 12 mil pesos e insitió que la liberalización de los controles es "lo que tiene que pasar en un país normal", porque "el intervencionismo de mercado generan distorsiones horribles".
+A pesar de todos los matices puestos por los representantes de la Mesa de Enlace para sostener su respaldo al gobierno de ultraderecha, Pino reconoció que "durante la campaña se dicen muchas cosas que, cuando llegás al sillón no son fáciles de cumplir".
+En ese sentido, luego de que se conociera la letra chica de los anuncios de Caputo, el ex secretario de Agricultura Juan José Bahillo criticó: "No cumplen las promesas de campaña y engañan a los productores, que creyeron en ellos, con una brutalidad innecesaria". Y agregó: "Estafaron a los productores de economías regionales, a quienes les volvieron a imponer retenciones".
+No se trata de la primera marcha atrás de un gobierno que cuenta con el respaldo de la Mesa de Enlace. Mauricio Macri había iniciado su gobierno con una baja de las retenciones a la soja, trigo, maíz y girasol; que tuvo que revertir en septiembre de 2018, luego de que su gobierno --con Caputo en el Gabinete-- acudiera al FMI a pedir el préstamo más grande de la historia. En aquellos días, Macri también redujo la cantidad de ministerios y anticipó: "Habrá más pobreza".
+[H2] El consorcio de la carne también se reunió con el Gobierno
+El presidente del Consorcio de Exportadores de Carnes Argentinas (ABC), Mario Ravettino, confirmó hoy que el Gobierno nacional incrementará las retenciones al sector frigorífico del 9% a 15%, tras una reunión informativa que mantuvo este mediodía con el secretario de Bioeconomía, Fernando Vilella."En el programa que tienen explicaron muy claramente el tema de las retenciones y nos hablaron de este incremento que van a hacer, pero también quedó a las claras la situación de mejora que vamos a tener con el tipo de cambio", subrayó Ravettino a la prensa a la salida del encuentro.La reunión fue convocada por el equipo de Bioeconomía para repasar algunos puntos del paquete de medidas económicas anunciado el martes por el ministro de Economía, Luis Caputo.En este sentido, el empresario indicó: "Pasamos a un tipo de cambio base $ 800 pero que, como es un 80/20 con el sistema que había, vamos a tener un tipo de cambio que sin las retenciones nos va a quedar en alrededor de $ 760", lo que consideró "un paso muy positivo" para la forma en que el sector venía liquidando."Es decir, se hace el esfuerzo de las retenciones pero hay una compensación muy importante que indudablemente determina que somos un sector considerado por el actual equipo económico", añadió.La reunión entre la industria frigorífica y las autoridades de Bioeconomía arrancó a las 12 en el edificio de la cartera en el centro porteño, y fue la antesala de un encuentro similar con representantes de la Mesa de Enlace Agropecuaria.</t>
+  </si>
+  <si>
     <t>En la AFIP suena un contador que daba consejos para evadir la facturación de granos</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/692250-para-la-afip-milei-quiere-a-un-contador-que-ayudaba-a-evitar</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    En la AFIP suena un contador que daba consejos para evadir la facturación de granos. A Marcos Sequeira lo posicionan -y se posiciona- al frente del ente recaudador. En un raid mediático, al contador se le escapó que Milei le ofreció quedarse a cargo de la Administración Federal de Ingresos Públicos. Precavido, pidió que no le pase lo mismo que "a Píparo". En las mismas entrevistas aprovechó para sacar la motosierra. La "ayuda" que le brindó a empresas del agro para evitar facturar...a la propia AFIP.. "Lo quiero ver oficializado porque no quiero que me pase lo que le pasó a Carolina Píparo en la ANSES." Precavido, el contador Marcos Sequeira evitó confirmar su rol al frente de la Administración Federal de Ingresos Públicos (AFIP) en la presidencia de Javier Milei. Su nombre surgió con fuerza en las últimas horas, Milei no habría logrado convencer Kuban Lisa, socio del estudio Brouchou-Funes de Rioja, y quedó descartado el nombre de Ramiro Marra, el primero que había sonado. El cordobés, voluntarioso, se adelantó y publicó en sus redes sociales nueve ejes centrales para su gestión en el organismo fiscal.
+Cuando su nombre comenzó a sonar, las radios cordobesas comenzaron a llamarlo para confirmar su lugar en el Gabinete de la ultraderecha. El tributarista, una recurrida fuente de los medios mediterráneos, evitó confirmar su lugar, pero sí adelantó algunas ideas afines a la motosierra. Habló de asumir con el permiso de "cortar varias cabezas" y argumentó que era necesario cortar "la cadena de corrupción" y marcó que no solo eliminará impuestos sino que propondrá "reesctructurar" el sistema fiscal porque "está todo mal hecho".
+Sequeira no viene de la gestión pública. Su carrera fue en el sector privado y académico, otra similitud con el perfil del círculo cercano al futuro presidente. Además, conoce a la futura canciller Diana Mondino, ya que trabajó en el Banco Roela, fundado por Víctor Mondino, padre de Diana. El cordobés también podría encontrar en las filas del futuro Gabinete a otros coterráneos, entre ellos, a Osvaldo Giordano, actual ministro de Finanzas de Córdoba en el gobierno de Juan Schiaretti, y futuro titular de la ANSES; el mismo que hizo caer a Píparo.
+Giordiano -con un acuerdo cada vez más claro con el peronismos cordobés- no sería el único cordobés en el futuro gobierno, también llegará al gobierno libertario Franco Mogetta, viajará desde la cartera de Transporte de Córdoba a la de Nación. Además, un ex funcionario del peronismo cordobés como Hugo Testa ya trabaja con Guillermo Ferraro, quien encabezará el Ministerio de Infraestructura; mientras que suena el arribo para esa cartera del titular de la Empresa Provincia de Energía de Córdoba (EPEC), Luis Giovine. El voto cordobés fue clave para poner a Milei en la Casa Rosada y el anarcocapitalista les está respondiendo con acuerdos políticos.
+Anticipándose a su posible nombramiento, Sequeira dejó su carta de presentación en sus redes sociales. Ayer hizo un posteo que no dejaba mucho lugar a dudas: "Propuestas de Gestión para la Administración Federal de Ingresos Públicos". Entre las diez propuestas aparecían palabras del mundo gerencial: "fortalecimiento", "transparencia", "modernización", "digitalización"; también ideas centrales de gestión pública como mejorar el acceso a las aplicaciones, la atención a los usuario y la formación de personal.
+En cuanto a las políticas centrales del organismo, Sequeira menciona algunas que podrían ser disruptivas con el pensamiento filosófico de Milei, que considera un "robo" los impuestos. El tributista habló de optimizar la recaudación, reforzar la lucha contra el fraude y la evasión, establecer mecanismos internacionales de intercambio de información e incluso apunta contra una de las políticas estrellas de los nuevos aliados macristas: "Revisión de Políticas sobre Blanqueos y Moratorias".
+Unprocessed element [figure]
+"Hay que intensificar las acciones de control y fiscalización, empleando tecnologías avanzadas y técnicas de análisis de datos para detectar y prevenir irregularidades", sostiene Sequeira en sus plan de gestión. Sin embargo, como reveló este diario, Sequeira ha participado de mecanismos complejos evasión.
+Cuando, en 2008, el gobierno de Cristina Kirchner intentó subir las retenciones a los granos, abrió una disputa con el agronegocio, que unió a pooles de siembra y productores pequeños, y significa, hasta estos días, gran parte del rechazo al "kirchnerismo" en Córdoba. Entonces, Sequeira participa de mecanismos que integraba junto a jueces y oficinas de la AFIP para favorecer a empresas del agro en la evasión de la facturación de granos.
+"Si se abordan con decisión y transparencia los desafíos actuales, podemos pensar en un futuro próspero para el país", promete el cordobés.</t>
+  </si>
+  <si>
     <t>La Libertad Avanza y la casta tiene cargo</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/689257-la-libertad-avanza-y-la-casta-tiene-cargo</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La Libertad Avanza y la casta tiene cargo. Otro cambio en el caótico armado de gabinete de Milei y un claro ganador. El segundo candidato al Banco Central, Demian Reidel, también se bajó antes de asumir. Aun sin confirmación oficial, el "Messi de las finanzas" de Macri sigue avanzando en los hechos.. En etapas frenéticas, el nuevo gobierno va delineando algunas formas no sin antes pasar por un desgastante juego de anuncios y desmentidas, todos los días y a toda hora. E incluso a las mismas horas en que los protagonistas aludidos desmienten o afirman lo que cerca de Javier Milei dejan trascender. Una cosa queda clara: los primeros anuncios de tono más "anarco capitalista" en cuanto a nombres y contenidos, incluidas las figuras "de la primera hora" de La Libertad Avanza (¿eso que la gente votó?) van bajando del barco de gobierno o relegados a asientos de tercera clase, y van siendo reemplazados por referentes de Juntos por el Cambio, a los que se sumaron nombres cercanos al otrora prescindente Juan Schiaretti. Esta loca danza de nombres que sale del piso 21 del Hotel Libertador, el lugar "energéticamente" elegido para sentar las bases de la "oficina del Presidente electo", no se toma descanso el fin de semana.
+El sábado hubo una baja significativa y, entre tanto baile de nombres, uno que apareció y fue desmentido, pero no tanto. La baja, otro que sigue a Milei "desde Cemento", Demian Reidel, que a su vez había aparecido para reemplazar en el Banco Central a Emilio Ocampo, el padre del plan de dolarización, cuando Luis "Toto" Caputo entró oficialmente en escena. El nombre que cayó sin que lo llamen fue el de Daniel Scioli, que el sábado sonó como posible secretario de Turismo, algo que luego fue desmentido.
+[H2] Las fuerzas del cielo por asalto
+La salida de Reidel refuerza la toma por asalto macrista que, en rigor, comenzó a ser silenciosamente tejida mucho antes del 19 de noviembre, y que se completa con el plan económico en el que que "el Messi de las finanzas" viene trabajando hace meses. El paso al costado de este ferviente mileísta cercano a Sturzenegger, que militó con ahínco en las redes llamando "a votar a Milei y a erradicar el cáncer kirchnerista de la Argentina", fue amablemente comunicada: "Para evitar especulaciones, quiero confirmar que en este momento no voy a ejercer la presidencia del BCRA. El presidente Javier Milei cuenta con mi apoyo absoluto". En los hechos, parece confirmar que el "sí" de Caputo al ofrecimiento de la cartera viene con más condiciones a sortear que la de una supuesta negativa familiar, según se dejó trascender. Y que lo que fue promesa de campaña y tuvo que ser reafirmado en un comunicado, también comienza a ser de lejano cumplimiento: "el cierre del Banco Central no es un asunto negociable". Y con ello, claro, la mentada "dolarización".
+Por otra parte, tanto desde La Libertad Avanza como desde el entorno de Scioli negaron a Página/12 que haya habido ofrecimiento alguno para integrar el gabinete. Pero, en el mismo momento, otras fuentes de LLA aseguraban a este medio que "sí hubo un acercamiento, pero de parte de él, que ya dijo que quiere quedarse en Brasil". Se sabe que el actual embajador mantiene una relación cercana con Guillermo Francos, actualmente confirmado como ministro del Interior del futuro gobierno y hombre que ganó peso en el armado. Entre otros cargos en diversas gestiones (incluida la actual, donde Francos fue director ejecutivo por Argentina del Banco Interamericano de Desarrollo, cargo al que renunció para subirse a la aventura libertaria), Francos fue presidente del Banco Provincia durante toda la primera gobernación de Scioli, desde 2007 hasta 2011.
+[H2] Fotos borrosas
+Si hubiera que hacer una foto de la conformación del gabinete al día de hoy, tendría algunos detalles curiosos y hasta contradictorios (aunque, se sabe, en la lógica de estos días tumultuosos en el Libertador cualquier foto que se tome puede durar menos que una storie de Instagram).
+Uno es el de la puja a cielo abierto que por estas horas se da en las áreas de Seguridad y Defensa, con Patricia Bullrich y Victoria Villarruel como protagonistas, de la que informa en extenso Luciana Bertoia en este diario.
+Un dato no menor sobre esta puja: a Villarruel, se sabe, la mueve una misión política en la que viene trabajando denodadamente desde hace años, un "cambio de relato", en sus propias palabras, vinculado a la impunidad de los genocidas. Bullrich tiene varias tareas que retomar si se concreta este "segundo tiempo". No solo represivas: su paso por el ministerio de Seguridad abrió importantes negocios, fundamentalmente con el Estado de Israel. Dejó un tendal de compras hechas pero de imposible uso tras su salida, desde sistemas de comunicación que no servían porque no eran aptos para las zonas geográficas en que se necesitaban, hasta lanchas compradas sin licitación y con grandes sobreprecios, que nunca pudieron usarse porque su calado no se adecuaba a los ríos del norte argentino.
+Una aparente contradicción surge en el casillero de Agricultura, para el que por ahora queda en pie un "no PRO duro", Fernando Vilella. Ex decano de la Facultad de Agronomía de la UBA, profesor de Mercados Agropecuarios y director de Bioeconomía de esa facultad, Vilella es conocido por su proyecto de "vaca viva", que armó con el exsecretario del área durante el kirchnerismo y exinterventor de Vicentin Gabriel Delgado (quien fue nuevamente convocado por Massa). Lo particular de este proyecto vinculado a la producción de proteína animal y vegetal es que es de neto corte productivista: valor agregado a la exportación. Y que su éxito está vinculado a la consolidación de un mercado como el de los Brics, que el nuevo Presidente en su discurso viene a derribar.
+Pero al mismo tiempo, en la agenda que dejó trascender Vilella figura la receta anarco capitalista: eliminación total de las retenciones a la soja, el trigo y el maíz, quita absoluta de todas las regulaciones del sector, incluidas las exportaciones de carne y los fondos para la harina y el aceite. La cartera cambiaría de nombre (pasaría a ser Secretaría de Bioeconomía), pero básicamente sería una jugadora a favor del agronegocio.
+Con logo de estética Casa Blanca estrenado la misma noche de las elecciones, desde la "Oficina del Presidente electo" salieron hasta ahora pocas muy confirmaciones oficiales. Y hubo una que picó en punta: Horacio Marin, un hombre que hizo toda su carrera en Techint, al frente de YPF. Favor con favorazo se paga: como informó Leandro Renou en este diario, después de las primarias la empresa de Paolo Rocca pasó de aportarle fondos a la campaña de Patricia Bullrich a derivar buena parte de ellos a financiar la carrera presidencial de Javier Milei, transformándose en el único aportante privado que oficialmente tuvo la campaña de La Libertad Avanza.</t>
+  </si>
+  <si>
     <t>Un estudio vincula el uso de pesticidas en Brasil con las muertes por leucemia infantil</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/612161-un-estudio-vincula-el-uso-de-pesticidas-en-brasil-con-las-mu</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Un estudio vincula el uso de pesticidas en Brasil con las muertes por leucemia infantil. Los peligros del agronegocio. Un estudio publicado en la revista Proceedings of the National Academy of Sciences (PNAS) relaciona la rápida expansión de la soja y el aumento del uso de los pesticidas en los biomas. Un estudio publicado en la revista Proceedings of the National Academy of Sciences (PNAS) relaciona la rápida expansión de la soja y el aumento del uso de los pesticidas en los biomas Cerrado y amazónico de Brasil con un incremento de la mortalidad por leucemia infantil.El trabajo, que no proporciona un vínculo causal, analiza 15 años de datos sobre la mortalidad de la leucemia linfoblástica aguda (LLA), el tipo de leucemia más común en los niños.
+[H2] El uso de pesticidas y herbicidas en Brasil
+Unprocessed element [b]
+Unprocessed element [br]
+[H2] El estudio
+[H2] La punta del iceberg
+"Nuestra preocupación es que nuestros resultados son sólo la punta del iceberg (...). La exposición a plaguicidas también puede dar lugar a casos no mortales de leucemia y existe el riesgo de que repercuta en la comunidad adulta y adolescente", afirma Skidmore.Los investigadores indican que hay varias formas de mitigar esta relación: formación y educación de los trabajadores agrícolas, una normativa inteligente para el uso de pesticidas y el acceso a la atención sanitaria (la LLA es tratable pero requiere de centros sanitarios adecuados).Brasil está desarrollando actualmente un programa de certificación que exige a los aplicadores de plaguicidas formación y educación en materia de seguridad, según la Universidad de Illinois.</t>
+  </si>
+  <si>
     <t>La Asamblea Constituyente  de los Pueblos Riojanos demanda transparencia en materia de litio</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/612035-la-asamblea-constituyente-de-los-pueblos-riojanos-demanda-tr</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La Asamblea Constituyente de los Pueblos Riojanos demanda transparencia en materia de litio. Exigen información sobre proyectos con impacto medio ambiental. La Asamblea informó este martes sobre la medida cautelar solicitada a la Comisión Interamericana de Derechos Humanos en relación con los proyectos de minería de litio y el acuerdo con la empresa israelí Mekorot.. Este martes la Asamblea Constituyente de los Pueblos Riojanos convocó a una conferencia de prensa en la que se dio a conocer la petición de una medida cautelar ante la Comisión Interamericana de Derechos Humanos relacionada con los proyectos de minería de litio y el acuerdo con la empresa israelí Mekorot.
+La abogada Ivana Cattaneo, quien representa a la asamblea ante la CIDH, hizo hincapié en la importancia del acceso a la información en el contexto de los megaproyectos de extracción de litio, que involucran no solo la explotación de recursos naturales, sino también cuestiones de derechos humanos y preservación del medio ambiente.
+En la presentación, Cattaneo destacó que la asamblea invoca los derechos de las comunidades por la vida y amparándose en las disposiciones de la Ley Nacional N° 27.275 y la Ley Provincial N° 10,119/18. La Ley Provincial establece la obligación de "garantizar el efectivo ejercicio del derecho de acceso a la información pública en formato digital abierto y gratuito". Sin embargo, la falta de acceso a información sobre los proyectos de minería y el acuerdo con Mekorot ha llevado a la presentación de una medida cautelar.
+La preocupación principal de este reclamo se centra en el agua, un recurso vital para la subsistencia de la población riojana, que viene en disputa debido a los megaproyectos mineros, industriales y agronegocios. La población reunida en asamblea reclama que no ha tenido acceso a la información necesaria sobre estos proyectos y a pesar de haberla solicitado por vias formales.
+La asamblea sostiene la necesidad de la clausura temporal de los proyectos de litio debido a la violación flagrante de la ley y la falta de conocimiento de la población sobre los proyectos y sus impactos. Además, se destaca la ausencia del informe de Impacto Ambiental, que es obligatorio según el Código de Minería.
+El documento consensuado en asamblea argumenta que la extracción de litio en Argentina se ha convertido en un asunto de defensa de derechos humanos, ya que los recursos extraídos enriquecen a países del primer mundo mientras afectan negativamente a las comunidades locales y el medio ambiente. El litio contribuye al agravamiento de la crisis climática en curso.
+Una medida cautelar es un mecanismo de protección de la Comisión Interamericana de Derechos Humanos (CIDH), mediante la cual esta solicita a un Estado que proteja a una o más personas que estén en una situación grave y urgente de sufrir un daño irreparable. Actualmente la presentación MC-726-23 se encuentra en estudio desde el 11 de septiembre, esta es la etapa procesal de revisión, la cual finaliza con la decisión de la Comisión de requerir información al Estado, o rechazar la solicitud de medidas cautelares.
+En esta lucha por el acceso a la información y la protección de los derechos humanos, se denuncia la falta de conocimiento sobre la tierra de la provincia, donde se llevan a cabo proyectos de exploración de litio. La asamblea señala que estas áreas no son desiertos, como se ha argumentado, y que existen comunidades cercanas que son afectadas por las empresas extractivas.
+La Asamblea Constituyente de los Pueblos Riojanos ha tomado medidas legales para proteger los derechos humanos y exigir acceso a la información en relación a los proyectos de minería de litio y el acuerdo con Mekorot, mientras destaca la importancia de preservar el medio ambiente en el contexto de la crisis climática. Por un lado ha presentado ante la convención constituyente un documento elaborado colectivamente producto de varias asambleas que se fueron concretando en distintos puntos de la provincia y recolectando miles de firmas que adhieren a esta preocupación popular. Y por el otro con esta medida solicitando la intervención de organismos internacionales para que se respeten los tratados a los que la Argentina suscribe ante situaciones como esta.
+La reciente aparición de flamencos muertos en la Reserva Natural de la Laguna Brava reaviva los reclamos sobre la falta de información sobre el impacto mediambiental de la exploración de litio en la región, y a pesar de que este factor ha sido desechado como causa por el Secretario de Ambiente, Santiago Azulay, la falta de acceso a la información no contribuye a la tranquilidad de la población sobre el manejo responsable ante la posibilidad del desarrollo de este tipo de actividad en la región.</t>
+  </si>
+  <si>
     <t>El alimento debe ser parte del acuerdo nacional</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/610468-el-alimento-debe-ser-parte-del-acuerdo-nacional</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    El alimento debe ser parte del acuerdo nacional. Opinión. Como parte del campo popular sabemos diferenciar entre una propuesta con un contrato social inhumano, basado en el individualismo, el sálvese quien pueda y el mercado como regulador de las relacion. Como parte del campo popular sabemos diferenciar entre una propuesta con un contrato social inhumano, basado en el individualismo, el sálvese quien pueda y el mercado como regulador de las relaciones económicas. Frente a otro que pone en el centro la justicia social, la construcción desde el amor, la solidaridad y el estado como regulador de las desigualdades que atravesamos como sociedad. La crisis social y económica que vive la Argentina requiere un accionar colectivo, de la comunidad organizada, que está representado en el Estado, a pesar de sus falencias en muchas políticas públicas, en particular en términos de soberanía alimentaria.
+En estas elecciones hay dos modelos en disputa: uno de imposible discusión. El de Milei. Y otro, el de Massa, donde podremos continuar la batalla de hacer entender al alimento como un derecho para quienes producen y consumen.
+Hoy es Massa la única opción concreta para nuestro pueblo, más allá de la histórica ausencia de la discusión del modelo agroalimentario en todas las propuestas de campaña.
+[H3] El alimento como derecho
+Apenas asumió el actual gobierno, desde el sector de pequeños y medianos productores de alimento (que cubren el 60% de esta necesidad), presentamos nuestras propuestas en una articulación con diferentes organizaciones que hoy se nucléan en la Mesa Agroalimentaria Argentina, el campo que alimenta. Tuvimos la oportunidad de ser parte de la gestión del Mercado Central, implementando novedosas y exitosas políticas a nivel micro pero incapaces de incidir en políticas macroeconómicas, lo que derivó en mi renuncia.
+Con la marcha atrás de la expropiación de Vicentín y la posibilidad de la creación de una Empresa Pública de Alimentos (que además hubiera servido de control para la evasión fiscal en el sector agroexportador) comenzó un declive del actual gobierno de Alberto Fernández, que culminó con la contratación como asesor presidencial de Antonio Aracre, representante del agronegocio y con quién sostuve un debate televisivo acerca de si el alimento era una mercancía o un derecho.
+Reforzando el planteo histórico de nuestro sector, hay una falta de lectura en la dirigencia política de un modelo agrario que vea al campo no solo en función de la exportación y la acumulación de divisas, sino también desde su función primaria, urgente y necesaria, que es la producción de alimento para su posible acceso en la mesa de los argentinos y argentinas.
+Se trata de roles que pueden ser complementarios, pero en un modelo político y tecnológico de soberanía alimentaria.
+No es posible el desarrollo de una industria exportadora en un país donde el mito de la producción de alimento para 400 millones de personas se contradice con el aumento descontrolado de los precios de estos alimentos a nivel local y el hambre de buena parte de los argentinos y argentinas.
+[H3] Un camino abierto
+Los pequeños y medianos productores que hoy tienen su representación gremial en la Mesa Agroalimentaria Argentina han demostrado la capacidad, no solo de producir alimento sano y barato, sino también de agregarles valor y comercializarlos a través de miles de ferias, almacenes y mercados de cercanía que los acercan a los consumidores, generando un esquema federal y de trabajo digno, y sorteando la estructura claramente inflacionaria que produce la concentración económica y geográfica.
+Los índices del Centro de Estudios Scalabrini Ortiz (CESO) vienen demostrando la efectividad de la Economía Social, Solidaria y Popular a la hora de reducir los índices de inflación en comparación con las estructuras económicas concentradas. Desde la UTT también hemos avanzado en la articulación con municipios de la provincia de Buenos Aires en ese sentido. Esta estructura de menor inflación tiene que ver con los avances que desde las organizaciones se han implementado en términos de logística y articulación, pero también con entender el alimento como un derecho y no solo un negocio.
+Incluso la Mesa Agroalimentaria Nacional cuenta con organizaciones que exportan alimento, donde el sector cooperativo y de pymes del campo que alimenta han incrementado notablemente sus ventas al exterior. Profundizar este sistema virtuoso a través del Estado es de vital importancia a la hora de reducir los índices de inflación y generar trabajo digno con alimento sano y barato para las familias argentinas.
+[H3] Parte de un acuerdo nacional
+Entendemos que un gobierno de acuerdo nacional no puede dejar de lado las contradicciones primarias que hay en los distintos modelos de desarrollo económico, destacando que tanto el FMI como el agronegocio son contrarios directamente a la posibilidad de soberanía alimentaria, de bienestar y justicia social. Ya es hora que la dirigencia política entienda que la agenda del modelo agroalimentario es urgente y necesaria para poder dar transformaciones reales para el pueblo argentino.
+Frente al debate de las próximas elecciones, nosotros fomentamos un estado presente y activo, un modelo de inclusión, acuerdo nacional y justicia social.
+Desde la UTT y la Mesa Agroalimentaria Argentina venimos llevando adelante estas políticas en los territorios y ya hemos presentado al gobierno un Programa Agrario para el Alimento con una serie de medidas, muchas de las cuales ya son proyecto de ley.
+No debe plantearse ni entenderse como contradictorio la necesidad de recaudar dólares, escasos debido a la deuda ilegítima con el FMI y la sequía, con las acciones concretas para construir una agenda de soberanía alimentaria, en la que prime garantizar el acceso a los alimentos. Para esto deben desarrollarse políticas públicas activas, partiendo de lo ya construido, y sin miedo a ir por más.
+Porque frente a la necesidad, como siempre, el alimento es un derecho.
+*Coordinador Nacional de la Unión de Trabajadores de la Tierra (UTT) y referente de la Mesa Agroalimentaria Argentina.</t>
+  </si>
+  <si>
     <t>"El 2024 va a ser un año muy bueno para Argentina, gobierne quien gobierne", asegura Massa</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/2023/10/16/el-2024-va-a-ser-un-ano-muy-bueno-para-argentina-gobierne-quien-gobierne-asegura-massa/</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    "El 2024 va a ser un año muy bueno para Argentina, gobierne quien gobierne", asegura Massa. "El 2024 va a ser un año muy bueno para Argentina, gobierne quien gobierne", asegura Massa. . "El 2024 va a ser un año muy bueno gobierne quien gobierne. El año que viene vamos a exportar gas y petróleo. En segundo lugar, vamos a tener 18 mil millones más de ingresos por agronegocios. Y en tercer lugar, un gran crecimiento del sector mineral, que nos va a dar 40 mil millones de dólares más de crecimiento de reservas, que es lo que hace fuerte la moneda", explicó Massa.
+(c) 2025 Página 12</t>
+  </si>
+  <si>
     <t>Pese a los destratos, Patricia Bullrich vuelve a apostar por Mauricio Macri</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/597869-pese-a-los-destratos-patricia-bullrich-vuelve-a-apostar-por-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Pese a los destratos, Patricia Bullrich vuelve a apostar por Mauricio Macri. Ambos saldrán de gira juntos por primera vez desde las PASO. La recorrida de campaña incluirá paradas en Junín y Pergamino, fotos de unidad y discursos contra Sergio Massa por la inflación. La idea es no mostrar fisuras en una relación que quedó lesionada luego del coqueteo del expresidente con el libertario. También buscarán pasar la página del escándalo de los audios de Melconian. Luis Brandoni sumó su voz para el último spot.. Las localidades de Pergamino y Junín, corazón del agronegocio bonaerense, fueron los puntos en el mapa elegidos para que Mauricio Macri finalmente le ponga el cuerpo a la campaña de Patricia Bullrich. La recorrida, planificada para este viernes a bordo de la “Patoneta” –así fue bautizado el Motorhome proselitista de la candidata– tendrá el tono de un reencuentro, dado que no compartían una actividad juntos en el territorio desde antes de las PASO. En medio corrió mucha agua bajo el puente y hubo más de un cimbronazo público entre ambos, sobre todo cada vez que el expresidente le tiró flores a Javier Milei. La última vez, hace dos semanas desde Harvard, directamente dijo que se ocuparía de brindarle apoyo parlamentario al libertario en caso de que llegue a la Rosada, lo que desató la furia en el campamento bullrichista. Esa herida está lejos de sanar, mas allá de las apariencias. Con la actividad, Bullrich también planea dejar atrás la incómoda filtración de los audios de Carlos Melconián, su jefe de equipos económicos y potencial ministro de Economía. Por ahora no parece dispuesta a soltarle la mano. Incluso lo defendió diciendo que las grabaciones son “falsas” y que la voz de Melconian chantajeando sexualmente a una empleada fue fraguada por la inteligencia artificial.
+El reencuentro entre Macri y Bullrich no será el último antes de las generales del 22 de este mes. En agenda hay una nueva foto de unidad pautada en principio para el acto del cierre de campaña el próximo miércoles en Lanús, aunque a confirmarse. El expresidente ya dió muestras de dejarla plantada, como lo hizo en el debate presidencial, para el que solo estuvo en la previa. El cierre en el municipio que gobierna su candidato a gobernador, Néstor Grindetti, tiene como objetivo hacer pie en la provincia más importante del país, en la que deberá mejorar sus números de agosto si quiere contar con alguna chance de ingresar al balotaje. Macri no es precisamente el dirigente con mejor imagen en el conurbano, por eso el punto elegido para sumarse a la Patoneta fue varios kilómetros más adentro, en el sector provincial dedicado al agronegocio.
+Luego de las recorridas por Pergamino y Junín, ambos seguirán cada uno por su lado: la exministra tiene planeado en el sprint final visitar Mendoza, Córdoba y también CABA. Este jueves estuvo en Comodoro Rivadavia (Chubut) junto a Ignacio Torres. Macri, en tanto, saldrá a recolectar votos en otros distritos, con su propio itinerario. Esta semana estuvo en Vicente López, luego en Santa Fe y más tarde en Misiones. La idea es juntar todos los votos posibles para evitar un trágico tercer lugar en las generales para Juntos por el Cambio, que dejaría al espacio al borde de la ruptura.
+En esa línea, Bullrich no deja sector por ir a buscar: este jueves estuvo junto a referentes evangélicos. Visitó a las autoridades de la Alianza Cristiana de Iglesias Evangélicas de la República Argentina (Aciera), que están en contra del aborto legal, para compartir "sus proyectos respecto a medidas para afrontar la pobreza, como también el tema de la libertad religiosa, capellanías y el derecho a la vida", según el comunicado posterior de ese organismo religioso.
+[H2] Especulando con la inflación
+Junto a Macri, Bullrich hará hincapié en la crecida inflacionaria. Tuvo la mala suerte de que su referente económico estuvo envuelto en el escándalo de la filtración de los audios, así que deberá ser ella la que hable de economía. Este jueves lo hizo desde su cuenta de Twitter, luego de que el INDEC diera a conocer el número de inflación de septiembre. "Massa nos deja tierra arrasada con su incompetencia. La inflación mensual sigue subiendo. En septiembre fue de 12,7 % y ya acumula 138,3% en un año", dijo.
+"Nosotros tenemos un equipo sólido, un plan desarrollado por decenas de economistas y mayorías en el Congreso para ordenar la economía. Vamos por un país ordenado", remató.
+En la misma línea la siguió Mario Negri: "Por su ambición desmedida de poder tomó decisiones irresponsables que clavaron la inflación de septiembre en 12,7% y la anual en 138,3%. Repetimos al oficialismo: la inflación genera pobreza, no presidentes", le espetó a Massa.
+[H3] Brandoni, la voz del spot
+“Cuando Milei no estaba y Massa estaba con ellos, ella estaba con vos defendiéndote”, dice la voz en off del actor y militante cambiemita Luis Brandoni en el último spot de la candidata. “La fuerza es ella”, sigue y el montaje la muestra en distintas secuencias de su biografía política, como cuando se cruzaba con Hugo Moyano en los estudios de televisión durante su etapa como ministra de Trabajo de Fernando de La Rúa. El texto redunda en la idea de que, a diferencia de Milei, Bullrich tiene una estructura de gobernabilidad. El video tiene varios cambios más abajo que el último en el que propuso construir una cárcel de máxima seguridad con el nombre de Cristina Kirchner, lo que le valió una denuncia ante la justicia electoral por parte de organismos de Derechos Humanos de la Provincia de Santa Fe, que le piden retractarse por "la estigmatización del peronismo para justificar proscripciones, intentos de magnicidio y violaciones múltiples a los derechos humanos".</t>
+  </si>
+  <si>
     <t>Se fue la segunda y quedaron los ecos</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/596357-se-fue-la-segunda-y-quedaron-los-ecos</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Se fue la segunda y quedaron los ecos. . Y llegó el día, nomás, con ansiedades multiformes y un hombre, en Santa Fe, que como el rayo que no cesa ­–parafraseando al enorme poeta Miguel Hernández– renueva contra viento y marea sus denuncia. Y llegó el día, nomás, con ansiedades multiformes y un hombre, en Santa Fe, que como el rayo que no cesa ­–parafraseando al enorme poeta Miguel Hernández– renueva contra viento y marea sus denuncias de la proliferación de bandas narcos que actúan en cada uno de los 19 departamentos de esa provincia. Se llama Carlos del Frade y es diputado provincial y un patriota que con ejemplar tesón lleva años desnudando organizaciones delictivas y mafiosas en su provincia, donde según cómputos de medios de comunicación locales hoy es más que obvio que semejantes ejércitos malignos no podrían funcionar si hubiese políticas de prevención y sanción como sería de esperar en la tercera provincia argentina, con más de 3,5 millones de habitantes.
+Y provincia que de las grandes causas patrióticas de los últimos dos siglos pasó a ser asentamiento ­–Menem lo hizo– de las más grandes corporaciones de agronegocios, casi todas extranjeras. Y donde hoy anidan agroexportadoras que mueven miles de millones de dólares casi sin beneficios para el país. Pruebas al canto: sólo en la última semana hubo denuncias de un cargamento de 200 kilos de cocaína pura encontrados en el "Chemster", un buque que llegó a Australia procedente de uno de los puertos privados de San Lorenzo, al lado de Rosario. Y que parece ser nada más ni menos que otro caso escandaloso silenciado –o sea negado– continuando la "normalidad" de casi todos los gobiernos, tanto los de esa provincia litoraleña como del nacional. Porque de eso no se habla.
+Y es éste nada más que otro ejemplo de silenciamiento, como se ha venido constituyendo en norma de los poderes concentrados de esta república en la que la verdad es lo más negado y la sanata o sarasa –la mentira, vamos– es la norma principal y más poderosa de la politización forzada del pueblo argentino.
+Sólo así es explicable el sistema mentimediático que impone temas y asuntos de hartante frivolidad mientras los intereses ciudadanos y la democracia, la paz y el trabajo son abrumadora y canallescamente silenciados, negados o distorsionados para que la confusión impere, el descreimiento y el desaliento reluzcan y –consecuencia lógica– la democracia pase a ser a la vez farsa carnavalesca y perfecta promoción de desalientos.
+Así, las carencias argumentales –como se vio en los debates en la tele y están más cantadas que "Sólo le pido a Dios"– llevan a confusión y a crecientes abstenciones, voto-blanquismo y votos-rabia por causas –no razones– facilongas y oscuras como las que no se cansó de promover el candidato despeinado y gritón. Lo cierto es que la estupidez y la mentira también se enseñorearon en este segundo y último debate entre los cinco candidatos, con disimulitos leves, y en los que fue fenomenalmente engañosa la perorata –amenazante– de la señora Bullrich, quien en lugar de un ignoto compañero de fórmula podía haber elegido para secundarla –y sincerar más las cosas– al incalificable gobernador jujeño.
+Pero si algo se sabía al inicio del debate era que abundarían chicanas, mentiras, desmentidos y el descontrol de ese gritón sacado que la semana anterior se moderó de mentirita pero sin dejar de formar parte del dueto de bestias amenazantes. Como también se sabía de la vocación de violencia de la ex ministra que en el último gobierno radical rebajó los sueldos de medio país y que siempre fue incapaz de autocrítica y encima ahora pretendió dar cátedra de carcelera.
+Claro que también se sabía y quedó claro que la Sra.Bregman era la única diferente, porque guste o no tiene ideas y lenguaje claros. Y agradable por si faltara algo. Pero esa candidata es zurda, o sea de izquierda, troska, populista y contrera de alma y encima con firme discurso, por todo lo cual resultaría imbancable para las almas gorilas, y especialmente las porteñas.
+Entonces por ahí el gritón se descontrola y parece desequilibrado, en tanto machito que por eso mismo puede afanar en el voto joven, resentido y machirulo. Lo absurdo será que las mujeres lo voten, ahora que se logró igualdad de géneros como jamás antes, y cuando se garantiza el aborto seguro y todo lo que se hizo por la igualdad de géneros. No se puede creer que tantas mujeres argentinas y sobre todo jóvenes, voten a semejante tipo. Pero sí, hay que reconocer que sería otro más de los pistoletazos en la sien que en los últimos 50 años ha sabido darse esta nación.
+Y además estuvo ausente Malvinas, otra vez. Como también el Paraná, y el Canal Magdalena. Se habló de la unidad territorial. Y una vez más no existió la palabra "Soberanía" y todo fluyó como si el río estuviera maldito desde el maldito falsario de los 90 que no dijo lo que haría porque si lo decía no lo votaba nadie. O sea.
+Tampoco se habló de Derechos Humanos ni de que sí fueron 30.000 las víctimas de la dictadura. Ni se dijo que la dictadura fue eso: una dictadura, y feroz. Con lo que el negacionismo pareció reverdecer por momentos, y se les notó contrariedad a algunos, especialmente la nerviosísima Bullrich, quien parecía temer la presencia de su jefe lento, Mauricio Macri.
+Hubo también chicaneos con la desregulación de armas, y fue chocante que nadie defendiera a Raúl Zaffaroni, injusta y ridículamente atacado por Milei. Quien además mezcló economía con juridicidad y mintió con falsedades, como pareció costumbre de varios de los dialogantes. También se le chupó la media a la Justicia y se hablaron sarasas de leyes y códigos penales y Milei, claro, dijo respetar la ley de armas (sic) y negó que impulsa la venta de órganos, que sin embargo ha sido uno de sus argumentos de campaña. Y supo ser gelatinoso, como todos. A excepción de Massa por momentos, y de Bregman que fue clara y precisa en todos los órdenes y no se amilanó ante ningún tema.
+Pero lo que quedó en el aire fue que el peligro tiene ojos de loco. Este domingo quedó claro. El tipo se muestra como un cipayo perfecto, porque lo es. Un antipatriota, acaso agente de las internacionales que se relamen por quedarse con todo los bienes de nuestra Patria. El tipo parece un charlatán, y seguramente lo sea, antes que un hombre sensato. No debe haber leído ni El Principito ni el Martín Fierro, ni un poema de Borges o un cuento de Cortazar, apuesta este columnista. Y no podría sostener una conversación sensata –este columnista se descompone de sólo imaginarlo– si por ejemplo encima designa a la canciller que ya prometió que las Malvinas deben ser inglesas.
+Es un tipo que no escucha ni parece reflexionar (que es un acto que supone serenidad, modestia, análisis y buena fe). Todo eso se diría que falta en este tipo que ve claramente que además de machirulo parece violento, como se mostró cuando empezó su campaña a puros gritos y amenazas.
+Además, no ha dicho una sola idea completa en los dos debates: sólo enunciados furibundos. Contenido ahora, pero con ojos de loco a full. Y en general sin desarrollo, que se suma al hecho de que no se le conoce una sola idea propia. Y su vice ni se diga: es la mujer a la sombra, fenómeno típicamente machista.
+Y en fin, todos hicieron lo que pudieron y mejor que los analicen colegas más sabios, en los próximos días. Por ahora esta columna se confiesa alarmada por la Patria. Por el pueblo que quizás en dos semanas podría decidir suicidarse como democracia. Y si acaso sucediera, como augura la mayoría de las encuestas, ahora sí que al pueblo argentino no lo unirá el amor, sino el espanto.</t>
+  </si>
+  <si>
     <t>Brasil: la ultraderecha desafía a la Corte contra los indígenas y apunta a  homosexuales</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/592933-brasil-la-ultraderecha-desafia-a-la-corte-contra-los-indigen</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Brasil: la ultraderecha desafía a la Corte contra los indígenas y apunta a homosexuales. El Senado aprobó una ley que limita el reconocimiento de tierras indígenas. La agenda conservadora revivió con fuerza para responder a las últimas decisiones del máximo tribunal, que van a contramano del sector agropecuario y las iglesias evangélicas.. La ultraderecha brasileña exhibió su músculo parlamentario desafiando a la Corte Suprema con la aprobación de una ley que restringe los derechos de los pueblos originarios a la tierra, mientras avanza en un proyecto para prohibir el matrimonio homosexual. La agenda conservadora revivió con fuerza en pleno gobierno de Luiz Inácio Lula da Silva y es una suerte de respuesta a las últimas decisiones del máximo tribunal sobre temas espinosos que van a contramano del poderoso sector agropecuario y, sobre todo, de las influyentes iglesias evangélicas.
+[H2] Triunfo de la derecha y el lobby agrícola
+El primer paso de esta ofensiva parlamentaria, encabezada por el Partido Liberal (PL) del expresidente Jair Bolsonaro, fue la aprobación del llamado "marco temporal", que limita los derechos de los indígenas a las tierras que ocupaban al 5 de octubre de 1988, cuando fue promulgada la actual Constitución brasileña. El proyecto fue aprobado con urgencia por el pleno del Senado en un debate convocado una semana después de que la Corte rechazara esa tesis jurídica por nueve votos contra dos y consagrara el derecho de los indígenas a la tierra que han ocupado tradicionalmente.
+En las últimas semanas el tribunal también admitió a trámite sendas demandas que proponen descriminalizar el aborto hasta las 12 semanas y liberar, con límites, la marihuana para fines recreativos. "Atentan contra el campo y ahora quieren el aborto y las drogas", sostuvo el senador Jorge Seif, un exministro de Bolsonaro que es una de las voces de la ultraderecha en el Parlamento.
+Principal motor del PBI de Brasil, el agronegocio celebró la aprobación por 43 a 21 votos del marco temporal. La Confederación Brasileña de Agricultura y Ganadería, principal entidad ruralista, difundió una nota felicitando al Frente Parlamentario Agropecuario y al Senado por la medida. "La aprobación en el Congreso Nacional restablece la seguridad jurídica y trae pacificación social", destacó la entidad.
+El presidente del Senado, Rodrigo Pacheco, defendió la potestad del legislativo para decidir sobre el tema. "No hay ningún tipo de enfrentamiento con el tribunal supremo, es apenas una posición del Congreso, considerando que juzgamos que temas de esa naturaleza deben ser deliberados por el Congreso", dijo Pacheco.
+Una vez aprobado el marco temporal el proyecto queda en manos de Lula, cuya base parlamentaria ya anunció que el mandatario lo vetará. Eso sólo lo devolvería a las cámaras para una nueva deliberación, que puede desgastar más al gobierno en el Congreso.
+La Corte Suprema dispuso, el mismo miércoles en que se votó en el Congreso, que aquellos productores que hayan adquirido "de buena fe" tierras que tradicionalmente pertenecen a los indígenas tienen derecho a una indemnización por parte del Estado.
+La demarcación de tierras indígenas, una obligación del Estado según la Constitución, estuvo suspendida entre 2019 y 2022, durante la gestión del entonces presidente Jair Bolsonaro, y fue retomada este mismo año por el gobierno de Lula. Durante todo su mandato Bolsonaro justificó su negativa al reconocimiento de tierras indígenas con el argumento de que eso haría "inviable" un mayor desarrollo del sector agropecuario.
+Según datos oficiales los indígenas ocupan cerca del 14 por ciento del territorio nacional, representado por unas 500 áreas ya delimitadas, a las que se pueden sumar otras 200 que aún son analizadas por las instituciones del Estado.
+[H2] Homosexuales y aborto en la mira
+Esta misma semana, en protesta por las decisiones de la Corte Suprema, los conservadores se declararon en obstrucción en el Parlamento y ya impidieron varias votaciones. Aún así promovieron el debate sobre el marco temporal y otros proyectos opuestos al máximo tribunal y que afectan indirectamente a Lula, hasta ahora apoyado en el Parlamento en materia económica y tributaria pero no en la "agenda de valores y costumbres".
+Un proyecto que avanza propone terminar con el matrimonio entre personas del mismo sexo, consagrado en 2011 por el Supremo y sobre el cual el Parlamento nunca legisló. El texto tramita en una comisión de Diputados, con clara mayoría bolsonarista, y será votado dentro de diez días para luego pasar al pleno de la Cámara Baja.
+La derecha pretende convocar un plebiscito para consultar a la población sobre el aborto, algo que será decidido por las cámaras en las próximas semanas. También anunciaron una movilización nacional el 12 de octubre, cuando en Brasil se celebra el Día del Niño, preparando el terreno para una eventual campaña hacia ese plebiscito.
+Se trata de otra respuesta directa al máximo tribunal, que aceptó a trámite una demanda para descriminalizar el aborto hasta las 12 semanas, presentada por el oficialista Partido Socialismo y Libertad que tiene sólo 14 de los 513 diputados y ningún escaño en el Senado. Esos asuntos deberán tramitarse en el Legislativo, pero la agenda antiderechos le devolvió el oxígeno a un conservadurismo arrinconado desde enero, cuando activistas de ultraderecha asaltaron las sedes de los tres poderes de la nación en un intento de derrocar a Lula.
+El 45 por ciento de la población está de acuerdo con el aborto y un 52 por ciento lo rechaza, mientras que los restantes no saben o no tienen una posición definida, según un sondeo reciente de la consultora Datafolha. La encuesta nacional de aborto de 2021, financiada por el Fondo Nacional de Salud brasileño, mostró que una de cada siete mujeres tuvo un aborto al llegar a sus 40 años y el 43 por ciento de ellas debió ser hospitalizada para completar el procedimiento.</t>
+  </si>
+  <si>
     <t>Una Escuela Campesina para fomentar el arraigo en el pueblo de Palma Sola</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/591479-una-escuela-campesina-para-fomentar-el-arraigo-en-el-pueblo-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Una Escuela Campesina para fomentar el arraigo en el pueblo de Palma Sola. "Era un sueño que nosotros teníamos". Funciona en el predio de la organización Tierra Fértil, en el departamento Santa Bárbara, de Jujuy. Por ahora dictan cursos de producción bovina, conservas saladas y dulces y turismo rural.. El pequeño pueblo de Palma Sola, en la provincia de Jujuy, fue el escenario, el jueves 7 de septiembre, de la inauguración del Centro de Formación “Escuela Campesina”, una iniciativa de la organización Tierra Fértil, que reúne al campesinado que reside en los parajes de esa zona.
+El proyecto, un sueño del campesinado de Palma Sola, en palabras de Gloria Mamaní, se lleva a cabo en el marco del convenio entre el Instituto Nacional de Tecnología Agropecuaria (INTA) y el Ministerio de Trabajo, Empleo y Seguridad Social de la Nación, con la adhesión del Parque Nacional Calilegua y el Instituto Nacional de Agricultura Familiar, Campesina e Indígena.
+Gloria Mamaní, campesina y militante de Tierra Fértil dijo a Salta/12 que la escuela "es un sueño que nosotros teníamos" y el Ministerio de Trabajo les dió "una manito, una ayudita con el tema económico", con el que se financió la Escuela de donde chicas y chicos salen con un título de reconocimiento nacional "y puedan también conseguir un trabajo a futuro". Tres de los cursos previstos por ahora ya comenzaron, y la cursada irá desde septiembre a diciembre de 2023.
+"Todos los cursos van a ser referidos a la agricultura familiar, al valor agregado a la producción que hacen los pequeños productores de la agricultura familiar", informó Mamaní, quien destacó que en la zona hay mucha producción de bovinos y en agricultura se cultiva citrus preferentemente. Cada curso tiene un cupo máximo de veinte personas y se entrega un certificado oficial del Ministerio de Trabajo, Empleo y Seguridad Social. El requisito es ser mayor de 18 años. La Escuela funciona en el predio de la organización, donde también está la Casa Campesina.
+El financiamiento de la Nación permitirá cubrir gastos del equipo docente, comprar de insumos y solventar otras cuestiones vinculadas a la gestión. También posibilitó mejoras edilicias en la cocina y el baño de la Escuela.
+Se informó que la necesidad de contar con un Centro de Formación para el Trabajo surgió del diagnóstico participativo realizado desde la organización campesina junto a organismos del Estado nacional con trabajo territorial en la zona. En sus diferentes espacios participativos a los que asisten jóvenes surgió la necesidad de contar con herramientas de formación y capacitación que promuevan el arraigo, favorezcan la posibilidad de conseguir trabajo local con mejores ingresos y valoricen la producción campesina.
+De esta manera se busca mitigar la migración a espacios urbanos en búsqueda de trabajos de bajísima calidad y con pésimas remuneraciones. La oferta de cursos se propone constituirse en "una alternativa para evitar el actual éxodo rural que sufre la población especialmente la más joven causada por la inaccesibilidad hacia el sistema educativo, la falta de capacidades para acceder al mercado laboral local y la falta de equipamiento e infraestructura básica para la población rural".
+También se propone "proyectar y fortalecer nuevas propuestas para el trabajo local que contrapese la marcada estacionalidad de los empleos en la zona". Crear empleo local revalorizando saberes y posibilidades, y "brindar propuestas laborales alternativas fortaleciendo oficios tradicionales e incorporando nuevos oficios".
+En la Escuela Campesina se dictan cursos gratuitos de Auxiliar en producción animal, Gestión del turismo rural comunitario, Auxiliar en preparación de conservas de frutas y hortalizas, y a futuro, ya para marzo de 2024, se prevé dictar los cursos de Auxiliar en comercialización de la producción campesina y Gestión de medios y redes sociales.
+El INTA, el Parque Nacional Calilegua y Agricultura Familiar acompañarán en la gestión y con el aporte de docentes para los cursos propuestos.
+Palma sola está ubicada a 160 kilómetros de San Salvador de Jujuy, en el cordón montañoso de Santa Bárbara, en la zona de transición entre la zona chaqueña y la selva de Yunga. El pueblo sufre un grave proceso de desarraigo debido a que no existen propuestas formativas luego de terminar el ciclo secundario. La mayoría de las y los jóvenes que se va a estudiar a las ciudades no regresa, y quienes se quedan realizan trabajos precarios haciendo changas.
+[H2] ​Organización frente a la presión
+Gloria Mamaní, que además de integrante de Tierra Fértil es coordinadora en la zona del Instituto Nacional de Agricultura Familiar, contó a Salta/12 que comenzaron a organizarse en 2006 "cuando empezó a pecharnos fuerte el agronegocio con el tema de la soja, la caña, y a hacernos muchos desmontes y a querer desalojar a familias campesinas". En 2008 se conformó Tierra Fértil. La organización tiene una demanda en la que empresarios de la zona la "acusan de usurpar la tierra y darla a la gente".
+Mamaní destacó que el gobierno nacional ya reconoció la posesión del campesinado en la zona, a través de la Ley nacional de reparación histórica de la agricultura familiar. Y en Palma Sola la organización consiguió además que se declare por ordenanza municipal "área campesina" a todos los parajes, con la salvedad del ejido urbano. En el marco de esa ordenza se hizo un relevamiento del campesinado. Después de ese relevamiento recibieron una demanda del gobierno de Jujuy, "y ahora estos empresarios se agarran de esa demanda" para demandar a la organización, afirmó Gloria Mamaní, es lo que pasa, dijo, con un empresario de apellido Quintana, que trata de desalojar a la familia Centeno, en el paraje Las Goteras, a 55 kilómetros de Palma Sola.
+Sobre la Escuela Campesina, Mamaní destacó que hubo mucho interés y de hecho, "quedó mucha demanda del curso de producción bovina", por lo que el año que viene se dictará nuevamente. "De ahora a diciembre ya no tenemos cupo", dijo Mamaní, pero añadió que proyectan que en marzo de 2024 abrirán las inscripciones para dictar nuevamente los cursos de producción bovina y de turismo rural.
+Y adelantó que también piensan dictar cursos de contabilidad, "referida a la producción, que el productor que está metido en el campo aprenda a sacar cálculos, para, por ejemplo, poner en venta una vaca, saber si le conviene el porcentaje, el flete cuánto le sale, o un cabrito, un lechón".
+En Palma Sola "casi toda la gente vive en los parajes", el pueblo en sí mismo "es chiquitito", tiene entre 6 y 7 mil habitantes, y viene disminuyendo debido al desarraigo. Mamaní destacó que "la mayoría de los habitantes vive a 30 kilómetros, 15, a 50 kilómetros".
+Estas personas se dedican a la ganadería y también a la agricultura, con citrus y floricultura. También crían animales de granja, cabras, lechones y gallinas. "El año pasado con el tema de la sequía fue muy difícil, muy complicado, porque secó mucho la plantación no solamente las hortalizas, sino también el citrus, era como si le hubieran prendido fuego", eran plantaciones de diez años y muchos productores que "quedaron sin nada", contó Mamaní.
+El campesinado vive en parcelas en calidad de poseedores, algunas son tierras fiscales y otras tienen titulares registrales que no residen ahí. Mamaní explicó que en el caso de quienes se dedican a la agricultura, tienen tres o cuatro hectáreas, mientras que los ganaderos "tienen un poquito más, 100, 200 hectáreas.
+La producción se vende los mercados de Perico y Monterrico, ciudades de Jujuy, y de San Ramón de la Nueva Orán, en la provincia de Salta.</t>
+  </si>
+  <si>
     <t>Uno de los inviernos más calurosos de la historia en la región</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/590365-uno-de-los-inviernos-mas-calurosos-de-la-historia-en-la-regi</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Uno de los inviernos más calurosos de la historia en la región. Olas de calor en Argentina, Uruguay y Chile, y lluvias torrenciales en Brasil, que provocaron casi medio centenar de muertes. Temperaturas muy altas marcaron el invierno austral de este año en toda la región del Cono Sur latinoamericano, donde además del cambio climático, el fenómeno de El Niño hizo que los termómetros ro. Temperaturas muy altas marcaron el invierno austral de este año en toda la región del Cono Sur latinoamericano, donde además del cambio climático, el fenómeno de El Niño hizo que los termómetros rozaran los 30ºC en Buenos Aires, y provocó intensas lluvias en Chile o ciclones en el sur de Brasil.
+En pleno agosto, se vivieron olas de calor en Argentina, Uruguay y Chile. En localidades como Tartagal, Salta, la temperatura alcanzó los 40,2ºC, mientras en Vicuña, al pie de la cordillera del lado chileno, a la altura de La Rioja, y a unos 450 km al norte de Santiago, se elevó a 37ºC, la más alta en 70 años.
+Pero también hubo lluvias torrenciales en Chile, las mayores en 30 años, que dejaron inundaciones, seis muertos y un superávit en zonas afectadas por una sequía de 13 años, como el centro del país, rico en producción agrícola.
+En Muçum y otras ciudades del estado Rio Grande do Sul, en Brasil, un ciclón provocó grandes inundaciones y deslaves que dejaron 46 muertos a inicios de septiembre. El río Taquari se desbordó, lo que golpeó zonas elevadas y apartadas de su cauce. En esta región de Brasil fronteriza con Uruguay, este invierno hubo granizos, vientos fuertes y tempestades. Más de 147.000 personas fueron afectadas en todo el estado brasileño.
+Expertos prevén que estos eventos extremos comiencen a ser habituales, producto del cambio climático que agrava los efectos de fenómenos meteorológicos como El Niño y La Niña.
+"Lo más probable es que ya no tengamos más escenarios con lluvias bien distribuidas y temperaturas amenas en los próximos años", dijo a la AFP Pedro Côrtes, profesor del instituto de Energía y Ambiente de la Universidad de Sao Paulo.
+[H2] Olas de calor y baja humedad
+En julio, los termómetros en el centro y norte de Argentina se elevaron con valores de hasta 6ºC y 7°C por encima del promedio, mientras en Santiago de Chile el promedio de temperaturas máximas para el trimestre junio-agosto fue de 17,3ºC, el cuarto más alto desde 1960.
+Brasil vivió el mes de julio más caluroso desde 1961. La temperatura promedio fue un grado más alta respecto del período 1991-2020, de acuerdo al Instituto Nacional de Meteorología de Brasil (Inmet).
+Las regiones que más experimentaron el aumento de temperatura fueron el sur de la Amazonia, el centro-oeste del país -corazón del agronegocio-, y la región sur.
+"Este incremento de las temperaturas podría deberse a una sequedad de la atmósfera. No es el cambio climático el único responsable", explica el meteorólogo de la Dirección Meteorológica de Chile.
+En Uruguay el invierno "se caracterizó por un déficit en las precipitaciones muy marcado (...) y por temperaturas elevadas" en comparación con los últimos 30 años, dijo la meteoróloga Madeleine Renom, profesora de la Universidad de La República.
+[H2] Efectos en la agricultura
+La sequía venía golpeando las economías de varios países de la región. En Argentina, el gobierno estimó las pérdidas para este año a causa de la falta de agua en 20.000 millones de dólares, casi el 3% del PIB.
+La sequía, que desde hace tres años afecta a la cuenca del Río de la Plata, impactó también en el suministro de agua potable en el suroeste de Uruguay y en el agro.
+En el segundo trimestre del año el PIB uruguayo cayó 2,5% interanual, arrastrado por el impacto de las menores lluvias en la actividad agropecuaria y en el sector de la energía eléctrica, gas y agua.
+"La cantidad de agua que cae anualmente es parecida pero ahora son lluvias muy fuertes en poco tiempo, causando destrucciones en áreas agrícolas y de infraestructura urbana", explica Adolfo Pria, profesor de la Universidad Nacional de Brasil en el área de agricultura y medio ambiente.
+Pria destaca que la concentración de lluvias con vientos fuertes presenta un riesgo para plantaciones expuestas a una erosión agresiva del suelo, como la soja y el maíz, de las que Brasil es el primer y segundo productor mundial, respectivamente.
+"Todos los productores se han jugado en sus siembras a las precipitaciones que traiga consigo El Niño desde septiembre y consideran que existe un gran potencial para una excelente cosecha 'gruesa' (soja, maíz, girasol) para 2024", dijo el meteorólogo Mauricio Saldivar, de la organización Meteored.</t>
+  </si>
+  <si>
     <t>36% de la tierra productiva está en manos del 1% más rico</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/585926-36-de-la-tierra-productiva-esta-en-manos-del-1-mas-rico</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    36% de la tierra productiva está en manos del 1% más rico. LA CIFRA. El 36 por ciento de la tierra productiva en la Argentina rural está en manos del 1% más rico de los propietarios de tierra. Según los censos nacionales agropecuarios del Indec -de 1988, 2002. El 36 por ciento de la tierra productiva en la Argentina rural está en manos del 1% más rico de los propietarios de tierra. Según los censos nacionales agropecuarios del Indec -de 1988, 2002, 2008, 2018-, entre 1988 y 2018 desaparecieron más de 156 mil establecimientos agropecuarios, en su gran mayoría pequeñxs y medianxs productorxs de alimentos, y se duplicó la concentración de la tierra en cada vez menos dueños: los dueños de la tierra. Los efectos de este despojo coinciden con el arrase y cercamiento de los extractivismos sobre territorios indígenas, campesinos e incluso de productorxs chacarerxs, “que pierden sus espacios de producción y de vida, acrecentando el éxodo rural hacia las grandes ciudades y destruyendo diversas formas de vida y culturas rurales”.
+El informe de Juan Wahren, investigador del Conicet y del Grupo de Estudios Rurales (GER-Gemsal) del Instituto Gino Germani, que publica la Agencia de noticias TierraViva, confirma que el período 1988-2018 coincide, “no casualmente, con el surgimiento y consolidación del modelo de agronegocios a escala nacional y global, cuyo cultivo estrella en la Argentina es la soja transgénica (al que acompañan el maíz, trigo, arroz y otros cultivos modificados genéticamente). Y también con el avance exponencial de otras actividades extractivas como los hidrocarburos, la megaminería y los emprendimientos forestales”.
+Wahren subraya que al mismo tiempo, en la Argentina urbana “se incrementaron exponencialmente los procesos de gentrificación y especulación inmobiliaria en las grandes ciudades, en un proceso de tal magnitud que se lo ha caracterizado como una forma de extractivismo urbano”. Esas actividades impactan directamente sobre las zonas rurales-urbanas y humedales, bosques nativos, salares y otros ecosistemas que sufren enormes transformaciones “y que provocan, entre otras cosas, un aumento de las inundaciones, incendios y una creciente contaminación de las fuentes de agua (ríos, lagos, acuíferos, etcétera)”.
+Capítulo aparte para las afecciones que generan a la salud humana, por el uso masivo de agrotóxicos para las fumigaciones de los cultivos transgénicos y químicos peligrosos, que se utilizan en la actividad de la megaminería y el “fracking” de los hidrocarburos no convencionales. Las consecuencias del extractivismo se extienden además hacia los territorios urbanos, remarca el investigador, “donde miles de personas viven hacinadas en villas y asentamientos populares como si fueran ´guetos´, sin acceso real a las ciudades, a sus infraestructuras (plazas, escuelas, hospitales, calles) o a sus servicios básicos (agua, cloacas, electricidad, gas); mientras proliferan barrios privados y ´countries´ que profundizan la segregación espacial en las grandes urbes y sus suburbios”.
+Frente a estos avances territoriales, organizaciones campesinas, pueblos indígenas, asambleas de vecinos y vecinas de pueblos rurales, agrupaciones ambientalistas, artistas y académicxs del Conicet impulsan un ciclo de Asambleas Públicas performativas en la Manzana de las Luces, para debatir sobre los elementos principales de la Naturaleza, Tierra, Fuego y Agua. “Será una puesta en escena del arte de la política. De la política de los territorios. De la política de las calles. De la política de los barrios. De la política que emana de los poros de los cuerpos despojados -concluye Wahren-. De la política que no delibera en espacios obturados a la voluntad colectiva, sino que los abre e invita a pensarlo todo, a debatirlo todo, a cambiarlo todo.”
+Más información: manzanadelasluces.cultura.gob.ar</t>
+  </si>
+  <si>
     <t>Lula creó dos nuevas reservas indígenas en la región amazónica</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/585474-lula-creo-dos-nuevas-reservas-indigenas-en-la-region-amazoni</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Lula creó dos nuevas reservas indígenas en la región amazónica. Luego de que Bolsonaro anulara la concesión de territorios ancestrales para los pueblos originarios. El presidente de Brasil, Luiz Inácio Lula da Silva, creó por decreto dos nuevas reservas indígenas en la región amazónica, a la vez que destacó la unidad de los países amazónicos, africanos. El presidente de Brasil, Luiz Inácio Lula da Silva, creó por decreto dos nuevas reservas indígenas en la región amazónica, a la vez que destacó la unidad de los países amazónicos, africanos y asiáticos para reclamar compensaciones financieras a las naciones ricas por preservar la selva. Su política ambiental, dijo, tiene como meta la deforestación cero en 2030.
+Con la decisión, ya son ocho las reservas oficializadas desde el inicio de su mandato el 1° de enero, luego de que su antecesor, Jair Bolsonaro, anulara las políticas de concesión de territorios ancestrales a los pueblos originarios, un añejo reclamo del agronegocio.
+Los dos nuevos territorios son Rio Gregório, en el estado de Acre, y Acapuri de Cima, en Amazonas, donde viven los pueblos originarios Katukina Pano, Yawanawá y Kokama, con una población estimada en alrededor de 1.000 personas, que conviven bajo amenaza de la minería ilegal y los ocupantes ilegales de tierras para cría de ganado y explotación maderera.
+La aprobación de las nuevas demarcaciones fue realizada por Lula en una ceremonia en el Palacio del Planalto en celebración del Día de la Amazonia.
+[H2] Crimen organizado y mafias
+El mandatario dijo al lado de las ministras de Ambiente y Cambio Climático, Marina Silva, y de Pueblos Indígenas, Sonia Guajajara, que durante su gestión la Policía Federal y las Fuerzas Armadas trabajarán en el control fronterizo y en el combate a las mafias que operan en la selva amazónica, de la cual Brasil tiene 60%.
+"No podemos permitir que la Amazonia sea escenario del crimen organizado en este país; vamos a combatir todo tipo de ilegalidad en este país para que la gente de la Amazonia pueda vivir feliz”, afirmó el presidente.
+Lula aseguró que "es necesario que las naciones ricas financien la preservación del bosque tropical en pie", al recordar que desde 2009 que los países desarrollados prometen sin cumplir aportes para que los países con selvas tropicales puedan mantener sus biomas.
+En ese sentido, aseguró que en los foros internacionales Brasil llegará con un discurso unido al lado de los países amazónicos y de otras tres naciones con las mayores selvas tropicales, como República del Congo, República Democrática del Congo e Indonesia.</t>
+  </si>
+  <si>
     <t>Se reabre la mesa de negociación UE-Mercosur</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/584886-se-reabre-la-mesa-de-negociacion-ue-mercosur</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Se reabre la mesa de negociación UE-Mercosur. El 15 de septiembre habrá una nueva reunión en Brasilia. Las nuevas restricciones en materia ambiental que tiene en carpeta la Unión Europea encendió alarmas en los países del bloque sudamericano.. Representantes de la Unión Europea y del Mercosur se reunirán el próximo 15 de septiembre en Brasilia para continuar las negociaciones sobre el acuerdo de libre comercio. Así lo afirmó el ministro brasileño de Asuntos Exteriores, Mauro Vieira, quien reiteró la posición del Mercosur de que “la salvaguarda del medio ambiente que propone la UE no se convierta en un pretexto para aplicar medidas proteccionistas”.
+A pesar de que se trata de un tema que viene con amagues desde hace dos décadas, Vieira se mostró “optimista” sobre el curso de las negociaciones y dijo que se sigue apuntando a cerrar el acuerdo antes de fin de año. “Los demás países del Mercosur tienen la misma posición. Ya hablé con los cancilleres de Uruguay (Francisco Bustillo Bonasso), Argentina (Santiago Cafiero) y Paraguay (Rubén Ramírez Lezcano)”, precisó.
+[H2] Diferencias
+En el último tiempo surgió una nueva diferencia entre los bloques, que ahora está en el centro de la mesa de negociación. Se trata de las normas contra la deforestación que busca aplicar la UE y que tendrían un impacto negativo sobre las exportaciones sudamericanas hacia el Viejo Continente, particularmente sobre las ventas de Brasil.
+Ante ello, la Federación de Asociaciones Rurales del Mercosur emitió un comunicado en donde manifiesta su "preocupación por las medidas unilaterales de la UE". Otros importantes damnificados en el concierto global de los socios comerciales de la UE serían Honduras, Indonesia y Malasia, que son los mayores proveedores de café, aceite de palma, y caucho del continente.
+En esa línea, el mes que viene la Unión Europea (UE) comenzará a poner en vigencia su Mecanismo de Ajuste en Frontera por Carbono (CBAM, por sus siglas en inglés). Se trata de una herramienta de carácter ambiental que tendrá en los hechos un impacto proteccionista sobre las importaciones que realiza esa región, especialmente en el caso de los orígenes de países en desarrollo. La implementación de este mecanismo, de todos modos, será paulatina, de acá a comienzos de 2026.
+La idea del "Mecanismo" es castigar las importaciones de bienes que contienen una carga de emisiones de carbono que supera las exigencias que tienen las empresas que operan en territorio europeo. Así, los primeros perjudicados serían los exportadores de los países emergentes.
+[H2] Impacto
+Al margen del tema ambiental, un puntilloso informe elaborado por los especialistas Luciana Ghiotto y Javier Echaide, advierte que "el Mercosur y la UE tienen innegables asimetrías económicas. Este acuerdo mantendrá y profundizará las asimetrías existentes. El aumento en la exportación de productos agrícolas hacia la UE conducirá a una profundización del modelo de agronegocios, mientras que los países del Mercosur podrían sufrir una mayor desindustrialización y la exacerbación de las consecuencias ambientales y sociales negativas, que se derivan de la profundización de la producción basada en monocultivos y explotación de minerales".
+Además, sostienen que "el acuerdo tendrá un impacto directo en sectores productivos que hoy generan una importante cantidad de empleo, especialmente en los sectores de autopartes, maquinarias, químicos, textiles y calzado". Concluyen que "los grandes ganadores de este acuerdo son las grandes corporaciones europeas. Estas son económicamente más fuertes y están mejor posicionadas que sus contrapartes del Mercosur".
+De acuerdo a un informe de la consultora LLYC, Portugal sería unos de los países más beneficiados por el acuerdo comercial. Ese documento detalla que "las exportaciones portuguesas a Brasil han disminuido en los últimos años, por lo que el acuerdo podría conllevar un nuevo incremento que revierta el estado actual de la balanza comercial entre los países, actualmente desfavorable para Portugal". Asimismo, el país luso oportunidades para mejorar la inserción de su producción de vino en Brasil y de automóviles.
+Por otro lado, el informe destaca oportunidades para el sector autopartista de Brasil y Argentina, ya que la UE importa piezas por 63 mil millones de dólares anuales. También habría potencial de mercado en empresas del sector químico, textil, calzado, productos de higiene y limpieza, lácteos, carne vacuna y aves, fruta y verduras y cereales.</t>
+  </si>
+  <si>
     <t>Carta abierta a los jueces de la Corte Suprema</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/583983-carta-abierta-a-los-jueces-de-la-corte-suprema</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Carta abierta a los jueces de la Corte Suprema. . A los Ministros de la Corte Suprema de Justicia de la NaciónHoracio Rosatti - Carlos Fernando RosenkrantzJuan Carlos Maqueda - Ricardo Lorenzetti. A los Ministros de la Corte Suprema de Justicia de la Nación
+Horacio Rosatti - Carlos Fernando Rosenkrantz
+Juan Carlos Maqueda - Ricardo Lorenzetti
+Reciban el saludo de Paz y Bien.
+Esta es una carta abierta, ante la imposibilidad de llegar a ustedes personalmente, dado que hasta ahora se han negado a escuchar y recibir a los pueblos originarios que viajaron 1.500 Km. desde la provincia de Jujuy a la Capital Federal con la esperanza de ser recibidos por la Corte Suprema para presentar su rechazo a la Reforma Parcial de la Constitución votada en la Provincia de Jujuy que transgrede y no respeta la Constitución Nacional, violando el Convenio 169 de la OIT sobre Pueblos Indígenas y Tribales en países independientes y la Declaración Universal de los Derechos de los Pueblos Indígenas promulgado por las Naciones Unidas.
+El proceso de reforma también incumplió las normativas existentes para asegurar el acceso a la información y participación ciudadana en materia ambiental en temas sensibles como la regulación del agua y las tierras. Se incumplieron los principios de consulta a la comunidad previstos en el Acuerdo de Escazú, firmado por nuestro país y de jerarquía normativa superior a las normas provinciales.
+La convocatoria de la Constituyente en Jujuy, estuvo afectada por diversas irregularidades de procedimiento, entre estas cabe destacar las licencias alternadas del gobernador de la Provincia, para ejercer a la vez como presidente de la Constituyente, que no dejaran expresar sus opiniones de muchas organizaciones sociales que manifestaron su interés para participar. Pese a que el plazo para debatir la reforma era de 90 días, adrede se evitó el debate y en menos de tres semanas se aprobó en forma exprés, una constitución que transgrede la Constitución Nacional.
+Fueron las movilizaciones de cientos de comunidades de pueblos indígenas quienes cuestionaron esta reforma, gravitaron para que se eliminaran algunos artículos cuestionados ya votados que no pasaron el trámite de ser nuevamente votados por la convención constituyente. El punto es que el gobernador, a su vez presidente de la constituyente terminó de imponer una reforma sin consulta alguna con el pueblo, violando sus derechos y cuando aparecieron los reclamos populares contrarios a la reforma respondió con la represión policial y la persecución a docentes y comunidades indígenas.
+El Gobierno de Morales no sólo ha reprimido violentamente protestas sociales pacíficas, habilitó métodos de la última dictadura militar, persecución ideológica a quienes disienten como es el caso de la acusación por sedición del Dr. Hallar por cuestionar la reforma constitucional, se han dado detenciones arbitrarias, allanamientos domiciliarios sin orden judicial, represión parapolicial y grupos de tareas civiles, operando con camionetas sin patentes, las fuerzas policiales han disparado adrede a los ojos de manifestantes, la justicia controlada por el Poder Ejecutivo provincial desestima toda investigación sobre los hechos represivos, convalida causas con acusaciones fraguadas y aplica masivamente contravenciones altamente onerosas para amedrentar a quienes osen manifestar por sus derechos.
+La nueva Constitución habilita la criminalización de la protesta social, artículos ambiguos permiten tipificar como sedición reclamos que se expresen en defensa del pueblo. La penalización del derecho a la protesta, contraviene el Sistema Interamericano de Derechos Humanos.
+Con relación a los pueblos indígenas no se respetaron los protocolos previstos en el Convenio 169 de la OIT, que establece que debe garantizarse la consulta libre, previa e informada a pueblos indígenas sobre cuestiones susceptibles de afectarlos.
+En el Artículo 7 el Convenio dispone que los pueblos indígenas deberán “participar en la formulación, aplicación y evaluación de los planes y programas de desarrollo nacional y regional susceptibles de afectarles directamente.”
+En todos los casos los pueblos indígenas deben poder decidir sobre la utilización, administración y conservación de los Bienes Comunes. Para lo cual deben asegurarse la información previa oportuna y suficiente para fortalecer las capacidades de los pueblos originarios en su interlocución con las diversas reparticiones estatales. Las consultas deben realizarse de buena fe, el objetivo de esos procesos es tratar de alcanzar acuerdos, basados en el respeto mutuo. No puede considerarse una consulta realizar una reunión meramente informativa para escuchar algunas preguntas, pero sin que las comunidades puedan tener posibilidades de intervenir en las decisiones que se adopten. Aún en el caso que no se arribe a un acuerdo, el Estado debe respetar los derechos originarios reconocidos por el Convenio. La política pública no puede propasarse y terminar imponiendo su voluntad cuando encuentre oposición a sus contenidos y/o implementación.
+La Convención Constituyente votada para reformar la constitución provincial, incumplió este tratado internacional que tiene rango constitucional.
+En diversas Constituciones Provinciales, se han reconocidos derechos más amplios que los contemplados en la Carta Magna Nacional. No sólo se reconoce la preexistencia de los pueblos indígenas, su identidad étnica y cultural, su personería jurídica, sino también la propiedad comunitaria de la tierra que ocupan y las que puedan asignárseles como reparación histórica en forma gratuita y exentas de todo gravamen. Tales tierras son inembargables, imprescriptibles, indivisibles e intransferibles a terceros. Estos criterios debieran haber sido objeto del diálogo en la Convención Constituyente jujeña, sin embargo, la reforma aprobada legaliza a nivel constitucional que el Poder Ejecutivo Provincial, pueda disponer de las tierras de los pueblos originarios haciéndolas pasar por fiscales y poder así expandir el extractivismo minero, los agronegocios y los intereses inmobiliarios para las minorías privilegiadas.
+Frente a esa situación de indefensión y violencia El Malón por la Paz viajo a Buenos Aires solicitando ser recibidos por los integrantes de la Corte Suprema, sin resultado alguno hasta el momento.
+Lamentamos el silencio y la discriminación de la Corte Suprema que se niega a escucharlos, sabiendo que los indígenas están en Plaza Lavalle desde hace una semana a la intemperie y con necesidades básicas y de higiene, en particular mujeres y niños.
+El Jefe de Gobierno de la Ciudad, compañero de fórmula presidencial con el gobernador Morales también ha mantenido una actitud represiva y de maltrato a los hermanos indígenas impidiendo instalar una carpa lo cual pone en evidencia su racismo y la intolerancia violando los derechos humanos de las comunidades quienes soportan hambre, frío esperando que los miembros de la Corte Suprema los escuchen.
+Señores Ministros les pregunto: ¿qué piensan hacer frente a esta grave situación que viven los pueblos originarios en Jujuy? ¡Qué piensan hacer frente a las graves violaciones de los DDHH y al derecho que tienen los pueblos a sus territorios, agua y recursos naturales que les quiere sacar la gobernación de Jujuy?
+La Corte Suprema intervino con celeridad en vísperas de elecciones provinciales prontas a realizarse, para vetar las candidaturas de gobernadores oficialistas, en función de “desalentar la posibilidad de perpetuación en el poder”. Esta intervención se dio a partir de cautelares presentadas por fuerzas de la oposición y la CSJ entendió que la vulneración del principio de la alternancia tornaba ineludible la intervención de la Corte.
+Como es posible qué frente a la reforma de la Constitución Jujeña, donde hay presentadas cautelares, la CSJ no haya intervenido con la misma celeridad, ante un caso mucho más grave que es una constituyente con vocación secesionista que vulnera la unión nacional, altera el equilibrio de poderes y contrapesos republicanos habilitando una alta concentración del poder en el Ejecutivo provincial y contraviene la Constitución Nacional y los Tratados Internacionales.
+Los pueblos indígenas están aquí para reclamar sus derechos, evitar la violencia y la discriminación, racismo e intolerancia y ustedes tienen la obligación de escucharlos y protegerlos en sus derechos.
+Espero que escuchen el clamor de los pueblos y actúen con verdad y justicia. A cuarenta años del retorno a la democracia, honren el Nunca Más que supimos conseguir.
+Les reitero el saludo de Paz y Bien que tanto necesita nuestro país y el mundo.
+Adolfo Pérez Esquivel
+Premio Nobel de la Paz
+Presidente del Servicio Paz y Justicia</t>
+  </si>
+  <si>
     <t>Javier Milei, a lo Donald Trump: no quiere hacer negocios con China</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/579834-javier-milei-a-lo-donald-trump-no-quiere-hacer-negocios-con-</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Javier Milei, a lo Donald Trump: no quiere hacer negocios con China. El diputado ultraderechista prefiere volver a las relaciones carnales con EE.UU.. Pese a que China es el segundo socio comercial de la Argentina en materia de exportación y el primero en importaciones, el candidato más votado de las PASO expresa que no se deberían hacer negocios con el gigante asiático. "No negocio mi moral a cambio de dinero", dijo, en una entrevista, el exasesor de Ricardo Bussi, condenado por el terrorismo de Estado.. El candidato de la Libertad Avanza Javier Milei confirmó en la ronda de entrevistas que dio tras su victoria en las PASO que romperá relaciones comerciales con China en caso de llegar a la Casa Rosada. Milei aseguró que él no realizaría "transacciones con comunistas" ya en 2021, cuando aún no había sido electo como diputado, pero ahora con las posibilidades de ingresar a un balotaje presidencial sostener esa posición parece una amenaza para la macroeconomía del país.
+China es el segundo socio comercial de la Argentina en materia de exportación el 9,1 por ciento del total, detrás de Brasil 14,3 por ciento principal socio del país. En materia de importaciones, Argentina demanda el 21,5 por ciento de sus compras al gigante asiático, seguido por Brasil con el 19,7 por ciento.
+Lo que Milei repitió esta semana en las entrevistas que lo tuvieron como la sorpresa de las PASO ya lo dijo en octubre de 2021, cuando en una entrevista al Canal de la Ciudad, respondió: "Yo no haría negocios con China". Ante la consulta de lo que implicaría para la macroeconómica del país, el entonces economista mediático sostuvo: "Es falso que sería una transacción macroeconómica, podríamos hacer transacciones con el lado civilizado de la vida, Occidente. Yo no hago transacciones con comunistas. No negocio mi moral a cambio de dinero". Milei fue asesor de Ricardo Bussi, condenado por el terrorismo de Estado en la última dictadura militar argentina.
+El lineamiento planteado por Milei es con Estados Unidos a nivel comercial y diplomático. El país del norte se ubica en el tercer lugar en materia de exportaciones de Argentina con 7,5 por ciento, y en la misma ubicación en materia de importaciones con 12,7 por ciento. En tanto, la Unión Europea es el destino del 12,3 por ciento de las exportaciones del país.
+Cortar la relación con China parece contraponerse con la promesa de Milei a los sectores del agronegocio, ya que quitar el mercado chino del mapa significaría borrar al principal socio comercial en materia de exportaciones agropecuarias. La novela entre el gobierno de Mauricio Macri y el de su aliado Donald Trump por la exportación de limones, marca un ejemplo de la falta de complementariedad del mercado agropecuaria argentino con el norteamericano, en el que son competidores.
+Romper relaciones con China implicaría un impacto a otros niveles. Recientemente, Argentina utilizó el swap con el gigante asiático para pagar su deuda con el FMI, lo que le permitió cumplir con los compromisos del organismo en el que China también tiene un lugar importante. Además, la relación de inversiones chinas en el país crecieron exponencialmente desde el acuerdo firmado en el gobierno de Néstor Kirchner.
+La decisión del gigante asiático de invertir en toda la región, como fuente de materias primas, ocurre desde principios de este siglo y no fue modificado por ningún ejecutivo ni progresista ni de derecha. Macri también se encargó de afianzar la relación comercial con China, mientras que en Brasil, el ex presidente Jair Bolsonaro, también lo hizo y mantuvo su integración al BRICS, mientras boicoteó la política económica regional del Mercosur.
+Argentina está solicitando ingresar al bloque de países integrado por Brasil, Rusia, India, China y Sudáfrica y a su Banco de Desarrollo, que tendrá su reunión de directorio la próxima semana. Con la posibilidad de que Milei acceda a la Casa Rosada esos intento quedarían frustrados.
+En materia de inversiones, Argentina integra el acuerdo con China denominado la Iniciativa de la Franja y la Ruta (BRI por sus siglas en inglés), anunciado en 2013, para expandir la presencia de las inversiones a nivel global para disputar el rol de Occidente, con quien Milei asegura se alineara directamente, en un mundo marcado por la multipolaridad.
+Según un informe del Green Finance &amp; Development Center de la Universidad de Fudan, en China, en los primeros seis meses del año, los compromisos de China hacia los 148 países de la Iniciativa de la Franja y la Ruta muestran alrededor de 102 acuerdos bilaterales por valor de 43.300 millones de dólares, lo que equivale al 60 por ciento de las promesas de inversión que el país asiático hizo en todo el año pasado.</t>
+  </si>
+  <si>
     <t>La economía de la transhumancia</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/576286-la-economia-de-la-transhumancia</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La economía de la transhumancia. Una cultura ancestral en peligro. El pastoreo de ganado en diferentes territorios, para el invierno y verano, de las zonas cordilleranas, tiene miles de años, pero se ve impedido por el avance inmobiliario.. La trashumancia ha sido utilizada como metáfora e inspiración para décimas, coplas y canciones, desde cantos ancestrales a buena parte de la obra de Atahualpa Yupanqui, Saúl Huenchul o Rally Barrionuevo. Es una práctica milenaria que tiene al menos 2000 años en nuestro continente y ocupa a unos 200 millones de personas en el mundo y 30 millones de kilométros cuadrados (el doble de las tierras dedicadas a la agricultura). Fue declarada en 2019 Patrimonio Cultural Inmaterial de la Humanidad por la Unesco.
+Sin embargo, desde el Movimiento Nacional Campesino Indígena Somos Tierra (MNCI), parte de la Mesa Agroalimentaria Argentina (MAA), se viene denunciando que el avance del negocio inmobiliario y el agronegocio viene amenazando esta práctica. “Si de por sí es difícil que los fiscales necios de la ciudad comprendan el uso de posesión de un campo, imaginen la dificultad para que comprenda está dinámica que incluye dos áreas y un camino”, explica Diego Montón, dirigente del MNCI Somos Tierra y la MAA.
+[H2] Una práctica ancestral amenazada
+Desde los pueblos mapuches y la cultura campesina patagónica, la transhumancia es una forma de producción de carne vacuna, bovina o caprina, que tiene en cuenta las condiciones climáticas y de suelo. Durante el invierno se utilizan las zonas de llanura o precordillera, donde se puede proteger al ganado. Sin embargo en primavera o verano (en la llamada veraneada), las familias campesinas llevan sus animales a la zona de cordillera donde el derretimiento de la nieve crea nuevas pasturas que engordan el ganado y dejan descansar los suelos de las zonas desérticas donde se desarrolla la invernada.
+“A los hechos del uso del territorio, es importante que las familias tienen su casa principal en el llano, donde pasan el invierno. Pero también en la alta montaña tienen un refugio o una casa más pequeña, donde van a pasar la veranada, con corrales y el territorio ocupado. Sumado a los caminos de arreo, que es una de las cosas que ha entrado en conflicto”, explica Montón. “Acá en Mendoza, por ejemplo, tenemos el caso del El Azufre, un centro de ski que van a construir en Malargue en terrenos fiscales cedidos por el estado provincial con una donación de entre 20 mil y 50 mil hectáreas, desconociendo que son tierras utilizadas para la veranada en el marco de las transhumancia”, cuenta.
+“Siempre viene gente de afuera a hacerse dueña de lo que nuestros abuelos y toda la gente anciana ha trabajado en esos campos. El Estado acá siempre ha sido ausente. Se acuerdan de los puesteros sólo cuando hay elecciones. Conocen las condiciones en que vivimos pero nunca han solucionan nada”, relata Natalia Arroyo, productora caprina de Malargue y miembro del MNCI Somos Tierra. “Acá es complicada la comercialización por el tema de la distancia, los caminos malos, la pastura, el daño del puma y del zorro. Gracias a ser parte del movimiento campesino pude conocer mis derechos y el tema de la tierra o el agua. Nos han apoyado mucho. Pero el Estado no. No tenemos vehículos y muchas veces sacan el colectivo”, se queja. “En Malargue se hace la fiesta del chivo, pero algunos puesteros ni se enteran. Hacen oídos sordos a todos nuestros reclamos. Cuando podrían recaudar en la fiesta fondos para ayudarnos con el forraje o mejorar nuestras condiciones de vida y producción”, opina.
+[H2] Los beneficios de organizarse
+“Al ser parte del MNCI nos hemos beneficiado en tener más fuerza y unirnos frente al atropello de los terratenientes. También ha sido más fácil entrar en programas provinciales o nacionales y finalmente lograr que se apruebe una ley de arreos, muy necesaria para nuestro sistema de producción”, cuenta desde Neuquén, Antonio Vázquez, también productor caprino y miembro del MNCI. “Yo crío cabras y vendo chivito, pero hay compañeros que producen verduras, quesos, dulces, escabeche, miel, medias de lana, fieltro o talabartería”, agrega.
+En 2016, Neuquén sancionó la ley 3016 que garantiza el derecho de las familias trashumantes a transitar con su ganado por las huellas de arreo para trasladarse de ida y vuelta entre veranadas e invernadas. Además de la delimitación de huellas de arreo e infraestructura de alojos.
+“La práctica de la transhumancia tiene toda una dimensión cultural que está plasmada en décimas y poesía del folklore, pero también una importante dimensión productiva y de sostenibilidad de los pastizales y la capacidad de carga de los campos. Estas zonas son las de mayor producción caprina del país”, explica Montón, refiriéndose al sur de Mendoza y el norte de Neuquén. Entre los beneficios socioambientales de la práctica transhumante también se encuentra la prevención de incendios.
+“La ley 3016 toma muchas de las reivindicaciones de las organizaciones campesinas y comunidades mapuches que nuclean a las familias arrieras. Pero quedan muchas cosas por trabajar, como el relevamiento de muchas huellas históricas. También, si bien la autoridad de aplicación es el ministerio de Producción y Turismo de la provincia, en la práctica no ha sido así. Han tenido que ser las organizaciones las que en los territorios estamos buscando que se cumpla y respete la ley”, reclama Solverio Alarcón, referente del MNCI Somos Tierra de Neuquén y parte de Organizaciones Unidas en Defensa de los Arrieros, el frente que presionó para la aprobación de esta ley.
+* Licenciado en Economía de la Universidad Torcuato Di Tella y master en Periodismo de la Universidad del País Vasco.</t>
+  </si>
+  <si>
     <t>Con el dólar maíz, el Gobierno lograría obtener US$ 2.000 millones en 15 días</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/lbpupdates/572947</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2026
+    Página 12. . . [NÃO ENCONTRADO]</t>
+  </si>
+  <si>
     <t>Andrea Ribeiro Hoffmann: "La extrema derecha es un problema global"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/571280-andrea-ribeiro-hoffmann-la-extrema-derecha-es-un-problema-gl</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Andrea Ribeiro Hoffmann: "La extrema derecha es un problema global". Académica de la Universidad Católica de Río de Janeiro. La doctora en Ciencias Políticas y Relaciones Internacionales analiza el fenómeno de los ultras en el mundo, así como también el antes y después del gobierno de Jair Bolsonaro en Brasil.. Andrea Ribeiro Hoffmann es profesora de la Universidad Católica de Río de Janeiro (PUC-Rio) y forma parte de un proyecto de investigación llamado "Multilateralismo y Derecha Radical en América Latina" (Mudral), en colaboración con otros colegas. Tras su participación en el Congreso Mundial de Ciencia Política en Buenos Aires, la académica dialogó con PáginaI12 sobre la cuestión de las derechas en diferentes países y el impacto que tuvo en Brasil la experiencia bolsonarista.
+-¿Cómo surgió el proyecto de investigación y qué avances lograron?
+-La idea apareció a partir de la experiencia que tuvimos con el gobierno de Jair Bolsonaro en Brasil, cuyo impacto fue devastador en diversas esferas: desde la política y la salud, hasta el medio ambiente y la política exterior. La extrema derecha es un problema global, no es una coincidencia que haya un Donald Trump, un Bolsonaro y tantos otros gobiernos como esos. Tienen causas comunes, aunque también dinámicas locales muy específicas. En el caso de Bolsonaro, hubo una colaboración muy fuerte con el gobierno de Trump en muchos foros multilaterales. Por ejemplo, el Consenso de Ginebra, que fue una iniciativa conjunta para intentar cambiar normas internacionales respecto a cuestiones de género y derechos sexuales.
+-¿Por qué cree que hay países que dan giros hacia gobiernos de derecha o extrema derecha?
+-Es un fenómeno complejo. Hay una insatisfacción general de la población muy grande desde los últimos años, debido a la crisis económica y la pandemia, que afectó fuertemente a América Latina. Hay un desencanto con los gobiernos democráticos, que deberían proveer buenas condiciones de vida, con inclusión y una reducción de las asimetrías. Aquí entra también una cuestión nueva: las redes sociales. Se usaron como estrategia política en las campañas para captar votos, incluso con fakenews, como fue el caso de Trump. Entonces, gran parte de las poblaciones votan muchas veces en contra de sus propios intereses. Aún así, es muy difícil de comprender estos cambios que fueron muy rápidos, donde en América Latina, en general, hay una inclinación hacia los gobiernos de izquierda con sus propuestas de redistribución. Por ejemplo, en Brasil, una gran mayoría apoyó el primer y segundo mandato de Lula da Silva, sin embargo, esta misma población eligió un líder de extrema derecha. Es importante comprender esta complejidad, porque durante mucho tiempo no se creyó que fuera posible.
+-¿Puede volver a repetirse un acontecimiento similar al intento de golpe de Estado de enero en Brasil?
+-Lo que se vio es que las fuerzas armadas participaron en la toma de poder. Este fenómeno fue específico de Brasil, aun cuando América Latina comparte un pasado de dictaduras militares. Aunque se creía que este tema estaba resuelto en la región después del final de la Guerra Fría, Brasil muestra diferencias con Argentina o Chile, países donde se instauraron procesos de justicia transicional, una política de memoria. Durante la transición democrática en Brasil, se hizo uso de amnistías. Esto fue un punto de discusión muy importante, especialmente bajo la gestión de Dilma Rousseff, cuyo pasado como presa y torturada durante la dictadura destacó la importancia del tema. Sin embargo, el proceso fue incipiente y rápidamente se dio lugar a la destitución constitucional de este gobierno elegido por un movimiento político. Se percibió la presencia creciente de liderazgos y fuerzas militares, aunque no su dimensión hasta la tentativa de golpe en enero de este año, que mostró la disposición de los militares a participar activamente. Lula y su ministro de Justicia estuvieron muy preparados y atentos a este riesgo, porque era una crónica de la muerte denunciada.
+-¿En qué sentido?
+-Se esperaba que Bolsonaro no iba a aceptar la derrota, pero sí fue una sorpresa el nivel de violencia y destrucción. El bolsonarismo es un fenómeno social, no es solo de militares y no se terminó de un día al otro con el fin del mandato de Bolsonaro. Sus raíces son profundas, hay cuestiones estructurales y sociales que permanecen en la sociedad, con un sentimiento que podría llevar nuevamente al poder a políticos que compartieron su visión durante su gobierno. Mucha gente realmente dejó de creer que los sistemas democráticos son capaces de traer cambios en sus vidas. El desafío es conseguir que se confíe que la democracia es la forma de gobierno que permite más inclusión y redistribución.
+-¿Qué análisis hace sobre los primeros seis meses del gobierno de Lula?
+-Creo que enfrenta muchos desafíos debido al contexto diverso, tanto a nivel internacional como local. Todas las fuerzas políticas se unieron para formar su gobierno, lo que generó divergencias en la formulación de políticas. Así que lo que se ve en estos primeros meses fue una gran tentativa de Lula de conseguir gobernar, porque muchos bolsonaristas fueron electos, y también aprobar medidas importantes. Una de ellas fueron los cambios en el ámbito fiscal. Sin embargo, en la coalición de gobierno hay visiones distintas del rol de China y la guerra de Ucrania, en la que Lula se entrometió mucho. Entonces, formular una propuesta coherente y viable será un gran desafío, porque diversos agentes económicos y sociales no están de acuerdo con ciertas políticas. Aunque la agenda ambiental podría ser un área de convergencia, enfrenta resistencia de poderosos sectores del agronegocio en Brasil. Además, el gobierno está recomponiendo los cuadros ministeriales tras la disminución realizada durante el gobierno de Bolsonaro y, a nivel regional, Lula intentó retomar la integración, pero no hubo consensos, por ejemplo, entre el Mercosur y la Unión Europea. A pesar de las dificultades, yo siempre permaneceré optimista.
+Entrevista: Axel Schwarzfeld</t>
+  </si>
+  <si>
     <t>Candidatos con música para los oídos de la Sociedad Rural</t>
   </si>
   <si>
@@ -668,48 +2049,187 @@
     <t>https://www.pagina12.com.ar/571002-musica-para-los-oidos-de-la-sociedad-rural</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Música para los oídos de la Sociedad Rural. Promesas para los empresarios ruralistas de los candidatos de la oposición: eliminar retenciones, ajustar el gasto y abrir la economía. En el marco de la Exposición Rural, Bullrich, Larreta, Schiaretti y Milei revelaron detalles de sus programas económicos por primera vez desde que se lanzó formalmente la campaña. Hablaron explícitamente de un ajuste y de unificar el tipo de cambio, y se comprometieron a garantizar la rentabilidad del sector. Los candidatos de Juntos por el Cambio se cruzaron por los tiempos y las formas para salir del cepo, mientras que el ultraderechista Milei insistió con la dolarización.. Los principales candidatos de la oposición se animaron a explicitar, por primera vez desde que empezó formalmente la campaña, qué tienen pensado hacer en materia económica en caso de llegar a la Rosada. Tuvo que convocarlos la Sociedad Rural Argentina, en el marco de la Expo Rural 2023, para que tal cosa sucediera. Horacio Rodríguez Larreta y Patricia Bullrich, por Juntos por el Cambio; Juan Schiaretti, de Hacemos por Nuestro País, y Javier Milei, de La Libertad Avanza, disertaron frente a los empresarios que concentran buena parte parte de los dólares del agronegocio y desplegaron su menú de políticas para el sector. Los discursos, también, dejaron varias pistas sobre el trazo grueso de sus planes de gobierno. Hubo coincidencias –eliminar o bajar al mínimo las retenciones, abrir la economía, recortar el gasto público, suprimir "el cepo" y unificar el tipo de cambio, entre otras–, aunque afloraron matices –y en algunos casos diferencias, como entre Larreta y Bullrich– sobre las formas y los tiempos para hacerlo.
+Las propuestas de los opositores sonaron como música para los oídos del auditorio del Salón Rojo del predio de Palermo: todos hablaron de la necesidad de ampliar la rentabilidad del campo, de reducir impuestos y controles y de la apertura “a los mercados”. Muchos, incluso, habían tomado nota del pliego con “Lineamientos Generales para el Desarrollo de Políticas Públicas” que la SRA le había entregado a los candidatos en abril de este año, y que contiene nueve puntos que los chacareros esperan que lleve adelante el próximo gobierno, desde “una política fiscal que devuelva competitividad”, hasta “un programa para estabilizar la macroeconomía” e “instituciones que garanticen las reglas de juego”.
+El más aplicado en seguir esa hoja de ruta fue Rodríguez Larreta, aunque desde el bullrichismo remarcan que la exministra arrasó a la hora del aplausómetro, con un discurso más duro y más en sintonía con el adutiorio. Ninguno de los dos pudo evitar volver a chicanearse, aunque no hubo nada parecido a un debate mano a mano. Bullrich prometió “eliminar el cepo desde el primer día, de forma inmediata", y dijo tener “el coraje necesario” para hacerlo; mientras que el Jefe de Gobierno porteño –que habló antes– ya se había atajado al respecto, con el planteo que la idea "no es seria”, porque “no va a haber dólares en el Banco Central”.
+[H2] Bullrich, de local
+La exministra de Mauricio Macri y Fernando De La Rúa llegó a la Rural acompañada por el diputado nacional Luciano Laspina (su principal asesor económico), el presidente de la UCR bonaerense, Maximiliano Abad, y el legislador porteño Juan Pablo Arenaza (jefe de campaña). Ni bien se subió al atril, recordó su lazo con la exposición rural, “a la que vengo prácticamente desde que nací y que conozco profundamente”, dijo. Desde su entorno aseguraron que “se sintió como en familia, ante un público cautivo, de gente con varios apellidos”, en referencia al linaje de los Luro Pueyrredón.
+En confianza, Bullrich dijo que está “trabajando con una cantidad de dólares que todavía no podemos decir de dónde van a salir, pero que estamos negociando a nivel internacional” lo que permitiría blindar al Banco Central “para salir del cepo lo antes posible, de manera urgente, el primer día” de su hipotético gobierno. Para eso, dijo tener “el coraje necesario”, en una chicana típica de su campaña contra su rival interno.
+“Vamos a mandar una ley el primer día para que nadie pueda limitar las exportaciones, para que ningún burócrata de bajo nivel pueda decidir hacer eso”, siguió, en uno de los tramos más festejados por el auditorio. El otro fue cuando prometió “desarmar el estado autoritario que le da órdenes al campo de lo que tiene que hacer” y “eliminar los trámites insoportables”, entre ellos, incluso, los que les exige la Aduana.
+En el bullrichismo sostienen que salieron ganadores en el contrapunto con Larreta. "Es un público que también podría votarlo, pero no lo aplaudieron casi nada. Se nota que él tiene acuerdos con todo el mundo y entonces no puede ser sincero como Patricia, que dice lo que siente y hace un diferencial", se explayaron.
+[H2] Larreta y la gestión
+El eje del discurso del jefe de Gobierno –quien llegó junto al ministro de Economía de Macri, Alfonso Prat Gay, y a otro especialista en la materia, José Luis Espert– fue diferenciarse de Bullrich haciendo hincapié en su gestión. Su muletilla fue “como ya lo hicimos en la Ciudad”, que repitió a la hora de graficar cómo bajar impuestos y ajustar el gasto sin recortar la obra pública.
+“Tenemos que ir a un tipo de cambio único”, propuso y aprovechó el malestar de los empresarios del agro con las medidas que había anunciado Sergio Massa horas antes: “Basta de parches”, lo criticó. También prometió “apertura de mercados” y llegar al “déficit fiscal cero el primer año” de un hipotético gobierno suyo.
+También arremetió contra el planteo de Bullrich de eliminar el cepo el primer día. “No es un plan serio, el que les diga eso, miente”, dijo. En la misma línea, apuntó a “ir bajando las retenciones paulatinamente”. También prometió “aplicar el bisturí” sobre el presupuesto. Sobre el final, dijo que “el mercado de la carne es el más intervenido del país”, en una búsqueda por congraciarse con el presidente de la SRA, Nicolás Pino, que proviene precisamente de ese sector.
+[H2] Schiaretti, el anti-K
+El gobernador de Córdoba también prometió eliminar retenciones, y aseguró que el costo fiscal lo recuperaría eliminando subsidios. “Es mentira que no se puede por el costo fiscal que implicaría la medida, como dicen algunos. Lo que el Estado recauda por retenciones equivale a lo que gasta en subsidios, así que ahí tenemos una de las claves”, apuntó, aunque matizó con que “no es necesario un ajuste salvaje” a partir del 10 de diciembre.
+Luego se dedicó a criticar al kirchnerismo y recordar el conflicto por la 125. “El Kirchnerismo agrede a quien no le responde, eso hizo con el campo y con la prensa y, ahora con la Corte.. Reitero mi más enérgico rechazo al pretendido juicio político”, dijo.
+[H2] Milei, contra el “papa Estado”
+El economista Milei se presentó de la mano de su compañera de fórmula, la ultraderechista Victoria Villarruel, y de su hermana, Karina Milei. Como es habitual, apeló a los adjetivos llamativos, como cuando se refirió al cepo como “inmoral”. “Consideramos que el campo argentino es el mejor del mundo. Trabajaremos para devolverle la rentabilidad y la vitalidad que se le ha quitado en los últimos años chupándole la sangre”, dijo.
+Milei insistió con su plan de dolarización, al que le agregó el detalle de que podría llevarlo a cabo entre "9 y 24 meses". También habló de una "unificación cambiaria de facto" y de la “idea nefasta de la justicia social”.
+Sobre el final, el autodenominado libertario sostuvo que irá “contra todas las partidas donde roba la política” y, en ese mercado, que va a “eliminar la obra pública”. “La va a hacer el sector privado, que va a tener rentabilidad”, agregó y apuntó contra los contratistas: “ustedes son grandes y no necesitan de un papá Estado”. Recibió aplausos encendidos.</t>
+  </si>
+  <si>
     <t>El hombre de la silla de ruedas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/569502-el-hombre-de-la-silla-de-ruedas</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    El hombre de la silla de ruedas. . Germán Abdala nació el 12 de febrero de 1955, en Santa Teresita y falleció el 13 de julio de 1993 en un hospital porteño.. Germán Abdala nació el 12 de febrero de 1955, en Santa Teresita y falleció el 13 de julio de 1993 en un hospital porteño. Su familia decidió que sus restos fueron lanzados al mar que amó, desde la playa de la ciudad que lo viera nacer. Fue dirigente de la Asociación Trabajadores del Estado, desde el 6 de noviembre de 1984 hasta su deceso, como así también uno de los fundadores de la CTA. Fue elegido diputado nacional en 1989, cargo que también ejerció hasta 1993. Pero con decir esto nada se diría.
+La vigencia y actualidad de Germán tampoco son hallables en la estatuaria ni en los monumentos autorreferenciales de quienes, so pretexto de hablar sobre él, te cuentan cómo lo conocieron, dónde estaban y por qué estaban ahí, justo en ese momento trascendental de la Historia en el que Germán se topó con ellos.
+Lo cierto es que hay un Abdala que, a lo largo de estos treinta años, ha podido eludir la trampa de los panteones, la rigidez del bronce de las placas y la frialdad de los mármoles. Se trata de aquel dirigente sindical que en los albores de la restauración democrática consiguió entender, antes que nadie, que no bastaría con tener un sindicato democrático, combativo y memorioso de las luchas que lo precedían para poder defender los intereses de las y los trabajadores afiliados. Su concepción de la política arrancaba desde la asimilación de la derrota sufrida por el campo popular a partir de la dictadura cívico militar y eclesiástica y, precisamente por eso, hacía de la construcción colectiva una condición inexcusable para establecer el sentido de las alianzas.
+Es a partir de ese principio que hoy es posible entender el abanico de representaciones políticas que logró constituir en ATE Capital para su primer mandato como secretario general. No le importó que a su izquierda confluyeran militantes que provenían de la lucha armada de los años 70 y que a su derecha se formaran los que provenían de un peronismo tradicional; para Germán lo decisivo había sido que cada uno manifestara su voluntad de arrancarle el gremio a la burocracia prodictatorial que encabezaba Horvarth. La determinación de unir en un colectivo a todas esas voluntades dispersas y carentes de conducción política hizo que él, mucho antes del triunfo en las decisivas elecciones del 6 de noviembre de 1984, se convirtiera en un dirigente natural de los estatales porteños.
+Los conflictos laborales que fueron escalonándose durante el gobierno de Raúl Alfonsín y la seguidilla de los trece paros nacionales convocados por la CGT dirigida por Saúl Ubaldini, lo llevaron a la conclusión de que esas luchas no alcanzarían sus objetivos, ni frenarían la hiperinflación desatada por los grandes grupos económicos, si el movimiento obrero no atinaba a entender que no debía resignar su representación política a manos de los profesionales de la rosca. Fue por eso que en 1988, cuando ATE aún era un gremio con poco más de 60.000 afiliados en todo el país, Germán se alineó en la interna del PJ con el sector de la Renovación que encabezaba Antonio Cafiero quien, al cabo, fue derrotado por Carlos Menem. Pero esa decisión temprana, tomada antes de que finalizara su primer mandato como secretario general de ATE Capital, lo situó como candidato a diputado nacional.
+Tenía apenas 34 años cuando asumió la banca y ya contaba con la certeza de que Menem traicionaría los postulados de la campaña electoral. Esta convicción lo proyectó más allá de las fronteras del recinto parlamentario porque desde un primer momento no hubo conflicto o reclamo laboral que no lo viera acudir en su condición de legislador. Los principales debates en la Cámara también lo contaron como protagonista. La suya fue una banca al servicio de la clase trabajadora y toda su actividad parlamentaria giró en torno al protagonismo colectivo antes que a la figuración personal. Dijo sin titubear: “La política del imperio para nuestro país, no solo fue matarnos a los mejores compañeros, no solo fue perseguir a los mejores compañeros, intervenirnos las organizaciones sindicales, prohibir la política, saquear el país con la deuda externa, sino que fue cambiar las conductas humanas, quebrarnos a nosotros en eso tan íntimo como es la voluntad de lo colectivo.” Para Germán Abdala se había pasado “del decir si nos juntamos solidaria y colectivamente, vamos a ser más que la voluntad individual” a esto otro de “hacer valer el reino éste de si cuerpeo, le meto el codazo en la cara al otro, hago mérito, delato, hago buena letra, no transgredo, me mimetizo dentro de las posibilidades del sistema, a lo mejor tengo la suerte de ser uno de los 8 millones de argentinos que se salve.”
+En poco tiempo confrontó con el menemato y creó y lideró el Grupo de los Ocho, pero supo comprender que aquello no bastaría si no se era capaz de organizar al movimiento obrero sobre un cimiento antagónico al del colaboracionismo sindical que primaba en la fracción antiubaldinista de la CGT: "Mi visión hoy es que el Grupo de los Ocho y el peronismo disidente han cumplido una etapa, de la cual queda como autocrítica que no fuimos capaces de construir una oposición al modelo liberal menemista desde adentro. Nosotros quisimos ser la conducción del verdadero peronismo, pero en esto hay que ser sinceros: hemos perdido (...) Hay que construir una nueva alternativa popular en la Argentina que sintetice a todos los sectores. Un nuevo partido o frente que rompa con el bipartidismo". Allí, en esas definiciones, anidaban tanto la inminente fundación de la CTA, como los fundamentos estratégicos para la creación de una herramienta política que sacara a la democracia de sus cepos burgueses.
+Está claro que Germán no se refería a ninguna clase de tercer movimiento histórico, esa quimera del alfonsinismo que se desintegró con la hiperinflación y las elecciones anticipadas; tampoco aludía al experimento progresista que, tras su muerte en 1993, sería encabezado por Carlos Chacho Álvarez y que terminaría como aliado de los radicales en la Alianza con Fernando de la Rúa y Domingo Cavallo. Por el contrario, la idea de romper con el bipartidismo remitía a un tipo de representación y práctica política que ensancharan y profundizasen los estrechos límites de la democracia formal.
+Nadie mejor que Abdala para explicar eso: “Es el principio de algo que tiene que lograr salir de la resistencia para poder plantear a esta sociedad, que no sólo está el discurso de la derecha para evitar la crisis política, sino que también los sectores populares tenemos una propuesta, un planteo para explicar por qué hoy las dirigencias políticas, sociales, forman parte todas del mismo esquema de prebenda y prostitución que han hecho que el conjunto de las masas dejen de creer que es posible un país distinto.” Cuando uno ve los increíbles porcentajes del abstencionismo que se registran en las actuales PASO, a treinta años de la partida de Germán, no puede menos que afirmar que sus palabras de entonces tienen una vigencia dramática.
+“Los restaurantes están llenos, los cines están llenos, pero cuando uno empieza a discutir en cada una de las provincias las realidades de las economías regionales, la integración económica, vivimos en un mundo feudal. Vivimos en un mundo donde todo está por hacerse. Toda la gente nos dice: “¿Por qué no se dan créditos a la pequeña y mediana industria en vez de estar favoreciendo a Bunge y Born para que exporte 7000 millones de granos?”. Aquí uno piensa en el fiasco de Vicentín, en las ganancias fabulosas de los bancos mientras cada vez más personas deben dormir en la calle, en las facilidades cambiarias para el agronegocio mientras se aduce la falta de fondos para otorgarles a los estatales un bono compensatorio de todo lo que han perdido en este tiempo.
+El Abdala final, el de Parque Sarmiento, casi sin fuerzas ni voz porque la enfermedad lo ha consumido y ya ni caminar puede, lanza su último desafío histórico en aquel noviembre de 1992: “No me va a doblegar el cáncer, pero me mataría, eso sí, la tristeza, si no logramos dar forma organizativa y presencia a este maravilloso fervor militante.” Aquel Abdala no hablaba de colonizar el aparato del Estado con adeptos obedientes y ubicuos; tampoco creía que la militancia pasaba por escalar cargos, ni sumar minutos en las pantallas televisivas, ni que la hegemonía política era tan solo una sumatoria de los propios ni, mucho menos, que había que fundar un partidito de morondonga.
+Germán, aquel último que habla para el futuro desde la fragilidad de su figura en la silla de ruedas, es más vigente que nunca porque la estrategia de poder popular que él supo diseñar está cada vez más lejos de ser refutada por nadie. Y menos hoy, a treinta años de su muerte.</t>
+  </si>
+  <si>
     <t>Juntos por el Cambio no tiene paz</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/564911-juntos-por-el-cambio-no-tiene-paz</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Juntos por el Cambio no tiene paz. De acusaciones por complicidad con el narcotráfico a cruces por reelecciones. Carolina Losada, precandidata a gobernadora por Santa Fe, está decidida a dinamitar la interna que organizó el macrismo en la provincia litoraleña. Dijo que si pierde no apoyará a Maximiliano Pullaro, a quien le volvió a recordar que tiene "muertos en el placard". En Formosa, el clima también está picado.. La precandidata a gobernadora por Santa Fe y senadora nacional, Carolina Losada, continúa dinamitando la interna de Juntos por el Cambio a nivel provincial y nacional. A doce días de las PASO en Santa Fe, Losada volvió a cargar contra el precandidato a gobernador por el radicalismo en la interna de "Unidos para Cambiar Santa Fe", el ex ministro de Seguridad Maximiliano Pullaro, a quien le volvió a recordar que tiene "muertos en el placard" de su gestión respecto de la relación entre la policía provincial y el narcotráfico. Además, la pareja del senador Luis Naidenoff, se metió en la interna de Formosa para apuntar contra candidatos a legisladores nacionales.
+Losada mantiene una disputa descarnada con Pullaro por los votos del próximo 16 de julio, cuando se definirán las candidaturas para las elecciones generales del 10 de septiembre. "No lo tomo como una pelea, sino como alguien que viene y recuerda cuál es la situación y la verdad", consideró la senadora nacional ante de volver a atacar a Pullaro por "los vínculos que hablo son conocidos, su mano derecha es tan peligroso que está preso".
+La precandidata por el PRO en Santa Fe -aunque vive en Nordelta- viene desde hace semanas apuntando sobre el "muerto en el placard" de Pullaro. Se refiere al ex jefe antinarcóticos Alejandro Druetta, quien fue designado por el precandidato del radicalismo durante su gestión como ministro de Seguridad en el gobierno de Miguel Lifschitz. Druetta fue condenado a 10 años de prisión por ser miembro de una banda narco que comerciaba estupefacientes en el sur de la provincia de Santa Fe.
+"Los audios donde corrompe a la policía en primera persona son conocidos de cuando él era ministro", recordó Losada para despegarse de las críticas por fomentar la interna santafecina. En ese tono, la senadora reiteró que no trabajará con los precandidatos de Pullaro en caso de que ella gane la interna. "No voy a convocar a ninguna persona que haya tenido o tenga vínculos con el narcotráfico", apuntó en diálogo con Radio Continental.
+"Voy a convocar a todo el sector, en mi Gobierno quiero ir hasta el hueso contra el narcotráfico y hay que tener las manos limpias y no tener muertos en el placard", sentenció Losada. La lista de Pullaro es respaldada a nivel nacional por el senador radical Martín Losteau, quien va como precandidato a jefe de gobierno porteño. Mientras que Losada es respaldada por Patricia Bullrich, Horacio Rodríguez Larreta y Elisa Carrió. La otra precandidata a gobernadora dentro de espacio cambiemita es la socialista Mónica Fein.
+La senadora ya había declarado no tener ninguna relación ni "ética ni moral" con Pullaro y Losteau, acusando al senador por la recordada resolución 125, que buscó crear retenciones móviles para las exportaciones del agronegocio.
+[H2] De Santa Fe a Formosa
+No conforme con mantener encendida la interna provincial, la senadora también salió al cruce de la decisión de los referentes formoseños de Juntos por el Cambio Fernando Carbajal, Gabriela Neme y Francisco Paoltroni, quienes en el cierre de listas nacionales del 24 de junio se anotaron para competir en la lista de diputados por Formosa, cuando ese domingo 25 también competían a nivel provincial. De hecho, Carbajal fue el candidato a gobernador que perdió frente a otra arrasadora elección del gobernador Gildo Insfrán.
+"De alguna forma es un fraude a la gente. Tienen los peores vicios de la casta", lanzó la ex conductora de televisión y pareja del senador nacional formoseño Luis Naidenoff. Neme, surgida del peronismo, apeló a las redes sociales para responder los cuestionamientos: "No, Carolina, te equivocás. El fraude al electorado viene de la mano de los que se abusan de la re-re-reeleción y se perpetúan en las bancas, igual que Gildo Insfrán".
+Con esas palabras, Neme reveló otra interna entre su sector y el de la pareja de Losada. "Como el caso de la casa de Luis Naidenoff y Ricardo Buryaile, más de 20 años en las bancas. Nuestra lucha firme, decidida y comprometida es contra la reelección", dejó claro en otro tuit.</t>
+  </si>
+  <si>
     <t>Bolsonaro fue inhabilitado electoralmente hasta 2030</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/563852-bolsonaro-fue-inhabilitado-electoralmente-hasta-2030</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Bolsonaro fue inhabilitado electoralmente hasta 2030. La justicia electoral de Brasil dictaminó que es culpable de difundir mentiras sobre las elecciones. El ministro de Justicia, Flávio Dino, dijo que el gobierno le exigirá al expresidente una indemnización "por los daños que le causó al Poder Judicial y a la propia sociedad".. La justicia electoral de Brasil determinó por mayoría inhabilitar al expresidente Jair Bolsonaro para presentarse a cargos públicos hasta 2030, al declararlo culpable de "abusos de poder" por diseminar mentiras y sospechas infundadas sobre el sistema de comicios brasileño ante embajadores de países extranjeros.
+Con esta decisión, adoptada por cinco votos frente a dos en el Tribunal Superior Electoral (TSE), el líder de la ultraderecha, de 68 años, no podrá concurrir a cargos electivos ni ejercer puestos en la administración pública durante un plazo de ocho años, contados a partir de octubre de 2022, cuando se celebraron los comicios en los que le ganó Luiz Inácio Lula da Silva.
+El presidente del TSE, el juez Alexandre de Moraes, profirió el último voto. Según él, la sentencia es una respuesta al "degradante populismo nacido en los discursos de odio y antidemocráticos, que propagan una asquerosa desinformación no sólo en Brasil, sino en todo el mundo, con el único objetivo de engañar a los electores". De Moraes había sido objeto de virulentos y permanentes ataques del bolsonarismo antes y durante la campaña electoral, en la que fue acusado, sin prueba alguna, de maniobrar para favorecer a Lula.
+Tras conocerse la condena, el líder ultraderechista tachó el fallo de "puñalada en la espalda" y señaló que apelará ante la corte suprema. "No estoy muerto, vamos a seguir trabajando. Mi apelación será ante el Supremo Tribunal Federal", afirmó Bolsonaro a periodistas en Belo Horizonte, al sureste de Minas Gerais, estimando que con la decisión judicial, Brasil se encamina "hacia una dictadura". También está esperanzado en la posibilidad ya anticipada por algunos de sus correligionarios políticos de que el Congreso apruebe un proyecto de ley amnistiando a los condenados por delitos electorales en 2022, que lo beneficiaría y lo volvería a habilitar políticamente.
+[H2] Es un "gran dia"
+El ministro de Justicia de Brasil, Flávio Dino, aseguró que el gobierno le exigirá a Bolsonaro una indemnización: "La decisión del tribunal prueba que fueron perpetrados ataques abusivos al sistema de justicia y al orden jurídico. Por ese motivo, enviaré una petición a la Abogacía General del Gobierno para que analice la posibilidad de exigirle una indemnización por los daños que le causó al Poder Judicial y a la propia sociedad", indicó.
+El ministro de Relaciones Institucionales, Alexandre Padilha, afirmó que la condena contra el exmandatario fue el primer paso "hacia la rendición de cuentas por los crímenes en serie cometidos y la organización criminal que encabeza". Y añadió: "No se trata de festejar que Bolsonaro no pueda disputar las elecciones (presidenciales) de 2026, que es algo muy distante de nuestras preocupaciones. Se trata de dejar claro el papel del expresidente en los ataques a la democracia y en no aceptar el resultado de las urnas".
+Gleisi Hoffmann, presidenta del Partido de los Trabajadores (PT), consideró que la decisión de los magistrados "tiene una enorme forma didáctica y condena los métodos de la extrema derecha, la diseminación industrial de mentiras, amenazas a la democracia y el uso del poder público para perseguir adversarios y prevalecer en la disputa electoral". Para ella, se trata de un "gran día" --frase que usaba el exmandatario de ultraderecha para celebrar sus logros-- demostrando que "la defensa de la democracia y el enfrentamiento al fascismo permanecen en el orden del día" de la sociedad brasileña.
+[H2] La causa judicial
+El TSE estudió una demanda del Partido Democrático Laborista (PDT) contra Bolsonaro, quien en julio de 2022 organizó en el Palacio del Planalto una reunión con diplomáticos y embajadores extranjeros. De acuerdo con esta denuncia, el exmandatario utilizó el encuentro para difundir, sin pruebas, acusaciones sobre la fiabilidad de las elecciones de 2022.
+Ese hecho, según dice la sentencia, constituyó un "abuso de poder político, conductas vedadas y desorden informativo" y también un "uso indebido de predios públicos y medios de comunicación", pues Bolsonaro ordenó que la televisión pública transmitiera el evento. Es más, según dijeron algunos jueces, dicha situación pudo incitar el asalto a las sedes de los tres poderes el pasado 8 de enero, cuando una horda de bolsonaristas sembró el caos con la intención de llevar a las Fuerzas Armadas a derrocar a Lula.
+Entre los jueces que votaron en contra de la inhabilitación, estaba el juez Raul Araújo. Si bien reconoció que Bolsonaro difundió información falsa sobre el sistema electoral en aquella reunión con embajadores, consideró que no cumplía con "el requisito de gravedad suficiente". También defendió que se tomaron medidas suficientes para que esa reunión no tuviera repercusiones electorales, citando la retirada de la grabación de internet, además de desestimar el impacto que pudo haber tenido, porque eran argumentos ya conocidos por los seguidores del expresidente brasileño.
+[H2] El derrotero de Bolsonaro
+Conocido por su estilo provocador y divisivo que le hizo ganar el apodo de "Trump tropical", Bolsonaro irrumpió en el escenario nacional como candidato presidencial en 2018. Con un seductor discurso anticorrupción y de "outsider", cautivó durante la campaña a muchos brasileños, hartos de los partidos tradicionales salpicados por polémicas. Sobrevivió a un ataque con cuchillo perpetrado durante un acto electoral y eso solo hizo incrementar la fe de sus seguidores en su "Mesias", segundo nombre de Bolsonaro. Contó con el apoyo de los influyentes 'lobbies' de las armas, el agronegocio y el vasto electorado evangélico.
+Su presidencia se erosionó especialmente por su manejo de la pandemia del coronavirus, que en Brasil dejó 700.000 muertos, solo por debajo de Estados Unidos en números absolutos. El exmandatario restó importancia al covid-19, desafió los datos científicos para combatirlo, se burló del uso de mascarillas y advirtió que las vacunas podrían convertir a las personas en cocodrilo. A su vez, fue criticado internacionalmente por la deforestación de la Amazonía, que aumentó más del 70% durante su mandato respecto al promedio anual de la década anterior.
+Luego de perder por un estrecho margen las elecciones, Bolsonaro se negó a felicitar a su adversario y a admitir abiertamente su derrota. Cayó en un silencio inédito, incluso en sus redes sociales, donde había sido hiperactivo. Viajó a Estados Unidos dos días antes del fin de su mandato y no asistió a la toma de posesión de Lula el 1 de enero. Una semana después, miles de seguidores de Bolsonaro invadieron y vandalizaron el palacio presidencial, el Congreso y la sede de la corte suprema, en un intento fallido por derrocar a Lula.
+A su regreso a Brasil, el exmandatario enfrenta cinco procesos ante el máximo tribunal que podrían enviarlo a prisión. El más reciente investiga si instigó la asonada del 8 de enero. También es investigado por la policía y las autoridades tributarias por supuestamente haber intentado importar ilegalmente joyas valoradas en millones de dólares que él y su esposa, Michelle, recibieron de Arabia Saudita.
+[H2] Adiós a los derechos políticos
+Tras confirmarse la reciente condena, el exmandatario se convirtió en el tercer expresidente brasileño que es inhabilitado para disputar cargos electivos o ejercer cargos públicos desde el restablecimiento de la democracia, en 1985. El primero fue Fernando Collor, quien a principios de los años 90 fue acusado de participar en una trama corrupta, lo que desencadenó que el Congreso pusiera en marcha un juicio político con fines de destitución en su contra. En un contexto de grave crisis económica, Collor renunció a la presidencia con el objetivo de mantener sus derechos políticos. Pese a ello, el Senado aprobó su inhabilitación durante ocho años.
+El actual presidente, Lula da Silva, también había sido declarado inelegible, pero por un motivo distinto. En 2018, el dirigente progresista fue condenado en segunda instancia a 12 años y 1 mes de cárcel por un caso de corrupción. Esa sentencia se encuadró en la llamada "Ley de Ficha Limpia", que impide a condenados en segunda instancia concurrir a cargos electivos. Sin embargo, en 2021, la Corte Suprema anuló esa y otra condena por corrupción contra Lula, un fallo que le permitió recuperar sus derechos políticos y presentarse a las presidenciales de 2022 y ganarle a Bolsonaro.</t>
+  </si>
+  <si>
     <t>La muerte de Emmily Rodrigues: el empresario Sáenz Valiente quedó procesado por "homicidio culposo"</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/563037-la-muerte-de-emmily-rodrigues-el-empresario-sanchez-valiente</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La muerte de Emmily Rodrigues: el empresario Sáenz Valiente quedó procesado por "homicidio culposo". No deberá cumplir prisión preventiva pero sí usar tobillera electrónica. La resolución la Sala 6 de la Cámara del Crimen da por probado que Saénz Valiente estuvo involucrado en la muerte de Emmily, aunque quedó descartado el pedido de la querella, que solicitaba la carátula de femicidio o de homicidio con intención de ocultar un abuso sexual.. El empresario Francisco Sáenz Valiente quedó procesado por el “homicidio culposo” y la “facilitación de drogas” a Emmily Rodrigues, la modelo brasileña que hace casi tres meses murió tras caer del departamento del imputado. La Sala 6 de la Cámara del Crimen dispuso que Sáenz Valiente no cumpla prisión preventiva, pero sí la obligación de llevar una tobillera electrónica.
+La resolución la Sala 6 de la Cámara del Crimen, que elevó la calificación de la pena para el empresario del agronegocio y la minería, da por probado que Saénz Valiente estuvo involucrado en la muerte de Emmily, aunque quedó descartado el pedido de la querella, que solicitaba la carátula de femicidio o de homicidio con intención de ocultar un abuso sexual. La fiscalía también había solicitado otra calificación, la de “abandono de persona agravado por el resultado muerte”.
+Otro pedido de la querella y la fiscalía que fue rechazado por el tribunal fue el de la detención preventiva del empresario. Los camaristas Magdalena Laiño, Ricardo Matías Pinto e Ignacio Rodríguez Varela ordenaron que Sáenz Valiente lleve una tobillera con geolocalización, bajo el control de "Programa de Asistencia de Personas Bajo Vigilancia Electrónica", dependiente del Ministerio de Justicia.
+En otro de los puntos, los camaristas decidieron mantener las mismas medidas cautelares ya dictadas para Sáenz Valiente por el juez de la causa el 18 de abril. La prohibición de acercamiento a los familiares de la damnificada y a los testigos que declararon en la causa, prohibición de salida del país, la obligación de asistir cada 15 días a la sede del tribunal y fijar un nuevo lugar de residencia distinto a la casa donde ocurrió el hecho.La decisión de la Sala 6 de la Cámara del Crimen ocurre 24 horas después de que se conociera la incorporación de un peritaje clave a cargo de la Policía de la Ciudad en el que detectó sangre y semen en 25 muestras levantadas en preservativos, sábanas, acolchados y hasta en el corsé que usaba Emmily la noche en la que falleció al caer al vacío.
+El hecho ocurrió el 30 de marzo pasado, cuando luego de cenar en un restaurante de la Costanera norte y de pasar por un bar de Palermo, Emmily llegó a las 3.21 con dos amigas al departamento de Sáenz Valiente, en el sexto piso del edificio de Libertad 1542, en Retiro, donde ya se encontraba una cuarta mujer.Tras una madrugada de excesos con ingesta de alcohol, marihuana, cocaína y "tuci", Rodrigues cayó desnuda por una ventana al patio interno del pulmón del edificio, cuando en el departamento solo estaban Sáenz Valiente y una de sus amigas.Los estudios toxicológicos revelaron que, antes de caer al vacío, la modelo brasileña consumió alcohol (1.0 gramos en sangre fue el dosaje), cocaína, marihuana, ketamina y MDMA (uno de los componentes de la droga sintética "Tuci", la forma abreviada de llamar al "Tucibi" por la pronunciación en inglés de la sigla 2C-B, que es la mal denominada "cocaína rosa").A Sáenz Valiente lo comprometen una serie de mensajes de esa noche con su dealer y con dos de las mujeres que fueron a su casa, donde les decía que tenía "tuci, faso y coca" en su departamento.</t>
+  </si>
+  <si>
     <t>Elecciones Córdoba 2023: el mapa interactivo con los resultados</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/562215-elecciones-cordoba-2023-el-mapa-interactivo-con-los-resultad</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Elecciones Córdoba 2023: el mapa interactivo con los resultados. Distrito por distrito, la pulseada entre Llaryora y Juez. El peronismo de Córdoba extendió en estas elecciones 2023 su hegemonía de 24 años en la provincia mediterránea por 57,209 votos de diferencia.. El peronismo de Córdoba extendió en estas elecciones 2023 su hegemonía de 24 años en la provincia mediterránea por 57,209 votos de diferencia. Con el 94,9 por ciento de las mesas escrutadas, Martín Llaryora, candidato oficialista y actual intendente de Córdoba capital, logró imponerse en las elecciones provinciales para suceder al gobernador Juan Schiaretti, mientras que el senador Luis Juez (Juntos por el Cambio) se quedó, otra vez, sin poder acceder al "Panal", como se denomina la casa de gobierno cordobesa.
+[H3] Elecciones Córdoba 2023, minuto a minuto
+El mapa provincial se partió en dos. Llaryora con un 42,8% de los votos totales se impuso mayoritariamente en los departamentos del norte provincial, donde se concentra el polo turístico, las sierras y las producción de pequeña escala. Por su parte, Juez, que alcanzó un 39,8 por ciento de los votos, se impuso en el sur provincial, dominado por el agronegocio.
+El voto en blanco fue la tercera opción más elegida por los cordobeses con un 4,8%. La tercera fuerza política fue la de Encuentro Vecinal, que llevó como candidato a Aurelio García Elorrio (3%); aunque a nivel departamental el lugar en el podio se repartió entre La Libertad Avanza (2,5%), Frente de Izquierda (2,4%) y Creo en Córdoba de Todos (2,2%). La fuerza de la ultraderecha de Javier Milei volvió a hacer un pobre papel y sus mejores performance coincidieron con las de Juez, en el sur de la provincia.
+[H2] La distribución del voto en los departamentos cordobeses
+Los departamentos de centro provincial como Tercero Arriba (43,6% para Juez sobre un 40,7% de Llaryora) y Río Segundo (43,5% para Larryora sobre un 41% de Juez), podría decirse que funcionan como frontera: hacia el norte dominó Hacemos Unidos por Córdoba y hacia el sur Juntos por el Cambio. Con escasas excepciones.
+Juez logró imponerse en tres departamentos serranos: San Javier (42% sobre un 41,2% del oficialismo), Punilla (43,7% sobre 37,9%) y Totoral (39,6% sobre 37,1%). Mientras que Llaryora logró su única victoria en el sur provincial en el departamento de Roque Sáenz Peña (43,2% sobre 41,9%).
+En el inico del conteo, Juez comenzó ganando la elección y luego se revirtió por el orden de carga de los resultados. Desde el búnker de Juntos por el Cambio se quejaron porque se cargaban las urnas de la capital provincial, donde LLaryora jugaba de local.
+Pero la capital cordobesa es determinante en la elección, allí están un tercio de los votantes de la provincia. Son 1.130.587 electores sobre un total de 3.051.544. Y allí logró imponerse Llaryora con un 44,6% de los votos sobre el 37,2% de Juez. Así, el actual intendente revalidó su gestión y se quedó con un bastión clave para la victoria provincial.
+Alrededor de la capital provincial y hacia el sur también se encuentran los departamentos más densamente poblados, que los candidatos se los repartieron por igual: Colón, Santa María y Río Segundo fueron para el oficialismo, mientras que Punilla, Tercero Arriba y General San Martín quedaron en manos de Juez.
+Como si se tratara de un anticipo por osmosis de lo que sigue en el cronograma electoral, los departamentos donde los candidatos hicieron mejor elección fueron San Justo y Marcos Juárez, ambos limítrofes con la provincia de Santa Fe, que el próximo 16 de julio irá a las PASO.
+En San Justo, a la altura de Santa Fe capital, Llaryora se impuso con el 51,3 % de los votos sobre el 35,1% de Juez. Mientras que en Marcos Juárez, a la altura de Rosario, el candidato de Juntos por el Cambio ganó con el 48,5% de los votos sobre un 36,1% de Llaryora. En esos departamentos los terceros puestos fueron a contramano: La Libertad Avanza quedó en el podio donde ganó el peronismo cordobés y Creo en Córdoba de Todos lo hizo donde Juez arrasó.</t>
+  </si>
+  <si>
     <t>Rosalía y la tierra</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/561287-rosalia-y-la-tierra</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Rosalía y la tierra. . Rosalía siembra, planta, cosecha, compra, vende, anda en el surco.. Rosalía siembra, planta, cosecha, compra, vende, anda en el surco.
+Rosalía cría hijo e hija y además trabaja para la organización que fundó. Pero ahora no. En este mismo momento espera un café en un bar, después de la movilización apoyando a los jujeños que están siendo apresados, secuestrados, lastimados en el norte del país: “Finalmente el tema es siempre la tierra y el territorio. La tenencia. Y la explotación con lucro al que los originarios tienen derecho y se les niega, claro”.
+Rosalía Pellegrini vive y produce en las quintas del Parque Pereyra, a donde llegó “hace mas de diez años. Venía de una experiencia rural larga en San Vicente, una cooperativa. Llegamos al Parque Pereyra a vivir en un galpón prestado que compartíamos con lagartos, serpientes y una que otra alimaña” recuerda y sonríe sobre el recuerdo de la aventura que arrancó cuando su hijo Aluén tenía poco más de un año y Amanda todavía no había nacido.
+El café tarda en llegar y la calle es un desfile de gentes con banderas enrolladas ya en las cañas. Casi todas, menos alguna wiphala que aun ondea en las manos de alguien que no bajó la euforia, y Jujuy vuelve a la charla: ”El tema del territorio rural es claro: lo ocultan, te proponen no mirar esos lugares. Pensá que el noventa por ciento de la tierra en Argentina es rural, y el ochenta por ciento de la población es urbana, entonces los dueños de los grandes negociados, te proponen no mirar para ahí, para las tierras originarias, porque ahí están las ganancias, el agronegocio, la minería…entonces mientras no se mire, ellos saquean libremente y los pueblos quedan afuera. Cuando habitás el territorio desde la ruralidad, los intereses son el agua, el clima, las consecuencias positivas o negativas de lo que haces, y otros factores, porque eso te afecta de forma directa, y finalmente también está el derecho a la riqueza que genere ese territorio como una cuestión de soberanía. El colectivo y la organización son todo para lograrlo. Y esa es la cuestión en Jujuy; La idea del gobierno jujeño es retroceder en derechos para vender todo lo que hay en el campo, y hoy van contra leyes como la de reparación histórica, que se tomaron 10 años para reglamentar, pero ya está, existe el banco de tierras para agricultura familiar, pero pasan por encima de las leyes. Arrasan con violencia y se quedan con todo lo que de plata.”
+Rosalía habla sin pausa, marcando con el dedo un mapa imaginario sobre la mesa, esquivando los pocillos de café y los vasitos de agua que ya llegaron. Ahora se saca el gorro de lana, mira hacia adentro del bar, parece que pensó algo nuevo para decir y mientras revuelve el café, repite ”la cuestión es la tierra…” mientras aprieta los labios y asiente con la cabeza.
+Del galpón prestado en el Parque Pereyra pasó a construir una casa de madera “muy linda, donde nació Amanda. Ahí ya funcionaba la UTT (unión trabajadores y trabajadoras de la tierra) porque la idea siempre fue armar un espacio colectivo de arraigo con la tierra”. Las palabras comunidad y colectivo pueblan la voz de Rosalía todo el tiempo porque “mirá, esa casa tan hermosa que teníamos, un día de 2013 se incendió. El papá de los chicos había ido a repartir los bolsones de verduras y yo volvía de dejarlos en la escuela. Era de mañana y llegando veía humo y una compañera me dijo que se quemaba mi casa. No quedó nada de nada. Se había quemado todo: ropa, juguetes, zapatos, muebles, papeles. Quedamos literalmente con lo que teníamos puesto. Todo era humo y cenizas. Y ahí llegaron los compañeros a ayudar y compañeras de otra organización trajeron comida, ropa, mantas. Todo era el colectivo, y ellos mismos nos ayudaron a levantar otra casa, que construimos con los bloques de la bloquera donde trabajaba Darío Santillán, que también fue donación de ese colectivo. Ahí vivo, en una prueba tangible de la solidaridad, de la comunidad, de lo colectivo.”
+Rosalía ve pasar la gente de la marcha que se va desconcentrando. Mira atenta a cada uno que pasa. Seria, como si los estuviera contando. Tan concentrada que ni notó que el pocillo de café quedó a medio camino de su boca.
+En la mesa de al lado alguien dice algo a propósito del caos que provocaron “estos jujeños” pero tampoco los escuchó.
+Ahora su mirada vuelve y cuenta que el parque Pereyra Iraola es enorme, que es el lugar ideal para vivir y que “tiene unos caminitos naturales, raros, por donde voy recogiendo semillas con las que hago un vivero de árboles nativos. Ya tengo un vivero con mil plantines de bosque nativo, porque recuperar eso es importante. Sueño, sin ningún romanticismo, con llegar a reforestar con diez mil nativas mientras sigo haciendo huerta y armando ahora plantas aromáticas que son importantes para intercalar en los sembradíos de otros compañeros: se usan para combatir naturalmente plagas y pestes. En eso las compañeras que llegaron hace años del norte, son fundamentales. Ellas saben de esas plantas. Saben y enseñan, comparten. Tienen también enormes conocimientos de plantas medicinales, por ejemplo, y eso también trabajamos mucho”.
+En eso estaba una mañana de agosto de 2020: cosechando artemisas con su vecina, Carolina Rodríguez, sobre el surco y entierrada hasta el cuello, cuando recibió la noticia de que Lucía Correa -otra mujer de la organización- había sido asesinada de un balazo frente a su hijo: “ella iba a charlas sobre cuidados y prevención de femicidios, porque habíamos armado una red muy grande y ella iba, así que la noticia fue horrible. Fuimos, conectamos a la familia, nos ocupamos del entierro. Nosotras ya teníamos el trabajo comunitario de ver la cuestión de genero al interior de las comunidades rurales, pero es arduo que llegue, y en pandemia, que es como estábamos, fue mucho peor”.
+Rosalía, a los cuarenta años de su edad, amanece temprano: “a veces a las seis, otras a las ocho, depende de si los chicos están conmigo o con su papá, y en esta época ¡me levanto vestida hasta las orejas! Hace mucho frio, así que lo primero es encender la leña de la estufa y la cocina y recién de ahí, el primer mate de la mañana” y mientras amanece en su bosque, mira por la ventana crecer los duraznos, o el estado de las chivas en el corral, y decide -una vez más- que cree en la humanidad, en sus compañeras y compañeros de historia, como la del primer verdurazo del año 2015, o el segundo con la consiga “palo o lechuga” contra el gobierno de Macri y que fuera violentamente reprimido. Mientras amanece, cada día decide también que cree a pie juntillas que tanto en el Parque Pereyra como en Jujuy no se puede pensar la vida sin las comunidades rurales adentro, sin lo colectivo, y porfía en que la batalla es para que eso suceda con todos los derechos de sus habitantes como parte fundamental de un todo.
+Por eso dejó su quinta y fue con sus compañeras de Mujeres de la Tierra, a la marcha por Jujuy porque “es fácil y no hay ambigüedad posible: la tierra es nuestra.”</t>
+  </si>
+  <si>
     <t>En Uruguay tienen que tomar mate salado</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/559510-en-uruguay-tienen-que-tomar-mate-salado</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    En Uruguay tienen que tomar mate salado. Por la sequía de tres años, las fuentes de agua potable se están secando. En la canilla el líquido sale con muchos minerales: el río Santa Lucía, su principal fuente, está muy bajo. “No es sequía, es saqueo”, denuncian las ONG.. Página/12 en Uruguay
+Desde Montevideo
+La frase más famosa de Carlitos Balá se está reescribiendo en versión uruguaya, como si fuera el preludio de una pesadilla. ¿Qué gusto tiene el agua? En Montevideo, la respuesta llega al unísono de niñas, vendedores ambulantes, artesanas, peluqueros y jubiladas: ¡Salada!
+En 2004 Uruguay incorporó a su carta magna un artículo que establece que el agua es un recurso natural esencial para la vida. Esta reforma constitucional, votada por el 64 por ciento de los ciudadanos, convirtió al país en el primero del mundo en declarar el acceso al agua como derecho humano. Casi veinte años después, la zona donde habita el 60 por ciento de la población del país podría quedarse sin agua dulce a fines de junio, según la estimación de Obras Sanitarias del Estado (OSE).
+La vida cotidiana está trastornada porque el agua potable ya no se puede utilizar para el mate ni el café. Tomar mate salado es una afrenta al abolengo matero. Comprar el agua embotellada es un gasto que excluye a las familias de menores recursos. El agua mineral, denuncia una artesana, está también “sucia” y le quedan restos de salitre en el termo. “No es sequía, es saqueo”, manifiestan los movimientos ambientalistas.
+Desde principios de mayo, el agua está en boca de todos porque sale más salada de las canillas. El agua de OSE (Obras Sanitarias del Estado), la empresa estatal uruguaya, proviene de fuentes superficiales del río Santa Lucía y la represa de Paso Severino, la principal reserva de agua dulce. La explicación oficial es que el caudal del río ha disminuido como consecuencia de la sequía que afecta a la región desde hace tres años. De los 67 millones de metros cúbicos de agua que puede albergar, actualmente tiene 3,7 millones, según informó OSE.
+El gobierno de Luis Lacalle Pou tomó recursos hídricos del Río de la Plata, más salinizado por las corrientes del océano que recibe. OSE solicitó al Ministerio de Salud Pública que permitiera aumentar los niveles de sodio y de cloro, que pasaaron de 200 a 440 miligramos y 700 miligramos por litro respectivamente. La OMS recomienda que el umbral de sodio sea un máximo de 200 mg. En Uruguay ese umbral se duplicó.
+[H2] “Nos roban el agua dulce”
+El barrio Sur parece una Londres en miniatura. Martín, vendedor de frutas y verduras de un puesto de la feria popular de la calle Julio Herrera y Obes, gambetea la neblina del viernes con mucho ingenio. “Vamos que el dinero no es todo, pero cómo ayuda cuando hay”, exclama e invita a comprar dos lechugas por 50 pesos uruguayos (300 pesos argentinos al cambio oficial, 650 pesos al cambio paralelo). “Elija y agarre”, “¡Vamos, arriba la celeste!”, “¡Vamos, arriba los gurises!”, arenga este vendedor carismático con un aire de familia a Ragnar, el personaje de la serie Vikingos. “El agua salada está rompiendo los termofones y calefones; es complicado el tema”, se queja. Micaela, de 12 años, compra frutillas junto con su hermana Martina, de 8 años. “Tiran cosas al agua y la contaminan; por eso está salada”, dice Martina. “Antes usábamos el agua de la canilla para hacer el mate, ahora no podemos”, confirma Micaela el cambio de hábito.
+“Salus, un agua con leyenda propia”, se lee en la etiqueta de uno de los bidones de 6,25 litros que en este supermercado sobre la calle Maldonado cuesta 129 pesos uruguayos. Un cartel informa que “la compra de bidones y botellas es solo para consumo familiar” y que está permitido hasta tres bidones por persona. Una señora empuja el changuito con los tres bidones autorizados rumbo a una de las cajas.
+Mirta, jubilada con gorrito de lana violeta y ojazos celestes, compró dos packs de cuatro botellas de agua Vitale de 1,75 litros (138 pesos uruguayos cada pack). Habla del problema del agua con una amabilidad que se desdibuja por la rabia. “Al gobierno le importa satisfacer a las empresas extranjeras y que la población se joda. Dan agua para UPM (la empresa finlandesa que se dedica a la fabricación de pulpa de celulosa, papel y madera), agua para todas las pasteras habidas y por haber, por eso pretenden sacar agua del Acuífero Guaraní en tambores”, describe Mirta. “Me duele, me irrita, porque nuestro país siempre tuvo agua dulce. Y ahora nos roban hasta el agua; es la corrupción más absoluta que no pensé que llegaría a pasar con esta magnitud”, agrega y señala que el principal trastorno en la vida cotidiana tiene que ver con lo económico, el gasto extra que significa comprar bidones o botellas. Hasta sus gatos toman agua mineral para evitar que tengan consecuencias en la salud.
+[H2] Las aguas bajan turbias
+Marcela, artesana que tiene su puesto con aros, anillos y pulseras que ella diseña con piedras y acero sobre la peatonal Sarandí, en Ciudad Vieja, cuenta que toma agua embotellada, especialmente para preparar el mate. “Después que hiervo el agua de bidón noto que está super manchada, me deja la jarra llena de salitre”, revela para informar que tampoco resulta ciento por ciento confiable el agua de las distintas marcas que va comprando en la UAM (Unidad Agroalimentaria Metropolitana), un lugar de ventas al por mayor, similar al Mercado Central de Buenos Aires. Compró cuatro bidones de 10 litros a 150 pesos uruguayos cada bidón (1.950 pesos argentinos). “En casa tomamos mucho mate”, resume lo que viven la mayoría de las familias. “El agua mineral está también sucia, no sé si tan mal como la de la canilla, pero limpia no está”.
+A metros de Marcela, Damián, vendedor de libros usados y discos, toma mate “con agua de la canilla”, subraya con un tono desafiante. El agua “no está tan salada” para Damián, que considera que se está “exagerando”, según la perspectiva de este hombre que toma entre dos y tres termos de mate por día. “El agua es cierto que está más salada, pero el problema no es para nosotros solos, es para todo el mundo. Que nos toque después de tantos años... ¡qué se le va hacer! No somos el paraíso”, suelta, mate en mano, este vendedor que trabaja en la peatonal Sarandí de siete de la mañana a seis de la tarde. “La venta está horrible”, se queja y afirma que hay “mucha pobreza” en Montevideo. “No vivimos, sobrevivimos”, aclara y regresa al tema del agua. “Es el cambio climático; que llueva o no llueva, nosotros no mandamos llover. Era obvio que un día iba a llegar”.
+El agua salada llega hasta las peluquerías. Los cabellos de las damas y caballeros se estremecen. La sal seca el pelo y puede afectar al color de las tinturas. En la peluquería “Enrique”, sobre la calle Convención, a metros de la 18 de julio, Enrique confiesa que como él usa productos de una “excelente” línea, libre de sulfatos y parabenos, está a salvo de que el daño sea mayor. Una clienta, que eligió el sábado a la tarde para hacerse el color y cortarse el pelo, está esperando y leyendo algo en su teléfono celular. Desde hace un mes, cuando empezaron los problemas con el agua, percibe que sus clientas, que evidentemente “no se duchan con agua mineral”, tienen los cabellos más deshidratados y perdieron “suavidad y brillo”.
+“Los termofones o calefones están teniendo problemas de oxidación y están acumulando sales en los metales”, revela Luis Aubriot, doctor en Ciencias Biológicas e integrante del Instituto de Ecología y Ciencias Ambientales de la Facultad de Ciencias de la Universidad de la República. “Montevideo tiene una red de distribución de agua por cañerías muy antigua, con caños en algunas zonas que tienen más de cien años. Se calcula que del agua que se potabiliza en la planta principal una vez que llega a la ciudad, se pierde la mitad. En Montevideo hay una cultura del exceso de agua, del agua barata y que no hace falta ciudarla. Hay un dicho que se repite: ‘es más barato potabilizar agua que arreglar caños’; es duro escucharlo, pero ya no estamos en esa situación y el cambio ha sido muy radical”.
+[H2] Menos presupuesto, mala gestión
+“Venimos de un proceso donde la OSE ha perdido funcionarios, ha bajado su inversión y eso repercute en sus capacidades”, declara el senador por el Frente Amplio, Alejandro “Pacha” Sánchez, y precisa que el gobierno de Lacalle Pou ajustó el presupuesto un 30 por ciento y también recortó las inversiones aproximadamente 30 millones con respecto a la década anterior: de 100 millones de dólares anuales a 68 millones. “Este gobierno decidió no seguir adelante con la represa de Casupá, que es una solución más estructural, plantea el senador frenteamplista. El gobierno frenó algo que ya estaba proyectado, que había pasado por todos los procesos, se había financiado, ya estaban hechos los estudios ambientales, ya estaban las expropiaciones, y estaba pronto el llamado a licitación. Y lo frenaron por una iniciativa privada que vale mucho más caro (el proyecto Neptuno) y es mucho más incierta”.
+Karin Nansen, de Redes Amigos de la Tierra Uruguay, asegura que no se trata sólo de un problema de calidad, sino de cantidad de agua. “Por un mal manejo se vació el Canelón Grande y por falta de previsión se acabó la reserva de agua en la represa de Paso Severino”, recuerda Nansen y observa que aunque el gobierno dice que el origen de la crisis es por la fuerte sequía que ha afectado al país, desde las organizaciones ambientales y movimientos sociales entienden que se debe también a “una mala gestión” de la cuenca del río Santa Lucía que abastece de agua al 60 por ciento de la población del país: 1.800.000 uruguayos.
+María Selva Ortiz, también de REDES Amigos de la Tierra, postula que la crisis hídrica demuestra que hay un vínculo entre la dimensión ambiental y la realización de derechos. “Si no tenemos territorios saludables y si no gestionamos las cuencas hidrográficas en forma justa y sustentable, dando prioridad al derecho humano al agua, este derecho se ve seriamente vulnerado. Antes de esta crisis ya había problemas de calidad de agua por la contaminación con agrotóxicos y la cantidad también se vio afectada por las plantaciones de eucaliptus sobre todo en las nacientes de la cuenca”.
+Nansen sostiene que a largo plazo es necesario avanzar en la gestión sustentable de las cuencas tal como establece la constitución. “El agua que se distribuye en la región metropolitana, además de ser salada y presentar riesgos para quienes sufren hipertensión o problemas cardíacos y no ser aptas para la niñez, tiene valores mayores de trihalometanos que pueden provocar problemas de salud crónicos”, explica Nansen. “Como todos los problemas socio-ambientales, esta situación afecta en mayor medida a la población con menores recursos y se reproduce la injusticia -añade Ortiz-. Un derecho fundamental para la vida pasó a estar mediado por el mercado; acceden a agua potable quienes pueden pagar por el agua embotellada. Y esto no es lo que plantea la Constitución, sino todo lo contrario”.
+[H2] Extractivismo puro y duro
+Anahit Aharonian, ingeniera agrónoma diplomada en Gestión de Políticas Ambientales que integra la Comisión Nacional en Defensa del Agua y la Vida (CNDAV), enfatiza que la CNDAV propone la restauración del monte indígena en las riberas del río Santa Lucía. “Esa flora nativa se ha destruido con las plantaciones de soja a través de las cuales cae nitrógeno y fósforo a los cauces de agua. A eso hay que sumarle los pesticidas y los agrotóxicos como el glifosato, que es potencialmente cancerígeno y provoca junto con otros pesticidas efectos en la salud humana. Hay que restaurar el monte indígena, dejar de plantar soja y los cultivos que son negativos para nuestros ecosistemas y el campo natural reverdece y eso hace que absorba el exceso de nitrógeno y fósforo”.
+El proyecto Neptuno o también llamado Arazatí, que busca producir agua potable a partir del agua captada desde el Río de la Plata es “inapropiado”, en palabras de Aharonian, porque sería realizado por empresas privadas, algo que está prohibido por la Constitución. “Sacar agua del Río de la Plata tiene un problema, que es la salinidad, y también la enorme proliferación de floraciones algales, las cianobacterias, cuyas toxinas son hepatóxicas; la OSE estaría potabilizando agua con toxinas incluidas”, advierte la ingeniera agrónoma. “El agua embotellada es agua nuestra. ¿Por qué tenemos que pagar por esa agua? ¿Por qué mientras en Minas están extrayendo agua para exportar, su población no tiene agua? Los negocios son más importantes que abastecer de agua potable a toda la población del Estado, sea el gobierno que sea. En un país cuya riqueza mayor es tanta agua dulce cruzando el territorio, no podemos estar impidiendo que la población acceda al agua”.
+“No es sequía, es saqueo”. La consigna elegida por los movimientos ambientales cuestiona el discurso oficial de que la crisis del agua es por la sequía. “La falta de lluvias no es porque tata Dios no manda agua del cielo, sino que está relacionada con el cambio del uso del suelo que implica que no haya evapotranspiración suficiente por la vegetación que quitan, ese cambio de la plantación natural por la exótica de los agronegocios. Al no haber evapotranspiración suficiente, al no haber posibilidades de cosecha de agua, se provocan sequías e inundaciones; por eso los deslaves que ustedes han sufrido en varias provincias del norte de Argentina y que en Uruguay también se ha visto. Todo eso sucede por el cambio del uso del suelo, provocado por quienes lucran y no miden las consecuencias. No es sequía, es extractivismo puro y duro”, concluye.</t>
+  </si>
+  <si>
     <t>Nace un gigante agroindustrial: Bunge compra Viterra</t>
   </si>
   <si>
@@ -722,7 +2242,23 @@
     <t>https://www.pagina12.com.ar/558279-alimentos-lo-que-no-se-discute</t>
   </si>
   <si>
-    <t>https://www.pagina12.com.ar/558145-nace-un-gigante-agroindustrial-bunge-compra-viterra</t>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Alimentos: lo que no se discute. . Acaba de conocerse el índice FAO de inflación para alimentos en América Latina:. Acaba de conocerse el índice FAO de inflación para alimentos en América Latina:
+Venezuela pica en punta con 110,4%. Es un histórico importador de alimentos, situación que, bloqueo mediante, está revirtiendo aceleradamente y con éxito.
+Le sigue con un 86,6% Argentina, vendedora neta de materias primas con destino alimentario. Exportamos todo, pero todo, lo que comemos: trigo, soja, maíz, poroto, lentejas, ajo, cebolla, carnes y un largo etc. Marcamos récord histórico de exportaciones, y tenemos 40% de pobreza y una inflación por las nubes. Está claro que el modelo no funciona ¿no? Sin embargo, no se les ocurre siquiera poner en debate la posibilidad de cambiar. Al contrario: proponen profundizarlo!
+El país de menor inflación en alimentos del continente es Bolivia, con el 2,2%. Ahí la soberanía alimentaria es un valor tangible, no un mero discurso sobre lo que hay que conquistar.
+El precio de los alimentos es un factor clave de la estabilidad democrática en todo el mundo; y es un instrumento central en la puja distributiva. Un gobierno peronista tiene atada su supervivencia política al bienestar de los sectores populares. Alimentos y salarios son inseparables, y bases esenciales para una buena salud electoral.
+El debate de la producción y el precio de los alimentos en Argentina está dominado por falsos supuestos que propagan los voceros interesados de los agronegocios monopólicos. Para estos grupos, los parámetros se reducen a volumen, producción y exportación. Ellos invisibilizan “partes” que son centrales para entender el “todo”. ¿Cuáles? Van algunas, sustanciales, que nunca entran en debate: concentración de tierras, rentas y producción, medio ambiente, deforestación, arraigo, migraciones rurales, logística, puertos etc. Como si dónde se siembra y quién lo hace fuera una cuestión inocua en el tema. Otro gran ausente en el debate, es el impacto del acuerdo con el FMI en el precio de los alimentos.
+Veamos: el día 4 de junio se realizó en Rosario un encuentro sobre la soberanía. En el panel referido a Soberanía Alimentaria habló Albina Albides, productora hortícola del cordón verde platense, integrante de la organización ASOMA (Asociación de Medieros y Afines) y de la Federación Nacional Campesina. Albina produce verduras y hortalizas que comercializa a través de mayoristas que le pagan lo que se les antoja . Ella debe alquilar la tierra donde siembra y por la que paga $40.000 la hectárea. La superficie mínima para que pueda vivir una familia es de 2,5 hectáreas, es decir $100.000 mensuales; y no le permiten construir una casa de material, deben morar en casillas de chapas y plásticos. Es irracional e inexplicable que en la Argentina no se pueda garantizar tierras para la producción alimentaria de cercanía. Y más inexplicable aún, que el campo nacional y popular no lo ponga en agenda.
+La contracara de Albina es la producción hortícola mega-concentrada; integrada verticalmente, con posición dominante en el mercado. Un ejemplo de esta forma de producción es Hijos de Salvador Muñoz: una empresa salteña que maneja 28.700 hectáreas (contra ninguna de Albina). Esta compañía siembra 24.000 hectáreas de poroto (destinado a la exportación) y la complementa con ganadería. También planta unas 1.700 hectáreas de pimiento, tomate, zapallo, berenjena, lechuga etc.
+“La participación de la firma en el mercado argentino de conservas de pimientos alcanza a más del 70%, siendo líderes absolutos en todos los segmentos; ya sea de consumo domiciliario con marcas propias y de terceros, como a través del canal gastronómico. Los pimientos y tomates para “conservas” salen a la venta enlatados con las marcas propias y con “marcas blancas” destinadas a terceros clientes mayoristas locales, para atender el consumo minorista y el canal gastronómico " (página Bichos de Campo; 3/6/2023). Obsérvese el concepto: “líder absoluto en todos los segmentos” y 70% del mercado del pimiento. Agreguemos que exporta a 15 países, lo que le permite elegir adónde van sus productos, en función del precio. “Parece” posición dominante ¿no?
+Ahora, cuando el pimiento aumenta, este monopolio ¿no tiene nada que ver? Pero sumemos otro “detalle”, no menor: de Embarcación (Salta) a CABA hay 1.386 km, es un día y medio de viaje. Ese recorrido tienen que hacer los pimientos y demás productos para llegar a destino, todo en camión. Semejante travesía encarece el producto en un 30% estimativamente. El 50% de esa logística es en dólares. Cada vez que se devalúa, de acuerdo con las exigencias del acuerdo con el FMI, va al precio de los alimentos.A esto hay que sumarle pasivos ocultos que nunca se computan: costo ambiental, accidentes viales, mantenimiento de rutas etc .
+Latifundio, destrucción de la chacra mixta, producción sin productores, integración vertical, posición dominante, deforestación, depredación ambiental, migraciones rurales y deslocalización productiva para sembrar soja hasta en las banquinas. Este es el modelo productivo dominante instalado por el mercado a partir de la década del noventa. Todo está mal en esta forma de producir los alimentos. Y el precio que pagan los consumidores es la certificación final del desquicio productivo que padecemos.
+La Argentina debe rediscutir su modelo agrícola. Hay tres interrogantes que la política debe responder en torno a este tema:
+1. ¿Quién es el sujeto que produce los alimentos ? Se puede hacer de las dos maneras: con Albina o con los Hijos de Salvador Muñoz. Si es con Albina hace falta más Estado y más recursos. Si es con los segundos, a no quejarse por los precios .
+2. ¿Dónde se producen? O se garantiza el acceso a la tierra a los pequeños productores y se va a la producción cercanía, con chacra mixta incluida, o se sigue con la deslocalización productiva como sucede hoy, con alimentos viajeros y caros.
+3. ¿Cómo se produce? O se va hacia un modelo agroecológico, amigable con el medio ambiente y la salud, o se sigue este rumbo de producción industrial con uso de agrotóxicos.
+Debemos cambiar la forma de producir alimentos. Cuanto más demoremos, más costo político pagamos. Uno cambia cuando toma la decisión política de cambiar; después, implementar el cambio lleva tiempo ya sea por motivos políticos o biológicos. No es soplar y hacer botellas. Pero si se pudo, se puede.</t>
   </si>
   <si>
     <t>Se necesitan políticas públicas dirigidas a la producción de alimentos y no al agronegocio</t>
@@ -731,511 +2267,2149 @@
     <t>https://www.pagina12.com.ar/556126-se-necesitan-politicas-publicas-dirigidas-a-la-produccion-de</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Se necesitan políticas públicas dirigidas a la producción de alimentos y no al agronegocio. En tres décadas se perdieron 156 mil establecimientos productivos. De la tierras cultivadas en el país, un millón de hectáreas están destinadas a legumbres para consumo humano, frutales y hortalizas, mientras que 30 millones se destinan a commodities para la exportación.. La crisis económica en la Argentina ha impactado fuertemente en el sector de pequeños y medianos productores agrícolas. Se trata de un segmento que además de garantizar un alimento sano y barato para los argentinos, tiene capacidad de exportación y de sustitución de importaciones.
+“Es necesario y urgente una política pública integral de acceso a los alimentos y que apunte a ocupar el territorio de la Argentina. Que las producciones de todo el país puedan llegar a través de un mercado de cercanías a un precio justo y con alimentos sanos”, reclama Juan Manuel Rossi, presidente de la Federación de Cooperativas Federadas (FeCoFe), que nuclea, en 10 provincias, a 53 cooperativas dedicadas a la actividad agrícola, ganadera y de producción de alimentos elaborados.
+[H2] Cooperativas que exportan
+Un reciente informe del Instituto Nacional de Asociativismo y Economía Social (INAES) junto con la Agencia Argentina de Inversiones y Comercio Internacional y el Ministerio de Relaciones Exteriores destaca que en 2022 las cooperativas del país exportaron 160 productos a 121 destinos, pasando de una participación en el comercio internacional del 2,4 por ciento en 2018 al 4,4 por ciento en 2022.
+A nivel interno, según datos del Ministerio de Agricultura de la Nación, los pequeños y medianos productores son responsables del 60 por ciento de los alimentos frescos que se consumen en el país, generando el 53 por ciento del empleo en el sector.
+Sin embargo, la falta de crédito y acceso a la tierra, el aumento de la tasa de interés, los insumos y maquinarias importadas, los alquileres, la sequía y el avance del agronegocio --con excedentes producto de la concentración económica y la especulación financiera-- han puesto en jaque a este sector.
+“Las medidas que se van tomando son en función al modelo agroexportador, más allá de algunas iniciativas sueltas. Es necesario que todas las instancias del Estado nacional, provincial y municipal generen políticas de comercialización propias de los productores. Ahí es donde, por oferta y demanda, van a bajar los precios. Porque por el canal de comercialización establecido, que es concentrado, es muy difícil intervenir en la cadena”, opina Nahuel Levaggi, coordinador de la Unión de Trabajadores de la Tierra (UTT) y ex director del Mercado Central.
+Fecofe y la UTT, junto al Movimiento Nacional Campesino Indígena Somos Tierra, la Federación de Organizaciones Nucleadas de la Agricultura Familiar y Bases Federadas --un espacio disidente de la conducción actual de la Federación Agraria Argentina--, conforman la Mesa Agroalimentaria Argentina, que en 2020 le presentó al nuevo presidente Alberto Fernández leyes como la de Acceso a la Tierra, ley de Arrendamientos Rurales, ley de Protección y Fortalecimiento de los Territorios Campesinos y de la Agricultura Familiar, ley de Segmentación de las Políticas Impositivas y Agrarias y ley de Financiamiento y Fomento del Cooperativismo y la Transición Agroecológica.
+Ninguna de estas medidas han sido tomadas en cuenta. Por ejemplo, la ley de Acceso a la Tierra ya es la cuarta vez que ingresa al Congreso Nacional. La iniciativa propone crear un Fondo Fiduciario Público de Crédito para la Agricultura Familiar (Crepaf), para facilitar el acceso a créditos destinados a la adquisición de inmuebles rurales y la construcción de viviendas para las familias productoras que carezcan de tierra propia. Más del 80 por ciento de las familias productoras de alimentos alquilan la tierra.
+[H2] Mucha tierra poco alimento
+Según datos del 2018 del Censo Agropecuario Nacional (CNA), el 40 por ciento de las tierras cultivadas está en manos de solo 1200 familias y empresas. En sólo tres décadas se perdieron 156 mil establecimientos productivos. En su mayoría, de menos de 50 hectáreas.
+De las tierras cultivadas en el país, un millón de hectáreas están destinadas a legumbres para consumo humano, frutales y hortalizas. Mientras que 30 millones se destinan a commodities para la exportación (soja, maíz, trigo, girasol, algodón).
+Argentina es uno de los países del mundo con mayor concentración de la población en las ciudades. Solo el 8 por ciento de su población vive en zonas rurales produciendo alimento para el mercado interno. En este sentido, desde la UTT se viene implementando un plan de Colonias Agrícolas para desconcentrar las población urbana y disminuir los índices de pobreza, aumentado la oferta de alimentos sanos a través de emprendimientos productivos. Entre ellos está la producción de bioinsumos que permiten reemplazar la importación de agrotóxicos.
+“Es un programa agrario que se centra en garantizar el plato de los argentinos y las argentinas. Nace de la Mesa Agroalimentaria Argentina, pero también de la historia de lucha de todas las organizaciones campesinas e indígenas. Justamente en función de entender el alimento como un derecho y ver que en nuestro país el modelo agrario siempre estuvo en mano de los grandes intereses concentrados. Nunca hubo un modelo agrario popular”, comenta Levaggi.
+* Integrante de la Coordinación Nacional de la UTT</t>
+  </si>
+  <si>
     <t>Los indígenas brasileños contra el “marco temporal” que impulsa el agronegocio</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/555728-los-indigenas-brasilenos-contra-el-marco-temporal-que-impuls</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Los indígenas brasileños contra el “marco temporal” que impulsa el agronegocio. La defensa de los derechos ancestrales. Los indígenas brasileños se movilizan desde este martes contra las iniciativas que se tramitan tanto en el Congreso como en la Corte Suprema y que buscan poner una fecha límite para el r. Los indígenas brasileños se movilizan desde este martes contra las iniciativas que se tramitan tanto en el Congreso como en la Corte Suprema y que buscan poner una fecha límite para el reclamo de los territorios ancestrales.
+En el flanco judicial, el máximo tribunal se apresta a retomar un juicio sobre el llamado "marco temporal", que reconoce como tierras indígenas sólo aquellas que los pueblos originarios ocupaban al día 5 de octubre de 1988, cuando se promulgó la actual Constitución. Ese mismo asunto se tramita en el Parlamento, en el que la semana pasada la Cámara de Diputados aprobó un proyecto que da forma de ley a la tesis del "marco temporal", que todavía deberá ser debatido por el Senado.
+La Comisión Interamericana de Derechos Humanos (CIDH) ya expresó su preocupación por la ley 490 porque “contradice estándares universales e interamericanos de derechos humanos y pone en riesgo la propia existencia de pueblos indígenas y tribales en Brasil”.
+Por su parte, Amnistía Internacional instó al Senado a rechazar el proyecto tras advertir que la iniciativa “afecta a los derechos de los pueblos indígenas, especialmente en lo relativo al derecho a la libre determinación y al territorio tradicional, y refuerza las violaciones de derechos humanos sistémicas sufridas por los pueblos indígenas de Brasil, que durante siglos han sido expulsados de sus territorios”.
+[H2] “Limitar y reescribir la historia"
+Unprocessed element [b]
+Desde la Apib, adelantaron que prepararan movilizaciones en todo el país contra una tesis que intenta "limitar y reescribir la historia" a partir de 1988 y "desconoce el pasado", pues "cientos de años antes" los pueblos originarios ya ocupaban esos territorios. Sostienen que eso está debidamente garantizado en el artículo 231 de la Constitución, que reconoce el derecho de los indígenas a "su organización social, costumbres, creencias y tradiciones", y los "derechos originarios sobre tierras que tradicionalmente ocupan", que deben ser delimitadas por el Estado. Según la Apib, el "marco temporal" también ignora que muchos pueblos indígenas fueron desalojados a la fuerza de tierras que ocupaban antes de 1988, por colonos que luego se apropiaron en forma "ilegítima" de esas zonas, lo cual ha generado recurrentes y violentos conflictos.
+[H2] Los territorios en disputa
+Unprocessed element [br]
+[H2] La palabra del Supremo Tribunal Federal
+La Corte Suprema brasileña tiene previsto retomar este miércoles un proceso que puede sentar jurisprudencia y ser decisivo en la polémica del "marco temporal". El juicio comenzó el año pasado: hay hasta ahora un voto a favor y otro en contra de esa tesis y todavía deben pronunciarse ocho de los miembros del tribunal. La causa llegó al Supremo desde tribunales inferiores y a través de una demanda intentada por el Estado contra un fallo de segunda instancia que reconoció como propietario de unas tierras a un organismo público del sureño estado de Santa Catarina. Durante siglos, esas áreas fueron ocupadas por las etnias Xokleng, Guaraní y Kaingang, desalojadas a la fuerza a mediados del siglo pasado, y acabaron en manos de la Fundación para el Amparo Tecnológico de Santa Catarina, favorecida por la sentencia que ahora discute el Supremo. Ese fallo, apoyado en el concepto del "marco temporal", sostuvo que en octubre de 1988 esas tierras estaban en poder de ese organismo de Santa Catarina y desconoció que, a partir de 1996, los indígenas habían retomado algunos de esos asentamientos.</t>
+  </si>
+  <si>
     <t>Diputados brasileños aprueban proyecto para limitar la demarcación de tierras indígenas</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/554157-diputados-brasilenos-aprueban-proyecto-para-limitar-la-demar</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Diputados brasileños aprueban proyecto para limitar la demarcación de tierras indígenas. La policía reprimió las protestas en contra del proyecto de ley. El proyecto de ley establece que sólo pueden ser demarcados los territorios que estaban ocupados por pueblos indígenas al momento de la sanción de la Constitución de 1988. Organizaciones indígenas reclaman que en 1988 no podían ocupar algunos territorios porque habían sido expulsados.. La demarcación de tierras indígenas, una de las claves del gobierno de Lula da Silva para proteger la Amazonia y los pueblos indígenas que lo habitan, podría ser frenada por un proyecto de ley aprobado esta semana en la cámara de Diputados.
+El texto establece que las tierras reservadas para las comunidades originarias deben limitarse a aquellas que ya estaban ocupadas por pueblos indígenas al momento de la sanción de la actual Constitución en 1988.
+Según científicos, la demarcación de tierras indígenas es una barrera importante para frenar la deforestación de la Amazonia. Esto se evidenció durante el gobierno del expresidente Jair Bolsonaro. El exmandatario se negó a demarcar territorios indígenas y en cambio permitió el ingreso de mineros y promovió el avance del agronegocio en la Amazonia.
+El ministerio de Pueblos Indígenas y organizaciones sociales repudiaron la decisión de los diputados y aseguraron que se trata de un retroceso y una amenaza a los pueblos originarios.
+[H2] Genocidio legislado
+El proyecto "representa un genocidio legislado porque afecta directamente a pueblos indígenas aislados, ya que autoriza el acceso deliberado a territorios en los que viven pueblos que aún no tuvieron ningún contacto con la sociedad ni con otros pueblos indígenas", denunció el ministerio en un duro comunicado.
+El proyecto fue impulsado por diputados afines al agronegocio y opositores del gobierno de Lula fue aprobado por 283 votos contra 155. El texto todavía tiene que pasar por la cámara de Senadores para convertirse en ley.
+Brasil tiene un total de 764 territorios indígenas, pero cerca de un tercio de ellos todavía no fueron demarcados, indicó la Fundación Nacional de los Pueblos Indígenas (FUNAI).
+https://twitter.com/GuajajaraSonia/status/1663709090458091521
+Durante los primeros meses de gobierno de Lula da Silva se logró la demarcación de seis territorios y desde el nuevo ministerio de Pueblos Indígenas habían anunciado la demarcación de otros 14 territorios.
+"No vamos a detenernos. Tenemos el Senado por delante y muchos diálogos para garantizar la preservación de nuestras vidas y territorios”, tuiteó la ministra los Pueblos Indígenas, Sonia Guajajara.
+“La mayoría del Congreso votó contra los pueblos indígenas y la naturaleza", denunció la ministra. Guajajara le solicitó a Lula que vete la iniciativa en caso de que llegue a sanción
+[H2] Protestas y represión policial
+La policía reprimió las protestas que sea realizaban de manera pacífica en la ciudad de San Pablo. Cientos de personas se manifestaron en contra del proyecto aprobado por los diputados brasileños.
+Los pueblos indígenas rechazaron el “marco temporal” que promueve el texto. Además, reclaman que en 1988 muchos pueblos indígenas no podían ocupar algunos territorios porque fueron expulsados y esta situación se agravó durante la última dictadura militar (1964-1985).
+https://twitter.com/LeoDiCaprio/status/1663366909369233410
+La votación del proyecto de ley 490 sobre el marco temporal para demarcar tierras indígenas despertó indignación internacional. Organizaciones y activistas de todo el mundo se manifestaron en contra.
+"Bolsonaro se fue pero el exterminio continúa", denunció el Observatorio del Clima. La organización dijo que el proyecto “viola la Constitución” y que era un día vergonzoso para la historia de los diputados y pidieron a los senadores “revertir los absurdos aprobados”.
+Los actores de Hollywood Leonardo Di Caprio y Mark Ruffalo, conocidos por sus militancias sociales, rechazaron el proyecto de ley y llamaron a defender la demarcación de tierras impulsada por Lula.
+"Hay una guerra contra los pueblos indígenas y las selvas. Nuestro planeta está en riesgo. Lula, sea el héroe que su pueblo eligió, impida (el avance) del proyecto", tuiteó Ruffalo en vísperas del debate.</t>
+  </si>
+  <si>
     <t>Cristina Kirchner no señaló un candidato pero marcó el rumbo: los ejes del plan de gobierno que propuso en Plaza de Mayo</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/552840-cristina-kirchner-no-senalo-un-candidato-pero-marco-el-rumbo</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    Cristina Kirchner no señaló un candidato pero marcó el rumbo: los ejes del plan de gobierno que propuso en Plaza de Mayo. Lo que dejó el discurso de la vicepresidenta. De las candidaturas solo hubo espacio para conjeturas a partir de los lugares que cada uno ocupó en el escenario. Lo que sí quedó claro fue el camino que plantea CFK: la definición de un programa sobre 3 o 4 ejes. Qué dijo al respecto.. La Plaza de Mayo habló bajo la lluvia: "¡Cristina presidental!", "Una más y no jodemos más!", "La proscripción se va a la puta que lo parió!". La vicepresidenta escuchó sin responder, eligió ya no hablar más ni dejar dudas sobre su posible candidatura, que dio por cerrada con su carta del 16 de mayo, y abrió paso a un nuevo rol como conductora del movimiento: "Esto no es tarea de una persona, es tarea militante. Basta de pedirle al otro que haga cosas que no estamos dispuestos a hacer", convocó en su discurso en el acto del 25 de mayo por los 20 años de la llegada de Néstor Kirchner a la Presidencia.
+[H3] Quiénes son las principales figura políticas que estuvieron en el acto de CFK¿Quiénes son los niños que acompañaron a Cristina Kirchner en el escenario?
+En ese rol, Cristina tampoco tomó el bastón de mando para señalar a quiénes ocuparán la candidatura que ella deja vacante en el Frente de Todos. No habló ni de Sergio Massa, ni de Eduardo "Wado" De Pedro, que sí estuvieron en la primera línea del palco uno al lado del otro --sumando a las especulaciones de un posible binomio presidencial--. Tampoco habló de Axel Kicillof, también en primera línea, pero con intenciones de ir por la reelección provincial.
+Si las posiciones que ocuparon los invitados de Cristina al escenario del homenaje por los 20 años de la asunción de Néstor Kirchner sumaran puntos, los precandidatos presidenciales menos bendecidos deberían ser el referente social Juan Grabois y el jefe de Gabinete, Agustín Rossi, quienes quedaron en las gradas que se escaparon a la foto principal. El embajador en Brasil, Daniel Scioli, directamente no se subió al avión para llegar a Plaza de Mayo.
+[H2] Un modelo de país con un Estado grande
+Los 20 años de la asunción de Néstor Kirchner fueron el motivo de otro baño de popularidad para la ex presidenta y eligió repasar las dos décadas de kirchnerismo con logros y ejes programáticos que permitan enfrentar la vuelta de los discursos neoliberales de los precandidatos de Juntos por el Cambio y del ultraderechista Javier Milei.
+"El país que recibió Néstor venía de una gran crisis en el 2001. En estos tiempos que se habla tanto del Estado, que es necesario un Estado pequeñito, que no moleste, que deje que los argentinos vivan en paz. Quiero contarles que cuando él llegó, el Estado era muy chiquitito (...) pero la deuda era muy grande", reseñó como paso previo a marcar hitos de la recuperación del rol del Estado durante los tres gobiernos kirchneristas: la reestatización de Aerolíneas Argentinas, el Correo Argentino y el sistema jubilatorio, además de la recuperación de YPF.
+"Cuando el compañero llegó a presidente de la República, el producto bruto de este país era de 164.000 millones de dólares. Cuando su compañera entregó el gobierno el 10 de diciembre del 2015, el producto bruto era de 647.000 millones de dólares. Pagamos durante 12 años y medio 100.000 millones de deuda en dólares que no habíamos contraído nosotros", sintetizó la vicepresidenta como contestándole a quienes relación el crecimiento económico con el achicamiento del Estado.
+"¿Fue magia? ¿Somos unos genios? No, fue el modelo de construcción de la sociedad, un modelo de producción, de valor agregado, de inclusión social, de sostenimiento de la industria nacional, de buenos salarios. Porque no es pecado pagar buenos salarios, al contrario, es de buenos cristianos", planteó Cristina para los libros de la era kirchnerista.
+[H2] "El programa de gobierno que necesita la Argentina"
+La vicepresidenta no habló de candidaturas, pero volvió a hablar del programa de gobierno. Algo que había hecho a fines de abril en el Teatro Argentino de La Plata, cuando comenzó a desarmar el operativo clamor y a poner sobre la mesa un eslogan similar al que circuló en 2015 con Daniel Scioli como candidato, aquel de "el candidato es el proyecto".
+Entre esos puntos programáticos, y como parte de la reivindicación de los gobiernos kirchneristas en contraposición al actual gobierno del Frente de Todos, marcó el "acuciante problema de la redistribución de a riqueza", momento del discurso en el que mencionó sus diferencias con el presidente Alberto Fernández. "Lo he dicho un 20 de diciembre en La Plata cuando dije 'va a haber crecimiento, pero ojo, cuiden los precios de la economía porque sino el crecimiento se lo van a llevar 4 vivos'", le criticó y señaló: "Para distribuir el ingreso muchas veces hay que ponerle carita fea a los que tienen mucho".
+"Argentina necesita imperiosamente 3 o 4 ejes sobre los que desarrollar ese programa", marcó la vicepresidenta retomando la idea del proyecto como candidato e hizo hincapié en la explotación de los recursos naturales: petróleo, gas y litio. Destacó que Vaca Muerta fue recuperada "por los kukas" de la mano de la YPF con mayoría estatal y luego marcó un rumbo para el litio: "Que vengan a explotarlo pero queremos... no digo que los autos los hagan acá eléctricos, pero, por lo menos hermano, una parte de la batería o la batería entera hacela acá, si te la estás llevando toda".
+En ese sentido, Cristina consideró que el país debe tomar el camino de la industrialización para alejarse del modelo dependendiente de los commodities del agronegocio. "No podemos seguir atados a una economía primarizada, no podemos seguir atados a los precios internacionales o a que llueva o que salga el sol", sostuvo y puso la mirada en las últimas dos décadas de crecimiento económico de los países asiáticos con "modelos de acumulación acordados entre el sector público y el privado en las actividades que más retorno provocan, con tecnología, valor agregado y trabajo calificado".
+"Esta es la discusión que están esperando millones de argentinos y no las boludeces que se dicen todos los días en los medios de comunicación", consideró.
+[H2] La renegociación con el FMI
+Mientras Massa continúa intentando cerrar una renegociación de la deuda con el FMI, Cristina ató la posibilidad de llevar adelante un programa de gobierno con las condiciones que se negocien con el organismos multilateral de crédito. "Si nosotros los argentinos y argentinas no logramos que ese programa que el FMI impone a todos sus deudores sea dejado de lado y nos permita elaborar un programa propio de crecimiento, de industrialización, de innovación tecnológica, va a ser imposible pagarlo".
+La vicepresidenta insitió en la idea de que no se puede pagar sin crecer, otra reivindicación de la política de Néstor Kirchner, y volvió a proponer la idea de condicionar los pagos al crecimiento económico o al volumen de exportaciones. Sin olvidar la decisión política que tomó el FMI al otorgar el préstamo para sostener la campaña reelectoral de Mauricio Macri, por lo que también dejó en claro que la renegociación no debe quedar solo atada a las cláusulas económicas: "Fue un préstamo político y política debe ser la solución".
+[H2] Renovación del Poder Judicial
+En los ejes programáticos para un próximo gobierno Cristina también planteó la necesidad de "repensar el diseño institucional argentino" con énfasis en el Poder Judicial, sobre el que cargó una dura crítica a la Corte Suprema, a la que calificó de "mamarracho".
+"Es necesario la renovación de ese pacto democrático volver a darle al país un Poder Judicial que se ha evaporado entre las tramoyas de una camarilla indigna para la historia de la Argentina. No importa si es un jurista de una u otra orientación, pero por favor, los argentinos se merecen volver a tener una Corte Suprema de Justicia que pueda llamarse como tal sin ponerse colorados", sostuvo la vicepresidenta en una convocatoria a todos los partidos políticos.
+La ex presidenta --que en su gobierno impulsó la elección por voto popular del Consejo de la Magistratura-- calificó de "rémora monárquica" al Poder Judicial y resaltó que los poderes Ejecutivo y Legislativo tienen otra relación con la sociedad, ya que se exponen a su escrutinio cada dos y cuatro años.
+[H2] Cristina conducción
+El cantito de "¡Cristina presidenta!" sonó antes, durante y después del discurso, pero la vicepresidenta se encargó de dejarlo pasar y ubicarse en lo que parece ser su nuevo rol de conducción. "Es necesario construir organización, profundidad territorial de la organización, profundidad sectorial en los sindicatos, en las fábricas. Una sola persona no puede", se sinceró.
+"Tiene que haber una organización, tiene que haber cuadros que tomen la posta y lleven adelante el programa de gobierno que necesita la Argentina", pidió la vicepresidenta ya sin referirse solo a que tomen la posta los hijos de la generación diezmada, como expresó la semana pasada.
+"Quiero convocarlos para que cada uno en su lugar, en el bondi o el subte o en la bici, cuente y permita que este entramado de desinformación en cuanto a los verdaderos responsables de endeudamiento, esta vez la gente pueda decidir con claridad, pero sobre todo con información", pidió en referencia al acuerdo con el FMI, pero como invitación general para recuperar el protagonismo político en la calle, en los barrios y en los lugares de trabajo.
+"Esto no es tarea de una persona, es tarea militante. Basta de pedirle al otro que haga cosas que no estamos dispuestos a hacer. Hay que hacerlo entre todos y todas", sentenció Cristina y le confirmó a la plaza que el operativo clamor será por el proyecto.
+[H3] Las 23 definiciones claves del discurso de Cristina Fernández en Plaza de Mayo</t>
+  </si>
+  <si>
     <t>La elección de Néstor Kirchner: una enseñanza inolvidable</t>
   </si>
   <si>
     <t>https://www.pagina12.com.ar/552525-la-eleccion-de-nestor-kirchner-una-ensenanza-inolvidable</t>
   </si>
   <si>
+    <t>**** *pais_ag *jornal_pagina12 *ano_2023
+    La elección de Néstor Kirchner: una enseñanza inolvidable. A 20 años de la asunción. Hace veinte años la Argentina presenció un acontecimiento inusual en su vida política: Néstor Kirchner asumía la presidencia de un país devastado por el catastrófico derrumbe del experimento neo. Hace veinte años la Argentina presenció un acontecimiento inusual en su vida política: Néstor Kirchner asumía la presidencia de un país devastado por el catastrófico derrumbe del experimento neoliberal iniciado por la dictadura genocida que la presidencia de Carlos S. Menem llevara hasta sus últimas consecuencias y por la mentirosa política de la Convertibili